--- a/database/RAIZ4.xlsx
+++ b/database/RAIZ4.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1275"/>
+  <dimension ref="A1:F1276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44413</v>
       </c>
       <c r="B2" t="n">
-        <v>6.384481430053711</v>
+        <v>6.384481906890869</v>
       </c>
       <c r="C2" t="n">
-        <v>6.70194196042671</v>
+        <v>6.701942460974013</v>
       </c>
       <c r="D2" t="n">
-        <v>6.331571411740119</v>
+        <v>6.331571884625592</v>
       </c>
       <c r="E2" t="n">
-        <v>6.596121923799527</v>
+        <v>6.596122416443459</v>
       </c>
       <c r="F2" t="n">
         <v>98849900</v>
@@ -472,16 +472,16 @@
         <v>44414</v>
       </c>
       <c r="B3" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="C3" t="n">
-        <v>6.481483579964149</v>
+        <v>6.48148308633695</v>
       </c>
       <c r="D3" t="n">
-        <v>6.199296805201136</v>
+        <v>6.19929633306517</v>
       </c>
       <c r="E3" t="n">
-        <v>6.393300212850708</v>
+        <v>6.393299725939519</v>
       </c>
       <c r="F3" t="n">
         <v>28799900</v>
@@ -512,16 +512,16 @@
         <v>44418</v>
       </c>
       <c r="B5" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="C5" t="n">
-        <v>6.313934972202879</v>
+        <v>6.313934491336116</v>
       </c>
       <c r="D5" t="n">
-        <v>6.216933478623825</v>
+        <v>6.216933005144656</v>
       </c>
       <c r="E5" t="n">
-        <v>6.278661625357502</v>
+        <v>6.278661147177143</v>
       </c>
       <c r="F5" t="n">
         <v>9988600</v>
@@ -532,16 +532,16 @@
         <v>44419</v>
       </c>
       <c r="B6" t="n">
-        <v>6.058202743530273</v>
+        <v>6.058203220367432</v>
       </c>
       <c r="C6" t="n">
-        <v>6.296298035007707</v>
+        <v>6.296298530585189</v>
       </c>
       <c r="D6" t="n">
-        <v>5.996474599382589</v>
+        <v>5.996475071361166</v>
       </c>
       <c r="E6" t="n">
-        <v>6.287479908911514</v>
+        <v>6.287480403794928</v>
       </c>
       <c r="F6" t="n">
         <v>31978000</v>
@@ -592,16 +592,16 @@
         <v>44424</v>
       </c>
       <c r="B9" t="n">
-        <v>6.190477848052979</v>
+        <v>6.190478801727295</v>
       </c>
       <c r="C9" t="n">
-        <v>6.278661209323248</v>
+        <v>6.278662176582655</v>
       </c>
       <c r="D9" t="n">
-        <v>5.978837781004333</v>
+        <v>5.978838702074429</v>
       </c>
       <c r="E9" t="n">
-        <v>6.146385957172127</v>
+        <v>6.146386904053864</v>
       </c>
       <c r="F9" t="n">
         <v>13434600</v>
@@ -612,16 +612,16 @@
         <v>44425</v>
       </c>
       <c r="B10" t="n">
-        <v>6.014111042022705</v>
+        <v>6.014111518859863</v>
       </c>
       <c r="C10" t="n">
-        <v>6.164022543855327</v>
+        <v>6.164023032578428</v>
       </c>
       <c r="D10" t="n">
-        <v>5.961201025995057</v>
+        <v>5.961201498637171</v>
       </c>
       <c r="E10" t="n">
-        <v>6.111112527827679</v>
+        <v>6.111113012355736</v>
       </c>
       <c r="F10" t="n">
         <v>17772000</v>
@@ -652,16 +652,16 @@
         <v>44427</v>
       </c>
       <c r="B12" t="n">
-        <v>6.11111307144165</v>
+        <v>6.111112117767334</v>
       </c>
       <c r="C12" t="n">
-        <v>6.11111307144165</v>
+        <v>6.111112117767334</v>
       </c>
       <c r="D12" t="n">
-        <v>5.66137768495472</v>
+        <v>5.661376801464195</v>
       </c>
       <c r="E12" t="n">
-        <v>5.908291115047926</v>
+        <v>5.908290193025142</v>
       </c>
       <c r="F12" t="n">
         <v>5423700</v>
@@ -672,16 +672,16 @@
         <v>44428</v>
       </c>
       <c r="B13" t="n">
-        <v>6.155205249786377</v>
+        <v>6.155205726623535</v>
       </c>
       <c r="C13" t="n">
-        <v>6.216933820405099</v>
+        <v>6.216934302024303</v>
       </c>
       <c r="D13" t="n">
-        <v>6.022929981598537</v>
+        <v>6.022930448188472</v>
       </c>
       <c r="E13" t="n">
-        <v>6.075840004775376</v>
+        <v>6.075840475464193</v>
       </c>
       <c r="F13" t="n">
         <v>3109200</v>
@@ -712,16 +712,16 @@
         <v>44432</v>
       </c>
       <c r="B15" t="n">
-        <v>6.39330005645752</v>
+        <v>6.393300533294678</v>
       </c>
       <c r="C15" t="n">
-        <v>6.525575314137689</v>
+        <v>6.525575800840451</v>
       </c>
       <c r="D15" t="n">
-        <v>6.331571490742386</v>
+        <v>6.331571962975588</v>
       </c>
       <c r="E15" t="n">
-        <v>6.384481509716164</v>
+        <v>6.384481985895601</v>
       </c>
       <c r="F15" t="n">
         <v>6054100</v>
@@ -732,16 +732,16 @@
         <v>44433</v>
       </c>
       <c r="B16" t="n">
-        <v>6.472665309906006</v>
+        <v>6.472664833068848</v>
       </c>
       <c r="C16" t="n">
-        <v>6.507938655968863</v>
+        <v>6.507938176533139</v>
       </c>
       <c r="D16" t="n">
-        <v>6.402118617780292</v>
+        <v>6.402118146140264</v>
       </c>
       <c r="E16" t="n">
-        <v>6.455028636874578</v>
+        <v>6.455028161336702</v>
       </c>
       <c r="F16" t="n">
         <v>5190100</v>
@@ -752,16 +752,16 @@
         <v>44434</v>
       </c>
       <c r="B17" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="C17" t="n">
-        <v>6.507938800343913</v>
+        <v>6.507938304701895</v>
       </c>
       <c r="D17" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="E17" t="n">
-        <v>6.472665453498537</v>
+        <v>6.472664960542923</v>
       </c>
       <c r="F17" t="n">
         <v>7968100</v>
@@ -772,16 +772,16 @@
         <v>44435</v>
       </c>
       <c r="B18" t="n">
-        <v>6.340390205383301</v>
+        <v>6.340389728546143</v>
       </c>
       <c r="C18" t="n">
-        <v>6.384481678783307</v>
+        <v>6.384481198630192</v>
       </c>
       <c r="D18" t="n">
-        <v>6.278661638033537</v>
+        <v>6.278661165838754</v>
       </c>
       <c r="E18" t="n">
-        <v>6.305116858466711</v>
+        <v>6.305116384282329</v>
       </c>
       <c r="F18" t="n">
         <v>5881000</v>
@@ -792,16 +792,16 @@
         <v>44438</v>
       </c>
       <c r="B19" t="n">
-        <v>6.269844055175781</v>
+        <v>6.269843101501465</v>
       </c>
       <c r="C19" t="n">
-        <v>6.419756002815109</v>
+        <v>6.419755026338443</v>
       </c>
       <c r="D19" t="n">
-        <v>6.252207380188302</v>
+        <v>6.252206429196611</v>
       </c>
       <c r="E19" t="n">
-        <v>6.39330078008814</v>
+        <v>6.393299807635444</v>
       </c>
       <c r="F19" t="n">
         <v>4966000</v>
@@ -812,16 +812,16 @@
         <v>44439</v>
       </c>
       <c r="B20" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="C20" t="n">
-        <v>6.305116845737266</v>
+        <v>6.305116365542087</v>
       </c>
       <c r="D20" t="n">
-        <v>6.181660131778449</v>
+        <v>6.181659660985684</v>
       </c>
       <c r="E20" t="n">
-        <v>6.305116845737266</v>
+        <v>6.305116365542087</v>
       </c>
       <c r="F20" t="n">
         <v>3704100</v>
@@ -872,16 +872,16 @@
         <v>44442</v>
       </c>
       <c r="B23" t="n">
-        <v>6.172841548919678</v>
+        <v>6.17284107208252</v>
       </c>
       <c r="C23" t="n">
-        <v>6.172841548919678</v>
+        <v>6.17284107208252</v>
       </c>
       <c r="D23" t="n">
-        <v>5.934746248852434</v>
+        <v>5.934745790407565</v>
       </c>
       <c r="E23" t="n">
-        <v>6.031748162358781</v>
+        <v>6.031747696420747</v>
       </c>
       <c r="F23" t="n">
         <v>3705400</v>
@@ -892,16 +892,16 @@
         <v>44445</v>
       </c>
       <c r="B24" t="n">
-        <v>6.11111307144165</v>
+        <v>6.111112117767334</v>
       </c>
       <c r="C24" t="n">
-        <v>6.190478312788771</v>
+        <v>6.190477346729052</v>
       </c>
       <c r="D24" t="n">
-        <v>6.067021597742168</v>
+        <v>6.06702065094858</v>
       </c>
       <c r="E24" t="n">
-        <v>6.119931618476427</v>
+        <v>6.119930663425925</v>
       </c>
       <c r="F24" t="n">
         <v>1654400</v>
@@ -912,16 +912,16 @@
         <v>44447</v>
       </c>
       <c r="B25" t="n">
-        <v>5.758379459381104</v>
+        <v>5.758378982543945</v>
       </c>
       <c r="C25" t="n">
-        <v>6.111112922336476</v>
+        <v>6.111112416290331</v>
       </c>
       <c r="D25" t="n">
-        <v>5.661377546822648</v>
+        <v>5.661377078017978</v>
       </c>
       <c r="E25" t="n">
-        <v>6.111112922336476</v>
+        <v>6.111112416290331</v>
       </c>
       <c r="F25" t="n">
         <v>10251100</v>
@@ -932,16 +932,16 @@
         <v>44448</v>
       </c>
       <c r="B26" t="n">
-        <v>5.652559280395508</v>
+        <v>5.652558326721191</v>
       </c>
       <c r="C26" t="n">
-        <v>5.837744567878833</v>
+        <v>5.837743582960889</v>
       </c>
       <c r="D26" t="n">
-        <v>5.599649258327626</v>
+        <v>5.59964831358005</v>
       </c>
       <c r="E26" t="n">
-        <v>5.758379745022749</v>
+        <v>5.75837877349488</v>
       </c>
       <c r="F26" t="n">
         <v>5428200</v>
@@ -972,16 +972,16 @@
         <v>44452</v>
       </c>
       <c r="B28" t="n">
-        <v>6.128748893737793</v>
+        <v>6.128749370574951</v>
       </c>
       <c r="C28" t="n">
-        <v>6.172840781804387</v>
+        <v>6.172841262072042</v>
       </c>
       <c r="D28" t="n">
-        <v>5.925926965515992</v>
+        <v>5.925927426572926</v>
       </c>
       <c r="E28" t="n">
-        <v>5.95238218245423</v>
+        <v>5.952382645569469</v>
       </c>
       <c r="F28" t="n">
         <v>8999600</v>
@@ -992,16 +992,16 @@
         <v>44453</v>
       </c>
       <c r="B29" t="n">
-        <v>6.340390205383301</v>
+        <v>6.340389728546143</v>
       </c>
       <c r="C29" t="n">
-        <v>6.507938813482836</v>
+        <v>6.50793832404497</v>
       </c>
       <c r="D29" t="n">
-        <v>6.225751617658651</v>
+        <v>6.225751149443035</v>
       </c>
       <c r="E29" t="n">
-        <v>6.225751617658651</v>
+        <v>6.225751149443035</v>
       </c>
       <c r="F29" t="n">
         <v>9730300</v>
@@ -1012,16 +1012,16 @@
         <v>44454</v>
       </c>
       <c r="B30" t="n">
-        <v>6.384481430053711</v>
+        <v>6.384481906890869</v>
       </c>
       <c r="C30" t="n">
-        <v>6.50793855994354</v>
+        <v>6.507939046001328</v>
       </c>
       <c r="D30" t="n">
-        <v>6.296298066197724</v>
+        <v>6.29629853644874</v>
       </c>
       <c r="E30" t="n">
-        <v>6.384481430053711</v>
+        <v>6.384481906890869</v>
       </c>
       <c r="F30" t="n">
         <v>7265900</v>
@@ -1032,16 +1032,16 @@
         <v>44455</v>
       </c>
       <c r="B31" t="n">
-        <v>6.278661251068115</v>
+        <v>6.278660774230957</v>
       </c>
       <c r="C31" t="n">
-        <v>6.428573176470008</v>
+        <v>6.428572688247688</v>
       </c>
       <c r="D31" t="n">
-        <v>6.172841216840228</v>
+        <v>6.172840748039643</v>
       </c>
       <c r="E31" t="n">
-        <v>6.349207940553374</v>
+        <v>6.349207458358499</v>
       </c>
       <c r="F31" t="n">
         <v>6142600</v>
@@ -1052,16 +1052,16 @@
         <v>44456</v>
       </c>
       <c r="B32" t="n">
-        <v>6.384481430053711</v>
+        <v>6.384481906890869</v>
       </c>
       <c r="C32" t="n">
-        <v>6.384481430053711</v>
+        <v>6.384481906890869</v>
       </c>
       <c r="D32" t="n">
-        <v>5.978837956316171</v>
+        <v>5.978838402857074</v>
       </c>
       <c r="E32" t="n">
-        <v>6.261024720655329</v>
+        <v>6.261025188271888</v>
       </c>
       <c r="F32" t="n">
         <v>16008100</v>
@@ -1072,16 +1072,16 @@
         <v>44459</v>
       </c>
       <c r="B33" t="n">
-        <v>6.269844055175781</v>
+        <v>6.269843101501465</v>
       </c>
       <c r="C33" t="n">
-        <v>6.32275408013822</v>
+        <v>6.322753118416027</v>
       </c>
       <c r="D33" t="n">
-        <v>6.067022082574015</v>
+        <v>6.067021159749924</v>
       </c>
       <c r="E33" t="n">
-        <v>6.164023584759403</v>
+        <v>6.164022647180904</v>
       </c>
       <c r="F33" t="n">
         <v>9065700</v>
@@ -1092,16 +1092,16 @@
         <v>44460</v>
       </c>
       <c r="B34" t="n">
-        <v>6.419754981994629</v>
+        <v>6.419755458831787</v>
       </c>
       <c r="C34" t="n">
-        <v>6.525575015092812</v>
+        <v>6.525575499789916</v>
       </c>
       <c r="D34" t="n">
-        <v>6.269843058193152</v>
+        <v>6.269843523895372</v>
       </c>
       <c r="E34" t="n">
-        <v>6.349207872771073</v>
+        <v>6.349208344368237</v>
       </c>
       <c r="F34" t="n">
         <v>11102500</v>
@@ -1152,16 +1152,16 @@
         <v>44463</v>
       </c>
       <c r="B37" t="n">
-        <v>6.172841548919678</v>
+        <v>6.17284107208252</v>
       </c>
       <c r="C37" t="n">
-        <v>6.375663502346697</v>
+        <v>6.375663009842031</v>
       </c>
       <c r="D37" t="n">
-        <v>6.164023002013892</v>
+        <v>6.164022525857945</v>
       </c>
       <c r="E37" t="n">
-        <v>6.340390155706473</v>
+        <v>6.340389665926588</v>
       </c>
       <c r="F37" t="n">
         <v>5138200</v>
@@ -1172,16 +1172,16 @@
         <v>44466</v>
       </c>
       <c r="B38" t="n">
-        <v>6.305116176605225</v>
+        <v>6.305116653442383</v>
       </c>
       <c r="C38" t="n">
-        <v>6.340389519707209</v>
+        <v>6.340389999211985</v>
       </c>
       <c r="D38" t="n">
-        <v>6.102294243523106</v>
+        <v>6.102294705021446</v>
       </c>
       <c r="E38" t="n">
-        <v>6.172840929727075</v>
+        <v>6.17284139656065</v>
       </c>
       <c r="F38" t="n">
         <v>6343700</v>
@@ -1192,16 +1192,16 @@
         <v>44467</v>
       </c>
       <c r="B39" t="n">
-        <v>6.119931697845459</v>
+        <v>6.119932174682617</v>
       </c>
       <c r="C39" t="n">
-        <v>6.278661762106795</v>
+        <v>6.278662251311475</v>
       </c>
       <c r="D39" t="n">
-        <v>6.119931697845459</v>
+        <v>6.119932174682617</v>
       </c>
       <c r="E39" t="n">
-        <v>6.26102508829998</v>
+        <v>6.261025576130491</v>
       </c>
       <c r="F39" t="n">
         <v>6782400</v>
@@ -1212,16 +1212,16 @@
         <v>44468</v>
       </c>
       <c r="B40" t="n">
-        <v>6.040565967559814</v>
+        <v>6.040565490722656</v>
       </c>
       <c r="C40" t="n">
-        <v>6.25220645663842</v>
+        <v>6.252205963094541</v>
       </c>
       <c r="D40" t="n">
-        <v>6.040565967559814</v>
+        <v>6.040565490722656</v>
       </c>
       <c r="E40" t="n">
-        <v>6.216933111873892</v>
+        <v>6.216932621114461</v>
       </c>
       <c r="F40" t="n">
         <v>6482600</v>
@@ -1232,16 +1232,16 @@
         <v>44469</v>
       </c>
       <c r="B41" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="C41" t="n">
-        <v>6.349208319048255</v>
+        <v>6.349207835495088</v>
       </c>
       <c r="D41" t="n">
-        <v>6.058202997328168</v>
+        <v>6.058202535937849</v>
       </c>
       <c r="E41" t="n">
-        <v>6.084658217707932</v>
+        <v>6.084657754302794</v>
       </c>
       <c r="F41" t="n">
         <v>15990100</v>
@@ -1252,16 +1252,16 @@
         <v>44470</v>
       </c>
       <c r="B42" t="n">
-        <v>6.499119758605957</v>
+        <v>6.499120235443115</v>
       </c>
       <c r="C42" t="n">
-        <v>6.569666446925959</v>
+        <v>6.569666928939093</v>
       </c>
       <c r="D42" t="n">
-        <v>6.331571163600236</v>
+        <v>6.331571628144438</v>
       </c>
       <c r="E42" t="n">
-        <v>6.331571163600236</v>
+        <v>6.331571628144438</v>
       </c>
       <c r="F42" t="n">
         <v>15528000</v>
@@ -1272,16 +1272,16 @@
         <v>44473</v>
       </c>
       <c r="B43" t="n">
-        <v>6.190477848052979</v>
+        <v>6.190478801727295</v>
       </c>
       <c r="C43" t="n">
-        <v>6.552029839506799</v>
+        <v>6.552030848880022</v>
       </c>
       <c r="D43" t="n">
-        <v>6.190477848052979</v>
+        <v>6.190478801727295</v>
       </c>
       <c r="E43" t="n">
-        <v>6.525575041371436</v>
+        <v>6.525576046669164</v>
       </c>
       <c r="F43" t="n">
         <v>12019000</v>
@@ -1292,16 +1292,16 @@
         <v>44474</v>
       </c>
       <c r="B44" t="n">
-        <v>6.287480354309082</v>
+        <v>6.287479877471924</v>
       </c>
       <c r="C44" t="n">
-        <v>6.366845176762705</v>
+        <v>6.366844693906587</v>
       </c>
       <c r="D44" t="n">
-        <v>6.243388459230366</v>
+        <v>6.2433879857371</v>
       </c>
       <c r="E44" t="n">
-        <v>6.29629848102994</v>
+        <v>6.296298003524023</v>
       </c>
       <c r="F44" t="n">
         <v>12888200</v>
@@ -1352,16 +1352,16 @@
         <v>44477</v>
       </c>
       <c r="B47" t="n">
-        <v>6.310670852661133</v>
+        <v>6.310671329498291</v>
       </c>
       <c r="C47" t="n">
-        <v>6.655371671310609</v>
+        <v>6.655372174193518</v>
       </c>
       <c r="D47" t="n">
-        <v>6.292993920021518</v>
+        <v>6.292994395522999</v>
       </c>
       <c r="E47" t="n">
-        <v>6.363701650579979</v>
+        <v>6.363702131424168</v>
       </c>
       <c r="F47" t="n">
         <v>20480700</v>
@@ -1372,16 +1372,16 @@
         <v>44480</v>
       </c>
       <c r="B48" t="n">
-        <v>6.213447570800781</v>
+        <v>6.213448047637939</v>
       </c>
       <c r="C48" t="n">
-        <v>6.407893818474543</v>
+        <v>6.407894310234044</v>
       </c>
       <c r="D48" t="n">
-        <v>6.213447570800781</v>
+        <v>6.213448047637939</v>
       </c>
       <c r="E48" t="n">
-        <v>6.363701278732132</v>
+        <v>6.363701767100176</v>
       </c>
       <c r="F48" t="n">
         <v>10407400</v>
@@ -1392,16 +1392,16 @@
         <v>44482</v>
       </c>
       <c r="B49" t="n">
-        <v>6.231125354766846</v>
+        <v>6.231124877929688</v>
       </c>
       <c r="C49" t="n">
-        <v>6.292994413127774</v>
+        <v>6.292993931556084</v>
       </c>
       <c r="D49" t="n">
-        <v>6.213448420742101</v>
+        <v>6.213447945257672</v>
       </c>
       <c r="E49" t="n">
-        <v>6.248802288791589</v>
+        <v>6.248801810601703</v>
       </c>
       <c r="F49" t="n">
         <v>8146000</v>
@@ -1452,16 +1452,16 @@
         <v>44487</v>
       </c>
       <c r="B52" t="n">
-        <v>6.16925573348999</v>
+        <v>6.169256210327148</v>
       </c>
       <c r="C52" t="n">
-        <v>6.266479079122371</v>
+        <v>6.266479563474164</v>
       </c>
       <c r="D52" t="n">
-        <v>6.151578799870589</v>
+        <v>6.151579275341452</v>
       </c>
       <c r="E52" t="n">
-        <v>6.257640401587</v>
+        <v>6.257640885255628</v>
       </c>
       <c r="F52" t="n">
         <v>7596500</v>
@@ -1472,16 +1472,16 @@
         <v>44488</v>
       </c>
       <c r="B53" t="n">
-        <v>5.91294002532959</v>
+        <v>5.912939071655273</v>
       </c>
       <c r="C53" t="n">
-        <v>6.186932709011659</v>
+        <v>6.186931711146165</v>
       </c>
       <c r="D53" t="n">
-        <v>5.895263091590468</v>
+        <v>5.895262140767192</v>
       </c>
       <c r="E53" t="n">
-        <v>6.169255775272537</v>
+        <v>6.169254780258083</v>
       </c>
       <c r="F53" t="n">
         <v>11473400</v>
@@ -1492,16 +1492,16 @@
         <v>44489</v>
       </c>
       <c r="B54" t="n">
-        <v>5.904100894927979</v>
+        <v>5.904101371765137</v>
       </c>
       <c r="C54" t="n">
-        <v>6.045516775446618</v>
+        <v>6.045517263705048</v>
       </c>
       <c r="D54" t="n">
-        <v>5.842231842311679</v>
+        <v>5.842232314152062</v>
       </c>
       <c r="E54" t="n">
-        <v>6.010162910679786</v>
+        <v>6.010163396082907</v>
       </c>
       <c r="F54" t="n">
         <v>6234400</v>
@@ -1532,16 +1532,16 @@
         <v>44491</v>
       </c>
       <c r="B56" t="n">
-        <v>5.630108833312988</v>
+        <v>5.63010835647583</v>
       </c>
       <c r="C56" t="n">
-        <v>5.656624445444495</v>
+        <v>5.656623966361621</v>
       </c>
       <c r="D56" t="n">
-        <v>5.197023732958769</v>
+        <v>5.197023292801376</v>
       </c>
       <c r="E56" t="n">
-        <v>5.603593642632838</v>
+        <v>5.60359316804136</v>
       </c>
       <c r="F56" t="n">
         <v>18890200</v>
@@ -1552,16 +1552,16 @@
         <v>44494</v>
       </c>
       <c r="B57" t="n">
-        <v>5.859910011291504</v>
+        <v>5.859909534454346</v>
       </c>
       <c r="C57" t="n">
-        <v>5.877586947405223</v>
+        <v>5.877586469129643</v>
       </c>
       <c r="D57" t="n">
-        <v>5.550563418575734</v>
+        <v>5.550562966910968</v>
       </c>
       <c r="E57" t="n">
-        <v>5.683140228702921</v>
+        <v>5.683139766250011</v>
       </c>
       <c r="F57" t="n">
         <v>11428100</v>
@@ -1572,16 +1572,16 @@
         <v>44495</v>
       </c>
       <c r="B58" t="n">
-        <v>5.81571626663208</v>
+        <v>5.815716743469238</v>
       </c>
       <c r="C58" t="n">
-        <v>5.868747064088904</v>
+        <v>5.868747545274117</v>
       </c>
       <c r="D58" t="n">
-        <v>5.683139062264364</v>
+        <v>5.683139528231368</v>
       </c>
       <c r="E58" t="n">
-        <v>5.833393199117688</v>
+        <v>5.833393677404199</v>
       </c>
       <c r="F58" t="n">
         <v>8470300</v>
@@ -1592,16 +1592,16 @@
         <v>44496</v>
       </c>
       <c r="B59" t="n">
-        <v>5.859910011291504</v>
+        <v>5.859909534454346</v>
       </c>
       <c r="C59" t="n">
-        <v>5.965971627973814</v>
+        <v>5.965971142506127</v>
       </c>
       <c r="D59" t="n">
-        <v>5.789202266836631</v>
+        <v>5.789201795753159</v>
       </c>
       <c r="E59" t="n">
-        <v>5.833394396395226</v>
+        <v>5.833393921715717</v>
       </c>
       <c r="F59" t="n">
         <v>7675900</v>
@@ -1612,16 +1612,16 @@
         <v>44497</v>
       </c>
       <c r="B60" t="n">
-        <v>5.992486476898193</v>
+        <v>5.992486000061035</v>
       </c>
       <c r="C60" t="n">
-        <v>6.027840344606625</v>
+        <v>6.027839864956272</v>
       </c>
       <c r="D60" t="n">
-        <v>5.727332047633601</v>
+        <v>5.727331591895446</v>
       </c>
       <c r="E60" t="n">
-        <v>5.753847659140599</v>
+        <v>5.75384720129253</v>
       </c>
       <c r="F60" t="n">
         <v>8299700</v>
@@ -1632,16 +1632,16 @@
         <v>44498</v>
       </c>
       <c r="B61" t="n">
-        <v>5.992486476898193</v>
+        <v>5.992486000061035</v>
       </c>
       <c r="C61" t="n">
-        <v>6.019001666953844</v>
+        <v>6.019001188006806</v>
       </c>
       <c r="D61" t="n">
-        <v>5.842232328411681</v>
+        <v>5.842231863530622</v>
       </c>
       <c r="E61" t="n">
-        <v>5.957132187738413</v>
+        <v>5.957131713714485</v>
       </c>
       <c r="F61" t="n">
         <v>3926300</v>
@@ -1652,16 +1652,16 @@
         <v>44501</v>
       </c>
       <c r="B62" t="n">
-        <v>6.00132417678833</v>
+        <v>6.001324653625488</v>
       </c>
       <c r="C62" t="n">
-        <v>6.063193650268579</v>
+        <v>6.063194132021597</v>
       </c>
       <c r="D62" t="n">
-        <v>5.948293380141535</v>
+        <v>5.948293852765114</v>
       </c>
       <c r="E62" t="n">
-        <v>5.965970312357133</v>
+        <v>5.965970786385239</v>
       </c>
       <c r="F62" t="n">
         <v>5059700</v>
@@ -1672,16 +1672,16 @@
         <v>44503</v>
       </c>
       <c r="B63" t="n">
-        <v>6.098546981811523</v>
+        <v>6.098548412322998</v>
       </c>
       <c r="C63" t="n">
-        <v>6.186931635166506</v>
+        <v>6.18693308641001</v>
       </c>
       <c r="D63" t="n">
-        <v>5.92177725365029</v>
+        <v>5.921778642697604</v>
       </c>
       <c r="E63" t="n">
-        <v>5.983646721724412</v>
+        <v>5.983648125284198</v>
       </c>
       <c r="F63" t="n">
         <v>5711600</v>
@@ -1692,16 +1692,16 @@
         <v>44504</v>
       </c>
       <c r="B64" t="n">
-        <v>5.965970993041992</v>
+        <v>5.965970516204834</v>
       </c>
       <c r="C64" t="n">
-        <v>6.160417269598838</v>
+        <v>6.160416777220335</v>
       </c>
       <c r="D64" t="n">
-        <v>5.842232453414908</v>
+        <v>5.842231986467696</v>
       </c>
       <c r="E64" t="n">
-        <v>6.098548210510975</v>
+        <v>6.098547723077428</v>
       </c>
       <c r="F64" t="n">
         <v>8687600</v>
@@ -1712,16 +1712,16 @@
         <v>44505</v>
       </c>
       <c r="B65" t="n">
-        <v>5.965970993041992</v>
+        <v>5.965970516204834</v>
       </c>
       <c r="C65" t="n">
-        <v>6.054355664204195</v>
+        <v>6.054355180302789</v>
       </c>
       <c r="D65" t="n">
-        <v>5.939455380967654</v>
+        <v>5.939454906249786</v>
       </c>
       <c r="E65" t="n">
-        <v>6.001324861506873</v>
+        <v>6.001324381844015</v>
       </c>
       <c r="F65" t="n">
         <v>3123600</v>
@@ -1732,16 +1732,16 @@
         <v>44508</v>
       </c>
       <c r="B66" t="n">
-        <v>5.983647346496582</v>
+        <v>5.983646869659424</v>
       </c>
       <c r="C66" t="n">
-        <v>6.036678144046689</v>
+        <v>6.036677662983505</v>
       </c>
       <c r="D66" t="n">
-        <v>5.939454804479167</v>
+        <v>5.939454331163716</v>
       </c>
       <c r="E66" t="n">
-        <v>6.010162955997293</v>
+        <v>6.010162477047105</v>
       </c>
       <c r="F66" t="n">
         <v>3898000</v>
@@ -1772,16 +1772,16 @@
         <v>44510</v>
       </c>
       <c r="B68" t="n">
-        <v>5.745009422302246</v>
+        <v>5.745008945465088</v>
       </c>
       <c r="C68" t="n">
-        <v>6.010163871912132</v>
+        <v>6.010163373067091</v>
       </c>
       <c r="D68" t="n">
-        <v>5.745009422302246</v>
+        <v>5.745008945465088</v>
       </c>
       <c r="E68" t="n">
-        <v>5.957132644829051</v>
+        <v>5.957132150385616</v>
       </c>
       <c r="F68" t="n">
         <v>10074000</v>
@@ -1792,16 +1792,16 @@
         <v>44511</v>
       </c>
       <c r="B69" t="n">
-        <v>6.0101637840271</v>
+        <v>6.010162830352783</v>
       </c>
       <c r="C69" t="n">
-        <v>6.036678975729536</v>
+        <v>6.036678017847871</v>
       </c>
       <c r="D69" t="n">
-        <v>5.80687882135247</v>
+        <v>5.806877899934787</v>
       </c>
       <c r="E69" t="n">
-        <v>5.833394013054906</v>
+        <v>5.833393087429874</v>
       </c>
       <c r="F69" t="n">
         <v>8604300</v>
@@ -1812,16 +1812,16 @@
         <v>44512</v>
       </c>
       <c r="B70" t="n">
-        <v>5.762685298919678</v>
+        <v>5.762686252593994</v>
       </c>
       <c r="C70" t="n">
-        <v>6.080870495711316</v>
+        <v>6.080871502042515</v>
       </c>
       <c r="D70" t="n">
-        <v>5.532885183396102</v>
+        <v>5.532886099040496</v>
       </c>
       <c r="E70" t="n">
-        <v>6.080870495711316</v>
+        <v>6.080871502042515</v>
       </c>
       <c r="F70" t="n">
         <v>20568500</v>
@@ -1832,16 +1832,16 @@
         <v>44516</v>
       </c>
       <c r="B71" t="n">
-        <v>5.320762157440186</v>
+        <v>5.320761680603027</v>
       </c>
       <c r="C71" t="n">
-        <v>5.815716727730977</v>
+        <v>5.815716206536877</v>
       </c>
       <c r="D71" t="n">
-        <v>5.223538810335335</v>
+        <v>5.223538342211159</v>
       </c>
       <c r="E71" t="n">
-        <v>5.789201537625966</v>
+        <v>5.789201018808111</v>
       </c>
       <c r="F71" t="n">
         <v>27445700</v>
@@ -1852,16 +1852,16 @@
         <v>44517</v>
       </c>
       <c r="B72" t="n">
-        <v>5.17050838470459</v>
+        <v>5.170507907867432</v>
       </c>
       <c r="C72" t="n">
-        <v>5.462178025779772</v>
+        <v>5.462177522044113</v>
       </c>
       <c r="D72" t="n">
-        <v>5.002577289838284</v>
+        <v>5.002576828488149</v>
       </c>
       <c r="E72" t="n">
-        <v>5.364955093055631</v>
+        <v>5.364954598286112</v>
       </c>
       <c r="F72" t="n">
         <v>24600900</v>
@@ -1892,16 +1892,16 @@
         <v>44519</v>
       </c>
       <c r="B74" t="n">
-        <v>5.241215229034424</v>
+        <v>5.241215705871582</v>
       </c>
       <c r="C74" t="n">
-        <v>5.285407770133975</v>
+        <v>5.285408250991699</v>
       </c>
       <c r="D74" t="n">
-        <v>5.090961516488821</v>
+        <v>5.090961979656143</v>
       </c>
       <c r="E74" t="n">
-        <v>5.161669245087059</v>
+        <v>5.161669714687254</v>
       </c>
       <c r="F74" t="n">
         <v>11364600</v>
@@ -1932,16 +1932,16 @@
         <v>44523</v>
       </c>
       <c r="B76" t="n">
-        <v>5.011415481567383</v>
+        <v>5.011415958404541</v>
       </c>
       <c r="C76" t="n">
-        <v>5.099800148849164</v>
+        <v>5.09980063409614</v>
       </c>
       <c r="D76" t="n">
-        <v>4.781614925183414</v>
+        <v>4.781615380155004</v>
       </c>
       <c r="E76" t="n">
-        <v>5.002576804113536</v>
+        <v>5.002577280109692</v>
       </c>
       <c r="F76" t="n">
         <v>9084200</v>
@@ -1972,16 +1972,16 @@
         <v>44525</v>
       </c>
       <c r="B78" t="n">
-        <v>5.373793125152588</v>
+        <v>5.373792171478271</v>
       </c>
       <c r="C78" t="n">
-        <v>5.373793125152588</v>
+        <v>5.373792171478271</v>
       </c>
       <c r="D78" t="n">
-        <v>4.799292123891901</v>
+        <v>4.799291272172914</v>
       </c>
       <c r="E78" t="n">
-        <v>4.949546277300996</v>
+        <v>4.949545398916761</v>
       </c>
       <c r="F78" t="n">
         <v>20546100</v>
@@ -1992,16 +1992,16 @@
         <v>44526</v>
       </c>
       <c r="B79" t="n">
-        <v>5.223539352416992</v>
+        <v>5.223538875579834</v>
       </c>
       <c r="C79" t="n">
-        <v>5.338439645332938</v>
+        <v>5.338439158006967</v>
       </c>
       <c r="D79" t="n">
-        <v>5.020254380893162</v>
+        <v>5.02025392261312</v>
       </c>
       <c r="E79" t="n">
-        <v>5.037931316614738</v>
+        <v>5.037930856721036</v>
       </c>
       <c r="F79" t="n">
         <v>8564200</v>
@@ -2012,16 +2012,16 @@
         <v>44529</v>
       </c>
       <c r="B80" t="n">
-        <v>5.117477416992188</v>
+        <v>5.117476940155029</v>
       </c>
       <c r="C80" t="n">
-        <v>5.391470114210696</v>
+        <v>5.391469611843401</v>
       </c>
       <c r="D80" t="n">
-        <v>5.117477416992188</v>
+        <v>5.117476940155029</v>
       </c>
       <c r="E80" t="n">
-        <v>5.285408506536053</v>
+        <v>5.285408014051384</v>
       </c>
       <c r="F80" t="n">
         <v>7811800</v>
@@ -2032,16 +2032,16 @@
         <v>44530</v>
       </c>
       <c r="B81" t="n">
-        <v>4.825806617736816</v>
+        <v>4.825807571411133</v>
       </c>
       <c r="C81" t="n">
-        <v>5.126314854902876</v>
+        <v>5.126315867963532</v>
       </c>
       <c r="D81" t="n">
-        <v>4.790452757064487</v>
+        <v>4.790453703752186</v>
       </c>
       <c r="E81" t="n">
-        <v>5.07328364244312</v>
+        <v>5.073284645023764</v>
       </c>
       <c r="F81" t="n">
         <v>11282700</v>
@@ -2052,16 +2052,16 @@
         <v>44531</v>
       </c>
       <c r="B82" t="n">
-        <v>4.852323055267334</v>
+        <v>4.852323532104492</v>
       </c>
       <c r="C82" t="n">
-        <v>5.152831370017339</v>
+        <v>5.15283187638541</v>
       </c>
       <c r="D82" t="n">
-        <v>4.852323055267334</v>
+        <v>4.852323532104492</v>
       </c>
       <c r="E82" t="n">
-        <v>4.896515603242819</v>
+        <v>4.896516084422773</v>
       </c>
       <c r="F82" t="n">
         <v>12492100</v>
@@ -2072,16 +2072,16 @@
         <v>44532</v>
       </c>
       <c r="B83" t="n">
-        <v>5.029092788696289</v>
+        <v>5.029092311859131</v>
       </c>
       <c r="C83" t="n">
-        <v>5.029092788696289</v>
+        <v>5.029092311859131</v>
       </c>
       <c r="D83" t="n">
-        <v>4.746261410928263</v>
+        <v>4.746260960907972</v>
       </c>
       <c r="E83" t="n">
-        <v>4.905354245307752</v>
+        <v>4.905353780202955</v>
       </c>
       <c r="F83" t="n">
         <v>18379200</v>
@@ -2092,16 +2092,16 @@
         <v>44533</v>
       </c>
       <c r="B84" t="n">
-        <v>5.320762157440186</v>
+        <v>5.320761680603027</v>
       </c>
       <c r="C84" t="n">
-        <v>5.329600835109421</v>
+        <v>5.329600357480157</v>
       </c>
       <c r="D84" t="n">
-        <v>4.976061735915614</v>
+        <v>4.97606128996989</v>
       </c>
       <c r="E84" t="n">
-        <v>5.020253859907747</v>
+        <v>5.020253410001604</v>
       </c>
       <c r="F84" t="n">
         <v>10548200</v>
@@ -2132,16 +2132,16 @@
         <v>44537</v>
       </c>
       <c r="B86" t="n">
-        <v>5.232377052307129</v>
+        <v>5.232376575469971</v>
       </c>
       <c r="C86" t="n">
-        <v>5.258892240204233</v>
+        <v>5.258891760950692</v>
       </c>
       <c r="D86" t="n">
-        <v>4.914191847382692</v>
+        <v>4.914191399542398</v>
       </c>
       <c r="E86" t="n">
-        <v>5.24121530778906</v>
+        <v>5.241214830146453</v>
       </c>
       <c r="F86" t="n">
         <v>9906100</v>
@@ -2172,16 +2172,16 @@
         <v>44539</v>
       </c>
       <c r="B88" t="n">
-        <v>5.232377052307129</v>
+        <v>5.232376575469971</v>
       </c>
       <c r="C88" t="n">
-        <v>5.435661985807282</v>
+        <v>5.435661490444354</v>
       </c>
       <c r="D88" t="n">
-        <v>5.179346255061608</v>
+        <v>5.179345783057254</v>
       </c>
       <c r="E88" t="n">
-        <v>5.205861442958712</v>
+        <v>5.205860968537976</v>
       </c>
       <c r="F88" t="n">
         <v>9205900</v>
@@ -2192,16 +2192,16 @@
         <v>44540</v>
       </c>
       <c r="B89" t="n">
-        <v>5.444499969482422</v>
+        <v>5.444500923156738</v>
       </c>
       <c r="C89" t="n">
-        <v>5.568238911662507</v>
+        <v>5.568239887011294</v>
       </c>
       <c r="D89" t="n">
-        <v>5.2412150461309</v>
+        <v>5.241215964197243</v>
       </c>
       <c r="E89" t="n">
-        <v>5.267730654155574</v>
+        <v>5.267731576866467</v>
       </c>
       <c r="F89" t="n">
         <v>8741300</v>
@@ -2212,16 +2212,16 @@
         <v>44543</v>
       </c>
       <c r="B90" t="n">
-        <v>5.497531890869141</v>
+        <v>5.497531414031982</v>
       </c>
       <c r="C90" t="n">
-        <v>5.621270858411092</v>
+        <v>5.621270370841238</v>
       </c>
       <c r="D90" t="n">
-        <v>5.426824150245956</v>
+        <v>5.426823679541746</v>
       </c>
       <c r="E90" t="n">
-        <v>5.444501085401752</v>
+        <v>5.444500613164305</v>
       </c>
       <c r="F90" t="n">
         <v>8265100</v>
@@ -2232,16 +2232,16 @@
         <v>44544</v>
       </c>
       <c r="B91" t="n">
-        <v>5.453338623046875</v>
+        <v>5.453339099884033</v>
       </c>
       <c r="C91" t="n">
-        <v>5.603592751168627</v>
+        <v>5.60359324114393</v>
       </c>
       <c r="D91" t="n">
-        <v>5.426823015133682</v>
+        <v>5.426823489652329</v>
       </c>
       <c r="E91" t="n">
-        <v>5.497530740967144</v>
+        <v>5.497531221668439</v>
       </c>
       <c r="F91" t="n">
         <v>6640900</v>
@@ -2272,16 +2272,16 @@
         <v>44546</v>
       </c>
       <c r="B93" t="n">
-        <v>5.400308609008789</v>
+        <v>5.400308132171631</v>
       </c>
       <c r="C93" t="n">
-        <v>5.550562758842054</v>
+        <v>5.550562268737735</v>
       </c>
       <c r="D93" t="n">
-        <v>5.347277806970816</v>
+        <v>5.347277334816178</v>
       </c>
       <c r="E93" t="n">
-        <v>5.515208469365389</v>
+        <v>5.515207982382787</v>
       </c>
       <c r="F93" t="n">
         <v>9238300</v>
@@ -2292,16 +2292,16 @@
         <v>44547</v>
       </c>
       <c r="B94" t="n">
-        <v>5.241215229034424</v>
+        <v>5.241215705871582</v>
       </c>
       <c r="C94" t="n">
-        <v>5.347277243383087</v>
+        <v>5.347277729869593</v>
       </c>
       <c r="D94" t="n">
-        <v>5.241215229034424</v>
+        <v>5.241215705871582</v>
       </c>
       <c r="E94" t="n">
-        <v>5.320761634433095</v>
+        <v>5.320762118507254</v>
       </c>
       <c r="F94" t="n">
         <v>50153800</v>
@@ -2312,16 +2312,16 @@
         <v>44550</v>
       </c>
       <c r="B95" t="n">
-        <v>5.14399242401123</v>
+        <v>5.143992900848389</v>
       </c>
       <c r="C95" t="n">
-        <v>5.179346289073743</v>
+        <v>5.179346769188129</v>
       </c>
       <c r="D95" t="n">
-        <v>4.949545744716101</v>
+        <v>4.949546203528466</v>
       </c>
       <c r="E95" t="n">
-        <v>5.179346289073743</v>
+        <v>5.179346769188129</v>
       </c>
       <c r="F95" t="n">
         <v>8433600</v>
@@ -2332,16 +2332,16 @@
         <v>44551</v>
       </c>
       <c r="B96" t="n">
-        <v>5.082122802734375</v>
+        <v>5.082123279571533</v>
       </c>
       <c r="C96" t="n">
-        <v>5.223538258902567</v>
+        <v>5.223538749008224</v>
       </c>
       <c r="D96" t="n">
-        <v>5.020253329935139</v>
+        <v>5.020253800967309</v>
       </c>
       <c r="E96" t="n">
-        <v>5.170507462839494</v>
+        <v>5.170507947969465</v>
       </c>
       <c r="F96" t="n">
         <v>5049800</v>
@@ -2352,16 +2352,16 @@
         <v>44552</v>
       </c>
       <c r="B97" t="n">
-        <v>5.011415481567383</v>
+        <v>5.011415958404541</v>
       </c>
       <c r="C97" t="n">
-        <v>5.073284537938961</v>
+        <v>5.073285020662972</v>
       </c>
       <c r="D97" t="n">
-        <v>4.914192136831755</v>
+        <v>4.914192604418092</v>
       </c>
       <c r="E97" t="n">
-        <v>5.055607604482605</v>
+        <v>5.055608085524652</v>
       </c>
       <c r="F97" t="n">
         <v>4649500</v>
@@ -2372,16 +2372,16 @@
         <v>44553</v>
       </c>
       <c r="B98" t="n">
-        <v>5.055606842041016</v>
+        <v>5.055607318878174</v>
       </c>
       <c r="C98" t="n">
-        <v>5.073283772831495</v>
+        <v>5.073284251335914</v>
       </c>
       <c r="D98" t="n">
-        <v>4.96722218808862</v>
+        <v>4.967222656589472</v>
       </c>
       <c r="E98" t="n">
-        <v>4.993737794999975</v>
+        <v>4.993738266001739</v>
       </c>
       <c r="F98" t="n">
         <v>3174500</v>
@@ -2392,16 +2392,16 @@
         <v>44557</v>
       </c>
       <c r="B99" t="n">
-        <v>5.232377052307129</v>
+        <v>5.232376575469971</v>
       </c>
       <c r="C99" t="n">
-        <v>5.232377052307129</v>
+        <v>5.232376575469971</v>
       </c>
       <c r="D99" t="n">
-        <v>5.011415186391803</v>
+        <v>5.011414729691348</v>
       </c>
       <c r="E99" t="n">
-        <v>5.04676905122215</v>
+        <v>5.046768591299826</v>
       </c>
       <c r="F99" t="n">
         <v>4493500</v>
@@ -2412,16 +2412,16 @@
         <v>44558</v>
       </c>
       <c r="B100" t="n">
-        <v>5.347277164459229</v>
+        <v>5.347278118133545</v>
       </c>
       <c r="C100" t="n">
-        <v>5.347277164459229</v>
+        <v>5.347278118133545</v>
       </c>
       <c r="D100" t="n">
-        <v>5.188184356010038</v>
+        <v>5.188185281310526</v>
       </c>
       <c r="E100" t="n">
-        <v>5.21469996456867</v>
+        <v>5.214700894598154</v>
       </c>
       <c r="F100" t="n">
         <v>4379800</v>
@@ -2452,16 +2452,16 @@
         <v>44560</v>
       </c>
       <c r="B102" t="n">
-        <v>5.700815677642822</v>
+        <v>5.70081615447998</v>
       </c>
       <c r="C102" t="n">
-        <v>5.709654354119633</v>
+        <v>5.70965483169609</v>
       </c>
       <c r="D102" t="n">
-        <v>5.258891968633261</v>
+        <v>5.258892408506298</v>
       </c>
       <c r="E102" t="n">
-        <v>5.320761439617065</v>
+        <v>5.320761884665091</v>
       </c>
       <c r="F102" t="n">
         <v>23096200</v>
@@ -2492,16 +2492,16 @@
         <v>44565</v>
       </c>
       <c r="B104" t="n">
-        <v>5.594754695892334</v>
+        <v>5.594754219055176</v>
       </c>
       <c r="C104" t="n">
-        <v>5.612431629313347</v>
+        <v>5.612431150969596</v>
       </c>
       <c r="D104" t="n">
-        <v>5.444500551088055</v>
+        <v>5.444500087056956</v>
       </c>
       <c r="E104" t="n">
-        <v>5.532885639644457</v>
+        <v>5.532885168080356</v>
       </c>
       <c r="F104" t="n">
         <v>10613100</v>
@@ -2512,16 +2512,16 @@
         <v>44566</v>
       </c>
       <c r="B105" t="n">
-        <v>5.117477416992188</v>
+        <v>5.117476940155029</v>
       </c>
       <c r="C105" t="n">
-        <v>5.568239881786464</v>
+        <v>5.568239362948087</v>
       </c>
       <c r="D105" t="n">
-        <v>5.117477416992188</v>
+        <v>5.117476940155029</v>
       </c>
       <c r="E105" t="n">
-        <v>5.550562947174024</v>
+        <v>5.550562429982751</v>
       </c>
       <c r="F105" t="n">
         <v>7203400</v>
@@ -2552,16 +2552,16 @@
         <v>44568</v>
       </c>
       <c r="B107" t="n">
-        <v>5.163622379302979</v>
+        <v>5.163622856140137</v>
       </c>
       <c r="C107" t="n">
-        <v>5.278960698586984</v>
+        <v>5.278961186075115</v>
       </c>
       <c r="D107" t="n">
-        <v>4.941817300823532</v>
+        <v>4.941817757177995</v>
       </c>
       <c r="E107" t="n">
-        <v>4.977306079535475</v>
+        <v>4.977306539167166</v>
       </c>
       <c r="F107" t="n">
         <v>10961100</v>
@@ -2592,16 +2592,16 @@
         <v>44572</v>
       </c>
       <c r="B109" t="n">
-        <v>5.234600067138672</v>
+        <v>5.234601020812988</v>
       </c>
       <c r="C109" t="n">
-        <v>5.234600067138672</v>
+        <v>5.234601020812988</v>
       </c>
       <c r="D109" t="n">
-        <v>5.021666966502512</v>
+        <v>5.021667881383257</v>
       </c>
       <c r="E109" t="n">
-        <v>5.021666966502512</v>
+        <v>5.021667881383257</v>
       </c>
       <c r="F109" t="n">
         <v>5425200</v>
@@ -2632,16 +2632,16 @@
         <v>44574</v>
       </c>
       <c r="B111" t="n">
-        <v>5.42091703414917</v>
+        <v>5.420916080474854</v>
       </c>
       <c r="C111" t="n">
-        <v>5.50963899398392</v>
+        <v>5.509638024701201</v>
       </c>
       <c r="D111" t="n">
-        <v>5.358811450735008</v>
+        <v>5.358810507986609</v>
       </c>
       <c r="E111" t="n">
-        <v>5.358811450735008</v>
+        <v>5.358810507986609</v>
       </c>
       <c r="F111" t="n">
         <v>4388600</v>
@@ -2672,16 +2672,16 @@
         <v>44578</v>
       </c>
       <c r="B113" t="n">
-        <v>5.483021259307861</v>
+        <v>5.48302173614502</v>
       </c>
       <c r="C113" t="n">
-        <v>5.624976793890898</v>
+        <v>5.62497728307338</v>
       </c>
       <c r="D113" t="n">
-        <v>5.447532481427003</v>
+        <v>5.447532955177839</v>
       </c>
       <c r="E113" t="n">
-        <v>5.447532481427003</v>
+        <v>5.447532955177839</v>
       </c>
       <c r="F113" t="n">
         <v>3137800</v>
@@ -2692,16 +2692,16 @@
         <v>44579</v>
       </c>
       <c r="B114" t="n">
-        <v>5.483021259307861</v>
+        <v>5.48302173614502</v>
       </c>
       <c r="C114" t="n">
-        <v>5.536254426129148</v>
+        <v>5.536254907595789</v>
       </c>
       <c r="D114" t="n">
-        <v>5.376554925665286</v>
+        <v>5.376555393243478</v>
       </c>
       <c r="E114" t="n">
-        <v>5.474149276367449</v>
+        <v>5.474149752433044</v>
       </c>
       <c r="F114" t="n">
         <v>3854900</v>
@@ -2712,16 +2712,16 @@
         <v>44580</v>
       </c>
       <c r="B115" t="n">
-        <v>5.651593685150146</v>
+        <v>5.651593208312988</v>
       </c>
       <c r="C115" t="n">
-        <v>5.749188044821177</v>
+        <v>5.749187559749773</v>
       </c>
       <c r="D115" t="n">
-        <v>5.509638560581113</v>
+        <v>5.509638095721016</v>
       </c>
       <c r="E115" t="n">
-        <v>5.509638560581113</v>
+        <v>5.509638095721016</v>
       </c>
       <c r="F115" t="n">
         <v>12660500</v>
@@ -2752,16 +2752,16 @@
         <v>44582</v>
       </c>
       <c r="B117" t="n">
-        <v>5.527382373809814</v>
+        <v>5.527383327484131</v>
       </c>
       <c r="C117" t="n">
-        <v>5.687081872269151</v>
+        <v>5.687082853497435</v>
       </c>
       <c r="D117" t="n">
-        <v>5.483021190485755</v>
+        <v>5.483022136506155</v>
       </c>
       <c r="E117" t="n">
-        <v>5.678209889440098</v>
+        <v>5.678210869137642</v>
       </c>
       <c r="F117" t="n">
         <v>7609900</v>
@@ -2772,16 +2772,16 @@
         <v>44585</v>
       </c>
       <c r="B118" t="n">
-        <v>5.456405639648438</v>
+        <v>5.456405162811279</v>
       </c>
       <c r="C118" t="n">
-        <v>5.491894422421788</v>
+        <v>5.491893942483253</v>
       </c>
       <c r="D118" t="n">
-        <v>5.349939291328385</v>
+        <v>5.349938823795358</v>
       </c>
       <c r="E118" t="n">
-        <v>5.465277623811945</v>
+        <v>5.465277146199461</v>
       </c>
       <c r="F118" t="n">
         <v>8531700</v>
@@ -2792,16 +2792,16 @@
         <v>44586</v>
       </c>
       <c r="B119" t="n">
-        <v>5.500765800476074</v>
+        <v>5.500766277313232</v>
       </c>
       <c r="C119" t="n">
-        <v>5.571743781261634</v>
+        <v>5.57174426425156</v>
       </c>
       <c r="D119" t="n">
-        <v>5.367683091269735</v>
+        <v>5.36768355657054</v>
       </c>
       <c r="E119" t="n">
-        <v>5.394299463887157</v>
+        <v>5.394299931495218</v>
       </c>
       <c r="F119" t="n">
         <v>8097000</v>
@@ -2812,16 +2812,16 @@
         <v>44587</v>
       </c>
       <c r="B120" t="n">
-        <v>5.518511295318604</v>
+        <v>5.518510818481445</v>
       </c>
       <c r="C120" t="n">
-        <v>5.678211255251036</v>
+        <v>5.678210764614708</v>
       </c>
       <c r="D120" t="n">
-        <v>5.491894917369664</v>
+        <v>5.491894442832344</v>
       </c>
       <c r="E120" t="n">
-        <v>5.59836127528482</v>
+        <v>5.598360791548077</v>
       </c>
       <c r="F120" t="n">
         <v>11610000</v>
@@ -2832,16 +2832,16 @@
         <v>44588</v>
       </c>
       <c r="B121" t="n">
-        <v>5.545126914978027</v>
+        <v>5.545127391815186</v>
       </c>
       <c r="C121" t="n">
-        <v>5.749187602371603</v>
+        <v>5.74918809675637</v>
       </c>
       <c r="D121" t="n">
-        <v>5.527382525772483</v>
+        <v>5.527383001083763</v>
       </c>
       <c r="E121" t="n">
-        <v>5.580615693389118</v>
+        <v>5.580616173278031</v>
       </c>
       <c r="F121" t="n">
         <v>8501200</v>
@@ -2872,16 +2872,16 @@
         <v>44592</v>
       </c>
       <c r="B123" t="n">
-        <v>5.6959547996521</v>
+        <v>5.695955276489258</v>
       </c>
       <c r="C123" t="n">
-        <v>5.793549158064543</v>
+        <v>5.793549643071818</v>
       </c>
       <c r="D123" t="n">
-        <v>5.571744067256032</v>
+        <v>5.571744533694882</v>
       </c>
       <c r="E123" t="n">
-        <v>5.607232847940623</v>
+        <v>5.607233317350418</v>
       </c>
       <c r="F123" t="n">
         <v>7514700</v>
@@ -2912,16 +2912,16 @@
         <v>44594</v>
       </c>
       <c r="B125" t="n">
-        <v>5.669337749481201</v>
+        <v>5.669337272644043</v>
       </c>
       <c r="C125" t="n">
-        <v>5.882270847141231</v>
+        <v>5.882270352394677</v>
       </c>
       <c r="D125" t="n">
-        <v>5.651593359931167</v>
+        <v>5.651592884586456</v>
       </c>
       <c r="E125" t="n">
-        <v>5.722570918131304</v>
+        <v>5.722570436816806</v>
       </c>
       <c r="F125" t="n">
         <v>8808600</v>
@@ -2972,16 +2972,16 @@
         <v>44599</v>
       </c>
       <c r="B128" t="n">
-        <v>5.562872409820557</v>
+        <v>5.56287145614624</v>
       </c>
       <c r="C128" t="n">
-        <v>5.775805545667787</v>
+        <v>5.775804555489152</v>
       </c>
       <c r="D128" t="n">
-        <v>5.554000424984256</v>
+        <v>5.553999472830914</v>
       </c>
       <c r="E128" t="n">
-        <v>5.704827551678914</v>
+        <v>5.704826573668434</v>
       </c>
       <c r="F128" t="n">
         <v>7178800</v>
@@ -3012,16 +3012,16 @@
         <v>44601</v>
       </c>
       <c r="B130" t="n">
-        <v>5.633849143981934</v>
+        <v>5.633848667144775</v>
       </c>
       <c r="C130" t="n">
-        <v>5.740315484562782</v>
+        <v>5.740314998714537</v>
       </c>
       <c r="D130" t="n">
-        <v>5.58948838026973</v>
+        <v>5.589487907187173</v>
       </c>
       <c r="E130" t="n">
-        <v>5.616104753885126</v>
+        <v>5.616104278549815</v>
       </c>
       <c r="F130" t="n">
         <v>8867400</v>
@@ -3052,16 +3052,16 @@
         <v>44603</v>
       </c>
       <c r="B132" t="n">
-        <v>5.633849143981934</v>
+        <v>5.633848667144775</v>
       </c>
       <c r="C132" t="n">
-        <v>5.775804687816029</v>
+        <v>5.775804198964051</v>
       </c>
       <c r="D132" t="n">
-        <v>5.58948838026973</v>
+        <v>5.589487907187173</v>
       </c>
       <c r="E132" t="n">
-        <v>5.731443501044193</v>
+        <v>5.731443015946853</v>
       </c>
       <c r="F132" t="n">
         <v>8001300</v>
@@ -3072,16 +3072,16 @@
         <v>44606</v>
       </c>
       <c r="B133" t="n">
-        <v>5.6959547996521</v>
+        <v>5.695955276489258</v>
       </c>
       <c r="C133" t="n">
-        <v>5.766932361021281</v>
+        <v>5.76693284380033</v>
       </c>
       <c r="D133" t="n">
-        <v>5.642721628625214</v>
+        <v>5.642722101005954</v>
       </c>
       <c r="E133" t="n">
-        <v>5.642721628625214</v>
+        <v>5.642722101005954</v>
       </c>
       <c r="F133" t="n">
         <v>12680200</v>
@@ -3092,16 +3092,16 @@
         <v>44607</v>
       </c>
       <c r="B134" t="n">
-        <v>5.6959547996521</v>
+        <v>5.695955276489258</v>
       </c>
       <c r="C134" t="n">
-        <v>5.811293548406838</v>
+        <v>5.811294034899586</v>
       </c>
       <c r="D134" t="n">
-        <v>5.518510473169509</v>
+        <v>5.518510935151906</v>
       </c>
       <c r="E134" t="n">
-        <v>5.811293548406838</v>
+        <v>5.811294034899586</v>
       </c>
       <c r="F134" t="n">
         <v>17426200</v>
@@ -3152,16 +3152,16 @@
         <v>44610</v>
       </c>
       <c r="B137" t="n">
-        <v>5.42091703414917</v>
+        <v>5.420916080474854</v>
       </c>
       <c r="C137" t="n">
-        <v>5.61610534578562</v>
+        <v>5.616104357772818</v>
       </c>
       <c r="D137" t="n">
-        <v>5.305578274834157</v>
+        <v>5.305577341450801</v>
       </c>
       <c r="E137" t="n">
-        <v>5.59836095381867</v>
+        <v>5.598359968927548</v>
       </c>
       <c r="F137" t="n">
         <v>12852100</v>
@@ -3192,16 +3192,16 @@
         <v>44614</v>
       </c>
       <c r="B139" t="n">
-        <v>5.012795448303223</v>
+        <v>5.012794971466064</v>
       </c>
       <c r="C139" t="n">
-        <v>5.234600552891333</v>
+        <v>5.234600054955186</v>
       </c>
       <c r="D139" t="n">
-        <v>4.977306665413898</v>
+        <v>4.977306191952575</v>
       </c>
       <c r="E139" t="n">
-        <v>5.172494971305183</v>
+        <v>5.172494479276767</v>
       </c>
       <c r="F139" t="n">
         <v>7346000</v>
@@ -3212,16 +3212,16 @@
         <v>44615</v>
       </c>
       <c r="B140" t="n">
-        <v>5.021667003631592</v>
+        <v>5.021666526794434</v>
       </c>
       <c r="C140" t="n">
-        <v>5.101516969842998</v>
+        <v>5.10151648542361</v>
       </c>
       <c r="D140" t="n">
-        <v>4.968433833843864</v>
+        <v>4.968433362061512</v>
       </c>
       <c r="E140" t="n">
-        <v>5.057155783490078</v>
+        <v>5.057155303283048</v>
       </c>
       <c r="F140" t="n">
         <v>10772600</v>
@@ -3272,16 +3272,16 @@
         <v>44622</v>
       </c>
       <c r="B143" t="n">
-        <v>5.314449310302734</v>
+        <v>5.314448833465576</v>
       </c>
       <c r="C143" t="n">
-        <v>5.349938510959111</v>
+        <v>5.349938030937696</v>
       </c>
       <c r="D143" t="n">
-        <v>5.03053908952852</v>
+        <v>5.030538638165109</v>
       </c>
       <c r="E143" t="n">
-        <v>5.101516644722073</v>
+        <v>5.101516186990226</v>
       </c>
       <c r="F143" t="n">
         <v>7030100</v>
@@ -3292,16 +3292,16 @@
         <v>44623</v>
       </c>
       <c r="B144" t="n">
-        <v>5.465277194976807</v>
+        <v>5.465277671813965</v>
       </c>
       <c r="C144" t="n">
-        <v>5.545127161481217</v>
+        <v>5.545127645285164</v>
       </c>
       <c r="D144" t="n">
-        <v>5.323322075021968</v>
+        <v>5.323322539473757</v>
       </c>
       <c r="E144" t="n">
-        <v>5.323322075021968</v>
+        <v>5.323322539473757</v>
       </c>
       <c r="F144" t="n">
         <v>18057800</v>
@@ -3332,16 +3332,16 @@
         <v>44627</v>
       </c>
       <c r="B146" t="n">
-        <v>5.483021259307861</v>
+        <v>5.48302173614502</v>
       </c>
       <c r="C146" t="n">
-        <v>5.58948801601004</v>
+        <v>5.5894885021062</v>
       </c>
       <c r="D146" t="n">
-        <v>5.403171720605732</v>
+        <v>5.403172190498684</v>
       </c>
       <c r="E146" t="n">
-        <v>5.491893665307877</v>
+        <v>5.491894142916634</v>
       </c>
       <c r="F146" t="n">
         <v>12429900</v>
@@ -3352,16 +3352,16 @@
         <v>44628</v>
       </c>
       <c r="B147" t="n">
-        <v>5.589488506317139</v>
+        <v>5.58948802947998</v>
       </c>
       <c r="C147" t="n">
-        <v>5.589488506317139</v>
+        <v>5.58948802947998</v>
       </c>
       <c r="D147" t="n">
-        <v>5.420916585066217</v>
+        <v>5.420916122609865</v>
       </c>
       <c r="E147" t="n">
-        <v>5.500766130772708</v>
+        <v>5.500765661504422</v>
       </c>
       <c r="F147" t="n">
         <v>5566500</v>
@@ -3372,16 +3372,16 @@
         <v>44629</v>
       </c>
       <c r="B148" t="n">
-        <v>5.6959547996521</v>
+        <v>5.695955276489258</v>
       </c>
       <c r="C148" t="n">
-        <v>5.704826783293429</v>
+        <v>5.704827260873306</v>
       </c>
       <c r="D148" t="n">
-        <v>5.553999676913737</v>
+        <v>5.554000141867114</v>
       </c>
       <c r="E148" t="n">
-        <v>5.589488457598327</v>
+        <v>5.58948892552265</v>
       </c>
       <c r="F148" t="n">
         <v>9079900</v>
@@ -3392,16 +3392,16 @@
         <v>44630</v>
       </c>
       <c r="B149" t="n">
-        <v>5.6959547996521</v>
+        <v>5.695955276489258</v>
       </c>
       <c r="C149" t="n">
-        <v>5.829037938749134</v>
+        <v>5.829038426727354</v>
       </c>
       <c r="D149" t="n">
-        <v>5.553999676913737</v>
+        <v>5.554000141867114</v>
       </c>
       <c r="E149" t="n">
-        <v>5.624977238282918</v>
+        <v>5.624977709178186</v>
       </c>
       <c r="F149" t="n">
         <v>15215200</v>
@@ -3412,16 +3412,16 @@
         <v>44631</v>
       </c>
       <c r="B150" t="n">
-        <v>5.598360061645508</v>
+        <v>5.59835958480835</v>
       </c>
       <c r="C150" t="n">
-        <v>5.97986463966694</v>
+        <v>5.979864130335345</v>
       </c>
       <c r="D150" t="n">
-        <v>5.527382505088926</v>
+        <v>5.527382034297241</v>
       </c>
       <c r="E150" t="n">
-        <v>5.695954413440612</v>
+        <v>5.69595392829091</v>
       </c>
       <c r="F150" t="n">
         <v>16712700</v>
@@ -3432,16 +3432,16 @@
         <v>44634</v>
       </c>
       <c r="B151" t="n">
-        <v>5.589488506317139</v>
+        <v>5.58948802947998</v>
       </c>
       <c r="C151" t="n">
-        <v>5.722571223514505</v>
+        <v>5.72257073532411</v>
       </c>
       <c r="D151" t="n">
-        <v>5.518510521269666</v>
+        <v>5.518510050487613</v>
       </c>
       <c r="E151" t="n">
-        <v>5.607232896814097</v>
+        <v>5.607232418463171</v>
       </c>
       <c r="F151" t="n">
         <v>7706100</v>
@@ -3452,16 +3452,16 @@
         <v>44635</v>
       </c>
       <c r="B152" t="n">
-        <v>5.651593685150146</v>
+        <v>5.651593208312988</v>
       </c>
       <c r="C152" t="n">
-        <v>5.687082466292404</v>
+        <v>5.687081986460981</v>
       </c>
       <c r="D152" t="n">
-        <v>5.500766153765728</v>
+        <v>5.500765689654214</v>
       </c>
       <c r="E152" t="n">
-        <v>5.509638560581113</v>
+        <v>5.509638095721016</v>
       </c>
       <c r="F152" t="n">
         <v>5880900</v>
@@ -3472,16 +3472,16 @@
         <v>44636</v>
       </c>
       <c r="B153" t="n">
-        <v>5.624976634979248</v>
+        <v>5.624977111816406</v>
       </c>
       <c r="C153" t="n">
-        <v>5.766931742492297</v>
+        <v>5.766932231363189</v>
       </c>
       <c r="D153" t="n">
-        <v>5.51850988128487</v>
+        <v>5.518510349096693</v>
       </c>
       <c r="E153" t="n">
-        <v>5.713698577174903</v>
+        <v>5.713699061533146</v>
       </c>
       <c r="F153" t="n">
         <v>10739100</v>
@@ -3512,16 +3512,16 @@
         <v>44638</v>
       </c>
       <c r="B155" t="n">
-        <v>6.201670169830322</v>
+        <v>6.20167064666748</v>
       </c>
       <c r="C155" t="n">
-        <v>6.201670169830322</v>
+        <v>6.20167064666748</v>
       </c>
       <c r="D155" t="n">
-        <v>5.891143125613262</v>
+        <v>5.891143578574458</v>
       </c>
       <c r="E155" t="n">
-        <v>5.891143125613262</v>
+        <v>5.891143578574458</v>
       </c>
       <c r="F155" t="n">
         <v>17710700</v>
@@ -3532,16 +3532,16 @@
         <v>44641</v>
       </c>
       <c r="B156" t="n">
-        <v>6.104075908660889</v>
+        <v>6.104076385498047</v>
       </c>
       <c r="C156" t="n">
-        <v>6.34362537835539</v>
+        <v>6.343625873905633</v>
       </c>
       <c r="D156" t="n">
-        <v>6.024225944409515</v>
+        <v>6.024226415008968</v>
       </c>
       <c r="E156" t="n">
-        <v>6.183925449852644</v>
+        <v>6.183925932927476</v>
       </c>
       <c r="F156" t="n">
         <v>14982100</v>
@@ -3572,16 +3572,16 @@
         <v>44643</v>
       </c>
       <c r="B158" t="n">
-        <v>6.308136940002441</v>
+        <v>6.308136463165283</v>
       </c>
       <c r="C158" t="n">
-        <v>6.334753314150418</v>
+        <v>6.334752835301306</v>
       </c>
       <c r="D158" t="n">
-        <v>6.201670174231618</v>
+        <v>6.201669705442368</v>
       </c>
       <c r="E158" t="n">
-        <v>6.263775752342961</v>
+        <v>6.263775278859101</v>
       </c>
       <c r="F158" t="n">
         <v>8187500</v>
@@ -3592,16 +3592,16 @@
         <v>44644</v>
       </c>
       <c r="B159" t="n">
-        <v>6.343625545501709</v>
+        <v>6.343625068664551</v>
       </c>
       <c r="C159" t="n">
-        <v>6.432347495307822</v>
+        <v>6.432347011801619</v>
       </c>
       <c r="D159" t="n">
-        <v>6.254903595695596</v>
+        <v>6.254903125527482</v>
       </c>
       <c r="E159" t="n">
-        <v>6.299264359068839</v>
+        <v>6.299263885566218</v>
       </c>
       <c r="F159" t="n">
         <v>11578200</v>
@@ -3612,16 +3612,16 @@
         <v>44645</v>
       </c>
       <c r="B160" t="n">
-        <v>6.450092315673828</v>
+        <v>6.45009183883667</v>
       </c>
       <c r="C160" t="n">
-        <v>6.512197896212132</v>
+        <v>6.512197414783683</v>
       </c>
       <c r="D160" t="n">
-        <v>6.237159621930483</v>
+        <v>6.237159160834839</v>
       </c>
       <c r="E160" t="n">
-        <v>6.343625968802155</v>
+        <v>6.343625499835754</v>
       </c>
       <c r="F160" t="n">
         <v>15324200</v>
@@ -3712,16 +3712,16 @@
         <v>44652</v>
       </c>
       <c r="B165" t="n">
-        <v>6.139564990997314</v>
+        <v>6.139564514160156</v>
       </c>
       <c r="C165" t="n">
-        <v>6.299264504331019</v>
+        <v>6.299264015090594</v>
       </c>
       <c r="D165" t="n">
-        <v>5.926631883492739</v>
+        <v>5.926631423193302</v>
       </c>
       <c r="E165" t="n">
-        <v>6.254903739934808</v>
+        <v>6.254903254139719</v>
       </c>
       <c r="F165" t="n">
         <v>18919700</v>
@@ -3732,16 +3732,16 @@
         <v>44655</v>
       </c>
       <c r="B166" t="n">
-        <v>6.210542678833008</v>
+        <v>6.21054220199585</v>
       </c>
       <c r="C166" t="n">
-        <v>6.237159476459965</v>
+        <v>6.237158997579204</v>
       </c>
       <c r="D166" t="n">
-        <v>6.050843162250203</v>
+        <v>6.050842697674559</v>
       </c>
       <c r="E166" t="n">
-        <v>6.15730950663874</v>
+        <v>6.157309033888753</v>
       </c>
       <c r="F166" t="n">
         <v>13343800</v>
@@ -3832,16 +3832,16 @@
         <v>44662</v>
       </c>
       <c r="B171" t="n">
-        <v>6.14585018157959</v>
+        <v>6.145850658416748</v>
       </c>
       <c r="C171" t="n">
-        <v>6.21710634662882</v>
+        <v>6.21710682899452</v>
       </c>
       <c r="D171" t="n">
-        <v>6.021151892743435</v>
+        <v>6.021152359905646</v>
       </c>
       <c r="E171" t="n">
-        <v>6.119128907326005</v>
+        <v>6.119129382089944</v>
       </c>
       <c r="F171" t="n">
         <v>4955900</v>
@@ -3852,16 +3852,16 @@
         <v>44663</v>
       </c>
       <c r="B172" t="n">
-        <v>6.217106342315674</v>
+        <v>6.217106819152832</v>
       </c>
       <c r="C172" t="n">
-        <v>6.359618672315267</v>
+        <v>6.359619160082779</v>
       </c>
       <c r="D172" t="n">
-        <v>6.145850177315878</v>
+        <v>6.145850648687858</v>
       </c>
       <c r="E172" t="n">
-        <v>6.190385068080627</v>
+        <v>6.190385542868328</v>
       </c>
       <c r="F172" t="n">
         <v>15598900</v>
@@ -3952,16 +3952,16 @@
         <v>44671</v>
       </c>
       <c r="B177" t="n">
-        <v>6.208199024200439</v>
+        <v>6.208198547363281</v>
       </c>
       <c r="C177" t="n">
-        <v>6.279455612943373</v>
+        <v>6.279455130633163</v>
       </c>
       <c r="D177" t="n">
-        <v>6.110222011029355</v>
+        <v>6.11022154171758</v>
       </c>
       <c r="E177" t="n">
-        <v>6.190384983194765</v>
+        <v>6.190384507725862</v>
       </c>
       <c r="F177" t="n">
         <v>7897000</v>
@@ -3972,16 +3972,16 @@
         <v>44673</v>
       </c>
       <c r="B178" t="n">
-        <v>6.128035545349121</v>
+        <v>6.128036499023438</v>
       </c>
       <c r="C178" t="n">
-        <v>6.190384471353647</v>
+        <v>6.190385434731002</v>
       </c>
       <c r="D178" t="n">
-        <v>5.98552280436691</v>
+        <v>5.98552373586271</v>
       </c>
       <c r="E178" t="n">
-        <v>6.136942352755394</v>
+        <v>6.136943307815831</v>
       </c>
       <c r="F178" t="n">
         <v>9926800</v>
@@ -4032,16 +4032,16 @@
         <v>44678</v>
       </c>
       <c r="B181" t="n">
-        <v>6.332897663116455</v>
+        <v>6.332897186279297</v>
       </c>
       <c r="C181" t="n">
-        <v>6.35961851195749</v>
+        <v>6.359618033108378</v>
       </c>
       <c r="D181" t="n">
-        <v>6.208198952790844</v>
+        <v>6.208198485342908</v>
       </c>
       <c r="E181" t="n">
-        <v>6.288362348754418</v>
+        <v>6.288361875270557</v>
       </c>
       <c r="F181" t="n">
         <v>11357200</v>
@@ -4072,16 +4072,16 @@
         <v>44680</v>
       </c>
       <c r="B183" t="n">
-        <v>6.14585018157959</v>
+        <v>6.145850658416748</v>
       </c>
       <c r="C183" t="n">
-        <v>6.44868888303882</v>
+        <v>6.44868938337228</v>
       </c>
       <c r="D183" t="n">
-        <v>6.065686783539082</v>
+        <v>6.065687254156614</v>
       </c>
       <c r="E183" t="n">
-        <v>6.413060800514205</v>
+        <v>6.413061298083393</v>
       </c>
       <c r="F183" t="n">
         <v>21979100</v>
@@ -4112,16 +4112,16 @@
         <v>44684</v>
       </c>
       <c r="B185" t="n">
-        <v>5.52235746383667</v>
+        <v>5.522357940673828</v>
       </c>
       <c r="C185" t="n">
-        <v>5.905359958641743</v>
+        <v>5.905360468549889</v>
       </c>
       <c r="D185" t="n">
-        <v>5.228425593222683</v>
+        <v>5.228426044679804</v>
       </c>
       <c r="E185" t="n">
-        <v>5.905359958641743</v>
+        <v>5.905360468549889</v>
       </c>
       <c r="F185" t="n">
         <v>36500900</v>
@@ -4132,16 +4132,16 @@
         <v>44685</v>
       </c>
       <c r="B186" t="n">
-        <v>5.388752460479736</v>
+        <v>5.388753414154053</v>
       </c>
       <c r="C186" t="n">
-        <v>5.51345074167094</v>
+        <v>5.513451717413731</v>
       </c>
       <c r="D186" t="n">
-        <v>5.210611634057798</v>
+        <v>5.210612556205647</v>
       </c>
       <c r="E186" t="n">
-        <v>5.51345074167094</v>
+        <v>5.513451717413731</v>
       </c>
       <c r="F186" t="n">
         <v>18834300</v>
@@ -4152,16 +4152,16 @@
         <v>44686</v>
       </c>
       <c r="B187" t="n">
-        <v>4.943401336669922</v>
+        <v>4.943400859832764</v>
       </c>
       <c r="C187" t="n">
-        <v>5.379845560141698</v>
+        <v>5.379845041205424</v>
       </c>
       <c r="D187" t="n">
-        <v>4.925587295400058</v>
+        <v>4.925586820281231</v>
       </c>
       <c r="E187" t="n">
-        <v>5.379845560141698</v>
+        <v>5.379845041205424</v>
       </c>
       <c r="F187" t="n">
         <v>16863600</v>
@@ -4192,16 +4192,16 @@
         <v>44690</v>
       </c>
       <c r="B189" t="n">
-        <v>4.622748374938965</v>
+        <v>4.622747898101807</v>
       </c>
       <c r="C189" t="n">
-        <v>4.934494323403464</v>
+        <v>4.934493814409667</v>
       </c>
       <c r="D189" t="n">
-        <v>4.435700720916212</v>
+        <v>4.435700263373046</v>
       </c>
       <c r="E189" t="n">
-        <v>4.934494323403464</v>
+        <v>4.934493814409667</v>
       </c>
       <c r="F189" t="n">
         <v>21341300</v>
@@ -4212,16 +4212,16 @@
         <v>44691</v>
       </c>
       <c r="B190" t="n">
-        <v>4.631655693054199</v>
+        <v>4.631655216217041</v>
       </c>
       <c r="C190" t="n">
-        <v>4.711819103515624</v>
+        <v>4.7118186184255</v>
       </c>
       <c r="D190" t="n">
-        <v>4.56930675133559</v>
+        <v>4.569306280917366</v>
       </c>
       <c r="E190" t="n">
-        <v>4.658376971448112</v>
+        <v>4.65837649185995</v>
       </c>
       <c r="F190" t="n">
         <v>9825600</v>
@@ -4232,16 +4232,16 @@
         <v>44692</v>
       </c>
       <c r="B191" t="n">
-        <v>4.640562057495117</v>
+        <v>4.640562534332275</v>
       </c>
       <c r="C191" t="n">
-        <v>4.694004179544246</v>
+        <v>4.694004661872806</v>
       </c>
       <c r="D191" t="n">
-        <v>4.489142499329136</v>
+        <v>4.489142960607302</v>
       </c>
       <c r="E191" t="n">
-        <v>4.640562057495117</v>
+        <v>4.640562534332275</v>
       </c>
       <c r="F191" t="n">
         <v>17331100</v>
@@ -4252,16 +4252,16 @@
         <v>44693</v>
       </c>
       <c r="B192" t="n">
-        <v>4.79198169708252</v>
+        <v>4.791981220245361</v>
       </c>
       <c r="C192" t="n">
-        <v>4.809795738068244</v>
+        <v>4.809795259458459</v>
       </c>
       <c r="D192" t="n">
-        <v>4.55149193141512</v>
+        <v>4.551491478508448</v>
       </c>
       <c r="E192" t="n">
-        <v>4.587120013386569</v>
+        <v>4.587119556934643</v>
       </c>
       <c r="F192" t="n">
         <v>13350100</v>
@@ -4312,16 +4312,16 @@
         <v>44698</v>
       </c>
       <c r="B195" t="n">
-        <v>5.005749702453613</v>
+        <v>5.005750179290771</v>
       </c>
       <c r="C195" t="n">
-        <v>5.183890519719414</v>
+        <v>5.183891013525891</v>
       </c>
       <c r="D195" t="n">
-        <v>4.881051427671691</v>
+        <v>4.881051892630355</v>
       </c>
       <c r="E195" t="n">
-        <v>4.952307584689932</v>
+        <v>4.952308056436308</v>
       </c>
       <c r="F195" t="n">
         <v>40878000</v>
@@ -4352,16 +4352,16 @@
         <v>44700</v>
       </c>
       <c r="B197" t="n">
-        <v>5.050285339355469</v>
+        <v>5.050285816192627</v>
       </c>
       <c r="C197" t="n">
-        <v>5.183890854759837</v>
+        <v>5.183891344211743</v>
       </c>
       <c r="D197" t="n">
-        <v>4.898865783545199</v>
+        <v>4.898866246085646</v>
       </c>
       <c r="E197" t="n">
-        <v>4.987935985574703</v>
+        <v>4.987936456524968</v>
       </c>
       <c r="F197" t="n">
         <v>12233400</v>
@@ -4452,16 +4452,16 @@
         <v>44707</v>
       </c>
       <c r="B202" t="n">
-        <v>5.504543304443359</v>
+        <v>5.504543781280518</v>
       </c>
       <c r="C202" t="n">
-        <v>5.647056045223134</v>
+        <v>5.647056534405616</v>
       </c>
       <c r="D202" t="n">
-        <v>5.281867598240178</v>
+        <v>5.281868055787807</v>
       </c>
       <c r="E202" t="n">
-        <v>5.281867598240178</v>
+        <v>5.281868055787807</v>
       </c>
       <c r="F202" t="n">
         <v>14781100</v>
@@ -4672,16 +4672,16 @@
         <v>44722</v>
       </c>
       <c r="B213" t="n">
-        <v>4.738539695739746</v>
+        <v>4.738539218902588</v>
       </c>
       <c r="C213" t="n">
-        <v>4.783074586986924</v>
+        <v>4.78307410566824</v>
       </c>
       <c r="D213" t="n">
-        <v>4.676190338329397</v>
+        <v>4.676189867766428</v>
       </c>
       <c r="E213" t="n">
-        <v>4.774167778625588</v>
+        <v>4.774167298203192</v>
       </c>
       <c r="F213" t="n">
         <v>4786300</v>
@@ -4732,16 +4732,16 @@
         <v>44727</v>
       </c>
       <c r="B216" t="n">
-        <v>4.560399055480957</v>
+        <v>4.560399532318115</v>
       </c>
       <c r="C216" t="n">
-        <v>4.649469266580143</v>
+        <v>4.649469752730517</v>
       </c>
       <c r="D216" t="n">
-        <v>4.480236077851825</v>
+        <v>4.480236546307109</v>
       </c>
       <c r="E216" t="n">
-        <v>4.54258501326112</v>
+        <v>4.542585488235635</v>
       </c>
       <c r="F216" t="n">
         <v>10830000</v>
@@ -4752,16 +4752,16 @@
         <v>44729</v>
       </c>
       <c r="B217" t="n">
-        <v>4.524771690368652</v>
+        <v>4.524771213531494</v>
       </c>
       <c r="C217" t="n">
-        <v>4.524771690368652</v>
+        <v>4.524771213531494</v>
       </c>
       <c r="D217" t="n">
-        <v>4.31100314974667</v>
+        <v>4.311002695437231</v>
       </c>
       <c r="E217" t="n">
-        <v>4.50695764531682</v>
+        <v>4.506957170356972</v>
       </c>
       <c r="F217" t="n">
         <v>10891400</v>
@@ -4772,16 +4772,16 @@
         <v>44732</v>
       </c>
       <c r="B218" t="n">
-        <v>4.524771690368652</v>
+        <v>4.524771213531494</v>
       </c>
       <c r="C218" t="n">
-        <v>4.649470005731476</v>
+        <v>4.649469515753148</v>
       </c>
       <c r="D218" t="n">
-        <v>4.453515510161325</v>
+        <v>4.453515040833406</v>
       </c>
       <c r="E218" t="n">
-        <v>4.524771690368652</v>
+        <v>4.524771213531494</v>
       </c>
       <c r="F218" t="n">
         <v>7841400</v>
@@ -4792,16 +4792,16 @@
         <v>44733</v>
       </c>
       <c r="B219" t="n">
-        <v>4.489142417907715</v>
+        <v>4.489142894744873</v>
       </c>
       <c r="C219" t="n">
-        <v>4.596026660067369</v>
+        <v>4.596027148257782</v>
       </c>
       <c r="D219" t="n">
-        <v>4.444607104647747</v>
+        <v>4.44460757675436</v>
       </c>
       <c r="E219" t="n">
-        <v>4.560398579347484</v>
+        <v>4.560399063753479</v>
       </c>
       <c r="F219" t="n">
         <v>7411800</v>
@@ -4852,16 +4852,16 @@
         <v>44736</v>
       </c>
       <c r="B222" t="n">
-        <v>4.257559776306152</v>
+        <v>4.257560253143311</v>
       </c>
       <c r="C222" t="n">
-        <v>4.337722743364323</v>
+        <v>4.337723229179554</v>
       </c>
       <c r="D222" t="n">
-        <v>4.230838504139954</v>
+        <v>4.23083897798439</v>
       </c>
       <c r="E222" t="n">
-        <v>4.319908703493595</v>
+        <v>4.319909187313693</v>
       </c>
       <c r="F222" t="n">
         <v>7941200</v>
@@ -4872,16 +4872,16 @@
         <v>44739</v>
       </c>
       <c r="B223" t="n">
-        <v>4.275374889373779</v>
+        <v>4.275374412536621</v>
       </c>
       <c r="C223" t="n">
-        <v>4.337723832211941</v>
+        <v>4.337723348420938</v>
       </c>
       <c r="D223" t="n">
-        <v>4.239746800689025</v>
+        <v>4.239746327825506</v>
       </c>
       <c r="E223" t="n">
-        <v>4.275374889373779</v>
+        <v>4.275374412536621</v>
       </c>
       <c r="F223" t="n">
         <v>10516900</v>
@@ -4892,16 +4892,16 @@
         <v>44740</v>
       </c>
       <c r="B224" t="n">
-        <v>4.29318904876709</v>
+        <v>4.293188095092773</v>
       </c>
       <c r="C224" t="n">
-        <v>4.471329496964757</v>
+        <v>4.471328503718931</v>
       </c>
       <c r="D224" t="n">
-        <v>4.29318904876709</v>
+        <v>4.293188095092773</v>
       </c>
       <c r="E224" t="n">
-        <v>4.319909903636574</v>
+        <v>4.319908944026579</v>
       </c>
       <c r="F224" t="n">
         <v>8975600</v>
@@ -4912,16 +4912,16 @@
         <v>44741</v>
       </c>
       <c r="B225" t="n">
-        <v>4.275374889373779</v>
+        <v>4.275374412536621</v>
       </c>
       <c r="C225" t="n">
-        <v>4.355537876554319</v>
+        <v>4.355537390776496</v>
       </c>
       <c r="D225" t="n">
-        <v>4.248653610500054</v>
+        <v>4.248653136643148</v>
       </c>
       <c r="E225" t="n">
-        <v>4.311002978058535</v>
+        <v>4.311002497247737</v>
       </c>
       <c r="F225" t="n">
         <v>7179800</v>
@@ -4932,16 +4932,16 @@
         <v>44742</v>
       </c>
       <c r="B226" t="n">
-        <v>4.088326454162598</v>
+        <v>4.088325977325439</v>
       </c>
       <c r="C226" t="n">
-        <v>4.239746015386434</v>
+        <v>4.239745520888632</v>
       </c>
       <c r="D226" t="n">
-        <v>4.052698372077018</v>
+        <v>4.052697899395299</v>
       </c>
       <c r="E226" t="n">
-        <v>4.239746015386434</v>
+        <v>4.239745520888632</v>
       </c>
       <c r="F226" t="n">
         <v>6721700</v>
@@ -4972,16 +4972,16 @@
         <v>44746</v>
       </c>
       <c r="B228" t="n">
-        <v>4.0437912940979</v>
+        <v>4.043790340423584</v>
       </c>
       <c r="C228" t="n">
-        <v>4.195210861122049</v>
+        <v>4.195209871737444</v>
       </c>
       <c r="D228" t="n">
-        <v>4.008163210647543</v>
+        <v>4.008162265375636</v>
       </c>
       <c r="E228" t="n">
-        <v>4.034884485595439</v>
+        <v>4.034883534021676</v>
       </c>
       <c r="F228" t="n">
         <v>5003300</v>
@@ -5052,16 +5052,16 @@
         <v>44750</v>
       </c>
       <c r="B232" t="n">
-        <v>3.919092893600464</v>
+        <v>3.919093132019043</v>
       </c>
       <c r="C232" t="n">
-        <v>4.132861388388733</v>
+        <v>4.132861639811949</v>
       </c>
       <c r="D232" t="n">
-        <v>3.919092893600464</v>
+        <v>3.919093132019043</v>
       </c>
       <c r="E232" t="n">
-        <v>4.034884373970899</v>
+        <v>4.03488461943367</v>
       </c>
       <c r="F232" t="n">
         <v>7050900</v>
@@ -5072,16 +5072,16 @@
         <v>44753</v>
       </c>
       <c r="B233" t="n">
-        <v>3.705323457717896</v>
+        <v>3.705323696136475</v>
       </c>
       <c r="C233" t="n">
-        <v>3.901278308685776</v>
+        <v>3.901278559713046</v>
       </c>
       <c r="D233" t="n">
-        <v>3.678602611953303</v>
+        <v>3.678602848652532</v>
       </c>
       <c r="E233" t="n">
-        <v>3.892371076950788</v>
+        <v>3.892371327404923</v>
       </c>
       <c r="F233" t="n">
         <v>13261200</v>
@@ -5092,16 +5092,16 @@
         <v>44754</v>
       </c>
       <c r="B234" t="n">
-        <v>3.580625772476196</v>
+        <v>3.580625534057617</v>
       </c>
       <c r="C234" t="n">
-        <v>3.705324064132908</v>
+        <v>3.705323817411202</v>
       </c>
       <c r="D234" t="n">
-        <v>3.580625772476196</v>
+        <v>3.580625534057617</v>
       </c>
       <c r="E234" t="n">
-        <v>3.696417255660414</v>
+        <v>3.696417009531774</v>
       </c>
       <c r="F234" t="n">
         <v>14771600</v>
@@ -5132,16 +5132,16 @@
         <v>44756</v>
       </c>
       <c r="B236" t="n">
-        <v>3.821115016937256</v>
+        <v>3.821115732192993</v>
       </c>
       <c r="C236" t="n">
-        <v>3.856743095322483</v>
+        <v>3.856743817247265</v>
       </c>
       <c r="D236" t="n">
-        <v>3.651881432247329</v>
+        <v>3.651882115825064</v>
       </c>
       <c r="E236" t="n">
-        <v>3.687509510632557</v>
+        <v>3.687510200879336</v>
       </c>
       <c r="F236" t="n">
         <v>9774500</v>
@@ -5172,16 +5172,16 @@
         <v>44760</v>
       </c>
       <c r="B238" t="n">
-        <v>3.830023050308228</v>
+        <v>3.830022811889648</v>
       </c>
       <c r="C238" t="n">
-        <v>4.0883268850101</v>
+        <v>4.088326630512132</v>
       </c>
       <c r="D238" t="n">
-        <v>3.830023050308228</v>
+        <v>3.830022811889648</v>
       </c>
       <c r="E238" t="n">
-        <v>3.990349436589301</v>
+        <v>3.99034918819042</v>
       </c>
       <c r="F238" t="n">
         <v>5011900</v>
@@ -5212,16 +5212,16 @@
         <v>44762</v>
       </c>
       <c r="B240" t="n">
-        <v>3.999255895614624</v>
+        <v>3.999256372451782</v>
       </c>
       <c r="C240" t="n">
-        <v>4.025977170015901</v>
+        <v>4.025977650039076</v>
       </c>
       <c r="D240" t="n">
-        <v>3.803301440646171</v>
+        <v>3.803301894119392</v>
       </c>
       <c r="E240" t="n">
-        <v>3.830022715047448</v>
+        <v>3.830023171706685</v>
       </c>
       <c r="F240" t="n">
         <v>11021800</v>
@@ -5232,16 +5232,16 @@
         <v>44763</v>
       </c>
       <c r="B241" t="n">
-        <v>3.96362829208374</v>
+        <v>3.963627815246582</v>
       </c>
       <c r="C241" t="n">
-        <v>4.025977656744403</v>
+        <v>4.025977172406417</v>
       </c>
       <c r="D241" t="n">
-        <v>3.936907439172241</v>
+        <v>3.936906965549687</v>
       </c>
       <c r="E241" t="n">
-        <v>4.025977656744403</v>
+        <v>4.025977172406417</v>
       </c>
       <c r="F241" t="n">
         <v>6658500</v>
@@ -5292,16 +5292,16 @@
         <v>44768</v>
       </c>
       <c r="B244" t="n">
-        <v>3.714231252670288</v>
+        <v>3.714231491088867</v>
       </c>
       <c r="C244" t="n">
-        <v>3.8122086930113</v>
+        <v>3.812208937719106</v>
       </c>
       <c r="D244" t="n">
-        <v>3.669695936682488</v>
+        <v>3.66969617224232</v>
       </c>
       <c r="E244" t="n">
-        <v>3.705324019584628</v>
+        <v>3.705324257431447</v>
       </c>
       <c r="F244" t="n">
         <v>4594100</v>
@@ -5312,16 +5312,16 @@
         <v>44769</v>
       </c>
       <c r="B245" t="n">
-        <v>3.999255895614624</v>
+        <v>3.999256372451782</v>
       </c>
       <c r="C245" t="n">
-        <v>3.999255895614624</v>
+        <v>3.999256372451782</v>
       </c>
       <c r="D245" t="n">
-        <v>3.723138042162589</v>
+        <v>3.72313848607781</v>
       </c>
       <c r="E245" t="n">
-        <v>3.740952083523358</v>
+        <v>3.740952529562573</v>
       </c>
       <c r="F245" t="n">
         <v>8689000</v>
@@ -5332,16 +5332,16 @@
         <v>44770</v>
       </c>
       <c r="B246" t="n">
-        <v>3.999255895614624</v>
+        <v>3.999256372451782</v>
       </c>
       <c r="C246" t="n">
-        <v>4.070512485777946</v>
+        <v>4.070512971111132</v>
       </c>
       <c r="D246" t="n">
-        <v>3.892371647450013</v>
+        <v>3.892372111543206</v>
       </c>
       <c r="E246" t="n">
-        <v>4.025977170015901</v>
+        <v>4.025977650039076</v>
       </c>
       <c r="F246" t="n">
         <v>3634200</v>
@@ -5392,16 +5392,16 @@
         <v>44775</v>
       </c>
       <c r="B249" t="n">
-        <v>4.10614013671875</v>
+        <v>4.106140613555908</v>
       </c>
       <c r="C249" t="n">
-        <v>4.115046944102415</v>
+        <v>4.115047421973903</v>
       </c>
       <c r="D249" t="n">
-        <v>3.901278470251996</v>
+        <v>3.901278923299012</v>
       </c>
       <c r="E249" t="n">
-        <v>3.927999317123196</v>
+        <v>3.927999773273247</v>
       </c>
       <c r="F249" t="n">
         <v>12885400</v>
@@ -5432,16 +5432,16 @@
         <v>44777</v>
       </c>
       <c r="B251" t="n">
-        <v>4.498050212860107</v>
+        <v>4.498049736022949</v>
       </c>
       <c r="C251" t="n">
-        <v>4.791982127910954</v>
+        <v>4.791981619914148</v>
       </c>
       <c r="D251" t="n">
-        <v>4.32881659592047</v>
+        <v>4.328816137023725</v>
       </c>
       <c r="E251" t="n">
-        <v>4.32881659592047</v>
+        <v>4.328816137023725</v>
       </c>
       <c r="F251" t="n">
         <v>17206200</v>
@@ -5452,16 +5452,16 @@
         <v>44778</v>
       </c>
       <c r="B252" t="n">
-        <v>4.328815460205078</v>
+        <v>4.328815937042236</v>
       </c>
       <c r="C252" t="n">
-        <v>4.54258391516821</v>
+        <v>4.542584415552859</v>
       </c>
       <c r="D252" t="n">
-        <v>4.248652077233821</v>
+        <v>4.248652545240646</v>
       </c>
       <c r="E252" t="n">
-        <v>4.54258391516821</v>
+        <v>4.542584415552859</v>
       </c>
       <c r="F252" t="n">
         <v>11124100</v>
@@ -5472,16 +5472,16 @@
         <v>44781</v>
       </c>
       <c r="B253" t="n">
-        <v>4.408979415893555</v>
+        <v>4.408978462219238</v>
       </c>
       <c r="C253" t="n">
-        <v>4.50695685894371</v>
+        <v>4.506955884076604</v>
       </c>
       <c r="D253" t="n">
-        <v>4.355537290062633</v>
+        <v>4.355536347947995</v>
       </c>
       <c r="E253" t="n">
-        <v>4.391165373949914</v>
+        <v>4.391164424128823</v>
       </c>
       <c r="F253" t="n">
         <v>6283600</v>
@@ -5532,16 +5532,16 @@
         <v>44784</v>
       </c>
       <c r="B256" t="n">
-        <v>4.346629619598389</v>
+        <v>4.346630573272705</v>
       </c>
       <c r="C256" t="n">
-        <v>4.685096774136335</v>
+        <v>4.685097802072197</v>
       </c>
       <c r="D256" t="n">
-        <v>4.311001542775466</v>
+        <v>4.311002488632787</v>
       </c>
       <c r="E256" t="n">
-        <v>4.613840195770312</v>
+        <v>4.61384120807209</v>
       </c>
       <c r="F256" t="n">
         <v>11482900</v>
@@ -5552,16 +5552,16 @@
         <v>44785</v>
       </c>
       <c r="B257" t="n">
-        <v>4.694003582000732</v>
+        <v>4.694004058837891</v>
       </c>
       <c r="C257" t="n">
-        <v>4.694003582000732</v>
+        <v>4.694004058837891</v>
       </c>
       <c r="D257" t="n">
-        <v>4.498049159432127</v>
+        <v>4.498049616363389</v>
       </c>
       <c r="E257" t="n">
-        <v>4.578212119941013</v>
+        <v>4.578212585015574</v>
       </c>
       <c r="F257" t="n">
         <v>15222800</v>
@@ -5572,16 +5572,16 @@
         <v>44788</v>
       </c>
       <c r="B258" t="n">
-        <v>4.640562057495117</v>
+        <v>4.640562534332275</v>
       </c>
       <c r="C258" t="n">
-        <v>4.729632260910332</v>
+        <v>4.729632746899826</v>
       </c>
       <c r="D258" t="n">
-        <v>4.560398662061308</v>
+        <v>4.560399130661343</v>
       </c>
       <c r="E258" t="n">
-        <v>4.640562057495117</v>
+        <v>4.640562534332275</v>
       </c>
       <c r="F258" t="n">
         <v>10250500</v>
@@ -5592,16 +5592,16 @@
         <v>44789</v>
       </c>
       <c r="B259" t="n">
-        <v>4.622748374938965</v>
+        <v>4.622747898101807</v>
       </c>
       <c r="C259" t="n">
-        <v>4.702911776583077</v>
+        <v>4.702911291477053</v>
       </c>
       <c r="D259" t="n">
-        <v>4.560399015357959</v>
+        <v>4.560398544952146</v>
       </c>
       <c r="E259" t="n">
-        <v>4.676190501128285</v>
+        <v>4.676190018778564</v>
       </c>
       <c r="F259" t="n">
         <v>5754000</v>
@@ -5652,16 +5652,16 @@
         <v>44792</v>
       </c>
       <c r="B262" t="n">
-        <v>4.31990909576416</v>
+        <v>4.319909572601318</v>
       </c>
       <c r="C262" t="n">
-        <v>4.533678018344458</v>
+        <v>4.533678518777706</v>
       </c>
       <c r="D262" t="n">
-        <v>4.22193165521818</v>
+        <v>4.221932121240462</v>
       </c>
       <c r="E262" t="n">
-        <v>4.524770785240164</v>
+        <v>4.52477128469022</v>
       </c>
       <c r="F262" t="n">
         <v>17743000</v>
@@ -5672,16 +5672,16 @@
         <v>44795</v>
       </c>
       <c r="B263" t="n">
-        <v>4.31990909576416</v>
+        <v>4.319909572601318</v>
       </c>
       <c r="C263" t="n">
-        <v>4.364444411845128</v>
+        <v>4.364444893598153</v>
       </c>
       <c r="D263" t="n">
-        <v>4.177396763857463</v>
+        <v>4.177397224963925</v>
       </c>
       <c r="E263" t="n">
-        <v>4.302095054275823</v>
+        <v>4.302095529146644</v>
       </c>
       <c r="F263" t="n">
         <v>9829500</v>
@@ -5692,16 +5692,16 @@
         <v>44796</v>
       </c>
       <c r="B264" t="n">
-        <v>4.471328735351562</v>
+        <v>4.471328258514404</v>
       </c>
       <c r="C264" t="n">
-        <v>4.471328735351562</v>
+        <v>4.471328258514404</v>
       </c>
       <c r="D264" t="n">
-        <v>4.311002359282476</v>
+        <v>4.311001899543048</v>
       </c>
       <c r="E264" t="n">
-        <v>4.311002359282476</v>
+        <v>4.311001899543048</v>
       </c>
       <c r="F264" t="n">
         <v>6333000</v>
@@ -5732,16 +5732,16 @@
         <v>44798</v>
       </c>
       <c r="B266" t="n">
-        <v>4.480235576629639</v>
+        <v>4.480236053466797</v>
       </c>
       <c r="C266" t="n">
-        <v>4.604933858217994</v>
+        <v>4.604934348326948</v>
       </c>
       <c r="D266" t="n">
-        <v>4.453514303929166</v>
+        <v>4.453514777922345</v>
       </c>
       <c r="E266" t="n">
-        <v>4.587119817991086</v>
+        <v>4.587120306204069</v>
       </c>
       <c r="F266" t="n">
         <v>4135100</v>
@@ -5752,16 +5752,16 @@
         <v>44799</v>
       </c>
       <c r="B267" t="n">
-        <v>4.31990909576416</v>
+        <v>4.319909572601318</v>
       </c>
       <c r="C267" t="n">
-        <v>4.524770785240164</v>
+        <v>4.52477128469022</v>
       </c>
       <c r="D267" t="n">
-        <v>4.29318824589178</v>
+        <v>4.293188719779456</v>
       </c>
       <c r="E267" t="n">
-        <v>4.489142702263489</v>
+        <v>4.489143197780872</v>
       </c>
       <c r="F267" t="n">
         <v>6692300</v>
@@ -5812,16 +5812,16 @@
         <v>44804</v>
       </c>
       <c r="B270" t="n">
-        <v>4.311002254486084</v>
+        <v>4.311002731323242</v>
       </c>
       <c r="C270" t="n">
-        <v>4.435700543952965</v>
+        <v>4.43570103458292</v>
       </c>
       <c r="D270" t="n">
-        <v>4.284280980097343</v>
+        <v>4.284281453978878</v>
       </c>
       <c r="E270" t="n">
-        <v>4.382258419895731</v>
+        <v>4.382258904614487</v>
       </c>
       <c r="F270" t="n">
         <v>8375100</v>
@@ -5832,16 +5832,16 @@
         <v>44805</v>
       </c>
       <c r="B271" t="n">
-        <v>4.248652935028076</v>
+        <v>4.248653411865234</v>
       </c>
       <c r="C271" t="n">
-        <v>4.426793350130201</v>
+        <v>4.426793846960512</v>
       </c>
       <c r="D271" t="n">
-        <v>4.177396768987227</v>
+        <v>4.177397237827122</v>
       </c>
       <c r="E271" t="n">
-        <v>4.346630375694371</v>
+        <v>4.346630863527787</v>
       </c>
       <c r="F271" t="n">
         <v>13026600</v>
@@ -5872,16 +5872,16 @@
         <v>44809</v>
       </c>
       <c r="B273" t="n">
-        <v>4.115046501159668</v>
+        <v>4.115046977996826</v>
       </c>
       <c r="C273" t="n">
-        <v>4.221930726579882</v>
+        <v>4.221931215802409</v>
       </c>
       <c r="D273" t="n">
-        <v>4.115046501159668</v>
+        <v>4.115046977996826</v>
       </c>
       <c r="E273" t="n">
-        <v>4.123953732304765</v>
+        <v>4.123954210174062</v>
       </c>
       <c r="F273" t="n">
         <v>7604300</v>
@@ -6012,16 +6012,16 @@
         <v>44819</v>
       </c>
       <c r="B280" t="n">
-        <v>3.74985933303833</v>
+        <v>3.749859571456909</v>
       </c>
       <c r="C280" t="n">
-        <v>3.758766141397721</v>
+        <v>3.758766380382601</v>
       </c>
       <c r="D280" t="n">
-        <v>3.634067851324498</v>
+        <v>3.634068082380977</v>
       </c>
       <c r="E280" t="n">
-        <v>3.740952099958689</v>
+        <v>3.740952337810941</v>
       </c>
       <c r="F280" t="n">
         <v>12717200</v>
@@ -6032,16 +6032,16 @@
         <v>44820</v>
       </c>
       <c r="B281" t="n">
-        <v>3.821115016937256</v>
+        <v>3.821115732192993</v>
       </c>
       <c r="C281" t="n">
-        <v>3.892371173707709</v>
+        <v>3.892371902301537</v>
       </c>
       <c r="D281" t="n">
-        <v>3.660788664203734</v>
+        <v>3.66078934944877</v>
       </c>
       <c r="E281" t="n">
-        <v>3.696416742588962</v>
+        <v>3.696417434503042</v>
       </c>
       <c r="F281" t="n">
         <v>19813000</v>
@@ -6072,16 +6072,16 @@
         <v>44824</v>
       </c>
       <c r="B283" t="n">
-        <v>3.96362829208374</v>
+        <v>3.963627815246582</v>
       </c>
       <c r="C283" t="n">
-        <v>4.132861917830997</v>
+        <v>4.132861420634493</v>
       </c>
       <c r="D283" t="n">
-        <v>3.919093395657809</v>
+        <v>3.919092924178341</v>
       </c>
       <c r="E283" t="n">
-        <v>3.990349569715538</v>
+        <v>3.990349089663725</v>
       </c>
       <c r="F283" t="n">
         <v>10696200</v>
@@ -6092,16 +6092,16 @@
         <v>44825</v>
       </c>
       <c r="B284" t="n">
-        <v>3.883465051651001</v>
+        <v>3.883464813232422</v>
       </c>
       <c r="C284" t="n">
-        <v>4.034884623864039</v>
+        <v>4.034884376149319</v>
       </c>
       <c r="D284" t="n">
-        <v>3.830022924644094</v>
+        <v>3.830022689506502</v>
       </c>
       <c r="E284" t="n">
-        <v>3.972535263329179</v>
+        <v>3.972535019442289</v>
       </c>
       <c r="F284" t="n">
         <v>18275700</v>
@@ -6152,16 +6152,16 @@
         <v>44830</v>
       </c>
       <c r="B287" t="n">
-        <v>3.821115016937256</v>
+        <v>3.821115732192993</v>
       </c>
       <c r="C287" t="n">
-        <v>3.936906484049341</v>
+        <v>3.936907220979514</v>
       </c>
       <c r="D287" t="n">
-        <v>3.794394170508434</v>
+        <v>3.794394880762427</v>
       </c>
       <c r="E287" t="n">
-        <v>3.901278405664114</v>
+        <v>3.901279135925243</v>
       </c>
       <c r="F287" t="n">
         <v>9718800</v>
@@ -6172,16 +6172,16 @@
         <v>44831</v>
       </c>
       <c r="B288" t="n">
-        <v>3.732045412063599</v>
+        <v>3.73204517364502</v>
       </c>
       <c r="C288" t="n">
-        <v>3.91909306557115</v>
+        <v>3.919092815203188</v>
       </c>
       <c r="D288" t="n">
-        <v>3.732045412063599</v>
+        <v>3.73204517364502</v>
       </c>
       <c r="E288" t="n">
-        <v>3.838929664147838</v>
+        <v>3.838929418901048</v>
       </c>
       <c r="F288" t="n">
         <v>11052300</v>
@@ -6232,16 +6232,16 @@
         <v>44834</v>
       </c>
       <c r="B291" t="n">
-        <v>3.732045412063599</v>
+        <v>3.73204517364502</v>
       </c>
       <c r="C291" t="n">
-        <v>3.79439477147287</v>
+        <v>3.794394529071154</v>
       </c>
       <c r="D291" t="n">
-        <v>3.651882010640287</v>
+        <v>3.651881777342879</v>
       </c>
       <c r="E291" t="n">
-        <v>3.660789244007439</v>
+        <v>3.660789010141</v>
       </c>
       <c r="F291" t="n">
         <v>11827700</v>
@@ -6272,16 +6272,16 @@
         <v>44838</v>
       </c>
       <c r="B293" t="n">
-        <v>3.930919885635376</v>
+        <v>3.930920124053955</v>
       </c>
       <c r="C293" t="n">
-        <v>4.056565603620654</v>
+        <v>4.05656584965991</v>
       </c>
       <c r="D293" t="n">
-        <v>3.895021109068154</v>
+        <v>3.895021345309396</v>
       </c>
       <c r="E293" t="n">
-        <v>3.975793142370817</v>
+        <v>3.975793383511054</v>
       </c>
       <c r="F293" t="n">
         <v>11413300</v>
@@ -6292,16 +6292,16 @@
         <v>44839</v>
       </c>
       <c r="B294" t="n">
-        <v>3.975793600082397</v>
+        <v>3.975793123245239</v>
       </c>
       <c r="C294" t="n">
-        <v>3.975793600082397</v>
+        <v>3.975793123245239</v>
       </c>
       <c r="D294" t="n">
-        <v>3.868097257982235</v>
+        <v>3.868096794061647</v>
       </c>
       <c r="E294" t="n">
-        <v>3.921945429032316</v>
+        <v>3.921944958653443</v>
       </c>
       <c r="F294" t="n">
         <v>8368900</v>
@@ -6312,16 +6312,16 @@
         <v>44840</v>
       </c>
       <c r="B295" t="n">
-        <v>4.002717971801758</v>
+        <v>4.0027174949646</v>
       </c>
       <c r="C295" t="n">
-        <v>4.029641843838973</v>
+        <v>4.029641363794418</v>
       </c>
       <c r="D295" t="n">
-        <v>3.975793671817313</v>
+        <v>3.975793198187602</v>
       </c>
       <c r="E295" t="n">
-        <v>3.9937430624912</v>
+        <v>3.993742586723207</v>
       </c>
       <c r="F295" t="n">
         <v>5975200</v>
@@ -6332,16 +6332,16 @@
         <v>44841</v>
       </c>
       <c r="B296" t="n">
-        <v>3.760401010513306</v>
+        <v>3.760400533676147</v>
       </c>
       <c r="C296" t="n">
-        <v>4.002718000310238</v>
+        <v>4.002717492746105</v>
       </c>
       <c r="D296" t="n">
-        <v>3.715527319535371</v>
+        <v>3.715526848388416</v>
       </c>
       <c r="E296" t="n">
-        <v>3.984768609508511</v>
+        <v>3.984768104220449</v>
       </c>
       <c r="F296" t="n">
         <v>16354500</v>
@@ -6372,16 +6372,16 @@
         <v>44845</v>
       </c>
       <c r="B298" t="n">
-        <v>3.903996229171753</v>
+        <v>3.903995752334595</v>
       </c>
       <c r="C298" t="n">
-        <v>3.948869921209974</v>
+        <v>3.948869438891908</v>
       </c>
       <c r="D298" t="n">
-        <v>3.634755360784154</v>
+        <v>3.634754916832287</v>
       </c>
       <c r="E298" t="n">
-        <v>3.661679233649292</v>
+        <v>3.661678786408922</v>
       </c>
       <c r="F298" t="n">
         <v>30833900</v>
@@ -6392,16 +6392,16 @@
         <v>44847</v>
       </c>
       <c r="B299" t="n">
-        <v>3.814248561859131</v>
+        <v>3.814249038696289</v>
       </c>
       <c r="C299" t="n">
-        <v>3.903995501254619</v>
+        <v>3.903995989311464</v>
       </c>
       <c r="D299" t="n">
-        <v>3.796299173980033</v>
+        <v>3.796299648573254</v>
       </c>
       <c r="E299" t="n">
-        <v>3.895021021288652</v>
+        <v>3.895021508223556</v>
       </c>
       <c r="F299" t="n">
         <v>15027200</v>
@@ -6452,16 +6452,16 @@
         <v>44852</v>
       </c>
       <c r="B302" t="n">
-        <v>3.715527296066284</v>
+        <v>3.715527057647705</v>
       </c>
       <c r="C302" t="n">
-        <v>3.787324858819684</v>
+        <v>3.787324615793987</v>
       </c>
       <c r="D302" t="n">
-        <v>3.661679124001235</v>
+        <v>3.661678889037994</v>
       </c>
       <c r="E302" t="n">
-        <v>3.724502205384074</v>
+        <v>3.724501966389592</v>
       </c>
       <c r="F302" t="n">
         <v>13196400</v>
@@ -6472,16 +6472,16 @@
         <v>44853</v>
       </c>
       <c r="B303" t="n">
-        <v>3.733476161956787</v>
+        <v>3.733476400375366</v>
       </c>
       <c r="C303" t="n">
-        <v>3.769374938287358</v>
+        <v>3.769375178998422</v>
       </c>
       <c r="D303" t="n">
-        <v>3.670653517351873</v>
+        <v>3.670653751758618</v>
       </c>
       <c r="E303" t="n">
-        <v>3.715526773791502</v>
+        <v>3.715527011063839</v>
       </c>
       <c r="F303" t="n">
         <v>12625300</v>
@@ -6572,16 +6572,16 @@
         <v>44860</v>
       </c>
       <c r="B308" t="n">
-        <v>3.562957286834717</v>
+        <v>3.562957048416138</v>
       </c>
       <c r="C308" t="n">
-        <v>3.670653839244302</v>
+        <v>3.670653593619109</v>
       </c>
       <c r="D308" t="n">
-        <v>3.545007897095387</v>
+        <v>3.545007659877907</v>
       </c>
       <c r="E308" t="n">
-        <v>3.661678930401033</v>
+        <v>3.661678685376404</v>
       </c>
       <c r="F308" t="n">
         <v>15630800</v>
@@ -6612,16 +6612,16 @@
         <v>44862</v>
       </c>
       <c r="B310" t="n">
-        <v>3.724502325057983</v>
+        <v>3.724502086639404</v>
       </c>
       <c r="C310" t="n">
-        <v>3.733476806716907</v>
+        <v>3.73347656772384</v>
       </c>
       <c r="D310" t="n">
-        <v>3.643729850391451</v>
+        <v>3.643729617143404</v>
       </c>
       <c r="E310" t="n">
-        <v>3.688603542527801</v>
+        <v>3.68860330640723</v>
       </c>
       <c r="F310" t="n">
         <v>9985100</v>
@@ -6632,16 +6632,16 @@
         <v>44865</v>
       </c>
       <c r="B311" t="n">
-        <v>3.850147485733032</v>
+        <v>3.85014796257019</v>
       </c>
       <c r="C311" t="n">
-        <v>3.868096874302645</v>
+        <v>3.868097353362819</v>
       </c>
       <c r="D311" t="n">
-        <v>3.54500766607602</v>
+        <v>3.545008105121898</v>
       </c>
       <c r="E311" t="n">
-        <v>3.589881137500053</v>
+        <v>3.589881582103468</v>
       </c>
       <c r="F311" t="n">
         <v>19491700</v>
@@ -6652,16 +6652,16 @@
         <v>44866</v>
       </c>
       <c r="B312" t="n">
-        <v>4.047590732574463</v>
+        <v>4.047591209411621</v>
       </c>
       <c r="C312" t="n">
-        <v>4.09246398497647</v>
+        <v>4.092464467100041</v>
       </c>
       <c r="D312" t="n">
-        <v>3.81424827947435</v>
+        <v>3.814248728821982</v>
       </c>
       <c r="E312" t="n">
-        <v>3.868096439125038</v>
+        <v>3.868096894816395</v>
       </c>
       <c r="F312" t="n">
         <v>23695600</v>
@@ -6692,16 +6692,16 @@
         <v>44869</v>
       </c>
       <c r="B314" t="n">
-        <v>4.236060619354248</v>
+        <v>4.23606014251709</v>
       </c>
       <c r="C314" t="n">
-        <v>4.343757405805654</v>
+        <v>4.34375691684548</v>
       </c>
       <c r="D314" t="n">
-        <v>4.155288564449803</v>
+        <v>4.155288096704846</v>
       </c>
       <c r="E314" t="n">
-        <v>4.218111226270229</v>
+        <v>4.218110751453565</v>
       </c>
       <c r="F314" t="n">
         <v>12500600</v>
@@ -6792,16 +6792,16 @@
         <v>44876</v>
       </c>
       <c r="B319" t="n">
-        <v>3.715527296066284</v>
+        <v>3.715527057647705</v>
       </c>
       <c r="C319" t="n">
-        <v>3.751426077442984</v>
+        <v>3.751425836720846</v>
       </c>
       <c r="D319" t="n">
-        <v>3.437311526423245</v>
+        <v>3.437311305857262</v>
       </c>
       <c r="E319" t="n">
-        <v>3.634755251942325</v>
+        <v>3.634755018706739</v>
       </c>
       <c r="F319" t="n">
         <v>24235200</v>
@@ -6812,16 +6812,16 @@
         <v>44879</v>
       </c>
       <c r="B320" t="n">
-        <v>3.697577714920044</v>
+        <v>3.697577476501465</v>
       </c>
       <c r="C320" t="n">
-        <v>3.796299572594537</v>
+        <v>3.796299327810405</v>
       </c>
       <c r="D320" t="n">
-        <v>3.64372954562865</v>
+        <v>3.643729310682183</v>
       </c>
       <c r="E320" t="n">
-        <v>3.760400793066941</v>
+        <v>3.760400550597551</v>
       </c>
       <c r="F320" t="n">
         <v>10873300</v>
@@ -6952,16 +6952,16 @@
         <v>44889</v>
       </c>
       <c r="B327" t="n">
-        <v>3.724502325057983</v>
+        <v>3.724502086639404</v>
       </c>
       <c r="C327" t="n">
-        <v>3.742451716323075</v>
+        <v>3.742451476755492</v>
       </c>
       <c r="D327" t="n">
-        <v>3.598856586202345</v>
+        <v>3.598856355826795</v>
       </c>
       <c r="E327" t="n">
-        <v>3.634755368732528</v>
+        <v>3.634755136058969</v>
       </c>
       <c r="F327" t="n">
         <v>5511600</v>
@@ -6972,16 +6972,16 @@
         <v>44890</v>
       </c>
       <c r="B328" t="n">
-        <v>3.634754657745361</v>
+        <v>3.63475489616394</v>
       </c>
       <c r="C328" t="n">
-        <v>3.760400372023689</v>
+        <v>3.76040061868389</v>
       </c>
       <c r="D328" t="n">
-        <v>3.58090628050964</v>
+        <v>3.580906515396082</v>
       </c>
       <c r="E328" t="n">
-        <v>3.733476076419039</v>
+        <v>3.733476321313164</v>
       </c>
       <c r="F328" t="n">
         <v>8739900</v>
@@ -6992,16 +6992,16 @@
         <v>44893</v>
       </c>
       <c r="B329" t="n">
-        <v>3.607831001281738</v>
+        <v>3.607830762863159</v>
       </c>
       <c r="C329" t="n">
-        <v>3.670654083523831</v>
+        <v>3.670653840953675</v>
       </c>
       <c r="D329" t="n">
-        <v>3.589881610347888</v>
+        <v>3.58988137311547</v>
       </c>
       <c r="E329" t="n">
-        <v>3.589881610347888</v>
+        <v>3.58988137311547</v>
       </c>
       <c r="F329" t="n">
         <v>7386900</v>
@@ -7032,16 +7032,16 @@
         <v>44895</v>
       </c>
       <c r="B331" t="n">
-        <v>3.634754657745361</v>
+        <v>3.63475489616394</v>
       </c>
       <c r="C331" t="n">
-        <v>3.661678525402851</v>
+        <v>3.661678765587478</v>
       </c>
       <c r="D331" t="n">
-        <v>3.518083423370476</v>
+        <v>3.518083654136107</v>
       </c>
       <c r="E331" t="n">
-        <v>3.571931586632617</v>
+        <v>3.571931820930371</v>
       </c>
       <c r="F331" t="n">
         <v>16877200</v>
@@ -7052,16 +7052,16 @@
         <v>44896</v>
       </c>
       <c r="B332" t="n">
-        <v>3.446286201477051</v>
+        <v>3.446285963058472</v>
       </c>
       <c r="C332" t="n">
-        <v>3.589881540112033</v>
+        <v>3.589881291759341</v>
       </c>
       <c r="D332" t="n">
-        <v>3.428336810894379</v>
+        <v>3.428336573717563</v>
       </c>
       <c r="E332" t="n">
-        <v>3.589881540112033</v>
+        <v>3.589881291759341</v>
       </c>
       <c r="F332" t="n">
         <v>22625600</v>
@@ -7112,16 +7112,16 @@
         <v>44901</v>
       </c>
       <c r="B335" t="n">
-        <v>3.302690744400024</v>
+        <v>3.302690982818604</v>
       </c>
       <c r="C335" t="n">
-        <v>3.401412382668387</v>
+        <v>3.401412628213602</v>
       </c>
       <c r="D335" t="n">
-        <v>3.248842364098234</v>
+        <v>3.248842598629542</v>
       </c>
       <c r="E335" t="n">
-        <v>3.383462993892321</v>
+        <v>3.383463238141784</v>
       </c>
       <c r="F335" t="n">
         <v>13327400</v>
@@ -7152,16 +7152,16 @@
         <v>44903</v>
       </c>
       <c r="B337" t="n">
-        <v>3.073575735092163</v>
+        <v>3.073575973510742</v>
       </c>
       <c r="C337" t="n">
-        <v>3.266824548925589</v>
+        <v>3.266824802334561</v>
       </c>
       <c r="D337" t="n">
-        <v>3.064373421071546</v>
+        <v>3.064373658776298</v>
       </c>
       <c r="E337" t="n">
-        <v>3.220812978822505</v>
+        <v>3.22081322866234</v>
       </c>
       <c r="F337" t="n">
         <v>19978800</v>
@@ -7192,16 +7192,16 @@
         <v>44907</v>
       </c>
       <c r="B339" t="n">
-        <v>3.036766290664673</v>
+        <v>3.036766529083252</v>
       </c>
       <c r="C339" t="n">
-        <v>3.119587331114006</v>
+        <v>3.119587576034921</v>
       </c>
       <c r="D339" t="n">
-        <v>2.972350096515548</v>
+        <v>2.972350329876769</v>
       </c>
       <c r="E339" t="n">
-        <v>3.082777857914047</v>
+        <v>3.082778099945025</v>
       </c>
       <c r="F339" t="n">
         <v>24013800</v>
@@ -7232,16 +7232,16 @@
         <v>44909</v>
       </c>
       <c r="B341" t="n">
-        <v>3.073575735092163</v>
+        <v>3.073575973510742</v>
       </c>
       <c r="C341" t="n">
-        <v>3.101182677154013</v>
+        <v>3.101182917714075</v>
       </c>
       <c r="D341" t="n">
-        <v>2.935541024782911</v>
+        <v>2.935541252494079</v>
       </c>
       <c r="E341" t="n">
-        <v>2.981552594885995</v>
+        <v>2.9815528261663</v>
       </c>
       <c r="F341" t="n">
         <v>15438000</v>
@@ -7252,16 +7252,16 @@
         <v>44910</v>
       </c>
       <c r="B342" t="n">
-        <v>3.036766290664673</v>
+        <v>3.036766529083252</v>
       </c>
       <c r="C342" t="n">
-        <v>3.137991958013755</v>
+        <v>3.13799220437963</v>
       </c>
       <c r="D342" t="n">
-        <v>3.009159350315048</v>
+        <v>3.009159586566188</v>
       </c>
       <c r="E342" t="n">
-        <v>3.055170917564423</v>
+        <v>3.055171157427961</v>
       </c>
       <c r="F342" t="n">
         <v>8858500</v>
@@ -7292,16 +7292,16 @@
         <v>44914</v>
       </c>
       <c r="B344" t="n">
-        <v>3.073575735092163</v>
+        <v>3.073575973510742</v>
       </c>
       <c r="C344" t="n">
-        <v>3.091980363133397</v>
+        <v>3.091980602979631</v>
       </c>
       <c r="D344" t="n">
-        <v>2.990754908906612</v>
+        <v>2.990755140900744</v>
       </c>
       <c r="E344" t="n">
-        <v>3.009159536947845</v>
+        <v>3.009159770369632</v>
       </c>
       <c r="F344" t="n">
         <v>6693400</v>
@@ -7332,16 +7332,16 @@
         <v>44916</v>
       </c>
       <c r="B346" t="n">
-        <v>3.331240653991699</v>
+        <v>3.331240892410278</v>
       </c>
       <c r="C346" t="n">
-        <v>3.37725244220964</v>
+        <v>3.377252683921307</v>
       </c>
       <c r="D346" t="n">
-        <v>3.23921751635675</v>
+        <v>3.239217748189187</v>
       </c>
       <c r="E346" t="n">
-        <v>3.266824457647235</v>
+        <v>3.266824691455514</v>
       </c>
       <c r="F346" t="n">
         <v>14610300</v>
@@ -7412,16 +7412,16 @@
         <v>44922</v>
       </c>
       <c r="B350" t="n">
-        <v>3.386454582214355</v>
+        <v>3.386454820632935</v>
       </c>
       <c r="C350" t="n">
-        <v>3.39565689550568</v>
+        <v>3.395657134572136</v>
       </c>
       <c r="D350" t="n">
-        <v>3.276026603318003</v>
+        <v>3.276026833962055</v>
       </c>
       <c r="E350" t="n">
-        <v>3.349645329049056</v>
+        <v>3.349645564876132</v>
       </c>
       <c r="F350" t="n">
         <v>5669100</v>
@@ -7492,16 +7492,16 @@
         <v>44929</v>
       </c>
       <c r="B354" t="n">
-        <v>3.073575735092163</v>
+        <v>3.073575973510742</v>
       </c>
       <c r="C354" t="n">
-        <v>3.285229176966823</v>
+        <v>3.28522943180345</v>
       </c>
       <c r="D354" t="n">
-        <v>3.064373421071546</v>
+        <v>3.064373658776298</v>
       </c>
       <c r="E354" t="n">
-        <v>3.257622234904972</v>
+        <v>3.257622487600117</v>
       </c>
       <c r="F354" t="n">
         <v>9560100</v>
@@ -7512,16 +7512,16 @@
         <v>44930</v>
       </c>
       <c r="B355" t="n">
-        <v>3.055170774459839</v>
+        <v>3.055171012878418</v>
       </c>
       <c r="C355" t="n">
-        <v>3.147194124048661</v>
+        <v>3.147194369648533</v>
       </c>
       <c r="D355" t="n">
-        <v>3.036766148422164</v>
+        <v>3.036766385404488</v>
       </c>
       <c r="E355" t="n">
-        <v>3.110384871973312</v>
+        <v>3.110385114700673</v>
       </c>
       <c r="F355" t="n">
         <v>10680900</v>
@@ -7612,16 +7612,16 @@
         <v>44937</v>
       </c>
       <c r="B360" t="n">
-        <v>3.294431209564209</v>
+        <v>3.294431447982788</v>
       </c>
       <c r="C360" t="n">
-        <v>3.294431209564209</v>
+        <v>3.294431447982788</v>
       </c>
       <c r="D360" t="n">
-        <v>3.091980099004334</v>
+        <v>3.091980322771489</v>
       </c>
       <c r="E360" t="n">
-        <v>3.091980099004334</v>
+        <v>3.091980322771489</v>
       </c>
       <c r="F360" t="n">
         <v>21444400</v>
@@ -7652,16 +7652,16 @@
         <v>44939</v>
       </c>
       <c r="B362" t="n">
-        <v>3.073575735092163</v>
+        <v>3.073575973510742</v>
       </c>
       <c r="C362" t="n">
-        <v>3.220812978822505</v>
+        <v>3.22081322866234</v>
       </c>
       <c r="D362" t="n">
-        <v>3.05517110705093</v>
+        <v>3.055171344041854</v>
       </c>
       <c r="E362" t="n">
-        <v>3.184003722740037</v>
+        <v>3.184003969724563</v>
       </c>
       <c r="F362" t="n">
         <v>14486700</v>
@@ -7672,16 +7672,16 @@
         <v>44942</v>
       </c>
       <c r="B363" t="n">
-        <v>3.036766290664673</v>
+        <v>3.036766529083252</v>
       </c>
       <c r="C363" t="n">
-        <v>3.082777857914047</v>
+        <v>3.082778099945025</v>
       </c>
       <c r="D363" t="n">
-        <v>3.009159350315048</v>
+        <v>3.009159586566188</v>
       </c>
       <c r="E363" t="n">
-        <v>3.055170917564423</v>
+        <v>3.055171157427961</v>
       </c>
       <c r="F363" t="n">
         <v>8730700</v>
@@ -7992,16 +7992,16 @@
         <v>44964</v>
       </c>
       <c r="B379" t="n">
-        <v>2.880327224731445</v>
+        <v>2.880326986312866</v>
       </c>
       <c r="C379" t="n">
-        <v>2.953945739045189</v>
+        <v>2.95394549453285</v>
       </c>
       <c r="D379" t="n">
-        <v>2.843517748174095</v>
+        <v>2.843517512802413</v>
       </c>
       <c r="E379" t="n">
-        <v>2.926338796177535</v>
+        <v>2.926338553950356</v>
       </c>
       <c r="F379" t="n">
         <v>31913300</v>
@@ -8012,16 +8012,16 @@
         <v>44965</v>
       </c>
       <c r="B380" t="n">
-        <v>3.036766290664673</v>
+        <v>3.036766529083252</v>
       </c>
       <c r="C380" t="n">
-        <v>3.036766290664673</v>
+        <v>3.036766529083252</v>
       </c>
       <c r="D380" t="n">
-        <v>2.861922115716591</v>
+        <v>2.861922340408036</v>
       </c>
       <c r="E380" t="n">
-        <v>2.907933902366425</v>
+        <v>2.907934130670286</v>
       </c>
       <c r="F380" t="n">
         <v>50518000</v>
@@ -8032,16 +8032,16 @@
         <v>44966</v>
       </c>
       <c r="B381" t="n">
-        <v>3.018362045288086</v>
+        <v>3.018361806869507</v>
       </c>
       <c r="C381" t="n">
-        <v>3.091980562192519</v>
+        <v>3.091980317958858</v>
       </c>
       <c r="D381" t="n">
-        <v>2.935541213770599</v>
+        <v>2.935540981893987</v>
       </c>
       <c r="E381" t="n">
-        <v>3.036766674514194</v>
+        <v>3.036766434641845</v>
       </c>
       <c r="F381" t="n">
         <v>43678900</v>
@@ -8052,16 +8052,16 @@
         <v>44967</v>
       </c>
       <c r="B382" t="n">
-        <v>2.953945636749268</v>
+        <v>2.953945875167847</v>
       </c>
       <c r="C382" t="n">
-        <v>3.045968776454661</v>
+        <v>3.045969022300604</v>
       </c>
       <c r="D382" t="n">
-        <v>2.92633869483765</v>
+        <v>2.92633893102802</v>
       </c>
       <c r="E382" t="n">
-        <v>3.018361834543043</v>
+        <v>3.018362078160776</v>
       </c>
       <c r="F382" t="n">
         <v>23226200</v>
@@ -8132,16 +8132,16 @@
         <v>44973</v>
       </c>
       <c r="B386" t="n">
-        <v>2.834315299987793</v>
+        <v>2.834315538406372</v>
       </c>
       <c r="C386" t="n">
-        <v>2.871124555405743</v>
+        <v>2.871124796920665</v>
       </c>
       <c r="D386" t="n">
-        <v>2.760696789151893</v>
+        <v>2.760697021377787</v>
       </c>
       <c r="E386" t="n">
-        <v>2.825112986133305</v>
+        <v>2.825113223777799</v>
       </c>
       <c r="F386" t="n">
         <v>21149000</v>
@@ -8172,16 +8172,16 @@
         <v>44979</v>
       </c>
       <c r="B388" t="n">
-        <v>2.834315299987793</v>
+        <v>2.834315538406372</v>
       </c>
       <c r="C388" t="n">
-        <v>2.84351761384228</v>
+        <v>2.843517853034945</v>
       </c>
       <c r="D388" t="n">
-        <v>2.714685219879454</v>
+        <v>2.714685448234921</v>
       </c>
       <c r="E388" t="n">
-        <v>2.76989910300638</v>
+        <v>2.76989933600636</v>
       </c>
       <c r="F388" t="n">
         <v>20601900</v>
@@ -8192,16 +8192,16 @@
         <v>44980</v>
       </c>
       <c r="B389" t="n">
-        <v>2.797505855560303</v>
+        <v>2.797506093978882</v>
       </c>
       <c r="C389" t="n">
-        <v>2.898731520520965</v>
+        <v>2.898731767566543</v>
       </c>
       <c r="D389" t="n">
-        <v>2.751494289396572</v>
+        <v>2.751494523893796</v>
       </c>
       <c r="E389" t="n">
-        <v>2.85271973495678</v>
+        <v>2.852719978080985</v>
       </c>
       <c r="F389" t="n">
         <v>24919500</v>
@@ -8232,16 +8232,16 @@
         <v>44984</v>
       </c>
       <c r="B391" t="n">
-        <v>2.797505855560303</v>
+        <v>2.797506093978882</v>
       </c>
       <c r="C391" t="n">
-        <v>2.834315108491288</v>
+        <v>2.83431535004695</v>
       </c>
       <c r="D391" t="n">
-        <v>2.641066311203163</v>
+        <v>2.641066536289118</v>
       </c>
       <c r="E391" t="n">
-        <v>2.677875783534602</v>
+        <v>2.677876011757659</v>
       </c>
       <c r="F391" t="n">
         <v>32246200</v>
@@ -8252,16 +8252,16 @@
         <v>44985</v>
       </c>
       <c r="B392" t="n">
-        <v>2.834315299987793</v>
+        <v>2.834315538406372</v>
       </c>
       <c r="C392" t="n">
-        <v>2.889529402515187</v>
+        <v>2.889529645578298</v>
       </c>
       <c r="D392" t="n">
-        <v>2.797506044569843</v>
+        <v>2.79750627989208</v>
       </c>
       <c r="E392" t="n">
-        <v>2.825112986133305</v>
+        <v>2.825113223777799</v>
       </c>
       <c r="F392" t="n">
         <v>28842300</v>
@@ -8272,16 +8272,16 @@
         <v>44986</v>
       </c>
       <c r="B393" t="n">
-        <v>2.779101371765137</v>
+        <v>2.779101610183716</v>
       </c>
       <c r="C393" t="n">
-        <v>2.917136296743063</v>
+        <v>2.917136547003632</v>
       </c>
       <c r="D393" t="n">
-        <v>2.751494430649644</v>
+        <v>2.751494666699829</v>
       </c>
       <c r="E393" t="n">
-        <v>2.843517567701285</v>
+        <v>2.843517811646118</v>
       </c>
       <c r="F393" t="n">
         <v>32788900</v>
@@ -8412,16 +8412,16 @@
         <v>44995</v>
       </c>
       <c r="B400" t="n">
-        <v>2.503031730651855</v>
+        <v>2.503031969070435</v>
       </c>
       <c r="C400" t="n">
-        <v>2.595054867315339</v>
+        <v>2.595055114499298</v>
       </c>
       <c r="D400" t="n">
-        <v>2.493829416985507</v>
+        <v>2.493829654527548</v>
       </c>
       <c r="E400" t="n">
-        <v>2.576650239982643</v>
+        <v>2.576650485413526</v>
       </c>
       <c r="F400" t="n">
         <v>23735100</v>
@@ -8512,16 +8512,16 @@
         <v>45002</v>
       </c>
       <c r="B405" t="n">
-        <v>2.349630117416382</v>
+        <v>2.349629878997803</v>
       </c>
       <c r="C405" t="n">
-        <v>2.549396274733532</v>
+        <v>2.549396016044544</v>
       </c>
       <c r="D405" t="n">
-        <v>2.349630117416382</v>
+        <v>2.349629878997803</v>
       </c>
       <c r="E405" t="n">
-        <v>2.492320067785928</v>
+        <v>2.492319814888502</v>
       </c>
       <c r="F405" t="n">
         <v>44089800</v>
@@ -8532,16 +8532,16 @@
         <v>45005</v>
       </c>
       <c r="B406" t="n">
-        <v>2.349630117416382</v>
+        <v>2.349629878997803</v>
       </c>
       <c r="C406" t="n">
-        <v>2.406706097564201</v>
+        <v>2.406705853354083</v>
       </c>
       <c r="D406" t="n">
-        <v>2.311579463984502</v>
+        <v>2.311579229426949</v>
       </c>
       <c r="E406" t="n">
-        <v>2.359142780774352</v>
+        <v>2.359142541390516</v>
       </c>
       <c r="F406" t="n">
         <v>20939200</v>
@@ -8572,16 +8572,16 @@
         <v>45007</v>
       </c>
       <c r="B408" t="n">
-        <v>2.216452598571777</v>
+        <v>2.216452836990356</v>
       </c>
       <c r="C408" t="n">
-        <v>2.273528805389769</v>
+        <v>2.273529049947901</v>
       </c>
       <c r="D408" t="n">
-        <v>2.197427271899042</v>
+        <v>2.197427508271111</v>
       </c>
       <c r="E408" t="n">
-        <v>2.254503251917249</v>
+        <v>2.254503494428847</v>
       </c>
       <c r="F408" t="n">
         <v>26704400</v>
@@ -8612,16 +8612,16 @@
         <v>45009</v>
       </c>
       <c r="B410" t="n">
-        <v>2.292554378509521</v>
+        <v>2.292554140090942</v>
       </c>
       <c r="C410" t="n">
-        <v>2.30206704286849</v>
+        <v>2.302066803460623</v>
       </c>
       <c r="D410" t="n">
-        <v>2.149864186325184</v>
+        <v>2.149863962745944</v>
       </c>
       <c r="E410" t="n">
-        <v>2.159376850684152</v>
+        <v>2.159376626115625</v>
       </c>
       <c r="F410" t="n">
         <v>19141800</v>
@@ -8632,16 +8632,16 @@
         <v>45012</v>
       </c>
       <c r="B411" t="n">
-        <v>2.387680768966675</v>
+        <v>2.387681007385254</v>
       </c>
       <c r="C411" t="n">
-        <v>2.416218759018095</v>
+        <v>2.416219000286296</v>
       </c>
       <c r="D411" t="n">
-        <v>2.302066798812414</v>
+        <v>2.302067028682128</v>
       </c>
       <c r="E411" t="n">
-        <v>2.311579462162887</v>
+        <v>2.311579692982475</v>
       </c>
       <c r="F411" t="n">
         <v>19684900</v>
@@ -8652,16 +8652,16 @@
         <v>45013</v>
       </c>
       <c r="B412" t="n">
-        <v>2.520858287811279</v>
+        <v>2.5208580493927</v>
       </c>
       <c r="C412" t="n">
-        <v>2.549396277920867</v>
+        <v>2.549396036803213</v>
       </c>
       <c r="D412" t="n">
-        <v>2.340117456984101</v>
+        <v>2.340117235659689</v>
       </c>
       <c r="E412" t="n">
-        <v>2.368655447093689</v>
+        <v>2.368655223070202</v>
       </c>
       <c r="F412" t="n">
         <v>69618900</v>
@@ -8732,16 +8732,16 @@
         <v>45019</v>
       </c>
       <c r="B416" t="n">
-        <v>2.692086458206177</v>
+        <v>2.692086219787598</v>
       </c>
       <c r="C416" t="n">
-        <v>2.76818799845922</v>
+        <v>2.768187753300879</v>
       </c>
       <c r="D416" t="n">
-        <v>2.673061129842867</v>
+        <v>2.673060893109223</v>
       </c>
       <c r="E416" t="n">
-        <v>2.739650005914255</v>
+        <v>2.739649763283318</v>
       </c>
       <c r="F416" t="n">
         <v>18815900</v>
@@ -8752,16 +8752,16 @@
         <v>45020</v>
       </c>
       <c r="B417" t="n">
-        <v>2.692086458206177</v>
+        <v>2.692086219787598</v>
       </c>
       <c r="C417" t="n">
-        <v>2.739650005914255</v>
+        <v>2.739649763283318</v>
       </c>
       <c r="D417" t="n">
-        <v>2.654035801479557</v>
+        <v>2.654035566430849</v>
       </c>
       <c r="E417" t="n">
-        <v>2.720624450751141</v>
+        <v>2.720624209805159</v>
       </c>
       <c r="F417" t="n">
         <v>21012200</v>
@@ -8832,16 +8832,16 @@
         <v>45027</v>
       </c>
       <c r="B421" t="n">
-        <v>2.91087794303894</v>
+        <v>2.910877704620361</v>
       </c>
       <c r="C421" t="n">
-        <v>2.920390607161298</v>
+        <v>2.920390367963574</v>
       </c>
       <c r="D421" t="n">
-        <v>2.692086441424922</v>
+        <v>2.692086220926695</v>
       </c>
       <c r="E421" t="n">
-        <v>2.711111769669636</v>
+        <v>2.71111154761312</v>
       </c>
       <c r="F421" t="n">
         <v>33609000</v>
@@ -8852,16 +8852,16 @@
         <v>45028</v>
       </c>
       <c r="B422" t="n">
-        <v>2.91087794303894</v>
+        <v>2.910877704620361</v>
       </c>
       <c r="C422" t="n">
-        <v>3.015517475184673</v>
+        <v>3.01551722819548</v>
       </c>
       <c r="D422" t="n">
-        <v>2.891852614794226</v>
+        <v>2.891852377933937</v>
       </c>
       <c r="E422" t="n">
-        <v>2.920390607161298</v>
+        <v>2.920390367963574</v>
       </c>
       <c r="F422" t="n">
         <v>32421000</v>
@@ -8932,16 +8932,16 @@
         <v>45034</v>
       </c>
       <c r="B426" t="n">
-        <v>3.025029897689819</v>
+        <v>3.025030136108398</v>
       </c>
       <c r="C426" t="n">
-        <v>3.034542561052375</v>
+        <v>3.034542800220697</v>
       </c>
       <c r="D426" t="n">
-        <v>2.948928363989592</v>
+        <v>2.948928596410207</v>
       </c>
       <c r="E426" t="n">
-        <v>2.986979244239598</v>
+        <v>2.986979479659204</v>
       </c>
       <c r="F426" t="n">
         <v>13884000</v>
@@ -9012,16 +9012,16 @@
         <v>45041</v>
       </c>
       <c r="B430" t="n">
-        <v>3.025029897689819</v>
+        <v>3.025030136108398</v>
       </c>
       <c r="C430" t="n">
-        <v>3.14869452140304</v>
+        <v>3.148694769568281</v>
       </c>
       <c r="D430" t="n">
-        <v>2.977466580877042</v>
+        <v>2.977466815546905</v>
       </c>
       <c r="E430" t="n">
-        <v>3.072593214502596</v>
+        <v>3.072593456669892</v>
       </c>
       <c r="F430" t="n">
         <v>18942800</v>
@@ -9132,16 +9132,16 @@
         <v>45050</v>
       </c>
       <c r="B436" t="n">
-        <v>3.025029897689819</v>
+        <v>3.025030136108398</v>
       </c>
       <c r="C436" t="n">
-        <v>3.063080551140041</v>
+        <v>3.063080792557593</v>
       </c>
       <c r="D436" t="n">
-        <v>2.958441027352147</v>
+        <v>2.958441260522505</v>
       </c>
       <c r="E436" t="n">
-        <v>3.015517234327264</v>
+        <v>3.0155174719961</v>
       </c>
       <c r="F436" t="n">
         <v>20441800</v>
@@ -9192,16 +9192,16 @@
         <v>45055</v>
       </c>
       <c r="B439" t="n">
-        <v>3.025029897689819</v>
+        <v>3.025030136108398</v>
       </c>
       <c r="C439" t="n">
-        <v>3.158207184765595</v>
+        <v>3.158207433680579</v>
       </c>
       <c r="D439" t="n">
-        <v>3.015517234327264</v>
+        <v>3.0155174719961</v>
       </c>
       <c r="E439" t="n">
-        <v>3.129669194677929</v>
+        <v>3.129669441343684</v>
       </c>
       <c r="F439" t="n">
         <v>32144800</v>
@@ -9272,16 +9272,16 @@
         <v>45061</v>
       </c>
       <c r="B443" t="n">
-        <v>2.986979484558105</v>
+        <v>2.986979246139526</v>
       </c>
       <c r="C443" t="n">
-        <v>3.20577075949981</v>
+        <v>3.205770503617468</v>
       </c>
       <c r="D443" t="n">
-        <v>2.901365280607201</v>
+        <v>2.901365049022286</v>
       </c>
       <c r="E443" t="n">
-        <v>3.18674543124401</v>
+        <v>3.186745176880255</v>
       </c>
       <c r="F443" t="n">
         <v>71533500</v>
@@ -9432,16 +9432,16 @@
         <v>45071</v>
       </c>
       <c r="B451" t="n">
-        <v>3.281871795654297</v>
+        <v>3.281872034072876</v>
       </c>
       <c r="C451" t="n">
-        <v>3.42456173567419</v>
+        <v>3.424561984458784</v>
       </c>
       <c r="D451" t="n">
-        <v>3.272359132986304</v>
+        <v>3.272359370713815</v>
       </c>
       <c r="E451" t="n">
-        <v>3.376998422334226</v>
+        <v>3.376998667663482</v>
       </c>
       <c r="F451" t="n">
         <v>36092900</v>
@@ -9532,16 +9532,16 @@
         <v>45078</v>
       </c>
       <c r="B456" t="n">
-        <v>3.576764822006226</v>
+        <v>3.576765060424805</v>
       </c>
       <c r="C456" t="n">
-        <v>3.662378792166026</v>
+        <v>3.662379036291428</v>
       </c>
       <c r="D456" t="n">
-        <v>3.376998664833572</v>
+        <v>3.376998889936218</v>
       </c>
       <c r="E456" t="n">
-        <v>3.472125525144246</v>
+        <v>3.472125756587821</v>
       </c>
       <c r="F456" t="n">
         <v>28377100</v>
@@ -9552,16 +9552,16 @@
         <v>45079</v>
       </c>
       <c r="B457" t="n">
-        <v>3.52920126914978</v>
+        <v>3.529201507568359</v>
       </c>
       <c r="C457" t="n">
-        <v>3.643353221726165</v>
+        <v>3.643353467856389</v>
       </c>
       <c r="D457" t="n">
-        <v>3.491150618290985</v>
+        <v>3.491150854139016</v>
       </c>
       <c r="E457" t="n">
-        <v>3.614815233582069</v>
+        <v>3.614815477784382</v>
       </c>
       <c r="F457" t="n">
         <v>24144300</v>
@@ -9652,16 +9652,16 @@
         <v>45089</v>
       </c>
       <c r="B462" t="n">
-        <v>3.795556306838989</v>
+        <v>3.795556545257568</v>
       </c>
       <c r="C462" t="n">
-        <v>3.805068970192479</v>
+        <v>3.805069209208598</v>
       </c>
       <c r="D462" t="n">
-        <v>3.74799299007154</v>
+        <v>3.747993225502421</v>
       </c>
       <c r="E462" t="n">
-        <v>3.786043643485499</v>
+        <v>3.786043881306539</v>
       </c>
       <c r="F462" t="n">
         <v>16242400</v>
@@ -9672,16 +9672,16 @@
         <v>45090</v>
       </c>
       <c r="B463" t="n">
-        <v>3.700429677963257</v>
+        <v>3.700429916381836</v>
       </c>
       <c r="C463" t="n">
-        <v>3.814581865148647</v>
+        <v>3.814582110922048</v>
       </c>
       <c r="D463" t="n">
-        <v>3.662378797701604</v>
+        <v>3.662379033668566</v>
       </c>
       <c r="E463" t="n">
-        <v>3.78604364825246</v>
+        <v>3.786043892187145</v>
       </c>
       <c r="F463" t="n">
         <v>19986600</v>
@@ -9692,16 +9692,16 @@
         <v>45091</v>
       </c>
       <c r="B464" t="n">
-        <v>3.747992992401123</v>
+        <v>3.747993230819702</v>
       </c>
       <c r="C464" t="n">
-        <v>3.795556309198135</v>
+        <v>3.795556550642328</v>
       </c>
       <c r="D464" t="n">
-        <v>3.662378795366716</v>
+        <v>3.662379028339177</v>
       </c>
       <c r="E464" t="n">
-        <v>3.709942338963513</v>
+        <v>3.709942574961601</v>
       </c>
       <c r="F464" t="n">
         <v>25840400</v>
@@ -9752,16 +9752,16 @@
         <v>45096</v>
       </c>
       <c r="B467" t="n">
-        <v>3.776530981063843</v>
+        <v>3.776531219482422</v>
       </c>
       <c r="C467" t="n">
-        <v>3.814581861286975</v>
+        <v>3.814582102107769</v>
       </c>
       <c r="D467" t="n">
-        <v>3.738480327640495</v>
+        <v>3.738480563656874</v>
       </c>
       <c r="E467" t="n">
-        <v>3.78604364441968</v>
+        <v>3.786043883438809</v>
       </c>
       <c r="F467" t="n">
         <v>9550900</v>
@@ -9772,16 +9772,16 @@
         <v>45097</v>
       </c>
       <c r="B468" t="n">
-        <v>3.947759628295898</v>
+        <v>3.94775915145874</v>
       </c>
       <c r="C468" t="n">
-        <v>3.966784957320954</v>
+        <v>3.966784478185788</v>
       </c>
       <c r="D468" t="n">
-        <v>3.767018775758055</v>
+        <v>3.767018320752002</v>
       </c>
       <c r="E468" t="n">
-        <v>3.786044104783111</v>
+        <v>3.78604364747905</v>
       </c>
       <c r="F468" t="n">
         <v>35176100</v>
@@ -9832,16 +9832,16 @@
         <v>45100</v>
       </c>
       <c r="B471" t="n">
-        <v>4.138012886047363</v>
+        <v>4.138012409210205</v>
       </c>
       <c r="C471" t="n">
-        <v>4.157038214922999</v>
+        <v>4.157037735893487</v>
       </c>
       <c r="D471" t="n">
-        <v>4.033373350431561</v>
+        <v>4.033372885652369</v>
       </c>
       <c r="E471" t="n">
-        <v>4.071424461782451</v>
+        <v>4.071423992618501</v>
       </c>
       <c r="F471" t="n">
         <v>23532100</v>
@@ -9852,16 +9852,16 @@
         <v>45103</v>
       </c>
       <c r="B472" t="n">
-        <v>4.204601287841797</v>
+        <v>4.204600811004639</v>
       </c>
       <c r="C472" t="n">
-        <v>4.280702594727692</v>
+        <v>4.280702109260005</v>
       </c>
       <c r="D472" t="n">
-        <v>4.128499980955902</v>
+        <v>4.128499512749272</v>
       </c>
       <c r="E472" t="n">
-        <v>4.138012417516855</v>
+        <v>4.138011948231434</v>
       </c>
       <c r="F472" t="n">
         <v>42881900</v>
@@ -9992,16 +9992,16 @@
         <v>45112</v>
       </c>
       <c r="B479" t="n">
-        <v>4.080936431884766</v>
+        <v>4.080936908721924</v>
       </c>
       <c r="C479" t="n">
-        <v>4.185575955512459</v>
+        <v>4.185576444576225</v>
       </c>
       <c r="D479" t="n">
-        <v>4.023860451796815</v>
+        <v>4.023860921964928</v>
       </c>
       <c r="E479" t="n">
-        <v>4.166550628816475</v>
+        <v>4.166551115657227</v>
       </c>
       <c r="F479" t="n">
         <v>33346200</v>
@@ -10052,16 +10052,16 @@
         <v>45117</v>
       </c>
       <c r="B482" t="n">
-        <v>4.033372402191162</v>
+        <v>4.03337287902832</v>
       </c>
       <c r="C482" t="n">
-        <v>4.099961264400743</v>
+        <v>4.099961749110232</v>
       </c>
       <c r="D482" t="n">
-        <v>3.947758669178288</v>
+        <v>3.947759135893939</v>
       </c>
       <c r="E482" t="n">
-        <v>3.995321753385549</v>
+        <v>3.995322225724247</v>
       </c>
       <c r="F482" t="n">
         <v>16685100</v>
@@ -10132,16 +10132,16 @@
         <v>45121</v>
       </c>
       <c r="B486" t="n">
-        <v>3.881170034408569</v>
+        <v>3.881170511245728</v>
       </c>
       <c r="C486" t="n">
-        <v>4.014347313032519</v>
+        <v>4.014347806231721</v>
       </c>
       <c r="D486" t="n">
-        <v>3.814581621896365</v>
+        <v>3.814582090552529</v>
       </c>
       <c r="E486" t="n">
-        <v>3.995321987514812</v>
+        <v>3.995322478376579</v>
       </c>
       <c r="F486" t="n">
         <v>16845900</v>
@@ -10232,16 +10232,16 @@
         <v>45128</v>
       </c>
       <c r="B491" t="n">
-        <v>4.061911106109619</v>
+        <v>4.061911582946777</v>
       </c>
       <c r="C491" t="n">
-        <v>4.099961759510212</v>
+        <v>4.099962240814224</v>
       </c>
       <c r="D491" t="n">
-        <v>3.976296909158501</v>
+        <v>3.97629737594521</v>
       </c>
       <c r="E491" t="n">
-        <v>4.00483512600873</v>
+        <v>4.004835596145607</v>
       </c>
       <c r="F491" t="n">
         <v>9991000</v>
@@ -10432,16 +10432,16 @@
         <v>45142</v>
       </c>
       <c r="B501" t="n">
-        <v>3.903565406799316</v>
+        <v>3.903565883636475</v>
       </c>
       <c r="C501" t="n">
-        <v>3.960970726756138</v>
+        <v>3.960971210605601</v>
       </c>
       <c r="D501" t="n">
-        <v>3.865295193494769</v>
+        <v>3.865295665657057</v>
       </c>
       <c r="E501" t="n">
-        <v>3.903565406799316</v>
+        <v>3.903565883636475</v>
       </c>
       <c r="F501" t="n">
         <v>16409800</v>
@@ -10472,16 +10472,16 @@
         <v>45146</v>
       </c>
       <c r="B503" t="n">
-        <v>3.798322677612305</v>
+        <v>3.798322916030884</v>
       </c>
       <c r="C503" t="n">
-        <v>3.817457786065083</v>
+        <v>3.817458025684763</v>
       </c>
       <c r="D503" t="n">
-        <v>3.702646907239926</v>
+        <v>3.702647139652991</v>
       </c>
       <c r="E503" t="n">
-        <v>3.798322677612305</v>
+        <v>3.798322916030884</v>
       </c>
       <c r="F503" t="n">
         <v>17862300</v>
@@ -10532,16 +10532,16 @@
         <v>45149</v>
       </c>
       <c r="B506" t="n">
-        <v>3.683511972427368</v>
+        <v>3.683511734008789</v>
       </c>
       <c r="C506" t="n">
-        <v>3.750485083277681</v>
+        <v>3.750484840524209</v>
       </c>
       <c r="D506" t="n">
-        <v>3.635674199040356</v>
+        <v>3.63567396371812</v>
       </c>
       <c r="E506" t="n">
-        <v>3.731349973922877</v>
+        <v>3.731349732407941</v>
       </c>
       <c r="F506" t="n">
         <v>13400900</v>
@@ -10772,16 +10772,16 @@
         <v>45167</v>
       </c>
       <c r="B518" t="n">
-        <v>3.654809236526489</v>
+        <v>3.65480899810791</v>
       </c>
       <c r="C518" t="n">
-        <v>3.664376791015754</v>
+        <v>3.664376551973043</v>
       </c>
       <c r="D518" t="n">
-        <v>3.578268800612372</v>
+        <v>3.578268567186847</v>
       </c>
       <c r="E518" t="n">
-        <v>3.61653901856943</v>
+        <v>3.616538782647379</v>
       </c>
       <c r="F518" t="n">
         <v>13520200</v>
@@ -10912,16 +10912,16 @@
         <v>45177</v>
       </c>
       <c r="B525" t="n">
-        <v>3.54956579208374</v>
+        <v>3.549566030502319</v>
       </c>
       <c r="C525" t="n">
-        <v>3.58783600632047</v>
+        <v>3.587836247309597</v>
       </c>
       <c r="D525" t="n">
-        <v>3.51129557784701</v>
+        <v>3.511295813695041</v>
       </c>
       <c r="E525" t="n">
-        <v>3.530430684965375</v>
+        <v>3.53043092209868</v>
       </c>
       <c r="F525" t="n">
         <v>26042800</v>
@@ -10952,16 +10952,16 @@
         <v>45181</v>
       </c>
       <c r="B527" t="n">
-        <v>3.712214708328247</v>
+        <v>3.712214469909668</v>
       </c>
       <c r="C527" t="n">
-        <v>3.769620033976584</v>
+        <v>3.769619791871123</v>
       </c>
       <c r="D527" t="n">
-        <v>3.616538937472532</v>
+        <v>3.61653870519877</v>
       </c>
       <c r="E527" t="n">
-        <v>3.635674046021977</v>
+        <v>3.635673812519255</v>
       </c>
       <c r="F527" t="n">
         <v>15715300</v>
@@ -10972,16 +10972,16 @@
         <v>45182</v>
       </c>
       <c r="B528" t="n">
-        <v>3.769619941711426</v>
+        <v>3.769620180130005</v>
       </c>
       <c r="C528" t="n">
-        <v>3.846160374035806</v>
+        <v>3.846160617295367</v>
       </c>
       <c r="D528" t="n">
-        <v>3.712214617468141</v>
+        <v>3.712214852255983</v>
       </c>
       <c r="E528" t="n">
-        <v>3.712214617468141</v>
+        <v>3.712214852255983</v>
       </c>
       <c r="F528" t="n">
         <v>17575000</v>
@@ -10992,16 +10992,16 @@
         <v>45183</v>
       </c>
       <c r="B529" t="n">
-        <v>3.798322677612305</v>
+        <v>3.798322916030884</v>
       </c>
       <c r="C529" t="n">
-        <v>3.836593122626347</v>
+        <v>3.836593363447141</v>
       </c>
       <c r="D529" t="n">
-        <v>3.760052460706747</v>
+        <v>3.760052696723127</v>
       </c>
       <c r="E529" t="n">
-        <v>3.798322677612305</v>
+        <v>3.798322916030884</v>
       </c>
       <c r="F529" t="n">
         <v>9553000</v>
@@ -11032,16 +11032,16 @@
         <v>45187</v>
       </c>
       <c r="B531" t="n">
-        <v>3.817457675933838</v>
+        <v>3.817457914352417</v>
       </c>
       <c r="C531" t="n">
-        <v>3.884430553586438</v>
+        <v>3.884430796187795</v>
       </c>
       <c r="D531" t="n">
-        <v>3.740917244330867</v>
+        <v>3.740917477969129</v>
       </c>
       <c r="E531" t="n">
-        <v>3.817457675933838</v>
+        <v>3.817457914352417</v>
       </c>
       <c r="F531" t="n">
         <v>23371600</v>
@@ -11072,16 +11072,16 @@
         <v>45189</v>
       </c>
       <c r="B533" t="n">
-        <v>3.645241498947144</v>
+        <v>3.645241737365723</v>
       </c>
       <c r="C533" t="n">
-        <v>3.769619929168903</v>
+        <v>3.769620175722507</v>
       </c>
       <c r="D533" t="n">
-        <v>3.645241498947144</v>
+        <v>3.645241737365723</v>
       </c>
       <c r="E533" t="n">
-        <v>3.740917267142762</v>
+        <v>3.740917511819056</v>
       </c>
       <c r="F533" t="n">
         <v>23728500</v>
@@ -11212,16 +11212,16 @@
         <v>45198</v>
       </c>
       <c r="B540" t="n">
-        <v>3.425187349319458</v>
+        <v>3.425187587738037</v>
       </c>
       <c r="C540" t="n">
-        <v>3.492160451982693</v>
+        <v>3.492160695063099</v>
       </c>
       <c r="D540" t="n">
-        <v>3.386917135288163</v>
+        <v>3.38691737104285</v>
       </c>
       <c r="E540" t="n">
-        <v>3.463457563350753</v>
+        <v>3.463457804433224</v>
       </c>
       <c r="F540" t="n">
         <v>13661300</v>
@@ -11372,16 +11372,16 @@
         <v>45210</v>
       </c>
       <c r="B548" t="n">
-        <v>3.482593297958374</v>
+        <v>3.482593059539795</v>
       </c>
       <c r="C548" t="n">
-        <v>3.511295961774288</v>
+        <v>3.511295721390723</v>
       </c>
       <c r="D548" t="n">
-        <v>3.396485078402136</v>
+        <v>3.396484845878531</v>
       </c>
       <c r="E548" t="n">
-        <v>3.415620187612745</v>
+        <v>3.41561995377915</v>
       </c>
       <c r="F548" t="n">
         <v>15610900</v>
@@ -25912,19 +25912,39 @@
         <v>46276</v>
       </c>
       <c r="B1275" t="n">
-        <v>0.28</v>
+        <v>0.2800000011920929</v>
       </c>
       <c r="C1275" t="n">
-        <v>0.29</v>
+        <v>0.2899999916553497</v>
       </c>
       <c r="D1275" t="n">
-        <v>0.27</v>
+        <v>0.2700000107288361</v>
       </c>
       <c r="E1275" t="n">
-        <v>0.27</v>
+        <v>0.2700000107288361</v>
       </c>
       <c r="F1275" t="n">
         <v>15613200</v>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B1276" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C1276" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D1276" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E1276" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F1276" t="n">
+        <v>6072700</v>
       </c>
     </row>
   </sheetData>

--- a/database/RAIZ4.xlsx
+++ b/database/RAIZ4.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1276"/>
+  <dimension ref="A1:F1277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44413</v>
       </c>
       <c r="B2" t="n">
-        <v>6.384481906890869</v>
+        <v>6.384481430053711</v>
       </c>
       <c r="C2" t="n">
-        <v>6.701942460974013</v>
+        <v>6.70194196042671</v>
       </c>
       <c r="D2" t="n">
-        <v>6.331571884625592</v>
+        <v>6.331571411740119</v>
       </c>
       <c r="E2" t="n">
-        <v>6.596122416443459</v>
+        <v>6.596121923799527</v>
       </c>
       <c r="F2" t="n">
         <v>98849900</v>
@@ -472,16 +472,16 @@
         <v>44414</v>
       </c>
       <c r="B3" t="n">
-        <v>6.261024475097656</v>
+        <v>6.261024951934814</v>
       </c>
       <c r="C3" t="n">
-        <v>6.48148308633695</v>
+        <v>6.481483579964149</v>
       </c>
       <c r="D3" t="n">
-        <v>6.19929633306517</v>
+        <v>6.199296805201136</v>
       </c>
       <c r="E3" t="n">
-        <v>6.393299725939519</v>
+        <v>6.393300212850708</v>
       </c>
       <c r="F3" t="n">
         <v>28799900</v>
@@ -512,16 +512,16 @@
         <v>44418</v>
       </c>
       <c r="B5" t="n">
-        <v>6.261024475097656</v>
+        <v>6.261024951934814</v>
       </c>
       <c r="C5" t="n">
-        <v>6.313934491336116</v>
+        <v>6.313934972202879</v>
       </c>
       <c r="D5" t="n">
-        <v>6.216933005144656</v>
+        <v>6.216933478623825</v>
       </c>
       <c r="E5" t="n">
-        <v>6.278661147177143</v>
+        <v>6.278661625357502</v>
       </c>
       <c r="F5" t="n">
         <v>9988600</v>
@@ -532,16 +532,16 @@
         <v>44419</v>
       </c>
       <c r="B6" t="n">
-        <v>6.058203220367432</v>
+        <v>6.058202743530273</v>
       </c>
       <c r="C6" t="n">
-        <v>6.296298530585189</v>
+        <v>6.296298035007707</v>
       </c>
       <c r="D6" t="n">
-        <v>5.996475071361166</v>
+        <v>5.996474599382589</v>
       </c>
       <c r="E6" t="n">
-        <v>6.287480403794928</v>
+        <v>6.287479908911514</v>
       </c>
       <c r="F6" t="n">
         <v>31978000</v>
@@ -552,16 +552,16 @@
         <v>44420</v>
       </c>
       <c r="B7" t="n">
-        <v>6.137568473815918</v>
+        <v>6.137567520141602</v>
       </c>
       <c r="C7" t="n">
-        <v>6.155205147916306</v>
+        <v>6.155204191501549</v>
       </c>
       <c r="D7" t="n">
-        <v>5.952383185516099</v>
+        <v>5.952382260616443</v>
       </c>
       <c r="E7" t="n">
-        <v>6.146386600620373</v>
+        <v>6.146385645575868</v>
       </c>
       <c r="F7" t="n">
         <v>17054100</v>
@@ -572,16 +572,16 @@
         <v>44421</v>
       </c>
       <c r="B8" t="n">
-        <v>6.18165922164917</v>
+        <v>6.181661128997803</v>
       </c>
       <c r="C8" t="n">
-        <v>6.208114017642516</v>
+        <v>6.208115933153766</v>
       </c>
       <c r="D8" t="n">
-        <v>6.049383980208238</v>
+        <v>6.049385846743395</v>
       </c>
       <c r="E8" t="n">
-        <v>6.155204005164423</v>
+        <v>6.155205904350309</v>
       </c>
       <c r="F8" t="n">
         <v>21141500</v>
@@ -592,16 +592,16 @@
         <v>44424</v>
       </c>
       <c r="B9" t="n">
-        <v>6.190478801727295</v>
+        <v>6.190478324890137</v>
       </c>
       <c r="C9" t="n">
-        <v>6.278662176582655</v>
+        <v>6.278661692952952</v>
       </c>
       <c r="D9" t="n">
-        <v>5.978838702074429</v>
+        <v>5.978838241539382</v>
       </c>
       <c r="E9" t="n">
-        <v>6.146386904053864</v>
+        <v>6.146386430612996</v>
       </c>
       <c r="F9" t="n">
         <v>13434600</v>
@@ -652,16 +652,16 @@
         <v>44427</v>
       </c>
       <c r="B12" t="n">
-        <v>6.111112117767334</v>
+        <v>6.11111307144165</v>
       </c>
       <c r="C12" t="n">
-        <v>6.111112117767334</v>
+        <v>6.11111307144165</v>
       </c>
       <c r="D12" t="n">
-        <v>5.661376801464195</v>
+        <v>5.66137768495472</v>
       </c>
       <c r="E12" t="n">
-        <v>5.908290193025142</v>
+        <v>5.908291115047926</v>
       </c>
       <c r="F12" t="n">
         <v>5423700</v>
@@ -672,16 +672,16 @@
         <v>44428</v>
       </c>
       <c r="B13" t="n">
-        <v>6.155205726623535</v>
+        <v>6.155204772949219</v>
       </c>
       <c r="C13" t="n">
-        <v>6.216934302024303</v>
+        <v>6.216933338785894</v>
       </c>
       <c r="D13" t="n">
-        <v>6.022930448188472</v>
+        <v>6.022929515008602</v>
       </c>
       <c r="E13" t="n">
-        <v>6.075840475464193</v>
+        <v>6.075839534086558</v>
       </c>
       <c r="F13" t="n">
         <v>3109200</v>
@@ -692,16 +692,16 @@
         <v>44431</v>
       </c>
       <c r="B14" t="n">
-        <v>6.322753429412842</v>
+        <v>6.322752952575684</v>
       </c>
       <c r="C14" t="n">
-        <v>6.349208228925635</v>
+        <v>6.349207750093361</v>
       </c>
       <c r="D14" t="n">
-        <v>6.181660044034058</v>
+        <v>6.181659577837608</v>
       </c>
       <c r="E14" t="n">
-        <v>6.208114843546852</v>
+        <v>6.208114375355285</v>
       </c>
       <c r="F14" t="n">
         <v>6128800</v>
@@ -712,16 +712,16 @@
         <v>44432</v>
       </c>
       <c r="B15" t="n">
-        <v>6.393300533294678</v>
+        <v>6.39330005645752</v>
       </c>
       <c r="C15" t="n">
-        <v>6.525575800840451</v>
+        <v>6.525575314137689</v>
       </c>
       <c r="D15" t="n">
-        <v>6.331571962975588</v>
+        <v>6.331571490742386</v>
       </c>
       <c r="E15" t="n">
-        <v>6.384481985895601</v>
+        <v>6.384481509716164</v>
       </c>
       <c r="F15" t="n">
         <v>6054100</v>
@@ -732,16 +732,16 @@
         <v>44433</v>
       </c>
       <c r="B16" t="n">
-        <v>6.472664833068848</v>
+        <v>6.472664356231689</v>
       </c>
       <c r="C16" t="n">
-        <v>6.507938176533139</v>
+        <v>6.507937697097415</v>
       </c>
       <c r="D16" t="n">
-        <v>6.402118146140264</v>
+        <v>6.402117674500237</v>
       </c>
       <c r="E16" t="n">
-        <v>6.455028161336702</v>
+        <v>6.455027685798826</v>
       </c>
       <c r="F16" t="n">
         <v>5190100</v>
@@ -752,16 +752,16 @@
         <v>44434</v>
       </c>
       <c r="B17" t="n">
-        <v>6.261024475097656</v>
+        <v>6.261024951934814</v>
       </c>
       <c r="C17" t="n">
-        <v>6.507938304701895</v>
+        <v>6.507938800343913</v>
       </c>
       <c r="D17" t="n">
-        <v>6.261024475097656</v>
+        <v>6.261024951934814</v>
       </c>
       <c r="E17" t="n">
-        <v>6.472664960542923</v>
+        <v>6.472665453498537</v>
       </c>
       <c r="F17" t="n">
         <v>7968100</v>
@@ -772,16 +772,16 @@
         <v>44435</v>
       </c>
       <c r="B18" t="n">
-        <v>6.340389728546143</v>
+        <v>6.340390205383301</v>
       </c>
       <c r="C18" t="n">
-        <v>6.384481198630192</v>
+        <v>6.384481678783307</v>
       </c>
       <c r="D18" t="n">
-        <v>6.278661165838754</v>
+        <v>6.278661638033537</v>
       </c>
       <c r="E18" t="n">
-        <v>6.305116384282329</v>
+        <v>6.305116858466711</v>
       </c>
       <c r="F18" t="n">
         <v>5881000</v>
@@ -792,16 +792,16 @@
         <v>44438</v>
       </c>
       <c r="B19" t="n">
-        <v>6.269843101501465</v>
+        <v>6.269843578338623</v>
       </c>
       <c r="C19" t="n">
-        <v>6.419755026338443</v>
+        <v>6.419755514576775</v>
       </c>
       <c r="D19" t="n">
-        <v>6.252206429196611</v>
+        <v>6.252206904692456</v>
       </c>
       <c r="E19" t="n">
-        <v>6.393299807635444</v>
+        <v>6.393300293861791</v>
       </c>
       <c r="F19" t="n">
         <v>4966000</v>
@@ -812,16 +812,16 @@
         <v>44439</v>
       </c>
       <c r="B20" t="n">
-        <v>6.261024475097656</v>
+        <v>6.261024951934814</v>
       </c>
       <c r="C20" t="n">
-        <v>6.305116365542087</v>
+        <v>6.305116845737266</v>
       </c>
       <c r="D20" t="n">
-        <v>6.181659660985684</v>
+        <v>6.181660131778449</v>
       </c>
       <c r="E20" t="n">
-        <v>6.305116365542087</v>
+        <v>6.305116845737266</v>
       </c>
       <c r="F20" t="n">
         <v>3704100</v>
@@ -852,16 +852,16 @@
         <v>44441</v>
       </c>
       <c r="B22" t="n">
-        <v>5.996474742889404</v>
+        <v>5.996475696563721</v>
       </c>
       <c r="C22" t="n">
-        <v>6.252206713170811</v>
+        <v>6.252207707516526</v>
       </c>
       <c r="D22" t="n">
-        <v>5.970019522984813</v>
+        <v>5.970020472451714</v>
       </c>
       <c r="E22" t="n">
-        <v>6.234570040064902</v>
+        <v>6.234571031605695</v>
       </c>
       <c r="F22" t="n">
         <v>3746900</v>
@@ -892,16 +892,16 @@
         <v>44445</v>
       </c>
       <c r="B24" t="n">
-        <v>6.111112117767334</v>
+        <v>6.11111307144165</v>
       </c>
       <c r="C24" t="n">
-        <v>6.190477346729052</v>
+        <v>6.190478312788771</v>
       </c>
       <c r="D24" t="n">
-        <v>6.06702065094858</v>
+        <v>6.067021597742168</v>
       </c>
       <c r="E24" t="n">
-        <v>6.119930663425925</v>
+        <v>6.119931618476427</v>
       </c>
       <c r="F24" t="n">
         <v>1654400</v>
@@ -932,16 +932,16 @@
         <v>44448</v>
       </c>
       <c r="B26" t="n">
-        <v>5.652558326721191</v>
+        <v>5.65255880355835</v>
       </c>
       <c r="C26" t="n">
-        <v>5.837743582960889</v>
+        <v>5.837744075419861</v>
       </c>
       <c r="D26" t="n">
-        <v>5.59964831358005</v>
+        <v>5.599648785953838</v>
       </c>
       <c r="E26" t="n">
-        <v>5.75837877349488</v>
+        <v>5.758379259258814</v>
       </c>
       <c r="F26" t="n">
         <v>5428200</v>
@@ -972,16 +972,16 @@
         <v>44452</v>
       </c>
       <c r="B28" t="n">
-        <v>6.128749370574951</v>
+        <v>6.128748893737793</v>
       </c>
       <c r="C28" t="n">
-        <v>6.172841262072042</v>
+        <v>6.172840781804387</v>
       </c>
       <c r="D28" t="n">
-        <v>5.925927426572926</v>
+        <v>5.925926965515992</v>
       </c>
       <c r="E28" t="n">
-        <v>5.952382645569469</v>
+        <v>5.95238218245423</v>
       </c>
       <c r="F28" t="n">
         <v>8999600</v>
@@ -992,16 +992,16 @@
         <v>44453</v>
       </c>
       <c r="B29" t="n">
-        <v>6.340389728546143</v>
+        <v>6.340390205383301</v>
       </c>
       <c r="C29" t="n">
-        <v>6.50793832404497</v>
+        <v>6.507938813482836</v>
       </c>
       <c r="D29" t="n">
-        <v>6.225751149443035</v>
+        <v>6.225751617658651</v>
       </c>
       <c r="E29" t="n">
-        <v>6.225751149443035</v>
+        <v>6.225751617658651</v>
       </c>
       <c r="F29" t="n">
         <v>9730300</v>
@@ -1012,16 +1012,16 @@
         <v>44454</v>
       </c>
       <c r="B30" t="n">
-        <v>6.384481906890869</v>
+        <v>6.384481430053711</v>
       </c>
       <c r="C30" t="n">
-        <v>6.507939046001328</v>
+        <v>6.50793855994354</v>
       </c>
       <c r="D30" t="n">
-        <v>6.29629853644874</v>
+        <v>6.296298066197724</v>
       </c>
       <c r="E30" t="n">
-        <v>6.384481906890869</v>
+        <v>6.384481430053711</v>
       </c>
       <c r="F30" t="n">
         <v>7265900</v>
@@ -1032,16 +1032,16 @@
         <v>44455</v>
       </c>
       <c r="B31" t="n">
-        <v>6.278660774230957</v>
+        <v>6.278661251068115</v>
       </c>
       <c r="C31" t="n">
-        <v>6.428572688247688</v>
+        <v>6.428573176470008</v>
       </c>
       <c r="D31" t="n">
-        <v>6.172840748039643</v>
+        <v>6.172841216840228</v>
       </c>
       <c r="E31" t="n">
-        <v>6.349207458358499</v>
+        <v>6.349207940553374</v>
       </c>
       <c r="F31" t="n">
         <v>6142600</v>
@@ -1052,16 +1052,16 @@
         <v>44456</v>
       </c>
       <c r="B32" t="n">
-        <v>6.384481906890869</v>
+        <v>6.384481430053711</v>
       </c>
       <c r="C32" t="n">
-        <v>6.384481906890869</v>
+        <v>6.384481430053711</v>
       </c>
       <c r="D32" t="n">
-        <v>5.978838402857074</v>
+        <v>5.978837956316171</v>
       </c>
       <c r="E32" t="n">
-        <v>6.261025188271888</v>
+        <v>6.261024720655329</v>
       </c>
       <c r="F32" t="n">
         <v>16008100</v>
@@ -1072,16 +1072,16 @@
         <v>44459</v>
       </c>
       <c r="B33" t="n">
-        <v>6.269843101501465</v>
+        <v>6.269843578338623</v>
       </c>
       <c r="C33" t="n">
-        <v>6.322753118416027</v>
+        <v>6.322753599277124</v>
       </c>
       <c r="D33" t="n">
-        <v>6.067021159749924</v>
+        <v>6.067021621161969</v>
       </c>
       <c r="E33" t="n">
-        <v>6.164022647180904</v>
+        <v>6.164023115970153</v>
       </c>
       <c r="F33" t="n">
         <v>9065700</v>
@@ -1112,16 +1112,16 @@
         <v>44461</v>
       </c>
       <c r="B35" t="n">
-        <v>6.446210384368896</v>
+        <v>6.446210861206055</v>
       </c>
       <c r="C35" t="n">
-        <v>6.560848974551915</v>
+        <v>6.560849459869084</v>
       </c>
       <c r="D35" t="n">
-        <v>6.40211891002337</v>
+        <v>6.402119383599007</v>
       </c>
       <c r="E35" t="n">
-        <v>6.463847058205402</v>
+        <v>6.463847536347174</v>
       </c>
       <c r="F35" t="n">
         <v>10254600</v>
@@ -1172,16 +1172,16 @@
         <v>44466</v>
       </c>
       <c r="B38" t="n">
-        <v>6.305116653442383</v>
+        <v>6.305117607116699</v>
       </c>
       <c r="C38" t="n">
-        <v>6.340389999211985</v>
+        <v>6.340390958221537</v>
       </c>
       <c r="D38" t="n">
-        <v>6.102294705021446</v>
+        <v>6.102295628018125</v>
       </c>
       <c r="E38" t="n">
-        <v>6.17284139656065</v>
+        <v>6.172842330227801</v>
       </c>
       <c r="F38" t="n">
         <v>6343700</v>
@@ -1192,16 +1192,16 @@
         <v>44467</v>
       </c>
       <c r="B39" t="n">
-        <v>6.119932174682617</v>
+        <v>6.119931221008301</v>
       </c>
       <c r="C39" t="n">
-        <v>6.278662251311475</v>
+        <v>6.278661272902115</v>
       </c>
       <c r="D39" t="n">
-        <v>6.119932174682617</v>
+        <v>6.119931221008301</v>
       </c>
       <c r="E39" t="n">
-        <v>6.261025576130491</v>
+        <v>6.261024600469469</v>
       </c>
       <c r="F39" t="n">
         <v>6782400</v>
@@ -1212,16 +1212,16 @@
         <v>44468</v>
       </c>
       <c r="B40" t="n">
-        <v>6.040565490722656</v>
+        <v>6.040566444396973</v>
       </c>
       <c r="C40" t="n">
-        <v>6.252205963094541</v>
+        <v>6.252206950182298</v>
       </c>
       <c r="D40" t="n">
-        <v>6.040565490722656</v>
+        <v>6.040566444396973</v>
       </c>
       <c r="E40" t="n">
-        <v>6.216932621114461</v>
+        <v>6.216933602633323</v>
       </c>
       <c r="F40" t="n">
         <v>6482600</v>
@@ -1232,16 +1232,16 @@
         <v>44469</v>
       </c>
       <c r="B41" t="n">
-        <v>6.261024475097656</v>
+        <v>6.261024951934814</v>
       </c>
       <c r="C41" t="n">
-        <v>6.349207835495088</v>
+        <v>6.349208319048255</v>
       </c>
       <c r="D41" t="n">
-        <v>6.058202535937849</v>
+        <v>6.058202997328168</v>
       </c>
       <c r="E41" t="n">
-        <v>6.084657754302794</v>
+        <v>6.084658217707932</v>
       </c>
       <c r="F41" t="n">
         <v>15990100</v>
@@ -1272,16 +1272,16 @@
         <v>44473</v>
       </c>
       <c r="B43" t="n">
-        <v>6.190478801727295</v>
+        <v>6.190478324890137</v>
       </c>
       <c r="C43" t="n">
-        <v>6.552030848880022</v>
+        <v>6.552030344193411</v>
       </c>
       <c r="D43" t="n">
-        <v>6.190478801727295</v>
+        <v>6.190478324890137</v>
       </c>
       <c r="E43" t="n">
-        <v>6.525576046669164</v>
+        <v>6.5255755440203</v>
       </c>
       <c r="F43" t="n">
         <v>12019000</v>
@@ -1292,16 +1292,16 @@
         <v>44474</v>
       </c>
       <c r="B44" t="n">
-        <v>6.287479877471924</v>
+        <v>6.287480354309082</v>
       </c>
       <c r="C44" t="n">
-        <v>6.366844693906587</v>
+        <v>6.366845176762705</v>
       </c>
       <c r="D44" t="n">
-        <v>6.2433879857371</v>
+        <v>6.243388459230366</v>
       </c>
       <c r="E44" t="n">
-        <v>6.296298003524023</v>
+        <v>6.29629848102994</v>
       </c>
       <c r="F44" t="n">
         <v>12888200</v>
@@ -1312,16 +1312,16 @@
         <v>44475</v>
       </c>
       <c r="B45" t="n">
-        <v>6.178094387054443</v>
+        <v>6.178093910217285</v>
       </c>
       <c r="C45" t="n">
-        <v>6.275317738941888</v>
+        <v>6.275317254600846</v>
       </c>
       <c r="D45" t="n">
-        <v>6.080871456618367</v>
+        <v>6.080870987285061</v>
       </c>
       <c r="E45" t="n">
-        <v>6.248802547532548</v>
+        <v>6.248802065237998</v>
       </c>
       <c r="F45" t="n">
         <v>10376100</v>
@@ -1332,16 +1332,16 @@
         <v>44476</v>
       </c>
       <c r="B46" t="n">
-        <v>6.301832675933838</v>
+        <v>6.301833152770996</v>
       </c>
       <c r="C46" t="n">
-        <v>6.478602004542243</v>
+        <v>6.478602494754905</v>
       </c>
       <c r="D46" t="n">
-        <v>6.213448011629635</v>
+        <v>6.213448481779042</v>
       </c>
       <c r="E46" t="n">
-        <v>6.284155743072997</v>
+        <v>6.284156218572606</v>
       </c>
       <c r="F46" t="n">
         <v>18438800</v>
@@ -1372,16 +1372,16 @@
         <v>44480</v>
       </c>
       <c r="B48" t="n">
-        <v>6.213448047637939</v>
+        <v>6.213448524475098</v>
       </c>
       <c r="C48" t="n">
-        <v>6.407894310234044</v>
+        <v>6.407894801993546</v>
       </c>
       <c r="D48" t="n">
-        <v>6.213448047637939</v>
+        <v>6.213448524475098</v>
       </c>
       <c r="E48" t="n">
-        <v>6.363701767100176</v>
+        <v>6.363702255468219</v>
       </c>
       <c r="F48" t="n">
         <v>10407400</v>
@@ -1392,16 +1392,16 @@
         <v>44482</v>
       </c>
       <c r="B49" t="n">
-        <v>6.231124877929688</v>
+        <v>6.231125354766846</v>
       </c>
       <c r="C49" t="n">
-        <v>6.292993931556084</v>
+        <v>6.292994413127774</v>
       </c>
       <c r="D49" t="n">
-        <v>6.213447945257672</v>
+        <v>6.213448420742101</v>
       </c>
       <c r="E49" t="n">
-        <v>6.248801810601703</v>
+        <v>6.248802288791589</v>
       </c>
       <c r="F49" t="n">
         <v>8146000</v>
@@ -1432,16 +1432,16 @@
         <v>44484</v>
       </c>
       <c r="B51" t="n">
-        <v>6.275317192077637</v>
+        <v>6.275316715240479</v>
       </c>
       <c r="C51" t="n">
-        <v>6.354863602276304</v>
+        <v>6.354863119394721</v>
       </c>
       <c r="D51" t="n">
-        <v>6.222286392428969</v>
+        <v>6.222285919621418</v>
       </c>
       <c r="E51" t="n">
-        <v>6.337186669060081</v>
+        <v>6.3371861875217</v>
       </c>
       <c r="F51" t="n">
         <v>34203500</v>
@@ -1472,16 +1472,16 @@
         <v>44488</v>
       </c>
       <c r="B53" t="n">
-        <v>5.912939071655273</v>
+        <v>5.91294002532959</v>
       </c>
       <c r="C53" t="n">
-        <v>6.186931711146165</v>
+        <v>6.186932709011659</v>
       </c>
       <c r="D53" t="n">
-        <v>5.895262140767192</v>
+        <v>5.895263091590468</v>
       </c>
       <c r="E53" t="n">
-        <v>6.169254780258083</v>
+        <v>6.169255775272537</v>
       </c>
       <c r="F53" t="n">
         <v>11473400</v>
@@ -1492,16 +1492,16 @@
         <v>44489</v>
       </c>
       <c r="B54" t="n">
-        <v>5.904101371765137</v>
+        <v>5.904100894927979</v>
       </c>
       <c r="C54" t="n">
-        <v>6.045517263705048</v>
+        <v>6.045516775446618</v>
       </c>
       <c r="D54" t="n">
-        <v>5.842232314152062</v>
+        <v>5.842231842311679</v>
       </c>
       <c r="E54" t="n">
-        <v>6.010163396082907</v>
+        <v>6.010162910679786</v>
       </c>
       <c r="F54" t="n">
         <v>6234400</v>
@@ -1552,16 +1552,16 @@
         <v>44494</v>
       </c>
       <c r="B57" t="n">
-        <v>5.859909534454346</v>
+        <v>5.859909057617188</v>
       </c>
       <c r="C57" t="n">
-        <v>5.877586469129643</v>
+        <v>5.877585990854064</v>
       </c>
       <c r="D57" t="n">
-        <v>5.550562966910968</v>
+        <v>5.550562515246201</v>
       </c>
       <c r="E57" t="n">
-        <v>5.683139766250011</v>
+        <v>5.683139303797101</v>
       </c>
       <c r="F57" t="n">
         <v>11428100</v>
@@ -1592,16 +1592,16 @@
         <v>44496</v>
       </c>
       <c r="B59" t="n">
-        <v>5.859909534454346</v>
+        <v>5.859909057617188</v>
       </c>
       <c r="C59" t="n">
-        <v>5.965971142506127</v>
+        <v>5.96597065703844</v>
       </c>
       <c r="D59" t="n">
-        <v>5.789201795753159</v>
+        <v>5.789201324669686</v>
       </c>
       <c r="E59" t="n">
-        <v>5.833393921715717</v>
+        <v>5.833393447036208</v>
       </c>
       <c r="F59" t="n">
         <v>7675900</v>
@@ -1612,16 +1612,16 @@
         <v>44497</v>
       </c>
       <c r="B60" t="n">
-        <v>5.992486000061035</v>
+        <v>5.992486476898193</v>
       </c>
       <c r="C60" t="n">
-        <v>6.027839864956272</v>
+        <v>6.027840344606625</v>
       </c>
       <c r="D60" t="n">
-        <v>5.727331591895446</v>
+        <v>5.727332047633601</v>
       </c>
       <c r="E60" t="n">
-        <v>5.75384720129253</v>
+        <v>5.753847659140599</v>
       </c>
       <c r="F60" t="n">
         <v>8299700</v>
@@ -1632,16 +1632,16 @@
         <v>44498</v>
       </c>
       <c r="B61" t="n">
-        <v>5.992486000061035</v>
+        <v>5.992486476898193</v>
       </c>
       <c r="C61" t="n">
-        <v>6.019001188006806</v>
+        <v>6.019001666953844</v>
       </c>
       <c r="D61" t="n">
-        <v>5.842231863530622</v>
+        <v>5.842232328411681</v>
       </c>
       <c r="E61" t="n">
-        <v>5.957131713714485</v>
+        <v>5.957132187738413</v>
       </c>
       <c r="F61" t="n">
         <v>3926300</v>
@@ -1672,16 +1672,16 @@
         <v>44503</v>
       </c>
       <c r="B63" t="n">
-        <v>6.098548412322998</v>
+        <v>6.09854793548584</v>
       </c>
       <c r="C63" t="n">
-        <v>6.18693308641001</v>
+        <v>6.186932602662175</v>
       </c>
       <c r="D63" t="n">
-        <v>5.921778642697604</v>
+        <v>5.921778179681833</v>
       </c>
       <c r="E63" t="n">
-        <v>5.983648125284198</v>
+        <v>5.983647657430936</v>
       </c>
       <c r="F63" t="n">
         <v>5711600</v>
@@ -1692,16 +1692,16 @@
         <v>44504</v>
       </c>
       <c r="B64" t="n">
-        <v>5.965970516204834</v>
+        <v>5.965970993041992</v>
       </c>
       <c r="C64" t="n">
-        <v>6.160416777220335</v>
+        <v>6.160417269598838</v>
       </c>
       <c r="D64" t="n">
-        <v>5.842231986467696</v>
+        <v>5.842232453414908</v>
       </c>
       <c r="E64" t="n">
-        <v>6.098547723077428</v>
+        <v>6.098548210510975</v>
       </c>
       <c r="F64" t="n">
         <v>8687600</v>
@@ -1712,16 +1712,16 @@
         <v>44505</v>
       </c>
       <c r="B65" t="n">
-        <v>5.965970516204834</v>
+        <v>5.965970993041992</v>
       </c>
       <c r="C65" t="n">
-        <v>6.054355180302789</v>
+        <v>6.054355664204195</v>
       </c>
       <c r="D65" t="n">
-        <v>5.939454906249786</v>
+        <v>5.939455380967654</v>
       </c>
       <c r="E65" t="n">
-        <v>6.001324381844015</v>
+        <v>6.001324861506873</v>
       </c>
       <c r="F65" t="n">
         <v>3123600</v>
@@ -1732,16 +1732,16 @@
         <v>44508</v>
       </c>
       <c r="B66" t="n">
-        <v>5.983646869659424</v>
+        <v>5.983647346496582</v>
       </c>
       <c r="C66" t="n">
-        <v>6.036677662983505</v>
+        <v>6.036678144046689</v>
       </c>
       <c r="D66" t="n">
-        <v>5.939454331163716</v>
+        <v>5.939454804479167</v>
       </c>
       <c r="E66" t="n">
-        <v>6.010162477047105</v>
+        <v>6.010162955997293</v>
       </c>
       <c r="F66" t="n">
         <v>3898000</v>
@@ -1792,16 +1792,16 @@
         <v>44511</v>
       </c>
       <c r="B69" t="n">
-        <v>6.010162830352783</v>
+        <v>6.010164260864258</v>
       </c>
       <c r="C69" t="n">
-        <v>6.036678017847871</v>
+        <v>6.036679454670368</v>
       </c>
       <c r="D69" t="n">
-        <v>5.806877899934787</v>
+        <v>5.806879282061312</v>
       </c>
       <c r="E69" t="n">
-        <v>5.833393087429874</v>
+        <v>5.833394475867422</v>
       </c>
       <c r="F69" t="n">
         <v>8604300</v>
@@ -1812,16 +1812,16 @@
         <v>44512</v>
       </c>
       <c r="B70" t="n">
-        <v>5.762686252593994</v>
+        <v>5.762685775756836</v>
       </c>
       <c r="C70" t="n">
-        <v>6.080871502042515</v>
+        <v>6.080870998876915</v>
       </c>
       <c r="D70" t="n">
-        <v>5.532886099040496</v>
+        <v>5.532885641218299</v>
       </c>
       <c r="E70" t="n">
-        <v>6.080871502042515</v>
+        <v>6.080870998876915</v>
       </c>
       <c r="F70" t="n">
         <v>20568500</v>
@@ -1872,16 +1872,16 @@
         <v>44518</v>
       </c>
       <c r="B73" t="n">
-        <v>5.16166877746582</v>
+        <v>5.161669731140137</v>
       </c>
       <c r="C73" t="n">
-        <v>5.338438082947006</v>
+        <v>5.338439069281368</v>
       </c>
       <c r="D73" t="n">
-        <v>5.07328370327396</v>
+        <v>5.073284640618174</v>
       </c>
       <c r="E73" t="n">
-        <v>5.214699569110176</v>
+        <v>5.214700532582506</v>
       </c>
       <c r="F73" t="n">
         <v>17735600</v>
@@ -1912,16 +1912,16 @@
         <v>44522</v>
       </c>
       <c r="B75" t="n">
-        <v>4.976061820983887</v>
+        <v>4.976061344146729</v>
       </c>
       <c r="C75" t="n">
-        <v>5.329600926221622</v>
+        <v>5.32960041550615</v>
       </c>
       <c r="D75" t="n">
-        <v>4.976061820983887</v>
+        <v>4.976061344146729</v>
       </c>
       <c r="E75" t="n">
-        <v>5.23237757745469</v>
+        <v>5.232377076055763</v>
       </c>
       <c r="F75" t="n">
         <v>8516000</v>
@@ -1932,16 +1932,16 @@
         <v>44523</v>
       </c>
       <c r="B76" t="n">
-        <v>5.011415958404541</v>
+        <v>5.011415004730225</v>
       </c>
       <c r="C76" t="n">
-        <v>5.09980063409614</v>
+        <v>5.099799663602187</v>
       </c>
       <c r="D76" t="n">
-        <v>4.781615380155004</v>
+        <v>4.781614470211824</v>
       </c>
       <c r="E76" t="n">
-        <v>5.002577280109692</v>
+        <v>5.00257632811738</v>
       </c>
       <c r="F76" t="n">
         <v>9084200</v>
@@ -1952,16 +1952,16 @@
         <v>44524</v>
       </c>
       <c r="B77" t="n">
-        <v>4.923030853271484</v>
+        <v>4.923030376434326</v>
       </c>
       <c r="C77" t="n">
-        <v>5.020253777325691</v>
+        <v>5.020253291071671</v>
       </c>
       <c r="D77" t="n">
-        <v>4.825807507765937</v>
+        <v>4.825807040345681</v>
       </c>
       <c r="E77" t="n">
-        <v>4.923030853271484</v>
+        <v>4.923030376434326</v>
       </c>
       <c r="F77" t="n">
         <v>8397000</v>
@@ -1972,16 +1972,16 @@
         <v>44525</v>
       </c>
       <c r="B78" t="n">
-        <v>5.373792171478271</v>
+        <v>5.37379264831543</v>
       </c>
       <c r="C78" t="n">
-        <v>5.373792171478271</v>
+        <v>5.37379264831543</v>
       </c>
       <c r="D78" t="n">
-        <v>4.799291272172914</v>
+        <v>4.799291698032407</v>
       </c>
       <c r="E78" t="n">
-        <v>4.949545398916761</v>
+        <v>4.949545838108879</v>
       </c>
       <c r="F78" t="n">
         <v>20546100</v>
@@ -2032,16 +2032,16 @@
         <v>44530</v>
       </c>
       <c r="B81" t="n">
-        <v>4.825807571411133</v>
+        <v>4.825807094573975</v>
       </c>
       <c r="C81" t="n">
-        <v>5.126315867963532</v>
+        <v>5.126315361433205</v>
       </c>
       <c r="D81" t="n">
-        <v>4.790453703752186</v>
+        <v>4.790453230408336</v>
       </c>
       <c r="E81" t="n">
-        <v>5.073284645023764</v>
+        <v>5.073284143733442</v>
       </c>
       <c r="F81" t="n">
         <v>11282700</v>
@@ -2072,16 +2072,16 @@
         <v>44532</v>
       </c>
       <c r="B83" t="n">
-        <v>5.029092311859131</v>
+        <v>5.029092788696289</v>
       </c>
       <c r="C83" t="n">
-        <v>5.029092311859131</v>
+        <v>5.029092788696289</v>
       </c>
       <c r="D83" t="n">
-        <v>4.746260960907972</v>
+        <v>4.746261410928263</v>
       </c>
       <c r="E83" t="n">
-        <v>4.905353780202955</v>
+        <v>4.905354245307752</v>
       </c>
       <c r="F83" t="n">
         <v>18379200</v>
@@ -2132,16 +2132,16 @@
         <v>44537</v>
       </c>
       <c r="B86" t="n">
-        <v>5.232376575469971</v>
+        <v>5.232377052307129</v>
       </c>
       <c r="C86" t="n">
-        <v>5.258891760950692</v>
+        <v>5.258892240204233</v>
       </c>
       <c r="D86" t="n">
-        <v>4.914191399542398</v>
+        <v>4.914191847382692</v>
       </c>
       <c r="E86" t="n">
-        <v>5.241214830146453</v>
+        <v>5.24121530778906</v>
       </c>
       <c r="F86" t="n">
         <v>9906100</v>
@@ -2172,16 +2172,16 @@
         <v>44539</v>
       </c>
       <c r="B88" t="n">
-        <v>5.232376575469971</v>
+        <v>5.232377052307129</v>
       </c>
       <c r="C88" t="n">
-        <v>5.435661490444354</v>
+        <v>5.435661985807282</v>
       </c>
       <c r="D88" t="n">
-        <v>5.179345783057254</v>
+        <v>5.179346255061608</v>
       </c>
       <c r="E88" t="n">
-        <v>5.205860968537976</v>
+        <v>5.205861442958712</v>
       </c>
       <c r="F88" t="n">
         <v>9205900</v>
@@ -2192,16 +2192,16 @@
         <v>44540</v>
       </c>
       <c r="B89" t="n">
-        <v>5.444500923156738</v>
+        <v>5.444501399993896</v>
       </c>
       <c r="C89" t="n">
-        <v>5.568239887011294</v>
+        <v>5.568240374685687</v>
       </c>
       <c r="D89" t="n">
-        <v>5.241215964197243</v>
+        <v>5.241216423230415</v>
       </c>
       <c r="E89" t="n">
-        <v>5.267731576866467</v>
+        <v>5.267732038221914</v>
       </c>
       <c r="F89" t="n">
         <v>8741300</v>
@@ -2212,16 +2212,16 @@
         <v>44543</v>
       </c>
       <c r="B90" t="n">
-        <v>5.497531414031982</v>
+        <v>5.497530937194824</v>
       </c>
       <c r="C90" t="n">
-        <v>5.621270370841238</v>
+        <v>5.621269883271384</v>
       </c>
       <c r="D90" t="n">
-        <v>5.426823679541746</v>
+        <v>5.426823208837535</v>
       </c>
       <c r="E90" t="n">
-        <v>5.444500613164305</v>
+        <v>5.444500140926858</v>
       </c>
       <c r="F90" t="n">
         <v>8265100</v>
@@ -2232,16 +2232,16 @@
         <v>44544</v>
       </c>
       <c r="B91" t="n">
-        <v>5.453339099884033</v>
+        <v>5.453338623046875</v>
       </c>
       <c r="C91" t="n">
-        <v>5.60359324114393</v>
+        <v>5.603592751168627</v>
       </c>
       <c r="D91" t="n">
-        <v>5.426823489652329</v>
+        <v>5.426823015133682</v>
       </c>
       <c r="E91" t="n">
-        <v>5.497531221668439</v>
+        <v>5.497530740967144</v>
       </c>
       <c r="F91" t="n">
         <v>6640900</v>
@@ -2252,16 +2252,16 @@
         <v>44545</v>
       </c>
       <c r="B92" t="n">
-        <v>5.479854583740234</v>
+        <v>5.479853630065918</v>
       </c>
       <c r="C92" t="n">
-        <v>5.524047129355619</v>
+        <v>5.524046167990352</v>
       </c>
       <c r="D92" t="n">
-        <v>5.329600855840895</v>
+        <v>5.329599928315653</v>
       </c>
       <c r="E92" t="n">
-        <v>5.479854583740234</v>
+        <v>5.479853630065918</v>
       </c>
       <c r="F92" t="n">
         <v>4791400</v>
@@ -2272,16 +2272,16 @@
         <v>44546</v>
       </c>
       <c r="B93" t="n">
-        <v>5.400308132171631</v>
+        <v>5.400308609008789</v>
       </c>
       <c r="C93" t="n">
-        <v>5.550562268737735</v>
+        <v>5.550562758842054</v>
       </c>
       <c r="D93" t="n">
-        <v>5.347277334816178</v>
+        <v>5.347277806970816</v>
       </c>
       <c r="E93" t="n">
-        <v>5.515207982382787</v>
+        <v>5.515208469365389</v>
       </c>
       <c r="F93" t="n">
         <v>9238300</v>
@@ -2312,16 +2312,16 @@
         <v>44550</v>
       </c>
       <c r="B95" t="n">
-        <v>5.143992900848389</v>
+        <v>5.143991947174072</v>
       </c>
       <c r="C95" t="n">
-        <v>5.179346769188129</v>
+        <v>5.179345808959355</v>
       </c>
       <c r="D95" t="n">
-        <v>4.949546203528466</v>
+        <v>4.949545285903736</v>
       </c>
       <c r="E95" t="n">
-        <v>5.179346769188129</v>
+        <v>5.179345808959355</v>
       </c>
       <c r="F95" t="n">
         <v>8433600</v>
@@ -2352,16 +2352,16 @@
         <v>44552</v>
       </c>
       <c r="B97" t="n">
-        <v>5.011415958404541</v>
+        <v>5.011415004730225</v>
       </c>
       <c r="C97" t="n">
-        <v>5.073285020662972</v>
+        <v>5.07328405521495</v>
       </c>
       <c r="D97" t="n">
-        <v>4.914192604418092</v>
+        <v>4.914191669245416</v>
       </c>
       <c r="E97" t="n">
-        <v>5.055608085524652</v>
+        <v>5.055607123440558</v>
       </c>
       <c r="F97" t="n">
         <v>4649500</v>
@@ -2392,16 +2392,16 @@
         <v>44557</v>
       </c>
       <c r="B99" t="n">
-        <v>5.232376575469971</v>
+        <v>5.232377052307129</v>
       </c>
       <c r="C99" t="n">
-        <v>5.232376575469971</v>
+        <v>5.232377052307129</v>
       </c>
       <c r="D99" t="n">
-        <v>5.011414729691348</v>
+        <v>5.011415186391803</v>
       </c>
       <c r="E99" t="n">
-        <v>5.046768591299826</v>
+        <v>5.04676905122215</v>
       </c>
       <c r="F99" t="n">
         <v>4493500</v>
@@ -2412,16 +2412,16 @@
         <v>44558</v>
       </c>
       <c r="B100" t="n">
-        <v>5.347278118133545</v>
+        <v>5.347277164459229</v>
       </c>
       <c r="C100" t="n">
-        <v>5.347278118133545</v>
+        <v>5.347277164459229</v>
       </c>
       <c r="D100" t="n">
-        <v>5.188185281310526</v>
+        <v>5.188184356010038</v>
       </c>
       <c r="E100" t="n">
-        <v>5.214700894598154</v>
+        <v>5.21469996456867</v>
       </c>
       <c r="F100" t="n">
         <v>4379800</v>
@@ -2432,16 +2432,16 @@
         <v>44559</v>
       </c>
       <c r="B101" t="n">
-        <v>5.311923980712891</v>
+        <v>5.311924457550049</v>
       </c>
       <c r="C101" t="n">
-        <v>5.382631717319493</v>
+        <v>5.382632200503894</v>
       </c>
       <c r="D101" t="n">
-        <v>5.214700632153136</v>
+        <v>5.214701100262815</v>
       </c>
       <c r="E101" t="n">
-        <v>5.320762237063039</v>
+        <v>5.320762714693583</v>
       </c>
       <c r="F101" t="n">
         <v>5394800</v>
@@ -2452,16 +2452,16 @@
         <v>44560</v>
       </c>
       <c r="B102" t="n">
-        <v>5.70081615447998</v>
+        <v>5.700815677642822</v>
       </c>
       <c r="C102" t="n">
-        <v>5.70965483169609</v>
+        <v>5.709654354119633</v>
       </c>
       <c r="D102" t="n">
-        <v>5.258892408506298</v>
+        <v>5.258891968633261</v>
       </c>
       <c r="E102" t="n">
-        <v>5.320761884665091</v>
+        <v>5.320761439617065</v>
       </c>
       <c r="F102" t="n">
         <v>23096200</v>
@@ -2472,16 +2472,16 @@
         <v>44564</v>
       </c>
       <c r="B103" t="n">
-        <v>5.54172420501709</v>
+        <v>5.541723728179932</v>
       </c>
       <c r="C103" t="n">
-        <v>5.745009161433563</v>
+        <v>5.745008667104768</v>
       </c>
       <c r="D103" t="n">
-        <v>5.5063703362013</v>
+        <v>5.506369862406162</v>
       </c>
       <c r="E103" t="n">
-        <v>5.691978358209878</v>
+        <v>5.691977868444114</v>
       </c>
       <c r="F103" t="n">
         <v>7451800</v>
@@ -2492,16 +2492,16 @@
         <v>44565</v>
       </c>
       <c r="B104" t="n">
-        <v>5.594754219055176</v>
+        <v>5.594754695892334</v>
       </c>
       <c r="C104" t="n">
-        <v>5.612431150969596</v>
+        <v>5.612431629313347</v>
       </c>
       <c r="D104" t="n">
-        <v>5.444500087056956</v>
+        <v>5.444500551088055</v>
       </c>
       <c r="E104" t="n">
-        <v>5.532885168080356</v>
+        <v>5.532885639644457</v>
       </c>
       <c r="F104" t="n">
         <v>10613100</v>
@@ -2552,16 +2552,16 @@
         <v>44568</v>
       </c>
       <c r="B107" t="n">
-        <v>5.163622856140137</v>
+        <v>5.163622379302979</v>
       </c>
       <c r="C107" t="n">
-        <v>5.278961186075115</v>
+        <v>5.278960698586984</v>
       </c>
       <c r="D107" t="n">
-        <v>4.941817757177995</v>
+        <v>4.941817300823532</v>
       </c>
       <c r="E107" t="n">
-        <v>4.977306539167166</v>
+        <v>4.977306079535475</v>
       </c>
       <c r="F107" t="n">
         <v>10961100</v>
@@ -2572,16 +2572,16 @@
         <v>44571</v>
       </c>
       <c r="B108" t="n">
-        <v>5.057155609130859</v>
+        <v>5.057156085968018</v>
       </c>
       <c r="C108" t="n">
-        <v>5.128133589460298</v>
+        <v>5.128134072989941</v>
       </c>
       <c r="D108" t="n">
-        <v>4.906328511462285</v>
+        <v>4.906328974078017</v>
       </c>
       <c r="E108" t="n">
-        <v>5.057155609130859</v>
+        <v>5.057156085968018</v>
       </c>
       <c r="F108" t="n">
         <v>11253600</v>
@@ -2592,16 +2592,16 @@
         <v>44572</v>
       </c>
       <c r="B109" t="n">
-        <v>5.234601020812988</v>
+        <v>5.23460054397583</v>
       </c>
       <c r="C109" t="n">
-        <v>5.234601020812988</v>
+        <v>5.23460054397583</v>
       </c>
       <c r="D109" t="n">
-        <v>5.021667881383257</v>
+        <v>5.021667423942884</v>
       </c>
       <c r="E109" t="n">
-        <v>5.021667881383257</v>
+        <v>5.021667423942884</v>
       </c>
       <c r="F109" t="n">
         <v>5425200</v>
@@ -2612,16 +2612,16 @@
         <v>44573</v>
       </c>
       <c r="B110" t="n">
-        <v>5.438661098480225</v>
+        <v>5.438660621643066</v>
       </c>
       <c r="C110" t="n">
-        <v>5.518510645991364</v>
+        <v>5.51851016215336</v>
       </c>
       <c r="D110" t="n">
-        <v>5.225727984644668</v>
+        <v>5.225727526476521</v>
       </c>
       <c r="E110" t="n">
-        <v>5.261216766440652</v>
+        <v>5.261216305161009</v>
       </c>
       <c r="F110" t="n">
         <v>9077500</v>
@@ -2632,16 +2632,16 @@
         <v>44574</v>
       </c>
       <c r="B111" t="n">
-        <v>5.420916080474854</v>
+        <v>5.420916557312012</v>
       </c>
       <c r="C111" t="n">
-        <v>5.509638024701201</v>
+        <v>5.50963850934256</v>
       </c>
       <c r="D111" t="n">
-        <v>5.358810507986609</v>
+        <v>5.358810979360809</v>
       </c>
       <c r="E111" t="n">
-        <v>5.358810507986609</v>
+        <v>5.358810979360809</v>
       </c>
       <c r="F111" t="n">
         <v>4388600</v>
@@ -2652,16 +2652,16 @@
         <v>44575</v>
       </c>
       <c r="B112" t="n">
-        <v>5.491894245147705</v>
+        <v>5.491893768310547</v>
       </c>
       <c r="C112" t="n">
-        <v>5.500766229024832</v>
+        <v>5.500765751417357</v>
       </c>
       <c r="D112" t="n">
-        <v>5.332194727822603</v>
+        <v>5.332194264851456</v>
       </c>
       <c r="E112" t="n">
-        <v>5.420916681892105</v>
+        <v>5.420916211217618</v>
       </c>
       <c r="F112" t="n">
         <v>4745900</v>
@@ -2672,16 +2672,16 @@
         <v>44578</v>
       </c>
       <c r="B113" t="n">
-        <v>5.48302173614502</v>
+        <v>5.483021259307861</v>
       </c>
       <c r="C113" t="n">
-        <v>5.62497728307338</v>
+        <v>5.624976793890898</v>
       </c>
       <c r="D113" t="n">
-        <v>5.447532955177839</v>
+        <v>5.447532481427003</v>
       </c>
       <c r="E113" t="n">
-        <v>5.447532955177839</v>
+        <v>5.447532481427003</v>
       </c>
       <c r="F113" t="n">
         <v>3137800</v>
@@ -2692,16 +2692,16 @@
         <v>44579</v>
       </c>
       <c r="B114" t="n">
-        <v>5.48302173614502</v>
+        <v>5.483021259307861</v>
       </c>
       <c r="C114" t="n">
-        <v>5.536254907595789</v>
+        <v>5.536254426129148</v>
       </c>
       <c r="D114" t="n">
-        <v>5.376555393243478</v>
+        <v>5.376554925665286</v>
       </c>
       <c r="E114" t="n">
-        <v>5.474149752433044</v>
+        <v>5.474149276367449</v>
       </c>
       <c r="F114" t="n">
         <v>3854900</v>
@@ -2712,16 +2712,16 @@
         <v>44580</v>
       </c>
       <c r="B115" t="n">
-        <v>5.651593208312988</v>
+        <v>5.651593685150146</v>
       </c>
       <c r="C115" t="n">
-        <v>5.749187559749773</v>
+        <v>5.749188044821177</v>
       </c>
       <c r="D115" t="n">
-        <v>5.509638095721016</v>
+        <v>5.509638560581113</v>
       </c>
       <c r="E115" t="n">
-        <v>5.509638095721016</v>
+        <v>5.509638560581113</v>
       </c>
       <c r="F115" t="n">
         <v>12660500</v>
@@ -2752,16 +2752,16 @@
         <v>44582</v>
       </c>
       <c r="B117" t="n">
-        <v>5.527383327484131</v>
+        <v>5.527382850646973</v>
       </c>
       <c r="C117" t="n">
-        <v>5.687082853497435</v>
+        <v>5.687082362883293</v>
       </c>
       <c r="D117" t="n">
-        <v>5.483022136506155</v>
+        <v>5.483021663495955</v>
       </c>
       <c r="E117" t="n">
-        <v>5.678210869137642</v>
+        <v>5.678210379288871</v>
       </c>
       <c r="F117" t="n">
         <v>7609900</v>
@@ -2792,16 +2792,16 @@
         <v>44586</v>
       </c>
       <c r="B119" t="n">
-        <v>5.500766277313232</v>
+        <v>5.500765323638916</v>
       </c>
       <c r="C119" t="n">
-        <v>5.57174426425156</v>
+        <v>5.571743298271707</v>
       </c>
       <c r="D119" t="n">
-        <v>5.36768355657054</v>
+        <v>5.367682625968931</v>
       </c>
       <c r="E119" t="n">
-        <v>5.394299931495218</v>
+        <v>5.394298996279097</v>
       </c>
       <c r="F119" t="n">
         <v>8097000</v>
@@ -2812,16 +2812,16 @@
         <v>44587</v>
       </c>
       <c r="B120" t="n">
-        <v>5.518510818481445</v>
+        <v>5.518509864807129</v>
       </c>
       <c r="C120" t="n">
-        <v>5.678210764614708</v>
+        <v>5.678209783342052</v>
       </c>
       <c r="D120" t="n">
-        <v>5.491894442832344</v>
+        <v>5.491893493757702</v>
       </c>
       <c r="E120" t="n">
-        <v>5.598360791548077</v>
+        <v>5.59835982407459</v>
       </c>
       <c r="F120" t="n">
         <v>11610000</v>
@@ -2832,16 +2832,16 @@
         <v>44588</v>
       </c>
       <c r="B121" t="n">
-        <v>5.545127391815186</v>
+        <v>5.545126914978027</v>
       </c>
       <c r="C121" t="n">
-        <v>5.74918809675637</v>
+        <v>5.749187602371603</v>
       </c>
       <c r="D121" t="n">
-        <v>5.527383001083763</v>
+        <v>5.527382525772483</v>
       </c>
       <c r="E121" t="n">
-        <v>5.580616173278031</v>
+        <v>5.580615693389118</v>
       </c>
       <c r="F121" t="n">
         <v>8501200</v>
@@ -2852,16 +2852,16 @@
         <v>44589</v>
       </c>
       <c r="B122" t="n">
-        <v>5.660465717315674</v>
+        <v>5.660466194152832</v>
       </c>
       <c r="C122" t="n">
-        <v>5.731443274902391</v>
+        <v>5.731443757718693</v>
       </c>
       <c r="D122" t="n">
-        <v>5.509638195914094</v>
+        <v>5.509638660045554</v>
       </c>
       <c r="E122" t="n">
-        <v>5.509638195914094</v>
+        <v>5.509638660045554</v>
       </c>
       <c r="F122" t="n">
         <v>15566700</v>
@@ -2872,16 +2872,16 @@
         <v>44592</v>
       </c>
       <c r="B123" t="n">
-        <v>5.695955276489258</v>
+        <v>5.695953845977783</v>
       </c>
       <c r="C123" t="n">
-        <v>5.793549643071818</v>
+        <v>5.793548188049992</v>
       </c>
       <c r="D123" t="n">
-        <v>5.571744533694882</v>
+        <v>5.571743134378331</v>
       </c>
       <c r="E123" t="n">
-        <v>5.607233317350418</v>
+        <v>5.607231909121031</v>
       </c>
       <c r="F123" t="n">
         <v>7514700</v>
@@ -2892,16 +2892,16 @@
         <v>44593</v>
       </c>
       <c r="B124" t="n">
-        <v>5.678209781646729</v>
+        <v>5.678210258483887</v>
       </c>
       <c r="C124" t="n">
-        <v>5.79354851765205</v>
+        <v>5.793549004174971</v>
       </c>
       <c r="D124" t="n">
-        <v>5.536254251540337</v>
+        <v>5.536254716456543</v>
       </c>
       <c r="E124" t="n">
-        <v>5.76693172355098</v>
+        <v>5.766932207838711</v>
       </c>
       <c r="F124" t="n">
         <v>8050400</v>
@@ -2912,16 +2912,16 @@
         <v>44594</v>
       </c>
       <c r="B125" t="n">
-        <v>5.669337272644043</v>
+        <v>5.669338703155518</v>
       </c>
       <c r="C125" t="n">
-        <v>5.882270352394677</v>
+        <v>5.882271836634339</v>
       </c>
       <c r="D125" t="n">
-        <v>5.651592884586456</v>
+        <v>5.65159431062059</v>
       </c>
       <c r="E125" t="n">
-        <v>5.722570436816806</v>
+        <v>5.722571880760301</v>
       </c>
       <c r="F125" t="n">
         <v>8808600</v>
@@ -2952,16 +2952,16 @@
         <v>44596</v>
       </c>
       <c r="B127" t="n">
-        <v>5.660465717315674</v>
+        <v>5.660466194152832</v>
       </c>
       <c r="C127" t="n">
-        <v>5.820165221885787</v>
+        <v>5.820165712176019</v>
       </c>
       <c r="D127" t="n">
-        <v>5.633848921690848</v>
+        <v>5.63384939628581</v>
       </c>
       <c r="E127" t="n">
-        <v>5.722570868674245</v>
+        <v>5.722571350743135</v>
       </c>
       <c r="F127" t="n">
         <v>8483700</v>
@@ -2972,16 +2972,16 @@
         <v>44599</v>
       </c>
       <c r="B128" t="n">
-        <v>5.56287145614624</v>
+        <v>5.562871932983398</v>
       </c>
       <c r="C128" t="n">
-        <v>5.775804555489152</v>
+        <v>5.775805050578469</v>
       </c>
       <c r="D128" t="n">
-        <v>5.553999472830914</v>
+        <v>5.553999948907585</v>
       </c>
       <c r="E128" t="n">
-        <v>5.704826573668434</v>
+        <v>5.704827062673674</v>
       </c>
       <c r="F128" t="n">
         <v>7178800</v>
@@ -2992,16 +2992,16 @@
         <v>44600</v>
       </c>
       <c r="B129" t="n">
-        <v>5.616104125976562</v>
+        <v>5.616104602813721</v>
       </c>
       <c r="C129" t="n">
-        <v>5.695954084014389</v>
+        <v>5.695954567631234</v>
       </c>
       <c r="D129" t="n">
-        <v>5.483021003600046</v>
+        <v>5.483021469137738</v>
       </c>
       <c r="E129" t="n">
-        <v>5.58061534975077</v>
+        <v>5.580615823574741</v>
       </c>
       <c r="F129" t="n">
         <v>9770800</v>
@@ -3012,16 +3012,16 @@
         <v>44601</v>
       </c>
       <c r="B130" t="n">
-        <v>5.633848667144775</v>
+        <v>5.633849143981934</v>
       </c>
       <c r="C130" t="n">
-        <v>5.740314998714537</v>
+        <v>5.740315484562782</v>
       </c>
       <c r="D130" t="n">
-        <v>5.589487907187173</v>
+        <v>5.58948838026973</v>
       </c>
       <c r="E130" t="n">
-        <v>5.616104278549815</v>
+        <v>5.616104753885126</v>
       </c>
       <c r="F130" t="n">
         <v>8867400</v>
@@ -3032,16 +3032,16 @@
         <v>44602</v>
       </c>
       <c r="B131" t="n">
-        <v>5.704826354980469</v>
+        <v>5.704825878143311</v>
       </c>
       <c r="C131" t="n">
-        <v>5.740315133000595</v>
+        <v>5.740314653197113</v>
       </c>
       <c r="D131" t="n">
-        <v>5.562871242899961</v>
+        <v>5.562870777928103</v>
       </c>
       <c r="E131" t="n">
-        <v>5.678209982995176</v>
+        <v>5.678209508382744</v>
       </c>
       <c r="F131" t="n">
         <v>9667400</v>
@@ -3052,16 +3052,16 @@
         <v>44603</v>
       </c>
       <c r="B132" t="n">
-        <v>5.633848667144775</v>
+        <v>5.633849143981934</v>
       </c>
       <c r="C132" t="n">
-        <v>5.775804198964051</v>
+        <v>5.775804687816029</v>
       </c>
       <c r="D132" t="n">
-        <v>5.589487907187173</v>
+        <v>5.58948838026973</v>
       </c>
       <c r="E132" t="n">
-        <v>5.731443015946853</v>
+        <v>5.731443501044193</v>
       </c>
       <c r="F132" t="n">
         <v>8001300</v>
@@ -3072,16 +3072,16 @@
         <v>44606</v>
       </c>
       <c r="B133" t="n">
-        <v>5.695955276489258</v>
+        <v>5.695953845977783</v>
       </c>
       <c r="C133" t="n">
-        <v>5.76693284380033</v>
+        <v>5.766931395463184</v>
       </c>
       <c r="D133" t="n">
-        <v>5.642722101005954</v>
+        <v>5.642720683863732</v>
       </c>
       <c r="E133" t="n">
-        <v>5.642722101005954</v>
+        <v>5.642720683863732</v>
       </c>
       <c r="F133" t="n">
         <v>12680200</v>
@@ -3092,16 +3092,16 @@
         <v>44607</v>
       </c>
       <c r="B134" t="n">
-        <v>5.695955276489258</v>
+        <v>5.695953845977783</v>
       </c>
       <c r="C134" t="n">
-        <v>5.811294034899586</v>
+        <v>5.811292575421342</v>
       </c>
       <c r="D134" t="n">
-        <v>5.518510935151906</v>
+        <v>5.518509549204714</v>
       </c>
       <c r="E134" t="n">
-        <v>5.811294034899586</v>
+        <v>5.811292575421342</v>
       </c>
       <c r="F134" t="n">
         <v>17426200</v>
@@ -3112,16 +3112,16 @@
         <v>44608</v>
       </c>
       <c r="B135" t="n">
-        <v>5.704826354980469</v>
+        <v>5.704825878143311</v>
       </c>
       <c r="C135" t="n">
-        <v>5.811293112100454</v>
+        <v>5.811292626364287</v>
       </c>
       <c r="D135" t="n">
-        <v>5.651593187950278</v>
+        <v>5.651592715562607</v>
       </c>
       <c r="E135" t="n">
-        <v>5.713698761015302</v>
+        <v>5.713698283436546</v>
       </c>
       <c r="F135" t="n">
         <v>12029900</v>
@@ -3132,16 +3132,16 @@
         <v>44609</v>
       </c>
       <c r="B136" t="n">
-        <v>5.580615520477295</v>
+        <v>5.580616474151611</v>
       </c>
       <c r="C136" t="n">
-        <v>5.740315018379015</v>
+        <v>5.740315999344462</v>
       </c>
       <c r="D136" t="n">
-        <v>5.509637965854308</v>
+        <v>5.509638907399233</v>
       </c>
       <c r="E136" t="n">
-        <v>5.73144303558094</v>
+        <v>5.73144401503025</v>
       </c>
       <c r="F136" t="n">
         <v>16171600</v>
@@ -3152,16 +3152,16 @@
         <v>44610</v>
       </c>
       <c r="B137" t="n">
-        <v>5.420916080474854</v>
+        <v>5.420916557312012</v>
       </c>
       <c r="C137" t="n">
-        <v>5.616104357772818</v>
+        <v>5.616104851779219</v>
       </c>
       <c r="D137" t="n">
-        <v>5.305577341450801</v>
+        <v>5.305577808142479</v>
       </c>
       <c r="E137" t="n">
-        <v>5.598359968927548</v>
+        <v>5.598360461373109</v>
       </c>
       <c r="F137" t="n">
         <v>12852100</v>
@@ -3172,16 +3172,16 @@
         <v>44613</v>
       </c>
       <c r="B138" t="n">
-        <v>5.119261264801025</v>
+        <v>5.119260787963867</v>
       </c>
       <c r="C138" t="n">
-        <v>5.456405090261659</v>
+        <v>5.456404582021004</v>
       </c>
       <c r="D138" t="n">
-        <v>5.074900079271083</v>
+        <v>5.074899606565978</v>
       </c>
       <c r="E138" t="n">
-        <v>5.447532683931823</v>
+        <v>5.447532176517594</v>
       </c>
       <c r="F138" t="n">
         <v>8726900</v>
@@ -3232,16 +3232,16 @@
         <v>44616</v>
       </c>
       <c r="B141" t="n">
-        <v>5.119261264801025</v>
+        <v>5.119260787963867</v>
       </c>
       <c r="C141" t="n">
-        <v>5.137005654401078</v>
+        <v>5.137005175911107</v>
       </c>
       <c r="D141" t="n">
-        <v>4.773245456070175</v>
+        <v>4.7732450114629</v>
       </c>
       <c r="E141" t="n">
-        <v>4.924072979200438</v>
+        <v>4.924072520544229</v>
       </c>
       <c r="F141" t="n">
         <v>11357100</v>
@@ -3252,16 +3252,16 @@
         <v>44617</v>
       </c>
       <c r="B142" t="n">
-        <v>5.066027641296387</v>
+        <v>5.066028594970703</v>
       </c>
       <c r="C142" t="n">
-        <v>5.163621986866849</v>
+        <v>5.163622958913197</v>
       </c>
       <c r="D142" t="n">
-        <v>4.986177683733319</v>
+        <v>4.986178622375967</v>
       </c>
       <c r="E142" t="n">
-        <v>5.110388822844664</v>
+        <v>5.110389784869926</v>
       </c>
       <c r="F142" t="n">
         <v>6795000</v>
@@ -3272,16 +3272,16 @@
         <v>44622</v>
       </c>
       <c r="B143" t="n">
-        <v>5.314448833465576</v>
+        <v>5.314449310302734</v>
       </c>
       <c r="C143" t="n">
-        <v>5.349938030937696</v>
+        <v>5.349938510959111</v>
       </c>
       <c r="D143" t="n">
-        <v>5.030538638165109</v>
+        <v>5.03053908952852</v>
       </c>
       <c r="E143" t="n">
-        <v>5.101516186990226</v>
+        <v>5.101516644722073</v>
       </c>
       <c r="F143" t="n">
         <v>7030100</v>
@@ -3312,16 +3312,16 @@
         <v>44624</v>
       </c>
       <c r="B145" t="n">
-        <v>5.50963830947876</v>
+        <v>5.509637832641602</v>
       </c>
       <c r="C145" t="n">
-        <v>5.536254682592588</v>
+        <v>5.53625420345189</v>
       </c>
       <c r="D145" t="n">
-        <v>5.376555174730749</v>
+        <v>5.376554709411403</v>
       </c>
       <c r="E145" t="n">
-        <v>5.483021513305308</v>
+        <v>5.483021038771727</v>
       </c>
       <c r="F145" t="n">
         <v>9336900</v>
@@ -3332,16 +3332,16 @@
         <v>44627</v>
       </c>
       <c r="B146" t="n">
-        <v>5.48302173614502</v>
+        <v>5.483021259307861</v>
       </c>
       <c r="C146" t="n">
-        <v>5.5894885021062</v>
+        <v>5.58948801601004</v>
       </c>
       <c r="D146" t="n">
-        <v>5.403172190498684</v>
+        <v>5.403171720605732</v>
       </c>
       <c r="E146" t="n">
-        <v>5.491894142916634</v>
+        <v>5.491893665307877</v>
       </c>
       <c r="F146" t="n">
         <v>12429900</v>
@@ -3352,16 +3352,16 @@
         <v>44628</v>
       </c>
       <c r="B147" t="n">
-        <v>5.58948802947998</v>
+        <v>5.589488506317139</v>
       </c>
       <c r="C147" t="n">
-        <v>5.58948802947998</v>
+        <v>5.589488506317139</v>
       </c>
       <c r="D147" t="n">
-        <v>5.420916122609865</v>
+        <v>5.420916585066217</v>
       </c>
       <c r="E147" t="n">
-        <v>5.500765661504422</v>
+        <v>5.500766130772708</v>
       </c>
       <c r="F147" t="n">
         <v>5566500</v>
@@ -3372,16 +3372,16 @@
         <v>44629</v>
       </c>
       <c r="B148" t="n">
-        <v>5.695955276489258</v>
+        <v>5.695953845977783</v>
       </c>
       <c r="C148" t="n">
-        <v>5.704827260873306</v>
+        <v>5.704825828133675</v>
       </c>
       <c r="D148" t="n">
-        <v>5.554000141867114</v>
+        <v>5.553998747006981</v>
       </c>
       <c r="E148" t="n">
-        <v>5.58948892552265</v>
+        <v>5.589487521749682</v>
       </c>
       <c r="F148" t="n">
         <v>9079900</v>
@@ -3392,16 +3392,16 @@
         <v>44630</v>
       </c>
       <c r="B149" t="n">
-        <v>5.695955276489258</v>
+        <v>5.695953845977783</v>
       </c>
       <c r="C149" t="n">
-        <v>5.829038426727354</v>
+        <v>5.829036962792693</v>
       </c>
       <c r="D149" t="n">
-        <v>5.554000141867114</v>
+        <v>5.553998747006981</v>
       </c>
       <c r="E149" t="n">
-        <v>5.624977709178186</v>
+        <v>5.624976296492382</v>
       </c>
       <c r="F149" t="n">
         <v>15215200</v>
@@ -3412,16 +3412,16 @@
         <v>44631</v>
       </c>
       <c r="B150" t="n">
-        <v>5.59835958480835</v>
+        <v>5.598360538482666</v>
       </c>
       <c r="C150" t="n">
-        <v>5.979864130335345</v>
+        <v>5.979865148998535</v>
       </c>
       <c r="D150" t="n">
-        <v>5.527382034297241</v>
+        <v>5.52738297588061</v>
       </c>
       <c r="E150" t="n">
-        <v>5.69595392829091</v>
+        <v>5.695954898590315</v>
       </c>
       <c r="F150" t="n">
         <v>16712700</v>
@@ -3432,16 +3432,16 @@
         <v>44634</v>
       </c>
       <c r="B151" t="n">
-        <v>5.58948802947998</v>
+        <v>5.589488506317139</v>
       </c>
       <c r="C151" t="n">
-        <v>5.72257073532411</v>
+        <v>5.722571223514505</v>
       </c>
       <c r="D151" t="n">
-        <v>5.518510050487613</v>
+        <v>5.518510521269666</v>
       </c>
       <c r="E151" t="n">
-        <v>5.607232418463171</v>
+        <v>5.607232896814097</v>
       </c>
       <c r="F151" t="n">
         <v>7706100</v>
@@ -3452,16 +3452,16 @@
         <v>44635</v>
       </c>
       <c r="B152" t="n">
-        <v>5.651593208312988</v>
+        <v>5.651593685150146</v>
       </c>
       <c r="C152" t="n">
-        <v>5.687081986460981</v>
+        <v>5.687082466292404</v>
       </c>
       <c r="D152" t="n">
-        <v>5.500765689654214</v>
+        <v>5.500766153765728</v>
       </c>
       <c r="E152" t="n">
-        <v>5.509638095721016</v>
+        <v>5.509638560581113</v>
       </c>
       <c r="F152" t="n">
         <v>5880900</v>
@@ -3492,16 +3492,16 @@
         <v>44637</v>
       </c>
       <c r="B154" t="n">
-        <v>5.891142845153809</v>
+        <v>5.89114236831665</v>
       </c>
       <c r="C154" t="n">
-        <v>5.926631624342837</v>
+        <v>5.926631144633169</v>
       </c>
       <c r="D154" t="n">
-        <v>5.536254630203903</v>
+        <v>5.536254182091882</v>
       </c>
       <c r="E154" t="n">
-        <v>5.607232611641579</v>
+        <v>5.607232157784503</v>
       </c>
       <c r="F154" t="n">
         <v>10001800</v>
@@ -3512,16 +3512,16 @@
         <v>44638</v>
       </c>
       <c r="B155" t="n">
-        <v>6.20167064666748</v>
+        <v>6.201670169830322</v>
       </c>
       <c r="C155" t="n">
-        <v>6.20167064666748</v>
+        <v>6.201670169830322</v>
       </c>
       <c r="D155" t="n">
-        <v>5.891143578574458</v>
+        <v>5.891143125613262</v>
       </c>
       <c r="E155" t="n">
-        <v>5.891143578574458</v>
+        <v>5.891143125613262</v>
       </c>
       <c r="F155" t="n">
         <v>17710700</v>
@@ -3532,16 +3532,16 @@
         <v>44641</v>
       </c>
       <c r="B156" t="n">
-        <v>6.104076385498047</v>
+        <v>6.10407543182373</v>
       </c>
       <c r="C156" t="n">
-        <v>6.343625873905633</v>
+        <v>6.343624882805147</v>
       </c>
       <c r="D156" t="n">
-        <v>6.024226415008968</v>
+        <v>6.024225473810064</v>
       </c>
       <c r="E156" t="n">
-        <v>6.183925932927476</v>
+        <v>6.183924966777814</v>
       </c>
       <c r="F156" t="n">
         <v>14982100</v>
@@ -3552,16 +3552,16 @@
         <v>44642</v>
       </c>
       <c r="B157" t="n">
-        <v>6.299264430999756</v>
+        <v>6.299263477325439</v>
       </c>
       <c r="C157" t="n">
-        <v>6.308136837611495</v>
+        <v>6.308135882593944</v>
       </c>
       <c r="D157" t="n">
-        <v>6.07745934242188</v>
+        <v>6.077458422327646</v>
       </c>
       <c r="E157" t="n">
-        <v>6.07745934242188</v>
+        <v>6.077458422327646</v>
       </c>
       <c r="F157" t="n">
         <v>9703800</v>
@@ -3572,16 +3572,16 @@
         <v>44643</v>
       </c>
       <c r="B158" t="n">
-        <v>6.308136463165283</v>
+        <v>6.308136940002441</v>
       </c>
       <c r="C158" t="n">
-        <v>6.334752835301306</v>
+        <v>6.334753314150418</v>
       </c>
       <c r="D158" t="n">
-        <v>6.201669705442368</v>
+        <v>6.201670174231618</v>
       </c>
       <c r="E158" t="n">
-        <v>6.263775278859101</v>
+        <v>6.263775752342961</v>
       </c>
       <c r="F158" t="n">
         <v>8187500</v>
@@ -3612,16 +3612,16 @@
         <v>44645</v>
       </c>
       <c r="B160" t="n">
-        <v>6.45009183883667</v>
+        <v>6.450092315673828</v>
       </c>
       <c r="C160" t="n">
-        <v>6.512197414783683</v>
+        <v>6.512197896212132</v>
       </c>
       <c r="D160" t="n">
-        <v>6.237159160834839</v>
+        <v>6.237159621930483</v>
       </c>
       <c r="E160" t="n">
-        <v>6.343625499835754</v>
+        <v>6.343625968802155</v>
       </c>
       <c r="F160" t="n">
         <v>15324200</v>
@@ -3672,16 +3672,16 @@
         <v>44650</v>
       </c>
       <c r="B163" t="n">
-        <v>6.503325462341309</v>
+        <v>6.50332498550415</v>
       </c>
       <c r="C163" t="n">
-        <v>6.618664215840703</v>
+        <v>6.61866373054667</v>
       </c>
       <c r="D163" t="n">
-        <v>6.450092289124586</v>
+        <v>6.450091816190593</v>
       </c>
       <c r="E163" t="n">
-        <v>6.547686651551738</v>
+        <v>6.547686171461927</v>
       </c>
       <c r="F163" t="n">
         <v>10697600</v>
@@ -3712,16 +3712,16 @@
         <v>44652</v>
       </c>
       <c r="B165" t="n">
-        <v>6.139564514160156</v>
+        <v>6.139564990997314</v>
       </c>
       <c r="C165" t="n">
-        <v>6.299264015090594</v>
+        <v>6.299264504331019</v>
       </c>
       <c r="D165" t="n">
-        <v>5.926631423193302</v>
+        <v>5.926631883492739</v>
       </c>
       <c r="E165" t="n">
-        <v>6.254903254139719</v>
+        <v>6.254903739934808</v>
       </c>
       <c r="F165" t="n">
         <v>18919700</v>
@@ -3732,16 +3732,16 @@
         <v>44655</v>
       </c>
       <c r="B166" t="n">
-        <v>6.21054220199585</v>
+        <v>6.210542678833008</v>
       </c>
       <c r="C166" t="n">
-        <v>6.237158997579204</v>
+        <v>6.237159476459965</v>
       </c>
       <c r="D166" t="n">
-        <v>6.050842697674559</v>
+        <v>6.050843162250203</v>
       </c>
       <c r="E166" t="n">
-        <v>6.157309033888753</v>
+        <v>6.15730950663874</v>
       </c>
       <c r="F166" t="n">
         <v>13343800</v>
@@ -3752,16 +3752,16 @@
         <v>44656</v>
       </c>
       <c r="B167" t="n">
-        <v>6.299264430999756</v>
+        <v>6.299263477325439</v>
       </c>
       <c r="C167" t="n">
-        <v>6.32588122777534</v>
+        <v>6.325880270071385</v>
       </c>
       <c r="D167" t="n">
-        <v>6.148436903077259</v>
+        <v>6.148435972237409</v>
       </c>
       <c r="E167" t="n">
-        <v>6.228286870344377</v>
+        <v>6.228285927415676</v>
       </c>
       <c r="F167" t="n">
         <v>6962400</v>
@@ -3772,16 +3772,16 @@
         <v>44657</v>
       </c>
       <c r="B168" t="n">
-        <v>6.350711345672607</v>
+        <v>6.350711822509766</v>
       </c>
       <c r="C168" t="n">
-        <v>6.39524623280219</v>
+        <v>6.395246712983208</v>
       </c>
       <c r="D168" t="n">
-        <v>6.136942443401892</v>
+        <v>6.136942904188415</v>
       </c>
       <c r="E168" t="n">
-        <v>6.243827106897355</v>
+        <v>6.243827575709211</v>
       </c>
       <c r="F168" t="n">
         <v>10002000</v>
@@ -3832,16 +3832,16 @@
         <v>44662</v>
       </c>
       <c r="B171" t="n">
-        <v>6.145850658416748</v>
+        <v>6.14585018157959</v>
       </c>
       <c r="C171" t="n">
-        <v>6.21710682899452</v>
+        <v>6.21710634662882</v>
       </c>
       <c r="D171" t="n">
-        <v>6.021152359905646</v>
+        <v>6.021151892743435</v>
       </c>
       <c r="E171" t="n">
-        <v>6.119129382089944</v>
+        <v>6.119128907326005</v>
       </c>
       <c r="F171" t="n">
         <v>4955900</v>
@@ -3912,16 +3912,16 @@
         <v>44669</v>
       </c>
       <c r="B175" t="n">
-        <v>6.350711345672607</v>
+        <v>6.350711822509766</v>
       </c>
       <c r="C175" t="n">
-        <v>6.39524623280219</v>
+        <v>6.395246712983208</v>
       </c>
       <c r="D175" t="n">
-        <v>6.190384562789519</v>
+        <v>6.190385027588691</v>
       </c>
       <c r="E175" t="n">
-        <v>6.315083266080856</v>
+        <v>6.315083740242914</v>
       </c>
       <c r="F175" t="n">
         <v>6987700</v>
@@ -3972,16 +3972,16 @@
         <v>44673</v>
       </c>
       <c r="B178" t="n">
-        <v>6.128036499023438</v>
+        <v>6.128035545349121</v>
       </c>
       <c r="C178" t="n">
-        <v>6.190385434731002</v>
+        <v>6.190384471353647</v>
       </c>
       <c r="D178" t="n">
-        <v>5.98552373586271</v>
+        <v>5.98552280436691</v>
       </c>
       <c r="E178" t="n">
-        <v>6.136943307815831</v>
+        <v>6.136942352755394</v>
       </c>
       <c r="F178" t="n">
         <v>9926800</v>
@@ -4012,16 +4012,16 @@
         <v>44677</v>
       </c>
       <c r="B180" t="n">
-        <v>6.252734661102295</v>
+        <v>6.252734184265137</v>
       </c>
       <c r="C180" t="n">
-        <v>6.33289806211651</v>
+        <v>6.332897579166045</v>
       </c>
       <c r="D180" t="n">
-        <v>6.11912913431869</v>
+        <v>6.119128667670365</v>
       </c>
       <c r="E180" t="n">
-        <v>6.243827852500861</v>
+        <v>6.24382737634294</v>
       </c>
       <c r="F180" t="n">
         <v>9190800</v>
@@ -4032,16 +4032,16 @@
         <v>44678</v>
       </c>
       <c r="B181" t="n">
-        <v>6.332897186279297</v>
+        <v>6.332897663116455</v>
       </c>
       <c r="C181" t="n">
-        <v>6.359618033108378</v>
+        <v>6.35961851195749</v>
       </c>
       <c r="D181" t="n">
-        <v>6.208198485342908</v>
+        <v>6.208198952790844</v>
       </c>
       <c r="E181" t="n">
-        <v>6.288361875270557</v>
+        <v>6.288362348754418</v>
       </c>
       <c r="F181" t="n">
         <v>11357200</v>
@@ -4072,16 +4072,16 @@
         <v>44680</v>
       </c>
       <c r="B183" t="n">
-        <v>6.145850658416748</v>
+        <v>6.14585018157959</v>
       </c>
       <c r="C183" t="n">
-        <v>6.44868938337228</v>
+        <v>6.44868888303882</v>
       </c>
       <c r="D183" t="n">
-        <v>6.065687254156614</v>
+        <v>6.065686783539082</v>
       </c>
       <c r="E183" t="n">
-        <v>6.413061298083393</v>
+        <v>6.413060800514205</v>
       </c>
       <c r="F183" t="n">
         <v>21979100</v>
@@ -4092,16 +4092,16 @@
         <v>44683</v>
       </c>
       <c r="B184" t="n">
-        <v>5.86973237991333</v>
+        <v>5.869731903076172</v>
       </c>
       <c r="C184" t="n">
-        <v>6.19038512538046</v>
+        <v>6.19038462249456</v>
       </c>
       <c r="D184" t="n">
-        <v>5.745033665289197</v>
+        <v>5.745033198582139</v>
       </c>
       <c r="E184" t="n">
-        <v>6.145850234203484</v>
+        <v>6.145849734935447</v>
       </c>
       <c r="F184" t="n">
         <v>12404500</v>
@@ -4112,16 +4112,16 @@
         <v>44684</v>
       </c>
       <c r="B185" t="n">
-        <v>5.522357940673828</v>
+        <v>5.52235746383667</v>
       </c>
       <c r="C185" t="n">
-        <v>5.905360468549889</v>
+        <v>5.905359958641743</v>
       </c>
       <c r="D185" t="n">
-        <v>5.228426044679804</v>
+        <v>5.228425593222683</v>
       </c>
       <c r="E185" t="n">
-        <v>5.905360468549889</v>
+        <v>5.905359958641743</v>
       </c>
       <c r="F185" t="n">
         <v>36500900</v>
@@ -4132,16 +4132,16 @@
         <v>44685</v>
       </c>
       <c r="B186" t="n">
-        <v>5.388753414154053</v>
+        <v>5.388752460479736</v>
       </c>
       <c r="C186" t="n">
-        <v>5.513451717413731</v>
+        <v>5.51345074167094</v>
       </c>
       <c r="D186" t="n">
-        <v>5.210612556205647</v>
+        <v>5.210611634057798</v>
       </c>
       <c r="E186" t="n">
-        <v>5.513451717413731</v>
+        <v>5.51345074167094</v>
       </c>
       <c r="F186" t="n">
         <v>18834300</v>
@@ -4172,16 +4172,16 @@
         <v>44687</v>
       </c>
       <c r="B188" t="n">
-        <v>4.95230770111084</v>
+        <v>4.952308654785156</v>
       </c>
       <c r="C188" t="n">
-        <v>5.068099171347654</v>
+        <v>5.068100147320131</v>
       </c>
       <c r="D188" t="n">
-        <v>4.863237502744139</v>
+        <v>4.863238439266056</v>
       </c>
       <c r="E188" t="n">
-        <v>4.97012174078418</v>
+        <v>4.970122697888977</v>
       </c>
       <c r="F188" t="n">
         <v>14479200</v>
@@ -4212,16 +4212,16 @@
         <v>44691</v>
       </c>
       <c r="B190" t="n">
-        <v>4.631655216217041</v>
+        <v>4.631654739379883</v>
       </c>
       <c r="C190" t="n">
-        <v>4.7118186184255</v>
+        <v>4.711818133335377</v>
       </c>
       <c r="D190" t="n">
-        <v>4.569306280917366</v>
+        <v>4.569305810499142</v>
       </c>
       <c r="E190" t="n">
-        <v>4.65837649185995</v>
+        <v>4.658376012271789</v>
       </c>
       <c r="F190" t="n">
         <v>9825600</v>
@@ -4232,16 +4232,16 @@
         <v>44692</v>
       </c>
       <c r="B191" t="n">
-        <v>4.640562534332275</v>
+        <v>4.640562057495117</v>
       </c>
       <c r="C191" t="n">
-        <v>4.694004661872806</v>
+        <v>4.694004179544246</v>
       </c>
       <c r="D191" t="n">
-        <v>4.489142960607302</v>
+        <v>4.489142499329136</v>
       </c>
       <c r="E191" t="n">
-        <v>4.640562534332275</v>
+        <v>4.640562057495117</v>
       </c>
       <c r="F191" t="n">
         <v>17331100</v>
@@ -4252,16 +4252,16 @@
         <v>44693</v>
       </c>
       <c r="B192" t="n">
-        <v>4.791981220245361</v>
+        <v>4.79198169708252</v>
       </c>
       <c r="C192" t="n">
-        <v>4.809795259458459</v>
+        <v>4.809795738068244</v>
       </c>
       <c r="D192" t="n">
-        <v>4.551491478508448</v>
+        <v>4.55149193141512</v>
       </c>
       <c r="E192" t="n">
-        <v>4.587119556934643</v>
+        <v>4.587120013386569</v>
       </c>
       <c r="F192" t="n">
         <v>13350100</v>
@@ -4272,16 +4272,16 @@
         <v>44694</v>
       </c>
       <c r="B193" t="n">
-        <v>4.604934215545654</v>
+        <v>4.604933738708496</v>
       </c>
       <c r="C193" t="n">
-        <v>4.800888673247058</v>
+        <v>4.800888176118977</v>
       </c>
       <c r="D193" t="n">
-        <v>4.515864007499562</v>
+        <v>4.51586353988555</v>
       </c>
       <c r="E193" t="n">
-        <v>4.800888673247058</v>
+        <v>4.800888176118977</v>
       </c>
       <c r="F193" t="n">
         <v>51332400</v>
@@ -4332,16 +4332,16 @@
         <v>44699</v>
       </c>
       <c r="B196" t="n">
-        <v>4.95230770111084</v>
+        <v>4.952308654785156</v>
       </c>
       <c r="C196" t="n">
-        <v>5.112634058170901</v>
+        <v>5.112635042719536</v>
       </c>
       <c r="D196" t="n">
-        <v>4.89886558209082</v>
+        <v>4.898866525473696</v>
       </c>
       <c r="E196" t="n">
-        <v>4.98793578045752</v>
+        <v>4.987936740992796</v>
       </c>
       <c r="F196" t="n">
         <v>17779600</v>
@@ -4352,16 +4352,16 @@
         <v>44700</v>
       </c>
       <c r="B197" t="n">
-        <v>5.050285816192627</v>
+        <v>5.050285339355469</v>
       </c>
       <c r="C197" t="n">
-        <v>5.183891344211743</v>
+        <v>5.183890854759837</v>
       </c>
       <c r="D197" t="n">
-        <v>4.898866246085646</v>
+        <v>4.898865783545199</v>
       </c>
       <c r="E197" t="n">
-        <v>4.987936456524968</v>
+        <v>4.987935985574703</v>
       </c>
       <c r="F197" t="n">
         <v>12233400</v>
@@ -4372,16 +4372,16 @@
         <v>44701</v>
       </c>
       <c r="B198" t="n">
-        <v>4.934494495391846</v>
+        <v>4.934494018554688</v>
       </c>
       <c r="C198" t="n">
-        <v>5.121542155934015</v>
+        <v>5.121541661021799</v>
       </c>
       <c r="D198" t="n">
-        <v>4.82761023928783</v>
+        <v>4.827609772779264</v>
       </c>
       <c r="E198" t="n">
-        <v>5.09482087954787</v>
+        <v>5.094820387217823</v>
       </c>
       <c r="F198" t="n">
         <v>10517400</v>
@@ -4392,16 +4392,16 @@
         <v>44704</v>
       </c>
       <c r="B199" t="n">
-        <v>5.023563861846924</v>
+        <v>5.023565292358398</v>
       </c>
       <c r="C199" t="n">
-        <v>5.103727252769655</v>
+        <v>5.10372870610848</v>
       </c>
       <c r="D199" t="n">
-        <v>4.881051544402253</v>
+        <v>4.88105293433188</v>
       </c>
       <c r="E199" t="n">
-        <v>4.979028975005568</v>
+        <v>4.979030392835275</v>
       </c>
       <c r="F199" t="n">
         <v>11444200</v>
@@ -4432,16 +4432,16 @@
         <v>44706</v>
       </c>
       <c r="B201" t="n">
-        <v>5.272960662841797</v>
+        <v>5.272961139678955</v>
       </c>
       <c r="C201" t="n">
-        <v>5.326402780066791</v>
+        <v>5.326403261736754</v>
       </c>
       <c r="D201" t="n">
-        <v>5.112633886446619</v>
+        <v>5.112634348785326</v>
       </c>
       <c r="E201" t="n">
-        <v>5.148262389316809</v>
+        <v>5.148262854877424</v>
       </c>
       <c r="F201" t="n">
         <v>9738900</v>
@@ -4472,16 +4472,16 @@
         <v>44708</v>
       </c>
       <c r="B203" t="n">
-        <v>5.406566143035889</v>
+        <v>5.406566619873047</v>
       </c>
       <c r="C203" t="n">
-        <v>5.58470653295462</v>
+        <v>5.584707025503037</v>
       </c>
       <c r="D203" t="n">
-        <v>5.388752104044015</v>
+        <v>5.388752579310048</v>
       </c>
       <c r="E203" t="n">
-        <v>5.522357184122968</v>
+        <v>5.522357671172426</v>
       </c>
       <c r="F203" t="n">
         <v>11400800</v>
@@ -4492,16 +4492,16 @@
         <v>44711</v>
       </c>
       <c r="B204" t="n">
-        <v>5.602520942687988</v>
+        <v>5.602521419525146</v>
       </c>
       <c r="C204" t="n">
-        <v>5.67377710337079</v>
+        <v>5.673777586272644</v>
       </c>
       <c r="D204" t="n">
-        <v>5.317495875236564</v>
+        <v>5.317496327814903</v>
       </c>
       <c r="E204" t="n">
-        <v>5.460008621322386</v>
+        <v>5.460009086030153</v>
       </c>
       <c r="F204" t="n">
         <v>7527500</v>
@@ -4512,16 +4512,16 @@
         <v>44712</v>
       </c>
       <c r="B205" t="n">
-        <v>5.460009098052979</v>
+        <v>5.46000862121582</v>
       </c>
       <c r="C205" t="n">
-        <v>5.691591640492284</v>
+        <v>5.691591143430404</v>
       </c>
       <c r="D205" t="n">
-        <v>5.460009098052979</v>
+        <v>5.46000862121582</v>
       </c>
       <c r="E205" t="n">
-        <v>5.629242706811061</v>
+        <v>5.62924221519428</v>
       </c>
       <c r="F205" t="n">
         <v>13931800</v>
@@ -4532,16 +4532,16 @@
         <v>44713</v>
       </c>
       <c r="B206" t="n">
-        <v>5.513451099395752</v>
+        <v>5.513450622558594</v>
       </c>
       <c r="C206" t="n">
-        <v>5.549079182047723</v>
+        <v>5.54907870212923</v>
       </c>
       <c r="D206" t="n">
-        <v>5.406566851439836</v>
+        <v>5.406566383846685</v>
       </c>
       <c r="E206" t="n">
-        <v>5.495637058069765</v>
+        <v>5.495636582773276</v>
       </c>
       <c r="F206" t="n">
         <v>9091200</v>
@@ -4572,16 +4572,16 @@
         <v>44715</v>
       </c>
       <c r="B208" t="n">
-        <v>5.513451099395752</v>
+        <v>5.513450622558594</v>
       </c>
       <c r="C208" t="n">
-        <v>5.602521306025682</v>
+        <v>5.602520821485185</v>
       </c>
       <c r="D208" t="n">
-        <v>5.451101742394677</v>
+        <v>5.451101270949875</v>
       </c>
       <c r="E208" t="n">
-        <v>5.575800456396826</v>
+        <v>5.575799974167312</v>
       </c>
       <c r="F208" t="n">
         <v>9326300</v>
@@ -4612,16 +4612,16 @@
         <v>44719</v>
       </c>
       <c r="B210" t="n">
-        <v>5.023563861846924</v>
+        <v>5.023565292358398</v>
       </c>
       <c r="C210" t="n">
-        <v>5.299681689256077</v>
+        <v>5.299683198394942</v>
       </c>
       <c r="D210" t="n">
-        <v>4.987935782485756</v>
+        <v>4.987937202851769</v>
       </c>
       <c r="E210" t="n">
-        <v>5.281867649575493</v>
+        <v>5.281869153641628</v>
       </c>
       <c r="F210" t="n">
         <v>18881300</v>
@@ -4632,16 +4632,16 @@
         <v>44720</v>
       </c>
       <c r="B211" t="n">
-        <v>4.916679859161377</v>
+        <v>4.916679382324219</v>
       </c>
       <c r="C211" t="n">
-        <v>5.005750061828747</v>
+        <v>5.005749576353243</v>
       </c>
       <c r="D211" t="n">
-        <v>4.783074342800206</v>
+        <v>4.783073878920588</v>
       </c>
       <c r="E211" t="n">
-        <v>4.996843253922124</v>
+        <v>4.996842769310434</v>
       </c>
       <c r="F211" t="n">
         <v>13996400</v>
@@ -4652,16 +4652,16 @@
         <v>44721</v>
       </c>
       <c r="B212" t="n">
-        <v>4.818702697753906</v>
+        <v>4.818703174591064</v>
       </c>
       <c r="C212" t="n">
-        <v>4.996843537934095</v>
+        <v>4.996844032399269</v>
       </c>
       <c r="D212" t="n">
-        <v>4.809795889341036</v>
+        <v>4.809796365296816</v>
       </c>
       <c r="E212" t="n">
-        <v>4.88105205552501</v>
+        <v>4.88105253853198</v>
       </c>
       <c r="F212" t="n">
         <v>8480000</v>
@@ -4712,16 +4712,16 @@
         <v>44726</v>
       </c>
       <c r="B215" t="n">
-        <v>4.462421417236328</v>
+        <v>4.462421894073486</v>
       </c>
       <c r="C215" t="n">
-        <v>4.640561814748269</v>
+        <v>4.640562310620824</v>
       </c>
       <c r="D215" t="n">
-        <v>4.453514185000626</v>
+        <v>4.453514660885992</v>
       </c>
       <c r="E215" t="n">
-        <v>4.587119695494687</v>
+        <v>4.587120185656623</v>
       </c>
       <c r="F215" t="n">
         <v>9819800</v>
@@ -4732,16 +4732,16 @@
         <v>44727</v>
       </c>
       <c r="B216" t="n">
-        <v>4.560399532318115</v>
+        <v>4.560399055480957</v>
       </c>
       <c r="C216" t="n">
-        <v>4.649469752730517</v>
+        <v>4.649469266580143</v>
       </c>
       <c r="D216" t="n">
-        <v>4.480236546307109</v>
+        <v>4.480236077851825</v>
       </c>
       <c r="E216" t="n">
-        <v>4.542585488235635</v>
+        <v>4.54258501326112</v>
       </c>
       <c r="F216" t="n">
         <v>10830000</v>
@@ -4752,16 +4752,16 @@
         <v>44729</v>
       </c>
       <c r="B217" t="n">
-        <v>4.524771213531494</v>
+        <v>4.524770736694336</v>
       </c>
       <c r="C217" t="n">
-        <v>4.524771213531494</v>
+        <v>4.524770736694336</v>
       </c>
       <c r="D217" t="n">
-        <v>4.311002695437231</v>
+        <v>4.311002241127791</v>
       </c>
       <c r="E217" t="n">
-        <v>4.506957170356972</v>
+        <v>4.506956695397124</v>
       </c>
       <c r="F217" t="n">
         <v>10891400</v>
@@ -4772,16 +4772,16 @@
         <v>44732</v>
       </c>
       <c r="B218" t="n">
-        <v>4.524771213531494</v>
+        <v>4.524770736694336</v>
       </c>
       <c r="C218" t="n">
-        <v>4.649469515753148</v>
+        <v>4.64946902577482</v>
       </c>
       <c r="D218" t="n">
-        <v>4.453515040833406</v>
+        <v>4.453514571505488</v>
       </c>
       <c r="E218" t="n">
-        <v>4.524771213531494</v>
+        <v>4.524770736694336</v>
       </c>
       <c r="F218" t="n">
         <v>7841400</v>
@@ -4812,16 +4812,16 @@
         <v>44734</v>
       </c>
       <c r="B220" t="n">
-        <v>4.444606304168701</v>
+        <v>4.444606781005859</v>
       </c>
       <c r="C220" t="n">
-        <v>4.533676914646911</v>
+        <v>4.53367740103996</v>
       </c>
       <c r="D220" t="n">
-        <v>4.400071423649744</v>
+        <v>4.400071895709002</v>
       </c>
       <c r="E220" t="n">
-        <v>4.480234803192074</v>
+        <v>4.480235283851616</v>
       </c>
       <c r="F220" t="n">
         <v>8433900</v>
@@ -4852,16 +4852,16 @@
         <v>44736</v>
       </c>
       <c r="B222" t="n">
-        <v>4.257560253143311</v>
+        <v>4.257559776306152</v>
       </c>
       <c r="C222" t="n">
-        <v>4.337723229179554</v>
+        <v>4.337722743364323</v>
       </c>
       <c r="D222" t="n">
-        <v>4.23083897798439</v>
+        <v>4.230838504139954</v>
       </c>
       <c r="E222" t="n">
-        <v>4.319909187313693</v>
+        <v>4.319908703493595</v>
       </c>
       <c r="F222" t="n">
         <v>7941200</v>
@@ -4892,16 +4892,16 @@
         <v>44740</v>
       </c>
       <c r="B224" t="n">
-        <v>4.293188095092773</v>
+        <v>4.293188571929932</v>
       </c>
       <c r="C224" t="n">
-        <v>4.471328503718931</v>
+        <v>4.471329000341845</v>
       </c>
       <c r="D224" t="n">
-        <v>4.293188095092773</v>
+        <v>4.293188571929932</v>
       </c>
       <c r="E224" t="n">
-        <v>4.319908944026579</v>
+        <v>4.319909423831577</v>
       </c>
       <c r="F224" t="n">
         <v>8975600</v>
@@ -4932,16 +4932,16 @@
         <v>44742</v>
       </c>
       <c r="B226" t="n">
-        <v>4.088325977325439</v>
+        <v>4.088326930999756</v>
       </c>
       <c r="C226" t="n">
-        <v>4.239745520888632</v>
+        <v>4.239746509884235</v>
       </c>
       <c r="D226" t="n">
-        <v>4.052697899395299</v>
+        <v>4.052698844758736</v>
       </c>
       <c r="E226" t="n">
-        <v>4.239745520888632</v>
+        <v>4.239746509884235</v>
       </c>
       <c r="F226" t="n">
         <v>6721700</v>
@@ -4952,16 +4952,16 @@
         <v>44743</v>
       </c>
       <c r="B227" t="n">
-        <v>4.025976657867432</v>
+        <v>4.02597713470459</v>
       </c>
       <c r="C227" t="n">
-        <v>4.186303009719074</v>
+        <v>4.186303505545305</v>
       </c>
       <c r="D227" t="n">
-        <v>4.025976657867432</v>
+        <v>4.02597713470459</v>
       </c>
       <c r="E227" t="n">
-        <v>4.025976657867432</v>
+        <v>4.02597713470459</v>
       </c>
       <c r="F227" t="n">
         <v>12849200</v>
@@ -4972,16 +4972,16 @@
         <v>44746</v>
       </c>
       <c r="B228" t="n">
-        <v>4.043790340423584</v>
+        <v>4.043790817260742</v>
       </c>
       <c r="C228" t="n">
-        <v>4.195209871737444</v>
+        <v>4.195210366429746</v>
       </c>
       <c r="D228" t="n">
-        <v>4.008162265375636</v>
+        <v>4.008162738011589</v>
       </c>
       <c r="E228" t="n">
-        <v>4.034883534021676</v>
+        <v>4.034884009808557</v>
       </c>
       <c r="F228" t="n">
         <v>5003300</v>
@@ -4992,16 +4992,16 @@
         <v>44747</v>
       </c>
       <c r="B229" t="n">
-        <v>4.034883975982666</v>
+        <v>4.034884452819824</v>
       </c>
       <c r="C229" t="n">
-        <v>4.061604822835417</v>
+        <v>4.061605302830409</v>
       </c>
       <c r="D229" t="n">
-        <v>3.901278467558302</v>
+        <v>3.901278928606141</v>
       </c>
       <c r="E229" t="n">
-        <v>4.061604822835417</v>
+        <v>4.061605302830409</v>
       </c>
       <c r="F229" t="n">
         <v>9503300</v>
@@ -5032,16 +5032,16 @@
         <v>44749</v>
       </c>
       <c r="B231" t="n">
-        <v>4.052698135375977</v>
+        <v>4.052698612213135</v>
       </c>
       <c r="C231" t="n">
-        <v>4.141768335387711</v>
+        <v>4.141768822704797</v>
       </c>
       <c r="D231" t="n">
-        <v>3.927999430639332</v>
+        <v>3.927999892804543</v>
       </c>
       <c r="E231" t="n">
-        <v>3.927999430639332</v>
+        <v>3.927999892804543</v>
       </c>
       <c r="F231" t="n">
         <v>10027800</v>
@@ -5072,16 +5072,16 @@
         <v>44753</v>
       </c>
       <c r="B233" t="n">
-        <v>3.705323696136475</v>
+        <v>3.705323934555054</v>
       </c>
       <c r="C233" t="n">
-        <v>3.901278559713046</v>
+        <v>3.901278810740315</v>
       </c>
       <c r="D233" t="n">
-        <v>3.678602848652532</v>
+        <v>3.678603085351762</v>
       </c>
       <c r="E233" t="n">
-        <v>3.892371327404923</v>
+        <v>3.892371577859058</v>
       </c>
       <c r="F233" t="n">
         <v>13261200</v>
@@ -5092,16 +5092,16 @@
         <v>44754</v>
       </c>
       <c r="B234" t="n">
-        <v>3.580625534057617</v>
+        <v>3.580625295639038</v>
       </c>
       <c r="C234" t="n">
-        <v>3.705323817411202</v>
+        <v>3.705323570689496</v>
       </c>
       <c r="D234" t="n">
-        <v>3.580625534057617</v>
+        <v>3.580625295639038</v>
       </c>
       <c r="E234" t="n">
-        <v>3.696417009531774</v>
+        <v>3.696416763403135</v>
       </c>
       <c r="F234" t="n">
         <v>14771600</v>
@@ -5112,16 +5112,16 @@
         <v>44755</v>
       </c>
       <c r="B235" t="n">
-        <v>3.687510013580322</v>
+        <v>3.687510251998901</v>
       </c>
       <c r="C235" t="n">
-        <v>3.723138096824944</v>
+        <v>3.723138337547081</v>
       </c>
       <c r="D235" t="n">
-        <v>3.473741514112596</v>
+        <v>3.47374173870982</v>
       </c>
       <c r="E235" t="n">
-        <v>3.589532997017741</v>
+        <v>3.589533229101546</v>
       </c>
       <c r="F235" t="n">
         <v>14925600</v>
@@ -5132,16 +5132,16 @@
         <v>44756</v>
       </c>
       <c r="B236" t="n">
-        <v>3.821115732192993</v>
+        <v>3.821115493774414</v>
       </c>
       <c r="C236" t="n">
-        <v>3.856743817247265</v>
+        <v>3.856743576605671</v>
       </c>
       <c r="D236" t="n">
-        <v>3.651882115825064</v>
+        <v>3.651881887965819</v>
       </c>
       <c r="E236" t="n">
-        <v>3.687510200879336</v>
+        <v>3.687509970797076</v>
       </c>
       <c r="F236" t="n">
         <v>9774500</v>
@@ -5152,16 +5152,16 @@
         <v>44757</v>
       </c>
       <c r="B237" t="n">
-        <v>3.936906814575195</v>
+        <v>3.936907052993774</v>
       </c>
       <c r="C237" t="n">
-        <v>3.9547208552634</v>
+        <v>3.954721094760794</v>
       </c>
       <c r="D237" t="n">
-        <v>3.776580023661126</v>
+        <v>3.776580252370335</v>
       </c>
       <c r="E237" t="n">
-        <v>3.830022570445971</v>
+        <v>3.830022802391653</v>
       </c>
       <c r="F237" t="n">
         <v>4881500</v>
@@ -5172,16 +5172,16 @@
         <v>44760</v>
       </c>
       <c r="B238" t="n">
-        <v>3.830022811889648</v>
+        <v>3.830022096633911</v>
       </c>
       <c r="C238" t="n">
-        <v>4.088326630512132</v>
+        <v>4.088325867018225</v>
       </c>
       <c r="D238" t="n">
-        <v>3.830022811889648</v>
+        <v>3.830022096633911</v>
       </c>
       <c r="E238" t="n">
-        <v>3.99034918819042</v>
+        <v>3.990348442993775</v>
       </c>
       <c r="F238" t="n">
         <v>5011900</v>
@@ -5192,16 +5192,16 @@
         <v>44761</v>
       </c>
       <c r="B239" t="n">
-        <v>3.856743574142456</v>
+        <v>3.856743812561035</v>
       </c>
       <c r="C239" t="n">
-        <v>3.93690697282171</v>
+        <v>3.93690721619588</v>
       </c>
       <c r="D239" t="n">
-        <v>3.830022724396204</v>
+        <v>3.830022961162937</v>
       </c>
       <c r="E239" t="n">
-        <v>3.838929532738205</v>
+        <v>3.838929770055544</v>
       </c>
       <c r="F239" t="n">
         <v>5270100</v>
@@ -5212,16 +5212,16 @@
         <v>44762</v>
       </c>
       <c r="B240" t="n">
-        <v>3.999256372451782</v>
+        <v>3.999255657196045</v>
       </c>
       <c r="C240" t="n">
-        <v>4.025977650039076</v>
+        <v>4.025976930004314</v>
       </c>
       <c r="D240" t="n">
-        <v>3.803301894119392</v>
+        <v>3.803301213909561</v>
       </c>
       <c r="E240" t="n">
-        <v>3.830023171706685</v>
+        <v>3.830022486717829</v>
       </c>
       <c r="F240" t="n">
         <v>11021800</v>
@@ -5252,16 +5252,16 @@
         <v>44764</v>
       </c>
       <c r="B242" t="n">
-        <v>3.740952253341675</v>
+        <v>3.740952014923096</v>
       </c>
       <c r="C242" t="n">
-        <v>3.999256077158491</v>
+        <v>3.999255822277678</v>
       </c>
       <c r="D242" t="n">
-        <v>3.740952253341675</v>
+        <v>3.740952014923096</v>
       </c>
       <c r="E242" t="n">
-        <v>3.999256077158491</v>
+        <v>3.999255822277678</v>
       </c>
       <c r="F242" t="n">
         <v>6536400</v>
@@ -5272,16 +5272,16 @@
         <v>44767</v>
       </c>
       <c r="B243" t="n">
-        <v>3.696417331695557</v>
+        <v>3.696416616439819</v>
       </c>
       <c r="C243" t="n">
-        <v>3.78548754185395</v>
+        <v>3.785486809363151</v>
       </c>
       <c r="D243" t="n">
-        <v>3.651882014256228</v>
+        <v>3.651881307618063</v>
       </c>
       <c r="E243" t="n">
-        <v>3.767673499822271</v>
+        <v>3.767672770778485</v>
       </c>
       <c r="F243" t="n">
         <v>10514300</v>
@@ -5292,16 +5292,16 @@
         <v>44768</v>
       </c>
       <c r="B244" t="n">
-        <v>3.714231491088867</v>
+        <v>3.714231252670288</v>
       </c>
       <c r="C244" t="n">
-        <v>3.812208937719106</v>
+        <v>3.8122086930113</v>
       </c>
       <c r="D244" t="n">
-        <v>3.66969617224232</v>
+        <v>3.669695936682488</v>
       </c>
       <c r="E244" t="n">
-        <v>3.705324257431447</v>
+        <v>3.705324019584628</v>
       </c>
       <c r="F244" t="n">
         <v>4594100</v>
@@ -5312,16 +5312,16 @@
         <v>44769</v>
       </c>
       <c r="B245" t="n">
-        <v>3.999256372451782</v>
+        <v>3.999255657196045</v>
       </c>
       <c r="C245" t="n">
-        <v>3.999256372451782</v>
+        <v>3.999255657196045</v>
       </c>
       <c r="D245" t="n">
-        <v>3.72313848607781</v>
+        <v>3.723137820204979</v>
       </c>
       <c r="E245" t="n">
-        <v>3.740952529562573</v>
+        <v>3.74095186050375</v>
       </c>
       <c r="F245" t="n">
         <v>8689000</v>
@@ -5332,16 +5332,16 @@
         <v>44770</v>
       </c>
       <c r="B246" t="n">
-        <v>3.999256372451782</v>
+        <v>3.999255657196045</v>
       </c>
       <c r="C246" t="n">
-        <v>4.070512971111132</v>
+        <v>4.070512243111353</v>
       </c>
       <c r="D246" t="n">
-        <v>3.892372111543206</v>
+        <v>3.892371415403418</v>
       </c>
       <c r="E246" t="n">
-        <v>4.025977650039076</v>
+        <v>4.025976930004314</v>
       </c>
       <c r="F246" t="n">
         <v>3634200</v>
@@ -5352,16 +5352,16 @@
         <v>44771</v>
       </c>
       <c r="B247" t="n">
-        <v>3.927999973297119</v>
+        <v>3.927999019622803</v>
       </c>
       <c r="C247" t="n">
-        <v>4.088326780187793</v>
+        <v>4.088325787587928</v>
       </c>
       <c r="D247" t="n">
-        <v>3.919093164425567</v>
+        <v>3.919092212913724</v>
       </c>
       <c r="E247" t="n">
-        <v>4.025977419205834</v>
+        <v>4.025976441743693</v>
       </c>
       <c r="F247" t="n">
         <v>8694600</v>
@@ -5372,16 +5372,16 @@
         <v>44774</v>
       </c>
       <c r="B248" t="n">
-        <v>3.927999973297119</v>
+        <v>3.927999019622803</v>
       </c>
       <c r="C248" t="n">
-        <v>3.990349334279078</v>
+        <v>3.990348365467037</v>
       </c>
       <c r="D248" t="n">
-        <v>3.874557845906986</v>
+        <v>3.874556905207819</v>
       </c>
       <c r="E248" t="n">
-        <v>3.981442100687252</v>
+        <v>3.981441134037787</v>
       </c>
       <c r="F248" t="n">
         <v>7696400</v>
@@ -5392,16 +5392,16 @@
         <v>44775</v>
       </c>
       <c r="B249" t="n">
-        <v>4.106140613555908</v>
+        <v>4.10614013671875</v>
       </c>
       <c r="C249" t="n">
-        <v>4.115047421973903</v>
+        <v>4.115046944102415</v>
       </c>
       <c r="D249" t="n">
-        <v>3.901278923299012</v>
+        <v>3.901278470251996</v>
       </c>
       <c r="E249" t="n">
-        <v>3.927999773273247</v>
+        <v>3.927999317123196</v>
       </c>
       <c r="F249" t="n">
         <v>12885400</v>
@@ -5412,16 +5412,16 @@
         <v>44776</v>
       </c>
       <c r="B250" t="n">
-        <v>4.284281253814697</v>
+        <v>4.284280300140381</v>
       </c>
       <c r="C250" t="n">
-        <v>4.37335146626734</v>
+        <v>4.373350492766133</v>
       </c>
       <c r="D250" t="n">
-        <v>4.123954871399942</v>
+        <v>4.123953953414027</v>
       </c>
       <c r="E250" t="n">
-        <v>4.123954871399942</v>
+        <v>4.123953953414027</v>
       </c>
       <c r="F250" t="n">
         <v>8750200</v>
@@ -5472,16 +5472,16 @@
         <v>44781</v>
       </c>
       <c r="B253" t="n">
-        <v>4.408978462219238</v>
+        <v>4.408978939056396</v>
       </c>
       <c r="C253" t="n">
-        <v>4.506955884076604</v>
+        <v>4.506956371510157</v>
       </c>
       <c r="D253" t="n">
-        <v>4.355536347947995</v>
+        <v>4.355536819005313</v>
       </c>
       <c r="E253" t="n">
-        <v>4.391164424128823</v>
+        <v>4.391164899039369</v>
       </c>
       <c r="F253" t="n">
         <v>6283600</v>
@@ -5492,16 +5492,16 @@
         <v>44782</v>
       </c>
       <c r="B254" t="n">
-        <v>4.382258892059326</v>
+        <v>4.382258415222168</v>
       </c>
       <c r="C254" t="n">
-        <v>4.578213368048839</v>
+        <v>4.578212869889715</v>
       </c>
       <c r="D254" t="n">
-        <v>4.364444848787552</v>
+        <v>4.364444373888754</v>
       </c>
       <c r="E254" t="n">
-        <v>4.453515065146422</v>
+        <v>4.453514580555821</v>
       </c>
       <c r="F254" t="n">
         <v>9216300</v>
@@ -5512,16 +5512,16 @@
         <v>44783</v>
       </c>
       <c r="B255" t="n">
-        <v>4.587120056152344</v>
+        <v>4.587119579315186</v>
       </c>
       <c r="C255" t="n">
-        <v>4.702911535999198</v>
+        <v>4.702911047125363</v>
       </c>
       <c r="D255" t="n">
-        <v>4.426793261065856</v>
+        <v>4.426792800894878</v>
       </c>
       <c r="E255" t="n">
-        <v>4.426793261065856</v>
+        <v>4.426792800894878</v>
       </c>
       <c r="F255" t="n">
         <v>9044400</v>
@@ -5552,16 +5552,16 @@
         <v>44785</v>
       </c>
       <c r="B257" t="n">
-        <v>4.694004058837891</v>
+        <v>4.694004535675049</v>
       </c>
       <c r="C257" t="n">
-        <v>4.694004058837891</v>
+        <v>4.694004535675049</v>
       </c>
       <c r="D257" t="n">
-        <v>4.498049616363389</v>
+        <v>4.49805007329465</v>
       </c>
       <c r="E257" t="n">
-        <v>4.578212585015574</v>
+        <v>4.578213050090135</v>
       </c>
       <c r="F257" t="n">
         <v>15222800</v>
@@ -5572,16 +5572,16 @@
         <v>44788</v>
       </c>
       <c r="B258" t="n">
-        <v>4.640562534332275</v>
+        <v>4.640562057495117</v>
       </c>
       <c r="C258" t="n">
-        <v>4.729632746899826</v>
+        <v>4.729632260910332</v>
       </c>
       <c r="D258" t="n">
-        <v>4.560399130661343</v>
+        <v>4.560398662061308</v>
       </c>
       <c r="E258" t="n">
-        <v>4.640562534332275</v>
+        <v>4.640562057495117</v>
       </c>
       <c r="F258" t="n">
         <v>10250500</v>
@@ -5612,16 +5612,16 @@
         <v>44790</v>
       </c>
       <c r="B260" t="n">
-        <v>4.702911376953125</v>
+        <v>4.702911853790283</v>
       </c>
       <c r="C260" t="n">
-        <v>4.774167539150558</v>
+        <v>4.774168023212515</v>
       </c>
       <c r="D260" t="n">
-        <v>4.560398627838029</v>
+        <v>4.560399090225548</v>
       </c>
       <c r="E260" t="n">
-        <v>4.596026708936746</v>
+        <v>4.596027174936664</v>
       </c>
       <c r="F260" t="n">
         <v>27272900</v>
@@ -5652,16 +5652,16 @@
         <v>44792</v>
       </c>
       <c r="B262" t="n">
-        <v>4.319909572601318</v>
+        <v>4.31990909576416</v>
       </c>
       <c r="C262" t="n">
-        <v>4.533678518777706</v>
+        <v>4.533678018344458</v>
       </c>
       <c r="D262" t="n">
-        <v>4.221932121240462</v>
+        <v>4.22193165521818</v>
       </c>
       <c r="E262" t="n">
-        <v>4.52477128469022</v>
+        <v>4.524770785240164</v>
       </c>
       <c r="F262" t="n">
         <v>17743000</v>
@@ -5672,16 +5672,16 @@
         <v>44795</v>
       </c>
       <c r="B263" t="n">
-        <v>4.319909572601318</v>
+        <v>4.31990909576416</v>
       </c>
       <c r="C263" t="n">
-        <v>4.364444893598153</v>
+        <v>4.364444411845128</v>
       </c>
       <c r="D263" t="n">
-        <v>4.177397224963925</v>
+        <v>4.177396763857463</v>
       </c>
       <c r="E263" t="n">
-        <v>4.302095529146644</v>
+        <v>4.302095054275823</v>
       </c>
       <c r="F263" t="n">
         <v>9829500</v>
@@ -5732,16 +5732,16 @@
         <v>44798</v>
       </c>
       <c r="B266" t="n">
-        <v>4.480236053466797</v>
+        <v>4.480235576629639</v>
       </c>
       <c r="C266" t="n">
-        <v>4.604934348326948</v>
+        <v>4.604933858217994</v>
       </c>
       <c r="D266" t="n">
-        <v>4.453514777922345</v>
+        <v>4.453514303929166</v>
       </c>
       <c r="E266" t="n">
-        <v>4.587120306204069</v>
+        <v>4.587119817991086</v>
       </c>
       <c r="F266" t="n">
         <v>4135100</v>
@@ -5752,16 +5752,16 @@
         <v>44799</v>
       </c>
       <c r="B267" t="n">
-        <v>4.319909572601318</v>
+        <v>4.31990909576416</v>
       </c>
       <c r="C267" t="n">
-        <v>4.52477128469022</v>
+        <v>4.524770785240164</v>
       </c>
       <c r="D267" t="n">
-        <v>4.293188719779456</v>
+        <v>4.29318824589178</v>
       </c>
       <c r="E267" t="n">
-        <v>4.489143197780872</v>
+        <v>4.489142702263489</v>
       </c>
       <c r="F267" t="n">
         <v>6692300</v>
@@ -5772,16 +5772,16 @@
         <v>44802</v>
       </c>
       <c r="B268" t="n">
-        <v>4.453514575958252</v>
+        <v>4.453514099121094</v>
       </c>
       <c r="C268" t="n">
-        <v>4.48023585029091</v>
+        <v>4.480235370592709</v>
       </c>
       <c r="D268" t="n">
-        <v>4.266466929790385</v>
+        <v>4.266466472980391</v>
       </c>
       <c r="E268" t="n">
-        <v>4.275374162808021</v>
+        <v>4.275373705044331</v>
       </c>
       <c r="F268" t="n">
         <v>7870400</v>
@@ -5792,16 +5792,16 @@
         <v>44803</v>
       </c>
       <c r="B269" t="n">
-        <v>4.364443778991699</v>
+        <v>4.364444255828857</v>
       </c>
       <c r="C269" t="n">
-        <v>4.480235244236013</v>
+        <v>4.480235733723964</v>
       </c>
       <c r="D269" t="n">
-        <v>4.337722508273708</v>
+        <v>4.337722982191434</v>
       </c>
       <c r="E269" t="n">
-        <v>4.471328012423286</v>
+        <v>4.471328500938078</v>
       </c>
       <c r="F269" t="n">
         <v>7827400</v>
@@ -5812,16 +5812,16 @@
         <v>44804</v>
       </c>
       <c r="B270" t="n">
-        <v>4.311002731323242</v>
+        <v>4.311001777648926</v>
       </c>
       <c r="C270" t="n">
-        <v>4.43570103458292</v>
+        <v>4.43570005332301</v>
       </c>
       <c r="D270" t="n">
-        <v>4.284281453978878</v>
+        <v>4.284280506215807</v>
       </c>
       <c r="E270" t="n">
-        <v>4.382258904614487</v>
+        <v>4.382257935176974</v>
       </c>
       <c r="F270" t="n">
         <v>8375100</v>
@@ -5832,16 +5832,16 @@
         <v>44805</v>
       </c>
       <c r="B271" t="n">
-        <v>4.248653411865234</v>
+        <v>4.248652458190918</v>
       </c>
       <c r="C271" t="n">
-        <v>4.426793846960512</v>
+        <v>4.42679285329989</v>
       </c>
       <c r="D271" t="n">
-        <v>4.177397237827122</v>
+        <v>4.177396300147329</v>
       </c>
       <c r="E271" t="n">
-        <v>4.346630863527787</v>
+        <v>4.346629887860955</v>
       </c>
       <c r="F271" t="n">
         <v>13026600</v>
@@ -5892,16 +5892,16 @@
         <v>44810</v>
       </c>
       <c r="B274" t="n">
-        <v>3.954721212387085</v>
+        <v>3.954721450805664</v>
       </c>
       <c r="C274" t="n">
-        <v>4.177396953458067</v>
+        <v>4.177397205301117</v>
       </c>
       <c r="D274" t="n">
-        <v>3.945813978878516</v>
+        <v>3.945814216760104</v>
       </c>
       <c r="E274" t="n">
-        <v>4.141768868864331</v>
+        <v>4.141769118559468</v>
       </c>
       <c r="F274" t="n">
         <v>14609100</v>
@@ -5952,16 +5952,16 @@
         <v>44816</v>
       </c>
       <c r="B277" t="n">
-        <v>3.856743574142456</v>
+        <v>3.856743812561035</v>
       </c>
       <c r="C277" t="n">
-        <v>3.990349097034463</v>
+        <v>3.990349343712352</v>
       </c>
       <c r="D277" t="n">
-        <v>3.838929532738205</v>
+        <v>3.838929770055544</v>
       </c>
       <c r="E277" t="n">
-        <v>3.954721014225961</v>
+        <v>3.95472125870137</v>
       </c>
       <c r="F277" t="n">
         <v>15738600</v>
@@ -5972,16 +5972,16 @@
         <v>44817</v>
       </c>
       <c r="B278" t="n">
-        <v>3.696417331695557</v>
+        <v>3.696416616439819</v>
       </c>
       <c r="C278" t="n">
-        <v>3.883464985388314</v>
+        <v>3.883464233938907</v>
       </c>
       <c r="D278" t="n">
-        <v>3.678603289663878</v>
+        <v>3.678602577855153</v>
       </c>
       <c r="E278" t="n">
-        <v>3.874557752012343</v>
+        <v>3.874557002286483</v>
       </c>
       <c r="F278" t="n">
         <v>21443000</v>
@@ -5992,16 +5992,16 @@
         <v>44818</v>
       </c>
       <c r="B279" t="n">
-        <v>3.740952253341675</v>
+        <v>3.740952014923096</v>
       </c>
       <c r="C279" t="n">
-        <v>3.821115655464227</v>
+        <v>3.821115411936669</v>
       </c>
       <c r="D279" t="n">
-        <v>3.678603318108816</v>
+        <v>3.678603083663863</v>
       </c>
       <c r="E279" t="n">
-        <v>3.705324169002822</v>
+        <v>3.705323932854894</v>
       </c>
       <c r="F279" t="n">
         <v>13539100</v>
@@ -6012,16 +6012,16 @@
         <v>44819</v>
       </c>
       <c r="B280" t="n">
-        <v>3.749859571456909</v>
+        <v>3.749858856201172</v>
       </c>
       <c r="C280" t="n">
-        <v>3.758766380382601</v>
+        <v>3.758765663427961</v>
       </c>
       <c r="D280" t="n">
-        <v>3.634068082380977</v>
+        <v>3.63406738921154</v>
       </c>
       <c r="E280" t="n">
-        <v>3.740952337810941</v>
+        <v>3.740951624254187</v>
       </c>
       <c r="F280" t="n">
         <v>12717200</v>
@@ -6032,16 +6032,16 @@
         <v>44820</v>
       </c>
       <c r="B281" t="n">
-        <v>3.821115732192993</v>
+        <v>3.821115493774414</v>
       </c>
       <c r="C281" t="n">
-        <v>3.892371902301537</v>
+        <v>3.892371659436928</v>
       </c>
       <c r="D281" t="n">
-        <v>3.66078934944877</v>
+        <v>3.660789121033758</v>
       </c>
       <c r="E281" t="n">
-        <v>3.696417434503042</v>
+        <v>3.696417203865015</v>
       </c>
       <c r="F281" t="n">
         <v>19813000</v>
@@ -6052,16 +6052,16 @@
         <v>44823</v>
       </c>
       <c r="B282" t="n">
-        <v>3.990349292755127</v>
+        <v>3.990348815917969</v>
       </c>
       <c r="C282" t="n">
-        <v>4.00816333503313</v>
+        <v>4.008162856067236</v>
       </c>
       <c r="D282" t="n">
-        <v>3.794394827697093</v>
+        <v>3.794394374276022</v>
       </c>
       <c r="E282" t="n">
-        <v>3.830022912253099</v>
+        <v>3.830022454574558</v>
       </c>
       <c r="F282" t="n">
         <v>8945000</v>
@@ -6112,16 +6112,16 @@
         <v>44826</v>
       </c>
       <c r="B285" t="n">
-        <v>4.052698135375977</v>
+        <v>4.052698612213135</v>
       </c>
       <c r="C285" t="n">
-        <v>4.097233023021737</v>
+        <v>4.097233505098832</v>
       </c>
       <c r="D285" t="n">
-        <v>3.90127858299592</v>
+        <v>3.901279042017177</v>
       </c>
       <c r="E285" t="n">
-        <v>3.936906663000614</v>
+        <v>3.936907126213841</v>
       </c>
       <c r="F285" t="n">
         <v>13589200</v>
@@ -6152,16 +6152,16 @@
         <v>44830</v>
       </c>
       <c r="B287" t="n">
-        <v>3.821115732192993</v>
+        <v>3.821115493774414</v>
       </c>
       <c r="C287" t="n">
-        <v>3.936907220979514</v>
+        <v>3.936906975336123</v>
       </c>
       <c r="D287" t="n">
-        <v>3.794394880762427</v>
+        <v>3.794394644011096</v>
       </c>
       <c r="E287" t="n">
-        <v>3.901279135925243</v>
+        <v>3.901278892504866</v>
       </c>
       <c r="F287" t="n">
         <v>9718800</v>
@@ -6172,16 +6172,16 @@
         <v>44831</v>
       </c>
       <c r="B288" t="n">
-        <v>3.73204517364502</v>
+        <v>3.732045412063599</v>
       </c>
       <c r="C288" t="n">
-        <v>3.919092815203188</v>
+        <v>3.91909306557115</v>
       </c>
       <c r="D288" t="n">
-        <v>3.73204517364502</v>
+        <v>3.732045412063599</v>
       </c>
       <c r="E288" t="n">
-        <v>3.838929418901048</v>
+        <v>3.838929664147838</v>
       </c>
       <c r="F288" t="n">
         <v>11052300</v>
@@ -6192,16 +6192,16 @@
         <v>44832</v>
       </c>
       <c r="B289" t="n">
-        <v>3.687510013580322</v>
+        <v>3.687510251998901</v>
       </c>
       <c r="C289" t="n">
-        <v>3.767673413240847</v>
+        <v>3.767673656842447</v>
       </c>
       <c r="D289" t="n">
-        <v>3.687510013580322</v>
+        <v>3.687510251998901</v>
       </c>
       <c r="E289" t="n">
-        <v>3.749859371618537</v>
+        <v>3.749859614068357</v>
       </c>
       <c r="F289" t="n">
         <v>11148900</v>
@@ -6212,16 +6212,16 @@
         <v>44833</v>
       </c>
       <c r="B290" t="n">
-        <v>3.696417331695557</v>
+        <v>3.696416616439819</v>
       </c>
       <c r="C290" t="n">
-        <v>3.714231373727235</v>
+        <v>3.714230655024486</v>
       </c>
       <c r="D290" t="n">
-        <v>3.616253930192871</v>
+        <v>3.61625323044873</v>
       </c>
       <c r="E290" t="n">
-        <v>3.660789247632199</v>
+        <v>3.660788539270487</v>
       </c>
       <c r="F290" t="n">
         <v>12380300</v>
@@ -6232,16 +6232,16 @@
         <v>44834</v>
       </c>
       <c r="B291" t="n">
-        <v>3.73204517364502</v>
+        <v>3.732045412063599</v>
       </c>
       <c r="C291" t="n">
-        <v>3.794394529071154</v>
+        <v>3.79439477147287</v>
       </c>
       <c r="D291" t="n">
-        <v>3.651881777342879</v>
+        <v>3.651882010640287</v>
       </c>
       <c r="E291" t="n">
-        <v>3.660789010141</v>
+        <v>3.660789244007439</v>
       </c>
       <c r="F291" t="n">
         <v>11827700</v>
@@ -6252,16 +6252,16 @@
         <v>44837</v>
       </c>
       <c r="B292" t="n">
-        <v>3.939894676208496</v>
+        <v>3.939894914627075</v>
       </c>
       <c r="C292" t="n">
-        <v>3.939894676208497</v>
+        <v>3.939894914627075</v>
       </c>
       <c r="D292" t="n">
-        <v>3.796299558626456</v>
+        <v>3.796299788355527</v>
       </c>
       <c r="E292" t="n">
-        <v>3.814248948324211</v>
+        <v>3.814249179139471</v>
       </c>
       <c r="F292" t="n">
         <v>14167700</v>
@@ -6292,16 +6292,16 @@
         <v>44839</v>
       </c>
       <c r="B294" t="n">
-        <v>3.975793123245239</v>
+        <v>3.975793361663818</v>
       </c>
       <c r="C294" t="n">
-        <v>3.975793123245239</v>
+        <v>3.975793361663818</v>
       </c>
       <c r="D294" t="n">
-        <v>3.868096794061647</v>
+        <v>3.868097026021941</v>
       </c>
       <c r="E294" t="n">
-        <v>3.921944958653443</v>
+        <v>3.92194519384288</v>
       </c>
       <c r="F294" t="n">
         <v>8368900</v>
@@ -6332,16 +6332,16 @@
         <v>44841</v>
       </c>
       <c r="B296" t="n">
-        <v>3.760400533676147</v>
+        <v>3.760401010513306</v>
       </c>
       <c r="C296" t="n">
-        <v>4.002717492746105</v>
+        <v>4.002718000310238</v>
       </c>
       <c r="D296" t="n">
-        <v>3.715526848388416</v>
+        <v>3.715527319535371</v>
       </c>
       <c r="E296" t="n">
-        <v>3.984768104220449</v>
+        <v>3.984768609508511</v>
       </c>
       <c r="F296" t="n">
         <v>16354500</v>
@@ -6352,16 +6352,16 @@
         <v>44844</v>
       </c>
       <c r="B297" t="n">
-        <v>3.661679029464722</v>
+        <v>3.661678791046143</v>
       </c>
       <c r="C297" t="n">
-        <v>3.80527415126421</v>
+        <v>3.805273903495892</v>
       </c>
       <c r="D297" t="n">
-        <v>3.634755158100927</v>
+        <v>3.63475492143541</v>
       </c>
       <c r="E297" t="n">
-        <v>3.80527415126421</v>
+        <v>3.805273903495892</v>
       </c>
       <c r="F297" t="n">
         <v>18862600</v>
@@ -6372,16 +6372,16 @@
         <v>44845</v>
       </c>
       <c r="B298" t="n">
-        <v>3.903995752334595</v>
+        <v>3.903995990753174</v>
       </c>
       <c r="C298" t="n">
-        <v>3.948869438891908</v>
+        <v>3.948869680050941</v>
       </c>
       <c r="D298" t="n">
-        <v>3.634754916832287</v>
+        <v>3.63475513880822</v>
       </c>
       <c r="E298" t="n">
-        <v>3.661678786408922</v>
+        <v>3.661679010029107</v>
       </c>
       <c r="F298" t="n">
         <v>30833900</v>
@@ -6412,16 +6412,16 @@
         <v>44848</v>
       </c>
       <c r="B300" t="n">
-        <v>3.688603162765503</v>
+        <v>3.688603401184082</v>
       </c>
       <c r="C300" t="n">
-        <v>3.832198278102312</v>
+        <v>3.832198525802385</v>
       </c>
       <c r="D300" t="n">
-        <v>3.679628254083352</v>
+        <v>3.679628491921824</v>
       </c>
       <c r="E300" t="n">
-        <v>3.823223797367362</v>
+        <v>3.823224044487355</v>
       </c>
       <c r="F300" t="n">
         <v>10535000</v>
@@ -6452,16 +6452,16 @@
         <v>44852</v>
       </c>
       <c r="B302" t="n">
-        <v>3.715527057647705</v>
+        <v>3.715527296066284</v>
       </c>
       <c r="C302" t="n">
-        <v>3.787324615793987</v>
+        <v>3.787324858819684</v>
       </c>
       <c r="D302" t="n">
-        <v>3.661678889037994</v>
+        <v>3.661679124001235</v>
       </c>
       <c r="E302" t="n">
-        <v>3.724501966389592</v>
+        <v>3.724502205384074</v>
       </c>
       <c r="F302" t="n">
         <v>13196400</v>
@@ -6492,16 +6492,16 @@
         <v>44854</v>
       </c>
       <c r="B304" t="n">
-        <v>3.769375562667847</v>
+        <v>3.769375324249268</v>
       </c>
       <c r="C304" t="n">
-        <v>3.796299863349252</v>
+        <v>3.796299623227672</v>
       </c>
       <c r="D304" t="n">
-        <v>3.706552907656635</v>
+        <v>3.706552673211682</v>
       </c>
       <c r="E304" t="n">
-        <v>3.760401081072205</v>
+        <v>3.760400843221276</v>
       </c>
       <c r="F304" t="n">
         <v>13428400</v>
@@ -6532,16 +6532,16 @@
         <v>44858</v>
       </c>
       <c r="B306" t="n">
-        <v>3.706552743911743</v>
+        <v>3.706552982330322</v>
       </c>
       <c r="C306" t="n">
-        <v>3.778350305294026</v>
+        <v>3.778350548330878</v>
       </c>
       <c r="D306" t="n">
-        <v>3.697577834765347</v>
+        <v>3.697578072606628</v>
       </c>
       <c r="E306" t="n">
-        <v>3.76937539614763</v>
+        <v>3.769375638607184</v>
       </c>
       <c r="F306" t="n">
         <v>9021900</v>
@@ -6552,16 +6552,16 @@
         <v>44859</v>
       </c>
       <c r="B307" t="n">
-        <v>3.670653820037842</v>
+        <v>3.670654058456421</v>
       </c>
       <c r="C307" t="n">
-        <v>3.769375249114001</v>
+        <v>3.769375493944795</v>
       </c>
       <c r="D307" t="n">
-        <v>3.661678911241534</v>
+        <v>3.661679149077169</v>
       </c>
       <c r="E307" t="n">
-        <v>3.706552599328664</v>
+        <v>3.706552840078963</v>
       </c>
       <c r="F307" t="n">
         <v>12220200</v>
@@ -6592,16 +6592,16 @@
         <v>44861</v>
       </c>
       <c r="B309" t="n">
-        <v>3.706552743911743</v>
+        <v>3.706552982330322</v>
       </c>
       <c r="C309" t="n">
-        <v>3.760400914948455</v>
+        <v>3.760401156830739</v>
       </c>
       <c r="D309" t="n">
-        <v>3.580906797519137</v>
+        <v>3.580907027855725</v>
       </c>
       <c r="E309" t="n">
-        <v>3.580906797519137</v>
+        <v>3.580907027855725</v>
       </c>
       <c r="F309" t="n">
         <v>15175200</v>
@@ -6612,16 +6612,16 @@
         <v>44862</v>
       </c>
       <c r="B310" t="n">
-        <v>3.724502086639404</v>
+        <v>3.724501609802246</v>
       </c>
       <c r="C310" t="n">
-        <v>3.73347656772384</v>
+        <v>3.733476089737704</v>
       </c>
       <c r="D310" t="n">
-        <v>3.643729617143404</v>
+        <v>3.64372915064731</v>
       </c>
       <c r="E310" t="n">
-        <v>3.68860330640723</v>
+        <v>3.688602834166089</v>
       </c>
       <c r="F310" t="n">
         <v>9985100</v>
@@ -6672,16 +6672,16 @@
         <v>44868</v>
       </c>
       <c r="B313" t="n">
-        <v>4.21811056137085</v>
+        <v>4.218111038208008</v>
       </c>
       <c r="C313" t="n">
-        <v>4.254009341880177</v>
+        <v>4.25400982277552</v>
       </c>
       <c r="D313" t="n">
-        <v>3.895021536786911</v>
+        <v>3.895021977100405</v>
       </c>
       <c r="E313" t="n">
-        <v>3.975793578959285</v>
+        <v>3.975794028403671</v>
       </c>
       <c r="F313" t="n">
         <v>15015300</v>
@@ -6692,16 +6692,16 @@
         <v>44869</v>
       </c>
       <c r="B314" t="n">
-        <v>4.23606014251709</v>
+        <v>4.236059665679932</v>
       </c>
       <c r="C314" t="n">
-        <v>4.34375691684548</v>
+        <v>4.343756427885306</v>
       </c>
       <c r="D314" t="n">
-        <v>4.155288096704846</v>
+        <v>4.15528762895989</v>
       </c>
       <c r="E314" t="n">
-        <v>4.218110751453565</v>
+        <v>4.218110276636901</v>
       </c>
       <c r="F314" t="n">
         <v>12500600</v>
@@ -6712,16 +6712,16 @@
         <v>44872</v>
       </c>
       <c r="B315" t="n">
-        <v>4.011692523956299</v>
+        <v>4.011692047119141</v>
       </c>
       <c r="C315" t="n">
-        <v>4.379655681184977</v>
+        <v>4.37965516061104</v>
       </c>
       <c r="D315" t="n">
-        <v>4.011692523956299</v>
+        <v>4.011692047119141</v>
       </c>
       <c r="E315" t="n">
-        <v>4.316832598744169</v>
+        <v>4.3168320856375</v>
       </c>
       <c r="F315" t="n">
         <v>17217400</v>
@@ -6732,16 +6732,16 @@
         <v>44873</v>
       </c>
       <c r="B316" t="n">
-        <v>4.083489894866943</v>
+        <v>4.083490371704102</v>
       </c>
       <c r="C316" t="n">
-        <v>4.110413763284799</v>
+        <v>4.110414243265911</v>
       </c>
       <c r="D316" t="n">
-        <v>3.966818657197105</v>
+        <v>3.966819120410333</v>
       </c>
       <c r="E316" t="n">
-        <v>4.011691913875923</v>
+        <v>4.01169238232909</v>
       </c>
       <c r="F316" t="n">
         <v>15444300</v>
@@ -6752,16 +6752,16 @@
         <v>44874</v>
       </c>
       <c r="B317" t="n">
-        <v>4.011692523956299</v>
+        <v>4.011692047119141</v>
       </c>
       <c r="C317" t="n">
-        <v>4.173237470819165</v>
+        <v>4.173236974780477</v>
       </c>
       <c r="D317" t="n">
-        <v>3.98476865144398</v>
+        <v>3.984768177807042</v>
       </c>
       <c r="E317" t="n">
-        <v>4.065541124875413</v>
+        <v>4.06554064163771</v>
       </c>
       <c r="F317" t="n">
         <v>11339500</v>
@@ -6772,16 +6772,16 @@
         <v>44875</v>
       </c>
       <c r="B318" t="n">
-        <v>3.688603162765503</v>
+        <v>3.688603401184082</v>
       </c>
       <c r="C318" t="n">
-        <v>3.975793393439122</v>
+        <v>3.975793650420687</v>
       </c>
       <c r="D318" t="n">
-        <v>3.670653773348401</v>
+        <v>3.670654010606794</v>
       </c>
       <c r="E318" t="n">
-        <v>3.921945225187819</v>
+        <v>3.921945478688824</v>
       </c>
       <c r="F318" t="n">
         <v>22566600</v>
@@ -6792,16 +6792,16 @@
         <v>44876</v>
       </c>
       <c r="B319" t="n">
-        <v>3.715527057647705</v>
+        <v>3.715527296066284</v>
       </c>
       <c r="C319" t="n">
-        <v>3.751425836720846</v>
+        <v>3.751426077442984</v>
       </c>
       <c r="D319" t="n">
-        <v>3.437311305857262</v>
+        <v>3.437311526423245</v>
       </c>
       <c r="E319" t="n">
-        <v>3.634755018706739</v>
+        <v>3.634755251942325</v>
       </c>
       <c r="F319" t="n">
         <v>24235200</v>
@@ -6832,16 +6832,16 @@
         <v>44881</v>
       </c>
       <c r="B321" t="n">
-        <v>3.616805791854858</v>
+        <v>3.616805553436279</v>
       </c>
       <c r="C321" t="n">
-        <v>3.760400914606361</v>
+        <v>3.760400666722041</v>
       </c>
       <c r="D321" t="n">
-        <v>3.553982711677465</v>
+        <v>3.553982477400161</v>
       </c>
       <c r="E321" t="n">
-        <v>3.697577834428968</v>
+        <v>3.697577590685923</v>
       </c>
       <c r="F321" t="n">
         <v>16148800</v>
@@ -6852,16 +6852,16 @@
         <v>44882</v>
       </c>
       <c r="B322" t="n">
-        <v>3.509108781814575</v>
+        <v>3.509109020233154</v>
       </c>
       <c r="C322" t="n">
-        <v>3.571931639890434</v>
+        <v>3.571931882577372</v>
       </c>
       <c r="D322" t="n">
-        <v>3.356538769656764</v>
+        <v>3.356538997709313</v>
       </c>
       <c r="E322" t="n">
-        <v>3.562956945879597</v>
+        <v>3.56295718795677</v>
       </c>
       <c r="F322" t="n">
         <v>25106400</v>
@@ -6892,16 +6892,16 @@
         <v>44886</v>
       </c>
       <c r="B324" t="n">
-        <v>3.616805791854858</v>
+        <v>3.616805553436279</v>
       </c>
       <c r="C324" t="n">
-        <v>3.733476615116843</v>
+        <v>3.733476369007364</v>
       </c>
       <c r="D324" t="n">
-        <v>3.545008016505496</v>
+        <v>3.545007782819801</v>
       </c>
       <c r="E324" t="n">
-        <v>3.67962844408503</v>
+        <v>3.679628201525203</v>
       </c>
       <c r="F324" t="n">
         <v>11314600</v>
@@ -6912,16 +6912,16 @@
         <v>44887</v>
       </c>
       <c r="B325" t="n">
-        <v>3.616805791854858</v>
+        <v>3.616805553436279</v>
       </c>
       <c r="C325" t="n">
-        <v>3.661679053741092</v>
+        <v>3.661678812364483</v>
       </c>
       <c r="D325" t="n">
-        <v>3.562957406849434</v>
+        <v>3.562957171980521</v>
       </c>
       <c r="E325" t="n">
-        <v>3.616805791854858</v>
+        <v>3.616805553436279</v>
       </c>
       <c r="F325" t="n">
         <v>10439300</v>
@@ -6952,16 +6952,16 @@
         <v>44889</v>
       </c>
       <c r="B327" t="n">
-        <v>3.724502086639404</v>
+        <v>3.724501609802246</v>
       </c>
       <c r="C327" t="n">
-        <v>3.742451476755492</v>
+        <v>3.742450997620325</v>
       </c>
       <c r="D327" t="n">
-        <v>3.598856355826795</v>
+        <v>3.598855895075694</v>
       </c>
       <c r="E327" t="n">
-        <v>3.634755136058969</v>
+        <v>3.634754670711852</v>
       </c>
       <c r="F327" t="n">
         <v>5511600</v>
@@ -6972,16 +6972,16 @@
         <v>44890</v>
       </c>
       <c r="B328" t="n">
-        <v>3.63475489616394</v>
+        <v>3.634755373001099</v>
       </c>
       <c r="C328" t="n">
-        <v>3.76040061868389</v>
+        <v>3.760401112004292</v>
       </c>
       <c r="D328" t="n">
-        <v>3.580906515396082</v>
+        <v>3.580906985168965</v>
       </c>
       <c r="E328" t="n">
-        <v>3.733476321313164</v>
+        <v>3.733476811101414</v>
       </c>
       <c r="F328" t="n">
         <v>8739900</v>
@@ -6992,16 +6992,16 @@
         <v>44893</v>
       </c>
       <c r="B329" t="n">
-        <v>3.607830762863159</v>
+        <v>3.60783052444458</v>
       </c>
       <c r="C329" t="n">
-        <v>3.670653840953675</v>
+        <v>3.670653598383518</v>
       </c>
       <c r="D329" t="n">
-        <v>3.58988137311547</v>
+        <v>3.589881135883052</v>
       </c>
       <c r="E329" t="n">
-        <v>3.58988137311547</v>
+        <v>3.589881135883052</v>
       </c>
       <c r="F329" t="n">
         <v>7386900</v>
@@ -7032,16 +7032,16 @@
         <v>44895</v>
       </c>
       <c r="B331" t="n">
-        <v>3.63475489616394</v>
+        <v>3.634755373001099</v>
       </c>
       <c r="C331" t="n">
-        <v>3.661678765587478</v>
+        <v>3.661679245956732</v>
       </c>
       <c r="D331" t="n">
-        <v>3.518083654136107</v>
+        <v>3.518084115667368</v>
       </c>
       <c r="E331" t="n">
-        <v>3.571931820930371</v>
+        <v>3.57193228952588</v>
       </c>
       <c r="F331" t="n">
         <v>16877200</v>
@@ -7052,16 +7052,16 @@
         <v>44896</v>
       </c>
       <c r="B332" t="n">
-        <v>3.446285963058472</v>
+        <v>3.446286201477051</v>
       </c>
       <c r="C332" t="n">
-        <v>3.589881291759341</v>
+        <v>3.589881540112033</v>
       </c>
       <c r="D332" t="n">
-        <v>3.428336573717563</v>
+        <v>3.428336810894379</v>
       </c>
       <c r="E332" t="n">
-        <v>3.589881291759341</v>
+        <v>3.589881540112033</v>
       </c>
       <c r="F332" t="n">
         <v>22625600</v>
@@ -7132,16 +7132,16 @@
         <v>44902</v>
       </c>
       <c r="B336" t="n">
-        <v>3.23089337348938</v>
+        <v>3.230893135070801</v>
       </c>
       <c r="C336" t="n">
-        <v>3.320640542403519</v>
+        <v>3.320640297362192</v>
       </c>
       <c r="D336" t="n">
-        <v>3.212943982501276</v>
+        <v>3.212943745407243</v>
       </c>
       <c r="E336" t="n">
-        <v>3.302691151415415</v>
+        <v>3.302690907698634</v>
       </c>
       <c r="F336" t="n">
         <v>13628700</v>
@@ -7152,16 +7152,16 @@
         <v>44903</v>
       </c>
       <c r="B337" t="n">
-        <v>3.073575973510742</v>
+        <v>3.073575735092163</v>
       </c>
       <c r="C337" t="n">
-        <v>3.266824802334561</v>
+        <v>3.266824548925589</v>
       </c>
       <c r="D337" t="n">
-        <v>3.064373658776298</v>
+        <v>3.064373421071546</v>
       </c>
       <c r="E337" t="n">
-        <v>3.22081322866234</v>
+        <v>3.220812978822505</v>
       </c>
       <c r="F337" t="n">
         <v>19978800</v>
@@ -7192,16 +7192,16 @@
         <v>44907</v>
       </c>
       <c r="B339" t="n">
-        <v>3.036766529083252</v>
+        <v>3.036766290664673</v>
       </c>
       <c r="C339" t="n">
-        <v>3.119587576034921</v>
+        <v>3.119587331114006</v>
       </c>
       <c r="D339" t="n">
-        <v>2.972350329876769</v>
+        <v>2.972350096515548</v>
       </c>
       <c r="E339" t="n">
-        <v>3.082778099945025</v>
+        <v>3.082777857914047</v>
       </c>
       <c r="F339" t="n">
         <v>24013800</v>
@@ -7232,16 +7232,16 @@
         <v>44909</v>
       </c>
       <c r="B341" t="n">
-        <v>3.073575973510742</v>
+        <v>3.073575735092163</v>
       </c>
       <c r="C341" t="n">
-        <v>3.101182917714075</v>
+        <v>3.101182677154013</v>
       </c>
       <c r="D341" t="n">
-        <v>2.935541252494079</v>
+        <v>2.935541024782911</v>
       </c>
       <c r="E341" t="n">
-        <v>2.9815528261663</v>
+        <v>2.981552594885995</v>
       </c>
       <c r="F341" t="n">
         <v>15438000</v>
@@ -7252,16 +7252,16 @@
         <v>44910</v>
       </c>
       <c r="B342" t="n">
-        <v>3.036766529083252</v>
+        <v>3.036766290664673</v>
       </c>
       <c r="C342" t="n">
-        <v>3.13799220437963</v>
+        <v>3.137991958013755</v>
       </c>
       <c r="D342" t="n">
-        <v>3.009159586566188</v>
+        <v>3.009159350315048</v>
       </c>
       <c r="E342" t="n">
-        <v>3.055171157427961</v>
+        <v>3.055170917564423</v>
       </c>
       <c r="F342" t="n">
         <v>8858500</v>
@@ -7292,16 +7292,16 @@
         <v>44914</v>
       </c>
       <c r="B344" t="n">
-        <v>3.073575973510742</v>
+        <v>3.073575735092163</v>
       </c>
       <c r="C344" t="n">
-        <v>3.091980602979631</v>
+        <v>3.091980363133397</v>
       </c>
       <c r="D344" t="n">
-        <v>2.990755140900744</v>
+        <v>2.990754908906612</v>
       </c>
       <c r="E344" t="n">
-        <v>3.009159770369632</v>
+        <v>3.009159536947845</v>
       </c>
       <c r="F344" t="n">
         <v>6693400</v>
@@ -7312,16 +7312,16 @@
         <v>44915</v>
       </c>
       <c r="B345" t="n">
-        <v>3.257622241973877</v>
+        <v>3.257622003555298</v>
       </c>
       <c r="C345" t="n">
-        <v>3.31283612621739</v>
+        <v>3.312835883757822</v>
       </c>
       <c r="D345" t="n">
-        <v>3.036766485599353</v>
+        <v>3.036766263344746</v>
       </c>
       <c r="E345" t="n">
-        <v>3.036766485599353</v>
+        <v>3.036766263344746</v>
       </c>
       <c r="F345" t="n">
         <v>12943700</v>
@@ -7332,16 +7332,16 @@
         <v>44916</v>
       </c>
       <c r="B346" t="n">
-        <v>3.331240892410278</v>
+        <v>3.331240653991699</v>
       </c>
       <c r="C346" t="n">
-        <v>3.377252683921307</v>
+        <v>3.37725244220964</v>
       </c>
       <c r="D346" t="n">
-        <v>3.239217748189187</v>
+        <v>3.23921751635675</v>
       </c>
       <c r="E346" t="n">
-        <v>3.266824691455514</v>
+        <v>3.266824457647235</v>
       </c>
       <c r="F346" t="n">
         <v>14610300</v>
@@ -7452,16 +7452,16 @@
         <v>44924</v>
       </c>
       <c r="B352" t="n">
-        <v>3.441668748855591</v>
+        <v>3.441668510437012</v>
       </c>
       <c r="C352" t="n">
-        <v>3.598108307249177</v>
+        <v>3.598108057993386</v>
       </c>
       <c r="D352" t="n">
-        <v>3.404859492621917</v>
+        <v>3.404859256753267</v>
       </c>
       <c r="E352" t="n">
-        <v>3.524489575381356</v>
+        <v>3.524489331225437</v>
       </c>
       <c r="F352" t="n">
         <v>7177700</v>
@@ -7472,16 +7472,16 @@
         <v>44928</v>
       </c>
       <c r="B353" t="n">
-        <v>3.257622241973877</v>
+        <v>3.257622003555298</v>
       </c>
       <c r="C353" t="n">
-        <v>3.414061800064303</v>
+        <v>3.414061550196239</v>
       </c>
       <c r="D353" t="n">
-        <v>3.23001529985212</v>
+        <v>3.230015063454036</v>
       </c>
       <c r="E353" t="n">
-        <v>3.395657171983132</v>
+        <v>3.395656923462064</v>
       </c>
       <c r="F353" t="n">
         <v>9470500</v>
@@ -7492,16 +7492,16 @@
         <v>44929</v>
       </c>
       <c r="B354" t="n">
-        <v>3.073575973510742</v>
+        <v>3.073575735092163</v>
       </c>
       <c r="C354" t="n">
-        <v>3.28522943180345</v>
+        <v>3.285229176966823</v>
       </c>
       <c r="D354" t="n">
-        <v>3.064373658776298</v>
+        <v>3.064373421071546</v>
       </c>
       <c r="E354" t="n">
-        <v>3.257622487600117</v>
+        <v>3.257622234904972</v>
       </c>
       <c r="F354" t="n">
         <v>9560100</v>
@@ -7632,16 +7632,16 @@
         <v>44938</v>
       </c>
       <c r="B361" t="n">
-        <v>3.211610555648804</v>
+        <v>3.211610794067383</v>
       </c>
       <c r="C361" t="n">
-        <v>3.349645480667133</v>
+        <v>3.349645729332935</v>
       </c>
       <c r="D361" t="n">
-        <v>3.165598987109516</v>
+        <v>3.165599222112359</v>
       </c>
       <c r="E361" t="n">
-        <v>3.266824437895949</v>
+        <v>3.266824680413411</v>
       </c>
       <c r="F361" t="n">
         <v>13176700</v>
@@ -7652,16 +7652,16 @@
         <v>44939</v>
       </c>
       <c r="B362" t="n">
-        <v>3.073575973510742</v>
+        <v>3.073575735092163</v>
       </c>
       <c r="C362" t="n">
-        <v>3.22081322866234</v>
+        <v>3.220812978822505</v>
       </c>
       <c r="D362" t="n">
-        <v>3.055171344041854</v>
+        <v>3.05517110705093</v>
       </c>
       <c r="E362" t="n">
-        <v>3.184003969724563</v>
+        <v>3.184003722740037</v>
       </c>
       <c r="F362" t="n">
         <v>14486700</v>
@@ -7672,16 +7672,16 @@
         <v>44942</v>
       </c>
       <c r="B363" t="n">
-        <v>3.036766529083252</v>
+        <v>3.036766290664673</v>
       </c>
       <c r="C363" t="n">
-        <v>3.082778099945025</v>
+        <v>3.082777857914047</v>
       </c>
       <c r="D363" t="n">
-        <v>3.009159586566188</v>
+        <v>3.009159350315048</v>
       </c>
       <c r="E363" t="n">
-        <v>3.055171157427961</v>
+        <v>3.055170917564423</v>
       </c>
       <c r="F363" t="n">
         <v>8730700</v>
@@ -7692,16 +7692,16 @@
         <v>44943</v>
       </c>
       <c r="B364" t="n">
-        <v>3.091980457305908</v>
+        <v>3.091980218887329</v>
       </c>
       <c r="C364" t="n">
-        <v>3.128789933909955</v>
+        <v>3.128789692653045</v>
       </c>
       <c r="D364" t="n">
-        <v>3.027564257199665</v>
+        <v>3.027564023748135</v>
       </c>
       <c r="E364" t="n">
-        <v>3.055171200102341</v>
+        <v>3.055170964522075</v>
       </c>
       <c r="F364" t="n">
         <v>11859400</v>
@@ -7752,16 +7752,16 @@
         <v>44946</v>
       </c>
       <c r="B367" t="n">
-        <v>3.02756404876709</v>
+        <v>3.027564287185669</v>
       </c>
       <c r="C367" t="n">
-        <v>3.13799203217586</v>
+        <v>3.137992279290566</v>
       </c>
       <c r="D367" t="n">
-        <v>3.009159421432372</v>
+        <v>3.009159658401599</v>
       </c>
       <c r="E367" t="n">
-        <v>3.128789718508501</v>
+        <v>3.128789964898532</v>
       </c>
       <c r="F367" t="n">
         <v>19274300</v>
@@ -7772,16 +7772,16 @@
         <v>44949</v>
       </c>
       <c r="B368" t="n">
-        <v>3.02756404876709</v>
+        <v>3.027564287185669</v>
       </c>
       <c r="C368" t="n">
-        <v>3.082777930771243</v>
+        <v>3.082778173537877</v>
       </c>
       <c r="D368" t="n">
-        <v>2.990754794097655</v>
+        <v>2.99075502961753</v>
       </c>
       <c r="E368" t="n">
-        <v>3.018361735099731</v>
+        <v>3.018361972793634</v>
       </c>
       <c r="F368" t="n">
         <v>10637200</v>
@@ -7792,16 +7792,16 @@
         <v>44950</v>
       </c>
       <c r="B369" t="n">
-        <v>3.193206071853638</v>
+        <v>3.193205833435059</v>
       </c>
       <c r="C369" t="n">
-        <v>3.202408385975387</v>
+        <v>3.202408146869723</v>
       </c>
       <c r="D369" t="n">
-        <v>3.018361884139927</v>
+        <v>3.018361658775971</v>
       </c>
       <c r="E369" t="n">
-        <v>3.045968826505175</v>
+        <v>3.045968599079965</v>
       </c>
       <c r="F369" t="n">
         <v>12703800</v>
@@ -7812,16 +7812,16 @@
         <v>44951</v>
       </c>
       <c r="B370" t="n">
-        <v>3.248420000076294</v>
+        <v>3.248420238494873</v>
       </c>
       <c r="C370" t="n">
-        <v>3.248420000076294</v>
+        <v>3.248420238494873</v>
       </c>
       <c r="D370" t="n">
-        <v>3.147194543381774</v>
+        <v>3.147194774370885</v>
       </c>
       <c r="E370" t="n">
-        <v>3.193206114606555</v>
+        <v>3.193206348972698</v>
       </c>
       <c r="F370" t="n">
         <v>7649000</v>
@@ -7852,16 +7852,16 @@
         <v>44953</v>
       </c>
       <c r="B372" t="n">
-        <v>3.147194147109985</v>
+        <v>3.147194385528564</v>
       </c>
       <c r="C372" t="n">
-        <v>3.22081265180013</v>
+        <v>3.220812895795746</v>
       </c>
       <c r="D372" t="n">
-        <v>3.128789520937449</v>
+        <v>3.128789757961769</v>
       </c>
       <c r="E372" t="n">
-        <v>3.211610338713862</v>
+        <v>3.211610582012349</v>
       </c>
       <c r="F372" t="n">
         <v>8557200</v>
@@ -7872,16 +7872,16 @@
         <v>44956</v>
       </c>
       <c r="B373" t="n">
-        <v>2.990755081176758</v>
+        <v>2.990754842758179</v>
       </c>
       <c r="C373" t="n">
-        <v>3.156396962489453</v>
+        <v>3.156396710866147</v>
       </c>
       <c r="D373" t="n">
-        <v>2.963148137524723</v>
+        <v>2.963147901306928</v>
       </c>
       <c r="E373" t="n">
-        <v>3.128790018837418</v>
+        <v>3.128789769414897</v>
       </c>
       <c r="F373" t="n">
         <v>24955900</v>
@@ -7892,16 +7892,16 @@
         <v>44957</v>
       </c>
       <c r="B374" t="n">
-        <v>3.02756404876709</v>
+        <v>3.027564287185669</v>
       </c>
       <c r="C374" t="n">
-        <v>3.082777930771243</v>
+        <v>3.082778173537877</v>
       </c>
       <c r="D374" t="n">
-        <v>2.990754794097655</v>
+        <v>2.99075502961753</v>
       </c>
       <c r="E374" t="n">
-        <v>2.990754794097655</v>
+        <v>2.99075502961753</v>
       </c>
       <c r="F374" t="n">
         <v>20039900</v>
@@ -7952,16 +7952,16 @@
         <v>44960</v>
       </c>
       <c r="B377" t="n">
-        <v>2.843517303466797</v>
+        <v>2.843517541885376</v>
       </c>
       <c r="C377" t="n">
-        <v>2.871124242016908</v>
+        <v>2.871124482750229</v>
       </c>
       <c r="D377" t="n">
-        <v>2.705482610716241</v>
+        <v>2.705482837561113</v>
       </c>
       <c r="E377" t="n">
-        <v>2.806708052066648</v>
+        <v>2.806708287398906</v>
       </c>
       <c r="F377" t="n">
         <v>53290600</v>
@@ -8012,16 +8012,16 @@
         <v>44965</v>
       </c>
       <c r="B380" t="n">
-        <v>3.036766529083252</v>
+        <v>3.036766290664673</v>
       </c>
       <c r="C380" t="n">
-        <v>3.036766529083252</v>
+        <v>3.036766290664673</v>
       </c>
       <c r="D380" t="n">
-        <v>2.861922340408036</v>
+        <v>2.861922115716591</v>
       </c>
       <c r="E380" t="n">
-        <v>2.907934130670286</v>
+        <v>2.907933902366425</v>
       </c>
       <c r="F380" t="n">
         <v>50518000</v>
@@ -8052,16 +8052,16 @@
         <v>44967</v>
       </c>
       <c r="B382" t="n">
-        <v>2.953945875167847</v>
+        <v>2.953945398330688</v>
       </c>
       <c r="C382" t="n">
-        <v>3.045969022300604</v>
+        <v>3.045968530608719</v>
       </c>
       <c r="D382" t="n">
-        <v>2.92633893102802</v>
+        <v>2.926338458647279</v>
       </c>
       <c r="E382" t="n">
-        <v>3.018362078160776</v>
+        <v>3.01836159092531</v>
       </c>
       <c r="F382" t="n">
         <v>23226200</v>
@@ -8112,16 +8112,16 @@
         <v>44972</v>
       </c>
       <c r="B385" t="n">
-        <v>2.843517303466797</v>
+        <v>2.843517541885376</v>
       </c>
       <c r="C385" t="n">
-        <v>2.852719616316834</v>
+        <v>2.852719855506993</v>
       </c>
       <c r="D385" t="n">
-        <v>2.631863888515499</v>
+        <v>2.631864109187709</v>
       </c>
       <c r="E385" t="n">
-        <v>2.733089549266352</v>
+        <v>2.733089778425966</v>
       </c>
       <c r="F385" t="n">
         <v>42760100</v>
@@ -8212,16 +8212,16 @@
         <v>44981</v>
       </c>
       <c r="B390" t="n">
-        <v>2.65947151184082</v>
+        <v>2.659471273422241</v>
       </c>
       <c r="C390" t="n">
-        <v>2.806708543206081</v>
+        <v>2.806708291587871</v>
       </c>
       <c r="D390" t="n">
-        <v>2.650269197380491</v>
+        <v>2.65026895978689</v>
       </c>
       <c r="E390" t="n">
-        <v>2.797506228745752</v>
+        <v>2.797505977952519</v>
       </c>
       <c r="F390" t="n">
         <v>27929600</v>
@@ -8272,16 +8272,16 @@
         <v>44986</v>
       </c>
       <c r="B393" t="n">
-        <v>2.779101610183716</v>
+        <v>2.779101371765137</v>
       </c>
       <c r="C393" t="n">
-        <v>2.917136547003632</v>
+        <v>2.917136296743063</v>
       </c>
       <c r="D393" t="n">
-        <v>2.751494666699829</v>
+        <v>2.751494430649644</v>
       </c>
       <c r="E393" t="n">
-        <v>2.843517811646118</v>
+        <v>2.843517567701285</v>
       </c>
       <c r="F393" t="n">
         <v>32788900</v>
@@ -8292,16 +8292,16 @@
         <v>44987</v>
       </c>
       <c r="B394" t="n">
-        <v>2.68707799911499</v>
+        <v>2.687078237533569</v>
       </c>
       <c r="C394" t="n">
-        <v>2.797505753894839</v>
+        <v>2.797506002111432</v>
       </c>
       <c r="D394" t="n">
-        <v>2.68707799911499</v>
+        <v>2.687078237533569</v>
       </c>
       <c r="E394" t="n">
-        <v>2.779101128098197</v>
+        <v>2.779101374681788</v>
       </c>
       <c r="F394" t="n">
         <v>21864000</v>
@@ -8372,16 +8372,16 @@
         <v>44993</v>
       </c>
       <c r="B398" t="n">
-        <v>2.705482959747314</v>
+        <v>2.705482721328735</v>
       </c>
       <c r="C398" t="n">
-        <v>2.733089901858964</v>
+        <v>2.733089661007544</v>
       </c>
       <c r="D398" t="n">
-        <v>2.659471389561232</v>
+        <v>2.659471155197387</v>
       </c>
       <c r="E398" t="n">
-        <v>2.677876017635665</v>
+        <v>2.677875781649926</v>
       </c>
       <c r="F398" t="n">
         <v>21816400</v>
@@ -8392,16 +8392,16 @@
         <v>44994</v>
       </c>
       <c r="B399" t="n">
-        <v>2.576650381088257</v>
+        <v>2.576650142669678</v>
       </c>
       <c r="C399" t="n">
-        <v>2.705482998872884</v>
+        <v>2.705482748533367</v>
       </c>
       <c r="D399" t="n">
-        <v>2.558245752747664</v>
+        <v>2.558245516032073</v>
       </c>
       <c r="E399" t="n">
-        <v>2.687078370532291</v>
+        <v>2.687078121895762</v>
       </c>
       <c r="F399" t="n">
         <v>41324600</v>
@@ -8432,16 +8432,16 @@
         <v>44998</v>
       </c>
       <c r="B401" t="n">
-        <v>2.411008358001709</v>
+        <v>2.411008596420288</v>
       </c>
       <c r="C401" t="n">
-        <v>2.475424772623468</v>
+        <v>2.475425017412025</v>
       </c>
       <c r="D401" t="n">
-        <v>2.401806044398667</v>
+        <v>2.401806281907252</v>
       </c>
       <c r="E401" t="n">
-        <v>2.475424772623468</v>
+        <v>2.475425017412025</v>
       </c>
       <c r="F401" t="n">
         <v>31528700</v>
@@ -8512,16 +8512,16 @@
         <v>45002</v>
       </c>
       <c r="B405" t="n">
-        <v>2.349629878997803</v>
+        <v>2.349630117416382</v>
       </c>
       <c r="C405" t="n">
-        <v>2.549396016044544</v>
+        <v>2.549396274733532</v>
       </c>
       <c r="D405" t="n">
-        <v>2.349629878997803</v>
+        <v>2.349630117416382</v>
       </c>
       <c r="E405" t="n">
-        <v>2.492319814888502</v>
+        <v>2.492320067785928</v>
       </c>
       <c r="F405" t="n">
         <v>44089800</v>
@@ -8532,16 +8532,16 @@
         <v>45005</v>
       </c>
       <c r="B406" t="n">
-        <v>2.349629878997803</v>
+        <v>2.349630117416382</v>
       </c>
       <c r="C406" t="n">
-        <v>2.406705853354083</v>
+        <v>2.406706097564201</v>
       </c>
       <c r="D406" t="n">
-        <v>2.311579229426949</v>
+        <v>2.311579463984502</v>
       </c>
       <c r="E406" t="n">
-        <v>2.359142541390516</v>
+        <v>2.359142780774352</v>
       </c>
       <c r="F406" t="n">
         <v>20939200</v>
@@ -8552,16 +8552,16 @@
         <v>45006</v>
       </c>
       <c r="B407" t="n">
-        <v>2.264015913009644</v>
+        <v>2.264016151428223</v>
       </c>
       <c r="C407" t="n">
-        <v>2.397193186245646</v>
+        <v>2.397193438688833</v>
       </c>
       <c r="D407" t="n">
-        <v>2.244990361461882</v>
+        <v>2.244990597876922</v>
       </c>
       <c r="E407" t="n">
-        <v>2.368655199123645</v>
+        <v>2.368655448561559</v>
       </c>
       <c r="F407" t="n">
         <v>26738200</v>
@@ -8572,16 +8572,16 @@
         <v>45007</v>
       </c>
       <c r="B408" t="n">
-        <v>2.216452836990356</v>
+        <v>2.216452598571777</v>
       </c>
       <c r="C408" t="n">
-        <v>2.273529049947901</v>
+        <v>2.273528805389769</v>
       </c>
       <c r="D408" t="n">
-        <v>2.197427508271111</v>
+        <v>2.197427271899042</v>
       </c>
       <c r="E408" t="n">
-        <v>2.254503494428847</v>
+        <v>2.254503251917249</v>
       </c>
       <c r="F408" t="n">
         <v>26704400</v>
@@ -8612,16 +8612,16 @@
         <v>45009</v>
       </c>
       <c r="B410" t="n">
-        <v>2.292554140090942</v>
+        <v>2.292554378509521</v>
       </c>
       <c r="C410" t="n">
-        <v>2.302066803460623</v>
+        <v>2.30206704286849</v>
       </c>
       <c r="D410" t="n">
-        <v>2.149863962745944</v>
+        <v>2.149864186325184</v>
       </c>
       <c r="E410" t="n">
-        <v>2.159376626115625</v>
+        <v>2.159376850684152</v>
       </c>
       <c r="F410" t="n">
         <v>19141800</v>
@@ -8652,16 +8652,16 @@
         <v>45013</v>
       </c>
       <c r="B412" t="n">
-        <v>2.5208580493927</v>
+        <v>2.520858287811279</v>
       </c>
       <c r="C412" t="n">
-        <v>2.549396036803213</v>
+        <v>2.549396277920867</v>
       </c>
       <c r="D412" t="n">
-        <v>2.340117235659689</v>
+        <v>2.340117456984101</v>
       </c>
       <c r="E412" t="n">
-        <v>2.368655223070202</v>
+        <v>2.368655447093689</v>
       </c>
       <c r="F412" t="n">
         <v>69618900</v>
@@ -8672,16 +8672,16 @@
         <v>45014</v>
       </c>
       <c r="B413" t="n">
-        <v>2.615985155105591</v>
+        <v>2.615984916687012</v>
       </c>
       <c r="C413" t="n">
-        <v>2.644523147763493</v>
+        <v>2.644522906743987</v>
       </c>
       <c r="D413" t="n">
-        <v>2.492320293454875</v>
+        <v>2.492320066307002</v>
       </c>
       <c r="E413" t="n">
-        <v>2.539883841351184</v>
+        <v>2.539883609868411</v>
       </c>
       <c r="F413" t="n">
         <v>36856900</v>
@@ -8692,16 +8692,16 @@
         <v>45015</v>
       </c>
       <c r="B414" t="n">
-        <v>2.749162435531616</v>
+        <v>2.749162673950195</v>
       </c>
       <c r="C414" t="n">
-        <v>2.796725752381689</v>
+        <v>2.796725994925153</v>
       </c>
       <c r="D414" t="n">
-        <v>2.644522911661672</v>
+        <v>2.644523141005484</v>
       </c>
       <c r="E414" t="n">
-        <v>2.673060901771716</v>
+        <v>2.673061133590459</v>
       </c>
       <c r="F414" t="n">
         <v>39786400</v>
@@ -8712,16 +8712,16 @@
         <v>45016</v>
       </c>
       <c r="B415" t="n">
-        <v>2.711111545562744</v>
+        <v>2.711111783981323</v>
       </c>
       <c r="C415" t="n">
-        <v>2.787213079050672</v>
+        <v>2.787213324161716</v>
       </c>
       <c r="D415" t="n">
-        <v>2.654035565546636</v>
+        <v>2.654035798945881</v>
       </c>
       <c r="E415" t="n">
-        <v>2.777700415714654</v>
+        <v>2.777700659989142</v>
       </c>
       <c r="F415" t="n">
         <v>25812800</v>
@@ -8772,16 +8772,16 @@
         <v>45021</v>
       </c>
       <c r="B418" t="n">
-        <v>2.682573556900024</v>
+        <v>2.682573795318604</v>
       </c>
       <c r="C418" t="n">
-        <v>2.720624210263179</v>
+        <v>2.720624452063579</v>
       </c>
       <c r="D418" t="n">
-        <v>2.615984913514504</v>
+        <v>2.615985146014897</v>
       </c>
       <c r="E418" t="n">
-        <v>2.701598883581602</v>
+        <v>2.701599123691091</v>
       </c>
       <c r="F418" t="n">
         <v>22336100</v>
@@ -8832,16 +8832,16 @@
         <v>45027</v>
       </c>
       <c r="B421" t="n">
-        <v>2.910877704620361</v>
+        <v>2.91087794303894</v>
       </c>
       <c r="C421" t="n">
-        <v>2.920390367963574</v>
+        <v>2.920390607161298</v>
       </c>
       <c r="D421" t="n">
-        <v>2.692086220926695</v>
+        <v>2.692086441424922</v>
       </c>
       <c r="E421" t="n">
-        <v>2.71111154761312</v>
+        <v>2.711111769669636</v>
       </c>
       <c r="F421" t="n">
         <v>33609000</v>
@@ -8852,16 +8852,16 @@
         <v>45028</v>
       </c>
       <c r="B422" t="n">
-        <v>2.910877704620361</v>
+        <v>2.91087794303894</v>
       </c>
       <c r="C422" t="n">
-        <v>3.01551722819548</v>
+        <v>3.015517475184673</v>
       </c>
       <c r="D422" t="n">
-        <v>2.891852377933937</v>
+        <v>2.891852614794226</v>
       </c>
       <c r="E422" t="n">
-        <v>2.920390367963574</v>
+        <v>2.920390607161298</v>
       </c>
       <c r="F422" t="n">
         <v>32421000</v>
@@ -8932,16 +8932,16 @@
         <v>45034</v>
       </c>
       <c r="B426" t="n">
-        <v>3.025030136108398</v>
+        <v>3.025029897689819</v>
       </c>
       <c r="C426" t="n">
-        <v>3.034542800220697</v>
+        <v>3.034542561052375</v>
       </c>
       <c r="D426" t="n">
-        <v>2.948928596410207</v>
+        <v>2.948928363989592</v>
       </c>
       <c r="E426" t="n">
-        <v>2.986979479659204</v>
+        <v>2.986979244239598</v>
       </c>
       <c r="F426" t="n">
         <v>13884000</v>
@@ -8972,16 +8972,16 @@
         <v>45036</v>
       </c>
       <c r="B428" t="n">
-        <v>2.958441019058228</v>
+        <v>2.958441257476807</v>
       </c>
       <c r="C428" t="n">
-        <v>2.977466572529786</v>
+        <v>2.977466812481619</v>
       </c>
       <c r="D428" t="n">
-        <v>2.844289059027585</v>
+        <v>2.844289288246741</v>
       </c>
       <c r="E428" t="n">
-        <v>2.882339712371133</v>
+        <v>2.882339944656763</v>
       </c>
       <c r="F428" t="n">
         <v>11874200</v>
@@ -8992,16 +8992,16 @@
         <v>45040</v>
       </c>
       <c r="B429" t="n">
-        <v>3.072593212127686</v>
+        <v>3.072593450546265</v>
       </c>
       <c r="C429" t="n">
-        <v>3.110643865548496</v>
+        <v>3.110644106919625</v>
       </c>
       <c r="D429" t="n">
-        <v>2.891852381579049</v>
+        <v>2.891852605973001</v>
       </c>
       <c r="E429" t="n">
-        <v>2.948928361710265</v>
+        <v>2.948928590533042</v>
       </c>
       <c r="F429" t="n">
         <v>37103600</v>
@@ -9012,16 +9012,16 @@
         <v>45041</v>
       </c>
       <c r="B430" t="n">
-        <v>3.025030136108398</v>
+        <v>3.025029897689819</v>
       </c>
       <c r="C430" t="n">
-        <v>3.148694769568281</v>
+        <v>3.14869452140304</v>
       </c>
       <c r="D430" t="n">
-        <v>2.977466815546905</v>
+        <v>2.977466580877042</v>
       </c>
       <c r="E430" t="n">
-        <v>3.072593456669892</v>
+        <v>3.072593214502596</v>
       </c>
       <c r="F430" t="n">
         <v>18942800</v>
@@ -9132,16 +9132,16 @@
         <v>45050</v>
       </c>
       <c r="B436" t="n">
-        <v>3.025030136108398</v>
+        <v>3.025029897689819</v>
       </c>
       <c r="C436" t="n">
-        <v>3.063080792557593</v>
+        <v>3.063080551140041</v>
       </c>
       <c r="D436" t="n">
-        <v>2.958441260522505</v>
+        <v>2.958441027352147</v>
       </c>
       <c r="E436" t="n">
-        <v>3.0155174719961</v>
+        <v>3.015517234327264</v>
       </c>
       <c r="F436" t="n">
         <v>20441800</v>
@@ -9172,16 +9172,16 @@
         <v>45054</v>
       </c>
       <c r="B438" t="n">
-        <v>3.148694515228271</v>
+        <v>3.148694276809692</v>
       </c>
       <c r="C438" t="n">
-        <v>3.215283385435359</v>
+        <v>3.215283141974683</v>
       </c>
       <c r="D438" t="n">
-        <v>3.139181851884371</v>
+        <v>3.139181614186089</v>
       </c>
       <c r="E438" t="n">
-        <v>3.139181851884371</v>
+        <v>3.139181614186089</v>
       </c>
       <c r="F438" t="n">
         <v>16113900</v>
@@ -9192,16 +9192,16 @@
         <v>45055</v>
       </c>
       <c r="B439" t="n">
-        <v>3.025030136108398</v>
+        <v>3.025029897689819</v>
       </c>
       <c r="C439" t="n">
-        <v>3.158207433680579</v>
+        <v>3.158207184765595</v>
       </c>
       <c r="D439" t="n">
-        <v>3.0155174719961</v>
+        <v>3.015517234327264</v>
       </c>
       <c r="E439" t="n">
-        <v>3.129669441343684</v>
+        <v>3.129669194677929</v>
       </c>
       <c r="F439" t="n">
         <v>32144800</v>
@@ -9312,16 +9312,16 @@
         <v>45063</v>
       </c>
       <c r="B445" t="n">
-        <v>3.253334283828735</v>
+        <v>3.253334045410156</v>
       </c>
       <c r="C445" t="n">
-        <v>3.300897604130366</v>
+        <v>3.300897362226138</v>
       </c>
       <c r="D445" t="n">
-        <v>3.082106103943065</v>
+        <v>3.082105878072837</v>
       </c>
       <c r="E445" t="n">
-        <v>3.091618768003391</v>
+        <v>3.091618541436033</v>
       </c>
       <c r="F445" t="n">
         <v>27916800</v>
@@ -9332,16 +9332,16 @@
         <v>45064</v>
       </c>
       <c r="B446" t="n">
-        <v>3.300897598266602</v>
+        <v>3.300897121429443</v>
       </c>
       <c r="C446" t="n">
-        <v>3.338948254440312</v>
+        <v>3.338947772106478</v>
       </c>
       <c r="D446" t="n">
-        <v>3.177232738902241</v>
+        <v>3.177232279929315</v>
       </c>
       <c r="E446" t="n">
-        <v>3.253334278049463</v>
+        <v>3.253333808083151</v>
       </c>
       <c r="F446" t="n">
         <v>40825600</v>
@@ -9412,16 +9412,16 @@
         <v>45070</v>
       </c>
       <c r="B450" t="n">
-        <v>3.319922685623169</v>
+        <v>3.319922924041748</v>
       </c>
       <c r="C450" t="n">
-        <v>3.529201506203401</v>
+        <v>3.529201759651233</v>
       </c>
       <c r="D450" t="n">
-        <v>3.262846705501229</v>
+        <v>3.262846939820925</v>
       </c>
       <c r="E450" t="n">
-        <v>3.462612862727804</v>
+        <v>3.462613111393607</v>
       </c>
       <c r="F450" t="n">
         <v>35329500</v>
@@ -9432,16 +9432,16 @@
         <v>45071</v>
       </c>
       <c r="B451" t="n">
-        <v>3.281872034072876</v>
+        <v>3.281872272491455</v>
       </c>
       <c r="C451" t="n">
-        <v>3.424561984458784</v>
+        <v>3.424562233243379</v>
       </c>
       <c r="D451" t="n">
-        <v>3.272359370713815</v>
+        <v>3.272359608441327</v>
       </c>
       <c r="E451" t="n">
-        <v>3.376998667663482</v>
+        <v>3.376998912992737</v>
       </c>
       <c r="F451" t="n">
         <v>36092900</v>
@@ -9452,16 +9452,16 @@
         <v>45072</v>
       </c>
       <c r="B452" t="n">
-        <v>3.291384935379028</v>
+        <v>3.291384696960449</v>
       </c>
       <c r="C452" t="n">
-        <v>3.348460919659638</v>
+        <v>3.348460677106637</v>
       </c>
       <c r="D452" t="n">
-        <v>3.177232740018008</v>
+        <v>3.17723250986829</v>
       </c>
       <c r="E452" t="n">
-        <v>3.33894825561287</v>
+        <v>3.338948013748939</v>
       </c>
       <c r="F452" t="n">
         <v>25686400</v>
@@ -9472,16 +9472,16 @@
         <v>45075</v>
       </c>
       <c r="B453" t="n">
-        <v>3.357973337173462</v>
+        <v>3.357973575592041</v>
       </c>
       <c r="C453" t="n">
-        <v>3.415049317263714</v>
+        <v>3.415049559734729</v>
       </c>
       <c r="D453" t="n">
-        <v>3.291384693734835</v>
+        <v>3.291384927425571</v>
       </c>
       <c r="E453" t="n">
-        <v>3.319922683779961</v>
+        <v>3.319922919496916</v>
       </c>
       <c r="F453" t="n">
         <v>14544800</v>
@@ -9532,16 +9532,16 @@
         <v>45078</v>
       </c>
       <c r="B456" t="n">
-        <v>3.576765060424805</v>
+        <v>3.576764822006226</v>
       </c>
       <c r="C456" t="n">
-        <v>3.662379036291428</v>
+        <v>3.662378792166026</v>
       </c>
       <c r="D456" t="n">
-        <v>3.376998889936218</v>
+        <v>3.376998664833572</v>
       </c>
       <c r="E456" t="n">
-        <v>3.472125756587821</v>
+        <v>3.472125525144246</v>
       </c>
       <c r="F456" t="n">
         <v>28377100</v>
@@ -9552,16 +9552,16 @@
         <v>45079</v>
       </c>
       <c r="B457" t="n">
-        <v>3.529201507568359</v>
+        <v>3.529201745986938</v>
       </c>
       <c r="C457" t="n">
-        <v>3.643353467856389</v>
+        <v>3.643353713986613</v>
       </c>
       <c r="D457" t="n">
-        <v>3.491150854139016</v>
+        <v>3.491151089987047</v>
       </c>
       <c r="E457" t="n">
-        <v>3.614815477784382</v>
+        <v>3.614815721986695</v>
       </c>
       <c r="F457" t="n">
         <v>24144300</v>
@@ -9612,16 +9612,16 @@
         <v>45084</v>
       </c>
       <c r="B460" t="n">
-        <v>3.757505893707275</v>
+        <v>3.757505655288696</v>
       </c>
       <c r="C460" t="n">
-        <v>3.852632760125061</v>
+        <v>3.85263251567056</v>
       </c>
       <c r="D460" t="n">
-        <v>3.681404355213087</v>
+        <v>3.681404121623248</v>
       </c>
       <c r="E460" t="n">
-        <v>3.747993229745477</v>
+        <v>3.747992991930488</v>
       </c>
       <c r="F460" t="n">
         <v>19382700</v>
@@ -9652,16 +9652,16 @@
         <v>45089</v>
       </c>
       <c r="B462" t="n">
-        <v>3.795556545257568</v>
+        <v>3.795556306838989</v>
       </c>
       <c r="C462" t="n">
-        <v>3.805069209208598</v>
+        <v>3.805068970192479</v>
       </c>
       <c r="D462" t="n">
-        <v>3.747993225502421</v>
+        <v>3.74799299007154</v>
       </c>
       <c r="E462" t="n">
-        <v>3.786043881306539</v>
+        <v>3.786043643485499</v>
       </c>
       <c r="F462" t="n">
         <v>16242400</v>
@@ -9672,16 +9672,16 @@
         <v>45090</v>
       </c>
       <c r="B463" t="n">
-        <v>3.700429916381836</v>
+        <v>3.700429677963257</v>
       </c>
       <c r="C463" t="n">
-        <v>3.814582110922048</v>
+        <v>3.814581865148647</v>
       </c>
       <c r="D463" t="n">
-        <v>3.662379033668566</v>
+        <v>3.662378797701604</v>
       </c>
       <c r="E463" t="n">
-        <v>3.786043892187145</v>
+        <v>3.78604364825246</v>
       </c>
       <c r="F463" t="n">
         <v>19986600</v>
@@ -9712,16 +9712,16 @@
         <v>45092</v>
       </c>
       <c r="B465" t="n">
-        <v>3.757505893707275</v>
+        <v>3.757505655288696</v>
       </c>
       <c r="C465" t="n">
-        <v>3.79555654955447</v>
+        <v>3.795556308721528</v>
       </c>
       <c r="D465" t="n">
-        <v>3.71945523786008</v>
+        <v>3.719455001855864</v>
       </c>
       <c r="E465" t="n">
-        <v>3.757505893707275</v>
+        <v>3.757505655288696</v>
       </c>
       <c r="F465" t="n">
         <v>13781200</v>
@@ -9732,16 +9732,16 @@
         <v>45093</v>
       </c>
       <c r="B466" t="n">
-        <v>3.757505893707275</v>
+        <v>3.757505655288696</v>
       </c>
       <c r="C466" t="n">
-        <v>3.776531221630873</v>
+        <v>3.776530982005112</v>
       </c>
       <c r="D466" t="n">
-        <v>3.709942573898282</v>
+        <v>3.709942338497656</v>
       </c>
       <c r="E466" t="n">
-        <v>3.728967901821879</v>
+        <v>3.728967665214073</v>
       </c>
       <c r="F466" t="n">
         <v>14449100</v>
@@ -9752,16 +9752,16 @@
         <v>45096</v>
       </c>
       <c r="B467" t="n">
-        <v>3.776531219482422</v>
+        <v>3.776530981063843</v>
       </c>
       <c r="C467" t="n">
-        <v>3.814582102107769</v>
+        <v>3.814581861286975</v>
       </c>
       <c r="D467" t="n">
-        <v>3.738480563656874</v>
+        <v>3.738480327640495</v>
       </c>
       <c r="E467" t="n">
-        <v>3.786043883438809</v>
+        <v>3.78604364441968</v>
       </c>
       <c r="F467" t="n">
         <v>9550900</v>
@@ -9772,16 +9772,16 @@
         <v>45097</v>
       </c>
       <c r="B468" t="n">
-        <v>3.94775915145874</v>
+        <v>3.947758913040161</v>
       </c>
       <c r="C468" t="n">
-        <v>3.966784478185788</v>
+        <v>3.966784238618205</v>
       </c>
       <c r="D468" t="n">
-        <v>3.767018320752002</v>
+        <v>3.767018093248975</v>
       </c>
       <c r="E468" t="n">
-        <v>3.78604364747905</v>
+        <v>3.786043418827019</v>
       </c>
       <c r="F468" t="n">
         <v>35176100</v>
@@ -9852,16 +9852,16 @@
         <v>45103</v>
       </c>
       <c r="B472" t="n">
-        <v>4.204600811004639</v>
+        <v>4.204601287841797</v>
       </c>
       <c r="C472" t="n">
-        <v>4.280702109260005</v>
+        <v>4.280702594727692</v>
       </c>
       <c r="D472" t="n">
-        <v>4.128499512749272</v>
+        <v>4.128499980955902</v>
       </c>
       <c r="E472" t="n">
-        <v>4.138011948231434</v>
+        <v>4.138012417516855</v>
       </c>
       <c r="F472" t="n">
         <v>42881900</v>
@@ -9872,16 +9872,16 @@
         <v>45104</v>
       </c>
       <c r="B473" t="n">
-        <v>4.223626136779785</v>
+        <v>4.223626613616943</v>
       </c>
       <c r="C473" t="n">
-        <v>4.290214999572086</v>
+        <v>4.290215483926966</v>
       </c>
       <c r="D473" t="n">
-        <v>4.080935975710292</v>
+        <v>4.080936436438077</v>
       </c>
       <c r="E473" t="n">
-        <v>4.233138572264675</v>
+        <v>4.233139050175764</v>
       </c>
       <c r="F473" t="n">
         <v>76576700</v>
@@ -9892,16 +9892,16 @@
         <v>45105</v>
       </c>
       <c r="B474" t="n">
-        <v>4.176063060760498</v>
+        <v>4.176063537597656</v>
       </c>
       <c r="C474" t="n">
-        <v>4.261677257597817</v>
+        <v>4.261677744210696</v>
       </c>
       <c r="D474" t="n">
-        <v>4.090449317522748</v>
+        <v>4.090449784584236</v>
       </c>
       <c r="E474" t="n">
-        <v>4.223626604247801</v>
+        <v>4.223627086515927</v>
       </c>
       <c r="F474" t="n">
         <v>30177100</v>
@@ -9912,16 +9912,16 @@
         <v>45106</v>
       </c>
       <c r="B475" t="n">
-        <v>4.366316795349121</v>
+        <v>4.366317272186279</v>
       </c>
       <c r="C475" t="n">
-        <v>4.366316795349121</v>
+        <v>4.366317272186279</v>
       </c>
       <c r="D475" t="n">
-        <v>4.185575964547351</v>
+        <v>4.185576421646147</v>
       </c>
       <c r="E475" t="n">
-        <v>4.185575964547351</v>
+        <v>4.185576421646147</v>
       </c>
       <c r="F475" t="n">
         <v>40765500</v>
@@ -9952,16 +9952,16 @@
         <v>45110</v>
       </c>
       <c r="B477" t="n">
-        <v>4.252164363861084</v>
+        <v>4.252163887023926</v>
       </c>
       <c r="C477" t="n">
-        <v>4.299727907308124</v>
+        <v>4.299727425137196</v>
       </c>
       <c r="D477" t="n">
-        <v>4.195088383884376</v>
+        <v>4.19508791344771</v>
       </c>
       <c r="E477" t="n">
-        <v>4.233139037202181</v>
+        <v>4.233138562498521</v>
       </c>
       <c r="F477" t="n">
         <v>20197900</v>
@@ -10012,16 +10012,16 @@
         <v>45113</v>
       </c>
       <c r="B480" t="n">
-        <v>3.957271814346313</v>
+        <v>3.957271575927734</v>
       </c>
       <c r="C480" t="n">
-        <v>4.061911344129392</v>
+        <v>4.061911099406468</v>
       </c>
       <c r="D480" t="n">
-        <v>3.909708721608256</v>
+        <v>3.909708486055269</v>
       </c>
       <c r="E480" t="n">
-        <v>4.061911344129392</v>
+        <v>4.061911099406468</v>
       </c>
       <c r="F480" t="n">
         <v>22675100</v>
@@ -10032,16 +10032,16 @@
         <v>45114</v>
       </c>
       <c r="B481" t="n">
-        <v>3.995322704315186</v>
+        <v>3.995322465896606</v>
       </c>
       <c r="C481" t="n">
-        <v>4.042886253442594</v>
+        <v>4.042886012185687</v>
       </c>
       <c r="D481" t="n">
-        <v>3.947759608787399</v>
+        <v>3.94775937320712</v>
       </c>
       <c r="E481" t="n">
-        <v>3.976297375384147</v>
+        <v>3.976297138100893</v>
       </c>
       <c r="F481" t="n">
         <v>19055100</v>
@@ -10092,16 +10092,16 @@
         <v>45119</v>
       </c>
       <c r="B484" t="n">
-        <v>4.014348030090332</v>
+        <v>4.014347553253174</v>
       </c>
       <c r="C484" t="n">
-        <v>4.128500457186447</v>
+        <v>4.128499966789897</v>
       </c>
       <c r="D484" t="n">
-        <v>4.004835592432102</v>
+        <v>4.004835116724861</v>
       </c>
       <c r="E484" t="n">
-        <v>4.090449799354283</v>
+        <v>4.090449313477511</v>
       </c>
       <c r="F484" t="n">
         <v>6157400</v>
@@ -10112,16 +10112,16 @@
         <v>45120</v>
       </c>
       <c r="B485" t="n">
-        <v>3.995322704315186</v>
+        <v>3.995322465896606</v>
       </c>
       <c r="C485" t="n">
-        <v>4.071424473638964</v>
+        <v>4.071424230679055</v>
       </c>
       <c r="D485" t="n">
-        <v>3.957272046453107</v>
+        <v>3.957271810305179</v>
       </c>
       <c r="E485" t="n">
-        <v>4.023860924511555</v>
+        <v>4.023860684389974</v>
       </c>
       <c r="F485" t="n">
         <v>10522300</v>
@@ -10132,16 +10132,16 @@
         <v>45121</v>
       </c>
       <c r="B486" t="n">
-        <v>3.881170511245728</v>
+        <v>3.881170272827148</v>
       </c>
       <c r="C486" t="n">
-        <v>4.014347806231721</v>
+        <v>4.01434755963212</v>
       </c>
       <c r="D486" t="n">
-        <v>3.814582090552529</v>
+        <v>3.814581856224446</v>
       </c>
       <c r="E486" t="n">
-        <v>3.995322478376579</v>
+        <v>3.995322232945695</v>
       </c>
       <c r="F486" t="n">
         <v>16845900</v>
@@ -10172,16 +10172,16 @@
         <v>45125</v>
       </c>
       <c r="B488" t="n">
-        <v>4.071424007415771</v>
+        <v>4.07142448425293</v>
       </c>
       <c r="C488" t="n">
-        <v>4.185575967930341</v>
+        <v>4.185576458136752</v>
       </c>
       <c r="D488" t="n">
-        <v>4.004835136982487</v>
+        <v>4.004835606020889</v>
       </c>
       <c r="E488" t="n">
-        <v>4.023860463734916</v>
+        <v>4.023860935001526</v>
       </c>
       <c r="F488" t="n">
         <v>19854400</v>
@@ -10212,16 +10212,16 @@
         <v>45127</v>
       </c>
       <c r="B490" t="n">
-        <v>3.995322704315186</v>
+        <v>3.995322465896606</v>
       </c>
       <c r="C490" t="n">
-        <v>4.080936911304672</v>
+        <v>4.080936667777115</v>
       </c>
       <c r="D490" t="n">
-        <v>3.947759608787399</v>
+        <v>3.94775937320712</v>
       </c>
       <c r="E490" t="n">
-        <v>4.071424473638964</v>
+        <v>4.071424230679055</v>
       </c>
       <c r="F490" t="n">
         <v>13981900</v>
@@ -10232,16 +10232,16 @@
         <v>45128</v>
       </c>
       <c r="B491" t="n">
-        <v>4.061911582946777</v>
+        <v>4.061910629272461</v>
       </c>
       <c r="C491" t="n">
-        <v>4.099962240814224</v>
+        <v>4.099961278206199</v>
       </c>
       <c r="D491" t="n">
-        <v>3.97629737594521</v>
+        <v>3.976296442371792</v>
       </c>
       <c r="E491" t="n">
-        <v>4.004835596145607</v>
+        <v>4.004834655871853</v>
       </c>
       <c r="F491" t="n">
         <v>9991000</v>
@@ -10272,16 +10272,16 @@
         <v>45132</v>
       </c>
       <c r="B493" t="n">
-        <v>3.995322704315186</v>
+        <v>3.995322465896606</v>
       </c>
       <c r="C493" t="n">
-        <v>4.090449802570003</v>
+        <v>4.090449558474769</v>
       </c>
       <c r="D493" t="n">
-        <v>3.966784937718438</v>
+        <v>3.966784701002833</v>
       </c>
       <c r="E493" t="n">
-        <v>4.061911582373633</v>
+        <v>4.061911339981402</v>
       </c>
       <c r="F493" t="n">
         <v>14413200</v>
@@ -10292,16 +10292,16 @@
         <v>45133</v>
       </c>
       <c r="B494" t="n">
-        <v>4.014348030090332</v>
+        <v>4.014347553253174</v>
       </c>
       <c r="C494" t="n">
-        <v>4.033373359006414</v>
+        <v>4.033372879909367</v>
       </c>
       <c r="D494" t="n">
-        <v>3.957272043342085</v>
+        <v>3.957271573284596</v>
       </c>
       <c r="E494" t="n">
-        <v>3.99532270117425</v>
+        <v>3.995322226596981</v>
       </c>
       <c r="F494" t="n">
         <v>6399600</v>
@@ -10352,16 +10352,16 @@
         <v>45138</v>
       </c>
       <c r="B497" t="n">
-        <v>3.980106353759766</v>
+        <v>3.980106115341187</v>
       </c>
       <c r="C497" t="n">
-        <v>4.008809245599202</v>
+        <v>4.008809005461245</v>
       </c>
       <c r="D497" t="n">
-        <v>3.922701026297883</v>
+        <v>3.922700791318031</v>
       </c>
       <c r="E497" t="n">
-        <v>3.941836135451844</v>
+        <v>3.941835899325749</v>
       </c>
       <c r="F497" t="n">
         <v>13989300</v>
@@ -10372,16 +10372,16 @@
         <v>45139</v>
       </c>
       <c r="B498" t="n">
-        <v>3.980106353759766</v>
+        <v>3.980106115341187</v>
       </c>
       <c r="C498" t="n">
-        <v>4.018376572067687</v>
+        <v>4.018376331356624</v>
       </c>
       <c r="D498" t="n">
-        <v>3.884430807989962</v>
+        <v>3.884430575302593</v>
       </c>
       <c r="E498" t="n">
-        <v>3.970539027291279</v>
+        <v>3.970538789445808</v>
       </c>
       <c r="F498" t="n">
         <v>24308900</v>
@@ -10412,16 +10412,16 @@
         <v>45141</v>
       </c>
       <c r="B500" t="n">
-        <v>3.922701120376587</v>
+        <v>3.922700643539429</v>
       </c>
       <c r="C500" t="n">
-        <v>4.037511778053872</v>
+        <v>4.037511287260518</v>
       </c>
       <c r="D500" t="n">
-        <v>3.893998684065766</v>
+        <v>3.893998210717629</v>
       </c>
       <c r="E500" t="n">
-        <v>4.027944451355932</v>
+        <v>4.027943961725565</v>
       </c>
       <c r="F500" t="n">
         <v>21426900</v>
@@ -10452,16 +10452,16 @@
         <v>45145</v>
       </c>
       <c r="B502" t="n">
-        <v>3.846160650253296</v>
+        <v>3.846160411834717</v>
       </c>
       <c r="C502" t="n">
-        <v>3.922701088074537</v>
+        <v>3.922700844911313</v>
       </c>
       <c r="D502" t="n">
-        <v>3.817457986070331</v>
+        <v>3.817457749430993</v>
       </c>
       <c r="E502" t="n">
-        <v>3.913133761455379</v>
+        <v>3.913133518885223</v>
       </c>
       <c r="F502" t="n">
         <v>14729300</v>
@@ -10472,16 +10472,16 @@
         <v>45146</v>
       </c>
       <c r="B503" t="n">
-        <v>3.798322916030884</v>
+        <v>3.798322677612305</v>
       </c>
       <c r="C503" t="n">
-        <v>3.817458025684763</v>
+        <v>3.817457786065083</v>
       </c>
       <c r="D503" t="n">
-        <v>3.702647139652991</v>
+        <v>3.702646907239926</v>
       </c>
       <c r="E503" t="n">
-        <v>3.798322916030884</v>
+        <v>3.798322677612305</v>
       </c>
       <c r="F503" t="n">
         <v>17862300</v>
@@ -10512,16 +10512,16 @@
         <v>45148</v>
       </c>
       <c r="B505" t="n">
-        <v>3.740917444229126</v>
+        <v>3.740917205810547</v>
       </c>
       <c r="C505" t="n">
-        <v>3.788755216537224</v>
+        <v>3.788754975069817</v>
       </c>
       <c r="D505" t="n">
-        <v>3.702646998274156</v>
+        <v>3.702646762294654</v>
       </c>
       <c r="E505" t="n">
-        <v>3.760052553152365</v>
+        <v>3.760052313514255</v>
       </c>
       <c r="F505" t="n">
         <v>11449000</v>
@@ -10532,16 +10532,16 @@
         <v>45149</v>
       </c>
       <c r="B506" t="n">
-        <v>3.683511734008789</v>
+        <v>3.683511972427368</v>
       </c>
       <c r="C506" t="n">
-        <v>3.750484840524209</v>
+        <v>3.750485083277681</v>
       </c>
       <c r="D506" t="n">
-        <v>3.63567396371812</v>
+        <v>3.635674199040356</v>
       </c>
       <c r="E506" t="n">
-        <v>3.731349732407941</v>
+        <v>3.731349973922877</v>
       </c>
       <c r="F506" t="n">
         <v>13400900</v>
@@ -10712,16 +10712,16 @@
         <v>45162</v>
       </c>
       <c r="B515" t="n">
-        <v>3.568701267242432</v>
+        <v>3.568701028823853</v>
       </c>
       <c r="C515" t="n">
-        <v>3.64524170360951</v>
+        <v>3.645241460077401</v>
       </c>
       <c r="D515" t="n">
-        <v>3.444322830037436</v>
+        <v>3.444322599928359</v>
       </c>
       <c r="E515" t="n">
-        <v>3.453890384583321</v>
+        <v>3.453890153835052</v>
       </c>
       <c r="F515" t="n">
         <v>42127000</v>
@@ -10732,16 +10732,16 @@
         <v>45163</v>
       </c>
       <c r="B516" t="n">
-        <v>3.62610650062561</v>
+        <v>3.626106739044189</v>
       </c>
       <c r="C516" t="n">
-        <v>3.664376717818205</v>
+        <v>3.664376958753072</v>
       </c>
       <c r="D516" t="n">
-        <v>3.549566066240422</v>
+        <v>3.549566299626424</v>
       </c>
       <c r="E516" t="n">
-        <v>3.616538946327462</v>
+        <v>3.616539184116969</v>
       </c>
       <c r="F516" t="n">
         <v>21198200</v>
@@ -10772,16 +10772,16 @@
         <v>45167</v>
       </c>
       <c r="B518" t="n">
-        <v>3.65480899810791</v>
+        <v>3.654809236526489</v>
       </c>
       <c r="C518" t="n">
-        <v>3.664376551973043</v>
+        <v>3.664376791015754</v>
       </c>
       <c r="D518" t="n">
-        <v>3.578268567186847</v>
+        <v>3.578268800612372</v>
       </c>
       <c r="E518" t="n">
-        <v>3.616538782647379</v>
+        <v>3.61653901856943</v>
       </c>
       <c r="F518" t="n">
         <v>13520200</v>
@@ -10912,16 +10912,16 @@
         <v>45177</v>
       </c>
       <c r="B525" t="n">
-        <v>3.549566030502319</v>
+        <v>3.549566268920898</v>
       </c>
       <c r="C525" t="n">
-        <v>3.587836247309597</v>
+        <v>3.587836488298725</v>
       </c>
       <c r="D525" t="n">
-        <v>3.511295813695041</v>
+        <v>3.511296049543073</v>
       </c>
       <c r="E525" t="n">
-        <v>3.53043092209868</v>
+        <v>3.530431159231985</v>
       </c>
       <c r="F525" t="n">
         <v>26042800</v>
@@ -10952,16 +10952,16 @@
         <v>45181</v>
       </c>
       <c r="B527" t="n">
-        <v>3.712214469909668</v>
+        <v>3.712214708328247</v>
       </c>
       <c r="C527" t="n">
-        <v>3.769619791871123</v>
+        <v>3.769620033976584</v>
       </c>
       <c r="D527" t="n">
-        <v>3.61653870519877</v>
+        <v>3.616538937472532</v>
       </c>
       <c r="E527" t="n">
-        <v>3.635673812519255</v>
+        <v>3.635674046021977</v>
       </c>
       <c r="F527" t="n">
         <v>15715300</v>
@@ -10992,16 +10992,16 @@
         <v>45183</v>
       </c>
       <c r="B529" t="n">
-        <v>3.798322916030884</v>
+        <v>3.798322677612305</v>
       </c>
       <c r="C529" t="n">
-        <v>3.836593363447141</v>
+        <v>3.836593122626347</v>
       </c>
       <c r="D529" t="n">
-        <v>3.760052696723127</v>
+        <v>3.760052460706747</v>
       </c>
       <c r="E529" t="n">
-        <v>3.798322916030884</v>
+        <v>3.798322677612305</v>
       </c>
       <c r="F529" t="n">
         <v>9553000</v>
@@ -11032,16 +11032,16 @@
         <v>45187</v>
       </c>
       <c r="B531" t="n">
-        <v>3.817457914352417</v>
+        <v>3.817457675933838</v>
       </c>
       <c r="C531" t="n">
-        <v>3.884430796187795</v>
+        <v>3.884430553586438</v>
       </c>
       <c r="D531" t="n">
-        <v>3.740917477969129</v>
+        <v>3.740917244330867</v>
       </c>
       <c r="E531" t="n">
-        <v>3.817457914352417</v>
+        <v>3.817457675933838</v>
       </c>
       <c r="F531" t="n">
         <v>23371600</v>
@@ -11072,16 +11072,16 @@
         <v>45189</v>
       </c>
       <c r="B533" t="n">
-        <v>3.645241737365723</v>
+        <v>3.645241498947144</v>
       </c>
       <c r="C533" t="n">
-        <v>3.769620175722507</v>
+        <v>3.769619929168903</v>
       </c>
       <c r="D533" t="n">
-        <v>3.645241737365723</v>
+        <v>3.645241498947144</v>
       </c>
       <c r="E533" t="n">
-        <v>3.740917511819056</v>
+        <v>3.740917267142762</v>
       </c>
       <c r="F533" t="n">
         <v>23728500</v>
@@ -11172,16 +11172,16 @@
         <v>45196</v>
       </c>
       <c r="B538" t="n">
-        <v>3.396485090255737</v>
+        <v>3.396484851837158</v>
       </c>
       <c r="C538" t="n">
-        <v>3.492160864751185</v>
+        <v>3.49216061961658</v>
       </c>
       <c r="D538" t="n">
-        <v>3.358214871700957</v>
+        <v>3.358214635968781</v>
       </c>
       <c r="E538" t="n">
-        <v>3.453890418087908</v>
+        <v>3.453890175639724</v>
       </c>
       <c r="F538" t="n">
         <v>21389800</v>
@@ -11252,16 +11252,16 @@
         <v>45202</v>
       </c>
       <c r="B542" t="n">
-        <v>3.31037712097168</v>
+        <v>3.310376882553101</v>
       </c>
       <c r="C542" t="n">
-        <v>3.406052668007885</v>
+        <v>3.406052422698603</v>
       </c>
       <c r="D542" t="n">
-        <v>3.272106902157197</v>
+        <v>3.2721066664949</v>
       </c>
       <c r="E542" t="n">
-        <v>3.3199446756753</v>
+        <v>3.31994443656765</v>
       </c>
       <c r="F542" t="n">
         <v>29291500</v>
@@ -11272,16 +11272,16 @@
         <v>45203</v>
       </c>
       <c r="B543" t="n">
-        <v>3.319944620132446</v>
+        <v>3.319944381713867</v>
       </c>
       <c r="C543" t="n">
-        <v>3.348647283763111</v>
+        <v>3.348647043283278</v>
       </c>
       <c r="D543" t="n">
-        <v>3.300809511045337</v>
+        <v>3.300809274000926</v>
       </c>
       <c r="E543" t="n">
-        <v>3.319944620132446</v>
+        <v>3.319944381713867</v>
       </c>
       <c r="F543" t="n">
         <v>10591900</v>
@@ -11372,16 +11372,16 @@
         <v>45210</v>
       </c>
       <c r="B548" t="n">
-        <v>3.482593059539795</v>
+        <v>3.482593297958374</v>
       </c>
       <c r="C548" t="n">
-        <v>3.511295721390723</v>
+        <v>3.511295961774288</v>
       </c>
       <c r="D548" t="n">
-        <v>3.396484845878531</v>
+        <v>3.396485078402136</v>
       </c>
       <c r="E548" t="n">
-        <v>3.41561995377915</v>
+        <v>3.415620187612745</v>
       </c>
       <c r="F548" t="n">
         <v>15610900</v>
@@ -11472,16 +11472,16 @@
         <v>45218</v>
       </c>
       <c r="B553" t="n">
-        <v>3.42021107673645</v>
+        <v>3.420210838317871</v>
       </c>
       <c r="C553" t="n">
-        <v>3.449114241758219</v>
+        <v>3.449114001324837</v>
       </c>
       <c r="D553" t="n">
-        <v>3.304598416649374</v>
+        <v>3.304598186290007</v>
       </c>
       <c r="E553" t="n">
-        <v>3.314232804989964</v>
+        <v>3.314232573958996</v>
       </c>
       <c r="F553" t="n">
         <v>35125300</v>
@@ -11492,16 +11492,16 @@
         <v>45219</v>
       </c>
       <c r="B554" t="n">
-        <v>3.449113845825195</v>
+        <v>3.449114084243774</v>
       </c>
       <c r="C554" t="n">
-        <v>3.478017007529093</v>
+        <v>3.478017247945591</v>
       </c>
       <c r="D554" t="n">
-        <v>3.381673135182768</v>
+        <v>3.381673368939535</v>
       </c>
       <c r="E554" t="n">
-        <v>3.381673135182768</v>
+        <v>3.381673368939535</v>
       </c>
       <c r="F554" t="n">
         <v>22281100</v>
@@ -11532,16 +11532,16 @@
         <v>45223</v>
       </c>
       <c r="B556" t="n">
-        <v>3.612898826599121</v>
+        <v>3.6128990650177</v>
       </c>
       <c r="C556" t="n">
-        <v>3.632167601964829</v>
+        <v>3.632167841654973</v>
       </c>
       <c r="D556" t="n">
-        <v>3.487651557020096</v>
+        <v>3.48765178717349</v>
       </c>
       <c r="E556" t="n">
-        <v>3.497286174404871</v>
+        <v>3.497286405194064</v>
       </c>
       <c r="F556" t="n">
         <v>18123000</v>
@@ -11552,16 +11552,16 @@
         <v>45224</v>
       </c>
       <c r="B557" t="n">
-        <v>3.593630313873291</v>
+        <v>3.593630075454712</v>
       </c>
       <c r="C557" t="n">
-        <v>3.738146369379956</v>
+        <v>3.738146121373493</v>
       </c>
       <c r="D557" t="n">
-        <v>3.545458371938382</v>
+        <v>3.545458136715759</v>
       </c>
       <c r="E557" t="n">
-        <v>3.6418022558082</v>
+        <v>3.641802014193664</v>
       </c>
       <c r="F557" t="n">
         <v>23871300</v>
@@ -11572,16 +11572,16 @@
         <v>45225</v>
       </c>
       <c r="B558" t="n">
-        <v>3.651436328887939</v>
+        <v>3.651436567306519</v>
       </c>
       <c r="C558" t="n">
-        <v>3.670705103998014</v>
+        <v>3.670705343674738</v>
       </c>
       <c r="D558" t="n">
-        <v>3.545458065782528</v>
+        <v>3.545458297281314</v>
       </c>
       <c r="E558" t="n">
-        <v>3.593630003557715</v>
+        <v>3.593630238201861</v>
       </c>
       <c r="F558" t="n">
         <v>21310400</v>
@@ -11632,16 +11632,16 @@
         <v>45230</v>
       </c>
       <c r="B561" t="n">
-        <v>3.497286081314087</v>
+        <v>3.497286319732666</v>
       </c>
       <c r="C561" t="n">
-        <v>3.516554856166899</v>
+        <v>3.516555095899078</v>
       </c>
       <c r="D561" t="n">
-        <v>3.420210752200924</v>
+        <v>3.420210985365089</v>
       </c>
       <c r="E561" t="n">
-        <v>3.506920468740493</v>
+        <v>3.506920707815872</v>
       </c>
       <c r="F561" t="n">
         <v>11282600</v>
@@ -11652,16 +11652,16 @@
         <v>45231</v>
       </c>
       <c r="B562" t="n">
-        <v>3.612898826599121</v>
+        <v>3.6128990650177</v>
       </c>
       <c r="C562" t="n">
-        <v>3.612898826599121</v>
+        <v>3.6128990650177</v>
       </c>
       <c r="D562" t="n">
-        <v>3.506920562087725</v>
+        <v>3.5069207935127</v>
       </c>
       <c r="E562" t="n">
-        <v>3.506920562087725</v>
+        <v>3.5069207935127</v>
       </c>
       <c r="F562" t="n">
         <v>18109500</v>
@@ -11672,16 +11672,16 @@
         <v>45233</v>
       </c>
       <c r="B563" t="n">
-        <v>3.651436328887939</v>
+        <v>3.651436567306519</v>
       </c>
       <c r="C563" t="n">
-        <v>3.709242654218164</v>
+        <v>3.709242896411176</v>
       </c>
       <c r="D563" t="n">
-        <v>3.61289877866779</v>
+        <v>3.61289901457008</v>
       </c>
       <c r="E563" t="n">
-        <v>3.661070716442977</v>
+        <v>3.661070955490628</v>
       </c>
       <c r="F563" t="n">
         <v>16239100</v>
@@ -11692,16 +11692,16 @@
         <v>45236</v>
       </c>
       <c r="B564" t="n">
-        <v>3.651436328887939</v>
+        <v>3.651436567306519</v>
       </c>
       <c r="C564" t="n">
-        <v>3.699608266663126</v>
+        <v>3.699608508227067</v>
       </c>
       <c r="D564" t="n">
-        <v>3.622533166222827</v>
+        <v>3.62253340275419</v>
       </c>
       <c r="E564" t="n">
-        <v>3.670705103998014</v>
+        <v>3.670705343674738</v>
       </c>
       <c r="F564" t="n">
         <v>9299300</v>
@@ -11892,16 +11892,16 @@
         <v>45251</v>
       </c>
       <c r="B574" t="n">
-        <v>3.506920576095581</v>
+        <v>3.50692081451416</v>
       </c>
       <c r="C574" t="n">
-        <v>3.622533228751628</v>
+        <v>3.622533475030152</v>
       </c>
       <c r="D574" t="n">
-        <v>3.506920576095581</v>
+        <v>3.50692081451416</v>
       </c>
       <c r="E574" t="n">
-        <v>3.612898841030291</v>
+        <v>3.612899086653819</v>
       </c>
       <c r="F574" t="n">
         <v>23500900</v>
@@ -11912,16 +11912,16 @@
         <v>45252</v>
       </c>
       <c r="B575" t="n">
-        <v>3.516555070877075</v>
+        <v>3.516554832458496</v>
       </c>
       <c r="C575" t="n">
-        <v>3.555092622935685</v>
+        <v>3.555092381904302</v>
       </c>
       <c r="D575" t="n">
-        <v>3.497286294847771</v>
+        <v>3.497286057735593</v>
       </c>
       <c r="E575" t="n">
-        <v>3.545458234921032</v>
+        <v>3.545457994542851</v>
       </c>
       <c r="F575" t="n">
         <v>29127900</v>
@@ -11932,16 +11932,16 @@
         <v>45253</v>
       </c>
       <c r="B576" t="n">
-        <v>3.583995819091797</v>
+        <v>3.583995580673218</v>
       </c>
       <c r="C576" t="n">
-        <v>3.583995819091797</v>
+        <v>3.583995580673218</v>
       </c>
       <c r="D576" t="n">
-        <v>3.478017320279137</v>
+        <v>3.478017088910578</v>
       </c>
       <c r="E576" t="n">
-        <v>3.506920714283994</v>
+        <v>3.506920480992691</v>
       </c>
       <c r="F576" t="n">
         <v>15777100</v>
@@ -11972,16 +11972,16 @@
         <v>45257</v>
       </c>
       <c r="B578" t="n">
-        <v>3.42021107673645</v>
+        <v>3.420210838317871</v>
       </c>
       <c r="C578" t="n">
-        <v>3.63216784993136</v>
+        <v>3.632167596737543</v>
       </c>
       <c r="D578" t="n">
-        <v>3.410576688395861</v>
+        <v>3.410576450648882</v>
       </c>
       <c r="E578" t="n">
-        <v>3.603264684909591</v>
+        <v>3.603264433730577</v>
       </c>
       <c r="F578" t="n">
         <v>29619500</v>
@@ -11992,16 +11992,16 @@
         <v>45258</v>
       </c>
       <c r="B579" t="n">
-        <v>3.497286081314087</v>
+        <v>3.497286319732666</v>
       </c>
       <c r="C579" t="n">
-        <v>3.497286081314087</v>
+        <v>3.497286319732666</v>
       </c>
       <c r="D579" t="n">
-        <v>3.3816732024953</v>
+        <v>3.381673433032266</v>
       </c>
       <c r="E579" t="n">
-        <v>3.420210752200924</v>
+        <v>3.420210985365089</v>
       </c>
       <c r="F579" t="n">
         <v>15991300</v>
@@ -12032,16 +12032,16 @@
         <v>45260</v>
       </c>
       <c r="B581" t="n">
-        <v>3.516555070877075</v>
+        <v>3.516554832458496</v>
       </c>
       <c r="C581" t="n">
-        <v>3.564727010950338</v>
+        <v>3.564726769265754</v>
       </c>
       <c r="D581" t="n">
-        <v>3.468382901101884</v>
+        <v>3.468382665949325</v>
       </c>
       <c r="E581" t="n">
-        <v>3.555092622935685</v>
+        <v>3.555092381904302</v>
       </c>
       <c r="F581" t="n">
         <v>22087700</v>
@@ -12152,16 +12152,16 @@
         <v>45268</v>
       </c>
       <c r="B587" t="n">
-        <v>3.506920576095581</v>
+        <v>3.50692081451416</v>
       </c>
       <c r="C587" t="n">
-        <v>3.555092514702267</v>
+        <v>3.555092756395823</v>
       </c>
       <c r="D587" t="n">
-        <v>3.439479632344298</v>
+        <v>3.439479866177894</v>
       </c>
       <c r="E587" t="n">
-        <v>3.54545812698093</v>
+        <v>3.545458368019491</v>
       </c>
       <c r="F587" t="n">
         <v>14112100</v>
@@ -12232,16 +12232,16 @@
         <v>45274</v>
       </c>
       <c r="B591" t="n">
-        <v>3.516555070877075</v>
+        <v>3.516554832458496</v>
       </c>
       <c r="C591" t="n">
-        <v>3.805586941018577</v>
+        <v>3.805586683003954</v>
       </c>
       <c r="D591" t="n">
-        <v>3.487651677131189</v>
+        <v>3.487651440672228</v>
       </c>
       <c r="E591" t="n">
-        <v>3.487651677131189</v>
+        <v>3.487651440672228</v>
       </c>
       <c r="F591" t="n">
         <v>64134600</v>
@@ -12252,16 +12252,16 @@
         <v>45275</v>
       </c>
       <c r="B592" t="n">
-        <v>3.593630313873291</v>
+        <v>3.593630075454712</v>
       </c>
       <c r="C592" t="n">
-        <v>3.6418022558082</v>
+        <v>3.641802014193664</v>
       </c>
       <c r="D592" t="n">
-        <v>3.497286430003473</v>
+        <v>3.497286197976806</v>
       </c>
       <c r="E592" t="n">
-        <v>3.564727148712346</v>
+        <v>3.56472691221134</v>
       </c>
       <c r="F592" t="n">
         <v>53571000</v>
@@ -12312,16 +12312,16 @@
         <v>45280</v>
       </c>
       <c r="B595" t="n">
-        <v>3.873027801513672</v>
+        <v>3.873027563095093</v>
       </c>
       <c r="C595" t="n">
-        <v>3.892296578261347</v>
+        <v>3.892296338656607</v>
       </c>
       <c r="D595" t="n">
-        <v>3.76704952940146</v>
+        <v>3.767049297506766</v>
       </c>
       <c r="E595" t="n">
-        <v>3.834490248018322</v>
+        <v>3.834490011972065</v>
       </c>
       <c r="F595" t="n">
         <v>18861600</v>
@@ -25932,19 +25932,39 @@
         <v>46279</v>
       </c>
       <c r="B1276" t="n">
-        <v>0.27</v>
+        <v>0.2700000107288361</v>
       </c>
       <c r="C1276" t="n">
-        <v>0.28</v>
+        <v>0.2800000011920929</v>
       </c>
       <c r="D1276" t="n">
-        <v>0.27</v>
+        <v>0.2700000107288361</v>
       </c>
       <c r="E1276" t="n">
-        <v>0.28</v>
+        <v>0.2800000011920929</v>
       </c>
       <c r="F1276" t="n">
         <v>6072700</v>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1277" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C1277" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D1277" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E1277" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="F1277" t="n">
+        <v>6483800</v>
       </c>
     </row>
   </sheetData>

--- a/database/RAIZ4.xlsx
+++ b/database/RAIZ4.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1277"/>
+  <dimension ref="A1:F1278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>44414</v>
       </c>
       <c r="B3" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="C3" t="n">
-        <v>6.481483579964149</v>
+        <v>6.48148308633695</v>
       </c>
       <c r="D3" t="n">
-        <v>6.199296805201136</v>
+        <v>6.19929633306517</v>
       </c>
       <c r="E3" t="n">
-        <v>6.393300212850708</v>
+        <v>6.393299725939519</v>
       </c>
       <c r="F3" t="n">
         <v>28799900</v>
@@ -492,16 +492,16 @@
         <v>44417</v>
       </c>
       <c r="B4" t="n">
-        <v>6.234570026397705</v>
+        <v>6.234569549560547</v>
       </c>
       <c r="C4" t="n">
-        <v>6.446210103204662</v>
+        <v>6.446209610180686</v>
       </c>
       <c r="D4" t="n">
-        <v>6.234570026397705</v>
+        <v>6.234569549560547</v>
       </c>
       <c r="E4" t="n">
-        <v>6.331571518021834</v>
+        <v>6.331571033765733</v>
       </c>
       <c r="F4" t="n">
         <v>14491100</v>
@@ -512,16 +512,16 @@
         <v>44418</v>
       </c>
       <c r="B5" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="C5" t="n">
-        <v>6.313934972202879</v>
+        <v>6.313934491336116</v>
       </c>
       <c r="D5" t="n">
-        <v>6.216933478623825</v>
+        <v>6.216933005144656</v>
       </c>
       <c r="E5" t="n">
-        <v>6.278661625357502</v>
+        <v>6.278661147177143</v>
       </c>
       <c r="F5" t="n">
         <v>9988600</v>
@@ -532,16 +532,16 @@
         <v>44419</v>
       </c>
       <c r="B6" t="n">
-        <v>6.058202743530273</v>
+        <v>6.058203220367432</v>
       </c>
       <c r="C6" t="n">
-        <v>6.296298035007707</v>
+        <v>6.296298530585189</v>
       </c>
       <c r="D6" t="n">
-        <v>5.996474599382589</v>
+        <v>5.996475071361166</v>
       </c>
       <c r="E6" t="n">
-        <v>6.287479908911514</v>
+        <v>6.287480403794928</v>
       </c>
       <c r="F6" t="n">
         <v>31978000</v>
@@ -572,16 +572,16 @@
         <v>44421</v>
       </c>
       <c r="B8" t="n">
-        <v>6.181661128997803</v>
+        <v>6.181660652160645</v>
       </c>
       <c r="C8" t="n">
-        <v>6.208115933153766</v>
+        <v>6.208115454275954</v>
       </c>
       <c r="D8" t="n">
-        <v>6.049385846743395</v>
+        <v>6.049385380109605</v>
       </c>
       <c r="E8" t="n">
-        <v>6.155205904350309</v>
+        <v>6.155205429553837</v>
       </c>
       <c r="F8" t="n">
         <v>21141500</v>
@@ -612,16 +612,16 @@
         <v>44425</v>
       </c>
       <c r="B10" t="n">
-        <v>6.014111518859863</v>
+        <v>6.014111042022705</v>
       </c>
       <c r="C10" t="n">
-        <v>6.164023032578428</v>
+        <v>6.164022543855327</v>
       </c>
       <c r="D10" t="n">
-        <v>5.961201498637171</v>
+        <v>5.961201025995057</v>
       </c>
       <c r="E10" t="n">
-        <v>6.111113012355736</v>
+        <v>6.111112527827679</v>
       </c>
       <c r="F10" t="n">
         <v>17772000</v>
@@ -652,16 +652,16 @@
         <v>44427</v>
       </c>
       <c r="B12" t="n">
-        <v>6.11111307144165</v>
+        <v>6.111112594604492</v>
       </c>
       <c r="C12" t="n">
-        <v>6.11111307144165</v>
+        <v>6.111112594604492</v>
       </c>
       <c r="D12" t="n">
-        <v>5.66137768495472</v>
+        <v>5.661377243209458</v>
       </c>
       <c r="E12" t="n">
-        <v>5.908291115047926</v>
+        <v>5.908290654036534</v>
       </c>
       <c r="F12" t="n">
         <v>5423700</v>
@@ -692,16 +692,16 @@
         <v>44431</v>
       </c>
       <c r="B14" t="n">
-        <v>6.322752952575684</v>
+        <v>6.322752475738525</v>
       </c>
       <c r="C14" t="n">
-        <v>6.349207750093361</v>
+        <v>6.349207271261085</v>
       </c>
       <c r="D14" t="n">
-        <v>6.181659577837608</v>
+        <v>6.181659111641157</v>
       </c>
       <c r="E14" t="n">
-        <v>6.208114375355285</v>
+        <v>6.208113907163717</v>
       </c>
       <c r="F14" t="n">
         <v>6128800</v>
@@ -712,16 +712,16 @@
         <v>44432</v>
       </c>
       <c r="B15" t="n">
-        <v>6.39330005645752</v>
+        <v>6.393300533294678</v>
       </c>
       <c r="C15" t="n">
-        <v>6.525575314137689</v>
+        <v>6.525575800840451</v>
       </c>
       <c r="D15" t="n">
-        <v>6.331571490742386</v>
+        <v>6.331571962975588</v>
       </c>
       <c r="E15" t="n">
-        <v>6.384481509716164</v>
+        <v>6.384481985895601</v>
       </c>
       <c r="F15" t="n">
         <v>6054100</v>
@@ -732,16 +732,16 @@
         <v>44433</v>
       </c>
       <c r="B16" t="n">
-        <v>6.472664356231689</v>
+        <v>6.472665309906006</v>
       </c>
       <c r="C16" t="n">
-        <v>6.507937697097415</v>
+        <v>6.507938655968863</v>
       </c>
       <c r="D16" t="n">
-        <v>6.402117674500237</v>
+        <v>6.402118617780292</v>
       </c>
       <c r="E16" t="n">
-        <v>6.455027685798826</v>
+        <v>6.455028636874578</v>
       </c>
       <c r="F16" t="n">
         <v>5190100</v>
@@ -752,16 +752,16 @@
         <v>44434</v>
       </c>
       <c r="B17" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="C17" t="n">
-        <v>6.507938800343913</v>
+        <v>6.507938304701895</v>
       </c>
       <c r="D17" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="E17" t="n">
-        <v>6.472665453498537</v>
+        <v>6.472664960542923</v>
       </c>
       <c r="F17" t="n">
         <v>7968100</v>
@@ -792,16 +792,16 @@
         <v>44438</v>
       </c>
       <c r="B19" t="n">
-        <v>6.269843578338623</v>
+        <v>6.269844055175781</v>
       </c>
       <c r="C19" t="n">
-        <v>6.419755514576775</v>
+        <v>6.419756002815109</v>
       </c>
       <c r="D19" t="n">
-        <v>6.252206904692456</v>
+        <v>6.252207380188302</v>
       </c>
       <c r="E19" t="n">
-        <v>6.393300293861791</v>
+        <v>6.39330078008814</v>
       </c>
       <c r="F19" t="n">
         <v>4966000</v>
@@ -812,16 +812,16 @@
         <v>44439</v>
       </c>
       <c r="B20" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="C20" t="n">
-        <v>6.305116845737266</v>
+        <v>6.305116365542087</v>
       </c>
       <c r="D20" t="n">
-        <v>6.181660131778449</v>
+        <v>6.181659660985684</v>
       </c>
       <c r="E20" t="n">
-        <v>6.305116845737266</v>
+        <v>6.305116365542087</v>
       </c>
       <c r="F20" t="n">
         <v>3704100</v>
@@ -832,16 +832,16 @@
         <v>44440</v>
       </c>
       <c r="B21" t="n">
-        <v>6.234570026397705</v>
+        <v>6.234569549560547</v>
       </c>
       <c r="C21" t="n">
-        <v>6.305116718666691</v>
+        <v>6.305116236433927</v>
       </c>
       <c r="D21" t="n">
-        <v>6.199296680263212</v>
+        <v>6.199296206123857</v>
       </c>
       <c r="E21" t="n">
-        <v>6.261024825752847</v>
+        <v>6.261024346892354</v>
       </c>
       <c r="F21" t="n">
         <v>6468600</v>
@@ -852,16 +852,16 @@
         <v>44441</v>
       </c>
       <c r="B22" t="n">
-        <v>5.996475696563721</v>
+        <v>5.996474742889404</v>
       </c>
       <c r="C22" t="n">
-        <v>6.252207707516526</v>
+        <v>6.252206713170811</v>
       </c>
       <c r="D22" t="n">
-        <v>5.970020472451714</v>
+        <v>5.970019522984813</v>
       </c>
       <c r="E22" t="n">
-        <v>6.234571031605695</v>
+        <v>6.234570040064902</v>
       </c>
       <c r="F22" t="n">
         <v>3746900</v>
@@ -892,16 +892,16 @@
         <v>44445</v>
       </c>
       <c r="B24" t="n">
-        <v>6.11111307144165</v>
+        <v>6.111112594604492</v>
       </c>
       <c r="C24" t="n">
-        <v>6.190478312788771</v>
+        <v>6.190477829758912</v>
       </c>
       <c r="D24" t="n">
-        <v>6.067021597742168</v>
+        <v>6.067021124345374</v>
       </c>
       <c r="E24" t="n">
-        <v>6.119931618476427</v>
+        <v>6.119931140951175</v>
       </c>
       <c r="F24" t="n">
         <v>1654400</v>
@@ -912,16 +912,16 @@
         <v>44447</v>
       </c>
       <c r="B25" t="n">
-        <v>5.758378982543945</v>
+        <v>5.758379459381104</v>
       </c>
       <c r="C25" t="n">
-        <v>6.111112416290331</v>
+        <v>6.111112922336476</v>
       </c>
       <c r="D25" t="n">
-        <v>5.661377078017978</v>
+        <v>5.661377546822648</v>
       </c>
       <c r="E25" t="n">
-        <v>6.111112416290331</v>
+        <v>6.111112922336476</v>
       </c>
       <c r="F25" t="n">
         <v>10251100</v>
@@ -972,16 +972,16 @@
         <v>44452</v>
       </c>
       <c r="B28" t="n">
-        <v>6.128748893737793</v>
+        <v>6.128749847412109</v>
       </c>
       <c r="C28" t="n">
-        <v>6.172840781804387</v>
+        <v>6.172841742339696</v>
       </c>
       <c r="D28" t="n">
-        <v>5.925926965515992</v>
+        <v>5.92592788762986</v>
       </c>
       <c r="E28" t="n">
-        <v>5.95238218245423</v>
+        <v>5.952383108684708</v>
       </c>
       <c r="F28" t="n">
         <v>8999600</v>
@@ -1032,16 +1032,16 @@
         <v>44455</v>
       </c>
       <c r="B31" t="n">
-        <v>6.278661251068115</v>
+        <v>6.278661727905273</v>
       </c>
       <c r="C31" t="n">
-        <v>6.428573176470008</v>
+        <v>6.428573664692329</v>
       </c>
       <c r="D31" t="n">
-        <v>6.172841216840228</v>
+        <v>6.172841685640813</v>
       </c>
       <c r="E31" t="n">
-        <v>6.349207940553374</v>
+        <v>6.349208422748248</v>
       </c>
       <c r="F31" t="n">
         <v>6142600</v>
@@ -1072,16 +1072,16 @@
         <v>44459</v>
       </c>
       <c r="B33" t="n">
-        <v>6.269843578338623</v>
+        <v>6.269844055175781</v>
       </c>
       <c r="C33" t="n">
-        <v>6.322753599277124</v>
+        <v>6.32275408013822</v>
       </c>
       <c r="D33" t="n">
-        <v>6.067021621161969</v>
+        <v>6.067022082574015</v>
       </c>
       <c r="E33" t="n">
-        <v>6.164023115970153</v>
+        <v>6.164023584759403</v>
       </c>
       <c r="F33" t="n">
         <v>9065700</v>
@@ -1092,16 +1092,16 @@
         <v>44460</v>
       </c>
       <c r="B34" t="n">
-        <v>6.419755458831787</v>
+        <v>6.419754505157471</v>
       </c>
       <c r="C34" t="n">
-        <v>6.525575499789916</v>
+        <v>6.525574530395708</v>
       </c>
       <c r="D34" t="n">
-        <v>6.269843523895372</v>
+        <v>6.269842592490932</v>
       </c>
       <c r="E34" t="n">
-        <v>6.349208344368237</v>
+        <v>6.34920740117391</v>
       </c>
       <c r="F34" t="n">
         <v>11102500</v>
@@ -1112,16 +1112,16 @@
         <v>44461</v>
       </c>
       <c r="B35" t="n">
-        <v>6.446210861206055</v>
+        <v>6.44620943069458</v>
       </c>
       <c r="C35" t="n">
-        <v>6.560849459869084</v>
+        <v>6.560848003917575</v>
       </c>
       <c r="D35" t="n">
-        <v>6.402119383599007</v>
+        <v>6.402117962872096</v>
       </c>
       <c r="E35" t="n">
-        <v>6.463847536347174</v>
+        <v>6.463846101921855</v>
       </c>
       <c r="F35" t="n">
         <v>10254600</v>
@@ -1132,16 +1132,16 @@
         <v>44462</v>
       </c>
       <c r="B36" t="n">
-        <v>6.375663280487061</v>
+        <v>6.375663757324219</v>
       </c>
       <c r="C36" t="n">
-        <v>6.543211881443518</v>
+        <v>6.54321237081167</v>
       </c>
       <c r="D36" t="n">
-        <v>6.340389935074274</v>
+        <v>6.340390409273332</v>
       </c>
       <c r="E36" t="n">
-        <v>6.507938536030731</v>
+        <v>6.507939022760783</v>
       </c>
       <c r="F36" t="n">
         <v>6341600</v>
@@ -1172,16 +1172,16 @@
         <v>44466</v>
       </c>
       <c r="B38" t="n">
-        <v>6.305117607116699</v>
+        <v>6.305116653442383</v>
       </c>
       <c r="C38" t="n">
-        <v>6.340390958221537</v>
+        <v>6.340389999211985</v>
       </c>
       <c r="D38" t="n">
-        <v>6.102295628018125</v>
+        <v>6.102294705021446</v>
       </c>
       <c r="E38" t="n">
-        <v>6.172842330227801</v>
+        <v>6.17284139656065</v>
       </c>
       <c r="F38" t="n">
         <v>6343700</v>
@@ -1192,16 +1192,16 @@
         <v>44467</v>
       </c>
       <c r="B39" t="n">
-        <v>6.119931221008301</v>
+        <v>6.119932174682617</v>
       </c>
       <c r="C39" t="n">
-        <v>6.278661272902115</v>
+        <v>6.278662251311475</v>
       </c>
       <c r="D39" t="n">
-        <v>6.119931221008301</v>
+        <v>6.119932174682617</v>
       </c>
       <c r="E39" t="n">
-        <v>6.261024600469469</v>
+        <v>6.261025576130491</v>
       </c>
       <c r="F39" t="n">
         <v>6782400</v>
@@ -1232,16 +1232,16 @@
         <v>44469</v>
       </c>
       <c r="B41" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="C41" t="n">
-        <v>6.349208319048255</v>
+        <v>6.349207835495088</v>
       </c>
       <c r="D41" t="n">
-        <v>6.058202997328168</v>
+        <v>6.058202535937849</v>
       </c>
       <c r="E41" t="n">
-        <v>6.084658217707932</v>
+        <v>6.084657754302794</v>
       </c>
       <c r="F41" t="n">
         <v>15990100</v>
@@ -1252,16 +1252,16 @@
         <v>44470</v>
       </c>
       <c r="B42" t="n">
-        <v>6.499120235443115</v>
+        <v>6.499119758605957</v>
       </c>
       <c r="C42" t="n">
-        <v>6.569666928939093</v>
+        <v>6.569666446925959</v>
       </c>
       <c r="D42" t="n">
-        <v>6.331571628144438</v>
+        <v>6.331571163600236</v>
       </c>
       <c r="E42" t="n">
-        <v>6.331571628144438</v>
+        <v>6.331571163600236</v>
       </c>
       <c r="F42" t="n">
         <v>15528000</v>
@@ -1292,16 +1292,16 @@
         <v>44474</v>
       </c>
       <c r="B44" t="n">
-        <v>6.287480354309082</v>
+        <v>6.287479877471924</v>
       </c>
       <c r="C44" t="n">
-        <v>6.366845176762705</v>
+        <v>6.366844693906587</v>
       </c>
       <c r="D44" t="n">
-        <v>6.243388459230366</v>
+        <v>6.2433879857371</v>
       </c>
       <c r="E44" t="n">
-        <v>6.29629848102994</v>
+        <v>6.296298003524023</v>
       </c>
       <c r="F44" t="n">
         <v>12888200</v>
@@ -1312,16 +1312,16 @@
         <v>44475</v>
       </c>
       <c r="B45" t="n">
-        <v>6.178093910217285</v>
+        <v>6.178094387054443</v>
       </c>
       <c r="C45" t="n">
-        <v>6.275317254600846</v>
+        <v>6.275317738941888</v>
       </c>
       <c r="D45" t="n">
-        <v>6.080870987285061</v>
+        <v>6.080871456618367</v>
       </c>
       <c r="E45" t="n">
-        <v>6.248802065237998</v>
+        <v>6.248802547532548</v>
       </c>
       <c r="F45" t="n">
         <v>10376100</v>
@@ -1332,16 +1332,16 @@
         <v>44476</v>
       </c>
       <c r="B46" t="n">
-        <v>6.301833152770996</v>
+        <v>6.301832675933838</v>
       </c>
       <c r="C46" t="n">
-        <v>6.478602494754905</v>
+        <v>6.478602004542243</v>
       </c>
       <c r="D46" t="n">
-        <v>6.213448481779042</v>
+        <v>6.213448011629635</v>
       </c>
       <c r="E46" t="n">
-        <v>6.284156218572606</v>
+        <v>6.284155743072997</v>
       </c>
       <c r="F46" t="n">
         <v>18438800</v>
@@ -1352,16 +1352,16 @@
         <v>44477</v>
       </c>
       <c r="B47" t="n">
-        <v>6.310671329498291</v>
+        <v>6.310670852661133</v>
       </c>
       <c r="C47" t="n">
-        <v>6.655372174193518</v>
+        <v>6.655371671310609</v>
       </c>
       <c r="D47" t="n">
-        <v>6.292994395522999</v>
+        <v>6.292993920021518</v>
       </c>
       <c r="E47" t="n">
-        <v>6.363702131424168</v>
+        <v>6.363701650579979</v>
       </c>
       <c r="F47" t="n">
         <v>20480700</v>
@@ -1372,16 +1372,16 @@
         <v>44480</v>
       </c>
       <c r="B48" t="n">
-        <v>6.213448524475098</v>
+        <v>6.213448047637939</v>
       </c>
       <c r="C48" t="n">
-        <v>6.407894801993546</v>
+        <v>6.407894310234044</v>
       </c>
       <c r="D48" t="n">
-        <v>6.213448524475098</v>
+        <v>6.213448047637939</v>
       </c>
       <c r="E48" t="n">
-        <v>6.363702255468219</v>
+        <v>6.363701767100176</v>
       </c>
       <c r="F48" t="n">
         <v>10407400</v>
@@ -1412,16 +1412,16 @@
         <v>44483</v>
       </c>
       <c r="B50" t="n">
-        <v>6.319509506225586</v>
+        <v>6.319509983062744</v>
       </c>
       <c r="C50" t="n">
-        <v>6.381378559508698</v>
+        <v>6.381379041014171</v>
       </c>
       <c r="D50" t="n">
-        <v>6.239963098917224</v>
+        <v>6.239963569752225</v>
       </c>
       <c r="E50" t="n">
-        <v>6.24880177592985</v>
+        <v>6.248802247431771</v>
       </c>
       <c r="F50" t="n">
         <v>10992200</v>
@@ -1432,16 +1432,16 @@
         <v>44484</v>
       </c>
       <c r="B51" t="n">
-        <v>6.275316715240479</v>
+        <v>6.275317668914795</v>
       </c>
       <c r="C51" t="n">
-        <v>6.354863119394721</v>
+        <v>6.354864085157887</v>
       </c>
       <c r="D51" t="n">
-        <v>6.222285919621418</v>
+        <v>6.222286865236521</v>
       </c>
       <c r="E51" t="n">
-        <v>6.3371861875217</v>
+        <v>6.337187150598463</v>
       </c>
       <c r="F51" t="n">
         <v>34203500</v>
@@ -1452,16 +1452,16 @@
         <v>44487</v>
       </c>
       <c r="B52" t="n">
-        <v>6.169256210327148</v>
+        <v>6.16925573348999</v>
       </c>
       <c r="C52" t="n">
-        <v>6.266479563474164</v>
+        <v>6.266479079122371</v>
       </c>
       <c r="D52" t="n">
-        <v>6.151579275341452</v>
+        <v>6.151578799870589</v>
       </c>
       <c r="E52" t="n">
-        <v>6.257640885255628</v>
+        <v>6.257640401587</v>
       </c>
       <c r="F52" t="n">
         <v>7596500</v>
@@ -1472,16 +1472,16 @@
         <v>44488</v>
       </c>
       <c r="B53" t="n">
-        <v>5.91294002532959</v>
+        <v>5.912939548492432</v>
       </c>
       <c r="C53" t="n">
-        <v>6.186932709011659</v>
+        <v>6.186932210078912</v>
       </c>
       <c r="D53" t="n">
-        <v>5.895263091590468</v>
+        <v>5.89526261617883</v>
       </c>
       <c r="E53" t="n">
-        <v>6.169255775272537</v>
+        <v>6.169255277765311</v>
       </c>
       <c r="F53" t="n">
         <v>11473400</v>
@@ -1512,16 +1512,16 @@
         <v>44490</v>
       </c>
       <c r="B55" t="n">
-        <v>5.683138847351074</v>
+        <v>5.683139324188232</v>
       </c>
       <c r="C55" t="n">
-        <v>5.842231655156614</v>
+        <v>5.84223214534227</v>
       </c>
       <c r="D55" t="n">
-        <v>5.471015665545419</v>
+        <v>5.471016124584628</v>
       </c>
       <c r="E55" t="n">
-        <v>5.79803911488812</v>
+        <v>5.798039601365852</v>
       </c>
       <c r="F55" t="n">
         <v>12472300</v>
@@ -1532,16 +1532,16 @@
         <v>44491</v>
       </c>
       <c r="B56" t="n">
-        <v>5.63010835647583</v>
+        <v>5.630108833312988</v>
       </c>
       <c r="C56" t="n">
-        <v>5.656623966361621</v>
+        <v>5.656624445444495</v>
       </c>
       <c r="D56" t="n">
-        <v>5.197023292801376</v>
+        <v>5.197023732958769</v>
       </c>
       <c r="E56" t="n">
-        <v>5.60359316804136</v>
+        <v>5.603593642632838</v>
       </c>
       <c r="F56" t="n">
         <v>18890200</v>
@@ -1572,16 +1572,16 @@
         <v>44495</v>
       </c>
       <c r="B58" t="n">
-        <v>5.815716743469238</v>
+        <v>5.815715789794922</v>
       </c>
       <c r="C58" t="n">
-        <v>5.868747545274117</v>
+        <v>5.86874658290369</v>
       </c>
       <c r="D58" t="n">
-        <v>5.683139528231368</v>
+        <v>5.68313859629736</v>
       </c>
       <c r="E58" t="n">
-        <v>5.833393677404199</v>
+        <v>5.833392720831178</v>
       </c>
       <c r="F58" t="n">
         <v>8470300</v>
@@ -1612,16 +1612,16 @@
         <v>44497</v>
       </c>
       <c r="B60" t="n">
-        <v>5.992486476898193</v>
+        <v>5.992486000061035</v>
       </c>
       <c r="C60" t="n">
-        <v>6.027840344606625</v>
+        <v>6.027839864956272</v>
       </c>
       <c r="D60" t="n">
-        <v>5.727332047633601</v>
+        <v>5.727331591895446</v>
       </c>
       <c r="E60" t="n">
-        <v>5.753847659140599</v>
+        <v>5.75384720129253</v>
       </c>
       <c r="F60" t="n">
         <v>8299700</v>
@@ -1632,16 +1632,16 @@
         <v>44498</v>
       </c>
       <c r="B61" t="n">
-        <v>5.992486476898193</v>
+        <v>5.992486000061035</v>
       </c>
       <c r="C61" t="n">
-        <v>6.019001666953844</v>
+        <v>6.019001188006806</v>
       </c>
       <c r="D61" t="n">
-        <v>5.842232328411681</v>
+        <v>5.842231863530622</v>
       </c>
       <c r="E61" t="n">
-        <v>5.957132187738413</v>
+        <v>5.957131713714485</v>
       </c>
       <c r="F61" t="n">
         <v>3926300</v>
@@ -1652,16 +1652,16 @@
         <v>44501</v>
       </c>
       <c r="B62" t="n">
-        <v>6.001324653625488</v>
+        <v>6.001325130462646</v>
       </c>
       <c r="C62" t="n">
-        <v>6.063194132021597</v>
+        <v>6.063194613774614</v>
       </c>
       <c r="D62" t="n">
-        <v>5.948293852765114</v>
+        <v>5.948294325388693</v>
       </c>
       <c r="E62" t="n">
-        <v>5.965970786385239</v>
+        <v>5.965971260413344</v>
       </c>
       <c r="F62" t="n">
         <v>5059700</v>
@@ -1672,16 +1672,16 @@
         <v>44503</v>
       </c>
       <c r="B63" t="n">
-        <v>6.09854793548584</v>
+        <v>6.098548412322998</v>
       </c>
       <c r="C63" t="n">
-        <v>6.186932602662175</v>
+        <v>6.18693308641001</v>
       </c>
       <c r="D63" t="n">
-        <v>5.921778179681833</v>
+        <v>5.921778642697604</v>
       </c>
       <c r="E63" t="n">
-        <v>5.983647657430936</v>
+        <v>5.983648125284198</v>
       </c>
       <c r="F63" t="n">
         <v>5711600</v>
@@ -1732,16 +1732,16 @@
         <v>44508</v>
       </c>
       <c r="B66" t="n">
-        <v>5.983647346496582</v>
+        <v>5.983648300170898</v>
       </c>
       <c r="C66" t="n">
-        <v>6.036678144046689</v>
+        <v>6.03667910617306</v>
       </c>
       <c r="D66" t="n">
-        <v>5.939454804479167</v>
+        <v>5.939455751110073</v>
       </c>
       <c r="E66" t="n">
-        <v>6.010162955997293</v>
+        <v>6.010163913897671</v>
       </c>
       <c r="F66" t="n">
         <v>3898000</v>
@@ -1752,16 +1752,16 @@
         <v>44509</v>
       </c>
       <c r="B67" t="n">
-        <v>5.948293209075928</v>
+        <v>5.948294162750244</v>
       </c>
       <c r="C67" t="n">
-        <v>6.169255066141971</v>
+        <v>6.169256055242525</v>
       </c>
       <c r="D67" t="n">
-        <v>5.948293209075928</v>
+        <v>5.948294162750244</v>
       </c>
       <c r="E67" t="n">
-        <v>5.992485749069655</v>
+        <v>5.992486709829246</v>
       </c>
       <c r="F67" t="n">
         <v>5176300</v>
@@ -1772,16 +1772,16 @@
         <v>44510</v>
       </c>
       <c r="B68" t="n">
-        <v>5.745008945465088</v>
+        <v>5.74500846862793</v>
       </c>
       <c r="C68" t="n">
-        <v>6.010163373067091</v>
+        <v>6.010162874222051</v>
       </c>
       <c r="D68" t="n">
-        <v>5.745008945465088</v>
+        <v>5.74500846862793</v>
       </c>
       <c r="E68" t="n">
-        <v>5.957132150385616</v>
+        <v>5.957131655942178</v>
       </c>
       <c r="F68" t="n">
         <v>10074000</v>
@@ -1792,16 +1792,16 @@
         <v>44511</v>
       </c>
       <c r="B69" t="n">
-        <v>6.010164260864258</v>
+        <v>6.010163307189941</v>
       </c>
       <c r="C69" t="n">
-        <v>6.036679454670368</v>
+        <v>6.036678496788703</v>
       </c>
       <c r="D69" t="n">
-        <v>5.806879282061312</v>
+        <v>5.806878360643628</v>
       </c>
       <c r="E69" t="n">
-        <v>5.833394475867422</v>
+        <v>5.833393550242389</v>
       </c>
       <c r="F69" t="n">
         <v>8604300</v>
@@ -1812,16 +1812,16 @@
         <v>44512</v>
       </c>
       <c r="B70" t="n">
-        <v>5.762685775756836</v>
+        <v>5.762686252593994</v>
       </c>
       <c r="C70" t="n">
-        <v>6.080870998876915</v>
+        <v>6.080871502042515</v>
       </c>
       <c r="D70" t="n">
-        <v>5.532885641218299</v>
+        <v>5.532886099040496</v>
       </c>
       <c r="E70" t="n">
-        <v>6.080870998876915</v>
+        <v>6.080871502042515</v>
       </c>
       <c r="F70" t="n">
         <v>20568500</v>
@@ -1832,16 +1832,16 @@
         <v>44516</v>
       </c>
       <c r="B71" t="n">
-        <v>5.320761680603027</v>
+        <v>5.320762157440186</v>
       </c>
       <c r="C71" t="n">
-        <v>5.815716206536877</v>
+        <v>5.815716727730977</v>
       </c>
       <c r="D71" t="n">
-        <v>5.223538342211159</v>
+        <v>5.223538810335335</v>
       </c>
       <c r="E71" t="n">
-        <v>5.789201018808111</v>
+        <v>5.789201537625966</v>
       </c>
       <c r="F71" t="n">
         <v>27445700</v>
@@ -1852,16 +1852,16 @@
         <v>44517</v>
       </c>
       <c r="B72" t="n">
-        <v>5.170507907867432</v>
+        <v>5.17050838470459</v>
       </c>
       <c r="C72" t="n">
-        <v>5.462177522044113</v>
+        <v>5.462178025779772</v>
       </c>
       <c r="D72" t="n">
-        <v>5.002576828488149</v>
+        <v>5.002577289838284</v>
       </c>
       <c r="E72" t="n">
-        <v>5.364954598286112</v>
+        <v>5.364955093055631</v>
       </c>
       <c r="F72" t="n">
         <v>24600900</v>
@@ -1872,16 +1872,16 @@
         <v>44518</v>
       </c>
       <c r="B73" t="n">
-        <v>5.161669731140137</v>
+        <v>5.161669254302979</v>
       </c>
       <c r="C73" t="n">
-        <v>5.338439069281368</v>
+        <v>5.338438576114187</v>
       </c>
       <c r="D73" t="n">
-        <v>5.073284640618174</v>
+        <v>5.073284171946066</v>
       </c>
       <c r="E73" t="n">
-        <v>5.214700532582506</v>
+        <v>5.214700050846341</v>
       </c>
       <c r="F73" t="n">
         <v>17735600</v>
@@ -1912,16 +1912,16 @@
         <v>44522</v>
       </c>
       <c r="B75" t="n">
-        <v>4.976061344146729</v>
+        <v>4.976061820983887</v>
       </c>
       <c r="C75" t="n">
-        <v>5.32960041550615</v>
+        <v>5.329600926221622</v>
       </c>
       <c r="D75" t="n">
-        <v>4.976061344146729</v>
+        <v>4.976061820983887</v>
       </c>
       <c r="E75" t="n">
-        <v>5.232377076055763</v>
+        <v>5.23237757745469</v>
       </c>
       <c r="F75" t="n">
         <v>8516000</v>
@@ -1952,16 +1952,16 @@
         <v>44524</v>
       </c>
       <c r="B77" t="n">
-        <v>4.923030376434326</v>
+        <v>4.923030853271484</v>
       </c>
       <c r="C77" t="n">
-        <v>5.020253291071671</v>
+        <v>5.020253777325691</v>
       </c>
       <c r="D77" t="n">
-        <v>4.825807040345681</v>
+        <v>4.825807507765937</v>
       </c>
       <c r="E77" t="n">
-        <v>4.923030376434326</v>
+        <v>4.923030853271484</v>
       </c>
       <c r="F77" t="n">
         <v>8397000</v>
@@ -1992,16 +1992,16 @@
         <v>44526</v>
       </c>
       <c r="B79" t="n">
-        <v>5.223538875579834</v>
+        <v>5.223538398742676</v>
       </c>
       <c r="C79" t="n">
-        <v>5.338439158006967</v>
+        <v>5.338438670680995</v>
       </c>
       <c r="D79" t="n">
-        <v>5.02025392261312</v>
+        <v>5.020253464333078</v>
       </c>
       <c r="E79" t="n">
-        <v>5.037930856721036</v>
+        <v>5.037930396827334</v>
       </c>
       <c r="F79" t="n">
         <v>8564200</v>
@@ -2012,16 +2012,16 @@
         <v>44529</v>
       </c>
       <c r="B80" t="n">
-        <v>5.117476940155029</v>
+        <v>5.117477416992188</v>
       </c>
       <c r="C80" t="n">
-        <v>5.391469611843401</v>
+        <v>5.391470114210696</v>
       </c>
       <c r="D80" t="n">
-        <v>5.117476940155029</v>
+        <v>5.117477416992188</v>
       </c>
       <c r="E80" t="n">
-        <v>5.285408014051384</v>
+        <v>5.285408506536053</v>
       </c>
       <c r="F80" t="n">
         <v>7811800</v>
@@ -2052,16 +2052,16 @@
         <v>44531</v>
       </c>
       <c r="B82" t="n">
-        <v>4.852323532104492</v>
+        <v>4.852322578430176</v>
       </c>
       <c r="C82" t="n">
-        <v>5.15283187638541</v>
+        <v>5.152830863649267</v>
       </c>
       <c r="D82" t="n">
-        <v>4.852323532104492</v>
+        <v>4.852322578430176</v>
       </c>
       <c r="E82" t="n">
-        <v>4.896516084422773</v>
+        <v>4.896515122062865</v>
       </c>
       <c r="F82" t="n">
         <v>12492100</v>
@@ -2072,16 +2072,16 @@
         <v>44532</v>
       </c>
       <c r="B83" t="n">
-        <v>5.029092788696289</v>
+        <v>5.029092311859131</v>
       </c>
       <c r="C83" t="n">
-        <v>5.029092788696289</v>
+        <v>5.029092311859131</v>
       </c>
       <c r="D83" t="n">
-        <v>4.746261410928263</v>
+        <v>4.746260960907972</v>
       </c>
       <c r="E83" t="n">
-        <v>4.905354245307752</v>
+        <v>4.905353780202955</v>
       </c>
       <c r="F83" t="n">
         <v>18379200</v>
@@ -2092,16 +2092,16 @@
         <v>44533</v>
       </c>
       <c r="B84" t="n">
-        <v>5.320761680603027</v>
+        <v>5.320762157440186</v>
       </c>
       <c r="C84" t="n">
-        <v>5.329600357480157</v>
+        <v>5.329600835109421</v>
       </c>
       <c r="D84" t="n">
-        <v>4.97606128996989</v>
+        <v>4.976061735915614</v>
       </c>
       <c r="E84" t="n">
-        <v>5.020253410001604</v>
+        <v>5.020253859907747</v>
       </c>
       <c r="F84" t="n">
         <v>10548200</v>
@@ -2112,16 +2112,16 @@
         <v>44536</v>
       </c>
       <c r="B85" t="n">
-        <v>5.152830600738525</v>
+        <v>5.152831077575684</v>
       </c>
       <c r="C85" t="n">
-        <v>5.417985006103135</v>
+        <v>5.417985507477384</v>
       </c>
       <c r="D85" t="n">
-        <v>5.152830600738525</v>
+        <v>5.152831077575684</v>
       </c>
       <c r="E85" t="n">
-        <v>5.373792464725264</v>
+        <v>5.373792962009984</v>
       </c>
       <c r="F85" t="n">
         <v>5884400</v>
@@ -2152,16 +2152,16 @@
         <v>44538</v>
       </c>
       <c r="B87" t="n">
-        <v>5.285408020019531</v>
+        <v>5.285407543182373</v>
       </c>
       <c r="C87" t="n">
-        <v>5.33843881897542</v>
+        <v>5.338438337353947</v>
       </c>
       <c r="D87" t="n">
-        <v>5.126315623151864</v>
+        <v>5.12631516066765</v>
       </c>
       <c r="E87" t="n">
-        <v>5.223538543845331</v>
+        <v>5.223538072589892</v>
       </c>
       <c r="F87" t="n">
         <v>9204000</v>
@@ -2192,16 +2192,16 @@
         <v>44540</v>
       </c>
       <c r="B89" t="n">
-        <v>5.444501399993896</v>
+        <v>5.444499969482422</v>
       </c>
       <c r="C89" t="n">
-        <v>5.568240374685687</v>
+        <v>5.568238911662507</v>
       </c>
       <c r="D89" t="n">
-        <v>5.241216423230415</v>
+        <v>5.2412150461309</v>
       </c>
       <c r="E89" t="n">
-        <v>5.267732038221914</v>
+        <v>5.267730654155574</v>
       </c>
       <c r="F89" t="n">
         <v>8741300</v>
@@ -2272,16 +2272,16 @@
         <v>44546</v>
       </c>
       <c r="B93" t="n">
-        <v>5.400308609008789</v>
+        <v>5.400308132171631</v>
       </c>
       <c r="C93" t="n">
-        <v>5.550562758842054</v>
+        <v>5.550562268737735</v>
       </c>
       <c r="D93" t="n">
-        <v>5.347277806970816</v>
+        <v>5.347277334816178</v>
       </c>
       <c r="E93" t="n">
-        <v>5.515208469365389</v>
+        <v>5.515207982382787</v>
       </c>
       <c r="F93" t="n">
         <v>9238300</v>
@@ -2312,16 +2312,16 @@
         <v>44550</v>
       </c>
       <c r="B95" t="n">
-        <v>5.143991947174072</v>
+        <v>5.14399242401123</v>
       </c>
       <c r="C95" t="n">
-        <v>5.179345808959355</v>
+        <v>5.179346289073743</v>
       </c>
       <c r="D95" t="n">
-        <v>4.949545285903736</v>
+        <v>4.949545744716101</v>
       </c>
       <c r="E95" t="n">
-        <v>5.179345808959355</v>
+        <v>5.179346289073743</v>
       </c>
       <c r="F95" t="n">
         <v>8433600</v>
@@ -2332,16 +2332,16 @@
         <v>44551</v>
       </c>
       <c r="B96" t="n">
-        <v>5.082123279571533</v>
+        <v>5.082122325897217</v>
       </c>
       <c r="C96" t="n">
-        <v>5.223538749008224</v>
+        <v>5.223537768796909</v>
       </c>
       <c r="D96" t="n">
-        <v>5.020253800967309</v>
+        <v>5.020252858902969</v>
       </c>
       <c r="E96" t="n">
-        <v>5.170507947969465</v>
+        <v>5.170506977709524</v>
       </c>
       <c r="F96" t="n">
         <v>5049800</v>
@@ -2412,16 +2412,16 @@
         <v>44558</v>
       </c>
       <c r="B100" t="n">
-        <v>5.347277164459229</v>
+        <v>5.347277641296387</v>
       </c>
       <c r="C100" t="n">
-        <v>5.347277164459229</v>
+        <v>5.347277641296387</v>
       </c>
       <c r="D100" t="n">
-        <v>5.188184356010038</v>
+        <v>5.188184818660282</v>
       </c>
       <c r="E100" t="n">
-        <v>5.21469996456867</v>
+        <v>5.214700429583412</v>
       </c>
       <c r="F100" t="n">
         <v>4379800</v>
@@ -2432,16 +2432,16 @@
         <v>44559</v>
       </c>
       <c r="B101" t="n">
-        <v>5.311924457550049</v>
+        <v>5.311923503875732</v>
       </c>
       <c r="C101" t="n">
-        <v>5.382632200503894</v>
+        <v>5.38263123413509</v>
       </c>
       <c r="D101" t="n">
-        <v>5.214701100262815</v>
+        <v>5.214700164043457</v>
       </c>
       <c r="E101" t="n">
-        <v>5.320762714693583</v>
+        <v>5.320761759432494</v>
       </c>
       <c r="F101" t="n">
         <v>5394800</v>
@@ -2452,16 +2452,16 @@
         <v>44560</v>
       </c>
       <c r="B102" t="n">
-        <v>5.700815677642822</v>
+        <v>5.70081615447998</v>
       </c>
       <c r="C102" t="n">
-        <v>5.709654354119633</v>
+        <v>5.70965483169609</v>
       </c>
       <c r="D102" t="n">
-        <v>5.258891968633261</v>
+        <v>5.258892408506298</v>
       </c>
       <c r="E102" t="n">
-        <v>5.320761439617065</v>
+        <v>5.320761884665091</v>
       </c>
       <c r="F102" t="n">
         <v>23096200</v>
@@ -2492,16 +2492,16 @@
         <v>44565</v>
       </c>
       <c r="B104" t="n">
-        <v>5.594754695892334</v>
+        <v>5.594754219055176</v>
       </c>
       <c r="C104" t="n">
-        <v>5.612431629313347</v>
+        <v>5.612431150969596</v>
       </c>
       <c r="D104" t="n">
-        <v>5.444500551088055</v>
+        <v>5.444500087056956</v>
       </c>
       <c r="E104" t="n">
-        <v>5.532885639644457</v>
+        <v>5.532885168080356</v>
       </c>
       <c r="F104" t="n">
         <v>10613100</v>
@@ -2512,16 +2512,16 @@
         <v>44566</v>
       </c>
       <c r="B105" t="n">
-        <v>5.117476940155029</v>
+        <v>5.117477416992188</v>
       </c>
       <c r="C105" t="n">
-        <v>5.568239362948087</v>
+        <v>5.568239881786464</v>
       </c>
       <c r="D105" t="n">
-        <v>5.117476940155029</v>
+        <v>5.117477416992188</v>
       </c>
       <c r="E105" t="n">
-        <v>5.550562429982751</v>
+        <v>5.550562947174024</v>
       </c>
       <c r="F105" t="n">
         <v>7203400</v>
@@ -2552,16 +2552,16 @@
         <v>44568</v>
       </c>
       <c r="B107" t="n">
-        <v>5.163622379302979</v>
+        <v>5.16362190246582</v>
       </c>
       <c r="C107" t="n">
-        <v>5.278960698586984</v>
+        <v>5.278960211098854</v>
       </c>
       <c r="D107" t="n">
-        <v>4.941817300823532</v>
+        <v>4.941816844469068</v>
       </c>
       <c r="E107" t="n">
-        <v>4.977306079535475</v>
+        <v>4.977305619903783</v>
       </c>
       <c r="F107" t="n">
         <v>10961100</v>
@@ -2572,16 +2572,16 @@
         <v>44571</v>
       </c>
       <c r="B108" t="n">
-        <v>5.057156085968018</v>
+        <v>5.057155609130859</v>
       </c>
       <c r="C108" t="n">
-        <v>5.128134072989941</v>
+        <v>5.128133589460298</v>
       </c>
       <c r="D108" t="n">
-        <v>4.906328974078017</v>
+        <v>4.906328511462285</v>
       </c>
       <c r="E108" t="n">
-        <v>5.057156085968018</v>
+        <v>5.057155609130859</v>
       </c>
       <c r="F108" t="n">
         <v>11253600</v>
@@ -2592,16 +2592,16 @@
         <v>44572</v>
       </c>
       <c r="B109" t="n">
-        <v>5.23460054397583</v>
+        <v>5.234600067138672</v>
       </c>
       <c r="C109" t="n">
-        <v>5.23460054397583</v>
+        <v>5.234600067138672</v>
       </c>
       <c r="D109" t="n">
-        <v>5.021667423942884</v>
+        <v>5.021666966502512</v>
       </c>
       <c r="E109" t="n">
-        <v>5.021667423942884</v>
+        <v>5.021666966502512</v>
       </c>
       <c r="F109" t="n">
         <v>5425200</v>
@@ -2612,16 +2612,16 @@
         <v>44573</v>
       </c>
       <c r="B110" t="n">
-        <v>5.438660621643066</v>
+        <v>5.438660144805908</v>
       </c>
       <c r="C110" t="n">
-        <v>5.51851016215336</v>
+        <v>5.518509678315355</v>
       </c>
       <c r="D110" t="n">
-        <v>5.225727526476521</v>
+        <v>5.225727068308373</v>
       </c>
       <c r="E110" t="n">
-        <v>5.261216305161009</v>
+        <v>5.261215843881367</v>
       </c>
       <c r="F110" t="n">
         <v>9077500</v>
@@ -2632,16 +2632,16 @@
         <v>44574</v>
       </c>
       <c r="B111" t="n">
-        <v>5.420916557312012</v>
+        <v>5.42091703414917</v>
       </c>
       <c r="C111" t="n">
-        <v>5.50963850934256</v>
+        <v>5.50963899398392</v>
       </c>
       <c r="D111" t="n">
-        <v>5.358810979360809</v>
+        <v>5.358811450735008</v>
       </c>
       <c r="E111" t="n">
-        <v>5.358810979360809</v>
+        <v>5.358811450735008</v>
       </c>
       <c r="F111" t="n">
         <v>4388600</v>
@@ -2752,16 +2752,16 @@
         <v>44582</v>
       </c>
       <c r="B117" t="n">
-        <v>5.527382850646973</v>
+        <v>5.527382373809814</v>
       </c>
       <c r="C117" t="n">
-        <v>5.687082362883293</v>
+        <v>5.687081872269151</v>
       </c>
       <c r="D117" t="n">
-        <v>5.483021663495955</v>
+        <v>5.483021190485755</v>
       </c>
       <c r="E117" t="n">
-        <v>5.678210379288871</v>
+        <v>5.678209889440098</v>
       </c>
       <c r="F117" t="n">
         <v>7609900</v>
@@ -2812,16 +2812,16 @@
         <v>44587</v>
       </c>
       <c r="B120" t="n">
-        <v>5.518509864807129</v>
+        <v>5.518510341644287</v>
       </c>
       <c r="C120" t="n">
-        <v>5.678209783342052</v>
+        <v>5.67821027397838</v>
       </c>
       <c r="D120" t="n">
-        <v>5.491893493757702</v>
+        <v>5.491893968295023</v>
       </c>
       <c r="E120" t="n">
-        <v>5.59835982407459</v>
+        <v>5.598360307811333</v>
       </c>
       <c r="F120" t="n">
         <v>11610000</v>
@@ -2852,16 +2852,16 @@
         <v>44589</v>
       </c>
       <c r="B122" t="n">
-        <v>5.660466194152832</v>
+        <v>5.660465717315674</v>
       </c>
       <c r="C122" t="n">
-        <v>5.731443757718693</v>
+        <v>5.731443274902391</v>
       </c>
       <c r="D122" t="n">
-        <v>5.509638660045554</v>
+        <v>5.509638195914094</v>
       </c>
       <c r="E122" t="n">
-        <v>5.509638660045554</v>
+        <v>5.509638195914094</v>
       </c>
       <c r="F122" t="n">
         <v>15566700</v>
@@ -2872,16 +2872,16 @@
         <v>44592</v>
       </c>
       <c r="B123" t="n">
-        <v>5.695953845977783</v>
+        <v>5.6959547996521</v>
       </c>
       <c r="C123" t="n">
-        <v>5.793548188049992</v>
+        <v>5.793549158064543</v>
       </c>
       <c r="D123" t="n">
-        <v>5.571743134378331</v>
+        <v>5.571744067256032</v>
       </c>
       <c r="E123" t="n">
-        <v>5.607231909121031</v>
+        <v>5.607232847940623</v>
       </c>
       <c r="F123" t="n">
         <v>7514700</v>
@@ -2912,16 +2912,16 @@
         <v>44594</v>
       </c>
       <c r="B125" t="n">
-        <v>5.669338703155518</v>
+        <v>5.669338226318359</v>
       </c>
       <c r="C125" t="n">
-        <v>5.882271836634339</v>
+        <v>5.882271341887785</v>
       </c>
       <c r="D125" t="n">
-        <v>5.65159431062059</v>
+        <v>5.651593835275879</v>
       </c>
       <c r="E125" t="n">
-        <v>5.722571880760301</v>
+        <v>5.722571399445803</v>
       </c>
       <c r="F125" t="n">
         <v>8808600</v>
@@ -2932,16 +2932,16 @@
         <v>44595</v>
       </c>
       <c r="B126" t="n">
-        <v>5.731443881988525</v>
+        <v>5.731442928314209</v>
       </c>
       <c r="C126" t="n">
-        <v>5.793549462985059</v>
+        <v>5.793548498976785</v>
       </c>
       <c r="D126" t="n">
-        <v>5.616105127163388</v>
+        <v>5.616104192680678</v>
       </c>
       <c r="E126" t="n">
-        <v>5.678210708159922</v>
+        <v>5.678209763343253</v>
       </c>
       <c r="F126" t="n">
         <v>8390300</v>
@@ -2952,16 +2952,16 @@
         <v>44596</v>
       </c>
       <c r="B127" t="n">
-        <v>5.660466194152832</v>
+        <v>5.660465717315674</v>
       </c>
       <c r="C127" t="n">
-        <v>5.820165712176019</v>
+        <v>5.820165221885787</v>
       </c>
       <c r="D127" t="n">
-        <v>5.63384939628581</v>
+        <v>5.633848921690848</v>
       </c>
       <c r="E127" t="n">
-        <v>5.722571350743135</v>
+        <v>5.722570868674245</v>
       </c>
       <c r="F127" t="n">
         <v>8483700</v>
@@ -2972,16 +2972,16 @@
         <v>44599</v>
       </c>
       <c r="B128" t="n">
-        <v>5.562871932983398</v>
+        <v>5.562870979309082</v>
       </c>
       <c r="C128" t="n">
-        <v>5.775805050578469</v>
+        <v>5.775804060399835</v>
       </c>
       <c r="D128" t="n">
-        <v>5.553999948907585</v>
+        <v>5.553998996754243</v>
       </c>
       <c r="E128" t="n">
-        <v>5.704827062673674</v>
+        <v>5.704826084663194</v>
       </c>
       <c r="F128" t="n">
         <v>7178800</v>
@@ -2992,16 +2992,16 @@
         <v>44600</v>
       </c>
       <c r="B129" t="n">
-        <v>5.616104602813721</v>
+        <v>5.616105079650879</v>
       </c>
       <c r="C129" t="n">
-        <v>5.695954567631234</v>
+        <v>5.695955051248079</v>
       </c>
       <c r="D129" t="n">
-        <v>5.483021469137738</v>
+        <v>5.48302193467543</v>
       </c>
       <c r="E129" t="n">
-        <v>5.580615823574741</v>
+        <v>5.580616297398714</v>
       </c>
       <c r="F129" t="n">
         <v>9770800</v>
@@ -3012,16 +3012,16 @@
         <v>44601</v>
       </c>
       <c r="B130" t="n">
-        <v>5.633849143981934</v>
+        <v>5.633848667144775</v>
       </c>
       <c r="C130" t="n">
-        <v>5.740315484562782</v>
+        <v>5.740314998714537</v>
       </c>
       <c r="D130" t="n">
-        <v>5.58948838026973</v>
+        <v>5.589487907187173</v>
       </c>
       <c r="E130" t="n">
-        <v>5.616104753885126</v>
+        <v>5.616104278549815</v>
       </c>
       <c r="F130" t="n">
         <v>8867400</v>
@@ -3032,16 +3032,16 @@
         <v>44602</v>
       </c>
       <c r="B131" t="n">
-        <v>5.704825878143311</v>
+        <v>5.704826831817627</v>
       </c>
       <c r="C131" t="n">
-        <v>5.740314653197113</v>
+        <v>5.740315612804078</v>
       </c>
       <c r="D131" t="n">
-        <v>5.562870777928103</v>
+        <v>5.56287170787182</v>
       </c>
       <c r="E131" t="n">
-        <v>5.678209508382744</v>
+        <v>5.678210457607609</v>
       </c>
       <c r="F131" t="n">
         <v>9667400</v>
@@ -3052,16 +3052,16 @@
         <v>44603</v>
       </c>
       <c r="B132" t="n">
-        <v>5.633849143981934</v>
+        <v>5.633848667144775</v>
       </c>
       <c r="C132" t="n">
-        <v>5.775804687816029</v>
+        <v>5.775804198964051</v>
       </c>
       <c r="D132" t="n">
-        <v>5.58948838026973</v>
+        <v>5.589487907187173</v>
       </c>
       <c r="E132" t="n">
-        <v>5.731443501044193</v>
+        <v>5.731443015946853</v>
       </c>
       <c r="F132" t="n">
         <v>8001300</v>
@@ -3072,16 +3072,16 @@
         <v>44606</v>
       </c>
       <c r="B133" t="n">
-        <v>5.695953845977783</v>
+        <v>5.6959547996521</v>
       </c>
       <c r="C133" t="n">
-        <v>5.766931395463184</v>
+        <v>5.766932361021281</v>
       </c>
       <c r="D133" t="n">
-        <v>5.642720683863732</v>
+        <v>5.642721628625214</v>
       </c>
       <c r="E133" t="n">
-        <v>5.642720683863732</v>
+        <v>5.642721628625214</v>
       </c>
       <c r="F133" t="n">
         <v>12680200</v>
@@ -3092,16 +3092,16 @@
         <v>44607</v>
       </c>
       <c r="B134" t="n">
-        <v>5.695953845977783</v>
+        <v>5.6959547996521</v>
       </c>
       <c r="C134" t="n">
-        <v>5.811292575421342</v>
+        <v>5.811293548406838</v>
       </c>
       <c r="D134" t="n">
-        <v>5.518509549204714</v>
+        <v>5.518510473169509</v>
       </c>
       <c r="E134" t="n">
-        <v>5.811292575421342</v>
+        <v>5.811293548406838</v>
       </c>
       <c r="F134" t="n">
         <v>17426200</v>
@@ -3112,16 +3112,16 @@
         <v>44608</v>
       </c>
       <c r="B135" t="n">
-        <v>5.704825878143311</v>
+        <v>5.704826831817627</v>
       </c>
       <c r="C135" t="n">
-        <v>5.811292626364287</v>
+        <v>5.811293597836623</v>
       </c>
       <c r="D135" t="n">
-        <v>5.651592715562607</v>
+        <v>5.651593660337949</v>
       </c>
       <c r="E135" t="n">
-        <v>5.713698283436546</v>
+        <v>5.71369923859406</v>
       </c>
       <c r="F135" t="n">
         <v>12029900</v>
@@ -3132,16 +3132,16 @@
         <v>44609</v>
       </c>
       <c r="B136" t="n">
-        <v>5.580616474151611</v>
+        <v>5.580615997314453</v>
       </c>
       <c r="C136" t="n">
-        <v>5.740315999344462</v>
+        <v>5.740315508861739</v>
       </c>
       <c r="D136" t="n">
-        <v>5.509638907399233</v>
+        <v>5.509638436626771</v>
       </c>
       <c r="E136" t="n">
-        <v>5.73144401503025</v>
+        <v>5.731443525305595</v>
       </c>
       <c r="F136" t="n">
         <v>16171600</v>
@@ -3152,16 +3152,16 @@
         <v>44610</v>
       </c>
       <c r="B137" t="n">
-        <v>5.420916557312012</v>
+        <v>5.42091703414917</v>
       </c>
       <c r="C137" t="n">
-        <v>5.616104851779219</v>
+        <v>5.61610534578562</v>
       </c>
       <c r="D137" t="n">
-        <v>5.305577808142479</v>
+        <v>5.305578274834157</v>
       </c>
       <c r="E137" t="n">
-        <v>5.598360461373109</v>
+        <v>5.59836095381867</v>
       </c>
       <c r="F137" t="n">
         <v>12852100</v>
@@ -3172,16 +3172,16 @@
         <v>44613</v>
       </c>
       <c r="B138" t="n">
-        <v>5.119260787963867</v>
+        <v>5.119261741638184</v>
       </c>
       <c r="C138" t="n">
-        <v>5.456404582021004</v>
+        <v>5.456405598502314</v>
       </c>
       <c r="D138" t="n">
-        <v>5.074899606565978</v>
+        <v>5.074900551976187</v>
       </c>
       <c r="E138" t="n">
-        <v>5.447532176517594</v>
+        <v>5.447533191346051</v>
       </c>
       <c r="F138" t="n">
         <v>8726900</v>
@@ -3212,16 +3212,16 @@
         <v>44615</v>
       </c>
       <c r="B140" t="n">
-        <v>5.021666526794434</v>
+        <v>5.021667003631592</v>
       </c>
       <c r="C140" t="n">
-        <v>5.10151648542361</v>
+        <v>5.101516969842998</v>
       </c>
       <c r="D140" t="n">
-        <v>4.968433362061512</v>
+        <v>4.968433833843864</v>
       </c>
       <c r="E140" t="n">
-        <v>5.057155303283048</v>
+        <v>5.057155783490078</v>
       </c>
       <c r="F140" t="n">
         <v>10772600</v>
@@ -3232,16 +3232,16 @@
         <v>44616</v>
       </c>
       <c r="B141" t="n">
-        <v>5.119260787963867</v>
+        <v>5.119261741638184</v>
       </c>
       <c r="C141" t="n">
-        <v>5.137005175911107</v>
+        <v>5.137006132891051</v>
       </c>
       <c r="D141" t="n">
-        <v>4.7732450114629</v>
+        <v>4.773245900677449</v>
       </c>
       <c r="E141" t="n">
-        <v>4.924072520544229</v>
+        <v>4.924073437856647</v>
       </c>
       <c r="F141" t="n">
         <v>11357100</v>
@@ -3252,16 +3252,16 @@
         <v>44617</v>
       </c>
       <c r="B142" t="n">
-        <v>5.066028594970703</v>
+        <v>5.066027641296387</v>
       </c>
       <c r="C142" t="n">
-        <v>5.163622958913197</v>
+        <v>5.163621986866849</v>
       </c>
       <c r="D142" t="n">
-        <v>4.986178622375967</v>
+        <v>4.986177683733319</v>
       </c>
       <c r="E142" t="n">
-        <v>5.110389784869926</v>
+        <v>5.110388822844664</v>
       </c>
       <c r="F142" t="n">
         <v>6795000</v>
@@ -3272,16 +3272,16 @@
         <v>44622</v>
       </c>
       <c r="B143" t="n">
-        <v>5.314449310302734</v>
+        <v>5.314450263977051</v>
       </c>
       <c r="C143" t="n">
-        <v>5.349938510959111</v>
+        <v>5.349939471001941</v>
       </c>
       <c r="D143" t="n">
-        <v>5.03053908952852</v>
+        <v>5.030539992255339</v>
       </c>
       <c r="E143" t="n">
-        <v>5.101516644722073</v>
+        <v>5.101517560185767</v>
       </c>
       <c r="F143" t="n">
         <v>7030100</v>
@@ -3312,16 +3312,16 @@
         <v>44624</v>
       </c>
       <c r="B145" t="n">
-        <v>5.509637832641602</v>
+        <v>5.50963830947876</v>
       </c>
       <c r="C145" t="n">
-        <v>5.53625420345189</v>
+        <v>5.536254682592588</v>
       </c>
       <c r="D145" t="n">
-        <v>5.376554709411403</v>
+        <v>5.376555174730749</v>
       </c>
       <c r="E145" t="n">
-        <v>5.483021038771727</v>
+        <v>5.483021513305308</v>
       </c>
       <c r="F145" t="n">
         <v>9336900</v>
@@ -3372,16 +3372,16 @@
         <v>44629</v>
       </c>
       <c r="B148" t="n">
-        <v>5.695953845977783</v>
+        <v>5.6959547996521</v>
       </c>
       <c r="C148" t="n">
-        <v>5.704825828133675</v>
+        <v>5.704826783293429</v>
       </c>
       <c r="D148" t="n">
-        <v>5.553998747006981</v>
+        <v>5.553999676913737</v>
       </c>
       <c r="E148" t="n">
-        <v>5.589487521749682</v>
+        <v>5.589488457598327</v>
       </c>
       <c r="F148" t="n">
         <v>9079900</v>
@@ -3392,16 +3392,16 @@
         <v>44630</v>
       </c>
       <c r="B149" t="n">
-        <v>5.695953845977783</v>
+        <v>5.6959547996521</v>
       </c>
       <c r="C149" t="n">
-        <v>5.829036962792693</v>
+        <v>5.829037938749134</v>
       </c>
       <c r="D149" t="n">
-        <v>5.553998747006981</v>
+        <v>5.553999676913737</v>
       </c>
       <c r="E149" t="n">
-        <v>5.624976296492382</v>
+        <v>5.624977238282918</v>
       </c>
       <c r="F149" t="n">
         <v>15215200</v>
@@ -3412,16 +3412,16 @@
         <v>44631</v>
       </c>
       <c r="B150" t="n">
-        <v>5.598360538482666</v>
+        <v>5.59835958480835</v>
       </c>
       <c r="C150" t="n">
-        <v>5.979865148998535</v>
+        <v>5.979864130335345</v>
       </c>
       <c r="D150" t="n">
-        <v>5.52738297588061</v>
+        <v>5.527382034297241</v>
       </c>
       <c r="E150" t="n">
-        <v>5.695954898590315</v>
+        <v>5.69595392829091</v>
       </c>
       <c r="F150" t="n">
         <v>16712700</v>
@@ -3492,16 +3492,16 @@
         <v>44637</v>
       </c>
       <c r="B154" t="n">
-        <v>5.89114236831665</v>
+        <v>5.891142845153809</v>
       </c>
       <c r="C154" t="n">
-        <v>5.926631144633169</v>
+        <v>5.926631624342837</v>
       </c>
       <c r="D154" t="n">
-        <v>5.536254182091882</v>
+        <v>5.536254630203903</v>
       </c>
       <c r="E154" t="n">
-        <v>5.607232157784503</v>
+        <v>5.607232611641579</v>
       </c>
       <c r="F154" t="n">
         <v>10001800</v>
@@ -3512,16 +3512,16 @@
         <v>44638</v>
       </c>
       <c r="B155" t="n">
-        <v>6.201670169830322</v>
+        <v>6.201669692993164</v>
       </c>
       <c r="C155" t="n">
-        <v>6.201670169830322</v>
+        <v>6.201669692993164</v>
       </c>
       <c r="D155" t="n">
-        <v>5.891143125613262</v>
+        <v>5.891142672652063</v>
       </c>
       <c r="E155" t="n">
-        <v>5.891143125613262</v>
+        <v>5.891142672652063</v>
       </c>
       <c r="F155" t="n">
         <v>17710700</v>
@@ -3532,16 +3532,16 @@
         <v>44641</v>
       </c>
       <c r="B156" t="n">
-        <v>6.10407543182373</v>
+        <v>6.104075908660889</v>
       </c>
       <c r="C156" t="n">
-        <v>6.343624882805147</v>
+        <v>6.34362537835539</v>
       </c>
       <c r="D156" t="n">
-        <v>6.024225473810064</v>
+        <v>6.024225944409515</v>
       </c>
       <c r="E156" t="n">
-        <v>6.183924966777814</v>
+        <v>6.183925449852644</v>
       </c>
       <c r="F156" t="n">
         <v>14982100</v>
@@ -3552,16 +3552,16 @@
         <v>44642</v>
       </c>
       <c r="B157" t="n">
-        <v>6.299263477325439</v>
+        <v>6.299264430999756</v>
       </c>
       <c r="C157" t="n">
-        <v>6.308135882593944</v>
+        <v>6.308136837611495</v>
       </c>
       <c r="D157" t="n">
-        <v>6.077458422327646</v>
+        <v>6.07745934242188</v>
       </c>
       <c r="E157" t="n">
-        <v>6.077458422327646</v>
+        <v>6.07745934242188</v>
       </c>
       <c r="F157" t="n">
         <v>9703800</v>
@@ -3592,16 +3592,16 @@
         <v>44644</v>
       </c>
       <c r="B159" t="n">
-        <v>6.343625068664551</v>
+        <v>6.343625545501709</v>
       </c>
       <c r="C159" t="n">
-        <v>6.432347011801619</v>
+        <v>6.432347495307822</v>
       </c>
       <c r="D159" t="n">
-        <v>6.254903125527482</v>
+        <v>6.254903595695596</v>
       </c>
       <c r="E159" t="n">
-        <v>6.299263885566218</v>
+        <v>6.299264359068839</v>
       </c>
       <c r="F159" t="n">
         <v>11578200</v>
@@ -3612,16 +3612,16 @@
         <v>44645</v>
       </c>
       <c r="B160" t="n">
-        <v>6.450092315673828</v>
+        <v>6.45009183883667</v>
       </c>
       <c r="C160" t="n">
-        <v>6.512197896212132</v>
+        <v>6.512197414783683</v>
       </c>
       <c r="D160" t="n">
-        <v>6.237159621930483</v>
+        <v>6.237159160834839</v>
       </c>
       <c r="E160" t="n">
-        <v>6.343625968802155</v>
+        <v>6.343625499835754</v>
       </c>
       <c r="F160" t="n">
         <v>15324200</v>
@@ -3672,16 +3672,16 @@
         <v>44650</v>
       </c>
       <c r="B163" t="n">
-        <v>6.50332498550415</v>
+        <v>6.503324508666992</v>
       </c>
       <c r="C163" t="n">
-        <v>6.61866373054667</v>
+        <v>6.618663245252637</v>
       </c>
       <c r="D163" t="n">
-        <v>6.450091816190593</v>
+        <v>6.4500913432566</v>
       </c>
       <c r="E163" t="n">
-        <v>6.547686171461927</v>
+        <v>6.547685691372115</v>
       </c>
       <c r="F163" t="n">
         <v>10697600</v>
@@ -3712,16 +3712,16 @@
         <v>44652</v>
       </c>
       <c r="B165" t="n">
-        <v>6.139564990997314</v>
+        <v>6.139564514160156</v>
       </c>
       <c r="C165" t="n">
-        <v>6.299264504331019</v>
+        <v>6.299264015090594</v>
       </c>
       <c r="D165" t="n">
-        <v>5.926631883492739</v>
+        <v>5.926631423193302</v>
       </c>
       <c r="E165" t="n">
-        <v>6.254903739934808</v>
+        <v>6.254903254139719</v>
       </c>
       <c r="F165" t="n">
         <v>18919700</v>
@@ -3732,16 +3732,16 @@
         <v>44655</v>
       </c>
       <c r="B166" t="n">
-        <v>6.210542678833008</v>
+        <v>6.21054220199585</v>
       </c>
       <c r="C166" t="n">
-        <v>6.237159476459965</v>
+        <v>6.237158997579204</v>
       </c>
       <c r="D166" t="n">
-        <v>6.050843162250203</v>
+        <v>6.050842697674559</v>
       </c>
       <c r="E166" t="n">
-        <v>6.15730950663874</v>
+        <v>6.157309033888753</v>
       </c>
       <c r="F166" t="n">
         <v>13343800</v>
@@ -3752,16 +3752,16 @@
         <v>44656</v>
       </c>
       <c r="B167" t="n">
-        <v>6.299263477325439</v>
+        <v>6.299264430999756</v>
       </c>
       <c r="C167" t="n">
-        <v>6.325880270071385</v>
+        <v>6.32588122777534</v>
       </c>
       <c r="D167" t="n">
-        <v>6.148435972237409</v>
+        <v>6.148436903077259</v>
       </c>
       <c r="E167" t="n">
-        <v>6.228285927415676</v>
+        <v>6.228286870344377</v>
       </c>
       <c r="F167" t="n">
         <v>6962400</v>
@@ -3792,16 +3792,16 @@
         <v>44658</v>
       </c>
       <c r="B169" t="n">
-        <v>6.261641502380371</v>
+        <v>6.261641025543213</v>
       </c>
       <c r="C169" t="n">
-        <v>6.395246596078652</v>
+        <v>6.395246109067186</v>
       </c>
       <c r="D169" t="n">
-        <v>6.208198955236777</v>
+        <v>6.208198482469381</v>
       </c>
       <c r="E169" t="n">
-        <v>6.323990432847507</v>
+        <v>6.323989951262346</v>
       </c>
       <c r="F169" t="n">
         <v>10216600</v>
@@ -3832,16 +3832,16 @@
         <v>44662</v>
       </c>
       <c r="B171" t="n">
-        <v>6.14585018157959</v>
+        <v>6.145849704742432</v>
       </c>
       <c r="C171" t="n">
-        <v>6.21710634662882</v>
+        <v>6.217105864263122</v>
       </c>
       <c r="D171" t="n">
-        <v>6.021151892743435</v>
+        <v>6.021151425581226</v>
       </c>
       <c r="E171" t="n">
-        <v>6.119128907326005</v>
+        <v>6.119128432562067</v>
       </c>
       <c r="F171" t="n">
         <v>4955900</v>
@@ -3852,16 +3852,16 @@
         <v>44663</v>
       </c>
       <c r="B172" t="n">
-        <v>6.217106819152832</v>
+        <v>6.217105865478516</v>
       </c>
       <c r="C172" t="n">
-        <v>6.359619160082779</v>
+        <v>6.359618184547754</v>
       </c>
       <c r="D172" t="n">
-        <v>6.145850648687858</v>
+        <v>6.145849705943896</v>
       </c>
       <c r="E172" t="n">
-        <v>6.190385542868328</v>
+        <v>6.190384593292927</v>
       </c>
       <c r="F172" t="n">
         <v>15598900</v>
@@ -3892,16 +3892,16 @@
         <v>44665</v>
       </c>
       <c r="B174" t="n">
-        <v>6.323990345001221</v>
+        <v>6.323990821838379</v>
       </c>
       <c r="C174" t="n">
-        <v>6.350711618201833</v>
+        <v>6.350712097053812</v>
       </c>
       <c r="D174" t="n">
-        <v>6.226012909559278</v>
+        <v>6.226013379008809</v>
       </c>
       <c r="E174" t="n">
-        <v>6.297269496520836</v>
+        <v>6.297269971343208</v>
       </c>
       <c r="F174" t="n">
         <v>4947000</v>
@@ -3972,16 +3972,16 @@
         <v>44673</v>
       </c>
       <c r="B178" t="n">
-        <v>6.128035545349121</v>
+        <v>6.128036022186279</v>
       </c>
       <c r="C178" t="n">
-        <v>6.190384471353647</v>
+        <v>6.190384953042324</v>
       </c>
       <c r="D178" t="n">
-        <v>5.98552280436691</v>
+        <v>5.98552327011481</v>
       </c>
       <c r="E178" t="n">
-        <v>6.136942352755394</v>
+        <v>6.136942830285612</v>
       </c>
       <c r="F178" t="n">
         <v>9926800</v>
@@ -4072,16 +4072,16 @@
         <v>44680</v>
       </c>
       <c r="B183" t="n">
-        <v>6.14585018157959</v>
+        <v>6.145849704742432</v>
       </c>
       <c r="C183" t="n">
-        <v>6.44868888303882</v>
+        <v>6.448688382705361</v>
       </c>
       <c r="D183" t="n">
-        <v>6.065686783539082</v>
+        <v>6.06568631292155</v>
       </c>
       <c r="E183" t="n">
-        <v>6.413060800514205</v>
+        <v>6.413060302945017</v>
       </c>
       <c r="F183" t="n">
         <v>21979100</v>
@@ -4092,16 +4092,16 @@
         <v>44683</v>
       </c>
       <c r="B184" t="n">
-        <v>5.869731903076172</v>
+        <v>5.86973237991333</v>
       </c>
       <c r="C184" t="n">
-        <v>6.19038462249456</v>
+        <v>6.19038512538046</v>
       </c>
       <c r="D184" t="n">
-        <v>5.745033198582139</v>
+        <v>5.745033665289197</v>
       </c>
       <c r="E184" t="n">
-        <v>6.145849734935447</v>
+        <v>6.145850234203484</v>
       </c>
       <c r="F184" t="n">
         <v>12404500</v>
@@ -4172,16 +4172,16 @@
         <v>44687</v>
       </c>
       <c r="B188" t="n">
-        <v>4.952308654785156</v>
+        <v>4.952307224273682</v>
       </c>
       <c r="C188" t="n">
-        <v>5.068100147320131</v>
+        <v>5.068098683361416</v>
       </c>
       <c r="D188" t="n">
-        <v>4.863238439266056</v>
+        <v>4.863237034483181</v>
       </c>
       <c r="E188" t="n">
-        <v>4.970122697888977</v>
+        <v>4.970121262231782</v>
       </c>
       <c r="F188" t="n">
         <v>14479200</v>
@@ -4212,16 +4212,16 @@
         <v>44691</v>
       </c>
       <c r="B190" t="n">
-        <v>4.631654739379883</v>
+        <v>4.631655216217041</v>
       </c>
       <c r="C190" t="n">
-        <v>4.711818133335377</v>
+        <v>4.7118186184255</v>
       </c>
       <c r="D190" t="n">
-        <v>4.569305810499142</v>
+        <v>4.569306280917366</v>
       </c>
       <c r="E190" t="n">
-        <v>4.658376012271789</v>
+        <v>4.65837649185995</v>
       </c>
       <c r="F190" t="n">
         <v>9825600</v>
@@ -4232,16 +4232,16 @@
         <v>44692</v>
       </c>
       <c r="B191" t="n">
-        <v>4.640562057495117</v>
+        <v>4.640562534332275</v>
       </c>
       <c r="C191" t="n">
-        <v>4.694004179544246</v>
+        <v>4.694004661872806</v>
       </c>
       <c r="D191" t="n">
-        <v>4.489142499329136</v>
+        <v>4.489142960607302</v>
       </c>
       <c r="E191" t="n">
-        <v>4.640562057495117</v>
+        <v>4.640562534332275</v>
       </c>
       <c r="F191" t="n">
         <v>17331100</v>
@@ -4272,16 +4272,16 @@
         <v>44694</v>
       </c>
       <c r="B193" t="n">
-        <v>4.604933738708496</v>
+        <v>4.604934215545654</v>
       </c>
       <c r="C193" t="n">
-        <v>4.800888176118977</v>
+        <v>4.800888673247058</v>
       </c>
       <c r="D193" t="n">
-        <v>4.51586353988555</v>
+        <v>4.515864007499562</v>
       </c>
       <c r="E193" t="n">
-        <v>4.800888176118977</v>
+        <v>4.800888673247058</v>
       </c>
       <c r="F193" t="n">
         <v>51332400</v>
@@ -4312,16 +4312,16 @@
         <v>44698</v>
       </c>
       <c r="B195" t="n">
-        <v>5.005750179290771</v>
+        <v>5.00575065612793</v>
       </c>
       <c r="C195" t="n">
-        <v>5.183891013525891</v>
+        <v>5.183891507332367</v>
       </c>
       <c r="D195" t="n">
-        <v>4.881051892630355</v>
+        <v>4.881052357589018</v>
       </c>
       <c r="E195" t="n">
-        <v>4.952308056436308</v>
+        <v>4.952308528182682</v>
       </c>
       <c r="F195" t="n">
         <v>40878000</v>
@@ -4332,16 +4332,16 @@
         <v>44699</v>
       </c>
       <c r="B196" t="n">
-        <v>4.952308654785156</v>
+        <v>4.952307224273682</v>
       </c>
       <c r="C196" t="n">
-        <v>5.112635042719536</v>
+        <v>5.112633565896584</v>
       </c>
       <c r="D196" t="n">
-        <v>4.898866525473696</v>
+        <v>4.898865110399381</v>
       </c>
       <c r="E196" t="n">
-        <v>4.987936740992796</v>
+        <v>4.987935300189882</v>
       </c>
       <c r="F196" t="n">
         <v>17779600</v>
@@ -4392,16 +4392,16 @@
         <v>44704</v>
       </c>
       <c r="B199" t="n">
-        <v>5.023565292358398</v>
+        <v>5.023564338684082</v>
       </c>
       <c r="C199" t="n">
-        <v>5.10372870610848</v>
+        <v>5.10372773721593</v>
       </c>
       <c r="D199" t="n">
-        <v>4.88105293433188</v>
+        <v>4.881052007712129</v>
       </c>
       <c r="E199" t="n">
-        <v>4.979030392835275</v>
+        <v>4.979029447615471</v>
       </c>
       <c r="F199" t="n">
         <v>11444200</v>
@@ -4412,16 +4412,16 @@
         <v>44705</v>
       </c>
       <c r="B200" t="n">
-        <v>5.157169818878174</v>
+        <v>5.157169342041016</v>
       </c>
       <c r="C200" t="n">
-        <v>5.201705134300433</v>
+        <v>5.201704653345494</v>
       </c>
       <c r="D200" t="n">
-        <v>4.961215365404775</v>
+        <v>4.961214906685765</v>
       </c>
       <c r="E200" t="n">
-        <v>4.979029406629629</v>
+        <v>4.979028946263514</v>
       </c>
       <c r="F200" t="n">
         <v>9007600</v>
@@ -4492,16 +4492,16 @@
         <v>44711</v>
       </c>
       <c r="B204" t="n">
-        <v>5.602521419525146</v>
+        <v>5.602520942687988</v>
       </c>
       <c r="C204" t="n">
-        <v>5.673777586272644</v>
+        <v>5.67377710337079</v>
       </c>
       <c r="D204" t="n">
-        <v>5.317496327814903</v>
+        <v>5.317495875236564</v>
       </c>
       <c r="E204" t="n">
-        <v>5.460009086030153</v>
+        <v>5.460008621322386</v>
       </c>
       <c r="F204" t="n">
         <v>7527500</v>
@@ -4552,16 +4552,16 @@
         <v>44714</v>
       </c>
       <c r="B207" t="n">
-        <v>5.611428260803223</v>
+        <v>5.611427783966064</v>
       </c>
       <c r="C207" t="n">
-        <v>5.655963149549779</v>
+        <v>5.65596266892822</v>
       </c>
       <c r="D207" t="n">
-        <v>5.504543593426991</v>
+        <v>5.504543125672473</v>
       </c>
       <c r="E207" t="n">
-        <v>5.549078906893773</v>
+        <v>5.549078435354819</v>
       </c>
       <c r="F207" t="n">
         <v>14163200</v>
@@ -4592,16 +4592,16 @@
         <v>44718</v>
       </c>
       <c r="B209" t="n">
-        <v>5.308588981628418</v>
+        <v>5.308589458465576</v>
       </c>
       <c r="C209" t="n">
-        <v>5.566892772284817</v>
+        <v>5.566893272323779</v>
       </c>
       <c r="D209" t="n">
-        <v>5.246239629679551</v>
+        <v>5.24624010091626</v>
       </c>
       <c r="E209" t="n">
-        <v>5.566892772284817</v>
+        <v>5.566893272323779</v>
       </c>
       <c r="F209" t="n">
         <v>9845400</v>
@@ -4612,16 +4612,16 @@
         <v>44719</v>
       </c>
       <c r="B210" t="n">
-        <v>5.023565292358398</v>
+        <v>5.023564338684082</v>
       </c>
       <c r="C210" t="n">
-        <v>5.299683198394942</v>
+        <v>5.299682192302366</v>
       </c>
       <c r="D210" t="n">
-        <v>4.987937202851769</v>
+        <v>4.987936255941094</v>
       </c>
       <c r="E210" t="n">
-        <v>5.281869153641628</v>
+        <v>5.281868150930872</v>
       </c>
       <c r="F210" t="n">
         <v>18881300</v>
@@ -4652,16 +4652,16 @@
         <v>44721</v>
       </c>
       <c r="B212" t="n">
-        <v>4.818703174591064</v>
+        <v>4.818702697753906</v>
       </c>
       <c r="C212" t="n">
-        <v>4.996844032399269</v>
+        <v>4.996843537934095</v>
       </c>
       <c r="D212" t="n">
-        <v>4.809796365296816</v>
+        <v>4.809795889341036</v>
       </c>
       <c r="E212" t="n">
-        <v>4.88105253853198</v>
+        <v>4.88105205552501</v>
       </c>
       <c r="F212" t="n">
         <v>8480000</v>
@@ -4672,16 +4672,16 @@
         <v>44722</v>
       </c>
       <c r="B213" t="n">
-        <v>4.738539218902588</v>
+        <v>4.738539695739746</v>
       </c>
       <c r="C213" t="n">
-        <v>4.78307410566824</v>
+        <v>4.783074586986924</v>
       </c>
       <c r="D213" t="n">
-        <v>4.676189867766428</v>
+        <v>4.676190338329397</v>
       </c>
       <c r="E213" t="n">
-        <v>4.774167298203192</v>
+        <v>4.774167778625588</v>
       </c>
       <c r="F213" t="n">
         <v>4786300</v>
@@ -4712,16 +4712,16 @@
         <v>44726</v>
       </c>
       <c r="B215" t="n">
-        <v>4.462421894073486</v>
+        <v>4.462421417236328</v>
       </c>
       <c r="C215" t="n">
-        <v>4.640562310620824</v>
+        <v>4.640561814748269</v>
       </c>
       <c r="D215" t="n">
-        <v>4.453514660885992</v>
+        <v>4.453514185000626</v>
       </c>
       <c r="E215" t="n">
-        <v>4.587120185656623</v>
+        <v>4.587119695494687</v>
       </c>
       <c r="F215" t="n">
         <v>9819800</v>
@@ -4732,16 +4732,16 @@
         <v>44727</v>
       </c>
       <c r="B216" t="n">
-        <v>4.560399055480957</v>
+        <v>4.560398578643799</v>
       </c>
       <c r="C216" t="n">
-        <v>4.649469266580143</v>
+        <v>4.649468780429767</v>
       </c>
       <c r="D216" t="n">
-        <v>4.480236077851825</v>
+        <v>4.48023560939654</v>
       </c>
       <c r="E216" t="n">
-        <v>4.54258501326112</v>
+        <v>4.542584538286605</v>
       </c>
       <c r="F216" t="n">
         <v>10830000</v>
@@ -4752,16 +4752,16 @@
         <v>44729</v>
       </c>
       <c r="B217" t="n">
-        <v>4.524770736694336</v>
+        <v>4.524770259857178</v>
       </c>
       <c r="C217" t="n">
-        <v>4.524770736694336</v>
+        <v>4.524770259857178</v>
       </c>
       <c r="D217" t="n">
-        <v>4.311002241127791</v>
+        <v>4.311001786818351</v>
       </c>
       <c r="E217" t="n">
-        <v>4.506956695397124</v>
+        <v>4.506956220437275</v>
       </c>
       <c r="F217" t="n">
         <v>10891400</v>
@@ -4772,16 +4772,16 @@
         <v>44732</v>
       </c>
       <c r="B218" t="n">
-        <v>4.524770736694336</v>
+        <v>4.524770259857178</v>
       </c>
       <c r="C218" t="n">
-        <v>4.64946902577482</v>
+        <v>4.649468535796493</v>
       </c>
       <c r="D218" t="n">
-        <v>4.453514571505488</v>
+        <v>4.453514102177569</v>
       </c>
       <c r="E218" t="n">
-        <v>4.524770736694336</v>
+        <v>4.524770259857178</v>
       </c>
       <c r="F218" t="n">
         <v>7841400</v>
@@ -4792,16 +4792,16 @@
         <v>44733</v>
       </c>
       <c r="B219" t="n">
-        <v>4.489142894744873</v>
+        <v>4.489142417907715</v>
       </c>
       <c r="C219" t="n">
-        <v>4.596027148257782</v>
+        <v>4.596026660067369</v>
       </c>
       <c r="D219" t="n">
-        <v>4.44460757675436</v>
+        <v>4.444607104647747</v>
       </c>
       <c r="E219" t="n">
-        <v>4.560399063753479</v>
+        <v>4.560398579347484</v>
       </c>
       <c r="F219" t="n">
         <v>7411800</v>
@@ -4812,16 +4812,16 @@
         <v>44734</v>
       </c>
       <c r="B220" t="n">
-        <v>4.444606781005859</v>
+        <v>4.444607257843018</v>
       </c>
       <c r="C220" t="n">
-        <v>4.53367740103996</v>
+        <v>4.533677887433011</v>
       </c>
       <c r="D220" t="n">
-        <v>4.400071895709002</v>
+        <v>4.40007236776826</v>
       </c>
       <c r="E220" t="n">
-        <v>4.480235283851616</v>
+        <v>4.480235764511158</v>
       </c>
       <c r="F220" t="n">
         <v>8433900</v>
@@ -4852,16 +4852,16 @@
         <v>44736</v>
       </c>
       <c r="B222" t="n">
-        <v>4.257559776306152</v>
+        <v>4.257560253143311</v>
       </c>
       <c r="C222" t="n">
-        <v>4.337722743364323</v>
+        <v>4.337723229179554</v>
       </c>
       <c r="D222" t="n">
-        <v>4.230838504139954</v>
+        <v>4.23083897798439</v>
       </c>
       <c r="E222" t="n">
-        <v>4.319908703493595</v>
+        <v>4.319909187313693</v>
       </c>
       <c r="F222" t="n">
         <v>7941200</v>
@@ -4872,16 +4872,16 @@
         <v>44739</v>
       </c>
       <c r="B223" t="n">
-        <v>4.275374412536621</v>
+        <v>4.275373935699463</v>
       </c>
       <c r="C223" t="n">
-        <v>4.337723348420938</v>
+        <v>4.337722864629935</v>
       </c>
       <c r="D223" t="n">
-        <v>4.239746327825506</v>
+        <v>4.239745854961986</v>
       </c>
       <c r="E223" t="n">
-        <v>4.275374412536621</v>
+        <v>4.275373935699463</v>
       </c>
       <c r="F223" t="n">
         <v>10516900</v>
@@ -4892,16 +4892,16 @@
         <v>44740</v>
       </c>
       <c r="B224" t="n">
-        <v>4.293188571929932</v>
+        <v>4.293187141418457</v>
       </c>
       <c r="C224" t="n">
-        <v>4.471329000341845</v>
+        <v>4.471327510473106</v>
       </c>
       <c r="D224" t="n">
-        <v>4.293188571929932</v>
+        <v>4.293187141418457</v>
       </c>
       <c r="E224" t="n">
-        <v>4.319909423831577</v>
+        <v>4.319907984416584</v>
       </c>
       <c r="F224" t="n">
         <v>8975600</v>
@@ -4912,16 +4912,16 @@
         <v>44741</v>
       </c>
       <c r="B225" t="n">
-        <v>4.275374412536621</v>
+        <v>4.275373935699463</v>
       </c>
       <c r="C225" t="n">
-        <v>4.355537390776496</v>
+        <v>4.355536904998673</v>
       </c>
       <c r="D225" t="n">
-        <v>4.248653136643148</v>
+        <v>4.248652662786244</v>
       </c>
       <c r="E225" t="n">
-        <v>4.311002497247737</v>
+        <v>4.31100201643694</v>
       </c>
       <c r="F225" t="n">
         <v>7179800</v>
@@ -4932,16 +4932,16 @@
         <v>44742</v>
       </c>
       <c r="B226" t="n">
-        <v>4.088326930999756</v>
+        <v>4.088326454162598</v>
       </c>
       <c r="C226" t="n">
-        <v>4.239746509884235</v>
+        <v>4.239746015386434</v>
       </c>
       <c r="D226" t="n">
-        <v>4.052698844758736</v>
+        <v>4.052698372077018</v>
       </c>
       <c r="E226" t="n">
-        <v>4.239746509884235</v>
+        <v>4.239746015386434</v>
       </c>
       <c r="F226" t="n">
         <v>6721700</v>
@@ -5012,16 +5012,16 @@
         <v>44748</v>
       </c>
       <c r="B230" t="n">
-        <v>3.910185575485229</v>
+        <v>3.910185813903809</v>
       </c>
       <c r="C230" t="n">
-        <v>4.0526983269613</v>
+        <v>4.052698574069413</v>
       </c>
       <c r="D230" t="n">
-        <v>3.785487289573874</v>
+        <v>3.785487520389134</v>
       </c>
       <c r="E230" t="n">
-        <v>4.034884286116821</v>
+        <v>4.034884532138745</v>
       </c>
       <c r="F230" t="n">
         <v>11922900</v>
@@ -5072,16 +5072,16 @@
         <v>44753</v>
       </c>
       <c r="B233" t="n">
-        <v>3.705323934555054</v>
+        <v>3.705323696136475</v>
       </c>
       <c r="C233" t="n">
-        <v>3.901278810740315</v>
+        <v>3.901278559713046</v>
       </c>
       <c r="D233" t="n">
-        <v>3.678603085351762</v>
+        <v>3.678602848652532</v>
       </c>
       <c r="E233" t="n">
-        <v>3.892371577859058</v>
+        <v>3.892371327404923</v>
       </c>
       <c r="F233" t="n">
         <v>13261200</v>
@@ -5112,16 +5112,16 @@
         <v>44755</v>
       </c>
       <c r="B235" t="n">
-        <v>3.687510251998901</v>
+        <v>3.687509775161743</v>
       </c>
       <c r="C235" t="n">
-        <v>3.723138337547081</v>
+        <v>3.723137856102805</v>
       </c>
       <c r="D235" t="n">
-        <v>3.47374173870982</v>
+        <v>3.47374128951537</v>
       </c>
       <c r="E235" t="n">
-        <v>3.589533229101546</v>
+        <v>3.589532764933936</v>
       </c>
       <c r="F235" t="n">
         <v>14925600</v>
@@ -5132,16 +5132,16 @@
         <v>44756</v>
       </c>
       <c r="B236" t="n">
-        <v>3.821115493774414</v>
+        <v>3.821115255355835</v>
       </c>
       <c r="C236" t="n">
-        <v>3.856743576605671</v>
+        <v>3.856743335964077</v>
       </c>
       <c r="D236" t="n">
-        <v>3.651881887965819</v>
+        <v>3.651881660106575</v>
       </c>
       <c r="E236" t="n">
-        <v>3.687509970797076</v>
+        <v>3.687509740714817</v>
       </c>
       <c r="F236" t="n">
         <v>9774500</v>
@@ -5172,16 +5172,16 @@
         <v>44760</v>
       </c>
       <c r="B238" t="n">
-        <v>3.830022096633911</v>
+        <v>3.83002233505249</v>
       </c>
       <c r="C238" t="n">
-        <v>4.088325867018225</v>
+        <v>4.088326121516194</v>
       </c>
       <c r="D238" t="n">
-        <v>3.830022096633911</v>
+        <v>3.83002233505249</v>
       </c>
       <c r="E238" t="n">
-        <v>3.990348442993775</v>
+        <v>3.990348691392656</v>
       </c>
       <c r="F238" t="n">
         <v>5011900</v>
@@ -5192,16 +5192,16 @@
         <v>44761</v>
       </c>
       <c r="B239" t="n">
-        <v>3.856743812561035</v>
+        <v>3.856743335723877</v>
       </c>
       <c r="C239" t="n">
-        <v>3.93690721619588</v>
+        <v>3.93690672944754</v>
       </c>
       <c r="D239" t="n">
-        <v>3.830022961162937</v>
+        <v>3.830022487629471</v>
       </c>
       <c r="E239" t="n">
-        <v>3.838929770055544</v>
+        <v>3.838929295420866</v>
       </c>
       <c r="F239" t="n">
         <v>5270100</v>
@@ -5212,16 +5212,16 @@
         <v>44762</v>
       </c>
       <c r="B240" t="n">
-        <v>3.999255657196045</v>
+        <v>3.999255895614624</v>
       </c>
       <c r="C240" t="n">
-        <v>4.025976930004314</v>
+        <v>4.025977170015901</v>
       </c>
       <c r="D240" t="n">
-        <v>3.803301213909561</v>
+        <v>3.803301440646171</v>
       </c>
       <c r="E240" t="n">
-        <v>3.830022486717829</v>
+        <v>3.830022715047448</v>
       </c>
       <c r="F240" t="n">
         <v>11021800</v>
@@ -5232,16 +5232,16 @@
         <v>44763</v>
       </c>
       <c r="B241" t="n">
-        <v>3.963627815246582</v>
+        <v>3.963627338409424</v>
       </c>
       <c r="C241" t="n">
-        <v>4.025977172406417</v>
+        <v>4.025976688068431</v>
       </c>
       <c r="D241" t="n">
-        <v>3.936906965549687</v>
+        <v>3.936906491927133</v>
       </c>
       <c r="E241" t="n">
-        <v>4.025977172406417</v>
+        <v>4.025976688068431</v>
       </c>
       <c r="F241" t="n">
         <v>6658500</v>
@@ -5252,16 +5252,16 @@
         <v>44764</v>
       </c>
       <c r="B242" t="n">
-        <v>3.740952014923096</v>
+        <v>3.740951776504517</v>
       </c>
       <c r="C242" t="n">
-        <v>3.999255822277678</v>
+        <v>3.999255567396865</v>
       </c>
       <c r="D242" t="n">
-        <v>3.740952014923096</v>
+        <v>3.740951776504517</v>
       </c>
       <c r="E242" t="n">
-        <v>3.999255822277678</v>
+        <v>3.999255567396865</v>
       </c>
       <c r="F242" t="n">
         <v>6536400</v>
@@ -5272,16 +5272,16 @@
         <v>44767</v>
       </c>
       <c r="B243" t="n">
-        <v>3.696416616439819</v>
+        <v>3.696416854858398</v>
       </c>
       <c r="C243" t="n">
-        <v>3.785486809363151</v>
+        <v>3.78548705352675</v>
       </c>
       <c r="D243" t="n">
-        <v>3.651881307618063</v>
+        <v>3.651881543164118</v>
       </c>
       <c r="E243" t="n">
-        <v>3.767672770778485</v>
+        <v>3.76767301379308</v>
       </c>
       <c r="F243" t="n">
         <v>10514300</v>
@@ -5292,16 +5292,16 @@
         <v>44768</v>
       </c>
       <c r="B244" t="n">
-        <v>3.714231252670288</v>
+        <v>3.714231491088867</v>
       </c>
       <c r="C244" t="n">
-        <v>3.8122086930113</v>
+        <v>3.812208937719106</v>
       </c>
       <c r="D244" t="n">
-        <v>3.669695936682488</v>
+        <v>3.66969617224232</v>
       </c>
       <c r="E244" t="n">
-        <v>3.705324019584628</v>
+        <v>3.705324257431447</v>
       </c>
       <c r="F244" t="n">
         <v>4594100</v>
@@ -5312,16 +5312,16 @@
         <v>44769</v>
       </c>
       <c r="B245" t="n">
-        <v>3.999255657196045</v>
+        <v>3.999255895614624</v>
       </c>
       <c r="C245" t="n">
-        <v>3.999255657196045</v>
+        <v>3.999255895614624</v>
       </c>
       <c r="D245" t="n">
-        <v>3.723137820204979</v>
+        <v>3.723138042162589</v>
       </c>
       <c r="E245" t="n">
-        <v>3.74095186050375</v>
+        <v>3.740952083523358</v>
       </c>
       <c r="F245" t="n">
         <v>8689000</v>
@@ -5332,16 +5332,16 @@
         <v>44770</v>
       </c>
       <c r="B246" t="n">
-        <v>3.999255657196045</v>
+        <v>3.999255895614624</v>
       </c>
       <c r="C246" t="n">
-        <v>4.070512243111353</v>
+        <v>4.070512485777946</v>
       </c>
       <c r="D246" t="n">
-        <v>3.892371415403418</v>
+        <v>3.892371647450013</v>
       </c>
       <c r="E246" t="n">
-        <v>4.025976930004314</v>
+        <v>4.025977170015901</v>
       </c>
       <c r="F246" t="n">
         <v>3634200</v>
@@ -5352,16 +5352,16 @@
         <v>44771</v>
       </c>
       <c r="B247" t="n">
-        <v>3.927999019622803</v>
+        <v>3.92799973487854</v>
       </c>
       <c r="C247" t="n">
-        <v>4.088325787587928</v>
+        <v>4.088326532037827</v>
       </c>
       <c r="D247" t="n">
-        <v>3.919092212913724</v>
+        <v>3.919092926547607</v>
       </c>
       <c r="E247" t="n">
-        <v>4.025976441743693</v>
+        <v>4.025977174840299</v>
       </c>
       <c r="F247" t="n">
         <v>8694600</v>
@@ -5372,16 +5372,16 @@
         <v>44774</v>
       </c>
       <c r="B248" t="n">
-        <v>3.927999019622803</v>
+        <v>3.92799973487854</v>
       </c>
       <c r="C248" t="n">
-        <v>3.990348365467037</v>
+        <v>3.990349092076068</v>
       </c>
       <c r="D248" t="n">
-        <v>3.874556905207819</v>
+        <v>3.874557610732194</v>
       </c>
       <c r="E248" t="n">
-        <v>3.981441134037787</v>
+        <v>3.981441859024886</v>
       </c>
       <c r="F248" t="n">
         <v>7696400</v>
@@ -5392,16 +5392,16 @@
         <v>44775</v>
       </c>
       <c r="B249" t="n">
-        <v>4.10614013671875</v>
+        <v>4.106140613555908</v>
       </c>
       <c r="C249" t="n">
-        <v>4.115046944102415</v>
+        <v>4.115047421973903</v>
       </c>
       <c r="D249" t="n">
-        <v>3.901278470251996</v>
+        <v>3.901278923299012</v>
       </c>
       <c r="E249" t="n">
-        <v>3.927999317123196</v>
+        <v>3.927999773273247</v>
       </c>
       <c r="F249" t="n">
         <v>12885400</v>
@@ -5432,16 +5432,16 @@
         <v>44777</v>
       </c>
       <c r="B251" t="n">
-        <v>4.498049736022949</v>
+        <v>4.498049259185791</v>
       </c>
       <c r="C251" t="n">
-        <v>4.791981619914148</v>
+        <v>4.791981111917343</v>
       </c>
       <c r="D251" t="n">
-        <v>4.328816137023725</v>
+        <v>4.328815678126979</v>
       </c>
       <c r="E251" t="n">
-        <v>4.328816137023725</v>
+        <v>4.328815678126979</v>
       </c>
       <c r="F251" t="n">
         <v>17206200</v>
@@ -5472,16 +5472,16 @@
         <v>44781</v>
       </c>
       <c r="B253" t="n">
-        <v>4.408978939056396</v>
+        <v>4.408979415893555</v>
       </c>
       <c r="C253" t="n">
-        <v>4.506956371510157</v>
+        <v>4.50695685894371</v>
       </c>
       <c r="D253" t="n">
-        <v>4.355536819005313</v>
+        <v>4.355537290062633</v>
       </c>
       <c r="E253" t="n">
-        <v>4.391164899039369</v>
+        <v>4.391165373949914</v>
       </c>
       <c r="F253" t="n">
         <v>6283600</v>
@@ -5512,16 +5512,16 @@
         <v>44783</v>
       </c>
       <c r="B255" t="n">
-        <v>4.587119579315186</v>
+        <v>4.587120056152344</v>
       </c>
       <c r="C255" t="n">
-        <v>4.702911047125363</v>
+        <v>4.702911535999198</v>
       </c>
       <c r="D255" t="n">
-        <v>4.426792800894878</v>
+        <v>4.426793261065856</v>
       </c>
       <c r="E255" t="n">
-        <v>4.426792800894878</v>
+        <v>4.426793261065856</v>
       </c>
       <c r="F255" t="n">
         <v>9044400</v>
@@ -5552,16 +5552,16 @@
         <v>44785</v>
       </c>
       <c r="B257" t="n">
-        <v>4.694004535675049</v>
+        <v>4.694004058837891</v>
       </c>
       <c r="C257" t="n">
-        <v>4.694004535675049</v>
+        <v>4.694004058837891</v>
       </c>
       <c r="D257" t="n">
-        <v>4.49805007329465</v>
+        <v>4.498049616363389</v>
       </c>
       <c r="E257" t="n">
-        <v>4.578213050090135</v>
+        <v>4.578212585015574</v>
       </c>
       <c r="F257" t="n">
         <v>15222800</v>
@@ -5572,16 +5572,16 @@
         <v>44788</v>
       </c>
       <c r="B258" t="n">
-        <v>4.640562057495117</v>
+        <v>4.640562534332275</v>
       </c>
       <c r="C258" t="n">
-        <v>4.729632260910332</v>
+        <v>4.729632746899826</v>
       </c>
       <c r="D258" t="n">
-        <v>4.560398662061308</v>
+        <v>4.560399130661343</v>
       </c>
       <c r="E258" t="n">
-        <v>4.640562057495117</v>
+        <v>4.640562534332275</v>
       </c>
       <c r="F258" t="n">
         <v>10250500</v>
@@ -5692,16 +5692,16 @@
         <v>44796</v>
       </c>
       <c r="B264" t="n">
-        <v>4.471328258514404</v>
+        <v>4.471328735351562</v>
       </c>
       <c r="C264" t="n">
-        <v>4.471328258514404</v>
+        <v>4.471328735351562</v>
       </c>
       <c r="D264" t="n">
-        <v>4.311001899543048</v>
+        <v>4.311002359282476</v>
       </c>
       <c r="E264" t="n">
-        <v>4.311001899543048</v>
+        <v>4.311002359282476</v>
       </c>
       <c r="F264" t="n">
         <v>6333000</v>
@@ -5812,16 +5812,16 @@
         <v>44804</v>
       </c>
       <c r="B270" t="n">
-        <v>4.311001777648926</v>
+        <v>4.311002731323242</v>
       </c>
       <c r="C270" t="n">
-        <v>4.43570005332301</v>
+        <v>4.43570103458292</v>
       </c>
       <c r="D270" t="n">
-        <v>4.284280506215807</v>
+        <v>4.284281453978878</v>
       </c>
       <c r="E270" t="n">
-        <v>4.382257935176974</v>
+        <v>4.382258904614487</v>
       </c>
       <c r="F270" t="n">
         <v>8375100</v>
@@ -5832,16 +5832,16 @@
         <v>44805</v>
       </c>
       <c r="B271" t="n">
-        <v>4.248652458190918</v>
+        <v>4.24865198135376</v>
       </c>
       <c r="C271" t="n">
-        <v>4.42679285329989</v>
+        <v>4.426792356469578</v>
       </c>
       <c r="D271" t="n">
-        <v>4.177396300147329</v>
+        <v>4.177395831307432</v>
       </c>
       <c r="E271" t="n">
-        <v>4.346629887860955</v>
+        <v>4.346629400027538</v>
       </c>
       <c r="F271" t="n">
         <v>13026600</v>
@@ -5852,16 +5852,16 @@
         <v>44806</v>
       </c>
       <c r="B272" t="n">
-        <v>4.097233295440674</v>
+        <v>4.097233772277832</v>
       </c>
       <c r="C272" t="n">
-        <v>4.355537105009048</v>
+        <v>4.355537611907676</v>
       </c>
       <c r="D272" t="n">
-        <v>4.097233295440674</v>
+        <v>4.097233772277832</v>
       </c>
       <c r="E272" t="n">
-        <v>4.319909022635495</v>
+        <v>4.319909525387717</v>
       </c>
       <c r="F272" t="n">
         <v>69570300</v>
@@ -5872,16 +5872,16 @@
         <v>44809</v>
       </c>
       <c r="B273" t="n">
-        <v>4.115046977996826</v>
+        <v>4.115047931671143</v>
       </c>
       <c r="C273" t="n">
-        <v>4.221931215802409</v>
+        <v>4.221932194247465</v>
       </c>
       <c r="D273" t="n">
-        <v>4.115046977996826</v>
+        <v>4.115047931671143</v>
       </c>
       <c r="E273" t="n">
-        <v>4.123954210174062</v>
+        <v>4.123955165912656</v>
       </c>
       <c r="F273" t="n">
         <v>7604300</v>
@@ -5892,16 +5892,16 @@
         <v>44810</v>
       </c>
       <c r="B274" t="n">
-        <v>3.954721450805664</v>
+        <v>3.954720973968506</v>
       </c>
       <c r="C274" t="n">
-        <v>4.177397205301117</v>
+        <v>4.177396701615019</v>
       </c>
       <c r="D274" t="n">
-        <v>3.945814216760104</v>
+        <v>3.945813740996928</v>
       </c>
       <c r="E274" t="n">
-        <v>4.141769118559468</v>
+        <v>4.141768619169197</v>
       </c>
       <c r="F274" t="n">
         <v>14609100</v>
@@ -5912,16 +5912,16 @@
         <v>44812</v>
       </c>
       <c r="B275" t="n">
-        <v>3.910185575485229</v>
+        <v>3.910185813903809</v>
       </c>
       <c r="C275" t="n">
-        <v>4.008163012489984</v>
+        <v>4.008163256882613</v>
       </c>
       <c r="D275" t="n">
-        <v>3.856743452951791</v>
+        <v>3.856743688111805</v>
       </c>
       <c r="E275" t="n">
-        <v>3.990348971645505</v>
+        <v>3.990349214951944</v>
       </c>
       <c r="F275" t="n">
         <v>9864000</v>
@@ -5932,16 +5932,16 @@
         <v>44813</v>
       </c>
       <c r="B276" t="n">
-        <v>3.910185575485229</v>
+        <v>3.910185813903809</v>
       </c>
       <c r="C276" t="n">
-        <v>4.043791094178943</v>
+        <v>4.043791340743948</v>
       </c>
       <c r="D276" t="n">
-        <v>3.883464726578628</v>
+        <v>3.883464963367938</v>
       </c>
       <c r="E276" t="n">
-        <v>3.945813657174188</v>
+        <v>3.945813897765144</v>
       </c>
       <c r="F276" t="n">
         <v>15548300</v>
@@ -5952,16 +5952,16 @@
         <v>44816</v>
       </c>
       <c r="B277" t="n">
-        <v>3.856743812561035</v>
+        <v>3.856743335723877</v>
       </c>
       <c r="C277" t="n">
-        <v>3.990349343712352</v>
+        <v>3.990348850356574</v>
       </c>
       <c r="D277" t="n">
-        <v>3.838929770055544</v>
+        <v>3.838929295420866</v>
       </c>
       <c r="E277" t="n">
-        <v>3.95472125870137</v>
+        <v>3.954720769750552</v>
       </c>
       <c r="F277" t="n">
         <v>15738600</v>
@@ -5972,16 +5972,16 @@
         <v>44817</v>
       </c>
       <c r="B278" t="n">
-        <v>3.696416616439819</v>
+        <v>3.696416854858398</v>
       </c>
       <c r="C278" t="n">
-        <v>3.883464233938907</v>
+        <v>3.883464484422043</v>
       </c>
       <c r="D278" t="n">
-        <v>3.678602577855153</v>
+        <v>3.678602815124728</v>
       </c>
       <c r="E278" t="n">
-        <v>3.874557002286483</v>
+        <v>3.874557252195103</v>
       </c>
       <c r="F278" t="n">
         <v>21443000</v>
@@ -5992,16 +5992,16 @@
         <v>44818</v>
       </c>
       <c r="B279" t="n">
-        <v>3.740952014923096</v>
+        <v>3.740951776504517</v>
       </c>
       <c r="C279" t="n">
-        <v>3.821115411936669</v>
+        <v>3.821115168409112</v>
       </c>
       <c r="D279" t="n">
-        <v>3.678603083663863</v>
+        <v>3.67860284921891</v>
       </c>
       <c r="E279" t="n">
-        <v>3.705323932854894</v>
+        <v>3.705323696706966</v>
       </c>
       <c r="F279" t="n">
         <v>13539100</v>
@@ -6012,16 +6012,16 @@
         <v>44819</v>
       </c>
       <c r="B280" t="n">
-        <v>3.749858856201172</v>
+        <v>3.749859571456909</v>
       </c>
       <c r="C280" t="n">
-        <v>3.758765663427961</v>
+        <v>3.758766380382601</v>
       </c>
       <c r="D280" t="n">
-        <v>3.63406738921154</v>
+        <v>3.634068082380977</v>
       </c>
       <c r="E280" t="n">
-        <v>3.740951624254187</v>
+        <v>3.740952337810941</v>
       </c>
       <c r="F280" t="n">
         <v>12717200</v>
@@ -6032,16 +6032,16 @@
         <v>44820</v>
       </c>
       <c r="B281" t="n">
-        <v>3.821115493774414</v>
+        <v>3.821115255355835</v>
       </c>
       <c r="C281" t="n">
-        <v>3.892371659436928</v>
+        <v>3.892371416572319</v>
       </c>
       <c r="D281" t="n">
-        <v>3.660789121033758</v>
+        <v>3.660788892618747</v>
       </c>
       <c r="E281" t="n">
-        <v>3.696417203865015</v>
+        <v>3.696416973226988</v>
       </c>
       <c r="F281" t="n">
         <v>19813000</v>
@@ -6052,16 +6052,16 @@
         <v>44823</v>
       </c>
       <c r="B282" t="n">
-        <v>3.990348815917969</v>
+        <v>3.990349292755127</v>
       </c>
       <c r="C282" t="n">
-        <v>4.008162856067236</v>
+        <v>4.00816333503313</v>
       </c>
       <c r="D282" t="n">
-        <v>3.794394374276022</v>
+        <v>3.794394827697093</v>
       </c>
       <c r="E282" t="n">
-        <v>3.830022454574558</v>
+        <v>3.830022912253099</v>
       </c>
       <c r="F282" t="n">
         <v>8945000</v>
@@ -6072,16 +6072,16 @@
         <v>44824</v>
       </c>
       <c r="B283" t="n">
-        <v>3.963627815246582</v>
+        <v>3.963627338409424</v>
       </c>
       <c r="C283" t="n">
-        <v>4.132861420634493</v>
+        <v>4.132860923437988</v>
       </c>
       <c r="D283" t="n">
-        <v>3.919092924178341</v>
+        <v>3.919092452698874</v>
       </c>
       <c r="E283" t="n">
-        <v>3.990349089663725</v>
+        <v>3.990348609611912</v>
       </c>
       <c r="F283" t="n">
         <v>10696200</v>
@@ -6092,16 +6092,16 @@
         <v>44825</v>
       </c>
       <c r="B284" t="n">
-        <v>3.883464813232422</v>
+        <v>3.883465051651001</v>
       </c>
       <c r="C284" t="n">
-        <v>4.034884376149319</v>
+        <v>4.034884623864039</v>
       </c>
       <c r="D284" t="n">
-        <v>3.830022689506502</v>
+        <v>3.830022924644094</v>
       </c>
       <c r="E284" t="n">
-        <v>3.972535019442289</v>
+        <v>3.972535263329179</v>
       </c>
       <c r="F284" t="n">
         <v>18275700</v>
@@ -6132,16 +6132,16 @@
         <v>44827</v>
       </c>
       <c r="B286" t="n">
-        <v>3.910185575485229</v>
+        <v>3.910185813903809</v>
       </c>
       <c r="C286" t="n">
-        <v>3.990348971645505</v>
+        <v>3.990349214951944</v>
       </c>
       <c r="D286" t="n">
-        <v>3.847836644889669</v>
+        <v>3.847836879506602</v>
       </c>
       <c r="E286" t="n">
-        <v>3.963627698018668</v>
+        <v>3.963627939695812</v>
       </c>
       <c r="F286" t="n">
         <v>14173200</v>
@@ -6152,16 +6152,16 @@
         <v>44830</v>
       </c>
       <c r="B287" t="n">
-        <v>3.821115493774414</v>
+        <v>3.821115255355835</v>
       </c>
       <c r="C287" t="n">
-        <v>3.936906975336123</v>
+        <v>3.936906729692732</v>
       </c>
       <c r="D287" t="n">
-        <v>3.794394644011096</v>
+        <v>3.794394407259765</v>
       </c>
       <c r="E287" t="n">
-        <v>3.901278892504866</v>
+        <v>3.901278649084491</v>
       </c>
       <c r="F287" t="n">
         <v>9718800</v>
@@ -6172,16 +6172,16 @@
         <v>44831</v>
       </c>
       <c r="B288" t="n">
-        <v>3.732045412063599</v>
+        <v>3.732044696807861</v>
       </c>
       <c r="C288" t="n">
-        <v>3.91909306557115</v>
+        <v>3.919092314467266</v>
       </c>
       <c r="D288" t="n">
-        <v>3.732045412063599</v>
+        <v>3.732044696807861</v>
       </c>
       <c r="E288" t="n">
-        <v>3.838929664147838</v>
+        <v>3.838928928407469</v>
       </c>
       <c r="F288" t="n">
         <v>11052300</v>
@@ -6192,16 +6192,16 @@
         <v>44832</v>
       </c>
       <c r="B289" t="n">
-        <v>3.687510251998901</v>
+        <v>3.687509775161743</v>
       </c>
       <c r="C289" t="n">
-        <v>3.767673656842447</v>
+        <v>3.767673169639246</v>
       </c>
       <c r="D289" t="n">
-        <v>3.687510251998901</v>
+        <v>3.687509775161743</v>
       </c>
       <c r="E289" t="n">
-        <v>3.749859614068357</v>
+        <v>3.749859129168715</v>
       </c>
       <c r="F289" t="n">
         <v>11148900</v>
@@ -6212,16 +6212,16 @@
         <v>44833</v>
       </c>
       <c r="B290" t="n">
-        <v>3.696416616439819</v>
+        <v>3.696416854858398</v>
       </c>
       <c r="C290" t="n">
-        <v>3.714230655024486</v>
+        <v>3.714230894592069</v>
       </c>
       <c r="D290" t="n">
-        <v>3.61625323044873</v>
+        <v>3.616253463696776</v>
       </c>
       <c r="E290" t="n">
-        <v>3.660788539270487</v>
+        <v>3.660788775391057</v>
       </c>
       <c r="F290" t="n">
         <v>12380300</v>
@@ -6232,16 +6232,16 @@
         <v>44834</v>
       </c>
       <c r="B291" t="n">
-        <v>3.732045412063599</v>
+        <v>3.732044696807861</v>
       </c>
       <c r="C291" t="n">
-        <v>3.79439477147287</v>
+        <v>3.794394044267724</v>
       </c>
       <c r="D291" t="n">
-        <v>3.651882010640287</v>
+        <v>3.651881310748065</v>
       </c>
       <c r="E291" t="n">
-        <v>3.660789244007439</v>
+        <v>3.660788542408123</v>
       </c>
       <c r="F291" t="n">
         <v>11827700</v>
@@ -6252,16 +6252,16 @@
         <v>44837</v>
       </c>
       <c r="B292" t="n">
-        <v>3.939894914627075</v>
+        <v>3.939895391464233</v>
       </c>
       <c r="C292" t="n">
-        <v>3.939894914627075</v>
+        <v>3.939895391464233</v>
       </c>
       <c r="D292" t="n">
-        <v>3.796299788355527</v>
+        <v>3.79630024781367</v>
       </c>
       <c r="E292" t="n">
-        <v>3.814249179139471</v>
+        <v>3.814249640769991</v>
       </c>
       <c r="F292" t="n">
         <v>14167700</v>
@@ -6272,16 +6272,16 @@
         <v>44838</v>
       </c>
       <c r="B293" t="n">
-        <v>3.930920124053955</v>
+        <v>3.930919647216797</v>
       </c>
       <c r="C293" t="n">
-        <v>4.05656584965991</v>
+        <v>4.056565357581396</v>
       </c>
       <c r="D293" t="n">
-        <v>3.895021345309396</v>
+        <v>3.895020872826911</v>
       </c>
       <c r="E293" t="n">
-        <v>3.975793383511054</v>
+        <v>3.97579290123058</v>
       </c>
       <c r="F293" t="n">
         <v>11413300</v>
@@ -6312,16 +6312,16 @@
         <v>44840</v>
       </c>
       <c r="B295" t="n">
-        <v>4.0027174949646</v>
+        <v>4.002717018127441</v>
       </c>
       <c r="C295" t="n">
-        <v>4.029641363794418</v>
+        <v>4.029640883749863</v>
       </c>
       <c r="D295" t="n">
-        <v>3.975793198187602</v>
+        <v>3.975792724557891</v>
       </c>
       <c r="E295" t="n">
-        <v>3.993742586723207</v>
+        <v>3.993742110955215</v>
       </c>
       <c r="F295" t="n">
         <v>5975200</v>
@@ -6332,16 +6332,16 @@
         <v>44841</v>
       </c>
       <c r="B296" t="n">
-        <v>3.760401010513306</v>
+        <v>3.760400533676147</v>
       </c>
       <c r="C296" t="n">
-        <v>4.002718000310238</v>
+        <v>4.002717492746105</v>
       </c>
       <c r="D296" t="n">
-        <v>3.715527319535371</v>
+        <v>3.715526848388416</v>
       </c>
       <c r="E296" t="n">
-        <v>3.984768609508511</v>
+        <v>3.984768104220449</v>
       </c>
       <c r="F296" t="n">
         <v>16354500</v>
@@ -6372,16 +6372,16 @@
         <v>44845</v>
       </c>
       <c r="B298" t="n">
-        <v>3.903995990753174</v>
+        <v>3.903995752334595</v>
       </c>
       <c r="C298" t="n">
-        <v>3.948869680050941</v>
+        <v>3.948869438891908</v>
       </c>
       <c r="D298" t="n">
-        <v>3.63475513880822</v>
+        <v>3.634754916832287</v>
       </c>
       <c r="E298" t="n">
-        <v>3.661679010029107</v>
+        <v>3.661678786408922</v>
       </c>
       <c r="F298" t="n">
         <v>30833900</v>
@@ -6412,16 +6412,16 @@
         <v>44848</v>
       </c>
       <c r="B300" t="n">
-        <v>3.688603401184082</v>
+        <v>3.688603162765503</v>
       </c>
       <c r="C300" t="n">
-        <v>3.832198525802385</v>
+        <v>3.832198278102312</v>
       </c>
       <c r="D300" t="n">
-        <v>3.679628491921824</v>
+        <v>3.679628254083352</v>
       </c>
       <c r="E300" t="n">
-        <v>3.823224044487355</v>
+        <v>3.823223797367362</v>
       </c>
       <c r="F300" t="n">
         <v>10535000</v>
@@ -6432,16 +6432,16 @@
         <v>44851</v>
       </c>
       <c r="B301" t="n">
-        <v>3.679628133773804</v>
+        <v>3.679628372192383</v>
       </c>
       <c r="C301" t="n">
-        <v>3.769375077924933</v>
+        <v>3.769375322158595</v>
       </c>
       <c r="D301" t="n">
-        <v>3.670653653332284</v>
+        <v>3.670653891169369</v>
       </c>
       <c r="E301" t="n">
-        <v>3.724501819822962</v>
+        <v>3.724502061149096</v>
       </c>
       <c r="F301" t="n">
         <v>8129100</v>
@@ -6452,16 +6452,16 @@
         <v>44852</v>
       </c>
       <c r="B302" t="n">
-        <v>3.715527296066284</v>
+        <v>3.715527057647705</v>
       </c>
       <c r="C302" t="n">
-        <v>3.787324858819684</v>
+        <v>3.787324615793987</v>
       </c>
       <c r="D302" t="n">
-        <v>3.661679124001235</v>
+        <v>3.661678889037994</v>
       </c>
       <c r="E302" t="n">
-        <v>3.724502205384074</v>
+        <v>3.724501966389592</v>
       </c>
       <c r="F302" t="n">
         <v>13196400</v>
@@ -6492,16 +6492,16 @@
         <v>44854</v>
       </c>
       <c r="B304" t="n">
-        <v>3.769375324249268</v>
+        <v>3.769374847412109</v>
       </c>
       <c r="C304" t="n">
-        <v>3.796299623227672</v>
+        <v>3.796299142984509</v>
       </c>
       <c r="D304" t="n">
-        <v>3.706552673211682</v>
+        <v>3.706552204321775</v>
       </c>
       <c r="E304" t="n">
-        <v>3.760400843221276</v>
+        <v>3.760400367519416</v>
       </c>
       <c r="F304" t="n">
         <v>13428400</v>
@@ -6512,16 +6512,16 @@
         <v>44855</v>
       </c>
       <c r="B305" t="n">
-        <v>3.832197904586792</v>
+        <v>3.83219838142395</v>
       </c>
       <c r="C305" t="n">
-        <v>3.859122200061794</v>
+        <v>3.85912268024912</v>
       </c>
       <c r="D305" t="n">
-        <v>3.733476058441326</v>
+        <v>3.733476522994609</v>
       </c>
       <c r="E305" t="n">
-        <v>3.760400353916329</v>
+        <v>3.760400821819779</v>
       </c>
       <c r="F305" t="n">
         <v>14614900</v>
@@ -6552,16 +6552,16 @@
         <v>44859</v>
       </c>
       <c r="B307" t="n">
-        <v>3.670654058456421</v>
+        <v>3.670653820037842</v>
       </c>
       <c r="C307" t="n">
-        <v>3.769375493944795</v>
+        <v>3.769375249114001</v>
       </c>
       <c r="D307" t="n">
-        <v>3.661679149077169</v>
+        <v>3.661678911241534</v>
       </c>
       <c r="E307" t="n">
-        <v>3.706552840078963</v>
+        <v>3.706552599328664</v>
       </c>
       <c r="F307" t="n">
         <v>12220200</v>
@@ -6612,16 +6612,16 @@
         <v>44862</v>
       </c>
       <c r="B310" t="n">
-        <v>3.724501609802246</v>
+        <v>3.724502086639404</v>
       </c>
       <c r="C310" t="n">
-        <v>3.733476089737704</v>
+        <v>3.73347656772384</v>
       </c>
       <c r="D310" t="n">
-        <v>3.64372915064731</v>
+        <v>3.643729617143404</v>
       </c>
       <c r="E310" t="n">
-        <v>3.688602834166089</v>
+        <v>3.68860330640723</v>
       </c>
       <c r="F310" t="n">
         <v>9985100</v>
@@ -6632,16 +6632,16 @@
         <v>44865</v>
       </c>
       <c r="B311" t="n">
-        <v>3.85014796257019</v>
+        <v>3.850147485733032</v>
       </c>
       <c r="C311" t="n">
-        <v>3.868097353362819</v>
+        <v>3.868096874302645</v>
       </c>
       <c r="D311" t="n">
-        <v>3.545008105121898</v>
+        <v>3.54500766607602</v>
       </c>
       <c r="E311" t="n">
-        <v>3.589881582103468</v>
+        <v>3.589881137500053</v>
       </c>
       <c r="F311" t="n">
         <v>19491700</v>
@@ -6652,16 +6652,16 @@
         <v>44866</v>
       </c>
       <c r="B312" t="n">
-        <v>4.047591209411621</v>
+        <v>4.047591686248779</v>
       </c>
       <c r="C312" t="n">
-        <v>4.092464467100041</v>
+        <v>4.092464949223611</v>
       </c>
       <c r="D312" t="n">
-        <v>3.814248728821982</v>
+        <v>3.814249178169614</v>
       </c>
       <c r="E312" t="n">
-        <v>3.868096894816395</v>
+        <v>3.868097350507752</v>
       </c>
       <c r="F312" t="n">
         <v>23695600</v>
@@ -6672,16 +6672,16 @@
         <v>44868</v>
       </c>
       <c r="B313" t="n">
-        <v>4.218111038208008</v>
+        <v>4.21811056137085</v>
       </c>
       <c r="C313" t="n">
-        <v>4.25400982277552</v>
+        <v>4.254009341880177</v>
       </c>
       <c r="D313" t="n">
-        <v>3.895021977100405</v>
+        <v>3.895021536786911</v>
       </c>
       <c r="E313" t="n">
-        <v>3.975794028403671</v>
+        <v>3.975793578959285</v>
       </c>
       <c r="F313" t="n">
         <v>15015300</v>
@@ -6692,16 +6692,16 @@
         <v>44869</v>
       </c>
       <c r="B314" t="n">
-        <v>4.236059665679932</v>
+        <v>4.236059188842773</v>
       </c>
       <c r="C314" t="n">
-        <v>4.343756427885306</v>
+        <v>4.343755938925132</v>
       </c>
       <c r="D314" t="n">
-        <v>4.15528762895989</v>
+        <v>4.155287161214933</v>
       </c>
       <c r="E314" t="n">
-        <v>4.218110276636901</v>
+        <v>4.218109801820237</v>
       </c>
       <c r="F314" t="n">
         <v>12500600</v>
@@ -6732,16 +6732,16 @@
         <v>44873</v>
       </c>
       <c r="B316" t="n">
-        <v>4.083490371704102</v>
+        <v>4.083489894866943</v>
       </c>
       <c r="C316" t="n">
-        <v>4.110414243265911</v>
+        <v>4.110413763284799</v>
       </c>
       <c r="D316" t="n">
-        <v>3.966819120410333</v>
+        <v>3.966818657197105</v>
       </c>
       <c r="E316" t="n">
-        <v>4.01169238232909</v>
+        <v>4.011691913875923</v>
       </c>
       <c r="F316" t="n">
         <v>15444300</v>
@@ -6772,16 +6772,16 @@
         <v>44875</v>
       </c>
       <c r="B318" t="n">
-        <v>3.688603401184082</v>
+        <v>3.688603162765503</v>
       </c>
       <c r="C318" t="n">
-        <v>3.975793650420687</v>
+        <v>3.975793393439122</v>
       </c>
       <c r="D318" t="n">
-        <v>3.670654010606794</v>
+        <v>3.670653773348401</v>
       </c>
       <c r="E318" t="n">
-        <v>3.921945478688824</v>
+        <v>3.921945225187819</v>
       </c>
       <c r="F318" t="n">
         <v>22566600</v>
@@ -6792,16 +6792,16 @@
         <v>44876</v>
       </c>
       <c r="B319" t="n">
-        <v>3.715527296066284</v>
+        <v>3.715527057647705</v>
       </c>
       <c r="C319" t="n">
-        <v>3.751426077442984</v>
+        <v>3.751425836720846</v>
       </c>
       <c r="D319" t="n">
-        <v>3.437311526423245</v>
+        <v>3.437311305857262</v>
       </c>
       <c r="E319" t="n">
-        <v>3.634755251942325</v>
+        <v>3.634755018706739</v>
       </c>
       <c r="F319" t="n">
         <v>24235200</v>
@@ -6812,16 +6812,16 @@
         <v>44879</v>
       </c>
       <c r="B320" t="n">
-        <v>3.697577476501465</v>
+        <v>3.697577714920044</v>
       </c>
       <c r="C320" t="n">
-        <v>3.796299327810405</v>
+        <v>3.796299572594537</v>
       </c>
       <c r="D320" t="n">
-        <v>3.643729310682183</v>
+        <v>3.64372954562865</v>
       </c>
       <c r="E320" t="n">
-        <v>3.760400550597551</v>
+        <v>3.760400793066941</v>
       </c>
       <c r="F320" t="n">
         <v>10873300</v>
@@ -6832,16 +6832,16 @@
         <v>44881</v>
       </c>
       <c r="B321" t="n">
-        <v>3.616805553436279</v>
+        <v>3.616805791854858</v>
       </c>
       <c r="C321" t="n">
-        <v>3.760400666722041</v>
+        <v>3.760400914606361</v>
       </c>
       <c r="D321" t="n">
-        <v>3.553982477400161</v>
+        <v>3.553982711677465</v>
       </c>
       <c r="E321" t="n">
-        <v>3.697577590685923</v>
+        <v>3.697577834428968</v>
       </c>
       <c r="F321" t="n">
         <v>16148800</v>
@@ -6892,16 +6892,16 @@
         <v>44886</v>
       </c>
       <c r="B324" t="n">
-        <v>3.616805553436279</v>
+        <v>3.616805791854858</v>
       </c>
       <c r="C324" t="n">
-        <v>3.733476369007364</v>
+        <v>3.733476615116843</v>
       </c>
       <c r="D324" t="n">
-        <v>3.545007782819801</v>
+        <v>3.545008016505496</v>
       </c>
       <c r="E324" t="n">
-        <v>3.679628201525203</v>
+        <v>3.67962844408503</v>
       </c>
       <c r="F324" t="n">
         <v>11314600</v>
@@ -6912,16 +6912,16 @@
         <v>44887</v>
       </c>
       <c r="B325" t="n">
-        <v>3.616805553436279</v>
+        <v>3.616805791854858</v>
       </c>
       <c r="C325" t="n">
-        <v>3.661678812364483</v>
+        <v>3.661679053741092</v>
       </c>
       <c r="D325" t="n">
-        <v>3.562957171980521</v>
+        <v>3.562957406849434</v>
       </c>
       <c r="E325" t="n">
-        <v>3.616805553436279</v>
+        <v>3.616805791854858</v>
       </c>
       <c r="F325" t="n">
         <v>10439300</v>
@@ -6932,16 +6932,16 @@
         <v>44888</v>
       </c>
       <c r="B326" t="n">
-        <v>3.589881420135498</v>
+        <v>3.589881181716919</v>
       </c>
       <c r="C326" t="n">
-        <v>3.643729590083865</v>
+        <v>3.643729348089011</v>
       </c>
       <c r="D326" t="n">
-        <v>3.545007945178526</v>
+        <v>3.545007709740176</v>
       </c>
       <c r="E326" t="n">
-        <v>3.571932030152709</v>
+        <v>3.571931792926222</v>
       </c>
       <c r="F326" t="n">
         <v>6531500</v>
@@ -6952,16 +6952,16 @@
         <v>44889</v>
       </c>
       <c r="B327" t="n">
-        <v>3.724501609802246</v>
+        <v>3.724502086639404</v>
       </c>
       <c r="C327" t="n">
-        <v>3.742450997620325</v>
+        <v>3.742451476755492</v>
       </c>
       <c r="D327" t="n">
-        <v>3.598855895075694</v>
+        <v>3.598856355826795</v>
       </c>
       <c r="E327" t="n">
-        <v>3.634754670711852</v>
+        <v>3.634755136058969</v>
       </c>
       <c r="F327" t="n">
         <v>5511600</v>
@@ -6972,16 +6972,16 @@
         <v>44890</v>
       </c>
       <c r="B328" t="n">
-        <v>3.634755373001099</v>
+        <v>3.63475513458252</v>
       </c>
       <c r="C328" t="n">
-        <v>3.760401112004292</v>
+        <v>3.760400865344091</v>
       </c>
       <c r="D328" t="n">
-        <v>3.580906985168965</v>
+        <v>3.580906750282523</v>
       </c>
       <c r="E328" t="n">
-        <v>3.733476811101414</v>
+        <v>3.733476566207289</v>
       </c>
       <c r="F328" t="n">
         <v>8739900</v>
@@ -7012,16 +7012,16 @@
         <v>44894</v>
       </c>
       <c r="B330" t="n">
-        <v>3.589881420135498</v>
+        <v>3.589881181716919</v>
       </c>
       <c r="C330" t="n">
-        <v>3.715527150015021</v>
+        <v>3.715526903251799</v>
       </c>
       <c r="D330" t="n">
-        <v>3.518083860204342</v>
+        <v>3.51808362655413</v>
       </c>
       <c r="E330" t="n">
-        <v>3.616805719083288</v>
+        <v>3.616805478876557</v>
       </c>
       <c r="F330" t="n">
         <v>13237500</v>
@@ -7032,16 +7032,16 @@
         <v>44895</v>
       </c>
       <c r="B331" t="n">
-        <v>3.634755373001099</v>
+        <v>3.63475513458252</v>
       </c>
       <c r="C331" t="n">
-        <v>3.661679245956732</v>
+        <v>3.661679005772105</v>
       </c>
       <c r="D331" t="n">
-        <v>3.518084115667368</v>
+        <v>3.518083884901738</v>
       </c>
       <c r="E331" t="n">
-        <v>3.57193228952588</v>
+        <v>3.571932055228125</v>
       </c>
       <c r="F331" t="n">
         <v>16877200</v>
@@ -7052,16 +7052,16 @@
         <v>44896</v>
       </c>
       <c r="B332" t="n">
-        <v>3.446286201477051</v>
+        <v>3.446285963058472</v>
       </c>
       <c r="C332" t="n">
-        <v>3.589881540112033</v>
+        <v>3.589881291759341</v>
       </c>
       <c r="D332" t="n">
-        <v>3.428336810894379</v>
+        <v>3.428336573717563</v>
       </c>
       <c r="E332" t="n">
-        <v>3.589881540112033</v>
+        <v>3.589881291759341</v>
       </c>
       <c r="F332" t="n">
         <v>22625600</v>
@@ -7072,16 +7072,16 @@
         <v>44897</v>
       </c>
       <c r="B333" t="n">
-        <v>3.500134706497192</v>
+        <v>3.500134468078613</v>
       </c>
       <c r="C333" t="n">
-        <v>3.625780444858396</v>
+        <v>3.62578019788121</v>
       </c>
       <c r="D333" t="n">
-        <v>3.455261014537427</v>
+        <v>3.455260779175508</v>
       </c>
       <c r="E333" t="n">
-        <v>3.473210405731884</v>
+        <v>3.473210169147307</v>
       </c>
       <c r="F333" t="n">
         <v>16610700</v>
@@ -7092,16 +7092,16 @@
         <v>44900</v>
       </c>
       <c r="B334" t="n">
-        <v>3.347564220428467</v>
+        <v>3.347563982009888</v>
       </c>
       <c r="C334" t="n">
-        <v>3.545007711179917</v>
+        <v>3.545007458699114</v>
       </c>
       <c r="D334" t="n">
-        <v>3.32961483163048</v>
+        <v>3.329614594490283</v>
       </c>
       <c r="E334" t="n">
-        <v>3.545007711179917</v>
+        <v>3.545007458699114</v>
       </c>
       <c r="F334" t="n">
         <v>14607600</v>
@@ -7172,16 +7172,16 @@
         <v>44904</v>
       </c>
       <c r="B338" t="n">
-        <v>3.082777976989746</v>
+        <v>3.082778215408325</v>
       </c>
       <c r="C338" t="n">
-        <v>3.119587451611511</v>
+        <v>3.119587692876894</v>
       </c>
       <c r="D338" t="n">
-        <v>2.990754838936502</v>
+        <v>2.990755070238115</v>
       </c>
       <c r="E338" t="n">
-        <v>3.101182604600395</v>
+        <v>3.101182844442367</v>
       </c>
       <c r="F338" t="n">
         <v>12963000</v>
@@ -7192,16 +7192,16 @@
         <v>44907</v>
       </c>
       <c r="B339" t="n">
-        <v>3.036766290664673</v>
+        <v>3.036766529083252</v>
       </c>
       <c r="C339" t="n">
-        <v>3.119587331114006</v>
+        <v>3.119587576034921</v>
       </c>
       <c r="D339" t="n">
-        <v>2.972350096515548</v>
+        <v>2.972350329876769</v>
       </c>
       <c r="E339" t="n">
-        <v>3.082777857914047</v>
+        <v>3.082778099945025</v>
       </c>
       <c r="F339" t="n">
         <v>24013800</v>
@@ -7252,16 +7252,16 @@
         <v>44910</v>
       </c>
       <c r="B342" t="n">
-        <v>3.036766290664673</v>
+        <v>3.036766529083252</v>
       </c>
       <c r="C342" t="n">
-        <v>3.137991958013755</v>
+        <v>3.13799220437963</v>
       </c>
       <c r="D342" t="n">
-        <v>3.009159350315048</v>
+        <v>3.009159586566188</v>
       </c>
       <c r="E342" t="n">
-        <v>3.055170917564423</v>
+        <v>3.055171157427961</v>
       </c>
       <c r="F342" t="n">
         <v>8858500</v>
@@ -7372,16 +7372,16 @@
         <v>44918</v>
       </c>
       <c r="B348" t="n">
-        <v>3.414061784744263</v>
+        <v>3.414062023162842</v>
       </c>
       <c r="C348" t="n">
-        <v>3.441668726742138</v>
+        <v>3.441668967088628</v>
       </c>
       <c r="D348" t="n">
-        <v>3.34044327274993</v>
+        <v>3.340443506027412</v>
       </c>
       <c r="E348" t="n">
-        <v>3.358847900748513</v>
+        <v>3.35884813531127</v>
       </c>
       <c r="F348" t="n">
         <v>4486400</v>
@@ -7452,16 +7452,16 @@
         <v>44924</v>
       </c>
       <c r="B352" t="n">
-        <v>3.441668510437012</v>
+        <v>3.441668748855591</v>
       </c>
       <c r="C352" t="n">
-        <v>3.598108057993386</v>
+        <v>3.598108307249177</v>
       </c>
       <c r="D352" t="n">
-        <v>3.404859256753267</v>
+        <v>3.404859492621917</v>
       </c>
       <c r="E352" t="n">
-        <v>3.524489331225437</v>
+        <v>3.524489575381356</v>
       </c>
       <c r="F352" t="n">
         <v>7177700</v>
@@ -7532,16 +7532,16 @@
         <v>44931</v>
       </c>
       <c r="B356" t="n">
-        <v>2.972350358963013</v>
+        <v>2.972350120544434</v>
       </c>
       <c r="C356" t="n">
-        <v>3.11958760656197</v>
+        <v>3.119587356333176</v>
       </c>
       <c r="D356" t="n">
-        <v>2.935541101913393</v>
+        <v>2.935540866447363</v>
       </c>
       <c r="E356" t="n">
-        <v>3.082778130111872</v>
+        <v>3.082777882835645</v>
       </c>
       <c r="F356" t="n">
         <v>35445300</v>
@@ -7572,16 +7572,16 @@
         <v>44935</v>
       </c>
       <c r="B358" t="n">
-        <v>2.972350358963013</v>
+        <v>2.972350120544434</v>
       </c>
       <c r="C358" t="n">
-        <v>3.027564244537442</v>
+        <v>3.027564001690039</v>
       </c>
       <c r="D358" t="n">
-        <v>2.907934159126178</v>
+        <v>2.90793392587456</v>
       </c>
       <c r="E358" t="n">
-        <v>2.944743416175798</v>
+        <v>2.944743179971631</v>
       </c>
       <c r="F358" t="n">
         <v>15633700</v>
@@ -7592,16 +7592,16 @@
         <v>44936</v>
       </c>
       <c r="B359" t="n">
-        <v>3.082777976989746</v>
+        <v>3.082778215408325</v>
       </c>
       <c r="C359" t="n">
-        <v>3.082777976989746</v>
+        <v>3.082778215408325</v>
       </c>
       <c r="D359" t="n">
-        <v>2.953945583715205</v>
+        <v>2.953945812170032</v>
       </c>
       <c r="E359" t="n">
-        <v>2.963147897520529</v>
+        <v>2.963148126687053</v>
       </c>
       <c r="F359" t="n">
         <v>12594800</v>
@@ -7632,16 +7632,16 @@
         <v>44938</v>
       </c>
       <c r="B361" t="n">
-        <v>3.211610794067383</v>
+        <v>3.211610555648804</v>
       </c>
       <c r="C361" t="n">
-        <v>3.349645729332935</v>
+        <v>3.349645480667133</v>
       </c>
       <c r="D361" t="n">
-        <v>3.165599222112359</v>
+        <v>3.165598987109516</v>
       </c>
       <c r="E361" t="n">
-        <v>3.266824680413411</v>
+        <v>3.266824437895949</v>
       </c>
       <c r="F361" t="n">
         <v>13176700</v>
@@ -7672,16 +7672,16 @@
         <v>44942</v>
       </c>
       <c r="B363" t="n">
-        <v>3.036766290664673</v>
+        <v>3.036766529083252</v>
       </c>
       <c r="C363" t="n">
-        <v>3.082777857914047</v>
+        <v>3.082778099945025</v>
       </c>
       <c r="D363" t="n">
-        <v>3.009159350315048</v>
+        <v>3.009159586566188</v>
       </c>
       <c r="E363" t="n">
-        <v>3.055170917564423</v>
+        <v>3.055171157427961</v>
       </c>
       <c r="F363" t="n">
         <v>8730700</v>
@@ -7712,16 +7712,16 @@
         <v>44944</v>
       </c>
       <c r="B365" t="n">
-        <v>3.082777976989746</v>
+        <v>3.082778215408325</v>
       </c>
       <c r="C365" t="n">
-        <v>3.174801334443457</v>
+        <v>3.174801579979019</v>
       </c>
       <c r="D365" t="n">
-        <v>3.064373349379097</v>
+        <v>3.064373586374283</v>
       </c>
       <c r="E365" t="n">
-        <v>3.128789765416836</v>
+        <v>3.128790007393915</v>
       </c>
       <c r="F365" t="n">
         <v>13324700</v>
@@ -7732,16 +7732,16 @@
         <v>44945</v>
       </c>
       <c r="B366" t="n">
-        <v>3.137991905212402</v>
+        <v>3.137991666793823</v>
       </c>
       <c r="C366" t="n">
-        <v>3.147194218507435</v>
+        <v>3.147193979389681</v>
       </c>
       <c r="D366" t="n">
-        <v>2.99075467309143</v>
+        <v>2.990754445859652</v>
       </c>
       <c r="E366" t="n">
-        <v>3.082777806041753</v>
+        <v>3.082777571818235</v>
       </c>
       <c r="F366" t="n">
         <v>23712400</v>
@@ -7792,16 +7792,16 @@
         <v>44950</v>
       </c>
       <c r="B369" t="n">
-        <v>3.193205833435059</v>
+        <v>3.193206071853638</v>
       </c>
       <c r="C369" t="n">
-        <v>3.202408146869723</v>
+        <v>3.202408385975387</v>
       </c>
       <c r="D369" t="n">
-        <v>3.018361658775971</v>
+        <v>3.018361884139927</v>
       </c>
       <c r="E369" t="n">
-        <v>3.045968599079965</v>
+        <v>3.045968826505175</v>
       </c>
       <c r="F369" t="n">
         <v>12703800</v>
@@ -7812,16 +7812,16 @@
         <v>44951</v>
       </c>
       <c r="B370" t="n">
-        <v>3.248420238494873</v>
+        <v>3.248420000076294</v>
       </c>
       <c r="C370" t="n">
-        <v>3.248420238494873</v>
+        <v>3.248420000076294</v>
       </c>
       <c r="D370" t="n">
-        <v>3.147194774370885</v>
+        <v>3.147194543381774</v>
       </c>
       <c r="E370" t="n">
-        <v>3.193206348972698</v>
+        <v>3.193206114606555</v>
       </c>
       <c r="F370" t="n">
         <v>7649000</v>
@@ -7872,16 +7872,16 @@
         <v>44956</v>
       </c>
       <c r="B373" t="n">
-        <v>2.990754842758179</v>
+        <v>2.990755081176758</v>
       </c>
       <c r="C373" t="n">
-        <v>3.156396710866147</v>
+        <v>3.156396962489453</v>
       </c>
       <c r="D373" t="n">
-        <v>2.963147901306928</v>
+        <v>2.963148137524723</v>
       </c>
       <c r="E373" t="n">
-        <v>3.128789769414897</v>
+        <v>3.128790018837418</v>
       </c>
       <c r="F373" t="n">
         <v>24955900</v>
@@ -7992,16 +7992,16 @@
         <v>44964</v>
       </c>
       <c r="B379" t="n">
-        <v>2.880326986312866</v>
+        <v>2.880326747894287</v>
       </c>
       <c r="C379" t="n">
-        <v>2.95394549453285</v>
+        <v>2.953945250020512</v>
       </c>
       <c r="D379" t="n">
-        <v>2.843517512802413</v>
+        <v>2.843517277430732</v>
       </c>
       <c r="E379" t="n">
-        <v>2.926338553950356</v>
+        <v>2.926338311723177</v>
       </c>
       <c r="F379" t="n">
         <v>31913300</v>
@@ -8012,16 +8012,16 @@
         <v>44965</v>
       </c>
       <c r="B380" t="n">
-        <v>3.036766290664673</v>
+        <v>3.036766529083252</v>
       </c>
       <c r="C380" t="n">
-        <v>3.036766290664673</v>
+        <v>3.036766529083252</v>
       </c>
       <c r="D380" t="n">
-        <v>2.861922115716591</v>
+        <v>2.861922340408036</v>
       </c>
       <c r="E380" t="n">
-        <v>2.907933902366425</v>
+        <v>2.907934130670286</v>
       </c>
       <c r="F380" t="n">
         <v>50518000</v>
@@ -8052,16 +8052,16 @@
         <v>44967</v>
       </c>
       <c r="B382" t="n">
-        <v>2.953945398330688</v>
+        <v>2.953945636749268</v>
       </c>
       <c r="C382" t="n">
-        <v>3.045968530608719</v>
+        <v>3.045968776454661</v>
       </c>
       <c r="D382" t="n">
-        <v>2.926338458647279</v>
+        <v>2.92633869483765</v>
       </c>
       <c r="E382" t="n">
-        <v>3.01836159092531</v>
+        <v>3.018361834543043</v>
       </c>
       <c r="F382" t="n">
         <v>23226200</v>
@@ -8132,16 +8132,16 @@
         <v>44973</v>
       </c>
       <c r="B386" t="n">
-        <v>2.834315538406372</v>
+        <v>2.834315299987793</v>
       </c>
       <c r="C386" t="n">
-        <v>2.871124796920665</v>
+        <v>2.871124555405743</v>
       </c>
       <c r="D386" t="n">
-        <v>2.760697021377787</v>
+        <v>2.760696789151893</v>
       </c>
       <c r="E386" t="n">
-        <v>2.825113223777799</v>
+        <v>2.825112986133305</v>
       </c>
       <c r="F386" t="n">
         <v>21149000</v>
@@ -8172,16 +8172,16 @@
         <v>44979</v>
       </c>
       <c r="B388" t="n">
-        <v>2.834315538406372</v>
+        <v>2.834315299987793</v>
       </c>
       <c r="C388" t="n">
-        <v>2.843517853034945</v>
+        <v>2.84351761384228</v>
       </c>
       <c r="D388" t="n">
-        <v>2.714685448234921</v>
+        <v>2.714685219879454</v>
       </c>
       <c r="E388" t="n">
-        <v>2.76989933600636</v>
+        <v>2.76989910300638</v>
       </c>
       <c r="F388" t="n">
         <v>20601900</v>
@@ -8252,16 +8252,16 @@
         <v>44985</v>
       </c>
       <c r="B392" t="n">
-        <v>2.834315538406372</v>
+        <v>2.834315299987793</v>
       </c>
       <c r="C392" t="n">
-        <v>2.889529645578298</v>
+        <v>2.889529402515187</v>
       </c>
       <c r="D392" t="n">
-        <v>2.79750627989208</v>
+        <v>2.797506044569843</v>
       </c>
       <c r="E392" t="n">
-        <v>2.825113223777799</v>
+        <v>2.825112986133305</v>
       </c>
       <c r="F392" t="n">
         <v>28842300</v>
@@ -8272,16 +8272,16 @@
         <v>44986</v>
       </c>
       <c r="B393" t="n">
-        <v>2.779101371765137</v>
+        <v>2.779101610183716</v>
       </c>
       <c r="C393" t="n">
-        <v>2.917136296743063</v>
+        <v>2.917136547003632</v>
       </c>
       <c r="D393" t="n">
-        <v>2.751494430649644</v>
+        <v>2.751494666699829</v>
       </c>
       <c r="E393" t="n">
-        <v>2.843517567701285</v>
+        <v>2.843517811646118</v>
       </c>
       <c r="F393" t="n">
         <v>32788900</v>
@@ -8312,16 +8312,16 @@
         <v>44988</v>
       </c>
       <c r="B395" t="n">
-        <v>2.604257106781006</v>
+        <v>2.604257345199585</v>
       </c>
       <c r="C395" t="n">
-        <v>2.714685087031328</v>
+        <v>2.71468533555954</v>
       </c>
       <c r="D395" t="n">
-        <v>2.558245539760229</v>
+        <v>2.55824577396647</v>
       </c>
       <c r="E395" t="n">
-        <v>2.714685087031328</v>
+        <v>2.71468533555954</v>
       </c>
       <c r="F395" t="n">
         <v>36019100</v>
@@ -8432,16 +8432,16 @@
         <v>44998</v>
       </c>
       <c r="B401" t="n">
-        <v>2.411008596420288</v>
+        <v>2.411008358001709</v>
       </c>
       <c r="C401" t="n">
-        <v>2.475425017412025</v>
+        <v>2.475424772623468</v>
       </c>
       <c r="D401" t="n">
-        <v>2.401806281907252</v>
+        <v>2.401806044398667</v>
       </c>
       <c r="E401" t="n">
-        <v>2.475425017412025</v>
+        <v>2.475424772623468</v>
       </c>
       <c r="F401" t="n">
         <v>31528700</v>
@@ -8452,16 +8452,16 @@
         <v>44999</v>
       </c>
       <c r="B402" t="n">
-        <v>2.493829488754272</v>
+        <v>2.493829250335693</v>
       </c>
       <c r="C402" t="n">
-        <v>2.585852628066047</v>
+        <v>2.585852380849743</v>
       </c>
       <c r="D402" t="n">
-        <v>2.46622254696074</v>
+        <v>2.466222311181478</v>
       </c>
       <c r="E402" t="n">
-        <v>2.475424860891918</v>
+        <v>2.475424624232883</v>
       </c>
       <c r="F402" t="n">
         <v>40119200</v>
@@ -8472,16 +8472,16 @@
         <v>45000</v>
       </c>
       <c r="B403" t="n">
-        <v>2.493829488754272</v>
+        <v>2.493829250335693</v>
       </c>
       <c r="C403" t="n">
-        <v>2.521436430547805</v>
+        <v>2.521436189489909</v>
       </c>
       <c r="D403" t="n">
-        <v>2.447817919098385</v>
+        <v>2.447817685078669</v>
       </c>
       <c r="E403" t="n">
-        <v>2.475424860891918</v>
+        <v>2.475424624232883</v>
       </c>
       <c r="F403" t="n">
         <v>17612600</v>
@@ -8492,16 +8492,16 @@
         <v>45001</v>
       </c>
       <c r="B404" t="n">
-        <v>2.512233972549438</v>
+        <v>2.512234449386597</v>
       </c>
       <c r="C404" t="n">
-        <v>2.539840912759816</v>
+        <v>2.539841394836938</v>
       </c>
       <c r="D404" t="n">
-        <v>2.447817778725223</v>
+        <v>2.447818243335799</v>
       </c>
       <c r="E404" t="n">
-        <v>2.530638599356357</v>
+        <v>2.530639079686825</v>
       </c>
       <c r="F404" t="n">
         <v>22197500</v>
@@ -8572,16 +8572,16 @@
         <v>45007</v>
       </c>
       <c r="B408" t="n">
-        <v>2.216452598571777</v>
+        <v>2.216452836990356</v>
       </c>
       <c r="C408" t="n">
-        <v>2.273528805389769</v>
+        <v>2.273529049947901</v>
       </c>
       <c r="D408" t="n">
-        <v>2.197427271899042</v>
+        <v>2.197427508271111</v>
       </c>
       <c r="E408" t="n">
-        <v>2.254503251917249</v>
+        <v>2.254503494428847</v>
       </c>
       <c r="F408" t="n">
         <v>26704400</v>
@@ -8612,16 +8612,16 @@
         <v>45009</v>
       </c>
       <c r="B410" t="n">
-        <v>2.292554378509521</v>
+        <v>2.292554140090942</v>
       </c>
       <c r="C410" t="n">
-        <v>2.30206704286849</v>
+        <v>2.302066803460623</v>
       </c>
       <c r="D410" t="n">
-        <v>2.149864186325184</v>
+        <v>2.149863962745944</v>
       </c>
       <c r="E410" t="n">
-        <v>2.159376850684152</v>
+        <v>2.159376626115625</v>
       </c>
       <c r="F410" t="n">
         <v>19141800</v>
@@ -8672,16 +8672,16 @@
         <v>45014</v>
       </c>
       <c r="B413" t="n">
-        <v>2.615984916687012</v>
+        <v>2.615985155105591</v>
       </c>
       <c r="C413" t="n">
-        <v>2.644522906743987</v>
+        <v>2.644523147763493</v>
       </c>
       <c r="D413" t="n">
-        <v>2.492320066307002</v>
+        <v>2.492320293454875</v>
       </c>
       <c r="E413" t="n">
-        <v>2.539883609868411</v>
+        <v>2.539883841351184</v>
       </c>
       <c r="F413" t="n">
         <v>36856900</v>
@@ -8692,16 +8692,16 @@
         <v>45015</v>
       </c>
       <c r="B414" t="n">
-        <v>2.749162673950195</v>
+        <v>2.749162435531616</v>
       </c>
       <c r="C414" t="n">
-        <v>2.796725994925153</v>
+        <v>2.796725752381689</v>
       </c>
       <c r="D414" t="n">
-        <v>2.644523141005484</v>
+        <v>2.644522911661672</v>
       </c>
       <c r="E414" t="n">
-        <v>2.673061133590459</v>
+        <v>2.673060901771716</v>
       </c>
       <c r="F414" t="n">
         <v>39786400</v>
@@ -8712,16 +8712,16 @@
         <v>45016</v>
       </c>
       <c r="B415" t="n">
-        <v>2.711111783981323</v>
+        <v>2.711111545562744</v>
       </c>
       <c r="C415" t="n">
-        <v>2.787213324161716</v>
+        <v>2.787213079050672</v>
       </c>
       <c r="D415" t="n">
-        <v>2.654035798945881</v>
+        <v>2.654035565546636</v>
       </c>
       <c r="E415" t="n">
-        <v>2.777700659989142</v>
+        <v>2.777700415714654</v>
       </c>
       <c r="F415" t="n">
         <v>25812800</v>
@@ -8772,16 +8772,16 @@
         <v>45021</v>
       </c>
       <c r="B418" t="n">
-        <v>2.682573795318604</v>
+        <v>2.682573556900024</v>
       </c>
       <c r="C418" t="n">
-        <v>2.720624452063579</v>
+        <v>2.720624210263179</v>
       </c>
       <c r="D418" t="n">
-        <v>2.615985146014897</v>
+        <v>2.615984913514504</v>
       </c>
       <c r="E418" t="n">
-        <v>2.701599123691091</v>
+        <v>2.701598883581602</v>
       </c>
       <c r="F418" t="n">
         <v>22336100</v>
@@ -8812,16 +8812,16 @@
         <v>45026</v>
       </c>
       <c r="B420" t="n">
-        <v>2.673060894012451</v>
+        <v>2.67306113243103</v>
       </c>
       <c r="C420" t="n">
-        <v>2.701598884039655</v>
+        <v>2.701599125003626</v>
       </c>
       <c r="D420" t="n">
-        <v>2.644522903985246</v>
+        <v>2.644523139858434</v>
       </c>
       <c r="E420" t="n">
-        <v>2.673060894012451</v>
+        <v>2.67306113243103</v>
       </c>
       <c r="F420" t="n">
         <v>14149600</v>
@@ -8832,16 +8832,16 @@
         <v>45027</v>
       </c>
       <c r="B421" t="n">
-        <v>2.91087794303894</v>
+        <v>2.910877704620361</v>
       </c>
       <c r="C421" t="n">
-        <v>2.920390607161298</v>
+        <v>2.920390367963574</v>
       </c>
       <c r="D421" t="n">
-        <v>2.692086441424922</v>
+        <v>2.692086220926695</v>
       </c>
       <c r="E421" t="n">
-        <v>2.711111769669636</v>
+        <v>2.71111154761312</v>
       </c>
       <c r="F421" t="n">
         <v>33609000</v>
@@ -8852,16 +8852,16 @@
         <v>45028</v>
       </c>
       <c r="B422" t="n">
-        <v>2.91087794303894</v>
+        <v>2.910877704620361</v>
       </c>
       <c r="C422" t="n">
-        <v>3.015517475184673</v>
+        <v>3.01551722819548</v>
       </c>
       <c r="D422" t="n">
-        <v>2.891852614794226</v>
+        <v>2.891852377933937</v>
       </c>
       <c r="E422" t="n">
-        <v>2.920390607161298</v>
+        <v>2.920390367963574</v>
       </c>
       <c r="F422" t="n">
         <v>32421000</v>
@@ -8872,16 +8872,16 @@
         <v>45029</v>
       </c>
       <c r="B423" t="n">
-        <v>2.882339715957642</v>
+        <v>2.882339954376221</v>
       </c>
       <c r="C423" t="n">
-        <v>2.95844102273943</v>
+        <v>2.958441267452883</v>
       </c>
       <c r="D423" t="n">
-        <v>2.853801725914471</v>
+        <v>2.853801961972472</v>
       </c>
       <c r="E423" t="n">
-        <v>2.929903032696259</v>
+        <v>2.929903275049135</v>
       </c>
       <c r="F423" t="n">
         <v>15780900</v>
@@ -8912,16 +8912,16 @@
         <v>45033</v>
       </c>
       <c r="B425" t="n">
-        <v>2.96795392036438</v>
+        <v>2.967953681945801</v>
       </c>
       <c r="C425" t="n">
-        <v>2.986979475361405</v>
+        <v>2.986979235414485</v>
       </c>
       <c r="D425" t="n">
-        <v>2.872827279378266</v>
+        <v>2.872827048601301</v>
       </c>
       <c r="E425" t="n">
-        <v>2.9013652716741</v>
+        <v>2.901365038604651</v>
       </c>
       <c r="F425" t="n">
         <v>14970900</v>
@@ -8932,16 +8932,16 @@
         <v>45034</v>
       </c>
       <c r="B426" t="n">
-        <v>3.025029897689819</v>
+        <v>3.025030136108398</v>
       </c>
       <c r="C426" t="n">
-        <v>3.034542561052375</v>
+        <v>3.034542800220697</v>
       </c>
       <c r="D426" t="n">
-        <v>2.948928363989592</v>
+        <v>2.948928596410207</v>
       </c>
       <c r="E426" t="n">
-        <v>2.986979244239598</v>
+        <v>2.986979479659204</v>
       </c>
       <c r="F426" t="n">
         <v>13884000</v>
@@ -8952,16 +8952,16 @@
         <v>45035</v>
       </c>
       <c r="B427" t="n">
-        <v>2.882339715957642</v>
+        <v>2.882339954376221</v>
       </c>
       <c r="C427" t="n">
-        <v>2.996491902930108</v>
+        <v>2.996492150791017</v>
       </c>
       <c r="D427" t="n">
-        <v>2.872827052609918</v>
+        <v>2.872827290241638</v>
       </c>
       <c r="E427" t="n">
-        <v>2.986979239582385</v>
+        <v>2.986979486656434</v>
       </c>
       <c r="F427" t="n">
         <v>19845900</v>
@@ -8972,16 +8972,16 @@
         <v>45036</v>
       </c>
       <c r="B428" t="n">
-        <v>2.958441257476807</v>
+        <v>2.958441019058228</v>
       </c>
       <c r="C428" t="n">
-        <v>2.977466812481619</v>
+        <v>2.977466572529786</v>
       </c>
       <c r="D428" t="n">
-        <v>2.844289288246741</v>
+        <v>2.844289059027585</v>
       </c>
       <c r="E428" t="n">
-        <v>2.882339944656763</v>
+        <v>2.882339712371133</v>
       </c>
       <c r="F428" t="n">
         <v>11874200</v>
@@ -8992,16 +8992,16 @@
         <v>45040</v>
       </c>
       <c r="B429" t="n">
-        <v>3.072593450546265</v>
+        <v>3.072593212127686</v>
       </c>
       <c r="C429" t="n">
-        <v>3.110644106919625</v>
+        <v>3.110643865548496</v>
       </c>
       <c r="D429" t="n">
-        <v>2.891852605973001</v>
+        <v>2.891852381579049</v>
       </c>
       <c r="E429" t="n">
-        <v>2.948928590533042</v>
+        <v>2.948928361710265</v>
       </c>
       <c r="F429" t="n">
         <v>37103600</v>
@@ -9012,16 +9012,16 @@
         <v>45041</v>
       </c>
       <c r="B430" t="n">
-        <v>3.025029897689819</v>
+        <v>3.025030136108398</v>
       </c>
       <c r="C430" t="n">
-        <v>3.14869452140304</v>
+        <v>3.148694769568281</v>
       </c>
       <c r="D430" t="n">
-        <v>2.977466580877042</v>
+        <v>2.977466815546905</v>
       </c>
       <c r="E430" t="n">
-        <v>3.072593214502596</v>
+        <v>3.072593456669892</v>
       </c>
       <c r="F430" t="n">
         <v>18942800</v>
@@ -9052,16 +9052,16 @@
         <v>45043</v>
       </c>
       <c r="B432" t="n">
-        <v>2.977466583251953</v>
+        <v>2.977466344833374</v>
       </c>
       <c r="C432" t="n">
-        <v>3.006004573362382</v>
+        <v>3.006004332658643</v>
       </c>
       <c r="D432" t="n">
-        <v>2.891852386120882</v>
+        <v>2.8918521545578</v>
       </c>
       <c r="E432" t="n">
-        <v>2.901365049491024</v>
+        <v>2.901364817166223</v>
       </c>
       <c r="F432" t="n">
         <v>12242300</v>
@@ -9132,16 +9132,16 @@
         <v>45050</v>
       </c>
       <c r="B436" t="n">
-        <v>3.025029897689819</v>
+        <v>3.025030136108398</v>
       </c>
       <c r="C436" t="n">
-        <v>3.063080551140041</v>
+        <v>3.063080792557593</v>
       </c>
       <c r="D436" t="n">
-        <v>2.958441027352147</v>
+        <v>2.958441260522505</v>
       </c>
       <c r="E436" t="n">
-        <v>3.015517234327264</v>
+        <v>3.0155174719961</v>
       </c>
       <c r="F436" t="n">
         <v>20441800</v>
@@ -9172,16 +9172,16 @@
         <v>45054</v>
       </c>
       <c r="B438" t="n">
-        <v>3.148694276809692</v>
+        <v>3.148694515228271</v>
       </c>
       <c r="C438" t="n">
-        <v>3.215283141974683</v>
+        <v>3.215283385435359</v>
       </c>
       <c r="D438" t="n">
-        <v>3.139181614186089</v>
+        <v>3.139181851884371</v>
       </c>
       <c r="E438" t="n">
-        <v>3.139181614186089</v>
+        <v>3.139181851884371</v>
       </c>
       <c r="F438" t="n">
         <v>16113900</v>
@@ -9192,16 +9192,16 @@
         <v>45055</v>
       </c>
       <c r="B439" t="n">
-        <v>3.025029897689819</v>
+        <v>3.025030136108398</v>
       </c>
       <c r="C439" t="n">
-        <v>3.158207184765595</v>
+        <v>3.158207433680579</v>
       </c>
       <c r="D439" t="n">
-        <v>3.015517234327264</v>
+        <v>3.0155174719961</v>
       </c>
       <c r="E439" t="n">
-        <v>3.129669194677929</v>
+        <v>3.129669441343684</v>
       </c>
       <c r="F439" t="n">
         <v>32144800</v>
@@ -9272,16 +9272,16 @@
         <v>45061</v>
       </c>
       <c r="B443" t="n">
-        <v>2.986979246139526</v>
+        <v>2.986979007720947</v>
       </c>
       <c r="C443" t="n">
-        <v>3.205770503617468</v>
+        <v>3.205770247735124</v>
       </c>
       <c r="D443" t="n">
-        <v>2.901365049022286</v>
+        <v>2.901364817437372</v>
       </c>
       <c r="E443" t="n">
-        <v>3.186745176880255</v>
+        <v>3.1867449225165</v>
       </c>
       <c r="F443" t="n">
         <v>71533500</v>
@@ -9292,16 +9292,16 @@
         <v>45062</v>
       </c>
       <c r="B444" t="n">
-        <v>3.082105875015259</v>
+        <v>3.082106113433838</v>
       </c>
       <c r="C444" t="n">
-        <v>3.139181855137815</v>
+        <v>3.139182097971549</v>
       </c>
       <c r="D444" t="n">
-        <v>2.977466578123905</v>
+        <v>2.977466808448034</v>
       </c>
       <c r="E444" t="n">
-        <v>2.977466578123905</v>
+        <v>2.977466808448034</v>
       </c>
       <c r="F444" t="n">
         <v>45623200</v>
@@ -9312,16 +9312,16 @@
         <v>45063</v>
       </c>
       <c r="B445" t="n">
-        <v>3.253334045410156</v>
+        <v>3.253334283828735</v>
       </c>
       <c r="C445" t="n">
-        <v>3.300897362226138</v>
+        <v>3.300897604130366</v>
       </c>
       <c r="D445" t="n">
-        <v>3.082105878072837</v>
+        <v>3.082106103943065</v>
       </c>
       <c r="E445" t="n">
-        <v>3.091618541436033</v>
+        <v>3.091618768003391</v>
       </c>
       <c r="F445" t="n">
         <v>27916800</v>
@@ -9332,16 +9332,16 @@
         <v>45064</v>
       </c>
       <c r="B446" t="n">
-        <v>3.300897121429443</v>
+        <v>3.300897598266602</v>
       </c>
       <c r="C446" t="n">
-        <v>3.338947772106478</v>
+        <v>3.338948254440312</v>
       </c>
       <c r="D446" t="n">
-        <v>3.177232279929315</v>
+        <v>3.177232738902241</v>
       </c>
       <c r="E446" t="n">
-        <v>3.253333808083151</v>
+        <v>3.253334278049463</v>
       </c>
       <c r="F446" t="n">
         <v>40825600</v>
@@ -9412,16 +9412,16 @@
         <v>45070</v>
       </c>
       <c r="B450" t="n">
-        <v>3.319922924041748</v>
+        <v>3.319922685623169</v>
       </c>
       <c r="C450" t="n">
-        <v>3.529201759651233</v>
+        <v>3.529201506203401</v>
       </c>
       <c r="D450" t="n">
-        <v>3.262846939820925</v>
+        <v>3.262846705501229</v>
       </c>
       <c r="E450" t="n">
-        <v>3.462613111393607</v>
+        <v>3.462612862727804</v>
       </c>
       <c r="F450" t="n">
         <v>35329500</v>
@@ -9452,16 +9452,16 @@
         <v>45072</v>
       </c>
       <c r="B452" t="n">
-        <v>3.291384696960449</v>
+        <v>3.291384935379028</v>
       </c>
       <c r="C452" t="n">
-        <v>3.348460677106637</v>
+        <v>3.348460919659638</v>
       </c>
       <c r="D452" t="n">
-        <v>3.17723250986829</v>
+        <v>3.177232740018008</v>
       </c>
       <c r="E452" t="n">
-        <v>3.338948013748939</v>
+        <v>3.33894825561287</v>
       </c>
       <c r="F452" t="n">
         <v>25686400</v>
@@ -9472,16 +9472,16 @@
         <v>45075</v>
       </c>
       <c r="B453" t="n">
-        <v>3.357973575592041</v>
+        <v>3.357973337173462</v>
       </c>
       <c r="C453" t="n">
-        <v>3.415049559734729</v>
+        <v>3.415049317263714</v>
       </c>
       <c r="D453" t="n">
-        <v>3.291384927425571</v>
+        <v>3.291384693734835</v>
       </c>
       <c r="E453" t="n">
-        <v>3.319922919496916</v>
+        <v>3.319922683779961</v>
       </c>
       <c r="F453" t="n">
         <v>14544800</v>
@@ -9532,16 +9532,16 @@
         <v>45078</v>
       </c>
       <c r="B456" t="n">
-        <v>3.576764822006226</v>
+        <v>3.576765060424805</v>
       </c>
       <c r="C456" t="n">
-        <v>3.662378792166026</v>
+        <v>3.662379036291428</v>
       </c>
       <c r="D456" t="n">
-        <v>3.376998664833572</v>
+        <v>3.376998889936218</v>
       </c>
       <c r="E456" t="n">
-        <v>3.472125525144246</v>
+        <v>3.472125756587821</v>
       </c>
       <c r="F456" t="n">
         <v>28377100</v>
@@ -9612,16 +9612,16 @@
         <v>45084</v>
       </c>
       <c r="B460" t="n">
-        <v>3.757505655288696</v>
+        <v>3.757505893707275</v>
       </c>
       <c r="C460" t="n">
-        <v>3.85263251567056</v>
+        <v>3.852632760125061</v>
       </c>
       <c r="D460" t="n">
-        <v>3.681404121623248</v>
+        <v>3.681404355213087</v>
       </c>
       <c r="E460" t="n">
-        <v>3.747992991930488</v>
+        <v>3.747993229745477</v>
       </c>
       <c r="F460" t="n">
         <v>19382700</v>
@@ -9632,16 +9632,16 @@
         <v>45086</v>
       </c>
       <c r="B461" t="n">
-        <v>3.786043882369995</v>
+        <v>3.786043643951416</v>
       </c>
       <c r="C461" t="n">
-        <v>3.824094538184801</v>
+        <v>3.824094297370058</v>
       </c>
       <c r="D461" t="n">
-        <v>3.728967898647786</v>
+        <v>3.728967663823453</v>
       </c>
       <c r="E461" t="n">
-        <v>3.795556546323696</v>
+        <v>3.795556307306077</v>
       </c>
       <c r="F461" t="n">
         <v>14031500</v>
@@ -9652,16 +9652,16 @@
         <v>45089</v>
       </c>
       <c r="B462" t="n">
-        <v>3.795556306838989</v>
+        <v>3.795556545257568</v>
       </c>
       <c r="C462" t="n">
-        <v>3.805068970192479</v>
+        <v>3.805069209208598</v>
       </c>
       <c r="D462" t="n">
-        <v>3.74799299007154</v>
+        <v>3.747993225502421</v>
       </c>
       <c r="E462" t="n">
-        <v>3.786043643485499</v>
+        <v>3.786043881306539</v>
       </c>
       <c r="F462" t="n">
         <v>16242400</v>
@@ -9672,16 +9672,16 @@
         <v>45090</v>
       </c>
       <c r="B463" t="n">
-        <v>3.700429677963257</v>
+        <v>3.700429916381836</v>
       </c>
       <c r="C463" t="n">
-        <v>3.814581865148647</v>
+        <v>3.814582110922048</v>
       </c>
       <c r="D463" t="n">
-        <v>3.662378797701604</v>
+        <v>3.662379033668566</v>
       </c>
       <c r="E463" t="n">
-        <v>3.78604364825246</v>
+        <v>3.786043892187145</v>
       </c>
       <c r="F463" t="n">
         <v>19986600</v>
@@ -9712,16 +9712,16 @@
         <v>45092</v>
       </c>
       <c r="B465" t="n">
-        <v>3.757505655288696</v>
+        <v>3.757505893707275</v>
       </c>
       <c r="C465" t="n">
-        <v>3.795556308721528</v>
+        <v>3.79555654955447</v>
       </c>
       <c r="D465" t="n">
-        <v>3.719455001855864</v>
+        <v>3.71945523786008</v>
       </c>
       <c r="E465" t="n">
-        <v>3.757505655288696</v>
+        <v>3.757505893707275</v>
       </c>
       <c r="F465" t="n">
         <v>13781200</v>
@@ -9732,16 +9732,16 @@
         <v>45093</v>
       </c>
       <c r="B466" t="n">
-        <v>3.757505655288696</v>
+        <v>3.757505893707275</v>
       </c>
       <c r="C466" t="n">
-        <v>3.776530982005112</v>
+        <v>3.776531221630873</v>
       </c>
       <c r="D466" t="n">
-        <v>3.709942338497656</v>
+        <v>3.709942573898282</v>
       </c>
       <c r="E466" t="n">
-        <v>3.728967665214073</v>
+        <v>3.728967901821879</v>
       </c>
       <c r="F466" t="n">
         <v>14449100</v>
@@ -9772,16 +9772,16 @@
         <v>45097</v>
       </c>
       <c r="B468" t="n">
-        <v>3.947758913040161</v>
+        <v>3.94775915145874</v>
       </c>
       <c r="C468" t="n">
-        <v>3.966784238618205</v>
+        <v>3.966784478185788</v>
       </c>
       <c r="D468" t="n">
-        <v>3.767018093248975</v>
+        <v>3.767018320752002</v>
       </c>
       <c r="E468" t="n">
-        <v>3.786043418827019</v>
+        <v>3.78604364747905</v>
       </c>
       <c r="F468" t="n">
         <v>35176100</v>
@@ -9892,16 +9892,16 @@
         <v>45105</v>
       </c>
       <c r="B474" t="n">
-        <v>4.176063537597656</v>
+        <v>4.176063060760498</v>
       </c>
       <c r="C474" t="n">
-        <v>4.261677744210696</v>
+        <v>4.261677257597817</v>
       </c>
       <c r="D474" t="n">
-        <v>4.090449784584236</v>
+        <v>4.090449317522748</v>
       </c>
       <c r="E474" t="n">
-        <v>4.223627086515927</v>
+        <v>4.223626604247801</v>
       </c>
       <c r="F474" t="n">
         <v>30177100</v>
@@ -9912,16 +9912,16 @@
         <v>45106</v>
       </c>
       <c r="B475" t="n">
-        <v>4.366317272186279</v>
+        <v>4.366316795349121</v>
       </c>
       <c r="C475" t="n">
-        <v>4.366317272186279</v>
+        <v>4.366316795349121</v>
       </c>
       <c r="D475" t="n">
-        <v>4.185576421646147</v>
+        <v>4.185575964547351</v>
       </c>
       <c r="E475" t="n">
-        <v>4.185576421646147</v>
+        <v>4.185575964547351</v>
       </c>
       <c r="F475" t="n">
         <v>40765500</v>
@@ -9952,16 +9952,16 @@
         <v>45110</v>
       </c>
       <c r="B477" t="n">
-        <v>4.252163887023926</v>
+        <v>4.252164363861084</v>
       </c>
       <c r="C477" t="n">
-        <v>4.299727425137196</v>
+        <v>4.299727907308124</v>
       </c>
       <c r="D477" t="n">
-        <v>4.19508791344771</v>
+        <v>4.195088383884376</v>
       </c>
       <c r="E477" t="n">
-        <v>4.233138562498521</v>
+        <v>4.233139037202181</v>
       </c>
       <c r="F477" t="n">
         <v>20197900</v>
@@ -10012,16 +10012,16 @@
         <v>45113</v>
       </c>
       <c r="B480" t="n">
-        <v>3.957271575927734</v>
+        <v>3.957271814346313</v>
       </c>
       <c r="C480" t="n">
-        <v>4.061911099406468</v>
+        <v>4.061911344129392</v>
       </c>
       <c r="D480" t="n">
-        <v>3.909708486055269</v>
+        <v>3.909708721608256</v>
       </c>
       <c r="E480" t="n">
-        <v>4.061911099406468</v>
+        <v>4.061911344129392</v>
       </c>
       <c r="F480" t="n">
         <v>22675100</v>
@@ -10032,16 +10032,16 @@
         <v>45114</v>
       </c>
       <c r="B481" t="n">
-        <v>3.995322465896606</v>
+        <v>3.995322227478027</v>
       </c>
       <c r="C481" t="n">
-        <v>4.042886012185687</v>
+        <v>4.042885770928781</v>
       </c>
       <c r="D481" t="n">
-        <v>3.94775937320712</v>
+        <v>3.947759137626841</v>
       </c>
       <c r="E481" t="n">
-        <v>3.976297138100893</v>
+        <v>3.976296900817639</v>
       </c>
       <c r="F481" t="n">
         <v>19055100</v>
@@ -10112,16 +10112,16 @@
         <v>45120</v>
       </c>
       <c r="B485" t="n">
-        <v>3.995322465896606</v>
+        <v>3.995322227478027</v>
       </c>
       <c r="C485" t="n">
-        <v>4.071424230679055</v>
+        <v>4.071423987719147</v>
       </c>
       <c r="D485" t="n">
-        <v>3.957271810305179</v>
+        <v>3.957271574157251</v>
       </c>
       <c r="E485" t="n">
-        <v>4.023860684389974</v>
+        <v>4.023860444268393</v>
       </c>
       <c r="F485" t="n">
         <v>10522300</v>
@@ -10132,16 +10132,16 @@
         <v>45121</v>
       </c>
       <c r="B486" t="n">
-        <v>3.881170272827148</v>
+        <v>3.881170511245728</v>
       </c>
       <c r="C486" t="n">
-        <v>4.01434755963212</v>
+        <v>4.014347806231721</v>
       </c>
       <c r="D486" t="n">
-        <v>3.814581856224446</v>
+        <v>3.814582090552529</v>
       </c>
       <c r="E486" t="n">
-        <v>3.995322232945695</v>
+        <v>3.995322478376579</v>
       </c>
       <c r="F486" t="n">
         <v>16845900</v>
@@ -10172,16 +10172,16 @@
         <v>45125</v>
       </c>
       <c r="B488" t="n">
-        <v>4.07142448425293</v>
+        <v>4.071424007415771</v>
       </c>
       <c r="C488" t="n">
-        <v>4.185576458136752</v>
+        <v>4.185575967930341</v>
       </c>
       <c r="D488" t="n">
-        <v>4.004835606020889</v>
+        <v>4.004835136982487</v>
       </c>
       <c r="E488" t="n">
-        <v>4.023860935001526</v>
+        <v>4.023860463734916</v>
       </c>
       <c r="F488" t="n">
         <v>19854400</v>
@@ -10212,16 +10212,16 @@
         <v>45127</v>
       </c>
       <c r="B490" t="n">
-        <v>3.995322465896606</v>
+        <v>3.995322227478027</v>
       </c>
       <c r="C490" t="n">
-        <v>4.080936667777115</v>
+        <v>4.080936424249557</v>
       </c>
       <c r="D490" t="n">
-        <v>3.94775937320712</v>
+        <v>3.947759137626841</v>
       </c>
       <c r="E490" t="n">
-        <v>4.071424230679055</v>
+        <v>4.071423987719147</v>
       </c>
       <c r="F490" t="n">
         <v>13981900</v>
@@ -10232,16 +10232,16 @@
         <v>45128</v>
       </c>
       <c r="B491" t="n">
-        <v>4.061910629272461</v>
+        <v>4.061911582946777</v>
       </c>
       <c r="C491" t="n">
-        <v>4.099961278206199</v>
+        <v>4.099962240814224</v>
       </c>
       <c r="D491" t="n">
-        <v>3.976296442371792</v>
+        <v>3.97629737594521</v>
       </c>
       <c r="E491" t="n">
-        <v>4.004834655871853</v>
+        <v>4.004835596145607</v>
       </c>
       <c r="F491" t="n">
         <v>9991000</v>
@@ -10272,16 +10272,16 @@
         <v>45132</v>
       </c>
       <c r="B493" t="n">
-        <v>3.995322465896606</v>
+        <v>3.995322227478027</v>
       </c>
       <c r="C493" t="n">
-        <v>4.090449558474769</v>
+        <v>4.090449314379534</v>
       </c>
       <c r="D493" t="n">
-        <v>3.966784701002833</v>
+        <v>3.966784464287229</v>
       </c>
       <c r="E493" t="n">
-        <v>4.061911339981402</v>
+        <v>4.061911097589169</v>
       </c>
       <c r="F493" t="n">
         <v>14413200</v>
@@ -10352,16 +10352,16 @@
         <v>45138</v>
       </c>
       <c r="B497" t="n">
-        <v>3.980106115341187</v>
+        <v>3.980106353759766</v>
       </c>
       <c r="C497" t="n">
-        <v>4.008809005461245</v>
+        <v>4.008809245599202</v>
       </c>
       <c r="D497" t="n">
-        <v>3.922700791318031</v>
+        <v>3.922701026297883</v>
       </c>
       <c r="E497" t="n">
-        <v>3.941835899325749</v>
+        <v>3.941836135451844</v>
       </c>
       <c r="F497" t="n">
         <v>13989300</v>
@@ -10372,16 +10372,16 @@
         <v>45139</v>
       </c>
       <c r="B498" t="n">
-        <v>3.980106115341187</v>
+        <v>3.980106353759766</v>
       </c>
       <c r="C498" t="n">
-        <v>4.018376331356624</v>
+        <v>4.018376572067687</v>
       </c>
       <c r="D498" t="n">
-        <v>3.884430575302593</v>
+        <v>3.884430807989962</v>
       </c>
       <c r="E498" t="n">
-        <v>3.970538789445808</v>
+        <v>3.970539027291279</v>
       </c>
       <c r="F498" t="n">
         <v>24308900</v>
@@ -10392,16 +10392,16 @@
         <v>45140</v>
       </c>
       <c r="B499" t="n">
-        <v>4.008809089660645</v>
+        <v>4.008808612823486</v>
       </c>
       <c r="C499" t="n">
-        <v>4.018376415756972</v>
+        <v>4.018375937781805</v>
       </c>
       <c r="D499" t="n">
-        <v>3.932268656022146</v>
+        <v>3.932268188289268</v>
       </c>
       <c r="E499" t="n">
-        <v>3.95140376443177</v>
+        <v>3.951403294422822</v>
       </c>
       <c r="F499" t="n">
         <v>25721100</v>
@@ -10412,16 +10412,16 @@
         <v>45141</v>
       </c>
       <c r="B500" t="n">
-        <v>3.922700643539429</v>
+        <v>3.922700881958008</v>
       </c>
       <c r="C500" t="n">
-        <v>4.037511287260518</v>
+        <v>4.037511532657195</v>
       </c>
       <c r="D500" t="n">
-        <v>3.893998210717629</v>
+        <v>3.893998447391697</v>
       </c>
       <c r="E500" t="n">
-        <v>4.027943961725565</v>
+        <v>4.027944206540749</v>
       </c>
       <c r="F500" t="n">
         <v>21426900</v>
@@ -10452,16 +10452,16 @@
         <v>45145</v>
       </c>
       <c r="B502" t="n">
-        <v>3.846160411834717</v>
+        <v>3.846160650253296</v>
       </c>
       <c r="C502" t="n">
-        <v>3.922700844911313</v>
+        <v>3.922701088074537</v>
       </c>
       <c r="D502" t="n">
-        <v>3.817457749430993</v>
+        <v>3.817457986070331</v>
       </c>
       <c r="E502" t="n">
-        <v>3.913133518885223</v>
+        <v>3.913133761455379</v>
       </c>
       <c r="F502" t="n">
         <v>14729300</v>
@@ -10512,16 +10512,16 @@
         <v>45148</v>
       </c>
       <c r="B505" t="n">
-        <v>3.740917205810547</v>
+        <v>3.740917444229126</v>
       </c>
       <c r="C505" t="n">
-        <v>3.788754975069817</v>
+        <v>3.788755216537224</v>
       </c>
       <c r="D505" t="n">
-        <v>3.702646762294654</v>
+        <v>3.702646998274156</v>
       </c>
       <c r="E505" t="n">
-        <v>3.760052313514255</v>
+        <v>3.760052553152365</v>
       </c>
       <c r="F505" t="n">
         <v>11449000</v>
@@ -10712,16 +10712,16 @@
         <v>45162</v>
       </c>
       <c r="B515" t="n">
-        <v>3.568701028823853</v>
+        <v>3.568701267242432</v>
       </c>
       <c r="C515" t="n">
-        <v>3.645241460077401</v>
+        <v>3.64524170360951</v>
       </c>
       <c r="D515" t="n">
-        <v>3.444322599928359</v>
+        <v>3.444322830037436</v>
       </c>
       <c r="E515" t="n">
-        <v>3.453890153835052</v>
+        <v>3.453890384583321</v>
       </c>
       <c r="F515" t="n">
         <v>42127000</v>
@@ -10732,16 +10732,16 @@
         <v>45163</v>
       </c>
       <c r="B516" t="n">
-        <v>3.626106739044189</v>
+        <v>3.62610650062561</v>
       </c>
       <c r="C516" t="n">
-        <v>3.664376958753072</v>
+        <v>3.664376717818205</v>
       </c>
       <c r="D516" t="n">
-        <v>3.549566299626424</v>
+        <v>3.549566066240422</v>
       </c>
       <c r="E516" t="n">
-        <v>3.616539184116969</v>
+        <v>3.616538946327462</v>
       </c>
       <c r="F516" t="n">
         <v>21198200</v>
@@ -10772,16 +10772,16 @@
         <v>45167</v>
       </c>
       <c r="B518" t="n">
-        <v>3.654809236526489</v>
+        <v>3.65480899810791</v>
       </c>
       <c r="C518" t="n">
-        <v>3.664376791015754</v>
+        <v>3.664376551973043</v>
       </c>
       <c r="D518" t="n">
-        <v>3.578268800612372</v>
+        <v>3.578268567186847</v>
       </c>
       <c r="E518" t="n">
-        <v>3.61653901856943</v>
+        <v>3.616538782647379</v>
       </c>
       <c r="F518" t="n">
         <v>13520200</v>
@@ -11012,16 +11012,16 @@
         <v>45184</v>
       </c>
       <c r="B530" t="n">
-        <v>3.80789041519165</v>
+        <v>3.807890176773071</v>
       </c>
       <c r="C530" t="n">
-        <v>3.941836180810695</v>
+        <v>3.941835934005541</v>
       </c>
       <c r="D530" t="n">
-        <v>3.788755305817501</v>
+        <v>3.788755068597004</v>
       </c>
       <c r="E530" t="n">
-        <v>3.788755305817501</v>
+        <v>3.788755068597004</v>
       </c>
       <c r="F530" t="n">
         <v>34682000</v>
@@ -11032,16 +11032,16 @@
         <v>45187</v>
       </c>
       <c r="B531" t="n">
-        <v>3.817457675933838</v>
+        <v>3.817457914352417</v>
       </c>
       <c r="C531" t="n">
-        <v>3.884430553586438</v>
+        <v>3.884430796187795</v>
       </c>
       <c r="D531" t="n">
-        <v>3.740917244330867</v>
+        <v>3.740917477969129</v>
       </c>
       <c r="E531" t="n">
-        <v>3.817457675933838</v>
+        <v>3.817457914352417</v>
       </c>
       <c r="F531" t="n">
         <v>23371600</v>
@@ -11252,16 +11252,16 @@
         <v>45202</v>
       </c>
       <c r="B542" t="n">
-        <v>3.310376882553101</v>
+        <v>3.31037712097168</v>
       </c>
       <c r="C542" t="n">
-        <v>3.406052422698603</v>
+        <v>3.406052668007885</v>
       </c>
       <c r="D542" t="n">
-        <v>3.2721066664949</v>
+        <v>3.272106902157197</v>
       </c>
       <c r="E542" t="n">
-        <v>3.31994443656765</v>
+        <v>3.3199446756753</v>
       </c>
       <c r="F542" t="n">
         <v>29291500</v>
@@ -11272,16 +11272,16 @@
         <v>45203</v>
       </c>
       <c r="B543" t="n">
-        <v>3.319944381713867</v>
+        <v>3.319944620132446</v>
       </c>
       <c r="C543" t="n">
-        <v>3.348647043283278</v>
+        <v>3.348647283763111</v>
       </c>
       <c r="D543" t="n">
-        <v>3.300809274000926</v>
+        <v>3.300809511045337</v>
       </c>
       <c r="E543" t="n">
-        <v>3.319944381713867</v>
+        <v>3.319944620132446</v>
       </c>
       <c r="F543" t="n">
         <v>10591900</v>
@@ -11292,16 +11292,16 @@
         <v>45204</v>
       </c>
       <c r="B544" t="n">
-        <v>3.233836650848389</v>
+        <v>3.23383641242981</v>
       </c>
       <c r="C544" t="n">
-        <v>3.358214860745675</v>
+        <v>3.35821461315716</v>
       </c>
       <c r="D544" t="n">
-        <v>3.205133758917443</v>
+        <v>3.20513352261502</v>
       </c>
       <c r="E544" t="n">
-        <v>3.310377087708257</v>
+        <v>3.310376843646641</v>
       </c>
       <c r="F544" t="n">
         <v>37198300</v>
@@ -11312,16 +11312,16 @@
         <v>45205</v>
       </c>
       <c r="B545" t="n">
-        <v>3.233836650848389</v>
+        <v>3.23383641242981</v>
       </c>
       <c r="C545" t="n">
-        <v>3.262539314670839</v>
+        <v>3.262539074136121</v>
       </c>
       <c r="D545" t="n">
-        <v>3.138160876665057</v>
+        <v>3.138160645300292</v>
       </c>
       <c r="E545" t="n">
-        <v>3.205133758917443</v>
+        <v>3.20513352261502</v>
       </c>
       <c r="F545" t="n">
         <v>15875400</v>
@@ -11372,16 +11372,16 @@
         <v>45210</v>
       </c>
       <c r="B548" t="n">
-        <v>3.482593297958374</v>
+        <v>3.482593059539795</v>
       </c>
       <c r="C548" t="n">
-        <v>3.511295961774288</v>
+        <v>3.511295721390723</v>
       </c>
       <c r="D548" t="n">
-        <v>3.396485078402136</v>
+        <v>3.396484845878531</v>
       </c>
       <c r="E548" t="n">
-        <v>3.415620187612745</v>
+        <v>3.41561995377915</v>
       </c>
       <c r="F548" t="n">
         <v>15610900</v>
@@ -25952,19 +25952,39 @@
         <v>46280</v>
       </c>
       <c r="B1277" t="n">
-        <v>0.27</v>
+        <v>0.2700000107288361</v>
       </c>
       <c r="C1277" t="n">
-        <v>0.28</v>
+        <v>0.2800000011920929</v>
       </c>
       <c r="D1277" t="n">
-        <v>0.27</v>
+        <v>0.2700000107288361</v>
       </c>
       <c r="E1277" t="n">
-        <v>0.27</v>
+        <v>0.2700000107288361</v>
       </c>
       <c r="F1277" t="n">
         <v>6483800</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1278" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C1278" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D1278" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E1278" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F1278" t="n">
+        <v>11076100</v>
       </c>
     </row>
   </sheetData>

--- a/database/RAIZ4.xlsx
+++ b/database/RAIZ4.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1278"/>
+  <dimension ref="A1:F1279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44413</v>
       </c>
       <c r="B2" t="n">
-        <v>6.384481430053711</v>
+        <v>6.384482383728027</v>
       </c>
       <c r="C2" t="n">
-        <v>6.70194196042671</v>
+        <v>6.701942961521317</v>
       </c>
       <c r="D2" t="n">
-        <v>6.331571411740119</v>
+        <v>6.331572357511064</v>
       </c>
       <c r="E2" t="n">
-        <v>6.596121923799527</v>
+        <v>6.59612290908739</v>
       </c>
       <c r="F2" t="n">
         <v>98849900</v>
@@ -472,16 +472,16 @@
         <v>44414</v>
       </c>
       <c r="B3" t="n">
-        <v>6.261024475097656</v>
+        <v>6.261024951934814</v>
       </c>
       <c r="C3" t="n">
-        <v>6.48148308633695</v>
+        <v>6.481483579964149</v>
       </c>
       <c r="D3" t="n">
-        <v>6.19929633306517</v>
+        <v>6.199296805201136</v>
       </c>
       <c r="E3" t="n">
-        <v>6.393299725939519</v>
+        <v>6.393300212850708</v>
       </c>
       <c r="F3" t="n">
         <v>28799900</v>
@@ -492,16 +492,16 @@
         <v>44417</v>
       </c>
       <c r="B4" t="n">
-        <v>6.234569549560547</v>
+        <v>6.234570026397705</v>
       </c>
       <c r="C4" t="n">
-        <v>6.446209610180686</v>
+        <v>6.446210103204662</v>
       </c>
       <c r="D4" t="n">
-        <v>6.234569549560547</v>
+        <v>6.234570026397705</v>
       </c>
       <c r="E4" t="n">
-        <v>6.331571033765733</v>
+        <v>6.331571518021834</v>
       </c>
       <c r="F4" t="n">
         <v>14491100</v>
@@ -512,16 +512,16 @@
         <v>44418</v>
       </c>
       <c r="B5" t="n">
-        <v>6.261024475097656</v>
+        <v>6.261024951934814</v>
       </c>
       <c r="C5" t="n">
-        <v>6.313934491336116</v>
+        <v>6.313934972202879</v>
       </c>
       <c r="D5" t="n">
-        <v>6.216933005144656</v>
+        <v>6.216933478623825</v>
       </c>
       <c r="E5" t="n">
-        <v>6.278661147177143</v>
+        <v>6.278661625357502</v>
       </c>
       <c r="F5" t="n">
         <v>9988600</v>
@@ -532,16 +532,16 @@
         <v>44419</v>
       </c>
       <c r="B6" t="n">
-        <v>6.058203220367432</v>
+        <v>6.058201789855957</v>
       </c>
       <c r="C6" t="n">
-        <v>6.296298530585189</v>
+        <v>6.296297043852743</v>
       </c>
       <c r="D6" t="n">
-        <v>5.996475071361166</v>
+        <v>5.996473655425436</v>
       </c>
       <c r="E6" t="n">
-        <v>6.287480403794928</v>
+        <v>6.287478919144688</v>
       </c>
       <c r="F6" t="n">
         <v>31978000</v>
@@ -552,16 +552,16 @@
         <v>44420</v>
       </c>
       <c r="B7" t="n">
-        <v>6.137567520141602</v>
+        <v>6.137568473815918</v>
       </c>
       <c r="C7" t="n">
-        <v>6.155204191501549</v>
+        <v>6.155205147916306</v>
       </c>
       <c r="D7" t="n">
-        <v>5.952382260616443</v>
+        <v>5.952383185516099</v>
       </c>
       <c r="E7" t="n">
-        <v>6.146385645575868</v>
+        <v>6.146386600620373</v>
       </c>
       <c r="F7" t="n">
         <v>17054100</v>
@@ -612,16 +612,16 @@
         <v>44425</v>
       </c>
       <c r="B10" t="n">
-        <v>6.014111042022705</v>
+        <v>6.014110565185547</v>
       </c>
       <c r="C10" t="n">
-        <v>6.164022543855327</v>
+        <v>6.164022055132227</v>
       </c>
       <c r="D10" t="n">
-        <v>5.961201025995057</v>
+        <v>5.961200553352942</v>
       </c>
       <c r="E10" t="n">
-        <v>6.111112527827679</v>
+        <v>6.111112043299623</v>
       </c>
       <c r="F10" t="n">
         <v>17772000</v>
@@ -632,16 +632,16 @@
         <v>44426</v>
       </c>
       <c r="B11" t="n">
-        <v>6.005292415618896</v>
+        <v>6.005292892456055</v>
       </c>
       <c r="C11" t="n">
-        <v>6.17284100771587</v>
+        <v>6.172841497856859</v>
       </c>
       <c r="D11" t="n">
-        <v>5.925927182391009</v>
+        <v>5.925927652926344</v>
       </c>
       <c r="E11" t="n">
-        <v>6.022929087392713</v>
+        <v>6.022929565630274</v>
       </c>
       <c r="F11" t="n">
         <v>8841700</v>
@@ -652,16 +652,16 @@
         <v>44427</v>
       </c>
       <c r="B12" t="n">
-        <v>6.111112594604492</v>
+        <v>6.11111307144165</v>
       </c>
       <c r="C12" t="n">
-        <v>6.111112594604492</v>
+        <v>6.11111307144165</v>
       </c>
       <c r="D12" t="n">
-        <v>5.661377243209458</v>
+        <v>5.66137768495472</v>
       </c>
       <c r="E12" t="n">
-        <v>5.908290654036534</v>
+        <v>5.908291115047926</v>
       </c>
       <c r="F12" t="n">
         <v>5423700</v>
@@ -672,16 +672,16 @@
         <v>44428</v>
       </c>
       <c r="B13" t="n">
-        <v>6.155204772949219</v>
+        <v>6.155204296112061</v>
       </c>
       <c r="C13" t="n">
-        <v>6.216933338785894</v>
+        <v>6.21693285716669</v>
       </c>
       <c r="D13" t="n">
-        <v>6.022929515008602</v>
+        <v>6.022929048418668</v>
       </c>
       <c r="E13" t="n">
-        <v>6.075839534086558</v>
+        <v>6.075839063397741</v>
       </c>
       <c r="F13" t="n">
         <v>3109200</v>
@@ -692,16 +692,16 @@
         <v>44431</v>
       </c>
       <c r="B14" t="n">
-        <v>6.322752475738525</v>
+        <v>6.322753429412842</v>
       </c>
       <c r="C14" t="n">
-        <v>6.349207271261085</v>
+        <v>6.349208228925635</v>
       </c>
       <c r="D14" t="n">
-        <v>6.181659111641157</v>
+        <v>6.181660044034058</v>
       </c>
       <c r="E14" t="n">
-        <v>6.208113907163717</v>
+        <v>6.208114843546852</v>
       </c>
       <c r="F14" t="n">
         <v>6128800</v>
@@ -712,16 +712,16 @@
         <v>44432</v>
       </c>
       <c r="B15" t="n">
-        <v>6.393300533294678</v>
+        <v>6.393299579620361</v>
       </c>
       <c r="C15" t="n">
-        <v>6.525575800840451</v>
+        <v>6.525574827434928</v>
       </c>
       <c r="D15" t="n">
-        <v>6.331571962975588</v>
+        <v>6.331571018509184</v>
       </c>
       <c r="E15" t="n">
-        <v>6.384481985895601</v>
+        <v>6.384481033536726</v>
       </c>
       <c r="F15" t="n">
         <v>6054100</v>
@@ -752,16 +752,16 @@
         <v>44434</v>
       </c>
       <c r="B17" t="n">
-        <v>6.261024475097656</v>
+        <v>6.261024951934814</v>
       </c>
       <c r="C17" t="n">
-        <v>6.507938304701895</v>
+        <v>6.507938800343913</v>
       </c>
       <c r="D17" t="n">
-        <v>6.261024475097656</v>
+        <v>6.261024951934814</v>
       </c>
       <c r="E17" t="n">
-        <v>6.472664960542923</v>
+        <v>6.472665453498537</v>
       </c>
       <c r="F17" t="n">
         <v>7968100</v>
@@ -772,16 +772,16 @@
         <v>44435</v>
       </c>
       <c r="B18" t="n">
-        <v>6.340390205383301</v>
+        <v>6.340389251708984</v>
       </c>
       <c r="C18" t="n">
-        <v>6.384481678783307</v>
+        <v>6.38448071847708</v>
       </c>
       <c r="D18" t="n">
-        <v>6.278661638033537</v>
+        <v>6.278660693643972</v>
       </c>
       <c r="E18" t="n">
-        <v>6.305116858466711</v>
+        <v>6.305115910097949</v>
       </c>
       <c r="F18" t="n">
         <v>5881000</v>
@@ -792,16 +792,16 @@
         <v>44438</v>
       </c>
       <c r="B19" t="n">
-        <v>6.269844055175781</v>
+        <v>6.269843578338623</v>
       </c>
       <c r="C19" t="n">
-        <v>6.419756002815109</v>
+        <v>6.419755514576775</v>
       </c>
       <c r="D19" t="n">
-        <v>6.252207380188302</v>
+        <v>6.252206904692456</v>
       </c>
       <c r="E19" t="n">
-        <v>6.39330078008814</v>
+        <v>6.393300293861791</v>
       </c>
       <c r="F19" t="n">
         <v>4966000</v>
@@ -812,16 +812,16 @@
         <v>44439</v>
       </c>
       <c r="B20" t="n">
-        <v>6.261024475097656</v>
+        <v>6.261024951934814</v>
       </c>
       <c r="C20" t="n">
-        <v>6.305116365542087</v>
+        <v>6.305116845737266</v>
       </c>
       <c r="D20" t="n">
-        <v>6.181659660985684</v>
+        <v>6.181660131778449</v>
       </c>
       <c r="E20" t="n">
-        <v>6.305116365542087</v>
+        <v>6.305116845737266</v>
       </c>
       <c r="F20" t="n">
         <v>3704100</v>
@@ -832,16 +832,16 @@
         <v>44440</v>
       </c>
       <c r="B21" t="n">
-        <v>6.234569549560547</v>
+        <v>6.234570026397705</v>
       </c>
       <c r="C21" t="n">
-        <v>6.305116236433927</v>
+        <v>6.305116718666691</v>
       </c>
       <c r="D21" t="n">
-        <v>6.199296206123857</v>
+        <v>6.199296680263212</v>
       </c>
       <c r="E21" t="n">
-        <v>6.261024346892354</v>
+        <v>6.261024825752847</v>
       </c>
       <c r="F21" t="n">
         <v>6468600</v>
@@ -852,16 +852,16 @@
         <v>44441</v>
       </c>
       <c r="B22" t="n">
-        <v>5.996474742889404</v>
+        <v>5.996475219726562</v>
       </c>
       <c r="C22" t="n">
-        <v>6.252206713170811</v>
+        <v>6.252207210343668</v>
       </c>
       <c r="D22" t="n">
-        <v>5.970019522984813</v>
+        <v>5.970019997718263</v>
       </c>
       <c r="E22" t="n">
-        <v>6.234570040064902</v>
+        <v>6.234570535835299</v>
       </c>
       <c r="F22" t="n">
         <v>3746900</v>
@@ -892,16 +892,16 @@
         <v>44445</v>
       </c>
       <c r="B24" t="n">
-        <v>6.111112594604492</v>
+        <v>6.11111307144165</v>
       </c>
       <c r="C24" t="n">
-        <v>6.190477829758912</v>
+        <v>6.190478312788771</v>
       </c>
       <c r="D24" t="n">
-        <v>6.067021124345374</v>
+        <v>6.067021597742168</v>
       </c>
       <c r="E24" t="n">
-        <v>6.119931140951175</v>
+        <v>6.119931618476427</v>
       </c>
       <c r="F24" t="n">
         <v>1654400</v>
@@ -952,16 +952,16 @@
         <v>44449</v>
       </c>
       <c r="B27" t="n">
-        <v>5.731924533843994</v>
+        <v>5.731924057006836</v>
       </c>
       <c r="C27" t="n">
-        <v>5.89947314759995</v>
+        <v>5.899472656824471</v>
       </c>
       <c r="D27" t="n">
-        <v>5.617285942249159</v>
+        <v>5.617285474948753</v>
       </c>
       <c r="E27" t="n">
-        <v>5.767197881951408</v>
+        <v>5.76719740217987</v>
       </c>
       <c r="F27" t="n">
         <v>5905500</v>
@@ -972,16 +972,16 @@
         <v>44452</v>
       </c>
       <c r="B28" t="n">
-        <v>6.128749847412109</v>
+        <v>6.128749370574951</v>
       </c>
       <c r="C28" t="n">
-        <v>6.172841742339696</v>
+        <v>6.172841262072042</v>
       </c>
       <c r="D28" t="n">
-        <v>5.92592788762986</v>
+        <v>5.925927426572926</v>
       </c>
       <c r="E28" t="n">
-        <v>5.952383108684708</v>
+        <v>5.952382645569469</v>
       </c>
       <c r="F28" t="n">
         <v>8999600</v>
@@ -992,16 +992,16 @@
         <v>44453</v>
       </c>
       <c r="B29" t="n">
-        <v>6.340390205383301</v>
+        <v>6.340389251708984</v>
       </c>
       <c r="C29" t="n">
-        <v>6.507938813482836</v>
+        <v>6.507937834607105</v>
       </c>
       <c r="D29" t="n">
-        <v>6.225751617658651</v>
+        <v>6.225750681227418</v>
       </c>
       <c r="E29" t="n">
-        <v>6.225751617658651</v>
+        <v>6.225750681227418</v>
       </c>
       <c r="F29" t="n">
         <v>9730300</v>
@@ -1012,16 +1012,16 @@
         <v>44454</v>
       </c>
       <c r="B30" t="n">
-        <v>6.384481430053711</v>
+        <v>6.384482383728027</v>
       </c>
       <c r="C30" t="n">
-        <v>6.50793855994354</v>
+        <v>6.507939532059118</v>
       </c>
       <c r="D30" t="n">
-        <v>6.296298066197724</v>
+        <v>6.296299006699756</v>
       </c>
       <c r="E30" t="n">
-        <v>6.384481430053711</v>
+        <v>6.384482383728027</v>
       </c>
       <c r="F30" t="n">
         <v>7265900</v>
@@ -1052,16 +1052,16 @@
         <v>44456</v>
       </c>
       <c r="B32" t="n">
-        <v>6.384481430053711</v>
+        <v>6.384482383728027</v>
       </c>
       <c r="C32" t="n">
-        <v>6.384481430053711</v>
+        <v>6.384482383728027</v>
       </c>
       <c r="D32" t="n">
-        <v>5.978837956316171</v>
+        <v>5.978838849397976</v>
       </c>
       <c r="E32" t="n">
-        <v>6.261024720655329</v>
+        <v>6.261025655888447</v>
       </c>
       <c r="F32" t="n">
         <v>16008100</v>
@@ -1072,16 +1072,16 @@
         <v>44459</v>
       </c>
       <c r="B33" t="n">
-        <v>6.269844055175781</v>
+        <v>6.269843578338623</v>
       </c>
       <c r="C33" t="n">
-        <v>6.32275408013822</v>
+        <v>6.322753599277124</v>
       </c>
       <c r="D33" t="n">
-        <v>6.067022082574015</v>
+        <v>6.067021621161969</v>
       </c>
       <c r="E33" t="n">
-        <v>6.164023584759403</v>
+        <v>6.164023115970153</v>
       </c>
       <c r="F33" t="n">
         <v>9065700</v>
@@ -1092,16 +1092,16 @@
         <v>44460</v>
       </c>
       <c r="B34" t="n">
-        <v>6.419754505157471</v>
+        <v>6.419754981994629</v>
       </c>
       <c r="C34" t="n">
-        <v>6.525574530395708</v>
+        <v>6.525575015092812</v>
       </c>
       <c r="D34" t="n">
-        <v>6.269842592490932</v>
+        <v>6.269843058193152</v>
       </c>
       <c r="E34" t="n">
-        <v>6.34920740117391</v>
+        <v>6.349207872771073</v>
       </c>
       <c r="F34" t="n">
         <v>11102500</v>
@@ -1112,16 +1112,16 @@
         <v>44461</v>
       </c>
       <c r="B35" t="n">
-        <v>6.44620943069458</v>
+        <v>6.446209907531738</v>
       </c>
       <c r="C35" t="n">
-        <v>6.560848003917575</v>
+        <v>6.560848489234745</v>
       </c>
       <c r="D35" t="n">
-        <v>6.402117962872096</v>
+        <v>6.402118436447734</v>
       </c>
       <c r="E35" t="n">
-        <v>6.463846101921855</v>
+        <v>6.463846580063628</v>
       </c>
       <c r="F35" t="n">
         <v>10254600</v>
@@ -1132,16 +1132,16 @@
         <v>44462</v>
       </c>
       <c r="B36" t="n">
-        <v>6.375663757324219</v>
+        <v>6.375664234161377</v>
       </c>
       <c r="C36" t="n">
-        <v>6.54321237081167</v>
+        <v>6.543212860179822</v>
       </c>
       <c r="D36" t="n">
-        <v>6.340390409273332</v>
+        <v>6.34039088347239</v>
       </c>
       <c r="E36" t="n">
-        <v>6.507939022760783</v>
+        <v>6.507939509490835</v>
       </c>
       <c r="F36" t="n">
         <v>6341600</v>
@@ -1172,16 +1172,16 @@
         <v>44466</v>
       </c>
       <c r="B38" t="n">
-        <v>6.305116653442383</v>
+        <v>6.305117130279541</v>
       </c>
       <c r="C38" t="n">
-        <v>6.340389999211985</v>
+        <v>6.340390478716762</v>
       </c>
       <c r="D38" t="n">
-        <v>6.102294705021446</v>
+        <v>6.102295166519786</v>
       </c>
       <c r="E38" t="n">
-        <v>6.17284139656065</v>
+        <v>6.172841863394225</v>
       </c>
       <c r="F38" t="n">
         <v>6343700</v>
@@ -1192,16 +1192,16 @@
         <v>44467</v>
       </c>
       <c r="B39" t="n">
-        <v>6.119932174682617</v>
+        <v>6.119931221008301</v>
       </c>
       <c r="C39" t="n">
-        <v>6.278662251311475</v>
+        <v>6.278661272902115</v>
       </c>
       <c r="D39" t="n">
-        <v>6.119932174682617</v>
+        <v>6.119931221008301</v>
       </c>
       <c r="E39" t="n">
-        <v>6.261025576130491</v>
+        <v>6.261024600469469</v>
       </c>
       <c r="F39" t="n">
         <v>6782400</v>
@@ -1232,16 +1232,16 @@
         <v>44469</v>
       </c>
       <c r="B41" t="n">
-        <v>6.261024475097656</v>
+        <v>6.261024951934814</v>
       </c>
       <c r="C41" t="n">
-        <v>6.349207835495088</v>
+        <v>6.349208319048255</v>
       </c>
       <c r="D41" t="n">
-        <v>6.058202535937849</v>
+        <v>6.058202997328168</v>
       </c>
       <c r="E41" t="n">
-        <v>6.084657754302794</v>
+        <v>6.084658217707932</v>
       </c>
       <c r="F41" t="n">
         <v>15990100</v>
@@ -1252,16 +1252,16 @@
         <v>44470</v>
       </c>
       <c r="B42" t="n">
-        <v>6.499119758605957</v>
+        <v>6.499119281768799</v>
       </c>
       <c r="C42" t="n">
-        <v>6.569666446925959</v>
+        <v>6.569665964912827</v>
       </c>
       <c r="D42" t="n">
-        <v>6.331571163600236</v>
+        <v>6.331570699056035</v>
       </c>
       <c r="E42" t="n">
-        <v>6.331571163600236</v>
+        <v>6.331570699056035</v>
       </c>
       <c r="F42" t="n">
         <v>15528000</v>
@@ -1292,16 +1292,16 @@
         <v>44474</v>
       </c>
       <c r="B44" t="n">
-        <v>6.287479877471924</v>
+        <v>6.287480354309082</v>
       </c>
       <c r="C44" t="n">
-        <v>6.366844693906587</v>
+        <v>6.366845176762705</v>
       </c>
       <c r="D44" t="n">
-        <v>6.2433879857371</v>
+        <v>6.243388459230366</v>
       </c>
       <c r="E44" t="n">
-        <v>6.296298003524023</v>
+        <v>6.29629848102994</v>
       </c>
       <c r="F44" t="n">
         <v>12888200</v>
@@ -1312,16 +1312,16 @@
         <v>44475</v>
       </c>
       <c r="B45" t="n">
-        <v>6.178094387054443</v>
+        <v>6.178093910217285</v>
       </c>
       <c r="C45" t="n">
-        <v>6.275317738941888</v>
+        <v>6.275317254600846</v>
       </c>
       <c r="D45" t="n">
-        <v>6.080871456618367</v>
+        <v>6.080870987285061</v>
       </c>
       <c r="E45" t="n">
-        <v>6.248802547532548</v>
+        <v>6.248802065237998</v>
       </c>
       <c r="F45" t="n">
         <v>10376100</v>
@@ -1332,16 +1332,16 @@
         <v>44476</v>
       </c>
       <c r="B46" t="n">
-        <v>6.301832675933838</v>
+        <v>6.301833152770996</v>
       </c>
       <c r="C46" t="n">
-        <v>6.478602004542243</v>
+        <v>6.478602494754905</v>
       </c>
       <c r="D46" t="n">
-        <v>6.213448011629635</v>
+        <v>6.213448481779042</v>
       </c>
       <c r="E46" t="n">
-        <v>6.284155743072997</v>
+        <v>6.284156218572606</v>
       </c>
       <c r="F46" t="n">
         <v>18438800</v>
@@ -1352,16 +1352,16 @@
         <v>44477</v>
       </c>
       <c r="B47" t="n">
-        <v>6.310670852661133</v>
+        <v>6.310671329498291</v>
       </c>
       <c r="C47" t="n">
-        <v>6.655371671310609</v>
+        <v>6.655372174193518</v>
       </c>
       <c r="D47" t="n">
-        <v>6.292993920021518</v>
+        <v>6.292994395522999</v>
       </c>
       <c r="E47" t="n">
-        <v>6.363701650579979</v>
+        <v>6.363702131424168</v>
       </c>
       <c r="F47" t="n">
         <v>20480700</v>
@@ -1392,16 +1392,16 @@
         <v>44482</v>
       </c>
       <c r="B49" t="n">
-        <v>6.231125354766846</v>
+        <v>6.231124401092529</v>
       </c>
       <c r="C49" t="n">
-        <v>6.292994413127774</v>
+        <v>6.292993449984393</v>
       </c>
       <c r="D49" t="n">
-        <v>6.213448420742101</v>
+        <v>6.213447469773242</v>
       </c>
       <c r="E49" t="n">
-        <v>6.248802288791589</v>
+        <v>6.248801332411817</v>
       </c>
       <c r="F49" t="n">
         <v>8146000</v>
@@ -1412,16 +1412,16 @@
         <v>44483</v>
       </c>
       <c r="B50" t="n">
-        <v>6.319509983062744</v>
+        <v>6.319509506225586</v>
       </c>
       <c r="C50" t="n">
-        <v>6.381379041014171</v>
+        <v>6.381378559508698</v>
       </c>
       <c r="D50" t="n">
-        <v>6.239963569752225</v>
+        <v>6.239963098917224</v>
       </c>
       <c r="E50" t="n">
-        <v>6.248802247431771</v>
+        <v>6.24880177592985</v>
       </c>
       <c r="F50" t="n">
         <v>10992200</v>
@@ -1432,16 +1432,16 @@
         <v>44484</v>
       </c>
       <c r="B51" t="n">
-        <v>6.275317668914795</v>
+        <v>6.275316715240479</v>
       </c>
       <c r="C51" t="n">
-        <v>6.354864085157887</v>
+        <v>6.354863119394721</v>
       </c>
       <c r="D51" t="n">
-        <v>6.222286865236521</v>
+        <v>6.222285919621418</v>
       </c>
       <c r="E51" t="n">
-        <v>6.337187150598463</v>
+        <v>6.3371861875217</v>
       </c>
       <c r="F51" t="n">
         <v>34203500</v>
@@ -1452,16 +1452,16 @@
         <v>44487</v>
       </c>
       <c r="B52" t="n">
-        <v>6.16925573348999</v>
+        <v>6.169255256652832</v>
       </c>
       <c r="C52" t="n">
-        <v>6.266479079122371</v>
+        <v>6.266478594770578</v>
       </c>
       <c r="D52" t="n">
-        <v>6.151578799870589</v>
+        <v>6.151578324399725</v>
       </c>
       <c r="E52" t="n">
-        <v>6.257640401587</v>
+        <v>6.25763991791837</v>
       </c>
       <c r="F52" t="n">
         <v>7596500</v>
@@ -1472,16 +1472,16 @@
         <v>44488</v>
       </c>
       <c r="B53" t="n">
-        <v>5.912939548492432</v>
+        <v>5.912939071655273</v>
       </c>
       <c r="C53" t="n">
-        <v>6.186932210078912</v>
+        <v>6.186931711146165</v>
       </c>
       <c r="D53" t="n">
-        <v>5.89526261617883</v>
+        <v>5.895262140767192</v>
       </c>
       <c r="E53" t="n">
-        <v>6.169255277765311</v>
+        <v>6.169254780258083</v>
       </c>
       <c r="F53" t="n">
         <v>11473400</v>
@@ -1512,16 +1512,16 @@
         <v>44490</v>
       </c>
       <c r="B55" t="n">
-        <v>5.683139324188232</v>
+        <v>5.683138847351074</v>
       </c>
       <c r="C55" t="n">
-        <v>5.84223214534227</v>
+        <v>5.842231655156614</v>
       </c>
       <c r="D55" t="n">
-        <v>5.471016124584628</v>
+        <v>5.471015665545419</v>
       </c>
       <c r="E55" t="n">
-        <v>5.798039601365852</v>
+        <v>5.79803911488812</v>
       </c>
       <c r="F55" t="n">
         <v>12472300</v>
@@ -1532,16 +1532,16 @@
         <v>44491</v>
       </c>
       <c r="B56" t="n">
-        <v>5.630108833312988</v>
+        <v>5.63010835647583</v>
       </c>
       <c r="C56" t="n">
-        <v>5.656624445444495</v>
+        <v>5.656623966361621</v>
       </c>
       <c r="D56" t="n">
-        <v>5.197023732958769</v>
+        <v>5.197023292801376</v>
       </c>
       <c r="E56" t="n">
-        <v>5.603593642632838</v>
+        <v>5.60359316804136</v>
       </c>
       <c r="F56" t="n">
         <v>18890200</v>
@@ -1572,16 +1572,16 @@
         <v>44495</v>
       </c>
       <c r="B58" t="n">
-        <v>5.815715789794922</v>
+        <v>5.815716743469238</v>
       </c>
       <c r="C58" t="n">
-        <v>5.86874658290369</v>
+        <v>5.868747545274117</v>
       </c>
       <c r="D58" t="n">
-        <v>5.68313859629736</v>
+        <v>5.683139528231368</v>
       </c>
       <c r="E58" t="n">
-        <v>5.833392720831178</v>
+        <v>5.833393677404199</v>
       </c>
       <c r="F58" t="n">
         <v>8470300</v>
@@ -1612,16 +1612,16 @@
         <v>44497</v>
       </c>
       <c r="B60" t="n">
-        <v>5.992486000061035</v>
+        <v>5.992486953735352</v>
       </c>
       <c r="C60" t="n">
-        <v>6.027839864956272</v>
+        <v>6.02784082425698</v>
       </c>
       <c r="D60" t="n">
-        <v>5.727331591895446</v>
+        <v>5.727332503371757</v>
       </c>
       <c r="E60" t="n">
-        <v>5.75384720129253</v>
+        <v>5.753848116988669</v>
       </c>
       <c r="F60" t="n">
         <v>8299700</v>
@@ -1632,16 +1632,16 @@
         <v>44498</v>
       </c>
       <c r="B61" t="n">
-        <v>5.992486000061035</v>
+        <v>5.992486953735352</v>
       </c>
       <c r="C61" t="n">
-        <v>6.019001188006806</v>
+        <v>6.019002145900882</v>
       </c>
       <c r="D61" t="n">
-        <v>5.842231863530622</v>
+        <v>5.84223279329274</v>
       </c>
       <c r="E61" t="n">
-        <v>5.957131713714485</v>
+        <v>5.957132661762342</v>
       </c>
       <c r="F61" t="n">
         <v>3926300</v>
@@ -1652,16 +1652,16 @@
         <v>44501</v>
       </c>
       <c r="B62" t="n">
-        <v>6.001325130462646</v>
+        <v>6.001323699951172</v>
       </c>
       <c r="C62" t="n">
-        <v>6.063194613774614</v>
+        <v>6.063193168515561</v>
       </c>
       <c r="D62" t="n">
-        <v>5.948294325388693</v>
+        <v>5.948292907517955</v>
       </c>
       <c r="E62" t="n">
-        <v>5.965971260413344</v>
+        <v>5.965969838329028</v>
       </c>
       <c r="F62" t="n">
         <v>5059700</v>
@@ -1672,16 +1672,16 @@
         <v>44503</v>
       </c>
       <c r="B63" t="n">
-        <v>6.098548412322998</v>
+        <v>6.098547458648682</v>
       </c>
       <c r="C63" t="n">
-        <v>6.18693308641001</v>
+        <v>6.186932118914339</v>
       </c>
       <c r="D63" t="n">
-        <v>5.921778642697604</v>
+        <v>5.92177771666606</v>
       </c>
       <c r="E63" t="n">
-        <v>5.983648125284198</v>
+        <v>5.983647189577673</v>
       </c>
       <c r="F63" t="n">
         <v>5711600</v>
@@ -1692,16 +1692,16 @@
         <v>44504</v>
       </c>
       <c r="B64" t="n">
-        <v>5.965970993041992</v>
+        <v>5.965971946716309</v>
       </c>
       <c r="C64" t="n">
-        <v>6.160417269598838</v>
+        <v>6.160418254355843</v>
       </c>
       <c r="D64" t="n">
-        <v>5.842232453414908</v>
+        <v>5.842233387309332</v>
       </c>
       <c r="E64" t="n">
-        <v>6.098548210510975</v>
+        <v>6.098549185378067</v>
       </c>
       <c r="F64" t="n">
         <v>8687600</v>
@@ -1712,16 +1712,16 @@
         <v>44505</v>
       </c>
       <c r="B65" t="n">
-        <v>5.965970993041992</v>
+        <v>5.965971946716309</v>
       </c>
       <c r="C65" t="n">
-        <v>6.054355664204195</v>
+        <v>6.054356632007006</v>
       </c>
       <c r="D65" t="n">
-        <v>5.939455380967654</v>
+        <v>5.939456330403387</v>
       </c>
       <c r="E65" t="n">
-        <v>6.001324861506873</v>
+        <v>6.001325820832587</v>
       </c>
       <c r="F65" t="n">
         <v>3123600</v>
@@ -1752,16 +1752,16 @@
         <v>44509</v>
       </c>
       <c r="B67" t="n">
-        <v>5.948294162750244</v>
+        <v>5.948293685913086</v>
       </c>
       <c r="C67" t="n">
-        <v>6.169256055242525</v>
+        <v>6.169255560692247</v>
       </c>
       <c r="D67" t="n">
-        <v>5.948294162750244</v>
+        <v>5.948293685913086</v>
       </c>
       <c r="E67" t="n">
-        <v>5.992486709829246</v>
+        <v>5.99248622944945</v>
       </c>
       <c r="F67" t="n">
         <v>5176300</v>
@@ -1772,16 +1772,16 @@
         <v>44510</v>
       </c>
       <c r="B68" t="n">
-        <v>5.74500846862793</v>
+        <v>5.745008945465088</v>
       </c>
       <c r="C68" t="n">
-        <v>6.010162874222051</v>
+        <v>6.010163373067091</v>
       </c>
       <c r="D68" t="n">
-        <v>5.74500846862793</v>
+        <v>5.745008945465088</v>
       </c>
       <c r="E68" t="n">
-        <v>5.957131655942178</v>
+        <v>5.957132150385616</v>
       </c>
       <c r="F68" t="n">
         <v>10074000</v>
@@ -1852,16 +1852,16 @@
         <v>44517</v>
       </c>
       <c r="B72" t="n">
-        <v>5.17050838470459</v>
+        <v>5.170507907867432</v>
       </c>
       <c r="C72" t="n">
-        <v>5.462178025779772</v>
+        <v>5.462177522044113</v>
       </c>
       <c r="D72" t="n">
-        <v>5.002577289838284</v>
+        <v>5.002576828488149</v>
       </c>
       <c r="E72" t="n">
-        <v>5.364955093055631</v>
+        <v>5.364954598286112</v>
       </c>
       <c r="F72" t="n">
         <v>24600900</v>
@@ -1872,16 +1872,16 @@
         <v>44518</v>
       </c>
       <c r="B73" t="n">
-        <v>5.161669254302979</v>
+        <v>5.161669731140137</v>
       </c>
       <c r="C73" t="n">
-        <v>5.338438576114187</v>
+        <v>5.338439069281368</v>
       </c>
       <c r="D73" t="n">
-        <v>5.073284171946066</v>
+        <v>5.073284640618174</v>
       </c>
       <c r="E73" t="n">
-        <v>5.214700050846341</v>
+        <v>5.214700532582506</v>
       </c>
       <c r="F73" t="n">
         <v>17735600</v>
@@ -1892,16 +1892,16 @@
         <v>44519</v>
       </c>
       <c r="B74" t="n">
-        <v>5.241215705871582</v>
+        <v>5.241215229034424</v>
       </c>
       <c r="C74" t="n">
-        <v>5.285408250991699</v>
+        <v>5.285407770133975</v>
       </c>
       <c r="D74" t="n">
-        <v>5.090961979656143</v>
+        <v>5.090961516488821</v>
       </c>
       <c r="E74" t="n">
-        <v>5.161669714687254</v>
+        <v>5.161669245087059</v>
       </c>
       <c r="F74" t="n">
         <v>11364600</v>
@@ -1912,16 +1912,16 @@
         <v>44522</v>
       </c>
       <c r="B75" t="n">
-        <v>4.976061820983887</v>
+        <v>4.97606086730957</v>
       </c>
       <c r="C75" t="n">
-        <v>5.329600926221622</v>
+        <v>5.329599904790679</v>
       </c>
       <c r="D75" t="n">
-        <v>4.976061820983887</v>
+        <v>4.97606086730957</v>
       </c>
       <c r="E75" t="n">
-        <v>5.23237757745469</v>
+        <v>5.232376574656837</v>
       </c>
       <c r="F75" t="n">
         <v>8516000</v>
@@ -1972,16 +1972,16 @@
         <v>44525</v>
       </c>
       <c r="B78" t="n">
-        <v>5.37379264831543</v>
+        <v>5.373793125152588</v>
       </c>
       <c r="C78" t="n">
-        <v>5.37379264831543</v>
+        <v>5.373793125152588</v>
       </c>
       <c r="D78" t="n">
-        <v>4.799291698032407</v>
+        <v>4.799292123891901</v>
       </c>
       <c r="E78" t="n">
-        <v>4.949545838108879</v>
+        <v>4.949546277300996</v>
       </c>
       <c r="F78" t="n">
         <v>20546100</v>
@@ -1992,16 +1992,16 @@
         <v>44526</v>
       </c>
       <c r="B79" t="n">
-        <v>5.223538398742676</v>
+        <v>5.223538875579834</v>
       </c>
       <c r="C79" t="n">
-        <v>5.338438670680995</v>
+        <v>5.338439158006967</v>
       </c>
       <c r="D79" t="n">
-        <v>5.020253464333078</v>
+        <v>5.02025392261312</v>
       </c>
       <c r="E79" t="n">
-        <v>5.037930396827334</v>
+        <v>5.037930856721036</v>
       </c>
       <c r="F79" t="n">
         <v>8564200</v>
@@ -2032,16 +2032,16 @@
         <v>44530</v>
       </c>
       <c r="B81" t="n">
-        <v>4.825807094573975</v>
+        <v>4.825807571411133</v>
       </c>
       <c r="C81" t="n">
-        <v>5.126315361433205</v>
+        <v>5.126315867963532</v>
       </c>
       <c r="D81" t="n">
-        <v>4.790453230408336</v>
+        <v>4.790453703752186</v>
       </c>
       <c r="E81" t="n">
-        <v>5.073284143733442</v>
+        <v>5.073284645023764</v>
       </c>
       <c r="F81" t="n">
         <v>11282700</v>
@@ -2052,16 +2052,16 @@
         <v>44531</v>
       </c>
       <c r="B82" t="n">
-        <v>4.852322578430176</v>
+        <v>4.852322101593018</v>
       </c>
       <c r="C82" t="n">
-        <v>5.152830863649267</v>
+        <v>5.152830357281196</v>
       </c>
       <c r="D82" t="n">
-        <v>4.852322578430176</v>
+        <v>4.852322101593018</v>
       </c>
       <c r="E82" t="n">
-        <v>4.896515122062865</v>
+        <v>4.896514640882911</v>
       </c>
       <c r="F82" t="n">
         <v>12492100</v>
@@ -2112,16 +2112,16 @@
         <v>44536</v>
       </c>
       <c r="B85" t="n">
-        <v>5.152831077575684</v>
+        <v>5.152831554412842</v>
       </c>
       <c r="C85" t="n">
-        <v>5.417985507477384</v>
+        <v>5.417986008851633</v>
       </c>
       <c r="D85" t="n">
-        <v>5.152831077575684</v>
+        <v>5.152831554412842</v>
       </c>
       <c r="E85" t="n">
-        <v>5.373792962009984</v>
+        <v>5.373793459294705</v>
       </c>
       <c r="F85" t="n">
         <v>5884400</v>
@@ -2152,16 +2152,16 @@
         <v>44538</v>
       </c>
       <c r="B87" t="n">
-        <v>5.285407543182373</v>
+        <v>5.285408020019531</v>
       </c>
       <c r="C87" t="n">
-        <v>5.338438337353947</v>
+        <v>5.33843881897542</v>
       </c>
       <c r="D87" t="n">
-        <v>5.12631516066765</v>
+        <v>5.126315623151864</v>
       </c>
       <c r="E87" t="n">
-        <v>5.223538072589892</v>
+        <v>5.223538543845331</v>
       </c>
       <c r="F87" t="n">
         <v>9204000</v>
@@ -2192,16 +2192,16 @@
         <v>44540</v>
       </c>
       <c r="B89" t="n">
-        <v>5.444499969482422</v>
+        <v>5.444500923156738</v>
       </c>
       <c r="C89" t="n">
-        <v>5.568238911662507</v>
+        <v>5.568239887011294</v>
       </c>
       <c r="D89" t="n">
-        <v>5.2412150461309</v>
+        <v>5.241215964197243</v>
       </c>
       <c r="E89" t="n">
-        <v>5.267730654155574</v>
+        <v>5.267731576866467</v>
       </c>
       <c r="F89" t="n">
         <v>8741300</v>
@@ -2212,16 +2212,16 @@
         <v>44543</v>
       </c>
       <c r="B90" t="n">
-        <v>5.497530937194824</v>
+        <v>5.497531414031982</v>
       </c>
       <c r="C90" t="n">
-        <v>5.621269883271384</v>
+        <v>5.621270370841238</v>
       </c>
       <c r="D90" t="n">
-        <v>5.426823208837535</v>
+        <v>5.426823679541746</v>
       </c>
       <c r="E90" t="n">
-        <v>5.444500140926858</v>
+        <v>5.444500613164305</v>
       </c>
       <c r="F90" t="n">
         <v>8265100</v>
@@ -2252,16 +2252,16 @@
         <v>44545</v>
       </c>
       <c r="B92" t="n">
-        <v>5.479853630065918</v>
+        <v>5.479854583740234</v>
       </c>
       <c r="C92" t="n">
-        <v>5.524046167990352</v>
+        <v>5.524047129355619</v>
       </c>
       <c r="D92" t="n">
-        <v>5.329599928315653</v>
+        <v>5.329600855840895</v>
       </c>
       <c r="E92" t="n">
-        <v>5.479853630065918</v>
+        <v>5.479854583740234</v>
       </c>
       <c r="F92" t="n">
         <v>4791400</v>
@@ -2272,16 +2272,16 @@
         <v>44546</v>
       </c>
       <c r="B93" t="n">
-        <v>5.400308132171631</v>
+        <v>5.400308609008789</v>
       </c>
       <c r="C93" t="n">
-        <v>5.550562268737735</v>
+        <v>5.550562758842054</v>
       </c>
       <c r="D93" t="n">
-        <v>5.347277334816178</v>
+        <v>5.347277806970816</v>
       </c>
       <c r="E93" t="n">
-        <v>5.515207982382787</v>
+        <v>5.515208469365389</v>
       </c>
       <c r="F93" t="n">
         <v>9238300</v>
@@ -2292,16 +2292,16 @@
         <v>44547</v>
       </c>
       <c r="B94" t="n">
-        <v>5.241215705871582</v>
+        <v>5.241215229034424</v>
       </c>
       <c r="C94" t="n">
-        <v>5.347277729869593</v>
+        <v>5.347277243383087</v>
       </c>
       <c r="D94" t="n">
-        <v>5.241215705871582</v>
+        <v>5.241215229034424</v>
       </c>
       <c r="E94" t="n">
-        <v>5.320762118507254</v>
+        <v>5.320761634433095</v>
       </c>
       <c r="F94" t="n">
         <v>50153800</v>
@@ -2332,16 +2332,16 @@
         <v>44551</v>
       </c>
       <c r="B96" t="n">
-        <v>5.082122325897217</v>
+        <v>5.082123279571533</v>
       </c>
       <c r="C96" t="n">
-        <v>5.223537768796909</v>
+        <v>5.223538749008224</v>
       </c>
       <c r="D96" t="n">
-        <v>5.020252858902969</v>
+        <v>5.020253800967309</v>
       </c>
       <c r="E96" t="n">
-        <v>5.170506977709524</v>
+        <v>5.170507947969465</v>
       </c>
       <c r="F96" t="n">
         <v>5049800</v>
@@ -2372,16 +2372,16 @@
         <v>44553</v>
       </c>
       <c r="B98" t="n">
-        <v>5.055607318878174</v>
+        <v>5.055607795715332</v>
       </c>
       <c r="C98" t="n">
-        <v>5.073284251335914</v>
+        <v>5.073284729840333</v>
       </c>
       <c r="D98" t="n">
-        <v>4.967222656589472</v>
+        <v>4.967223125090324</v>
       </c>
       <c r="E98" t="n">
-        <v>4.993738266001739</v>
+        <v>4.993738737003503</v>
       </c>
       <c r="F98" t="n">
         <v>3174500</v>
@@ -2412,16 +2412,16 @@
         <v>44558</v>
       </c>
       <c r="B100" t="n">
-        <v>5.347277641296387</v>
+        <v>5.347278118133545</v>
       </c>
       <c r="C100" t="n">
-        <v>5.347277641296387</v>
+        <v>5.347278118133545</v>
       </c>
       <c r="D100" t="n">
-        <v>5.188184818660282</v>
+        <v>5.188185281310526</v>
       </c>
       <c r="E100" t="n">
-        <v>5.214700429583412</v>
+        <v>5.214700894598154</v>
       </c>
       <c r="F100" t="n">
         <v>4379800</v>
@@ -2452,16 +2452,16 @@
         <v>44560</v>
       </c>
       <c r="B102" t="n">
-        <v>5.70081615447998</v>
+        <v>5.700816631317139</v>
       </c>
       <c r="C102" t="n">
-        <v>5.70965483169609</v>
+        <v>5.709655309272549</v>
       </c>
       <c r="D102" t="n">
-        <v>5.258892408506298</v>
+        <v>5.258892848379334</v>
       </c>
       <c r="E102" t="n">
-        <v>5.320761884665091</v>
+        <v>5.320762329713117</v>
       </c>
       <c r="F102" t="n">
         <v>23096200</v>
@@ -2472,16 +2472,16 @@
         <v>44564</v>
       </c>
       <c r="B103" t="n">
-        <v>5.541723728179932</v>
+        <v>5.54172420501709</v>
       </c>
       <c r="C103" t="n">
-        <v>5.745008667104768</v>
+        <v>5.745009161433563</v>
       </c>
       <c r="D103" t="n">
-        <v>5.506369862406162</v>
+        <v>5.5063703362013</v>
       </c>
       <c r="E103" t="n">
-        <v>5.691977868444114</v>
+        <v>5.691978358209878</v>
       </c>
       <c r="F103" t="n">
         <v>7451800</v>
@@ -2492,16 +2492,16 @@
         <v>44565</v>
       </c>
       <c r="B104" t="n">
-        <v>5.594754219055176</v>
+        <v>5.594754695892334</v>
       </c>
       <c r="C104" t="n">
-        <v>5.612431150969596</v>
+        <v>5.612431629313347</v>
       </c>
       <c r="D104" t="n">
-        <v>5.444500087056956</v>
+        <v>5.444500551088055</v>
       </c>
       <c r="E104" t="n">
-        <v>5.532885168080356</v>
+        <v>5.532885639644457</v>
       </c>
       <c r="F104" t="n">
         <v>10613100</v>
@@ -2552,16 +2552,16 @@
         <v>44568</v>
       </c>
       <c r="B107" t="n">
-        <v>5.16362190246582</v>
+        <v>5.163622856140137</v>
       </c>
       <c r="C107" t="n">
-        <v>5.278960211098854</v>
+        <v>5.278961186075115</v>
       </c>
       <c r="D107" t="n">
-        <v>4.941816844469068</v>
+        <v>4.941817757177995</v>
       </c>
       <c r="E107" t="n">
-        <v>4.977305619903783</v>
+        <v>4.977306539167166</v>
       </c>
       <c r="F107" t="n">
         <v>10961100</v>
@@ -2572,16 +2572,16 @@
         <v>44571</v>
       </c>
       <c r="B108" t="n">
-        <v>5.057155609130859</v>
+        <v>5.057155132293701</v>
       </c>
       <c r="C108" t="n">
-        <v>5.128133589460298</v>
+        <v>5.128133105930655</v>
       </c>
       <c r="D108" t="n">
-        <v>4.906328511462285</v>
+        <v>4.906328048846553</v>
       </c>
       <c r="E108" t="n">
-        <v>5.057155609130859</v>
+        <v>5.057155132293701</v>
       </c>
       <c r="F108" t="n">
         <v>11253600</v>
@@ -2592,16 +2592,16 @@
         <v>44572</v>
       </c>
       <c r="B109" t="n">
-        <v>5.234600067138672</v>
+        <v>5.23460054397583</v>
       </c>
       <c r="C109" t="n">
-        <v>5.234600067138672</v>
+        <v>5.23460054397583</v>
       </c>
       <c r="D109" t="n">
-        <v>5.021666966502512</v>
+        <v>5.021667423942884</v>
       </c>
       <c r="E109" t="n">
-        <v>5.021666966502512</v>
+        <v>5.021667423942884</v>
       </c>
       <c r="F109" t="n">
         <v>5425200</v>
@@ -2612,16 +2612,16 @@
         <v>44573</v>
       </c>
       <c r="B110" t="n">
-        <v>5.438660144805908</v>
+        <v>5.438660621643066</v>
       </c>
       <c r="C110" t="n">
-        <v>5.518509678315355</v>
+        <v>5.51851016215336</v>
       </c>
       <c r="D110" t="n">
-        <v>5.225727068308373</v>
+        <v>5.225727526476521</v>
       </c>
       <c r="E110" t="n">
-        <v>5.261215843881367</v>
+        <v>5.261216305161009</v>
       </c>
       <c r="F110" t="n">
         <v>9077500</v>
@@ -2632,16 +2632,16 @@
         <v>44574</v>
       </c>
       <c r="B111" t="n">
-        <v>5.42091703414917</v>
+        <v>5.420916557312012</v>
       </c>
       <c r="C111" t="n">
-        <v>5.50963899398392</v>
+        <v>5.50963850934256</v>
       </c>
       <c r="D111" t="n">
-        <v>5.358811450735008</v>
+        <v>5.358810979360809</v>
       </c>
       <c r="E111" t="n">
-        <v>5.358811450735008</v>
+        <v>5.358810979360809</v>
       </c>
       <c r="F111" t="n">
         <v>4388600</v>
@@ -2652,16 +2652,16 @@
         <v>44575</v>
       </c>
       <c r="B112" t="n">
-        <v>5.491893768310547</v>
+        <v>5.491894721984863</v>
       </c>
       <c r="C112" t="n">
-        <v>5.500765751417357</v>
+        <v>5.500766706632305</v>
       </c>
       <c r="D112" t="n">
-        <v>5.332194264851456</v>
+        <v>5.332195190793751</v>
       </c>
       <c r="E112" t="n">
-        <v>5.420916211217618</v>
+        <v>5.420917152566591</v>
       </c>
       <c r="F112" t="n">
         <v>4745900</v>
@@ -2732,16 +2732,16 @@
         <v>44581</v>
       </c>
       <c r="B116" t="n">
-        <v>5.713698863983154</v>
+        <v>5.713699340820312</v>
       </c>
       <c r="C116" t="n">
-        <v>5.837909589292028</v>
+        <v>5.837910076495201</v>
       </c>
       <c r="D116" t="n">
-        <v>5.633848900469072</v>
+        <v>5.633849370642346</v>
       </c>
       <c r="E116" t="n">
-        <v>5.651593289798911</v>
+        <v>5.651593761453044</v>
       </c>
       <c r="F116" t="n">
         <v>9343500</v>
@@ -2752,16 +2752,16 @@
         <v>44582</v>
       </c>
       <c r="B117" t="n">
-        <v>5.527382373809814</v>
+        <v>5.527382850646973</v>
       </c>
       <c r="C117" t="n">
-        <v>5.687081872269151</v>
+        <v>5.687082362883293</v>
       </c>
       <c r="D117" t="n">
-        <v>5.483021190485755</v>
+        <v>5.483021663495955</v>
       </c>
       <c r="E117" t="n">
-        <v>5.678209889440098</v>
+        <v>5.678210379288871</v>
       </c>
       <c r="F117" t="n">
         <v>7609900</v>
@@ -2792,16 +2792,16 @@
         <v>44586</v>
       </c>
       <c r="B119" t="n">
-        <v>5.500765323638916</v>
+        <v>5.500766277313232</v>
       </c>
       <c r="C119" t="n">
-        <v>5.571743298271707</v>
+        <v>5.57174426425156</v>
       </c>
       <c r="D119" t="n">
-        <v>5.367682625968931</v>
+        <v>5.36768355657054</v>
       </c>
       <c r="E119" t="n">
-        <v>5.394298996279097</v>
+        <v>5.394299931495218</v>
       </c>
       <c r="F119" t="n">
         <v>8097000</v>
@@ -2812,16 +2812,16 @@
         <v>44587</v>
       </c>
       <c r="B120" t="n">
-        <v>5.518510341644287</v>
+        <v>5.518510818481445</v>
       </c>
       <c r="C120" t="n">
-        <v>5.67821027397838</v>
+        <v>5.678210764614708</v>
       </c>
       <c r="D120" t="n">
-        <v>5.491893968295023</v>
+        <v>5.491894442832344</v>
       </c>
       <c r="E120" t="n">
-        <v>5.598360307811333</v>
+        <v>5.598360791548077</v>
       </c>
       <c r="F120" t="n">
         <v>11610000</v>
@@ -2832,16 +2832,16 @@
         <v>44588</v>
       </c>
       <c r="B121" t="n">
-        <v>5.545126914978027</v>
+        <v>5.545127391815186</v>
       </c>
       <c r="C121" t="n">
-        <v>5.749187602371603</v>
+        <v>5.74918809675637</v>
       </c>
       <c r="D121" t="n">
-        <v>5.527382525772483</v>
+        <v>5.527383001083763</v>
       </c>
       <c r="E121" t="n">
-        <v>5.580615693389118</v>
+        <v>5.580616173278031</v>
       </c>
       <c r="F121" t="n">
         <v>8501200</v>
@@ -2892,16 +2892,16 @@
         <v>44593</v>
       </c>
       <c r="B124" t="n">
-        <v>5.678210258483887</v>
+        <v>5.678209781646729</v>
       </c>
       <c r="C124" t="n">
-        <v>5.793549004174971</v>
+        <v>5.79354851765205</v>
       </c>
       <c r="D124" t="n">
-        <v>5.536254716456543</v>
+        <v>5.536254251540337</v>
       </c>
       <c r="E124" t="n">
-        <v>5.766932207838711</v>
+        <v>5.76693172355098</v>
       </c>
       <c r="F124" t="n">
         <v>8050400</v>
@@ -2912,16 +2912,16 @@
         <v>44594</v>
       </c>
       <c r="B125" t="n">
-        <v>5.669338226318359</v>
+        <v>5.669337749481201</v>
       </c>
       <c r="C125" t="n">
-        <v>5.882271341887785</v>
+        <v>5.882270847141231</v>
       </c>
       <c r="D125" t="n">
-        <v>5.651593835275879</v>
+        <v>5.651593359931167</v>
       </c>
       <c r="E125" t="n">
-        <v>5.722571399445803</v>
+        <v>5.722570918131304</v>
       </c>
       <c r="F125" t="n">
         <v>8808600</v>
@@ -2932,16 +2932,16 @@
         <v>44595</v>
       </c>
       <c r="B126" t="n">
-        <v>5.731442928314209</v>
+        <v>5.731443405151367</v>
       </c>
       <c r="C126" t="n">
-        <v>5.793548498976785</v>
+        <v>5.793548980980922</v>
       </c>
       <c r="D126" t="n">
-        <v>5.616104192680678</v>
+        <v>5.616104659922033</v>
       </c>
       <c r="E126" t="n">
-        <v>5.678209763343253</v>
+        <v>5.678210235751588</v>
       </c>
       <c r="F126" t="n">
         <v>8390300</v>
@@ -2972,16 +2972,16 @@
         <v>44599</v>
       </c>
       <c r="B128" t="n">
-        <v>5.562870979309082</v>
+        <v>5.562871932983398</v>
       </c>
       <c r="C128" t="n">
-        <v>5.775804060399835</v>
+        <v>5.775805050578469</v>
       </c>
       <c r="D128" t="n">
-        <v>5.553998996754243</v>
+        <v>5.553999948907585</v>
       </c>
       <c r="E128" t="n">
-        <v>5.704826084663194</v>
+        <v>5.704827062673674</v>
       </c>
       <c r="F128" t="n">
         <v>7178800</v>
@@ -2992,16 +2992,16 @@
         <v>44600</v>
       </c>
       <c r="B129" t="n">
-        <v>5.616105079650879</v>
+        <v>5.616104602813721</v>
       </c>
       <c r="C129" t="n">
-        <v>5.695955051248079</v>
+        <v>5.695954567631234</v>
       </c>
       <c r="D129" t="n">
-        <v>5.48302193467543</v>
+        <v>5.483021469137738</v>
       </c>
       <c r="E129" t="n">
-        <v>5.580616297398714</v>
+        <v>5.580615823574741</v>
       </c>
       <c r="F129" t="n">
         <v>9770800</v>
@@ -3012,16 +3012,16 @@
         <v>44601</v>
       </c>
       <c r="B130" t="n">
-        <v>5.633848667144775</v>
+        <v>5.633849620819092</v>
       </c>
       <c r="C130" t="n">
-        <v>5.740314998714537</v>
+        <v>5.740315970411027</v>
       </c>
       <c r="D130" t="n">
-        <v>5.589487907187173</v>
+        <v>5.589488853352285</v>
       </c>
       <c r="E130" t="n">
-        <v>5.616104278549815</v>
+        <v>5.616105229220436</v>
       </c>
       <c r="F130" t="n">
         <v>8867400</v>
@@ -3032,16 +3032,16 @@
         <v>44602</v>
       </c>
       <c r="B131" t="n">
-        <v>5.704826831817627</v>
+        <v>5.704826354980469</v>
       </c>
       <c r="C131" t="n">
-        <v>5.740315612804078</v>
+        <v>5.740315133000595</v>
       </c>
       <c r="D131" t="n">
-        <v>5.56287170787182</v>
+        <v>5.562871242899961</v>
       </c>
       <c r="E131" t="n">
-        <v>5.678210457607609</v>
+        <v>5.678209982995176</v>
       </c>
       <c r="F131" t="n">
         <v>9667400</v>
@@ -3052,16 +3052,16 @@
         <v>44603</v>
       </c>
       <c r="B132" t="n">
-        <v>5.633848667144775</v>
+        <v>5.633849620819092</v>
       </c>
       <c r="C132" t="n">
-        <v>5.775804198964051</v>
+        <v>5.775805176668006</v>
       </c>
       <c r="D132" t="n">
-        <v>5.589487907187173</v>
+        <v>5.589488853352285</v>
       </c>
       <c r="E132" t="n">
-        <v>5.731443015946853</v>
+        <v>5.731443986141532</v>
       </c>
       <c r="F132" t="n">
         <v>8001300</v>
@@ -3112,16 +3112,16 @@
         <v>44608</v>
       </c>
       <c r="B135" t="n">
-        <v>5.704826831817627</v>
+        <v>5.704826354980469</v>
       </c>
       <c r="C135" t="n">
-        <v>5.811293597836623</v>
+        <v>5.811293112100454</v>
       </c>
       <c r="D135" t="n">
-        <v>5.651593660337949</v>
+        <v>5.651593187950278</v>
       </c>
       <c r="E135" t="n">
-        <v>5.71369923859406</v>
+        <v>5.713698761015302</v>
       </c>
       <c r="F135" t="n">
         <v>12029900</v>
@@ -3132,16 +3132,16 @@
         <v>44609</v>
       </c>
       <c r="B136" t="n">
-        <v>5.580615997314453</v>
+        <v>5.580616474151611</v>
       </c>
       <c r="C136" t="n">
-        <v>5.740315508861739</v>
+        <v>5.740315999344462</v>
       </c>
       <c r="D136" t="n">
-        <v>5.509638436626771</v>
+        <v>5.509638907399233</v>
       </c>
       <c r="E136" t="n">
-        <v>5.731443525305595</v>
+        <v>5.73144401503025</v>
       </c>
       <c r="F136" t="n">
         <v>16171600</v>
@@ -3152,16 +3152,16 @@
         <v>44610</v>
       </c>
       <c r="B137" t="n">
-        <v>5.42091703414917</v>
+        <v>5.420916557312012</v>
       </c>
       <c r="C137" t="n">
-        <v>5.61610534578562</v>
+        <v>5.616104851779219</v>
       </c>
       <c r="D137" t="n">
-        <v>5.305578274834157</v>
+        <v>5.305577808142479</v>
       </c>
       <c r="E137" t="n">
-        <v>5.59836095381867</v>
+        <v>5.598360461373109</v>
       </c>
       <c r="F137" t="n">
         <v>12852100</v>
@@ -3172,16 +3172,16 @@
         <v>44613</v>
       </c>
       <c r="B138" t="n">
-        <v>5.119261741638184</v>
+        <v>5.119261264801025</v>
       </c>
       <c r="C138" t="n">
-        <v>5.456405598502314</v>
+        <v>5.456405090261659</v>
       </c>
       <c r="D138" t="n">
-        <v>5.074900551976187</v>
+        <v>5.074900079271083</v>
       </c>
       <c r="E138" t="n">
-        <v>5.447533191346051</v>
+        <v>5.447532683931823</v>
       </c>
       <c r="F138" t="n">
         <v>8726900</v>
@@ -3232,16 +3232,16 @@
         <v>44616</v>
       </c>
       <c r="B141" t="n">
-        <v>5.119261741638184</v>
+        <v>5.119261264801025</v>
       </c>
       <c r="C141" t="n">
-        <v>5.137006132891051</v>
+        <v>5.137005654401078</v>
       </c>
       <c r="D141" t="n">
-        <v>4.773245900677449</v>
+        <v>4.773245456070175</v>
       </c>
       <c r="E141" t="n">
-        <v>4.924073437856647</v>
+        <v>4.924072979200438</v>
       </c>
       <c r="F141" t="n">
         <v>11357100</v>
@@ -3252,16 +3252,16 @@
         <v>44617</v>
       </c>
       <c r="B142" t="n">
-        <v>5.066027641296387</v>
+        <v>5.066028118133545</v>
       </c>
       <c r="C142" t="n">
-        <v>5.163621986866849</v>
+        <v>5.163622472890022</v>
       </c>
       <c r="D142" t="n">
-        <v>4.986177683733319</v>
+        <v>4.986178153054643</v>
       </c>
       <c r="E142" t="n">
-        <v>5.110388822844664</v>
+        <v>5.110389303857295</v>
       </c>
       <c r="F142" t="n">
         <v>6795000</v>
@@ -3272,16 +3272,16 @@
         <v>44622</v>
       </c>
       <c r="B143" t="n">
-        <v>5.314450263977051</v>
+        <v>5.314449787139893</v>
       </c>
       <c r="C143" t="n">
-        <v>5.349939471001941</v>
+        <v>5.349938990980526</v>
       </c>
       <c r="D143" t="n">
-        <v>5.030539992255339</v>
+        <v>5.03053954089193</v>
       </c>
       <c r="E143" t="n">
-        <v>5.101517560185767</v>
+        <v>5.10151710245392</v>
       </c>
       <c r="F143" t="n">
         <v>7030100</v>
@@ -3292,16 +3292,16 @@
         <v>44623</v>
       </c>
       <c r="B144" t="n">
-        <v>5.465277671813965</v>
+        <v>5.465277194976807</v>
       </c>
       <c r="C144" t="n">
-        <v>5.545127645285164</v>
+        <v>5.545127161481217</v>
       </c>
       <c r="D144" t="n">
-        <v>5.323322539473757</v>
+        <v>5.323322075021968</v>
       </c>
       <c r="E144" t="n">
-        <v>5.323322539473757</v>
+        <v>5.323322075021968</v>
       </c>
       <c r="F144" t="n">
         <v>18057800</v>
@@ -3312,16 +3312,16 @@
         <v>44624</v>
       </c>
       <c r="B145" t="n">
-        <v>5.50963830947876</v>
+        <v>5.509638786315918</v>
       </c>
       <c r="C145" t="n">
-        <v>5.536254682592588</v>
+        <v>5.536255161733287</v>
       </c>
       <c r="D145" t="n">
-        <v>5.376555174730749</v>
+        <v>5.376555640050094</v>
       </c>
       <c r="E145" t="n">
-        <v>5.483021513305308</v>
+        <v>5.483021987838889</v>
       </c>
       <c r="F145" t="n">
         <v>9336900</v>
@@ -3412,16 +3412,16 @@
         <v>44631</v>
       </c>
       <c r="B150" t="n">
-        <v>5.59835958480835</v>
+        <v>5.598360538482666</v>
       </c>
       <c r="C150" t="n">
-        <v>5.979864130335345</v>
+        <v>5.979865148998535</v>
       </c>
       <c r="D150" t="n">
-        <v>5.527382034297241</v>
+        <v>5.52738297588061</v>
       </c>
       <c r="E150" t="n">
-        <v>5.69595392829091</v>
+        <v>5.695954898590315</v>
       </c>
       <c r="F150" t="n">
         <v>16712700</v>
@@ -3492,16 +3492,16 @@
         <v>44637</v>
       </c>
       <c r="B154" t="n">
-        <v>5.891142845153809</v>
+        <v>5.891143321990967</v>
       </c>
       <c r="C154" t="n">
-        <v>5.926631624342837</v>
+        <v>5.926632104052506</v>
       </c>
       <c r="D154" t="n">
-        <v>5.536254630203903</v>
+        <v>5.536255078315924</v>
       </c>
       <c r="E154" t="n">
-        <v>5.607232611641579</v>
+        <v>5.607233065498654</v>
       </c>
       <c r="F154" t="n">
         <v>10001800</v>
@@ -3512,16 +3512,16 @@
         <v>44638</v>
       </c>
       <c r="B155" t="n">
-        <v>6.201669692993164</v>
+        <v>6.201670169830322</v>
       </c>
       <c r="C155" t="n">
-        <v>6.201669692993164</v>
+        <v>6.201670169830322</v>
       </c>
       <c r="D155" t="n">
-        <v>5.891142672652063</v>
+        <v>5.891143125613262</v>
       </c>
       <c r="E155" t="n">
-        <v>5.891142672652063</v>
+        <v>5.891143125613262</v>
       </c>
       <c r="F155" t="n">
         <v>17710700</v>
@@ -3552,16 +3552,16 @@
         <v>44642</v>
       </c>
       <c r="B157" t="n">
-        <v>6.299264430999756</v>
+        <v>6.299263954162598</v>
       </c>
       <c r="C157" t="n">
-        <v>6.308136837611495</v>
+        <v>6.308136360102719</v>
       </c>
       <c r="D157" t="n">
-        <v>6.07745934242188</v>
+        <v>6.077458882374763</v>
       </c>
       <c r="E157" t="n">
-        <v>6.07745934242188</v>
+        <v>6.077458882374763</v>
       </c>
       <c r="F157" t="n">
         <v>9703800</v>
@@ -3592,16 +3592,16 @@
         <v>44644</v>
       </c>
       <c r="B159" t="n">
-        <v>6.343625545501709</v>
+        <v>6.343625068664551</v>
       </c>
       <c r="C159" t="n">
-        <v>6.432347495307822</v>
+        <v>6.432347011801619</v>
       </c>
       <c r="D159" t="n">
-        <v>6.254903595695596</v>
+        <v>6.254903125527482</v>
       </c>
       <c r="E159" t="n">
-        <v>6.299264359068839</v>
+        <v>6.299263885566218</v>
       </c>
       <c r="F159" t="n">
         <v>11578200</v>
@@ -3612,16 +3612,16 @@
         <v>44645</v>
       </c>
       <c r="B160" t="n">
-        <v>6.45009183883667</v>
+        <v>6.450092315673828</v>
       </c>
       <c r="C160" t="n">
-        <v>6.512197414783683</v>
+        <v>6.512197896212132</v>
       </c>
       <c r="D160" t="n">
-        <v>6.237159160834839</v>
+        <v>6.237159621930483</v>
       </c>
       <c r="E160" t="n">
-        <v>6.343625499835754</v>
+        <v>6.343625968802155</v>
       </c>
       <c r="F160" t="n">
         <v>15324200</v>
@@ -3632,16 +3632,16 @@
         <v>44648</v>
       </c>
       <c r="B161" t="n">
-        <v>6.538814067840576</v>
+        <v>6.538814544677734</v>
       </c>
       <c r="C161" t="n">
-        <v>6.592047239619212</v>
+        <v>6.592047720338352</v>
       </c>
       <c r="D161" t="n">
-        <v>6.35249775508553</v>
+        <v>6.352498218335738</v>
       </c>
       <c r="E161" t="n">
-        <v>6.432347724283304</v>
+        <v>6.4323481933565</v>
       </c>
       <c r="F161" t="n">
         <v>10802600</v>
@@ -3672,16 +3672,16 @@
         <v>44650</v>
       </c>
       <c r="B163" t="n">
-        <v>6.503324508666992</v>
+        <v>6.50332498550415</v>
       </c>
       <c r="C163" t="n">
-        <v>6.618663245252637</v>
+        <v>6.61866373054667</v>
       </c>
       <c r="D163" t="n">
-        <v>6.4500913432566</v>
+        <v>6.450091816190593</v>
       </c>
       <c r="E163" t="n">
-        <v>6.547685691372115</v>
+        <v>6.547686171461927</v>
       </c>
       <c r="F163" t="n">
         <v>10697600</v>
@@ -3752,16 +3752,16 @@
         <v>44656</v>
       </c>
       <c r="B167" t="n">
-        <v>6.299264430999756</v>
+        <v>6.299263954162598</v>
       </c>
       <c r="C167" t="n">
-        <v>6.32588122777534</v>
+        <v>6.325880748923362</v>
       </c>
       <c r="D167" t="n">
-        <v>6.148436903077259</v>
+        <v>6.148436437657334</v>
       </c>
       <c r="E167" t="n">
-        <v>6.228286870344377</v>
+        <v>6.228286398880027</v>
       </c>
       <c r="F167" t="n">
         <v>6962400</v>
@@ -3792,16 +3792,16 @@
         <v>44658</v>
       </c>
       <c r="B169" t="n">
-        <v>6.261641025543213</v>
+        <v>6.261641502380371</v>
       </c>
       <c r="C169" t="n">
-        <v>6.395246109067186</v>
+        <v>6.395246596078652</v>
       </c>
       <c r="D169" t="n">
-        <v>6.208198482469381</v>
+        <v>6.208198955236777</v>
       </c>
       <c r="E169" t="n">
-        <v>6.323989951262346</v>
+        <v>6.323990432847507</v>
       </c>
       <c r="F169" t="n">
         <v>10216600</v>
@@ -3812,16 +3812,16 @@
         <v>44659</v>
       </c>
       <c r="B170" t="n">
-        <v>6.190384864807129</v>
+        <v>6.190385341644287</v>
       </c>
       <c r="C170" t="n">
-        <v>6.323990382154669</v>
+        <v>6.323990869283284</v>
       </c>
       <c r="D170" t="n">
-        <v>6.136942742812159</v>
+        <v>6.136943215532741</v>
       </c>
       <c r="E170" t="n">
-        <v>6.23492017882972</v>
+        <v>6.234920659097374</v>
       </c>
       <c r="F170" t="n">
         <v>10722400</v>
@@ -3832,16 +3832,16 @@
         <v>44662</v>
       </c>
       <c r="B171" t="n">
-        <v>6.145849704742432</v>
+        <v>6.14585018157959</v>
       </c>
       <c r="C171" t="n">
-        <v>6.217105864263122</v>
+        <v>6.21710634662882</v>
       </c>
       <c r="D171" t="n">
-        <v>6.021151425581226</v>
+        <v>6.021151892743435</v>
       </c>
       <c r="E171" t="n">
-        <v>6.119128432562067</v>
+        <v>6.119128907326005</v>
       </c>
       <c r="F171" t="n">
         <v>4955900</v>
@@ -3852,16 +3852,16 @@
         <v>44663</v>
       </c>
       <c r="B172" t="n">
-        <v>6.217105865478516</v>
+        <v>6.217106342315674</v>
       </c>
       <c r="C172" t="n">
-        <v>6.359618184547754</v>
+        <v>6.359618672315267</v>
       </c>
       <c r="D172" t="n">
-        <v>6.145849705943896</v>
+        <v>6.145850177315878</v>
       </c>
       <c r="E172" t="n">
-        <v>6.190384593292927</v>
+        <v>6.190385068080627</v>
       </c>
       <c r="F172" t="n">
         <v>15598900</v>
@@ -3872,16 +3872,16 @@
         <v>44664</v>
       </c>
       <c r="B173" t="n">
-        <v>6.30617618560791</v>
+        <v>6.306176662445068</v>
       </c>
       <c r="C173" t="n">
-        <v>6.323990225832556</v>
+        <v>6.323990704016711</v>
       </c>
       <c r="D173" t="n">
-        <v>6.172570671562951</v>
+        <v>6.172571138297622</v>
       </c>
       <c r="E173" t="n">
-        <v>6.261641297406404</v>
+        <v>6.261641770876088</v>
       </c>
       <c r="F173" t="n">
         <v>5828500</v>
@@ -3892,16 +3892,16 @@
         <v>44665</v>
       </c>
       <c r="B174" t="n">
-        <v>6.323990821838379</v>
+        <v>6.323989868164062</v>
       </c>
       <c r="C174" t="n">
-        <v>6.350712097053812</v>
+        <v>6.350711139349857</v>
       </c>
       <c r="D174" t="n">
-        <v>6.226013379008809</v>
+        <v>6.226012440109747</v>
       </c>
       <c r="E174" t="n">
-        <v>6.297269971343208</v>
+        <v>6.297269021698465</v>
       </c>
       <c r="F174" t="n">
         <v>4947000</v>
@@ -3932,16 +3932,16 @@
         <v>44670</v>
       </c>
       <c r="B176" t="n">
-        <v>6.190384864807129</v>
+        <v>6.190385341644287</v>
       </c>
       <c r="C176" t="n">
-        <v>6.413060585479618</v>
+        <v>6.413061079469193</v>
       </c>
       <c r="D176" t="n">
-        <v>6.18147805683475</v>
+        <v>6.181478532985828</v>
       </c>
       <c r="E176" t="n">
-        <v>6.359618463484649</v>
+        <v>6.359618953357647</v>
       </c>
       <c r="F176" t="n">
         <v>12659600</v>
@@ -3952,16 +3952,16 @@
         <v>44671</v>
       </c>
       <c r="B177" t="n">
-        <v>6.208198547363281</v>
+        <v>6.208199024200439</v>
       </c>
       <c r="C177" t="n">
-        <v>6.279455130633163</v>
+        <v>6.279455612943373</v>
       </c>
       <c r="D177" t="n">
-        <v>6.11022154171758</v>
+        <v>6.110222011029355</v>
       </c>
       <c r="E177" t="n">
-        <v>6.190384507725862</v>
+        <v>6.190384983194765</v>
       </c>
       <c r="F177" t="n">
         <v>7897000</v>
@@ -4072,16 +4072,16 @@
         <v>44680</v>
       </c>
       <c r="B183" t="n">
-        <v>6.145849704742432</v>
+        <v>6.14585018157959</v>
       </c>
       <c r="C183" t="n">
-        <v>6.448688382705361</v>
+        <v>6.44868888303882</v>
       </c>
       <c r="D183" t="n">
-        <v>6.06568631292155</v>
+        <v>6.065686783539082</v>
       </c>
       <c r="E183" t="n">
-        <v>6.413060302945017</v>
+        <v>6.413060800514205</v>
       </c>
       <c r="F183" t="n">
         <v>21979100</v>
@@ -4092,16 +4092,16 @@
         <v>44683</v>
       </c>
       <c r="B184" t="n">
-        <v>5.86973237991333</v>
+        <v>5.869731903076172</v>
       </c>
       <c r="C184" t="n">
-        <v>6.19038512538046</v>
+        <v>6.19038462249456</v>
       </c>
       <c r="D184" t="n">
-        <v>5.745033665289197</v>
+        <v>5.745033198582139</v>
       </c>
       <c r="E184" t="n">
-        <v>6.145850234203484</v>
+        <v>6.145849734935447</v>
       </c>
       <c r="F184" t="n">
         <v>12404500</v>
@@ -4132,16 +4132,16 @@
         <v>44685</v>
       </c>
       <c r="B186" t="n">
-        <v>5.388752460479736</v>
+        <v>5.388752937316895</v>
       </c>
       <c r="C186" t="n">
-        <v>5.51345074167094</v>
+        <v>5.513451229542335</v>
       </c>
       <c r="D186" t="n">
-        <v>5.210611634057798</v>
+        <v>5.210612095131722</v>
       </c>
       <c r="E186" t="n">
-        <v>5.51345074167094</v>
+        <v>5.513451229542335</v>
       </c>
       <c r="F186" t="n">
         <v>18834300</v>
@@ -4152,16 +4152,16 @@
         <v>44686</v>
       </c>
       <c r="B187" t="n">
-        <v>4.943400859832764</v>
+        <v>4.943401336669922</v>
       </c>
       <c r="C187" t="n">
-        <v>5.379845041205424</v>
+        <v>5.379845560141698</v>
       </c>
       <c r="D187" t="n">
-        <v>4.925586820281231</v>
+        <v>4.925587295400058</v>
       </c>
       <c r="E187" t="n">
-        <v>5.379845041205424</v>
+        <v>5.379845560141698</v>
       </c>
       <c r="F187" t="n">
         <v>16863600</v>
@@ -4172,16 +4172,16 @@
         <v>44687</v>
       </c>
       <c r="B188" t="n">
-        <v>4.952307224273682</v>
+        <v>4.95230770111084</v>
       </c>
       <c r="C188" t="n">
-        <v>5.068098683361416</v>
+        <v>5.068099171347654</v>
       </c>
       <c r="D188" t="n">
-        <v>4.863237034483181</v>
+        <v>4.863237502744139</v>
       </c>
       <c r="E188" t="n">
-        <v>4.970121262231782</v>
+        <v>4.97012174078418</v>
       </c>
       <c r="F188" t="n">
         <v>14479200</v>
@@ -4192,16 +4192,16 @@
         <v>44690</v>
       </c>
       <c r="B189" t="n">
-        <v>4.622747898101807</v>
+        <v>4.62274694442749</v>
       </c>
       <c r="C189" t="n">
-        <v>4.934493814409667</v>
+        <v>4.934492796422071</v>
       </c>
       <c r="D189" t="n">
-        <v>4.435700263373046</v>
+        <v>4.435699348286715</v>
       </c>
       <c r="E189" t="n">
-        <v>4.934493814409667</v>
+        <v>4.934492796422071</v>
       </c>
       <c r="F189" t="n">
         <v>21341300</v>
@@ -4232,16 +4232,16 @@
         <v>44692</v>
       </c>
       <c r="B191" t="n">
-        <v>4.640562534332275</v>
+        <v>4.640562057495117</v>
       </c>
       <c r="C191" t="n">
-        <v>4.694004661872806</v>
+        <v>4.694004179544246</v>
       </c>
       <c r="D191" t="n">
-        <v>4.489142960607302</v>
+        <v>4.489142499329136</v>
       </c>
       <c r="E191" t="n">
-        <v>4.640562534332275</v>
+        <v>4.640562057495117</v>
       </c>
       <c r="F191" t="n">
         <v>17331100</v>
@@ -4252,16 +4252,16 @@
         <v>44693</v>
       </c>
       <c r="B192" t="n">
-        <v>4.79198169708252</v>
+        <v>4.791982173919678</v>
       </c>
       <c r="C192" t="n">
-        <v>4.809795738068244</v>
+        <v>4.809796216678029</v>
       </c>
       <c r="D192" t="n">
-        <v>4.55149193141512</v>
+        <v>4.55149238432179</v>
       </c>
       <c r="E192" t="n">
-        <v>4.587120013386569</v>
+        <v>4.587120469838493</v>
       </c>
       <c r="F192" t="n">
         <v>13350100</v>
@@ -4292,16 +4292,16 @@
         <v>44697</v>
       </c>
       <c r="B194" t="n">
-        <v>4.881052017211914</v>
+        <v>4.881051540374756</v>
       </c>
       <c r="C194" t="n">
-        <v>4.881052017211914</v>
+        <v>4.881051540374756</v>
       </c>
       <c r="D194" t="n">
-        <v>4.542584805774532</v>
+        <v>4.542584362002735</v>
       </c>
       <c r="E194" t="n">
-        <v>4.604934163056234</v>
+        <v>4.604933713193436</v>
       </c>
       <c r="F194" t="n">
         <v>29391700</v>
@@ -4312,16 +4312,16 @@
         <v>44698</v>
       </c>
       <c r="B195" t="n">
-        <v>5.00575065612793</v>
+        <v>5.005750179290771</v>
       </c>
       <c r="C195" t="n">
-        <v>5.183891507332367</v>
+        <v>5.183891013525891</v>
       </c>
       <c r="D195" t="n">
-        <v>4.881052357589018</v>
+        <v>4.881051892630355</v>
       </c>
       <c r="E195" t="n">
-        <v>4.952308528182682</v>
+        <v>4.952308056436308</v>
       </c>
       <c r="F195" t="n">
         <v>40878000</v>
@@ -4332,16 +4332,16 @@
         <v>44699</v>
       </c>
       <c r="B196" t="n">
-        <v>4.952307224273682</v>
+        <v>4.95230770111084</v>
       </c>
       <c r="C196" t="n">
-        <v>5.112633565896584</v>
+        <v>5.112634058170901</v>
       </c>
       <c r="D196" t="n">
-        <v>4.898865110399381</v>
+        <v>4.89886558209082</v>
       </c>
       <c r="E196" t="n">
-        <v>4.987935300189882</v>
+        <v>4.98793578045752</v>
       </c>
       <c r="F196" t="n">
         <v>17779600</v>
@@ -4352,16 +4352,16 @@
         <v>44700</v>
       </c>
       <c r="B197" t="n">
-        <v>5.050285339355469</v>
+        <v>5.050285816192627</v>
       </c>
       <c r="C197" t="n">
-        <v>5.183890854759837</v>
+        <v>5.183891344211743</v>
       </c>
       <c r="D197" t="n">
-        <v>4.898865783545199</v>
+        <v>4.898866246085646</v>
       </c>
       <c r="E197" t="n">
-        <v>4.987935985574703</v>
+        <v>4.987936456524968</v>
       </c>
       <c r="F197" t="n">
         <v>12233400</v>
@@ -4372,16 +4372,16 @@
         <v>44701</v>
       </c>
       <c r="B198" t="n">
-        <v>4.934494018554688</v>
+        <v>4.934493541717529</v>
       </c>
       <c r="C198" t="n">
-        <v>5.121541661021799</v>
+        <v>5.121541166109582</v>
       </c>
       <c r="D198" t="n">
-        <v>4.827609772779264</v>
+        <v>4.827609306270698</v>
       </c>
       <c r="E198" t="n">
-        <v>5.094820387217823</v>
+        <v>5.094819894887776</v>
       </c>
       <c r="F198" t="n">
         <v>10517400</v>
@@ -4392,16 +4392,16 @@
         <v>44704</v>
       </c>
       <c r="B199" t="n">
-        <v>5.023564338684082</v>
+        <v>5.023563861846924</v>
       </c>
       <c r="C199" t="n">
-        <v>5.10372773721593</v>
+        <v>5.103727252769655</v>
       </c>
       <c r="D199" t="n">
-        <v>4.881052007712129</v>
+        <v>4.881051544402253</v>
       </c>
       <c r="E199" t="n">
-        <v>4.979029447615471</v>
+        <v>4.979028975005568</v>
       </c>
       <c r="F199" t="n">
         <v>11444200</v>
@@ -4412,16 +4412,16 @@
         <v>44705</v>
       </c>
       <c r="B200" t="n">
-        <v>5.157169342041016</v>
+        <v>5.157169818878174</v>
       </c>
       <c r="C200" t="n">
-        <v>5.201704653345494</v>
+        <v>5.201705134300433</v>
       </c>
       <c r="D200" t="n">
-        <v>4.961214906685765</v>
+        <v>4.961215365404775</v>
       </c>
       <c r="E200" t="n">
-        <v>4.979028946263514</v>
+        <v>4.979029406629629</v>
       </c>
       <c r="F200" t="n">
         <v>9007600</v>
@@ -4472,16 +4472,16 @@
         <v>44708</v>
       </c>
       <c r="B203" t="n">
-        <v>5.406566619873047</v>
+        <v>5.406566143035889</v>
       </c>
       <c r="C203" t="n">
-        <v>5.584707025503037</v>
+        <v>5.58470653295462</v>
       </c>
       <c r="D203" t="n">
-        <v>5.388752579310048</v>
+        <v>5.388752104044015</v>
       </c>
       <c r="E203" t="n">
-        <v>5.522357671172426</v>
+        <v>5.522357184122968</v>
       </c>
       <c r="F203" t="n">
         <v>11400800</v>
@@ -4512,16 +4512,16 @@
         <v>44712</v>
       </c>
       <c r="B205" t="n">
-        <v>5.46000862121582</v>
+        <v>5.460009574890137</v>
       </c>
       <c r="C205" t="n">
-        <v>5.691591143430404</v>
+        <v>5.691592137554163</v>
       </c>
       <c r="D205" t="n">
-        <v>5.46000862121582</v>
+        <v>5.460009574890137</v>
       </c>
       <c r="E205" t="n">
-        <v>5.62924221519428</v>
+        <v>5.629243198427841</v>
       </c>
       <c r="F205" t="n">
         <v>13931800</v>
@@ -4532,16 +4532,16 @@
         <v>44713</v>
       </c>
       <c r="B206" t="n">
-        <v>5.513450622558594</v>
+        <v>5.513451099395752</v>
       </c>
       <c r="C206" t="n">
-        <v>5.54907870212923</v>
+        <v>5.549079182047723</v>
       </c>
       <c r="D206" t="n">
-        <v>5.406566383846685</v>
+        <v>5.406566851439836</v>
       </c>
       <c r="E206" t="n">
-        <v>5.495636582773276</v>
+        <v>5.495637058069765</v>
       </c>
       <c r="F206" t="n">
         <v>9091200</v>
@@ -4552,16 +4552,16 @@
         <v>44714</v>
       </c>
       <c r="B207" t="n">
-        <v>5.611427783966064</v>
+        <v>5.611428260803223</v>
       </c>
       <c r="C207" t="n">
-        <v>5.65596266892822</v>
+        <v>5.655963149549779</v>
       </c>
       <c r="D207" t="n">
-        <v>5.504543125672473</v>
+        <v>5.504543593426991</v>
       </c>
       <c r="E207" t="n">
-        <v>5.549078435354819</v>
+        <v>5.549078906893773</v>
       </c>
       <c r="F207" t="n">
         <v>14163200</v>
@@ -4572,16 +4572,16 @@
         <v>44715</v>
       </c>
       <c r="B208" t="n">
-        <v>5.513450622558594</v>
+        <v>5.513451099395752</v>
       </c>
       <c r="C208" t="n">
-        <v>5.602520821485185</v>
+        <v>5.602521306025682</v>
       </c>
       <c r="D208" t="n">
-        <v>5.451101270949875</v>
+        <v>5.451101742394677</v>
       </c>
       <c r="E208" t="n">
-        <v>5.575799974167312</v>
+        <v>5.575800456396826</v>
       </c>
       <c r="F208" t="n">
         <v>9326300</v>
@@ -4612,16 +4612,16 @@
         <v>44719</v>
       </c>
       <c r="B210" t="n">
-        <v>5.023564338684082</v>
+        <v>5.023563861846924</v>
       </c>
       <c r="C210" t="n">
-        <v>5.299682192302366</v>
+        <v>5.299681689256077</v>
       </c>
       <c r="D210" t="n">
-        <v>4.987936255941094</v>
+        <v>4.987935782485756</v>
       </c>
       <c r="E210" t="n">
-        <v>5.281868150930872</v>
+        <v>5.281867649575493</v>
       </c>
       <c r="F210" t="n">
         <v>18881300</v>
@@ -4632,16 +4632,16 @@
         <v>44720</v>
       </c>
       <c r="B211" t="n">
-        <v>4.916679382324219</v>
+        <v>4.916679859161377</v>
       </c>
       <c r="C211" t="n">
-        <v>5.005749576353243</v>
+        <v>5.005750061828747</v>
       </c>
       <c r="D211" t="n">
-        <v>4.783073878920588</v>
+        <v>4.783074342800206</v>
       </c>
       <c r="E211" t="n">
-        <v>4.996842769310434</v>
+        <v>4.996843253922124</v>
       </c>
       <c r="F211" t="n">
         <v>13996400</v>
@@ -4652,16 +4652,16 @@
         <v>44721</v>
       </c>
       <c r="B212" t="n">
-        <v>4.818702697753906</v>
+        <v>4.81870174407959</v>
       </c>
       <c r="C212" t="n">
-        <v>4.996843537934095</v>
+        <v>4.996842549003744</v>
       </c>
       <c r="D212" t="n">
-        <v>4.809795889341036</v>
+        <v>4.809794937429475</v>
       </c>
       <c r="E212" t="n">
-        <v>4.88105205552501</v>
+        <v>4.881051089511069</v>
       </c>
       <c r="F212" t="n">
         <v>8480000</v>
@@ -4692,16 +4692,16 @@
         <v>44725</v>
       </c>
       <c r="B214" t="n">
-        <v>4.569306373596191</v>
+        <v>4.569305896759033</v>
       </c>
       <c r="C214" t="n">
-        <v>4.676190628895216</v>
+        <v>4.676190140903983</v>
       </c>
       <c r="D214" t="n">
-        <v>4.506957012311623</v>
+        <v>4.50695654198103</v>
       </c>
       <c r="E214" t="n">
-        <v>4.631655310160484</v>
+        <v>4.631654826816805</v>
       </c>
       <c r="F214" t="n">
         <v>7709600</v>
@@ -4752,16 +4752,16 @@
         <v>44729</v>
       </c>
       <c r="B217" t="n">
-        <v>4.524770259857178</v>
+        <v>4.524770736694336</v>
       </c>
       <c r="C217" t="n">
-        <v>4.524770259857178</v>
+        <v>4.524770736694336</v>
       </c>
       <c r="D217" t="n">
-        <v>4.311001786818351</v>
+        <v>4.311002241127791</v>
       </c>
       <c r="E217" t="n">
-        <v>4.506956220437275</v>
+        <v>4.506956695397124</v>
       </c>
       <c r="F217" t="n">
         <v>10891400</v>
@@ -4772,16 +4772,16 @@
         <v>44732</v>
       </c>
       <c r="B218" t="n">
-        <v>4.524770259857178</v>
+        <v>4.524770736694336</v>
       </c>
       <c r="C218" t="n">
-        <v>4.649468535796493</v>
+        <v>4.64946902577482</v>
       </c>
       <c r="D218" t="n">
-        <v>4.453514102177569</v>
+        <v>4.453514571505488</v>
       </c>
       <c r="E218" t="n">
-        <v>4.524770259857178</v>
+        <v>4.524770736694336</v>
       </c>
       <c r="F218" t="n">
         <v>7841400</v>
@@ -4792,16 +4792,16 @@
         <v>44733</v>
       </c>
       <c r="B219" t="n">
-        <v>4.489142417907715</v>
+        <v>4.489142894744873</v>
       </c>
       <c r="C219" t="n">
-        <v>4.596026660067369</v>
+        <v>4.596027148257782</v>
       </c>
       <c r="D219" t="n">
-        <v>4.444607104647747</v>
+        <v>4.44460757675436</v>
       </c>
       <c r="E219" t="n">
-        <v>4.560398579347484</v>
+        <v>4.560399063753479</v>
       </c>
       <c r="F219" t="n">
         <v>7411800</v>
@@ -4832,16 +4832,16 @@
         <v>44735</v>
       </c>
       <c r="B221" t="n">
-        <v>4.266466617584229</v>
+        <v>4.26646614074707</v>
       </c>
       <c r="C221" t="n">
-        <v>4.515863602464738</v>
+        <v>4.515863097753988</v>
       </c>
       <c r="D221" t="n">
-        <v>4.266466617584229</v>
+        <v>4.26646614074707</v>
       </c>
       <c r="E221" t="n">
-        <v>4.471328290076007</v>
+        <v>4.471327790342699</v>
       </c>
       <c r="F221" t="n">
         <v>8059200</v>
@@ -4852,16 +4852,16 @@
         <v>44736</v>
       </c>
       <c r="B222" t="n">
-        <v>4.257560253143311</v>
+        <v>4.257559776306152</v>
       </c>
       <c r="C222" t="n">
-        <v>4.337723229179554</v>
+        <v>4.337722743364323</v>
       </c>
       <c r="D222" t="n">
-        <v>4.23083897798439</v>
+        <v>4.230838504139954</v>
       </c>
       <c r="E222" t="n">
-        <v>4.319909187313693</v>
+        <v>4.319908703493595</v>
       </c>
       <c r="F222" t="n">
         <v>7941200</v>
@@ -4892,16 +4892,16 @@
         <v>44740</v>
       </c>
       <c r="B224" t="n">
-        <v>4.293187141418457</v>
+        <v>4.293188571929932</v>
       </c>
       <c r="C224" t="n">
-        <v>4.471327510473106</v>
+        <v>4.471329000341845</v>
       </c>
       <c r="D224" t="n">
-        <v>4.293187141418457</v>
+        <v>4.293188571929932</v>
       </c>
       <c r="E224" t="n">
-        <v>4.319907984416584</v>
+        <v>4.319909423831577</v>
       </c>
       <c r="F224" t="n">
         <v>8975600</v>
@@ -4932,16 +4932,16 @@
         <v>44742</v>
       </c>
       <c r="B226" t="n">
-        <v>4.088326454162598</v>
+        <v>4.088326930999756</v>
       </c>
       <c r="C226" t="n">
-        <v>4.239746015386434</v>
+        <v>4.239746509884235</v>
       </c>
       <c r="D226" t="n">
-        <v>4.052698372077018</v>
+        <v>4.052698844758736</v>
       </c>
       <c r="E226" t="n">
-        <v>4.239746015386434</v>
+        <v>4.239746509884235</v>
       </c>
       <c r="F226" t="n">
         <v>6721700</v>
@@ -4952,16 +4952,16 @@
         <v>44743</v>
       </c>
       <c r="B227" t="n">
-        <v>4.02597713470459</v>
+        <v>4.025976657867432</v>
       </c>
       <c r="C227" t="n">
-        <v>4.186303505545305</v>
+        <v>4.186303009719074</v>
       </c>
       <c r="D227" t="n">
-        <v>4.02597713470459</v>
+        <v>4.025976657867432</v>
       </c>
       <c r="E227" t="n">
-        <v>4.02597713470459</v>
+        <v>4.025976657867432</v>
       </c>
       <c r="F227" t="n">
         <v>12849200</v>
@@ -5012,16 +5012,16 @@
         <v>44748</v>
       </c>
       <c r="B230" t="n">
-        <v>3.910185813903809</v>
+        <v>3.910186052322388</v>
       </c>
       <c r="C230" t="n">
-        <v>4.052698574069413</v>
+        <v>4.052698821177525</v>
       </c>
       <c r="D230" t="n">
-        <v>3.785487520389134</v>
+        <v>3.785487751204394</v>
       </c>
       <c r="E230" t="n">
-        <v>4.034884532138745</v>
+        <v>4.034884778160668</v>
       </c>
       <c r="F230" t="n">
         <v>11922900</v>
@@ -5052,16 +5052,16 @@
         <v>44750</v>
       </c>
       <c r="B232" t="n">
-        <v>3.919093132019043</v>
+        <v>3.919092655181885</v>
       </c>
       <c r="C232" t="n">
-        <v>4.132861639811949</v>
+        <v>4.132861136965516</v>
       </c>
       <c r="D232" t="n">
-        <v>3.919093132019043</v>
+        <v>3.919092655181885</v>
       </c>
       <c r="E232" t="n">
-        <v>4.03488461943367</v>
+        <v>4.034884128508128</v>
       </c>
       <c r="F232" t="n">
         <v>7050900</v>
@@ -5092,16 +5092,16 @@
         <v>44754</v>
       </c>
       <c r="B234" t="n">
-        <v>3.580625295639038</v>
+        <v>3.580625534057617</v>
       </c>
       <c r="C234" t="n">
-        <v>3.705323570689496</v>
+        <v>3.705323817411202</v>
       </c>
       <c r="D234" t="n">
-        <v>3.580625295639038</v>
+        <v>3.580625534057617</v>
       </c>
       <c r="E234" t="n">
-        <v>3.696416763403135</v>
+        <v>3.696417009531774</v>
       </c>
       <c r="F234" t="n">
         <v>14771600</v>
@@ -5112,16 +5112,16 @@
         <v>44755</v>
       </c>
       <c r="B235" t="n">
-        <v>3.687509775161743</v>
+        <v>3.687510013580322</v>
       </c>
       <c r="C235" t="n">
-        <v>3.723137856102805</v>
+        <v>3.723138096824944</v>
       </c>
       <c r="D235" t="n">
-        <v>3.47374128951537</v>
+        <v>3.473741514112596</v>
       </c>
       <c r="E235" t="n">
-        <v>3.589532764933936</v>
+        <v>3.589532997017741</v>
       </c>
       <c r="F235" t="n">
         <v>14925600</v>
@@ -5132,16 +5132,16 @@
         <v>44756</v>
       </c>
       <c r="B236" t="n">
-        <v>3.821115255355835</v>
+        <v>3.821115493774414</v>
       </c>
       <c r="C236" t="n">
-        <v>3.856743335964077</v>
+        <v>3.856743576605671</v>
       </c>
       <c r="D236" t="n">
-        <v>3.651881660106575</v>
+        <v>3.651881887965819</v>
       </c>
       <c r="E236" t="n">
-        <v>3.687509740714817</v>
+        <v>3.687509970797076</v>
       </c>
       <c r="F236" t="n">
         <v>9774500</v>
@@ -5172,16 +5172,16 @@
         <v>44760</v>
       </c>
       <c r="B238" t="n">
-        <v>3.83002233505249</v>
+        <v>3.830022573471069</v>
       </c>
       <c r="C238" t="n">
-        <v>4.088326121516194</v>
+        <v>4.088326376014163</v>
       </c>
       <c r="D238" t="n">
-        <v>3.83002233505249</v>
+        <v>3.830022573471069</v>
       </c>
       <c r="E238" t="n">
-        <v>3.990348691392656</v>
+        <v>3.990348939791538</v>
       </c>
       <c r="F238" t="n">
         <v>5011900</v>
@@ -5192,16 +5192,16 @@
         <v>44761</v>
       </c>
       <c r="B239" t="n">
-        <v>3.856743335723877</v>
+        <v>3.856743574142456</v>
       </c>
       <c r="C239" t="n">
-        <v>3.93690672944754</v>
+        <v>3.93690697282171</v>
       </c>
       <c r="D239" t="n">
-        <v>3.830022487629471</v>
+        <v>3.830022724396204</v>
       </c>
       <c r="E239" t="n">
-        <v>3.838929295420866</v>
+        <v>3.838929532738205</v>
       </c>
       <c r="F239" t="n">
         <v>5270100</v>
@@ -5212,16 +5212,16 @@
         <v>44762</v>
       </c>
       <c r="B240" t="n">
-        <v>3.999255895614624</v>
+        <v>3.999255657196045</v>
       </c>
       <c r="C240" t="n">
-        <v>4.025977170015901</v>
+        <v>4.025976930004314</v>
       </c>
       <c r="D240" t="n">
-        <v>3.803301440646171</v>
+        <v>3.803301213909561</v>
       </c>
       <c r="E240" t="n">
-        <v>3.830022715047448</v>
+        <v>3.830022486717829</v>
       </c>
       <c r="F240" t="n">
         <v>11021800</v>
@@ -5232,16 +5232,16 @@
         <v>44763</v>
       </c>
       <c r="B241" t="n">
-        <v>3.963627338409424</v>
+        <v>3.963628053665161</v>
       </c>
       <c r="C241" t="n">
-        <v>4.025976688068431</v>
+        <v>4.02597741457541</v>
       </c>
       <c r="D241" t="n">
-        <v>3.936906491927133</v>
+        <v>3.936907202360965</v>
       </c>
       <c r="E241" t="n">
-        <v>4.025976688068431</v>
+        <v>4.02597741457541</v>
       </c>
       <c r="F241" t="n">
         <v>6658500</v>
@@ -5252,16 +5252,16 @@
         <v>44764</v>
       </c>
       <c r="B242" t="n">
-        <v>3.740951776504517</v>
+        <v>3.740952491760254</v>
       </c>
       <c r="C242" t="n">
-        <v>3.999255567396865</v>
+        <v>3.999256332039304</v>
       </c>
       <c r="D242" t="n">
-        <v>3.740951776504517</v>
+        <v>3.740952491760254</v>
       </c>
       <c r="E242" t="n">
-        <v>3.999255567396865</v>
+        <v>3.999256332039304</v>
       </c>
       <c r="F242" t="n">
         <v>6536400</v>
@@ -5272,16 +5272,16 @@
         <v>44767</v>
       </c>
       <c r="B243" t="n">
-        <v>3.696416854858398</v>
+        <v>3.696417570114136</v>
       </c>
       <c r="C243" t="n">
-        <v>3.78548705352675</v>
+        <v>3.78548778601755</v>
       </c>
       <c r="D243" t="n">
-        <v>3.651881543164118</v>
+        <v>3.651882249802283</v>
       </c>
       <c r="E243" t="n">
-        <v>3.76767301379308</v>
+        <v>3.767673742836867</v>
       </c>
       <c r="F243" t="n">
         <v>10514300</v>
@@ -5292,16 +5292,16 @@
         <v>44768</v>
       </c>
       <c r="B244" t="n">
-        <v>3.714231491088867</v>
+        <v>3.714231014251709</v>
       </c>
       <c r="C244" t="n">
-        <v>3.812208937719106</v>
+        <v>3.812208448303494</v>
       </c>
       <c r="D244" t="n">
-        <v>3.66969617224232</v>
+        <v>3.669695701122655</v>
       </c>
       <c r="E244" t="n">
-        <v>3.705324257431447</v>
+        <v>3.705323781737809</v>
       </c>
       <c r="F244" t="n">
         <v>4594100</v>
@@ -5312,16 +5312,16 @@
         <v>44769</v>
       </c>
       <c r="B245" t="n">
-        <v>3.999255895614624</v>
+        <v>3.999255657196045</v>
       </c>
       <c r="C245" t="n">
-        <v>3.999255895614624</v>
+        <v>3.999255657196045</v>
       </c>
       <c r="D245" t="n">
-        <v>3.723138042162589</v>
+        <v>3.723137820204979</v>
       </c>
       <c r="E245" t="n">
-        <v>3.740952083523358</v>
+        <v>3.74095186050375</v>
       </c>
       <c r="F245" t="n">
         <v>8689000</v>
@@ -5332,16 +5332,16 @@
         <v>44770</v>
       </c>
       <c r="B246" t="n">
-        <v>3.999255895614624</v>
+        <v>3.999255657196045</v>
       </c>
       <c r="C246" t="n">
-        <v>4.070512485777946</v>
+        <v>4.070512243111353</v>
       </c>
       <c r="D246" t="n">
-        <v>3.892371647450013</v>
+        <v>3.892371415403418</v>
       </c>
       <c r="E246" t="n">
-        <v>4.025977170015901</v>
+        <v>4.025976930004314</v>
       </c>
       <c r="F246" t="n">
         <v>3634200</v>
@@ -5412,16 +5412,16 @@
         <v>44776</v>
       </c>
       <c r="B250" t="n">
-        <v>4.284280300140381</v>
+        <v>4.284280776977539</v>
       </c>
       <c r="C250" t="n">
-        <v>4.373350492766133</v>
+        <v>4.373350979516736</v>
       </c>
       <c r="D250" t="n">
-        <v>4.123953953414027</v>
+        <v>4.123954412406984</v>
       </c>
       <c r="E250" t="n">
-        <v>4.123953953414027</v>
+        <v>4.123954412406984</v>
       </c>
       <c r="F250" t="n">
         <v>8750200</v>
@@ -5432,16 +5432,16 @@
         <v>44777</v>
       </c>
       <c r="B251" t="n">
-        <v>4.498049259185791</v>
+        <v>4.498049736022949</v>
       </c>
       <c r="C251" t="n">
-        <v>4.791981111917343</v>
+        <v>4.791981619914148</v>
       </c>
       <c r="D251" t="n">
-        <v>4.328815678126979</v>
+        <v>4.328816137023725</v>
       </c>
       <c r="E251" t="n">
-        <v>4.328815678126979</v>
+        <v>4.328816137023725</v>
       </c>
       <c r="F251" t="n">
         <v>17206200</v>
@@ -5452,16 +5452,16 @@
         <v>44778</v>
       </c>
       <c r="B252" t="n">
-        <v>4.328815937042236</v>
+        <v>4.328816413879395</v>
       </c>
       <c r="C252" t="n">
-        <v>4.542584415552859</v>
+        <v>4.542584915937508</v>
       </c>
       <c r="D252" t="n">
-        <v>4.248652545240646</v>
+        <v>4.248653013247472</v>
       </c>
       <c r="E252" t="n">
-        <v>4.542584415552859</v>
+        <v>4.542584915937508</v>
       </c>
       <c r="F252" t="n">
         <v>11124100</v>
@@ -5512,16 +5512,16 @@
         <v>44783</v>
       </c>
       <c r="B255" t="n">
-        <v>4.587120056152344</v>
+        <v>4.587119579315186</v>
       </c>
       <c r="C255" t="n">
-        <v>4.702911535999198</v>
+        <v>4.702911047125363</v>
       </c>
       <c r="D255" t="n">
-        <v>4.426793261065856</v>
+        <v>4.426792800894878</v>
       </c>
       <c r="E255" t="n">
-        <v>4.426793261065856</v>
+        <v>4.426792800894878</v>
       </c>
       <c r="F255" t="n">
         <v>9044400</v>
@@ -5532,16 +5532,16 @@
         <v>44784</v>
       </c>
       <c r="B256" t="n">
-        <v>4.346630573272705</v>
+        <v>4.346629619598389</v>
       </c>
       <c r="C256" t="n">
-        <v>4.685097802072197</v>
+        <v>4.685096774136335</v>
       </c>
       <c r="D256" t="n">
-        <v>4.311002488632787</v>
+        <v>4.311001542775466</v>
       </c>
       <c r="E256" t="n">
-        <v>4.61384120807209</v>
+        <v>4.613840195770312</v>
       </c>
       <c r="F256" t="n">
         <v>11482900</v>
@@ -5572,16 +5572,16 @@
         <v>44788</v>
       </c>
       <c r="B258" t="n">
-        <v>4.640562534332275</v>
+        <v>4.640562057495117</v>
       </c>
       <c r="C258" t="n">
-        <v>4.729632746899826</v>
+        <v>4.729632260910332</v>
       </c>
       <c r="D258" t="n">
-        <v>4.560399130661343</v>
+        <v>4.560398662061308</v>
       </c>
       <c r="E258" t="n">
-        <v>4.640562534332275</v>
+        <v>4.640562057495117</v>
       </c>
       <c r="F258" t="n">
         <v>10250500</v>
@@ -5592,16 +5592,16 @@
         <v>44789</v>
       </c>
       <c r="B259" t="n">
-        <v>4.622747898101807</v>
+        <v>4.62274694442749</v>
       </c>
       <c r="C259" t="n">
-        <v>4.702911291477053</v>
+        <v>4.702910321265003</v>
       </c>
       <c r="D259" t="n">
-        <v>4.560398544952146</v>
+        <v>4.560397604140521</v>
       </c>
       <c r="E259" t="n">
-        <v>4.676190018778564</v>
+        <v>4.676189054079122</v>
       </c>
       <c r="F259" t="n">
         <v>5754000</v>
@@ -5612,16 +5612,16 @@
         <v>44790</v>
       </c>
       <c r="B260" t="n">
-        <v>4.702911853790283</v>
+        <v>4.702911376953125</v>
       </c>
       <c r="C260" t="n">
-        <v>4.774168023212515</v>
+        <v>4.774167539150558</v>
       </c>
       <c r="D260" t="n">
-        <v>4.560399090225548</v>
+        <v>4.560398627838029</v>
       </c>
       <c r="E260" t="n">
-        <v>4.596027174936664</v>
+        <v>4.596026708936746</v>
       </c>
       <c r="F260" t="n">
         <v>27272900</v>
@@ -5632,16 +5632,16 @@
         <v>44791</v>
       </c>
       <c r="B261" t="n">
-        <v>4.533677577972412</v>
+        <v>4.53367805480957</v>
       </c>
       <c r="C261" t="n">
-        <v>4.711817975552381</v>
+        <v>4.711818471125755</v>
       </c>
       <c r="D261" t="n">
-        <v>4.515863538214415</v>
+        <v>4.515864013177952</v>
       </c>
       <c r="E261" t="n">
-        <v>4.640561816520393</v>
+        <v>4.640562304599281</v>
       </c>
       <c r="F261" t="n">
         <v>8785600</v>
@@ -5692,16 +5692,16 @@
         <v>44796</v>
       </c>
       <c r="B264" t="n">
-        <v>4.471328735351562</v>
+        <v>4.471328258514404</v>
       </c>
       <c r="C264" t="n">
-        <v>4.471328735351562</v>
+        <v>4.471328258514404</v>
       </c>
       <c r="D264" t="n">
-        <v>4.311002359282476</v>
+        <v>4.311001899543048</v>
       </c>
       <c r="E264" t="n">
-        <v>4.311002359282476</v>
+        <v>4.311001899543048</v>
       </c>
       <c r="F264" t="n">
         <v>6333000</v>
@@ -5712,16 +5712,16 @@
         <v>44797</v>
       </c>
       <c r="B265" t="n">
-        <v>4.533677577972412</v>
+        <v>4.53367805480957</v>
       </c>
       <c r="C265" t="n">
-        <v>4.6049337370044</v>
+        <v>4.604934221336045</v>
       </c>
       <c r="D265" t="n">
-        <v>4.426792914704221</v>
+        <v>4.426793380299605</v>
       </c>
       <c r="E265" t="n">
-        <v>4.453514186701321</v>
+        <v>4.45351465510716</v>
       </c>
       <c r="F265" t="n">
         <v>5861300</v>
@@ -5732,16 +5732,16 @@
         <v>44798</v>
       </c>
       <c r="B266" t="n">
-        <v>4.480235576629639</v>
+        <v>4.480236053466797</v>
       </c>
       <c r="C266" t="n">
-        <v>4.604933858217994</v>
+        <v>4.604934348326948</v>
       </c>
       <c r="D266" t="n">
-        <v>4.453514303929166</v>
+        <v>4.453514777922345</v>
       </c>
       <c r="E266" t="n">
-        <v>4.587119817991086</v>
+        <v>4.587120306204069</v>
       </c>
       <c r="F266" t="n">
         <v>4135100</v>
@@ -5772,16 +5772,16 @@
         <v>44802</v>
       </c>
       <c r="B268" t="n">
-        <v>4.453514099121094</v>
+        <v>4.453514575958252</v>
       </c>
       <c r="C268" t="n">
-        <v>4.480235370592709</v>
+        <v>4.48023585029091</v>
       </c>
       <c r="D268" t="n">
-        <v>4.266466472980391</v>
+        <v>4.266466929790385</v>
       </c>
       <c r="E268" t="n">
-        <v>4.275373705044331</v>
+        <v>4.275374162808021</v>
       </c>
       <c r="F268" t="n">
         <v>7870400</v>
@@ -5812,16 +5812,16 @@
         <v>44804</v>
       </c>
       <c r="B270" t="n">
-        <v>4.311002731323242</v>
+        <v>4.311001777648926</v>
       </c>
       <c r="C270" t="n">
-        <v>4.43570103458292</v>
+        <v>4.43570005332301</v>
       </c>
       <c r="D270" t="n">
-        <v>4.284281453978878</v>
+        <v>4.284280506215807</v>
       </c>
       <c r="E270" t="n">
-        <v>4.382258904614487</v>
+        <v>4.382257935176974</v>
       </c>
       <c r="F270" t="n">
         <v>8375100</v>
@@ -5832,16 +5832,16 @@
         <v>44805</v>
       </c>
       <c r="B271" t="n">
-        <v>4.24865198135376</v>
+        <v>4.248652458190918</v>
       </c>
       <c r="C271" t="n">
-        <v>4.426792356469578</v>
+        <v>4.42679285329989</v>
       </c>
       <c r="D271" t="n">
-        <v>4.177395831307432</v>
+        <v>4.177396300147329</v>
       </c>
       <c r="E271" t="n">
-        <v>4.346629400027538</v>
+        <v>4.346629887860955</v>
       </c>
       <c r="F271" t="n">
         <v>13026600</v>
@@ -5872,16 +5872,16 @@
         <v>44809</v>
       </c>
       <c r="B273" t="n">
-        <v>4.115047931671143</v>
+        <v>4.115046501159668</v>
       </c>
       <c r="C273" t="n">
-        <v>4.221932194247465</v>
+        <v>4.221930726579882</v>
       </c>
       <c r="D273" t="n">
-        <v>4.115047931671143</v>
+        <v>4.115046501159668</v>
       </c>
       <c r="E273" t="n">
-        <v>4.123955165912656</v>
+        <v>4.123953732304765</v>
       </c>
       <c r="F273" t="n">
         <v>7604300</v>
@@ -5912,16 +5912,16 @@
         <v>44812</v>
       </c>
       <c r="B275" t="n">
-        <v>3.910185813903809</v>
+        <v>3.910186052322388</v>
       </c>
       <c r="C275" t="n">
-        <v>4.008163256882613</v>
+        <v>4.008163501275241</v>
       </c>
       <c r="D275" t="n">
-        <v>3.856743688111805</v>
+        <v>3.856743923271819</v>
       </c>
       <c r="E275" t="n">
-        <v>3.990349214951944</v>
+        <v>3.990349458258384</v>
       </c>
       <c r="F275" t="n">
         <v>9864000</v>
@@ -5932,16 +5932,16 @@
         <v>44813</v>
       </c>
       <c r="B276" t="n">
-        <v>3.910185813903809</v>
+        <v>3.910186052322388</v>
       </c>
       <c r="C276" t="n">
-        <v>4.043791340743948</v>
+        <v>4.043791587308953</v>
       </c>
       <c r="D276" t="n">
-        <v>3.883464963367938</v>
+        <v>3.883465200157247</v>
       </c>
       <c r="E276" t="n">
-        <v>3.945813897765144</v>
+        <v>3.9458141383561</v>
       </c>
       <c r="F276" t="n">
         <v>15548300</v>
@@ -5952,16 +5952,16 @@
         <v>44816</v>
       </c>
       <c r="B277" t="n">
-        <v>3.856743335723877</v>
+        <v>3.856743574142456</v>
       </c>
       <c r="C277" t="n">
-        <v>3.990348850356574</v>
+        <v>3.990349097034463</v>
       </c>
       <c r="D277" t="n">
-        <v>3.838929295420866</v>
+        <v>3.838929532738205</v>
       </c>
       <c r="E277" t="n">
-        <v>3.954720769750552</v>
+        <v>3.954721014225961</v>
       </c>
       <c r="F277" t="n">
         <v>15738600</v>
@@ -5972,16 +5972,16 @@
         <v>44817</v>
       </c>
       <c r="B278" t="n">
-        <v>3.696416854858398</v>
+        <v>3.696417570114136</v>
       </c>
       <c r="C278" t="n">
-        <v>3.883464484422043</v>
+        <v>3.88346523587145</v>
       </c>
       <c r="D278" t="n">
-        <v>3.678602815124728</v>
+        <v>3.678603526933453</v>
       </c>
       <c r="E278" t="n">
-        <v>3.874557252195103</v>
+        <v>3.874558001920963</v>
       </c>
       <c r="F278" t="n">
         <v>21443000</v>
@@ -5992,16 +5992,16 @@
         <v>44818</v>
       </c>
       <c r="B279" t="n">
-        <v>3.740951776504517</v>
+        <v>3.740952491760254</v>
       </c>
       <c r="C279" t="n">
-        <v>3.821115168409112</v>
+        <v>3.821115898991784</v>
       </c>
       <c r="D279" t="n">
-        <v>3.67860284921891</v>
+        <v>3.678603552553769</v>
       </c>
       <c r="E279" t="n">
-        <v>3.705323696706966</v>
+        <v>3.70532440515075</v>
       </c>
       <c r="F279" t="n">
         <v>13539100</v>
@@ -6012,16 +6012,16 @@
         <v>44819</v>
       </c>
       <c r="B280" t="n">
-        <v>3.749859571456909</v>
+        <v>3.749859094619751</v>
       </c>
       <c r="C280" t="n">
-        <v>3.758766380382601</v>
+        <v>3.758765902412841</v>
       </c>
       <c r="D280" t="n">
-        <v>3.634068082380977</v>
+        <v>3.634067620268019</v>
       </c>
       <c r="E280" t="n">
-        <v>3.740952337810941</v>
+        <v>3.740951862106438</v>
       </c>
       <c r="F280" t="n">
         <v>12717200</v>
@@ -6032,16 +6032,16 @@
         <v>44820</v>
       </c>
       <c r="B281" t="n">
-        <v>3.821115255355835</v>
+        <v>3.821115493774414</v>
       </c>
       <c r="C281" t="n">
-        <v>3.892371416572319</v>
+        <v>3.892371659436928</v>
       </c>
       <c r="D281" t="n">
-        <v>3.660788892618747</v>
+        <v>3.660789121033758</v>
       </c>
       <c r="E281" t="n">
-        <v>3.696416973226988</v>
+        <v>3.696417203865015</v>
       </c>
       <c r="F281" t="n">
         <v>19813000</v>
@@ -6052,16 +6052,16 @@
         <v>44823</v>
       </c>
       <c r="B282" t="n">
-        <v>3.990349292755127</v>
+        <v>3.99034857749939</v>
       </c>
       <c r="C282" t="n">
-        <v>4.00816333503313</v>
+        <v>4.00816261658429</v>
       </c>
       <c r="D282" t="n">
-        <v>3.794394827697093</v>
+        <v>3.794394147565487</v>
       </c>
       <c r="E282" t="n">
-        <v>3.830022912253099</v>
+        <v>3.830022225735288</v>
       </c>
       <c r="F282" t="n">
         <v>8945000</v>
@@ -6072,16 +6072,16 @@
         <v>44824</v>
       </c>
       <c r="B283" t="n">
-        <v>3.963627338409424</v>
+        <v>3.963628053665161</v>
       </c>
       <c r="C283" t="n">
-        <v>4.132860923437988</v>
+        <v>4.132861669232745</v>
       </c>
       <c r="D283" t="n">
-        <v>3.919092452698874</v>
+        <v>3.919093159918075</v>
       </c>
       <c r="E283" t="n">
-        <v>3.990348609611912</v>
+        <v>3.990349329689632</v>
       </c>
       <c r="F283" t="n">
         <v>10696200</v>
@@ -6092,16 +6092,16 @@
         <v>44825</v>
       </c>
       <c r="B284" t="n">
-        <v>3.883465051651001</v>
+        <v>3.883464574813843</v>
       </c>
       <c r="C284" t="n">
-        <v>4.034884623864039</v>
+        <v>4.034884128434599</v>
       </c>
       <c r="D284" t="n">
-        <v>3.830022924644094</v>
+        <v>3.830022454368909</v>
       </c>
       <c r="E284" t="n">
-        <v>3.972535263329179</v>
+        <v>3.972534775555399</v>
       </c>
       <c r="F284" t="n">
         <v>18275700</v>
@@ -6132,16 +6132,16 @@
         <v>44827</v>
       </c>
       <c r="B286" t="n">
-        <v>3.910185813903809</v>
+        <v>3.910186052322388</v>
       </c>
       <c r="C286" t="n">
-        <v>3.990349214951944</v>
+        <v>3.990349458258384</v>
       </c>
       <c r="D286" t="n">
-        <v>3.847836879506602</v>
+        <v>3.847837114123534</v>
       </c>
       <c r="E286" t="n">
-        <v>3.963627939695812</v>
+        <v>3.963628181372956</v>
       </c>
       <c r="F286" t="n">
         <v>14173200</v>
@@ -6152,16 +6152,16 @@
         <v>44830</v>
       </c>
       <c r="B287" t="n">
-        <v>3.821115255355835</v>
+        <v>3.821115493774414</v>
       </c>
       <c r="C287" t="n">
-        <v>3.936906729692732</v>
+        <v>3.936906975336123</v>
       </c>
       <c r="D287" t="n">
-        <v>3.794394407259765</v>
+        <v>3.794394644011096</v>
       </c>
       <c r="E287" t="n">
-        <v>3.901278649084491</v>
+        <v>3.901278892504866</v>
       </c>
       <c r="F287" t="n">
         <v>9718800</v>
@@ -6172,16 +6172,16 @@
         <v>44831</v>
       </c>
       <c r="B288" t="n">
-        <v>3.732044696807861</v>
+        <v>3.732045412063599</v>
       </c>
       <c r="C288" t="n">
-        <v>3.919092314467266</v>
+        <v>3.91909306557115</v>
       </c>
       <c r="D288" t="n">
-        <v>3.732044696807861</v>
+        <v>3.732045412063599</v>
       </c>
       <c r="E288" t="n">
-        <v>3.838928928407469</v>
+        <v>3.838929664147838</v>
       </c>
       <c r="F288" t="n">
         <v>11052300</v>
@@ -6192,16 +6192,16 @@
         <v>44832</v>
       </c>
       <c r="B289" t="n">
-        <v>3.687509775161743</v>
+        <v>3.687510013580322</v>
       </c>
       <c r="C289" t="n">
-        <v>3.767673169639246</v>
+        <v>3.767673413240847</v>
       </c>
       <c r="D289" t="n">
-        <v>3.687509775161743</v>
+        <v>3.687510013580322</v>
       </c>
       <c r="E289" t="n">
-        <v>3.749859129168715</v>
+        <v>3.749859371618537</v>
       </c>
       <c r="F289" t="n">
         <v>11148900</v>
@@ -6212,16 +6212,16 @@
         <v>44833</v>
       </c>
       <c r="B290" t="n">
-        <v>3.696416854858398</v>
+        <v>3.696417570114136</v>
       </c>
       <c r="C290" t="n">
-        <v>3.714230894592069</v>
+        <v>3.714231613294819</v>
       </c>
       <c r="D290" t="n">
-        <v>3.616253463696776</v>
+        <v>3.616254163440918</v>
       </c>
       <c r="E290" t="n">
-        <v>3.660788775391057</v>
+        <v>3.660789483752771</v>
       </c>
       <c r="F290" t="n">
         <v>12380300</v>
@@ -6232,16 +6232,16 @@
         <v>44834</v>
       </c>
       <c r="B291" t="n">
-        <v>3.732044696807861</v>
+        <v>3.732045412063599</v>
       </c>
       <c r="C291" t="n">
-        <v>3.794394044267724</v>
+        <v>3.79439477147287</v>
       </c>
       <c r="D291" t="n">
-        <v>3.651881310748065</v>
+        <v>3.651882010640287</v>
       </c>
       <c r="E291" t="n">
-        <v>3.660788542408123</v>
+        <v>3.660789244007439</v>
       </c>
       <c r="F291" t="n">
         <v>11827700</v>
@@ -6252,16 +6252,16 @@
         <v>44837</v>
       </c>
       <c r="B292" t="n">
-        <v>3.939895391464233</v>
+        <v>3.939894676208496</v>
       </c>
       <c r="C292" t="n">
-        <v>3.939895391464233</v>
+        <v>3.939894676208497</v>
       </c>
       <c r="D292" t="n">
-        <v>3.79630024781367</v>
+        <v>3.796299558626456</v>
       </c>
       <c r="E292" t="n">
-        <v>3.814249640769991</v>
+        <v>3.814248948324211</v>
       </c>
       <c r="F292" t="n">
         <v>14167700</v>
@@ -6272,16 +6272,16 @@
         <v>44838</v>
       </c>
       <c r="B293" t="n">
-        <v>3.930919647216797</v>
+        <v>3.930920124053955</v>
       </c>
       <c r="C293" t="n">
-        <v>4.056565357581396</v>
+        <v>4.05656584965991</v>
       </c>
       <c r="D293" t="n">
-        <v>3.895020872826911</v>
+        <v>3.895021345309396</v>
       </c>
       <c r="E293" t="n">
-        <v>3.97579290123058</v>
+        <v>3.975793383511054</v>
       </c>
       <c r="F293" t="n">
         <v>11413300</v>
@@ -6292,16 +6292,16 @@
         <v>44839</v>
       </c>
       <c r="B294" t="n">
-        <v>3.975793361663818</v>
+        <v>3.975793600082397</v>
       </c>
       <c r="C294" t="n">
-        <v>3.975793361663818</v>
+        <v>3.975793600082397</v>
       </c>
       <c r="D294" t="n">
-        <v>3.868097026021941</v>
+        <v>3.868097257982235</v>
       </c>
       <c r="E294" t="n">
-        <v>3.92194519384288</v>
+        <v>3.921945429032316</v>
       </c>
       <c r="F294" t="n">
         <v>8368900</v>
@@ -6312,16 +6312,16 @@
         <v>44840</v>
       </c>
       <c r="B295" t="n">
-        <v>4.002717018127441</v>
+        <v>4.002717971801758</v>
       </c>
       <c r="C295" t="n">
-        <v>4.029640883749863</v>
+        <v>4.029641843838973</v>
       </c>
       <c r="D295" t="n">
-        <v>3.975792724557891</v>
+        <v>3.975793671817313</v>
       </c>
       <c r="E295" t="n">
-        <v>3.993742110955215</v>
+        <v>3.9937430624912</v>
       </c>
       <c r="F295" t="n">
         <v>5975200</v>
@@ -6332,16 +6332,16 @@
         <v>44841</v>
       </c>
       <c r="B296" t="n">
-        <v>3.760400533676147</v>
+        <v>3.760401010513306</v>
       </c>
       <c r="C296" t="n">
-        <v>4.002717492746105</v>
+        <v>4.002718000310238</v>
       </c>
       <c r="D296" t="n">
-        <v>3.715526848388416</v>
+        <v>3.715527319535371</v>
       </c>
       <c r="E296" t="n">
-        <v>3.984768104220449</v>
+        <v>3.984768609508511</v>
       </c>
       <c r="F296" t="n">
         <v>16354500</v>
@@ -6372,16 +6372,16 @@
         <v>44845</v>
       </c>
       <c r="B298" t="n">
-        <v>3.903995752334595</v>
+        <v>3.903995513916016</v>
       </c>
       <c r="C298" t="n">
-        <v>3.948869438891908</v>
+        <v>3.948869197732875</v>
       </c>
       <c r="D298" t="n">
-        <v>3.634754916832287</v>
+        <v>3.634754694856352</v>
       </c>
       <c r="E298" t="n">
-        <v>3.661678786408922</v>
+        <v>3.661678562788736</v>
       </c>
       <c r="F298" t="n">
         <v>30833900</v>
@@ -6392,16 +6392,16 @@
         <v>44847</v>
       </c>
       <c r="B299" t="n">
-        <v>3.814249038696289</v>
+        <v>3.81424880027771</v>
       </c>
       <c r="C299" t="n">
-        <v>3.903995989311464</v>
+        <v>3.903995745283042</v>
       </c>
       <c r="D299" t="n">
-        <v>3.796299648573254</v>
+        <v>3.796299411276644</v>
       </c>
       <c r="E299" t="n">
-        <v>3.895021508223556</v>
+        <v>3.895021264756104</v>
       </c>
       <c r="F299" t="n">
         <v>15027200</v>
@@ -6412,16 +6412,16 @@
         <v>44848</v>
       </c>
       <c r="B300" t="n">
-        <v>3.688603162765503</v>
+        <v>3.688603401184082</v>
       </c>
       <c r="C300" t="n">
-        <v>3.832198278102312</v>
+        <v>3.832198525802385</v>
       </c>
       <c r="D300" t="n">
-        <v>3.679628254083352</v>
+        <v>3.679628491921824</v>
       </c>
       <c r="E300" t="n">
-        <v>3.823223797367362</v>
+        <v>3.823224044487355</v>
       </c>
       <c r="F300" t="n">
         <v>10535000</v>
@@ -6472,16 +6472,16 @@
         <v>44853</v>
       </c>
       <c r="B303" t="n">
-        <v>3.733476400375366</v>
+        <v>3.733476161956787</v>
       </c>
       <c r="C303" t="n">
-        <v>3.769375178998422</v>
+        <v>3.769374938287358</v>
       </c>
       <c r="D303" t="n">
-        <v>3.670653751758618</v>
+        <v>3.670653517351873</v>
       </c>
       <c r="E303" t="n">
-        <v>3.715527011063839</v>
+        <v>3.715526773791502</v>
       </c>
       <c r="F303" t="n">
         <v>12625300</v>
@@ -6492,16 +6492,16 @@
         <v>44854</v>
       </c>
       <c r="B304" t="n">
-        <v>3.769374847412109</v>
+        <v>3.769375801086426</v>
       </c>
       <c r="C304" t="n">
-        <v>3.796299142984509</v>
+        <v>3.796300103470833</v>
       </c>
       <c r="D304" t="n">
-        <v>3.706552204321775</v>
+        <v>3.706553142101589</v>
       </c>
       <c r="E304" t="n">
-        <v>3.760400367519416</v>
+        <v>3.760401318923135</v>
       </c>
       <c r="F304" t="n">
         <v>13428400</v>
@@ -6512,16 +6512,16 @@
         <v>44855</v>
       </c>
       <c r="B305" t="n">
-        <v>3.83219838142395</v>
+        <v>3.832198143005371</v>
       </c>
       <c r="C305" t="n">
-        <v>3.85912268024912</v>
+        <v>3.859122440155458</v>
       </c>
       <c r="D305" t="n">
-        <v>3.733476522994609</v>
+        <v>3.733476290717968</v>
       </c>
       <c r="E305" t="n">
-        <v>3.760400821819779</v>
+        <v>3.760400587868054</v>
       </c>
       <c r="F305" t="n">
         <v>14614900</v>
@@ -6532,16 +6532,16 @@
         <v>44858</v>
       </c>
       <c r="B306" t="n">
-        <v>3.706552982330322</v>
+        <v>3.706552743911743</v>
       </c>
       <c r="C306" t="n">
-        <v>3.778350548330878</v>
+        <v>3.778350305294026</v>
       </c>
       <c r="D306" t="n">
-        <v>3.697578072606628</v>
+        <v>3.697577834765347</v>
       </c>
       <c r="E306" t="n">
-        <v>3.769375638607184</v>
+        <v>3.76937539614763</v>
       </c>
       <c r="F306" t="n">
         <v>9021900</v>
@@ -6572,16 +6572,16 @@
         <v>44860</v>
       </c>
       <c r="B308" t="n">
-        <v>3.562957048416138</v>
+        <v>3.562957286834717</v>
       </c>
       <c r="C308" t="n">
-        <v>3.670653593619109</v>
+        <v>3.670653839244302</v>
       </c>
       <c r="D308" t="n">
-        <v>3.545007659877907</v>
+        <v>3.545007897095387</v>
       </c>
       <c r="E308" t="n">
-        <v>3.661678685376404</v>
+        <v>3.661678930401033</v>
       </c>
       <c r="F308" t="n">
         <v>15630800</v>
@@ -6592,16 +6592,16 @@
         <v>44861</v>
       </c>
       <c r="B309" t="n">
-        <v>3.706552982330322</v>
+        <v>3.706552743911743</v>
       </c>
       <c r="C309" t="n">
-        <v>3.760401156830739</v>
+        <v>3.760400914948455</v>
       </c>
       <c r="D309" t="n">
-        <v>3.580907027855725</v>
+        <v>3.580906797519137</v>
       </c>
       <c r="E309" t="n">
-        <v>3.580907027855725</v>
+        <v>3.580906797519137</v>
       </c>
       <c r="F309" t="n">
         <v>15175200</v>
@@ -6612,16 +6612,16 @@
         <v>44862</v>
       </c>
       <c r="B310" t="n">
-        <v>3.724502086639404</v>
+        <v>3.724502325057983</v>
       </c>
       <c r="C310" t="n">
-        <v>3.73347656772384</v>
+        <v>3.733476806716907</v>
       </c>
       <c r="D310" t="n">
-        <v>3.643729617143404</v>
+        <v>3.643729850391451</v>
       </c>
       <c r="E310" t="n">
-        <v>3.68860330640723</v>
+        <v>3.688603542527801</v>
       </c>
       <c r="F310" t="n">
         <v>9985100</v>
@@ -6632,16 +6632,16 @@
         <v>44865</v>
       </c>
       <c r="B311" t="n">
-        <v>3.850147485733032</v>
+        <v>3.850147724151611</v>
       </c>
       <c r="C311" t="n">
-        <v>3.868096874302645</v>
+        <v>3.868097113832732</v>
       </c>
       <c r="D311" t="n">
-        <v>3.54500766607602</v>
+        <v>3.545007885598959</v>
       </c>
       <c r="E311" t="n">
-        <v>3.589881137500053</v>
+        <v>3.58988135980176</v>
       </c>
       <c r="F311" t="n">
         <v>19491700</v>
@@ -6692,16 +6692,16 @@
         <v>44869</v>
       </c>
       <c r="B314" t="n">
-        <v>4.236059188842773</v>
+        <v>4.23606014251709</v>
       </c>
       <c r="C314" t="n">
-        <v>4.343755938925132</v>
+        <v>4.34375691684548</v>
       </c>
       <c r="D314" t="n">
-        <v>4.155287161214933</v>
+        <v>4.155288096704846</v>
       </c>
       <c r="E314" t="n">
-        <v>4.218109801820237</v>
+        <v>4.218110751453565</v>
       </c>
       <c r="F314" t="n">
         <v>12500600</v>
@@ -6712,16 +6712,16 @@
         <v>44872</v>
       </c>
       <c r="B315" t="n">
-        <v>4.011692047119141</v>
+        <v>4.011692523956299</v>
       </c>
       <c r="C315" t="n">
-        <v>4.37965516061104</v>
+        <v>4.379655681184977</v>
       </c>
       <c r="D315" t="n">
-        <v>4.011692047119141</v>
+        <v>4.011692523956299</v>
       </c>
       <c r="E315" t="n">
-        <v>4.3168320856375</v>
+        <v>4.316832598744169</v>
       </c>
       <c r="F315" t="n">
         <v>17217400</v>
@@ -6732,16 +6732,16 @@
         <v>44873</v>
       </c>
       <c r="B316" t="n">
-        <v>4.083489894866943</v>
+        <v>4.083490371704102</v>
       </c>
       <c r="C316" t="n">
-        <v>4.110413763284799</v>
+        <v>4.110414243265911</v>
       </c>
       <c r="D316" t="n">
-        <v>3.966818657197105</v>
+        <v>3.966819120410333</v>
       </c>
       <c r="E316" t="n">
-        <v>4.011691913875923</v>
+        <v>4.01169238232909</v>
       </c>
       <c r="F316" t="n">
         <v>15444300</v>
@@ -6752,16 +6752,16 @@
         <v>44874</v>
       </c>
       <c r="B317" t="n">
-        <v>4.011692047119141</v>
+        <v>4.011692523956299</v>
       </c>
       <c r="C317" t="n">
-        <v>4.173236974780477</v>
+        <v>4.173237470819165</v>
       </c>
       <c r="D317" t="n">
-        <v>3.984768177807042</v>
+        <v>3.98476865144398</v>
       </c>
       <c r="E317" t="n">
-        <v>4.06554064163771</v>
+        <v>4.065541124875413</v>
       </c>
       <c r="F317" t="n">
         <v>11339500</v>
@@ -6772,16 +6772,16 @@
         <v>44875</v>
       </c>
       <c r="B318" t="n">
-        <v>3.688603162765503</v>
+        <v>3.688603401184082</v>
       </c>
       <c r="C318" t="n">
-        <v>3.975793393439122</v>
+        <v>3.975793650420687</v>
       </c>
       <c r="D318" t="n">
-        <v>3.670653773348401</v>
+        <v>3.670654010606794</v>
       </c>
       <c r="E318" t="n">
-        <v>3.921945225187819</v>
+        <v>3.921945478688824</v>
       </c>
       <c r="F318" t="n">
         <v>22566600</v>
@@ -6812,16 +6812,16 @@
         <v>44879</v>
       </c>
       <c r="B320" t="n">
-        <v>3.697577714920044</v>
+        <v>3.697577476501465</v>
       </c>
       <c r="C320" t="n">
-        <v>3.796299572594537</v>
+        <v>3.796299327810405</v>
       </c>
       <c r="D320" t="n">
-        <v>3.64372954562865</v>
+        <v>3.643729310682183</v>
       </c>
       <c r="E320" t="n">
-        <v>3.760400793066941</v>
+        <v>3.760400550597551</v>
       </c>
       <c r="F320" t="n">
         <v>10873300</v>
@@ -6832,16 +6832,16 @@
         <v>44881</v>
       </c>
       <c r="B321" t="n">
-        <v>3.616805791854858</v>
+        <v>3.616805553436279</v>
       </c>
       <c r="C321" t="n">
-        <v>3.760400914606361</v>
+        <v>3.760400666722041</v>
       </c>
       <c r="D321" t="n">
-        <v>3.553982711677465</v>
+        <v>3.553982477400161</v>
       </c>
       <c r="E321" t="n">
-        <v>3.697577834428968</v>
+        <v>3.697577590685923</v>
       </c>
       <c r="F321" t="n">
         <v>16148800</v>
@@ -6872,16 +6872,16 @@
         <v>44883</v>
       </c>
       <c r="B323" t="n">
-        <v>3.652704238891602</v>
+        <v>3.652704477310181</v>
       </c>
       <c r="C323" t="n">
-        <v>3.841173034261142</v>
+        <v>3.841173284981419</v>
       </c>
       <c r="D323" t="n">
-        <v>3.536032998339565</v>
+        <v>3.536033229142802</v>
       </c>
       <c r="E323" t="n">
-        <v>3.580906470100505</v>
+        <v>3.580906703832715</v>
       </c>
       <c r="F323" t="n">
         <v>23150300</v>
@@ -6892,16 +6892,16 @@
         <v>44886</v>
       </c>
       <c r="B324" t="n">
-        <v>3.616805791854858</v>
+        <v>3.616805553436279</v>
       </c>
       <c r="C324" t="n">
-        <v>3.733476615116843</v>
+        <v>3.733476369007364</v>
       </c>
       <c r="D324" t="n">
-        <v>3.545008016505496</v>
+        <v>3.545007782819801</v>
       </c>
       <c r="E324" t="n">
-        <v>3.67962844408503</v>
+        <v>3.679628201525203</v>
       </c>
       <c r="F324" t="n">
         <v>11314600</v>
@@ -6912,16 +6912,16 @@
         <v>44887</v>
       </c>
       <c r="B325" t="n">
-        <v>3.616805791854858</v>
+        <v>3.616805553436279</v>
       </c>
       <c r="C325" t="n">
-        <v>3.661679053741092</v>
+        <v>3.661678812364483</v>
       </c>
       <c r="D325" t="n">
-        <v>3.562957406849434</v>
+        <v>3.562957171980521</v>
       </c>
       <c r="E325" t="n">
-        <v>3.616805791854858</v>
+        <v>3.616805553436279</v>
       </c>
       <c r="F325" t="n">
         <v>10439300</v>
@@ -6932,16 +6932,16 @@
         <v>44888</v>
       </c>
       <c r="B326" t="n">
-        <v>3.589881181716919</v>
+        <v>3.589881420135498</v>
       </c>
       <c r="C326" t="n">
-        <v>3.643729348089011</v>
+        <v>3.643729590083865</v>
       </c>
       <c r="D326" t="n">
-        <v>3.545007709740176</v>
+        <v>3.545007945178526</v>
       </c>
       <c r="E326" t="n">
-        <v>3.571931792926222</v>
+        <v>3.571932030152709</v>
       </c>
       <c r="F326" t="n">
         <v>6531500</v>
@@ -6952,16 +6952,16 @@
         <v>44889</v>
       </c>
       <c r="B327" t="n">
-        <v>3.724502086639404</v>
+        <v>3.724502325057983</v>
       </c>
       <c r="C327" t="n">
-        <v>3.742451476755492</v>
+        <v>3.742451716323075</v>
       </c>
       <c r="D327" t="n">
-        <v>3.598856355826795</v>
+        <v>3.598856586202345</v>
       </c>
       <c r="E327" t="n">
-        <v>3.634755136058969</v>
+        <v>3.634755368732528</v>
       </c>
       <c r="F327" t="n">
         <v>5511600</v>
@@ -6972,16 +6972,16 @@
         <v>44890</v>
       </c>
       <c r="B328" t="n">
-        <v>3.63475513458252</v>
+        <v>3.63475489616394</v>
       </c>
       <c r="C328" t="n">
-        <v>3.760400865344091</v>
+        <v>3.76040061868389</v>
       </c>
       <c r="D328" t="n">
-        <v>3.580906750282523</v>
+        <v>3.580906515396082</v>
       </c>
       <c r="E328" t="n">
-        <v>3.733476566207289</v>
+        <v>3.733476321313164</v>
       </c>
       <c r="F328" t="n">
         <v>8739900</v>
@@ -6992,16 +6992,16 @@
         <v>44893</v>
       </c>
       <c r="B329" t="n">
-        <v>3.60783052444458</v>
+        <v>3.607830762863159</v>
       </c>
       <c r="C329" t="n">
-        <v>3.670653598383518</v>
+        <v>3.670653840953675</v>
       </c>
       <c r="D329" t="n">
-        <v>3.589881135883052</v>
+        <v>3.58988137311547</v>
       </c>
       <c r="E329" t="n">
-        <v>3.589881135883052</v>
+        <v>3.58988137311547</v>
       </c>
       <c r="F329" t="n">
         <v>7386900</v>
@@ -7012,16 +7012,16 @@
         <v>44894</v>
       </c>
       <c r="B330" t="n">
-        <v>3.589881181716919</v>
+        <v>3.589881420135498</v>
       </c>
       <c r="C330" t="n">
-        <v>3.715526903251799</v>
+        <v>3.715527150015021</v>
       </c>
       <c r="D330" t="n">
-        <v>3.51808362655413</v>
+        <v>3.518083860204342</v>
       </c>
       <c r="E330" t="n">
-        <v>3.616805478876557</v>
+        <v>3.616805719083288</v>
       </c>
       <c r="F330" t="n">
         <v>13237500</v>
@@ -7032,16 +7032,16 @@
         <v>44895</v>
       </c>
       <c r="B331" t="n">
-        <v>3.63475513458252</v>
+        <v>3.63475489616394</v>
       </c>
       <c r="C331" t="n">
-        <v>3.661679005772105</v>
+        <v>3.661678765587478</v>
       </c>
       <c r="D331" t="n">
-        <v>3.518083884901738</v>
+        <v>3.518083654136107</v>
       </c>
       <c r="E331" t="n">
-        <v>3.571932055228125</v>
+        <v>3.571931820930371</v>
       </c>
       <c r="F331" t="n">
         <v>16877200</v>
@@ -7092,16 +7092,16 @@
         <v>44900</v>
       </c>
       <c r="B334" t="n">
-        <v>3.347563982009888</v>
+        <v>3.347564458847046</v>
       </c>
       <c r="C334" t="n">
-        <v>3.545007458699114</v>
+        <v>3.545007963660719</v>
       </c>
       <c r="D334" t="n">
-        <v>3.329614594490283</v>
+        <v>3.329615068770676</v>
       </c>
       <c r="E334" t="n">
-        <v>3.545007458699114</v>
+        <v>3.545007963660719</v>
       </c>
       <c r="F334" t="n">
         <v>14607600</v>
@@ -7112,16 +7112,16 @@
         <v>44901</v>
       </c>
       <c r="B335" t="n">
-        <v>3.302690982818604</v>
+        <v>3.302690744400024</v>
       </c>
       <c r="C335" t="n">
-        <v>3.401412628213602</v>
+        <v>3.401412382668387</v>
       </c>
       <c r="D335" t="n">
-        <v>3.248842598629542</v>
+        <v>3.248842364098234</v>
       </c>
       <c r="E335" t="n">
-        <v>3.383463238141784</v>
+        <v>3.383462993892321</v>
       </c>
       <c r="F335" t="n">
         <v>13327400</v>
@@ -7172,16 +7172,16 @@
         <v>44904</v>
       </c>
       <c r="B338" t="n">
-        <v>3.082778215408325</v>
+        <v>3.082777976989746</v>
       </c>
       <c r="C338" t="n">
-        <v>3.119587692876894</v>
+        <v>3.119587451611511</v>
       </c>
       <c r="D338" t="n">
-        <v>2.990755070238115</v>
+        <v>2.990754838936502</v>
       </c>
       <c r="E338" t="n">
-        <v>3.101182844442367</v>
+        <v>3.101182604600395</v>
       </c>
       <c r="F338" t="n">
         <v>12963000</v>
@@ -7192,16 +7192,16 @@
         <v>44907</v>
       </c>
       <c r="B339" t="n">
-        <v>3.036766529083252</v>
+        <v>3.036766290664673</v>
       </c>
       <c r="C339" t="n">
-        <v>3.119587576034921</v>
+        <v>3.119587331114006</v>
       </c>
       <c r="D339" t="n">
-        <v>2.972350329876769</v>
+        <v>2.972350096515548</v>
       </c>
       <c r="E339" t="n">
-        <v>3.082778099945025</v>
+        <v>3.082777857914047</v>
       </c>
       <c r="F339" t="n">
         <v>24013800</v>
@@ -7252,16 +7252,16 @@
         <v>44910</v>
       </c>
       <c r="B342" t="n">
-        <v>3.036766529083252</v>
+        <v>3.036766290664673</v>
       </c>
       <c r="C342" t="n">
-        <v>3.13799220437963</v>
+        <v>3.137991958013755</v>
       </c>
       <c r="D342" t="n">
-        <v>3.009159586566188</v>
+        <v>3.009159350315048</v>
       </c>
       <c r="E342" t="n">
-        <v>3.055171157427961</v>
+        <v>3.055170917564423</v>
       </c>
       <c r="F342" t="n">
         <v>8858500</v>
@@ -7332,16 +7332,16 @@
         <v>44916</v>
       </c>
       <c r="B346" t="n">
-        <v>3.331240653991699</v>
+        <v>3.331240892410278</v>
       </c>
       <c r="C346" t="n">
-        <v>3.37725244220964</v>
+        <v>3.377252683921307</v>
       </c>
       <c r="D346" t="n">
-        <v>3.23921751635675</v>
+        <v>3.239217748189187</v>
       </c>
       <c r="E346" t="n">
-        <v>3.266824457647235</v>
+        <v>3.266824691455514</v>
       </c>
       <c r="F346" t="n">
         <v>14610300</v>
@@ -7372,16 +7372,16 @@
         <v>44918</v>
       </c>
       <c r="B348" t="n">
-        <v>3.414062023162842</v>
+        <v>3.414061546325684</v>
       </c>
       <c r="C348" t="n">
-        <v>3.441668967088628</v>
+        <v>3.441668486395647</v>
       </c>
       <c r="D348" t="n">
-        <v>3.340443506027412</v>
+        <v>3.340443039472447</v>
       </c>
       <c r="E348" t="n">
-        <v>3.35884813531127</v>
+        <v>3.358847666185756</v>
       </c>
       <c r="F348" t="n">
         <v>4486400</v>
@@ -7412,16 +7412,16 @@
         <v>44922</v>
       </c>
       <c r="B350" t="n">
-        <v>3.386454820632935</v>
+        <v>3.386454582214355</v>
       </c>
       <c r="C350" t="n">
-        <v>3.395657134572136</v>
+        <v>3.39565689550568</v>
       </c>
       <c r="D350" t="n">
-        <v>3.276026833962055</v>
+        <v>3.276026603318003</v>
       </c>
       <c r="E350" t="n">
-        <v>3.349645564876132</v>
+        <v>3.349645329049056</v>
       </c>
       <c r="F350" t="n">
         <v>5669100</v>
@@ -7592,16 +7592,16 @@
         <v>44936</v>
       </c>
       <c r="B359" t="n">
-        <v>3.082778215408325</v>
+        <v>3.082777976989746</v>
       </c>
       <c r="C359" t="n">
-        <v>3.082778215408325</v>
+        <v>3.082777976989746</v>
       </c>
       <c r="D359" t="n">
-        <v>2.953945812170032</v>
+        <v>2.953945583715205</v>
       </c>
       <c r="E359" t="n">
-        <v>2.963148126687053</v>
+        <v>2.963147897520529</v>
       </c>
       <c r="F359" t="n">
         <v>12594800</v>
@@ -7612,16 +7612,16 @@
         <v>44937</v>
       </c>
       <c r="B360" t="n">
-        <v>3.294431447982788</v>
+        <v>3.294431209564209</v>
       </c>
       <c r="C360" t="n">
-        <v>3.294431447982788</v>
+        <v>3.294431209564209</v>
       </c>
       <c r="D360" t="n">
-        <v>3.091980322771489</v>
+        <v>3.091980099004334</v>
       </c>
       <c r="E360" t="n">
-        <v>3.091980322771489</v>
+        <v>3.091980099004334</v>
       </c>
       <c r="F360" t="n">
         <v>21444400</v>
@@ -7632,16 +7632,16 @@
         <v>44938</v>
       </c>
       <c r="B361" t="n">
-        <v>3.211610555648804</v>
+        <v>3.211610794067383</v>
       </c>
       <c r="C361" t="n">
-        <v>3.349645480667133</v>
+        <v>3.349645729332935</v>
       </c>
       <c r="D361" t="n">
-        <v>3.165598987109516</v>
+        <v>3.165599222112359</v>
       </c>
       <c r="E361" t="n">
-        <v>3.266824437895949</v>
+        <v>3.266824680413411</v>
       </c>
       <c r="F361" t="n">
         <v>13176700</v>
@@ -7672,16 +7672,16 @@
         <v>44942</v>
       </c>
       <c r="B363" t="n">
-        <v>3.036766529083252</v>
+        <v>3.036766290664673</v>
       </c>
       <c r="C363" t="n">
-        <v>3.082778099945025</v>
+        <v>3.082777857914047</v>
       </c>
       <c r="D363" t="n">
-        <v>3.009159586566188</v>
+        <v>3.009159350315048</v>
       </c>
       <c r="E363" t="n">
-        <v>3.055171157427961</v>
+        <v>3.055170917564423</v>
       </c>
       <c r="F363" t="n">
         <v>8730700</v>
@@ -7712,16 +7712,16 @@
         <v>44944</v>
       </c>
       <c r="B365" t="n">
-        <v>3.082778215408325</v>
+        <v>3.082777976989746</v>
       </c>
       <c r="C365" t="n">
-        <v>3.174801579979019</v>
+        <v>3.174801334443457</v>
       </c>
       <c r="D365" t="n">
-        <v>3.064373586374283</v>
+        <v>3.064373349379097</v>
       </c>
       <c r="E365" t="n">
-        <v>3.128790007393915</v>
+        <v>3.128789765416836</v>
       </c>
       <c r="F365" t="n">
         <v>13324700</v>
@@ -7732,16 +7732,16 @@
         <v>44945</v>
       </c>
       <c r="B366" t="n">
-        <v>3.137991666793823</v>
+        <v>3.137992143630981</v>
       </c>
       <c r="C366" t="n">
-        <v>3.147193979389681</v>
+        <v>3.147194457625188</v>
       </c>
       <c r="D366" t="n">
-        <v>2.990754445859652</v>
+        <v>2.990754900323207</v>
       </c>
       <c r="E366" t="n">
-        <v>3.082777571818235</v>
+        <v>3.082778040265271</v>
       </c>
       <c r="F366" t="n">
         <v>23712400</v>
@@ -7752,16 +7752,16 @@
         <v>44946</v>
       </c>
       <c r="B367" t="n">
-        <v>3.027564287185669</v>
+        <v>3.02756404876709</v>
       </c>
       <c r="C367" t="n">
-        <v>3.137992279290566</v>
+        <v>3.13799203217586</v>
       </c>
       <c r="D367" t="n">
-        <v>3.009159658401599</v>
+        <v>3.009159421432372</v>
       </c>
       <c r="E367" t="n">
-        <v>3.128789964898532</v>
+        <v>3.128789718508501</v>
       </c>
       <c r="F367" t="n">
         <v>19274300</v>
@@ -7772,16 +7772,16 @@
         <v>44949</v>
       </c>
       <c r="B368" t="n">
-        <v>3.027564287185669</v>
+        <v>3.02756404876709</v>
       </c>
       <c r="C368" t="n">
-        <v>3.082778173537877</v>
+        <v>3.082777930771243</v>
       </c>
       <c r="D368" t="n">
-        <v>2.99075502961753</v>
+        <v>2.990754794097655</v>
       </c>
       <c r="E368" t="n">
-        <v>3.018361972793634</v>
+        <v>3.018361735099731</v>
       </c>
       <c r="F368" t="n">
         <v>10637200</v>
@@ -7792,16 +7792,16 @@
         <v>44950</v>
       </c>
       <c r="B369" t="n">
-        <v>3.193206071853638</v>
+        <v>3.193205833435059</v>
       </c>
       <c r="C369" t="n">
-        <v>3.202408385975387</v>
+        <v>3.202408146869723</v>
       </c>
       <c r="D369" t="n">
-        <v>3.018361884139927</v>
+        <v>3.018361658775971</v>
       </c>
       <c r="E369" t="n">
-        <v>3.045968826505175</v>
+        <v>3.045968599079965</v>
       </c>
       <c r="F369" t="n">
         <v>12703800</v>
@@ -7832,16 +7832,16 @@
         <v>44952</v>
       </c>
       <c r="B371" t="n">
-        <v>3.202408313751221</v>
+        <v>3.2024085521698</v>
       </c>
       <c r="C371" t="n">
-        <v>3.2852291389791</v>
+        <v>3.28522938356367</v>
       </c>
       <c r="D371" t="n">
-        <v>3.184003685922803</v>
+        <v>3.184003922971162</v>
       </c>
       <c r="E371" t="n">
-        <v>3.257622197236473</v>
+        <v>3.257622439765714</v>
       </c>
       <c r="F371" t="n">
         <v>8271800</v>
@@ -7852,16 +7852,16 @@
         <v>44953</v>
       </c>
       <c r="B372" t="n">
-        <v>3.147194385528564</v>
+        <v>3.147194147109985</v>
       </c>
       <c r="C372" t="n">
-        <v>3.220812895795746</v>
+        <v>3.22081265180013</v>
       </c>
       <c r="D372" t="n">
-        <v>3.128789757961769</v>
+        <v>3.128789520937449</v>
       </c>
       <c r="E372" t="n">
-        <v>3.211610582012349</v>
+        <v>3.211610338713862</v>
       </c>
       <c r="F372" t="n">
         <v>8557200</v>
@@ -7872,16 +7872,16 @@
         <v>44956</v>
       </c>
       <c r="B373" t="n">
-        <v>2.990755081176758</v>
+        <v>2.990754842758179</v>
       </c>
       <c r="C373" t="n">
-        <v>3.156396962489453</v>
+        <v>3.156396710866147</v>
       </c>
       <c r="D373" t="n">
-        <v>2.963148137524723</v>
+        <v>2.963147901306928</v>
       </c>
       <c r="E373" t="n">
-        <v>3.128790018837418</v>
+        <v>3.128789769414897</v>
       </c>
       <c r="F373" t="n">
         <v>24955900</v>
@@ -7892,16 +7892,16 @@
         <v>44957</v>
       </c>
       <c r="B374" t="n">
-        <v>3.027564287185669</v>
+        <v>3.02756404876709</v>
       </c>
       <c r="C374" t="n">
-        <v>3.082778173537877</v>
+        <v>3.082777930771243</v>
       </c>
       <c r="D374" t="n">
-        <v>2.99075502961753</v>
+        <v>2.990754794097655</v>
       </c>
       <c r="E374" t="n">
-        <v>2.99075502961753</v>
+        <v>2.990754794097655</v>
       </c>
       <c r="F374" t="n">
         <v>20039900</v>
@@ -7932,16 +7932,16 @@
         <v>44959</v>
       </c>
       <c r="B376" t="n">
-        <v>2.806708335876465</v>
+        <v>2.806708097457886</v>
       </c>
       <c r="C376" t="n">
-        <v>2.972350203327015</v>
+        <v>2.972349950837826</v>
       </c>
       <c r="D376" t="n">
-        <v>2.797506022095904</v>
+        <v>2.797505784459025</v>
       </c>
       <c r="E376" t="n">
-        <v>2.898731693082534</v>
+        <v>2.898731446846941</v>
       </c>
       <c r="F376" t="n">
         <v>50857000</v>
@@ -7992,16 +7992,16 @@
         <v>44964</v>
       </c>
       <c r="B379" t="n">
-        <v>2.880326747894287</v>
+        <v>2.880326986312866</v>
       </c>
       <c r="C379" t="n">
-        <v>2.953945250020512</v>
+        <v>2.95394549453285</v>
       </c>
       <c r="D379" t="n">
-        <v>2.843517277430732</v>
+        <v>2.843517512802413</v>
       </c>
       <c r="E379" t="n">
-        <v>2.926338311723177</v>
+        <v>2.926338553950356</v>
       </c>
       <c r="F379" t="n">
         <v>31913300</v>
@@ -8012,16 +8012,16 @@
         <v>44965</v>
       </c>
       <c r="B380" t="n">
-        <v>3.036766529083252</v>
+        <v>3.036766290664673</v>
       </c>
       <c r="C380" t="n">
-        <v>3.036766529083252</v>
+        <v>3.036766290664673</v>
       </c>
       <c r="D380" t="n">
-        <v>2.861922340408036</v>
+        <v>2.861922115716591</v>
       </c>
       <c r="E380" t="n">
-        <v>2.907934130670286</v>
+        <v>2.907933902366425</v>
       </c>
       <c r="F380" t="n">
         <v>50518000</v>
@@ -8032,16 +8032,16 @@
         <v>44966</v>
       </c>
       <c r="B381" t="n">
-        <v>3.018361806869507</v>
+        <v>3.018362045288086</v>
       </c>
       <c r="C381" t="n">
-        <v>3.091980317958858</v>
+        <v>3.091980562192519</v>
       </c>
       <c r="D381" t="n">
-        <v>2.935540981893987</v>
+        <v>2.935541213770599</v>
       </c>
       <c r="E381" t="n">
-        <v>3.036766434641845</v>
+        <v>3.036766674514194</v>
       </c>
       <c r="F381" t="n">
         <v>43678900</v>
@@ -8092,16 +8092,16 @@
         <v>44971</v>
       </c>
       <c r="B384" t="n">
-        <v>2.742292165756226</v>
+        <v>2.742292404174805</v>
       </c>
       <c r="C384" t="n">
-        <v>2.953945604142814</v>
+        <v>2.953945860962829</v>
       </c>
       <c r="D384" t="n">
-        <v>2.723887538018302</v>
+        <v>2.723887774836758</v>
       </c>
       <c r="E384" t="n">
-        <v>2.953945604142814</v>
+        <v>2.953945860962829</v>
       </c>
       <c r="F384" t="n">
         <v>40924300</v>
@@ -8152,16 +8152,16 @@
         <v>44974</v>
       </c>
       <c r="B387" t="n">
-        <v>2.78830361366272</v>
+        <v>2.788303852081299</v>
       </c>
       <c r="C387" t="n">
-        <v>2.8711244348763</v>
+        <v>2.871124680376612</v>
       </c>
       <c r="D387" t="n">
-        <v>2.769898986726369</v>
+        <v>2.769899223571229</v>
       </c>
       <c r="E387" t="n">
-        <v>2.825112867535422</v>
+        <v>2.825113109101438</v>
       </c>
       <c r="F387" t="n">
         <v>27974700</v>
@@ -8192,16 +8192,16 @@
         <v>44980</v>
       </c>
       <c r="B389" t="n">
-        <v>2.797506093978882</v>
+        <v>2.797505855560303</v>
       </c>
       <c r="C389" t="n">
-        <v>2.898731767566543</v>
+        <v>2.898731520520965</v>
       </c>
       <c r="D389" t="n">
-        <v>2.751494523893796</v>
+        <v>2.751494289396572</v>
       </c>
       <c r="E389" t="n">
-        <v>2.852719978080985</v>
+        <v>2.85271973495678</v>
       </c>
       <c r="F389" t="n">
         <v>24919500</v>
@@ -8212,16 +8212,16 @@
         <v>44981</v>
       </c>
       <c r="B390" t="n">
-        <v>2.659471273422241</v>
+        <v>2.65947151184082</v>
       </c>
       <c r="C390" t="n">
-        <v>2.806708291587871</v>
+        <v>2.806708543206081</v>
       </c>
       <c r="D390" t="n">
-        <v>2.65026895978689</v>
+        <v>2.650269197380491</v>
       </c>
       <c r="E390" t="n">
-        <v>2.797505977952519</v>
+        <v>2.797506228745752</v>
       </c>
       <c r="F390" t="n">
         <v>27929600</v>
@@ -8232,16 +8232,16 @@
         <v>44984</v>
       </c>
       <c r="B391" t="n">
-        <v>2.797506093978882</v>
+        <v>2.797505855560303</v>
       </c>
       <c r="C391" t="n">
-        <v>2.83431535004695</v>
+        <v>2.834315108491288</v>
       </c>
       <c r="D391" t="n">
-        <v>2.641066536289118</v>
+        <v>2.641066311203163</v>
       </c>
       <c r="E391" t="n">
-        <v>2.677876011757659</v>
+        <v>2.677875783534602</v>
       </c>
       <c r="F391" t="n">
         <v>32246200</v>
@@ -8272,16 +8272,16 @@
         <v>44986</v>
       </c>
       <c r="B393" t="n">
-        <v>2.779101610183716</v>
+        <v>2.779101371765137</v>
       </c>
       <c r="C393" t="n">
-        <v>2.917136547003632</v>
+        <v>2.917136296743063</v>
       </c>
       <c r="D393" t="n">
-        <v>2.751494666699829</v>
+        <v>2.751494430649644</v>
       </c>
       <c r="E393" t="n">
-        <v>2.843517811646118</v>
+        <v>2.843517567701285</v>
       </c>
       <c r="F393" t="n">
         <v>32788900</v>
@@ -8292,16 +8292,16 @@
         <v>44987</v>
       </c>
       <c r="B394" t="n">
-        <v>2.687078237533569</v>
+        <v>2.68707799911499</v>
       </c>
       <c r="C394" t="n">
-        <v>2.797506002111432</v>
+        <v>2.797505753894839</v>
       </c>
       <c r="D394" t="n">
-        <v>2.687078237533569</v>
+        <v>2.68707799911499</v>
       </c>
       <c r="E394" t="n">
-        <v>2.779101374681788</v>
+        <v>2.779101128098197</v>
       </c>
       <c r="F394" t="n">
         <v>21864000</v>
@@ -8312,16 +8312,16 @@
         <v>44988</v>
       </c>
       <c r="B395" t="n">
-        <v>2.604257345199585</v>
+        <v>2.604257106781006</v>
       </c>
       <c r="C395" t="n">
-        <v>2.71468533555954</v>
+        <v>2.714685087031328</v>
       </c>
       <c r="D395" t="n">
-        <v>2.55824577396647</v>
+        <v>2.558245539760229</v>
       </c>
       <c r="E395" t="n">
-        <v>2.71468533555954</v>
+        <v>2.714685087031328</v>
       </c>
       <c r="F395" t="n">
         <v>36019100</v>
@@ -8392,16 +8392,16 @@
         <v>44994</v>
       </c>
       <c r="B399" t="n">
-        <v>2.576650142669678</v>
+        <v>2.576650381088257</v>
       </c>
       <c r="C399" t="n">
-        <v>2.705482748533367</v>
+        <v>2.705482998872884</v>
       </c>
       <c r="D399" t="n">
-        <v>2.558245516032073</v>
+        <v>2.558245752747664</v>
       </c>
       <c r="E399" t="n">
-        <v>2.687078121895762</v>
+        <v>2.687078370532291</v>
       </c>
       <c r="F399" t="n">
         <v>41324600</v>
@@ -8492,16 +8492,16 @@
         <v>45001</v>
       </c>
       <c r="B404" t="n">
-        <v>2.512234449386597</v>
+        <v>2.512233972549438</v>
       </c>
       <c r="C404" t="n">
-        <v>2.539841394836938</v>
+        <v>2.539840912759816</v>
       </c>
       <c r="D404" t="n">
-        <v>2.447818243335799</v>
+        <v>2.447817778725223</v>
       </c>
       <c r="E404" t="n">
-        <v>2.530639079686825</v>
+        <v>2.530638599356357</v>
       </c>
       <c r="F404" t="n">
         <v>22197500</v>
@@ -8572,16 +8572,16 @@
         <v>45007</v>
       </c>
       <c r="B408" t="n">
-        <v>2.216452836990356</v>
+        <v>2.216452598571777</v>
       </c>
       <c r="C408" t="n">
-        <v>2.273529049947901</v>
+        <v>2.273528805389769</v>
       </c>
       <c r="D408" t="n">
-        <v>2.197427508271111</v>
+        <v>2.197427271899042</v>
       </c>
       <c r="E408" t="n">
-        <v>2.254503494428847</v>
+        <v>2.254503251917249</v>
       </c>
       <c r="F408" t="n">
         <v>26704400</v>
@@ -8612,16 +8612,16 @@
         <v>45009</v>
       </c>
       <c r="B410" t="n">
-        <v>2.292554140090942</v>
+        <v>2.292553901672363</v>
       </c>
       <c r="C410" t="n">
-        <v>2.302066803460623</v>
+        <v>2.302066564052756</v>
       </c>
       <c r="D410" t="n">
-        <v>2.149863962745944</v>
+        <v>2.149863739166705</v>
       </c>
       <c r="E410" t="n">
-        <v>2.159376626115625</v>
+        <v>2.159376401547098</v>
       </c>
       <c r="F410" t="n">
         <v>19141800</v>
@@ -8632,16 +8632,16 @@
         <v>45012</v>
       </c>
       <c r="B411" t="n">
-        <v>2.387681007385254</v>
+        <v>2.387680768966675</v>
       </c>
       <c r="C411" t="n">
-        <v>2.416219000286296</v>
+        <v>2.416218759018095</v>
       </c>
       <c r="D411" t="n">
-        <v>2.302067028682128</v>
+        <v>2.302066798812414</v>
       </c>
       <c r="E411" t="n">
-        <v>2.311579692982475</v>
+        <v>2.311579462162887</v>
       </c>
       <c r="F411" t="n">
         <v>19684900</v>
@@ -8672,16 +8672,16 @@
         <v>45014</v>
       </c>
       <c r="B413" t="n">
-        <v>2.615985155105591</v>
+        <v>2.615984916687012</v>
       </c>
       <c r="C413" t="n">
-        <v>2.644523147763493</v>
+        <v>2.644522906743987</v>
       </c>
       <c r="D413" t="n">
-        <v>2.492320293454875</v>
+        <v>2.492320066307002</v>
       </c>
       <c r="E413" t="n">
-        <v>2.539883841351184</v>
+        <v>2.539883609868411</v>
       </c>
       <c r="F413" t="n">
         <v>36856900</v>
@@ -8692,16 +8692,16 @@
         <v>45015</v>
       </c>
       <c r="B414" t="n">
-        <v>2.749162435531616</v>
+        <v>2.749162197113037</v>
       </c>
       <c r="C414" t="n">
-        <v>2.796725752381689</v>
+        <v>2.796725509838225</v>
       </c>
       <c r="D414" t="n">
-        <v>2.644522911661672</v>
+        <v>2.644522682317859</v>
       </c>
       <c r="E414" t="n">
-        <v>2.673060901771716</v>
+        <v>2.673060669952971</v>
       </c>
       <c r="F414" t="n">
         <v>39786400</v>
@@ -8732,16 +8732,16 @@
         <v>45019</v>
       </c>
       <c r="B416" t="n">
-        <v>2.692086219787598</v>
+        <v>2.692086458206177</v>
       </c>
       <c r="C416" t="n">
-        <v>2.768187753300879</v>
+        <v>2.76818799845922</v>
       </c>
       <c r="D416" t="n">
-        <v>2.673060893109223</v>
+        <v>2.673061129842867</v>
       </c>
       <c r="E416" t="n">
-        <v>2.739649763283318</v>
+        <v>2.739650005914255</v>
       </c>
       <c r="F416" t="n">
         <v>18815900</v>
@@ -8752,16 +8752,16 @@
         <v>45020</v>
       </c>
       <c r="B417" t="n">
-        <v>2.692086219787598</v>
+        <v>2.692086458206177</v>
       </c>
       <c r="C417" t="n">
-        <v>2.739649763283318</v>
+        <v>2.739650005914255</v>
       </c>
       <c r="D417" t="n">
-        <v>2.654035566430849</v>
+        <v>2.654035801479557</v>
       </c>
       <c r="E417" t="n">
-        <v>2.720624209805159</v>
+        <v>2.720624450751141</v>
       </c>
       <c r="F417" t="n">
         <v>21012200</v>
@@ -8792,16 +8792,16 @@
         <v>45022</v>
       </c>
       <c r="B419" t="n">
-        <v>2.654035568237305</v>
+        <v>2.654035329818726</v>
       </c>
       <c r="C419" t="n">
-        <v>2.68257355827429</v>
+        <v>2.682573317292073</v>
       </c>
       <c r="D419" t="n">
-        <v>2.615984914854657</v>
+        <v>2.615984679854262</v>
       </c>
       <c r="E419" t="n">
-        <v>2.673060894928629</v>
+        <v>2.673060654800957</v>
       </c>
       <c r="F419" t="n">
         <v>14613400</v>
@@ -8812,16 +8812,16 @@
         <v>45026</v>
       </c>
       <c r="B420" t="n">
-        <v>2.67306113243103</v>
+        <v>2.673060894012451</v>
       </c>
       <c r="C420" t="n">
-        <v>2.701599125003626</v>
+        <v>2.701598884039655</v>
       </c>
       <c r="D420" t="n">
-        <v>2.644523139858434</v>
+        <v>2.644522903985246</v>
       </c>
       <c r="E420" t="n">
-        <v>2.67306113243103</v>
+        <v>2.673060894012451</v>
       </c>
       <c r="F420" t="n">
         <v>14149600</v>
@@ -8872,16 +8872,16 @@
         <v>45029</v>
       </c>
       <c r="B423" t="n">
-        <v>2.882339954376221</v>
+        <v>2.882339715957642</v>
       </c>
       <c r="C423" t="n">
-        <v>2.958441267452883</v>
+        <v>2.95844102273943</v>
       </c>
       <c r="D423" t="n">
-        <v>2.853801961972472</v>
+        <v>2.853801725914471</v>
       </c>
       <c r="E423" t="n">
-        <v>2.929903275049135</v>
+        <v>2.929903032696259</v>
       </c>
       <c r="F423" t="n">
         <v>15780900</v>
@@ -8952,16 +8952,16 @@
         <v>45035</v>
       </c>
       <c r="B427" t="n">
-        <v>2.882339954376221</v>
+        <v>2.882339715957642</v>
       </c>
       <c r="C427" t="n">
-        <v>2.996492150791017</v>
+        <v>2.996491902930108</v>
       </c>
       <c r="D427" t="n">
-        <v>2.872827290241638</v>
+        <v>2.872827052609918</v>
       </c>
       <c r="E427" t="n">
-        <v>2.986979486656434</v>
+        <v>2.986979239582385</v>
       </c>
       <c r="F427" t="n">
         <v>19845900</v>
@@ -8972,16 +8972,16 @@
         <v>45036</v>
       </c>
       <c r="B428" t="n">
-        <v>2.958441019058228</v>
+        <v>2.958441257476807</v>
       </c>
       <c r="C428" t="n">
-        <v>2.977466572529786</v>
+        <v>2.977466812481619</v>
       </c>
       <c r="D428" t="n">
-        <v>2.844289059027585</v>
+        <v>2.844289288246741</v>
       </c>
       <c r="E428" t="n">
-        <v>2.882339712371133</v>
+        <v>2.882339944656763</v>
       </c>
       <c r="F428" t="n">
         <v>11874200</v>
@@ -9032,16 +9032,16 @@
         <v>45042</v>
       </c>
       <c r="B431" t="n">
-        <v>2.901365041732788</v>
+        <v>2.901365280151367</v>
       </c>
       <c r="C431" t="n">
-        <v>3.034542555358458</v>
+        <v>3.03454280472085</v>
       </c>
       <c r="D431" t="n">
-        <v>2.891852378388082</v>
+        <v>2.891852616024962</v>
       </c>
       <c r="E431" t="n">
-        <v>3.015517228669046</v>
+        <v>3.015517476468038</v>
       </c>
       <c r="F431" t="n">
         <v>15122100</v>
@@ -9052,16 +9052,16 @@
         <v>45043</v>
       </c>
       <c r="B432" t="n">
-        <v>2.977466344833374</v>
+        <v>2.977466821670532</v>
       </c>
       <c r="C432" t="n">
-        <v>3.006004332658643</v>
+        <v>3.006004814066121</v>
       </c>
       <c r="D432" t="n">
-        <v>2.8918521545578</v>
+        <v>2.891852617683963</v>
       </c>
       <c r="E432" t="n">
-        <v>2.901364817166223</v>
+        <v>2.901365281815826</v>
       </c>
       <c r="F432" t="n">
         <v>12242300</v>
@@ -9072,16 +9072,16 @@
         <v>45044</v>
       </c>
       <c r="B433" t="n">
-        <v>3.034542798995972</v>
+        <v>3.034542560577393</v>
       </c>
       <c r="C433" t="n">
-        <v>3.091618783646728</v>
+        <v>3.091618540743791</v>
       </c>
       <c r="D433" t="n">
-        <v>2.939415931111576</v>
+        <v>2.939415700166944</v>
       </c>
       <c r="E433" t="n">
-        <v>2.977466814345215</v>
+        <v>2.977466580410994</v>
       </c>
       <c r="F433" t="n">
         <v>20412700</v>
@@ -9152,16 +9152,16 @@
         <v>45051</v>
       </c>
       <c r="B437" t="n">
-        <v>3.120156526565552</v>
+        <v>3.120156764984131</v>
       </c>
       <c r="C437" t="n">
-        <v>3.129669189913626</v>
+        <v>3.12966942905909</v>
       </c>
       <c r="D437" t="n">
-        <v>3.025029893084809</v>
+        <v>3.025030124234536</v>
       </c>
       <c r="E437" t="n">
-        <v>3.034542556432883</v>
+        <v>3.034542788309496</v>
       </c>
       <c r="F437" t="n">
         <v>17709200</v>
@@ -9212,16 +9212,16 @@
         <v>45056</v>
       </c>
       <c r="B440" t="n">
-        <v>3.120156526565552</v>
+        <v>3.120156764984131</v>
       </c>
       <c r="C440" t="n">
-        <v>3.1391818532617</v>
+        <v>3.13918209313405</v>
       </c>
       <c r="D440" t="n">
-        <v>2.986979239692512</v>
+        <v>2.986979467934698</v>
       </c>
       <c r="E440" t="n">
-        <v>3.034542556432883</v>
+        <v>3.034542788309496</v>
       </c>
       <c r="F440" t="n">
         <v>20064700</v>
@@ -9232,16 +9232,16 @@
         <v>45057</v>
       </c>
       <c r="B441" t="n">
-        <v>3.167720079421997</v>
+        <v>3.167719841003418</v>
       </c>
       <c r="C441" t="n">
-        <v>3.167720079421997</v>
+        <v>3.167719841003418</v>
       </c>
       <c r="D441" t="n">
-        <v>3.053568110736427</v>
+        <v>3.0535678809095</v>
       </c>
       <c r="E441" t="n">
-        <v>3.110644095079212</v>
+        <v>3.110643860956459</v>
       </c>
       <c r="F441" t="n">
         <v>17152200</v>
@@ -9272,16 +9272,16 @@
         <v>45061</v>
       </c>
       <c r="B443" t="n">
-        <v>2.986979007720947</v>
+        <v>2.986979484558105</v>
       </c>
       <c r="C443" t="n">
-        <v>3.205770247735124</v>
+        <v>3.20577075949981</v>
       </c>
       <c r="D443" t="n">
-        <v>2.901364817437372</v>
+        <v>2.901365280607201</v>
       </c>
       <c r="E443" t="n">
-        <v>3.1867449225165</v>
+        <v>3.18674543124401</v>
       </c>
       <c r="F443" t="n">
         <v>71533500</v>
@@ -9292,16 +9292,16 @@
         <v>45062</v>
       </c>
       <c r="B444" t="n">
-        <v>3.082106113433838</v>
+        <v>3.082105875015259</v>
       </c>
       <c r="C444" t="n">
-        <v>3.139182097971549</v>
+        <v>3.139181855137815</v>
       </c>
       <c r="D444" t="n">
-        <v>2.977466808448034</v>
+        <v>2.977466578123905</v>
       </c>
       <c r="E444" t="n">
-        <v>2.977466808448034</v>
+        <v>2.977466578123905</v>
       </c>
       <c r="F444" t="n">
         <v>45623200</v>
@@ -9352,16 +9352,16 @@
         <v>45065</v>
       </c>
       <c r="B447" t="n">
-        <v>3.491151094436646</v>
+        <v>3.491150856018066</v>
       </c>
       <c r="C447" t="n">
-        <v>3.519689086472937</v>
+        <v>3.519688846105434</v>
       </c>
       <c r="D447" t="n">
-        <v>3.281872259370709</v>
+        <v>3.281872035244253</v>
       </c>
       <c r="E447" t="n">
-        <v>3.329435579431195</v>
+        <v>3.329435352056533</v>
       </c>
       <c r="F447" t="n">
         <v>32544700</v>
@@ -9412,16 +9412,16 @@
         <v>45070</v>
       </c>
       <c r="B450" t="n">
-        <v>3.319922685623169</v>
+        <v>3.319922924041748</v>
       </c>
       <c r="C450" t="n">
-        <v>3.529201506203401</v>
+        <v>3.529201759651233</v>
       </c>
       <c r="D450" t="n">
-        <v>3.262846705501229</v>
+        <v>3.262846939820925</v>
       </c>
       <c r="E450" t="n">
-        <v>3.462612862727804</v>
+        <v>3.462613111393607</v>
       </c>
       <c r="F450" t="n">
         <v>35329500</v>
@@ -9432,16 +9432,16 @@
         <v>45071</v>
       </c>
       <c r="B451" t="n">
-        <v>3.281872272491455</v>
+        <v>3.281872034072876</v>
       </c>
       <c r="C451" t="n">
-        <v>3.424562233243379</v>
+        <v>3.424561984458784</v>
       </c>
       <c r="D451" t="n">
-        <v>3.272359608441327</v>
+        <v>3.272359370713815</v>
       </c>
       <c r="E451" t="n">
-        <v>3.376998912992737</v>
+        <v>3.376998667663482</v>
       </c>
       <c r="F451" t="n">
         <v>36092900</v>
@@ -9452,16 +9452,16 @@
         <v>45072</v>
       </c>
       <c r="B452" t="n">
-        <v>3.291384935379028</v>
+        <v>3.291384696960449</v>
       </c>
       <c r="C452" t="n">
-        <v>3.348460919659638</v>
+        <v>3.348460677106637</v>
       </c>
       <c r="D452" t="n">
-        <v>3.177232740018008</v>
+        <v>3.17723250986829</v>
       </c>
       <c r="E452" t="n">
-        <v>3.33894825561287</v>
+        <v>3.338948013748939</v>
       </c>
       <c r="F452" t="n">
         <v>25686400</v>
@@ -9472,16 +9472,16 @@
         <v>45075</v>
       </c>
       <c r="B453" t="n">
-        <v>3.357973337173462</v>
+        <v>3.357973575592041</v>
       </c>
       <c r="C453" t="n">
-        <v>3.415049317263714</v>
+        <v>3.415049559734729</v>
       </c>
       <c r="D453" t="n">
-        <v>3.291384693734835</v>
+        <v>3.291384927425571</v>
       </c>
       <c r="E453" t="n">
-        <v>3.319922683779961</v>
+        <v>3.319922919496916</v>
       </c>
       <c r="F453" t="n">
         <v>14544800</v>
@@ -9532,16 +9532,16 @@
         <v>45078</v>
       </c>
       <c r="B456" t="n">
-        <v>3.576765060424805</v>
+        <v>3.576764583587646</v>
       </c>
       <c r="C456" t="n">
-        <v>3.662379036291428</v>
+        <v>3.662378548040625</v>
       </c>
       <c r="D456" t="n">
-        <v>3.376998889936218</v>
+        <v>3.376998439730927</v>
       </c>
       <c r="E456" t="n">
-        <v>3.472125756587821</v>
+        <v>3.472125293700673</v>
       </c>
       <c r="F456" t="n">
         <v>28377100</v>
@@ -9552,16 +9552,16 @@
         <v>45079</v>
       </c>
       <c r="B457" t="n">
-        <v>3.529201745986938</v>
+        <v>3.529201507568359</v>
       </c>
       <c r="C457" t="n">
-        <v>3.643353713986613</v>
+        <v>3.643353467856389</v>
       </c>
       <c r="D457" t="n">
-        <v>3.491151089987047</v>
+        <v>3.491150854139016</v>
       </c>
       <c r="E457" t="n">
-        <v>3.614815721986695</v>
+        <v>3.614815477784382</v>
       </c>
       <c r="F457" t="n">
         <v>24144300</v>
@@ -9612,16 +9612,16 @@
         <v>45084</v>
       </c>
       <c r="B460" t="n">
-        <v>3.757505893707275</v>
+        <v>3.757505655288696</v>
       </c>
       <c r="C460" t="n">
-        <v>3.852632760125061</v>
+        <v>3.85263251567056</v>
       </c>
       <c r="D460" t="n">
-        <v>3.681404355213087</v>
+        <v>3.681404121623248</v>
       </c>
       <c r="E460" t="n">
-        <v>3.747993229745477</v>
+        <v>3.747992991930488</v>
       </c>
       <c r="F460" t="n">
         <v>19382700</v>
@@ -9632,16 +9632,16 @@
         <v>45086</v>
       </c>
       <c r="B461" t="n">
-        <v>3.786043643951416</v>
+        <v>3.786043882369995</v>
       </c>
       <c r="C461" t="n">
-        <v>3.824094297370058</v>
+        <v>3.824094538184801</v>
       </c>
       <c r="D461" t="n">
-        <v>3.728967663823453</v>
+        <v>3.728967898647786</v>
       </c>
       <c r="E461" t="n">
-        <v>3.795556307306077</v>
+        <v>3.795556546323696</v>
       </c>
       <c r="F461" t="n">
         <v>14031500</v>
@@ -9652,16 +9652,16 @@
         <v>45089</v>
       </c>
       <c r="B462" t="n">
-        <v>3.795556545257568</v>
+        <v>3.795556306838989</v>
       </c>
       <c r="C462" t="n">
-        <v>3.805069209208598</v>
+        <v>3.805068970192479</v>
       </c>
       <c r="D462" t="n">
-        <v>3.747993225502421</v>
+        <v>3.74799299007154</v>
       </c>
       <c r="E462" t="n">
-        <v>3.786043881306539</v>
+        <v>3.786043643485499</v>
       </c>
       <c r="F462" t="n">
         <v>16242400</v>
@@ -9672,16 +9672,16 @@
         <v>45090</v>
       </c>
       <c r="B463" t="n">
-        <v>3.700429916381836</v>
+        <v>3.700429677963257</v>
       </c>
       <c r="C463" t="n">
-        <v>3.814582110922048</v>
+        <v>3.814581865148647</v>
       </c>
       <c r="D463" t="n">
-        <v>3.662379033668566</v>
+        <v>3.662378797701604</v>
       </c>
       <c r="E463" t="n">
-        <v>3.786043892187145</v>
+        <v>3.78604364825246</v>
       </c>
       <c r="F463" t="n">
         <v>19986600</v>
@@ -9692,16 +9692,16 @@
         <v>45091</v>
       </c>
       <c r="B464" t="n">
-        <v>3.747993230819702</v>
+        <v>3.747992992401123</v>
       </c>
       <c r="C464" t="n">
-        <v>3.795556550642328</v>
+        <v>3.795556309198135</v>
       </c>
       <c r="D464" t="n">
-        <v>3.662379028339177</v>
+        <v>3.662378795366716</v>
       </c>
       <c r="E464" t="n">
-        <v>3.709942574961601</v>
+        <v>3.709942338963513</v>
       </c>
       <c r="F464" t="n">
         <v>25840400</v>
@@ -9712,16 +9712,16 @@
         <v>45092</v>
       </c>
       <c r="B465" t="n">
-        <v>3.757505893707275</v>
+        <v>3.757505655288696</v>
       </c>
       <c r="C465" t="n">
-        <v>3.79555654955447</v>
+        <v>3.795556308721528</v>
       </c>
       <c r="D465" t="n">
-        <v>3.71945523786008</v>
+        <v>3.719455001855864</v>
       </c>
       <c r="E465" t="n">
-        <v>3.757505893707275</v>
+        <v>3.757505655288696</v>
       </c>
       <c r="F465" t="n">
         <v>13781200</v>
@@ -9732,16 +9732,16 @@
         <v>45093</v>
       </c>
       <c r="B466" t="n">
-        <v>3.757505893707275</v>
+        <v>3.757505655288696</v>
       </c>
       <c r="C466" t="n">
-        <v>3.776531221630873</v>
+        <v>3.776530982005112</v>
       </c>
       <c r="D466" t="n">
-        <v>3.709942573898282</v>
+        <v>3.709942338497656</v>
       </c>
       <c r="E466" t="n">
-        <v>3.728967901821879</v>
+        <v>3.728967665214073</v>
       </c>
       <c r="F466" t="n">
         <v>14449100</v>
@@ -9752,16 +9752,16 @@
         <v>45096</v>
       </c>
       <c r="B467" t="n">
-        <v>3.776530981063843</v>
+        <v>3.776530742645264</v>
       </c>
       <c r="C467" t="n">
-        <v>3.814581861286975</v>
+        <v>3.814581620466182</v>
       </c>
       <c r="D467" t="n">
-        <v>3.738480327640495</v>
+        <v>3.738480091624116</v>
       </c>
       <c r="E467" t="n">
-        <v>3.78604364441968</v>
+        <v>3.786043405400551</v>
       </c>
       <c r="F467" t="n">
         <v>9550900</v>
@@ -9772,16 +9772,16 @@
         <v>45097</v>
       </c>
       <c r="B468" t="n">
-        <v>3.94775915145874</v>
+        <v>3.947759389877319</v>
       </c>
       <c r="C468" t="n">
-        <v>3.966784478185788</v>
+        <v>3.966784717753371</v>
       </c>
       <c r="D468" t="n">
-        <v>3.767018320752002</v>
+        <v>3.767018548255029</v>
       </c>
       <c r="E468" t="n">
-        <v>3.78604364747905</v>
+        <v>3.786043876131081</v>
       </c>
       <c r="F468" t="n">
         <v>35176100</v>
@@ -9792,16 +9792,16 @@
         <v>45098</v>
       </c>
       <c r="B469" t="n">
-        <v>4.023860454559326</v>
+        <v>4.023859977722168</v>
       </c>
       <c r="C469" t="n">
-        <v>4.042885781268371</v>
+        <v>4.042885302176666</v>
       </c>
       <c r="D469" t="n">
-        <v>3.90019560415075</v>
+        <v>3.900195141968175</v>
       </c>
       <c r="E469" t="n">
-        <v>3.966784474432191</v>
+        <v>3.966784004358674</v>
       </c>
       <c r="F469" t="n">
         <v>23935400</v>
@@ -9852,16 +9852,16 @@
         <v>45103</v>
       </c>
       <c r="B472" t="n">
-        <v>4.204601287841797</v>
+        <v>4.204601764678955</v>
       </c>
       <c r="C472" t="n">
-        <v>4.280702594727692</v>
+        <v>4.280703080195378</v>
       </c>
       <c r="D472" t="n">
-        <v>4.128499980955902</v>
+        <v>4.128500449162532</v>
       </c>
       <c r="E472" t="n">
-        <v>4.138012417516855</v>
+        <v>4.138012886802275</v>
       </c>
       <c r="F472" t="n">
         <v>42881900</v>
@@ -9872,16 +9872,16 @@
         <v>45104</v>
       </c>
       <c r="B473" t="n">
-        <v>4.223626613616943</v>
+        <v>4.223626136779785</v>
       </c>
       <c r="C473" t="n">
-        <v>4.290215483926966</v>
+        <v>4.290214999572086</v>
       </c>
       <c r="D473" t="n">
-        <v>4.080936436438077</v>
+        <v>4.080935975710292</v>
       </c>
       <c r="E473" t="n">
-        <v>4.233139050175764</v>
+        <v>4.233138572264675</v>
       </c>
       <c r="F473" t="n">
         <v>76576700</v>
@@ -9912,16 +9912,16 @@
         <v>45106</v>
       </c>
       <c r="B475" t="n">
-        <v>4.366316795349121</v>
+        <v>4.366317272186279</v>
       </c>
       <c r="C475" t="n">
-        <v>4.366316795349121</v>
+        <v>4.366317272186279</v>
       </c>
       <c r="D475" t="n">
-        <v>4.185575964547351</v>
+        <v>4.185576421646147</v>
       </c>
       <c r="E475" t="n">
-        <v>4.185575964547351</v>
+        <v>4.185576421646147</v>
       </c>
       <c r="F475" t="n">
         <v>40765500</v>
@@ -9932,16 +9932,16 @@
         <v>45107</v>
       </c>
       <c r="B476" t="n">
-        <v>4.18557596206665</v>
+        <v>4.185575485229492</v>
       </c>
       <c r="C476" t="n">
-        <v>4.489981189679052</v>
+        <v>4.489980678162862</v>
       </c>
       <c r="D476" t="n">
-        <v>4.138012418452428</v>
+        <v>4.138011947033895</v>
       </c>
       <c r="E476" t="n">
-        <v>4.413879882775952</v>
+        <v>4.41387937992952</v>
       </c>
       <c r="F476" t="n">
         <v>35419200</v>
@@ -9972,16 +9972,16 @@
         <v>45111</v>
       </c>
       <c r="B478" t="n">
-        <v>4.195088386535645</v>
+        <v>4.195088863372803</v>
       </c>
       <c r="C478" t="n">
-        <v>4.261677256683671</v>
+        <v>4.261677741089692</v>
       </c>
       <c r="D478" t="n">
-        <v>4.138012406522865</v>
+        <v>4.138012876872448</v>
       </c>
       <c r="E478" t="n">
-        <v>4.252164366548425</v>
+        <v>4.252164849873157</v>
       </c>
       <c r="F478" t="n">
         <v>10806500</v>
@@ -9992,16 +9992,16 @@
         <v>45112</v>
       </c>
       <c r="B479" t="n">
-        <v>4.080936908721924</v>
+        <v>4.080936431884766</v>
       </c>
       <c r="C479" t="n">
-        <v>4.185576444576225</v>
+        <v>4.185575955512459</v>
       </c>
       <c r="D479" t="n">
-        <v>4.023860921964928</v>
+        <v>4.023860451796815</v>
       </c>
       <c r="E479" t="n">
-        <v>4.166551115657227</v>
+        <v>4.166550628816475</v>
       </c>
       <c r="F479" t="n">
         <v>33346200</v>
@@ -10032,16 +10032,16 @@
         <v>45114</v>
       </c>
       <c r="B481" t="n">
-        <v>3.995322227478027</v>
+        <v>3.995322465896606</v>
       </c>
       <c r="C481" t="n">
-        <v>4.042885770928781</v>
+        <v>4.042886012185687</v>
       </c>
       <c r="D481" t="n">
-        <v>3.947759137626841</v>
+        <v>3.94775937320712</v>
       </c>
       <c r="E481" t="n">
-        <v>3.976296900817639</v>
+        <v>3.976297138100893</v>
       </c>
       <c r="F481" t="n">
         <v>19055100</v>
@@ -10092,16 +10092,16 @@
         <v>45119</v>
       </c>
       <c r="B484" t="n">
-        <v>4.014347553253174</v>
+        <v>4.014348030090332</v>
       </c>
       <c r="C484" t="n">
-        <v>4.128499966789897</v>
+        <v>4.128500457186447</v>
       </c>
       <c r="D484" t="n">
-        <v>4.004835116724861</v>
+        <v>4.004835592432102</v>
       </c>
       <c r="E484" t="n">
-        <v>4.090449313477511</v>
+        <v>4.090449799354283</v>
       </c>
       <c r="F484" t="n">
         <v>6157400</v>
@@ -10112,16 +10112,16 @@
         <v>45120</v>
       </c>
       <c r="B485" t="n">
-        <v>3.995322227478027</v>
+        <v>3.995322465896606</v>
       </c>
       <c r="C485" t="n">
-        <v>4.071423987719147</v>
+        <v>4.071424230679055</v>
       </c>
       <c r="D485" t="n">
-        <v>3.957271574157251</v>
+        <v>3.957271810305179</v>
       </c>
       <c r="E485" t="n">
-        <v>4.023860444268393</v>
+        <v>4.023860684389974</v>
       </c>
       <c r="F485" t="n">
         <v>10522300</v>
@@ -10132,16 +10132,16 @@
         <v>45121</v>
       </c>
       <c r="B486" t="n">
-        <v>3.881170511245728</v>
+        <v>3.881170272827148</v>
       </c>
       <c r="C486" t="n">
-        <v>4.014347806231721</v>
+        <v>4.01434755963212</v>
       </c>
       <c r="D486" t="n">
-        <v>3.814582090552529</v>
+        <v>3.814581856224446</v>
       </c>
       <c r="E486" t="n">
-        <v>3.995322478376579</v>
+        <v>3.995322232945695</v>
       </c>
       <c r="F486" t="n">
         <v>16845900</v>
@@ -10152,16 +10152,16 @@
         <v>45124</v>
       </c>
       <c r="B487" t="n">
-        <v>4.023860454559326</v>
+        <v>4.023859977722168</v>
       </c>
       <c r="C487" t="n">
-        <v>4.042885781268371</v>
+        <v>4.042885302176666</v>
       </c>
       <c r="D487" t="n">
-        <v>3.852632514177922</v>
+        <v>3.852632057631688</v>
       </c>
       <c r="E487" t="n">
-        <v>3.881170277441705</v>
+        <v>3.881169817513677</v>
       </c>
       <c r="F487" t="n">
         <v>20863600</v>
@@ -10172,16 +10172,16 @@
         <v>45125</v>
       </c>
       <c r="B488" t="n">
-        <v>4.071424007415771</v>
+        <v>4.07142448425293</v>
       </c>
       <c r="C488" t="n">
-        <v>4.185575967930341</v>
+        <v>4.185576458136752</v>
       </c>
       <c r="D488" t="n">
-        <v>4.004835136982487</v>
+        <v>4.004835606020889</v>
       </c>
       <c r="E488" t="n">
-        <v>4.023860463734916</v>
+        <v>4.023860935001526</v>
       </c>
       <c r="F488" t="n">
         <v>19854400</v>
@@ -10212,16 +10212,16 @@
         <v>45127</v>
       </c>
       <c r="B490" t="n">
-        <v>3.995322227478027</v>
+        <v>3.995322465896606</v>
       </c>
       <c r="C490" t="n">
-        <v>4.080936424249557</v>
+        <v>4.080936667777115</v>
       </c>
       <c r="D490" t="n">
-        <v>3.947759137626841</v>
+        <v>3.94775937320712</v>
       </c>
       <c r="E490" t="n">
-        <v>4.071423987719147</v>
+        <v>4.071424230679055</v>
       </c>
       <c r="F490" t="n">
         <v>13981900</v>
@@ -10232,16 +10232,16 @@
         <v>45128</v>
       </c>
       <c r="B491" t="n">
-        <v>4.061911582946777</v>
+        <v>4.061911106109619</v>
       </c>
       <c r="C491" t="n">
-        <v>4.099962240814224</v>
+        <v>4.099961759510212</v>
       </c>
       <c r="D491" t="n">
-        <v>3.97629737594521</v>
+        <v>3.976296909158501</v>
       </c>
       <c r="E491" t="n">
-        <v>4.004835596145607</v>
+        <v>4.00483512600873</v>
       </c>
       <c r="F491" t="n">
         <v>9991000</v>
@@ -10252,16 +10252,16 @@
         <v>45131</v>
       </c>
       <c r="B492" t="n">
-        <v>4.023860454559326</v>
+        <v>4.023859977722168</v>
       </c>
       <c r="C492" t="n">
-        <v>4.080936434686461</v>
+        <v>4.080935951085661</v>
       </c>
       <c r="D492" t="n">
-        <v>3.947759147723147</v>
+        <v>3.947758679904177</v>
       </c>
       <c r="E492" t="n">
-        <v>4.061911107977416</v>
+        <v>4.061910626631164</v>
       </c>
       <c r="F492" t="n">
         <v>17283700</v>
@@ -10272,16 +10272,16 @@
         <v>45132</v>
       </c>
       <c r="B493" t="n">
-        <v>3.995322227478027</v>
+        <v>3.995322465896606</v>
       </c>
       <c r="C493" t="n">
-        <v>4.090449314379534</v>
+        <v>4.090449558474769</v>
       </c>
       <c r="D493" t="n">
-        <v>3.966784464287229</v>
+        <v>3.966784701002833</v>
       </c>
       <c r="E493" t="n">
-        <v>4.061911097589169</v>
+        <v>4.061911339981402</v>
       </c>
       <c r="F493" t="n">
         <v>14413200</v>
@@ -10292,16 +10292,16 @@
         <v>45133</v>
       </c>
       <c r="B494" t="n">
-        <v>4.014347553253174</v>
+        <v>4.014348030090332</v>
       </c>
       <c r="C494" t="n">
-        <v>4.033372879909367</v>
+        <v>4.033373359006414</v>
       </c>
       <c r="D494" t="n">
-        <v>3.957271573284596</v>
+        <v>3.957272043342085</v>
       </c>
       <c r="E494" t="n">
-        <v>3.995322226596981</v>
+        <v>3.99532270117425</v>
       </c>
       <c r="F494" t="n">
         <v>6399600</v>
@@ -10312,16 +10312,16 @@
         <v>45134</v>
       </c>
       <c r="B495" t="n">
-        <v>3.893998384475708</v>
+        <v>3.893998622894287</v>
       </c>
       <c r="C495" t="n">
-        <v>4.056646575563136</v>
+        <v>4.056646823940207</v>
       </c>
       <c r="D495" t="n">
-        <v>3.884430602296878</v>
+        <v>3.884430840129649</v>
       </c>
       <c r="E495" t="n">
-        <v>4.047079249601271</v>
+        <v>4.047079497392562</v>
       </c>
       <c r="F495" t="n">
         <v>18331700</v>
@@ -10352,16 +10352,16 @@
         <v>45138</v>
       </c>
       <c r="B497" t="n">
-        <v>3.980106353759766</v>
+        <v>3.980106115341187</v>
       </c>
       <c r="C497" t="n">
-        <v>4.008809245599202</v>
+        <v>4.008809005461245</v>
       </c>
       <c r="D497" t="n">
-        <v>3.922701026297883</v>
+        <v>3.922700791318031</v>
       </c>
       <c r="E497" t="n">
-        <v>3.941836135451844</v>
+        <v>3.941835899325749</v>
       </c>
       <c r="F497" t="n">
         <v>13989300</v>
@@ -10372,16 +10372,16 @@
         <v>45139</v>
       </c>
       <c r="B498" t="n">
-        <v>3.980106353759766</v>
+        <v>3.980106115341187</v>
       </c>
       <c r="C498" t="n">
-        <v>4.018376572067687</v>
+        <v>4.018376331356624</v>
       </c>
       <c r="D498" t="n">
-        <v>3.884430807989962</v>
+        <v>3.884430575302593</v>
       </c>
       <c r="E498" t="n">
-        <v>3.970539027291279</v>
+        <v>3.970538789445808</v>
       </c>
       <c r="F498" t="n">
         <v>24308900</v>
@@ -10392,16 +10392,16 @@
         <v>45140</v>
       </c>
       <c r="B499" t="n">
-        <v>4.008808612823486</v>
+        <v>4.008809089660645</v>
       </c>
       <c r="C499" t="n">
-        <v>4.018375937781805</v>
+        <v>4.018376415756972</v>
       </c>
       <c r="D499" t="n">
-        <v>3.932268188289268</v>
+        <v>3.932268656022146</v>
       </c>
       <c r="E499" t="n">
-        <v>3.951403294422822</v>
+        <v>3.95140376443177</v>
       </c>
       <c r="F499" t="n">
         <v>25721100</v>
@@ -10432,16 +10432,16 @@
         <v>45142</v>
       </c>
       <c r="B501" t="n">
-        <v>3.903565883636475</v>
+        <v>3.903565406799316</v>
       </c>
       <c r="C501" t="n">
-        <v>3.960971210605601</v>
+        <v>3.960970726756138</v>
       </c>
       <c r="D501" t="n">
-        <v>3.865295665657057</v>
+        <v>3.865295193494769</v>
       </c>
       <c r="E501" t="n">
-        <v>3.903565883636475</v>
+        <v>3.903565406799316</v>
       </c>
       <c r="F501" t="n">
         <v>16409800</v>
@@ -10552,16 +10552,16 @@
         <v>45152</v>
       </c>
       <c r="B507" t="n">
-        <v>3.606971502304077</v>
+        <v>3.606971263885498</v>
       </c>
       <c r="C507" t="n">
-        <v>3.664376829848003</v>
+        <v>3.664376587634967</v>
       </c>
       <c r="D507" t="n">
-        <v>3.56870128394146</v>
+        <v>3.568701048052518</v>
       </c>
       <c r="E507" t="n">
-        <v>3.664376829848003</v>
+        <v>3.664376587634967</v>
       </c>
       <c r="F507" t="n">
         <v>20072900</v>
@@ -10632,16 +10632,16 @@
         <v>45156</v>
       </c>
       <c r="B511" t="n">
-        <v>3.434755325317383</v>
+        <v>3.434755086898804</v>
       </c>
       <c r="C511" t="n">
-        <v>3.473025772164581</v>
+        <v>3.473025531089514</v>
       </c>
       <c r="D511" t="n">
-        <v>3.33907977847063</v>
+        <v>3.339079546693231</v>
       </c>
       <c r="E511" t="n">
-        <v>3.35821488783998</v>
+        <v>3.358214654734345</v>
       </c>
       <c r="F511" t="n">
         <v>15864700</v>
@@ -10692,16 +10692,16 @@
         <v>45161</v>
       </c>
       <c r="B514" t="n">
-        <v>3.453890323638916</v>
+        <v>3.453890085220337</v>
       </c>
       <c r="C514" t="n">
-        <v>3.559133649895108</v>
+        <v>3.559133404211688</v>
       </c>
       <c r="D514" t="n">
-        <v>3.377349888622405</v>
+        <v>3.377349655487335</v>
       </c>
       <c r="E514" t="n">
-        <v>3.396484997376533</v>
+        <v>3.396484762920585</v>
       </c>
       <c r="F514" t="n">
         <v>43718400</v>
@@ -10712,16 +10712,16 @@
         <v>45162</v>
       </c>
       <c r="B515" t="n">
-        <v>3.568701267242432</v>
+        <v>3.568701505661011</v>
       </c>
       <c r="C515" t="n">
-        <v>3.64524170360951</v>
+        <v>3.645241947141619</v>
       </c>
       <c r="D515" t="n">
-        <v>3.444322830037436</v>
+        <v>3.444323060146513</v>
       </c>
       <c r="E515" t="n">
-        <v>3.453890384583321</v>
+        <v>3.453890615331589</v>
       </c>
       <c r="F515" t="n">
         <v>42127000</v>
@@ -10772,16 +10772,16 @@
         <v>45167</v>
       </c>
       <c r="B518" t="n">
-        <v>3.65480899810791</v>
+        <v>3.654809236526489</v>
       </c>
       <c r="C518" t="n">
-        <v>3.664376551973043</v>
+        <v>3.664376791015754</v>
       </c>
       <c r="D518" t="n">
-        <v>3.578268567186847</v>
+        <v>3.578268800612372</v>
       </c>
       <c r="E518" t="n">
-        <v>3.616538782647379</v>
+        <v>3.61653901856943</v>
       </c>
       <c r="F518" t="n">
         <v>13520200</v>
@@ -10912,16 +10912,16 @@
         <v>45177</v>
       </c>
       <c r="B525" t="n">
-        <v>3.549566268920898</v>
+        <v>3.549566030502319</v>
       </c>
       <c r="C525" t="n">
-        <v>3.587836488298725</v>
+        <v>3.587836247309597</v>
       </c>
       <c r="D525" t="n">
-        <v>3.511296049543073</v>
+        <v>3.511295813695041</v>
       </c>
       <c r="E525" t="n">
-        <v>3.530431159231985</v>
+        <v>3.53043092209868</v>
       </c>
       <c r="F525" t="n">
         <v>26042800</v>
@@ -10952,16 +10952,16 @@
         <v>45181</v>
       </c>
       <c r="B527" t="n">
-        <v>3.712214708328247</v>
+        <v>3.712214946746826</v>
       </c>
       <c r="C527" t="n">
-        <v>3.769620033976584</v>
+        <v>3.769620276082045</v>
       </c>
       <c r="D527" t="n">
-        <v>3.616538937472532</v>
+        <v>3.616539169746294</v>
       </c>
       <c r="E527" t="n">
-        <v>3.635674046021977</v>
+        <v>3.6356742795247</v>
       </c>
       <c r="F527" t="n">
         <v>15715300</v>
@@ -10972,16 +10972,16 @@
         <v>45182</v>
       </c>
       <c r="B528" t="n">
-        <v>3.769620180130005</v>
+        <v>3.769619941711426</v>
       </c>
       <c r="C528" t="n">
-        <v>3.846160617295367</v>
+        <v>3.846160374035806</v>
       </c>
       <c r="D528" t="n">
-        <v>3.712214852255983</v>
+        <v>3.712214617468141</v>
       </c>
       <c r="E528" t="n">
-        <v>3.712214852255983</v>
+        <v>3.712214617468141</v>
       </c>
       <c r="F528" t="n">
         <v>17575000</v>
@@ -11012,16 +11012,16 @@
         <v>45184</v>
       </c>
       <c r="B530" t="n">
-        <v>3.807890176773071</v>
+        <v>3.80789041519165</v>
       </c>
       <c r="C530" t="n">
-        <v>3.941835934005541</v>
+        <v>3.941836180810695</v>
       </c>
       <c r="D530" t="n">
-        <v>3.788755068597004</v>
+        <v>3.788755305817501</v>
       </c>
       <c r="E530" t="n">
-        <v>3.788755068597004</v>
+        <v>3.788755305817501</v>
       </c>
       <c r="F530" t="n">
         <v>34682000</v>
@@ -11032,16 +11032,16 @@
         <v>45187</v>
       </c>
       <c r="B531" t="n">
-        <v>3.817457914352417</v>
+        <v>3.817457675933838</v>
       </c>
       <c r="C531" t="n">
-        <v>3.884430796187795</v>
+        <v>3.884430553586438</v>
       </c>
       <c r="D531" t="n">
-        <v>3.740917477969129</v>
+        <v>3.740917244330867</v>
       </c>
       <c r="E531" t="n">
-        <v>3.817457914352417</v>
+        <v>3.817457675933838</v>
       </c>
       <c r="F531" t="n">
         <v>23371600</v>
@@ -11112,16 +11112,16 @@
         <v>45191</v>
       </c>
       <c r="B535" t="n">
-        <v>3.606971502304077</v>
+        <v>3.606971263885498</v>
       </c>
       <c r="C535" t="n">
-        <v>3.664376829848003</v>
+        <v>3.664376587634967</v>
       </c>
       <c r="D535" t="n">
-        <v>3.559133729350806</v>
+        <v>3.559133494094274</v>
       </c>
       <c r="E535" t="n">
-        <v>3.597403947713423</v>
+        <v>3.597403709927253</v>
       </c>
       <c r="F535" t="n">
         <v>21984900</v>
@@ -11172,16 +11172,16 @@
         <v>45196</v>
       </c>
       <c r="B538" t="n">
-        <v>3.396484851837158</v>
+        <v>3.396485090255737</v>
       </c>
       <c r="C538" t="n">
-        <v>3.49216061961658</v>
+        <v>3.492160864751185</v>
       </c>
       <c r="D538" t="n">
-        <v>3.358214635968781</v>
+        <v>3.358214871700957</v>
       </c>
       <c r="E538" t="n">
-        <v>3.453890175639724</v>
+        <v>3.453890418087908</v>
       </c>
       <c r="F538" t="n">
         <v>21389800</v>
@@ -11192,16 +11192,16 @@
         <v>45197</v>
       </c>
       <c r="B539" t="n">
-        <v>3.415620088577271</v>
+        <v>3.41562032699585</v>
       </c>
       <c r="C539" t="n">
-        <v>3.444322751560954</v>
+        <v>3.444322991983049</v>
       </c>
       <c r="D539" t="n">
-        <v>3.329512099626217</v>
+        <v>3.32951233203425</v>
       </c>
       <c r="E539" t="n">
-        <v>3.415620088577271</v>
+        <v>3.41562032699585</v>
       </c>
       <c r="F539" t="n">
         <v>16733500</v>
@@ -11212,16 +11212,16 @@
         <v>45198</v>
       </c>
       <c r="B540" t="n">
-        <v>3.425187587738037</v>
+        <v>3.425187349319458</v>
       </c>
       <c r="C540" t="n">
-        <v>3.492160695063099</v>
+        <v>3.492160451982693</v>
       </c>
       <c r="D540" t="n">
-        <v>3.38691737104285</v>
+        <v>3.386917135288163</v>
       </c>
       <c r="E540" t="n">
-        <v>3.463457804433224</v>
+        <v>3.463457563350753</v>
       </c>
       <c r="F540" t="n">
         <v>13661300</v>
@@ -11252,16 +11252,16 @@
         <v>45202</v>
       </c>
       <c r="B542" t="n">
-        <v>3.31037712097168</v>
+        <v>3.310376882553101</v>
       </c>
       <c r="C542" t="n">
-        <v>3.406052668007885</v>
+        <v>3.406052422698603</v>
       </c>
       <c r="D542" t="n">
-        <v>3.272106902157197</v>
+        <v>3.2721066664949</v>
       </c>
       <c r="E542" t="n">
-        <v>3.3199446756753</v>
+        <v>3.31994443656765</v>
       </c>
       <c r="F542" t="n">
         <v>29291500</v>
@@ -11292,16 +11292,16 @@
         <v>45204</v>
       </c>
       <c r="B544" t="n">
-        <v>3.23383641242981</v>
+        <v>3.233836650848389</v>
       </c>
       <c r="C544" t="n">
-        <v>3.35821461315716</v>
+        <v>3.358214860745675</v>
       </c>
       <c r="D544" t="n">
-        <v>3.20513352261502</v>
+        <v>3.205133758917443</v>
       </c>
       <c r="E544" t="n">
-        <v>3.310376843646641</v>
+        <v>3.310377087708257</v>
       </c>
       <c r="F544" t="n">
         <v>37198300</v>
@@ -11312,16 +11312,16 @@
         <v>45205</v>
       </c>
       <c r="B545" t="n">
-        <v>3.23383641242981</v>
+        <v>3.233836650848389</v>
       </c>
       <c r="C545" t="n">
-        <v>3.262539074136121</v>
+        <v>3.262539314670839</v>
       </c>
       <c r="D545" t="n">
-        <v>3.138160645300292</v>
+        <v>3.138160876665057</v>
       </c>
       <c r="E545" t="n">
-        <v>3.20513352261502</v>
+        <v>3.205133758917443</v>
       </c>
       <c r="F545" t="n">
         <v>15875400</v>
@@ -11352,16 +11352,16 @@
         <v>45209</v>
       </c>
       <c r="B547" t="n">
-        <v>3.415620088577271</v>
+        <v>3.41562032699585</v>
       </c>
       <c r="C547" t="n">
-        <v>3.425187642905165</v>
+        <v>3.425187881991583</v>
       </c>
       <c r="D547" t="n">
-        <v>3.348647208282007</v>
+        <v>3.348647442025716</v>
       </c>
       <c r="E547" t="n">
-        <v>3.367782316937797</v>
+        <v>3.367782552017183</v>
       </c>
       <c r="F547" t="n">
         <v>9595500</v>
@@ -11372,16 +11372,16 @@
         <v>45210</v>
       </c>
       <c r="B548" t="n">
-        <v>3.482593059539795</v>
+        <v>3.482593297958374</v>
       </c>
       <c r="C548" t="n">
-        <v>3.511295721390723</v>
+        <v>3.511295961774288</v>
       </c>
       <c r="D548" t="n">
-        <v>3.396484845878531</v>
+        <v>3.396485078402136</v>
       </c>
       <c r="E548" t="n">
-        <v>3.41561995377915</v>
+        <v>3.415620187612745</v>
       </c>
       <c r="F548" t="n">
         <v>15610900</v>
@@ -11412,16 +11412,16 @@
         <v>45215</v>
       </c>
       <c r="B550" t="n">
-        <v>3.386917352676392</v>
+        <v>3.386917591094971</v>
       </c>
       <c r="C550" t="n">
-        <v>3.434755123285962</v>
+        <v>3.434755365072033</v>
       </c>
       <c r="D550" t="n">
-        <v>3.348647136188735</v>
+        <v>3.348647371913321</v>
       </c>
       <c r="E550" t="n">
-        <v>3.377349798554477</v>
+        <v>3.377350036299558</v>
       </c>
       <c r="F550" t="n">
         <v>12135900</v>
@@ -11472,16 +11472,16 @@
         <v>45218</v>
       </c>
       <c r="B553" t="n">
-        <v>3.420210838317871</v>
+        <v>3.42021107673645</v>
       </c>
       <c r="C553" t="n">
-        <v>3.449114001324837</v>
+        <v>3.449114241758219</v>
       </c>
       <c r="D553" t="n">
-        <v>3.304598186290007</v>
+        <v>3.304598416649374</v>
       </c>
       <c r="E553" t="n">
-        <v>3.314232573958996</v>
+        <v>3.314232804989964</v>
       </c>
       <c r="F553" t="n">
         <v>35125300</v>
@@ -11492,16 +11492,16 @@
         <v>45219</v>
       </c>
       <c r="B554" t="n">
-        <v>3.449114084243774</v>
+        <v>3.449113845825195</v>
       </c>
       <c r="C554" t="n">
-        <v>3.478017247945591</v>
+        <v>3.478017007529093</v>
       </c>
       <c r="D554" t="n">
-        <v>3.381673368939535</v>
+        <v>3.381673135182768</v>
       </c>
       <c r="E554" t="n">
-        <v>3.381673368939535</v>
+        <v>3.381673135182768</v>
       </c>
       <c r="F554" t="n">
         <v>22281100</v>
@@ -11532,16 +11532,16 @@
         <v>45223</v>
       </c>
       <c r="B556" t="n">
-        <v>3.6128990650177</v>
+        <v>3.612898826599121</v>
       </c>
       <c r="C556" t="n">
-        <v>3.632167841654973</v>
+        <v>3.632167601964829</v>
       </c>
       <c r="D556" t="n">
-        <v>3.48765178717349</v>
+        <v>3.487651557020096</v>
       </c>
       <c r="E556" t="n">
-        <v>3.497286405194064</v>
+        <v>3.497286174404871</v>
       </c>
       <c r="F556" t="n">
         <v>18123000</v>
@@ -11552,16 +11552,16 @@
         <v>45224</v>
       </c>
       <c r="B557" t="n">
-        <v>3.593630075454712</v>
+        <v>3.593630313873291</v>
       </c>
       <c r="C557" t="n">
-        <v>3.738146121373493</v>
+        <v>3.738146369379956</v>
       </c>
       <c r="D557" t="n">
-        <v>3.545458136715759</v>
+        <v>3.545458371938382</v>
       </c>
       <c r="E557" t="n">
-        <v>3.641802014193664</v>
+        <v>3.6418022558082</v>
       </c>
       <c r="F557" t="n">
         <v>23871300</v>
@@ -11572,16 +11572,16 @@
         <v>45225</v>
       </c>
       <c r="B558" t="n">
-        <v>3.651436567306519</v>
+        <v>3.651436328887939</v>
       </c>
       <c r="C558" t="n">
-        <v>3.670705343674738</v>
+        <v>3.670705103998014</v>
       </c>
       <c r="D558" t="n">
-        <v>3.545458297281314</v>
+        <v>3.545458065782528</v>
       </c>
       <c r="E558" t="n">
-        <v>3.593630238201861</v>
+        <v>3.593630003557715</v>
       </c>
       <c r="F558" t="n">
         <v>21310400</v>
@@ -11632,16 +11632,16 @@
         <v>45230</v>
       </c>
       <c r="B561" t="n">
-        <v>3.497286319732666</v>
+        <v>3.497286081314087</v>
       </c>
       <c r="C561" t="n">
-        <v>3.516555095899078</v>
+        <v>3.516554856166899</v>
       </c>
       <c r="D561" t="n">
-        <v>3.420210985365089</v>
+        <v>3.420210752200924</v>
       </c>
       <c r="E561" t="n">
-        <v>3.506920707815872</v>
+        <v>3.506920468740493</v>
       </c>
       <c r="F561" t="n">
         <v>11282600</v>
@@ -11652,16 +11652,16 @@
         <v>45231</v>
       </c>
       <c r="B562" t="n">
-        <v>3.6128990650177</v>
+        <v>3.612898826599121</v>
       </c>
       <c r="C562" t="n">
-        <v>3.6128990650177</v>
+        <v>3.612898826599121</v>
       </c>
       <c r="D562" t="n">
-        <v>3.5069207935127</v>
+        <v>3.506920562087725</v>
       </c>
       <c r="E562" t="n">
-        <v>3.5069207935127</v>
+        <v>3.506920562087725</v>
       </c>
       <c r="F562" t="n">
         <v>18109500</v>
@@ -11672,16 +11672,16 @@
         <v>45233</v>
       </c>
       <c r="B563" t="n">
-        <v>3.651436567306519</v>
+        <v>3.651436328887939</v>
       </c>
       <c r="C563" t="n">
-        <v>3.709242896411176</v>
+        <v>3.709242654218164</v>
       </c>
       <c r="D563" t="n">
-        <v>3.61289901457008</v>
+        <v>3.61289877866779</v>
       </c>
       <c r="E563" t="n">
-        <v>3.661070955490628</v>
+        <v>3.661070716442977</v>
       </c>
       <c r="F563" t="n">
         <v>16239100</v>
@@ -11692,16 +11692,16 @@
         <v>45236</v>
       </c>
       <c r="B564" t="n">
-        <v>3.651436567306519</v>
+        <v>3.651436328887939</v>
       </c>
       <c r="C564" t="n">
-        <v>3.699608508227067</v>
+        <v>3.699608266663126</v>
       </c>
       <c r="D564" t="n">
-        <v>3.62253340275419</v>
+        <v>3.622533166222827</v>
       </c>
       <c r="E564" t="n">
-        <v>3.670705343674738</v>
+        <v>3.670705103998014</v>
       </c>
       <c r="F564" t="n">
         <v>9299300</v>
@@ -11892,16 +11892,16 @@
         <v>45251</v>
       </c>
       <c r="B574" t="n">
-        <v>3.50692081451416</v>
+        <v>3.506920576095581</v>
       </c>
       <c r="C574" t="n">
-        <v>3.622533475030152</v>
+        <v>3.622533228751628</v>
       </c>
       <c r="D574" t="n">
-        <v>3.50692081451416</v>
+        <v>3.506920576095581</v>
       </c>
       <c r="E574" t="n">
-        <v>3.612899086653819</v>
+        <v>3.612898841030291</v>
       </c>
       <c r="F574" t="n">
         <v>23500900</v>
@@ -11912,16 +11912,16 @@
         <v>45252</v>
       </c>
       <c r="B575" t="n">
-        <v>3.516554832458496</v>
+        <v>3.516555070877075</v>
       </c>
       <c r="C575" t="n">
-        <v>3.555092381904302</v>
+        <v>3.555092622935685</v>
       </c>
       <c r="D575" t="n">
-        <v>3.497286057735593</v>
+        <v>3.497286294847771</v>
       </c>
       <c r="E575" t="n">
-        <v>3.545457994542851</v>
+        <v>3.545458234921032</v>
       </c>
       <c r="F575" t="n">
         <v>29127900</v>
@@ -11932,16 +11932,16 @@
         <v>45253</v>
       </c>
       <c r="B576" t="n">
-        <v>3.583995580673218</v>
+        <v>3.583995819091797</v>
       </c>
       <c r="C576" t="n">
-        <v>3.583995580673218</v>
+        <v>3.583995819091797</v>
       </c>
       <c r="D576" t="n">
-        <v>3.478017088910578</v>
+        <v>3.478017320279137</v>
       </c>
       <c r="E576" t="n">
-        <v>3.506920480992691</v>
+        <v>3.506920714283994</v>
       </c>
       <c r="F576" t="n">
         <v>15777100</v>
@@ -11972,16 +11972,16 @@
         <v>45257</v>
       </c>
       <c r="B578" t="n">
-        <v>3.420210838317871</v>
+        <v>3.42021107673645</v>
       </c>
       <c r="C578" t="n">
-        <v>3.632167596737543</v>
+        <v>3.63216784993136</v>
       </c>
       <c r="D578" t="n">
-        <v>3.410576450648882</v>
+        <v>3.410576688395861</v>
       </c>
       <c r="E578" t="n">
-        <v>3.603264433730577</v>
+        <v>3.603264684909591</v>
       </c>
       <c r="F578" t="n">
         <v>29619500</v>
@@ -11992,16 +11992,16 @@
         <v>45258</v>
       </c>
       <c r="B579" t="n">
-        <v>3.497286319732666</v>
+        <v>3.497286081314087</v>
       </c>
       <c r="C579" t="n">
-        <v>3.497286319732666</v>
+        <v>3.497286081314087</v>
       </c>
       <c r="D579" t="n">
-        <v>3.381673433032266</v>
+        <v>3.3816732024953</v>
       </c>
       <c r="E579" t="n">
-        <v>3.420210985365089</v>
+        <v>3.420210752200924</v>
       </c>
       <c r="F579" t="n">
         <v>15991300</v>
@@ -12032,16 +12032,16 @@
         <v>45260</v>
       </c>
       <c r="B581" t="n">
-        <v>3.516554832458496</v>
+        <v>3.516555070877075</v>
       </c>
       <c r="C581" t="n">
-        <v>3.564726769265754</v>
+        <v>3.564727010950338</v>
       </c>
       <c r="D581" t="n">
-        <v>3.468382665949325</v>
+        <v>3.468382901101884</v>
       </c>
       <c r="E581" t="n">
-        <v>3.555092381904302</v>
+        <v>3.555092622935685</v>
       </c>
       <c r="F581" t="n">
         <v>22087700</v>
@@ -12152,16 +12152,16 @@
         <v>45268</v>
       </c>
       <c r="B587" t="n">
-        <v>3.50692081451416</v>
+        <v>3.506920576095581</v>
       </c>
       <c r="C587" t="n">
-        <v>3.555092756395823</v>
+        <v>3.555092514702267</v>
       </c>
       <c r="D587" t="n">
-        <v>3.439479866177894</v>
+        <v>3.439479632344298</v>
       </c>
       <c r="E587" t="n">
-        <v>3.545458368019491</v>
+        <v>3.54545812698093</v>
       </c>
       <c r="F587" t="n">
         <v>14112100</v>
@@ -12232,16 +12232,16 @@
         <v>45274</v>
       </c>
       <c r="B591" t="n">
-        <v>3.516554832458496</v>
+        <v>3.516555070877075</v>
       </c>
       <c r="C591" t="n">
-        <v>3.805586683003954</v>
+        <v>3.805586941018577</v>
       </c>
       <c r="D591" t="n">
-        <v>3.487651440672228</v>
+        <v>3.487651677131189</v>
       </c>
       <c r="E591" t="n">
-        <v>3.487651440672228</v>
+        <v>3.487651677131189</v>
       </c>
       <c r="F591" t="n">
         <v>64134600</v>
@@ -12252,16 +12252,16 @@
         <v>45275</v>
       </c>
       <c r="B592" t="n">
-        <v>3.593630075454712</v>
+        <v>3.593630313873291</v>
       </c>
       <c r="C592" t="n">
-        <v>3.641802014193664</v>
+        <v>3.6418022558082</v>
       </c>
       <c r="D592" t="n">
-        <v>3.497286197976806</v>
+        <v>3.497286430003473</v>
       </c>
       <c r="E592" t="n">
-        <v>3.56472691221134</v>
+        <v>3.564727148712346</v>
       </c>
       <c r="F592" t="n">
         <v>53571000</v>
@@ -12312,16 +12312,16 @@
         <v>45280</v>
       </c>
       <c r="B595" t="n">
-        <v>3.873027563095093</v>
+        <v>3.873027801513672</v>
       </c>
       <c r="C595" t="n">
-        <v>3.892296338656607</v>
+        <v>3.892296578261347</v>
       </c>
       <c r="D595" t="n">
-        <v>3.767049297506766</v>
+        <v>3.76704952940146</v>
       </c>
       <c r="E595" t="n">
-        <v>3.834490011972065</v>
+        <v>3.834490248018322</v>
       </c>
       <c r="F595" t="n">
         <v>18861600</v>
@@ -25972,19 +25972,39 @@
         <v>46281</v>
       </c>
       <c r="B1278" t="n">
-        <v>0.28</v>
+        <v>0.2800000011920929</v>
       </c>
       <c r="C1278" t="n">
-        <v>0.28</v>
+        <v>0.2800000011920929</v>
       </c>
       <c r="D1278" t="n">
-        <v>0.26</v>
+        <v>0.2599999904632568</v>
       </c>
       <c r="E1278" t="n">
-        <v>0.28</v>
+        <v>0.2800000011920929</v>
       </c>
       <c r="F1278" t="n">
         <v>11076100</v>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B1279" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C1279" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D1279" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E1279" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F1279" t="n">
+        <v>12268900</v>
       </c>
     </row>
   </sheetData>

--- a/database/RAIZ4.xlsx
+++ b/database/RAIZ4.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1279"/>
+  <dimension ref="A1:F1280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44413</v>
       </c>
       <c r="B2" t="n">
-        <v>6.384482383728027</v>
+        <v>6.384480953216553</v>
       </c>
       <c r="C2" t="n">
-        <v>6.701942961521317</v>
+        <v>6.701941459879408</v>
       </c>
       <c r="D2" t="n">
-        <v>6.331572357511064</v>
+        <v>6.331570938854646</v>
       </c>
       <c r="E2" t="n">
-        <v>6.59612290908739</v>
+        <v>6.596121431155595</v>
       </c>
       <c r="F2" t="n">
         <v>98849900</v>
@@ -532,16 +532,16 @@
         <v>44419</v>
       </c>
       <c r="B6" t="n">
-        <v>6.058201789855957</v>
+        <v>6.058202743530273</v>
       </c>
       <c r="C6" t="n">
-        <v>6.296297043852743</v>
+        <v>6.296298035007707</v>
       </c>
       <c r="D6" t="n">
-        <v>5.996473655425436</v>
+        <v>5.996474599382589</v>
       </c>
       <c r="E6" t="n">
-        <v>6.287478919144688</v>
+        <v>6.287479908911514</v>
       </c>
       <c r="F6" t="n">
         <v>31978000</v>
@@ -552,16 +552,16 @@
         <v>44420</v>
       </c>
       <c r="B7" t="n">
-        <v>6.137568473815918</v>
+        <v>6.13756799697876</v>
       </c>
       <c r="C7" t="n">
-        <v>6.155205147916306</v>
+        <v>6.155204669708928</v>
       </c>
       <c r="D7" t="n">
-        <v>5.952383185516099</v>
+        <v>5.952382723066271</v>
       </c>
       <c r="E7" t="n">
-        <v>6.146386600620373</v>
+        <v>6.146386123098121</v>
       </c>
       <c r="F7" t="n">
         <v>17054100</v>
@@ -612,16 +612,16 @@
         <v>44425</v>
       </c>
       <c r="B10" t="n">
-        <v>6.014110565185547</v>
+        <v>6.014111042022705</v>
       </c>
       <c r="C10" t="n">
-        <v>6.164022055132227</v>
+        <v>6.164022543855327</v>
       </c>
       <c r="D10" t="n">
-        <v>5.961200553352942</v>
+        <v>5.961201025995057</v>
       </c>
       <c r="E10" t="n">
-        <v>6.111112043299623</v>
+        <v>6.111112527827679</v>
       </c>
       <c r="F10" t="n">
         <v>17772000</v>
@@ -632,16 +632,16 @@
         <v>44426</v>
       </c>
       <c r="B11" t="n">
-        <v>6.005292892456055</v>
+        <v>6.005292415618896</v>
       </c>
       <c r="C11" t="n">
-        <v>6.172841497856859</v>
+        <v>6.17284100771587</v>
       </c>
       <c r="D11" t="n">
-        <v>5.925927652926344</v>
+        <v>5.925927182391009</v>
       </c>
       <c r="E11" t="n">
-        <v>6.022929565630274</v>
+        <v>6.022929087392713</v>
       </c>
       <c r="F11" t="n">
         <v>8841700</v>
@@ -652,16 +652,16 @@
         <v>44427</v>
       </c>
       <c r="B12" t="n">
-        <v>6.11111307144165</v>
+        <v>6.111112594604492</v>
       </c>
       <c r="C12" t="n">
-        <v>6.11111307144165</v>
+        <v>6.111112594604492</v>
       </c>
       <c r="D12" t="n">
-        <v>5.66137768495472</v>
+        <v>5.661377243209458</v>
       </c>
       <c r="E12" t="n">
-        <v>5.908291115047926</v>
+        <v>5.908290654036534</v>
       </c>
       <c r="F12" t="n">
         <v>5423700</v>
@@ -732,16 +732,16 @@
         <v>44433</v>
       </c>
       <c r="B16" t="n">
-        <v>6.472665309906006</v>
+        <v>6.472664833068848</v>
       </c>
       <c r="C16" t="n">
-        <v>6.507938655968863</v>
+        <v>6.507938176533139</v>
       </c>
       <c r="D16" t="n">
-        <v>6.402118617780292</v>
+        <v>6.402118146140264</v>
       </c>
       <c r="E16" t="n">
-        <v>6.455028636874578</v>
+        <v>6.455028161336702</v>
       </c>
       <c r="F16" t="n">
         <v>5190100</v>
@@ -772,16 +772,16 @@
         <v>44435</v>
       </c>
       <c r="B18" t="n">
-        <v>6.340389251708984</v>
+        <v>6.340390205383301</v>
       </c>
       <c r="C18" t="n">
-        <v>6.38448071847708</v>
+        <v>6.384481678783307</v>
       </c>
       <c r="D18" t="n">
-        <v>6.278660693643972</v>
+        <v>6.278661638033537</v>
       </c>
       <c r="E18" t="n">
-        <v>6.305115910097949</v>
+        <v>6.305116858466711</v>
       </c>
       <c r="F18" t="n">
         <v>5881000</v>
@@ -852,16 +852,16 @@
         <v>44441</v>
       </c>
       <c r="B22" t="n">
-        <v>5.996475219726562</v>
+        <v>5.996474266052246</v>
       </c>
       <c r="C22" t="n">
-        <v>6.252207210343668</v>
+        <v>6.252206215997954</v>
       </c>
       <c r="D22" t="n">
-        <v>5.970019997718263</v>
+        <v>5.970019048251363</v>
       </c>
       <c r="E22" t="n">
-        <v>6.234570535835299</v>
+        <v>6.234569544294506</v>
       </c>
       <c r="F22" t="n">
         <v>3746900</v>
@@ -892,16 +892,16 @@
         <v>44445</v>
       </c>
       <c r="B24" t="n">
-        <v>6.11111307144165</v>
+        <v>6.111112594604492</v>
       </c>
       <c r="C24" t="n">
-        <v>6.190478312788771</v>
+        <v>6.190477829758912</v>
       </c>
       <c r="D24" t="n">
-        <v>6.067021597742168</v>
+        <v>6.067021124345374</v>
       </c>
       <c r="E24" t="n">
-        <v>6.119931618476427</v>
+        <v>6.119931140951175</v>
       </c>
       <c r="F24" t="n">
         <v>1654400</v>
@@ -912,16 +912,16 @@
         <v>44447</v>
       </c>
       <c r="B25" t="n">
-        <v>5.758379459381104</v>
+        <v>5.758378982543945</v>
       </c>
       <c r="C25" t="n">
-        <v>6.111112922336476</v>
+        <v>6.111112416290331</v>
       </c>
       <c r="D25" t="n">
-        <v>5.661377546822648</v>
+        <v>5.661377078017978</v>
       </c>
       <c r="E25" t="n">
-        <v>6.111112922336476</v>
+        <v>6.111112416290331</v>
       </c>
       <c r="F25" t="n">
         <v>10251100</v>
@@ -932,16 +932,16 @@
         <v>44448</v>
       </c>
       <c r="B26" t="n">
-        <v>5.65255880355835</v>
+        <v>5.652558326721191</v>
       </c>
       <c r="C26" t="n">
-        <v>5.837744075419861</v>
+        <v>5.837743582960889</v>
       </c>
       <c r="D26" t="n">
-        <v>5.599648785953838</v>
+        <v>5.59964831358005</v>
       </c>
       <c r="E26" t="n">
-        <v>5.758379259258814</v>
+        <v>5.75837877349488</v>
       </c>
       <c r="F26" t="n">
         <v>5428200</v>
@@ -952,16 +952,16 @@
         <v>44449</v>
       </c>
       <c r="B27" t="n">
-        <v>5.731924057006836</v>
+        <v>5.731924533843994</v>
       </c>
       <c r="C27" t="n">
-        <v>5.899472656824471</v>
+        <v>5.89947314759995</v>
       </c>
       <c r="D27" t="n">
-        <v>5.617285474948753</v>
+        <v>5.617285942249159</v>
       </c>
       <c r="E27" t="n">
-        <v>5.76719740217987</v>
+        <v>5.767197881951408</v>
       </c>
       <c r="F27" t="n">
         <v>5905500</v>
@@ -972,16 +972,16 @@
         <v>44452</v>
       </c>
       <c r="B28" t="n">
-        <v>6.128749370574951</v>
+        <v>6.128748893737793</v>
       </c>
       <c r="C28" t="n">
-        <v>6.172841262072042</v>
+        <v>6.172840781804387</v>
       </c>
       <c r="D28" t="n">
-        <v>5.925927426572926</v>
+        <v>5.925926965515992</v>
       </c>
       <c r="E28" t="n">
-        <v>5.952382645569469</v>
+        <v>5.95238218245423</v>
       </c>
       <c r="F28" t="n">
         <v>8999600</v>
@@ -992,16 +992,16 @@
         <v>44453</v>
       </c>
       <c r="B29" t="n">
-        <v>6.340389251708984</v>
+        <v>6.340390205383301</v>
       </c>
       <c r="C29" t="n">
-        <v>6.507937834607105</v>
+        <v>6.507938813482836</v>
       </c>
       <c r="D29" t="n">
-        <v>6.225750681227418</v>
+        <v>6.225751617658651</v>
       </c>
       <c r="E29" t="n">
-        <v>6.225750681227418</v>
+        <v>6.225751617658651</v>
       </c>
       <c r="F29" t="n">
         <v>9730300</v>
@@ -1012,16 +1012,16 @@
         <v>44454</v>
       </c>
       <c r="B30" t="n">
-        <v>6.384482383728027</v>
+        <v>6.384480953216553</v>
       </c>
       <c r="C30" t="n">
-        <v>6.507939532059118</v>
+        <v>6.50793807388575</v>
       </c>
       <c r="D30" t="n">
-        <v>6.296299006699756</v>
+        <v>6.296297595946708</v>
       </c>
       <c r="E30" t="n">
-        <v>6.384482383728027</v>
+        <v>6.384480953216553</v>
       </c>
       <c r="F30" t="n">
         <v>7265900</v>
@@ -1032,16 +1032,16 @@
         <v>44455</v>
       </c>
       <c r="B31" t="n">
-        <v>6.278661727905273</v>
+        <v>6.278661251068115</v>
       </c>
       <c r="C31" t="n">
-        <v>6.428573664692329</v>
+        <v>6.428573176470008</v>
       </c>
       <c r="D31" t="n">
-        <v>6.172841685640813</v>
+        <v>6.172841216840228</v>
       </c>
       <c r="E31" t="n">
-        <v>6.349208422748248</v>
+        <v>6.349207940553374</v>
       </c>
       <c r="F31" t="n">
         <v>6142600</v>
@@ -1052,16 +1052,16 @@
         <v>44456</v>
       </c>
       <c r="B32" t="n">
-        <v>6.384482383728027</v>
+        <v>6.384480953216553</v>
       </c>
       <c r="C32" t="n">
-        <v>6.384482383728027</v>
+        <v>6.384480953216553</v>
       </c>
       <c r="D32" t="n">
-        <v>5.978838849397976</v>
+        <v>5.978837509775269</v>
       </c>
       <c r="E32" t="n">
-        <v>6.261025655888447</v>
+        <v>6.26102425303877</v>
       </c>
       <c r="F32" t="n">
         <v>16008100</v>
@@ -1112,16 +1112,16 @@
         <v>44461</v>
       </c>
       <c r="B35" t="n">
-        <v>6.446209907531738</v>
+        <v>6.446210384368896</v>
       </c>
       <c r="C35" t="n">
-        <v>6.560848489234745</v>
+        <v>6.560848974551915</v>
       </c>
       <c r="D35" t="n">
-        <v>6.402118436447734</v>
+        <v>6.40211891002337</v>
       </c>
       <c r="E35" t="n">
-        <v>6.463846580063628</v>
+        <v>6.463847058205402</v>
       </c>
       <c r="F35" t="n">
         <v>10254600</v>
@@ -1132,16 +1132,16 @@
         <v>44462</v>
       </c>
       <c r="B36" t="n">
-        <v>6.375664234161377</v>
+        <v>6.375663757324219</v>
       </c>
       <c r="C36" t="n">
-        <v>6.543212860179822</v>
+        <v>6.54321237081167</v>
       </c>
       <c r="D36" t="n">
-        <v>6.34039088347239</v>
+        <v>6.340390409273332</v>
       </c>
       <c r="E36" t="n">
-        <v>6.507939509490835</v>
+        <v>6.507939022760783</v>
       </c>
       <c r="F36" t="n">
         <v>6341600</v>
@@ -1172,16 +1172,16 @@
         <v>44466</v>
       </c>
       <c r="B38" t="n">
-        <v>6.305117130279541</v>
+        <v>6.305117607116699</v>
       </c>
       <c r="C38" t="n">
-        <v>6.340390478716762</v>
+        <v>6.340390958221537</v>
       </c>
       <c r="D38" t="n">
-        <v>6.102295166519786</v>
+        <v>6.102295628018125</v>
       </c>
       <c r="E38" t="n">
-        <v>6.172841863394225</v>
+        <v>6.172842330227801</v>
       </c>
       <c r="F38" t="n">
         <v>6343700</v>
@@ -1192,16 +1192,16 @@
         <v>44467</v>
       </c>
       <c r="B39" t="n">
-        <v>6.119931221008301</v>
+        <v>6.119931697845459</v>
       </c>
       <c r="C39" t="n">
-        <v>6.278661272902115</v>
+        <v>6.278661762106795</v>
       </c>
       <c r="D39" t="n">
-        <v>6.119931221008301</v>
+        <v>6.119931697845459</v>
       </c>
       <c r="E39" t="n">
-        <v>6.261024600469469</v>
+        <v>6.26102508829998</v>
       </c>
       <c r="F39" t="n">
         <v>6782400</v>
@@ -1212,16 +1212,16 @@
         <v>44468</v>
       </c>
       <c r="B40" t="n">
-        <v>6.040566444396973</v>
+        <v>6.040565967559814</v>
       </c>
       <c r="C40" t="n">
-        <v>6.252206950182298</v>
+        <v>6.25220645663842</v>
       </c>
       <c r="D40" t="n">
-        <v>6.040566444396973</v>
+        <v>6.040565967559814</v>
       </c>
       <c r="E40" t="n">
-        <v>6.216933602633323</v>
+        <v>6.216933111873892</v>
       </c>
       <c r="F40" t="n">
         <v>6482600</v>
@@ -1252,16 +1252,16 @@
         <v>44470</v>
       </c>
       <c r="B42" t="n">
-        <v>6.499119281768799</v>
+        <v>6.499119758605957</v>
       </c>
       <c r="C42" t="n">
-        <v>6.569665964912827</v>
+        <v>6.569666446925959</v>
       </c>
       <c r="D42" t="n">
-        <v>6.331570699056035</v>
+        <v>6.331571163600236</v>
       </c>
       <c r="E42" t="n">
-        <v>6.331570699056035</v>
+        <v>6.331571163600236</v>
       </c>
       <c r="F42" t="n">
         <v>15528000</v>
@@ -1312,16 +1312,16 @@
         <v>44475</v>
       </c>
       <c r="B45" t="n">
-        <v>6.178093910217285</v>
+        <v>6.178093433380127</v>
       </c>
       <c r="C45" t="n">
-        <v>6.275317254600846</v>
+        <v>6.275316770259803</v>
       </c>
       <c r="D45" t="n">
-        <v>6.080870987285061</v>
+        <v>6.080870517951754</v>
       </c>
       <c r="E45" t="n">
-        <v>6.248802065237998</v>
+        <v>6.248801582943448</v>
       </c>
       <c r="F45" t="n">
         <v>10376100</v>
@@ -1332,16 +1332,16 @@
         <v>44476</v>
       </c>
       <c r="B46" t="n">
-        <v>6.301833152770996</v>
+        <v>6.301832675933838</v>
       </c>
       <c r="C46" t="n">
-        <v>6.478602494754905</v>
+        <v>6.478602004542243</v>
       </c>
       <c r="D46" t="n">
-        <v>6.213448481779042</v>
+        <v>6.213448011629635</v>
       </c>
       <c r="E46" t="n">
-        <v>6.284156218572606</v>
+        <v>6.284155743072997</v>
       </c>
       <c r="F46" t="n">
         <v>18438800</v>
@@ -1352,16 +1352,16 @@
         <v>44477</v>
       </c>
       <c r="B47" t="n">
-        <v>6.310671329498291</v>
+        <v>6.310670852661133</v>
       </c>
       <c r="C47" t="n">
-        <v>6.655372174193518</v>
+        <v>6.655371671310609</v>
       </c>
       <c r="D47" t="n">
-        <v>6.292994395522999</v>
+        <v>6.292993920021518</v>
       </c>
       <c r="E47" t="n">
-        <v>6.363702131424168</v>
+        <v>6.363701650579979</v>
       </c>
       <c r="F47" t="n">
         <v>20480700</v>
@@ -1372,16 +1372,16 @@
         <v>44480</v>
       </c>
       <c r="B48" t="n">
-        <v>6.213448047637939</v>
+        <v>6.213447570800781</v>
       </c>
       <c r="C48" t="n">
-        <v>6.407894310234044</v>
+        <v>6.407893818474543</v>
       </c>
       <c r="D48" t="n">
-        <v>6.213448047637939</v>
+        <v>6.213447570800781</v>
       </c>
       <c r="E48" t="n">
-        <v>6.363701767100176</v>
+        <v>6.363701278732132</v>
       </c>
       <c r="F48" t="n">
         <v>10407400</v>
@@ -1392,16 +1392,16 @@
         <v>44482</v>
       </c>
       <c r="B49" t="n">
-        <v>6.231124401092529</v>
+        <v>6.231124877929688</v>
       </c>
       <c r="C49" t="n">
-        <v>6.292993449984393</v>
+        <v>6.292993931556084</v>
       </c>
       <c r="D49" t="n">
-        <v>6.213447469773242</v>
+        <v>6.213447945257672</v>
       </c>
       <c r="E49" t="n">
-        <v>6.248801332411817</v>
+        <v>6.248801810601703</v>
       </c>
       <c r="F49" t="n">
         <v>8146000</v>
@@ -1412,16 +1412,16 @@
         <v>44483</v>
       </c>
       <c r="B50" t="n">
-        <v>6.319509506225586</v>
+        <v>6.319509983062744</v>
       </c>
       <c r="C50" t="n">
-        <v>6.381378559508698</v>
+        <v>6.381379041014171</v>
       </c>
       <c r="D50" t="n">
-        <v>6.239963098917224</v>
+        <v>6.239963569752225</v>
       </c>
       <c r="E50" t="n">
-        <v>6.24880177592985</v>
+        <v>6.248802247431771</v>
       </c>
       <c r="F50" t="n">
         <v>10992200</v>
@@ -1432,16 +1432,16 @@
         <v>44484</v>
       </c>
       <c r="B51" t="n">
-        <v>6.275316715240479</v>
+        <v>6.275317192077637</v>
       </c>
       <c r="C51" t="n">
-        <v>6.354863119394721</v>
+        <v>6.354863602276304</v>
       </c>
       <c r="D51" t="n">
-        <v>6.222285919621418</v>
+        <v>6.222286392428969</v>
       </c>
       <c r="E51" t="n">
-        <v>6.3371861875217</v>
+        <v>6.337186669060081</v>
       </c>
       <c r="F51" t="n">
         <v>34203500</v>
@@ -1452,16 +1452,16 @@
         <v>44487</v>
       </c>
       <c r="B52" t="n">
-        <v>6.169255256652832</v>
+        <v>6.169256210327148</v>
       </c>
       <c r="C52" t="n">
-        <v>6.266478594770578</v>
+        <v>6.266479563474164</v>
       </c>
       <c r="D52" t="n">
-        <v>6.151578324399725</v>
+        <v>6.151579275341452</v>
       </c>
       <c r="E52" t="n">
-        <v>6.25763991791837</v>
+        <v>6.257640885255628</v>
       </c>
       <c r="F52" t="n">
         <v>7596500</v>
@@ -1472,16 +1472,16 @@
         <v>44488</v>
       </c>
       <c r="B53" t="n">
-        <v>5.912939071655273</v>
+        <v>5.912940502166748</v>
       </c>
       <c r="C53" t="n">
-        <v>6.186931711146165</v>
+        <v>6.186933207944406</v>
       </c>
       <c r="D53" t="n">
-        <v>5.895262140767192</v>
+        <v>5.895263567002105</v>
       </c>
       <c r="E53" t="n">
-        <v>6.169254780258083</v>
+        <v>6.169256272779763</v>
       </c>
       <c r="F53" t="n">
         <v>11473400</v>
@@ -1492,16 +1492,16 @@
         <v>44489</v>
       </c>
       <c r="B54" t="n">
-        <v>5.904100894927979</v>
+        <v>5.904101371765137</v>
       </c>
       <c r="C54" t="n">
-        <v>6.045516775446618</v>
+        <v>6.045517263705048</v>
       </c>
       <c r="D54" t="n">
-        <v>5.842231842311679</v>
+        <v>5.842232314152062</v>
       </c>
       <c r="E54" t="n">
-        <v>6.010162910679786</v>
+        <v>6.010163396082907</v>
       </c>
       <c r="F54" t="n">
         <v>6234400</v>
@@ -1512,16 +1512,16 @@
         <v>44490</v>
       </c>
       <c r="B55" t="n">
-        <v>5.683138847351074</v>
+        <v>5.683139801025391</v>
       </c>
       <c r="C55" t="n">
-        <v>5.842231655156614</v>
+        <v>5.842232635527925</v>
       </c>
       <c r="D55" t="n">
-        <v>5.471015665545419</v>
+        <v>5.471016583623838</v>
       </c>
       <c r="E55" t="n">
-        <v>5.79803911488812</v>
+        <v>5.798040087843582</v>
       </c>
       <c r="F55" t="n">
         <v>12472300</v>
@@ -1532,16 +1532,16 @@
         <v>44491</v>
       </c>
       <c r="B56" t="n">
-        <v>5.63010835647583</v>
+        <v>5.630107879638672</v>
       </c>
       <c r="C56" t="n">
-        <v>5.656623966361621</v>
+        <v>5.656623487278746</v>
       </c>
       <c r="D56" t="n">
-        <v>5.197023292801376</v>
+        <v>5.197022852643983</v>
       </c>
       <c r="E56" t="n">
-        <v>5.60359316804136</v>
+        <v>5.603592693449883</v>
       </c>
       <c r="F56" t="n">
         <v>18890200</v>
@@ -1552,16 +1552,16 @@
         <v>44494</v>
       </c>
       <c r="B57" t="n">
-        <v>5.859909057617188</v>
+        <v>5.859909534454346</v>
       </c>
       <c r="C57" t="n">
-        <v>5.877585990854064</v>
+        <v>5.877586469129643</v>
       </c>
       <c r="D57" t="n">
-        <v>5.550562515246201</v>
+        <v>5.550562966910968</v>
       </c>
       <c r="E57" t="n">
-        <v>5.683139303797101</v>
+        <v>5.683139766250011</v>
       </c>
       <c r="F57" t="n">
         <v>11428100</v>
@@ -1592,16 +1592,16 @@
         <v>44496</v>
       </c>
       <c r="B59" t="n">
-        <v>5.859909057617188</v>
+        <v>5.859909534454346</v>
       </c>
       <c r="C59" t="n">
-        <v>5.96597065703844</v>
+        <v>5.965971142506127</v>
       </c>
       <c r="D59" t="n">
-        <v>5.789201324669686</v>
+        <v>5.789201795753159</v>
       </c>
       <c r="E59" t="n">
-        <v>5.833393447036208</v>
+        <v>5.833393921715717</v>
       </c>
       <c r="F59" t="n">
         <v>7675900</v>
@@ -1612,16 +1612,16 @@
         <v>44497</v>
       </c>
       <c r="B60" t="n">
-        <v>5.992486953735352</v>
+        <v>5.99248743057251</v>
       </c>
       <c r="C60" t="n">
-        <v>6.02784082425698</v>
+        <v>6.027841303907334</v>
       </c>
       <c r="D60" t="n">
-        <v>5.727332503371757</v>
+        <v>5.727332959109914</v>
       </c>
       <c r="E60" t="n">
-        <v>5.753848116988669</v>
+        <v>5.753848574836739</v>
       </c>
       <c r="F60" t="n">
         <v>8299700</v>
@@ -1632,16 +1632,16 @@
         <v>44498</v>
       </c>
       <c r="B61" t="n">
-        <v>5.992486953735352</v>
+        <v>5.99248743057251</v>
       </c>
       <c r="C61" t="n">
-        <v>6.019002145900882</v>
+        <v>6.01900262484792</v>
       </c>
       <c r="D61" t="n">
-        <v>5.84223279329274</v>
+        <v>5.8422332581738</v>
       </c>
       <c r="E61" t="n">
-        <v>5.957132661762342</v>
+        <v>5.957133135786272</v>
       </c>
       <c r="F61" t="n">
         <v>3926300</v>
@@ -1672,16 +1672,16 @@
         <v>44503</v>
       </c>
       <c r="B63" t="n">
-        <v>6.098547458648682</v>
+        <v>6.09854793548584</v>
       </c>
       <c r="C63" t="n">
-        <v>6.186932118914339</v>
+        <v>6.186932602662175</v>
       </c>
       <c r="D63" t="n">
-        <v>5.92177771666606</v>
+        <v>5.921778179681833</v>
       </c>
       <c r="E63" t="n">
-        <v>5.983647189577673</v>
+        <v>5.983647657430936</v>
       </c>
       <c r="F63" t="n">
         <v>5711600</v>
@@ -1692,16 +1692,16 @@
         <v>44504</v>
       </c>
       <c r="B64" t="n">
-        <v>5.965971946716309</v>
+        <v>5.965970516204834</v>
       </c>
       <c r="C64" t="n">
-        <v>6.160418254355843</v>
+        <v>6.160416777220335</v>
       </c>
       <c r="D64" t="n">
-        <v>5.842233387309332</v>
+        <v>5.842231986467696</v>
       </c>
       <c r="E64" t="n">
-        <v>6.098549185378067</v>
+        <v>6.098547723077428</v>
       </c>
       <c r="F64" t="n">
         <v>8687600</v>
@@ -1712,16 +1712,16 @@
         <v>44505</v>
       </c>
       <c r="B65" t="n">
-        <v>5.965971946716309</v>
+        <v>5.965970516204834</v>
       </c>
       <c r="C65" t="n">
-        <v>6.054356632007006</v>
+        <v>6.054355180302789</v>
       </c>
       <c r="D65" t="n">
-        <v>5.939456330403387</v>
+        <v>5.939454906249786</v>
       </c>
       <c r="E65" t="n">
-        <v>6.001325820832587</v>
+        <v>6.001324381844015</v>
       </c>
       <c r="F65" t="n">
         <v>3123600</v>
@@ -1732,16 +1732,16 @@
         <v>44508</v>
       </c>
       <c r="B66" t="n">
-        <v>5.983648300170898</v>
+        <v>5.983647346496582</v>
       </c>
       <c r="C66" t="n">
-        <v>6.03667910617306</v>
+        <v>6.036678144046689</v>
       </c>
       <c r="D66" t="n">
-        <v>5.939455751110073</v>
+        <v>5.939454804479167</v>
       </c>
       <c r="E66" t="n">
-        <v>6.010163913897671</v>
+        <v>6.010162955997293</v>
       </c>
       <c r="F66" t="n">
         <v>3898000</v>
@@ -1772,16 +1772,16 @@
         <v>44510</v>
       </c>
       <c r="B68" t="n">
-        <v>5.745008945465088</v>
+        <v>5.745007991790771</v>
       </c>
       <c r="C68" t="n">
-        <v>6.010163373067091</v>
+        <v>6.01016237537701</v>
       </c>
       <c r="D68" t="n">
-        <v>5.745008945465088</v>
+        <v>5.745007991790771</v>
       </c>
       <c r="E68" t="n">
-        <v>5.957132150385616</v>
+        <v>5.957131161498742</v>
       </c>
       <c r="F68" t="n">
         <v>10074000</v>
@@ -1792,16 +1792,16 @@
         <v>44511</v>
       </c>
       <c r="B69" t="n">
-        <v>6.010163307189941</v>
+        <v>6.010162830352783</v>
       </c>
       <c r="C69" t="n">
-        <v>6.036678496788703</v>
+        <v>6.036678017847871</v>
       </c>
       <c r="D69" t="n">
-        <v>5.806878360643628</v>
+        <v>5.806877899934787</v>
       </c>
       <c r="E69" t="n">
-        <v>5.833393550242389</v>
+        <v>5.833393087429874</v>
       </c>
       <c r="F69" t="n">
         <v>8604300</v>
@@ -1812,16 +1812,16 @@
         <v>44512</v>
       </c>
       <c r="B70" t="n">
-        <v>5.762686252593994</v>
+        <v>5.762685775756836</v>
       </c>
       <c r="C70" t="n">
-        <v>6.080871502042515</v>
+        <v>6.080870998876915</v>
       </c>
       <c r="D70" t="n">
-        <v>5.532886099040496</v>
+        <v>5.532885641218299</v>
       </c>
       <c r="E70" t="n">
-        <v>6.080871502042515</v>
+        <v>6.080870998876915</v>
       </c>
       <c r="F70" t="n">
         <v>20568500</v>
@@ -1852,16 +1852,16 @@
         <v>44517</v>
       </c>
       <c r="B72" t="n">
-        <v>5.170507907867432</v>
+        <v>5.170507431030273</v>
       </c>
       <c r="C72" t="n">
-        <v>5.462177522044113</v>
+        <v>5.462177018308454</v>
       </c>
       <c r="D72" t="n">
-        <v>5.002576828488149</v>
+        <v>5.002576367138015</v>
       </c>
       <c r="E72" t="n">
-        <v>5.364954598286112</v>
+        <v>5.364954103516594</v>
       </c>
       <c r="F72" t="n">
         <v>24600900</v>
@@ -1892,16 +1892,16 @@
         <v>44519</v>
       </c>
       <c r="B74" t="n">
-        <v>5.241215229034424</v>
+        <v>5.241215705871582</v>
       </c>
       <c r="C74" t="n">
-        <v>5.285407770133975</v>
+        <v>5.285408250991699</v>
       </c>
       <c r="D74" t="n">
-        <v>5.090961516488821</v>
+        <v>5.090961979656143</v>
       </c>
       <c r="E74" t="n">
-        <v>5.161669245087059</v>
+        <v>5.161669714687254</v>
       </c>
       <c r="F74" t="n">
         <v>11364600</v>
@@ -1912,16 +1912,16 @@
         <v>44522</v>
       </c>
       <c r="B75" t="n">
-        <v>4.97606086730957</v>
+        <v>4.976061344146729</v>
       </c>
       <c r="C75" t="n">
-        <v>5.329599904790679</v>
+        <v>5.32960041550615</v>
       </c>
       <c r="D75" t="n">
-        <v>4.97606086730957</v>
+        <v>4.976061344146729</v>
       </c>
       <c r="E75" t="n">
-        <v>5.232376574656837</v>
+        <v>5.232377076055763</v>
       </c>
       <c r="F75" t="n">
         <v>8516000</v>
@@ -1952,16 +1952,16 @@
         <v>44524</v>
       </c>
       <c r="B77" t="n">
-        <v>4.923030853271484</v>
+        <v>4.923030376434326</v>
       </c>
       <c r="C77" t="n">
-        <v>5.020253777325691</v>
+        <v>5.020253291071671</v>
       </c>
       <c r="D77" t="n">
-        <v>4.825807507765937</v>
+        <v>4.825807040345681</v>
       </c>
       <c r="E77" t="n">
-        <v>4.923030853271484</v>
+        <v>4.923030376434326</v>
       </c>
       <c r="F77" t="n">
         <v>8397000</v>
@@ -1972,16 +1972,16 @@
         <v>44525</v>
       </c>
       <c r="B78" t="n">
-        <v>5.373793125152588</v>
+        <v>5.37379264831543</v>
       </c>
       <c r="C78" t="n">
-        <v>5.373793125152588</v>
+        <v>5.37379264831543</v>
       </c>
       <c r="D78" t="n">
-        <v>4.799292123891901</v>
+        <v>4.799291698032407</v>
       </c>
       <c r="E78" t="n">
-        <v>4.949546277300996</v>
+        <v>4.949545838108879</v>
       </c>
       <c r="F78" t="n">
         <v>20546100</v>
@@ -1992,16 +1992,16 @@
         <v>44526</v>
       </c>
       <c r="B79" t="n">
-        <v>5.223538875579834</v>
+        <v>5.223537921905518</v>
       </c>
       <c r="C79" t="n">
-        <v>5.338439158006967</v>
+        <v>5.338438183355024</v>
       </c>
       <c r="D79" t="n">
-        <v>5.02025392261312</v>
+        <v>5.020253006053037</v>
       </c>
       <c r="E79" t="n">
-        <v>5.037930856721036</v>
+        <v>5.037929936933631</v>
       </c>
       <c r="F79" t="n">
         <v>8564200</v>
@@ -2012,16 +2012,16 @@
         <v>44529</v>
       </c>
       <c r="B80" t="n">
-        <v>5.117477416992188</v>
+        <v>5.117476940155029</v>
       </c>
       <c r="C80" t="n">
-        <v>5.391470114210696</v>
+        <v>5.391469611843401</v>
       </c>
       <c r="D80" t="n">
-        <v>5.117477416992188</v>
+        <v>5.117476940155029</v>
       </c>
       <c r="E80" t="n">
-        <v>5.285408506536053</v>
+        <v>5.285408014051384</v>
       </c>
       <c r="F80" t="n">
         <v>7811800</v>
@@ -2032,16 +2032,16 @@
         <v>44530</v>
       </c>
       <c r="B81" t="n">
-        <v>4.825807571411133</v>
+        <v>4.825808525085449</v>
       </c>
       <c r="C81" t="n">
-        <v>5.126315867963532</v>
+        <v>5.126316881024188</v>
       </c>
       <c r="D81" t="n">
-        <v>4.790453703752186</v>
+        <v>4.790454650439884</v>
       </c>
       <c r="E81" t="n">
-        <v>5.073284645023764</v>
+        <v>5.073285647604409</v>
       </c>
       <c r="F81" t="n">
         <v>11282700</v>
@@ -2052,16 +2052,16 @@
         <v>44531</v>
       </c>
       <c r="B82" t="n">
-        <v>4.852322101593018</v>
+        <v>4.852322578430176</v>
       </c>
       <c r="C82" t="n">
-        <v>5.152830357281196</v>
+        <v>5.152830863649267</v>
       </c>
       <c r="D82" t="n">
-        <v>4.852322101593018</v>
+        <v>4.852322578430176</v>
       </c>
       <c r="E82" t="n">
-        <v>4.896514640882911</v>
+        <v>4.896515122062865</v>
       </c>
       <c r="F82" t="n">
         <v>12492100</v>
@@ -2072,16 +2072,16 @@
         <v>44532</v>
       </c>
       <c r="B83" t="n">
-        <v>5.029092311859131</v>
+        <v>5.029092788696289</v>
       </c>
       <c r="C83" t="n">
-        <v>5.029092311859131</v>
+        <v>5.029092788696289</v>
       </c>
       <c r="D83" t="n">
-        <v>4.746260960907972</v>
+        <v>4.746261410928263</v>
       </c>
       <c r="E83" t="n">
-        <v>4.905353780202955</v>
+        <v>4.905354245307752</v>
       </c>
       <c r="F83" t="n">
         <v>18379200</v>
@@ -2112,16 +2112,16 @@
         <v>44536</v>
       </c>
       <c r="B85" t="n">
-        <v>5.152831554412842</v>
+        <v>5.152830600738525</v>
       </c>
       <c r="C85" t="n">
-        <v>5.417986008851633</v>
+        <v>5.417985006103135</v>
       </c>
       <c r="D85" t="n">
-        <v>5.152831554412842</v>
+        <v>5.152830600738525</v>
       </c>
       <c r="E85" t="n">
-        <v>5.373793459294705</v>
+        <v>5.373792464725264</v>
       </c>
       <c r="F85" t="n">
         <v>5884400</v>
@@ -2152,16 +2152,16 @@
         <v>44538</v>
       </c>
       <c r="B87" t="n">
-        <v>5.285408020019531</v>
+        <v>5.285407543182373</v>
       </c>
       <c r="C87" t="n">
-        <v>5.33843881897542</v>
+        <v>5.338438337353947</v>
       </c>
       <c r="D87" t="n">
-        <v>5.126315623151864</v>
+        <v>5.12631516066765</v>
       </c>
       <c r="E87" t="n">
-        <v>5.223538543845331</v>
+        <v>5.223538072589892</v>
       </c>
       <c r="F87" t="n">
         <v>9204000</v>
@@ -2232,16 +2232,16 @@
         <v>44544</v>
       </c>
       <c r="B91" t="n">
-        <v>5.453338623046875</v>
+        <v>5.453339099884033</v>
       </c>
       <c r="C91" t="n">
-        <v>5.603592751168627</v>
+        <v>5.60359324114393</v>
       </c>
       <c r="D91" t="n">
-        <v>5.426823015133682</v>
+        <v>5.426823489652329</v>
       </c>
       <c r="E91" t="n">
-        <v>5.497530740967144</v>
+        <v>5.497531221668439</v>
       </c>
       <c r="F91" t="n">
         <v>6640900</v>
@@ -2252,16 +2252,16 @@
         <v>44545</v>
       </c>
       <c r="B92" t="n">
-        <v>5.479854583740234</v>
+        <v>5.479854106903076</v>
       </c>
       <c r="C92" t="n">
-        <v>5.524047129355619</v>
+        <v>5.524046648672985</v>
       </c>
       <c r="D92" t="n">
-        <v>5.329600855840895</v>
+        <v>5.329600392078274</v>
       </c>
       <c r="E92" t="n">
-        <v>5.479854583740234</v>
+        <v>5.479854106903076</v>
       </c>
       <c r="F92" t="n">
         <v>4791400</v>
@@ -2272,16 +2272,16 @@
         <v>44546</v>
       </c>
       <c r="B93" t="n">
-        <v>5.400308609008789</v>
+        <v>5.400308132171631</v>
       </c>
       <c r="C93" t="n">
-        <v>5.550562758842054</v>
+        <v>5.550562268737735</v>
       </c>
       <c r="D93" t="n">
-        <v>5.347277806970816</v>
+        <v>5.347277334816178</v>
       </c>
       <c r="E93" t="n">
-        <v>5.515208469365389</v>
+        <v>5.515207982382787</v>
       </c>
       <c r="F93" t="n">
         <v>9238300</v>
@@ -2292,16 +2292,16 @@
         <v>44547</v>
       </c>
       <c r="B94" t="n">
-        <v>5.241215229034424</v>
+        <v>5.241215705871582</v>
       </c>
       <c r="C94" t="n">
-        <v>5.347277243383087</v>
+        <v>5.347277729869593</v>
       </c>
       <c r="D94" t="n">
-        <v>5.241215229034424</v>
+        <v>5.241215705871582</v>
       </c>
       <c r="E94" t="n">
-        <v>5.320761634433095</v>
+        <v>5.320762118507254</v>
       </c>
       <c r="F94" t="n">
         <v>50153800</v>
@@ -2332,16 +2332,16 @@
         <v>44551</v>
       </c>
       <c r="B96" t="n">
-        <v>5.082123279571533</v>
+        <v>5.082122325897217</v>
       </c>
       <c r="C96" t="n">
-        <v>5.223538749008224</v>
+        <v>5.223537768796909</v>
       </c>
       <c r="D96" t="n">
-        <v>5.020253800967309</v>
+        <v>5.020252858902969</v>
       </c>
       <c r="E96" t="n">
-        <v>5.170507947969465</v>
+        <v>5.170506977709524</v>
       </c>
       <c r="F96" t="n">
         <v>5049800</v>
@@ -2372,16 +2372,16 @@
         <v>44553</v>
       </c>
       <c r="B98" t="n">
-        <v>5.055607795715332</v>
+        <v>5.055607318878174</v>
       </c>
       <c r="C98" t="n">
-        <v>5.073284729840333</v>
+        <v>5.073284251335914</v>
       </c>
       <c r="D98" t="n">
-        <v>4.967223125090324</v>
+        <v>4.967222656589472</v>
       </c>
       <c r="E98" t="n">
-        <v>4.993738737003503</v>
+        <v>4.993738266001739</v>
       </c>
       <c r="F98" t="n">
         <v>3174500</v>
@@ -2432,16 +2432,16 @@
         <v>44559</v>
       </c>
       <c r="B101" t="n">
-        <v>5.311923503875732</v>
+        <v>5.311923980712891</v>
       </c>
       <c r="C101" t="n">
-        <v>5.38263123413509</v>
+        <v>5.382631717319493</v>
       </c>
       <c r="D101" t="n">
-        <v>5.214700164043457</v>
+        <v>5.214700632153136</v>
       </c>
       <c r="E101" t="n">
-        <v>5.320761759432494</v>
+        <v>5.320762237063039</v>
       </c>
       <c r="F101" t="n">
         <v>5394800</v>
@@ -2452,16 +2452,16 @@
         <v>44560</v>
       </c>
       <c r="B102" t="n">
-        <v>5.700816631317139</v>
+        <v>5.700815677642822</v>
       </c>
       <c r="C102" t="n">
-        <v>5.709655309272549</v>
+        <v>5.709654354119633</v>
       </c>
       <c r="D102" t="n">
-        <v>5.258892848379334</v>
+        <v>5.258891968633261</v>
       </c>
       <c r="E102" t="n">
-        <v>5.320762329713117</v>
+        <v>5.320761439617065</v>
       </c>
       <c r="F102" t="n">
         <v>23096200</v>
@@ -2472,16 +2472,16 @@
         <v>44564</v>
       </c>
       <c r="B103" t="n">
-        <v>5.54172420501709</v>
+        <v>5.541723251342773</v>
       </c>
       <c r="C103" t="n">
-        <v>5.745009161433563</v>
+        <v>5.745008172775975</v>
       </c>
       <c r="D103" t="n">
-        <v>5.5063703362013</v>
+        <v>5.506369388611025</v>
       </c>
       <c r="E103" t="n">
-        <v>5.691978358209878</v>
+        <v>5.691977378678351</v>
       </c>
       <c r="F103" t="n">
         <v>7451800</v>
@@ -2512,16 +2512,16 @@
         <v>44566</v>
       </c>
       <c r="B105" t="n">
-        <v>5.117477416992188</v>
+        <v>5.117476940155029</v>
       </c>
       <c r="C105" t="n">
-        <v>5.568239881786464</v>
+        <v>5.568239362948087</v>
       </c>
       <c r="D105" t="n">
-        <v>5.117477416992188</v>
+        <v>5.117476940155029</v>
       </c>
       <c r="E105" t="n">
-        <v>5.550562947174024</v>
+        <v>5.550562429982751</v>
       </c>
       <c r="F105" t="n">
         <v>7203400</v>
@@ -2532,16 +2532,16 @@
         <v>44567</v>
       </c>
       <c r="B106" t="n">
-        <v>4.932944774627686</v>
+        <v>4.932945251464844</v>
       </c>
       <c r="C106" t="n">
-        <v>5.190238625560705</v>
+        <v>5.190239127268864</v>
       </c>
       <c r="D106" t="n">
-        <v>4.870839201862625</v>
+        <v>4.870839672696422</v>
       </c>
       <c r="E106" t="n">
-        <v>5.145877864779607</v>
+        <v>5.145878362199686</v>
       </c>
       <c r="F106" t="n">
         <v>8427100</v>
@@ -2552,16 +2552,16 @@
         <v>44568</v>
       </c>
       <c r="B107" t="n">
-        <v>5.163622856140137</v>
+        <v>5.163623332977295</v>
       </c>
       <c r="C107" t="n">
-        <v>5.278961186075115</v>
+        <v>5.278961673563245</v>
       </c>
       <c r="D107" t="n">
-        <v>4.941817757177995</v>
+        <v>4.941818213532458</v>
       </c>
       <c r="E107" t="n">
-        <v>4.977306539167166</v>
+        <v>4.977306998798857</v>
       </c>
       <c r="F107" t="n">
         <v>10961100</v>
@@ -2572,16 +2572,16 @@
         <v>44571</v>
       </c>
       <c r="B108" t="n">
-        <v>5.057155132293701</v>
+        <v>5.057156085968018</v>
       </c>
       <c r="C108" t="n">
-        <v>5.128133105930655</v>
+        <v>5.128134072989941</v>
       </c>
       <c r="D108" t="n">
-        <v>4.906328048846553</v>
+        <v>4.906328974078017</v>
       </c>
       <c r="E108" t="n">
-        <v>5.057155132293701</v>
+        <v>5.057156085968018</v>
       </c>
       <c r="F108" t="n">
         <v>11253600</v>
@@ -2592,16 +2592,16 @@
         <v>44572</v>
       </c>
       <c r="B109" t="n">
-        <v>5.23460054397583</v>
+        <v>5.234600067138672</v>
       </c>
       <c r="C109" t="n">
-        <v>5.23460054397583</v>
+        <v>5.234600067138672</v>
       </c>
       <c r="D109" t="n">
-        <v>5.021667423942884</v>
+        <v>5.021666966502512</v>
       </c>
       <c r="E109" t="n">
-        <v>5.021667423942884</v>
+        <v>5.021666966502512</v>
       </c>
       <c r="F109" t="n">
         <v>5425200</v>
@@ -2652,16 +2652,16 @@
         <v>44575</v>
       </c>
       <c r="B112" t="n">
-        <v>5.491894721984863</v>
+        <v>5.491893768310547</v>
       </c>
       <c r="C112" t="n">
-        <v>5.500766706632305</v>
+        <v>5.500765751417357</v>
       </c>
       <c r="D112" t="n">
-        <v>5.332195190793751</v>
+        <v>5.332194264851456</v>
       </c>
       <c r="E112" t="n">
-        <v>5.420917152566591</v>
+        <v>5.420916211217618</v>
       </c>
       <c r="F112" t="n">
         <v>4745900</v>
@@ -2672,16 +2672,16 @@
         <v>44578</v>
       </c>
       <c r="B113" t="n">
-        <v>5.483021259307861</v>
+        <v>5.483022212982178</v>
       </c>
       <c r="C113" t="n">
-        <v>5.624976793890898</v>
+        <v>5.624977772255862</v>
       </c>
       <c r="D113" t="n">
-        <v>5.447532481427003</v>
+        <v>5.447533428928676</v>
       </c>
       <c r="E113" t="n">
-        <v>5.447532481427003</v>
+        <v>5.447533428928676</v>
       </c>
       <c r="F113" t="n">
         <v>3137800</v>
@@ -2692,16 +2692,16 @@
         <v>44579</v>
       </c>
       <c r="B114" t="n">
-        <v>5.483021259307861</v>
+        <v>5.483022212982178</v>
       </c>
       <c r="C114" t="n">
-        <v>5.536254426129148</v>
+        <v>5.53625538906243</v>
       </c>
       <c r="D114" t="n">
-        <v>5.376554925665286</v>
+        <v>5.376555860821671</v>
       </c>
       <c r="E114" t="n">
-        <v>5.474149276367449</v>
+        <v>5.47415022849864</v>
       </c>
       <c r="F114" t="n">
         <v>3854900</v>
@@ -2712,16 +2712,16 @@
         <v>44580</v>
       </c>
       <c r="B115" t="n">
-        <v>5.651593685150146</v>
+        <v>5.651593208312988</v>
       </c>
       <c r="C115" t="n">
-        <v>5.749188044821177</v>
+        <v>5.749187559749773</v>
       </c>
       <c r="D115" t="n">
-        <v>5.509638560581113</v>
+        <v>5.509638095721016</v>
       </c>
       <c r="E115" t="n">
-        <v>5.509638560581113</v>
+        <v>5.509638095721016</v>
       </c>
       <c r="F115" t="n">
         <v>12660500</v>
@@ -2732,16 +2732,16 @@
         <v>44581</v>
       </c>
       <c r="B116" t="n">
-        <v>5.713699340820312</v>
+        <v>5.713698387145996</v>
       </c>
       <c r="C116" t="n">
-        <v>5.837910076495201</v>
+        <v>5.837909102088854</v>
       </c>
       <c r="D116" t="n">
-        <v>5.633849370642346</v>
+        <v>5.633848430295799</v>
       </c>
       <c r="E116" t="n">
-        <v>5.651593761453044</v>
+        <v>5.651592818144779</v>
       </c>
       <c r="F116" t="n">
         <v>9343500</v>
@@ -2792,16 +2792,16 @@
         <v>44586</v>
       </c>
       <c r="B119" t="n">
-        <v>5.500766277313232</v>
+        <v>5.500765800476074</v>
       </c>
       <c r="C119" t="n">
-        <v>5.57174426425156</v>
+        <v>5.571743781261634</v>
       </c>
       <c r="D119" t="n">
-        <v>5.36768355657054</v>
+        <v>5.367683091269735</v>
       </c>
       <c r="E119" t="n">
-        <v>5.394299931495218</v>
+        <v>5.394299463887157</v>
       </c>
       <c r="F119" t="n">
         <v>8097000</v>
@@ -2812,16 +2812,16 @@
         <v>44587</v>
       </c>
       <c r="B120" t="n">
-        <v>5.518510818481445</v>
+        <v>5.518509864807129</v>
       </c>
       <c r="C120" t="n">
-        <v>5.678210764614708</v>
+        <v>5.678209783342052</v>
       </c>
       <c r="D120" t="n">
-        <v>5.491894442832344</v>
+        <v>5.491893493757702</v>
       </c>
       <c r="E120" t="n">
-        <v>5.598360791548077</v>
+        <v>5.59835982407459</v>
       </c>
       <c r="F120" t="n">
         <v>11610000</v>
@@ -2872,16 +2872,16 @@
         <v>44592</v>
       </c>
       <c r="B123" t="n">
-        <v>5.6959547996521</v>
+        <v>5.695954322814941</v>
       </c>
       <c r="C123" t="n">
-        <v>5.793549158064543</v>
+        <v>5.793548673057267</v>
       </c>
       <c r="D123" t="n">
-        <v>5.571744067256032</v>
+        <v>5.571743600817181</v>
       </c>
       <c r="E123" t="n">
-        <v>5.607232847940623</v>
+        <v>5.607232378530827</v>
       </c>
       <c r="F123" t="n">
         <v>7514700</v>
@@ -2892,16 +2892,16 @@
         <v>44593</v>
       </c>
       <c r="B124" t="n">
-        <v>5.678209781646729</v>
+        <v>5.678210258483887</v>
       </c>
       <c r="C124" t="n">
-        <v>5.79354851765205</v>
+        <v>5.793549004174971</v>
       </c>
       <c r="D124" t="n">
-        <v>5.536254251540337</v>
+        <v>5.536254716456543</v>
       </c>
       <c r="E124" t="n">
-        <v>5.76693172355098</v>
+        <v>5.766932207838711</v>
       </c>
       <c r="F124" t="n">
         <v>8050400</v>
@@ -2912,16 +2912,16 @@
         <v>44594</v>
       </c>
       <c r="B125" t="n">
-        <v>5.669337749481201</v>
+        <v>5.669338226318359</v>
       </c>
       <c r="C125" t="n">
-        <v>5.882270847141231</v>
+        <v>5.882271341887785</v>
       </c>
       <c r="D125" t="n">
-        <v>5.651593359931167</v>
+        <v>5.651593835275879</v>
       </c>
       <c r="E125" t="n">
-        <v>5.722570918131304</v>
+        <v>5.722571399445803</v>
       </c>
       <c r="F125" t="n">
         <v>8808600</v>
@@ -3012,16 +3012,16 @@
         <v>44601</v>
       </c>
       <c r="B130" t="n">
-        <v>5.633849620819092</v>
+        <v>5.633849143981934</v>
       </c>
       <c r="C130" t="n">
-        <v>5.740315970411027</v>
+        <v>5.740315484562782</v>
       </c>
       <c r="D130" t="n">
-        <v>5.589488853352285</v>
+        <v>5.58948838026973</v>
       </c>
       <c r="E130" t="n">
-        <v>5.616105229220436</v>
+        <v>5.616104753885126</v>
       </c>
       <c r="F130" t="n">
         <v>8867400</v>
@@ -3052,16 +3052,16 @@
         <v>44603</v>
       </c>
       <c r="B132" t="n">
-        <v>5.633849620819092</v>
+        <v>5.633849143981934</v>
       </c>
       <c r="C132" t="n">
-        <v>5.775805176668006</v>
+        <v>5.775804687816029</v>
       </c>
       <c r="D132" t="n">
-        <v>5.589488853352285</v>
+        <v>5.58948838026973</v>
       </c>
       <c r="E132" t="n">
-        <v>5.731443986141532</v>
+        <v>5.731443501044193</v>
       </c>
       <c r="F132" t="n">
         <v>8001300</v>
@@ -3072,16 +3072,16 @@
         <v>44606</v>
       </c>
       <c r="B133" t="n">
-        <v>5.6959547996521</v>
+        <v>5.695954322814941</v>
       </c>
       <c r="C133" t="n">
-        <v>5.766932361021281</v>
+        <v>5.766931878242232</v>
       </c>
       <c r="D133" t="n">
-        <v>5.642721628625214</v>
+        <v>5.642721156244472</v>
       </c>
       <c r="E133" t="n">
-        <v>5.642721628625214</v>
+        <v>5.642721156244472</v>
       </c>
       <c r="F133" t="n">
         <v>12680200</v>
@@ -3092,16 +3092,16 @@
         <v>44607</v>
       </c>
       <c r="B134" t="n">
-        <v>5.6959547996521</v>
+        <v>5.695954322814941</v>
       </c>
       <c r="C134" t="n">
-        <v>5.811293548406838</v>
+        <v>5.81129306191409</v>
       </c>
       <c r="D134" t="n">
-        <v>5.518510473169509</v>
+        <v>5.518510011187112</v>
       </c>
       <c r="E134" t="n">
-        <v>5.811293548406838</v>
+        <v>5.81129306191409</v>
       </c>
       <c r="F134" t="n">
         <v>17426200</v>
@@ -3132,16 +3132,16 @@
         <v>44609</v>
       </c>
       <c r="B136" t="n">
-        <v>5.580616474151611</v>
+        <v>5.580615997314453</v>
       </c>
       <c r="C136" t="n">
-        <v>5.740315999344462</v>
+        <v>5.740315508861739</v>
       </c>
       <c r="D136" t="n">
-        <v>5.509638907399233</v>
+        <v>5.509638436626771</v>
       </c>
       <c r="E136" t="n">
-        <v>5.73144401503025</v>
+        <v>5.731443525305595</v>
       </c>
       <c r="F136" t="n">
         <v>16171600</v>
@@ -3192,16 +3192,16 @@
         <v>44614</v>
       </c>
       <c r="B139" t="n">
-        <v>5.012794971466064</v>
+        <v>5.012794494628906</v>
       </c>
       <c r="C139" t="n">
-        <v>5.234600054955186</v>
+        <v>5.234599557019038</v>
       </c>
       <c r="D139" t="n">
-        <v>4.977306191952575</v>
+        <v>4.977305718491252</v>
       </c>
       <c r="E139" t="n">
-        <v>5.172494479276767</v>
+        <v>5.172493987248352</v>
       </c>
       <c r="F139" t="n">
         <v>7346000</v>
@@ -3212,16 +3212,16 @@
         <v>44615</v>
       </c>
       <c r="B140" t="n">
-        <v>5.021667003631592</v>
+        <v>5.021666526794434</v>
       </c>
       <c r="C140" t="n">
-        <v>5.101516969842998</v>
+        <v>5.10151648542361</v>
       </c>
       <c r="D140" t="n">
-        <v>4.968433833843864</v>
+        <v>4.968433362061512</v>
       </c>
       <c r="E140" t="n">
-        <v>5.057155783490078</v>
+        <v>5.057155303283048</v>
       </c>
       <c r="F140" t="n">
         <v>10772600</v>
@@ -3312,16 +3312,16 @@
         <v>44624</v>
       </c>
       <c r="B145" t="n">
-        <v>5.509638786315918</v>
+        <v>5.509637832641602</v>
       </c>
       <c r="C145" t="n">
-        <v>5.536255161733287</v>
+        <v>5.53625420345189</v>
       </c>
       <c r="D145" t="n">
-        <v>5.376555640050094</v>
+        <v>5.376554709411403</v>
       </c>
       <c r="E145" t="n">
-        <v>5.483021987838889</v>
+        <v>5.483021038771727</v>
       </c>
       <c r="F145" t="n">
         <v>9336900</v>
@@ -3332,16 +3332,16 @@
         <v>44627</v>
       </c>
       <c r="B146" t="n">
-        <v>5.483021259307861</v>
+        <v>5.483022212982178</v>
       </c>
       <c r="C146" t="n">
-        <v>5.58948801601004</v>
+        <v>5.58948898820236</v>
       </c>
       <c r="D146" t="n">
-        <v>5.403171720605732</v>
+        <v>5.403172660391636</v>
       </c>
       <c r="E146" t="n">
-        <v>5.491893665307877</v>
+        <v>5.491894620525391</v>
       </c>
       <c r="F146" t="n">
         <v>12429900</v>
@@ -3352,16 +3352,16 @@
         <v>44628</v>
       </c>
       <c r="B147" t="n">
-        <v>5.589488506317139</v>
+        <v>5.58948802947998</v>
       </c>
       <c r="C147" t="n">
-        <v>5.589488506317139</v>
+        <v>5.58948802947998</v>
       </c>
       <c r="D147" t="n">
-        <v>5.420916585066217</v>
+        <v>5.420916122609865</v>
       </c>
       <c r="E147" t="n">
-        <v>5.500766130772708</v>
+        <v>5.500765661504422</v>
       </c>
       <c r="F147" t="n">
         <v>5566500</v>
@@ -3372,16 +3372,16 @@
         <v>44629</v>
       </c>
       <c r="B148" t="n">
-        <v>5.6959547996521</v>
+        <v>5.695954322814941</v>
       </c>
       <c r="C148" t="n">
-        <v>5.704826783293429</v>
+        <v>5.704826305713552</v>
       </c>
       <c r="D148" t="n">
-        <v>5.553999676913737</v>
+        <v>5.553999211960359</v>
       </c>
       <c r="E148" t="n">
-        <v>5.589488457598327</v>
+        <v>5.589487989674004</v>
       </c>
       <c r="F148" t="n">
         <v>9079900</v>
@@ -3392,16 +3392,16 @@
         <v>44630</v>
       </c>
       <c r="B149" t="n">
-        <v>5.6959547996521</v>
+        <v>5.695954322814941</v>
       </c>
       <c r="C149" t="n">
-        <v>5.829037938749134</v>
+        <v>5.829037450770913</v>
       </c>
       <c r="D149" t="n">
-        <v>5.553999676913737</v>
+        <v>5.553999211960359</v>
       </c>
       <c r="E149" t="n">
-        <v>5.624977238282918</v>
+        <v>5.62497676738765</v>
       </c>
       <c r="F149" t="n">
         <v>15215200</v>
@@ -3432,16 +3432,16 @@
         <v>44634</v>
       </c>
       <c r="B151" t="n">
-        <v>5.589488506317139</v>
+        <v>5.58948802947998</v>
       </c>
       <c r="C151" t="n">
-        <v>5.722571223514505</v>
+        <v>5.72257073532411</v>
       </c>
       <c r="D151" t="n">
-        <v>5.518510521269666</v>
+        <v>5.518510050487613</v>
       </c>
       <c r="E151" t="n">
-        <v>5.607232896814097</v>
+        <v>5.607232418463171</v>
       </c>
       <c r="F151" t="n">
         <v>7706100</v>
@@ -3452,16 +3452,16 @@
         <v>44635</v>
       </c>
       <c r="B152" t="n">
-        <v>5.651593685150146</v>
+        <v>5.651593208312988</v>
       </c>
       <c r="C152" t="n">
-        <v>5.687082466292404</v>
+        <v>5.687081986460981</v>
       </c>
       <c r="D152" t="n">
-        <v>5.500766153765728</v>
+        <v>5.500765689654214</v>
       </c>
       <c r="E152" t="n">
-        <v>5.509638560581113</v>
+        <v>5.509638095721016</v>
       </c>
       <c r="F152" t="n">
         <v>5880900</v>
@@ -3472,16 +3472,16 @@
         <v>44636</v>
       </c>
       <c r="B153" t="n">
-        <v>5.624977111816406</v>
+        <v>5.62497615814209</v>
       </c>
       <c r="C153" t="n">
-        <v>5.766932231363189</v>
+        <v>5.766931253621405</v>
       </c>
       <c r="D153" t="n">
-        <v>5.518510349096693</v>
+        <v>5.518509413473048</v>
       </c>
       <c r="E153" t="n">
-        <v>5.713699061533146</v>
+        <v>5.713698092816662</v>
       </c>
       <c r="F153" t="n">
         <v>10739100</v>
@@ -3492,16 +3492,16 @@
         <v>44637</v>
       </c>
       <c r="B154" t="n">
-        <v>5.891143321990967</v>
+        <v>5.891142845153809</v>
       </c>
       <c r="C154" t="n">
-        <v>5.926632104052506</v>
+        <v>5.926631624342837</v>
       </c>
       <c r="D154" t="n">
-        <v>5.536255078315924</v>
+        <v>5.536254630203903</v>
       </c>
       <c r="E154" t="n">
-        <v>5.607233065498654</v>
+        <v>5.607232611641579</v>
       </c>
       <c r="F154" t="n">
         <v>10001800</v>
@@ -3512,16 +3512,16 @@
         <v>44638</v>
       </c>
       <c r="B155" t="n">
-        <v>6.201670169830322</v>
+        <v>6.20167064666748</v>
       </c>
       <c r="C155" t="n">
-        <v>6.201670169830322</v>
+        <v>6.20167064666748</v>
       </c>
       <c r="D155" t="n">
-        <v>5.891143125613262</v>
+        <v>5.891143578574458</v>
       </c>
       <c r="E155" t="n">
-        <v>5.891143125613262</v>
+        <v>5.891143578574458</v>
       </c>
       <c r="F155" t="n">
         <v>17710700</v>
@@ -3592,16 +3592,16 @@
         <v>44644</v>
       </c>
       <c r="B159" t="n">
-        <v>6.343625068664551</v>
+        <v>6.343626022338867</v>
       </c>
       <c r="C159" t="n">
-        <v>6.432347011801619</v>
+        <v>6.432347978814025</v>
       </c>
       <c r="D159" t="n">
-        <v>6.254903125527482</v>
+        <v>6.25490406586371</v>
       </c>
       <c r="E159" t="n">
-        <v>6.299263885566218</v>
+        <v>6.299264832571459</v>
       </c>
       <c r="F159" t="n">
         <v>11578200</v>
@@ -3612,16 +3612,16 @@
         <v>44645</v>
       </c>
       <c r="B160" t="n">
-        <v>6.450092315673828</v>
+        <v>6.45009183883667</v>
       </c>
       <c r="C160" t="n">
-        <v>6.512197896212132</v>
+        <v>6.512197414783683</v>
       </c>
       <c r="D160" t="n">
-        <v>6.237159621930483</v>
+        <v>6.237159160834839</v>
       </c>
       <c r="E160" t="n">
-        <v>6.343625968802155</v>
+        <v>6.343625499835754</v>
       </c>
       <c r="F160" t="n">
         <v>15324200</v>
@@ -3632,16 +3632,16 @@
         <v>44648</v>
       </c>
       <c r="B161" t="n">
-        <v>6.538814544677734</v>
+        <v>6.538814067840576</v>
       </c>
       <c r="C161" t="n">
-        <v>6.592047720338352</v>
+        <v>6.592047239619212</v>
       </c>
       <c r="D161" t="n">
-        <v>6.352498218335738</v>
+        <v>6.35249775508553</v>
       </c>
       <c r="E161" t="n">
-        <v>6.4323481933565</v>
+        <v>6.432347724283304</v>
       </c>
       <c r="F161" t="n">
         <v>10802600</v>
@@ -3672,16 +3672,16 @@
         <v>44650</v>
       </c>
       <c r="B163" t="n">
-        <v>6.50332498550415</v>
+        <v>6.503325462341309</v>
       </c>
       <c r="C163" t="n">
-        <v>6.61866373054667</v>
+        <v>6.618664215840703</v>
       </c>
       <c r="D163" t="n">
-        <v>6.450091816190593</v>
+        <v>6.450092289124586</v>
       </c>
       <c r="E163" t="n">
-        <v>6.547686171461927</v>
+        <v>6.547686651551738</v>
       </c>
       <c r="F163" t="n">
         <v>10697600</v>
@@ -3712,16 +3712,16 @@
         <v>44652</v>
       </c>
       <c r="B165" t="n">
-        <v>6.139564514160156</v>
+        <v>6.139564990997314</v>
       </c>
       <c r="C165" t="n">
-        <v>6.299264015090594</v>
+        <v>6.299264504331019</v>
       </c>
       <c r="D165" t="n">
-        <v>5.926631423193302</v>
+        <v>5.926631883492739</v>
       </c>
       <c r="E165" t="n">
-        <v>6.254903254139719</v>
+        <v>6.254903739934808</v>
       </c>
       <c r="F165" t="n">
         <v>18919700</v>
@@ -3732,16 +3732,16 @@
         <v>44655</v>
       </c>
       <c r="B166" t="n">
-        <v>6.21054220199585</v>
+        <v>6.210542678833008</v>
       </c>
       <c r="C166" t="n">
-        <v>6.237158997579204</v>
+        <v>6.237159476459965</v>
       </c>
       <c r="D166" t="n">
-        <v>6.050842697674559</v>
+        <v>6.050843162250203</v>
       </c>
       <c r="E166" t="n">
-        <v>6.157309033888753</v>
+        <v>6.15730950663874</v>
       </c>
       <c r="F166" t="n">
         <v>13343800</v>
@@ -3772,16 +3772,16 @@
         <v>44657</v>
       </c>
       <c r="B168" t="n">
-        <v>6.350711822509766</v>
+        <v>6.350711345672607</v>
       </c>
       <c r="C168" t="n">
-        <v>6.395246712983208</v>
+        <v>6.39524623280219</v>
       </c>
       <c r="D168" t="n">
-        <v>6.136942904188415</v>
+        <v>6.136942443401892</v>
       </c>
       <c r="E168" t="n">
-        <v>6.243827575709211</v>
+        <v>6.243827106897355</v>
       </c>
       <c r="F168" t="n">
         <v>10002000</v>
@@ -3792,16 +3792,16 @@
         <v>44658</v>
       </c>
       <c r="B169" t="n">
-        <v>6.261641502380371</v>
+        <v>6.261641025543213</v>
       </c>
       <c r="C169" t="n">
-        <v>6.395246596078652</v>
+        <v>6.395246109067186</v>
       </c>
       <c r="D169" t="n">
-        <v>6.208198955236777</v>
+        <v>6.208198482469381</v>
       </c>
       <c r="E169" t="n">
-        <v>6.323990432847507</v>
+        <v>6.323989951262346</v>
       </c>
       <c r="F169" t="n">
         <v>10216600</v>
@@ -3812,16 +3812,16 @@
         <v>44659</v>
       </c>
       <c r="B170" t="n">
-        <v>6.190385341644287</v>
+        <v>6.190384387969971</v>
       </c>
       <c r="C170" t="n">
-        <v>6.323990869283284</v>
+        <v>6.323989895026054</v>
       </c>
       <c r="D170" t="n">
-        <v>6.136943215532741</v>
+        <v>6.136942270091576</v>
       </c>
       <c r="E170" t="n">
-        <v>6.234920659097374</v>
+        <v>6.234919698562065</v>
       </c>
       <c r="F170" t="n">
         <v>10722400</v>
@@ -3852,16 +3852,16 @@
         <v>44663</v>
       </c>
       <c r="B172" t="n">
-        <v>6.217106342315674</v>
+        <v>6.217106819152832</v>
       </c>
       <c r="C172" t="n">
-        <v>6.359618672315267</v>
+        <v>6.359619160082779</v>
       </c>
       <c r="D172" t="n">
-        <v>6.145850177315878</v>
+        <v>6.145850648687858</v>
       </c>
       <c r="E172" t="n">
-        <v>6.190385068080627</v>
+        <v>6.190385542868328</v>
       </c>
       <c r="F172" t="n">
         <v>15598900</v>
@@ -3892,16 +3892,16 @@
         <v>44665</v>
       </c>
       <c r="B174" t="n">
-        <v>6.323989868164062</v>
+        <v>6.323990345001221</v>
       </c>
       <c r="C174" t="n">
-        <v>6.350711139349857</v>
+        <v>6.350711618201833</v>
       </c>
       <c r="D174" t="n">
-        <v>6.226012440109747</v>
+        <v>6.226012909559278</v>
       </c>
       <c r="E174" t="n">
-        <v>6.297269021698465</v>
+        <v>6.297269496520836</v>
       </c>
       <c r="F174" t="n">
         <v>4947000</v>
@@ -3912,16 +3912,16 @@
         <v>44669</v>
       </c>
       <c r="B175" t="n">
-        <v>6.350711822509766</v>
+        <v>6.350711345672607</v>
       </c>
       <c r="C175" t="n">
-        <v>6.395246712983208</v>
+        <v>6.39524623280219</v>
       </c>
       <c r="D175" t="n">
-        <v>6.190385027588691</v>
+        <v>6.190384562789519</v>
       </c>
       <c r="E175" t="n">
-        <v>6.315083740242914</v>
+        <v>6.315083266080856</v>
       </c>
       <c r="F175" t="n">
         <v>6987700</v>
@@ -3932,16 +3932,16 @@
         <v>44670</v>
       </c>
       <c r="B176" t="n">
-        <v>6.190385341644287</v>
+        <v>6.190384387969971</v>
       </c>
       <c r="C176" t="n">
-        <v>6.413061079469193</v>
+        <v>6.413060091490044</v>
       </c>
       <c r="D176" t="n">
-        <v>6.181478532985828</v>
+        <v>6.181477580683671</v>
       </c>
       <c r="E176" t="n">
-        <v>6.359618953357647</v>
+        <v>6.35961797361165</v>
       </c>
       <c r="F176" t="n">
         <v>12659600</v>
@@ -3952,16 +3952,16 @@
         <v>44671</v>
       </c>
       <c r="B177" t="n">
-        <v>6.208199024200439</v>
+        <v>6.208198547363281</v>
       </c>
       <c r="C177" t="n">
-        <v>6.279455612943373</v>
+        <v>6.279455130633163</v>
       </c>
       <c r="D177" t="n">
-        <v>6.110222011029355</v>
+        <v>6.11022154171758</v>
       </c>
       <c r="E177" t="n">
-        <v>6.190384983194765</v>
+        <v>6.190384507725862</v>
       </c>
       <c r="F177" t="n">
         <v>7897000</v>
@@ -3972,16 +3972,16 @@
         <v>44673</v>
       </c>
       <c r="B178" t="n">
-        <v>6.128036022186279</v>
+        <v>6.128035545349121</v>
       </c>
       <c r="C178" t="n">
-        <v>6.190384953042324</v>
+        <v>6.190384471353647</v>
       </c>
       <c r="D178" t="n">
-        <v>5.98552327011481</v>
+        <v>5.98552280436691</v>
       </c>
       <c r="E178" t="n">
-        <v>6.136942830285612</v>
+        <v>6.136942352755394</v>
       </c>
       <c r="F178" t="n">
         <v>9926800</v>
@@ -4012,16 +4012,16 @@
         <v>44677</v>
       </c>
       <c r="B180" t="n">
-        <v>6.252734184265137</v>
+        <v>6.252734661102295</v>
       </c>
       <c r="C180" t="n">
-        <v>6.332897579166045</v>
+        <v>6.33289806211651</v>
       </c>
       <c r="D180" t="n">
-        <v>6.119128667670365</v>
+        <v>6.11912913431869</v>
       </c>
       <c r="E180" t="n">
-        <v>6.24382737634294</v>
+        <v>6.243827852500861</v>
       </c>
       <c r="F180" t="n">
         <v>9190800</v>
@@ -4032,16 +4032,16 @@
         <v>44678</v>
       </c>
       <c r="B181" t="n">
-        <v>6.332897663116455</v>
+        <v>6.332898139953613</v>
       </c>
       <c r="C181" t="n">
-        <v>6.35961851195749</v>
+        <v>6.359618990806601</v>
       </c>
       <c r="D181" t="n">
-        <v>6.208198952790844</v>
+        <v>6.20819942023878</v>
       </c>
       <c r="E181" t="n">
-        <v>6.288362348754418</v>
+        <v>6.288362822238278</v>
       </c>
       <c r="F181" t="n">
         <v>11357200</v>
@@ -4172,16 +4172,16 @@
         <v>44687</v>
       </c>
       <c r="B188" t="n">
-        <v>4.95230770111084</v>
+        <v>4.952308654785156</v>
       </c>
       <c r="C188" t="n">
-        <v>5.068099171347654</v>
+        <v>5.068100147320131</v>
       </c>
       <c r="D188" t="n">
-        <v>4.863237502744139</v>
+        <v>4.863238439266056</v>
       </c>
       <c r="E188" t="n">
-        <v>4.97012174078418</v>
+        <v>4.970122697888977</v>
       </c>
       <c r="F188" t="n">
         <v>14479200</v>
@@ -4192,16 +4192,16 @@
         <v>44690</v>
       </c>
       <c r="B189" t="n">
-        <v>4.62274694442749</v>
+        <v>4.622747898101807</v>
       </c>
       <c r="C189" t="n">
-        <v>4.934492796422071</v>
+        <v>4.934493814409667</v>
       </c>
       <c r="D189" t="n">
-        <v>4.435699348286715</v>
+        <v>4.435700263373046</v>
       </c>
       <c r="E189" t="n">
-        <v>4.934492796422071</v>
+        <v>4.934493814409667</v>
       </c>
       <c r="F189" t="n">
         <v>21341300</v>
@@ -4212,16 +4212,16 @@
         <v>44691</v>
       </c>
       <c r="B190" t="n">
-        <v>4.631655216217041</v>
+        <v>4.631654739379883</v>
       </c>
       <c r="C190" t="n">
-        <v>4.7118186184255</v>
+        <v>4.711818133335377</v>
       </c>
       <c r="D190" t="n">
-        <v>4.569306280917366</v>
+        <v>4.569305810499142</v>
       </c>
       <c r="E190" t="n">
-        <v>4.65837649185995</v>
+        <v>4.658376012271789</v>
       </c>
       <c r="F190" t="n">
         <v>9825600</v>
@@ -4252,16 +4252,16 @@
         <v>44693</v>
       </c>
       <c r="B192" t="n">
-        <v>4.791982173919678</v>
+        <v>4.79198169708252</v>
       </c>
       <c r="C192" t="n">
-        <v>4.809796216678029</v>
+        <v>4.809795738068244</v>
       </c>
       <c r="D192" t="n">
-        <v>4.55149238432179</v>
+        <v>4.55149193141512</v>
       </c>
       <c r="E192" t="n">
-        <v>4.587120469838493</v>
+        <v>4.587120013386569</v>
       </c>
       <c r="F192" t="n">
         <v>13350100</v>
@@ -4312,16 +4312,16 @@
         <v>44698</v>
       </c>
       <c r="B195" t="n">
-        <v>5.005750179290771</v>
+        <v>5.005749702453613</v>
       </c>
       <c r="C195" t="n">
-        <v>5.183891013525891</v>
+        <v>5.183890519719414</v>
       </c>
       <c r="D195" t="n">
-        <v>4.881051892630355</v>
+        <v>4.881051427671691</v>
       </c>
       <c r="E195" t="n">
-        <v>4.952308056436308</v>
+        <v>4.952307584689932</v>
       </c>
       <c r="F195" t="n">
         <v>40878000</v>
@@ -4332,16 +4332,16 @@
         <v>44699</v>
       </c>
       <c r="B196" t="n">
-        <v>4.95230770111084</v>
+        <v>4.952308654785156</v>
       </c>
       <c r="C196" t="n">
-        <v>5.112634058170901</v>
+        <v>5.112635042719536</v>
       </c>
       <c r="D196" t="n">
-        <v>4.89886558209082</v>
+        <v>4.898866525473696</v>
       </c>
       <c r="E196" t="n">
-        <v>4.98793578045752</v>
+        <v>4.987936740992796</v>
       </c>
       <c r="F196" t="n">
         <v>17779600</v>
@@ -4352,16 +4352,16 @@
         <v>44700</v>
       </c>
       <c r="B197" t="n">
-        <v>5.050285816192627</v>
+        <v>5.050285339355469</v>
       </c>
       <c r="C197" t="n">
-        <v>5.183891344211743</v>
+        <v>5.183890854759837</v>
       </c>
       <c r="D197" t="n">
-        <v>4.898866246085646</v>
+        <v>4.898865783545199</v>
       </c>
       <c r="E197" t="n">
-        <v>4.987936456524968</v>
+        <v>4.987935985574703</v>
       </c>
       <c r="F197" t="n">
         <v>12233400</v>
@@ -4372,16 +4372,16 @@
         <v>44701</v>
       </c>
       <c r="B198" t="n">
-        <v>4.934493541717529</v>
+        <v>4.934494018554688</v>
       </c>
       <c r="C198" t="n">
-        <v>5.121541166109582</v>
+        <v>5.121541661021799</v>
       </c>
       <c r="D198" t="n">
-        <v>4.827609306270698</v>
+        <v>4.827609772779264</v>
       </c>
       <c r="E198" t="n">
-        <v>5.094819894887776</v>
+        <v>5.094820387217823</v>
       </c>
       <c r="F198" t="n">
         <v>10517400</v>
@@ -4392,16 +4392,16 @@
         <v>44704</v>
       </c>
       <c r="B199" t="n">
-        <v>5.023563861846924</v>
+        <v>5.023564338684082</v>
       </c>
       <c r="C199" t="n">
-        <v>5.103727252769655</v>
+        <v>5.10372773721593</v>
       </c>
       <c r="D199" t="n">
-        <v>4.881051544402253</v>
+        <v>4.881052007712129</v>
       </c>
       <c r="E199" t="n">
-        <v>4.979028975005568</v>
+        <v>4.979029447615471</v>
       </c>
       <c r="F199" t="n">
         <v>11444200</v>
@@ -4412,16 +4412,16 @@
         <v>44705</v>
       </c>
       <c r="B200" t="n">
-        <v>5.157169818878174</v>
+        <v>5.157169342041016</v>
       </c>
       <c r="C200" t="n">
-        <v>5.201705134300433</v>
+        <v>5.201704653345494</v>
       </c>
       <c r="D200" t="n">
-        <v>4.961215365404775</v>
+        <v>4.961214906685765</v>
       </c>
       <c r="E200" t="n">
-        <v>4.979029406629629</v>
+        <v>4.979028946263514</v>
       </c>
       <c r="F200" t="n">
         <v>9007600</v>
@@ -4452,16 +4452,16 @@
         <v>44707</v>
       </c>
       <c r="B202" t="n">
-        <v>5.504543781280518</v>
+        <v>5.504544258117676</v>
       </c>
       <c r="C202" t="n">
-        <v>5.647056534405616</v>
+        <v>5.647057023588098</v>
       </c>
       <c r="D202" t="n">
-        <v>5.281868055787807</v>
+        <v>5.281868513335436</v>
       </c>
       <c r="E202" t="n">
-        <v>5.281868055787807</v>
+        <v>5.281868513335436</v>
       </c>
       <c r="F202" t="n">
         <v>14781100</v>
@@ -4472,16 +4472,16 @@
         <v>44708</v>
       </c>
       <c r="B203" t="n">
-        <v>5.406566143035889</v>
+        <v>5.406566619873047</v>
       </c>
       <c r="C203" t="n">
-        <v>5.58470653295462</v>
+        <v>5.584707025503037</v>
       </c>
       <c r="D203" t="n">
-        <v>5.388752104044015</v>
+        <v>5.388752579310048</v>
       </c>
       <c r="E203" t="n">
-        <v>5.522357184122968</v>
+        <v>5.522357671172426</v>
       </c>
       <c r="F203" t="n">
         <v>11400800</v>
@@ -4492,16 +4492,16 @@
         <v>44711</v>
       </c>
       <c r="B204" t="n">
-        <v>5.602520942687988</v>
+        <v>5.602521419525146</v>
       </c>
       <c r="C204" t="n">
-        <v>5.67377710337079</v>
+        <v>5.673777586272644</v>
       </c>
       <c r="D204" t="n">
-        <v>5.317495875236564</v>
+        <v>5.317496327814903</v>
       </c>
       <c r="E204" t="n">
-        <v>5.460008621322386</v>
+        <v>5.460009086030153</v>
       </c>
       <c r="F204" t="n">
         <v>7527500</v>
@@ -4512,16 +4512,16 @@
         <v>44712</v>
       </c>
       <c r="B205" t="n">
-        <v>5.460009574890137</v>
+        <v>5.46000862121582</v>
       </c>
       <c r="C205" t="n">
-        <v>5.691592137554163</v>
+        <v>5.691591143430404</v>
       </c>
       <c r="D205" t="n">
-        <v>5.460009574890137</v>
+        <v>5.46000862121582</v>
       </c>
       <c r="E205" t="n">
-        <v>5.629243198427841</v>
+        <v>5.62924221519428</v>
       </c>
       <c r="F205" t="n">
         <v>13931800</v>
@@ -4532,16 +4532,16 @@
         <v>44713</v>
       </c>
       <c r="B206" t="n">
-        <v>5.513451099395752</v>
+        <v>5.513450622558594</v>
       </c>
       <c r="C206" t="n">
-        <v>5.549079182047723</v>
+        <v>5.54907870212923</v>
       </c>
       <c r="D206" t="n">
-        <v>5.406566851439836</v>
+        <v>5.406566383846685</v>
       </c>
       <c r="E206" t="n">
-        <v>5.495637058069765</v>
+        <v>5.495636582773276</v>
       </c>
       <c r="F206" t="n">
         <v>9091200</v>
@@ -4552,16 +4552,16 @@
         <v>44714</v>
       </c>
       <c r="B207" t="n">
-        <v>5.611428260803223</v>
+        <v>5.611427783966064</v>
       </c>
       <c r="C207" t="n">
-        <v>5.655963149549779</v>
+        <v>5.65596266892822</v>
       </c>
       <c r="D207" t="n">
-        <v>5.504543593426991</v>
+        <v>5.504543125672473</v>
       </c>
       <c r="E207" t="n">
-        <v>5.549078906893773</v>
+        <v>5.549078435354819</v>
       </c>
       <c r="F207" t="n">
         <v>14163200</v>
@@ -4572,16 +4572,16 @@
         <v>44715</v>
       </c>
       <c r="B208" t="n">
-        <v>5.513451099395752</v>
+        <v>5.513450622558594</v>
       </c>
       <c r="C208" t="n">
-        <v>5.602521306025682</v>
+        <v>5.602520821485185</v>
       </c>
       <c r="D208" t="n">
-        <v>5.451101742394677</v>
+        <v>5.451101270949875</v>
       </c>
       <c r="E208" t="n">
-        <v>5.575800456396826</v>
+        <v>5.575799974167312</v>
       </c>
       <c r="F208" t="n">
         <v>9326300</v>
@@ -4592,16 +4592,16 @@
         <v>44718</v>
       </c>
       <c r="B209" t="n">
-        <v>5.308589458465576</v>
+        <v>5.308588981628418</v>
       </c>
       <c r="C209" t="n">
-        <v>5.566893272323779</v>
+        <v>5.566892772284817</v>
       </c>
       <c r="D209" t="n">
-        <v>5.24624010091626</v>
+        <v>5.246239629679551</v>
       </c>
       <c r="E209" t="n">
-        <v>5.566893272323779</v>
+        <v>5.566892772284817</v>
       </c>
       <c r="F209" t="n">
         <v>9845400</v>
@@ -4612,16 +4612,16 @@
         <v>44719</v>
       </c>
       <c r="B210" t="n">
-        <v>5.023563861846924</v>
+        <v>5.023564338684082</v>
       </c>
       <c r="C210" t="n">
-        <v>5.299681689256077</v>
+        <v>5.299682192302366</v>
       </c>
       <c r="D210" t="n">
-        <v>4.987935782485756</v>
+        <v>4.987936255941094</v>
       </c>
       <c r="E210" t="n">
-        <v>5.281867649575493</v>
+        <v>5.281868150930872</v>
       </c>
       <c r="F210" t="n">
         <v>18881300</v>
@@ -4652,16 +4652,16 @@
         <v>44721</v>
       </c>
       <c r="B212" t="n">
-        <v>4.81870174407959</v>
+        <v>4.818702697753906</v>
       </c>
       <c r="C212" t="n">
-        <v>4.996842549003744</v>
+        <v>4.996843537934095</v>
       </c>
       <c r="D212" t="n">
-        <v>4.809794937429475</v>
+        <v>4.809795889341036</v>
       </c>
       <c r="E212" t="n">
-        <v>4.881051089511069</v>
+        <v>4.88105205552501</v>
       </c>
       <c r="F212" t="n">
         <v>8480000</v>
@@ -4712,16 +4712,16 @@
         <v>44726</v>
       </c>
       <c r="B215" t="n">
-        <v>4.462421417236328</v>
+        <v>4.462421894073486</v>
       </c>
       <c r="C215" t="n">
-        <v>4.640561814748269</v>
+        <v>4.640562310620824</v>
       </c>
       <c r="D215" t="n">
-        <v>4.453514185000626</v>
+        <v>4.453514660885992</v>
       </c>
       <c r="E215" t="n">
-        <v>4.587119695494687</v>
+        <v>4.587120185656623</v>
       </c>
       <c r="F215" t="n">
         <v>9819800</v>
@@ -4732,16 +4732,16 @@
         <v>44727</v>
       </c>
       <c r="B216" t="n">
-        <v>4.560398578643799</v>
+        <v>4.560399055480957</v>
       </c>
       <c r="C216" t="n">
-        <v>4.649468780429767</v>
+        <v>4.649469266580143</v>
       </c>
       <c r="D216" t="n">
-        <v>4.48023560939654</v>
+        <v>4.480236077851825</v>
       </c>
       <c r="E216" t="n">
-        <v>4.542584538286605</v>
+        <v>4.54258501326112</v>
       </c>
       <c r="F216" t="n">
         <v>10830000</v>
@@ -4752,16 +4752,16 @@
         <v>44729</v>
       </c>
       <c r="B217" t="n">
-        <v>4.524770736694336</v>
+        <v>4.524771213531494</v>
       </c>
       <c r="C217" t="n">
-        <v>4.524770736694336</v>
+        <v>4.524771213531494</v>
       </c>
       <c r="D217" t="n">
-        <v>4.311002241127791</v>
+        <v>4.311002695437231</v>
       </c>
       <c r="E217" t="n">
-        <v>4.506956695397124</v>
+        <v>4.506957170356972</v>
       </c>
       <c r="F217" t="n">
         <v>10891400</v>
@@ -4772,16 +4772,16 @@
         <v>44732</v>
       </c>
       <c r="B218" t="n">
-        <v>4.524770736694336</v>
+        <v>4.524771213531494</v>
       </c>
       <c r="C218" t="n">
-        <v>4.64946902577482</v>
+        <v>4.649469515753148</v>
       </c>
       <c r="D218" t="n">
-        <v>4.453514571505488</v>
+        <v>4.453515040833406</v>
       </c>
       <c r="E218" t="n">
-        <v>4.524770736694336</v>
+        <v>4.524771213531494</v>
       </c>
       <c r="F218" t="n">
         <v>7841400</v>
@@ -4812,16 +4812,16 @@
         <v>44734</v>
       </c>
       <c r="B220" t="n">
-        <v>4.444607257843018</v>
+        <v>4.444606781005859</v>
       </c>
       <c r="C220" t="n">
-        <v>4.533677887433011</v>
+        <v>4.53367740103996</v>
       </c>
       <c r="D220" t="n">
-        <v>4.40007236776826</v>
+        <v>4.400071895709002</v>
       </c>
       <c r="E220" t="n">
-        <v>4.480235764511158</v>
+        <v>4.480235283851616</v>
       </c>
       <c r="F220" t="n">
         <v>8433900</v>
@@ -4832,16 +4832,16 @@
         <v>44735</v>
       </c>
       <c r="B221" t="n">
-        <v>4.26646614074707</v>
+        <v>4.266467094421387</v>
       </c>
       <c r="C221" t="n">
-        <v>4.515863097753988</v>
+        <v>4.515864107175489</v>
       </c>
       <c r="D221" t="n">
-        <v>4.26646614074707</v>
+        <v>4.266467094421387</v>
       </c>
       <c r="E221" t="n">
-        <v>4.471327790342699</v>
+        <v>4.471328789809315</v>
       </c>
       <c r="F221" t="n">
         <v>8059200</v>
@@ -4892,16 +4892,16 @@
         <v>44740</v>
       </c>
       <c r="B224" t="n">
-        <v>4.293188571929932</v>
+        <v>4.293187618255615</v>
       </c>
       <c r="C224" t="n">
-        <v>4.471329000341845</v>
+        <v>4.471328007096019</v>
       </c>
       <c r="D224" t="n">
-        <v>4.293188571929932</v>
+        <v>4.293187618255615</v>
       </c>
       <c r="E224" t="n">
-        <v>4.319909423831577</v>
+        <v>4.319908464221581</v>
       </c>
       <c r="F224" t="n">
         <v>8975600</v>
@@ -4932,16 +4932,16 @@
         <v>44742</v>
       </c>
       <c r="B226" t="n">
-        <v>4.088326930999756</v>
+        <v>4.088326454162598</v>
       </c>
       <c r="C226" t="n">
-        <v>4.239746509884235</v>
+        <v>4.239746015386434</v>
       </c>
       <c r="D226" t="n">
-        <v>4.052698844758736</v>
+        <v>4.052698372077018</v>
       </c>
       <c r="E226" t="n">
-        <v>4.239746509884235</v>
+        <v>4.239746015386434</v>
       </c>
       <c r="F226" t="n">
         <v>6721700</v>
@@ -4952,16 +4952,16 @@
         <v>44743</v>
       </c>
       <c r="B227" t="n">
-        <v>4.025976657867432</v>
+        <v>4.02597713470459</v>
       </c>
       <c r="C227" t="n">
-        <v>4.186303009719074</v>
+        <v>4.186303505545305</v>
       </c>
       <c r="D227" t="n">
-        <v>4.025976657867432</v>
+        <v>4.02597713470459</v>
       </c>
       <c r="E227" t="n">
-        <v>4.025976657867432</v>
+        <v>4.02597713470459</v>
       </c>
       <c r="F227" t="n">
         <v>12849200</v>
@@ -4992,16 +4992,16 @@
         <v>44747</v>
       </c>
       <c r="B229" t="n">
-        <v>4.034884452819824</v>
+        <v>4.034883499145508</v>
       </c>
       <c r="C229" t="n">
-        <v>4.061605302830409</v>
+        <v>4.061604342840425</v>
       </c>
       <c r="D229" t="n">
-        <v>3.901278928606141</v>
+        <v>3.901278006510463</v>
       </c>
       <c r="E229" t="n">
-        <v>4.061605302830409</v>
+        <v>4.061604342840425</v>
       </c>
       <c r="F229" t="n">
         <v>9503300</v>
@@ -5012,16 +5012,16 @@
         <v>44748</v>
       </c>
       <c r="B230" t="n">
-        <v>3.910186052322388</v>
+        <v>3.910185575485229</v>
       </c>
       <c r="C230" t="n">
-        <v>4.052698821177525</v>
+        <v>4.0526983269613</v>
       </c>
       <c r="D230" t="n">
-        <v>3.785487751204394</v>
+        <v>3.785487289573874</v>
       </c>
       <c r="E230" t="n">
-        <v>4.034884778160668</v>
+        <v>4.034884286116821</v>
       </c>
       <c r="F230" t="n">
         <v>11922900</v>
@@ -5072,16 +5072,16 @@
         <v>44753</v>
       </c>
       <c r="B233" t="n">
-        <v>3.705323696136475</v>
+        <v>3.705324172973633</v>
       </c>
       <c r="C233" t="n">
-        <v>3.901278559713046</v>
+        <v>3.901279061767585</v>
       </c>
       <c r="D233" t="n">
-        <v>3.678602848652532</v>
+        <v>3.678603322050991</v>
       </c>
       <c r="E233" t="n">
-        <v>3.892371327404923</v>
+        <v>3.892371828313193</v>
       </c>
       <c r="F233" t="n">
         <v>13261200</v>
@@ -5092,16 +5092,16 @@
         <v>44754</v>
       </c>
       <c r="B234" t="n">
-        <v>3.580625534057617</v>
+        <v>3.580625772476196</v>
       </c>
       <c r="C234" t="n">
-        <v>3.705323817411202</v>
+        <v>3.705324064132908</v>
       </c>
       <c r="D234" t="n">
-        <v>3.580625534057617</v>
+        <v>3.580625772476196</v>
       </c>
       <c r="E234" t="n">
-        <v>3.696417009531774</v>
+        <v>3.696417255660414</v>
       </c>
       <c r="F234" t="n">
         <v>14771600</v>
@@ -5112,16 +5112,16 @@
         <v>44755</v>
       </c>
       <c r="B235" t="n">
-        <v>3.687510013580322</v>
+        <v>3.687509775161743</v>
       </c>
       <c r="C235" t="n">
-        <v>3.723138096824944</v>
+        <v>3.723137856102805</v>
       </c>
       <c r="D235" t="n">
-        <v>3.473741514112596</v>
+        <v>3.47374128951537</v>
       </c>
       <c r="E235" t="n">
-        <v>3.589532997017741</v>
+        <v>3.589532764933936</v>
       </c>
       <c r="F235" t="n">
         <v>14925600</v>
@@ -5132,16 +5132,16 @@
         <v>44756</v>
       </c>
       <c r="B236" t="n">
-        <v>3.821115493774414</v>
+        <v>3.821115255355835</v>
       </c>
       <c r="C236" t="n">
-        <v>3.856743576605671</v>
+        <v>3.856743335964077</v>
       </c>
       <c r="D236" t="n">
-        <v>3.651881887965819</v>
+        <v>3.651881660106575</v>
       </c>
       <c r="E236" t="n">
-        <v>3.687509970797076</v>
+        <v>3.687509740714817</v>
       </c>
       <c r="F236" t="n">
         <v>9774500</v>
@@ -5192,16 +5192,16 @@
         <v>44761</v>
       </c>
       <c r="B239" t="n">
-        <v>3.856743574142456</v>
+        <v>3.856743335723877</v>
       </c>
       <c r="C239" t="n">
-        <v>3.93690697282171</v>
+        <v>3.93690672944754</v>
       </c>
       <c r="D239" t="n">
-        <v>3.830022724396204</v>
+        <v>3.830022487629471</v>
       </c>
       <c r="E239" t="n">
-        <v>3.838929532738205</v>
+        <v>3.838929295420866</v>
       </c>
       <c r="F239" t="n">
         <v>5270100</v>
@@ -5212,16 +5212,16 @@
         <v>44762</v>
       </c>
       <c r="B240" t="n">
-        <v>3.999255657196045</v>
+        <v>3.999256134033203</v>
       </c>
       <c r="C240" t="n">
-        <v>4.025976930004314</v>
+        <v>4.025977410027488</v>
       </c>
       <c r="D240" t="n">
-        <v>3.803301213909561</v>
+        <v>3.803301667382781</v>
       </c>
       <c r="E240" t="n">
-        <v>3.830022486717829</v>
+        <v>3.830022943377066</v>
       </c>
       <c r="F240" t="n">
         <v>11021800</v>
@@ -5232,16 +5232,16 @@
         <v>44763</v>
       </c>
       <c r="B241" t="n">
-        <v>3.963628053665161</v>
+        <v>3.963627815246582</v>
       </c>
       <c r="C241" t="n">
-        <v>4.02597741457541</v>
+        <v>4.025977172406417</v>
       </c>
       <c r="D241" t="n">
-        <v>3.936907202360965</v>
+        <v>3.936906965549687</v>
       </c>
       <c r="E241" t="n">
-        <v>4.02597741457541</v>
+        <v>4.025977172406417</v>
       </c>
       <c r="F241" t="n">
         <v>6658500</v>
@@ -5252,16 +5252,16 @@
         <v>44764</v>
       </c>
       <c r="B242" t="n">
-        <v>3.740952491760254</v>
+        <v>3.740952253341675</v>
       </c>
       <c r="C242" t="n">
-        <v>3.999256332039304</v>
+        <v>3.999256077158491</v>
       </c>
       <c r="D242" t="n">
-        <v>3.740952491760254</v>
+        <v>3.740952253341675</v>
       </c>
       <c r="E242" t="n">
-        <v>3.999256332039304</v>
+        <v>3.999256077158491</v>
       </c>
       <c r="F242" t="n">
         <v>6536400</v>
@@ -5272,16 +5272,16 @@
         <v>44767</v>
       </c>
       <c r="B243" t="n">
-        <v>3.696417570114136</v>
+        <v>3.696417093276978</v>
       </c>
       <c r="C243" t="n">
-        <v>3.78548778601755</v>
+        <v>3.78548729769035</v>
       </c>
       <c r="D243" t="n">
-        <v>3.651882249802283</v>
+        <v>3.651881778710173</v>
       </c>
       <c r="E243" t="n">
-        <v>3.767673742836867</v>
+        <v>3.767673256807676</v>
       </c>
       <c r="F243" t="n">
         <v>10514300</v>
@@ -5312,16 +5312,16 @@
         <v>44769</v>
       </c>
       <c r="B245" t="n">
-        <v>3.999255657196045</v>
+        <v>3.999256134033203</v>
       </c>
       <c r="C245" t="n">
-        <v>3.999255657196045</v>
+        <v>3.999256134033203</v>
       </c>
       <c r="D245" t="n">
-        <v>3.723137820204979</v>
+        <v>3.723138264120199</v>
       </c>
       <c r="E245" t="n">
-        <v>3.74095186050375</v>
+        <v>3.740952306542965</v>
       </c>
       <c r="F245" t="n">
         <v>8689000</v>
@@ -5332,16 +5332,16 @@
         <v>44770</v>
       </c>
       <c r="B246" t="n">
-        <v>3.999255657196045</v>
+        <v>3.999256134033203</v>
       </c>
       <c r="C246" t="n">
-        <v>4.070512243111353</v>
+        <v>4.070512728444538</v>
       </c>
       <c r="D246" t="n">
-        <v>3.892371415403418</v>
+        <v>3.892371879496609</v>
       </c>
       <c r="E246" t="n">
-        <v>4.025976930004314</v>
+        <v>4.025977410027488</v>
       </c>
       <c r="F246" t="n">
         <v>3634200</v>
@@ -5352,16 +5352,16 @@
         <v>44771</v>
       </c>
       <c r="B247" t="n">
-        <v>3.92799973487854</v>
+        <v>3.927999973297119</v>
       </c>
       <c r="C247" t="n">
-        <v>4.088326532037827</v>
+        <v>4.088326780187793</v>
       </c>
       <c r="D247" t="n">
-        <v>3.919092926547607</v>
+        <v>3.919093164425567</v>
       </c>
       <c r="E247" t="n">
-        <v>4.025977174840299</v>
+        <v>4.025977419205834</v>
       </c>
       <c r="F247" t="n">
         <v>8694600</v>
@@ -5372,16 +5372,16 @@
         <v>44774</v>
       </c>
       <c r="B248" t="n">
-        <v>3.92799973487854</v>
+        <v>3.927999973297119</v>
       </c>
       <c r="C248" t="n">
-        <v>3.990349092076068</v>
+        <v>3.990349334279078</v>
       </c>
       <c r="D248" t="n">
-        <v>3.874557610732194</v>
+        <v>3.874557845906986</v>
       </c>
       <c r="E248" t="n">
-        <v>3.981441859024886</v>
+        <v>3.981442100687252</v>
       </c>
       <c r="F248" t="n">
         <v>7696400</v>
@@ -5412,16 +5412,16 @@
         <v>44776</v>
       </c>
       <c r="B250" t="n">
-        <v>4.284280776977539</v>
+        <v>4.284281253814697</v>
       </c>
       <c r="C250" t="n">
-        <v>4.373350979516736</v>
+        <v>4.37335146626734</v>
       </c>
       <c r="D250" t="n">
-        <v>4.123954412406984</v>
+        <v>4.123954871399942</v>
       </c>
       <c r="E250" t="n">
-        <v>4.123954412406984</v>
+        <v>4.123954871399942</v>
       </c>
       <c r="F250" t="n">
         <v>8750200</v>
@@ -5452,16 +5452,16 @@
         <v>44778</v>
       </c>
       <c r="B252" t="n">
-        <v>4.328816413879395</v>
+        <v>4.328815937042236</v>
       </c>
       <c r="C252" t="n">
-        <v>4.542584915937508</v>
+        <v>4.542584415552859</v>
       </c>
       <c r="D252" t="n">
-        <v>4.248653013247472</v>
+        <v>4.248652545240646</v>
       </c>
       <c r="E252" t="n">
-        <v>4.542584915937508</v>
+        <v>4.542584415552859</v>
       </c>
       <c r="F252" t="n">
         <v>11124100</v>
@@ -5472,16 +5472,16 @@
         <v>44781</v>
       </c>
       <c r="B253" t="n">
-        <v>4.408979415893555</v>
+        <v>4.408978939056396</v>
       </c>
       <c r="C253" t="n">
-        <v>4.50695685894371</v>
+        <v>4.506956371510157</v>
       </c>
       <c r="D253" t="n">
-        <v>4.355537290062633</v>
+        <v>4.355536819005313</v>
       </c>
       <c r="E253" t="n">
-        <v>4.391165373949914</v>
+        <v>4.391164899039369</v>
       </c>
       <c r="F253" t="n">
         <v>6283600</v>
@@ -5492,16 +5492,16 @@
         <v>44782</v>
       </c>
       <c r="B254" t="n">
-        <v>4.382258415222168</v>
+        <v>4.382258892059326</v>
       </c>
       <c r="C254" t="n">
-        <v>4.578212869889715</v>
+        <v>4.578213368048839</v>
       </c>
       <c r="D254" t="n">
-        <v>4.364444373888754</v>
+        <v>4.364444848787552</v>
       </c>
       <c r="E254" t="n">
-        <v>4.453514580555821</v>
+        <v>4.453515065146422</v>
       </c>
       <c r="F254" t="n">
         <v>9216300</v>
@@ -5532,16 +5532,16 @@
         <v>44784</v>
       </c>
       <c r="B256" t="n">
-        <v>4.346629619598389</v>
+        <v>4.346631050109863</v>
       </c>
       <c r="C256" t="n">
-        <v>4.685096774136335</v>
+        <v>4.685098316040128</v>
       </c>
       <c r="D256" t="n">
-        <v>4.311001542775466</v>
+        <v>4.311002961561448</v>
       </c>
       <c r="E256" t="n">
-        <v>4.613840195770312</v>
+        <v>4.613841714222979</v>
       </c>
       <c r="F256" t="n">
         <v>11482900</v>
@@ -5592,16 +5592,16 @@
         <v>44789</v>
       </c>
       <c r="B259" t="n">
-        <v>4.62274694442749</v>
+        <v>4.622747898101807</v>
       </c>
       <c r="C259" t="n">
-        <v>4.702910321265003</v>
+        <v>4.702911291477053</v>
       </c>
       <c r="D259" t="n">
-        <v>4.560397604140521</v>
+        <v>4.560398544952146</v>
       </c>
       <c r="E259" t="n">
-        <v>4.676189054079122</v>
+        <v>4.676190018778564</v>
       </c>
       <c r="F259" t="n">
         <v>5754000</v>
@@ -5652,16 +5652,16 @@
         <v>44792</v>
       </c>
       <c r="B262" t="n">
-        <v>4.31990909576416</v>
+        <v>4.319908618927002</v>
       </c>
       <c r="C262" t="n">
-        <v>4.533678018344458</v>
+        <v>4.533677517911209</v>
       </c>
       <c r="D262" t="n">
-        <v>4.22193165521818</v>
+        <v>4.221931189195899</v>
       </c>
       <c r="E262" t="n">
-        <v>4.524770785240164</v>
+        <v>4.524770285790107</v>
       </c>
       <c r="F262" t="n">
         <v>17743000</v>
@@ -5672,16 +5672,16 @@
         <v>44795</v>
       </c>
       <c r="B263" t="n">
-        <v>4.31990909576416</v>
+        <v>4.319908618927002</v>
       </c>
       <c r="C263" t="n">
-        <v>4.364444411845128</v>
+        <v>4.364443930092105</v>
       </c>
       <c r="D263" t="n">
-        <v>4.177396763857463</v>
+        <v>4.177396302751</v>
       </c>
       <c r="E263" t="n">
-        <v>4.302095054275823</v>
+        <v>4.302094579405002</v>
       </c>
       <c r="F263" t="n">
         <v>9829500</v>
@@ -5732,16 +5732,16 @@
         <v>44798</v>
       </c>
       <c r="B266" t="n">
-        <v>4.480236053466797</v>
+        <v>4.480235576629639</v>
       </c>
       <c r="C266" t="n">
-        <v>4.604934348326948</v>
+        <v>4.604933858217994</v>
       </c>
       <c r="D266" t="n">
-        <v>4.453514777922345</v>
+        <v>4.453514303929166</v>
       </c>
       <c r="E266" t="n">
-        <v>4.587120306204069</v>
+        <v>4.587119817991086</v>
       </c>
       <c r="F266" t="n">
         <v>4135100</v>
@@ -5752,16 +5752,16 @@
         <v>44799</v>
       </c>
       <c r="B267" t="n">
-        <v>4.31990909576416</v>
+        <v>4.319908618927002</v>
       </c>
       <c r="C267" t="n">
-        <v>4.524770785240164</v>
+        <v>4.524770285790107</v>
       </c>
       <c r="D267" t="n">
-        <v>4.29318824589178</v>
+        <v>4.293187772004104</v>
       </c>
       <c r="E267" t="n">
-        <v>4.489142702263489</v>
+        <v>4.489142206746107</v>
       </c>
       <c r="F267" t="n">
         <v>6692300</v>
@@ -5772,16 +5772,16 @@
         <v>44802</v>
       </c>
       <c r="B268" t="n">
-        <v>4.453514575958252</v>
+        <v>4.453514099121094</v>
       </c>
       <c r="C268" t="n">
-        <v>4.48023585029091</v>
+        <v>4.480235370592709</v>
       </c>
       <c r="D268" t="n">
-        <v>4.266466929790385</v>
+        <v>4.266466472980391</v>
       </c>
       <c r="E268" t="n">
-        <v>4.275374162808021</v>
+        <v>4.275373705044331</v>
       </c>
       <c r="F268" t="n">
         <v>7870400</v>
@@ -5792,16 +5792,16 @@
         <v>44803</v>
       </c>
       <c r="B269" t="n">
-        <v>4.364444255828857</v>
+        <v>4.364443778991699</v>
       </c>
       <c r="C269" t="n">
-        <v>4.480235733723964</v>
+        <v>4.480235244236013</v>
       </c>
       <c r="D269" t="n">
-        <v>4.337722982191434</v>
+        <v>4.337722508273708</v>
       </c>
       <c r="E269" t="n">
-        <v>4.471328500938078</v>
+        <v>4.471328012423286</v>
       </c>
       <c r="F269" t="n">
         <v>7827400</v>
@@ -5812,16 +5812,16 @@
         <v>44804</v>
       </c>
       <c r="B270" t="n">
-        <v>4.311001777648926</v>
+        <v>4.311002254486084</v>
       </c>
       <c r="C270" t="n">
-        <v>4.43570005332301</v>
+        <v>4.435700543952965</v>
       </c>
       <c r="D270" t="n">
-        <v>4.284280506215807</v>
+        <v>4.284280980097343</v>
       </c>
       <c r="E270" t="n">
-        <v>4.382257935176974</v>
+        <v>4.382258419895731</v>
       </c>
       <c r="F270" t="n">
         <v>8375100</v>
@@ -5852,16 +5852,16 @@
         <v>44806</v>
       </c>
       <c r="B272" t="n">
-        <v>4.097233772277832</v>
+        <v>4.097232818603516</v>
       </c>
       <c r="C272" t="n">
-        <v>4.355537611907676</v>
+        <v>4.35553659811042</v>
       </c>
       <c r="D272" t="n">
-        <v>4.097233772277832</v>
+        <v>4.097232818603516</v>
       </c>
       <c r="E272" t="n">
-        <v>4.319909525387717</v>
+        <v>4.319908519883274</v>
       </c>
       <c r="F272" t="n">
         <v>69570300</v>
@@ -5872,16 +5872,16 @@
         <v>44809</v>
       </c>
       <c r="B273" t="n">
-        <v>4.115046501159668</v>
+        <v>4.115046977996826</v>
       </c>
       <c r="C273" t="n">
-        <v>4.221930726579882</v>
+        <v>4.221931215802409</v>
       </c>
       <c r="D273" t="n">
-        <v>4.115046501159668</v>
+        <v>4.115046977996826</v>
       </c>
       <c r="E273" t="n">
-        <v>4.123953732304765</v>
+        <v>4.123954210174062</v>
       </c>
       <c r="F273" t="n">
         <v>7604300</v>
@@ -5892,16 +5892,16 @@
         <v>44810</v>
       </c>
       <c r="B274" t="n">
-        <v>3.954720973968506</v>
+        <v>3.954720497131348</v>
       </c>
       <c r="C274" t="n">
-        <v>4.177396701615019</v>
+        <v>4.177396197928922</v>
       </c>
       <c r="D274" t="n">
-        <v>3.945813740996928</v>
+        <v>3.945813265233752</v>
       </c>
       <c r="E274" t="n">
-        <v>4.141768619169197</v>
+        <v>4.141768119778925</v>
       </c>
       <c r="F274" t="n">
         <v>14609100</v>
@@ -5912,16 +5912,16 @@
         <v>44812</v>
       </c>
       <c r="B275" t="n">
-        <v>3.910186052322388</v>
+        <v>3.910185575485229</v>
       </c>
       <c r="C275" t="n">
-        <v>4.008163501275241</v>
+        <v>4.008163012489984</v>
       </c>
       <c r="D275" t="n">
-        <v>3.856743923271819</v>
+        <v>3.856743452951791</v>
       </c>
       <c r="E275" t="n">
-        <v>3.990349458258384</v>
+        <v>3.990348971645505</v>
       </c>
       <c r="F275" t="n">
         <v>9864000</v>
@@ -5932,16 +5932,16 @@
         <v>44813</v>
       </c>
       <c r="B276" t="n">
-        <v>3.910186052322388</v>
+        <v>3.910185575485229</v>
       </c>
       <c r="C276" t="n">
-        <v>4.043791587308953</v>
+        <v>4.043791094178943</v>
       </c>
       <c r="D276" t="n">
-        <v>3.883465200157247</v>
+        <v>3.883464726578628</v>
       </c>
       <c r="E276" t="n">
-        <v>3.9458141383561</v>
+        <v>3.945813657174188</v>
       </c>
       <c r="F276" t="n">
         <v>15548300</v>
@@ -5952,16 +5952,16 @@
         <v>44816</v>
       </c>
       <c r="B277" t="n">
-        <v>3.856743574142456</v>
+        <v>3.856743335723877</v>
       </c>
       <c r="C277" t="n">
-        <v>3.990349097034463</v>
+        <v>3.990348850356574</v>
       </c>
       <c r="D277" t="n">
-        <v>3.838929532738205</v>
+        <v>3.838929295420866</v>
       </c>
       <c r="E277" t="n">
-        <v>3.954721014225961</v>
+        <v>3.954720769750552</v>
       </c>
       <c r="F277" t="n">
         <v>15738600</v>
@@ -5972,16 +5972,16 @@
         <v>44817</v>
       </c>
       <c r="B278" t="n">
-        <v>3.696417570114136</v>
+        <v>3.696417093276978</v>
       </c>
       <c r="C278" t="n">
-        <v>3.88346523587145</v>
+        <v>3.883464734905179</v>
       </c>
       <c r="D278" t="n">
-        <v>3.678603526933453</v>
+        <v>3.678603052394303</v>
       </c>
       <c r="E278" t="n">
-        <v>3.874558001920963</v>
+        <v>3.874557502103723</v>
       </c>
       <c r="F278" t="n">
         <v>21443000</v>
@@ -5992,16 +5992,16 @@
         <v>44818</v>
       </c>
       <c r="B279" t="n">
-        <v>3.740952491760254</v>
+        <v>3.740952253341675</v>
       </c>
       <c r="C279" t="n">
-        <v>3.821115898991784</v>
+        <v>3.821115655464227</v>
       </c>
       <c r="D279" t="n">
-        <v>3.678603552553769</v>
+        <v>3.678603318108816</v>
       </c>
       <c r="E279" t="n">
-        <v>3.70532440515075</v>
+        <v>3.705324169002822</v>
       </c>
       <c r="F279" t="n">
         <v>13539100</v>
@@ -6032,16 +6032,16 @@
         <v>44820</v>
       </c>
       <c r="B281" t="n">
-        <v>3.821115493774414</v>
+        <v>3.821115255355835</v>
       </c>
       <c r="C281" t="n">
-        <v>3.892371659436928</v>
+        <v>3.892371416572319</v>
       </c>
       <c r="D281" t="n">
-        <v>3.660789121033758</v>
+        <v>3.660788892618747</v>
       </c>
       <c r="E281" t="n">
-        <v>3.696417203865015</v>
+        <v>3.696416973226988</v>
       </c>
       <c r="F281" t="n">
         <v>19813000</v>
@@ -6052,16 +6052,16 @@
         <v>44823</v>
       </c>
       <c r="B282" t="n">
-        <v>3.99034857749939</v>
+        <v>3.990349292755127</v>
       </c>
       <c r="C282" t="n">
-        <v>4.00816261658429</v>
+        <v>4.00816333503313</v>
       </c>
       <c r="D282" t="n">
-        <v>3.794394147565487</v>
+        <v>3.794394827697093</v>
       </c>
       <c r="E282" t="n">
-        <v>3.830022225735288</v>
+        <v>3.830022912253099</v>
       </c>
       <c r="F282" t="n">
         <v>8945000</v>
@@ -6072,16 +6072,16 @@
         <v>44824</v>
       </c>
       <c r="B283" t="n">
-        <v>3.963628053665161</v>
+        <v>3.963627815246582</v>
       </c>
       <c r="C283" t="n">
-        <v>4.132861669232745</v>
+        <v>4.132861420634493</v>
       </c>
       <c r="D283" t="n">
-        <v>3.919093159918075</v>
+        <v>3.919092924178341</v>
       </c>
       <c r="E283" t="n">
-        <v>3.990349329689632</v>
+        <v>3.990349089663725</v>
       </c>
       <c r="F283" t="n">
         <v>10696200</v>
@@ -6092,16 +6092,16 @@
         <v>44825</v>
       </c>
       <c r="B284" t="n">
-        <v>3.883464574813843</v>
+        <v>3.883464813232422</v>
       </c>
       <c r="C284" t="n">
-        <v>4.034884128434599</v>
+        <v>4.034884376149319</v>
       </c>
       <c r="D284" t="n">
-        <v>3.830022454368909</v>
+        <v>3.830022689506502</v>
       </c>
       <c r="E284" t="n">
-        <v>3.972534775555399</v>
+        <v>3.972535019442289</v>
       </c>
       <c r="F284" t="n">
         <v>18275700</v>
@@ -6132,16 +6132,16 @@
         <v>44827</v>
       </c>
       <c r="B286" t="n">
-        <v>3.910186052322388</v>
+        <v>3.910185575485229</v>
       </c>
       <c r="C286" t="n">
-        <v>3.990349458258384</v>
+        <v>3.990348971645505</v>
       </c>
       <c r="D286" t="n">
-        <v>3.847837114123534</v>
+        <v>3.847836644889669</v>
       </c>
       <c r="E286" t="n">
-        <v>3.963628181372956</v>
+        <v>3.963627698018668</v>
       </c>
       <c r="F286" t="n">
         <v>14173200</v>
@@ -6152,16 +6152,16 @@
         <v>44830</v>
       </c>
       <c r="B287" t="n">
-        <v>3.821115493774414</v>
+        <v>3.821115255355835</v>
       </c>
       <c r="C287" t="n">
-        <v>3.936906975336123</v>
+        <v>3.936906729692732</v>
       </c>
       <c r="D287" t="n">
-        <v>3.794394644011096</v>
+        <v>3.794394407259765</v>
       </c>
       <c r="E287" t="n">
-        <v>3.901278892504866</v>
+        <v>3.901278649084491</v>
       </c>
       <c r="F287" t="n">
         <v>9718800</v>
@@ -6172,16 +6172,16 @@
         <v>44831</v>
       </c>
       <c r="B288" t="n">
-        <v>3.732045412063599</v>
+        <v>3.73204517364502</v>
       </c>
       <c r="C288" t="n">
-        <v>3.91909306557115</v>
+        <v>3.919092815203188</v>
       </c>
       <c r="D288" t="n">
-        <v>3.732045412063599</v>
+        <v>3.73204517364502</v>
       </c>
       <c r="E288" t="n">
-        <v>3.838929664147838</v>
+        <v>3.838929418901048</v>
       </c>
       <c r="F288" t="n">
         <v>11052300</v>
@@ -6192,16 +6192,16 @@
         <v>44832</v>
       </c>
       <c r="B289" t="n">
-        <v>3.687510013580322</v>
+        <v>3.687509775161743</v>
       </c>
       <c r="C289" t="n">
-        <v>3.767673413240847</v>
+        <v>3.767673169639246</v>
       </c>
       <c r="D289" t="n">
-        <v>3.687510013580322</v>
+        <v>3.687509775161743</v>
       </c>
       <c r="E289" t="n">
-        <v>3.749859371618537</v>
+        <v>3.749859129168715</v>
       </c>
       <c r="F289" t="n">
         <v>11148900</v>
@@ -6212,16 +6212,16 @@
         <v>44833</v>
       </c>
       <c r="B290" t="n">
-        <v>3.696417570114136</v>
+        <v>3.696417093276978</v>
       </c>
       <c r="C290" t="n">
-        <v>3.714231613294819</v>
+        <v>3.714231134159652</v>
       </c>
       <c r="D290" t="n">
-        <v>3.616254163440918</v>
+        <v>3.616253696944824</v>
       </c>
       <c r="E290" t="n">
-        <v>3.660789483752771</v>
+        <v>3.660789011511628</v>
       </c>
       <c r="F290" t="n">
         <v>12380300</v>
@@ -6232,16 +6232,16 @@
         <v>44834</v>
       </c>
       <c r="B291" t="n">
-        <v>3.732045412063599</v>
+        <v>3.73204517364502</v>
       </c>
       <c r="C291" t="n">
-        <v>3.79439477147287</v>
+        <v>3.794394529071154</v>
       </c>
       <c r="D291" t="n">
-        <v>3.651882010640287</v>
+        <v>3.651881777342879</v>
       </c>
       <c r="E291" t="n">
-        <v>3.660789244007439</v>
+        <v>3.660789010141</v>
       </c>
       <c r="F291" t="n">
         <v>11827700</v>
@@ -6252,16 +6252,16 @@
         <v>44837</v>
       </c>
       <c r="B292" t="n">
-        <v>3.939894676208496</v>
+        <v>3.939894914627075</v>
       </c>
       <c r="C292" t="n">
-        <v>3.939894676208497</v>
+        <v>3.939894914627075</v>
       </c>
       <c r="D292" t="n">
-        <v>3.796299558626456</v>
+        <v>3.796299788355527</v>
       </c>
       <c r="E292" t="n">
-        <v>3.814248948324211</v>
+        <v>3.814249179139471</v>
       </c>
       <c r="F292" t="n">
         <v>14167700</v>
@@ -6292,16 +6292,16 @@
         <v>44839</v>
       </c>
       <c r="B294" t="n">
-        <v>3.975793600082397</v>
+        <v>3.975793361663818</v>
       </c>
       <c r="C294" t="n">
-        <v>3.975793600082397</v>
+        <v>3.975793361663818</v>
       </c>
       <c r="D294" t="n">
-        <v>3.868097257982235</v>
+        <v>3.868097026021941</v>
       </c>
       <c r="E294" t="n">
-        <v>3.921945429032316</v>
+        <v>3.92194519384288</v>
       </c>
       <c r="F294" t="n">
         <v>8368900</v>
@@ -6332,16 +6332,16 @@
         <v>44841</v>
       </c>
       <c r="B296" t="n">
-        <v>3.760401010513306</v>
+        <v>3.760400772094727</v>
       </c>
       <c r="C296" t="n">
-        <v>4.002718000310238</v>
+        <v>4.002717746528172</v>
       </c>
       <c r="D296" t="n">
-        <v>3.715527319535371</v>
+        <v>3.715527083961894</v>
       </c>
       <c r="E296" t="n">
-        <v>3.984768609508511</v>
+        <v>3.98476835686448</v>
       </c>
       <c r="F296" t="n">
         <v>16354500</v>
@@ -6372,16 +6372,16 @@
         <v>44845</v>
       </c>
       <c r="B298" t="n">
-        <v>3.903995513916016</v>
+        <v>3.903995990753174</v>
       </c>
       <c r="C298" t="n">
-        <v>3.948869197732875</v>
+        <v>3.948869680050941</v>
       </c>
       <c r="D298" t="n">
-        <v>3.634754694856352</v>
+        <v>3.63475513880822</v>
       </c>
       <c r="E298" t="n">
-        <v>3.661678562788736</v>
+        <v>3.661679010029107</v>
       </c>
       <c r="F298" t="n">
         <v>30833900</v>
@@ -6392,16 +6392,16 @@
         <v>44847</v>
       </c>
       <c r="B299" t="n">
-        <v>3.81424880027771</v>
+        <v>3.814249277114868</v>
       </c>
       <c r="C299" t="n">
-        <v>3.903995745283042</v>
+        <v>3.903996233339887</v>
       </c>
       <c r="D299" t="n">
-        <v>3.796299411276644</v>
+        <v>3.796299885869864</v>
       </c>
       <c r="E299" t="n">
-        <v>3.895021264756104</v>
+        <v>3.895021751691007</v>
       </c>
       <c r="F299" t="n">
         <v>15027200</v>
@@ -6412,16 +6412,16 @@
         <v>44848</v>
       </c>
       <c r="B300" t="n">
-        <v>3.688603401184082</v>
+        <v>3.688603639602661</v>
       </c>
       <c r="C300" t="n">
-        <v>3.832198525802385</v>
+        <v>3.832198773502456</v>
       </c>
       <c r="D300" t="n">
-        <v>3.679628491921824</v>
+        <v>3.679628729760296</v>
       </c>
       <c r="E300" t="n">
-        <v>3.823224044487355</v>
+        <v>3.823224291607347</v>
       </c>
       <c r="F300" t="n">
         <v>10535000</v>
@@ -6432,16 +6432,16 @@
         <v>44851</v>
       </c>
       <c r="B301" t="n">
-        <v>3.679628372192383</v>
+        <v>3.679628133773804</v>
       </c>
       <c r="C301" t="n">
-        <v>3.769375322158595</v>
+        <v>3.769375077924933</v>
       </c>
       <c r="D301" t="n">
-        <v>3.670653891169369</v>
+        <v>3.670653653332284</v>
       </c>
       <c r="E301" t="n">
-        <v>3.724502061149096</v>
+        <v>3.724501819822962</v>
       </c>
       <c r="F301" t="n">
         <v>8129100</v>
@@ -6472,16 +6472,16 @@
         <v>44853</v>
       </c>
       <c r="B303" t="n">
-        <v>3.733476161956787</v>
+        <v>3.733476638793945</v>
       </c>
       <c r="C303" t="n">
-        <v>3.769374938287358</v>
+        <v>3.769375419709485</v>
       </c>
       <c r="D303" t="n">
-        <v>3.670653517351873</v>
+        <v>3.670653986165363</v>
       </c>
       <c r="E303" t="n">
-        <v>3.715526773791502</v>
+        <v>3.715527248336175</v>
       </c>
       <c r="F303" t="n">
         <v>12625300</v>
@@ -6492,16 +6492,16 @@
         <v>44854</v>
       </c>
       <c r="B304" t="n">
-        <v>3.769375801086426</v>
+        <v>3.769375562667847</v>
       </c>
       <c r="C304" t="n">
-        <v>3.796300103470833</v>
+        <v>3.796299863349252</v>
       </c>
       <c r="D304" t="n">
-        <v>3.706553142101589</v>
+        <v>3.706552907656635</v>
       </c>
       <c r="E304" t="n">
-        <v>3.760401318923135</v>
+        <v>3.760401081072205</v>
       </c>
       <c r="F304" t="n">
         <v>13428400</v>
@@ -6532,16 +6532,16 @@
         <v>44858</v>
       </c>
       <c r="B306" t="n">
-        <v>3.706552743911743</v>
+        <v>3.706552505493164</v>
       </c>
       <c r="C306" t="n">
-        <v>3.778350305294026</v>
+        <v>3.778350062257174</v>
       </c>
       <c r="D306" t="n">
-        <v>3.697577834765347</v>
+        <v>3.697577596924065</v>
       </c>
       <c r="E306" t="n">
-        <v>3.76937539614763</v>
+        <v>3.769375153688075</v>
       </c>
       <c r="F306" t="n">
         <v>9021900</v>
@@ -6572,16 +6572,16 @@
         <v>44860</v>
       </c>
       <c r="B308" t="n">
-        <v>3.562957286834717</v>
+        <v>3.562956809997559</v>
       </c>
       <c r="C308" t="n">
-        <v>3.670653839244302</v>
+        <v>3.670653347993915</v>
       </c>
       <c r="D308" t="n">
-        <v>3.545007897095387</v>
+        <v>3.545007422660428</v>
       </c>
       <c r="E308" t="n">
-        <v>3.661678930401033</v>
+        <v>3.661678440351775</v>
       </c>
       <c r="F308" t="n">
         <v>15630800</v>
@@ -6592,16 +6592,16 @@
         <v>44861</v>
       </c>
       <c r="B309" t="n">
-        <v>3.706552743911743</v>
+        <v>3.706552505493164</v>
       </c>
       <c r="C309" t="n">
-        <v>3.760400914948455</v>
+        <v>3.760400673066171</v>
       </c>
       <c r="D309" t="n">
-        <v>3.580906797519137</v>
+        <v>3.580906567182549</v>
       </c>
       <c r="E309" t="n">
-        <v>3.580906797519137</v>
+        <v>3.580906567182549</v>
       </c>
       <c r="F309" t="n">
         <v>15175200</v>
@@ -6612,16 +6612,16 @@
         <v>44862</v>
       </c>
       <c r="B310" t="n">
-        <v>3.724502325057983</v>
+        <v>3.724502086639404</v>
       </c>
       <c r="C310" t="n">
-        <v>3.733476806716907</v>
+        <v>3.73347656772384</v>
       </c>
       <c r="D310" t="n">
-        <v>3.643729850391451</v>
+        <v>3.643729617143404</v>
       </c>
       <c r="E310" t="n">
-        <v>3.688603542527801</v>
+        <v>3.68860330640723</v>
       </c>
       <c r="F310" t="n">
         <v>9985100</v>
@@ -6672,16 +6672,16 @@
         <v>44868</v>
       </c>
       <c r="B313" t="n">
-        <v>4.21811056137085</v>
+        <v>4.218111038208008</v>
       </c>
       <c r="C313" t="n">
-        <v>4.254009341880177</v>
+        <v>4.25400982277552</v>
       </c>
       <c r="D313" t="n">
-        <v>3.895021536786911</v>
+        <v>3.895021977100405</v>
       </c>
       <c r="E313" t="n">
-        <v>3.975793578959285</v>
+        <v>3.975794028403671</v>
       </c>
       <c r="F313" t="n">
         <v>15015300</v>
@@ -6712,16 +6712,16 @@
         <v>44872</v>
       </c>
       <c r="B315" t="n">
-        <v>4.011692523956299</v>
+        <v>4.011692047119141</v>
       </c>
       <c r="C315" t="n">
-        <v>4.379655681184977</v>
+        <v>4.37965516061104</v>
       </c>
       <c r="D315" t="n">
-        <v>4.011692523956299</v>
+        <v>4.011692047119141</v>
       </c>
       <c r="E315" t="n">
-        <v>4.316832598744169</v>
+        <v>4.3168320856375</v>
       </c>
       <c r="F315" t="n">
         <v>17217400</v>
@@ -6752,16 +6752,16 @@
         <v>44874</v>
       </c>
       <c r="B317" t="n">
-        <v>4.011692523956299</v>
+        <v>4.011692047119141</v>
       </c>
       <c r="C317" t="n">
-        <v>4.173237470819165</v>
+        <v>4.173236974780477</v>
       </c>
       <c r="D317" t="n">
-        <v>3.98476865144398</v>
+        <v>3.984768177807042</v>
       </c>
       <c r="E317" t="n">
-        <v>4.065541124875413</v>
+        <v>4.06554064163771</v>
       </c>
       <c r="F317" t="n">
         <v>11339500</v>
@@ -6772,16 +6772,16 @@
         <v>44875</v>
       </c>
       <c r="B318" t="n">
-        <v>3.688603401184082</v>
+        <v>3.688603639602661</v>
       </c>
       <c r="C318" t="n">
-        <v>3.975793650420687</v>
+        <v>3.975793907402251</v>
       </c>
       <c r="D318" t="n">
-        <v>3.670654010606794</v>
+        <v>3.670654247865187</v>
       </c>
       <c r="E318" t="n">
-        <v>3.921945478688824</v>
+        <v>3.921945732189828</v>
       </c>
       <c r="F318" t="n">
         <v>22566600</v>
@@ -6812,16 +6812,16 @@
         <v>44879</v>
       </c>
       <c r="B320" t="n">
-        <v>3.697577476501465</v>
+        <v>3.697577953338623</v>
       </c>
       <c r="C320" t="n">
-        <v>3.796299327810405</v>
+        <v>3.796299817378669</v>
       </c>
       <c r="D320" t="n">
-        <v>3.643729310682183</v>
+        <v>3.643729780575117</v>
       </c>
       <c r="E320" t="n">
-        <v>3.760400550597551</v>
+        <v>3.760401035536331</v>
       </c>
       <c r="F320" t="n">
         <v>10873300</v>
@@ -6832,16 +6832,16 @@
         <v>44881</v>
       </c>
       <c r="B321" t="n">
-        <v>3.616805553436279</v>
+        <v>3.616805791854858</v>
       </c>
       <c r="C321" t="n">
-        <v>3.760400666722041</v>
+        <v>3.760400914606361</v>
       </c>
       <c r="D321" t="n">
-        <v>3.553982477400161</v>
+        <v>3.553982711677465</v>
       </c>
       <c r="E321" t="n">
-        <v>3.697577590685923</v>
+        <v>3.697577834428968</v>
       </c>
       <c r="F321" t="n">
         <v>16148800</v>
@@ -6852,16 +6852,16 @@
         <v>44882</v>
       </c>
       <c r="B322" t="n">
-        <v>3.509109020233154</v>
+        <v>3.509109497070312</v>
       </c>
       <c r="C322" t="n">
-        <v>3.571931882577372</v>
+        <v>3.571932367951248</v>
       </c>
       <c r="D322" t="n">
-        <v>3.356538997709313</v>
+        <v>3.356539453814412</v>
       </c>
       <c r="E322" t="n">
-        <v>3.56295718795677</v>
+        <v>3.562957672111115</v>
       </c>
       <c r="F322" t="n">
         <v>25106400</v>
@@ -6892,16 +6892,16 @@
         <v>44886</v>
       </c>
       <c r="B324" t="n">
-        <v>3.616805553436279</v>
+        <v>3.616805791854858</v>
       </c>
       <c r="C324" t="n">
-        <v>3.733476369007364</v>
+        <v>3.733476615116843</v>
       </c>
       <c r="D324" t="n">
-        <v>3.545007782819801</v>
+        <v>3.545008016505496</v>
       </c>
       <c r="E324" t="n">
-        <v>3.679628201525203</v>
+        <v>3.67962844408503</v>
       </c>
       <c r="F324" t="n">
         <v>11314600</v>
@@ -6912,16 +6912,16 @@
         <v>44887</v>
       </c>
       <c r="B325" t="n">
-        <v>3.616805553436279</v>
+        <v>3.616805791854858</v>
       </c>
       <c r="C325" t="n">
-        <v>3.661678812364483</v>
+        <v>3.661679053741092</v>
       </c>
       <c r="D325" t="n">
-        <v>3.562957171980521</v>
+        <v>3.562957406849434</v>
       </c>
       <c r="E325" t="n">
-        <v>3.616805553436279</v>
+        <v>3.616805791854858</v>
       </c>
       <c r="F325" t="n">
         <v>10439300</v>
@@ -6952,16 +6952,16 @@
         <v>44889</v>
       </c>
       <c r="B327" t="n">
-        <v>3.724502325057983</v>
+        <v>3.724502086639404</v>
       </c>
       <c r="C327" t="n">
-        <v>3.742451716323075</v>
+        <v>3.742451476755492</v>
       </c>
       <c r="D327" t="n">
-        <v>3.598856586202345</v>
+        <v>3.598856355826795</v>
       </c>
       <c r="E327" t="n">
-        <v>3.634755368732528</v>
+        <v>3.634755136058969</v>
       </c>
       <c r="F327" t="n">
         <v>5511600</v>
@@ -6972,16 +6972,16 @@
         <v>44890</v>
       </c>
       <c r="B328" t="n">
-        <v>3.63475489616394</v>
+        <v>3.63475513458252</v>
       </c>
       <c r="C328" t="n">
-        <v>3.76040061868389</v>
+        <v>3.760400865344091</v>
       </c>
       <c r="D328" t="n">
-        <v>3.580906515396082</v>
+        <v>3.580906750282523</v>
       </c>
       <c r="E328" t="n">
-        <v>3.733476321313164</v>
+        <v>3.733476566207289</v>
       </c>
       <c r="F328" t="n">
         <v>8739900</v>
@@ -6992,16 +6992,16 @@
         <v>44893</v>
       </c>
       <c r="B329" t="n">
-        <v>3.607830762863159</v>
+        <v>3.607831001281738</v>
       </c>
       <c r="C329" t="n">
-        <v>3.670653840953675</v>
+        <v>3.670654083523831</v>
       </c>
       <c r="D329" t="n">
-        <v>3.58988137311547</v>
+        <v>3.589881610347888</v>
       </c>
       <c r="E329" t="n">
-        <v>3.58988137311547</v>
+        <v>3.589881610347888</v>
       </c>
       <c r="F329" t="n">
         <v>7386900</v>
@@ -7032,16 +7032,16 @@
         <v>44895</v>
       </c>
       <c r="B331" t="n">
-        <v>3.63475489616394</v>
+        <v>3.63475513458252</v>
       </c>
       <c r="C331" t="n">
-        <v>3.661678765587478</v>
+        <v>3.661679005772105</v>
       </c>
       <c r="D331" t="n">
-        <v>3.518083654136107</v>
+        <v>3.518083884901738</v>
       </c>
       <c r="E331" t="n">
-        <v>3.571931820930371</v>
+        <v>3.571932055228125</v>
       </c>
       <c r="F331" t="n">
         <v>16877200</v>
@@ -7112,16 +7112,16 @@
         <v>44901</v>
       </c>
       <c r="B335" t="n">
-        <v>3.302690744400024</v>
+        <v>3.302690982818604</v>
       </c>
       <c r="C335" t="n">
-        <v>3.401412382668387</v>
+        <v>3.401412628213602</v>
       </c>
       <c r="D335" t="n">
-        <v>3.248842364098234</v>
+        <v>3.248842598629542</v>
       </c>
       <c r="E335" t="n">
-        <v>3.383462993892321</v>
+        <v>3.383463238141784</v>
       </c>
       <c r="F335" t="n">
         <v>13327400</v>
@@ -7152,16 +7152,16 @@
         <v>44903</v>
       </c>
       <c r="B337" t="n">
-        <v>3.073575735092163</v>
+        <v>3.073575496673584</v>
       </c>
       <c r="C337" t="n">
-        <v>3.266824548925589</v>
+        <v>3.266824295516617</v>
       </c>
       <c r="D337" t="n">
-        <v>3.064373421071546</v>
+        <v>3.064373183366795</v>
       </c>
       <c r="E337" t="n">
-        <v>3.220812978822505</v>
+        <v>3.22081272898267</v>
       </c>
       <c r="F337" t="n">
         <v>19978800</v>
@@ -7192,16 +7192,16 @@
         <v>44907</v>
       </c>
       <c r="B339" t="n">
-        <v>3.036766290664673</v>
+        <v>3.036766529083252</v>
       </c>
       <c r="C339" t="n">
-        <v>3.119587331114006</v>
+        <v>3.119587576034921</v>
       </c>
       <c r="D339" t="n">
-        <v>2.972350096515548</v>
+        <v>2.972350329876769</v>
       </c>
       <c r="E339" t="n">
-        <v>3.082777857914047</v>
+        <v>3.082778099945025</v>
       </c>
       <c r="F339" t="n">
         <v>24013800</v>
@@ -7232,16 +7232,16 @@
         <v>44909</v>
       </c>
       <c r="B341" t="n">
-        <v>3.073575735092163</v>
+        <v>3.073575496673584</v>
       </c>
       <c r="C341" t="n">
-        <v>3.101182677154013</v>
+        <v>3.101182436593952</v>
       </c>
       <c r="D341" t="n">
-        <v>2.935541024782911</v>
+        <v>2.935540797071743</v>
       </c>
       <c r="E341" t="n">
-        <v>2.981552594885995</v>
+        <v>2.98155236360569</v>
       </c>
       <c r="F341" t="n">
         <v>15438000</v>
@@ -7252,16 +7252,16 @@
         <v>44910</v>
       </c>
       <c r="B342" t="n">
-        <v>3.036766290664673</v>
+        <v>3.036766529083252</v>
       </c>
       <c r="C342" t="n">
-        <v>3.137991958013755</v>
+        <v>3.13799220437963</v>
       </c>
       <c r="D342" t="n">
-        <v>3.009159350315048</v>
+        <v>3.009159586566188</v>
       </c>
       <c r="E342" t="n">
-        <v>3.055170917564423</v>
+        <v>3.055171157427961</v>
       </c>
       <c r="F342" t="n">
         <v>8858500</v>
@@ -7292,16 +7292,16 @@
         <v>44914</v>
       </c>
       <c r="B344" t="n">
-        <v>3.073575735092163</v>
+        <v>3.073575496673584</v>
       </c>
       <c r="C344" t="n">
-        <v>3.091980363133397</v>
+        <v>3.091980123287163</v>
       </c>
       <c r="D344" t="n">
-        <v>2.990754908906612</v>
+        <v>2.990754676912479</v>
       </c>
       <c r="E344" t="n">
-        <v>3.009159536947845</v>
+        <v>3.009159303526058</v>
       </c>
       <c r="F344" t="n">
         <v>6693400</v>
@@ -7312,16 +7312,16 @@
         <v>44915</v>
       </c>
       <c r="B345" t="n">
-        <v>3.257622003555298</v>
+        <v>3.257622241973877</v>
       </c>
       <c r="C345" t="n">
-        <v>3.312835883757822</v>
+        <v>3.31283612621739</v>
       </c>
       <c r="D345" t="n">
-        <v>3.036766263344746</v>
+        <v>3.036766485599353</v>
       </c>
       <c r="E345" t="n">
-        <v>3.036766263344746</v>
+        <v>3.036766485599353</v>
       </c>
       <c r="F345" t="n">
         <v>12943700</v>
@@ -7352,16 +7352,16 @@
         <v>44917</v>
       </c>
       <c r="B347" t="n">
-        <v>3.340443134307861</v>
+        <v>3.340442895889282</v>
       </c>
       <c r="C347" t="n">
-        <v>3.358847761543679</v>
+        <v>3.3588475218115</v>
       </c>
       <c r="D347" t="n">
-        <v>3.257622092346219</v>
+        <v>3.257621859838854</v>
       </c>
       <c r="E347" t="n">
-        <v>3.33124060128949</v>
+        <v>3.331240363527726</v>
       </c>
       <c r="F347" t="n">
         <v>7727000</v>
@@ -7392,16 +7392,16 @@
         <v>44921</v>
       </c>
       <c r="B349" t="n">
-        <v>3.340443134307861</v>
+        <v>3.340442895889282</v>
       </c>
       <c r="C349" t="n">
-        <v>3.441668584104859</v>
+        <v>3.441668338461481</v>
       </c>
       <c r="D349" t="n">
-        <v>3.285229033199945</v>
+        <v>3.28522879872218</v>
       </c>
       <c r="E349" t="n">
-        <v>3.441668584104859</v>
+        <v>3.441668338461481</v>
       </c>
       <c r="F349" t="n">
         <v>5290600</v>
@@ -7412,16 +7412,16 @@
         <v>44922</v>
       </c>
       <c r="B350" t="n">
-        <v>3.386454582214355</v>
+        <v>3.386454820632935</v>
       </c>
       <c r="C350" t="n">
-        <v>3.39565689550568</v>
+        <v>3.395657134572136</v>
       </c>
       <c r="D350" t="n">
-        <v>3.276026603318003</v>
+        <v>3.276026833962055</v>
       </c>
       <c r="E350" t="n">
-        <v>3.349645329049056</v>
+        <v>3.349645564876132</v>
       </c>
       <c r="F350" t="n">
         <v>5669100</v>
@@ -7452,16 +7452,16 @@
         <v>44924</v>
       </c>
       <c r="B352" t="n">
-        <v>3.441668748855591</v>
+        <v>3.441668510437012</v>
       </c>
       <c r="C352" t="n">
-        <v>3.598108307249177</v>
+        <v>3.598108057993386</v>
       </c>
       <c r="D352" t="n">
-        <v>3.404859492621917</v>
+        <v>3.404859256753267</v>
       </c>
       <c r="E352" t="n">
-        <v>3.524489575381356</v>
+        <v>3.524489331225437</v>
       </c>
       <c r="F352" t="n">
         <v>7177700</v>
@@ -7472,16 +7472,16 @@
         <v>44928</v>
       </c>
       <c r="B353" t="n">
-        <v>3.257622003555298</v>
+        <v>3.257622241973877</v>
       </c>
       <c r="C353" t="n">
-        <v>3.414061550196239</v>
+        <v>3.414061800064303</v>
       </c>
       <c r="D353" t="n">
-        <v>3.230015063454036</v>
+        <v>3.23001529985212</v>
       </c>
       <c r="E353" t="n">
-        <v>3.395656923462064</v>
+        <v>3.395657171983132</v>
       </c>
       <c r="F353" t="n">
         <v>9470500</v>
@@ -7492,16 +7492,16 @@
         <v>44929</v>
       </c>
       <c r="B354" t="n">
-        <v>3.073575735092163</v>
+        <v>3.073575496673584</v>
       </c>
       <c r="C354" t="n">
-        <v>3.285229176966823</v>
+        <v>3.285228922130196</v>
       </c>
       <c r="D354" t="n">
-        <v>3.064373421071546</v>
+        <v>3.064373183366795</v>
       </c>
       <c r="E354" t="n">
-        <v>3.257622234904972</v>
+        <v>3.257621982209828</v>
       </c>
       <c r="F354" t="n">
         <v>9560100</v>
@@ -7512,16 +7512,16 @@
         <v>44930</v>
       </c>
       <c r="B355" t="n">
-        <v>3.055171012878418</v>
+        <v>3.055171251296997</v>
       </c>
       <c r="C355" t="n">
-        <v>3.147194369648533</v>
+        <v>3.147194615248405</v>
       </c>
       <c r="D355" t="n">
-        <v>3.036766385404488</v>
+        <v>3.036766622386812</v>
       </c>
       <c r="E355" t="n">
-        <v>3.110385114700673</v>
+        <v>3.110385357428035</v>
       </c>
       <c r="F355" t="n">
         <v>10680900</v>
@@ -7612,16 +7612,16 @@
         <v>44937</v>
       </c>
       <c r="B360" t="n">
-        <v>3.294431209564209</v>
+        <v>3.294431447982788</v>
       </c>
       <c r="C360" t="n">
-        <v>3.294431209564209</v>
+        <v>3.294431447982788</v>
       </c>
       <c r="D360" t="n">
-        <v>3.091980099004334</v>
+        <v>3.091980322771489</v>
       </c>
       <c r="E360" t="n">
-        <v>3.091980099004334</v>
+        <v>3.091980322771489</v>
       </c>
       <c r="F360" t="n">
         <v>21444400</v>
@@ -7652,16 +7652,16 @@
         <v>44939</v>
       </c>
       <c r="B362" t="n">
-        <v>3.073575735092163</v>
+        <v>3.073575496673584</v>
       </c>
       <c r="C362" t="n">
-        <v>3.220812978822505</v>
+        <v>3.22081272898267</v>
       </c>
       <c r="D362" t="n">
-        <v>3.05517110705093</v>
+        <v>3.055170870060005</v>
       </c>
       <c r="E362" t="n">
-        <v>3.184003722740037</v>
+        <v>3.184003475755512</v>
       </c>
       <c r="F362" t="n">
         <v>14486700</v>
@@ -7672,16 +7672,16 @@
         <v>44942</v>
       </c>
       <c r="B363" t="n">
-        <v>3.036766290664673</v>
+        <v>3.036766529083252</v>
       </c>
       <c r="C363" t="n">
-        <v>3.082777857914047</v>
+        <v>3.082778099945025</v>
       </c>
       <c r="D363" t="n">
-        <v>3.009159350315048</v>
+        <v>3.009159586566188</v>
       </c>
       <c r="E363" t="n">
-        <v>3.055170917564423</v>
+        <v>3.055171157427961</v>
       </c>
       <c r="F363" t="n">
         <v>8730700</v>
@@ -7692,16 +7692,16 @@
         <v>44943</v>
       </c>
       <c r="B364" t="n">
-        <v>3.091980218887329</v>
+        <v>3.09197998046875</v>
       </c>
       <c r="C364" t="n">
-        <v>3.128789692653045</v>
+        <v>3.128789451396135</v>
       </c>
       <c r="D364" t="n">
-        <v>3.027564023748135</v>
+        <v>3.027563790296605</v>
       </c>
       <c r="E364" t="n">
-        <v>3.055170964522075</v>
+        <v>3.05517072894181</v>
       </c>
       <c r="F364" t="n">
         <v>11859400</v>
@@ -7832,16 +7832,16 @@
         <v>44952</v>
       </c>
       <c r="B371" t="n">
-        <v>3.2024085521698</v>
+        <v>3.202408313751221</v>
       </c>
       <c r="C371" t="n">
-        <v>3.28522938356367</v>
+        <v>3.2852291389791</v>
       </c>
       <c r="D371" t="n">
-        <v>3.184003922971162</v>
+        <v>3.184003685922803</v>
       </c>
       <c r="E371" t="n">
-        <v>3.257622439765714</v>
+        <v>3.257622197236473</v>
       </c>
       <c r="F371" t="n">
         <v>8271800</v>
@@ -7852,16 +7852,16 @@
         <v>44953</v>
       </c>
       <c r="B372" t="n">
-        <v>3.147194147109985</v>
+        <v>3.147194385528564</v>
       </c>
       <c r="C372" t="n">
-        <v>3.22081265180013</v>
+        <v>3.220812895795746</v>
       </c>
       <c r="D372" t="n">
-        <v>3.128789520937449</v>
+        <v>3.128789757961769</v>
       </c>
       <c r="E372" t="n">
-        <v>3.211610338713862</v>
+        <v>3.211610582012349</v>
       </c>
       <c r="F372" t="n">
         <v>8557200</v>
@@ -7872,16 +7872,16 @@
         <v>44956</v>
       </c>
       <c r="B373" t="n">
-        <v>2.990754842758179</v>
+        <v>2.9907546043396</v>
       </c>
       <c r="C373" t="n">
-        <v>3.156396710866147</v>
+        <v>3.156396459242842</v>
       </c>
       <c r="D373" t="n">
-        <v>2.963147901306928</v>
+        <v>2.963147665089134</v>
       </c>
       <c r="E373" t="n">
-        <v>3.128789769414897</v>
+        <v>3.128789519992377</v>
       </c>
       <c r="F373" t="n">
         <v>24955900</v>
@@ -7912,16 +7912,16 @@
         <v>44958</v>
       </c>
       <c r="B375" t="n">
-        <v>2.898731708526611</v>
+        <v>2.898731470108032</v>
       </c>
       <c r="C375" t="n">
-        <v>3.073575671288802</v>
+        <v>3.073575418489434</v>
       </c>
       <c r="D375" t="n">
-        <v>2.815910664659842</v>
+        <v>2.815910433053234</v>
       </c>
       <c r="E375" t="n">
-        <v>3.027564102140857</v>
+        <v>3.027563853125907</v>
       </c>
       <c r="F375" t="n">
         <v>404695000</v>
@@ -7932,16 +7932,16 @@
         <v>44959</v>
       </c>
       <c r="B376" t="n">
-        <v>2.806708097457886</v>
+        <v>2.806708335876465</v>
       </c>
       <c r="C376" t="n">
-        <v>2.972349950837826</v>
+        <v>2.972350203327015</v>
       </c>
       <c r="D376" t="n">
-        <v>2.797505784459025</v>
+        <v>2.797506022095904</v>
       </c>
       <c r="E376" t="n">
-        <v>2.898731446846941</v>
+        <v>2.898731693082534</v>
       </c>
       <c r="F376" t="n">
         <v>50857000</v>
@@ -7952,16 +7952,16 @@
         <v>44960</v>
       </c>
       <c r="B377" t="n">
-        <v>2.843517541885376</v>
+        <v>2.843517780303955</v>
       </c>
       <c r="C377" t="n">
-        <v>2.871124482750229</v>
+        <v>2.871124723483549</v>
       </c>
       <c r="D377" t="n">
-        <v>2.705482837561113</v>
+        <v>2.705483064405985</v>
       </c>
       <c r="E377" t="n">
-        <v>2.806708287398906</v>
+        <v>2.806708522731163</v>
       </c>
       <c r="F377" t="n">
         <v>53290600</v>
@@ -7972,16 +7972,16 @@
         <v>44963</v>
       </c>
       <c r="B378" t="n">
-        <v>2.898731708526611</v>
+        <v>2.898731470108032</v>
       </c>
       <c r="C378" t="n">
-        <v>2.944743277674556</v>
+        <v>2.944743035471559</v>
       </c>
       <c r="D378" t="n">
-        <v>2.806708350830254</v>
+        <v>2.806708119980529</v>
       </c>
       <c r="E378" t="n">
-        <v>2.852719919978199</v>
+        <v>2.852719685344056</v>
       </c>
       <c r="F378" t="n">
         <v>34861900</v>
@@ -8012,16 +8012,16 @@
         <v>44965</v>
       </c>
       <c r="B380" t="n">
-        <v>3.036766290664673</v>
+        <v>3.036766529083252</v>
       </c>
       <c r="C380" t="n">
-        <v>3.036766290664673</v>
+        <v>3.036766529083252</v>
       </c>
       <c r="D380" t="n">
-        <v>2.861922115716591</v>
+        <v>2.861922340408036</v>
       </c>
       <c r="E380" t="n">
-        <v>2.907933902366425</v>
+        <v>2.907934130670286</v>
       </c>
       <c r="F380" t="n">
         <v>50518000</v>
@@ -8052,16 +8052,16 @@
         <v>44967</v>
       </c>
       <c r="B382" t="n">
-        <v>2.953945636749268</v>
+        <v>2.953945398330688</v>
       </c>
       <c r="C382" t="n">
-        <v>3.045968776454661</v>
+        <v>3.045968530608719</v>
       </c>
       <c r="D382" t="n">
-        <v>2.92633869483765</v>
+        <v>2.926338458647279</v>
       </c>
       <c r="E382" t="n">
-        <v>3.018361834543043</v>
+        <v>3.01836159092531</v>
       </c>
       <c r="F382" t="n">
         <v>23226200</v>
@@ -8092,16 +8092,16 @@
         <v>44971</v>
       </c>
       <c r="B384" t="n">
-        <v>2.742292404174805</v>
+        <v>2.742292165756226</v>
       </c>
       <c r="C384" t="n">
-        <v>2.953945860962829</v>
+        <v>2.953945604142814</v>
       </c>
       <c r="D384" t="n">
-        <v>2.723887774836758</v>
+        <v>2.723887538018302</v>
       </c>
       <c r="E384" t="n">
-        <v>2.953945860962829</v>
+        <v>2.953945604142814</v>
       </c>
       <c r="F384" t="n">
         <v>40924300</v>
@@ -8112,16 +8112,16 @@
         <v>44972</v>
       </c>
       <c r="B385" t="n">
-        <v>2.843517541885376</v>
+        <v>2.843517780303955</v>
       </c>
       <c r="C385" t="n">
-        <v>2.852719855506993</v>
+        <v>2.852720094697153</v>
       </c>
       <c r="D385" t="n">
-        <v>2.631864109187709</v>
+        <v>2.63186432985992</v>
       </c>
       <c r="E385" t="n">
-        <v>2.733089778425966</v>
+        <v>2.733090007585579</v>
       </c>
       <c r="F385" t="n">
         <v>42760100</v>
@@ -8152,16 +8152,16 @@
         <v>44974</v>
       </c>
       <c r="B387" t="n">
-        <v>2.788303852081299</v>
+        <v>2.78830361366272</v>
       </c>
       <c r="C387" t="n">
-        <v>2.871124680376612</v>
+        <v>2.8711244348763</v>
       </c>
       <c r="D387" t="n">
-        <v>2.769899223571229</v>
+        <v>2.769898986726369</v>
       </c>
       <c r="E387" t="n">
-        <v>2.825113109101438</v>
+        <v>2.825112867535422</v>
       </c>
       <c r="F387" t="n">
         <v>27974700</v>
@@ -8212,16 +8212,16 @@
         <v>44981</v>
       </c>
       <c r="B390" t="n">
-        <v>2.65947151184082</v>
+        <v>2.659471273422241</v>
       </c>
       <c r="C390" t="n">
-        <v>2.806708543206081</v>
+        <v>2.806708291587871</v>
       </c>
       <c r="D390" t="n">
-        <v>2.650269197380491</v>
+        <v>2.65026895978689</v>
       </c>
       <c r="E390" t="n">
-        <v>2.797506228745752</v>
+        <v>2.797505977952519</v>
       </c>
       <c r="F390" t="n">
         <v>27929600</v>
@@ -8272,16 +8272,16 @@
         <v>44986</v>
       </c>
       <c r="B393" t="n">
-        <v>2.779101371765137</v>
+        <v>2.779101133346558</v>
       </c>
       <c r="C393" t="n">
-        <v>2.917136296743063</v>
+        <v>2.917136046482494</v>
       </c>
       <c r="D393" t="n">
-        <v>2.751494430649644</v>
+        <v>2.75149419459946</v>
       </c>
       <c r="E393" t="n">
-        <v>2.843517567701285</v>
+        <v>2.843517323756453</v>
       </c>
       <c r="F393" t="n">
         <v>32788900</v>
@@ -8292,16 +8292,16 @@
         <v>44987</v>
       </c>
       <c r="B394" t="n">
-        <v>2.68707799911499</v>
+        <v>2.687078237533569</v>
       </c>
       <c r="C394" t="n">
-        <v>2.797505753894839</v>
+        <v>2.797506002111432</v>
       </c>
       <c r="D394" t="n">
-        <v>2.68707799911499</v>
+        <v>2.687078237533569</v>
       </c>
       <c r="E394" t="n">
-        <v>2.779101128098197</v>
+        <v>2.779101374681788</v>
       </c>
       <c r="F394" t="n">
         <v>21864000</v>
@@ -8412,16 +8412,16 @@
         <v>44995</v>
       </c>
       <c r="B400" t="n">
-        <v>2.503031969070435</v>
+        <v>2.503031730651855</v>
       </c>
       <c r="C400" t="n">
-        <v>2.595055114499298</v>
+        <v>2.595054867315339</v>
       </c>
       <c r="D400" t="n">
-        <v>2.493829654527548</v>
+        <v>2.493829416985507</v>
       </c>
       <c r="E400" t="n">
-        <v>2.576650485413526</v>
+        <v>2.576650239982643</v>
       </c>
       <c r="F400" t="n">
         <v>23735100</v>
@@ -8452,16 +8452,16 @@
         <v>44999</v>
       </c>
       <c r="B402" t="n">
-        <v>2.493829250335693</v>
+        <v>2.493829488754272</v>
       </c>
       <c r="C402" t="n">
-        <v>2.585852380849743</v>
+        <v>2.585852628066047</v>
       </c>
       <c r="D402" t="n">
-        <v>2.466222311181478</v>
+        <v>2.46622254696074</v>
       </c>
       <c r="E402" t="n">
-        <v>2.475424624232883</v>
+        <v>2.475424860891918</v>
       </c>
       <c r="F402" t="n">
         <v>40119200</v>
@@ -8472,16 +8472,16 @@
         <v>45000</v>
       </c>
       <c r="B403" t="n">
-        <v>2.493829250335693</v>
+        <v>2.493829488754272</v>
       </c>
       <c r="C403" t="n">
-        <v>2.521436189489909</v>
+        <v>2.521436430547805</v>
       </c>
       <c r="D403" t="n">
-        <v>2.447817685078669</v>
+        <v>2.447817919098385</v>
       </c>
       <c r="E403" t="n">
-        <v>2.475424624232883</v>
+        <v>2.475424860891918</v>
       </c>
       <c r="F403" t="n">
         <v>17612600</v>
@@ -8492,16 +8492,16 @@
         <v>45001</v>
       </c>
       <c r="B404" t="n">
-        <v>2.512233972549438</v>
+        <v>2.512234210968018</v>
       </c>
       <c r="C404" t="n">
-        <v>2.539840912759816</v>
+        <v>2.539841153798378</v>
       </c>
       <c r="D404" t="n">
-        <v>2.447817778725223</v>
+        <v>2.447818011030511</v>
       </c>
       <c r="E404" t="n">
-        <v>2.530638599356357</v>
+        <v>2.530638839521591</v>
       </c>
       <c r="F404" t="n">
         <v>22197500</v>
@@ -25991,20 +25991,32 @@
       <c r="A1279" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B1279" t="n">
+      <c r="B1279" t="inlineStr"/>
+      <c r="C1279" t="inlineStr"/>
+      <c r="D1279" t="inlineStr"/>
+      <c r="E1279" t="inlineStr"/>
+      <c r="F1279" t="n">
+        <v>64643300</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B1280" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="C1280" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D1280" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E1280" t="n">
         <v>0.27</v>
       </c>
-      <c r="C1279" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="D1279" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E1279" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="F1279" t="n">
-        <v>12268900</v>
+      <c r="F1280" t="n">
+        <v>64905500</v>
       </c>
     </row>
   </sheetData>

--- a/database/RAIZ4.xlsx
+++ b/database/RAIZ4.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1280"/>
+  <dimension ref="A1:F1281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44413</v>
       </c>
       <c r="B2" t="n">
-        <v>6.384480953216553</v>
+        <v>6.384481906890869</v>
       </c>
       <c r="C2" t="n">
-        <v>6.701941459879408</v>
+        <v>6.701942460974013</v>
       </c>
       <c r="D2" t="n">
-        <v>6.331570938854646</v>
+        <v>6.331571884625592</v>
       </c>
       <c r="E2" t="n">
-        <v>6.596121431155595</v>
+        <v>6.596122416443459</v>
       </c>
       <c r="F2" t="n">
         <v>98849900</v>
@@ -532,16 +532,16 @@
         <v>44419</v>
       </c>
       <c r="B6" t="n">
-        <v>6.058202743530273</v>
+        <v>6.058203220367432</v>
       </c>
       <c r="C6" t="n">
-        <v>6.296298035007707</v>
+        <v>6.296298530585189</v>
       </c>
       <c r="D6" t="n">
-        <v>5.996474599382589</v>
+        <v>5.996475071361166</v>
       </c>
       <c r="E6" t="n">
-        <v>6.287479908911514</v>
+        <v>6.287480403794928</v>
       </c>
       <c r="F6" t="n">
         <v>31978000</v>
@@ -552,16 +552,16 @@
         <v>44420</v>
       </c>
       <c r="B7" t="n">
-        <v>6.13756799697876</v>
+        <v>6.137568473815918</v>
       </c>
       <c r="C7" t="n">
-        <v>6.155204669708928</v>
+        <v>6.155205147916306</v>
       </c>
       <c r="D7" t="n">
-        <v>5.952382723066271</v>
+        <v>5.952383185516099</v>
       </c>
       <c r="E7" t="n">
-        <v>6.146386123098121</v>
+        <v>6.146386600620373</v>
       </c>
       <c r="F7" t="n">
         <v>17054100</v>
@@ -572,16 +572,16 @@
         <v>44421</v>
       </c>
       <c r="B8" t="n">
-        <v>6.181660652160645</v>
+        <v>6.181660175323486</v>
       </c>
       <c r="C8" t="n">
-        <v>6.208115454275954</v>
+        <v>6.208114975398141</v>
       </c>
       <c r="D8" t="n">
-        <v>6.049385380109605</v>
+        <v>6.049384913475816</v>
       </c>
       <c r="E8" t="n">
-        <v>6.155205429553837</v>
+        <v>6.155204954757366</v>
       </c>
       <c r="F8" t="n">
         <v>21141500</v>
@@ -592,16 +592,16 @@
         <v>44424</v>
       </c>
       <c r="B9" t="n">
-        <v>6.190478324890137</v>
+        <v>6.190478801727295</v>
       </c>
       <c r="C9" t="n">
-        <v>6.278661692952952</v>
+        <v>6.278662176582655</v>
       </c>
       <c r="D9" t="n">
-        <v>5.978838241539382</v>
+        <v>5.978838702074429</v>
       </c>
       <c r="E9" t="n">
-        <v>6.146386430612996</v>
+        <v>6.146386904053864</v>
       </c>
       <c r="F9" t="n">
         <v>13434600</v>
@@ -612,16 +612,16 @@
         <v>44425</v>
       </c>
       <c r="B10" t="n">
-        <v>6.014111042022705</v>
+        <v>6.014111518859863</v>
       </c>
       <c r="C10" t="n">
-        <v>6.164022543855327</v>
+        <v>6.164023032578428</v>
       </c>
       <c r="D10" t="n">
-        <v>5.961201025995057</v>
+        <v>5.961201498637171</v>
       </c>
       <c r="E10" t="n">
-        <v>6.111112527827679</v>
+        <v>6.111113012355736</v>
       </c>
       <c r="F10" t="n">
         <v>17772000</v>
@@ -632,16 +632,16 @@
         <v>44426</v>
       </c>
       <c r="B11" t="n">
-        <v>6.005292415618896</v>
+        <v>6.005292892456055</v>
       </c>
       <c r="C11" t="n">
-        <v>6.17284100771587</v>
+        <v>6.172841497856859</v>
       </c>
       <c r="D11" t="n">
-        <v>5.925927182391009</v>
+        <v>5.925927652926344</v>
       </c>
       <c r="E11" t="n">
-        <v>6.022929087392713</v>
+        <v>6.022929565630274</v>
       </c>
       <c r="F11" t="n">
         <v>8841700</v>
@@ -652,16 +652,16 @@
         <v>44427</v>
       </c>
       <c r="B12" t="n">
-        <v>6.111112594604492</v>
+        <v>6.11111307144165</v>
       </c>
       <c r="C12" t="n">
-        <v>6.111112594604492</v>
+        <v>6.11111307144165</v>
       </c>
       <c r="D12" t="n">
-        <v>5.661377243209458</v>
+        <v>5.66137768495472</v>
       </c>
       <c r="E12" t="n">
-        <v>5.908290654036534</v>
+        <v>5.908291115047926</v>
       </c>
       <c r="F12" t="n">
         <v>5423700</v>
@@ -672,16 +672,16 @@
         <v>44428</v>
       </c>
       <c r="B13" t="n">
-        <v>6.155204296112061</v>
+        <v>6.155205249786377</v>
       </c>
       <c r="C13" t="n">
-        <v>6.21693285716669</v>
+        <v>6.216933820405099</v>
       </c>
       <c r="D13" t="n">
-        <v>6.022929048418668</v>
+        <v>6.022929981598537</v>
       </c>
       <c r="E13" t="n">
-        <v>6.075839063397741</v>
+        <v>6.075840004775376</v>
       </c>
       <c r="F13" t="n">
         <v>3109200</v>
@@ -712,16 +712,16 @@
         <v>44432</v>
       </c>
       <c r="B15" t="n">
-        <v>6.393299579620361</v>
+        <v>6.393301010131836</v>
       </c>
       <c r="C15" t="n">
-        <v>6.525574827434928</v>
+        <v>6.525576287543212</v>
       </c>
       <c r="D15" t="n">
-        <v>6.331571018509184</v>
+        <v>6.33157243520879</v>
       </c>
       <c r="E15" t="n">
-        <v>6.384481033536726</v>
+        <v>6.384482462075037</v>
       </c>
       <c r="F15" t="n">
         <v>6054100</v>
@@ -852,16 +852,16 @@
         <v>44441</v>
       </c>
       <c r="B22" t="n">
-        <v>5.996474266052246</v>
+        <v>5.996475219726562</v>
       </c>
       <c r="C22" t="n">
-        <v>6.252206215997954</v>
+        <v>6.252207210343668</v>
       </c>
       <c r="D22" t="n">
-        <v>5.970019048251363</v>
+        <v>5.970019997718263</v>
       </c>
       <c r="E22" t="n">
-        <v>6.234569544294506</v>
+        <v>6.234570535835299</v>
       </c>
       <c r="F22" t="n">
         <v>3746900</v>
@@ -872,16 +872,16 @@
         <v>44442</v>
       </c>
       <c r="B23" t="n">
-        <v>6.17284107208252</v>
+        <v>6.172841548919678</v>
       </c>
       <c r="C23" t="n">
-        <v>6.17284107208252</v>
+        <v>6.172841548919678</v>
       </c>
       <c r="D23" t="n">
-        <v>5.934745790407565</v>
+        <v>5.934746248852434</v>
       </c>
       <c r="E23" t="n">
-        <v>6.031747696420747</v>
+        <v>6.031748162358781</v>
       </c>
       <c r="F23" t="n">
         <v>3705400</v>
@@ -892,16 +892,16 @@
         <v>44445</v>
       </c>
       <c r="B24" t="n">
-        <v>6.111112594604492</v>
+        <v>6.11111307144165</v>
       </c>
       <c r="C24" t="n">
-        <v>6.190477829758912</v>
+        <v>6.190478312788771</v>
       </c>
       <c r="D24" t="n">
-        <v>6.067021124345374</v>
+        <v>6.067021597742168</v>
       </c>
       <c r="E24" t="n">
-        <v>6.119931140951175</v>
+        <v>6.119931618476427</v>
       </c>
       <c r="F24" t="n">
         <v>1654400</v>
@@ -932,16 +932,16 @@
         <v>44448</v>
       </c>
       <c r="B26" t="n">
-        <v>5.652558326721191</v>
+        <v>5.65255880355835</v>
       </c>
       <c r="C26" t="n">
-        <v>5.837743582960889</v>
+        <v>5.837744075419861</v>
       </c>
       <c r="D26" t="n">
-        <v>5.59964831358005</v>
+        <v>5.599648785953838</v>
       </c>
       <c r="E26" t="n">
-        <v>5.75837877349488</v>
+        <v>5.758379259258814</v>
       </c>
       <c r="F26" t="n">
         <v>5428200</v>
@@ -952,16 +952,16 @@
         <v>44449</v>
       </c>
       <c r="B27" t="n">
-        <v>5.731924533843994</v>
+        <v>5.731923580169678</v>
       </c>
       <c r="C27" t="n">
-        <v>5.89947314759995</v>
+        <v>5.899472166048991</v>
       </c>
       <c r="D27" t="n">
-        <v>5.617285942249159</v>
+        <v>5.617285007648347</v>
       </c>
       <c r="E27" t="n">
-        <v>5.767197881951408</v>
+        <v>5.767196922408332</v>
       </c>
       <c r="F27" t="n">
         <v>5905500</v>
@@ -972,16 +972,16 @@
         <v>44452</v>
       </c>
       <c r="B28" t="n">
-        <v>6.128748893737793</v>
+        <v>6.128749370574951</v>
       </c>
       <c r="C28" t="n">
-        <v>6.172840781804387</v>
+        <v>6.172841262072042</v>
       </c>
       <c r="D28" t="n">
-        <v>5.925926965515992</v>
+        <v>5.925927426572926</v>
       </c>
       <c r="E28" t="n">
-        <v>5.95238218245423</v>
+        <v>5.952382645569469</v>
       </c>
       <c r="F28" t="n">
         <v>8999600</v>
@@ -1012,16 +1012,16 @@
         <v>44454</v>
       </c>
       <c r="B30" t="n">
-        <v>6.384480953216553</v>
+        <v>6.384481906890869</v>
       </c>
       <c r="C30" t="n">
-        <v>6.50793807388575</v>
+        <v>6.507939046001328</v>
       </c>
       <c r="D30" t="n">
-        <v>6.296297595946708</v>
+        <v>6.29629853644874</v>
       </c>
       <c r="E30" t="n">
-        <v>6.384480953216553</v>
+        <v>6.384481906890869</v>
       </c>
       <c r="F30" t="n">
         <v>7265900</v>
@@ -1032,16 +1032,16 @@
         <v>44455</v>
       </c>
       <c r="B31" t="n">
-        <v>6.278661251068115</v>
+        <v>6.278661727905273</v>
       </c>
       <c r="C31" t="n">
-        <v>6.428573176470008</v>
+        <v>6.428573664692329</v>
       </c>
       <c r="D31" t="n">
-        <v>6.172841216840228</v>
+        <v>6.172841685640813</v>
       </c>
       <c r="E31" t="n">
-        <v>6.349207940553374</v>
+        <v>6.349208422748248</v>
       </c>
       <c r="F31" t="n">
         <v>6142600</v>
@@ -1052,16 +1052,16 @@
         <v>44456</v>
       </c>
       <c r="B32" t="n">
-        <v>6.384480953216553</v>
+        <v>6.384481906890869</v>
       </c>
       <c r="C32" t="n">
-        <v>6.384480953216553</v>
+        <v>6.384481906890869</v>
       </c>
       <c r="D32" t="n">
-        <v>5.978837509775269</v>
+        <v>5.978838402857074</v>
       </c>
       <c r="E32" t="n">
-        <v>6.26102425303877</v>
+        <v>6.261025188271888</v>
       </c>
       <c r="F32" t="n">
         <v>16008100</v>
@@ -1112,16 +1112,16 @@
         <v>44461</v>
       </c>
       <c r="B35" t="n">
-        <v>6.446210384368896</v>
+        <v>6.446209907531738</v>
       </c>
       <c r="C35" t="n">
-        <v>6.560848974551915</v>
+        <v>6.560848489234745</v>
       </c>
       <c r="D35" t="n">
-        <v>6.40211891002337</v>
+        <v>6.402118436447734</v>
       </c>
       <c r="E35" t="n">
-        <v>6.463847058205402</v>
+        <v>6.463846580063628</v>
       </c>
       <c r="F35" t="n">
         <v>10254600</v>
@@ -1132,16 +1132,16 @@
         <v>44462</v>
       </c>
       <c r="B36" t="n">
-        <v>6.375663757324219</v>
+        <v>6.375663280487061</v>
       </c>
       <c r="C36" t="n">
-        <v>6.54321237081167</v>
+        <v>6.543211881443518</v>
       </c>
       <c r="D36" t="n">
-        <v>6.340390409273332</v>
+        <v>6.340389935074274</v>
       </c>
       <c r="E36" t="n">
-        <v>6.507939022760783</v>
+        <v>6.507938536030731</v>
       </c>
       <c r="F36" t="n">
         <v>6341600</v>
@@ -1152,16 +1152,16 @@
         <v>44463</v>
       </c>
       <c r="B37" t="n">
-        <v>6.17284107208252</v>
+        <v>6.172841548919678</v>
       </c>
       <c r="C37" t="n">
-        <v>6.375663009842031</v>
+        <v>6.375663502346697</v>
       </c>
       <c r="D37" t="n">
-        <v>6.164022525857945</v>
+        <v>6.164023002013892</v>
       </c>
       <c r="E37" t="n">
-        <v>6.340389665926588</v>
+        <v>6.340390155706473</v>
       </c>
       <c r="F37" t="n">
         <v>5138200</v>
@@ -1172,16 +1172,16 @@
         <v>44466</v>
       </c>
       <c r="B38" t="n">
-        <v>6.305117607116699</v>
+        <v>6.305116653442383</v>
       </c>
       <c r="C38" t="n">
-        <v>6.340390958221537</v>
+        <v>6.340389999211985</v>
       </c>
       <c r="D38" t="n">
-        <v>6.102295628018125</v>
+        <v>6.102294705021446</v>
       </c>
       <c r="E38" t="n">
-        <v>6.172842330227801</v>
+        <v>6.17284139656065</v>
       </c>
       <c r="F38" t="n">
         <v>6343700</v>
@@ -1252,16 +1252,16 @@
         <v>44470</v>
       </c>
       <c r="B42" t="n">
-        <v>6.499119758605957</v>
+        <v>6.499120235443115</v>
       </c>
       <c r="C42" t="n">
-        <v>6.569666446925959</v>
+        <v>6.569666928939093</v>
       </c>
       <c r="D42" t="n">
-        <v>6.331571163600236</v>
+        <v>6.331571628144438</v>
       </c>
       <c r="E42" t="n">
-        <v>6.331571163600236</v>
+        <v>6.331571628144438</v>
       </c>
       <c r="F42" t="n">
         <v>15528000</v>
@@ -1272,16 +1272,16 @@
         <v>44473</v>
       </c>
       <c r="B43" t="n">
-        <v>6.190478324890137</v>
+        <v>6.190478801727295</v>
       </c>
       <c r="C43" t="n">
-        <v>6.552030344193411</v>
+        <v>6.552030848880022</v>
       </c>
       <c r="D43" t="n">
-        <v>6.190478324890137</v>
+        <v>6.190478801727295</v>
       </c>
       <c r="E43" t="n">
-        <v>6.5255755440203</v>
+        <v>6.525576046669164</v>
       </c>
       <c r="F43" t="n">
         <v>12019000</v>
@@ -1292,16 +1292,16 @@
         <v>44474</v>
       </c>
       <c r="B44" t="n">
-        <v>6.287480354309082</v>
+        <v>6.287479877471924</v>
       </c>
       <c r="C44" t="n">
-        <v>6.366845176762705</v>
+        <v>6.366844693906587</v>
       </c>
       <c r="D44" t="n">
-        <v>6.243388459230366</v>
+        <v>6.2433879857371</v>
       </c>
       <c r="E44" t="n">
-        <v>6.29629848102994</v>
+        <v>6.296298003524023</v>
       </c>
       <c r="F44" t="n">
         <v>12888200</v>
@@ -1312,16 +1312,16 @@
         <v>44475</v>
       </c>
       <c r="B45" t="n">
-        <v>6.178093433380127</v>
+        <v>6.178093910217285</v>
       </c>
       <c r="C45" t="n">
-        <v>6.275316770259803</v>
+        <v>6.275317254600846</v>
       </c>
       <c r="D45" t="n">
-        <v>6.080870517951754</v>
+        <v>6.080870987285061</v>
       </c>
       <c r="E45" t="n">
-        <v>6.248801582943448</v>
+        <v>6.248802065237998</v>
       </c>
       <c r="F45" t="n">
         <v>10376100</v>
@@ -1372,16 +1372,16 @@
         <v>44480</v>
       </c>
       <c r="B48" t="n">
-        <v>6.213447570800781</v>
+        <v>6.213448047637939</v>
       </c>
       <c r="C48" t="n">
-        <v>6.407893818474543</v>
+        <v>6.407894310234044</v>
       </c>
       <c r="D48" t="n">
-        <v>6.213447570800781</v>
+        <v>6.213448047637939</v>
       </c>
       <c r="E48" t="n">
-        <v>6.363701278732132</v>
+        <v>6.363701767100176</v>
       </c>
       <c r="F48" t="n">
         <v>10407400</v>
@@ -1392,16 +1392,16 @@
         <v>44482</v>
       </c>
       <c r="B49" t="n">
-        <v>6.231124877929688</v>
+        <v>6.231125354766846</v>
       </c>
       <c r="C49" t="n">
-        <v>6.292993931556084</v>
+        <v>6.292994413127774</v>
       </c>
       <c r="D49" t="n">
-        <v>6.213447945257672</v>
+        <v>6.213448420742101</v>
       </c>
       <c r="E49" t="n">
-        <v>6.248801810601703</v>
+        <v>6.248802288791589</v>
       </c>
       <c r="F49" t="n">
         <v>8146000</v>
@@ -1412,16 +1412,16 @@
         <v>44483</v>
       </c>
       <c r="B50" t="n">
-        <v>6.319509983062744</v>
+        <v>6.319509506225586</v>
       </c>
       <c r="C50" t="n">
-        <v>6.381379041014171</v>
+        <v>6.381378559508698</v>
       </c>
       <c r="D50" t="n">
-        <v>6.239963569752225</v>
+        <v>6.239963098917224</v>
       </c>
       <c r="E50" t="n">
-        <v>6.248802247431771</v>
+        <v>6.24880177592985</v>
       </c>
       <c r="F50" t="n">
         <v>10992200</v>
@@ -1432,16 +1432,16 @@
         <v>44484</v>
       </c>
       <c r="B51" t="n">
-        <v>6.275317192077637</v>
+        <v>6.275317668914795</v>
       </c>
       <c r="C51" t="n">
-        <v>6.354863602276304</v>
+        <v>6.354864085157887</v>
       </c>
       <c r="D51" t="n">
-        <v>6.222286392428969</v>
+        <v>6.222286865236521</v>
       </c>
       <c r="E51" t="n">
-        <v>6.337186669060081</v>
+        <v>6.337187150598463</v>
       </c>
       <c r="F51" t="n">
         <v>34203500</v>
@@ -1472,16 +1472,16 @@
         <v>44488</v>
       </c>
       <c r="B53" t="n">
-        <v>5.912940502166748</v>
+        <v>5.91294002532959</v>
       </c>
       <c r="C53" t="n">
-        <v>6.186933207944406</v>
+        <v>6.186932709011659</v>
       </c>
       <c r="D53" t="n">
-        <v>5.895263567002105</v>
+        <v>5.895263091590468</v>
       </c>
       <c r="E53" t="n">
-        <v>6.169256272779763</v>
+        <v>6.169255775272537</v>
       </c>
       <c r="F53" t="n">
         <v>11473400</v>
@@ -1492,16 +1492,16 @@
         <v>44489</v>
       </c>
       <c r="B54" t="n">
-        <v>5.904101371765137</v>
+        <v>5.904100894927979</v>
       </c>
       <c r="C54" t="n">
-        <v>6.045517263705048</v>
+        <v>6.045516775446618</v>
       </c>
       <c r="D54" t="n">
-        <v>5.842232314152062</v>
+        <v>5.842231842311679</v>
       </c>
       <c r="E54" t="n">
-        <v>6.010163396082907</v>
+        <v>6.010162910679786</v>
       </c>
       <c r="F54" t="n">
         <v>6234400</v>
@@ -1512,16 +1512,16 @@
         <v>44490</v>
       </c>
       <c r="B55" t="n">
-        <v>5.683139801025391</v>
+        <v>5.683138847351074</v>
       </c>
       <c r="C55" t="n">
-        <v>5.842232635527925</v>
+        <v>5.842231655156614</v>
       </c>
       <c r="D55" t="n">
-        <v>5.471016583623838</v>
+        <v>5.471015665545419</v>
       </c>
       <c r="E55" t="n">
-        <v>5.798040087843582</v>
+        <v>5.79803911488812</v>
       </c>
       <c r="F55" t="n">
         <v>12472300</v>
@@ -1532,16 +1532,16 @@
         <v>44491</v>
       </c>
       <c r="B56" t="n">
-        <v>5.630107879638672</v>
+        <v>5.63010835647583</v>
       </c>
       <c r="C56" t="n">
-        <v>5.656623487278746</v>
+        <v>5.656623966361621</v>
       </c>
       <c r="D56" t="n">
-        <v>5.197022852643983</v>
+        <v>5.197023292801376</v>
       </c>
       <c r="E56" t="n">
-        <v>5.603592693449883</v>
+        <v>5.60359316804136</v>
       </c>
       <c r="F56" t="n">
         <v>18890200</v>
@@ -1572,16 +1572,16 @@
         <v>44495</v>
       </c>
       <c r="B58" t="n">
-        <v>5.815716743469238</v>
+        <v>5.81571626663208</v>
       </c>
       <c r="C58" t="n">
-        <v>5.868747545274117</v>
+        <v>5.868747064088904</v>
       </c>
       <c r="D58" t="n">
-        <v>5.683139528231368</v>
+        <v>5.683139062264364</v>
       </c>
       <c r="E58" t="n">
-        <v>5.833393677404199</v>
+        <v>5.833393199117688</v>
       </c>
       <c r="F58" t="n">
         <v>8470300</v>
@@ -1612,16 +1612,16 @@
         <v>44497</v>
       </c>
       <c r="B60" t="n">
-        <v>5.99248743057251</v>
+        <v>5.992486000061035</v>
       </c>
       <c r="C60" t="n">
-        <v>6.027841303907334</v>
+        <v>6.027839864956272</v>
       </c>
       <c r="D60" t="n">
-        <v>5.727332959109914</v>
+        <v>5.727331591895446</v>
       </c>
       <c r="E60" t="n">
-        <v>5.753848574836739</v>
+        <v>5.75384720129253</v>
       </c>
       <c r="F60" t="n">
         <v>8299700</v>
@@ -1632,16 +1632,16 @@
         <v>44498</v>
       </c>
       <c r="B61" t="n">
-        <v>5.99248743057251</v>
+        <v>5.992486000061035</v>
       </c>
       <c r="C61" t="n">
-        <v>6.01900262484792</v>
+        <v>6.019001188006806</v>
       </c>
       <c r="D61" t="n">
-        <v>5.8422332581738</v>
+        <v>5.842231863530622</v>
       </c>
       <c r="E61" t="n">
-        <v>5.957133135786272</v>
+        <v>5.957131713714485</v>
       </c>
       <c r="F61" t="n">
         <v>3926300</v>
@@ -1652,16 +1652,16 @@
         <v>44501</v>
       </c>
       <c r="B62" t="n">
-        <v>6.001323699951172</v>
+        <v>6.00132417678833</v>
       </c>
       <c r="C62" t="n">
-        <v>6.063193168515561</v>
+        <v>6.063193650268579</v>
       </c>
       <c r="D62" t="n">
-        <v>5.948292907517955</v>
+        <v>5.948293380141535</v>
       </c>
       <c r="E62" t="n">
-        <v>5.965969838329028</v>
+        <v>5.965970312357133</v>
       </c>
       <c r="F62" t="n">
         <v>5059700</v>
@@ -1672,16 +1672,16 @@
         <v>44503</v>
       </c>
       <c r="B63" t="n">
-        <v>6.09854793548584</v>
+        <v>6.098547458648682</v>
       </c>
       <c r="C63" t="n">
-        <v>6.186932602662175</v>
+        <v>6.186932118914339</v>
       </c>
       <c r="D63" t="n">
-        <v>5.921778179681833</v>
+        <v>5.92177771666606</v>
       </c>
       <c r="E63" t="n">
-        <v>5.983647657430936</v>
+        <v>5.983647189577673</v>
       </c>
       <c r="F63" t="n">
         <v>5711600</v>
@@ -1772,16 +1772,16 @@
         <v>44510</v>
       </c>
       <c r="B68" t="n">
-        <v>5.745007991790771</v>
+        <v>5.745008945465088</v>
       </c>
       <c r="C68" t="n">
-        <v>6.01016237537701</v>
+        <v>6.010163373067091</v>
       </c>
       <c r="D68" t="n">
-        <v>5.745007991790771</v>
+        <v>5.745008945465088</v>
       </c>
       <c r="E68" t="n">
-        <v>5.957131161498742</v>
+        <v>5.957132150385616</v>
       </c>
       <c r="F68" t="n">
         <v>10074000</v>
@@ -1792,16 +1792,16 @@
         <v>44511</v>
       </c>
       <c r="B69" t="n">
-        <v>6.010162830352783</v>
+        <v>6.0101637840271</v>
       </c>
       <c r="C69" t="n">
-        <v>6.036678017847871</v>
+        <v>6.036678975729536</v>
       </c>
       <c r="D69" t="n">
-        <v>5.806877899934787</v>
+        <v>5.80687882135247</v>
       </c>
       <c r="E69" t="n">
-        <v>5.833393087429874</v>
+        <v>5.833394013054906</v>
       </c>
       <c r="F69" t="n">
         <v>8604300</v>
@@ -1812,16 +1812,16 @@
         <v>44512</v>
       </c>
       <c r="B70" t="n">
-        <v>5.762685775756836</v>
+        <v>5.762685298919678</v>
       </c>
       <c r="C70" t="n">
-        <v>6.080870998876915</v>
+        <v>6.080870495711316</v>
       </c>
       <c r="D70" t="n">
-        <v>5.532885641218299</v>
+        <v>5.532885183396102</v>
       </c>
       <c r="E70" t="n">
-        <v>6.080870998876915</v>
+        <v>6.080870495711316</v>
       </c>
       <c r="F70" t="n">
         <v>20568500</v>
@@ -1852,16 +1852,16 @@
         <v>44517</v>
       </c>
       <c r="B72" t="n">
-        <v>5.170507431030273</v>
+        <v>5.17050838470459</v>
       </c>
       <c r="C72" t="n">
-        <v>5.462177018308454</v>
+        <v>5.462178025779772</v>
       </c>
       <c r="D72" t="n">
-        <v>5.002576367138015</v>
+        <v>5.002577289838284</v>
       </c>
       <c r="E72" t="n">
-        <v>5.364954103516594</v>
+        <v>5.364955093055631</v>
       </c>
       <c r="F72" t="n">
         <v>24600900</v>
@@ -1872,16 +1872,16 @@
         <v>44518</v>
       </c>
       <c r="B73" t="n">
-        <v>5.161669731140137</v>
+        <v>5.16166877746582</v>
       </c>
       <c r="C73" t="n">
-        <v>5.338439069281368</v>
+        <v>5.338438082947006</v>
       </c>
       <c r="D73" t="n">
-        <v>5.073284640618174</v>
+        <v>5.07328370327396</v>
       </c>
       <c r="E73" t="n">
-        <v>5.214700532582506</v>
+        <v>5.214699569110176</v>
       </c>
       <c r="F73" t="n">
         <v>17735600</v>
@@ -1892,16 +1892,16 @@
         <v>44519</v>
       </c>
       <c r="B74" t="n">
-        <v>5.241215705871582</v>
+        <v>5.241215229034424</v>
       </c>
       <c r="C74" t="n">
-        <v>5.285408250991699</v>
+        <v>5.285407770133975</v>
       </c>
       <c r="D74" t="n">
-        <v>5.090961979656143</v>
+        <v>5.090961516488821</v>
       </c>
       <c r="E74" t="n">
-        <v>5.161669714687254</v>
+        <v>5.161669245087059</v>
       </c>
       <c r="F74" t="n">
         <v>11364600</v>
@@ -1912,16 +1912,16 @@
         <v>44522</v>
       </c>
       <c r="B75" t="n">
-        <v>4.976061344146729</v>
+        <v>4.976062297821045</v>
       </c>
       <c r="C75" t="n">
-        <v>5.32960041550615</v>
+        <v>5.329601436937094</v>
       </c>
       <c r="D75" t="n">
-        <v>4.976061344146729</v>
+        <v>4.976062297821045</v>
       </c>
       <c r="E75" t="n">
-        <v>5.232377076055763</v>
+        <v>5.232378078853616</v>
       </c>
       <c r="F75" t="n">
         <v>8516000</v>
@@ -1932,16 +1932,16 @@
         <v>44523</v>
       </c>
       <c r="B76" t="n">
-        <v>5.011415004730225</v>
+        <v>5.011415481567383</v>
       </c>
       <c r="C76" t="n">
-        <v>5.099799663602187</v>
+        <v>5.099800148849164</v>
       </c>
       <c r="D76" t="n">
-        <v>4.781614470211824</v>
+        <v>4.781614925183414</v>
       </c>
       <c r="E76" t="n">
-        <v>5.00257632811738</v>
+        <v>5.002576804113536</v>
       </c>
       <c r="F76" t="n">
         <v>9084200</v>
@@ -1952,16 +1952,16 @@
         <v>44524</v>
       </c>
       <c r="B77" t="n">
-        <v>4.923030376434326</v>
+        <v>4.923030853271484</v>
       </c>
       <c r="C77" t="n">
-        <v>5.020253291071671</v>
+        <v>5.020253777325691</v>
       </c>
       <c r="D77" t="n">
-        <v>4.825807040345681</v>
+        <v>4.825807507765937</v>
       </c>
       <c r="E77" t="n">
-        <v>4.923030376434326</v>
+        <v>4.923030853271484</v>
       </c>
       <c r="F77" t="n">
         <v>8397000</v>
@@ -1992,16 +1992,16 @@
         <v>44526</v>
       </c>
       <c r="B79" t="n">
-        <v>5.223537921905518</v>
+        <v>5.223538398742676</v>
       </c>
       <c r="C79" t="n">
-        <v>5.338438183355024</v>
+        <v>5.338438670680995</v>
       </c>
       <c r="D79" t="n">
-        <v>5.020253006053037</v>
+        <v>5.020253464333078</v>
       </c>
       <c r="E79" t="n">
-        <v>5.037929936933631</v>
+        <v>5.037930396827334</v>
       </c>
       <c r="F79" t="n">
         <v>8564200</v>
@@ -2012,16 +2012,16 @@
         <v>44529</v>
       </c>
       <c r="B80" t="n">
-        <v>5.117476940155029</v>
+        <v>5.117477893829346</v>
       </c>
       <c r="C80" t="n">
-        <v>5.391469611843401</v>
+        <v>5.39147061657799</v>
       </c>
       <c r="D80" t="n">
-        <v>5.117476940155029</v>
+        <v>5.117477893829346</v>
       </c>
       <c r="E80" t="n">
-        <v>5.285408014051384</v>
+        <v>5.285408999020722</v>
       </c>
       <c r="F80" t="n">
         <v>7811800</v>
@@ -2032,16 +2032,16 @@
         <v>44530</v>
       </c>
       <c r="B81" t="n">
-        <v>4.825808525085449</v>
+        <v>4.825807571411133</v>
       </c>
       <c r="C81" t="n">
-        <v>5.126316881024188</v>
+        <v>5.126315867963532</v>
       </c>
       <c r="D81" t="n">
-        <v>4.790454650439884</v>
+        <v>4.790453703752186</v>
       </c>
       <c r="E81" t="n">
-        <v>5.073285647604409</v>
+        <v>5.073284645023764</v>
       </c>
       <c r="F81" t="n">
         <v>11282700</v>
@@ -2052,16 +2052,16 @@
         <v>44531</v>
       </c>
       <c r="B82" t="n">
-        <v>4.852322578430176</v>
+        <v>4.852322101593018</v>
       </c>
       <c r="C82" t="n">
-        <v>5.152830863649267</v>
+        <v>5.152830357281196</v>
       </c>
       <c r="D82" t="n">
-        <v>4.852322578430176</v>
+        <v>4.852322101593018</v>
       </c>
       <c r="E82" t="n">
-        <v>4.896515122062865</v>
+        <v>4.896514640882911</v>
       </c>
       <c r="F82" t="n">
         <v>12492100</v>
@@ -2072,16 +2072,16 @@
         <v>44532</v>
       </c>
       <c r="B83" t="n">
-        <v>5.029092788696289</v>
+        <v>5.029093265533447</v>
       </c>
       <c r="C83" t="n">
-        <v>5.029092788696289</v>
+        <v>5.029093265533447</v>
       </c>
       <c r="D83" t="n">
-        <v>4.746261410928263</v>
+        <v>4.746261860948556</v>
       </c>
       <c r="E83" t="n">
-        <v>4.905354245307752</v>
+        <v>4.905354710412548</v>
       </c>
       <c r="F83" t="n">
         <v>18379200</v>
@@ -2152,16 +2152,16 @@
         <v>44538</v>
       </c>
       <c r="B87" t="n">
-        <v>5.285407543182373</v>
+        <v>5.285408020019531</v>
       </c>
       <c r="C87" t="n">
-        <v>5.338438337353947</v>
+        <v>5.33843881897542</v>
       </c>
       <c r="D87" t="n">
-        <v>5.12631516066765</v>
+        <v>5.126315623151864</v>
       </c>
       <c r="E87" t="n">
-        <v>5.223538072589892</v>
+        <v>5.223538543845331</v>
       </c>
       <c r="F87" t="n">
         <v>9204000</v>
@@ -2192,16 +2192,16 @@
         <v>44540</v>
       </c>
       <c r="B89" t="n">
-        <v>5.444500923156738</v>
+        <v>5.44450044631958</v>
       </c>
       <c r="C89" t="n">
-        <v>5.568239887011294</v>
+        <v>5.568239399336901</v>
       </c>
       <c r="D89" t="n">
-        <v>5.241215964197243</v>
+        <v>5.241215505164072</v>
       </c>
       <c r="E89" t="n">
-        <v>5.267731576866467</v>
+        <v>5.267731115511021</v>
       </c>
       <c r="F89" t="n">
         <v>8741300</v>
@@ -2212,16 +2212,16 @@
         <v>44543</v>
       </c>
       <c r="B90" t="n">
-        <v>5.497531414031982</v>
+        <v>5.497531890869141</v>
       </c>
       <c r="C90" t="n">
-        <v>5.621270370841238</v>
+        <v>5.621270858411092</v>
       </c>
       <c r="D90" t="n">
-        <v>5.426823679541746</v>
+        <v>5.426824150245956</v>
       </c>
       <c r="E90" t="n">
-        <v>5.444500613164305</v>
+        <v>5.444501085401752</v>
       </c>
       <c r="F90" t="n">
         <v>8265100</v>
@@ -2272,16 +2272,16 @@
         <v>44546</v>
       </c>
       <c r="B93" t="n">
-        <v>5.400308132171631</v>
+        <v>5.400307655334473</v>
       </c>
       <c r="C93" t="n">
-        <v>5.550562268737735</v>
+        <v>5.550561778633416</v>
       </c>
       <c r="D93" t="n">
-        <v>5.347277334816178</v>
+        <v>5.347276862661541</v>
       </c>
       <c r="E93" t="n">
-        <v>5.515207982382787</v>
+        <v>5.515207495400186</v>
       </c>
       <c r="F93" t="n">
         <v>9238300</v>
@@ -2292,16 +2292,16 @@
         <v>44547</v>
       </c>
       <c r="B94" t="n">
-        <v>5.241215705871582</v>
+        <v>5.241215229034424</v>
       </c>
       <c r="C94" t="n">
-        <v>5.347277729869593</v>
+        <v>5.347277243383087</v>
       </c>
       <c r="D94" t="n">
-        <v>5.241215705871582</v>
+        <v>5.241215229034424</v>
       </c>
       <c r="E94" t="n">
-        <v>5.320762118507254</v>
+        <v>5.320761634433095</v>
       </c>
       <c r="F94" t="n">
         <v>50153800</v>
@@ -2312,16 +2312,16 @@
         <v>44550</v>
       </c>
       <c r="B95" t="n">
-        <v>5.14399242401123</v>
+        <v>5.143992900848389</v>
       </c>
       <c r="C95" t="n">
-        <v>5.179346289073743</v>
+        <v>5.179346769188129</v>
       </c>
       <c r="D95" t="n">
-        <v>4.949545744716101</v>
+        <v>4.949546203528466</v>
       </c>
       <c r="E95" t="n">
-        <v>5.179346289073743</v>
+        <v>5.179346769188129</v>
       </c>
       <c r="F95" t="n">
         <v>8433600</v>
@@ -2332,16 +2332,16 @@
         <v>44551</v>
       </c>
       <c r="B96" t="n">
-        <v>5.082122325897217</v>
+        <v>5.082122802734375</v>
       </c>
       <c r="C96" t="n">
-        <v>5.223537768796909</v>
+        <v>5.223538258902567</v>
       </c>
       <c r="D96" t="n">
-        <v>5.020252858902969</v>
+        <v>5.020253329935139</v>
       </c>
       <c r="E96" t="n">
-        <v>5.170506977709524</v>
+        <v>5.170507462839494</v>
       </c>
       <c r="F96" t="n">
         <v>5049800</v>
@@ -2352,16 +2352,16 @@
         <v>44552</v>
       </c>
       <c r="B97" t="n">
-        <v>5.011415004730225</v>
+        <v>5.011415481567383</v>
       </c>
       <c r="C97" t="n">
-        <v>5.07328405521495</v>
+        <v>5.073284537938961</v>
       </c>
       <c r="D97" t="n">
-        <v>4.914191669245416</v>
+        <v>4.914192136831755</v>
       </c>
       <c r="E97" t="n">
-        <v>5.055607123440558</v>
+        <v>5.055607604482605</v>
       </c>
       <c r="F97" t="n">
         <v>4649500</v>
@@ -2412,16 +2412,16 @@
         <v>44558</v>
       </c>
       <c r="B100" t="n">
-        <v>5.347278118133545</v>
+        <v>5.347277164459229</v>
       </c>
       <c r="C100" t="n">
-        <v>5.347278118133545</v>
+        <v>5.347277164459229</v>
       </c>
       <c r="D100" t="n">
-        <v>5.188185281310526</v>
+        <v>5.188184356010038</v>
       </c>
       <c r="E100" t="n">
-        <v>5.214700894598154</v>
+        <v>5.21469996456867</v>
       </c>
       <c r="F100" t="n">
         <v>4379800</v>
@@ -2452,16 +2452,16 @@
         <v>44560</v>
       </c>
       <c r="B102" t="n">
-        <v>5.700815677642822</v>
+        <v>5.700816631317139</v>
       </c>
       <c r="C102" t="n">
-        <v>5.709654354119633</v>
+        <v>5.709655309272549</v>
       </c>
       <c r="D102" t="n">
-        <v>5.258891968633261</v>
+        <v>5.258892848379334</v>
       </c>
       <c r="E102" t="n">
-        <v>5.320761439617065</v>
+        <v>5.320762329713117</v>
       </c>
       <c r="F102" t="n">
         <v>23096200</v>
@@ -2472,16 +2472,16 @@
         <v>44564</v>
       </c>
       <c r="B103" t="n">
-        <v>5.541723251342773</v>
+        <v>5.54172420501709</v>
       </c>
       <c r="C103" t="n">
-        <v>5.745008172775975</v>
+        <v>5.745009161433563</v>
       </c>
       <c r="D103" t="n">
-        <v>5.506369388611025</v>
+        <v>5.5063703362013</v>
       </c>
       <c r="E103" t="n">
-        <v>5.691977378678351</v>
+        <v>5.691978358209878</v>
       </c>
       <c r="F103" t="n">
         <v>7451800</v>
@@ -2492,16 +2492,16 @@
         <v>44565</v>
       </c>
       <c r="B104" t="n">
-        <v>5.594754695892334</v>
+        <v>5.594754219055176</v>
       </c>
       <c r="C104" t="n">
-        <v>5.612431629313347</v>
+        <v>5.612431150969596</v>
       </c>
       <c r="D104" t="n">
-        <v>5.444500551088055</v>
+        <v>5.444500087056956</v>
       </c>
       <c r="E104" t="n">
-        <v>5.532885639644457</v>
+        <v>5.532885168080356</v>
       </c>
       <c r="F104" t="n">
         <v>10613100</v>
@@ -2512,16 +2512,16 @@
         <v>44566</v>
       </c>
       <c r="B105" t="n">
-        <v>5.117476940155029</v>
+        <v>5.117477893829346</v>
       </c>
       <c r="C105" t="n">
-        <v>5.568239362948087</v>
+        <v>5.568240400624842</v>
       </c>
       <c r="D105" t="n">
-        <v>5.117476940155029</v>
+        <v>5.117477893829346</v>
       </c>
       <c r="E105" t="n">
-        <v>5.550562429982751</v>
+        <v>5.550563464365298</v>
       </c>
       <c r="F105" t="n">
         <v>7203400</v>
@@ -2552,16 +2552,16 @@
         <v>44568</v>
       </c>
       <c r="B107" t="n">
-        <v>5.163623332977295</v>
+        <v>5.163622379302979</v>
       </c>
       <c r="C107" t="n">
-        <v>5.278961673563245</v>
+        <v>5.278960698586984</v>
       </c>
       <c r="D107" t="n">
-        <v>4.941818213532458</v>
+        <v>4.941817300823532</v>
       </c>
       <c r="E107" t="n">
-        <v>4.977306998798857</v>
+        <v>4.977306079535475</v>
       </c>
       <c r="F107" t="n">
         <v>10961100</v>
@@ -2592,16 +2592,16 @@
         <v>44572</v>
       </c>
       <c r="B109" t="n">
-        <v>5.234600067138672</v>
+        <v>5.234599590301514</v>
       </c>
       <c r="C109" t="n">
-        <v>5.234600067138672</v>
+        <v>5.234599590301514</v>
       </c>
       <c r="D109" t="n">
-        <v>5.021666966502512</v>
+        <v>5.021666509062139</v>
       </c>
       <c r="E109" t="n">
-        <v>5.021666966502512</v>
+        <v>5.021666509062139</v>
       </c>
       <c r="F109" t="n">
         <v>5425200</v>
@@ -2652,16 +2652,16 @@
         <v>44575</v>
       </c>
       <c r="B112" t="n">
-        <v>5.491893768310547</v>
+        <v>5.491894245147705</v>
       </c>
       <c r="C112" t="n">
-        <v>5.500765751417357</v>
+        <v>5.500766229024832</v>
       </c>
       <c r="D112" t="n">
-        <v>5.332194264851456</v>
+        <v>5.332194727822603</v>
       </c>
       <c r="E112" t="n">
-        <v>5.420916211217618</v>
+        <v>5.420916681892105</v>
       </c>
       <c r="F112" t="n">
         <v>4745900</v>
@@ -2672,16 +2672,16 @@
         <v>44578</v>
       </c>
       <c r="B113" t="n">
-        <v>5.483022212982178</v>
+        <v>5.483021259307861</v>
       </c>
       <c r="C113" t="n">
-        <v>5.624977772255862</v>
+        <v>5.624976793890898</v>
       </c>
       <c r="D113" t="n">
-        <v>5.447533428928676</v>
+        <v>5.447532481427003</v>
       </c>
       <c r="E113" t="n">
-        <v>5.447533428928676</v>
+        <v>5.447532481427003</v>
       </c>
       <c r="F113" t="n">
         <v>3137800</v>
@@ -2692,16 +2692,16 @@
         <v>44579</v>
       </c>
       <c r="B114" t="n">
-        <v>5.483022212982178</v>
+        <v>5.483021259307861</v>
       </c>
       <c r="C114" t="n">
-        <v>5.53625538906243</v>
+        <v>5.536254426129148</v>
       </c>
       <c r="D114" t="n">
-        <v>5.376555860821671</v>
+        <v>5.376554925665286</v>
       </c>
       <c r="E114" t="n">
-        <v>5.47415022849864</v>
+        <v>5.474149276367449</v>
       </c>
       <c r="F114" t="n">
         <v>3854900</v>
@@ -2712,16 +2712,16 @@
         <v>44580</v>
       </c>
       <c r="B115" t="n">
-        <v>5.651593208312988</v>
+        <v>5.651593685150146</v>
       </c>
       <c r="C115" t="n">
-        <v>5.749187559749773</v>
+        <v>5.749188044821177</v>
       </c>
       <c r="D115" t="n">
-        <v>5.509638095721016</v>
+        <v>5.509638560581113</v>
       </c>
       <c r="E115" t="n">
-        <v>5.509638095721016</v>
+        <v>5.509638560581113</v>
       </c>
       <c r="F115" t="n">
         <v>12660500</v>
@@ -2732,16 +2732,16 @@
         <v>44581</v>
       </c>
       <c r="B116" t="n">
-        <v>5.713698387145996</v>
+        <v>5.713698863983154</v>
       </c>
       <c r="C116" t="n">
-        <v>5.837909102088854</v>
+        <v>5.837909589292028</v>
       </c>
       <c r="D116" t="n">
-        <v>5.633848430295799</v>
+        <v>5.633848900469072</v>
       </c>
       <c r="E116" t="n">
-        <v>5.651592818144779</v>
+        <v>5.651593289798911</v>
       </c>
       <c r="F116" t="n">
         <v>9343500</v>
@@ -2752,16 +2752,16 @@
         <v>44582</v>
       </c>
       <c r="B117" t="n">
-        <v>5.527382850646973</v>
+        <v>5.527382373809814</v>
       </c>
       <c r="C117" t="n">
-        <v>5.687082362883293</v>
+        <v>5.687081872269151</v>
       </c>
       <c r="D117" t="n">
-        <v>5.483021663495955</v>
+        <v>5.483021190485755</v>
       </c>
       <c r="E117" t="n">
-        <v>5.678210379288871</v>
+        <v>5.678209889440098</v>
       </c>
       <c r="F117" t="n">
         <v>7609900</v>
@@ -2772,16 +2772,16 @@
         <v>44585</v>
       </c>
       <c r="B118" t="n">
-        <v>5.456405162811279</v>
+        <v>5.456405639648438</v>
       </c>
       <c r="C118" t="n">
-        <v>5.491893942483253</v>
+        <v>5.491894422421788</v>
       </c>
       <c r="D118" t="n">
-        <v>5.349938823795358</v>
+        <v>5.349939291328385</v>
       </c>
       <c r="E118" t="n">
-        <v>5.465277146199461</v>
+        <v>5.465277623811945</v>
       </c>
       <c r="F118" t="n">
         <v>8531700</v>
@@ -2812,16 +2812,16 @@
         <v>44587</v>
       </c>
       <c r="B120" t="n">
-        <v>5.518509864807129</v>
+        <v>5.518511295318604</v>
       </c>
       <c r="C120" t="n">
-        <v>5.678209783342052</v>
+        <v>5.678211255251036</v>
       </c>
       <c r="D120" t="n">
-        <v>5.491893493757702</v>
+        <v>5.491894917369664</v>
       </c>
       <c r="E120" t="n">
-        <v>5.59835982407459</v>
+        <v>5.59836127528482</v>
       </c>
       <c r="F120" t="n">
         <v>11610000</v>
@@ -2872,16 +2872,16 @@
         <v>44592</v>
       </c>
       <c r="B123" t="n">
-        <v>5.695954322814941</v>
+        <v>5.6959547996521</v>
       </c>
       <c r="C123" t="n">
-        <v>5.793548673057267</v>
+        <v>5.793549158064543</v>
       </c>
       <c r="D123" t="n">
-        <v>5.571743600817181</v>
+        <v>5.571744067256032</v>
       </c>
       <c r="E123" t="n">
-        <v>5.607232378530827</v>
+        <v>5.607232847940623</v>
       </c>
       <c r="F123" t="n">
         <v>7514700</v>
@@ -2892,16 +2892,16 @@
         <v>44593</v>
       </c>
       <c r="B124" t="n">
-        <v>5.678210258483887</v>
+        <v>5.678210735321045</v>
       </c>
       <c r="C124" t="n">
-        <v>5.793549004174971</v>
+        <v>5.793549490697893</v>
       </c>
       <c r="D124" t="n">
-        <v>5.536254716456543</v>
+        <v>5.536255181372748</v>
       </c>
       <c r="E124" t="n">
-        <v>5.766932207838711</v>
+        <v>5.766932692126443</v>
       </c>
       <c r="F124" t="n">
         <v>8050400</v>
@@ -2912,16 +2912,16 @@
         <v>44594</v>
       </c>
       <c r="B125" t="n">
-        <v>5.669338226318359</v>
+        <v>5.669337749481201</v>
       </c>
       <c r="C125" t="n">
-        <v>5.882271341887785</v>
+        <v>5.882270847141231</v>
       </c>
       <c r="D125" t="n">
-        <v>5.651593835275879</v>
+        <v>5.651593359931167</v>
       </c>
       <c r="E125" t="n">
-        <v>5.722571399445803</v>
+        <v>5.722570918131304</v>
       </c>
       <c r="F125" t="n">
         <v>8808600</v>
@@ -2992,16 +2992,16 @@
         <v>44600</v>
       </c>
       <c r="B129" t="n">
-        <v>5.616104602813721</v>
+        <v>5.616105079650879</v>
       </c>
       <c r="C129" t="n">
-        <v>5.695954567631234</v>
+        <v>5.695955051248079</v>
       </c>
       <c r="D129" t="n">
-        <v>5.483021469137738</v>
+        <v>5.48302193467543</v>
       </c>
       <c r="E129" t="n">
-        <v>5.580615823574741</v>
+        <v>5.580616297398714</v>
       </c>
       <c r="F129" t="n">
         <v>9770800</v>
@@ -3012,16 +3012,16 @@
         <v>44601</v>
       </c>
       <c r="B130" t="n">
-        <v>5.633849143981934</v>
+        <v>5.633849620819092</v>
       </c>
       <c r="C130" t="n">
-        <v>5.740315484562782</v>
+        <v>5.740315970411027</v>
       </c>
       <c r="D130" t="n">
-        <v>5.58948838026973</v>
+        <v>5.589488853352285</v>
       </c>
       <c r="E130" t="n">
-        <v>5.616104753885126</v>
+        <v>5.616105229220436</v>
       </c>
       <c r="F130" t="n">
         <v>8867400</v>
@@ -3032,16 +3032,16 @@
         <v>44602</v>
       </c>
       <c r="B131" t="n">
-        <v>5.704826354980469</v>
+        <v>5.704826831817627</v>
       </c>
       <c r="C131" t="n">
-        <v>5.740315133000595</v>
+        <v>5.740315612804078</v>
       </c>
       <c r="D131" t="n">
-        <v>5.562871242899961</v>
+        <v>5.56287170787182</v>
       </c>
       <c r="E131" t="n">
-        <v>5.678209982995176</v>
+        <v>5.678210457607609</v>
       </c>
       <c r="F131" t="n">
         <v>9667400</v>
@@ -3052,16 +3052,16 @@
         <v>44603</v>
       </c>
       <c r="B132" t="n">
-        <v>5.633849143981934</v>
+        <v>5.633849620819092</v>
       </c>
       <c r="C132" t="n">
-        <v>5.775804687816029</v>
+        <v>5.775805176668006</v>
       </c>
       <c r="D132" t="n">
-        <v>5.58948838026973</v>
+        <v>5.589488853352285</v>
       </c>
       <c r="E132" t="n">
-        <v>5.731443501044193</v>
+        <v>5.731443986141532</v>
       </c>
       <c r="F132" t="n">
         <v>8001300</v>
@@ -3072,16 +3072,16 @@
         <v>44606</v>
       </c>
       <c r="B133" t="n">
-        <v>5.695954322814941</v>
+        <v>5.6959547996521</v>
       </c>
       <c r="C133" t="n">
-        <v>5.766931878242232</v>
+        <v>5.766932361021281</v>
       </c>
       <c r="D133" t="n">
-        <v>5.642721156244472</v>
+        <v>5.642721628625214</v>
       </c>
       <c r="E133" t="n">
-        <v>5.642721156244472</v>
+        <v>5.642721628625214</v>
       </c>
       <c r="F133" t="n">
         <v>12680200</v>
@@ -3092,16 +3092,16 @@
         <v>44607</v>
       </c>
       <c r="B134" t="n">
-        <v>5.695954322814941</v>
+        <v>5.6959547996521</v>
       </c>
       <c r="C134" t="n">
-        <v>5.81129306191409</v>
+        <v>5.811293548406838</v>
       </c>
       <c r="D134" t="n">
-        <v>5.518510011187112</v>
+        <v>5.518510473169509</v>
       </c>
       <c r="E134" t="n">
-        <v>5.81129306191409</v>
+        <v>5.811293548406838</v>
       </c>
       <c r="F134" t="n">
         <v>17426200</v>
@@ -3112,16 +3112,16 @@
         <v>44608</v>
       </c>
       <c r="B135" t="n">
-        <v>5.704826354980469</v>
+        <v>5.704826831817627</v>
       </c>
       <c r="C135" t="n">
-        <v>5.811293112100454</v>
+        <v>5.811293597836623</v>
       </c>
       <c r="D135" t="n">
-        <v>5.651593187950278</v>
+        <v>5.651593660337949</v>
       </c>
       <c r="E135" t="n">
-        <v>5.713698761015302</v>
+        <v>5.71369923859406</v>
       </c>
       <c r="F135" t="n">
         <v>12029900</v>
@@ -3192,16 +3192,16 @@
         <v>44614</v>
       </c>
       <c r="B139" t="n">
-        <v>5.012794494628906</v>
+        <v>5.012795448303223</v>
       </c>
       <c r="C139" t="n">
-        <v>5.234599557019038</v>
+        <v>5.234600552891333</v>
       </c>
       <c r="D139" t="n">
-        <v>4.977305718491252</v>
+        <v>4.977306665413898</v>
       </c>
       <c r="E139" t="n">
-        <v>5.172493987248352</v>
+        <v>5.172494971305183</v>
       </c>
       <c r="F139" t="n">
         <v>7346000</v>
@@ -3212,16 +3212,16 @@
         <v>44615</v>
       </c>
       <c r="B140" t="n">
-        <v>5.021666526794434</v>
+        <v>5.021667003631592</v>
       </c>
       <c r="C140" t="n">
-        <v>5.10151648542361</v>
+        <v>5.101516969842998</v>
       </c>
       <c r="D140" t="n">
-        <v>4.968433362061512</v>
+        <v>4.968433833843864</v>
       </c>
       <c r="E140" t="n">
-        <v>5.057155303283048</v>
+        <v>5.057155783490078</v>
       </c>
       <c r="F140" t="n">
         <v>10772600</v>
@@ -3292,16 +3292,16 @@
         <v>44623</v>
       </c>
       <c r="B144" t="n">
-        <v>5.465277194976807</v>
+        <v>5.465277671813965</v>
       </c>
       <c r="C144" t="n">
-        <v>5.545127161481217</v>
+        <v>5.545127645285164</v>
       </c>
       <c r="D144" t="n">
-        <v>5.323322075021968</v>
+        <v>5.323322539473757</v>
       </c>
       <c r="E144" t="n">
-        <v>5.323322075021968</v>
+        <v>5.323322539473757</v>
       </c>
       <c r="F144" t="n">
         <v>18057800</v>
@@ -3312,16 +3312,16 @@
         <v>44624</v>
       </c>
       <c r="B145" t="n">
-        <v>5.509637832641602</v>
+        <v>5.50963830947876</v>
       </c>
       <c r="C145" t="n">
-        <v>5.53625420345189</v>
+        <v>5.536254682592588</v>
       </c>
       <c r="D145" t="n">
-        <v>5.376554709411403</v>
+        <v>5.376555174730749</v>
       </c>
       <c r="E145" t="n">
-        <v>5.483021038771727</v>
+        <v>5.483021513305308</v>
       </c>
       <c r="F145" t="n">
         <v>9336900</v>
@@ -3332,16 +3332,16 @@
         <v>44627</v>
       </c>
       <c r="B146" t="n">
-        <v>5.483022212982178</v>
+        <v>5.483021259307861</v>
       </c>
       <c r="C146" t="n">
-        <v>5.58948898820236</v>
+        <v>5.58948801601004</v>
       </c>
       <c r="D146" t="n">
-        <v>5.403172660391636</v>
+        <v>5.403171720605732</v>
       </c>
       <c r="E146" t="n">
-        <v>5.491894620525391</v>
+        <v>5.491893665307877</v>
       </c>
       <c r="F146" t="n">
         <v>12429900</v>
@@ -3352,16 +3352,16 @@
         <v>44628</v>
       </c>
       <c r="B147" t="n">
-        <v>5.58948802947998</v>
+        <v>5.589488983154297</v>
       </c>
       <c r="C147" t="n">
-        <v>5.58948802947998</v>
+        <v>5.589488983154297</v>
       </c>
       <c r="D147" t="n">
-        <v>5.420916122609865</v>
+        <v>5.420917047522567</v>
       </c>
       <c r="E147" t="n">
-        <v>5.500765661504422</v>
+        <v>5.500766600040993</v>
       </c>
       <c r="F147" t="n">
         <v>5566500</v>
@@ -3372,16 +3372,16 @@
         <v>44629</v>
       </c>
       <c r="B148" t="n">
-        <v>5.695954322814941</v>
+        <v>5.6959547996521</v>
       </c>
       <c r="C148" t="n">
-        <v>5.704826305713552</v>
+        <v>5.704826783293429</v>
       </c>
       <c r="D148" t="n">
-        <v>5.553999211960359</v>
+        <v>5.553999676913737</v>
       </c>
       <c r="E148" t="n">
-        <v>5.589487989674004</v>
+        <v>5.589488457598327</v>
       </c>
       <c r="F148" t="n">
         <v>9079900</v>
@@ -3392,16 +3392,16 @@
         <v>44630</v>
       </c>
       <c r="B149" t="n">
-        <v>5.695954322814941</v>
+        <v>5.6959547996521</v>
       </c>
       <c r="C149" t="n">
-        <v>5.829037450770913</v>
+        <v>5.829037938749134</v>
       </c>
       <c r="D149" t="n">
-        <v>5.553999211960359</v>
+        <v>5.553999676913737</v>
       </c>
       <c r="E149" t="n">
-        <v>5.62497676738765</v>
+        <v>5.624977238282918</v>
       </c>
       <c r="F149" t="n">
         <v>15215200</v>
@@ -3412,16 +3412,16 @@
         <v>44631</v>
       </c>
       <c r="B150" t="n">
-        <v>5.598360538482666</v>
+        <v>5.598360061645508</v>
       </c>
       <c r="C150" t="n">
-        <v>5.979865148998535</v>
+        <v>5.97986463966694</v>
       </c>
       <c r="D150" t="n">
-        <v>5.52738297588061</v>
+        <v>5.527382505088926</v>
       </c>
       <c r="E150" t="n">
-        <v>5.695954898590315</v>
+        <v>5.695954413440612</v>
       </c>
       <c r="F150" t="n">
         <v>16712700</v>
@@ -3432,16 +3432,16 @@
         <v>44634</v>
       </c>
       <c r="B151" t="n">
-        <v>5.58948802947998</v>
+        <v>5.589488983154297</v>
       </c>
       <c r="C151" t="n">
-        <v>5.72257073532411</v>
+        <v>5.7225717117049</v>
       </c>
       <c r="D151" t="n">
-        <v>5.518510050487613</v>
+        <v>5.518510992051719</v>
       </c>
       <c r="E151" t="n">
-        <v>5.607232418463171</v>
+        <v>5.607233375165023</v>
       </c>
       <c r="F151" t="n">
         <v>7706100</v>
@@ -3452,16 +3452,16 @@
         <v>44635</v>
       </c>
       <c r="B152" t="n">
-        <v>5.651593208312988</v>
+        <v>5.651593685150146</v>
       </c>
       <c r="C152" t="n">
-        <v>5.687081986460981</v>
+        <v>5.687082466292404</v>
       </c>
       <c r="D152" t="n">
-        <v>5.500765689654214</v>
+        <v>5.500766153765728</v>
       </c>
       <c r="E152" t="n">
-        <v>5.509638095721016</v>
+        <v>5.509638560581113</v>
       </c>
       <c r="F152" t="n">
         <v>5880900</v>
@@ -3472,16 +3472,16 @@
         <v>44636</v>
       </c>
       <c r="B153" t="n">
-        <v>5.62497615814209</v>
+        <v>5.624977111816406</v>
       </c>
       <c r="C153" t="n">
-        <v>5.766931253621405</v>
+        <v>5.766932231363189</v>
       </c>
       <c r="D153" t="n">
-        <v>5.518509413473048</v>
+        <v>5.518510349096693</v>
       </c>
       <c r="E153" t="n">
-        <v>5.713698092816662</v>
+        <v>5.713699061533146</v>
       </c>
       <c r="F153" t="n">
         <v>10739100</v>
@@ -3492,16 +3492,16 @@
         <v>44637</v>
       </c>
       <c r="B154" t="n">
-        <v>5.891142845153809</v>
+        <v>5.891143798828125</v>
       </c>
       <c r="C154" t="n">
-        <v>5.926631624342837</v>
+        <v>5.926632583762174</v>
       </c>
       <c r="D154" t="n">
-        <v>5.536254630203903</v>
+        <v>5.536255526427944</v>
       </c>
       <c r="E154" t="n">
-        <v>5.607232611641579</v>
+        <v>5.607233519355731</v>
       </c>
       <c r="F154" t="n">
         <v>10001800</v>
@@ -3512,16 +3512,16 @@
         <v>44638</v>
       </c>
       <c r="B155" t="n">
-        <v>6.20167064666748</v>
+        <v>6.201669692993164</v>
       </c>
       <c r="C155" t="n">
-        <v>6.20167064666748</v>
+        <v>6.201669692993164</v>
       </c>
       <c r="D155" t="n">
-        <v>5.891143578574458</v>
+        <v>5.891142672652063</v>
       </c>
       <c r="E155" t="n">
-        <v>5.891143578574458</v>
+        <v>5.891142672652063</v>
       </c>
       <c r="F155" t="n">
         <v>17710700</v>
@@ -3532,16 +3532,16 @@
         <v>44641</v>
       </c>
       <c r="B156" t="n">
-        <v>6.104075908660889</v>
+        <v>6.104076385498047</v>
       </c>
       <c r="C156" t="n">
-        <v>6.34362537835539</v>
+        <v>6.343625873905633</v>
       </c>
       <c r="D156" t="n">
-        <v>6.024225944409515</v>
+        <v>6.024226415008968</v>
       </c>
       <c r="E156" t="n">
-        <v>6.183925449852644</v>
+        <v>6.183925932927476</v>
       </c>
       <c r="F156" t="n">
         <v>14982100</v>
@@ -3552,16 +3552,16 @@
         <v>44642</v>
       </c>
       <c r="B157" t="n">
-        <v>6.299263954162598</v>
+        <v>6.299264907836914</v>
       </c>
       <c r="C157" t="n">
-        <v>6.308136360102719</v>
+        <v>6.30813731512027</v>
       </c>
       <c r="D157" t="n">
-        <v>6.077458882374763</v>
+        <v>6.077459802468997</v>
       </c>
       <c r="E157" t="n">
-        <v>6.077458882374763</v>
+        <v>6.077459802468997</v>
       </c>
       <c r="F157" t="n">
         <v>9703800</v>
@@ -3572,16 +3572,16 @@
         <v>44643</v>
       </c>
       <c r="B158" t="n">
-        <v>6.308136940002441</v>
+        <v>6.308136463165283</v>
       </c>
       <c r="C158" t="n">
-        <v>6.334753314150418</v>
+        <v>6.334752835301306</v>
       </c>
       <c r="D158" t="n">
-        <v>6.201670174231618</v>
+        <v>6.201669705442368</v>
       </c>
       <c r="E158" t="n">
-        <v>6.263775752342961</v>
+        <v>6.263775278859101</v>
       </c>
       <c r="F158" t="n">
         <v>8187500</v>
@@ -3592,16 +3592,16 @@
         <v>44644</v>
       </c>
       <c r="B159" t="n">
-        <v>6.343626022338867</v>
+        <v>6.343625545501709</v>
       </c>
       <c r="C159" t="n">
-        <v>6.432347978814025</v>
+        <v>6.432347495307822</v>
       </c>
       <c r="D159" t="n">
-        <v>6.25490406586371</v>
+        <v>6.254903595695596</v>
       </c>
       <c r="E159" t="n">
-        <v>6.299264832571459</v>
+        <v>6.299264359068839</v>
       </c>
       <c r="F159" t="n">
         <v>11578200</v>
@@ -3612,16 +3612,16 @@
         <v>44645</v>
       </c>
       <c r="B160" t="n">
-        <v>6.45009183883667</v>
+        <v>6.450092315673828</v>
       </c>
       <c r="C160" t="n">
-        <v>6.512197414783683</v>
+        <v>6.512197896212132</v>
       </c>
       <c r="D160" t="n">
-        <v>6.237159160834839</v>
+        <v>6.237159621930483</v>
       </c>
       <c r="E160" t="n">
-        <v>6.343625499835754</v>
+        <v>6.343625968802155</v>
       </c>
       <c r="F160" t="n">
         <v>15324200</v>
@@ -3672,16 +3672,16 @@
         <v>44650</v>
       </c>
       <c r="B163" t="n">
-        <v>6.503325462341309</v>
+        <v>6.50332498550415</v>
       </c>
       <c r="C163" t="n">
-        <v>6.618664215840703</v>
+        <v>6.61866373054667</v>
       </c>
       <c r="D163" t="n">
-        <v>6.450092289124586</v>
+        <v>6.450091816190593</v>
       </c>
       <c r="E163" t="n">
-        <v>6.547686651551738</v>
+        <v>6.547686171461927</v>
       </c>
       <c r="F163" t="n">
         <v>10697600</v>
@@ -3712,16 +3712,16 @@
         <v>44652</v>
       </c>
       <c r="B165" t="n">
-        <v>6.139564990997314</v>
+        <v>6.139564514160156</v>
       </c>
       <c r="C165" t="n">
-        <v>6.299264504331019</v>
+        <v>6.299264015090594</v>
       </c>
       <c r="D165" t="n">
-        <v>5.926631883492739</v>
+        <v>5.926631423193302</v>
       </c>
       <c r="E165" t="n">
-        <v>6.254903739934808</v>
+        <v>6.254903254139719</v>
       </c>
       <c r="F165" t="n">
         <v>18919700</v>
@@ -3732,16 +3732,16 @@
         <v>44655</v>
       </c>
       <c r="B166" t="n">
-        <v>6.210542678833008</v>
+        <v>6.210543155670166</v>
       </c>
       <c r="C166" t="n">
-        <v>6.237159476459965</v>
+        <v>6.237159955340726</v>
       </c>
       <c r="D166" t="n">
-        <v>6.050843162250203</v>
+        <v>6.050843626825847</v>
       </c>
       <c r="E166" t="n">
-        <v>6.15730950663874</v>
+        <v>6.157309979388726</v>
       </c>
       <c r="F166" t="n">
         <v>13343800</v>
@@ -3752,16 +3752,16 @@
         <v>44656</v>
       </c>
       <c r="B167" t="n">
-        <v>6.299263954162598</v>
+        <v>6.299264907836914</v>
       </c>
       <c r="C167" t="n">
-        <v>6.325880748923362</v>
+        <v>6.325881706627317</v>
       </c>
       <c r="D167" t="n">
-        <v>6.148436437657334</v>
+        <v>6.148437368497184</v>
       </c>
       <c r="E167" t="n">
-        <v>6.228286398880027</v>
+        <v>6.228287341808727</v>
       </c>
       <c r="F167" t="n">
         <v>6962400</v>
@@ -3792,16 +3792,16 @@
         <v>44658</v>
       </c>
       <c r="B169" t="n">
-        <v>6.261641025543213</v>
+        <v>6.261641502380371</v>
       </c>
       <c r="C169" t="n">
-        <v>6.395246109067186</v>
+        <v>6.395246596078652</v>
       </c>
       <c r="D169" t="n">
-        <v>6.208198482469381</v>
+        <v>6.208198955236777</v>
       </c>
       <c r="E169" t="n">
-        <v>6.323989951262346</v>
+        <v>6.323990432847507</v>
       </c>
       <c r="F169" t="n">
         <v>10216600</v>
@@ -3812,16 +3812,16 @@
         <v>44659</v>
       </c>
       <c r="B170" t="n">
-        <v>6.190384387969971</v>
+        <v>6.190385341644287</v>
       </c>
       <c r="C170" t="n">
-        <v>6.323989895026054</v>
+        <v>6.323990869283284</v>
       </c>
       <c r="D170" t="n">
-        <v>6.136942270091576</v>
+        <v>6.136943215532741</v>
       </c>
       <c r="E170" t="n">
-        <v>6.234919698562065</v>
+        <v>6.234920659097374</v>
       </c>
       <c r="F170" t="n">
         <v>10722400</v>
@@ -3832,16 +3832,16 @@
         <v>44662</v>
       </c>
       <c r="B171" t="n">
-        <v>6.14585018157959</v>
+        <v>6.145850658416748</v>
       </c>
       <c r="C171" t="n">
-        <v>6.21710634662882</v>
+        <v>6.21710682899452</v>
       </c>
       <c r="D171" t="n">
-        <v>6.021151892743435</v>
+        <v>6.021152359905646</v>
       </c>
       <c r="E171" t="n">
-        <v>6.119128907326005</v>
+        <v>6.119129382089944</v>
       </c>
       <c r="F171" t="n">
         <v>4955900</v>
@@ -3852,16 +3852,16 @@
         <v>44663</v>
       </c>
       <c r="B172" t="n">
-        <v>6.217106819152832</v>
+        <v>6.217105865478516</v>
       </c>
       <c r="C172" t="n">
-        <v>6.359619160082779</v>
+        <v>6.359618184547754</v>
       </c>
       <c r="D172" t="n">
-        <v>6.145850648687858</v>
+        <v>6.145849705943896</v>
       </c>
       <c r="E172" t="n">
-        <v>6.190385542868328</v>
+        <v>6.190384593292927</v>
       </c>
       <c r="F172" t="n">
         <v>15598900</v>
@@ -3892,16 +3892,16 @@
         <v>44665</v>
       </c>
       <c r="B174" t="n">
-        <v>6.323990345001221</v>
+        <v>6.323990821838379</v>
       </c>
       <c r="C174" t="n">
-        <v>6.350711618201833</v>
+        <v>6.350712097053812</v>
       </c>
       <c r="D174" t="n">
-        <v>6.226012909559278</v>
+        <v>6.226013379008809</v>
       </c>
       <c r="E174" t="n">
-        <v>6.297269496520836</v>
+        <v>6.297269971343208</v>
       </c>
       <c r="F174" t="n">
         <v>4947000</v>
@@ -3932,16 +3932,16 @@
         <v>44670</v>
       </c>
       <c r="B176" t="n">
-        <v>6.190384387969971</v>
+        <v>6.190385341644287</v>
       </c>
       <c r="C176" t="n">
-        <v>6.413060091490044</v>
+        <v>6.413061079469193</v>
       </c>
       <c r="D176" t="n">
-        <v>6.181477580683671</v>
+        <v>6.181478532985828</v>
       </c>
       <c r="E176" t="n">
-        <v>6.35961797361165</v>
+        <v>6.359618953357647</v>
       </c>
       <c r="F176" t="n">
         <v>12659600</v>
@@ -3952,16 +3952,16 @@
         <v>44671</v>
       </c>
       <c r="B177" t="n">
-        <v>6.208198547363281</v>
+        <v>6.208199024200439</v>
       </c>
       <c r="C177" t="n">
-        <v>6.279455130633163</v>
+        <v>6.279455612943373</v>
       </c>
       <c r="D177" t="n">
-        <v>6.11022154171758</v>
+        <v>6.110222011029355</v>
       </c>
       <c r="E177" t="n">
-        <v>6.190384507725862</v>
+        <v>6.190384983194765</v>
       </c>
       <c r="F177" t="n">
         <v>7897000</v>
@@ -3972,16 +3972,16 @@
         <v>44673</v>
       </c>
       <c r="B178" t="n">
-        <v>6.128035545349121</v>
+        <v>6.128036022186279</v>
       </c>
       <c r="C178" t="n">
-        <v>6.190384471353647</v>
+        <v>6.190384953042324</v>
       </c>
       <c r="D178" t="n">
-        <v>5.98552280436691</v>
+        <v>5.98552327011481</v>
       </c>
       <c r="E178" t="n">
-        <v>6.136942352755394</v>
+        <v>6.136942830285612</v>
       </c>
       <c r="F178" t="n">
         <v>9926800</v>
@@ -3992,16 +3992,16 @@
         <v>44676</v>
       </c>
       <c r="B179" t="n">
-        <v>6.279455184936523</v>
+        <v>6.279455661773682</v>
       </c>
       <c r="C179" t="n">
-        <v>6.306176032263624</v>
+        <v>6.306176511129858</v>
       </c>
       <c r="D179" t="n">
-        <v>6.038965435391561</v>
+        <v>6.038965893966873</v>
       </c>
       <c r="E179" t="n">
-        <v>6.047872242927192</v>
+        <v>6.047872702178851</v>
       </c>
       <c r="F179" t="n">
         <v>9340700</v>
@@ -4032,16 +4032,16 @@
         <v>44678</v>
       </c>
       <c r="B181" t="n">
-        <v>6.332898139953613</v>
+        <v>6.332897186279297</v>
       </c>
       <c r="C181" t="n">
-        <v>6.359618990806601</v>
+        <v>6.359618033108378</v>
       </c>
       <c r="D181" t="n">
-        <v>6.20819942023878</v>
+        <v>6.208198485342908</v>
       </c>
       <c r="E181" t="n">
-        <v>6.288362822238278</v>
+        <v>6.288361875270557</v>
       </c>
       <c r="F181" t="n">
         <v>11357200</v>
@@ -4052,16 +4052,16 @@
         <v>44679</v>
       </c>
       <c r="B182" t="n">
-        <v>6.404153823852539</v>
+        <v>6.404154300689697</v>
       </c>
       <c r="C182" t="n">
-        <v>6.404153823852539</v>
+        <v>6.404154300689697</v>
       </c>
       <c r="D182" t="n">
-        <v>6.217106183156411</v>
+        <v>6.217106646066473</v>
       </c>
       <c r="E182" t="n">
-        <v>6.332897660676916</v>
+        <v>6.33289813220852</v>
       </c>
       <c r="F182" t="n">
         <v>9691200</v>
@@ -4072,16 +4072,16 @@
         <v>44680</v>
       </c>
       <c r="B183" t="n">
-        <v>6.14585018157959</v>
+        <v>6.145850658416748</v>
       </c>
       <c r="C183" t="n">
-        <v>6.44868888303882</v>
+        <v>6.44868938337228</v>
       </c>
       <c r="D183" t="n">
-        <v>6.065686783539082</v>
+        <v>6.065687254156614</v>
       </c>
       <c r="E183" t="n">
-        <v>6.413060800514205</v>
+        <v>6.413061298083393</v>
       </c>
       <c r="F183" t="n">
         <v>21979100</v>
@@ -4092,16 +4092,16 @@
         <v>44683</v>
       </c>
       <c r="B184" t="n">
-        <v>5.869731903076172</v>
+        <v>5.86973237991333</v>
       </c>
       <c r="C184" t="n">
-        <v>6.19038462249456</v>
+        <v>6.19038512538046</v>
       </c>
       <c r="D184" t="n">
-        <v>5.745033198582139</v>
+        <v>5.745033665289197</v>
       </c>
       <c r="E184" t="n">
-        <v>6.145849734935447</v>
+        <v>6.145850234203484</v>
       </c>
       <c r="F184" t="n">
         <v>12404500</v>
@@ -4132,16 +4132,16 @@
         <v>44685</v>
       </c>
       <c r="B186" t="n">
-        <v>5.388752937316895</v>
+        <v>5.388752460479736</v>
       </c>
       <c r="C186" t="n">
-        <v>5.513451229542335</v>
+        <v>5.51345074167094</v>
       </c>
       <c r="D186" t="n">
-        <v>5.210612095131722</v>
+        <v>5.210611634057798</v>
       </c>
       <c r="E186" t="n">
-        <v>5.513451229542335</v>
+        <v>5.51345074167094</v>
       </c>
       <c r="F186" t="n">
         <v>18834300</v>
@@ -4152,16 +4152,16 @@
         <v>44686</v>
       </c>
       <c r="B187" t="n">
-        <v>4.943401336669922</v>
+        <v>4.943400859832764</v>
       </c>
       <c r="C187" t="n">
-        <v>5.379845560141698</v>
+        <v>5.379845041205424</v>
       </c>
       <c r="D187" t="n">
-        <v>4.925587295400058</v>
+        <v>4.925586820281231</v>
       </c>
       <c r="E187" t="n">
-        <v>5.379845560141698</v>
+        <v>5.379845041205424</v>
       </c>
       <c r="F187" t="n">
         <v>16863600</v>
@@ -4172,16 +4172,16 @@
         <v>44687</v>
       </c>
       <c r="B188" t="n">
-        <v>4.952308654785156</v>
+        <v>4.952308177947998</v>
       </c>
       <c r="C188" t="n">
-        <v>5.068100147320131</v>
+        <v>5.068099659333893</v>
       </c>
       <c r="D188" t="n">
-        <v>4.863238439266056</v>
+        <v>4.863237971005097</v>
       </c>
       <c r="E188" t="n">
-        <v>4.970122697888977</v>
+        <v>4.970122219336578</v>
       </c>
       <c r="F188" t="n">
         <v>14479200</v>
@@ -4212,16 +4212,16 @@
         <v>44691</v>
       </c>
       <c r="B190" t="n">
-        <v>4.631654739379883</v>
+        <v>4.631655216217041</v>
       </c>
       <c r="C190" t="n">
-        <v>4.711818133335377</v>
+        <v>4.7118186184255</v>
       </c>
       <c r="D190" t="n">
-        <v>4.569305810499142</v>
+        <v>4.569306280917366</v>
       </c>
       <c r="E190" t="n">
-        <v>4.658376012271789</v>
+        <v>4.65837649185995</v>
       </c>
       <c r="F190" t="n">
         <v>9825600</v>
@@ -4272,16 +4272,16 @@
         <v>44694</v>
       </c>
       <c r="B193" t="n">
-        <v>4.604934215545654</v>
+        <v>4.604933738708496</v>
       </c>
       <c r="C193" t="n">
-        <v>4.800888673247058</v>
+        <v>4.800888176118977</v>
       </c>
       <c r="D193" t="n">
-        <v>4.515864007499562</v>
+        <v>4.51586353988555</v>
       </c>
       <c r="E193" t="n">
-        <v>4.800888673247058</v>
+        <v>4.800888176118977</v>
       </c>
       <c r="F193" t="n">
         <v>51332400</v>
@@ -4312,16 +4312,16 @@
         <v>44698</v>
       </c>
       <c r="B195" t="n">
-        <v>5.005749702453613</v>
+        <v>5.005750179290771</v>
       </c>
       <c r="C195" t="n">
-        <v>5.183890519719414</v>
+        <v>5.183891013525891</v>
       </c>
       <c r="D195" t="n">
-        <v>4.881051427671691</v>
+        <v>4.881051892630355</v>
       </c>
       <c r="E195" t="n">
-        <v>4.952307584689932</v>
+        <v>4.952308056436308</v>
       </c>
       <c r="F195" t="n">
         <v>40878000</v>
@@ -4332,16 +4332,16 @@
         <v>44699</v>
       </c>
       <c r="B196" t="n">
-        <v>4.952308654785156</v>
+        <v>4.952308177947998</v>
       </c>
       <c r="C196" t="n">
-        <v>5.112635042719536</v>
+        <v>5.112634550445218</v>
       </c>
       <c r="D196" t="n">
-        <v>4.898866525473696</v>
+        <v>4.898866053782258</v>
       </c>
       <c r="E196" t="n">
-        <v>4.987936740992796</v>
+        <v>4.987936260725158</v>
       </c>
       <c r="F196" t="n">
         <v>17779600</v>
@@ -4412,16 +4412,16 @@
         <v>44705</v>
       </c>
       <c r="B200" t="n">
-        <v>5.157169342041016</v>
+        <v>5.157169818878174</v>
       </c>
       <c r="C200" t="n">
-        <v>5.201704653345494</v>
+        <v>5.201705134300433</v>
       </c>
       <c r="D200" t="n">
-        <v>4.961214906685765</v>
+        <v>4.961215365404775</v>
       </c>
       <c r="E200" t="n">
-        <v>4.979028946263514</v>
+        <v>4.979029406629629</v>
       </c>
       <c r="F200" t="n">
         <v>9007600</v>
@@ -4452,16 +4452,16 @@
         <v>44707</v>
       </c>
       <c r="B202" t="n">
-        <v>5.504544258117676</v>
+        <v>5.504543304443359</v>
       </c>
       <c r="C202" t="n">
-        <v>5.647057023588098</v>
+        <v>5.647056045223134</v>
       </c>
       <c r="D202" t="n">
-        <v>5.281868513335436</v>
+        <v>5.281867598240178</v>
       </c>
       <c r="E202" t="n">
-        <v>5.281868513335436</v>
+        <v>5.281867598240178</v>
       </c>
       <c r="F202" t="n">
         <v>14781100</v>
@@ -4532,16 +4532,16 @@
         <v>44713</v>
       </c>
       <c r="B206" t="n">
-        <v>5.513450622558594</v>
+        <v>5.513451099395752</v>
       </c>
       <c r="C206" t="n">
-        <v>5.54907870212923</v>
+        <v>5.549079182047723</v>
       </c>
       <c r="D206" t="n">
-        <v>5.406566383846685</v>
+        <v>5.406566851439836</v>
       </c>
       <c r="E206" t="n">
-        <v>5.495636582773276</v>
+        <v>5.495637058069765</v>
       </c>
       <c r="F206" t="n">
         <v>9091200</v>
@@ -4552,16 +4552,16 @@
         <v>44714</v>
       </c>
       <c r="B207" t="n">
-        <v>5.611427783966064</v>
+        <v>5.611428737640381</v>
       </c>
       <c r="C207" t="n">
-        <v>5.65596266892822</v>
+        <v>5.655963630171337</v>
       </c>
       <c r="D207" t="n">
-        <v>5.504543125672473</v>
+        <v>5.50454406118151</v>
       </c>
       <c r="E207" t="n">
-        <v>5.549078435354819</v>
+        <v>5.549079378432728</v>
       </c>
       <c r="F207" t="n">
         <v>14163200</v>
@@ -4572,16 +4572,16 @@
         <v>44715</v>
       </c>
       <c r="B208" t="n">
-        <v>5.513450622558594</v>
+        <v>5.513451099395752</v>
       </c>
       <c r="C208" t="n">
-        <v>5.602520821485185</v>
+        <v>5.602521306025682</v>
       </c>
       <c r="D208" t="n">
-        <v>5.451101270949875</v>
+        <v>5.451101742394677</v>
       </c>
       <c r="E208" t="n">
-        <v>5.575799974167312</v>
+        <v>5.575800456396826</v>
       </c>
       <c r="F208" t="n">
         <v>9326300</v>
@@ -4652,16 +4652,16 @@
         <v>44721</v>
       </c>
       <c r="B212" t="n">
-        <v>4.818702697753906</v>
+        <v>4.818702220916748</v>
       </c>
       <c r="C212" t="n">
-        <v>4.996843537934095</v>
+        <v>4.996843043468919</v>
       </c>
       <c r="D212" t="n">
-        <v>4.809795889341036</v>
+        <v>4.809795413385255</v>
       </c>
       <c r="E212" t="n">
-        <v>4.88105205552501</v>
+        <v>4.881051572518039</v>
       </c>
       <c r="F212" t="n">
         <v>8480000</v>
@@ -4692,16 +4692,16 @@
         <v>44725</v>
       </c>
       <c r="B214" t="n">
-        <v>4.569305896759033</v>
+        <v>4.569305419921875</v>
       </c>
       <c r="C214" t="n">
-        <v>4.676190140903983</v>
+        <v>4.67618965291275</v>
       </c>
       <c r="D214" t="n">
-        <v>4.50695654198103</v>
+        <v>4.506956071650437</v>
       </c>
       <c r="E214" t="n">
-        <v>4.631654826816805</v>
+        <v>4.631654343473125</v>
       </c>
       <c r="F214" t="n">
         <v>7709600</v>
@@ -4752,16 +4752,16 @@
         <v>44729</v>
       </c>
       <c r="B217" t="n">
-        <v>4.524771213531494</v>
+        <v>4.524770259857178</v>
       </c>
       <c r="C217" t="n">
-        <v>4.524771213531494</v>
+        <v>4.524770259857178</v>
       </c>
       <c r="D217" t="n">
-        <v>4.311002695437231</v>
+        <v>4.311001786818351</v>
       </c>
       <c r="E217" t="n">
-        <v>4.506957170356972</v>
+        <v>4.506956220437275</v>
       </c>
       <c r="F217" t="n">
         <v>10891400</v>
@@ -4772,16 +4772,16 @@
         <v>44732</v>
       </c>
       <c r="B218" t="n">
-        <v>4.524771213531494</v>
+        <v>4.524770259857178</v>
       </c>
       <c r="C218" t="n">
-        <v>4.649469515753148</v>
+        <v>4.649468535796493</v>
       </c>
       <c r="D218" t="n">
-        <v>4.453515040833406</v>
+        <v>4.453514102177569</v>
       </c>
       <c r="E218" t="n">
-        <v>4.524771213531494</v>
+        <v>4.524770259857178</v>
       </c>
       <c r="F218" t="n">
         <v>7841400</v>
@@ -4812,16 +4812,16 @@
         <v>44734</v>
       </c>
       <c r="B220" t="n">
-        <v>4.444606781005859</v>
+        <v>4.444607257843018</v>
       </c>
       <c r="C220" t="n">
-        <v>4.53367740103996</v>
+        <v>4.533677887433011</v>
       </c>
       <c r="D220" t="n">
-        <v>4.400071895709002</v>
+        <v>4.40007236776826</v>
       </c>
       <c r="E220" t="n">
-        <v>4.480235283851616</v>
+        <v>4.480235764511158</v>
       </c>
       <c r="F220" t="n">
         <v>8433900</v>
@@ -4832,16 +4832,16 @@
         <v>44735</v>
       </c>
       <c r="B221" t="n">
-        <v>4.266467094421387</v>
+        <v>4.266467571258545</v>
       </c>
       <c r="C221" t="n">
-        <v>4.515864107175489</v>
+        <v>4.515864611886239</v>
       </c>
       <c r="D221" t="n">
-        <v>4.266467094421387</v>
+        <v>4.266467571258545</v>
       </c>
       <c r="E221" t="n">
-        <v>4.471328789809315</v>
+        <v>4.471329289542623</v>
       </c>
       <c r="F221" t="n">
         <v>8059200</v>
@@ -4892,16 +4892,16 @@
         <v>44740</v>
       </c>
       <c r="B224" t="n">
-        <v>4.293187618255615</v>
+        <v>4.293188095092773</v>
       </c>
       <c r="C224" t="n">
-        <v>4.471328007096019</v>
+        <v>4.471328503718931</v>
       </c>
       <c r="D224" t="n">
-        <v>4.293187618255615</v>
+        <v>4.293188095092773</v>
       </c>
       <c r="E224" t="n">
-        <v>4.319908464221581</v>
+        <v>4.319908944026579</v>
       </c>
       <c r="F224" t="n">
         <v>8975600</v>
@@ -4932,16 +4932,16 @@
         <v>44742</v>
       </c>
       <c r="B226" t="n">
-        <v>4.088326454162598</v>
+        <v>4.088326930999756</v>
       </c>
       <c r="C226" t="n">
-        <v>4.239746015386434</v>
+        <v>4.239746509884235</v>
       </c>
       <c r="D226" t="n">
-        <v>4.052698372077018</v>
+        <v>4.052698844758736</v>
       </c>
       <c r="E226" t="n">
-        <v>4.239746015386434</v>
+        <v>4.239746509884235</v>
       </c>
       <c r="F226" t="n">
         <v>6721700</v>
@@ -4992,16 +4992,16 @@
         <v>44747</v>
       </c>
       <c r="B229" t="n">
-        <v>4.034883499145508</v>
+        <v>4.034883975982666</v>
       </c>
       <c r="C229" t="n">
-        <v>4.061604342840425</v>
+        <v>4.061604822835417</v>
       </c>
       <c r="D229" t="n">
-        <v>3.901278006510463</v>
+        <v>3.901278467558302</v>
       </c>
       <c r="E229" t="n">
-        <v>4.061604342840425</v>
+        <v>4.061604822835417</v>
       </c>
       <c r="F229" t="n">
         <v>9503300</v>
@@ -5012,16 +5012,16 @@
         <v>44748</v>
       </c>
       <c r="B230" t="n">
-        <v>3.910185575485229</v>
+        <v>3.910185813903809</v>
       </c>
       <c r="C230" t="n">
-        <v>4.0526983269613</v>
+        <v>4.052698574069413</v>
       </c>
       <c r="D230" t="n">
-        <v>3.785487289573874</v>
+        <v>3.785487520389134</v>
       </c>
       <c r="E230" t="n">
-        <v>4.034884286116821</v>
+        <v>4.034884532138745</v>
       </c>
       <c r="F230" t="n">
         <v>11922900</v>
@@ -5072,16 +5072,16 @@
         <v>44753</v>
       </c>
       <c r="B233" t="n">
-        <v>3.705324172973633</v>
+        <v>3.705323457717896</v>
       </c>
       <c r="C233" t="n">
-        <v>3.901279061767585</v>
+        <v>3.901278308685776</v>
       </c>
       <c r="D233" t="n">
-        <v>3.678603322050991</v>
+        <v>3.678602611953303</v>
       </c>
       <c r="E233" t="n">
-        <v>3.892371828313193</v>
+        <v>3.892371076950788</v>
       </c>
       <c r="F233" t="n">
         <v>13261200</v>
@@ -5092,16 +5092,16 @@
         <v>44754</v>
       </c>
       <c r="B234" t="n">
-        <v>3.580625772476196</v>
+        <v>3.580625534057617</v>
       </c>
       <c r="C234" t="n">
-        <v>3.705324064132908</v>
+        <v>3.705323817411202</v>
       </c>
       <c r="D234" t="n">
-        <v>3.580625772476196</v>
+        <v>3.580625534057617</v>
       </c>
       <c r="E234" t="n">
-        <v>3.696417255660414</v>
+        <v>3.696417009531774</v>
       </c>
       <c r="F234" t="n">
         <v>14771600</v>
@@ -5132,16 +5132,16 @@
         <v>44756</v>
       </c>
       <c r="B236" t="n">
-        <v>3.821115255355835</v>
+        <v>3.821115732192993</v>
       </c>
       <c r="C236" t="n">
-        <v>3.856743335964077</v>
+        <v>3.856743817247265</v>
       </c>
       <c r="D236" t="n">
-        <v>3.651881660106575</v>
+        <v>3.651882115825064</v>
       </c>
       <c r="E236" t="n">
-        <v>3.687509740714817</v>
+        <v>3.687510200879336</v>
       </c>
       <c r="F236" t="n">
         <v>9774500</v>
@@ -5152,16 +5152,16 @@
         <v>44757</v>
       </c>
       <c r="B237" t="n">
-        <v>3.936907052993774</v>
+        <v>3.936906576156616</v>
       </c>
       <c r="C237" t="n">
-        <v>3.954721094760794</v>
+        <v>3.954720615766004</v>
       </c>
       <c r="D237" t="n">
-        <v>3.776580252370335</v>
+        <v>3.776579794951918</v>
       </c>
       <c r="E237" t="n">
-        <v>3.830022802391653</v>
+        <v>3.830022338500288</v>
       </c>
       <c r="F237" t="n">
         <v>4881500</v>
@@ -5172,16 +5172,16 @@
         <v>44760</v>
       </c>
       <c r="B238" t="n">
-        <v>3.830022573471069</v>
+        <v>3.830022811889648</v>
       </c>
       <c r="C238" t="n">
-        <v>4.088326376014163</v>
+        <v>4.088326630512132</v>
       </c>
       <c r="D238" t="n">
-        <v>3.830022573471069</v>
+        <v>3.830022811889648</v>
       </c>
       <c r="E238" t="n">
-        <v>3.990348939791538</v>
+        <v>3.99034918819042</v>
       </c>
       <c r="F238" t="n">
         <v>5011900</v>
@@ -5192,16 +5192,16 @@
         <v>44761</v>
       </c>
       <c r="B239" t="n">
-        <v>3.856743335723877</v>
+        <v>3.856743574142456</v>
       </c>
       <c r="C239" t="n">
-        <v>3.93690672944754</v>
+        <v>3.93690697282171</v>
       </c>
       <c r="D239" t="n">
-        <v>3.830022487629471</v>
+        <v>3.830022724396204</v>
       </c>
       <c r="E239" t="n">
-        <v>3.838929295420866</v>
+        <v>3.838929532738205</v>
       </c>
       <c r="F239" t="n">
         <v>5270100</v>
@@ -5212,16 +5212,16 @@
         <v>44762</v>
       </c>
       <c r="B240" t="n">
-        <v>3.999256134033203</v>
+        <v>3.999255895614624</v>
       </c>
       <c r="C240" t="n">
-        <v>4.025977410027488</v>
+        <v>4.025977170015901</v>
       </c>
       <c r="D240" t="n">
-        <v>3.803301667382781</v>
+        <v>3.803301440646171</v>
       </c>
       <c r="E240" t="n">
-        <v>3.830022943377066</v>
+        <v>3.830022715047448</v>
       </c>
       <c r="F240" t="n">
         <v>11021800</v>
@@ -5232,16 +5232,16 @@
         <v>44763</v>
       </c>
       <c r="B241" t="n">
-        <v>3.963627815246582</v>
+        <v>3.963627576828003</v>
       </c>
       <c r="C241" t="n">
-        <v>4.025977172406417</v>
+        <v>4.025976930237424</v>
       </c>
       <c r="D241" t="n">
-        <v>3.936906965549687</v>
+        <v>3.93690672873841</v>
       </c>
       <c r="E241" t="n">
-        <v>4.025977172406417</v>
+        <v>4.025976930237424</v>
       </c>
       <c r="F241" t="n">
         <v>6658500</v>
@@ -5252,16 +5252,16 @@
         <v>44764</v>
       </c>
       <c r="B242" t="n">
-        <v>3.740952253341675</v>
+        <v>3.740952014923096</v>
       </c>
       <c r="C242" t="n">
-        <v>3.999256077158491</v>
+        <v>3.999255822277678</v>
       </c>
       <c r="D242" t="n">
-        <v>3.740952253341675</v>
+        <v>3.740952014923096</v>
       </c>
       <c r="E242" t="n">
-        <v>3.999256077158491</v>
+        <v>3.999255822277678</v>
       </c>
       <c r="F242" t="n">
         <v>6536400</v>
@@ -5272,16 +5272,16 @@
         <v>44767</v>
       </c>
       <c r="B243" t="n">
-        <v>3.696417093276978</v>
+        <v>3.696417331695557</v>
       </c>
       <c r="C243" t="n">
-        <v>3.78548729769035</v>
+        <v>3.78548754185395</v>
       </c>
       <c r="D243" t="n">
-        <v>3.651881778710173</v>
+        <v>3.651882014256228</v>
       </c>
       <c r="E243" t="n">
-        <v>3.767673256807676</v>
+        <v>3.767673499822271</v>
       </c>
       <c r="F243" t="n">
         <v>10514300</v>
@@ -5292,16 +5292,16 @@
         <v>44768</v>
       </c>
       <c r="B244" t="n">
-        <v>3.714231014251709</v>
+        <v>3.714231252670288</v>
       </c>
       <c r="C244" t="n">
-        <v>3.812208448303494</v>
+        <v>3.8122086930113</v>
       </c>
       <c r="D244" t="n">
-        <v>3.669695701122655</v>
+        <v>3.669695936682488</v>
       </c>
       <c r="E244" t="n">
-        <v>3.705323781737809</v>
+        <v>3.705324019584628</v>
       </c>
       <c r="F244" t="n">
         <v>4594100</v>
@@ -5312,16 +5312,16 @@
         <v>44769</v>
       </c>
       <c r="B245" t="n">
-        <v>3.999256134033203</v>
+        <v>3.999255895614624</v>
       </c>
       <c r="C245" t="n">
-        <v>3.999256134033203</v>
+        <v>3.999255895614624</v>
       </c>
       <c r="D245" t="n">
-        <v>3.723138264120199</v>
+        <v>3.723138042162589</v>
       </c>
       <c r="E245" t="n">
-        <v>3.740952306542965</v>
+        <v>3.740952083523358</v>
       </c>
       <c r="F245" t="n">
         <v>8689000</v>
@@ -5332,16 +5332,16 @@
         <v>44770</v>
       </c>
       <c r="B246" t="n">
-        <v>3.999256134033203</v>
+        <v>3.999255895614624</v>
       </c>
       <c r="C246" t="n">
-        <v>4.070512728444538</v>
+        <v>4.070512485777946</v>
       </c>
       <c r="D246" t="n">
-        <v>3.892371879496609</v>
+        <v>3.892371647450013</v>
       </c>
       <c r="E246" t="n">
-        <v>4.025977410027488</v>
+        <v>4.025977170015901</v>
       </c>
       <c r="F246" t="n">
         <v>3634200</v>
@@ -5392,16 +5392,16 @@
         <v>44775</v>
       </c>
       <c r="B249" t="n">
-        <v>4.106140613555908</v>
+        <v>4.10614013671875</v>
       </c>
       <c r="C249" t="n">
-        <v>4.115047421973903</v>
+        <v>4.115046944102415</v>
       </c>
       <c r="D249" t="n">
-        <v>3.901278923299012</v>
+        <v>3.901278470251996</v>
       </c>
       <c r="E249" t="n">
-        <v>3.927999773273247</v>
+        <v>3.927999317123196</v>
       </c>
       <c r="F249" t="n">
         <v>12885400</v>
@@ -5412,16 +5412,16 @@
         <v>44776</v>
       </c>
       <c r="B250" t="n">
-        <v>4.284281253814697</v>
+        <v>4.284280776977539</v>
       </c>
       <c r="C250" t="n">
-        <v>4.37335146626734</v>
+        <v>4.373350979516736</v>
       </c>
       <c r="D250" t="n">
-        <v>4.123954871399942</v>
+        <v>4.123954412406984</v>
       </c>
       <c r="E250" t="n">
-        <v>4.123954871399942</v>
+        <v>4.123954412406984</v>
       </c>
       <c r="F250" t="n">
         <v>8750200</v>
@@ -5432,16 +5432,16 @@
         <v>44777</v>
       </c>
       <c r="B251" t="n">
-        <v>4.498049736022949</v>
+        <v>4.498050212860107</v>
       </c>
       <c r="C251" t="n">
-        <v>4.791981619914148</v>
+        <v>4.791982127910954</v>
       </c>
       <c r="D251" t="n">
-        <v>4.328816137023725</v>
+        <v>4.32881659592047</v>
       </c>
       <c r="E251" t="n">
-        <v>4.328816137023725</v>
+        <v>4.32881659592047</v>
       </c>
       <c r="F251" t="n">
         <v>17206200</v>
@@ -5472,16 +5472,16 @@
         <v>44781</v>
       </c>
       <c r="B253" t="n">
-        <v>4.408978939056396</v>
+        <v>4.408979415893555</v>
       </c>
       <c r="C253" t="n">
-        <v>4.506956371510157</v>
+        <v>4.50695685894371</v>
       </c>
       <c r="D253" t="n">
-        <v>4.355536819005313</v>
+        <v>4.355537290062633</v>
       </c>
       <c r="E253" t="n">
-        <v>4.391164899039369</v>
+        <v>4.391165373949914</v>
       </c>
       <c r="F253" t="n">
         <v>6283600</v>
@@ -5512,16 +5512,16 @@
         <v>44783</v>
       </c>
       <c r="B255" t="n">
-        <v>4.587119579315186</v>
+        <v>4.587120056152344</v>
       </c>
       <c r="C255" t="n">
-        <v>4.702911047125363</v>
+        <v>4.702911535999198</v>
       </c>
       <c r="D255" t="n">
-        <v>4.426792800894878</v>
+        <v>4.426793261065856</v>
       </c>
       <c r="E255" t="n">
-        <v>4.426792800894878</v>
+        <v>4.426793261065856</v>
       </c>
       <c r="F255" t="n">
         <v>9044400</v>
@@ -5532,16 +5532,16 @@
         <v>44784</v>
       </c>
       <c r="B256" t="n">
-        <v>4.346631050109863</v>
+        <v>4.346630096435547</v>
       </c>
       <c r="C256" t="n">
-        <v>4.685098316040128</v>
+        <v>4.685097288104267</v>
       </c>
       <c r="D256" t="n">
-        <v>4.311002961561448</v>
+        <v>4.311002015704126</v>
       </c>
       <c r="E256" t="n">
-        <v>4.613841714222979</v>
+        <v>4.613840701921201</v>
       </c>
       <c r="F256" t="n">
         <v>11482900</v>
@@ -5612,16 +5612,16 @@
         <v>44790</v>
       </c>
       <c r="B260" t="n">
-        <v>4.702911376953125</v>
+        <v>4.702910900115967</v>
       </c>
       <c r="C260" t="n">
-        <v>4.774167539150558</v>
+        <v>4.774167055088602</v>
       </c>
       <c r="D260" t="n">
-        <v>4.560398627838029</v>
+        <v>4.560398165450511</v>
       </c>
       <c r="E260" t="n">
-        <v>4.596026708936746</v>
+        <v>4.596026242936828</v>
       </c>
       <c r="F260" t="n">
         <v>27272900</v>
@@ -5652,16 +5652,16 @@
         <v>44792</v>
       </c>
       <c r="B262" t="n">
-        <v>4.319908618927002</v>
+        <v>4.31990909576416</v>
       </c>
       <c r="C262" t="n">
-        <v>4.533677517911209</v>
+        <v>4.533678018344458</v>
       </c>
       <c r="D262" t="n">
-        <v>4.221931189195899</v>
+        <v>4.22193165521818</v>
       </c>
       <c r="E262" t="n">
-        <v>4.524770285790107</v>
+        <v>4.524770785240164</v>
       </c>
       <c r="F262" t="n">
         <v>17743000</v>
@@ -5672,16 +5672,16 @@
         <v>44795</v>
       </c>
       <c r="B263" t="n">
-        <v>4.319908618927002</v>
+        <v>4.31990909576416</v>
       </c>
       <c r="C263" t="n">
-        <v>4.364443930092105</v>
+        <v>4.364444411845128</v>
       </c>
       <c r="D263" t="n">
-        <v>4.177396302751</v>
+        <v>4.177396763857463</v>
       </c>
       <c r="E263" t="n">
-        <v>4.302094579405002</v>
+        <v>4.302095054275823</v>
       </c>
       <c r="F263" t="n">
         <v>9829500</v>
@@ -5732,16 +5732,16 @@
         <v>44798</v>
       </c>
       <c r="B266" t="n">
-        <v>4.480235576629639</v>
+        <v>4.48023509979248</v>
       </c>
       <c r="C266" t="n">
-        <v>4.604933858217994</v>
+        <v>4.604933368109039</v>
       </c>
       <c r="D266" t="n">
-        <v>4.453514303929166</v>
+        <v>4.453513829935988</v>
       </c>
       <c r="E266" t="n">
-        <v>4.587119817991086</v>
+        <v>4.587119329778102</v>
       </c>
       <c r="F266" t="n">
         <v>4135100</v>
@@ -5752,16 +5752,16 @@
         <v>44799</v>
       </c>
       <c r="B267" t="n">
-        <v>4.319908618927002</v>
+        <v>4.31990909576416</v>
       </c>
       <c r="C267" t="n">
-        <v>4.524770285790107</v>
+        <v>4.524770785240164</v>
       </c>
       <c r="D267" t="n">
-        <v>4.293187772004104</v>
+        <v>4.29318824589178</v>
       </c>
       <c r="E267" t="n">
-        <v>4.489142206746107</v>
+        <v>4.489142702263489</v>
       </c>
       <c r="F267" t="n">
         <v>6692300</v>
@@ -5772,16 +5772,16 @@
         <v>44802</v>
       </c>
       <c r="B268" t="n">
-        <v>4.453514099121094</v>
+        <v>4.453514575958252</v>
       </c>
       <c r="C268" t="n">
-        <v>4.480235370592709</v>
+        <v>4.48023585029091</v>
       </c>
       <c r="D268" t="n">
-        <v>4.266466472980391</v>
+        <v>4.266466929790385</v>
       </c>
       <c r="E268" t="n">
-        <v>4.275373705044331</v>
+        <v>4.275374162808021</v>
       </c>
       <c r="F268" t="n">
         <v>7870400</v>
@@ -5812,16 +5812,16 @@
         <v>44804</v>
       </c>
       <c r="B270" t="n">
-        <v>4.311002254486084</v>
+        <v>4.311002731323242</v>
       </c>
       <c r="C270" t="n">
-        <v>4.435700543952965</v>
+        <v>4.43570103458292</v>
       </c>
       <c r="D270" t="n">
-        <v>4.284280980097343</v>
+        <v>4.284281453978878</v>
       </c>
       <c r="E270" t="n">
-        <v>4.382258419895731</v>
+        <v>4.382258904614487</v>
       </c>
       <c r="F270" t="n">
         <v>8375100</v>
@@ -5892,16 +5892,16 @@
         <v>44810</v>
       </c>
       <c r="B274" t="n">
-        <v>3.954720497131348</v>
+        <v>3.954720973968506</v>
       </c>
       <c r="C274" t="n">
-        <v>4.177396197928922</v>
+        <v>4.177396701615019</v>
       </c>
       <c r="D274" t="n">
-        <v>3.945813265233752</v>
+        <v>3.945813740996928</v>
       </c>
       <c r="E274" t="n">
-        <v>4.141768119778925</v>
+        <v>4.141768619169197</v>
       </c>
       <c r="F274" t="n">
         <v>14609100</v>
@@ -5912,16 +5912,16 @@
         <v>44812</v>
       </c>
       <c r="B275" t="n">
-        <v>3.910185575485229</v>
+        <v>3.910185813903809</v>
       </c>
       <c r="C275" t="n">
-        <v>4.008163012489984</v>
+        <v>4.008163256882613</v>
       </c>
       <c r="D275" t="n">
-        <v>3.856743452951791</v>
+        <v>3.856743688111805</v>
       </c>
       <c r="E275" t="n">
-        <v>3.990348971645505</v>
+        <v>3.990349214951944</v>
       </c>
       <c r="F275" t="n">
         <v>9864000</v>
@@ -5932,16 +5932,16 @@
         <v>44813</v>
       </c>
       <c r="B276" t="n">
-        <v>3.910185575485229</v>
+        <v>3.910185813903809</v>
       </c>
       <c r="C276" t="n">
-        <v>4.043791094178943</v>
+        <v>4.043791340743948</v>
       </c>
       <c r="D276" t="n">
-        <v>3.883464726578628</v>
+        <v>3.883464963367938</v>
       </c>
       <c r="E276" t="n">
-        <v>3.945813657174188</v>
+        <v>3.945813897765144</v>
       </c>
       <c r="F276" t="n">
         <v>15548300</v>
@@ -5952,16 +5952,16 @@
         <v>44816</v>
       </c>
       <c r="B277" t="n">
-        <v>3.856743335723877</v>
+        <v>3.856743574142456</v>
       </c>
       <c r="C277" t="n">
-        <v>3.990348850356574</v>
+        <v>3.990349097034463</v>
       </c>
       <c r="D277" t="n">
-        <v>3.838929295420866</v>
+        <v>3.838929532738205</v>
       </c>
       <c r="E277" t="n">
-        <v>3.954720769750552</v>
+        <v>3.954721014225961</v>
       </c>
       <c r="F277" t="n">
         <v>15738600</v>
@@ -5972,16 +5972,16 @@
         <v>44817</v>
       </c>
       <c r="B278" t="n">
-        <v>3.696417093276978</v>
+        <v>3.696417331695557</v>
       </c>
       <c r="C278" t="n">
-        <v>3.883464734905179</v>
+        <v>3.883464985388314</v>
       </c>
       <c r="D278" t="n">
-        <v>3.678603052394303</v>
+        <v>3.678603289663878</v>
       </c>
       <c r="E278" t="n">
-        <v>3.874557502103723</v>
+        <v>3.874557752012343</v>
       </c>
       <c r="F278" t="n">
         <v>21443000</v>
@@ -5992,16 +5992,16 @@
         <v>44818</v>
       </c>
       <c r="B279" t="n">
-        <v>3.740952253341675</v>
+        <v>3.740952014923096</v>
       </c>
       <c r="C279" t="n">
-        <v>3.821115655464227</v>
+        <v>3.821115411936669</v>
       </c>
       <c r="D279" t="n">
-        <v>3.678603318108816</v>
+        <v>3.678603083663863</v>
       </c>
       <c r="E279" t="n">
-        <v>3.705324169002822</v>
+        <v>3.705323932854894</v>
       </c>
       <c r="F279" t="n">
         <v>13539100</v>
@@ -6012,16 +6012,16 @@
         <v>44819</v>
       </c>
       <c r="B280" t="n">
-        <v>3.749859094619751</v>
+        <v>3.74985933303833</v>
       </c>
       <c r="C280" t="n">
-        <v>3.758765902412841</v>
+        <v>3.758766141397721</v>
       </c>
       <c r="D280" t="n">
-        <v>3.634067620268019</v>
+        <v>3.634067851324498</v>
       </c>
       <c r="E280" t="n">
-        <v>3.740951862106438</v>
+        <v>3.740952099958689</v>
       </c>
       <c r="F280" t="n">
         <v>12717200</v>
@@ -6032,16 +6032,16 @@
         <v>44820</v>
       </c>
       <c r="B281" t="n">
-        <v>3.821115255355835</v>
+        <v>3.821115732192993</v>
       </c>
       <c r="C281" t="n">
-        <v>3.892371416572319</v>
+        <v>3.892371902301537</v>
       </c>
       <c r="D281" t="n">
-        <v>3.660788892618747</v>
+        <v>3.66078934944877</v>
       </c>
       <c r="E281" t="n">
-        <v>3.696416973226988</v>
+        <v>3.696417434503042</v>
       </c>
       <c r="F281" t="n">
         <v>19813000</v>
@@ -6052,16 +6052,16 @@
         <v>44823</v>
       </c>
       <c r="B282" t="n">
-        <v>3.990349292755127</v>
+        <v>3.990348339080811</v>
       </c>
       <c r="C282" t="n">
-        <v>4.00816333503313</v>
+        <v>4.008162377101343</v>
       </c>
       <c r="D282" t="n">
-        <v>3.794394827697093</v>
+        <v>3.794393920854952</v>
       </c>
       <c r="E282" t="n">
-        <v>3.830022912253099</v>
+        <v>3.830021996896017</v>
       </c>
       <c r="F282" t="n">
         <v>8945000</v>
@@ -6072,16 +6072,16 @@
         <v>44824</v>
       </c>
       <c r="B283" t="n">
-        <v>3.963627815246582</v>
+        <v>3.963627576828003</v>
       </c>
       <c r="C283" t="n">
-        <v>4.132861420634493</v>
+        <v>4.13286117203624</v>
       </c>
       <c r="D283" t="n">
-        <v>3.919092924178341</v>
+        <v>3.919092688438607</v>
       </c>
       <c r="E283" t="n">
-        <v>3.990349089663725</v>
+        <v>3.990348849637818</v>
       </c>
       <c r="F283" t="n">
         <v>10696200</v>
@@ -6092,16 +6092,16 @@
         <v>44825</v>
       </c>
       <c r="B284" t="n">
-        <v>3.883464813232422</v>
+        <v>3.883465051651001</v>
       </c>
       <c r="C284" t="n">
-        <v>4.034884376149319</v>
+        <v>4.034884623864039</v>
       </c>
       <c r="D284" t="n">
-        <v>3.830022689506502</v>
+        <v>3.830022924644094</v>
       </c>
       <c r="E284" t="n">
-        <v>3.972535019442289</v>
+        <v>3.972535263329179</v>
       </c>
       <c r="F284" t="n">
         <v>18275700</v>
@@ -6132,16 +6132,16 @@
         <v>44827</v>
       </c>
       <c r="B286" t="n">
-        <v>3.910185575485229</v>
+        <v>3.910185813903809</v>
       </c>
       <c r="C286" t="n">
-        <v>3.990348971645505</v>
+        <v>3.990349214951944</v>
       </c>
       <c r="D286" t="n">
-        <v>3.847836644889669</v>
+        <v>3.847836879506602</v>
       </c>
       <c r="E286" t="n">
-        <v>3.963627698018668</v>
+        <v>3.963627939695812</v>
       </c>
       <c r="F286" t="n">
         <v>14173200</v>
@@ -6152,16 +6152,16 @@
         <v>44830</v>
       </c>
       <c r="B287" t="n">
-        <v>3.821115255355835</v>
+        <v>3.821115732192993</v>
       </c>
       <c r="C287" t="n">
-        <v>3.936906729692732</v>
+        <v>3.936907220979514</v>
       </c>
       <c r="D287" t="n">
-        <v>3.794394407259765</v>
+        <v>3.794394880762427</v>
       </c>
       <c r="E287" t="n">
-        <v>3.901278649084491</v>
+        <v>3.901279135925243</v>
       </c>
       <c r="F287" t="n">
         <v>9718800</v>
@@ -6212,16 +6212,16 @@
         <v>44833</v>
       </c>
       <c r="B290" t="n">
-        <v>3.696417093276978</v>
+        <v>3.696417331695557</v>
       </c>
       <c r="C290" t="n">
-        <v>3.714231134159652</v>
+        <v>3.714231373727235</v>
       </c>
       <c r="D290" t="n">
-        <v>3.616253696944824</v>
+        <v>3.616253930192871</v>
       </c>
       <c r="E290" t="n">
-        <v>3.660789011511628</v>
+        <v>3.660789247632199</v>
       </c>
       <c r="F290" t="n">
         <v>12380300</v>
@@ -6272,16 +6272,16 @@
         <v>44838</v>
       </c>
       <c r="B293" t="n">
-        <v>3.930920124053955</v>
+        <v>3.930919885635376</v>
       </c>
       <c r="C293" t="n">
-        <v>4.05656584965991</v>
+        <v>4.056565603620654</v>
       </c>
       <c r="D293" t="n">
-        <v>3.895021345309396</v>
+        <v>3.895021109068154</v>
       </c>
       <c r="E293" t="n">
-        <v>3.975793383511054</v>
+        <v>3.975793142370817</v>
       </c>
       <c r="F293" t="n">
         <v>11413300</v>
@@ -6292,16 +6292,16 @@
         <v>44839</v>
       </c>
       <c r="B294" t="n">
-        <v>3.975793361663818</v>
+        <v>3.97579288482666</v>
       </c>
       <c r="C294" t="n">
-        <v>3.975793361663818</v>
+        <v>3.97579288482666</v>
       </c>
       <c r="D294" t="n">
-        <v>3.868097026021941</v>
+        <v>3.868096562101353</v>
       </c>
       <c r="E294" t="n">
-        <v>3.92194519384288</v>
+        <v>3.921944723464007</v>
       </c>
       <c r="F294" t="n">
         <v>8368900</v>
@@ -6352,16 +6352,16 @@
         <v>44844</v>
       </c>
       <c r="B297" t="n">
-        <v>3.661678791046143</v>
+        <v>3.661679029464722</v>
       </c>
       <c r="C297" t="n">
-        <v>3.805273903495892</v>
+        <v>3.80527415126421</v>
       </c>
       <c r="D297" t="n">
-        <v>3.63475492143541</v>
+        <v>3.634755158100927</v>
       </c>
       <c r="E297" t="n">
-        <v>3.805273903495892</v>
+        <v>3.80527415126421</v>
       </c>
       <c r="F297" t="n">
         <v>18862600</v>
@@ -6392,16 +6392,16 @@
         <v>44847</v>
       </c>
       <c r="B299" t="n">
-        <v>3.814249277114868</v>
+        <v>3.81424880027771</v>
       </c>
       <c r="C299" t="n">
-        <v>3.903996233339887</v>
+        <v>3.903995745283042</v>
       </c>
       <c r="D299" t="n">
-        <v>3.796299885869864</v>
+        <v>3.796299411276644</v>
       </c>
       <c r="E299" t="n">
-        <v>3.895021751691007</v>
+        <v>3.895021264756104</v>
       </c>
       <c r="F299" t="n">
         <v>15027200</v>
@@ -6412,16 +6412,16 @@
         <v>44848</v>
       </c>
       <c r="B300" t="n">
-        <v>3.688603639602661</v>
+        <v>3.688603162765503</v>
       </c>
       <c r="C300" t="n">
-        <v>3.832198773502456</v>
+        <v>3.832198278102312</v>
       </c>
       <c r="D300" t="n">
-        <v>3.679628729760296</v>
+        <v>3.679628254083352</v>
       </c>
       <c r="E300" t="n">
-        <v>3.823224291607347</v>
+        <v>3.823223797367362</v>
       </c>
       <c r="F300" t="n">
         <v>10535000</v>
@@ -6432,16 +6432,16 @@
         <v>44851</v>
       </c>
       <c r="B301" t="n">
-        <v>3.679628133773804</v>
+        <v>3.679628372192383</v>
       </c>
       <c r="C301" t="n">
-        <v>3.769375077924933</v>
+        <v>3.769375322158595</v>
       </c>
       <c r="D301" t="n">
-        <v>3.670653653332284</v>
+        <v>3.670653891169369</v>
       </c>
       <c r="E301" t="n">
-        <v>3.724501819822962</v>
+        <v>3.724502061149096</v>
       </c>
       <c r="F301" t="n">
         <v>8129100</v>
@@ -6472,16 +6472,16 @@
         <v>44853</v>
       </c>
       <c r="B303" t="n">
-        <v>3.733476638793945</v>
+        <v>3.733476161956787</v>
       </c>
       <c r="C303" t="n">
-        <v>3.769375419709485</v>
+        <v>3.769374938287358</v>
       </c>
       <c r="D303" t="n">
-        <v>3.670653986165363</v>
+        <v>3.670653517351873</v>
       </c>
       <c r="E303" t="n">
-        <v>3.715527248336175</v>
+        <v>3.715526773791502</v>
       </c>
       <c r="F303" t="n">
         <v>12625300</v>
@@ -6492,16 +6492,16 @@
         <v>44854</v>
       </c>
       <c r="B304" t="n">
-        <v>3.769375562667847</v>
+        <v>3.769375324249268</v>
       </c>
       <c r="C304" t="n">
-        <v>3.796299863349252</v>
+        <v>3.796299623227672</v>
       </c>
       <c r="D304" t="n">
-        <v>3.706552907656635</v>
+        <v>3.706552673211682</v>
       </c>
       <c r="E304" t="n">
-        <v>3.760401081072205</v>
+        <v>3.760400843221276</v>
       </c>
       <c r="F304" t="n">
         <v>13428400</v>
@@ -6512,16 +6512,16 @@
         <v>44855</v>
       </c>
       <c r="B305" t="n">
-        <v>3.832198143005371</v>
+        <v>3.83219838142395</v>
       </c>
       <c r="C305" t="n">
-        <v>3.859122440155458</v>
+        <v>3.85912268024912</v>
       </c>
       <c r="D305" t="n">
-        <v>3.733476290717968</v>
+        <v>3.733476522994609</v>
       </c>
       <c r="E305" t="n">
-        <v>3.760400587868054</v>
+        <v>3.760400821819779</v>
       </c>
       <c r="F305" t="n">
         <v>14614900</v>
@@ -6572,16 +6572,16 @@
         <v>44860</v>
       </c>
       <c r="B308" t="n">
-        <v>3.562956809997559</v>
+        <v>3.562957048416138</v>
       </c>
       <c r="C308" t="n">
-        <v>3.670653347993915</v>
+        <v>3.670653593619109</v>
       </c>
       <c r="D308" t="n">
-        <v>3.545007422660428</v>
+        <v>3.545007659877907</v>
       </c>
       <c r="E308" t="n">
-        <v>3.661678440351775</v>
+        <v>3.661678685376404</v>
       </c>
       <c r="F308" t="n">
         <v>15630800</v>
@@ -6612,16 +6612,16 @@
         <v>44862</v>
       </c>
       <c r="B310" t="n">
-        <v>3.724502086639404</v>
+        <v>3.724502325057983</v>
       </c>
       <c r="C310" t="n">
-        <v>3.73347656772384</v>
+        <v>3.733476806716907</v>
       </c>
       <c r="D310" t="n">
-        <v>3.643729617143404</v>
+        <v>3.643729850391451</v>
       </c>
       <c r="E310" t="n">
-        <v>3.68860330640723</v>
+        <v>3.688603542527801</v>
       </c>
       <c r="F310" t="n">
         <v>9985100</v>
@@ -6632,16 +6632,16 @@
         <v>44865</v>
       </c>
       <c r="B311" t="n">
-        <v>3.850147724151611</v>
+        <v>3.85014820098877</v>
       </c>
       <c r="C311" t="n">
-        <v>3.868097113832732</v>
+        <v>3.868097592892905</v>
       </c>
       <c r="D311" t="n">
-        <v>3.545007885598959</v>
+        <v>3.545008324644836</v>
       </c>
       <c r="E311" t="n">
-        <v>3.58988135980176</v>
+        <v>3.589881804405175</v>
       </c>
       <c r="F311" t="n">
         <v>19491700</v>
@@ -6652,16 +6652,16 @@
         <v>44866</v>
       </c>
       <c r="B312" t="n">
-        <v>4.047591686248779</v>
+        <v>4.047591209411621</v>
       </c>
       <c r="C312" t="n">
-        <v>4.092464949223611</v>
+        <v>4.092464467100041</v>
       </c>
       <c r="D312" t="n">
-        <v>3.814249178169614</v>
+        <v>3.814248728821982</v>
       </c>
       <c r="E312" t="n">
-        <v>3.868097350507752</v>
+        <v>3.868096894816395</v>
       </c>
       <c r="F312" t="n">
         <v>23695600</v>
@@ -6672,16 +6672,16 @@
         <v>44868</v>
       </c>
       <c r="B313" t="n">
-        <v>4.218111038208008</v>
+        <v>4.21811056137085</v>
       </c>
       <c r="C313" t="n">
-        <v>4.25400982277552</v>
+        <v>4.254009341880177</v>
       </c>
       <c r="D313" t="n">
-        <v>3.895021977100405</v>
+        <v>3.895021536786911</v>
       </c>
       <c r="E313" t="n">
-        <v>3.975794028403671</v>
+        <v>3.975793578959285</v>
       </c>
       <c r="F313" t="n">
         <v>15015300</v>
@@ -6692,16 +6692,16 @@
         <v>44869</v>
       </c>
       <c r="B314" t="n">
-        <v>4.23606014251709</v>
+        <v>4.236059665679932</v>
       </c>
       <c r="C314" t="n">
-        <v>4.34375691684548</v>
+        <v>4.343756427885306</v>
       </c>
       <c r="D314" t="n">
-        <v>4.155288096704846</v>
+        <v>4.15528762895989</v>
       </c>
       <c r="E314" t="n">
-        <v>4.218110751453565</v>
+        <v>4.218110276636901</v>
       </c>
       <c r="F314" t="n">
         <v>12500600</v>
@@ -6772,16 +6772,16 @@
         <v>44875</v>
       </c>
       <c r="B318" t="n">
-        <v>3.688603639602661</v>
+        <v>3.688603162765503</v>
       </c>
       <c r="C318" t="n">
-        <v>3.975793907402251</v>
+        <v>3.975793393439122</v>
       </c>
       <c r="D318" t="n">
-        <v>3.670654247865187</v>
+        <v>3.670653773348401</v>
       </c>
       <c r="E318" t="n">
-        <v>3.921945732189828</v>
+        <v>3.921945225187819</v>
       </c>
       <c r="F318" t="n">
         <v>22566600</v>
@@ -6812,16 +6812,16 @@
         <v>44879</v>
       </c>
       <c r="B320" t="n">
-        <v>3.697577953338623</v>
+        <v>3.697577476501465</v>
       </c>
       <c r="C320" t="n">
-        <v>3.796299817378669</v>
+        <v>3.796299327810405</v>
       </c>
       <c r="D320" t="n">
-        <v>3.643729780575117</v>
+        <v>3.643729310682183</v>
       </c>
       <c r="E320" t="n">
-        <v>3.760401035536331</v>
+        <v>3.760400550597551</v>
       </c>
       <c r="F320" t="n">
         <v>10873300</v>
@@ -6832,16 +6832,16 @@
         <v>44881</v>
       </c>
       <c r="B321" t="n">
-        <v>3.616805791854858</v>
+        <v>3.616805553436279</v>
       </c>
       <c r="C321" t="n">
-        <v>3.760400914606361</v>
+        <v>3.760400666722041</v>
       </c>
       <c r="D321" t="n">
-        <v>3.553982711677465</v>
+        <v>3.553982477400161</v>
       </c>
       <c r="E321" t="n">
-        <v>3.697577834428968</v>
+        <v>3.697577590685923</v>
       </c>
       <c r="F321" t="n">
         <v>16148800</v>
@@ -6852,16 +6852,16 @@
         <v>44882</v>
       </c>
       <c r="B322" t="n">
-        <v>3.509109497070312</v>
+        <v>3.509109020233154</v>
       </c>
       <c r="C322" t="n">
-        <v>3.571932367951248</v>
+        <v>3.571931882577372</v>
       </c>
       <c r="D322" t="n">
-        <v>3.356539453814412</v>
+        <v>3.356538997709313</v>
       </c>
       <c r="E322" t="n">
-        <v>3.562957672111115</v>
+        <v>3.56295718795677</v>
       </c>
       <c r="F322" t="n">
         <v>25106400</v>
@@ -6872,16 +6872,16 @@
         <v>44883</v>
       </c>
       <c r="B323" t="n">
-        <v>3.652704477310181</v>
+        <v>3.652704238891602</v>
       </c>
       <c r="C323" t="n">
-        <v>3.841173284981419</v>
+        <v>3.841173034261142</v>
       </c>
       <c r="D323" t="n">
-        <v>3.536033229142802</v>
+        <v>3.536032998339565</v>
       </c>
       <c r="E323" t="n">
-        <v>3.580906703832715</v>
+        <v>3.580906470100505</v>
       </c>
       <c r="F323" t="n">
         <v>23150300</v>
@@ -6892,16 +6892,16 @@
         <v>44886</v>
       </c>
       <c r="B324" t="n">
-        <v>3.616805791854858</v>
+        <v>3.616805553436279</v>
       </c>
       <c r="C324" t="n">
-        <v>3.733476615116843</v>
+        <v>3.733476369007364</v>
       </c>
       <c r="D324" t="n">
-        <v>3.545008016505496</v>
+        <v>3.545007782819801</v>
       </c>
       <c r="E324" t="n">
-        <v>3.67962844408503</v>
+        <v>3.679628201525203</v>
       </c>
       <c r="F324" t="n">
         <v>11314600</v>
@@ -6912,16 +6912,16 @@
         <v>44887</v>
       </c>
       <c r="B325" t="n">
-        <v>3.616805791854858</v>
+        <v>3.616805553436279</v>
       </c>
       <c r="C325" t="n">
-        <v>3.661679053741092</v>
+        <v>3.661678812364483</v>
       </c>
       <c r="D325" t="n">
-        <v>3.562957406849434</v>
+        <v>3.562957171980521</v>
       </c>
       <c r="E325" t="n">
-        <v>3.616805791854858</v>
+        <v>3.616805553436279</v>
       </c>
       <c r="F325" t="n">
         <v>10439300</v>
@@ -6952,16 +6952,16 @@
         <v>44889</v>
       </c>
       <c r="B327" t="n">
-        <v>3.724502086639404</v>
+        <v>3.724502325057983</v>
       </c>
       <c r="C327" t="n">
-        <v>3.742451476755492</v>
+        <v>3.742451716323075</v>
       </c>
       <c r="D327" t="n">
-        <v>3.598856355826795</v>
+        <v>3.598856586202345</v>
       </c>
       <c r="E327" t="n">
-        <v>3.634755136058969</v>
+        <v>3.634755368732528</v>
       </c>
       <c r="F327" t="n">
         <v>5511600</v>
@@ -6972,16 +6972,16 @@
         <v>44890</v>
       </c>
       <c r="B328" t="n">
-        <v>3.63475513458252</v>
+        <v>3.634755373001099</v>
       </c>
       <c r="C328" t="n">
-        <v>3.760400865344091</v>
+        <v>3.760401112004292</v>
       </c>
       <c r="D328" t="n">
-        <v>3.580906750282523</v>
+        <v>3.580906985168965</v>
       </c>
       <c r="E328" t="n">
-        <v>3.733476566207289</v>
+        <v>3.733476811101414</v>
       </c>
       <c r="F328" t="n">
         <v>8739900</v>
@@ -6992,16 +6992,16 @@
         <v>44893</v>
       </c>
       <c r="B329" t="n">
-        <v>3.607831001281738</v>
+        <v>3.607830762863159</v>
       </c>
       <c r="C329" t="n">
-        <v>3.670654083523831</v>
+        <v>3.670653840953675</v>
       </c>
       <c r="D329" t="n">
-        <v>3.589881610347888</v>
+        <v>3.58988137311547</v>
       </c>
       <c r="E329" t="n">
-        <v>3.589881610347888</v>
+        <v>3.58988137311547</v>
       </c>
       <c r="F329" t="n">
         <v>7386900</v>
@@ -7032,16 +7032,16 @@
         <v>44895</v>
       </c>
       <c r="B331" t="n">
-        <v>3.63475513458252</v>
+        <v>3.634755373001099</v>
       </c>
       <c r="C331" t="n">
-        <v>3.661679005772105</v>
+        <v>3.661679245956732</v>
       </c>
       <c r="D331" t="n">
-        <v>3.518083884901738</v>
+        <v>3.518084115667368</v>
       </c>
       <c r="E331" t="n">
-        <v>3.571932055228125</v>
+        <v>3.57193228952588</v>
       </c>
       <c r="F331" t="n">
         <v>16877200</v>
@@ -7152,16 +7152,16 @@
         <v>44903</v>
       </c>
       <c r="B337" t="n">
-        <v>3.073575496673584</v>
+        <v>3.073575735092163</v>
       </c>
       <c r="C337" t="n">
-        <v>3.266824295516617</v>
+        <v>3.266824548925589</v>
       </c>
       <c r="D337" t="n">
-        <v>3.064373183366795</v>
+        <v>3.064373421071546</v>
       </c>
       <c r="E337" t="n">
-        <v>3.22081272898267</v>
+        <v>3.220812978822505</v>
       </c>
       <c r="F337" t="n">
         <v>19978800</v>
@@ -7192,16 +7192,16 @@
         <v>44907</v>
       </c>
       <c r="B339" t="n">
-        <v>3.036766529083252</v>
+        <v>3.036766290664673</v>
       </c>
       <c r="C339" t="n">
-        <v>3.119587576034921</v>
+        <v>3.119587331114006</v>
       </c>
       <c r="D339" t="n">
-        <v>2.972350329876769</v>
+        <v>2.972350096515548</v>
       </c>
       <c r="E339" t="n">
-        <v>3.082778099945025</v>
+        <v>3.082777857914047</v>
       </c>
       <c r="F339" t="n">
         <v>24013800</v>
@@ -7232,16 +7232,16 @@
         <v>44909</v>
       </c>
       <c r="B341" t="n">
-        <v>3.073575496673584</v>
+        <v>3.073575735092163</v>
       </c>
       <c r="C341" t="n">
-        <v>3.101182436593952</v>
+        <v>3.101182677154013</v>
       </c>
       <c r="D341" t="n">
-        <v>2.935540797071743</v>
+        <v>2.935541024782911</v>
       </c>
       <c r="E341" t="n">
-        <v>2.98155236360569</v>
+        <v>2.981552594885995</v>
       </c>
       <c r="F341" t="n">
         <v>15438000</v>
@@ -7252,16 +7252,16 @@
         <v>44910</v>
       </c>
       <c r="B342" t="n">
-        <v>3.036766529083252</v>
+        <v>3.036766290664673</v>
       </c>
       <c r="C342" t="n">
-        <v>3.13799220437963</v>
+        <v>3.137991958013755</v>
       </c>
       <c r="D342" t="n">
-        <v>3.009159586566188</v>
+        <v>3.009159350315048</v>
       </c>
       <c r="E342" t="n">
-        <v>3.055171157427961</v>
+        <v>3.055170917564423</v>
       </c>
       <c r="F342" t="n">
         <v>8858500</v>
@@ -7292,16 +7292,16 @@
         <v>44914</v>
       </c>
       <c r="B344" t="n">
-        <v>3.073575496673584</v>
+        <v>3.073575735092163</v>
       </c>
       <c r="C344" t="n">
-        <v>3.091980123287163</v>
+        <v>3.091980363133397</v>
       </c>
       <c r="D344" t="n">
-        <v>2.990754676912479</v>
+        <v>2.990754908906612</v>
       </c>
       <c r="E344" t="n">
-        <v>3.009159303526058</v>
+        <v>3.009159536947845</v>
       </c>
       <c r="F344" t="n">
         <v>6693400</v>
@@ -7352,16 +7352,16 @@
         <v>44917</v>
       </c>
       <c r="B347" t="n">
-        <v>3.340442895889282</v>
+        <v>3.340443134307861</v>
       </c>
       <c r="C347" t="n">
-        <v>3.3588475218115</v>
+        <v>3.358847761543679</v>
       </c>
       <c r="D347" t="n">
-        <v>3.257621859838854</v>
+        <v>3.257622092346219</v>
       </c>
       <c r="E347" t="n">
-        <v>3.331240363527726</v>
+        <v>3.33124060128949</v>
       </c>
       <c r="F347" t="n">
         <v>7727000</v>
@@ -7392,16 +7392,16 @@
         <v>44921</v>
       </c>
       <c r="B349" t="n">
-        <v>3.340442895889282</v>
+        <v>3.340443134307861</v>
       </c>
       <c r="C349" t="n">
-        <v>3.441668338461481</v>
+        <v>3.441668584104859</v>
       </c>
       <c r="D349" t="n">
-        <v>3.28522879872218</v>
+        <v>3.285229033199945</v>
       </c>
       <c r="E349" t="n">
-        <v>3.441668338461481</v>
+        <v>3.441668584104859</v>
       </c>
       <c r="F349" t="n">
         <v>5290600</v>
@@ -7492,16 +7492,16 @@
         <v>44929</v>
       </c>
       <c r="B354" t="n">
-        <v>3.073575496673584</v>
+        <v>3.073575735092163</v>
       </c>
       <c r="C354" t="n">
-        <v>3.285228922130196</v>
+        <v>3.285229176966823</v>
       </c>
       <c r="D354" t="n">
-        <v>3.064373183366795</v>
+        <v>3.064373421071546</v>
       </c>
       <c r="E354" t="n">
-        <v>3.257621982209828</v>
+        <v>3.257622234904972</v>
       </c>
       <c r="F354" t="n">
         <v>9560100</v>
@@ -7512,16 +7512,16 @@
         <v>44930</v>
       </c>
       <c r="B355" t="n">
-        <v>3.055171251296997</v>
+        <v>3.055171012878418</v>
       </c>
       <c r="C355" t="n">
-        <v>3.147194615248405</v>
+        <v>3.147194369648533</v>
       </c>
       <c r="D355" t="n">
-        <v>3.036766622386812</v>
+        <v>3.036766385404488</v>
       </c>
       <c r="E355" t="n">
-        <v>3.110385357428035</v>
+        <v>3.110385114700673</v>
       </c>
       <c r="F355" t="n">
         <v>10680900</v>
@@ -7652,16 +7652,16 @@
         <v>44939</v>
       </c>
       <c r="B362" t="n">
-        <v>3.073575496673584</v>
+        <v>3.073575735092163</v>
       </c>
       <c r="C362" t="n">
-        <v>3.22081272898267</v>
+        <v>3.220812978822505</v>
       </c>
       <c r="D362" t="n">
-        <v>3.055170870060005</v>
+        <v>3.05517110705093</v>
       </c>
       <c r="E362" t="n">
-        <v>3.184003475755512</v>
+        <v>3.184003722740037</v>
       </c>
       <c r="F362" t="n">
         <v>14486700</v>
@@ -7672,16 +7672,16 @@
         <v>44942</v>
       </c>
       <c r="B363" t="n">
-        <v>3.036766529083252</v>
+        <v>3.036766290664673</v>
       </c>
       <c r="C363" t="n">
-        <v>3.082778099945025</v>
+        <v>3.082777857914047</v>
       </c>
       <c r="D363" t="n">
-        <v>3.009159586566188</v>
+        <v>3.009159350315048</v>
       </c>
       <c r="E363" t="n">
-        <v>3.055171157427961</v>
+        <v>3.055170917564423</v>
       </c>
       <c r="F363" t="n">
         <v>8730700</v>
@@ -7692,16 +7692,16 @@
         <v>44943</v>
       </c>
       <c r="B364" t="n">
-        <v>3.09197998046875</v>
+        <v>3.091980218887329</v>
       </c>
       <c r="C364" t="n">
-        <v>3.128789451396135</v>
+        <v>3.128789692653045</v>
       </c>
       <c r="D364" t="n">
-        <v>3.027563790296605</v>
+        <v>3.027564023748135</v>
       </c>
       <c r="E364" t="n">
-        <v>3.05517072894181</v>
+        <v>3.055170964522075</v>
       </c>
       <c r="F364" t="n">
         <v>11859400</v>
@@ -7792,16 +7792,16 @@
         <v>44950</v>
       </c>
       <c r="B369" t="n">
-        <v>3.193205833435059</v>
+        <v>3.193206071853638</v>
       </c>
       <c r="C369" t="n">
-        <v>3.202408146869723</v>
+        <v>3.202408385975387</v>
       </c>
       <c r="D369" t="n">
-        <v>3.018361658775971</v>
+        <v>3.018361884139927</v>
       </c>
       <c r="E369" t="n">
-        <v>3.045968599079965</v>
+        <v>3.045968826505175</v>
       </c>
       <c r="F369" t="n">
         <v>12703800</v>
@@ -7812,16 +7812,16 @@
         <v>44951</v>
       </c>
       <c r="B370" t="n">
-        <v>3.248420000076294</v>
+        <v>3.248419761657715</v>
       </c>
       <c r="C370" t="n">
-        <v>3.248420000076294</v>
+        <v>3.248419761657715</v>
       </c>
       <c r="D370" t="n">
-        <v>3.147194543381774</v>
+        <v>3.147194312392662</v>
       </c>
       <c r="E370" t="n">
-        <v>3.193206114606555</v>
+        <v>3.193205880240413</v>
       </c>
       <c r="F370" t="n">
         <v>7649000</v>
@@ -7832,16 +7832,16 @@
         <v>44952</v>
       </c>
       <c r="B371" t="n">
-        <v>3.202408313751221</v>
+        <v>3.202408075332642</v>
       </c>
       <c r="C371" t="n">
-        <v>3.2852291389791</v>
+        <v>3.285228894394528</v>
       </c>
       <c r="D371" t="n">
-        <v>3.184003685922803</v>
+        <v>3.184003448874444</v>
       </c>
       <c r="E371" t="n">
-        <v>3.257622197236473</v>
+        <v>3.257621954707233</v>
       </c>
       <c r="F371" t="n">
         <v>8271800</v>
@@ -7852,16 +7852,16 @@
         <v>44953</v>
       </c>
       <c r="B372" t="n">
-        <v>3.147194385528564</v>
+        <v>3.147194623947144</v>
       </c>
       <c r="C372" t="n">
-        <v>3.220812895795746</v>
+        <v>3.220813139791363</v>
       </c>
       <c r="D372" t="n">
-        <v>3.128789757961769</v>
+        <v>3.128789994986088</v>
       </c>
       <c r="E372" t="n">
-        <v>3.211610582012349</v>
+        <v>3.211610825310835</v>
       </c>
       <c r="F372" t="n">
         <v>8557200</v>
@@ -7912,16 +7912,16 @@
         <v>44958</v>
       </c>
       <c r="B375" t="n">
-        <v>2.898731470108032</v>
+        <v>2.898731708526611</v>
       </c>
       <c r="C375" t="n">
-        <v>3.073575418489434</v>
+        <v>3.073575671288802</v>
       </c>
       <c r="D375" t="n">
-        <v>2.815910433053234</v>
+        <v>2.815910664659842</v>
       </c>
       <c r="E375" t="n">
-        <v>3.027563853125907</v>
+        <v>3.027564102140857</v>
       </c>
       <c r="F375" t="n">
         <v>404695000</v>
@@ -7972,16 +7972,16 @@
         <v>44963</v>
       </c>
       <c r="B378" t="n">
-        <v>2.898731470108032</v>
+        <v>2.898731708526611</v>
       </c>
       <c r="C378" t="n">
-        <v>2.944743035471559</v>
+        <v>2.944743277674556</v>
       </c>
       <c r="D378" t="n">
-        <v>2.806708119980529</v>
+        <v>2.806708350830254</v>
       </c>
       <c r="E378" t="n">
-        <v>2.852719685344056</v>
+        <v>2.852719919978199</v>
       </c>
       <c r="F378" t="n">
         <v>34861900</v>
@@ -7992,16 +7992,16 @@
         <v>44964</v>
       </c>
       <c r="B379" t="n">
-        <v>2.880326986312866</v>
+        <v>2.880327224731445</v>
       </c>
       <c r="C379" t="n">
-        <v>2.95394549453285</v>
+        <v>2.953945739045189</v>
       </c>
       <c r="D379" t="n">
-        <v>2.843517512802413</v>
+        <v>2.843517748174095</v>
       </c>
       <c r="E379" t="n">
-        <v>2.926338553950356</v>
+        <v>2.926338796177535</v>
       </c>
       <c r="F379" t="n">
         <v>31913300</v>
@@ -8012,16 +8012,16 @@
         <v>44965</v>
       </c>
       <c r="B380" t="n">
-        <v>3.036766529083252</v>
+        <v>3.036766290664673</v>
       </c>
       <c r="C380" t="n">
-        <v>3.036766529083252</v>
+        <v>3.036766290664673</v>
       </c>
       <c r="D380" t="n">
-        <v>2.861922340408036</v>
+        <v>2.861922115716591</v>
       </c>
       <c r="E380" t="n">
-        <v>2.907934130670286</v>
+        <v>2.907933902366425</v>
       </c>
       <c r="F380" t="n">
         <v>50518000</v>
@@ -8032,16 +8032,16 @@
         <v>44966</v>
       </c>
       <c r="B381" t="n">
-        <v>3.018362045288086</v>
+        <v>3.018361806869507</v>
       </c>
       <c r="C381" t="n">
-        <v>3.091980562192519</v>
+        <v>3.091980317958858</v>
       </c>
       <c r="D381" t="n">
-        <v>2.935541213770599</v>
+        <v>2.935540981893987</v>
       </c>
       <c r="E381" t="n">
-        <v>3.036766674514194</v>
+        <v>3.036766434641845</v>
       </c>
       <c r="F381" t="n">
         <v>43678900</v>
@@ -8092,16 +8092,16 @@
         <v>44971</v>
       </c>
       <c r="B384" t="n">
-        <v>2.742292165756226</v>
+        <v>2.742291927337646</v>
       </c>
       <c r="C384" t="n">
-        <v>2.953945604142814</v>
+        <v>2.9539453473228</v>
       </c>
       <c r="D384" t="n">
-        <v>2.723887538018302</v>
+        <v>2.723887301199846</v>
       </c>
       <c r="E384" t="n">
-        <v>2.953945604142814</v>
+        <v>2.9539453473228</v>
       </c>
       <c r="F384" t="n">
         <v>40924300</v>
@@ -8132,16 +8132,16 @@
         <v>44973</v>
       </c>
       <c r="B386" t="n">
-        <v>2.834315299987793</v>
+        <v>2.834315538406372</v>
       </c>
       <c r="C386" t="n">
-        <v>2.871124555405743</v>
+        <v>2.871124796920665</v>
       </c>
       <c r="D386" t="n">
-        <v>2.760696789151893</v>
+        <v>2.760697021377787</v>
       </c>
       <c r="E386" t="n">
-        <v>2.825112986133305</v>
+        <v>2.825113223777799</v>
       </c>
       <c r="F386" t="n">
         <v>21149000</v>
@@ -8172,16 +8172,16 @@
         <v>44979</v>
       </c>
       <c r="B388" t="n">
-        <v>2.834315299987793</v>
+        <v>2.834315538406372</v>
       </c>
       <c r="C388" t="n">
-        <v>2.84351761384228</v>
+        <v>2.843517853034945</v>
       </c>
       <c r="D388" t="n">
-        <v>2.714685219879454</v>
+        <v>2.714685448234921</v>
       </c>
       <c r="E388" t="n">
-        <v>2.76989910300638</v>
+        <v>2.76989933600636</v>
       </c>
       <c r="F388" t="n">
         <v>20601900</v>
@@ -8252,16 +8252,16 @@
         <v>44985</v>
       </c>
       <c r="B392" t="n">
-        <v>2.834315299987793</v>
+        <v>2.834315538406372</v>
       </c>
       <c r="C392" t="n">
-        <v>2.889529402515187</v>
+        <v>2.889529645578298</v>
       </c>
       <c r="D392" t="n">
-        <v>2.797506044569843</v>
+        <v>2.79750627989208</v>
       </c>
       <c r="E392" t="n">
-        <v>2.825112986133305</v>
+        <v>2.825113223777799</v>
       </c>
       <c r="F392" t="n">
         <v>28842300</v>
@@ -8292,16 +8292,16 @@
         <v>44987</v>
       </c>
       <c r="B394" t="n">
-        <v>2.687078237533569</v>
+        <v>2.687078475952148</v>
       </c>
       <c r="C394" t="n">
-        <v>2.797506002111432</v>
+        <v>2.797506250328025</v>
       </c>
       <c r="D394" t="n">
-        <v>2.687078237533569</v>
+        <v>2.687078475952148</v>
       </c>
       <c r="E394" t="n">
-        <v>2.779101374681788</v>
+        <v>2.779101621265379</v>
       </c>
       <c r="F394" t="n">
         <v>21864000</v>
@@ -8312,16 +8312,16 @@
         <v>44988</v>
       </c>
       <c r="B395" t="n">
-        <v>2.604257106781006</v>
+        <v>2.604257345199585</v>
       </c>
       <c r="C395" t="n">
-        <v>2.714685087031328</v>
+        <v>2.71468533555954</v>
       </c>
       <c r="D395" t="n">
-        <v>2.558245539760229</v>
+        <v>2.55824577396647</v>
       </c>
       <c r="E395" t="n">
-        <v>2.714685087031328</v>
+        <v>2.71468533555954</v>
       </c>
       <c r="F395" t="n">
         <v>36019100</v>
@@ -8572,16 +8572,16 @@
         <v>45007</v>
       </c>
       <c r="B408" t="n">
-        <v>2.216452598571777</v>
+        <v>2.216452836990356</v>
       </c>
       <c r="C408" t="n">
-        <v>2.273528805389769</v>
+        <v>2.273529049947901</v>
       </c>
       <c r="D408" t="n">
-        <v>2.197427271899042</v>
+        <v>2.197427508271111</v>
       </c>
       <c r="E408" t="n">
-        <v>2.254503251917249</v>
+        <v>2.254503494428847</v>
       </c>
       <c r="F408" t="n">
         <v>26704400</v>
@@ -8612,16 +8612,16 @@
         <v>45009</v>
       </c>
       <c r="B410" t="n">
-        <v>2.292553901672363</v>
+        <v>2.292554140090942</v>
       </c>
       <c r="C410" t="n">
-        <v>2.302066564052756</v>
+        <v>2.302066803460623</v>
       </c>
       <c r="D410" t="n">
-        <v>2.149863739166705</v>
+        <v>2.149863962745944</v>
       </c>
       <c r="E410" t="n">
-        <v>2.159376401547098</v>
+        <v>2.159376626115625</v>
       </c>
       <c r="F410" t="n">
         <v>19141800</v>
@@ -8652,16 +8652,16 @@
         <v>45013</v>
       </c>
       <c r="B412" t="n">
-        <v>2.520858287811279</v>
+        <v>2.520858526229858</v>
       </c>
       <c r="C412" t="n">
-        <v>2.549396277920867</v>
+        <v>2.549396519038522</v>
       </c>
       <c r="D412" t="n">
-        <v>2.340117456984101</v>
+        <v>2.340117678308513</v>
       </c>
       <c r="E412" t="n">
-        <v>2.368655447093689</v>
+        <v>2.368655671117177</v>
       </c>
       <c r="F412" t="n">
         <v>69618900</v>
@@ -8692,16 +8692,16 @@
         <v>45015</v>
       </c>
       <c r="B414" t="n">
-        <v>2.749162197113037</v>
+        <v>2.749162435531616</v>
       </c>
       <c r="C414" t="n">
-        <v>2.796725509838225</v>
+        <v>2.796725752381689</v>
       </c>
       <c r="D414" t="n">
-        <v>2.644522682317859</v>
+        <v>2.644522911661672</v>
       </c>
       <c r="E414" t="n">
-        <v>2.673060669952971</v>
+        <v>2.673060901771716</v>
       </c>
       <c r="F414" t="n">
         <v>39786400</v>
@@ -8732,16 +8732,16 @@
         <v>45019</v>
       </c>
       <c r="B416" t="n">
-        <v>2.692086458206177</v>
+        <v>2.692086219787598</v>
       </c>
       <c r="C416" t="n">
-        <v>2.76818799845922</v>
+        <v>2.768187753300879</v>
       </c>
       <c r="D416" t="n">
-        <v>2.673061129842867</v>
+        <v>2.673060893109223</v>
       </c>
       <c r="E416" t="n">
-        <v>2.739650005914255</v>
+        <v>2.739649763283318</v>
       </c>
       <c r="F416" t="n">
         <v>18815900</v>
@@ -8752,16 +8752,16 @@
         <v>45020</v>
       </c>
       <c r="B417" t="n">
-        <v>2.692086458206177</v>
+        <v>2.692086219787598</v>
       </c>
       <c r="C417" t="n">
-        <v>2.739650005914255</v>
+        <v>2.739649763283318</v>
       </c>
       <c r="D417" t="n">
-        <v>2.654035801479557</v>
+        <v>2.654035566430849</v>
       </c>
       <c r="E417" t="n">
-        <v>2.720624450751141</v>
+        <v>2.720624209805159</v>
       </c>
       <c r="F417" t="n">
         <v>21012200</v>
@@ -8772,16 +8772,16 @@
         <v>45021</v>
       </c>
       <c r="B418" t="n">
-        <v>2.682573556900024</v>
+        <v>2.682573795318604</v>
       </c>
       <c r="C418" t="n">
-        <v>2.720624210263179</v>
+        <v>2.720624452063579</v>
       </c>
       <c r="D418" t="n">
-        <v>2.615984913514504</v>
+        <v>2.615985146014897</v>
       </c>
       <c r="E418" t="n">
-        <v>2.701598883581602</v>
+        <v>2.701599123691091</v>
       </c>
       <c r="F418" t="n">
         <v>22336100</v>
@@ -8792,16 +8792,16 @@
         <v>45022</v>
       </c>
       <c r="B419" t="n">
-        <v>2.654035329818726</v>
+        <v>2.654035568237305</v>
       </c>
       <c r="C419" t="n">
-        <v>2.682573317292073</v>
+        <v>2.68257355827429</v>
       </c>
       <c r="D419" t="n">
-        <v>2.615984679854262</v>
+        <v>2.615984914854657</v>
       </c>
       <c r="E419" t="n">
-        <v>2.673060654800957</v>
+        <v>2.673060894928629</v>
       </c>
       <c r="F419" t="n">
         <v>14613400</v>
@@ -8872,16 +8872,16 @@
         <v>45029</v>
       </c>
       <c r="B423" t="n">
-        <v>2.882339715957642</v>
+        <v>2.882339954376221</v>
       </c>
       <c r="C423" t="n">
-        <v>2.95844102273943</v>
+        <v>2.958441267452883</v>
       </c>
       <c r="D423" t="n">
-        <v>2.853801725914471</v>
+        <v>2.853801961972472</v>
       </c>
       <c r="E423" t="n">
-        <v>2.929903032696259</v>
+        <v>2.929903275049135</v>
       </c>
       <c r="F423" t="n">
         <v>15780900</v>
@@ -8952,16 +8952,16 @@
         <v>45035</v>
       </c>
       <c r="B427" t="n">
-        <v>2.882339715957642</v>
+        <v>2.882339954376221</v>
       </c>
       <c r="C427" t="n">
-        <v>2.996491902930108</v>
+        <v>2.996492150791017</v>
       </c>
       <c r="D427" t="n">
-        <v>2.872827052609918</v>
+        <v>2.872827290241638</v>
       </c>
       <c r="E427" t="n">
-        <v>2.986979239582385</v>
+        <v>2.986979486656434</v>
       </c>
       <c r="F427" t="n">
         <v>19845900</v>
@@ -9052,16 +9052,16 @@
         <v>45043</v>
       </c>
       <c r="B432" t="n">
-        <v>2.977466821670532</v>
+        <v>2.977466583251953</v>
       </c>
       <c r="C432" t="n">
-        <v>3.006004814066121</v>
+        <v>3.006004573362382</v>
       </c>
       <c r="D432" t="n">
-        <v>2.891852617683963</v>
+        <v>2.891852386120882</v>
       </c>
       <c r="E432" t="n">
-        <v>2.901365281815826</v>
+        <v>2.901365049491024</v>
       </c>
       <c r="F432" t="n">
         <v>12242300</v>
@@ -9072,16 +9072,16 @@
         <v>45044</v>
       </c>
       <c r="B433" t="n">
-        <v>3.034542560577393</v>
+        <v>3.034542798995972</v>
       </c>
       <c r="C433" t="n">
-        <v>3.091618540743791</v>
+        <v>3.091618783646728</v>
       </c>
       <c r="D433" t="n">
-        <v>2.939415700166944</v>
+        <v>2.939415931111576</v>
       </c>
       <c r="E433" t="n">
-        <v>2.977466580410994</v>
+        <v>2.977466814345215</v>
       </c>
       <c r="F433" t="n">
         <v>20412700</v>
@@ -9112,16 +9112,16 @@
         <v>45049</v>
       </c>
       <c r="B435" t="n">
-        <v>2.9964919090271</v>
+        <v>2.996491670608521</v>
       </c>
       <c r="C435" t="n">
-        <v>3.034542562495416</v>
+        <v>3.034542321049302</v>
       </c>
       <c r="D435" t="n">
-        <v>2.853801731721129</v>
+        <v>2.853801504655823</v>
       </c>
       <c r="E435" t="n">
-        <v>2.910877711923603</v>
+        <v>2.910877480316995</v>
       </c>
       <c r="F435" t="n">
         <v>15681500</v>
@@ -9252,16 +9252,16 @@
         <v>45058</v>
       </c>
       <c r="B442" t="n">
-        <v>3.129669427871704</v>
+        <v>3.129669189453125</v>
       </c>
       <c r="C442" t="n">
-        <v>3.215283631313659</v>
+        <v>3.21528338637298</v>
       </c>
       <c r="D442" t="n">
-        <v>3.091618771586302</v>
+        <v>3.091618536066427</v>
       </c>
       <c r="E442" t="n">
-        <v>3.167720084157106</v>
+        <v>3.167719842839823</v>
       </c>
       <c r="F442" t="n">
         <v>13638800</v>
@@ -9272,16 +9272,16 @@
         <v>45061</v>
       </c>
       <c r="B443" t="n">
-        <v>2.986979484558105</v>
+        <v>2.986979246139526</v>
       </c>
       <c r="C443" t="n">
-        <v>3.20577075949981</v>
+        <v>3.205770503617468</v>
       </c>
       <c r="D443" t="n">
-        <v>2.901365280607201</v>
+        <v>2.901365049022286</v>
       </c>
       <c r="E443" t="n">
-        <v>3.18674543124401</v>
+        <v>3.186745176880255</v>
       </c>
       <c r="F443" t="n">
         <v>71533500</v>
@@ -9292,16 +9292,16 @@
         <v>45062</v>
       </c>
       <c r="B444" t="n">
-        <v>3.082105875015259</v>
+        <v>3.082106113433838</v>
       </c>
       <c r="C444" t="n">
-        <v>3.139181855137815</v>
+        <v>3.139182097971549</v>
       </c>
       <c r="D444" t="n">
-        <v>2.977466578123905</v>
+        <v>2.977466808448034</v>
       </c>
       <c r="E444" t="n">
-        <v>2.977466578123905</v>
+        <v>2.977466808448034</v>
       </c>
       <c r="F444" t="n">
         <v>45623200</v>
@@ -9352,16 +9352,16 @@
         <v>45065</v>
       </c>
       <c r="B447" t="n">
-        <v>3.491150856018066</v>
+        <v>3.491151094436646</v>
       </c>
       <c r="C447" t="n">
-        <v>3.519688846105434</v>
+        <v>3.519689086472937</v>
       </c>
       <c r="D447" t="n">
-        <v>3.281872035244253</v>
+        <v>3.281872259370709</v>
       </c>
       <c r="E447" t="n">
-        <v>3.329435352056533</v>
+        <v>3.329435579431195</v>
       </c>
       <c r="F447" t="n">
         <v>32544700</v>
@@ -9372,16 +9372,16 @@
         <v>45068</v>
       </c>
       <c r="B448" t="n">
-        <v>3.47212553024292</v>
+        <v>3.472125768661499</v>
       </c>
       <c r="C448" t="n">
-        <v>3.576764827258557</v>
+        <v>3.576765072862347</v>
       </c>
       <c r="D448" t="n">
-        <v>3.453100203512804</v>
+        <v>3.453100440624981</v>
       </c>
       <c r="E448" t="n">
-        <v>3.548226837163384</v>
+        <v>3.54822708080757</v>
       </c>
       <c r="F448" t="n">
         <v>14142300</v>
@@ -9392,16 +9392,16 @@
         <v>45069</v>
       </c>
       <c r="B449" t="n">
-        <v>3.47212553024292</v>
+        <v>3.472125768661499</v>
       </c>
       <c r="C449" t="n">
-        <v>3.5672521638935</v>
+        <v>3.567252408844088</v>
       </c>
       <c r="D449" t="n">
-        <v>3.443587313347962</v>
+        <v>3.443587549806922</v>
       </c>
       <c r="E449" t="n">
-        <v>3.47212553024292</v>
+        <v>3.472125768661499</v>
       </c>
       <c r="F449" t="n">
         <v>12031500</v>
@@ -9472,16 +9472,16 @@
         <v>45075</v>
       </c>
       <c r="B453" t="n">
-        <v>3.357973575592041</v>
+        <v>3.357973337173462</v>
       </c>
       <c r="C453" t="n">
-        <v>3.415049559734729</v>
+        <v>3.415049317263714</v>
       </c>
       <c r="D453" t="n">
-        <v>3.291384927425571</v>
+        <v>3.291384693734835</v>
       </c>
       <c r="E453" t="n">
-        <v>3.319922919496916</v>
+        <v>3.319922683779961</v>
       </c>
       <c r="F453" t="n">
         <v>14544800</v>
@@ -9492,16 +9492,16 @@
         <v>45076</v>
       </c>
       <c r="B454" t="n">
-        <v>3.424562215805054</v>
+        <v>3.424561977386475</v>
       </c>
       <c r="C454" t="n">
-        <v>3.462613098611607</v>
+        <v>3.46261285754392</v>
       </c>
       <c r="D454" t="n">
-        <v>3.310410247784792</v>
+        <v>3.310410017313492</v>
       </c>
       <c r="E454" t="n">
-        <v>3.396024223799988</v>
+        <v>3.396023987368229</v>
       </c>
       <c r="F454" t="n">
         <v>24140700</v>
@@ -9572,16 +9572,16 @@
         <v>45082</v>
       </c>
       <c r="B458" t="n">
-        <v>3.586277723312378</v>
+        <v>3.586277484893799</v>
       </c>
       <c r="C458" t="n">
-        <v>3.605303051276916</v>
+        <v>3.605302811593518</v>
       </c>
       <c r="D458" t="n">
-        <v>3.500663747471958</v>
+        <v>3.500663514745063</v>
       </c>
       <c r="E458" t="n">
-        <v>3.510176411454227</v>
+        <v>3.510176178094923</v>
       </c>
       <c r="F458" t="n">
         <v>11705300</v>
@@ -9652,16 +9652,16 @@
         <v>45089</v>
       </c>
       <c r="B462" t="n">
-        <v>3.795556306838989</v>
+        <v>3.79555606842041</v>
       </c>
       <c r="C462" t="n">
-        <v>3.805068970192479</v>
+        <v>3.80506873117636</v>
       </c>
       <c r="D462" t="n">
-        <v>3.74799299007154</v>
+        <v>3.74799275464066</v>
       </c>
       <c r="E462" t="n">
-        <v>3.786043643485499</v>
+        <v>3.78604340566446</v>
       </c>
       <c r="F462" t="n">
         <v>16242400</v>
@@ -9672,16 +9672,16 @@
         <v>45090</v>
       </c>
       <c r="B463" t="n">
-        <v>3.700429677963257</v>
+        <v>3.700429916381836</v>
       </c>
       <c r="C463" t="n">
-        <v>3.814581865148647</v>
+        <v>3.814582110922048</v>
       </c>
       <c r="D463" t="n">
-        <v>3.662378797701604</v>
+        <v>3.662379033668566</v>
       </c>
       <c r="E463" t="n">
-        <v>3.78604364825246</v>
+        <v>3.786043892187145</v>
       </c>
       <c r="F463" t="n">
         <v>19986600</v>
@@ -9752,16 +9752,16 @@
         <v>45096</v>
       </c>
       <c r="B467" t="n">
-        <v>3.776530742645264</v>
+        <v>3.776530981063843</v>
       </c>
       <c r="C467" t="n">
-        <v>3.814581620466182</v>
+        <v>3.814581861286975</v>
       </c>
       <c r="D467" t="n">
-        <v>3.738480091624116</v>
+        <v>3.738480327640495</v>
       </c>
       <c r="E467" t="n">
-        <v>3.786043405400551</v>
+        <v>3.78604364441968</v>
       </c>
       <c r="F467" t="n">
         <v>9550900</v>
@@ -9772,16 +9772,16 @@
         <v>45097</v>
       </c>
       <c r="B468" t="n">
-        <v>3.947759389877319</v>
+        <v>3.947758913040161</v>
       </c>
       <c r="C468" t="n">
-        <v>3.966784717753371</v>
+        <v>3.966784238618205</v>
       </c>
       <c r="D468" t="n">
-        <v>3.767018548255029</v>
+        <v>3.767018093248975</v>
       </c>
       <c r="E468" t="n">
-        <v>3.786043876131081</v>
+        <v>3.786043418827019</v>
       </c>
       <c r="F468" t="n">
         <v>35176100</v>
@@ -9792,16 +9792,16 @@
         <v>45098</v>
       </c>
       <c r="B469" t="n">
-        <v>4.023859977722168</v>
+        <v>4.023860454559326</v>
       </c>
       <c r="C469" t="n">
-        <v>4.042885302176666</v>
+        <v>4.042885781268371</v>
       </c>
       <c r="D469" t="n">
-        <v>3.900195141968175</v>
+        <v>3.90019560415075</v>
       </c>
       <c r="E469" t="n">
-        <v>3.966784004358674</v>
+        <v>3.966784474432191</v>
       </c>
       <c r="F469" t="n">
         <v>23935400</v>
@@ -9852,16 +9852,16 @@
         <v>45103</v>
       </c>
       <c r="B472" t="n">
-        <v>4.204601764678955</v>
+        <v>4.204601287841797</v>
       </c>
       <c r="C472" t="n">
-        <v>4.280703080195378</v>
+        <v>4.280702594727692</v>
       </c>
       <c r="D472" t="n">
-        <v>4.128500449162532</v>
+        <v>4.128499980955902</v>
       </c>
       <c r="E472" t="n">
-        <v>4.138012886802275</v>
+        <v>4.138012417516855</v>
       </c>
       <c r="F472" t="n">
         <v>42881900</v>
@@ -9912,16 +9912,16 @@
         <v>45106</v>
       </c>
       <c r="B475" t="n">
-        <v>4.366317272186279</v>
+        <v>4.366316795349121</v>
       </c>
       <c r="C475" t="n">
-        <v>4.366317272186279</v>
+        <v>4.366316795349121</v>
       </c>
       <c r="D475" t="n">
-        <v>4.185576421646147</v>
+        <v>4.185575964547351</v>
       </c>
       <c r="E475" t="n">
-        <v>4.185576421646147</v>
+        <v>4.185575964547351</v>
       </c>
       <c r="F475" t="n">
         <v>40765500</v>
@@ -9932,16 +9932,16 @@
         <v>45107</v>
       </c>
       <c r="B476" t="n">
-        <v>4.185575485229492</v>
+        <v>4.18557596206665</v>
       </c>
       <c r="C476" t="n">
-        <v>4.489980678162862</v>
+        <v>4.489981189679052</v>
       </c>
       <c r="D476" t="n">
-        <v>4.138011947033895</v>
+        <v>4.138012418452428</v>
       </c>
       <c r="E476" t="n">
-        <v>4.41387937992952</v>
+        <v>4.413879882775952</v>
       </c>
       <c r="F476" t="n">
         <v>35419200</v>
@@ -9992,16 +9992,16 @@
         <v>45112</v>
       </c>
       <c r="B479" t="n">
-        <v>4.080936431884766</v>
+        <v>4.080936908721924</v>
       </c>
       <c r="C479" t="n">
-        <v>4.185575955512459</v>
+        <v>4.185576444576225</v>
       </c>
       <c r="D479" t="n">
-        <v>4.023860451796815</v>
+        <v>4.023860921964928</v>
       </c>
       <c r="E479" t="n">
-        <v>4.166550628816475</v>
+        <v>4.166551115657227</v>
       </c>
       <c r="F479" t="n">
         <v>33346200</v>
@@ -10012,16 +10012,16 @@
         <v>45113</v>
       </c>
       <c r="B480" t="n">
-        <v>3.957271814346313</v>
+        <v>3.957271575927734</v>
       </c>
       <c r="C480" t="n">
-        <v>4.061911344129392</v>
+        <v>4.061911099406468</v>
       </c>
       <c r="D480" t="n">
-        <v>3.909708721608256</v>
+        <v>3.909708486055269</v>
       </c>
       <c r="E480" t="n">
-        <v>4.061911344129392</v>
+        <v>4.061911099406468</v>
       </c>
       <c r="F480" t="n">
         <v>22675100</v>
@@ -10032,16 +10032,16 @@
         <v>45114</v>
       </c>
       <c r="B481" t="n">
-        <v>3.995322465896606</v>
+        <v>3.995322704315186</v>
       </c>
       <c r="C481" t="n">
-        <v>4.042886012185687</v>
+        <v>4.042886253442594</v>
       </c>
       <c r="D481" t="n">
-        <v>3.94775937320712</v>
+        <v>3.947759608787399</v>
       </c>
       <c r="E481" t="n">
-        <v>3.976297138100893</v>
+        <v>3.976297375384147</v>
       </c>
       <c r="F481" t="n">
         <v>19055100</v>
@@ -10052,16 +10052,16 @@
         <v>45117</v>
       </c>
       <c r="B482" t="n">
-        <v>4.03337287902832</v>
+        <v>4.033373355865479</v>
       </c>
       <c r="C482" t="n">
-        <v>4.099961749110232</v>
+        <v>4.099962233819722</v>
       </c>
       <c r="D482" t="n">
-        <v>3.947759135893939</v>
+        <v>3.94775960260959</v>
       </c>
       <c r="E482" t="n">
-        <v>3.995322225724247</v>
+        <v>3.995322698062945</v>
       </c>
       <c r="F482" t="n">
         <v>16685100</v>
@@ -10112,16 +10112,16 @@
         <v>45120</v>
       </c>
       <c r="B485" t="n">
-        <v>3.995322465896606</v>
+        <v>3.995322704315186</v>
       </c>
       <c r="C485" t="n">
-        <v>4.071424230679055</v>
+        <v>4.071424473638964</v>
       </c>
       <c r="D485" t="n">
-        <v>3.957271810305179</v>
+        <v>3.957272046453107</v>
       </c>
       <c r="E485" t="n">
-        <v>4.023860684389974</v>
+        <v>4.023860924511555</v>
       </c>
       <c r="F485" t="n">
         <v>10522300</v>
@@ -10132,16 +10132,16 @@
         <v>45121</v>
       </c>
       <c r="B486" t="n">
-        <v>3.881170272827148</v>
+        <v>3.881170034408569</v>
       </c>
       <c r="C486" t="n">
-        <v>4.01434755963212</v>
+        <v>4.014347313032519</v>
       </c>
       <c r="D486" t="n">
-        <v>3.814581856224446</v>
+        <v>3.814581621896365</v>
       </c>
       <c r="E486" t="n">
-        <v>3.995322232945695</v>
+        <v>3.995321987514812</v>
       </c>
       <c r="F486" t="n">
         <v>16845900</v>
@@ -10152,16 +10152,16 @@
         <v>45124</v>
       </c>
       <c r="B487" t="n">
-        <v>4.023859977722168</v>
+        <v>4.023860454559326</v>
       </c>
       <c r="C487" t="n">
-        <v>4.042885302176666</v>
+        <v>4.042885781268371</v>
       </c>
       <c r="D487" t="n">
-        <v>3.852632057631688</v>
+        <v>3.852632514177922</v>
       </c>
       <c r="E487" t="n">
-        <v>3.881169817513677</v>
+        <v>3.881170277441705</v>
       </c>
       <c r="F487" t="n">
         <v>20863600</v>
@@ -10212,16 +10212,16 @@
         <v>45127</v>
       </c>
       <c r="B490" t="n">
-        <v>3.995322465896606</v>
+        <v>3.995322704315186</v>
       </c>
       <c r="C490" t="n">
-        <v>4.080936667777115</v>
+        <v>4.080936911304672</v>
       </c>
       <c r="D490" t="n">
-        <v>3.94775937320712</v>
+        <v>3.947759608787399</v>
       </c>
       <c r="E490" t="n">
-        <v>4.071424230679055</v>
+        <v>4.071424473638964</v>
       </c>
       <c r="F490" t="n">
         <v>13981900</v>
@@ -10252,16 +10252,16 @@
         <v>45131</v>
       </c>
       <c r="B492" t="n">
-        <v>4.023859977722168</v>
+        <v>4.023860454559326</v>
       </c>
       <c r="C492" t="n">
-        <v>4.080935951085661</v>
+        <v>4.080936434686461</v>
       </c>
       <c r="D492" t="n">
-        <v>3.947758679904177</v>
+        <v>3.947759147723147</v>
       </c>
       <c r="E492" t="n">
-        <v>4.061910626631164</v>
+        <v>4.061911107977416</v>
       </c>
       <c r="F492" t="n">
         <v>17283700</v>
@@ -10272,16 +10272,16 @@
         <v>45132</v>
       </c>
       <c r="B493" t="n">
-        <v>3.995322465896606</v>
+        <v>3.995322704315186</v>
       </c>
       <c r="C493" t="n">
-        <v>4.090449558474769</v>
+        <v>4.090449802570003</v>
       </c>
       <c r="D493" t="n">
-        <v>3.966784701002833</v>
+        <v>3.966784937718438</v>
       </c>
       <c r="E493" t="n">
-        <v>4.061911339981402</v>
+        <v>4.061911582373633</v>
       </c>
       <c r="F493" t="n">
         <v>14413200</v>
@@ -10312,16 +10312,16 @@
         <v>45134</v>
       </c>
       <c r="B495" t="n">
-        <v>3.893998622894287</v>
+        <v>3.893998384475708</v>
       </c>
       <c r="C495" t="n">
-        <v>4.056646823940207</v>
+        <v>4.056646575563136</v>
       </c>
       <c r="D495" t="n">
-        <v>3.884430840129649</v>
+        <v>3.884430602296878</v>
       </c>
       <c r="E495" t="n">
-        <v>4.047079497392562</v>
+        <v>4.047079249601271</v>
       </c>
       <c r="F495" t="n">
         <v>18331700</v>
@@ -10352,16 +10352,16 @@
         <v>45138</v>
       </c>
       <c r="B497" t="n">
-        <v>3.980106115341187</v>
+        <v>3.980106353759766</v>
       </c>
       <c r="C497" t="n">
-        <v>4.008809005461245</v>
+        <v>4.008809245599202</v>
       </c>
       <c r="D497" t="n">
-        <v>3.922700791318031</v>
+        <v>3.922701026297883</v>
       </c>
       <c r="E497" t="n">
-        <v>3.941835899325749</v>
+        <v>3.941836135451844</v>
       </c>
       <c r="F497" t="n">
         <v>13989300</v>
@@ -10372,16 +10372,16 @@
         <v>45139</v>
       </c>
       <c r="B498" t="n">
-        <v>3.980106115341187</v>
+        <v>3.980106353759766</v>
       </c>
       <c r="C498" t="n">
-        <v>4.018376331356624</v>
+        <v>4.018376572067687</v>
       </c>
       <c r="D498" t="n">
-        <v>3.884430575302593</v>
+        <v>3.884430807989962</v>
       </c>
       <c r="E498" t="n">
-        <v>3.970538789445808</v>
+        <v>3.970539027291279</v>
       </c>
       <c r="F498" t="n">
         <v>24308900</v>
@@ -10412,16 +10412,16 @@
         <v>45141</v>
       </c>
       <c r="B500" t="n">
-        <v>3.922700881958008</v>
+        <v>3.922701120376587</v>
       </c>
       <c r="C500" t="n">
-        <v>4.037511532657195</v>
+        <v>4.037511778053872</v>
       </c>
       <c r="D500" t="n">
-        <v>3.893998447391697</v>
+        <v>3.893998684065766</v>
       </c>
       <c r="E500" t="n">
-        <v>4.027944206540749</v>
+        <v>4.027944451355932</v>
       </c>
       <c r="F500" t="n">
         <v>21426900</v>
@@ -10552,16 +10552,16 @@
         <v>45152</v>
       </c>
       <c r="B507" t="n">
-        <v>3.606971263885498</v>
+        <v>3.606971502304077</v>
       </c>
       <c r="C507" t="n">
-        <v>3.664376587634967</v>
+        <v>3.664376829848003</v>
       </c>
       <c r="D507" t="n">
-        <v>3.568701048052518</v>
+        <v>3.56870128394146</v>
       </c>
       <c r="E507" t="n">
-        <v>3.664376587634967</v>
+        <v>3.664376829848003</v>
       </c>
       <c r="F507" t="n">
         <v>20072900</v>
@@ -10632,16 +10632,16 @@
         <v>45156</v>
       </c>
       <c r="B511" t="n">
-        <v>3.434755086898804</v>
+        <v>3.434755325317383</v>
       </c>
       <c r="C511" t="n">
-        <v>3.473025531089514</v>
+        <v>3.473025772164581</v>
       </c>
       <c r="D511" t="n">
-        <v>3.339079546693231</v>
+        <v>3.33907977847063</v>
       </c>
       <c r="E511" t="n">
-        <v>3.358214654734345</v>
+        <v>3.35821488783998</v>
       </c>
       <c r="F511" t="n">
         <v>15864700</v>
@@ -10692,16 +10692,16 @@
         <v>45161</v>
       </c>
       <c r="B514" t="n">
-        <v>3.453890085220337</v>
+        <v>3.453890323638916</v>
       </c>
       <c r="C514" t="n">
-        <v>3.559133404211688</v>
+        <v>3.559133649895108</v>
       </c>
       <c r="D514" t="n">
-        <v>3.377349655487335</v>
+        <v>3.377349888622405</v>
       </c>
       <c r="E514" t="n">
-        <v>3.396484762920585</v>
+        <v>3.396484997376533</v>
       </c>
       <c r="F514" t="n">
         <v>43718400</v>
@@ -10712,16 +10712,16 @@
         <v>45162</v>
       </c>
       <c r="B515" t="n">
-        <v>3.568701505661011</v>
+        <v>3.568701267242432</v>
       </c>
       <c r="C515" t="n">
-        <v>3.645241947141619</v>
+        <v>3.64524170360951</v>
       </c>
       <c r="D515" t="n">
-        <v>3.444323060146513</v>
+        <v>3.444322830037436</v>
       </c>
       <c r="E515" t="n">
-        <v>3.453890615331589</v>
+        <v>3.453890384583321</v>
       </c>
       <c r="F515" t="n">
         <v>42127000</v>
@@ -10912,16 +10912,16 @@
         <v>45177</v>
       </c>
       <c r="B525" t="n">
-        <v>3.549566030502319</v>
+        <v>3.54956579208374</v>
       </c>
       <c r="C525" t="n">
-        <v>3.587836247309597</v>
+        <v>3.58783600632047</v>
       </c>
       <c r="D525" t="n">
-        <v>3.511295813695041</v>
+        <v>3.51129557784701</v>
       </c>
       <c r="E525" t="n">
-        <v>3.53043092209868</v>
+        <v>3.530430684965375</v>
       </c>
       <c r="F525" t="n">
         <v>26042800</v>
@@ -10952,16 +10952,16 @@
         <v>45181</v>
       </c>
       <c r="B527" t="n">
-        <v>3.712214946746826</v>
+        <v>3.712214708328247</v>
       </c>
       <c r="C527" t="n">
-        <v>3.769620276082045</v>
+        <v>3.769620033976584</v>
       </c>
       <c r="D527" t="n">
-        <v>3.616539169746294</v>
+        <v>3.616538937472532</v>
       </c>
       <c r="E527" t="n">
-        <v>3.6356742795247</v>
+        <v>3.635674046021977</v>
       </c>
       <c r="F527" t="n">
         <v>15715300</v>
@@ -11112,16 +11112,16 @@
         <v>45191</v>
       </c>
       <c r="B535" t="n">
-        <v>3.606971263885498</v>
+        <v>3.606971502304077</v>
       </c>
       <c r="C535" t="n">
-        <v>3.664376587634967</v>
+        <v>3.664376829848003</v>
       </c>
       <c r="D535" t="n">
-        <v>3.559133494094274</v>
+        <v>3.559133729350806</v>
       </c>
       <c r="E535" t="n">
-        <v>3.597403709927253</v>
+        <v>3.597403947713423</v>
       </c>
       <c r="F535" t="n">
         <v>21984900</v>
@@ -11192,16 +11192,16 @@
         <v>45197</v>
       </c>
       <c r="B539" t="n">
-        <v>3.41562032699585</v>
+        <v>3.415620088577271</v>
       </c>
       <c r="C539" t="n">
-        <v>3.444322991983049</v>
+        <v>3.444322751560954</v>
       </c>
       <c r="D539" t="n">
-        <v>3.32951233203425</v>
+        <v>3.329512099626217</v>
       </c>
       <c r="E539" t="n">
-        <v>3.41562032699585</v>
+        <v>3.415620088577271</v>
       </c>
       <c r="F539" t="n">
         <v>16733500</v>
@@ -11252,16 +11252,16 @@
         <v>45202</v>
       </c>
       <c r="B542" t="n">
-        <v>3.310376882553101</v>
+        <v>3.31037712097168</v>
       </c>
       <c r="C542" t="n">
-        <v>3.406052422698603</v>
+        <v>3.406052668007885</v>
       </c>
       <c r="D542" t="n">
-        <v>3.2721066664949</v>
+        <v>3.272106902157197</v>
       </c>
       <c r="E542" t="n">
-        <v>3.31994443656765</v>
+        <v>3.3199446756753</v>
       </c>
       <c r="F542" t="n">
         <v>29291500</v>
@@ -11352,16 +11352,16 @@
         <v>45209</v>
       </c>
       <c r="B547" t="n">
-        <v>3.41562032699585</v>
+        <v>3.415620088577271</v>
       </c>
       <c r="C547" t="n">
-        <v>3.425187881991583</v>
+        <v>3.425187642905165</v>
       </c>
       <c r="D547" t="n">
-        <v>3.348647442025716</v>
+        <v>3.348647208282007</v>
       </c>
       <c r="E547" t="n">
-        <v>3.367782552017183</v>
+        <v>3.367782316937797</v>
       </c>
       <c r="F547" t="n">
         <v>9595500</v>
@@ -11412,16 +11412,16 @@
         <v>45215</v>
       </c>
       <c r="B550" t="n">
-        <v>3.386917591094971</v>
+        <v>3.386917352676392</v>
       </c>
       <c r="C550" t="n">
-        <v>3.434755365072033</v>
+        <v>3.434755123285962</v>
       </c>
       <c r="D550" t="n">
-        <v>3.348647371913321</v>
+        <v>3.348647136188735</v>
       </c>
       <c r="E550" t="n">
-        <v>3.377350036299558</v>
+        <v>3.377349798554477</v>
       </c>
       <c r="F550" t="n">
         <v>12135900</v>
@@ -25991,12 +25991,20 @@
       <c r="A1279" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B1279" t="inlineStr"/>
-      <c r="C1279" t="inlineStr"/>
-      <c r="D1279" t="inlineStr"/>
-      <c r="E1279" t="inlineStr"/>
+      <c r="B1279" t="n">
+        <v>0.2700000107288361</v>
+      </c>
+      <c r="C1279" t="n">
+        <v>0.2800000011920929</v>
+      </c>
+      <c r="D1279" t="n">
+        <v>0.2599999904632568</v>
+      </c>
+      <c r="E1279" t="n">
+        <v>0.2800000011920929</v>
+      </c>
       <c r="F1279" t="n">
-        <v>64643300</v>
+        <v>12268900</v>
       </c>
     </row>
     <row r="1280">
@@ -26004,19 +26012,39 @@
         <v>46283</v>
       </c>
       <c r="B1280" t="n">
-        <v>0.26</v>
+        <v>0.2599999904632568</v>
       </c>
       <c r="C1280" t="n">
-        <v>0.28</v>
+        <v>0.2800000011920929</v>
       </c>
       <c r="D1280" t="n">
-        <v>0.26</v>
+        <v>0.2599999904632568</v>
       </c>
       <c r="E1280" t="n">
-        <v>0.27</v>
+        <v>0.2700000107288361</v>
       </c>
       <c r="F1280" t="n">
         <v>64905500</v>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B1281" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C1281" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D1281" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E1281" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F1281" t="n">
+        <v>9702900</v>
       </c>
     </row>
   </sheetData>

--- a/database/RAIZ4.xlsx
+++ b/database/RAIZ4.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1281"/>
+  <dimension ref="A1:F1282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44413</v>
       </c>
       <c r="B2" t="n">
-        <v>6.384481906890869</v>
+        <v>6.384480953216553</v>
       </c>
       <c r="C2" t="n">
-        <v>6.701942460974013</v>
+        <v>6.701941459879408</v>
       </c>
       <c r="D2" t="n">
-        <v>6.331571884625592</v>
+        <v>6.331570938854646</v>
       </c>
       <c r="E2" t="n">
-        <v>6.596122416443459</v>
+        <v>6.596121431155595</v>
       </c>
       <c r="F2" t="n">
         <v>98849900</v>
@@ -492,16 +492,16 @@
         <v>44417</v>
       </c>
       <c r="B4" t="n">
-        <v>6.234570026397705</v>
+        <v>6.234570503234863</v>
       </c>
       <c r="C4" t="n">
-        <v>6.446210103204662</v>
+        <v>6.44621059622864</v>
       </c>
       <c r="D4" t="n">
-        <v>6.234570026397705</v>
+        <v>6.234570503234863</v>
       </c>
       <c r="E4" t="n">
-        <v>6.331571518021834</v>
+        <v>6.331572002277935</v>
       </c>
       <c r="F4" t="n">
         <v>14491100</v>
@@ -532,16 +532,16 @@
         <v>44419</v>
       </c>
       <c r="B6" t="n">
-        <v>6.058203220367432</v>
+        <v>6.058202743530273</v>
       </c>
       <c r="C6" t="n">
-        <v>6.296298530585189</v>
+        <v>6.296298035007707</v>
       </c>
       <c r="D6" t="n">
-        <v>5.996475071361166</v>
+        <v>5.996474599382589</v>
       </c>
       <c r="E6" t="n">
-        <v>6.287480403794928</v>
+        <v>6.287479908911514</v>
       </c>
       <c r="F6" t="n">
         <v>31978000</v>
@@ -552,16 +552,16 @@
         <v>44420</v>
       </c>
       <c r="B7" t="n">
-        <v>6.137568473815918</v>
+        <v>6.137567043304443</v>
       </c>
       <c r="C7" t="n">
-        <v>6.155205147916306</v>
+        <v>6.155203713294171</v>
       </c>
       <c r="D7" t="n">
-        <v>5.952383185516099</v>
+        <v>5.952381798166616</v>
       </c>
       <c r="E7" t="n">
-        <v>6.146386600620373</v>
+        <v>6.146385168053617</v>
       </c>
       <c r="F7" t="n">
         <v>17054100</v>
@@ -592,16 +592,16 @@
         <v>44424</v>
       </c>
       <c r="B9" t="n">
-        <v>6.190478801727295</v>
+        <v>6.190478324890137</v>
       </c>
       <c r="C9" t="n">
-        <v>6.278662176582655</v>
+        <v>6.278661692952952</v>
       </c>
       <c r="D9" t="n">
-        <v>5.978838702074429</v>
+        <v>5.978838241539382</v>
       </c>
       <c r="E9" t="n">
-        <v>6.146386904053864</v>
+        <v>6.146386430612996</v>
       </c>
       <c r="F9" t="n">
         <v>13434600</v>
@@ -612,16 +612,16 @@
         <v>44425</v>
       </c>
       <c r="B10" t="n">
-        <v>6.014111518859863</v>
+        <v>6.014111042022705</v>
       </c>
       <c r="C10" t="n">
-        <v>6.164023032578428</v>
+        <v>6.164022543855327</v>
       </c>
       <c r="D10" t="n">
-        <v>5.961201498637171</v>
+        <v>5.961201025995057</v>
       </c>
       <c r="E10" t="n">
-        <v>6.111113012355736</v>
+        <v>6.111112527827679</v>
       </c>
       <c r="F10" t="n">
         <v>17772000</v>
@@ -632,16 +632,16 @@
         <v>44426</v>
       </c>
       <c r="B11" t="n">
-        <v>6.005292892456055</v>
+        <v>6.005293369293213</v>
       </c>
       <c r="C11" t="n">
-        <v>6.172841497856859</v>
+        <v>6.172841987997847</v>
       </c>
       <c r="D11" t="n">
-        <v>5.925927652926344</v>
+        <v>5.925928123461678</v>
       </c>
       <c r="E11" t="n">
-        <v>6.022929565630274</v>
+        <v>6.022930043867833</v>
       </c>
       <c r="F11" t="n">
         <v>8841700</v>
@@ -672,16 +672,16 @@
         <v>44428</v>
       </c>
       <c r="B13" t="n">
-        <v>6.155205249786377</v>
+        <v>6.155204772949219</v>
       </c>
       <c r="C13" t="n">
-        <v>6.216933820405099</v>
+        <v>6.216933338785894</v>
       </c>
       <c r="D13" t="n">
-        <v>6.022929981598537</v>
+        <v>6.022929515008602</v>
       </c>
       <c r="E13" t="n">
-        <v>6.075840004775376</v>
+        <v>6.075839534086558</v>
       </c>
       <c r="F13" t="n">
         <v>3109200</v>
@@ -692,16 +692,16 @@
         <v>44431</v>
       </c>
       <c r="B14" t="n">
-        <v>6.322753429412842</v>
+        <v>6.322752952575684</v>
       </c>
       <c r="C14" t="n">
-        <v>6.349208228925635</v>
+        <v>6.349207750093361</v>
       </c>
       <c r="D14" t="n">
-        <v>6.181660044034058</v>
+        <v>6.181659577837608</v>
       </c>
       <c r="E14" t="n">
-        <v>6.208114843546852</v>
+        <v>6.208114375355285</v>
       </c>
       <c r="F14" t="n">
         <v>6128800</v>
@@ -712,16 +712,16 @@
         <v>44432</v>
       </c>
       <c r="B15" t="n">
-        <v>6.393301010131836</v>
+        <v>6.39330005645752</v>
       </c>
       <c r="C15" t="n">
-        <v>6.525576287543212</v>
+        <v>6.525575314137689</v>
       </c>
       <c r="D15" t="n">
-        <v>6.33157243520879</v>
+        <v>6.331571490742386</v>
       </c>
       <c r="E15" t="n">
-        <v>6.384482462075037</v>
+        <v>6.384481509716164</v>
       </c>
       <c r="F15" t="n">
         <v>6054100</v>
@@ -732,16 +732,16 @@
         <v>44433</v>
       </c>
       <c r="B16" t="n">
-        <v>6.472664833068848</v>
+        <v>6.472665309906006</v>
       </c>
       <c r="C16" t="n">
-        <v>6.507938176533139</v>
+        <v>6.507938655968863</v>
       </c>
       <c r="D16" t="n">
-        <v>6.402118146140264</v>
+        <v>6.402118617780292</v>
       </c>
       <c r="E16" t="n">
-        <v>6.455028161336702</v>
+        <v>6.455028636874578</v>
       </c>
       <c r="F16" t="n">
         <v>5190100</v>
@@ -772,16 +772,16 @@
         <v>44435</v>
       </c>
       <c r="B18" t="n">
-        <v>6.340390205383301</v>
+        <v>6.340389728546143</v>
       </c>
       <c r="C18" t="n">
-        <v>6.384481678783307</v>
+        <v>6.384481198630192</v>
       </c>
       <c r="D18" t="n">
-        <v>6.278661638033537</v>
+        <v>6.278661165838754</v>
       </c>
       <c r="E18" t="n">
-        <v>6.305116858466711</v>
+        <v>6.305116384282329</v>
       </c>
       <c r="F18" t="n">
         <v>5881000</v>
@@ -792,16 +792,16 @@
         <v>44438</v>
       </c>
       <c r="B19" t="n">
-        <v>6.269843578338623</v>
+        <v>6.269843101501465</v>
       </c>
       <c r="C19" t="n">
-        <v>6.419755514576775</v>
+        <v>6.419755026338443</v>
       </c>
       <c r="D19" t="n">
-        <v>6.252206904692456</v>
+        <v>6.252206429196611</v>
       </c>
       <c r="E19" t="n">
-        <v>6.393300293861791</v>
+        <v>6.393299807635444</v>
       </c>
       <c r="F19" t="n">
         <v>4966000</v>
@@ -832,16 +832,16 @@
         <v>44440</v>
       </c>
       <c r="B21" t="n">
-        <v>6.234570026397705</v>
+        <v>6.234570503234863</v>
       </c>
       <c r="C21" t="n">
-        <v>6.305116718666691</v>
+        <v>6.305117200899455</v>
       </c>
       <c r="D21" t="n">
-        <v>6.199296680263212</v>
+        <v>6.199297154402568</v>
       </c>
       <c r="E21" t="n">
-        <v>6.261024825752847</v>
+        <v>6.261025304613343</v>
       </c>
       <c r="F21" t="n">
         <v>6468600</v>
@@ -852,16 +852,16 @@
         <v>44441</v>
       </c>
       <c r="B22" t="n">
-        <v>5.996475219726562</v>
+        <v>5.996474742889404</v>
       </c>
       <c r="C22" t="n">
-        <v>6.252207210343668</v>
+        <v>6.252206713170811</v>
       </c>
       <c r="D22" t="n">
-        <v>5.970019997718263</v>
+        <v>5.970019522984813</v>
       </c>
       <c r="E22" t="n">
-        <v>6.234570535835299</v>
+        <v>6.234570040064902</v>
       </c>
       <c r="F22" t="n">
         <v>3746900</v>
@@ -872,16 +872,16 @@
         <v>44442</v>
       </c>
       <c r="B23" t="n">
-        <v>6.172841548919678</v>
+        <v>6.17284107208252</v>
       </c>
       <c r="C23" t="n">
-        <v>6.172841548919678</v>
+        <v>6.17284107208252</v>
       </c>
       <c r="D23" t="n">
-        <v>5.934746248852434</v>
+        <v>5.934745790407565</v>
       </c>
       <c r="E23" t="n">
-        <v>6.031748162358781</v>
+        <v>6.031747696420747</v>
       </c>
       <c r="F23" t="n">
         <v>3705400</v>
@@ -932,16 +932,16 @@
         <v>44448</v>
       </c>
       <c r="B26" t="n">
-        <v>5.65255880355835</v>
+        <v>5.652559280395508</v>
       </c>
       <c r="C26" t="n">
-        <v>5.837744075419861</v>
+        <v>5.837744567878833</v>
       </c>
       <c r="D26" t="n">
-        <v>5.599648785953838</v>
+        <v>5.599649258327626</v>
       </c>
       <c r="E26" t="n">
-        <v>5.758379259258814</v>
+        <v>5.758379745022749</v>
       </c>
       <c r="F26" t="n">
         <v>5428200</v>
@@ -952,16 +952,16 @@
         <v>44449</v>
       </c>
       <c r="B27" t="n">
-        <v>5.731923580169678</v>
+        <v>5.731925010681152</v>
       </c>
       <c r="C27" t="n">
-        <v>5.899472166048991</v>
+        <v>5.899473638375429</v>
       </c>
       <c r="D27" t="n">
-        <v>5.617285007648347</v>
+        <v>5.617286409549566</v>
       </c>
       <c r="E27" t="n">
-        <v>5.767196922408332</v>
+        <v>5.767198361722946</v>
       </c>
       <c r="F27" t="n">
         <v>5905500</v>
@@ -972,16 +972,16 @@
         <v>44452</v>
       </c>
       <c r="B28" t="n">
-        <v>6.128749370574951</v>
+        <v>6.128750324249268</v>
       </c>
       <c r="C28" t="n">
-        <v>6.172841262072042</v>
+        <v>6.172842222607351</v>
       </c>
       <c r="D28" t="n">
-        <v>5.925927426572926</v>
+        <v>5.925928348686794</v>
       </c>
       <c r="E28" t="n">
-        <v>5.952382645569469</v>
+        <v>5.952383571799945</v>
       </c>
       <c r="F28" t="n">
         <v>8999600</v>
@@ -992,16 +992,16 @@
         <v>44453</v>
       </c>
       <c r="B29" t="n">
-        <v>6.340390205383301</v>
+        <v>6.340389728546143</v>
       </c>
       <c r="C29" t="n">
-        <v>6.507938813482836</v>
+        <v>6.50793832404497</v>
       </c>
       <c r="D29" t="n">
-        <v>6.225751617658651</v>
+        <v>6.225751149443035</v>
       </c>
       <c r="E29" t="n">
-        <v>6.225751617658651</v>
+        <v>6.225751149443035</v>
       </c>
       <c r="F29" t="n">
         <v>9730300</v>
@@ -1012,16 +1012,16 @@
         <v>44454</v>
       </c>
       <c r="B30" t="n">
-        <v>6.384481906890869</v>
+        <v>6.384480953216553</v>
       </c>
       <c r="C30" t="n">
-        <v>6.507939046001328</v>
+        <v>6.50793807388575</v>
       </c>
       <c r="D30" t="n">
-        <v>6.29629853644874</v>
+        <v>6.296297595946708</v>
       </c>
       <c r="E30" t="n">
-        <v>6.384481906890869</v>
+        <v>6.384480953216553</v>
       </c>
       <c r="F30" t="n">
         <v>7265900</v>
@@ -1052,16 +1052,16 @@
         <v>44456</v>
       </c>
       <c r="B32" t="n">
-        <v>6.384481906890869</v>
+        <v>6.384480953216553</v>
       </c>
       <c r="C32" t="n">
-        <v>6.384481906890869</v>
+        <v>6.384480953216553</v>
       </c>
       <c r="D32" t="n">
-        <v>5.978838402857074</v>
+        <v>5.978837509775269</v>
       </c>
       <c r="E32" t="n">
-        <v>6.261025188271888</v>
+        <v>6.26102425303877</v>
       </c>
       <c r="F32" t="n">
         <v>16008100</v>
@@ -1072,16 +1072,16 @@
         <v>44459</v>
       </c>
       <c r="B33" t="n">
-        <v>6.269843578338623</v>
+        <v>6.269843101501465</v>
       </c>
       <c r="C33" t="n">
-        <v>6.322753599277124</v>
+        <v>6.322753118416027</v>
       </c>
       <c r="D33" t="n">
-        <v>6.067021621161969</v>
+        <v>6.067021159749924</v>
       </c>
       <c r="E33" t="n">
-        <v>6.164023115970153</v>
+        <v>6.164022647180904</v>
       </c>
       <c r="F33" t="n">
         <v>9065700</v>
@@ -1092,16 +1092,16 @@
         <v>44460</v>
       </c>
       <c r="B34" t="n">
-        <v>6.419754981994629</v>
+        <v>6.419755458831787</v>
       </c>
       <c r="C34" t="n">
-        <v>6.525575015092812</v>
+        <v>6.525575499789916</v>
       </c>
       <c r="D34" t="n">
-        <v>6.269843058193152</v>
+        <v>6.269843523895372</v>
       </c>
       <c r="E34" t="n">
-        <v>6.349207872771073</v>
+        <v>6.349208344368237</v>
       </c>
       <c r="F34" t="n">
         <v>11102500</v>
@@ -1112,16 +1112,16 @@
         <v>44461</v>
       </c>
       <c r="B35" t="n">
-        <v>6.446209907531738</v>
+        <v>6.44620943069458</v>
       </c>
       <c r="C35" t="n">
-        <v>6.560848489234745</v>
+        <v>6.560848003917575</v>
       </c>
       <c r="D35" t="n">
-        <v>6.402118436447734</v>
+        <v>6.402117962872096</v>
       </c>
       <c r="E35" t="n">
-        <v>6.463846580063628</v>
+        <v>6.463846101921855</v>
       </c>
       <c r="F35" t="n">
         <v>10254600</v>
@@ -1132,16 +1132,16 @@
         <v>44462</v>
       </c>
       <c r="B36" t="n">
-        <v>6.375663280487061</v>
+        <v>6.375663757324219</v>
       </c>
       <c r="C36" t="n">
-        <v>6.543211881443518</v>
+        <v>6.54321237081167</v>
       </c>
       <c r="D36" t="n">
-        <v>6.340389935074274</v>
+        <v>6.340390409273332</v>
       </c>
       <c r="E36" t="n">
-        <v>6.507938536030731</v>
+        <v>6.507939022760783</v>
       </c>
       <c r="F36" t="n">
         <v>6341600</v>
@@ -1152,16 +1152,16 @@
         <v>44463</v>
       </c>
       <c r="B37" t="n">
-        <v>6.172841548919678</v>
+        <v>6.17284107208252</v>
       </c>
       <c r="C37" t="n">
-        <v>6.375663502346697</v>
+        <v>6.375663009842031</v>
       </c>
       <c r="D37" t="n">
-        <v>6.164023002013892</v>
+        <v>6.164022525857945</v>
       </c>
       <c r="E37" t="n">
-        <v>6.340390155706473</v>
+        <v>6.340389665926588</v>
       </c>
       <c r="F37" t="n">
         <v>5138200</v>
@@ -1172,16 +1172,16 @@
         <v>44466</v>
       </c>
       <c r="B38" t="n">
-        <v>6.305116653442383</v>
+        <v>6.305116176605225</v>
       </c>
       <c r="C38" t="n">
-        <v>6.340389999211985</v>
+        <v>6.340389519707209</v>
       </c>
       <c r="D38" t="n">
-        <v>6.102294705021446</v>
+        <v>6.102294243523106</v>
       </c>
       <c r="E38" t="n">
-        <v>6.17284139656065</v>
+        <v>6.172840929727075</v>
       </c>
       <c r="F38" t="n">
         <v>6343700</v>
@@ -1192,16 +1192,16 @@
         <v>44467</v>
       </c>
       <c r="B39" t="n">
-        <v>6.119931697845459</v>
+        <v>6.119932174682617</v>
       </c>
       <c r="C39" t="n">
-        <v>6.278661762106795</v>
+        <v>6.278662251311475</v>
       </c>
       <c r="D39" t="n">
-        <v>6.119931697845459</v>
+        <v>6.119932174682617</v>
       </c>
       <c r="E39" t="n">
-        <v>6.26102508829998</v>
+        <v>6.261025576130491</v>
       </c>
       <c r="F39" t="n">
         <v>6782400</v>
@@ -1212,16 +1212,16 @@
         <v>44468</v>
       </c>
       <c r="B40" t="n">
-        <v>6.040565967559814</v>
+        <v>6.040566921234131</v>
       </c>
       <c r="C40" t="n">
-        <v>6.25220645663842</v>
+        <v>6.252207443726178</v>
       </c>
       <c r="D40" t="n">
-        <v>6.040565967559814</v>
+        <v>6.040566921234131</v>
       </c>
       <c r="E40" t="n">
-        <v>6.216933111873892</v>
+        <v>6.216934093392754</v>
       </c>
       <c r="F40" t="n">
         <v>6482600</v>
@@ -1272,16 +1272,16 @@
         <v>44473</v>
       </c>
       <c r="B43" t="n">
-        <v>6.190478801727295</v>
+        <v>6.190478324890137</v>
       </c>
       <c r="C43" t="n">
-        <v>6.552030848880022</v>
+        <v>6.552030344193411</v>
       </c>
       <c r="D43" t="n">
-        <v>6.190478801727295</v>
+        <v>6.190478324890137</v>
       </c>
       <c r="E43" t="n">
-        <v>6.525576046669164</v>
+        <v>6.5255755440203</v>
       </c>
       <c r="F43" t="n">
         <v>12019000</v>
@@ -1292,16 +1292,16 @@
         <v>44474</v>
       </c>
       <c r="B44" t="n">
-        <v>6.287479877471924</v>
+        <v>6.287480354309082</v>
       </c>
       <c r="C44" t="n">
-        <v>6.366844693906587</v>
+        <v>6.366845176762705</v>
       </c>
       <c r="D44" t="n">
-        <v>6.2433879857371</v>
+        <v>6.243388459230366</v>
       </c>
       <c r="E44" t="n">
-        <v>6.296298003524023</v>
+        <v>6.29629848102994</v>
       </c>
       <c r="F44" t="n">
         <v>12888200</v>
@@ -1312,16 +1312,16 @@
         <v>44475</v>
       </c>
       <c r="B45" t="n">
-        <v>6.178093910217285</v>
+        <v>6.178094863891602</v>
       </c>
       <c r="C45" t="n">
-        <v>6.275317254600846</v>
+        <v>6.275318223282931</v>
       </c>
       <c r="D45" t="n">
-        <v>6.080870987285061</v>
+        <v>6.080871925951673</v>
       </c>
       <c r="E45" t="n">
-        <v>6.248802065237998</v>
+        <v>6.248803029827096</v>
       </c>
       <c r="F45" t="n">
         <v>10376100</v>
@@ -1332,16 +1332,16 @@
         <v>44476</v>
       </c>
       <c r="B46" t="n">
-        <v>6.301832675933838</v>
+        <v>6.301833152770996</v>
       </c>
       <c r="C46" t="n">
-        <v>6.478602004542243</v>
+        <v>6.478602494754905</v>
       </c>
       <c r="D46" t="n">
-        <v>6.213448011629635</v>
+        <v>6.213448481779042</v>
       </c>
       <c r="E46" t="n">
-        <v>6.284155743072997</v>
+        <v>6.284156218572606</v>
       </c>
       <c r="F46" t="n">
         <v>18438800</v>
@@ -1372,16 +1372,16 @@
         <v>44480</v>
       </c>
       <c r="B48" t="n">
-        <v>6.213448047637939</v>
+        <v>6.213448524475098</v>
       </c>
       <c r="C48" t="n">
-        <v>6.407894310234044</v>
+        <v>6.407894801993546</v>
       </c>
       <c r="D48" t="n">
-        <v>6.213448047637939</v>
+        <v>6.213448524475098</v>
       </c>
       <c r="E48" t="n">
-        <v>6.363701767100176</v>
+        <v>6.363702255468219</v>
       </c>
       <c r="F48" t="n">
         <v>10407400</v>
@@ -1392,16 +1392,16 @@
         <v>44482</v>
       </c>
       <c r="B49" t="n">
-        <v>6.231125354766846</v>
+        <v>6.231124877929688</v>
       </c>
       <c r="C49" t="n">
-        <v>6.292994413127774</v>
+        <v>6.292993931556084</v>
       </c>
       <c r="D49" t="n">
-        <v>6.213448420742101</v>
+        <v>6.213447945257672</v>
       </c>
       <c r="E49" t="n">
-        <v>6.248802288791589</v>
+        <v>6.248801810601703</v>
       </c>
       <c r="F49" t="n">
         <v>8146000</v>
@@ -1412,16 +1412,16 @@
         <v>44483</v>
       </c>
       <c r="B50" t="n">
-        <v>6.319509506225586</v>
+        <v>6.319509029388428</v>
       </c>
       <c r="C50" t="n">
-        <v>6.381378559508698</v>
+        <v>6.381378078003224</v>
       </c>
       <c r="D50" t="n">
-        <v>6.239963098917224</v>
+        <v>6.239962628082221</v>
       </c>
       <c r="E50" t="n">
-        <v>6.24880177592985</v>
+        <v>6.248801304427927</v>
       </c>
       <c r="F50" t="n">
         <v>10992200</v>
@@ -1432,16 +1432,16 @@
         <v>44484</v>
       </c>
       <c r="B51" t="n">
-        <v>6.275317668914795</v>
+        <v>6.275317192077637</v>
       </c>
       <c r="C51" t="n">
-        <v>6.354864085157887</v>
+        <v>6.354863602276304</v>
       </c>
       <c r="D51" t="n">
-        <v>6.222286865236521</v>
+        <v>6.222286392428969</v>
       </c>
       <c r="E51" t="n">
-        <v>6.337187150598463</v>
+        <v>6.337186669060081</v>
       </c>
       <c r="F51" t="n">
         <v>34203500</v>
@@ -1452,16 +1452,16 @@
         <v>44487</v>
       </c>
       <c r="B52" t="n">
-        <v>6.169256210327148</v>
+        <v>6.169255256652832</v>
       </c>
       <c r="C52" t="n">
-        <v>6.266479563474164</v>
+        <v>6.266478594770578</v>
       </c>
       <c r="D52" t="n">
-        <v>6.151579275341452</v>
+        <v>6.151578324399725</v>
       </c>
       <c r="E52" t="n">
-        <v>6.257640885255628</v>
+        <v>6.25763991791837</v>
       </c>
       <c r="F52" t="n">
         <v>7596500</v>
@@ -1512,16 +1512,16 @@
         <v>44490</v>
       </c>
       <c r="B55" t="n">
-        <v>5.683138847351074</v>
+        <v>5.683139801025391</v>
       </c>
       <c r="C55" t="n">
-        <v>5.842231655156614</v>
+        <v>5.842232635527925</v>
       </c>
       <c r="D55" t="n">
-        <v>5.471015665545419</v>
+        <v>5.471016583623838</v>
       </c>
       <c r="E55" t="n">
-        <v>5.79803911488812</v>
+        <v>5.798040087843582</v>
       </c>
       <c r="F55" t="n">
         <v>12472300</v>
@@ -1532,16 +1532,16 @@
         <v>44491</v>
       </c>
       <c r="B56" t="n">
-        <v>5.63010835647583</v>
+        <v>5.630108833312988</v>
       </c>
       <c r="C56" t="n">
-        <v>5.656623966361621</v>
+        <v>5.656624445444495</v>
       </c>
       <c r="D56" t="n">
-        <v>5.197023292801376</v>
+        <v>5.197023732958769</v>
       </c>
       <c r="E56" t="n">
-        <v>5.60359316804136</v>
+        <v>5.603593642632838</v>
       </c>
       <c r="F56" t="n">
         <v>18890200</v>
@@ -1552,16 +1552,16 @@
         <v>44494</v>
       </c>
       <c r="B57" t="n">
-        <v>5.859909534454346</v>
+        <v>5.859909057617188</v>
       </c>
       <c r="C57" t="n">
-        <v>5.877586469129643</v>
+        <v>5.877585990854064</v>
       </c>
       <c r="D57" t="n">
-        <v>5.550562966910968</v>
+        <v>5.550562515246201</v>
       </c>
       <c r="E57" t="n">
-        <v>5.683139766250011</v>
+        <v>5.683139303797101</v>
       </c>
       <c r="F57" t="n">
         <v>11428100</v>
@@ -1592,16 +1592,16 @@
         <v>44496</v>
       </c>
       <c r="B59" t="n">
-        <v>5.859909534454346</v>
+        <v>5.859909057617188</v>
       </c>
       <c r="C59" t="n">
-        <v>5.965971142506127</v>
+        <v>5.96597065703844</v>
       </c>
       <c r="D59" t="n">
-        <v>5.789201795753159</v>
+        <v>5.789201324669686</v>
       </c>
       <c r="E59" t="n">
-        <v>5.833393921715717</v>
+        <v>5.833393447036208</v>
       </c>
       <c r="F59" t="n">
         <v>7675900</v>
@@ -1672,16 +1672,16 @@
         <v>44503</v>
       </c>
       <c r="B63" t="n">
-        <v>6.098547458648682</v>
+        <v>6.09854793548584</v>
       </c>
       <c r="C63" t="n">
-        <v>6.186932118914339</v>
+        <v>6.186932602662175</v>
       </c>
       <c r="D63" t="n">
-        <v>5.92177771666606</v>
+        <v>5.921778179681833</v>
       </c>
       <c r="E63" t="n">
-        <v>5.983647189577673</v>
+        <v>5.983647657430936</v>
       </c>
       <c r="F63" t="n">
         <v>5711600</v>
@@ -1732,16 +1732,16 @@
         <v>44508</v>
       </c>
       <c r="B66" t="n">
-        <v>5.983647346496582</v>
+        <v>5.983648300170898</v>
       </c>
       <c r="C66" t="n">
-        <v>6.036678144046689</v>
+        <v>6.03667910617306</v>
       </c>
       <c r="D66" t="n">
-        <v>5.939454804479167</v>
+        <v>5.939455751110073</v>
       </c>
       <c r="E66" t="n">
-        <v>6.010162955997293</v>
+        <v>6.010163913897671</v>
       </c>
       <c r="F66" t="n">
         <v>3898000</v>
@@ -1752,16 +1752,16 @@
         <v>44509</v>
       </c>
       <c r="B67" t="n">
-        <v>5.948293685913086</v>
+        <v>5.948294162750244</v>
       </c>
       <c r="C67" t="n">
-        <v>6.169255560692247</v>
+        <v>6.169256055242525</v>
       </c>
       <c r="D67" t="n">
-        <v>5.948293685913086</v>
+        <v>5.948294162750244</v>
       </c>
       <c r="E67" t="n">
-        <v>5.99248622944945</v>
+        <v>5.992486709829246</v>
       </c>
       <c r="F67" t="n">
         <v>5176300</v>
@@ -1772,16 +1772,16 @@
         <v>44510</v>
       </c>
       <c r="B68" t="n">
-        <v>5.745008945465088</v>
+        <v>5.745009422302246</v>
       </c>
       <c r="C68" t="n">
-        <v>6.010163373067091</v>
+        <v>6.010163871912132</v>
       </c>
       <c r="D68" t="n">
-        <v>5.745008945465088</v>
+        <v>5.745009422302246</v>
       </c>
       <c r="E68" t="n">
-        <v>5.957132150385616</v>
+        <v>5.957132644829051</v>
       </c>
       <c r="F68" t="n">
         <v>10074000</v>
@@ -1792,16 +1792,16 @@
         <v>44511</v>
       </c>
       <c r="B69" t="n">
-        <v>6.0101637840271</v>
+        <v>6.010163307189941</v>
       </c>
       <c r="C69" t="n">
-        <v>6.036678975729536</v>
+        <v>6.036678496788703</v>
       </c>
       <c r="D69" t="n">
-        <v>5.80687882135247</v>
+        <v>5.806878360643628</v>
       </c>
       <c r="E69" t="n">
-        <v>5.833394013054906</v>
+        <v>5.833393550242389</v>
       </c>
       <c r="F69" t="n">
         <v>8604300</v>
@@ -1812,16 +1812,16 @@
         <v>44512</v>
       </c>
       <c r="B70" t="n">
-        <v>5.762685298919678</v>
+        <v>5.762685775756836</v>
       </c>
       <c r="C70" t="n">
-        <v>6.080870495711316</v>
+        <v>6.080870998876915</v>
       </c>
       <c r="D70" t="n">
-        <v>5.532885183396102</v>
+        <v>5.532885641218299</v>
       </c>
       <c r="E70" t="n">
-        <v>6.080870495711316</v>
+        <v>6.080870998876915</v>
       </c>
       <c r="F70" t="n">
         <v>20568500</v>
@@ -1832,16 +1832,16 @@
         <v>44516</v>
       </c>
       <c r="B71" t="n">
-        <v>5.320762157440186</v>
+        <v>5.320761203765869</v>
       </c>
       <c r="C71" t="n">
-        <v>5.815716727730977</v>
+        <v>5.815715685342779</v>
       </c>
       <c r="D71" t="n">
-        <v>5.223538810335335</v>
+        <v>5.223537874086983</v>
       </c>
       <c r="E71" t="n">
-        <v>5.789201537625966</v>
+        <v>5.789200499990256</v>
       </c>
       <c r="F71" t="n">
         <v>27445700</v>
@@ -1852,16 +1852,16 @@
         <v>44517</v>
       </c>
       <c r="B72" t="n">
-        <v>5.17050838470459</v>
+        <v>5.170507907867432</v>
       </c>
       <c r="C72" t="n">
-        <v>5.462178025779772</v>
+        <v>5.462177522044113</v>
       </c>
       <c r="D72" t="n">
-        <v>5.002577289838284</v>
+        <v>5.002576828488149</v>
       </c>
       <c r="E72" t="n">
-        <v>5.364955093055631</v>
+        <v>5.364954598286112</v>
       </c>
       <c r="F72" t="n">
         <v>24600900</v>
@@ -1872,16 +1872,16 @@
         <v>44518</v>
       </c>
       <c r="B73" t="n">
-        <v>5.16166877746582</v>
+        <v>5.161669731140137</v>
       </c>
       <c r="C73" t="n">
-        <v>5.338438082947006</v>
+        <v>5.338439069281368</v>
       </c>
       <c r="D73" t="n">
-        <v>5.07328370327396</v>
+        <v>5.073284640618174</v>
       </c>
       <c r="E73" t="n">
-        <v>5.214699569110176</v>
+        <v>5.214700532582506</v>
       </c>
       <c r="F73" t="n">
         <v>17735600</v>
@@ -1892,16 +1892,16 @@
         <v>44519</v>
       </c>
       <c r="B74" t="n">
-        <v>5.241215229034424</v>
+        <v>5.241215705871582</v>
       </c>
       <c r="C74" t="n">
-        <v>5.285407770133975</v>
+        <v>5.285408250991699</v>
       </c>
       <c r="D74" t="n">
-        <v>5.090961516488821</v>
+        <v>5.090961979656143</v>
       </c>
       <c r="E74" t="n">
-        <v>5.161669245087059</v>
+        <v>5.161669714687254</v>
       </c>
       <c r="F74" t="n">
         <v>11364600</v>
@@ -1912,16 +1912,16 @@
         <v>44522</v>
       </c>
       <c r="B75" t="n">
-        <v>4.976062297821045</v>
+        <v>4.976061344146729</v>
       </c>
       <c r="C75" t="n">
-        <v>5.329601436937094</v>
+        <v>5.32960041550615</v>
       </c>
       <c r="D75" t="n">
-        <v>4.976062297821045</v>
+        <v>4.976061344146729</v>
       </c>
       <c r="E75" t="n">
-        <v>5.232378078853616</v>
+        <v>5.232377076055763</v>
       </c>
       <c r="F75" t="n">
         <v>8516000</v>
@@ -1992,16 +1992,16 @@
         <v>44526</v>
       </c>
       <c r="B79" t="n">
-        <v>5.223538398742676</v>
+        <v>5.223539352416992</v>
       </c>
       <c r="C79" t="n">
-        <v>5.338438670680995</v>
+        <v>5.338439645332938</v>
       </c>
       <c r="D79" t="n">
-        <v>5.020253464333078</v>
+        <v>5.020254380893162</v>
       </c>
       <c r="E79" t="n">
-        <v>5.037930396827334</v>
+        <v>5.037931316614738</v>
       </c>
       <c r="F79" t="n">
         <v>8564200</v>
@@ -2012,16 +2012,16 @@
         <v>44529</v>
       </c>
       <c r="B80" t="n">
-        <v>5.117477893829346</v>
+        <v>5.117476940155029</v>
       </c>
       <c r="C80" t="n">
-        <v>5.39147061657799</v>
+        <v>5.391469611843401</v>
       </c>
       <c r="D80" t="n">
-        <v>5.117477893829346</v>
+        <v>5.117476940155029</v>
       </c>
       <c r="E80" t="n">
-        <v>5.285408999020722</v>
+        <v>5.285408014051384</v>
       </c>
       <c r="F80" t="n">
         <v>7811800</v>
@@ -2032,16 +2032,16 @@
         <v>44530</v>
       </c>
       <c r="B81" t="n">
-        <v>4.825807571411133</v>
+        <v>4.825806617736816</v>
       </c>
       <c r="C81" t="n">
-        <v>5.126315867963532</v>
+        <v>5.126314854902876</v>
       </c>
       <c r="D81" t="n">
-        <v>4.790453703752186</v>
+        <v>4.790452757064487</v>
       </c>
       <c r="E81" t="n">
-        <v>5.073284645023764</v>
+        <v>5.07328364244312</v>
       </c>
       <c r="F81" t="n">
         <v>11282700</v>
@@ -2052,16 +2052,16 @@
         <v>44531</v>
       </c>
       <c r="B82" t="n">
-        <v>4.852322101593018</v>
+        <v>4.852322578430176</v>
       </c>
       <c r="C82" t="n">
-        <v>5.152830357281196</v>
+        <v>5.152830863649267</v>
       </c>
       <c r="D82" t="n">
-        <v>4.852322101593018</v>
+        <v>4.852322578430176</v>
       </c>
       <c r="E82" t="n">
-        <v>4.896514640882911</v>
+        <v>4.896515122062865</v>
       </c>
       <c r="F82" t="n">
         <v>12492100</v>
@@ -2072,16 +2072,16 @@
         <v>44532</v>
       </c>
       <c r="B83" t="n">
-        <v>5.029093265533447</v>
+        <v>5.029092788696289</v>
       </c>
       <c r="C83" t="n">
-        <v>5.029093265533447</v>
+        <v>5.029092788696289</v>
       </c>
       <c r="D83" t="n">
-        <v>4.746261860948556</v>
+        <v>4.746261410928263</v>
       </c>
       <c r="E83" t="n">
-        <v>4.905354710412548</v>
+        <v>4.905354245307752</v>
       </c>
       <c r="F83" t="n">
         <v>18379200</v>
@@ -2092,16 +2092,16 @@
         <v>44533</v>
       </c>
       <c r="B84" t="n">
-        <v>5.320762157440186</v>
+        <v>5.320761203765869</v>
       </c>
       <c r="C84" t="n">
-        <v>5.329600835109421</v>
+        <v>5.329599879850892</v>
       </c>
       <c r="D84" t="n">
-        <v>4.976061735915614</v>
+        <v>4.976060844024164</v>
       </c>
       <c r="E84" t="n">
-        <v>5.020253859907747</v>
+        <v>5.020252960095459</v>
       </c>
       <c r="F84" t="n">
         <v>10548200</v>
@@ -2192,16 +2192,16 @@
         <v>44540</v>
       </c>
       <c r="B89" t="n">
-        <v>5.44450044631958</v>
+        <v>5.444499969482422</v>
       </c>
       <c r="C89" t="n">
-        <v>5.568239399336901</v>
+        <v>5.568238911662507</v>
       </c>
       <c r="D89" t="n">
-        <v>5.241215505164072</v>
+        <v>5.2412150461309</v>
       </c>
       <c r="E89" t="n">
-        <v>5.267731115511021</v>
+        <v>5.267730654155574</v>
       </c>
       <c r="F89" t="n">
         <v>8741300</v>
@@ -2212,16 +2212,16 @@
         <v>44543</v>
       </c>
       <c r="B90" t="n">
-        <v>5.497531890869141</v>
+        <v>5.497531414031982</v>
       </c>
       <c r="C90" t="n">
-        <v>5.621270858411092</v>
+        <v>5.621270370841238</v>
       </c>
       <c r="D90" t="n">
-        <v>5.426824150245956</v>
+        <v>5.426823679541746</v>
       </c>
       <c r="E90" t="n">
-        <v>5.444501085401752</v>
+        <v>5.444500613164305</v>
       </c>
       <c r="F90" t="n">
         <v>8265100</v>
@@ -2272,16 +2272,16 @@
         <v>44546</v>
       </c>
       <c r="B93" t="n">
-        <v>5.400307655334473</v>
+        <v>5.400308132171631</v>
       </c>
       <c r="C93" t="n">
-        <v>5.550561778633416</v>
+        <v>5.550562268737735</v>
       </c>
       <c r="D93" t="n">
-        <v>5.347276862661541</v>
+        <v>5.347277334816178</v>
       </c>
       <c r="E93" t="n">
-        <v>5.515207495400186</v>
+        <v>5.515207982382787</v>
       </c>
       <c r="F93" t="n">
         <v>9238300</v>
@@ -2292,16 +2292,16 @@
         <v>44547</v>
       </c>
       <c r="B94" t="n">
-        <v>5.241215229034424</v>
+        <v>5.241215705871582</v>
       </c>
       <c r="C94" t="n">
-        <v>5.347277243383087</v>
+        <v>5.347277729869593</v>
       </c>
       <c r="D94" t="n">
-        <v>5.241215229034424</v>
+        <v>5.241215705871582</v>
       </c>
       <c r="E94" t="n">
-        <v>5.320761634433095</v>
+        <v>5.320762118507254</v>
       </c>
       <c r="F94" t="n">
         <v>50153800</v>
@@ -2332,16 +2332,16 @@
         <v>44551</v>
       </c>
       <c r="B96" t="n">
-        <v>5.082122802734375</v>
+        <v>5.082123279571533</v>
       </c>
       <c r="C96" t="n">
-        <v>5.223538258902567</v>
+        <v>5.223538749008224</v>
       </c>
       <c r="D96" t="n">
-        <v>5.020253329935139</v>
+        <v>5.020253800967309</v>
       </c>
       <c r="E96" t="n">
-        <v>5.170507462839494</v>
+        <v>5.170507947969465</v>
       </c>
       <c r="F96" t="n">
         <v>5049800</v>
@@ -2412,16 +2412,16 @@
         <v>44558</v>
       </c>
       <c r="B100" t="n">
-        <v>5.347277164459229</v>
+        <v>5.347277641296387</v>
       </c>
       <c r="C100" t="n">
-        <v>5.347277164459229</v>
+        <v>5.347277641296387</v>
       </c>
       <c r="D100" t="n">
-        <v>5.188184356010038</v>
+        <v>5.188184818660282</v>
       </c>
       <c r="E100" t="n">
-        <v>5.21469996456867</v>
+        <v>5.214700429583412</v>
       </c>
       <c r="F100" t="n">
         <v>4379800</v>
@@ -2452,16 +2452,16 @@
         <v>44560</v>
       </c>
       <c r="B102" t="n">
-        <v>5.700816631317139</v>
+        <v>5.70081615447998</v>
       </c>
       <c r="C102" t="n">
-        <v>5.709655309272549</v>
+        <v>5.70965483169609</v>
       </c>
       <c r="D102" t="n">
-        <v>5.258892848379334</v>
+        <v>5.258892408506298</v>
       </c>
       <c r="E102" t="n">
-        <v>5.320762329713117</v>
+        <v>5.320761884665091</v>
       </c>
       <c r="F102" t="n">
         <v>23096200</v>
@@ -2472,16 +2472,16 @@
         <v>44564</v>
       </c>
       <c r="B103" t="n">
-        <v>5.54172420501709</v>
+        <v>5.541723728179932</v>
       </c>
       <c r="C103" t="n">
-        <v>5.745009161433563</v>
+        <v>5.745008667104768</v>
       </c>
       <c r="D103" t="n">
-        <v>5.5063703362013</v>
+        <v>5.506369862406162</v>
       </c>
       <c r="E103" t="n">
-        <v>5.691978358209878</v>
+        <v>5.691977868444114</v>
       </c>
       <c r="F103" t="n">
         <v>7451800</v>
@@ -2492,16 +2492,16 @@
         <v>44565</v>
       </c>
       <c r="B104" t="n">
-        <v>5.594754219055176</v>
+        <v>5.594754695892334</v>
       </c>
       <c r="C104" t="n">
-        <v>5.612431150969596</v>
+        <v>5.612431629313347</v>
       </c>
       <c r="D104" t="n">
-        <v>5.444500087056956</v>
+        <v>5.444500551088055</v>
       </c>
       <c r="E104" t="n">
-        <v>5.532885168080356</v>
+        <v>5.532885639644457</v>
       </c>
       <c r="F104" t="n">
         <v>10613100</v>
@@ -2512,16 +2512,16 @@
         <v>44566</v>
       </c>
       <c r="B105" t="n">
-        <v>5.117477893829346</v>
+        <v>5.117476940155029</v>
       </c>
       <c r="C105" t="n">
-        <v>5.568240400624842</v>
+        <v>5.568239362948087</v>
       </c>
       <c r="D105" t="n">
-        <v>5.117477893829346</v>
+        <v>5.117476940155029</v>
       </c>
       <c r="E105" t="n">
-        <v>5.550563464365298</v>
+        <v>5.550562429982751</v>
       </c>
       <c r="F105" t="n">
         <v>7203400</v>
@@ -2572,16 +2572,16 @@
         <v>44571</v>
       </c>
       <c r="B108" t="n">
-        <v>5.057156085968018</v>
+        <v>5.057155609130859</v>
       </c>
       <c r="C108" t="n">
-        <v>5.128134072989941</v>
+        <v>5.128133589460298</v>
       </c>
       <c r="D108" t="n">
-        <v>4.906328974078017</v>
+        <v>4.906328511462285</v>
       </c>
       <c r="E108" t="n">
-        <v>5.057156085968018</v>
+        <v>5.057155609130859</v>
       </c>
       <c r="F108" t="n">
         <v>11253600</v>
@@ -2592,16 +2592,16 @@
         <v>44572</v>
       </c>
       <c r="B109" t="n">
-        <v>5.234599590301514</v>
+        <v>5.234600067138672</v>
       </c>
       <c r="C109" t="n">
-        <v>5.234599590301514</v>
+        <v>5.234600067138672</v>
       </c>
       <c r="D109" t="n">
-        <v>5.021666509062139</v>
+        <v>5.021666966502512</v>
       </c>
       <c r="E109" t="n">
-        <v>5.021666509062139</v>
+        <v>5.021666966502512</v>
       </c>
       <c r="F109" t="n">
         <v>5425200</v>
@@ -2612,16 +2612,16 @@
         <v>44573</v>
       </c>
       <c r="B110" t="n">
-        <v>5.438660621643066</v>
+        <v>5.438661098480225</v>
       </c>
       <c r="C110" t="n">
-        <v>5.51851016215336</v>
+        <v>5.518510645991364</v>
       </c>
       <c r="D110" t="n">
-        <v>5.225727526476521</v>
+        <v>5.225727984644668</v>
       </c>
       <c r="E110" t="n">
-        <v>5.261216305161009</v>
+        <v>5.261216766440652</v>
       </c>
       <c r="F110" t="n">
         <v>9077500</v>
@@ -2632,16 +2632,16 @@
         <v>44574</v>
       </c>
       <c r="B111" t="n">
-        <v>5.420916557312012</v>
+        <v>5.420916080474854</v>
       </c>
       <c r="C111" t="n">
-        <v>5.50963850934256</v>
+        <v>5.509638024701201</v>
       </c>
       <c r="D111" t="n">
-        <v>5.358810979360809</v>
+        <v>5.358810507986609</v>
       </c>
       <c r="E111" t="n">
-        <v>5.358810979360809</v>
+        <v>5.358810507986609</v>
       </c>
       <c r="F111" t="n">
         <v>4388600</v>
@@ -2652,16 +2652,16 @@
         <v>44575</v>
       </c>
       <c r="B112" t="n">
-        <v>5.491894245147705</v>
+        <v>5.491893768310547</v>
       </c>
       <c r="C112" t="n">
-        <v>5.500766229024832</v>
+        <v>5.500765751417357</v>
       </c>
       <c r="D112" t="n">
-        <v>5.332194727822603</v>
+        <v>5.332194264851456</v>
       </c>
       <c r="E112" t="n">
-        <v>5.420916681892105</v>
+        <v>5.420916211217618</v>
       </c>
       <c r="F112" t="n">
         <v>4745900</v>
@@ -2672,16 +2672,16 @@
         <v>44578</v>
       </c>
       <c r="B113" t="n">
-        <v>5.483021259307861</v>
+        <v>5.48302173614502</v>
       </c>
       <c r="C113" t="n">
-        <v>5.624976793890898</v>
+        <v>5.62497728307338</v>
       </c>
       <c r="D113" t="n">
-        <v>5.447532481427003</v>
+        <v>5.447532955177839</v>
       </c>
       <c r="E113" t="n">
-        <v>5.447532481427003</v>
+        <v>5.447532955177839</v>
       </c>
       <c r="F113" t="n">
         <v>3137800</v>
@@ -2692,16 +2692,16 @@
         <v>44579</v>
       </c>
       <c r="B114" t="n">
-        <v>5.483021259307861</v>
+        <v>5.48302173614502</v>
       </c>
       <c r="C114" t="n">
-        <v>5.536254426129148</v>
+        <v>5.536254907595789</v>
       </c>
       <c r="D114" t="n">
-        <v>5.376554925665286</v>
+        <v>5.376555393243478</v>
       </c>
       <c r="E114" t="n">
-        <v>5.474149276367449</v>
+        <v>5.474149752433044</v>
       </c>
       <c r="F114" t="n">
         <v>3854900</v>
@@ -2712,16 +2712,16 @@
         <v>44580</v>
       </c>
       <c r="B115" t="n">
-        <v>5.651593685150146</v>
+        <v>5.651593208312988</v>
       </c>
       <c r="C115" t="n">
-        <v>5.749188044821177</v>
+        <v>5.749187559749773</v>
       </c>
       <c r="D115" t="n">
-        <v>5.509638560581113</v>
+        <v>5.509638095721016</v>
       </c>
       <c r="E115" t="n">
-        <v>5.509638560581113</v>
+        <v>5.509638095721016</v>
       </c>
       <c r="F115" t="n">
         <v>12660500</v>
@@ -2732,16 +2732,16 @@
         <v>44581</v>
       </c>
       <c r="B116" t="n">
-        <v>5.713698863983154</v>
+        <v>5.713699340820312</v>
       </c>
       <c r="C116" t="n">
-        <v>5.837909589292028</v>
+        <v>5.837910076495201</v>
       </c>
       <c r="D116" t="n">
-        <v>5.633848900469072</v>
+        <v>5.633849370642346</v>
       </c>
       <c r="E116" t="n">
-        <v>5.651593289798911</v>
+        <v>5.651593761453044</v>
       </c>
       <c r="F116" t="n">
         <v>9343500</v>
@@ -2752,16 +2752,16 @@
         <v>44582</v>
       </c>
       <c r="B117" t="n">
-        <v>5.527382373809814</v>
+        <v>5.527382850646973</v>
       </c>
       <c r="C117" t="n">
-        <v>5.687081872269151</v>
+        <v>5.687082362883293</v>
       </c>
       <c r="D117" t="n">
-        <v>5.483021190485755</v>
+        <v>5.483021663495955</v>
       </c>
       <c r="E117" t="n">
-        <v>5.678209889440098</v>
+        <v>5.678210379288871</v>
       </c>
       <c r="F117" t="n">
         <v>7609900</v>
@@ -2772,16 +2772,16 @@
         <v>44585</v>
       </c>
       <c r="B118" t="n">
-        <v>5.456405639648438</v>
+        <v>5.456405162811279</v>
       </c>
       <c r="C118" t="n">
-        <v>5.491894422421788</v>
+        <v>5.491893942483253</v>
       </c>
       <c r="D118" t="n">
-        <v>5.349939291328385</v>
+        <v>5.349938823795358</v>
       </c>
       <c r="E118" t="n">
-        <v>5.465277623811945</v>
+        <v>5.465277146199461</v>
       </c>
       <c r="F118" t="n">
         <v>8531700</v>
@@ -2792,16 +2792,16 @@
         <v>44586</v>
       </c>
       <c r="B119" t="n">
-        <v>5.500765800476074</v>
+        <v>5.500766277313232</v>
       </c>
       <c r="C119" t="n">
-        <v>5.571743781261634</v>
+        <v>5.57174426425156</v>
       </c>
       <c r="D119" t="n">
-        <v>5.367683091269735</v>
+        <v>5.36768355657054</v>
       </c>
       <c r="E119" t="n">
-        <v>5.394299463887157</v>
+        <v>5.394299931495218</v>
       </c>
       <c r="F119" t="n">
         <v>8097000</v>
@@ -2812,16 +2812,16 @@
         <v>44587</v>
       </c>
       <c r="B120" t="n">
-        <v>5.518511295318604</v>
+        <v>5.518510341644287</v>
       </c>
       <c r="C120" t="n">
-        <v>5.678211255251036</v>
+        <v>5.67821027397838</v>
       </c>
       <c r="D120" t="n">
-        <v>5.491894917369664</v>
+        <v>5.491893968295023</v>
       </c>
       <c r="E120" t="n">
-        <v>5.59836127528482</v>
+        <v>5.598360307811333</v>
       </c>
       <c r="F120" t="n">
         <v>11610000</v>
@@ -2852,16 +2852,16 @@
         <v>44589</v>
       </c>
       <c r="B122" t="n">
-        <v>5.660465717315674</v>
+        <v>5.660465240478516</v>
       </c>
       <c r="C122" t="n">
-        <v>5.731443274902391</v>
+        <v>5.731442792086089</v>
       </c>
       <c r="D122" t="n">
-        <v>5.509638195914094</v>
+        <v>5.509637731782632</v>
       </c>
       <c r="E122" t="n">
-        <v>5.509638195914094</v>
+        <v>5.509637731782632</v>
       </c>
       <c r="F122" t="n">
         <v>15566700</v>
@@ -2872,16 +2872,16 @@
         <v>44592</v>
       </c>
       <c r="B123" t="n">
-        <v>5.6959547996521</v>
+        <v>5.695954322814941</v>
       </c>
       <c r="C123" t="n">
-        <v>5.793549158064543</v>
+        <v>5.793548673057267</v>
       </c>
       <c r="D123" t="n">
-        <v>5.571744067256032</v>
+        <v>5.571743600817181</v>
       </c>
       <c r="E123" t="n">
-        <v>5.607232847940623</v>
+        <v>5.607232378530827</v>
       </c>
       <c r="F123" t="n">
         <v>7514700</v>
@@ -2892,16 +2892,16 @@
         <v>44593</v>
       </c>
       <c r="B124" t="n">
-        <v>5.678210735321045</v>
+        <v>5.678210258483887</v>
       </c>
       <c r="C124" t="n">
-        <v>5.793549490697893</v>
+        <v>5.793549004174971</v>
       </c>
       <c r="D124" t="n">
-        <v>5.536255181372748</v>
+        <v>5.536254716456543</v>
       </c>
       <c r="E124" t="n">
-        <v>5.766932692126443</v>
+        <v>5.766932207838711</v>
       </c>
       <c r="F124" t="n">
         <v>8050400</v>
@@ -2912,16 +2912,16 @@
         <v>44594</v>
       </c>
       <c r="B125" t="n">
-        <v>5.669337749481201</v>
+        <v>5.669337272644043</v>
       </c>
       <c r="C125" t="n">
-        <v>5.882270847141231</v>
+        <v>5.882270352394677</v>
       </c>
       <c r="D125" t="n">
-        <v>5.651593359931167</v>
+        <v>5.651592884586456</v>
       </c>
       <c r="E125" t="n">
-        <v>5.722570918131304</v>
+        <v>5.722570436816806</v>
       </c>
       <c r="F125" t="n">
         <v>8808600</v>
@@ -2932,16 +2932,16 @@
         <v>44595</v>
       </c>
       <c r="B126" t="n">
-        <v>5.731443405151367</v>
+        <v>5.731442928314209</v>
       </c>
       <c r="C126" t="n">
-        <v>5.793548980980922</v>
+        <v>5.793548498976785</v>
       </c>
       <c r="D126" t="n">
-        <v>5.616104659922033</v>
+        <v>5.616104192680678</v>
       </c>
       <c r="E126" t="n">
-        <v>5.678210235751588</v>
+        <v>5.678209763343253</v>
       </c>
       <c r="F126" t="n">
         <v>8390300</v>
@@ -2952,16 +2952,16 @@
         <v>44596</v>
       </c>
       <c r="B127" t="n">
-        <v>5.660465717315674</v>
+        <v>5.660465240478516</v>
       </c>
       <c r="C127" t="n">
-        <v>5.820165221885787</v>
+        <v>5.820164731595556</v>
       </c>
       <c r="D127" t="n">
-        <v>5.633848921690848</v>
+        <v>5.633848447095886</v>
       </c>
       <c r="E127" t="n">
-        <v>5.722570868674245</v>
+        <v>5.722570386605353</v>
       </c>
       <c r="F127" t="n">
         <v>8483700</v>
@@ -2992,16 +2992,16 @@
         <v>44600</v>
       </c>
       <c r="B129" t="n">
-        <v>5.616105079650879</v>
+        <v>5.616104602813721</v>
       </c>
       <c r="C129" t="n">
-        <v>5.695955051248079</v>
+        <v>5.695954567631234</v>
       </c>
       <c r="D129" t="n">
-        <v>5.48302193467543</v>
+        <v>5.483021469137738</v>
       </c>
       <c r="E129" t="n">
-        <v>5.580616297398714</v>
+        <v>5.580615823574741</v>
       </c>
       <c r="F129" t="n">
         <v>9770800</v>
@@ -3012,16 +3012,16 @@
         <v>44601</v>
       </c>
       <c r="B130" t="n">
-        <v>5.633849620819092</v>
+        <v>5.633849143981934</v>
       </c>
       <c r="C130" t="n">
-        <v>5.740315970411027</v>
+        <v>5.740315484562782</v>
       </c>
       <c r="D130" t="n">
-        <v>5.589488853352285</v>
+        <v>5.58948838026973</v>
       </c>
       <c r="E130" t="n">
-        <v>5.616105229220436</v>
+        <v>5.616104753885126</v>
       </c>
       <c r="F130" t="n">
         <v>8867400</v>
@@ -3052,16 +3052,16 @@
         <v>44603</v>
       </c>
       <c r="B132" t="n">
-        <v>5.633849620819092</v>
+        <v>5.633849143981934</v>
       </c>
       <c r="C132" t="n">
-        <v>5.775805176668006</v>
+        <v>5.775804687816029</v>
       </c>
       <c r="D132" t="n">
-        <v>5.589488853352285</v>
+        <v>5.58948838026973</v>
       </c>
       <c r="E132" t="n">
-        <v>5.731443986141532</v>
+        <v>5.731443501044193</v>
       </c>
       <c r="F132" t="n">
         <v>8001300</v>
@@ -3072,16 +3072,16 @@
         <v>44606</v>
       </c>
       <c r="B133" t="n">
-        <v>5.6959547996521</v>
+        <v>5.695954322814941</v>
       </c>
       <c r="C133" t="n">
-        <v>5.766932361021281</v>
+        <v>5.766931878242232</v>
       </c>
       <c r="D133" t="n">
-        <v>5.642721628625214</v>
+        <v>5.642721156244472</v>
       </c>
       <c r="E133" t="n">
-        <v>5.642721628625214</v>
+        <v>5.642721156244472</v>
       </c>
       <c r="F133" t="n">
         <v>12680200</v>
@@ -3092,16 +3092,16 @@
         <v>44607</v>
       </c>
       <c r="B134" t="n">
-        <v>5.6959547996521</v>
+        <v>5.695954322814941</v>
       </c>
       <c r="C134" t="n">
-        <v>5.811293548406838</v>
+        <v>5.81129306191409</v>
       </c>
       <c r="D134" t="n">
-        <v>5.518510473169509</v>
+        <v>5.518510011187112</v>
       </c>
       <c r="E134" t="n">
-        <v>5.811293548406838</v>
+        <v>5.81129306191409</v>
       </c>
       <c r="F134" t="n">
         <v>17426200</v>
@@ -3152,16 +3152,16 @@
         <v>44610</v>
       </c>
       <c r="B137" t="n">
-        <v>5.420916557312012</v>
+        <v>5.420916080474854</v>
       </c>
       <c r="C137" t="n">
-        <v>5.616104851779219</v>
+        <v>5.616104357772818</v>
       </c>
       <c r="D137" t="n">
-        <v>5.305577808142479</v>
+        <v>5.305577341450801</v>
       </c>
       <c r="E137" t="n">
-        <v>5.598360461373109</v>
+        <v>5.598359968927548</v>
       </c>
       <c r="F137" t="n">
         <v>12852100</v>
@@ -3172,16 +3172,16 @@
         <v>44613</v>
       </c>
       <c r="B138" t="n">
-        <v>5.119261264801025</v>
+        <v>5.119261741638184</v>
       </c>
       <c r="C138" t="n">
-        <v>5.456405090261659</v>
+        <v>5.456405598502314</v>
       </c>
       <c r="D138" t="n">
-        <v>5.074900079271083</v>
+        <v>5.074900551976187</v>
       </c>
       <c r="E138" t="n">
-        <v>5.447532683931823</v>
+        <v>5.447533191346051</v>
       </c>
       <c r="F138" t="n">
         <v>8726900</v>
@@ -3212,16 +3212,16 @@
         <v>44615</v>
       </c>
       <c r="B140" t="n">
-        <v>5.021667003631592</v>
+        <v>5.02166748046875</v>
       </c>
       <c r="C140" t="n">
-        <v>5.101516969842998</v>
+        <v>5.101517454262385</v>
       </c>
       <c r="D140" t="n">
-        <v>4.968433833843864</v>
+        <v>4.968434305626215</v>
       </c>
       <c r="E140" t="n">
-        <v>5.057155783490078</v>
+        <v>5.057156263697106</v>
       </c>
       <c r="F140" t="n">
         <v>10772600</v>
@@ -3232,16 +3232,16 @@
         <v>44616</v>
       </c>
       <c r="B141" t="n">
-        <v>5.119261264801025</v>
+        <v>5.119261741638184</v>
       </c>
       <c r="C141" t="n">
-        <v>5.137005654401078</v>
+        <v>5.137006132891051</v>
       </c>
       <c r="D141" t="n">
-        <v>4.773245456070175</v>
+        <v>4.773245900677449</v>
       </c>
       <c r="E141" t="n">
-        <v>4.924072979200438</v>
+        <v>4.924073437856647</v>
       </c>
       <c r="F141" t="n">
         <v>11357100</v>
@@ -3252,16 +3252,16 @@
         <v>44617</v>
       </c>
       <c r="B142" t="n">
-        <v>5.066028118133545</v>
+        <v>5.066027641296387</v>
       </c>
       <c r="C142" t="n">
-        <v>5.163622472890022</v>
+        <v>5.163621986866849</v>
       </c>
       <c r="D142" t="n">
-        <v>4.986178153054643</v>
+        <v>4.986177683733319</v>
       </c>
       <c r="E142" t="n">
-        <v>5.110389303857295</v>
+        <v>5.110388822844664</v>
       </c>
       <c r="F142" t="n">
         <v>6795000</v>
@@ -3292,16 +3292,16 @@
         <v>44623</v>
       </c>
       <c r="B144" t="n">
-        <v>5.465277671813965</v>
+        <v>5.465277194976807</v>
       </c>
       <c r="C144" t="n">
-        <v>5.545127645285164</v>
+        <v>5.545127161481217</v>
       </c>
       <c r="D144" t="n">
-        <v>5.323322539473757</v>
+        <v>5.323322075021968</v>
       </c>
       <c r="E144" t="n">
-        <v>5.323322539473757</v>
+        <v>5.323322075021968</v>
       </c>
       <c r="F144" t="n">
         <v>18057800</v>
@@ -3332,16 +3332,16 @@
         <v>44627</v>
       </c>
       <c r="B146" t="n">
-        <v>5.483021259307861</v>
+        <v>5.48302173614502</v>
       </c>
       <c r="C146" t="n">
-        <v>5.58948801601004</v>
+        <v>5.5894885021062</v>
       </c>
       <c r="D146" t="n">
-        <v>5.403171720605732</v>
+        <v>5.403172190498684</v>
       </c>
       <c r="E146" t="n">
-        <v>5.491893665307877</v>
+        <v>5.491894142916634</v>
       </c>
       <c r="F146" t="n">
         <v>12429900</v>
@@ -3372,16 +3372,16 @@
         <v>44629</v>
       </c>
       <c r="B148" t="n">
-        <v>5.6959547996521</v>
+        <v>5.695954322814941</v>
       </c>
       <c r="C148" t="n">
-        <v>5.704826783293429</v>
+        <v>5.704826305713552</v>
       </c>
       <c r="D148" t="n">
-        <v>5.553999676913737</v>
+        <v>5.553999211960359</v>
       </c>
       <c r="E148" t="n">
-        <v>5.589488457598327</v>
+        <v>5.589487989674004</v>
       </c>
       <c r="F148" t="n">
         <v>9079900</v>
@@ -3392,16 +3392,16 @@
         <v>44630</v>
       </c>
       <c r="B149" t="n">
-        <v>5.6959547996521</v>
+        <v>5.695954322814941</v>
       </c>
       <c r="C149" t="n">
-        <v>5.829037938749134</v>
+        <v>5.829037450770913</v>
       </c>
       <c r="D149" t="n">
-        <v>5.553999676913737</v>
+        <v>5.553999211960359</v>
       </c>
       <c r="E149" t="n">
-        <v>5.624977238282918</v>
+        <v>5.62497676738765</v>
       </c>
       <c r="F149" t="n">
         <v>15215200</v>
@@ -3412,16 +3412,16 @@
         <v>44631</v>
       </c>
       <c r="B150" t="n">
-        <v>5.598360061645508</v>
+        <v>5.598360538482666</v>
       </c>
       <c r="C150" t="n">
-        <v>5.97986463966694</v>
+        <v>5.979865148998535</v>
       </c>
       <c r="D150" t="n">
-        <v>5.527382505088926</v>
+        <v>5.52738297588061</v>
       </c>
       <c r="E150" t="n">
-        <v>5.695954413440612</v>
+        <v>5.695954898590315</v>
       </c>
       <c r="F150" t="n">
         <v>16712700</v>
@@ -3452,16 +3452,16 @@
         <v>44635</v>
       </c>
       <c r="B152" t="n">
-        <v>5.651593685150146</v>
+        <v>5.651593208312988</v>
       </c>
       <c r="C152" t="n">
-        <v>5.687082466292404</v>
+        <v>5.687081986460981</v>
       </c>
       <c r="D152" t="n">
-        <v>5.500766153765728</v>
+        <v>5.500765689654214</v>
       </c>
       <c r="E152" t="n">
-        <v>5.509638560581113</v>
+        <v>5.509638095721016</v>
       </c>
       <c r="F152" t="n">
         <v>5880900</v>
@@ -3492,16 +3492,16 @@
         <v>44637</v>
       </c>
       <c r="B154" t="n">
-        <v>5.891143798828125</v>
+        <v>5.891142845153809</v>
       </c>
       <c r="C154" t="n">
-        <v>5.926632583762174</v>
+        <v>5.926631624342837</v>
       </c>
       <c r="D154" t="n">
-        <v>5.536255526427944</v>
+        <v>5.536254630203903</v>
       </c>
       <c r="E154" t="n">
-        <v>5.607233519355731</v>
+        <v>5.607232611641579</v>
       </c>
       <c r="F154" t="n">
         <v>10001800</v>
@@ -3512,16 +3512,16 @@
         <v>44638</v>
       </c>
       <c r="B155" t="n">
-        <v>6.201669692993164</v>
+        <v>6.201670169830322</v>
       </c>
       <c r="C155" t="n">
-        <v>6.201669692993164</v>
+        <v>6.201670169830322</v>
       </c>
       <c r="D155" t="n">
-        <v>5.891142672652063</v>
+        <v>5.891143125613262</v>
       </c>
       <c r="E155" t="n">
-        <v>5.891142672652063</v>
+        <v>5.891143125613262</v>
       </c>
       <c r="F155" t="n">
         <v>17710700</v>
@@ -3572,16 +3572,16 @@
         <v>44643</v>
       </c>
       <c r="B158" t="n">
-        <v>6.308136463165283</v>
+        <v>6.308136940002441</v>
       </c>
       <c r="C158" t="n">
-        <v>6.334752835301306</v>
+        <v>6.334753314150418</v>
       </c>
       <c r="D158" t="n">
-        <v>6.201669705442368</v>
+        <v>6.201670174231618</v>
       </c>
       <c r="E158" t="n">
-        <v>6.263775278859101</v>
+        <v>6.263775752342961</v>
       </c>
       <c r="F158" t="n">
         <v>8187500</v>
@@ -3612,16 +3612,16 @@
         <v>44645</v>
       </c>
       <c r="B160" t="n">
-        <v>6.450092315673828</v>
+        <v>6.450091361999512</v>
       </c>
       <c r="C160" t="n">
-        <v>6.512197896212132</v>
+        <v>6.512196933355233</v>
       </c>
       <c r="D160" t="n">
-        <v>6.237159621930483</v>
+        <v>6.237158699739195</v>
       </c>
       <c r="E160" t="n">
-        <v>6.343625968802155</v>
+        <v>6.343625030869354</v>
       </c>
       <c r="F160" t="n">
         <v>15324200</v>
@@ -3632,16 +3632,16 @@
         <v>44648</v>
       </c>
       <c r="B161" t="n">
-        <v>6.538814067840576</v>
+        <v>6.538813591003418</v>
       </c>
       <c r="C161" t="n">
-        <v>6.592047239619212</v>
+        <v>6.592046758900072</v>
       </c>
       <c r="D161" t="n">
-        <v>6.35249775508553</v>
+        <v>6.352497291835322</v>
       </c>
       <c r="E161" t="n">
-        <v>6.432347724283304</v>
+        <v>6.432347255210109</v>
       </c>
       <c r="F161" t="n">
         <v>10802600</v>
@@ -3652,16 +3652,16 @@
         <v>44649</v>
       </c>
       <c r="B162" t="n">
-        <v>6.512197494506836</v>
+        <v>6.512197017669678</v>
       </c>
       <c r="C162" t="n">
-        <v>6.645280208357383</v>
+        <v>6.645279721775622</v>
       </c>
       <c r="D162" t="n">
-        <v>6.387986341092201</v>
+        <v>6.387985873350052</v>
       </c>
       <c r="E162" t="n">
-        <v>6.476708714405406</v>
+        <v>6.476708240166813</v>
       </c>
       <c r="F162" t="n">
         <v>18100700</v>
@@ -3732,16 +3732,16 @@
         <v>44655</v>
       </c>
       <c r="B166" t="n">
-        <v>6.210543155670166</v>
+        <v>6.210542678833008</v>
       </c>
       <c r="C166" t="n">
-        <v>6.237159955340726</v>
+        <v>6.237159476459965</v>
       </c>
       <c r="D166" t="n">
-        <v>6.050843626825847</v>
+        <v>6.050843162250203</v>
       </c>
       <c r="E166" t="n">
-        <v>6.157309979388726</v>
+        <v>6.15730950663874</v>
       </c>
       <c r="F166" t="n">
         <v>13343800</v>
@@ -3812,16 +3812,16 @@
         <v>44659</v>
       </c>
       <c r="B170" t="n">
-        <v>6.190385341644287</v>
+        <v>6.190384864807129</v>
       </c>
       <c r="C170" t="n">
-        <v>6.323990869283284</v>
+        <v>6.323990382154669</v>
       </c>
       <c r="D170" t="n">
-        <v>6.136943215532741</v>
+        <v>6.136942742812159</v>
       </c>
       <c r="E170" t="n">
-        <v>6.234920659097374</v>
+        <v>6.23492017882972</v>
       </c>
       <c r="F170" t="n">
         <v>10722400</v>
@@ -3832,16 +3832,16 @@
         <v>44662</v>
       </c>
       <c r="B171" t="n">
-        <v>6.145850658416748</v>
+        <v>6.14585018157959</v>
       </c>
       <c r="C171" t="n">
-        <v>6.21710682899452</v>
+        <v>6.21710634662882</v>
       </c>
       <c r="D171" t="n">
-        <v>6.021152359905646</v>
+        <v>6.021151892743435</v>
       </c>
       <c r="E171" t="n">
-        <v>6.119129382089944</v>
+        <v>6.119128907326005</v>
       </c>
       <c r="F171" t="n">
         <v>4955900</v>
@@ -3852,16 +3852,16 @@
         <v>44663</v>
       </c>
       <c r="B172" t="n">
-        <v>6.217105865478516</v>
+        <v>6.217106342315674</v>
       </c>
       <c r="C172" t="n">
-        <v>6.359618184547754</v>
+        <v>6.359618672315267</v>
       </c>
       <c r="D172" t="n">
-        <v>6.145849705943896</v>
+        <v>6.145850177315878</v>
       </c>
       <c r="E172" t="n">
-        <v>6.190384593292927</v>
+        <v>6.190385068080627</v>
       </c>
       <c r="F172" t="n">
         <v>15598900</v>
@@ -3872,16 +3872,16 @@
         <v>44664</v>
       </c>
       <c r="B173" t="n">
-        <v>6.306176662445068</v>
+        <v>6.306175708770752</v>
       </c>
       <c r="C173" t="n">
-        <v>6.323990704016711</v>
+        <v>6.323989747648402</v>
       </c>
       <c r="D173" t="n">
-        <v>6.172571138297622</v>
+        <v>6.172570204828283</v>
       </c>
       <c r="E173" t="n">
-        <v>6.261641770876088</v>
+        <v>6.261640823936721</v>
       </c>
       <c r="F173" t="n">
         <v>5828500</v>
@@ -3892,16 +3892,16 @@
         <v>44665</v>
       </c>
       <c r="B174" t="n">
-        <v>6.323990821838379</v>
+        <v>6.323990345001221</v>
       </c>
       <c r="C174" t="n">
-        <v>6.350712097053812</v>
+        <v>6.350711618201833</v>
       </c>
       <c r="D174" t="n">
-        <v>6.226013379008809</v>
+        <v>6.226012909559278</v>
       </c>
       <c r="E174" t="n">
-        <v>6.297269971343208</v>
+        <v>6.297269496520836</v>
       </c>
       <c r="F174" t="n">
         <v>4947000</v>
@@ -3932,16 +3932,16 @@
         <v>44670</v>
       </c>
       <c r="B176" t="n">
-        <v>6.190385341644287</v>
+        <v>6.190384864807129</v>
       </c>
       <c r="C176" t="n">
-        <v>6.413061079469193</v>
+        <v>6.413060585479618</v>
       </c>
       <c r="D176" t="n">
-        <v>6.181478532985828</v>
+        <v>6.18147805683475</v>
       </c>
       <c r="E176" t="n">
-        <v>6.359618953357647</v>
+        <v>6.359618463484649</v>
       </c>
       <c r="F176" t="n">
         <v>12659600</v>
@@ -3952,16 +3952,16 @@
         <v>44671</v>
       </c>
       <c r="B177" t="n">
-        <v>6.208199024200439</v>
+        <v>6.208198547363281</v>
       </c>
       <c r="C177" t="n">
-        <v>6.279455612943373</v>
+        <v>6.279455130633163</v>
       </c>
       <c r="D177" t="n">
-        <v>6.110222011029355</v>
+        <v>6.11022154171758</v>
       </c>
       <c r="E177" t="n">
-        <v>6.190384983194765</v>
+        <v>6.190384507725862</v>
       </c>
       <c r="F177" t="n">
         <v>7897000</v>
@@ -3972,16 +3972,16 @@
         <v>44673</v>
       </c>
       <c r="B178" t="n">
-        <v>6.128036022186279</v>
+        <v>6.128035545349121</v>
       </c>
       <c r="C178" t="n">
-        <v>6.190384953042324</v>
+        <v>6.190384471353647</v>
       </c>
       <c r="D178" t="n">
-        <v>5.98552327011481</v>
+        <v>5.98552280436691</v>
       </c>
       <c r="E178" t="n">
-        <v>6.136942830285612</v>
+        <v>6.136942352755394</v>
       </c>
       <c r="F178" t="n">
         <v>9926800</v>
@@ -3992,16 +3992,16 @@
         <v>44676</v>
       </c>
       <c r="B179" t="n">
-        <v>6.279455661773682</v>
+        <v>6.279454708099365</v>
       </c>
       <c r="C179" t="n">
-        <v>6.306176511129858</v>
+        <v>6.306175553397391</v>
       </c>
       <c r="D179" t="n">
-        <v>6.038965893966873</v>
+        <v>6.038964976816251</v>
       </c>
       <c r="E179" t="n">
-        <v>6.047872702178851</v>
+        <v>6.047871783675533</v>
       </c>
       <c r="F179" t="n">
         <v>9340700</v>
@@ -4012,16 +4012,16 @@
         <v>44677</v>
       </c>
       <c r="B180" t="n">
-        <v>6.252734661102295</v>
+        <v>6.252734184265137</v>
       </c>
       <c r="C180" t="n">
-        <v>6.33289806211651</v>
+        <v>6.332897579166045</v>
       </c>
       <c r="D180" t="n">
-        <v>6.11912913431869</v>
+        <v>6.119128667670365</v>
       </c>
       <c r="E180" t="n">
-        <v>6.243827852500861</v>
+        <v>6.24382737634294</v>
       </c>
       <c r="F180" t="n">
         <v>9190800</v>
@@ -4032,16 +4032,16 @@
         <v>44678</v>
       </c>
       <c r="B181" t="n">
-        <v>6.332897186279297</v>
+        <v>6.332898139953613</v>
       </c>
       <c r="C181" t="n">
-        <v>6.359618033108378</v>
+        <v>6.359618990806601</v>
       </c>
       <c r="D181" t="n">
-        <v>6.208198485342908</v>
+        <v>6.20819942023878</v>
       </c>
       <c r="E181" t="n">
-        <v>6.288361875270557</v>
+        <v>6.288362822238278</v>
       </c>
       <c r="F181" t="n">
         <v>11357200</v>
@@ -4052,16 +4052,16 @@
         <v>44679</v>
       </c>
       <c r="B182" t="n">
-        <v>6.404154300689697</v>
+        <v>6.404153347015381</v>
       </c>
       <c r="C182" t="n">
-        <v>6.404154300689697</v>
+        <v>6.404153347015381</v>
       </c>
       <c r="D182" t="n">
-        <v>6.217106646066473</v>
+        <v>6.217105720246349</v>
       </c>
       <c r="E182" t="n">
-        <v>6.33289813220852</v>
+        <v>6.332897189145312</v>
       </c>
       <c r="F182" t="n">
         <v>9691200</v>
@@ -4072,16 +4072,16 @@
         <v>44680</v>
       </c>
       <c r="B183" t="n">
-        <v>6.145850658416748</v>
+        <v>6.14585018157959</v>
       </c>
       <c r="C183" t="n">
-        <v>6.44868938337228</v>
+        <v>6.44868888303882</v>
       </c>
       <c r="D183" t="n">
-        <v>6.065687254156614</v>
+        <v>6.065686783539082</v>
       </c>
       <c r="E183" t="n">
-        <v>6.413061298083393</v>
+        <v>6.413060800514205</v>
       </c>
       <c r="F183" t="n">
         <v>21979100</v>
@@ -4092,16 +4092,16 @@
         <v>44683</v>
       </c>
       <c r="B184" t="n">
-        <v>5.86973237991333</v>
+        <v>5.869731903076172</v>
       </c>
       <c r="C184" t="n">
-        <v>6.19038512538046</v>
+        <v>6.19038462249456</v>
       </c>
       <c r="D184" t="n">
-        <v>5.745033665289197</v>
+        <v>5.745033198582139</v>
       </c>
       <c r="E184" t="n">
-        <v>6.145850234203484</v>
+        <v>6.145849734935447</v>
       </c>
       <c r="F184" t="n">
         <v>12404500</v>
@@ -4132,16 +4132,16 @@
         <v>44685</v>
       </c>
       <c r="B186" t="n">
-        <v>5.388752460479736</v>
+        <v>5.388751983642578</v>
       </c>
       <c r="C186" t="n">
-        <v>5.51345074167094</v>
+        <v>5.513450253799544</v>
       </c>
       <c r="D186" t="n">
-        <v>5.210611634057798</v>
+        <v>5.210611172983874</v>
       </c>
       <c r="E186" t="n">
-        <v>5.51345074167094</v>
+        <v>5.513450253799544</v>
       </c>
       <c r="F186" t="n">
         <v>18834300</v>
@@ -4192,16 +4192,16 @@
         <v>44690</v>
       </c>
       <c r="B189" t="n">
-        <v>4.622747898101807</v>
+        <v>4.622747421264648</v>
       </c>
       <c r="C189" t="n">
-        <v>4.934493814409667</v>
+        <v>4.934493305415869</v>
       </c>
       <c r="D189" t="n">
-        <v>4.435700263373046</v>
+        <v>4.435699805829881</v>
       </c>
       <c r="E189" t="n">
-        <v>4.934493814409667</v>
+        <v>4.934493305415869</v>
       </c>
       <c r="F189" t="n">
         <v>21341300</v>
@@ -4212,16 +4212,16 @@
         <v>44691</v>
       </c>
       <c r="B190" t="n">
-        <v>4.631655216217041</v>
+        <v>4.631654739379883</v>
       </c>
       <c r="C190" t="n">
-        <v>4.7118186184255</v>
+        <v>4.711818133335377</v>
       </c>
       <c r="D190" t="n">
-        <v>4.569306280917366</v>
+        <v>4.569305810499142</v>
       </c>
       <c r="E190" t="n">
-        <v>4.65837649185995</v>
+        <v>4.658376012271789</v>
       </c>
       <c r="F190" t="n">
         <v>9825600</v>
@@ -4352,16 +4352,16 @@
         <v>44700</v>
       </c>
       <c r="B197" t="n">
-        <v>5.050285339355469</v>
+        <v>5.050285816192627</v>
       </c>
       <c r="C197" t="n">
-        <v>5.183890854759837</v>
+        <v>5.183891344211743</v>
       </c>
       <c r="D197" t="n">
-        <v>4.898865783545199</v>
+        <v>4.898866246085646</v>
       </c>
       <c r="E197" t="n">
-        <v>4.987935985574703</v>
+        <v>4.987936456524968</v>
       </c>
       <c r="F197" t="n">
         <v>12233400</v>
@@ -4372,16 +4372,16 @@
         <v>44701</v>
       </c>
       <c r="B198" t="n">
-        <v>4.934494018554688</v>
+        <v>4.934494495391846</v>
       </c>
       <c r="C198" t="n">
-        <v>5.121541661021799</v>
+        <v>5.121542155934015</v>
       </c>
       <c r="D198" t="n">
-        <v>4.827609772779264</v>
+        <v>4.82761023928783</v>
       </c>
       <c r="E198" t="n">
-        <v>5.094820387217823</v>
+        <v>5.09482087954787</v>
       </c>
       <c r="F198" t="n">
         <v>10517400</v>
@@ -4392,16 +4392,16 @@
         <v>44704</v>
       </c>
       <c r="B199" t="n">
-        <v>5.023564338684082</v>
+        <v>5.023563861846924</v>
       </c>
       <c r="C199" t="n">
-        <v>5.10372773721593</v>
+        <v>5.103727252769655</v>
       </c>
       <c r="D199" t="n">
-        <v>4.881052007712129</v>
+        <v>4.881051544402253</v>
       </c>
       <c r="E199" t="n">
-        <v>4.979029447615471</v>
+        <v>4.979028975005568</v>
       </c>
       <c r="F199" t="n">
         <v>11444200</v>
@@ -4412,16 +4412,16 @@
         <v>44705</v>
       </c>
       <c r="B200" t="n">
-        <v>5.157169818878174</v>
+        <v>5.157168865203857</v>
       </c>
       <c r="C200" t="n">
-        <v>5.201705134300433</v>
+        <v>5.201704172390555</v>
       </c>
       <c r="D200" t="n">
-        <v>4.961215365404775</v>
+        <v>4.961214447966753</v>
       </c>
       <c r="E200" t="n">
-        <v>4.979029406629629</v>
+        <v>4.979028485897399</v>
       </c>
       <c r="F200" t="n">
         <v>9007600</v>
@@ -4432,16 +4432,16 @@
         <v>44706</v>
       </c>
       <c r="B201" t="n">
-        <v>5.272961139678955</v>
+        <v>5.272961616516113</v>
       </c>
       <c r="C201" t="n">
-        <v>5.326403261736754</v>
+        <v>5.326403743406717</v>
       </c>
       <c r="D201" t="n">
-        <v>5.112634348785326</v>
+        <v>5.112634811124033</v>
       </c>
       <c r="E201" t="n">
-        <v>5.148262854877424</v>
+        <v>5.148263320438039</v>
       </c>
       <c r="F201" t="n">
         <v>9738900</v>
@@ -4452,16 +4452,16 @@
         <v>44707</v>
       </c>
       <c r="B202" t="n">
-        <v>5.504543304443359</v>
+        <v>5.504544258117676</v>
       </c>
       <c r="C202" t="n">
-        <v>5.647056045223134</v>
+        <v>5.647057023588098</v>
       </c>
       <c r="D202" t="n">
-        <v>5.281867598240178</v>
+        <v>5.281868513335436</v>
       </c>
       <c r="E202" t="n">
-        <v>5.281867598240178</v>
+        <v>5.281868513335436</v>
       </c>
       <c r="F202" t="n">
         <v>14781100</v>
@@ -4472,16 +4472,16 @@
         <v>44708</v>
       </c>
       <c r="B203" t="n">
-        <v>5.406566619873047</v>
+        <v>5.406567096710205</v>
       </c>
       <c r="C203" t="n">
-        <v>5.584707025503037</v>
+        <v>5.584707518051453</v>
       </c>
       <c r="D203" t="n">
-        <v>5.388752579310048</v>
+        <v>5.38875305457608</v>
       </c>
       <c r="E203" t="n">
-        <v>5.522357671172426</v>
+        <v>5.522358158221883</v>
       </c>
       <c r="F203" t="n">
         <v>11400800</v>
@@ -4532,16 +4532,16 @@
         <v>44713</v>
       </c>
       <c r="B206" t="n">
-        <v>5.513451099395752</v>
+        <v>5.513450622558594</v>
       </c>
       <c r="C206" t="n">
-        <v>5.549079182047723</v>
+        <v>5.54907870212923</v>
       </c>
       <c r="D206" t="n">
-        <v>5.406566851439836</v>
+        <v>5.406566383846685</v>
       </c>
       <c r="E206" t="n">
-        <v>5.495637058069765</v>
+        <v>5.495636582773276</v>
       </c>
       <c r="F206" t="n">
         <v>9091200</v>
@@ -4552,16 +4552,16 @@
         <v>44714</v>
       </c>
       <c r="B207" t="n">
-        <v>5.611428737640381</v>
+        <v>5.611428260803223</v>
       </c>
       <c r="C207" t="n">
-        <v>5.655963630171337</v>
+        <v>5.655963149549779</v>
       </c>
       <c r="D207" t="n">
-        <v>5.50454406118151</v>
+        <v>5.504543593426991</v>
       </c>
       <c r="E207" t="n">
-        <v>5.549079378432728</v>
+        <v>5.549078906893773</v>
       </c>
       <c r="F207" t="n">
         <v>14163200</v>
@@ -4572,16 +4572,16 @@
         <v>44715</v>
       </c>
       <c r="B208" t="n">
-        <v>5.513451099395752</v>
+        <v>5.513450622558594</v>
       </c>
       <c r="C208" t="n">
-        <v>5.602521306025682</v>
+        <v>5.602520821485185</v>
       </c>
       <c r="D208" t="n">
-        <v>5.451101742394677</v>
+        <v>5.451101270949875</v>
       </c>
       <c r="E208" t="n">
-        <v>5.575800456396826</v>
+        <v>5.575799974167312</v>
       </c>
       <c r="F208" t="n">
         <v>9326300</v>
@@ -4612,16 +4612,16 @@
         <v>44719</v>
       </c>
       <c r="B210" t="n">
-        <v>5.023564338684082</v>
+        <v>5.023563861846924</v>
       </c>
       <c r="C210" t="n">
-        <v>5.299682192302366</v>
+        <v>5.299681689256077</v>
       </c>
       <c r="D210" t="n">
-        <v>4.987936255941094</v>
+        <v>4.987935782485756</v>
       </c>
       <c r="E210" t="n">
-        <v>5.281868150930872</v>
+        <v>5.281867649575493</v>
       </c>
       <c r="F210" t="n">
         <v>18881300</v>
@@ -4652,16 +4652,16 @@
         <v>44721</v>
       </c>
       <c r="B212" t="n">
-        <v>4.818702220916748</v>
+        <v>4.818702697753906</v>
       </c>
       <c r="C212" t="n">
-        <v>4.996843043468919</v>
+        <v>4.996843537934095</v>
       </c>
       <c r="D212" t="n">
-        <v>4.809795413385255</v>
+        <v>4.809795889341036</v>
       </c>
       <c r="E212" t="n">
-        <v>4.881051572518039</v>
+        <v>4.88105205552501</v>
       </c>
       <c r="F212" t="n">
         <v>8480000</v>
@@ -4672,16 +4672,16 @@
         <v>44722</v>
       </c>
       <c r="B213" t="n">
-        <v>4.738539695739746</v>
+        <v>4.738540172576904</v>
       </c>
       <c r="C213" t="n">
-        <v>4.783074586986924</v>
+        <v>4.783075068305608</v>
       </c>
       <c r="D213" t="n">
-        <v>4.676190338329397</v>
+        <v>4.676190808892367</v>
       </c>
       <c r="E213" t="n">
-        <v>4.774167778625588</v>
+        <v>4.774168259047984</v>
       </c>
       <c r="F213" t="n">
         <v>4786300</v>
@@ -4692,16 +4692,16 @@
         <v>44725</v>
       </c>
       <c r="B214" t="n">
-        <v>4.569305419921875</v>
+        <v>4.569305896759033</v>
       </c>
       <c r="C214" t="n">
-        <v>4.67618965291275</v>
+        <v>4.676190140903983</v>
       </c>
       <c r="D214" t="n">
-        <v>4.506956071650437</v>
+        <v>4.50695654198103</v>
       </c>
       <c r="E214" t="n">
-        <v>4.631654343473125</v>
+        <v>4.631654826816805</v>
       </c>
       <c r="F214" t="n">
         <v>7709600</v>
@@ -4732,16 +4732,16 @@
         <v>44727</v>
       </c>
       <c r="B216" t="n">
-        <v>4.560399055480957</v>
+        <v>4.560398578643799</v>
       </c>
       <c r="C216" t="n">
-        <v>4.649469266580143</v>
+        <v>4.649468780429767</v>
       </c>
       <c r="D216" t="n">
-        <v>4.480236077851825</v>
+        <v>4.48023560939654</v>
       </c>
       <c r="E216" t="n">
-        <v>4.54258501326112</v>
+        <v>4.542584538286605</v>
       </c>
       <c r="F216" t="n">
         <v>10830000</v>
@@ -4792,16 +4792,16 @@
         <v>44733</v>
       </c>
       <c r="B219" t="n">
-        <v>4.489142894744873</v>
+        <v>4.489142417907715</v>
       </c>
       <c r="C219" t="n">
-        <v>4.596027148257782</v>
+        <v>4.596026660067369</v>
       </c>
       <c r="D219" t="n">
-        <v>4.44460757675436</v>
+        <v>4.444607104647747</v>
       </c>
       <c r="E219" t="n">
-        <v>4.560399063753479</v>
+        <v>4.560398579347484</v>
       </c>
       <c r="F219" t="n">
         <v>7411800</v>
@@ -4812,16 +4812,16 @@
         <v>44734</v>
       </c>
       <c r="B220" t="n">
-        <v>4.444607257843018</v>
+        <v>4.444606781005859</v>
       </c>
       <c r="C220" t="n">
-        <v>4.533677887433011</v>
+        <v>4.53367740103996</v>
       </c>
       <c r="D220" t="n">
-        <v>4.40007236776826</v>
+        <v>4.400071895709002</v>
       </c>
       <c r="E220" t="n">
-        <v>4.480235764511158</v>
+        <v>4.480235283851616</v>
       </c>
       <c r="F220" t="n">
         <v>8433900</v>
@@ -4832,16 +4832,16 @@
         <v>44735</v>
       </c>
       <c r="B221" t="n">
-        <v>4.266467571258545</v>
+        <v>4.266466617584229</v>
       </c>
       <c r="C221" t="n">
-        <v>4.515864611886239</v>
+        <v>4.515863602464738</v>
       </c>
       <c r="D221" t="n">
-        <v>4.266467571258545</v>
+        <v>4.266466617584229</v>
       </c>
       <c r="E221" t="n">
-        <v>4.471329289542623</v>
+        <v>4.471328290076007</v>
       </c>
       <c r="F221" t="n">
         <v>8059200</v>
@@ -4872,16 +4872,16 @@
         <v>44739</v>
       </c>
       <c r="B223" t="n">
-        <v>4.275373935699463</v>
+        <v>4.275373458862305</v>
       </c>
       <c r="C223" t="n">
-        <v>4.337722864629935</v>
+        <v>4.337722380838932</v>
       </c>
       <c r="D223" t="n">
-        <v>4.239745854961986</v>
+        <v>4.239745382098467</v>
       </c>
       <c r="E223" t="n">
-        <v>4.275373935699463</v>
+        <v>4.275373458862305</v>
       </c>
       <c r="F223" t="n">
         <v>10516900</v>
@@ -4892,16 +4892,16 @@
         <v>44740</v>
       </c>
       <c r="B224" t="n">
-        <v>4.293188095092773</v>
+        <v>4.293188571929932</v>
       </c>
       <c r="C224" t="n">
-        <v>4.471328503718931</v>
+        <v>4.471329000341845</v>
       </c>
       <c r="D224" t="n">
-        <v>4.293188095092773</v>
+        <v>4.293188571929932</v>
       </c>
       <c r="E224" t="n">
-        <v>4.319908944026579</v>
+        <v>4.319909423831577</v>
       </c>
       <c r="F224" t="n">
         <v>8975600</v>
@@ -4912,16 +4912,16 @@
         <v>44741</v>
       </c>
       <c r="B225" t="n">
-        <v>4.275373935699463</v>
+        <v>4.275373458862305</v>
       </c>
       <c r="C225" t="n">
-        <v>4.355536904998673</v>
+        <v>4.355536419220851</v>
       </c>
       <c r="D225" t="n">
-        <v>4.248652662786244</v>
+        <v>4.248652188929338</v>
       </c>
       <c r="E225" t="n">
-        <v>4.31100201643694</v>
+        <v>4.311001535626143</v>
       </c>
       <c r="F225" t="n">
         <v>7179800</v>
@@ -4932,16 +4932,16 @@
         <v>44742</v>
       </c>
       <c r="B226" t="n">
-        <v>4.088326930999756</v>
+        <v>4.088326454162598</v>
       </c>
       <c r="C226" t="n">
-        <v>4.239746509884235</v>
+        <v>4.239746015386434</v>
       </c>
       <c r="D226" t="n">
-        <v>4.052698844758736</v>
+        <v>4.052698372077018</v>
       </c>
       <c r="E226" t="n">
-        <v>4.239746509884235</v>
+        <v>4.239746015386434</v>
       </c>
       <c r="F226" t="n">
         <v>6721700</v>
@@ -4972,16 +4972,16 @@
         <v>44746</v>
       </c>
       <c r="B228" t="n">
-        <v>4.043790817260742</v>
+        <v>4.0437912940979</v>
       </c>
       <c r="C228" t="n">
-        <v>4.195210366429746</v>
+        <v>4.195210861122049</v>
       </c>
       <c r="D228" t="n">
-        <v>4.008162738011589</v>
+        <v>4.008163210647543</v>
       </c>
       <c r="E228" t="n">
-        <v>4.034884009808557</v>
+        <v>4.034884485595439</v>
       </c>
       <c r="F228" t="n">
         <v>5003300</v>
@@ -5012,16 +5012,16 @@
         <v>44748</v>
       </c>
       <c r="B230" t="n">
-        <v>3.910185813903809</v>
+        <v>3.910185575485229</v>
       </c>
       <c r="C230" t="n">
-        <v>4.052698574069413</v>
+        <v>4.0526983269613</v>
       </c>
       <c r="D230" t="n">
-        <v>3.785487520389134</v>
+        <v>3.785487289573874</v>
       </c>
       <c r="E230" t="n">
-        <v>4.034884532138745</v>
+        <v>4.034884286116821</v>
       </c>
       <c r="F230" t="n">
         <v>11922900</v>
@@ -5032,16 +5032,16 @@
         <v>44749</v>
       </c>
       <c r="B231" t="n">
-        <v>4.052698612213135</v>
+        <v>4.052698135375977</v>
       </c>
       <c r="C231" t="n">
-        <v>4.141768822704797</v>
+        <v>4.141768335387711</v>
       </c>
       <c r="D231" t="n">
-        <v>3.927999892804543</v>
+        <v>3.927999430639332</v>
       </c>
       <c r="E231" t="n">
-        <v>3.927999892804543</v>
+        <v>3.927999430639332</v>
       </c>
       <c r="F231" t="n">
         <v>10027800</v>
@@ -5052,16 +5052,16 @@
         <v>44750</v>
       </c>
       <c r="B232" t="n">
-        <v>3.919092655181885</v>
+        <v>3.919093132019043</v>
       </c>
       <c r="C232" t="n">
-        <v>4.132861136965516</v>
+        <v>4.132861639811949</v>
       </c>
       <c r="D232" t="n">
-        <v>3.919092655181885</v>
+        <v>3.919093132019043</v>
       </c>
       <c r="E232" t="n">
-        <v>4.034884128508128</v>
+        <v>4.03488461943367</v>
       </c>
       <c r="F232" t="n">
         <v>7050900</v>
@@ -5072,16 +5072,16 @@
         <v>44753</v>
       </c>
       <c r="B233" t="n">
-        <v>3.705323457717896</v>
+        <v>3.705323934555054</v>
       </c>
       <c r="C233" t="n">
-        <v>3.901278308685776</v>
+        <v>3.901278810740315</v>
       </c>
       <c r="D233" t="n">
-        <v>3.678602611953303</v>
+        <v>3.678603085351762</v>
       </c>
       <c r="E233" t="n">
-        <v>3.892371076950788</v>
+        <v>3.892371577859058</v>
       </c>
       <c r="F233" t="n">
         <v>13261200</v>
@@ -5112,16 +5112,16 @@
         <v>44755</v>
       </c>
       <c r="B235" t="n">
-        <v>3.687509775161743</v>
+        <v>3.687510251998901</v>
       </c>
       <c r="C235" t="n">
-        <v>3.723137856102805</v>
+        <v>3.723138337547081</v>
       </c>
       <c r="D235" t="n">
-        <v>3.47374128951537</v>
+        <v>3.47374173870982</v>
       </c>
       <c r="E235" t="n">
-        <v>3.589532764933936</v>
+        <v>3.589533229101546</v>
       </c>
       <c r="F235" t="n">
         <v>14925600</v>
@@ -5132,16 +5132,16 @@
         <v>44756</v>
       </c>
       <c r="B236" t="n">
-        <v>3.821115732192993</v>
+        <v>3.821115493774414</v>
       </c>
       <c r="C236" t="n">
-        <v>3.856743817247265</v>
+        <v>3.856743576605671</v>
       </c>
       <c r="D236" t="n">
-        <v>3.651882115825064</v>
+        <v>3.651881887965819</v>
       </c>
       <c r="E236" t="n">
-        <v>3.687510200879336</v>
+        <v>3.687509970797076</v>
       </c>
       <c r="F236" t="n">
         <v>9774500</v>
@@ -5172,16 +5172,16 @@
         <v>44760</v>
       </c>
       <c r="B238" t="n">
-        <v>3.830022811889648</v>
+        <v>3.83002233505249</v>
       </c>
       <c r="C238" t="n">
-        <v>4.088326630512132</v>
+        <v>4.088326121516194</v>
       </c>
       <c r="D238" t="n">
-        <v>3.830022811889648</v>
+        <v>3.83002233505249</v>
       </c>
       <c r="E238" t="n">
-        <v>3.99034918819042</v>
+        <v>3.990348691392656</v>
       </c>
       <c r="F238" t="n">
         <v>5011900</v>
@@ -5232,16 +5232,16 @@
         <v>44763</v>
       </c>
       <c r="B241" t="n">
-        <v>3.963627576828003</v>
+        <v>3.963627338409424</v>
       </c>
       <c r="C241" t="n">
-        <v>4.025976930237424</v>
+        <v>4.025976688068431</v>
       </c>
       <c r="D241" t="n">
-        <v>3.93690672873841</v>
+        <v>3.936906491927133</v>
       </c>
       <c r="E241" t="n">
-        <v>4.025976930237424</v>
+        <v>4.025976688068431</v>
       </c>
       <c r="F241" t="n">
         <v>6658500</v>
@@ -5252,16 +5252,16 @@
         <v>44764</v>
       </c>
       <c r="B242" t="n">
-        <v>3.740952014923096</v>
+        <v>3.740951538085938</v>
       </c>
       <c r="C242" t="n">
-        <v>3.999255822277678</v>
+        <v>3.999255312516052</v>
       </c>
       <c r="D242" t="n">
-        <v>3.740952014923096</v>
+        <v>3.740951538085938</v>
       </c>
       <c r="E242" t="n">
-        <v>3.999255822277678</v>
+        <v>3.999255312516052</v>
       </c>
       <c r="F242" t="n">
         <v>6536400</v>
@@ -5272,16 +5272,16 @@
         <v>44767</v>
       </c>
       <c r="B243" t="n">
-        <v>3.696417331695557</v>
+        <v>3.696417570114136</v>
       </c>
       <c r="C243" t="n">
-        <v>3.78548754185395</v>
+        <v>3.78548778601755</v>
       </c>
       <c r="D243" t="n">
-        <v>3.651882014256228</v>
+        <v>3.651882249802283</v>
       </c>
       <c r="E243" t="n">
-        <v>3.767673499822271</v>
+        <v>3.767673742836867</v>
       </c>
       <c r="F243" t="n">
         <v>10514300</v>
@@ -5392,16 +5392,16 @@
         <v>44775</v>
       </c>
       <c r="B249" t="n">
-        <v>4.10614013671875</v>
+        <v>4.106140613555908</v>
       </c>
       <c r="C249" t="n">
-        <v>4.115046944102415</v>
+        <v>4.115047421973903</v>
       </c>
       <c r="D249" t="n">
-        <v>3.901278470251996</v>
+        <v>3.901278923299012</v>
       </c>
       <c r="E249" t="n">
-        <v>3.927999317123196</v>
+        <v>3.927999773273247</v>
       </c>
       <c r="F249" t="n">
         <v>12885400</v>
@@ -5412,16 +5412,16 @@
         <v>44776</v>
       </c>
       <c r="B250" t="n">
-        <v>4.284280776977539</v>
+        <v>4.284281253814697</v>
       </c>
       <c r="C250" t="n">
-        <v>4.373350979516736</v>
+        <v>4.37335146626734</v>
       </c>
       <c r="D250" t="n">
-        <v>4.123954412406984</v>
+        <v>4.123954871399942</v>
       </c>
       <c r="E250" t="n">
-        <v>4.123954412406984</v>
+        <v>4.123954871399942</v>
       </c>
       <c r="F250" t="n">
         <v>8750200</v>
@@ -5432,16 +5432,16 @@
         <v>44777</v>
       </c>
       <c r="B251" t="n">
-        <v>4.498050212860107</v>
+        <v>4.498049259185791</v>
       </c>
       <c r="C251" t="n">
-        <v>4.791982127910954</v>
+        <v>4.791981111917343</v>
       </c>
       <c r="D251" t="n">
-        <v>4.32881659592047</v>
+        <v>4.328815678126979</v>
       </c>
       <c r="E251" t="n">
-        <v>4.32881659592047</v>
+        <v>4.328815678126979</v>
       </c>
       <c r="F251" t="n">
         <v>17206200</v>
@@ -5512,16 +5512,16 @@
         <v>44783</v>
       </c>
       <c r="B255" t="n">
-        <v>4.587120056152344</v>
+        <v>4.587120532989502</v>
       </c>
       <c r="C255" t="n">
-        <v>4.702911535999198</v>
+        <v>4.702912024873032</v>
       </c>
       <c r="D255" t="n">
-        <v>4.426793261065856</v>
+        <v>4.426793721236833</v>
       </c>
       <c r="E255" t="n">
-        <v>4.426793261065856</v>
+        <v>4.426793721236833</v>
       </c>
       <c r="F255" t="n">
         <v>9044400</v>
@@ -5532,16 +5532,16 @@
         <v>44784</v>
       </c>
       <c r="B256" t="n">
-        <v>4.346630096435547</v>
+        <v>4.346629619598389</v>
       </c>
       <c r="C256" t="n">
-        <v>4.685097288104267</v>
+        <v>4.685096774136335</v>
       </c>
       <c r="D256" t="n">
-        <v>4.311002015704126</v>
+        <v>4.311001542775466</v>
       </c>
       <c r="E256" t="n">
-        <v>4.613840701921201</v>
+        <v>4.613840195770312</v>
       </c>
       <c r="F256" t="n">
         <v>11482900</v>
@@ -5592,16 +5592,16 @@
         <v>44789</v>
       </c>
       <c r="B259" t="n">
-        <v>4.622747898101807</v>
+        <v>4.622747421264648</v>
       </c>
       <c r="C259" t="n">
-        <v>4.702911291477053</v>
+        <v>4.702910806371028</v>
       </c>
       <c r="D259" t="n">
-        <v>4.560398544952146</v>
+        <v>4.560398074546333</v>
       </c>
       <c r="E259" t="n">
-        <v>4.676190018778564</v>
+        <v>4.676189536428843</v>
       </c>
       <c r="F259" t="n">
         <v>5754000</v>
@@ -5612,16 +5612,16 @@
         <v>44790</v>
       </c>
       <c r="B260" t="n">
-        <v>4.702910900115967</v>
+        <v>4.702911376953125</v>
       </c>
       <c r="C260" t="n">
-        <v>4.774167055088602</v>
+        <v>4.774167539150558</v>
       </c>
       <c r="D260" t="n">
-        <v>4.560398165450511</v>
+        <v>4.560398627838029</v>
       </c>
       <c r="E260" t="n">
-        <v>4.596026242936828</v>
+        <v>4.596026708936746</v>
       </c>
       <c r="F260" t="n">
         <v>27272900</v>
@@ -5652,16 +5652,16 @@
         <v>44792</v>
       </c>
       <c r="B262" t="n">
-        <v>4.31990909576416</v>
+        <v>4.319908618927002</v>
       </c>
       <c r="C262" t="n">
-        <v>4.533678018344458</v>
+        <v>4.533677517911209</v>
       </c>
       <c r="D262" t="n">
-        <v>4.22193165521818</v>
+        <v>4.221931189195899</v>
       </c>
       <c r="E262" t="n">
-        <v>4.524770785240164</v>
+        <v>4.524770285790107</v>
       </c>
       <c r="F262" t="n">
         <v>17743000</v>
@@ -5672,16 +5672,16 @@
         <v>44795</v>
       </c>
       <c r="B263" t="n">
-        <v>4.31990909576416</v>
+        <v>4.319908618927002</v>
       </c>
       <c r="C263" t="n">
-        <v>4.364444411845128</v>
+        <v>4.364443930092105</v>
       </c>
       <c r="D263" t="n">
-        <v>4.177396763857463</v>
+        <v>4.177396302751</v>
       </c>
       <c r="E263" t="n">
-        <v>4.302095054275823</v>
+        <v>4.302094579405002</v>
       </c>
       <c r="F263" t="n">
         <v>9829500</v>
@@ -5692,16 +5692,16 @@
         <v>44796</v>
       </c>
       <c r="B264" t="n">
-        <v>4.471328258514404</v>
+        <v>4.471328735351562</v>
       </c>
       <c r="C264" t="n">
-        <v>4.471328258514404</v>
+        <v>4.471328735351562</v>
       </c>
       <c r="D264" t="n">
-        <v>4.311001899543048</v>
+        <v>4.311002359282476</v>
       </c>
       <c r="E264" t="n">
-        <v>4.311001899543048</v>
+        <v>4.311002359282476</v>
       </c>
       <c r="F264" t="n">
         <v>6333000</v>
@@ -5732,16 +5732,16 @@
         <v>44798</v>
       </c>
       <c r="B266" t="n">
-        <v>4.48023509979248</v>
+        <v>4.480236053466797</v>
       </c>
       <c r="C266" t="n">
-        <v>4.604933368109039</v>
+        <v>4.604934348326948</v>
       </c>
       <c r="D266" t="n">
-        <v>4.453513829935988</v>
+        <v>4.453514777922345</v>
       </c>
       <c r="E266" t="n">
-        <v>4.587119329778102</v>
+        <v>4.587120306204069</v>
       </c>
       <c r="F266" t="n">
         <v>4135100</v>
@@ -5752,16 +5752,16 @@
         <v>44799</v>
       </c>
       <c r="B267" t="n">
-        <v>4.31990909576416</v>
+        <v>4.319908618927002</v>
       </c>
       <c r="C267" t="n">
-        <v>4.524770785240164</v>
+        <v>4.524770285790107</v>
       </c>
       <c r="D267" t="n">
-        <v>4.29318824589178</v>
+        <v>4.293187772004104</v>
       </c>
       <c r="E267" t="n">
-        <v>4.489142702263489</v>
+        <v>4.489142206746107</v>
       </c>
       <c r="F267" t="n">
         <v>6692300</v>
@@ -5792,16 +5792,16 @@
         <v>44803</v>
       </c>
       <c r="B269" t="n">
-        <v>4.364443778991699</v>
+        <v>4.364444732666016</v>
       </c>
       <c r="C269" t="n">
-        <v>4.480235244236013</v>
+        <v>4.480236223211915</v>
       </c>
       <c r="D269" t="n">
-        <v>4.337722508273708</v>
+        <v>4.337723456109162</v>
       </c>
       <c r="E269" t="n">
-        <v>4.471328012423286</v>
+        <v>4.47132898945287</v>
       </c>
       <c r="F269" t="n">
         <v>7827400</v>
@@ -5852,16 +5852,16 @@
         <v>44806</v>
       </c>
       <c r="B272" t="n">
-        <v>4.097232818603516</v>
+        <v>4.097232341766357</v>
       </c>
       <c r="C272" t="n">
-        <v>4.35553659811042</v>
+        <v>4.355536091211792</v>
       </c>
       <c r="D272" t="n">
-        <v>4.097232818603516</v>
+        <v>4.097232341766357</v>
       </c>
       <c r="E272" t="n">
-        <v>4.319908519883274</v>
+        <v>4.319908017131052</v>
       </c>
       <c r="F272" t="n">
         <v>69570300</v>
@@ -5872,16 +5872,16 @@
         <v>44809</v>
       </c>
       <c r="B273" t="n">
-        <v>4.115046977996826</v>
+        <v>4.115047454833984</v>
       </c>
       <c r="C273" t="n">
-        <v>4.221931215802409</v>
+        <v>4.221931705024937</v>
       </c>
       <c r="D273" t="n">
-        <v>4.115046977996826</v>
+        <v>4.115047454833984</v>
       </c>
       <c r="E273" t="n">
-        <v>4.123954210174062</v>
+        <v>4.123954688043359</v>
       </c>
       <c r="F273" t="n">
         <v>7604300</v>
@@ -5892,16 +5892,16 @@
         <v>44810</v>
       </c>
       <c r="B274" t="n">
-        <v>3.954720973968506</v>
+        <v>3.954720735549927</v>
       </c>
       <c r="C274" t="n">
-        <v>4.177396701615019</v>
+        <v>4.177396449771971</v>
       </c>
       <c r="D274" t="n">
-        <v>3.945813740996928</v>
+        <v>3.94581350311534</v>
       </c>
       <c r="E274" t="n">
-        <v>4.141768619169197</v>
+        <v>4.141768369474061</v>
       </c>
       <c r="F274" t="n">
         <v>14609100</v>
@@ -5912,16 +5912,16 @@
         <v>44812</v>
       </c>
       <c r="B275" t="n">
-        <v>3.910185813903809</v>
+        <v>3.910185575485229</v>
       </c>
       <c r="C275" t="n">
-        <v>4.008163256882613</v>
+        <v>4.008163012489984</v>
       </c>
       <c r="D275" t="n">
-        <v>3.856743688111805</v>
+        <v>3.856743452951791</v>
       </c>
       <c r="E275" t="n">
-        <v>3.990349214951944</v>
+        <v>3.990348971645505</v>
       </c>
       <c r="F275" t="n">
         <v>9864000</v>
@@ -5932,16 +5932,16 @@
         <v>44813</v>
       </c>
       <c r="B276" t="n">
-        <v>3.910185813903809</v>
+        <v>3.910185575485229</v>
       </c>
       <c r="C276" t="n">
-        <v>4.043791340743948</v>
+        <v>4.043791094178943</v>
       </c>
       <c r="D276" t="n">
-        <v>3.883464963367938</v>
+        <v>3.883464726578628</v>
       </c>
       <c r="E276" t="n">
-        <v>3.945813897765144</v>
+        <v>3.945813657174188</v>
       </c>
       <c r="F276" t="n">
         <v>15548300</v>
@@ -5972,16 +5972,16 @@
         <v>44817</v>
       </c>
       <c r="B278" t="n">
-        <v>3.696417331695557</v>
+        <v>3.696417570114136</v>
       </c>
       <c r="C278" t="n">
-        <v>3.883464985388314</v>
+        <v>3.88346523587145</v>
       </c>
       <c r="D278" t="n">
-        <v>3.678603289663878</v>
+        <v>3.678603526933453</v>
       </c>
       <c r="E278" t="n">
-        <v>3.874557752012343</v>
+        <v>3.874558001920963</v>
       </c>
       <c r="F278" t="n">
         <v>21443000</v>
@@ -5992,16 +5992,16 @@
         <v>44818</v>
       </c>
       <c r="B279" t="n">
-        <v>3.740952014923096</v>
+        <v>3.740951538085938</v>
       </c>
       <c r="C279" t="n">
-        <v>3.821115411936669</v>
+        <v>3.821114924881555</v>
       </c>
       <c r="D279" t="n">
-        <v>3.678603083663863</v>
+        <v>3.678602614773957</v>
       </c>
       <c r="E279" t="n">
-        <v>3.705323932854894</v>
+        <v>3.705323460559038</v>
       </c>
       <c r="F279" t="n">
         <v>13539100</v>
@@ -6032,16 +6032,16 @@
         <v>44820</v>
       </c>
       <c r="B281" t="n">
-        <v>3.821115732192993</v>
+        <v>3.821115493774414</v>
       </c>
       <c r="C281" t="n">
-        <v>3.892371902301537</v>
+        <v>3.892371659436928</v>
       </c>
       <c r="D281" t="n">
-        <v>3.66078934944877</v>
+        <v>3.660789121033758</v>
       </c>
       <c r="E281" t="n">
-        <v>3.696417434503042</v>
+        <v>3.696417203865015</v>
       </c>
       <c r="F281" t="n">
         <v>19813000</v>
@@ -6052,16 +6052,16 @@
         <v>44823</v>
       </c>
       <c r="B282" t="n">
-        <v>3.990348339080811</v>
+        <v>3.990349054336548</v>
       </c>
       <c r="C282" t="n">
-        <v>4.008162377101343</v>
+        <v>4.008163095550183</v>
       </c>
       <c r="D282" t="n">
-        <v>3.794393920854952</v>
+        <v>3.794394600986558</v>
       </c>
       <c r="E282" t="n">
-        <v>3.830021996896017</v>
+        <v>3.830022683413829</v>
       </c>
       <c r="F282" t="n">
         <v>8945000</v>
@@ -6072,16 +6072,16 @@
         <v>44824</v>
       </c>
       <c r="B283" t="n">
-        <v>3.963627576828003</v>
+        <v>3.963627338409424</v>
       </c>
       <c r="C283" t="n">
-        <v>4.13286117203624</v>
+        <v>4.132860923437988</v>
       </c>
       <c r="D283" t="n">
-        <v>3.919092688438607</v>
+        <v>3.919092452698874</v>
       </c>
       <c r="E283" t="n">
-        <v>3.990348849637818</v>
+        <v>3.990348609611912</v>
       </c>
       <c r="F283" t="n">
         <v>10696200</v>
@@ -6092,16 +6092,16 @@
         <v>44825</v>
       </c>
       <c r="B284" t="n">
-        <v>3.883465051651001</v>
+        <v>3.883464813232422</v>
       </c>
       <c r="C284" t="n">
-        <v>4.034884623864039</v>
+        <v>4.034884376149319</v>
       </c>
       <c r="D284" t="n">
-        <v>3.830022924644094</v>
+        <v>3.830022689506502</v>
       </c>
       <c r="E284" t="n">
-        <v>3.972535263329179</v>
+        <v>3.972535019442289</v>
       </c>
       <c r="F284" t="n">
         <v>18275700</v>
@@ -6112,16 +6112,16 @@
         <v>44826</v>
       </c>
       <c r="B285" t="n">
-        <v>4.052698612213135</v>
+        <v>4.052698135375977</v>
       </c>
       <c r="C285" t="n">
-        <v>4.097233505098832</v>
+        <v>4.097233023021737</v>
       </c>
       <c r="D285" t="n">
-        <v>3.901279042017177</v>
+        <v>3.90127858299592</v>
       </c>
       <c r="E285" t="n">
-        <v>3.936907126213841</v>
+        <v>3.936906663000614</v>
       </c>
       <c r="F285" t="n">
         <v>13589200</v>
@@ -6132,16 +6132,16 @@
         <v>44827</v>
       </c>
       <c r="B286" t="n">
-        <v>3.910185813903809</v>
+        <v>3.910185575485229</v>
       </c>
       <c r="C286" t="n">
-        <v>3.990349214951944</v>
+        <v>3.990348971645505</v>
       </c>
       <c r="D286" t="n">
-        <v>3.847836879506602</v>
+        <v>3.847836644889669</v>
       </c>
       <c r="E286" t="n">
-        <v>3.963627939695812</v>
+        <v>3.963627698018668</v>
       </c>
       <c r="F286" t="n">
         <v>14173200</v>
@@ -6152,16 +6152,16 @@
         <v>44830</v>
       </c>
       <c r="B287" t="n">
-        <v>3.821115732192993</v>
+        <v>3.821115493774414</v>
       </c>
       <c r="C287" t="n">
-        <v>3.936907220979514</v>
+        <v>3.936906975336123</v>
       </c>
       <c r="D287" t="n">
-        <v>3.794394880762427</v>
+        <v>3.794394644011096</v>
       </c>
       <c r="E287" t="n">
-        <v>3.901279135925243</v>
+        <v>3.901278892504866</v>
       </c>
       <c r="F287" t="n">
         <v>9718800</v>
@@ -6172,16 +6172,16 @@
         <v>44831</v>
       </c>
       <c r="B288" t="n">
-        <v>3.73204517364502</v>
+        <v>3.732044696807861</v>
       </c>
       <c r="C288" t="n">
-        <v>3.919092815203188</v>
+        <v>3.919092314467266</v>
       </c>
       <c r="D288" t="n">
-        <v>3.73204517364502</v>
+        <v>3.732044696807861</v>
       </c>
       <c r="E288" t="n">
-        <v>3.838929418901048</v>
+        <v>3.838928928407469</v>
       </c>
       <c r="F288" t="n">
         <v>11052300</v>
@@ -6192,16 +6192,16 @@
         <v>44832</v>
       </c>
       <c r="B289" t="n">
-        <v>3.687509775161743</v>
+        <v>3.687510251998901</v>
       </c>
       <c r="C289" t="n">
-        <v>3.767673169639246</v>
+        <v>3.767673656842447</v>
       </c>
       <c r="D289" t="n">
-        <v>3.687509775161743</v>
+        <v>3.687510251998901</v>
       </c>
       <c r="E289" t="n">
-        <v>3.749859129168715</v>
+        <v>3.749859614068357</v>
       </c>
       <c r="F289" t="n">
         <v>11148900</v>
@@ -6212,16 +6212,16 @@
         <v>44833</v>
       </c>
       <c r="B290" t="n">
-        <v>3.696417331695557</v>
+        <v>3.696417570114136</v>
       </c>
       <c r="C290" t="n">
-        <v>3.714231373727235</v>
+        <v>3.714231613294819</v>
       </c>
       <c r="D290" t="n">
-        <v>3.616253930192871</v>
+        <v>3.616254163440918</v>
       </c>
       <c r="E290" t="n">
-        <v>3.660789247632199</v>
+        <v>3.660789483752771</v>
       </c>
       <c r="F290" t="n">
         <v>12380300</v>
@@ -6232,16 +6232,16 @@
         <v>44834</v>
       </c>
       <c r="B291" t="n">
-        <v>3.73204517364502</v>
+        <v>3.732044696807861</v>
       </c>
       <c r="C291" t="n">
-        <v>3.794394529071154</v>
+        <v>3.794394044267724</v>
       </c>
       <c r="D291" t="n">
-        <v>3.651881777342879</v>
+        <v>3.651881310748065</v>
       </c>
       <c r="E291" t="n">
-        <v>3.660789010141</v>
+        <v>3.660788542408123</v>
       </c>
       <c r="F291" t="n">
         <v>11827700</v>
@@ -6252,16 +6252,16 @@
         <v>44837</v>
       </c>
       <c r="B292" t="n">
-        <v>3.939894914627075</v>
+        <v>3.939895391464233</v>
       </c>
       <c r="C292" t="n">
-        <v>3.939894914627075</v>
+        <v>3.939895391464233</v>
       </c>
       <c r="D292" t="n">
-        <v>3.796299788355527</v>
+        <v>3.79630024781367</v>
       </c>
       <c r="E292" t="n">
-        <v>3.814249179139471</v>
+        <v>3.814249640769991</v>
       </c>
       <c r="F292" t="n">
         <v>14167700</v>
@@ -6292,16 +6292,16 @@
         <v>44839</v>
       </c>
       <c r="B294" t="n">
-        <v>3.97579288482666</v>
+        <v>3.975793361663818</v>
       </c>
       <c r="C294" t="n">
-        <v>3.97579288482666</v>
+        <v>3.975793361663818</v>
       </c>
       <c r="D294" t="n">
-        <v>3.868096562101353</v>
+        <v>3.868097026021941</v>
       </c>
       <c r="E294" t="n">
-        <v>3.921944723464007</v>
+        <v>3.92194519384288</v>
       </c>
       <c r="F294" t="n">
         <v>8368900</v>
@@ -6332,16 +6332,16 @@
         <v>44841</v>
       </c>
       <c r="B296" t="n">
-        <v>3.760400772094727</v>
+        <v>3.760400533676147</v>
       </c>
       <c r="C296" t="n">
-        <v>4.002717746528172</v>
+        <v>4.002717492746105</v>
       </c>
       <c r="D296" t="n">
-        <v>3.715527083961894</v>
+        <v>3.715526848388416</v>
       </c>
       <c r="E296" t="n">
-        <v>3.98476835686448</v>
+        <v>3.984768104220449</v>
       </c>
       <c r="F296" t="n">
         <v>16354500</v>
@@ -6372,16 +6372,16 @@
         <v>44845</v>
       </c>
       <c r="B298" t="n">
-        <v>3.903995990753174</v>
+        <v>3.903995513916016</v>
       </c>
       <c r="C298" t="n">
-        <v>3.948869680050941</v>
+        <v>3.948869197732875</v>
       </c>
       <c r="D298" t="n">
-        <v>3.63475513880822</v>
+        <v>3.634754694856352</v>
       </c>
       <c r="E298" t="n">
-        <v>3.661679010029107</v>
+        <v>3.661678562788736</v>
       </c>
       <c r="F298" t="n">
         <v>30833900</v>
@@ -6392,16 +6392,16 @@
         <v>44847</v>
       </c>
       <c r="B299" t="n">
-        <v>3.81424880027771</v>
+        <v>3.814249038696289</v>
       </c>
       <c r="C299" t="n">
-        <v>3.903995745283042</v>
+        <v>3.903995989311464</v>
       </c>
       <c r="D299" t="n">
-        <v>3.796299411276644</v>
+        <v>3.796299648573254</v>
       </c>
       <c r="E299" t="n">
-        <v>3.895021264756104</v>
+        <v>3.895021508223556</v>
       </c>
       <c r="F299" t="n">
         <v>15027200</v>
@@ -6432,16 +6432,16 @@
         <v>44851</v>
       </c>
       <c r="B301" t="n">
-        <v>3.679628372192383</v>
+        <v>3.679628133773804</v>
       </c>
       <c r="C301" t="n">
-        <v>3.769375322158595</v>
+        <v>3.769375077924933</v>
       </c>
       <c r="D301" t="n">
-        <v>3.670653891169369</v>
+        <v>3.670653653332284</v>
       </c>
       <c r="E301" t="n">
-        <v>3.724502061149096</v>
+        <v>3.724501819822962</v>
       </c>
       <c r="F301" t="n">
         <v>8129100</v>
@@ -6452,16 +6452,16 @@
         <v>44852</v>
       </c>
       <c r="B302" t="n">
-        <v>3.715527057647705</v>
+        <v>3.715527534484863</v>
       </c>
       <c r="C302" t="n">
-        <v>3.787324615793987</v>
+        <v>3.787325101845382</v>
       </c>
       <c r="D302" t="n">
-        <v>3.661678889037994</v>
+        <v>3.661679358964475</v>
       </c>
       <c r="E302" t="n">
-        <v>3.724501966389592</v>
+        <v>3.724502444378557</v>
       </c>
       <c r="F302" t="n">
         <v>13196400</v>
@@ -6472,16 +6472,16 @@
         <v>44853</v>
       </c>
       <c r="B303" t="n">
-        <v>3.733476161956787</v>
+        <v>3.733476400375366</v>
       </c>
       <c r="C303" t="n">
-        <v>3.769374938287358</v>
+        <v>3.769375178998422</v>
       </c>
       <c r="D303" t="n">
-        <v>3.670653517351873</v>
+        <v>3.670653751758618</v>
       </c>
       <c r="E303" t="n">
-        <v>3.715526773791502</v>
+        <v>3.715527011063839</v>
       </c>
       <c r="F303" t="n">
         <v>12625300</v>
@@ -6492,16 +6492,16 @@
         <v>44854</v>
       </c>
       <c r="B304" t="n">
-        <v>3.769375324249268</v>
+        <v>3.769374847412109</v>
       </c>
       <c r="C304" t="n">
-        <v>3.796299623227672</v>
+        <v>3.796299142984509</v>
       </c>
       <c r="D304" t="n">
-        <v>3.706552673211682</v>
+        <v>3.706552204321775</v>
       </c>
       <c r="E304" t="n">
-        <v>3.760400843221276</v>
+        <v>3.760400367519416</v>
       </c>
       <c r="F304" t="n">
         <v>13428400</v>
@@ -6512,16 +6512,16 @@
         <v>44855</v>
       </c>
       <c r="B305" t="n">
-        <v>3.83219838142395</v>
+        <v>3.832198143005371</v>
       </c>
       <c r="C305" t="n">
-        <v>3.85912268024912</v>
+        <v>3.859122440155458</v>
       </c>
       <c r="D305" t="n">
-        <v>3.733476522994609</v>
+        <v>3.733476290717968</v>
       </c>
       <c r="E305" t="n">
-        <v>3.760400821819779</v>
+        <v>3.760400587868054</v>
       </c>
       <c r="F305" t="n">
         <v>14614900</v>
@@ -6532,16 +6532,16 @@
         <v>44858</v>
       </c>
       <c r="B306" t="n">
-        <v>3.706552505493164</v>
+        <v>3.706552982330322</v>
       </c>
       <c r="C306" t="n">
-        <v>3.778350062257174</v>
+        <v>3.778350548330878</v>
       </c>
       <c r="D306" t="n">
-        <v>3.697577596924065</v>
+        <v>3.697578072606628</v>
       </c>
       <c r="E306" t="n">
-        <v>3.769375153688075</v>
+        <v>3.769375638607184</v>
       </c>
       <c r="F306" t="n">
         <v>9021900</v>
@@ -6572,16 +6572,16 @@
         <v>44860</v>
       </c>
       <c r="B308" t="n">
-        <v>3.562957048416138</v>
+        <v>3.562957286834717</v>
       </c>
       <c r="C308" t="n">
-        <v>3.670653593619109</v>
+        <v>3.670653839244302</v>
       </c>
       <c r="D308" t="n">
-        <v>3.545007659877907</v>
+        <v>3.545007897095387</v>
       </c>
       <c r="E308" t="n">
-        <v>3.661678685376404</v>
+        <v>3.661678930401033</v>
       </c>
       <c r="F308" t="n">
         <v>15630800</v>
@@ -6592,16 +6592,16 @@
         <v>44861</v>
       </c>
       <c r="B309" t="n">
-        <v>3.706552505493164</v>
+        <v>3.706552982330322</v>
       </c>
       <c r="C309" t="n">
-        <v>3.760400673066171</v>
+        <v>3.760401156830739</v>
       </c>
       <c r="D309" t="n">
-        <v>3.580906567182549</v>
+        <v>3.580907027855725</v>
       </c>
       <c r="E309" t="n">
-        <v>3.580906567182549</v>
+        <v>3.580907027855725</v>
       </c>
       <c r="F309" t="n">
         <v>15175200</v>
@@ -6612,16 +6612,16 @@
         <v>44862</v>
       </c>
       <c r="B310" t="n">
-        <v>3.724502325057983</v>
+        <v>3.724502086639404</v>
       </c>
       <c r="C310" t="n">
-        <v>3.733476806716907</v>
+        <v>3.73347656772384</v>
       </c>
       <c r="D310" t="n">
-        <v>3.643729850391451</v>
+        <v>3.643729617143404</v>
       </c>
       <c r="E310" t="n">
-        <v>3.688603542527801</v>
+        <v>3.68860330640723</v>
       </c>
       <c r="F310" t="n">
         <v>9985100</v>
@@ -6632,16 +6632,16 @@
         <v>44865</v>
       </c>
       <c r="B311" t="n">
-        <v>3.85014820098877</v>
+        <v>3.85014796257019</v>
       </c>
       <c r="C311" t="n">
-        <v>3.868097592892905</v>
+        <v>3.868097353362819</v>
       </c>
       <c r="D311" t="n">
-        <v>3.545008324644836</v>
+        <v>3.545008105121898</v>
       </c>
       <c r="E311" t="n">
-        <v>3.589881804405175</v>
+        <v>3.589881582103468</v>
       </c>
       <c r="F311" t="n">
         <v>19491700</v>
@@ -6652,16 +6652,16 @@
         <v>44866</v>
       </c>
       <c r="B312" t="n">
-        <v>4.047591209411621</v>
+        <v>4.047591686248779</v>
       </c>
       <c r="C312" t="n">
-        <v>4.092464467100041</v>
+        <v>4.092464949223611</v>
       </c>
       <c r="D312" t="n">
-        <v>3.814248728821982</v>
+        <v>3.814249178169614</v>
       </c>
       <c r="E312" t="n">
-        <v>3.868096894816395</v>
+        <v>3.868097350507752</v>
       </c>
       <c r="F312" t="n">
         <v>23695600</v>
@@ -6732,16 +6732,16 @@
         <v>44873</v>
       </c>
       <c r="B316" t="n">
-        <v>4.083490371704102</v>
+        <v>4.083489894866943</v>
       </c>
       <c r="C316" t="n">
-        <v>4.110414243265911</v>
+        <v>4.110413763284799</v>
       </c>
       <c r="D316" t="n">
-        <v>3.966819120410333</v>
+        <v>3.966818657197105</v>
       </c>
       <c r="E316" t="n">
-        <v>4.01169238232909</v>
+        <v>4.011691913875923</v>
       </c>
       <c r="F316" t="n">
         <v>15444300</v>
@@ -6792,16 +6792,16 @@
         <v>44876</v>
       </c>
       <c r="B319" t="n">
-        <v>3.715527057647705</v>
+        <v>3.715527534484863</v>
       </c>
       <c r="C319" t="n">
-        <v>3.751425836720846</v>
+        <v>3.751426318165122</v>
       </c>
       <c r="D319" t="n">
-        <v>3.437311305857262</v>
+        <v>3.437311746989228</v>
       </c>
       <c r="E319" t="n">
-        <v>3.634755018706739</v>
+        <v>3.63475548517791</v>
       </c>
       <c r="F319" t="n">
         <v>24235200</v>
@@ -6832,16 +6832,16 @@
         <v>44881</v>
       </c>
       <c r="B321" t="n">
-        <v>3.616805553436279</v>
+        <v>3.616805791854858</v>
       </c>
       <c r="C321" t="n">
-        <v>3.760400666722041</v>
+        <v>3.760400914606361</v>
       </c>
       <c r="D321" t="n">
-        <v>3.553982477400161</v>
+        <v>3.553982711677465</v>
       </c>
       <c r="E321" t="n">
-        <v>3.697577590685923</v>
+        <v>3.697577834428968</v>
       </c>
       <c r="F321" t="n">
         <v>16148800</v>
@@ -6852,16 +6852,16 @@
         <v>44882</v>
       </c>
       <c r="B322" t="n">
-        <v>3.509109020233154</v>
+        <v>3.509109258651733</v>
       </c>
       <c r="C322" t="n">
-        <v>3.571931882577372</v>
+        <v>3.57193212526431</v>
       </c>
       <c r="D322" t="n">
-        <v>3.356538997709313</v>
+        <v>3.356539225761863</v>
       </c>
       <c r="E322" t="n">
-        <v>3.56295718795677</v>
+        <v>3.562957430033942</v>
       </c>
       <c r="F322" t="n">
         <v>25106400</v>
@@ -6872,16 +6872,16 @@
         <v>44883</v>
       </c>
       <c r="B323" t="n">
-        <v>3.652704238891602</v>
+        <v>3.652704477310181</v>
       </c>
       <c r="C323" t="n">
-        <v>3.841173034261142</v>
+        <v>3.841173284981419</v>
       </c>
       <c r="D323" t="n">
-        <v>3.536032998339565</v>
+        <v>3.536033229142802</v>
       </c>
       <c r="E323" t="n">
-        <v>3.580906470100505</v>
+        <v>3.580906703832715</v>
       </c>
       <c r="F323" t="n">
         <v>23150300</v>
@@ -6892,16 +6892,16 @@
         <v>44886</v>
       </c>
       <c r="B324" t="n">
-        <v>3.616805553436279</v>
+        <v>3.616805791854858</v>
       </c>
       <c r="C324" t="n">
-        <v>3.733476369007364</v>
+        <v>3.733476615116843</v>
       </c>
       <c r="D324" t="n">
-        <v>3.545007782819801</v>
+        <v>3.545008016505496</v>
       </c>
       <c r="E324" t="n">
-        <v>3.679628201525203</v>
+        <v>3.67962844408503</v>
       </c>
       <c r="F324" t="n">
         <v>11314600</v>
@@ -6912,16 +6912,16 @@
         <v>44887</v>
       </c>
       <c r="B325" t="n">
-        <v>3.616805553436279</v>
+        <v>3.616805791854858</v>
       </c>
       <c r="C325" t="n">
-        <v>3.661678812364483</v>
+        <v>3.661679053741092</v>
       </c>
       <c r="D325" t="n">
-        <v>3.562957171980521</v>
+        <v>3.562957406849434</v>
       </c>
       <c r="E325" t="n">
-        <v>3.616805553436279</v>
+        <v>3.616805791854858</v>
       </c>
       <c r="F325" t="n">
         <v>10439300</v>
@@ -6952,16 +6952,16 @@
         <v>44889</v>
       </c>
       <c r="B327" t="n">
-        <v>3.724502325057983</v>
+        <v>3.724502086639404</v>
       </c>
       <c r="C327" t="n">
-        <v>3.742451716323075</v>
+        <v>3.742451476755492</v>
       </c>
       <c r="D327" t="n">
-        <v>3.598856586202345</v>
+        <v>3.598856355826795</v>
       </c>
       <c r="E327" t="n">
-        <v>3.634755368732528</v>
+        <v>3.634755136058969</v>
       </c>
       <c r="F327" t="n">
         <v>5511600</v>
@@ -6972,16 +6972,16 @@
         <v>44890</v>
       </c>
       <c r="B328" t="n">
-        <v>3.634755373001099</v>
+        <v>3.63475489616394</v>
       </c>
       <c r="C328" t="n">
-        <v>3.760401112004292</v>
+        <v>3.76040061868389</v>
       </c>
       <c r="D328" t="n">
-        <v>3.580906985168965</v>
+        <v>3.580906515396082</v>
       </c>
       <c r="E328" t="n">
-        <v>3.733476811101414</v>
+        <v>3.733476321313164</v>
       </c>
       <c r="F328" t="n">
         <v>8739900</v>
@@ -6992,16 +6992,16 @@
         <v>44893</v>
       </c>
       <c r="B329" t="n">
-        <v>3.607830762863159</v>
+        <v>3.60783052444458</v>
       </c>
       <c r="C329" t="n">
-        <v>3.670653840953675</v>
+        <v>3.670653598383518</v>
       </c>
       <c r="D329" t="n">
-        <v>3.58988137311547</v>
+        <v>3.589881135883052</v>
       </c>
       <c r="E329" t="n">
-        <v>3.58988137311547</v>
+        <v>3.589881135883052</v>
       </c>
       <c r="F329" t="n">
         <v>7386900</v>
@@ -7032,16 +7032,16 @@
         <v>44895</v>
       </c>
       <c r="B331" t="n">
-        <v>3.634755373001099</v>
+        <v>3.63475489616394</v>
       </c>
       <c r="C331" t="n">
-        <v>3.661679245956732</v>
+        <v>3.661678765587478</v>
       </c>
       <c r="D331" t="n">
-        <v>3.518084115667368</v>
+        <v>3.518083654136107</v>
       </c>
       <c r="E331" t="n">
-        <v>3.57193228952588</v>
+        <v>3.571931820930371</v>
       </c>
       <c r="F331" t="n">
         <v>16877200</v>
@@ -7052,16 +7052,16 @@
         <v>44896</v>
       </c>
       <c r="B332" t="n">
-        <v>3.446285963058472</v>
+        <v>3.446286201477051</v>
       </c>
       <c r="C332" t="n">
-        <v>3.589881291759341</v>
+        <v>3.589881540112033</v>
       </c>
       <c r="D332" t="n">
-        <v>3.428336573717563</v>
+        <v>3.428336810894379</v>
       </c>
       <c r="E332" t="n">
-        <v>3.589881291759341</v>
+        <v>3.589881540112033</v>
       </c>
       <c r="F332" t="n">
         <v>22625600</v>
@@ -7092,16 +7092,16 @@
         <v>44900</v>
       </c>
       <c r="B334" t="n">
-        <v>3.347564458847046</v>
+        <v>3.347564220428467</v>
       </c>
       <c r="C334" t="n">
-        <v>3.545007963660719</v>
+        <v>3.545007711179917</v>
       </c>
       <c r="D334" t="n">
-        <v>3.329615068770676</v>
+        <v>3.32961483163048</v>
       </c>
       <c r="E334" t="n">
-        <v>3.545007963660719</v>
+        <v>3.545007711179917</v>
       </c>
       <c r="F334" t="n">
         <v>14607600</v>
@@ -7312,16 +7312,16 @@
         <v>44915</v>
       </c>
       <c r="B345" t="n">
-        <v>3.257622241973877</v>
+        <v>3.257622003555298</v>
       </c>
       <c r="C345" t="n">
-        <v>3.31283612621739</v>
+        <v>3.312835883757822</v>
       </c>
       <c r="D345" t="n">
-        <v>3.036766485599353</v>
+        <v>3.036766263344746</v>
       </c>
       <c r="E345" t="n">
-        <v>3.036766485599353</v>
+        <v>3.036766263344746</v>
       </c>
       <c r="F345" t="n">
         <v>12943700</v>
@@ -7332,16 +7332,16 @@
         <v>44916</v>
       </c>
       <c r="B346" t="n">
-        <v>3.331240892410278</v>
+        <v>3.33124041557312</v>
       </c>
       <c r="C346" t="n">
-        <v>3.377252683921307</v>
+        <v>3.377252200497974</v>
       </c>
       <c r="D346" t="n">
-        <v>3.239217748189187</v>
+        <v>3.239217284524313</v>
       </c>
       <c r="E346" t="n">
-        <v>3.266824691455514</v>
+        <v>3.266824223838955</v>
       </c>
       <c r="F346" t="n">
         <v>14610300</v>
@@ -7372,16 +7372,16 @@
         <v>44918</v>
       </c>
       <c r="B348" t="n">
-        <v>3.414061546325684</v>
+        <v>3.414061784744263</v>
       </c>
       <c r="C348" t="n">
-        <v>3.441668486395647</v>
+        <v>3.441668726742138</v>
       </c>
       <c r="D348" t="n">
-        <v>3.340443039472447</v>
+        <v>3.34044327274993</v>
       </c>
       <c r="E348" t="n">
-        <v>3.358847666185756</v>
+        <v>3.358847900748513</v>
       </c>
       <c r="F348" t="n">
         <v>4486400</v>
@@ -7452,16 +7452,16 @@
         <v>44924</v>
       </c>
       <c r="B352" t="n">
-        <v>3.441668510437012</v>
+        <v>3.441668748855591</v>
       </c>
       <c r="C352" t="n">
-        <v>3.598108057993386</v>
+        <v>3.598108307249177</v>
       </c>
       <c r="D352" t="n">
-        <v>3.404859256753267</v>
+        <v>3.404859492621917</v>
       </c>
       <c r="E352" t="n">
-        <v>3.524489331225437</v>
+        <v>3.524489575381356</v>
       </c>
       <c r="F352" t="n">
         <v>7177700</v>
@@ -7472,16 +7472,16 @@
         <v>44928</v>
       </c>
       <c r="B353" t="n">
-        <v>3.257622241973877</v>
+        <v>3.257622003555298</v>
       </c>
       <c r="C353" t="n">
-        <v>3.414061800064303</v>
+        <v>3.414061550196239</v>
       </c>
       <c r="D353" t="n">
-        <v>3.23001529985212</v>
+        <v>3.230015063454036</v>
       </c>
       <c r="E353" t="n">
-        <v>3.395657171983132</v>
+        <v>3.395656923462064</v>
       </c>
       <c r="F353" t="n">
         <v>9470500</v>
@@ -7532,16 +7532,16 @@
         <v>44931</v>
       </c>
       <c r="B356" t="n">
-        <v>2.972350120544434</v>
+        <v>2.972350358963013</v>
       </c>
       <c r="C356" t="n">
-        <v>3.119587356333176</v>
+        <v>3.11958760656197</v>
       </c>
       <c r="D356" t="n">
-        <v>2.935540866447363</v>
+        <v>2.935541101913393</v>
       </c>
       <c r="E356" t="n">
-        <v>3.082777882835645</v>
+        <v>3.082778130111872</v>
       </c>
       <c r="F356" t="n">
         <v>35445300</v>
@@ -7572,16 +7572,16 @@
         <v>44935</v>
       </c>
       <c r="B358" t="n">
-        <v>2.972350120544434</v>
+        <v>2.972350358963013</v>
       </c>
       <c r="C358" t="n">
-        <v>3.027564001690039</v>
+        <v>3.027564244537442</v>
       </c>
       <c r="D358" t="n">
-        <v>2.90793392587456</v>
+        <v>2.907934159126178</v>
       </c>
       <c r="E358" t="n">
-        <v>2.944743179971631</v>
+        <v>2.944743416175798</v>
       </c>
       <c r="F358" t="n">
         <v>15633700</v>
@@ -7632,16 +7632,16 @@
         <v>44938</v>
       </c>
       <c r="B361" t="n">
-        <v>3.211610794067383</v>
+        <v>3.211610555648804</v>
       </c>
       <c r="C361" t="n">
-        <v>3.349645729332935</v>
+        <v>3.349645480667133</v>
       </c>
       <c r="D361" t="n">
-        <v>3.165599222112359</v>
+        <v>3.165598987109516</v>
       </c>
       <c r="E361" t="n">
-        <v>3.266824680413411</v>
+        <v>3.266824437895949</v>
       </c>
       <c r="F361" t="n">
         <v>13176700</v>
@@ -7692,16 +7692,16 @@
         <v>44943</v>
       </c>
       <c r="B364" t="n">
-        <v>3.091980218887329</v>
+        <v>3.091980457305908</v>
       </c>
       <c r="C364" t="n">
-        <v>3.128789692653045</v>
+        <v>3.128789933909955</v>
       </c>
       <c r="D364" t="n">
-        <v>3.027564023748135</v>
+        <v>3.027564257199665</v>
       </c>
       <c r="E364" t="n">
-        <v>3.055170964522075</v>
+        <v>3.055171200102341</v>
       </c>
       <c r="F364" t="n">
         <v>11859400</v>
@@ -7732,16 +7732,16 @@
         <v>44945</v>
       </c>
       <c r="B366" t="n">
-        <v>3.137992143630981</v>
+        <v>3.137991905212402</v>
       </c>
       <c r="C366" t="n">
-        <v>3.147194457625188</v>
+        <v>3.147194218507435</v>
       </c>
       <c r="D366" t="n">
-        <v>2.990754900323207</v>
+        <v>2.99075467309143</v>
       </c>
       <c r="E366" t="n">
-        <v>3.082778040265271</v>
+        <v>3.082777806041753</v>
       </c>
       <c r="F366" t="n">
         <v>23712400</v>
@@ -7832,16 +7832,16 @@
         <v>44952</v>
       </c>
       <c r="B371" t="n">
-        <v>3.202408075332642</v>
+        <v>3.202408313751221</v>
       </c>
       <c r="C371" t="n">
-        <v>3.285228894394528</v>
+        <v>3.2852291389791</v>
       </c>
       <c r="D371" t="n">
-        <v>3.184003448874444</v>
+        <v>3.184003685922803</v>
       </c>
       <c r="E371" t="n">
-        <v>3.257621954707233</v>
+        <v>3.257622197236473</v>
       </c>
       <c r="F371" t="n">
         <v>8271800</v>
@@ -7932,16 +7932,16 @@
         <v>44959</v>
       </c>
       <c r="B376" t="n">
-        <v>2.806708335876465</v>
+        <v>2.806708097457886</v>
       </c>
       <c r="C376" t="n">
-        <v>2.972350203327015</v>
+        <v>2.972349950837826</v>
       </c>
       <c r="D376" t="n">
-        <v>2.797506022095904</v>
+        <v>2.797505784459025</v>
       </c>
       <c r="E376" t="n">
-        <v>2.898731693082534</v>
+        <v>2.898731446846941</v>
       </c>
       <c r="F376" t="n">
         <v>50857000</v>
@@ -8052,16 +8052,16 @@
         <v>44967</v>
       </c>
       <c r="B382" t="n">
-        <v>2.953945398330688</v>
+        <v>2.953945636749268</v>
       </c>
       <c r="C382" t="n">
-        <v>3.045968530608719</v>
+        <v>3.045968776454661</v>
       </c>
       <c r="D382" t="n">
-        <v>2.926338458647279</v>
+        <v>2.92633869483765</v>
       </c>
       <c r="E382" t="n">
-        <v>3.01836159092531</v>
+        <v>3.018361834543043</v>
       </c>
       <c r="F382" t="n">
         <v>23226200</v>
@@ -8092,16 +8092,16 @@
         <v>44971</v>
       </c>
       <c r="B384" t="n">
-        <v>2.742291927337646</v>
+        <v>2.742292165756226</v>
       </c>
       <c r="C384" t="n">
-        <v>2.9539453473228</v>
+        <v>2.953945604142814</v>
       </c>
       <c r="D384" t="n">
-        <v>2.723887301199846</v>
+        <v>2.723887538018302</v>
       </c>
       <c r="E384" t="n">
-        <v>2.9539453473228</v>
+        <v>2.953945604142814</v>
       </c>
       <c r="F384" t="n">
         <v>40924300</v>
@@ -8132,16 +8132,16 @@
         <v>44973</v>
       </c>
       <c r="B386" t="n">
-        <v>2.834315538406372</v>
+        <v>2.834315299987793</v>
       </c>
       <c r="C386" t="n">
-        <v>2.871124796920665</v>
+        <v>2.871124555405743</v>
       </c>
       <c r="D386" t="n">
-        <v>2.760697021377787</v>
+        <v>2.760696789151893</v>
       </c>
       <c r="E386" t="n">
-        <v>2.825113223777799</v>
+        <v>2.825112986133305</v>
       </c>
       <c r="F386" t="n">
         <v>21149000</v>
@@ -8172,16 +8172,16 @@
         <v>44979</v>
       </c>
       <c r="B388" t="n">
-        <v>2.834315538406372</v>
+        <v>2.834315299987793</v>
       </c>
       <c r="C388" t="n">
-        <v>2.843517853034945</v>
+        <v>2.84351761384228</v>
       </c>
       <c r="D388" t="n">
-        <v>2.714685448234921</v>
+        <v>2.714685219879454</v>
       </c>
       <c r="E388" t="n">
-        <v>2.76989933600636</v>
+        <v>2.76989910300638</v>
       </c>
       <c r="F388" t="n">
         <v>20601900</v>
@@ -8252,16 +8252,16 @@
         <v>44985</v>
       </c>
       <c r="B392" t="n">
-        <v>2.834315538406372</v>
+        <v>2.834315299987793</v>
       </c>
       <c r="C392" t="n">
-        <v>2.889529645578298</v>
+        <v>2.889529402515187</v>
       </c>
       <c r="D392" t="n">
-        <v>2.79750627989208</v>
+        <v>2.797506044569843</v>
       </c>
       <c r="E392" t="n">
-        <v>2.825113223777799</v>
+        <v>2.825112986133305</v>
       </c>
       <c r="F392" t="n">
         <v>28842300</v>
@@ -8272,16 +8272,16 @@
         <v>44986</v>
       </c>
       <c r="B393" t="n">
-        <v>2.779101133346558</v>
+        <v>2.779101371765137</v>
       </c>
       <c r="C393" t="n">
-        <v>2.917136046482494</v>
+        <v>2.917136296743063</v>
       </c>
       <c r="D393" t="n">
-        <v>2.75149419459946</v>
+        <v>2.751494430649644</v>
       </c>
       <c r="E393" t="n">
-        <v>2.843517323756453</v>
+        <v>2.843517567701285</v>
       </c>
       <c r="F393" t="n">
         <v>32788900</v>
@@ -8292,16 +8292,16 @@
         <v>44987</v>
       </c>
       <c r="B394" t="n">
-        <v>2.687078475952148</v>
+        <v>2.687078237533569</v>
       </c>
       <c r="C394" t="n">
-        <v>2.797506250328025</v>
+        <v>2.797506002111432</v>
       </c>
       <c r="D394" t="n">
-        <v>2.687078475952148</v>
+        <v>2.687078237533569</v>
       </c>
       <c r="E394" t="n">
-        <v>2.779101621265379</v>
+        <v>2.779101374681788</v>
       </c>
       <c r="F394" t="n">
         <v>21864000</v>
@@ -8372,16 +8372,16 @@
         <v>44993</v>
       </c>
       <c r="B398" t="n">
-        <v>2.705482721328735</v>
+        <v>2.705482959747314</v>
       </c>
       <c r="C398" t="n">
-        <v>2.733089661007544</v>
+        <v>2.733089901858964</v>
       </c>
       <c r="D398" t="n">
-        <v>2.659471155197387</v>
+        <v>2.659471389561232</v>
       </c>
       <c r="E398" t="n">
-        <v>2.677875781649926</v>
+        <v>2.677876017635665</v>
       </c>
       <c r="F398" t="n">
         <v>21816400</v>
@@ -8412,16 +8412,16 @@
         <v>44995</v>
       </c>
       <c r="B400" t="n">
-        <v>2.503031730651855</v>
+        <v>2.503031969070435</v>
       </c>
       <c r="C400" t="n">
-        <v>2.595054867315339</v>
+        <v>2.595055114499298</v>
       </c>
       <c r="D400" t="n">
-        <v>2.493829416985507</v>
+        <v>2.493829654527548</v>
       </c>
       <c r="E400" t="n">
-        <v>2.576650239982643</v>
+        <v>2.576650485413526</v>
       </c>
       <c r="F400" t="n">
         <v>23735100</v>
@@ -8552,16 +8552,16 @@
         <v>45006</v>
       </c>
       <c r="B407" t="n">
-        <v>2.264016151428223</v>
+        <v>2.264015913009644</v>
       </c>
       <c r="C407" t="n">
-        <v>2.397193438688833</v>
+        <v>2.397193186245646</v>
       </c>
       <c r="D407" t="n">
-        <v>2.244990597876922</v>
+        <v>2.244990361461882</v>
       </c>
       <c r="E407" t="n">
-        <v>2.368655448561559</v>
+        <v>2.368655199123645</v>
       </c>
       <c r="F407" t="n">
         <v>26738200</v>
@@ -8592,16 +8592,16 @@
         <v>45008</v>
       </c>
       <c r="B409" t="n">
-        <v>2.149863958358765</v>
+        <v>2.149864196777344</v>
       </c>
       <c r="C409" t="n">
-        <v>2.235477928511182</v>
+        <v>2.235478176424297</v>
       </c>
       <c r="D409" t="n">
-        <v>2.140351295008496</v>
+        <v>2.140351532372127</v>
       </c>
       <c r="E409" t="n">
-        <v>2.225965265160914</v>
+        <v>2.22596551201908</v>
       </c>
       <c r="F409" t="n">
         <v>30902200</v>
@@ -8632,16 +8632,16 @@
         <v>45012</v>
       </c>
       <c r="B411" t="n">
-        <v>2.387680768966675</v>
+        <v>2.387681007385254</v>
       </c>
       <c r="C411" t="n">
-        <v>2.416218759018095</v>
+        <v>2.416219000286296</v>
       </c>
       <c r="D411" t="n">
-        <v>2.302066798812414</v>
+        <v>2.302067028682128</v>
       </c>
       <c r="E411" t="n">
-        <v>2.311579462162887</v>
+        <v>2.311579692982475</v>
       </c>
       <c r="F411" t="n">
         <v>19684900</v>
@@ -8652,16 +8652,16 @@
         <v>45013</v>
       </c>
       <c r="B412" t="n">
-        <v>2.520858526229858</v>
+        <v>2.520858287811279</v>
       </c>
       <c r="C412" t="n">
-        <v>2.549396519038522</v>
+        <v>2.549396277920867</v>
       </c>
       <c r="D412" t="n">
-        <v>2.340117678308513</v>
+        <v>2.340117456984101</v>
       </c>
       <c r="E412" t="n">
-        <v>2.368655671117177</v>
+        <v>2.368655447093689</v>
       </c>
       <c r="F412" t="n">
         <v>69618900</v>
@@ -8772,16 +8772,16 @@
         <v>45021</v>
       </c>
       <c r="B418" t="n">
-        <v>2.682573795318604</v>
+        <v>2.682573556900024</v>
       </c>
       <c r="C418" t="n">
-        <v>2.720624452063579</v>
+        <v>2.720624210263179</v>
       </c>
       <c r="D418" t="n">
-        <v>2.615985146014897</v>
+        <v>2.615984913514504</v>
       </c>
       <c r="E418" t="n">
-        <v>2.701599123691091</v>
+        <v>2.701598883581602</v>
       </c>
       <c r="F418" t="n">
         <v>22336100</v>
@@ -8872,16 +8872,16 @@
         <v>45029</v>
       </c>
       <c r="B423" t="n">
-        <v>2.882339954376221</v>
+        <v>2.882339715957642</v>
       </c>
       <c r="C423" t="n">
-        <v>2.958441267452883</v>
+        <v>2.95844102273943</v>
       </c>
       <c r="D423" t="n">
-        <v>2.853801961972472</v>
+        <v>2.853801725914471</v>
       </c>
       <c r="E423" t="n">
-        <v>2.929903275049135</v>
+        <v>2.929903032696259</v>
       </c>
       <c r="F423" t="n">
         <v>15780900</v>
@@ -8952,16 +8952,16 @@
         <v>45035</v>
       </c>
       <c r="B427" t="n">
-        <v>2.882339954376221</v>
+        <v>2.882339715957642</v>
       </c>
       <c r="C427" t="n">
-        <v>2.996492150791017</v>
+        <v>2.996491902930108</v>
       </c>
       <c r="D427" t="n">
-        <v>2.872827290241638</v>
+        <v>2.872827052609918</v>
       </c>
       <c r="E427" t="n">
-        <v>2.986979486656434</v>
+        <v>2.986979239582385</v>
       </c>
       <c r="F427" t="n">
         <v>19845900</v>
@@ -8972,16 +8972,16 @@
         <v>45036</v>
       </c>
       <c r="B428" t="n">
-        <v>2.958441257476807</v>
+        <v>2.958441019058228</v>
       </c>
       <c r="C428" t="n">
-        <v>2.977466812481619</v>
+        <v>2.977466572529786</v>
       </c>
       <c r="D428" t="n">
-        <v>2.844289288246741</v>
+        <v>2.844289059027585</v>
       </c>
       <c r="E428" t="n">
-        <v>2.882339944656763</v>
+        <v>2.882339712371133</v>
       </c>
       <c r="F428" t="n">
         <v>11874200</v>
@@ -9112,16 +9112,16 @@
         <v>45049</v>
       </c>
       <c r="B435" t="n">
-        <v>2.996491670608521</v>
+        <v>2.9964919090271</v>
       </c>
       <c r="C435" t="n">
-        <v>3.034542321049302</v>
+        <v>3.034542562495416</v>
       </c>
       <c r="D435" t="n">
-        <v>2.853801504655823</v>
+        <v>2.853801731721129</v>
       </c>
       <c r="E435" t="n">
-        <v>2.910877480316995</v>
+        <v>2.910877711923603</v>
       </c>
       <c r="F435" t="n">
         <v>15681500</v>
@@ -9292,16 +9292,16 @@
         <v>45062</v>
       </c>
       <c r="B444" t="n">
-        <v>3.082106113433838</v>
+        <v>3.082105875015259</v>
       </c>
       <c r="C444" t="n">
-        <v>3.139182097971549</v>
+        <v>3.139181855137815</v>
       </c>
       <c r="D444" t="n">
-        <v>2.977466808448034</v>
+        <v>2.977466578123905</v>
       </c>
       <c r="E444" t="n">
-        <v>2.977466808448034</v>
+        <v>2.977466578123905</v>
       </c>
       <c r="F444" t="n">
         <v>45623200</v>
@@ -9332,16 +9332,16 @@
         <v>45064</v>
       </c>
       <c r="B446" t="n">
-        <v>3.300897598266602</v>
+        <v>3.300897359848022</v>
       </c>
       <c r="C446" t="n">
-        <v>3.338948254440312</v>
+        <v>3.338948013273395</v>
       </c>
       <c r="D446" t="n">
-        <v>3.177232738902241</v>
+        <v>3.177232509415779</v>
       </c>
       <c r="E446" t="n">
-        <v>3.253334278049463</v>
+        <v>3.253334043066307</v>
       </c>
       <c r="F446" t="n">
         <v>40825600</v>
@@ -9412,16 +9412,16 @@
         <v>45070</v>
       </c>
       <c r="B450" t="n">
-        <v>3.319922924041748</v>
+        <v>3.319922685623169</v>
       </c>
       <c r="C450" t="n">
-        <v>3.529201759651233</v>
+        <v>3.529201506203401</v>
       </c>
       <c r="D450" t="n">
-        <v>3.262846939820925</v>
+        <v>3.262846705501229</v>
       </c>
       <c r="E450" t="n">
-        <v>3.462613111393607</v>
+        <v>3.462612862727804</v>
       </c>
       <c r="F450" t="n">
         <v>35329500</v>
@@ -9512,16 +9512,16 @@
         <v>45077</v>
       </c>
       <c r="B455" t="n">
-        <v>3.453100204467773</v>
+        <v>3.453099966049194</v>
       </c>
       <c r="C455" t="n">
-        <v>3.557739501512349</v>
+        <v>3.557739255868972</v>
       </c>
       <c r="D455" t="n">
-        <v>3.415049324197234</v>
+        <v>3.41504908840587</v>
       </c>
       <c r="E455" t="n">
-        <v>3.424561987564922</v>
+        <v>3.424561751116759</v>
       </c>
       <c r="F455" t="n">
         <v>23066900</v>
@@ -9532,16 +9532,16 @@
         <v>45078</v>
       </c>
       <c r="B456" t="n">
-        <v>3.576764583587646</v>
+        <v>3.576764822006226</v>
       </c>
       <c r="C456" t="n">
-        <v>3.662378548040625</v>
+        <v>3.662378792166026</v>
       </c>
       <c r="D456" t="n">
-        <v>3.376998439730927</v>
+        <v>3.376998664833572</v>
       </c>
       <c r="E456" t="n">
-        <v>3.472125293700673</v>
+        <v>3.472125525144246</v>
       </c>
       <c r="F456" t="n">
         <v>28377100</v>
@@ -9612,16 +9612,16 @@
         <v>45084</v>
       </c>
       <c r="B460" t="n">
-        <v>3.757505655288696</v>
+        <v>3.757505893707275</v>
       </c>
       <c r="C460" t="n">
-        <v>3.85263251567056</v>
+        <v>3.852632760125061</v>
       </c>
       <c r="D460" t="n">
-        <v>3.681404121623248</v>
+        <v>3.681404355213087</v>
       </c>
       <c r="E460" t="n">
-        <v>3.747992991930488</v>
+        <v>3.747993229745477</v>
       </c>
       <c r="F460" t="n">
         <v>19382700</v>
@@ -9652,16 +9652,16 @@
         <v>45089</v>
       </c>
       <c r="B462" t="n">
-        <v>3.79555606842041</v>
+        <v>3.795556306838989</v>
       </c>
       <c r="C462" t="n">
-        <v>3.80506873117636</v>
+        <v>3.805068970192479</v>
       </c>
       <c r="D462" t="n">
-        <v>3.74799275464066</v>
+        <v>3.74799299007154</v>
       </c>
       <c r="E462" t="n">
-        <v>3.78604340566446</v>
+        <v>3.786043643485499</v>
       </c>
       <c r="F462" t="n">
         <v>16242400</v>
@@ -9692,16 +9692,16 @@
         <v>45091</v>
       </c>
       <c r="B464" t="n">
-        <v>3.747992992401123</v>
+        <v>3.747993230819702</v>
       </c>
       <c r="C464" t="n">
-        <v>3.795556309198135</v>
+        <v>3.795556550642328</v>
       </c>
       <c r="D464" t="n">
-        <v>3.662378795366716</v>
+        <v>3.662379028339177</v>
       </c>
       <c r="E464" t="n">
-        <v>3.709942338963513</v>
+        <v>3.709942574961601</v>
       </c>
       <c r="F464" t="n">
         <v>25840400</v>
@@ -9712,16 +9712,16 @@
         <v>45092</v>
       </c>
       <c r="B465" t="n">
-        <v>3.757505655288696</v>
+        <v>3.757505893707275</v>
       </c>
       <c r="C465" t="n">
-        <v>3.795556308721528</v>
+        <v>3.79555654955447</v>
       </c>
       <c r="D465" t="n">
-        <v>3.719455001855864</v>
+        <v>3.71945523786008</v>
       </c>
       <c r="E465" t="n">
-        <v>3.757505655288696</v>
+        <v>3.757505893707275</v>
       </c>
       <c r="F465" t="n">
         <v>13781200</v>
@@ -9732,16 +9732,16 @@
         <v>45093</v>
       </c>
       <c r="B466" t="n">
-        <v>3.757505655288696</v>
+        <v>3.757505893707275</v>
       </c>
       <c r="C466" t="n">
-        <v>3.776530982005112</v>
+        <v>3.776531221630873</v>
       </c>
       <c r="D466" t="n">
-        <v>3.709942338497656</v>
+        <v>3.709942573898282</v>
       </c>
       <c r="E466" t="n">
-        <v>3.728967665214073</v>
+        <v>3.728967901821879</v>
       </c>
       <c r="F466" t="n">
         <v>14449100</v>
@@ -9752,16 +9752,16 @@
         <v>45096</v>
       </c>
       <c r="B467" t="n">
-        <v>3.776530981063843</v>
+        <v>3.776531219482422</v>
       </c>
       <c r="C467" t="n">
-        <v>3.814581861286975</v>
+        <v>3.814582102107769</v>
       </c>
       <c r="D467" t="n">
-        <v>3.738480327640495</v>
+        <v>3.738480563656874</v>
       </c>
       <c r="E467" t="n">
-        <v>3.78604364441968</v>
+        <v>3.786043883438809</v>
       </c>
       <c r="F467" t="n">
         <v>9550900</v>
@@ -9852,16 +9852,16 @@
         <v>45103</v>
       </c>
       <c r="B472" t="n">
-        <v>4.204601287841797</v>
+        <v>4.204600811004639</v>
       </c>
       <c r="C472" t="n">
-        <v>4.280702594727692</v>
+        <v>4.280702109260005</v>
       </c>
       <c r="D472" t="n">
-        <v>4.128499980955902</v>
+        <v>4.128499512749272</v>
       </c>
       <c r="E472" t="n">
-        <v>4.138012417516855</v>
+        <v>4.138011948231434</v>
       </c>
       <c r="F472" t="n">
         <v>42881900</v>
@@ -9972,16 +9972,16 @@
         <v>45111</v>
       </c>
       <c r="B478" t="n">
-        <v>4.195088863372803</v>
+        <v>4.195088386535645</v>
       </c>
       <c r="C478" t="n">
-        <v>4.261677741089692</v>
+        <v>4.261677256683671</v>
       </c>
       <c r="D478" t="n">
-        <v>4.138012876872448</v>
+        <v>4.138012406522865</v>
       </c>
       <c r="E478" t="n">
-        <v>4.252164849873157</v>
+        <v>4.252164366548425</v>
       </c>
       <c r="F478" t="n">
         <v>10806500</v>
@@ -10132,16 +10132,16 @@
         <v>45121</v>
       </c>
       <c r="B486" t="n">
-        <v>3.881170034408569</v>
+        <v>3.881170511245728</v>
       </c>
       <c r="C486" t="n">
-        <v>4.014347313032519</v>
+        <v>4.014347806231721</v>
       </c>
       <c r="D486" t="n">
-        <v>3.814581621896365</v>
+        <v>3.814582090552529</v>
       </c>
       <c r="E486" t="n">
-        <v>3.995321987514812</v>
+        <v>3.995322478376579</v>
       </c>
       <c r="F486" t="n">
         <v>16845900</v>
@@ -10172,16 +10172,16 @@
         <v>45125</v>
       </c>
       <c r="B488" t="n">
-        <v>4.07142448425293</v>
+        <v>4.071424007415771</v>
       </c>
       <c r="C488" t="n">
-        <v>4.185576458136752</v>
+        <v>4.185575967930341</v>
       </c>
       <c r="D488" t="n">
-        <v>4.004835606020889</v>
+        <v>4.004835136982487</v>
       </c>
       <c r="E488" t="n">
-        <v>4.023860935001526</v>
+        <v>4.023860463734916</v>
       </c>
       <c r="F488" t="n">
         <v>19854400</v>
@@ -10232,16 +10232,16 @@
         <v>45128</v>
       </c>
       <c r="B491" t="n">
-        <v>4.061911106109619</v>
+        <v>4.061911582946777</v>
       </c>
       <c r="C491" t="n">
-        <v>4.099961759510212</v>
+        <v>4.099962240814224</v>
       </c>
       <c r="D491" t="n">
-        <v>3.976296909158501</v>
+        <v>3.97629737594521</v>
       </c>
       <c r="E491" t="n">
-        <v>4.00483512600873</v>
+        <v>4.004835596145607</v>
       </c>
       <c r="F491" t="n">
         <v>9991000</v>
@@ -10432,16 +10432,16 @@
         <v>45142</v>
       </c>
       <c r="B501" t="n">
-        <v>3.903565406799316</v>
+        <v>3.903565883636475</v>
       </c>
       <c r="C501" t="n">
-        <v>3.960970726756138</v>
+        <v>3.960971210605601</v>
       </c>
       <c r="D501" t="n">
-        <v>3.865295193494769</v>
+        <v>3.865295665657057</v>
       </c>
       <c r="E501" t="n">
-        <v>3.903565406799316</v>
+        <v>3.903565883636475</v>
       </c>
       <c r="F501" t="n">
         <v>16409800</v>
@@ -10472,16 +10472,16 @@
         <v>45146</v>
       </c>
       <c r="B503" t="n">
-        <v>3.798322677612305</v>
+        <v>3.798322916030884</v>
       </c>
       <c r="C503" t="n">
-        <v>3.817457786065083</v>
+        <v>3.817458025684763</v>
       </c>
       <c r="D503" t="n">
-        <v>3.702646907239926</v>
+        <v>3.702647139652991</v>
       </c>
       <c r="E503" t="n">
-        <v>3.798322677612305</v>
+        <v>3.798322916030884</v>
       </c>
       <c r="F503" t="n">
         <v>17862300</v>
@@ -10532,16 +10532,16 @@
         <v>45149</v>
       </c>
       <c r="B506" t="n">
-        <v>3.683511972427368</v>
+        <v>3.683511734008789</v>
       </c>
       <c r="C506" t="n">
-        <v>3.750485083277681</v>
+        <v>3.750484840524209</v>
       </c>
       <c r="D506" t="n">
-        <v>3.635674199040356</v>
+        <v>3.63567396371812</v>
       </c>
       <c r="E506" t="n">
-        <v>3.731349973922877</v>
+        <v>3.731349732407941</v>
       </c>
       <c r="F506" t="n">
         <v>13400900</v>
@@ -10772,16 +10772,16 @@
         <v>45167</v>
       </c>
       <c r="B518" t="n">
-        <v>3.654809236526489</v>
+        <v>3.65480899810791</v>
       </c>
       <c r="C518" t="n">
-        <v>3.664376791015754</v>
+        <v>3.664376551973043</v>
       </c>
       <c r="D518" t="n">
-        <v>3.578268800612372</v>
+        <v>3.578268567186847</v>
       </c>
       <c r="E518" t="n">
-        <v>3.61653901856943</v>
+        <v>3.616538782647379</v>
       </c>
       <c r="F518" t="n">
         <v>13520200</v>
@@ -10912,16 +10912,16 @@
         <v>45177</v>
       </c>
       <c r="B525" t="n">
-        <v>3.54956579208374</v>
+        <v>3.549566030502319</v>
       </c>
       <c r="C525" t="n">
-        <v>3.58783600632047</v>
+        <v>3.587836247309597</v>
       </c>
       <c r="D525" t="n">
-        <v>3.51129557784701</v>
+        <v>3.511295813695041</v>
       </c>
       <c r="E525" t="n">
-        <v>3.530430684965375</v>
+        <v>3.53043092209868</v>
       </c>
       <c r="F525" t="n">
         <v>26042800</v>
@@ -10952,16 +10952,16 @@
         <v>45181</v>
       </c>
       <c r="B527" t="n">
-        <v>3.712214708328247</v>
+        <v>3.712214469909668</v>
       </c>
       <c r="C527" t="n">
-        <v>3.769620033976584</v>
+        <v>3.769619791871123</v>
       </c>
       <c r="D527" t="n">
-        <v>3.616538937472532</v>
+        <v>3.61653870519877</v>
       </c>
       <c r="E527" t="n">
-        <v>3.635674046021977</v>
+        <v>3.635673812519255</v>
       </c>
       <c r="F527" t="n">
         <v>15715300</v>
@@ -10972,16 +10972,16 @@
         <v>45182</v>
       </c>
       <c r="B528" t="n">
-        <v>3.769619941711426</v>
+        <v>3.769620180130005</v>
       </c>
       <c r="C528" t="n">
-        <v>3.846160374035806</v>
+        <v>3.846160617295367</v>
       </c>
       <c r="D528" t="n">
-        <v>3.712214617468141</v>
+        <v>3.712214852255983</v>
       </c>
       <c r="E528" t="n">
-        <v>3.712214617468141</v>
+        <v>3.712214852255983</v>
       </c>
       <c r="F528" t="n">
         <v>17575000</v>
@@ -10992,16 +10992,16 @@
         <v>45183</v>
       </c>
       <c r="B529" t="n">
-        <v>3.798322677612305</v>
+        <v>3.798322916030884</v>
       </c>
       <c r="C529" t="n">
-        <v>3.836593122626347</v>
+        <v>3.836593363447141</v>
       </c>
       <c r="D529" t="n">
-        <v>3.760052460706747</v>
+        <v>3.760052696723127</v>
       </c>
       <c r="E529" t="n">
-        <v>3.798322677612305</v>
+        <v>3.798322916030884</v>
       </c>
       <c r="F529" t="n">
         <v>9553000</v>
@@ -11032,16 +11032,16 @@
         <v>45187</v>
       </c>
       <c r="B531" t="n">
-        <v>3.817457675933838</v>
+        <v>3.817457914352417</v>
       </c>
       <c r="C531" t="n">
-        <v>3.884430553586438</v>
+        <v>3.884430796187795</v>
       </c>
       <c r="D531" t="n">
-        <v>3.740917244330867</v>
+        <v>3.740917477969129</v>
       </c>
       <c r="E531" t="n">
-        <v>3.817457675933838</v>
+        <v>3.817457914352417</v>
       </c>
       <c r="F531" t="n">
         <v>23371600</v>
@@ -11072,16 +11072,16 @@
         <v>45189</v>
       </c>
       <c r="B533" t="n">
-        <v>3.645241498947144</v>
+        <v>3.645241737365723</v>
       </c>
       <c r="C533" t="n">
-        <v>3.769619929168903</v>
+        <v>3.769620175722507</v>
       </c>
       <c r="D533" t="n">
-        <v>3.645241498947144</v>
+        <v>3.645241737365723</v>
       </c>
       <c r="E533" t="n">
-        <v>3.740917267142762</v>
+        <v>3.740917511819056</v>
       </c>
       <c r="F533" t="n">
         <v>23728500</v>
@@ -11212,16 +11212,16 @@
         <v>45198</v>
       </c>
       <c r="B540" t="n">
-        <v>3.425187349319458</v>
+        <v>3.425187587738037</v>
       </c>
       <c r="C540" t="n">
-        <v>3.492160451982693</v>
+        <v>3.492160695063099</v>
       </c>
       <c r="D540" t="n">
-        <v>3.386917135288163</v>
+        <v>3.38691737104285</v>
       </c>
       <c r="E540" t="n">
-        <v>3.463457563350753</v>
+        <v>3.463457804433224</v>
       </c>
       <c r="F540" t="n">
         <v>13661300</v>
@@ -11372,16 +11372,16 @@
         <v>45210</v>
       </c>
       <c r="B548" t="n">
-        <v>3.482593297958374</v>
+        <v>3.482593059539795</v>
       </c>
       <c r="C548" t="n">
-        <v>3.511295961774288</v>
+        <v>3.511295721390723</v>
       </c>
       <c r="D548" t="n">
-        <v>3.396485078402136</v>
+        <v>3.396484845878531</v>
       </c>
       <c r="E548" t="n">
-        <v>3.415620187612745</v>
+        <v>3.41561995377915</v>
       </c>
       <c r="F548" t="n">
         <v>15610900</v>
@@ -26032,19 +26032,39 @@
         <v>46286</v>
       </c>
       <c r="B1281" t="n">
-        <v>0.27</v>
+        <v>0.2700000107288361</v>
       </c>
       <c r="C1281" t="n">
-        <v>0.27</v>
+        <v>0.2700000107288361</v>
       </c>
       <c r="D1281" t="n">
-        <v>0.26</v>
+        <v>0.2599999904632568</v>
       </c>
       <c r="E1281" t="n">
-        <v>0.26</v>
+        <v>0.2599999904632568</v>
       </c>
       <c r="F1281" t="n">
         <v>9702900</v>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1282" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C1282" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D1282" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E1282" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="F1282" t="n">
+        <v>15773400</v>
       </c>
     </row>
   </sheetData>

--- a/database/RAIZ4.xlsx
+++ b/database/RAIZ4.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1282"/>
+  <dimension ref="A1:F1283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44413</v>
       </c>
       <c r="B2" t="n">
-        <v>6.384480953216553</v>
+        <v>6.384482383728027</v>
       </c>
       <c r="C2" t="n">
-        <v>6.701941459879408</v>
+        <v>6.701942961521317</v>
       </c>
       <c r="D2" t="n">
-        <v>6.331570938854646</v>
+        <v>6.331572357511064</v>
       </c>
       <c r="E2" t="n">
-        <v>6.596121431155595</v>
+        <v>6.59612290908739</v>
       </c>
       <c r="F2" t="n">
         <v>98849900</v>
@@ -472,16 +472,16 @@
         <v>44414</v>
       </c>
       <c r="B3" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="C3" t="n">
-        <v>6.481483579964149</v>
+        <v>6.48148308633695</v>
       </c>
       <c r="D3" t="n">
-        <v>6.199296805201136</v>
+        <v>6.19929633306517</v>
       </c>
       <c r="E3" t="n">
-        <v>6.393300212850708</v>
+        <v>6.393299725939519</v>
       </c>
       <c r="F3" t="n">
         <v>28799900</v>
@@ -512,16 +512,16 @@
         <v>44418</v>
       </c>
       <c r="B5" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="C5" t="n">
-        <v>6.313934972202879</v>
+        <v>6.313934491336116</v>
       </c>
       <c r="D5" t="n">
-        <v>6.216933478623825</v>
+        <v>6.216933005144656</v>
       </c>
       <c r="E5" t="n">
-        <v>6.278661625357502</v>
+        <v>6.278661147177143</v>
       </c>
       <c r="F5" t="n">
         <v>9988600</v>
@@ -552,16 +552,16 @@
         <v>44420</v>
       </c>
       <c r="B7" t="n">
-        <v>6.137567043304443</v>
+        <v>6.137567520141602</v>
       </c>
       <c r="C7" t="n">
-        <v>6.155203713294171</v>
+        <v>6.155204191501549</v>
       </c>
       <c r="D7" t="n">
-        <v>5.952381798166616</v>
+        <v>5.952382260616443</v>
       </c>
       <c r="E7" t="n">
-        <v>6.146385168053617</v>
+        <v>6.146385645575868</v>
       </c>
       <c r="F7" t="n">
         <v>17054100</v>
@@ -572,16 +572,16 @@
         <v>44421</v>
       </c>
       <c r="B8" t="n">
-        <v>6.181660175323486</v>
+        <v>6.181660652160645</v>
       </c>
       <c r="C8" t="n">
-        <v>6.208114975398141</v>
+        <v>6.208115454275954</v>
       </c>
       <c r="D8" t="n">
-        <v>6.049384913475816</v>
+        <v>6.049385380109605</v>
       </c>
       <c r="E8" t="n">
-        <v>6.155204954757366</v>
+        <v>6.155205429553837</v>
       </c>
       <c r="F8" t="n">
         <v>21141500</v>
@@ -612,16 +612,16 @@
         <v>44425</v>
       </c>
       <c r="B10" t="n">
-        <v>6.014111042022705</v>
+        <v>6.014111518859863</v>
       </c>
       <c r="C10" t="n">
-        <v>6.164022543855327</v>
+        <v>6.164023032578428</v>
       </c>
       <c r="D10" t="n">
-        <v>5.961201025995057</v>
+        <v>5.961201498637171</v>
       </c>
       <c r="E10" t="n">
-        <v>6.111112527827679</v>
+        <v>6.111113012355736</v>
       </c>
       <c r="F10" t="n">
         <v>17772000</v>
@@ -632,16 +632,16 @@
         <v>44426</v>
       </c>
       <c r="B11" t="n">
-        <v>6.005293369293213</v>
+        <v>6.005291938781738</v>
       </c>
       <c r="C11" t="n">
-        <v>6.172841987997847</v>
+        <v>6.172840517574881</v>
       </c>
       <c r="D11" t="n">
-        <v>5.925928123461678</v>
+        <v>5.925926711855674</v>
       </c>
       <c r="E11" t="n">
-        <v>6.022930043867833</v>
+        <v>6.022928609155154</v>
       </c>
       <c r="F11" t="n">
         <v>8841700</v>
@@ -672,16 +672,16 @@
         <v>44428</v>
       </c>
       <c r="B13" t="n">
-        <v>6.155204772949219</v>
+        <v>6.155204296112061</v>
       </c>
       <c r="C13" t="n">
-        <v>6.216933338785894</v>
+        <v>6.21693285716669</v>
       </c>
       <c r="D13" t="n">
-        <v>6.022929515008602</v>
+        <v>6.022929048418668</v>
       </c>
       <c r="E13" t="n">
-        <v>6.075839534086558</v>
+        <v>6.075839063397741</v>
       </c>
       <c r="F13" t="n">
         <v>3109200</v>
@@ -692,16 +692,16 @@
         <v>44431</v>
       </c>
       <c r="B14" t="n">
-        <v>6.322752952575684</v>
+        <v>6.322753429412842</v>
       </c>
       <c r="C14" t="n">
-        <v>6.349207750093361</v>
+        <v>6.349208228925635</v>
       </c>
       <c r="D14" t="n">
-        <v>6.181659577837608</v>
+        <v>6.181660044034058</v>
       </c>
       <c r="E14" t="n">
-        <v>6.208114375355285</v>
+        <v>6.208114843546852</v>
       </c>
       <c r="F14" t="n">
         <v>6128800</v>
@@ -712,16 +712,16 @@
         <v>44432</v>
       </c>
       <c r="B15" t="n">
-        <v>6.39330005645752</v>
+        <v>6.393299102783203</v>
       </c>
       <c r="C15" t="n">
-        <v>6.525575314137689</v>
+        <v>6.525574340732168</v>
       </c>
       <c r="D15" t="n">
-        <v>6.331571490742386</v>
+        <v>6.331570546275982</v>
       </c>
       <c r="E15" t="n">
-        <v>6.384481509716164</v>
+        <v>6.38448055735729</v>
       </c>
       <c r="F15" t="n">
         <v>6054100</v>
@@ -732,16 +732,16 @@
         <v>44433</v>
       </c>
       <c r="B16" t="n">
-        <v>6.472665309906006</v>
+        <v>6.472665786743164</v>
       </c>
       <c r="C16" t="n">
-        <v>6.507938655968863</v>
+        <v>6.507939135404586</v>
       </c>
       <c r="D16" t="n">
-        <v>6.402118617780292</v>
+        <v>6.40211908942032</v>
       </c>
       <c r="E16" t="n">
-        <v>6.455028636874578</v>
+        <v>6.455029112412453</v>
       </c>
       <c r="F16" t="n">
         <v>5190100</v>
@@ -752,16 +752,16 @@
         <v>44434</v>
       </c>
       <c r="B17" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="C17" t="n">
-        <v>6.507938800343913</v>
+        <v>6.507938304701895</v>
       </c>
       <c r="D17" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="E17" t="n">
-        <v>6.472665453498537</v>
+        <v>6.472664960542923</v>
       </c>
       <c r="F17" t="n">
         <v>7968100</v>
@@ -772,16 +772,16 @@
         <v>44435</v>
       </c>
       <c r="B18" t="n">
-        <v>6.340389728546143</v>
+        <v>6.340390205383301</v>
       </c>
       <c r="C18" t="n">
-        <v>6.384481198630192</v>
+        <v>6.384481678783307</v>
       </c>
       <c r="D18" t="n">
-        <v>6.278661165838754</v>
+        <v>6.278661638033537</v>
       </c>
       <c r="E18" t="n">
-        <v>6.305116384282329</v>
+        <v>6.305116858466711</v>
       </c>
       <c r="F18" t="n">
         <v>5881000</v>
@@ -792,16 +792,16 @@
         <v>44438</v>
       </c>
       <c r="B19" t="n">
-        <v>6.269843101501465</v>
+        <v>6.269844055175781</v>
       </c>
       <c r="C19" t="n">
-        <v>6.419755026338443</v>
+        <v>6.419756002815109</v>
       </c>
       <c r="D19" t="n">
-        <v>6.252206429196611</v>
+        <v>6.252207380188302</v>
       </c>
       <c r="E19" t="n">
-        <v>6.393299807635444</v>
+        <v>6.39330078008814</v>
       </c>
       <c r="F19" t="n">
         <v>4966000</v>
@@ -812,16 +812,16 @@
         <v>44439</v>
       </c>
       <c r="B20" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="C20" t="n">
-        <v>6.305116845737266</v>
+        <v>6.305116365542087</v>
       </c>
       <c r="D20" t="n">
-        <v>6.181660131778449</v>
+        <v>6.181659660985684</v>
       </c>
       <c r="E20" t="n">
-        <v>6.305116845737266</v>
+        <v>6.305116365542087</v>
       </c>
       <c r="F20" t="n">
         <v>3704100</v>
@@ -852,16 +852,16 @@
         <v>44441</v>
       </c>
       <c r="B22" t="n">
-        <v>5.996474742889404</v>
+        <v>5.996475219726562</v>
       </c>
       <c r="C22" t="n">
-        <v>6.252206713170811</v>
+        <v>6.252207210343668</v>
       </c>
       <c r="D22" t="n">
-        <v>5.970019522984813</v>
+        <v>5.970019997718263</v>
       </c>
       <c r="E22" t="n">
-        <v>6.234570040064902</v>
+        <v>6.234570535835299</v>
       </c>
       <c r="F22" t="n">
         <v>3746900</v>
@@ -912,16 +912,16 @@
         <v>44447</v>
       </c>
       <c r="B25" t="n">
-        <v>5.758378982543945</v>
+        <v>5.758379936218262</v>
       </c>
       <c r="C25" t="n">
-        <v>6.111112416290331</v>
+        <v>6.11111342838262</v>
       </c>
       <c r="D25" t="n">
-        <v>5.661377078017978</v>
+        <v>5.661378015627318</v>
       </c>
       <c r="E25" t="n">
-        <v>6.111112416290331</v>
+        <v>6.11111342838262</v>
       </c>
       <c r="F25" t="n">
         <v>10251100</v>
@@ -952,16 +952,16 @@
         <v>44449</v>
       </c>
       <c r="B27" t="n">
-        <v>5.731925010681152</v>
+        <v>5.731924057006836</v>
       </c>
       <c r="C27" t="n">
-        <v>5.899473638375429</v>
+        <v>5.899472656824471</v>
       </c>
       <c r="D27" t="n">
-        <v>5.617286409549566</v>
+        <v>5.617285474948753</v>
       </c>
       <c r="E27" t="n">
-        <v>5.767198361722946</v>
+        <v>5.76719740217987</v>
       </c>
       <c r="F27" t="n">
         <v>5905500</v>
@@ -972,16 +972,16 @@
         <v>44452</v>
       </c>
       <c r="B28" t="n">
-        <v>6.128750324249268</v>
+        <v>6.128749847412109</v>
       </c>
       <c r="C28" t="n">
-        <v>6.172842222607351</v>
+        <v>6.172841742339696</v>
       </c>
       <c r="D28" t="n">
-        <v>5.925928348686794</v>
+        <v>5.92592788762986</v>
       </c>
       <c r="E28" t="n">
-        <v>5.952383571799945</v>
+        <v>5.952383108684708</v>
       </c>
       <c r="F28" t="n">
         <v>8999600</v>
@@ -992,16 +992,16 @@
         <v>44453</v>
       </c>
       <c r="B29" t="n">
-        <v>6.340389728546143</v>
+        <v>6.340390205383301</v>
       </c>
       <c r="C29" t="n">
-        <v>6.50793832404497</v>
+        <v>6.507938813482836</v>
       </c>
       <c r="D29" t="n">
-        <v>6.225751149443035</v>
+        <v>6.225751617658651</v>
       </c>
       <c r="E29" t="n">
-        <v>6.225751149443035</v>
+        <v>6.225751617658651</v>
       </c>
       <c r="F29" t="n">
         <v>9730300</v>
@@ -1012,16 +1012,16 @@
         <v>44454</v>
       </c>
       <c r="B30" t="n">
-        <v>6.384480953216553</v>
+        <v>6.384482383728027</v>
       </c>
       <c r="C30" t="n">
-        <v>6.50793807388575</v>
+        <v>6.507939532059118</v>
       </c>
       <c r="D30" t="n">
-        <v>6.296297595946708</v>
+        <v>6.296299006699756</v>
       </c>
       <c r="E30" t="n">
-        <v>6.384480953216553</v>
+        <v>6.384482383728027</v>
       </c>
       <c r="F30" t="n">
         <v>7265900</v>
@@ -1032,16 +1032,16 @@
         <v>44455</v>
       </c>
       <c r="B31" t="n">
-        <v>6.278661727905273</v>
+        <v>6.278661251068115</v>
       </c>
       <c r="C31" t="n">
-        <v>6.428573664692329</v>
+        <v>6.428573176470008</v>
       </c>
       <c r="D31" t="n">
-        <v>6.172841685640813</v>
+        <v>6.172841216840228</v>
       </c>
       <c r="E31" t="n">
-        <v>6.349208422748248</v>
+        <v>6.349207940553374</v>
       </c>
       <c r="F31" t="n">
         <v>6142600</v>
@@ -1052,16 +1052,16 @@
         <v>44456</v>
       </c>
       <c r="B32" t="n">
-        <v>6.384480953216553</v>
+        <v>6.384482383728027</v>
       </c>
       <c r="C32" t="n">
-        <v>6.384480953216553</v>
+        <v>6.384482383728027</v>
       </c>
       <c r="D32" t="n">
-        <v>5.978837509775269</v>
+        <v>5.978838849397976</v>
       </c>
       <c r="E32" t="n">
-        <v>6.26102425303877</v>
+        <v>6.261025655888447</v>
       </c>
       <c r="F32" t="n">
         <v>16008100</v>
@@ -1072,16 +1072,16 @@
         <v>44459</v>
       </c>
       <c r="B33" t="n">
-        <v>6.269843101501465</v>
+        <v>6.269844055175781</v>
       </c>
       <c r="C33" t="n">
-        <v>6.322753118416027</v>
+        <v>6.32275408013822</v>
       </c>
       <c r="D33" t="n">
-        <v>6.067021159749924</v>
+        <v>6.067022082574015</v>
       </c>
       <c r="E33" t="n">
-        <v>6.164022647180904</v>
+        <v>6.164023584759403</v>
       </c>
       <c r="F33" t="n">
         <v>9065700</v>
@@ -1112,16 +1112,16 @@
         <v>44461</v>
       </c>
       <c r="B35" t="n">
-        <v>6.44620943069458</v>
+        <v>6.446209907531738</v>
       </c>
       <c r="C35" t="n">
-        <v>6.560848003917575</v>
+        <v>6.560848489234745</v>
       </c>
       <c r="D35" t="n">
-        <v>6.402117962872096</v>
+        <v>6.402118436447734</v>
       </c>
       <c r="E35" t="n">
-        <v>6.463846101921855</v>
+        <v>6.463846580063628</v>
       </c>
       <c r="F35" t="n">
         <v>10254600</v>
@@ -1172,16 +1172,16 @@
         <v>44466</v>
       </c>
       <c r="B38" t="n">
-        <v>6.305116176605225</v>
+        <v>6.305116653442383</v>
       </c>
       <c r="C38" t="n">
-        <v>6.340389519707209</v>
+        <v>6.340389999211985</v>
       </c>
       <c r="D38" t="n">
-        <v>6.102294243523106</v>
+        <v>6.102294705021446</v>
       </c>
       <c r="E38" t="n">
-        <v>6.172840929727075</v>
+        <v>6.17284139656065</v>
       </c>
       <c r="F38" t="n">
         <v>6343700</v>
@@ -1192,16 +1192,16 @@
         <v>44467</v>
       </c>
       <c r="B39" t="n">
-        <v>6.119932174682617</v>
+        <v>6.119931221008301</v>
       </c>
       <c r="C39" t="n">
-        <v>6.278662251311475</v>
+        <v>6.278661272902115</v>
       </c>
       <c r="D39" t="n">
-        <v>6.119932174682617</v>
+        <v>6.119931221008301</v>
       </c>
       <c r="E39" t="n">
-        <v>6.261025576130491</v>
+        <v>6.261024600469469</v>
       </c>
       <c r="F39" t="n">
         <v>6782400</v>
@@ -1212,16 +1212,16 @@
         <v>44468</v>
       </c>
       <c r="B40" t="n">
-        <v>6.040566921234131</v>
+        <v>6.040565967559814</v>
       </c>
       <c r="C40" t="n">
-        <v>6.252207443726178</v>
+        <v>6.25220645663842</v>
       </c>
       <c r="D40" t="n">
-        <v>6.040566921234131</v>
+        <v>6.040565967559814</v>
       </c>
       <c r="E40" t="n">
-        <v>6.216934093392754</v>
+        <v>6.216933111873892</v>
       </c>
       <c r="F40" t="n">
         <v>6482600</v>
@@ -1232,16 +1232,16 @@
         <v>44469</v>
       </c>
       <c r="B41" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="C41" t="n">
-        <v>6.349208319048255</v>
+        <v>6.349207835495088</v>
       </c>
       <c r="D41" t="n">
-        <v>6.058202997328168</v>
+        <v>6.058202535937849</v>
       </c>
       <c r="E41" t="n">
-        <v>6.084658217707932</v>
+        <v>6.084657754302794</v>
       </c>
       <c r="F41" t="n">
         <v>15990100</v>
@@ -1252,16 +1252,16 @@
         <v>44470</v>
       </c>
       <c r="B42" t="n">
-        <v>6.499120235443115</v>
+        <v>6.499119281768799</v>
       </c>
       <c r="C42" t="n">
-        <v>6.569666928939093</v>
+        <v>6.569665964912827</v>
       </c>
       <c r="D42" t="n">
-        <v>6.331571628144438</v>
+        <v>6.331570699056035</v>
       </c>
       <c r="E42" t="n">
-        <v>6.331571628144438</v>
+        <v>6.331570699056035</v>
       </c>
       <c r="F42" t="n">
         <v>15528000</v>
@@ -1292,16 +1292,16 @@
         <v>44474</v>
       </c>
       <c r="B44" t="n">
-        <v>6.287480354309082</v>
+        <v>6.287479877471924</v>
       </c>
       <c r="C44" t="n">
-        <v>6.366845176762705</v>
+        <v>6.366844693906587</v>
       </c>
       <c r="D44" t="n">
-        <v>6.243388459230366</v>
+        <v>6.2433879857371</v>
       </c>
       <c r="E44" t="n">
-        <v>6.29629848102994</v>
+        <v>6.296298003524023</v>
       </c>
       <c r="F44" t="n">
         <v>12888200</v>
@@ -1312,16 +1312,16 @@
         <v>44475</v>
       </c>
       <c r="B45" t="n">
-        <v>6.178094863891602</v>
+        <v>6.178093433380127</v>
       </c>
       <c r="C45" t="n">
-        <v>6.275318223282931</v>
+        <v>6.275316770259803</v>
       </c>
       <c r="D45" t="n">
-        <v>6.080871925951673</v>
+        <v>6.080870517951754</v>
       </c>
       <c r="E45" t="n">
-        <v>6.248803029827096</v>
+        <v>6.248801582943448</v>
       </c>
       <c r="F45" t="n">
         <v>10376100</v>
@@ -1352,16 +1352,16 @@
         <v>44477</v>
       </c>
       <c r="B47" t="n">
-        <v>6.310670852661133</v>
+        <v>6.310671329498291</v>
       </c>
       <c r="C47" t="n">
-        <v>6.655371671310609</v>
+        <v>6.655372174193518</v>
       </c>
       <c r="D47" t="n">
-        <v>6.292993920021518</v>
+        <v>6.292994395522999</v>
       </c>
       <c r="E47" t="n">
-        <v>6.363701650579979</v>
+        <v>6.363702131424168</v>
       </c>
       <c r="F47" t="n">
         <v>20480700</v>
@@ -1372,16 +1372,16 @@
         <v>44480</v>
       </c>
       <c r="B48" t="n">
-        <v>6.213448524475098</v>
+        <v>6.213447570800781</v>
       </c>
       <c r="C48" t="n">
-        <v>6.407894801993546</v>
+        <v>6.407893818474543</v>
       </c>
       <c r="D48" t="n">
-        <v>6.213448524475098</v>
+        <v>6.213447570800781</v>
       </c>
       <c r="E48" t="n">
-        <v>6.363702255468219</v>
+        <v>6.363701278732132</v>
       </c>
       <c r="F48" t="n">
         <v>10407400</v>
@@ -1412,16 +1412,16 @@
         <v>44483</v>
       </c>
       <c r="B50" t="n">
-        <v>6.319509029388428</v>
+        <v>6.319509506225586</v>
       </c>
       <c r="C50" t="n">
-        <v>6.381378078003224</v>
+        <v>6.381378559508698</v>
       </c>
       <c r="D50" t="n">
-        <v>6.239962628082221</v>
+        <v>6.239963098917224</v>
       </c>
       <c r="E50" t="n">
-        <v>6.248801304427927</v>
+        <v>6.24880177592985</v>
       </c>
       <c r="F50" t="n">
         <v>10992200</v>
@@ -1432,16 +1432,16 @@
         <v>44484</v>
       </c>
       <c r="B51" t="n">
-        <v>6.275317192077637</v>
+        <v>6.275317668914795</v>
       </c>
       <c r="C51" t="n">
-        <v>6.354863602276304</v>
+        <v>6.354864085157887</v>
       </c>
       <c r="D51" t="n">
-        <v>6.222286392428969</v>
+        <v>6.222286865236521</v>
       </c>
       <c r="E51" t="n">
-        <v>6.337186669060081</v>
+        <v>6.337187150598463</v>
       </c>
       <c r="F51" t="n">
         <v>34203500</v>
@@ -1452,16 +1452,16 @@
         <v>44487</v>
       </c>
       <c r="B52" t="n">
-        <v>6.169255256652832</v>
+        <v>6.16925573348999</v>
       </c>
       <c r="C52" t="n">
-        <v>6.266478594770578</v>
+        <v>6.266479079122371</v>
       </c>
       <c r="D52" t="n">
-        <v>6.151578324399725</v>
+        <v>6.151578799870589</v>
       </c>
       <c r="E52" t="n">
-        <v>6.25763991791837</v>
+        <v>6.257640401587</v>
       </c>
       <c r="F52" t="n">
         <v>7596500</v>
@@ -1492,16 +1492,16 @@
         <v>44489</v>
       </c>
       <c r="B54" t="n">
-        <v>5.904100894927979</v>
+        <v>5.904101371765137</v>
       </c>
       <c r="C54" t="n">
-        <v>6.045516775446618</v>
+        <v>6.045517263705048</v>
       </c>
       <c r="D54" t="n">
-        <v>5.842231842311679</v>
+        <v>5.842232314152062</v>
       </c>
       <c r="E54" t="n">
-        <v>6.010162910679786</v>
+        <v>6.010163396082907</v>
       </c>
       <c r="F54" t="n">
         <v>6234400</v>
@@ -1532,16 +1532,16 @@
         <v>44491</v>
       </c>
       <c r="B56" t="n">
-        <v>5.630108833312988</v>
+        <v>5.63010835647583</v>
       </c>
       <c r="C56" t="n">
-        <v>5.656624445444495</v>
+        <v>5.656623966361621</v>
       </c>
       <c r="D56" t="n">
-        <v>5.197023732958769</v>
+        <v>5.197023292801376</v>
       </c>
       <c r="E56" t="n">
-        <v>5.603593642632838</v>
+        <v>5.60359316804136</v>
       </c>
       <c r="F56" t="n">
         <v>18890200</v>
@@ -1552,16 +1552,16 @@
         <v>44494</v>
       </c>
       <c r="B57" t="n">
-        <v>5.859909057617188</v>
+        <v>5.859908580780029</v>
       </c>
       <c r="C57" t="n">
-        <v>5.877585990854064</v>
+        <v>5.877585512578483</v>
       </c>
       <c r="D57" t="n">
-        <v>5.550562515246201</v>
+        <v>5.550562063581435</v>
       </c>
       <c r="E57" t="n">
-        <v>5.683139303797101</v>
+        <v>5.683138841344191</v>
       </c>
       <c r="F57" t="n">
         <v>11428100</v>
@@ -1572,16 +1572,16 @@
         <v>44495</v>
       </c>
       <c r="B58" t="n">
-        <v>5.81571626663208</v>
+        <v>5.815716743469238</v>
       </c>
       <c r="C58" t="n">
-        <v>5.868747064088904</v>
+        <v>5.868747545274117</v>
       </c>
       <c r="D58" t="n">
-        <v>5.683139062264364</v>
+        <v>5.683139528231368</v>
       </c>
       <c r="E58" t="n">
-        <v>5.833393199117688</v>
+        <v>5.833393677404199</v>
       </c>
       <c r="F58" t="n">
         <v>8470300</v>
@@ -1592,16 +1592,16 @@
         <v>44496</v>
       </c>
       <c r="B59" t="n">
-        <v>5.859909057617188</v>
+        <v>5.859908580780029</v>
       </c>
       <c r="C59" t="n">
-        <v>5.96597065703844</v>
+        <v>5.965970171570753</v>
       </c>
       <c r="D59" t="n">
-        <v>5.789201324669686</v>
+        <v>5.789200853586213</v>
       </c>
       <c r="E59" t="n">
-        <v>5.833393447036208</v>
+        <v>5.833392972356699</v>
       </c>
       <c r="F59" t="n">
         <v>7675900</v>
@@ -1652,16 +1652,16 @@
         <v>44501</v>
       </c>
       <c r="B62" t="n">
-        <v>6.00132417678833</v>
+        <v>6.001324653625488</v>
       </c>
       <c r="C62" t="n">
-        <v>6.063193650268579</v>
+        <v>6.063194132021597</v>
       </c>
       <c r="D62" t="n">
-        <v>5.948293380141535</v>
+        <v>5.948293852765114</v>
       </c>
       <c r="E62" t="n">
-        <v>5.965970312357133</v>
+        <v>5.965970786385239</v>
       </c>
       <c r="F62" t="n">
         <v>5059700</v>
@@ -1692,16 +1692,16 @@
         <v>44504</v>
       </c>
       <c r="B64" t="n">
-        <v>5.965970516204834</v>
+        <v>5.965970993041992</v>
       </c>
       <c r="C64" t="n">
-        <v>6.160416777220335</v>
+        <v>6.160417269598838</v>
       </c>
       <c r="D64" t="n">
-        <v>5.842231986467696</v>
+        <v>5.842232453414908</v>
       </c>
       <c r="E64" t="n">
-        <v>6.098547723077428</v>
+        <v>6.098548210510975</v>
       </c>
       <c r="F64" t="n">
         <v>8687600</v>
@@ -1712,16 +1712,16 @@
         <v>44505</v>
       </c>
       <c r="B65" t="n">
-        <v>5.965970516204834</v>
+        <v>5.965970993041992</v>
       </c>
       <c r="C65" t="n">
-        <v>6.054355180302789</v>
+        <v>6.054355664204195</v>
       </c>
       <c r="D65" t="n">
-        <v>5.939454906249786</v>
+        <v>5.939455380967654</v>
       </c>
       <c r="E65" t="n">
-        <v>6.001324381844015</v>
+        <v>6.001324861506873</v>
       </c>
       <c r="F65" t="n">
         <v>3123600</v>
@@ -1732,16 +1732,16 @@
         <v>44508</v>
       </c>
       <c r="B66" t="n">
-        <v>5.983648300170898</v>
+        <v>5.98364782333374</v>
       </c>
       <c r="C66" t="n">
-        <v>6.03667910617306</v>
+        <v>6.036678625109875</v>
       </c>
       <c r="D66" t="n">
-        <v>5.939455751110073</v>
+        <v>5.93945527779462</v>
       </c>
       <c r="E66" t="n">
-        <v>6.010163913897671</v>
+        <v>6.010163434947482</v>
       </c>
       <c r="F66" t="n">
         <v>3898000</v>
@@ -1752,16 +1752,16 @@
         <v>44509</v>
       </c>
       <c r="B67" t="n">
-        <v>5.948294162750244</v>
+        <v>5.948293209075928</v>
       </c>
       <c r="C67" t="n">
-        <v>6.169256055242525</v>
+        <v>6.169255066141971</v>
       </c>
       <c r="D67" t="n">
-        <v>5.948294162750244</v>
+        <v>5.948293209075928</v>
       </c>
       <c r="E67" t="n">
-        <v>5.992486709829246</v>
+        <v>5.992485749069655</v>
       </c>
       <c r="F67" t="n">
         <v>5176300</v>
@@ -1772,16 +1772,16 @@
         <v>44510</v>
       </c>
       <c r="B68" t="n">
-        <v>5.745009422302246</v>
+        <v>5.745008945465088</v>
       </c>
       <c r="C68" t="n">
-        <v>6.010163871912132</v>
+        <v>6.010163373067091</v>
       </c>
       <c r="D68" t="n">
-        <v>5.745009422302246</v>
+        <v>5.745008945465088</v>
       </c>
       <c r="E68" t="n">
-        <v>5.957132644829051</v>
+        <v>5.957132150385616</v>
       </c>
       <c r="F68" t="n">
         <v>10074000</v>
@@ -1812,16 +1812,16 @@
         <v>44512</v>
       </c>
       <c r="B70" t="n">
-        <v>5.762685775756836</v>
+        <v>5.762686252593994</v>
       </c>
       <c r="C70" t="n">
-        <v>6.080870998876915</v>
+        <v>6.080871502042515</v>
       </c>
       <c r="D70" t="n">
-        <v>5.532885641218299</v>
+        <v>5.532886099040496</v>
       </c>
       <c r="E70" t="n">
-        <v>6.080870998876915</v>
+        <v>6.080871502042515</v>
       </c>
       <c r="F70" t="n">
         <v>20568500</v>
@@ -1832,16 +1832,16 @@
         <v>44516</v>
       </c>
       <c r="B71" t="n">
-        <v>5.320761203765869</v>
+        <v>5.320762157440186</v>
       </c>
       <c r="C71" t="n">
-        <v>5.815715685342779</v>
+        <v>5.815716727730977</v>
       </c>
       <c r="D71" t="n">
-        <v>5.223537874086983</v>
+        <v>5.223538810335335</v>
       </c>
       <c r="E71" t="n">
-        <v>5.789200499990256</v>
+        <v>5.789201537625966</v>
       </c>
       <c r="F71" t="n">
         <v>27445700</v>
@@ -1852,16 +1852,16 @@
         <v>44517</v>
       </c>
       <c r="B72" t="n">
-        <v>5.170507907867432</v>
+        <v>5.17050838470459</v>
       </c>
       <c r="C72" t="n">
-        <v>5.462177522044113</v>
+        <v>5.462178025779772</v>
       </c>
       <c r="D72" t="n">
-        <v>5.002576828488149</v>
+        <v>5.002577289838284</v>
       </c>
       <c r="E72" t="n">
-        <v>5.364954598286112</v>
+        <v>5.364955093055631</v>
       </c>
       <c r="F72" t="n">
         <v>24600900</v>
@@ -1872,16 +1872,16 @@
         <v>44518</v>
       </c>
       <c r="B73" t="n">
-        <v>5.161669731140137</v>
+        <v>5.161669254302979</v>
       </c>
       <c r="C73" t="n">
-        <v>5.338439069281368</v>
+        <v>5.338438576114187</v>
       </c>
       <c r="D73" t="n">
-        <v>5.073284640618174</v>
+        <v>5.073284171946066</v>
       </c>
       <c r="E73" t="n">
-        <v>5.214700532582506</v>
+        <v>5.214700050846341</v>
       </c>
       <c r="F73" t="n">
         <v>17735600</v>
@@ -1972,16 +1972,16 @@
         <v>44525</v>
       </c>
       <c r="B78" t="n">
-        <v>5.37379264831543</v>
+        <v>5.373792171478271</v>
       </c>
       <c r="C78" t="n">
-        <v>5.37379264831543</v>
+        <v>5.373792171478271</v>
       </c>
       <c r="D78" t="n">
-        <v>4.799291698032407</v>
+        <v>4.799291272172914</v>
       </c>
       <c r="E78" t="n">
-        <v>4.949545838108879</v>
+        <v>4.949545398916761</v>
       </c>
       <c r="F78" t="n">
         <v>20546100</v>
@@ -1992,16 +1992,16 @@
         <v>44526</v>
       </c>
       <c r="B79" t="n">
-        <v>5.223539352416992</v>
+        <v>5.223538875579834</v>
       </c>
       <c r="C79" t="n">
-        <v>5.338439645332938</v>
+        <v>5.338439158006967</v>
       </c>
       <c r="D79" t="n">
-        <v>5.020254380893162</v>
+        <v>5.02025392261312</v>
       </c>
       <c r="E79" t="n">
-        <v>5.037931316614738</v>
+        <v>5.037930856721036</v>
       </c>
       <c r="F79" t="n">
         <v>8564200</v>
@@ -2032,16 +2032,16 @@
         <v>44530</v>
       </c>
       <c r="B81" t="n">
-        <v>4.825806617736816</v>
+        <v>4.825807094573975</v>
       </c>
       <c r="C81" t="n">
-        <v>5.126314854902876</v>
+        <v>5.126315361433205</v>
       </c>
       <c r="D81" t="n">
-        <v>4.790452757064487</v>
+        <v>4.790453230408336</v>
       </c>
       <c r="E81" t="n">
-        <v>5.07328364244312</v>
+        <v>5.073284143733442</v>
       </c>
       <c r="F81" t="n">
         <v>11282700</v>
@@ -2052,16 +2052,16 @@
         <v>44531</v>
       </c>
       <c r="B82" t="n">
-        <v>4.852322578430176</v>
+        <v>4.852322101593018</v>
       </c>
       <c r="C82" t="n">
-        <v>5.152830863649267</v>
+        <v>5.152830357281196</v>
       </c>
       <c r="D82" t="n">
-        <v>4.852322578430176</v>
+        <v>4.852322101593018</v>
       </c>
       <c r="E82" t="n">
-        <v>4.896515122062865</v>
+        <v>4.896514640882911</v>
       </c>
       <c r="F82" t="n">
         <v>12492100</v>
@@ -2072,16 +2072,16 @@
         <v>44532</v>
       </c>
       <c r="B83" t="n">
-        <v>5.029092788696289</v>
+        <v>5.029092311859131</v>
       </c>
       <c r="C83" t="n">
-        <v>5.029092788696289</v>
+        <v>5.029092311859131</v>
       </c>
       <c r="D83" t="n">
-        <v>4.746261410928263</v>
+        <v>4.746260960907972</v>
       </c>
       <c r="E83" t="n">
-        <v>4.905354245307752</v>
+        <v>4.905353780202955</v>
       </c>
       <c r="F83" t="n">
         <v>18379200</v>
@@ -2092,16 +2092,16 @@
         <v>44533</v>
       </c>
       <c r="B84" t="n">
-        <v>5.320761203765869</v>
+        <v>5.320762157440186</v>
       </c>
       <c r="C84" t="n">
-        <v>5.329599879850892</v>
+        <v>5.329600835109421</v>
       </c>
       <c r="D84" t="n">
-        <v>4.976060844024164</v>
+        <v>4.976061735915614</v>
       </c>
       <c r="E84" t="n">
-        <v>5.020252960095459</v>
+        <v>5.020253859907747</v>
       </c>
       <c r="F84" t="n">
         <v>10548200</v>
@@ -2112,16 +2112,16 @@
         <v>44536</v>
       </c>
       <c r="B85" t="n">
-        <v>5.152830600738525</v>
+        <v>5.152831077575684</v>
       </c>
       <c r="C85" t="n">
-        <v>5.417985006103135</v>
+        <v>5.417985507477384</v>
       </c>
       <c r="D85" t="n">
-        <v>5.152830600738525</v>
+        <v>5.152831077575684</v>
       </c>
       <c r="E85" t="n">
-        <v>5.373792464725264</v>
+        <v>5.373792962009984</v>
       </c>
       <c r="F85" t="n">
         <v>5884400</v>
@@ -2192,16 +2192,16 @@
         <v>44540</v>
       </c>
       <c r="B89" t="n">
-        <v>5.444499969482422</v>
+        <v>5.44450044631958</v>
       </c>
       <c r="C89" t="n">
-        <v>5.568238911662507</v>
+        <v>5.568239399336901</v>
       </c>
       <c r="D89" t="n">
-        <v>5.2412150461309</v>
+        <v>5.241215505164072</v>
       </c>
       <c r="E89" t="n">
-        <v>5.267730654155574</v>
+        <v>5.267731115511021</v>
       </c>
       <c r="F89" t="n">
         <v>8741300</v>
@@ -2232,16 +2232,16 @@
         <v>44544</v>
       </c>
       <c r="B91" t="n">
-        <v>5.453339099884033</v>
+        <v>5.453338623046875</v>
       </c>
       <c r="C91" t="n">
-        <v>5.60359324114393</v>
+        <v>5.603592751168627</v>
       </c>
       <c r="D91" t="n">
-        <v>5.426823489652329</v>
+        <v>5.426823015133682</v>
       </c>
       <c r="E91" t="n">
-        <v>5.497531221668439</v>
+        <v>5.497530740967144</v>
       </c>
       <c r="F91" t="n">
         <v>6640900</v>
@@ -2252,16 +2252,16 @@
         <v>44545</v>
       </c>
       <c r="B92" t="n">
-        <v>5.479854106903076</v>
+        <v>5.479854583740234</v>
       </c>
       <c r="C92" t="n">
-        <v>5.524046648672985</v>
+        <v>5.524047129355619</v>
       </c>
       <c r="D92" t="n">
-        <v>5.329600392078274</v>
+        <v>5.329600855840895</v>
       </c>
       <c r="E92" t="n">
-        <v>5.479854106903076</v>
+        <v>5.479854583740234</v>
       </c>
       <c r="F92" t="n">
         <v>4791400</v>
@@ -2272,16 +2272,16 @@
         <v>44546</v>
       </c>
       <c r="B93" t="n">
-        <v>5.400308132171631</v>
+        <v>5.400308609008789</v>
       </c>
       <c r="C93" t="n">
-        <v>5.550562268737735</v>
+        <v>5.550562758842054</v>
       </c>
       <c r="D93" t="n">
-        <v>5.347277334816178</v>
+        <v>5.347277806970816</v>
       </c>
       <c r="E93" t="n">
-        <v>5.515207982382787</v>
+        <v>5.515208469365389</v>
       </c>
       <c r="F93" t="n">
         <v>9238300</v>
@@ -2312,16 +2312,16 @@
         <v>44550</v>
       </c>
       <c r="B95" t="n">
-        <v>5.143992900848389</v>
+        <v>5.143993377685547</v>
       </c>
       <c r="C95" t="n">
-        <v>5.179346769188129</v>
+        <v>5.179347249302515</v>
       </c>
       <c r="D95" t="n">
-        <v>4.949546203528466</v>
+        <v>4.94954666234083</v>
       </c>
       <c r="E95" t="n">
-        <v>5.179346769188129</v>
+        <v>5.179347249302515</v>
       </c>
       <c r="F95" t="n">
         <v>8433600</v>
@@ -2332,16 +2332,16 @@
         <v>44551</v>
       </c>
       <c r="B96" t="n">
-        <v>5.082123279571533</v>
+        <v>5.082122802734375</v>
       </c>
       <c r="C96" t="n">
-        <v>5.223538749008224</v>
+        <v>5.223538258902567</v>
       </c>
       <c r="D96" t="n">
-        <v>5.020253800967309</v>
+        <v>5.020253329935139</v>
       </c>
       <c r="E96" t="n">
-        <v>5.170507947969465</v>
+        <v>5.170507462839494</v>
       </c>
       <c r="F96" t="n">
         <v>5049800</v>
@@ -2412,16 +2412,16 @@
         <v>44558</v>
       </c>
       <c r="B100" t="n">
-        <v>5.347277641296387</v>
+        <v>5.347277164459229</v>
       </c>
       <c r="C100" t="n">
-        <v>5.347277641296387</v>
+        <v>5.347277164459229</v>
       </c>
       <c r="D100" t="n">
-        <v>5.188184818660282</v>
+        <v>5.188184356010038</v>
       </c>
       <c r="E100" t="n">
-        <v>5.214700429583412</v>
+        <v>5.21469996456867</v>
       </c>
       <c r="F100" t="n">
         <v>4379800</v>
@@ -2432,16 +2432,16 @@
         <v>44559</v>
       </c>
       <c r="B101" t="n">
-        <v>5.311923980712891</v>
+        <v>5.311923503875732</v>
       </c>
       <c r="C101" t="n">
-        <v>5.382631717319493</v>
+        <v>5.38263123413509</v>
       </c>
       <c r="D101" t="n">
-        <v>5.214700632153136</v>
+        <v>5.214700164043457</v>
       </c>
       <c r="E101" t="n">
-        <v>5.320762237063039</v>
+        <v>5.320761759432494</v>
       </c>
       <c r="F101" t="n">
         <v>5394800</v>
@@ -2452,16 +2452,16 @@
         <v>44560</v>
       </c>
       <c r="B102" t="n">
-        <v>5.70081615447998</v>
+        <v>5.700815677642822</v>
       </c>
       <c r="C102" t="n">
-        <v>5.70965483169609</v>
+        <v>5.709654354119633</v>
       </c>
       <c r="D102" t="n">
-        <v>5.258892408506298</v>
+        <v>5.258891968633261</v>
       </c>
       <c r="E102" t="n">
-        <v>5.320761884665091</v>
+        <v>5.320761439617065</v>
       </c>
       <c r="F102" t="n">
         <v>23096200</v>
@@ -2472,16 +2472,16 @@
         <v>44564</v>
       </c>
       <c r="B103" t="n">
-        <v>5.541723728179932</v>
+        <v>5.54172420501709</v>
       </c>
       <c r="C103" t="n">
-        <v>5.745008667104768</v>
+        <v>5.745009161433563</v>
       </c>
       <c r="D103" t="n">
-        <v>5.506369862406162</v>
+        <v>5.5063703362013</v>
       </c>
       <c r="E103" t="n">
-        <v>5.691977868444114</v>
+        <v>5.691978358209878</v>
       </c>
       <c r="F103" t="n">
         <v>7451800</v>
@@ -2532,16 +2532,16 @@
         <v>44567</v>
       </c>
       <c r="B106" t="n">
-        <v>4.932945251464844</v>
+        <v>4.932944774627686</v>
       </c>
       <c r="C106" t="n">
-        <v>5.190239127268864</v>
+        <v>5.190238625560705</v>
       </c>
       <c r="D106" t="n">
-        <v>4.870839672696422</v>
+        <v>4.870839201862625</v>
       </c>
       <c r="E106" t="n">
-        <v>5.145878362199686</v>
+        <v>5.145877864779607</v>
       </c>
       <c r="F106" t="n">
         <v>8427100</v>
@@ -2552,16 +2552,16 @@
         <v>44568</v>
       </c>
       <c r="B107" t="n">
-        <v>5.163622379302979</v>
+        <v>5.163623332977295</v>
       </c>
       <c r="C107" t="n">
-        <v>5.278960698586984</v>
+        <v>5.278961673563245</v>
       </c>
       <c r="D107" t="n">
-        <v>4.941817300823532</v>
+        <v>4.941818213532458</v>
       </c>
       <c r="E107" t="n">
-        <v>4.977306079535475</v>
+        <v>4.977306998798857</v>
       </c>
       <c r="F107" t="n">
         <v>10961100</v>
@@ -2592,16 +2592,16 @@
         <v>44572</v>
       </c>
       <c r="B109" t="n">
-        <v>5.234600067138672</v>
+        <v>5.23460054397583</v>
       </c>
       <c r="C109" t="n">
-        <v>5.234600067138672</v>
+        <v>5.23460054397583</v>
       </c>
       <c r="D109" t="n">
-        <v>5.021666966502512</v>
+        <v>5.021667423942884</v>
       </c>
       <c r="E109" t="n">
-        <v>5.021666966502512</v>
+        <v>5.021667423942884</v>
       </c>
       <c r="F109" t="n">
         <v>5425200</v>
@@ -2612,16 +2612,16 @@
         <v>44573</v>
       </c>
       <c r="B110" t="n">
-        <v>5.438661098480225</v>
+        <v>5.438661575317383</v>
       </c>
       <c r="C110" t="n">
-        <v>5.518510645991364</v>
+        <v>5.518511129829369</v>
       </c>
       <c r="D110" t="n">
-        <v>5.225727984644668</v>
+        <v>5.225728442812817</v>
       </c>
       <c r="E110" t="n">
-        <v>5.261216766440652</v>
+        <v>5.261217227720296</v>
       </c>
       <c r="F110" t="n">
         <v>9077500</v>
@@ -2652,16 +2652,16 @@
         <v>44575</v>
       </c>
       <c r="B112" t="n">
-        <v>5.491893768310547</v>
+        <v>5.491894721984863</v>
       </c>
       <c r="C112" t="n">
-        <v>5.500765751417357</v>
+        <v>5.500766706632305</v>
       </c>
       <c r="D112" t="n">
-        <v>5.332194264851456</v>
+        <v>5.332195190793751</v>
       </c>
       <c r="E112" t="n">
-        <v>5.420916211217618</v>
+        <v>5.420917152566591</v>
       </c>
       <c r="F112" t="n">
         <v>4745900</v>
@@ -2672,16 +2672,16 @@
         <v>44578</v>
       </c>
       <c r="B113" t="n">
-        <v>5.48302173614502</v>
+        <v>5.483021259307861</v>
       </c>
       <c r="C113" t="n">
-        <v>5.62497728307338</v>
+        <v>5.624976793890898</v>
       </c>
       <c r="D113" t="n">
-        <v>5.447532955177839</v>
+        <v>5.447532481427003</v>
       </c>
       <c r="E113" t="n">
-        <v>5.447532955177839</v>
+        <v>5.447532481427003</v>
       </c>
       <c r="F113" t="n">
         <v>3137800</v>
@@ -2692,16 +2692,16 @@
         <v>44579</v>
       </c>
       <c r="B114" t="n">
-        <v>5.48302173614502</v>
+        <v>5.483021259307861</v>
       </c>
       <c r="C114" t="n">
-        <v>5.536254907595789</v>
+        <v>5.536254426129148</v>
       </c>
       <c r="D114" t="n">
-        <v>5.376555393243478</v>
+        <v>5.376554925665286</v>
       </c>
       <c r="E114" t="n">
-        <v>5.474149752433044</v>
+        <v>5.474149276367449</v>
       </c>
       <c r="F114" t="n">
         <v>3854900</v>
@@ -2712,16 +2712,16 @@
         <v>44580</v>
       </c>
       <c r="B115" t="n">
-        <v>5.651593208312988</v>
+        <v>5.651593685150146</v>
       </c>
       <c r="C115" t="n">
-        <v>5.749187559749773</v>
+        <v>5.749188044821177</v>
       </c>
       <c r="D115" t="n">
-        <v>5.509638095721016</v>
+        <v>5.509638560581113</v>
       </c>
       <c r="E115" t="n">
-        <v>5.509638095721016</v>
+        <v>5.509638560581113</v>
       </c>
       <c r="F115" t="n">
         <v>12660500</v>
@@ -2812,16 +2812,16 @@
         <v>44587</v>
       </c>
       <c r="B120" t="n">
-        <v>5.518510341644287</v>
+        <v>5.518510818481445</v>
       </c>
       <c r="C120" t="n">
-        <v>5.67821027397838</v>
+        <v>5.678210764614708</v>
       </c>
       <c r="D120" t="n">
-        <v>5.491893968295023</v>
+        <v>5.491894442832344</v>
       </c>
       <c r="E120" t="n">
-        <v>5.598360307811333</v>
+        <v>5.598360791548077</v>
       </c>
       <c r="F120" t="n">
         <v>11610000</v>
@@ -2832,16 +2832,16 @@
         <v>44588</v>
       </c>
       <c r="B121" t="n">
-        <v>5.545127391815186</v>
+        <v>5.545126914978027</v>
       </c>
       <c r="C121" t="n">
-        <v>5.74918809675637</v>
+        <v>5.749187602371603</v>
       </c>
       <c r="D121" t="n">
-        <v>5.527383001083763</v>
+        <v>5.527382525772483</v>
       </c>
       <c r="E121" t="n">
-        <v>5.580616173278031</v>
+        <v>5.580615693389118</v>
       </c>
       <c r="F121" t="n">
         <v>8501200</v>
@@ -2852,16 +2852,16 @@
         <v>44589</v>
       </c>
       <c r="B122" t="n">
-        <v>5.660465240478516</v>
+        <v>5.660465717315674</v>
       </c>
       <c r="C122" t="n">
-        <v>5.731442792086089</v>
+        <v>5.731443274902391</v>
       </c>
       <c r="D122" t="n">
-        <v>5.509637731782632</v>
+        <v>5.509638195914094</v>
       </c>
       <c r="E122" t="n">
-        <v>5.509637731782632</v>
+        <v>5.509638195914094</v>
       </c>
       <c r="F122" t="n">
         <v>15566700</v>
@@ -2872,16 +2872,16 @@
         <v>44592</v>
       </c>
       <c r="B123" t="n">
-        <v>5.695954322814941</v>
+        <v>5.695953845977783</v>
       </c>
       <c r="C123" t="n">
-        <v>5.793548673057267</v>
+        <v>5.793548188049992</v>
       </c>
       <c r="D123" t="n">
-        <v>5.571743600817181</v>
+        <v>5.571743134378331</v>
       </c>
       <c r="E123" t="n">
-        <v>5.607232378530827</v>
+        <v>5.607231909121031</v>
       </c>
       <c r="F123" t="n">
         <v>7514700</v>
@@ -2912,16 +2912,16 @@
         <v>44594</v>
       </c>
       <c r="B125" t="n">
-        <v>5.669337272644043</v>
+        <v>5.669337749481201</v>
       </c>
       <c r="C125" t="n">
-        <v>5.882270352394677</v>
+        <v>5.882270847141231</v>
       </c>
       <c r="D125" t="n">
-        <v>5.651592884586456</v>
+        <v>5.651593359931167</v>
       </c>
       <c r="E125" t="n">
-        <v>5.722570436816806</v>
+        <v>5.722570918131304</v>
       </c>
       <c r="F125" t="n">
         <v>8808600</v>
@@ -2932,16 +2932,16 @@
         <v>44595</v>
       </c>
       <c r="B126" t="n">
-        <v>5.731442928314209</v>
+        <v>5.731443405151367</v>
       </c>
       <c r="C126" t="n">
-        <v>5.793548498976785</v>
+        <v>5.793548980980922</v>
       </c>
       <c r="D126" t="n">
-        <v>5.616104192680678</v>
+        <v>5.616104659922033</v>
       </c>
       <c r="E126" t="n">
-        <v>5.678209763343253</v>
+        <v>5.678210235751588</v>
       </c>
       <c r="F126" t="n">
         <v>8390300</v>
@@ -2952,16 +2952,16 @@
         <v>44596</v>
       </c>
       <c r="B127" t="n">
-        <v>5.660465240478516</v>
+        <v>5.660465717315674</v>
       </c>
       <c r="C127" t="n">
-        <v>5.820164731595556</v>
+        <v>5.820165221885787</v>
       </c>
       <c r="D127" t="n">
-        <v>5.633848447095886</v>
+        <v>5.633848921690848</v>
       </c>
       <c r="E127" t="n">
-        <v>5.722570386605353</v>
+        <v>5.722570868674245</v>
       </c>
       <c r="F127" t="n">
         <v>8483700</v>
@@ -2972,16 +2972,16 @@
         <v>44599</v>
       </c>
       <c r="B128" t="n">
-        <v>5.562871932983398</v>
+        <v>5.56287145614624</v>
       </c>
       <c r="C128" t="n">
-        <v>5.775805050578469</v>
+        <v>5.775804555489152</v>
       </c>
       <c r="D128" t="n">
-        <v>5.553999948907585</v>
+        <v>5.553999472830914</v>
       </c>
       <c r="E128" t="n">
-        <v>5.704827062673674</v>
+        <v>5.704826573668434</v>
       </c>
       <c r="F128" t="n">
         <v>7178800</v>
@@ -2992,16 +2992,16 @@
         <v>44600</v>
       </c>
       <c r="B129" t="n">
-        <v>5.616104602813721</v>
+        <v>5.616104125976562</v>
       </c>
       <c r="C129" t="n">
-        <v>5.695954567631234</v>
+        <v>5.695954084014389</v>
       </c>
       <c r="D129" t="n">
-        <v>5.483021469137738</v>
+        <v>5.483021003600046</v>
       </c>
       <c r="E129" t="n">
-        <v>5.580615823574741</v>
+        <v>5.58061534975077</v>
       </c>
       <c r="F129" t="n">
         <v>9770800</v>
@@ -3032,16 +3032,16 @@
         <v>44602</v>
       </c>
       <c r="B131" t="n">
-        <v>5.704826831817627</v>
+        <v>5.704827308654785</v>
       </c>
       <c r="C131" t="n">
-        <v>5.740315612804078</v>
+        <v>5.740316092607562</v>
       </c>
       <c r="D131" t="n">
-        <v>5.56287170787182</v>
+        <v>5.562872172843679</v>
       </c>
       <c r="E131" t="n">
-        <v>5.678210457607609</v>
+        <v>5.678210932220041</v>
       </c>
       <c r="F131" t="n">
         <v>9667400</v>
@@ -3072,16 +3072,16 @@
         <v>44606</v>
       </c>
       <c r="B133" t="n">
-        <v>5.695954322814941</v>
+        <v>5.695953845977783</v>
       </c>
       <c r="C133" t="n">
-        <v>5.766931878242232</v>
+        <v>5.766931395463184</v>
       </c>
       <c r="D133" t="n">
-        <v>5.642721156244472</v>
+        <v>5.642720683863732</v>
       </c>
       <c r="E133" t="n">
-        <v>5.642721156244472</v>
+        <v>5.642720683863732</v>
       </c>
       <c r="F133" t="n">
         <v>12680200</v>
@@ -3092,16 +3092,16 @@
         <v>44607</v>
       </c>
       <c r="B134" t="n">
-        <v>5.695954322814941</v>
+        <v>5.695953845977783</v>
       </c>
       <c r="C134" t="n">
-        <v>5.81129306191409</v>
+        <v>5.811292575421342</v>
       </c>
       <c r="D134" t="n">
-        <v>5.518510011187112</v>
+        <v>5.518509549204714</v>
       </c>
       <c r="E134" t="n">
-        <v>5.81129306191409</v>
+        <v>5.811292575421342</v>
       </c>
       <c r="F134" t="n">
         <v>17426200</v>
@@ -3112,16 +3112,16 @@
         <v>44608</v>
       </c>
       <c r="B135" t="n">
-        <v>5.704826831817627</v>
+        <v>5.704827308654785</v>
       </c>
       <c r="C135" t="n">
-        <v>5.811293597836623</v>
+        <v>5.811294083572791</v>
       </c>
       <c r="D135" t="n">
-        <v>5.651593660337949</v>
+        <v>5.65159413272562</v>
       </c>
       <c r="E135" t="n">
-        <v>5.71369923859406</v>
+        <v>5.713699716172817</v>
       </c>
       <c r="F135" t="n">
         <v>12029900</v>
@@ -3172,16 +3172,16 @@
         <v>44613</v>
       </c>
       <c r="B138" t="n">
-        <v>5.119261741638184</v>
+        <v>5.119260787963867</v>
       </c>
       <c r="C138" t="n">
-        <v>5.456405598502314</v>
+        <v>5.456404582021004</v>
       </c>
       <c r="D138" t="n">
-        <v>5.074900551976187</v>
+        <v>5.074899606565978</v>
       </c>
       <c r="E138" t="n">
-        <v>5.447533191346051</v>
+        <v>5.447532176517594</v>
       </c>
       <c r="F138" t="n">
         <v>8726900</v>
@@ -3192,16 +3192,16 @@
         <v>44614</v>
       </c>
       <c r="B139" t="n">
-        <v>5.012795448303223</v>
+        <v>5.012794971466064</v>
       </c>
       <c r="C139" t="n">
-        <v>5.234600552891333</v>
+        <v>5.234600054955186</v>
       </c>
       <c r="D139" t="n">
-        <v>4.977306665413898</v>
+        <v>4.977306191952575</v>
       </c>
       <c r="E139" t="n">
-        <v>5.172494971305183</v>
+        <v>5.172494479276767</v>
       </c>
       <c r="F139" t="n">
         <v>7346000</v>
@@ -3232,16 +3232,16 @@
         <v>44616</v>
       </c>
       <c r="B141" t="n">
-        <v>5.119261741638184</v>
+        <v>5.119260787963867</v>
       </c>
       <c r="C141" t="n">
-        <v>5.137006132891051</v>
+        <v>5.137005175911107</v>
       </c>
       <c r="D141" t="n">
-        <v>4.773245900677449</v>
+        <v>4.7732450114629</v>
       </c>
       <c r="E141" t="n">
-        <v>4.924073437856647</v>
+        <v>4.924072520544229</v>
       </c>
       <c r="F141" t="n">
         <v>11357100</v>
@@ -3272,16 +3272,16 @@
         <v>44622</v>
       </c>
       <c r="B143" t="n">
-        <v>5.314449787139893</v>
+        <v>5.314450263977051</v>
       </c>
       <c r="C143" t="n">
-        <v>5.349938990980526</v>
+        <v>5.349939471001941</v>
       </c>
       <c r="D143" t="n">
-        <v>5.03053954089193</v>
+        <v>5.030539992255339</v>
       </c>
       <c r="E143" t="n">
-        <v>5.10151710245392</v>
+        <v>5.101517560185767</v>
       </c>
       <c r="F143" t="n">
         <v>7030100</v>
@@ -3312,16 +3312,16 @@
         <v>44624</v>
       </c>
       <c r="B145" t="n">
-        <v>5.50963830947876</v>
+        <v>5.509639263153076</v>
       </c>
       <c r="C145" t="n">
-        <v>5.536254682592588</v>
+        <v>5.536255640873986</v>
       </c>
       <c r="D145" t="n">
-        <v>5.376555174730749</v>
+        <v>5.376556105369439</v>
       </c>
       <c r="E145" t="n">
-        <v>5.483021513305308</v>
+        <v>5.48302246237247</v>
       </c>
       <c r="F145" t="n">
         <v>9336900</v>
@@ -3332,16 +3332,16 @@
         <v>44627</v>
       </c>
       <c r="B146" t="n">
-        <v>5.48302173614502</v>
+        <v>5.483021259307861</v>
       </c>
       <c r="C146" t="n">
-        <v>5.5894885021062</v>
+        <v>5.58948801601004</v>
       </c>
       <c r="D146" t="n">
-        <v>5.403172190498684</v>
+        <v>5.403171720605732</v>
       </c>
       <c r="E146" t="n">
-        <v>5.491894142916634</v>
+        <v>5.491893665307877</v>
       </c>
       <c r="F146" t="n">
         <v>12429900</v>
@@ -3352,16 +3352,16 @@
         <v>44628</v>
       </c>
       <c r="B147" t="n">
-        <v>5.589488983154297</v>
+        <v>5.589488506317139</v>
       </c>
       <c r="C147" t="n">
-        <v>5.589488983154297</v>
+        <v>5.589488506317139</v>
       </c>
       <c r="D147" t="n">
-        <v>5.420917047522567</v>
+        <v>5.420916585066217</v>
       </c>
       <c r="E147" t="n">
-        <v>5.500766600040993</v>
+        <v>5.500766130772708</v>
       </c>
       <c r="F147" t="n">
         <v>5566500</v>
@@ -3372,16 +3372,16 @@
         <v>44629</v>
       </c>
       <c r="B148" t="n">
-        <v>5.695954322814941</v>
+        <v>5.695953845977783</v>
       </c>
       <c r="C148" t="n">
-        <v>5.704826305713552</v>
+        <v>5.704825828133675</v>
       </c>
       <c r="D148" t="n">
-        <v>5.553999211960359</v>
+        <v>5.553998747006981</v>
       </c>
       <c r="E148" t="n">
-        <v>5.589487989674004</v>
+        <v>5.589487521749682</v>
       </c>
       <c r="F148" t="n">
         <v>9079900</v>
@@ -3392,16 +3392,16 @@
         <v>44630</v>
       </c>
       <c r="B149" t="n">
-        <v>5.695954322814941</v>
+        <v>5.695953845977783</v>
       </c>
       <c r="C149" t="n">
-        <v>5.829037450770913</v>
+        <v>5.829036962792693</v>
       </c>
       <c r="D149" t="n">
-        <v>5.553999211960359</v>
+        <v>5.553998747006981</v>
       </c>
       <c r="E149" t="n">
-        <v>5.62497676738765</v>
+        <v>5.624976296492382</v>
       </c>
       <c r="F149" t="n">
         <v>15215200</v>
@@ -3412,16 +3412,16 @@
         <v>44631</v>
       </c>
       <c r="B150" t="n">
-        <v>5.598360538482666</v>
+        <v>5.598360061645508</v>
       </c>
       <c r="C150" t="n">
-        <v>5.979865148998535</v>
+        <v>5.97986463966694</v>
       </c>
       <c r="D150" t="n">
-        <v>5.52738297588061</v>
+        <v>5.527382505088926</v>
       </c>
       <c r="E150" t="n">
-        <v>5.695954898590315</v>
+        <v>5.695954413440612</v>
       </c>
       <c r="F150" t="n">
         <v>16712700</v>
@@ -3432,16 +3432,16 @@
         <v>44634</v>
       </c>
       <c r="B151" t="n">
-        <v>5.589488983154297</v>
+        <v>5.589488506317139</v>
       </c>
       <c r="C151" t="n">
-        <v>5.7225717117049</v>
+        <v>5.722571223514505</v>
       </c>
       <c r="D151" t="n">
-        <v>5.518510992051719</v>
+        <v>5.518510521269666</v>
       </c>
       <c r="E151" t="n">
-        <v>5.607233375165023</v>
+        <v>5.607232896814097</v>
       </c>
       <c r="F151" t="n">
         <v>7706100</v>
@@ -3452,16 +3452,16 @@
         <v>44635</v>
       </c>
       <c r="B152" t="n">
-        <v>5.651593208312988</v>
+        <v>5.651593685150146</v>
       </c>
       <c r="C152" t="n">
-        <v>5.687081986460981</v>
+        <v>5.687082466292404</v>
       </c>
       <c r="D152" t="n">
-        <v>5.500765689654214</v>
+        <v>5.500766153765728</v>
       </c>
       <c r="E152" t="n">
-        <v>5.509638095721016</v>
+        <v>5.509638560581113</v>
       </c>
       <c r="F152" t="n">
         <v>5880900</v>
@@ -3492,16 +3492,16 @@
         <v>44637</v>
       </c>
       <c r="B154" t="n">
-        <v>5.891142845153809</v>
+        <v>5.89114236831665</v>
       </c>
       <c r="C154" t="n">
-        <v>5.926631624342837</v>
+        <v>5.926631144633169</v>
       </c>
       <c r="D154" t="n">
-        <v>5.536254630203903</v>
+        <v>5.536254182091882</v>
       </c>
       <c r="E154" t="n">
-        <v>5.607232611641579</v>
+        <v>5.607232157784503</v>
       </c>
       <c r="F154" t="n">
         <v>10001800</v>
@@ -3532,16 +3532,16 @@
         <v>44641</v>
       </c>
       <c r="B156" t="n">
-        <v>6.104076385498047</v>
+        <v>6.104075908660889</v>
       </c>
       <c r="C156" t="n">
-        <v>6.343625873905633</v>
+        <v>6.34362537835539</v>
       </c>
       <c r="D156" t="n">
-        <v>6.024226415008968</v>
+        <v>6.024225944409515</v>
       </c>
       <c r="E156" t="n">
-        <v>6.183925932927476</v>
+        <v>6.183925449852644</v>
       </c>
       <c r="F156" t="n">
         <v>14982100</v>
@@ -3552,16 +3552,16 @@
         <v>44642</v>
       </c>
       <c r="B157" t="n">
-        <v>6.299264907836914</v>
+        <v>6.299264430999756</v>
       </c>
       <c r="C157" t="n">
-        <v>6.30813731512027</v>
+        <v>6.308136837611495</v>
       </c>
       <c r="D157" t="n">
-        <v>6.077459802468997</v>
+        <v>6.07745934242188</v>
       </c>
       <c r="E157" t="n">
-        <v>6.077459802468997</v>
+        <v>6.07745934242188</v>
       </c>
       <c r="F157" t="n">
         <v>9703800</v>
@@ -3612,16 +3612,16 @@
         <v>44645</v>
       </c>
       <c r="B160" t="n">
-        <v>6.450091361999512</v>
+        <v>6.45009183883667</v>
       </c>
       <c r="C160" t="n">
-        <v>6.512196933355233</v>
+        <v>6.512197414783683</v>
       </c>
       <c r="D160" t="n">
-        <v>6.237158699739195</v>
+        <v>6.237159160834839</v>
       </c>
       <c r="E160" t="n">
-        <v>6.343625030869354</v>
+        <v>6.343625499835754</v>
       </c>
       <c r="F160" t="n">
         <v>15324200</v>
@@ -3632,16 +3632,16 @@
         <v>44648</v>
       </c>
       <c r="B161" t="n">
-        <v>6.538813591003418</v>
+        <v>6.538814067840576</v>
       </c>
       <c r="C161" t="n">
-        <v>6.592046758900072</v>
+        <v>6.592047239619212</v>
       </c>
       <c r="D161" t="n">
-        <v>6.352497291835322</v>
+        <v>6.35249775508553</v>
       </c>
       <c r="E161" t="n">
-        <v>6.432347255210109</v>
+        <v>6.432347724283304</v>
       </c>
       <c r="F161" t="n">
         <v>10802600</v>
@@ -3732,16 +3732,16 @@
         <v>44655</v>
       </c>
       <c r="B166" t="n">
-        <v>6.210542678833008</v>
+        <v>6.21054220199585</v>
       </c>
       <c r="C166" t="n">
-        <v>6.237159476459965</v>
+        <v>6.237158997579204</v>
       </c>
       <c r="D166" t="n">
-        <v>6.050843162250203</v>
+        <v>6.050842697674559</v>
       </c>
       <c r="E166" t="n">
-        <v>6.15730950663874</v>
+        <v>6.157309033888753</v>
       </c>
       <c r="F166" t="n">
         <v>13343800</v>
@@ -3752,16 +3752,16 @@
         <v>44656</v>
       </c>
       <c r="B167" t="n">
-        <v>6.299264907836914</v>
+        <v>6.299264430999756</v>
       </c>
       <c r="C167" t="n">
-        <v>6.325881706627317</v>
+        <v>6.32588122777534</v>
       </c>
       <c r="D167" t="n">
-        <v>6.148437368497184</v>
+        <v>6.148436903077259</v>
       </c>
       <c r="E167" t="n">
-        <v>6.228287341808727</v>
+        <v>6.228286870344377</v>
       </c>
       <c r="F167" t="n">
         <v>6962400</v>
@@ -3792,16 +3792,16 @@
         <v>44658</v>
       </c>
       <c r="B169" t="n">
-        <v>6.261641502380371</v>
+        <v>6.261641979217529</v>
       </c>
       <c r="C169" t="n">
-        <v>6.395246596078652</v>
+        <v>6.39524708309012</v>
       </c>
       <c r="D169" t="n">
-        <v>6.208198955236777</v>
+        <v>6.208199428004173</v>
       </c>
       <c r="E169" t="n">
-        <v>6.323990432847507</v>
+        <v>6.323990914432667</v>
       </c>
       <c r="F169" t="n">
         <v>10216600</v>
@@ -3812,16 +3812,16 @@
         <v>44659</v>
       </c>
       <c r="B170" t="n">
-        <v>6.190384864807129</v>
+        <v>6.190385341644287</v>
       </c>
       <c r="C170" t="n">
-        <v>6.323990382154669</v>
+        <v>6.323990869283284</v>
       </c>
       <c r="D170" t="n">
-        <v>6.136942742812159</v>
+        <v>6.136943215532741</v>
       </c>
       <c r="E170" t="n">
-        <v>6.23492017882972</v>
+        <v>6.234920659097374</v>
       </c>
       <c r="F170" t="n">
         <v>10722400</v>
@@ -3852,16 +3852,16 @@
         <v>44663</v>
       </c>
       <c r="B172" t="n">
-        <v>6.217106342315674</v>
+        <v>6.217105865478516</v>
       </c>
       <c r="C172" t="n">
-        <v>6.359618672315267</v>
+        <v>6.359618184547754</v>
       </c>
       <c r="D172" t="n">
-        <v>6.145850177315878</v>
+        <v>6.145849705943896</v>
       </c>
       <c r="E172" t="n">
-        <v>6.190385068080627</v>
+        <v>6.190384593292927</v>
       </c>
       <c r="F172" t="n">
         <v>15598900</v>
@@ -3872,16 +3872,16 @@
         <v>44664</v>
       </c>
       <c r="B173" t="n">
-        <v>6.306175708770752</v>
+        <v>6.306176662445068</v>
       </c>
       <c r="C173" t="n">
-        <v>6.323989747648402</v>
+        <v>6.323990704016711</v>
       </c>
       <c r="D173" t="n">
-        <v>6.172570204828283</v>
+        <v>6.172571138297622</v>
       </c>
       <c r="E173" t="n">
-        <v>6.261640823936721</v>
+        <v>6.261641770876088</v>
       </c>
       <c r="F173" t="n">
         <v>5828500</v>
@@ -3932,16 +3932,16 @@
         <v>44670</v>
       </c>
       <c r="B176" t="n">
-        <v>6.190384864807129</v>
+        <v>6.190385341644287</v>
       </c>
       <c r="C176" t="n">
-        <v>6.413060585479618</v>
+        <v>6.413061079469193</v>
       </c>
       <c r="D176" t="n">
-        <v>6.18147805683475</v>
+        <v>6.181478532985828</v>
       </c>
       <c r="E176" t="n">
-        <v>6.359618463484649</v>
+        <v>6.359618953357647</v>
       </c>
       <c r="F176" t="n">
         <v>12659600</v>
@@ -3952,16 +3952,16 @@
         <v>44671</v>
       </c>
       <c r="B177" t="n">
-        <v>6.208198547363281</v>
+        <v>6.208199024200439</v>
       </c>
       <c r="C177" t="n">
-        <v>6.279455130633163</v>
+        <v>6.279455612943373</v>
       </c>
       <c r="D177" t="n">
-        <v>6.11022154171758</v>
+        <v>6.110222011029355</v>
       </c>
       <c r="E177" t="n">
-        <v>6.190384507725862</v>
+        <v>6.190384983194765</v>
       </c>
       <c r="F177" t="n">
         <v>7897000</v>
@@ -3992,16 +3992,16 @@
         <v>44676</v>
       </c>
       <c r="B179" t="n">
-        <v>6.279454708099365</v>
+        <v>6.279455184936523</v>
       </c>
       <c r="C179" t="n">
-        <v>6.306175553397391</v>
+        <v>6.306176032263624</v>
       </c>
       <c r="D179" t="n">
-        <v>6.038964976816251</v>
+        <v>6.038965435391561</v>
       </c>
       <c r="E179" t="n">
-        <v>6.047871783675533</v>
+        <v>6.047872242927192</v>
       </c>
       <c r="F179" t="n">
         <v>9340700</v>
@@ -4012,16 +4012,16 @@
         <v>44677</v>
       </c>
       <c r="B180" t="n">
-        <v>6.252734184265137</v>
+        <v>6.252734661102295</v>
       </c>
       <c r="C180" t="n">
-        <v>6.332897579166045</v>
+        <v>6.33289806211651</v>
       </c>
       <c r="D180" t="n">
-        <v>6.119128667670365</v>
+        <v>6.11912913431869</v>
       </c>
       <c r="E180" t="n">
-        <v>6.24382737634294</v>
+        <v>6.243827852500861</v>
       </c>
       <c r="F180" t="n">
         <v>9190800</v>
@@ -4032,16 +4032,16 @@
         <v>44678</v>
       </c>
       <c r="B181" t="n">
-        <v>6.332898139953613</v>
+        <v>6.332897186279297</v>
       </c>
       <c r="C181" t="n">
-        <v>6.359618990806601</v>
+        <v>6.359618033108378</v>
       </c>
       <c r="D181" t="n">
-        <v>6.20819942023878</v>
+        <v>6.208198485342908</v>
       </c>
       <c r="E181" t="n">
-        <v>6.288362822238278</v>
+        <v>6.288361875270557</v>
       </c>
       <c r="F181" t="n">
         <v>11357200</v>
@@ -4092,16 +4092,16 @@
         <v>44683</v>
       </c>
       <c r="B184" t="n">
-        <v>5.869731903076172</v>
+        <v>5.86973237991333</v>
       </c>
       <c r="C184" t="n">
-        <v>6.19038462249456</v>
+        <v>6.19038512538046</v>
       </c>
       <c r="D184" t="n">
-        <v>5.745033198582139</v>
+        <v>5.745033665289197</v>
       </c>
       <c r="E184" t="n">
-        <v>6.145849734935447</v>
+        <v>6.145850234203484</v>
       </c>
       <c r="F184" t="n">
         <v>12404500</v>
@@ -4132,16 +4132,16 @@
         <v>44685</v>
       </c>
       <c r="B186" t="n">
-        <v>5.388751983642578</v>
+        <v>5.388752460479736</v>
       </c>
       <c r="C186" t="n">
-        <v>5.513450253799544</v>
+        <v>5.51345074167094</v>
       </c>
       <c r="D186" t="n">
-        <v>5.210611172983874</v>
+        <v>5.210611634057798</v>
       </c>
       <c r="E186" t="n">
-        <v>5.513450253799544</v>
+        <v>5.51345074167094</v>
       </c>
       <c r="F186" t="n">
         <v>18834300</v>
@@ -4152,16 +4152,16 @@
         <v>44686</v>
       </c>
       <c r="B187" t="n">
-        <v>4.943400859832764</v>
+        <v>4.943401336669922</v>
       </c>
       <c r="C187" t="n">
-        <v>5.379845041205424</v>
+        <v>5.379845560141698</v>
       </c>
       <c r="D187" t="n">
-        <v>4.925586820281231</v>
+        <v>4.925587295400058</v>
       </c>
       <c r="E187" t="n">
-        <v>5.379845041205424</v>
+        <v>5.379845560141698</v>
       </c>
       <c r="F187" t="n">
         <v>16863600</v>
@@ -4192,16 +4192,16 @@
         <v>44690</v>
       </c>
       <c r="B189" t="n">
-        <v>4.622747421264648</v>
+        <v>4.622747898101807</v>
       </c>
       <c r="C189" t="n">
-        <v>4.934493305415869</v>
+        <v>4.934493814409667</v>
       </c>
       <c r="D189" t="n">
-        <v>4.435699805829881</v>
+        <v>4.435700263373046</v>
       </c>
       <c r="E189" t="n">
-        <v>4.934493305415869</v>
+        <v>4.934493814409667</v>
       </c>
       <c r="F189" t="n">
         <v>21341300</v>
@@ -4272,16 +4272,16 @@
         <v>44694</v>
       </c>
       <c r="B193" t="n">
-        <v>4.604933738708496</v>
+        <v>4.604934215545654</v>
       </c>
       <c r="C193" t="n">
-        <v>4.800888176118977</v>
+        <v>4.800888673247058</v>
       </c>
       <c r="D193" t="n">
-        <v>4.51586353988555</v>
+        <v>4.515864007499562</v>
       </c>
       <c r="E193" t="n">
-        <v>4.800888176118977</v>
+        <v>4.800888673247058</v>
       </c>
       <c r="F193" t="n">
         <v>51332400</v>
@@ -4292,16 +4292,16 @@
         <v>44697</v>
       </c>
       <c r="B194" t="n">
-        <v>4.881051540374756</v>
+        <v>4.881052494049072</v>
       </c>
       <c r="C194" t="n">
-        <v>4.881051540374756</v>
+        <v>4.881052494049072</v>
       </c>
       <c r="D194" t="n">
-        <v>4.542584362002735</v>
+        <v>4.542585249546331</v>
       </c>
       <c r="E194" t="n">
-        <v>4.604933713193436</v>
+        <v>4.604934612919033</v>
       </c>
       <c r="F194" t="n">
         <v>29391700</v>
@@ -4312,16 +4312,16 @@
         <v>44698</v>
       </c>
       <c r="B195" t="n">
-        <v>5.005750179290771</v>
+        <v>5.00575065612793</v>
       </c>
       <c r="C195" t="n">
-        <v>5.183891013525891</v>
+        <v>5.183891507332367</v>
       </c>
       <c r="D195" t="n">
-        <v>4.881051892630355</v>
+        <v>4.881052357589018</v>
       </c>
       <c r="E195" t="n">
-        <v>4.952308056436308</v>
+        <v>4.952308528182682</v>
       </c>
       <c r="F195" t="n">
         <v>40878000</v>
@@ -4372,16 +4372,16 @@
         <v>44701</v>
       </c>
       <c r="B198" t="n">
-        <v>4.934494495391846</v>
+        <v>4.934494018554688</v>
       </c>
       <c r="C198" t="n">
-        <v>5.121542155934015</v>
+        <v>5.121541661021799</v>
       </c>
       <c r="D198" t="n">
-        <v>4.82761023928783</v>
+        <v>4.827609772779264</v>
       </c>
       <c r="E198" t="n">
-        <v>5.09482087954787</v>
+        <v>5.094820387217823</v>
       </c>
       <c r="F198" t="n">
         <v>10517400</v>
@@ -4392,16 +4392,16 @@
         <v>44704</v>
       </c>
       <c r="B199" t="n">
-        <v>5.023563861846924</v>
+        <v>5.023564338684082</v>
       </c>
       <c r="C199" t="n">
-        <v>5.103727252769655</v>
+        <v>5.10372773721593</v>
       </c>
       <c r="D199" t="n">
-        <v>4.881051544402253</v>
+        <v>4.881052007712129</v>
       </c>
       <c r="E199" t="n">
-        <v>4.979028975005568</v>
+        <v>4.979029447615471</v>
       </c>
       <c r="F199" t="n">
         <v>11444200</v>
@@ -4412,16 +4412,16 @@
         <v>44705</v>
       </c>
       <c r="B200" t="n">
-        <v>5.157168865203857</v>
+        <v>5.157169818878174</v>
       </c>
       <c r="C200" t="n">
-        <v>5.201704172390555</v>
+        <v>5.201705134300433</v>
       </c>
       <c r="D200" t="n">
-        <v>4.961214447966753</v>
+        <v>4.961215365404775</v>
       </c>
       <c r="E200" t="n">
-        <v>4.979028485897399</v>
+        <v>4.979029406629629</v>
       </c>
       <c r="F200" t="n">
         <v>9007600</v>
@@ -4432,16 +4432,16 @@
         <v>44706</v>
       </c>
       <c r="B201" t="n">
-        <v>5.272961616516113</v>
+        <v>5.272961139678955</v>
       </c>
       <c r="C201" t="n">
-        <v>5.326403743406717</v>
+        <v>5.326403261736754</v>
       </c>
       <c r="D201" t="n">
-        <v>5.112634811124033</v>
+        <v>5.112634348785326</v>
       </c>
       <c r="E201" t="n">
-        <v>5.148263320438039</v>
+        <v>5.148262854877424</v>
       </c>
       <c r="F201" t="n">
         <v>9738900</v>
@@ -4452,16 +4452,16 @@
         <v>44707</v>
       </c>
       <c r="B202" t="n">
-        <v>5.504544258117676</v>
+        <v>5.504543304443359</v>
       </c>
       <c r="C202" t="n">
-        <v>5.647057023588098</v>
+        <v>5.647056045223134</v>
       </c>
       <c r="D202" t="n">
-        <v>5.281868513335436</v>
+        <v>5.281867598240178</v>
       </c>
       <c r="E202" t="n">
-        <v>5.281868513335436</v>
+        <v>5.281867598240178</v>
       </c>
       <c r="F202" t="n">
         <v>14781100</v>
@@ -4492,16 +4492,16 @@
         <v>44711</v>
       </c>
       <c r="B204" t="n">
-        <v>5.602521419525146</v>
+        <v>5.60252046585083</v>
       </c>
       <c r="C204" t="n">
-        <v>5.673777586272644</v>
+        <v>5.673776620468936</v>
       </c>
       <c r="D204" t="n">
-        <v>5.317496327814903</v>
+        <v>5.317495422658225</v>
       </c>
       <c r="E204" t="n">
-        <v>5.460009086030153</v>
+        <v>5.460008156614619</v>
       </c>
       <c r="F204" t="n">
         <v>7527500</v>
@@ -4512,16 +4512,16 @@
         <v>44712</v>
       </c>
       <c r="B205" t="n">
-        <v>5.46000862121582</v>
+        <v>5.460009098052979</v>
       </c>
       <c r="C205" t="n">
-        <v>5.691591143430404</v>
+        <v>5.691591640492284</v>
       </c>
       <c r="D205" t="n">
-        <v>5.46000862121582</v>
+        <v>5.460009098052979</v>
       </c>
       <c r="E205" t="n">
-        <v>5.62924221519428</v>
+        <v>5.629242706811061</v>
       </c>
       <c r="F205" t="n">
         <v>13931800</v>
@@ -4532,16 +4532,16 @@
         <v>44713</v>
       </c>
       <c r="B206" t="n">
-        <v>5.513450622558594</v>
+        <v>5.51345157623291</v>
       </c>
       <c r="C206" t="n">
-        <v>5.54907870212923</v>
+        <v>5.549079661966218</v>
       </c>
       <c r="D206" t="n">
-        <v>5.406566383846685</v>
+        <v>5.406567319032987</v>
       </c>
       <c r="E206" t="n">
-        <v>5.495636582773276</v>
+        <v>5.495637533366256</v>
       </c>
       <c r="F206" t="n">
         <v>9091200</v>
@@ -4552,16 +4552,16 @@
         <v>44714</v>
       </c>
       <c r="B207" t="n">
-        <v>5.611428260803223</v>
+        <v>5.611427783966064</v>
       </c>
       <c r="C207" t="n">
-        <v>5.655963149549779</v>
+        <v>5.65596266892822</v>
       </c>
       <c r="D207" t="n">
-        <v>5.504543593426991</v>
+        <v>5.504543125672473</v>
       </c>
       <c r="E207" t="n">
-        <v>5.549078906893773</v>
+        <v>5.549078435354819</v>
       </c>
       <c r="F207" t="n">
         <v>14163200</v>
@@ -4572,16 +4572,16 @@
         <v>44715</v>
       </c>
       <c r="B208" t="n">
-        <v>5.513450622558594</v>
+        <v>5.51345157623291</v>
       </c>
       <c r="C208" t="n">
-        <v>5.602520821485185</v>
+        <v>5.602521790566179</v>
       </c>
       <c r="D208" t="n">
-        <v>5.451101270949875</v>
+        <v>5.45110221383948</v>
       </c>
       <c r="E208" t="n">
-        <v>5.575799974167312</v>
+        <v>5.57580093862634</v>
       </c>
       <c r="F208" t="n">
         <v>9326300</v>
@@ -4592,16 +4592,16 @@
         <v>44718</v>
       </c>
       <c r="B209" t="n">
-        <v>5.308588981628418</v>
+        <v>5.308589458465576</v>
       </c>
       <c r="C209" t="n">
-        <v>5.566892772284817</v>
+        <v>5.566893272323779</v>
       </c>
       <c r="D209" t="n">
-        <v>5.246239629679551</v>
+        <v>5.24624010091626</v>
       </c>
       <c r="E209" t="n">
-        <v>5.566892772284817</v>
+        <v>5.566893272323779</v>
       </c>
       <c r="F209" t="n">
         <v>9845400</v>
@@ -4612,16 +4612,16 @@
         <v>44719</v>
       </c>
       <c r="B210" t="n">
-        <v>5.023563861846924</v>
+        <v>5.023564338684082</v>
       </c>
       <c r="C210" t="n">
-        <v>5.299681689256077</v>
+        <v>5.299682192302366</v>
       </c>
       <c r="D210" t="n">
-        <v>4.987935782485756</v>
+        <v>4.987936255941094</v>
       </c>
       <c r="E210" t="n">
-        <v>5.281867649575493</v>
+        <v>5.281868150930872</v>
       </c>
       <c r="F210" t="n">
         <v>18881300</v>
@@ -4632,16 +4632,16 @@
         <v>44720</v>
       </c>
       <c r="B211" t="n">
-        <v>4.916679859161377</v>
+        <v>4.916680335998535</v>
       </c>
       <c r="C211" t="n">
-        <v>5.005750061828747</v>
+        <v>5.005750547304253</v>
       </c>
       <c r="D211" t="n">
-        <v>4.783074342800206</v>
+        <v>4.783074806679825</v>
       </c>
       <c r="E211" t="n">
-        <v>4.996843253922124</v>
+        <v>4.996843738533816</v>
       </c>
       <c r="F211" t="n">
         <v>13996400</v>
@@ -4652,16 +4652,16 @@
         <v>44721</v>
       </c>
       <c r="B212" t="n">
-        <v>4.818702697753906</v>
+        <v>4.818702220916748</v>
       </c>
       <c r="C212" t="n">
-        <v>4.996843537934095</v>
+        <v>4.996843043468919</v>
       </c>
       <c r="D212" t="n">
-        <v>4.809795889341036</v>
+        <v>4.809795413385255</v>
       </c>
       <c r="E212" t="n">
-        <v>4.88105205552501</v>
+        <v>4.881051572518039</v>
       </c>
       <c r="F212" t="n">
         <v>8480000</v>
@@ -4672,16 +4672,16 @@
         <v>44722</v>
       </c>
       <c r="B213" t="n">
-        <v>4.738540172576904</v>
+        <v>4.738539218902588</v>
       </c>
       <c r="C213" t="n">
-        <v>4.783075068305608</v>
+        <v>4.78307410566824</v>
       </c>
       <c r="D213" t="n">
-        <v>4.676190808892367</v>
+        <v>4.676189867766428</v>
       </c>
       <c r="E213" t="n">
-        <v>4.774168259047984</v>
+        <v>4.774167298203192</v>
       </c>
       <c r="F213" t="n">
         <v>4786300</v>
@@ -4692,16 +4692,16 @@
         <v>44725</v>
       </c>
       <c r="B214" t="n">
-        <v>4.569305896759033</v>
+        <v>4.569306373596191</v>
       </c>
       <c r="C214" t="n">
-        <v>4.676190140903983</v>
+        <v>4.676190628895216</v>
       </c>
       <c r="D214" t="n">
-        <v>4.50695654198103</v>
+        <v>4.506957012311623</v>
       </c>
       <c r="E214" t="n">
-        <v>4.631654826816805</v>
+        <v>4.631655310160484</v>
       </c>
       <c r="F214" t="n">
         <v>7709600</v>
@@ -4732,16 +4732,16 @@
         <v>44727</v>
       </c>
       <c r="B216" t="n">
-        <v>4.560398578643799</v>
+        <v>4.560398101806641</v>
       </c>
       <c r="C216" t="n">
-        <v>4.649468780429767</v>
+        <v>4.649468294279392</v>
       </c>
       <c r="D216" t="n">
-        <v>4.48023560939654</v>
+        <v>4.480235140941255</v>
       </c>
       <c r="E216" t="n">
-        <v>4.542584538286605</v>
+        <v>4.54258406331209</v>
       </c>
       <c r="F216" t="n">
         <v>10830000</v>
@@ -4812,16 +4812,16 @@
         <v>44734</v>
       </c>
       <c r="B220" t="n">
-        <v>4.444606781005859</v>
+        <v>4.444607257843018</v>
       </c>
       <c r="C220" t="n">
-        <v>4.53367740103996</v>
+        <v>4.533677887433011</v>
       </c>
       <c r="D220" t="n">
-        <v>4.400071895709002</v>
+        <v>4.40007236776826</v>
       </c>
       <c r="E220" t="n">
-        <v>4.480235283851616</v>
+        <v>4.480235764511158</v>
       </c>
       <c r="F220" t="n">
         <v>8433900</v>
@@ -4852,16 +4852,16 @@
         <v>44736</v>
       </c>
       <c r="B222" t="n">
-        <v>4.257559776306152</v>
+        <v>4.257560729980469</v>
       </c>
       <c r="C222" t="n">
-        <v>4.337722743364323</v>
+        <v>4.337723714994785</v>
       </c>
       <c r="D222" t="n">
-        <v>4.230838504139954</v>
+        <v>4.230839451828825</v>
       </c>
       <c r="E222" t="n">
-        <v>4.319908703493595</v>
+        <v>4.319909671133791</v>
       </c>
       <c r="F222" t="n">
         <v>7941200</v>
@@ -4872,16 +4872,16 @@
         <v>44739</v>
       </c>
       <c r="B223" t="n">
-        <v>4.275373458862305</v>
+        <v>4.275374412536621</v>
       </c>
       <c r="C223" t="n">
-        <v>4.337722380838932</v>
+        <v>4.337723348420938</v>
       </c>
       <c r="D223" t="n">
-        <v>4.239745382098467</v>
+        <v>4.239746327825506</v>
       </c>
       <c r="E223" t="n">
-        <v>4.275373458862305</v>
+        <v>4.275374412536621</v>
       </c>
       <c r="F223" t="n">
         <v>10516900</v>
@@ -4912,16 +4912,16 @@
         <v>44741</v>
       </c>
       <c r="B225" t="n">
-        <v>4.275373458862305</v>
+        <v>4.275374412536621</v>
       </c>
       <c r="C225" t="n">
-        <v>4.355536419220851</v>
+        <v>4.355537390776496</v>
       </c>
       <c r="D225" t="n">
-        <v>4.248652188929338</v>
+        <v>4.248653136643148</v>
       </c>
       <c r="E225" t="n">
-        <v>4.311001535626143</v>
+        <v>4.311002497247737</v>
       </c>
       <c r="F225" t="n">
         <v>7179800</v>
@@ -5032,16 +5032,16 @@
         <v>44749</v>
       </c>
       <c r="B231" t="n">
-        <v>4.052698135375977</v>
+        <v>4.052698612213135</v>
       </c>
       <c r="C231" t="n">
-        <v>4.141768335387711</v>
+        <v>4.141768822704797</v>
       </c>
       <c r="D231" t="n">
-        <v>3.927999430639332</v>
+        <v>3.927999892804543</v>
       </c>
       <c r="E231" t="n">
-        <v>3.927999430639332</v>
+        <v>3.927999892804543</v>
       </c>
       <c r="F231" t="n">
         <v>10027800</v>
@@ -5052,16 +5052,16 @@
         <v>44750</v>
       </c>
       <c r="B232" t="n">
-        <v>3.919093132019043</v>
+        <v>3.919092655181885</v>
       </c>
       <c r="C232" t="n">
-        <v>4.132861639811949</v>
+        <v>4.132861136965516</v>
       </c>
       <c r="D232" t="n">
-        <v>3.919093132019043</v>
+        <v>3.919092655181885</v>
       </c>
       <c r="E232" t="n">
-        <v>4.03488461943367</v>
+        <v>4.034884128508128</v>
       </c>
       <c r="F232" t="n">
         <v>7050900</v>
@@ -5072,16 +5072,16 @@
         <v>44753</v>
       </c>
       <c r="B233" t="n">
-        <v>3.705323934555054</v>
+        <v>3.705323696136475</v>
       </c>
       <c r="C233" t="n">
-        <v>3.901278810740315</v>
+        <v>3.901278559713046</v>
       </c>
       <c r="D233" t="n">
-        <v>3.678603085351762</v>
+        <v>3.678602848652532</v>
       </c>
       <c r="E233" t="n">
-        <v>3.892371577859058</v>
+        <v>3.892371327404923</v>
       </c>
       <c r="F233" t="n">
         <v>13261200</v>
@@ -5112,16 +5112,16 @@
         <v>44755</v>
       </c>
       <c r="B235" t="n">
-        <v>3.687510251998901</v>
+        <v>3.687509775161743</v>
       </c>
       <c r="C235" t="n">
-        <v>3.723138337547081</v>
+        <v>3.723137856102805</v>
       </c>
       <c r="D235" t="n">
-        <v>3.47374173870982</v>
+        <v>3.47374128951537</v>
       </c>
       <c r="E235" t="n">
-        <v>3.589533229101546</v>
+        <v>3.589532764933936</v>
       </c>
       <c r="F235" t="n">
         <v>14925600</v>
@@ -5132,16 +5132,16 @@
         <v>44756</v>
       </c>
       <c r="B236" t="n">
-        <v>3.821115493774414</v>
+        <v>3.821115255355835</v>
       </c>
       <c r="C236" t="n">
-        <v>3.856743576605671</v>
+        <v>3.856743335964077</v>
       </c>
       <c r="D236" t="n">
-        <v>3.651881887965819</v>
+        <v>3.651881660106575</v>
       </c>
       <c r="E236" t="n">
-        <v>3.687509970797076</v>
+        <v>3.687509740714817</v>
       </c>
       <c r="F236" t="n">
         <v>9774500</v>
@@ -5152,16 +5152,16 @@
         <v>44757</v>
       </c>
       <c r="B237" t="n">
-        <v>3.936906576156616</v>
+        <v>3.936907291412354</v>
       </c>
       <c r="C237" t="n">
-        <v>3.954720615766004</v>
+        <v>3.95472133425819</v>
       </c>
       <c r="D237" t="n">
-        <v>3.776579794951918</v>
+        <v>3.776580481079544</v>
       </c>
       <c r="E237" t="n">
-        <v>3.830022338500288</v>
+        <v>3.830023034337336</v>
       </c>
       <c r="F237" t="n">
         <v>4881500</v>
@@ -5172,16 +5172,16 @@
         <v>44760</v>
       </c>
       <c r="B238" t="n">
-        <v>3.83002233505249</v>
+        <v>3.830022573471069</v>
       </c>
       <c r="C238" t="n">
-        <v>4.088326121516194</v>
+        <v>4.088326376014163</v>
       </c>
       <c r="D238" t="n">
-        <v>3.83002233505249</v>
+        <v>3.830022573471069</v>
       </c>
       <c r="E238" t="n">
-        <v>3.990348691392656</v>
+        <v>3.990348939791538</v>
       </c>
       <c r="F238" t="n">
         <v>5011900</v>
@@ -5192,16 +5192,16 @@
         <v>44761</v>
       </c>
       <c r="B239" t="n">
-        <v>3.856743574142456</v>
+        <v>3.856743335723877</v>
       </c>
       <c r="C239" t="n">
-        <v>3.93690697282171</v>
+        <v>3.93690672944754</v>
       </c>
       <c r="D239" t="n">
-        <v>3.830022724396204</v>
+        <v>3.830022487629471</v>
       </c>
       <c r="E239" t="n">
-        <v>3.838929532738205</v>
+        <v>3.838929295420866</v>
       </c>
       <c r="F239" t="n">
         <v>5270100</v>
@@ -5212,16 +5212,16 @@
         <v>44762</v>
       </c>
       <c r="B240" t="n">
-        <v>3.999255895614624</v>
+        <v>3.999255657196045</v>
       </c>
       <c r="C240" t="n">
-        <v>4.025977170015901</v>
+        <v>4.025976930004314</v>
       </c>
       <c r="D240" t="n">
-        <v>3.803301440646171</v>
+        <v>3.803301213909561</v>
       </c>
       <c r="E240" t="n">
-        <v>3.830022715047448</v>
+        <v>3.830022486717829</v>
       </c>
       <c r="F240" t="n">
         <v>11021800</v>
@@ -5232,16 +5232,16 @@
         <v>44763</v>
       </c>
       <c r="B241" t="n">
-        <v>3.963627338409424</v>
+        <v>3.963627815246582</v>
       </c>
       <c r="C241" t="n">
-        <v>4.025976688068431</v>
+        <v>4.025977172406417</v>
       </c>
       <c r="D241" t="n">
-        <v>3.936906491927133</v>
+        <v>3.936906965549687</v>
       </c>
       <c r="E241" t="n">
-        <v>4.025976688068431</v>
+        <v>4.025977172406417</v>
       </c>
       <c r="F241" t="n">
         <v>6658500</v>
@@ -5252,16 +5252,16 @@
         <v>44764</v>
       </c>
       <c r="B242" t="n">
-        <v>3.740951538085938</v>
+        <v>3.740952014923096</v>
       </c>
       <c r="C242" t="n">
-        <v>3.999255312516052</v>
+        <v>3.999255822277678</v>
       </c>
       <c r="D242" t="n">
-        <v>3.740951538085938</v>
+        <v>3.740952014923096</v>
       </c>
       <c r="E242" t="n">
-        <v>3.999255312516052</v>
+        <v>3.999255822277678</v>
       </c>
       <c r="F242" t="n">
         <v>6536400</v>
@@ -5272,16 +5272,16 @@
         <v>44767</v>
       </c>
       <c r="B243" t="n">
-        <v>3.696417570114136</v>
+        <v>3.696417093276978</v>
       </c>
       <c r="C243" t="n">
-        <v>3.78548778601755</v>
+        <v>3.78548729769035</v>
       </c>
       <c r="D243" t="n">
-        <v>3.651882249802283</v>
+        <v>3.651881778710173</v>
       </c>
       <c r="E243" t="n">
-        <v>3.767673742836867</v>
+        <v>3.767673256807676</v>
       </c>
       <c r="F243" t="n">
         <v>10514300</v>
@@ -5292,16 +5292,16 @@
         <v>44768</v>
       </c>
       <c r="B244" t="n">
-        <v>3.714231252670288</v>
+        <v>3.714231491088867</v>
       </c>
       <c r="C244" t="n">
-        <v>3.8122086930113</v>
+        <v>3.812208937719106</v>
       </c>
       <c r="D244" t="n">
-        <v>3.669695936682488</v>
+        <v>3.66969617224232</v>
       </c>
       <c r="E244" t="n">
-        <v>3.705324019584628</v>
+        <v>3.705324257431447</v>
       </c>
       <c r="F244" t="n">
         <v>4594100</v>
@@ -5312,16 +5312,16 @@
         <v>44769</v>
       </c>
       <c r="B245" t="n">
-        <v>3.999255895614624</v>
+        <v>3.999255657196045</v>
       </c>
       <c r="C245" t="n">
-        <v>3.999255895614624</v>
+        <v>3.999255657196045</v>
       </c>
       <c r="D245" t="n">
-        <v>3.723138042162589</v>
+        <v>3.723137820204979</v>
       </c>
       <c r="E245" t="n">
-        <v>3.740952083523358</v>
+        <v>3.74095186050375</v>
       </c>
       <c r="F245" t="n">
         <v>8689000</v>
@@ -5332,16 +5332,16 @@
         <v>44770</v>
       </c>
       <c r="B246" t="n">
-        <v>3.999255895614624</v>
+        <v>3.999255657196045</v>
       </c>
       <c r="C246" t="n">
-        <v>4.070512485777946</v>
+        <v>4.070512243111353</v>
       </c>
       <c r="D246" t="n">
-        <v>3.892371647450013</v>
+        <v>3.892371415403418</v>
       </c>
       <c r="E246" t="n">
-        <v>4.025977170015901</v>
+        <v>4.025976930004314</v>
       </c>
       <c r="F246" t="n">
         <v>3634200</v>
@@ -5352,16 +5352,16 @@
         <v>44771</v>
       </c>
       <c r="B247" t="n">
-        <v>3.927999973297119</v>
+        <v>3.927999496459961</v>
       </c>
       <c r="C247" t="n">
-        <v>4.088326780187793</v>
+        <v>4.08832628388786</v>
       </c>
       <c r="D247" t="n">
-        <v>3.919093164425567</v>
+        <v>3.919092688669646</v>
       </c>
       <c r="E247" t="n">
-        <v>4.025977419205834</v>
+        <v>4.025976930474763</v>
       </c>
       <c r="F247" t="n">
         <v>8694600</v>
@@ -5372,16 +5372,16 @@
         <v>44774</v>
       </c>
       <c r="B248" t="n">
-        <v>3.927999973297119</v>
+        <v>3.927999496459961</v>
       </c>
       <c r="C248" t="n">
-        <v>3.990349334279078</v>
+        <v>3.990348849873058</v>
       </c>
       <c r="D248" t="n">
-        <v>3.874557845906986</v>
+        <v>3.874557375557402</v>
       </c>
       <c r="E248" t="n">
-        <v>3.981442100687252</v>
+        <v>3.98144161736252</v>
       </c>
       <c r="F248" t="n">
         <v>7696400</v>
@@ -5392,16 +5392,16 @@
         <v>44775</v>
       </c>
       <c r="B249" t="n">
-        <v>4.106140613555908</v>
+        <v>4.10614013671875</v>
       </c>
       <c r="C249" t="n">
-        <v>4.115047421973903</v>
+        <v>4.115046944102415</v>
       </c>
       <c r="D249" t="n">
-        <v>3.901278923299012</v>
+        <v>3.901278470251996</v>
       </c>
       <c r="E249" t="n">
-        <v>3.927999773273247</v>
+        <v>3.927999317123196</v>
       </c>
       <c r="F249" t="n">
         <v>12885400</v>
@@ -5412,16 +5412,16 @@
         <v>44776</v>
       </c>
       <c r="B250" t="n">
-        <v>4.284281253814697</v>
+        <v>4.284280776977539</v>
       </c>
       <c r="C250" t="n">
-        <v>4.37335146626734</v>
+        <v>4.373350979516736</v>
       </c>
       <c r="D250" t="n">
-        <v>4.123954871399942</v>
+        <v>4.123954412406984</v>
       </c>
       <c r="E250" t="n">
-        <v>4.123954871399942</v>
+        <v>4.123954412406984</v>
       </c>
       <c r="F250" t="n">
         <v>8750200</v>
@@ -5432,16 +5432,16 @@
         <v>44777</v>
       </c>
       <c r="B251" t="n">
-        <v>4.498049259185791</v>
+        <v>4.498050212860107</v>
       </c>
       <c r="C251" t="n">
-        <v>4.791981111917343</v>
+        <v>4.791982127910954</v>
       </c>
       <c r="D251" t="n">
-        <v>4.328815678126979</v>
+        <v>4.32881659592047</v>
       </c>
       <c r="E251" t="n">
-        <v>4.328815678126979</v>
+        <v>4.32881659592047</v>
       </c>
       <c r="F251" t="n">
         <v>17206200</v>
@@ -5452,16 +5452,16 @@
         <v>44778</v>
       </c>
       <c r="B252" t="n">
-        <v>4.328815937042236</v>
+        <v>4.328816413879395</v>
       </c>
       <c r="C252" t="n">
-        <v>4.542584415552859</v>
+        <v>4.542584915937508</v>
       </c>
       <c r="D252" t="n">
-        <v>4.248652545240646</v>
+        <v>4.248653013247472</v>
       </c>
       <c r="E252" t="n">
-        <v>4.542584415552859</v>
+        <v>4.542584915937508</v>
       </c>
       <c r="F252" t="n">
         <v>11124100</v>
@@ -5492,16 +5492,16 @@
         <v>44782</v>
       </c>
       <c r="B254" t="n">
-        <v>4.382258892059326</v>
+        <v>4.382258415222168</v>
       </c>
       <c r="C254" t="n">
-        <v>4.578213368048839</v>
+        <v>4.578212869889715</v>
       </c>
       <c r="D254" t="n">
-        <v>4.364444848787552</v>
+        <v>4.364444373888754</v>
       </c>
       <c r="E254" t="n">
-        <v>4.453515065146422</v>
+        <v>4.453514580555821</v>
       </c>
       <c r="F254" t="n">
         <v>9216300</v>
@@ -5512,16 +5512,16 @@
         <v>44783</v>
       </c>
       <c r="B255" t="n">
-        <v>4.587120532989502</v>
+        <v>4.587120056152344</v>
       </c>
       <c r="C255" t="n">
-        <v>4.702912024873032</v>
+        <v>4.702911535999198</v>
       </c>
       <c r="D255" t="n">
-        <v>4.426793721236833</v>
+        <v>4.426793261065856</v>
       </c>
       <c r="E255" t="n">
-        <v>4.426793721236833</v>
+        <v>4.426793261065856</v>
       </c>
       <c r="F255" t="n">
         <v>9044400</v>
@@ -5532,16 +5532,16 @@
         <v>44784</v>
       </c>
       <c r="B256" t="n">
-        <v>4.346629619598389</v>
+        <v>4.346630096435547</v>
       </c>
       <c r="C256" t="n">
-        <v>4.685096774136335</v>
+        <v>4.685097288104267</v>
       </c>
       <c r="D256" t="n">
-        <v>4.311001542775466</v>
+        <v>4.311002015704126</v>
       </c>
       <c r="E256" t="n">
-        <v>4.613840195770312</v>
+        <v>4.613840701921201</v>
       </c>
       <c r="F256" t="n">
         <v>11482900</v>
@@ -5552,16 +5552,16 @@
         <v>44785</v>
       </c>
       <c r="B257" t="n">
-        <v>4.694004058837891</v>
+        <v>4.694004535675049</v>
       </c>
       <c r="C257" t="n">
-        <v>4.694004058837891</v>
+        <v>4.694004535675049</v>
       </c>
       <c r="D257" t="n">
-        <v>4.498049616363389</v>
+        <v>4.49805007329465</v>
       </c>
       <c r="E257" t="n">
-        <v>4.578212585015574</v>
+        <v>4.578213050090135</v>
       </c>
       <c r="F257" t="n">
         <v>15222800</v>
@@ -5592,16 +5592,16 @@
         <v>44789</v>
       </c>
       <c r="B259" t="n">
-        <v>4.622747421264648</v>
+        <v>4.622747898101807</v>
       </c>
       <c r="C259" t="n">
-        <v>4.702910806371028</v>
+        <v>4.702911291477053</v>
       </c>
       <c r="D259" t="n">
-        <v>4.560398074546333</v>
+        <v>4.560398544952146</v>
       </c>
       <c r="E259" t="n">
-        <v>4.676189536428843</v>
+        <v>4.676190018778564</v>
       </c>
       <c r="F259" t="n">
         <v>5754000</v>
@@ -5632,16 +5632,16 @@
         <v>44791</v>
       </c>
       <c r="B261" t="n">
-        <v>4.53367805480957</v>
+        <v>4.533677577972412</v>
       </c>
       <c r="C261" t="n">
-        <v>4.711818471125755</v>
+        <v>4.711817975552381</v>
       </c>
       <c r="D261" t="n">
-        <v>4.515864013177952</v>
+        <v>4.515863538214415</v>
       </c>
       <c r="E261" t="n">
-        <v>4.640562304599281</v>
+        <v>4.640561816520393</v>
       </c>
       <c r="F261" t="n">
         <v>8785600</v>
@@ -5652,16 +5652,16 @@
         <v>44792</v>
       </c>
       <c r="B262" t="n">
-        <v>4.319908618927002</v>
+        <v>4.31990909576416</v>
       </c>
       <c r="C262" t="n">
-        <v>4.533677517911209</v>
+        <v>4.533678018344458</v>
       </c>
       <c r="D262" t="n">
-        <v>4.221931189195899</v>
+        <v>4.22193165521818</v>
       </c>
       <c r="E262" t="n">
-        <v>4.524770285790107</v>
+        <v>4.524770785240164</v>
       </c>
       <c r="F262" t="n">
         <v>17743000</v>
@@ -5672,16 +5672,16 @@
         <v>44795</v>
       </c>
       <c r="B263" t="n">
-        <v>4.319908618927002</v>
+        <v>4.31990909576416</v>
       </c>
       <c r="C263" t="n">
-        <v>4.364443930092105</v>
+        <v>4.364444411845128</v>
       </c>
       <c r="D263" t="n">
-        <v>4.177396302751</v>
+        <v>4.177396763857463</v>
       </c>
       <c r="E263" t="n">
-        <v>4.302094579405002</v>
+        <v>4.302095054275823</v>
       </c>
       <c r="F263" t="n">
         <v>9829500</v>
@@ -5692,16 +5692,16 @@
         <v>44796</v>
       </c>
       <c r="B264" t="n">
-        <v>4.471328735351562</v>
+        <v>4.471328258514404</v>
       </c>
       <c r="C264" t="n">
-        <v>4.471328735351562</v>
+        <v>4.471328258514404</v>
       </c>
       <c r="D264" t="n">
-        <v>4.311002359282476</v>
+        <v>4.311001899543048</v>
       </c>
       <c r="E264" t="n">
-        <v>4.311002359282476</v>
+        <v>4.311001899543048</v>
       </c>
       <c r="F264" t="n">
         <v>6333000</v>
@@ -5712,16 +5712,16 @@
         <v>44797</v>
       </c>
       <c r="B265" t="n">
-        <v>4.53367805480957</v>
+        <v>4.533677577972412</v>
       </c>
       <c r="C265" t="n">
-        <v>4.604934221336045</v>
+        <v>4.6049337370044</v>
       </c>
       <c r="D265" t="n">
-        <v>4.426793380299605</v>
+        <v>4.426792914704221</v>
       </c>
       <c r="E265" t="n">
-        <v>4.45351465510716</v>
+        <v>4.453514186701321</v>
       </c>
       <c r="F265" t="n">
         <v>5861300</v>
@@ -5752,16 +5752,16 @@
         <v>44799</v>
       </c>
       <c r="B267" t="n">
-        <v>4.319908618927002</v>
+        <v>4.31990909576416</v>
       </c>
       <c r="C267" t="n">
-        <v>4.524770285790107</v>
+        <v>4.524770785240164</v>
       </c>
       <c r="D267" t="n">
-        <v>4.293187772004104</v>
+        <v>4.29318824589178</v>
       </c>
       <c r="E267" t="n">
-        <v>4.489142206746107</v>
+        <v>4.489142702263489</v>
       </c>
       <c r="F267" t="n">
         <v>6692300</v>
@@ -5772,16 +5772,16 @@
         <v>44802</v>
       </c>
       <c r="B268" t="n">
-        <v>4.453514575958252</v>
+        <v>4.453514099121094</v>
       </c>
       <c r="C268" t="n">
-        <v>4.48023585029091</v>
+        <v>4.480235370592709</v>
       </c>
       <c r="D268" t="n">
-        <v>4.266466929790385</v>
+        <v>4.266466472980391</v>
       </c>
       <c r="E268" t="n">
-        <v>4.275374162808021</v>
+        <v>4.275373705044331</v>
       </c>
       <c r="F268" t="n">
         <v>7870400</v>
@@ -5792,16 +5792,16 @@
         <v>44803</v>
       </c>
       <c r="B269" t="n">
-        <v>4.364444732666016</v>
+        <v>4.364444255828857</v>
       </c>
       <c r="C269" t="n">
-        <v>4.480236223211915</v>
+        <v>4.480235733723964</v>
       </c>
       <c r="D269" t="n">
-        <v>4.337723456109162</v>
+        <v>4.337722982191434</v>
       </c>
       <c r="E269" t="n">
-        <v>4.47132898945287</v>
+        <v>4.471328500938078</v>
       </c>
       <c r="F269" t="n">
         <v>7827400</v>
@@ -5812,16 +5812,16 @@
         <v>44804</v>
       </c>
       <c r="B270" t="n">
-        <v>4.311002731323242</v>
+        <v>4.311002254486084</v>
       </c>
       <c r="C270" t="n">
-        <v>4.43570103458292</v>
+        <v>4.435700543952965</v>
       </c>
       <c r="D270" t="n">
-        <v>4.284281453978878</v>
+        <v>4.284280980097343</v>
       </c>
       <c r="E270" t="n">
-        <v>4.382258904614487</v>
+        <v>4.382258419895731</v>
       </c>
       <c r="F270" t="n">
         <v>8375100</v>
@@ -5852,16 +5852,16 @@
         <v>44806</v>
       </c>
       <c r="B272" t="n">
-        <v>4.097232341766357</v>
+        <v>4.097233772277832</v>
       </c>
       <c r="C272" t="n">
-        <v>4.355536091211792</v>
+        <v>4.355537611907676</v>
       </c>
       <c r="D272" t="n">
-        <v>4.097232341766357</v>
+        <v>4.097233772277832</v>
       </c>
       <c r="E272" t="n">
-        <v>4.319908017131052</v>
+        <v>4.319909525387717</v>
       </c>
       <c r="F272" t="n">
         <v>69570300</v>
@@ -5892,16 +5892,16 @@
         <v>44810</v>
       </c>
       <c r="B274" t="n">
-        <v>3.954720735549927</v>
+        <v>3.954720973968506</v>
       </c>
       <c r="C274" t="n">
-        <v>4.177396449771971</v>
+        <v>4.177396701615019</v>
       </c>
       <c r="D274" t="n">
-        <v>3.94581350311534</v>
+        <v>3.945813740996928</v>
       </c>
       <c r="E274" t="n">
-        <v>4.141768369474061</v>
+        <v>4.141768619169197</v>
       </c>
       <c r="F274" t="n">
         <v>14609100</v>
@@ -5952,16 +5952,16 @@
         <v>44816</v>
       </c>
       <c r="B277" t="n">
-        <v>3.856743574142456</v>
+        <v>3.856743335723877</v>
       </c>
       <c r="C277" t="n">
-        <v>3.990349097034463</v>
+        <v>3.990348850356574</v>
       </c>
       <c r="D277" t="n">
-        <v>3.838929532738205</v>
+        <v>3.838929295420866</v>
       </c>
       <c r="E277" t="n">
-        <v>3.954721014225961</v>
+        <v>3.954720769750552</v>
       </c>
       <c r="F277" t="n">
         <v>15738600</v>
@@ -5972,16 +5972,16 @@
         <v>44817</v>
       </c>
       <c r="B278" t="n">
-        <v>3.696417570114136</v>
+        <v>3.696417093276978</v>
       </c>
       <c r="C278" t="n">
-        <v>3.88346523587145</v>
+        <v>3.883464734905179</v>
       </c>
       <c r="D278" t="n">
-        <v>3.678603526933453</v>
+        <v>3.678603052394303</v>
       </c>
       <c r="E278" t="n">
-        <v>3.874558001920963</v>
+        <v>3.874557502103723</v>
       </c>
       <c r="F278" t="n">
         <v>21443000</v>
@@ -5992,16 +5992,16 @@
         <v>44818</v>
       </c>
       <c r="B279" t="n">
-        <v>3.740951538085938</v>
+        <v>3.740952014923096</v>
       </c>
       <c r="C279" t="n">
-        <v>3.821114924881555</v>
+        <v>3.821115411936669</v>
       </c>
       <c r="D279" t="n">
-        <v>3.678602614773957</v>
+        <v>3.678603083663863</v>
       </c>
       <c r="E279" t="n">
-        <v>3.705323460559038</v>
+        <v>3.705323932854894</v>
       </c>
       <c r="F279" t="n">
         <v>13539100</v>
@@ -6032,16 +6032,16 @@
         <v>44820</v>
       </c>
       <c r="B281" t="n">
-        <v>3.821115493774414</v>
+        <v>3.821115255355835</v>
       </c>
       <c r="C281" t="n">
-        <v>3.892371659436928</v>
+        <v>3.892371416572319</v>
       </c>
       <c r="D281" t="n">
-        <v>3.660789121033758</v>
+        <v>3.660788892618747</v>
       </c>
       <c r="E281" t="n">
-        <v>3.696417203865015</v>
+        <v>3.696416973226988</v>
       </c>
       <c r="F281" t="n">
         <v>19813000</v>
@@ -6072,16 +6072,16 @@
         <v>44824</v>
       </c>
       <c r="B283" t="n">
-        <v>3.963627338409424</v>
+        <v>3.963627815246582</v>
       </c>
       <c r="C283" t="n">
-        <v>4.132860923437988</v>
+        <v>4.132861420634493</v>
       </c>
       <c r="D283" t="n">
-        <v>3.919092452698874</v>
+        <v>3.919092924178341</v>
       </c>
       <c r="E283" t="n">
-        <v>3.990348609611912</v>
+        <v>3.990349089663725</v>
       </c>
       <c r="F283" t="n">
         <v>10696200</v>
@@ -6092,16 +6092,16 @@
         <v>44825</v>
       </c>
       <c r="B284" t="n">
-        <v>3.883464813232422</v>
+        <v>3.883464336395264</v>
       </c>
       <c r="C284" t="n">
-        <v>4.034884376149319</v>
+        <v>4.034883880719878</v>
       </c>
       <c r="D284" t="n">
-        <v>3.830022689506502</v>
+        <v>3.830022219231316</v>
       </c>
       <c r="E284" t="n">
-        <v>3.972535019442289</v>
+        <v>3.97253453166851</v>
       </c>
       <c r="F284" t="n">
         <v>18275700</v>
@@ -6112,16 +6112,16 @@
         <v>44826</v>
       </c>
       <c r="B285" t="n">
-        <v>4.052698135375977</v>
+        <v>4.052698612213135</v>
       </c>
       <c r="C285" t="n">
-        <v>4.097233023021737</v>
+        <v>4.097233505098832</v>
       </c>
       <c r="D285" t="n">
-        <v>3.90127858299592</v>
+        <v>3.901279042017177</v>
       </c>
       <c r="E285" t="n">
-        <v>3.936906663000614</v>
+        <v>3.936907126213841</v>
       </c>
       <c r="F285" t="n">
         <v>13589200</v>
@@ -6152,16 +6152,16 @@
         <v>44830</v>
       </c>
       <c r="B287" t="n">
-        <v>3.821115493774414</v>
+        <v>3.821115255355835</v>
       </c>
       <c r="C287" t="n">
-        <v>3.936906975336123</v>
+        <v>3.936906729692732</v>
       </c>
       <c r="D287" t="n">
-        <v>3.794394644011096</v>
+        <v>3.794394407259765</v>
       </c>
       <c r="E287" t="n">
-        <v>3.901278892504866</v>
+        <v>3.901278649084491</v>
       </c>
       <c r="F287" t="n">
         <v>9718800</v>
@@ -6172,16 +6172,16 @@
         <v>44831</v>
       </c>
       <c r="B288" t="n">
-        <v>3.732044696807861</v>
+        <v>3.732045412063599</v>
       </c>
       <c r="C288" t="n">
-        <v>3.919092314467266</v>
+        <v>3.91909306557115</v>
       </c>
       <c r="D288" t="n">
-        <v>3.732044696807861</v>
+        <v>3.732045412063599</v>
       </c>
       <c r="E288" t="n">
-        <v>3.838928928407469</v>
+        <v>3.838929664147838</v>
       </c>
       <c r="F288" t="n">
         <v>11052300</v>
@@ -6192,16 +6192,16 @@
         <v>44832</v>
       </c>
       <c r="B289" t="n">
-        <v>3.687510251998901</v>
+        <v>3.687509775161743</v>
       </c>
       <c r="C289" t="n">
-        <v>3.767673656842447</v>
+        <v>3.767673169639246</v>
       </c>
       <c r="D289" t="n">
-        <v>3.687510251998901</v>
+        <v>3.687509775161743</v>
       </c>
       <c r="E289" t="n">
-        <v>3.749859614068357</v>
+        <v>3.749859129168715</v>
       </c>
       <c r="F289" t="n">
         <v>11148900</v>
@@ -6212,16 +6212,16 @@
         <v>44833</v>
       </c>
       <c r="B290" t="n">
-        <v>3.696417570114136</v>
+        <v>3.696417093276978</v>
       </c>
       <c r="C290" t="n">
-        <v>3.714231613294819</v>
+        <v>3.714231134159652</v>
       </c>
       <c r="D290" t="n">
-        <v>3.616254163440918</v>
+        <v>3.616253696944824</v>
       </c>
       <c r="E290" t="n">
-        <v>3.660789483752771</v>
+        <v>3.660789011511628</v>
       </c>
       <c r="F290" t="n">
         <v>12380300</v>
@@ -6232,16 +6232,16 @@
         <v>44834</v>
       </c>
       <c r="B291" t="n">
-        <v>3.732044696807861</v>
+        <v>3.732045412063599</v>
       </c>
       <c r="C291" t="n">
-        <v>3.794394044267724</v>
+        <v>3.79439477147287</v>
       </c>
       <c r="D291" t="n">
-        <v>3.651881310748065</v>
+        <v>3.651882010640287</v>
       </c>
       <c r="E291" t="n">
-        <v>3.660788542408123</v>
+        <v>3.660789244007439</v>
       </c>
       <c r="F291" t="n">
         <v>11827700</v>
@@ -6252,16 +6252,16 @@
         <v>44837</v>
       </c>
       <c r="B292" t="n">
-        <v>3.939895391464233</v>
+        <v>3.939894676208496</v>
       </c>
       <c r="C292" t="n">
-        <v>3.939895391464233</v>
+        <v>3.939894676208497</v>
       </c>
       <c r="D292" t="n">
-        <v>3.79630024781367</v>
+        <v>3.796299558626456</v>
       </c>
       <c r="E292" t="n">
-        <v>3.814249640769991</v>
+        <v>3.814248948324211</v>
       </c>
       <c r="F292" t="n">
         <v>14167700</v>
@@ -6272,16 +6272,16 @@
         <v>44838</v>
       </c>
       <c r="B293" t="n">
-        <v>3.930919885635376</v>
+        <v>3.930920124053955</v>
       </c>
       <c r="C293" t="n">
-        <v>4.056565603620654</v>
+        <v>4.05656584965991</v>
       </c>
       <c r="D293" t="n">
-        <v>3.895021109068154</v>
+        <v>3.895021345309396</v>
       </c>
       <c r="E293" t="n">
-        <v>3.975793142370817</v>
+        <v>3.975793383511054</v>
       </c>
       <c r="F293" t="n">
         <v>11413300</v>
@@ -6292,16 +6292,16 @@
         <v>44839</v>
       </c>
       <c r="B294" t="n">
-        <v>3.975793361663818</v>
+        <v>3.975793600082397</v>
       </c>
       <c r="C294" t="n">
-        <v>3.975793361663818</v>
+        <v>3.975793600082397</v>
       </c>
       <c r="D294" t="n">
-        <v>3.868097026021941</v>
+        <v>3.868097257982235</v>
       </c>
       <c r="E294" t="n">
-        <v>3.92194519384288</v>
+        <v>3.921945429032316</v>
       </c>
       <c r="F294" t="n">
         <v>8368900</v>
@@ -6312,16 +6312,16 @@
         <v>44840</v>
       </c>
       <c r="B295" t="n">
-        <v>4.002717971801758</v>
+        <v>4.0027174949646</v>
       </c>
       <c r="C295" t="n">
-        <v>4.029641843838973</v>
+        <v>4.029641363794418</v>
       </c>
       <c r="D295" t="n">
-        <v>3.975793671817313</v>
+        <v>3.975793198187602</v>
       </c>
       <c r="E295" t="n">
-        <v>3.9937430624912</v>
+        <v>3.993742586723207</v>
       </c>
       <c r="F295" t="n">
         <v>5975200</v>
@@ -6332,16 +6332,16 @@
         <v>44841</v>
       </c>
       <c r="B296" t="n">
-        <v>3.760400533676147</v>
+        <v>3.760401010513306</v>
       </c>
       <c r="C296" t="n">
-        <v>4.002717492746105</v>
+        <v>4.002718000310238</v>
       </c>
       <c r="D296" t="n">
-        <v>3.715526848388416</v>
+        <v>3.715527319535371</v>
       </c>
       <c r="E296" t="n">
-        <v>3.984768104220449</v>
+        <v>3.984768609508511</v>
       </c>
       <c r="F296" t="n">
         <v>16354500</v>
@@ -6352,16 +6352,16 @@
         <v>44844</v>
       </c>
       <c r="B297" t="n">
-        <v>3.661679029464722</v>
+        <v>3.661678791046143</v>
       </c>
       <c r="C297" t="n">
-        <v>3.80527415126421</v>
+        <v>3.805273903495892</v>
       </c>
       <c r="D297" t="n">
-        <v>3.634755158100927</v>
+        <v>3.63475492143541</v>
       </c>
       <c r="E297" t="n">
-        <v>3.80527415126421</v>
+        <v>3.805273903495892</v>
       </c>
       <c r="F297" t="n">
         <v>18862600</v>
@@ -6372,16 +6372,16 @@
         <v>44845</v>
       </c>
       <c r="B298" t="n">
-        <v>3.903995513916016</v>
+        <v>3.903995037078857</v>
       </c>
       <c r="C298" t="n">
-        <v>3.948869197732875</v>
+        <v>3.948868715414809</v>
       </c>
       <c r="D298" t="n">
-        <v>3.634754694856352</v>
+        <v>3.634754250904485</v>
       </c>
       <c r="E298" t="n">
-        <v>3.661678562788736</v>
+        <v>3.661678115548366</v>
       </c>
       <c r="F298" t="n">
         <v>30833900</v>
@@ -6392,16 +6392,16 @@
         <v>44847</v>
       </c>
       <c r="B299" t="n">
-        <v>3.814249038696289</v>
+        <v>3.81424880027771</v>
       </c>
       <c r="C299" t="n">
-        <v>3.903995989311464</v>
+        <v>3.903995745283042</v>
       </c>
       <c r="D299" t="n">
-        <v>3.796299648573254</v>
+        <v>3.796299411276644</v>
       </c>
       <c r="E299" t="n">
-        <v>3.895021508223556</v>
+        <v>3.895021264756104</v>
       </c>
       <c r="F299" t="n">
         <v>15027200</v>
@@ -6412,16 +6412,16 @@
         <v>44848</v>
       </c>
       <c r="B300" t="n">
-        <v>3.688603162765503</v>
+        <v>3.688603401184082</v>
       </c>
       <c r="C300" t="n">
-        <v>3.832198278102312</v>
+        <v>3.832198525802385</v>
       </c>
       <c r="D300" t="n">
-        <v>3.679628254083352</v>
+        <v>3.679628491921824</v>
       </c>
       <c r="E300" t="n">
-        <v>3.823223797367362</v>
+        <v>3.823224044487355</v>
       </c>
       <c r="F300" t="n">
         <v>10535000</v>
@@ -6452,16 +6452,16 @@
         <v>44852</v>
       </c>
       <c r="B302" t="n">
-        <v>3.715527534484863</v>
+        <v>3.715527057647705</v>
       </c>
       <c r="C302" t="n">
-        <v>3.787325101845382</v>
+        <v>3.787324615793987</v>
       </c>
       <c r="D302" t="n">
-        <v>3.661679358964475</v>
+        <v>3.661678889037994</v>
       </c>
       <c r="E302" t="n">
-        <v>3.724502444378557</v>
+        <v>3.724501966389592</v>
       </c>
       <c r="F302" t="n">
         <v>13196400</v>
@@ -6472,16 +6472,16 @@
         <v>44853</v>
       </c>
       <c r="B303" t="n">
-        <v>3.733476400375366</v>
+        <v>3.733476161956787</v>
       </c>
       <c r="C303" t="n">
-        <v>3.769375178998422</v>
+        <v>3.769374938287358</v>
       </c>
       <c r="D303" t="n">
-        <v>3.670653751758618</v>
+        <v>3.670653517351873</v>
       </c>
       <c r="E303" t="n">
-        <v>3.715527011063839</v>
+        <v>3.715526773791502</v>
       </c>
       <c r="F303" t="n">
         <v>12625300</v>
@@ -6492,16 +6492,16 @@
         <v>44854</v>
       </c>
       <c r="B304" t="n">
-        <v>3.769374847412109</v>
+        <v>3.769375324249268</v>
       </c>
       <c r="C304" t="n">
-        <v>3.796299142984509</v>
+        <v>3.796299623227672</v>
       </c>
       <c r="D304" t="n">
-        <v>3.706552204321775</v>
+        <v>3.706552673211682</v>
       </c>
       <c r="E304" t="n">
-        <v>3.760400367519416</v>
+        <v>3.760400843221276</v>
       </c>
       <c r="F304" t="n">
         <v>13428400</v>
@@ -6552,16 +6552,16 @@
         <v>44859</v>
       </c>
       <c r="B307" t="n">
-        <v>3.670653820037842</v>
+        <v>3.670654058456421</v>
       </c>
       <c r="C307" t="n">
-        <v>3.769375249114001</v>
+        <v>3.769375493944795</v>
       </c>
       <c r="D307" t="n">
-        <v>3.661678911241534</v>
+        <v>3.661679149077169</v>
       </c>
       <c r="E307" t="n">
-        <v>3.706552599328664</v>
+        <v>3.706552840078963</v>
       </c>
       <c r="F307" t="n">
         <v>12220200</v>
@@ -6572,16 +6572,16 @@
         <v>44860</v>
       </c>
       <c r="B308" t="n">
-        <v>3.562957286834717</v>
+        <v>3.562957048416138</v>
       </c>
       <c r="C308" t="n">
-        <v>3.670653839244302</v>
+        <v>3.670653593619109</v>
       </c>
       <c r="D308" t="n">
-        <v>3.545007897095387</v>
+        <v>3.545007659877907</v>
       </c>
       <c r="E308" t="n">
-        <v>3.661678930401033</v>
+        <v>3.661678685376404</v>
       </c>
       <c r="F308" t="n">
         <v>15630800</v>
@@ -6632,16 +6632,16 @@
         <v>44865</v>
       </c>
       <c r="B311" t="n">
-        <v>3.85014796257019</v>
+        <v>3.850147724151611</v>
       </c>
       <c r="C311" t="n">
-        <v>3.868097353362819</v>
+        <v>3.868097113832732</v>
       </c>
       <c r="D311" t="n">
-        <v>3.545008105121898</v>
+        <v>3.545007885598959</v>
       </c>
       <c r="E311" t="n">
-        <v>3.589881582103468</v>
+        <v>3.58988135980176</v>
       </c>
       <c r="F311" t="n">
         <v>19491700</v>
@@ -6712,16 +6712,16 @@
         <v>44872</v>
       </c>
       <c r="B315" t="n">
-        <v>4.011692047119141</v>
+        <v>4.011692523956299</v>
       </c>
       <c r="C315" t="n">
-        <v>4.37965516061104</v>
+        <v>4.379655681184977</v>
       </c>
       <c r="D315" t="n">
-        <v>4.011692047119141</v>
+        <v>4.011692523956299</v>
       </c>
       <c r="E315" t="n">
-        <v>4.3168320856375</v>
+        <v>4.316832598744169</v>
       </c>
       <c r="F315" t="n">
         <v>17217400</v>
@@ -6732,16 +6732,16 @@
         <v>44873</v>
       </c>
       <c r="B316" t="n">
-        <v>4.083489894866943</v>
+        <v>4.083490371704102</v>
       </c>
       <c r="C316" t="n">
-        <v>4.110413763284799</v>
+        <v>4.110414243265911</v>
       </c>
       <c r="D316" t="n">
-        <v>3.966818657197105</v>
+        <v>3.966819120410333</v>
       </c>
       <c r="E316" t="n">
-        <v>4.011691913875923</v>
+        <v>4.01169238232909</v>
       </c>
       <c r="F316" t="n">
         <v>15444300</v>
@@ -6752,16 +6752,16 @@
         <v>44874</v>
       </c>
       <c r="B317" t="n">
-        <v>4.011692047119141</v>
+        <v>4.011692523956299</v>
       </c>
       <c r="C317" t="n">
-        <v>4.173236974780477</v>
+        <v>4.173237470819165</v>
       </c>
       <c r="D317" t="n">
-        <v>3.984768177807042</v>
+        <v>3.98476865144398</v>
       </c>
       <c r="E317" t="n">
-        <v>4.06554064163771</v>
+        <v>4.065541124875413</v>
       </c>
       <c r="F317" t="n">
         <v>11339500</v>
@@ -6772,16 +6772,16 @@
         <v>44875</v>
       </c>
       <c r="B318" t="n">
-        <v>3.688603162765503</v>
+        <v>3.688603401184082</v>
       </c>
       <c r="C318" t="n">
-        <v>3.975793393439122</v>
+        <v>3.975793650420687</v>
       </c>
       <c r="D318" t="n">
-        <v>3.670653773348401</v>
+        <v>3.670654010606794</v>
       </c>
       <c r="E318" t="n">
-        <v>3.921945225187819</v>
+        <v>3.921945478688824</v>
       </c>
       <c r="F318" t="n">
         <v>22566600</v>
@@ -6792,16 +6792,16 @@
         <v>44876</v>
       </c>
       <c r="B319" t="n">
-        <v>3.715527534484863</v>
+        <v>3.715527057647705</v>
       </c>
       <c r="C319" t="n">
-        <v>3.751426318165122</v>
+        <v>3.751425836720846</v>
       </c>
       <c r="D319" t="n">
-        <v>3.437311746989228</v>
+        <v>3.437311305857262</v>
       </c>
       <c r="E319" t="n">
-        <v>3.63475548517791</v>
+        <v>3.634755018706739</v>
       </c>
       <c r="F319" t="n">
         <v>24235200</v>
@@ -6832,16 +6832,16 @@
         <v>44881</v>
       </c>
       <c r="B321" t="n">
-        <v>3.616805791854858</v>
+        <v>3.616805553436279</v>
       </c>
       <c r="C321" t="n">
-        <v>3.760400914606361</v>
+        <v>3.760400666722041</v>
       </c>
       <c r="D321" t="n">
-        <v>3.553982711677465</v>
+        <v>3.553982477400161</v>
       </c>
       <c r="E321" t="n">
-        <v>3.697577834428968</v>
+        <v>3.697577590685923</v>
       </c>
       <c r="F321" t="n">
         <v>16148800</v>
@@ -6892,16 +6892,16 @@
         <v>44886</v>
       </c>
       <c r="B324" t="n">
-        <v>3.616805791854858</v>
+        <v>3.616805553436279</v>
       </c>
       <c r="C324" t="n">
-        <v>3.733476615116843</v>
+        <v>3.733476369007364</v>
       </c>
       <c r="D324" t="n">
-        <v>3.545008016505496</v>
+        <v>3.545007782819801</v>
       </c>
       <c r="E324" t="n">
-        <v>3.67962844408503</v>
+        <v>3.679628201525203</v>
       </c>
       <c r="F324" t="n">
         <v>11314600</v>
@@ -6912,16 +6912,16 @@
         <v>44887</v>
       </c>
       <c r="B325" t="n">
-        <v>3.616805791854858</v>
+        <v>3.616805553436279</v>
       </c>
       <c r="C325" t="n">
-        <v>3.661679053741092</v>
+        <v>3.661678812364483</v>
       </c>
       <c r="D325" t="n">
-        <v>3.562957406849434</v>
+        <v>3.562957171980521</v>
       </c>
       <c r="E325" t="n">
-        <v>3.616805791854858</v>
+        <v>3.616805553436279</v>
       </c>
       <c r="F325" t="n">
         <v>10439300</v>
@@ -6992,16 +6992,16 @@
         <v>44893</v>
       </c>
       <c r="B329" t="n">
-        <v>3.60783052444458</v>
+        <v>3.607830762863159</v>
       </c>
       <c r="C329" t="n">
-        <v>3.670653598383518</v>
+        <v>3.670653840953675</v>
       </c>
       <c r="D329" t="n">
-        <v>3.589881135883052</v>
+        <v>3.58988137311547</v>
       </c>
       <c r="E329" t="n">
-        <v>3.589881135883052</v>
+        <v>3.58988137311547</v>
       </c>
       <c r="F329" t="n">
         <v>7386900</v>
@@ -7052,16 +7052,16 @@
         <v>44896</v>
       </c>
       <c r="B332" t="n">
-        <v>3.446286201477051</v>
+        <v>3.446285724639893</v>
       </c>
       <c r="C332" t="n">
-        <v>3.589881540112033</v>
+        <v>3.589881043406649</v>
       </c>
       <c r="D332" t="n">
-        <v>3.428336810894379</v>
+        <v>3.428336336540746</v>
       </c>
       <c r="E332" t="n">
-        <v>3.589881540112033</v>
+        <v>3.589881043406649</v>
       </c>
       <c r="F332" t="n">
         <v>22625600</v>
@@ -7092,16 +7092,16 @@
         <v>44900</v>
       </c>
       <c r="B334" t="n">
-        <v>3.347564220428467</v>
+        <v>3.347564458847046</v>
       </c>
       <c r="C334" t="n">
-        <v>3.545007711179917</v>
+        <v>3.545007963660719</v>
       </c>
       <c r="D334" t="n">
-        <v>3.32961483163048</v>
+        <v>3.329615068770676</v>
       </c>
       <c r="E334" t="n">
-        <v>3.545007711179917</v>
+        <v>3.545007963660719</v>
       </c>
       <c r="F334" t="n">
         <v>14607600</v>
@@ -7112,16 +7112,16 @@
         <v>44901</v>
       </c>
       <c r="B335" t="n">
-        <v>3.302690982818604</v>
+        <v>3.302690744400024</v>
       </c>
       <c r="C335" t="n">
-        <v>3.401412628213602</v>
+        <v>3.401412382668387</v>
       </c>
       <c r="D335" t="n">
-        <v>3.248842598629542</v>
+        <v>3.248842364098234</v>
       </c>
       <c r="E335" t="n">
-        <v>3.383463238141784</v>
+        <v>3.383462993892321</v>
       </c>
       <c r="F335" t="n">
         <v>13327400</v>
@@ -7132,16 +7132,16 @@
         <v>44902</v>
       </c>
       <c r="B336" t="n">
-        <v>3.230893135070801</v>
+        <v>3.230892896652222</v>
       </c>
       <c r="C336" t="n">
-        <v>3.320640297362192</v>
+        <v>3.320640052320865</v>
       </c>
       <c r="D336" t="n">
-        <v>3.212943745407243</v>
+        <v>3.212943508313211</v>
       </c>
       <c r="E336" t="n">
-        <v>3.302690907698634</v>
+        <v>3.302690663981854</v>
       </c>
       <c r="F336" t="n">
         <v>13628700</v>
@@ -7332,16 +7332,16 @@
         <v>44916</v>
       </c>
       <c r="B346" t="n">
-        <v>3.33124041557312</v>
+        <v>3.331240892410278</v>
       </c>
       <c r="C346" t="n">
-        <v>3.377252200497974</v>
+        <v>3.377252683921307</v>
       </c>
       <c r="D346" t="n">
-        <v>3.239217284524313</v>
+        <v>3.239217748189187</v>
       </c>
       <c r="E346" t="n">
-        <v>3.266824223838955</v>
+        <v>3.266824691455514</v>
       </c>
       <c r="F346" t="n">
         <v>14610300</v>
@@ -7372,16 +7372,16 @@
         <v>44918</v>
       </c>
       <c r="B348" t="n">
-        <v>3.414061784744263</v>
+        <v>3.414061546325684</v>
       </c>
       <c r="C348" t="n">
-        <v>3.441668726742138</v>
+        <v>3.441668486395647</v>
       </c>
       <c r="D348" t="n">
-        <v>3.34044327274993</v>
+        <v>3.340443039472447</v>
       </c>
       <c r="E348" t="n">
-        <v>3.358847900748513</v>
+        <v>3.358847666185756</v>
       </c>
       <c r="F348" t="n">
         <v>4486400</v>
@@ -7412,16 +7412,16 @@
         <v>44922</v>
       </c>
       <c r="B350" t="n">
-        <v>3.386454820632935</v>
+        <v>3.386454582214355</v>
       </c>
       <c r="C350" t="n">
-        <v>3.395657134572136</v>
+        <v>3.39565689550568</v>
       </c>
       <c r="D350" t="n">
-        <v>3.276026833962055</v>
+        <v>3.276026603318003</v>
       </c>
       <c r="E350" t="n">
-        <v>3.349645564876132</v>
+        <v>3.349645329049056</v>
       </c>
       <c r="F350" t="n">
         <v>5669100</v>
@@ -7532,16 +7532,16 @@
         <v>44931</v>
       </c>
       <c r="B356" t="n">
-        <v>2.972350358963013</v>
+        <v>2.972350120544434</v>
       </c>
       <c r="C356" t="n">
-        <v>3.11958760656197</v>
+        <v>3.119587356333176</v>
       </c>
       <c r="D356" t="n">
-        <v>2.935541101913393</v>
+        <v>2.935540866447363</v>
       </c>
       <c r="E356" t="n">
-        <v>3.082778130111872</v>
+        <v>3.082777882835645</v>
       </c>
       <c r="F356" t="n">
         <v>35445300</v>
@@ -7572,16 +7572,16 @@
         <v>44935</v>
       </c>
       <c r="B358" t="n">
-        <v>2.972350358963013</v>
+        <v>2.972350120544434</v>
       </c>
       <c r="C358" t="n">
-        <v>3.027564244537442</v>
+        <v>3.027564001690039</v>
       </c>
       <c r="D358" t="n">
-        <v>2.907934159126178</v>
+        <v>2.90793392587456</v>
       </c>
       <c r="E358" t="n">
-        <v>2.944743416175798</v>
+        <v>2.944743179971631</v>
       </c>
       <c r="F358" t="n">
         <v>15633700</v>
@@ -7612,16 +7612,16 @@
         <v>44937</v>
       </c>
       <c r="B360" t="n">
-        <v>3.294431447982788</v>
+        <v>3.294431209564209</v>
       </c>
       <c r="C360" t="n">
-        <v>3.294431447982788</v>
+        <v>3.294431209564209</v>
       </c>
       <c r="D360" t="n">
-        <v>3.091980322771489</v>
+        <v>3.091980099004334</v>
       </c>
       <c r="E360" t="n">
-        <v>3.091980322771489</v>
+        <v>3.091980099004334</v>
       </c>
       <c r="F360" t="n">
         <v>21444400</v>
@@ -7632,16 +7632,16 @@
         <v>44938</v>
       </c>
       <c r="B361" t="n">
-        <v>3.211610555648804</v>
+        <v>3.211610794067383</v>
       </c>
       <c r="C361" t="n">
-        <v>3.349645480667133</v>
+        <v>3.349645729332935</v>
       </c>
       <c r="D361" t="n">
-        <v>3.165598987109516</v>
+        <v>3.165599222112359</v>
       </c>
       <c r="E361" t="n">
-        <v>3.266824437895949</v>
+        <v>3.266824680413411</v>
       </c>
       <c r="F361" t="n">
         <v>13176700</v>
@@ -7692,16 +7692,16 @@
         <v>44943</v>
       </c>
       <c r="B364" t="n">
-        <v>3.091980457305908</v>
+        <v>3.091980218887329</v>
       </c>
       <c r="C364" t="n">
-        <v>3.128789933909955</v>
+        <v>3.128789692653045</v>
       </c>
       <c r="D364" t="n">
-        <v>3.027564257199665</v>
+        <v>3.027564023748135</v>
       </c>
       <c r="E364" t="n">
-        <v>3.055171200102341</v>
+        <v>3.055170964522075</v>
       </c>
       <c r="F364" t="n">
         <v>11859400</v>
@@ -7732,16 +7732,16 @@
         <v>44945</v>
       </c>
       <c r="B366" t="n">
-        <v>3.137991905212402</v>
+        <v>3.137992143630981</v>
       </c>
       <c r="C366" t="n">
-        <v>3.147194218507435</v>
+        <v>3.147194457625188</v>
       </c>
       <c r="D366" t="n">
-        <v>2.99075467309143</v>
+        <v>2.990754900323207</v>
       </c>
       <c r="E366" t="n">
-        <v>3.082777806041753</v>
+        <v>3.082778040265271</v>
       </c>
       <c r="F366" t="n">
         <v>23712400</v>
@@ -7792,16 +7792,16 @@
         <v>44950</v>
       </c>
       <c r="B369" t="n">
-        <v>3.193206071853638</v>
+        <v>3.193205833435059</v>
       </c>
       <c r="C369" t="n">
-        <v>3.202408385975387</v>
+        <v>3.202408146869723</v>
       </c>
       <c r="D369" t="n">
-        <v>3.018361884139927</v>
+        <v>3.018361658775971</v>
       </c>
       <c r="E369" t="n">
-        <v>3.045968826505175</v>
+        <v>3.045968599079965</v>
       </c>
       <c r="F369" t="n">
         <v>12703800</v>
@@ -7812,16 +7812,16 @@
         <v>44951</v>
       </c>
       <c r="B370" t="n">
-        <v>3.248419761657715</v>
+        <v>3.248420000076294</v>
       </c>
       <c r="C370" t="n">
-        <v>3.248419761657715</v>
+        <v>3.248420000076294</v>
       </c>
       <c r="D370" t="n">
-        <v>3.147194312392662</v>
+        <v>3.147194543381774</v>
       </c>
       <c r="E370" t="n">
-        <v>3.193205880240413</v>
+        <v>3.193206114606555</v>
       </c>
       <c r="F370" t="n">
         <v>7649000</v>
@@ -7832,16 +7832,16 @@
         <v>44952</v>
       </c>
       <c r="B371" t="n">
-        <v>3.202408313751221</v>
+        <v>3.2024085521698</v>
       </c>
       <c r="C371" t="n">
-        <v>3.2852291389791</v>
+        <v>3.28522938356367</v>
       </c>
       <c r="D371" t="n">
-        <v>3.184003685922803</v>
+        <v>3.184003922971162</v>
       </c>
       <c r="E371" t="n">
-        <v>3.257622197236473</v>
+        <v>3.257622439765714</v>
       </c>
       <c r="F371" t="n">
         <v>8271800</v>
@@ -7852,16 +7852,16 @@
         <v>44953</v>
       </c>
       <c r="B372" t="n">
-        <v>3.147194623947144</v>
+        <v>3.147194147109985</v>
       </c>
       <c r="C372" t="n">
-        <v>3.220813139791363</v>
+        <v>3.22081265180013</v>
       </c>
       <c r="D372" t="n">
-        <v>3.128789994986088</v>
+        <v>3.128789520937449</v>
       </c>
       <c r="E372" t="n">
-        <v>3.211610825310835</v>
+        <v>3.211610338713862</v>
       </c>
       <c r="F372" t="n">
         <v>8557200</v>
@@ -7872,16 +7872,16 @@
         <v>44956</v>
       </c>
       <c r="B373" t="n">
-        <v>2.9907546043396</v>
+        <v>2.990754842758179</v>
       </c>
       <c r="C373" t="n">
-        <v>3.156396459242842</v>
+        <v>3.156396710866147</v>
       </c>
       <c r="D373" t="n">
-        <v>2.963147665089134</v>
+        <v>2.963147901306928</v>
       </c>
       <c r="E373" t="n">
-        <v>3.128789519992377</v>
+        <v>3.128789769414897</v>
       </c>
       <c r="F373" t="n">
         <v>24955900</v>
@@ -7952,16 +7952,16 @@
         <v>44960</v>
       </c>
       <c r="B377" t="n">
-        <v>2.843517780303955</v>
+        <v>2.843517541885376</v>
       </c>
       <c r="C377" t="n">
-        <v>2.871124723483549</v>
+        <v>2.871124482750229</v>
       </c>
       <c r="D377" t="n">
-        <v>2.705483064405985</v>
+        <v>2.705482837561113</v>
       </c>
       <c r="E377" t="n">
-        <v>2.806708522731163</v>
+        <v>2.806708287398906</v>
       </c>
       <c r="F377" t="n">
         <v>53290600</v>
@@ -7992,16 +7992,16 @@
         <v>44964</v>
       </c>
       <c r="B379" t="n">
-        <v>2.880327224731445</v>
+        <v>2.880326986312866</v>
       </c>
       <c r="C379" t="n">
-        <v>2.953945739045189</v>
+        <v>2.95394549453285</v>
       </c>
       <c r="D379" t="n">
-        <v>2.843517748174095</v>
+        <v>2.843517512802413</v>
       </c>
       <c r="E379" t="n">
-        <v>2.926338796177535</v>
+        <v>2.926338553950356</v>
       </c>
       <c r="F379" t="n">
         <v>31913300</v>
@@ -8032,16 +8032,16 @@
         <v>44966</v>
       </c>
       <c r="B381" t="n">
-        <v>3.018361806869507</v>
+        <v>3.018362045288086</v>
       </c>
       <c r="C381" t="n">
-        <v>3.091980317958858</v>
+        <v>3.091980562192519</v>
       </c>
       <c r="D381" t="n">
-        <v>2.935540981893987</v>
+        <v>2.935541213770599</v>
       </c>
       <c r="E381" t="n">
-        <v>3.036766434641845</v>
+        <v>3.036766674514194</v>
       </c>
       <c r="F381" t="n">
         <v>43678900</v>
@@ -8092,16 +8092,16 @@
         <v>44971</v>
       </c>
       <c r="B384" t="n">
-        <v>2.742292165756226</v>
+        <v>2.742292404174805</v>
       </c>
       <c r="C384" t="n">
-        <v>2.953945604142814</v>
+        <v>2.953945860962829</v>
       </c>
       <c r="D384" t="n">
-        <v>2.723887538018302</v>
+        <v>2.723887774836758</v>
       </c>
       <c r="E384" t="n">
-        <v>2.953945604142814</v>
+        <v>2.953945860962829</v>
       </c>
       <c r="F384" t="n">
         <v>40924300</v>
@@ -8112,16 +8112,16 @@
         <v>44972</v>
       </c>
       <c r="B385" t="n">
-        <v>2.843517780303955</v>
+        <v>2.843517541885376</v>
       </c>
       <c r="C385" t="n">
-        <v>2.852720094697153</v>
+        <v>2.852719855506993</v>
       </c>
       <c r="D385" t="n">
-        <v>2.63186432985992</v>
+        <v>2.631864109187709</v>
       </c>
       <c r="E385" t="n">
-        <v>2.733090007585579</v>
+        <v>2.733089778425966</v>
       </c>
       <c r="F385" t="n">
         <v>42760100</v>
@@ -8152,16 +8152,16 @@
         <v>44974</v>
       </c>
       <c r="B387" t="n">
-        <v>2.78830361366272</v>
+        <v>2.788303852081299</v>
       </c>
       <c r="C387" t="n">
-        <v>2.8711244348763</v>
+        <v>2.871124680376612</v>
       </c>
       <c r="D387" t="n">
-        <v>2.769898986726369</v>
+        <v>2.769899223571229</v>
       </c>
       <c r="E387" t="n">
-        <v>2.825112867535422</v>
+        <v>2.825113109101438</v>
       </c>
       <c r="F387" t="n">
         <v>27974700</v>
@@ -8212,16 +8212,16 @@
         <v>44981</v>
       </c>
       <c r="B390" t="n">
-        <v>2.659471273422241</v>
+        <v>2.65947151184082</v>
       </c>
       <c r="C390" t="n">
-        <v>2.806708291587871</v>
+        <v>2.806708543206081</v>
       </c>
       <c r="D390" t="n">
-        <v>2.65026895978689</v>
+        <v>2.650269197380491</v>
       </c>
       <c r="E390" t="n">
-        <v>2.797505977952519</v>
+        <v>2.797506228745752</v>
       </c>
       <c r="F390" t="n">
         <v>27929600</v>
@@ -8292,16 +8292,16 @@
         <v>44987</v>
       </c>
       <c r="B394" t="n">
-        <v>2.687078237533569</v>
+        <v>2.68707799911499</v>
       </c>
       <c r="C394" t="n">
-        <v>2.797506002111432</v>
+        <v>2.797505753894839</v>
       </c>
       <c r="D394" t="n">
-        <v>2.687078237533569</v>
+        <v>2.68707799911499</v>
       </c>
       <c r="E394" t="n">
-        <v>2.779101374681788</v>
+        <v>2.779101128098197</v>
       </c>
       <c r="F394" t="n">
         <v>21864000</v>
@@ -8312,16 +8312,16 @@
         <v>44988</v>
       </c>
       <c r="B395" t="n">
-        <v>2.604257345199585</v>
+        <v>2.604257106781006</v>
       </c>
       <c r="C395" t="n">
-        <v>2.71468533555954</v>
+        <v>2.714685087031328</v>
       </c>
       <c r="D395" t="n">
-        <v>2.55824577396647</v>
+        <v>2.558245539760229</v>
       </c>
       <c r="E395" t="n">
-        <v>2.71468533555954</v>
+        <v>2.714685087031328</v>
       </c>
       <c r="F395" t="n">
         <v>36019100</v>
@@ -8372,16 +8372,16 @@
         <v>44993</v>
       </c>
       <c r="B398" t="n">
-        <v>2.705482959747314</v>
+        <v>2.705482721328735</v>
       </c>
       <c r="C398" t="n">
-        <v>2.733089901858964</v>
+        <v>2.733089661007544</v>
       </c>
       <c r="D398" t="n">
-        <v>2.659471389561232</v>
+        <v>2.659471155197387</v>
       </c>
       <c r="E398" t="n">
-        <v>2.677876017635665</v>
+        <v>2.677875781649926</v>
       </c>
       <c r="F398" t="n">
         <v>21816400</v>
@@ -8452,16 +8452,16 @@
         <v>44999</v>
       </c>
       <c r="B402" t="n">
-        <v>2.493829488754272</v>
+        <v>2.493829250335693</v>
       </c>
       <c r="C402" t="n">
-        <v>2.585852628066047</v>
+        <v>2.585852380849743</v>
       </c>
       <c r="D402" t="n">
-        <v>2.46622254696074</v>
+        <v>2.466222311181478</v>
       </c>
       <c r="E402" t="n">
-        <v>2.475424860891918</v>
+        <v>2.475424624232883</v>
       </c>
       <c r="F402" t="n">
         <v>40119200</v>
@@ -8472,16 +8472,16 @@
         <v>45000</v>
       </c>
       <c r="B403" t="n">
-        <v>2.493829488754272</v>
+        <v>2.493829250335693</v>
       </c>
       <c r="C403" t="n">
-        <v>2.521436430547805</v>
+        <v>2.521436189489909</v>
       </c>
       <c r="D403" t="n">
-        <v>2.447817919098385</v>
+        <v>2.447817685078669</v>
       </c>
       <c r="E403" t="n">
-        <v>2.475424860891918</v>
+        <v>2.475424624232883</v>
       </c>
       <c r="F403" t="n">
         <v>17612600</v>
@@ -8492,16 +8492,16 @@
         <v>45001</v>
       </c>
       <c r="B404" t="n">
-        <v>2.512234210968018</v>
+        <v>2.512233972549438</v>
       </c>
       <c r="C404" t="n">
-        <v>2.539841153798378</v>
+        <v>2.539840912759816</v>
       </c>
       <c r="D404" t="n">
-        <v>2.447818011030511</v>
+        <v>2.447817778725223</v>
       </c>
       <c r="E404" t="n">
-        <v>2.530638839521591</v>
+        <v>2.530638599356357</v>
       </c>
       <c r="F404" t="n">
         <v>22197500</v>
@@ -8552,16 +8552,16 @@
         <v>45006</v>
       </c>
       <c r="B407" t="n">
-        <v>2.264015913009644</v>
+        <v>2.264016151428223</v>
       </c>
       <c r="C407" t="n">
-        <v>2.397193186245646</v>
+        <v>2.397193438688833</v>
       </c>
       <c r="D407" t="n">
-        <v>2.244990361461882</v>
+        <v>2.244990597876922</v>
       </c>
       <c r="E407" t="n">
-        <v>2.368655199123645</v>
+        <v>2.368655448561559</v>
       </c>
       <c r="F407" t="n">
         <v>26738200</v>
@@ -8572,16 +8572,16 @@
         <v>45007</v>
       </c>
       <c r="B408" t="n">
-        <v>2.216452836990356</v>
+        <v>2.216452598571777</v>
       </c>
       <c r="C408" t="n">
-        <v>2.273529049947901</v>
+        <v>2.273528805389769</v>
       </c>
       <c r="D408" t="n">
-        <v>2.197427508271111</v>
+        <v>2.197427271899042</v>
       </c>
       <c r="E408" t="n">
-        <v>2.254503494428847</v>
+        <v>2.254503251917249</v>
       </c>
       <c r="F408" t="n">
         <v>26704400</v>
@@ -8592,16 +8592,16 @@
         <v>45008</v>
       </c>
       <c r="B409" t="n">
-        <v>2.149864196777344</v>
+        <v>2.149863958358765</v>
       </c>
       <c r="C409" t="n">
-        <v>2.235478176424297</v>
+        <v>2.235477928511182</v>
       </c>
       <c r="D409" t="n">
-        <v>2.140351532372127</v>
+        <v>2.140351295008496</v>
       </c>
       <c r="E409" t="n">
-        <v>2.22596551201908</v>
+        <v>2.225965265160914</v>
       </c>
       <c r="F409" t="n">
         <v>30902200</v>
@@ -8612,16 +8612,16 @@
         <v>45009</v>
       </c>
       <c r="B410" t="n">
-        <v>2.292554140090942</v>
+        <v>2.292553901672363</v>
       </c>
       <c r="C410" t="n">
-        <v>2.302066803460623</v>
+        <v>2.302066564052756</v>
       </c>
       <c r="D410" t="n">
-        <v>2.149863962745944</v>
+        <v>2.149863739166705</v>
       </c>
       <c r="E410" t="n">
-        <v>2.159376626115625</v>
+        <v>2.159376401547098</v>
       </c>
       <c r="F410" t="n">
         <v>19141800</v>
@@ -8632,16 +8632,16 @@
         <v>45012</v>
       </c>
       <c r="B411" t="n">
-        <v>2.387681007385254</v>
+        <v>2.387680768966675</v>
       </c>
       <c r="C411" t="n">
-        <v>2.416219000286296</v>
+        <v>2.416218759018095</v>
       </c>
       <c r="D411" t="n">
-        <v>2.302067028682128</v>
+        <v>2.302066798812414</v>
       </c>
       <c r="E411" t="n">
-        <v>2.311579692982475</v>
+        <v>2.311579462162887</v>
       </c>
       <c r="F411" t="n">
         <v>19684900</v>
@@ -8692,16 +8692,16 @@
         <v>45015</v>
       </c>
       <c r="B414" t="n">
-        <v>2.749162435531616</v>
+        <v>2.749162197113037</v>
       </c>
       <c r="C414" t="n">
-        <v>2.796725752381689</v>
+        <v>2.796725509838225</v>
       </c>
       <c r="D414" t="n">
-        <v>2.644522911661672</v>
+        <v>2.644522682317859</v>
       </c>
       <c r="E414" t="n">
-        <v>2.673060901771716</v>
+        <v>2.673060669952971</v>
       </c>
       <c r="F414" t="n">
         <v>39786400</v>
@@ -8732,16 +8732,16 @@
         <v>45019</v>
       </c>
       <c r="B416" t="n">
-        <v>2.692086219787598</v>
+        <v>2.692086458206177</v>
       </c>
       <c r="C416" t="n">
-        <v>2.768187753300879</v>
+        <v>2.76818799845922</v>
       </c>
       <c r="D416" t="n">
-        <v>2.673060893109223</v>
+        <v>2.673061129842867</v>
       </c>
       <c r="E416" t="n">
-        <v>2.739649763283318</v>
+        <v>2.739650005914255</v>
       </c>
       <c r="F416" t="n">
         <v>18815900</v>
@@ -8752,16 +8752,16 @@
         <v>45020</v>
       </c>
       <c r="B417" t="n">
-        <v>2.692086219787598</v>
+        <v>2.692086458206177</v>
       </c>
       <c r="C417" t="n">
-        <v>2.739649763283318</v>
+        <v>2.739650005914255</v>
       </c>
       <c r="D417" t="n">
-        <v>2.654035566430849</v>
+        <v>2.654035801479557</v>
       </c>
       <c r="E417" t="n">
-        <v>2.720624209805159</v>
+        <v>2.720624450751141</v>
       </c>
       <c r="F417" t="n">
         <v>21012200</v>
@@ -8792,16 +8792,16 @@
         <v>45022</v>
       </c>
       <c r="B419" t="n">
-        <v>2.654035568237305</v>
+        <v>2.654035329818726</v>
       </c>
       <c r="C419" t="n">
-        <v>2.68257355827429</v>
+        <v>2.682573317292073</v>
       </c>
       <c r="D419" t="n">
-        <v>2.615984914854657</v>
+        <v>2.615984679854262</v>
       </c>
       <c r="E419" t="n">
-        <v>2.673060894928629</v>
+        <v>2.673060654800957</v>
       </c>
       <c r="F419" t="n">
         <v>14613400</v>
@@ -8972,16 +8972,16 @@
         <v>45036</v>
       </c>
       <c r="B428" t="n">
-        <v>2.958441019058228</v>
+        <v>2.958441257476807</v>
       </c>
       <c r="C428" t="n">
-        <v>2.977466572529786</v>
+        <v>2.977466812481619</v>
       </c>
       <c r="D428" t="n">
-        <v>2.844289059027585</v>
+        <v>2.844289288246741</v>
       </c>
       <c r="E428" t="n">
-        <v>2.882339712371133</v>
+        <v>2.882339944656763</v>
       </c>
       <c r="F428" t="n">
         <v>11874200</v>
@@ -9052,16 +9052,16 @@
         <v>45043</v>
       </c>
       <c r="B432" t="n">
-        <v>2.977466583251953</v>
+        <v>2.977466821670532</v>
       </c>
       <c r="C432" t="n">
-        <v>3.006004573362382</v>
+        <v>3.006004814066121</v>
       </c>
       <c r="D432" t="n">
-        <v>2.891852386120882</v>
+        <v>2.891852617683963</v>
       </c>
       <c r="E432" t="n">
-        <v>2.901365049491024</v>
+        <v>2.901365281815826</v>
       </c>
       <c r="F432" t="n">
         <v>12242300</v>
@@ -9072,16 +9072,16 @@
         <v>45044</v>
       </c>
       <c r="B433" t="n">
-        <v>3.034542798995972</v>
+        <v>3.034542560577393</v>
       </c>
       <c r="C433" t="n">
-        <v>3.091618783646728</v>
+        <v>3.091618540743791</v>
       </c>
       <c r="D433" t="n">
-        <v>2.939415931111576</v>
+        <v>2.939415700166944</v>
       </c>
       <c r="E433" t="n">
-        <v>2.977466814345215</v>
+        <v>2.977466580410994</v>
       </c>
       <c r="F433" t="n">
         <v>20412700</v>
@@ -9252,16 +9252,16 @@
         <v>45058</v>
       </c>
       <c r="B442" t="n">
-        <v>3.129669189453125</v>
+        <v>3.129669427871704</v>
       </c>
       <c r="C442" t="n">
-        <v>3.21528338637298</v>
+        <v>3.215283631313659</v>
       </c>
       <c r="D442" t="n">
-        <v>3.091618536066427</v>
+        <v>3.091618771586302</v>
       </c>
       <c r="E442" t="n">
-        <v>3.167719842839823</v>
+        <v>3.167720084157106</v>
       </c>
       <c r="F442" t="n">
         <v>13638800</v>
@@ -9272,16 +9272,16 @@
         <v>45061</v>
       </c>
       <c r="B443" t="n">
-        <v>2.986979246139526</v>
+        <v>2.986979484558105</v>
       </c>
       <c r="C443" t="n">
-        <v>3.205770503617468</v>
+        <v>3.20577075949981</v>
       </c>
       <c r="D443" t="n">
-        <v>2.901365049022286</v>
+        <v>2.901365280607201</v>
       </c>
       <c r="E443" t="n">
-        <v>3.186745176880255</v>
+        <v>3.18674543124401</v>
       </c>
       <c r="F443" t="n">
         <v>71533500</v>
@@ -9332,16 +9332,16 @@
         <v>45064</v>
       </c>
       <c r="B446" t="n">
-        <v>3.300897359848022</v>
+        <v>3.300897598266602</v>
       </c>
       <c r="C446" t="n">
-        <v>3.338948013273395</v>
+        <v>3.338948254440312</v>
       </c>
       <c r="D446" t="n">
-        <v>3.177232509415779</v>
+        <v>3.177232738902241</v>
       </c>
       <c r="E446" t="n">
-        <v>3.253334043066307</v>
+        <v>3.253334278049463</v>
       </c>
       <c r="F446" t="n">
         <v>40825600</v>
@@ -9352,16 +9352,16 @@
         <v>45065</v>
       </c>
       <c r="B447" t="n">
-        <v>3.491151094436646</v>
+        <v>3.491150856018066</v>
       </c>
       <c r="C447" t="n">
-        <v>3.519689086472937</v>
+        <v>3.519688846105434</v>
       </c>
       <c r="D447" t="n">
-        <v>3.281872259370709</v>
+        <v>3.281872035244253</v>
       </c>
       <c r="E447" t="n">
-        <v>3.329435579431195</v>
+        <v>3.329435352056533</v>
       </c>
       <c r="F447" t="n">
         <v>32544700</v>
@@ -9372,16 +9372,16 @@
         <v>45068</v>
       </c>
       <c r="B448" t="n">
-        <v>3.472125768661499</v>
+        <v>3.47212553024292</v>
       </c>
       <c r="C448" t="n">
-        <v>3.576765072862347</v>
+        <v>3.576764827258557</v>
       </c>
       <c r="D448" t="n">
-        <v>3.453100440624981</v>
+        <v>3.453100203512804</v>
       </c>
       <c r="E448" t="n">
-        <v>3.54822708080757</v>
+        <v>3.548226837163384</v>
       </c>
       <c r="F448" t="n">
         <v>14142300</v>
@@ -9392,16 +9392,16 @@
         <v>45069</v>
       </c>
       <c r="B449" t="n">
-        <v>3.472125768661499</v>
+        <v>3.47212553024292</v>
       </c>
       <c r="C449" t="n">
-        <v>3.567252408844088</v>
+        <v>3.5672521638935</v>
       </c>
       <c r="D449" t="n">
-        <v>3.443587549806922</v>
+        <v>3.443587313347962</v>
       </c>
       <c r="E449" t="n">
-        <v>3.472125768661499</v>
+        <v>3.47212553024292</v>
       </c>
       <c r="F449" t="n">
         <v>12031500</v>
@@ -9412,16 +9412,16 @@
         <v>45070</v>
       </c>
       <c r="B450" t="n">
-        <v>3.319922685623169</v>
+        <v>3.319922924041748</v>
       </c>
       <c r="C450" t="n">
-        <v>3.529201506203401</v>
+        <v>3.529201759651233</v>
       </c>
       <c r="D450" t="n">
-        <v>3.262846705501229</v>
+        <v>3.262846939820925</v>
       </c>
       <c r="E450" t="n">
-        <v>3.462612862727804</v>
+        <v>3.462613111393607</v>
       </c>
       <c r="F450" t="n">
         <v>35329500</v>
@@ -9472,16 +9472,16 @@
         <v>45075</v>
       </c>
       <c r="B453" t="n">
-        <v>3.357973337173462</v>
+        <v>3.357973575592041</v>
       </c>
       <c r="C453" t="n">
-        <v>3.415049317263714</v>
+        <v>3.415049559734729</v>
       </c>
       <c r="D453" t="n">
-        <v>3.291384693734835</v>
+        <v>3.291384927425571</v>
       </c>
       <c r="E453" t="n">
-        <v>3.319922683779961</v>
+        <v>3.319922919496916</v>
       </c>
       <c r="F453" t="n">
         <v>14544800</v>
@@ -9492,16 +9492,16 @@
         <v>45076</v>
       </c>
       <c r="B454" t="n">
-        <v>3.424561977386475</v>
+        <v>3.424562215805054</v>
       </c>
       <c r="C454" t="n">
-        <v>3.46261285754392</v>
+        <v>3.462613098611607</v>
       </c>
       <c r="D454" t="n">
-        <v>3.310410017313492</v>
+        <v>3.310410247784792</v>
       </c>
       <c r="E454" t="n">
-        <v>3.396023987368229</v>
+        <v>3.396024223799988</v>
       </c>
       <c r="F454" t="n">
         <v>24140700</v>
@@ -9512,16 +9512,16 @@
         <v>45077</v>
       </c>
       <c r="B455" t="n">
-        <v>3.453099966049194</v>
+        <v>3.453100204467773</v>
       </c>
       <c r="C455" t="n">
-        <v>3.557739255868972</v>
+        <v>3.557739501512349</v>
       </c>
       <c r="D455" t="n">
-        <v>3.41504908840587</v>
+        <v>3.415049324197234</v>
       </c>
       <c r="E455" t="n">
-        <v>3.424561751116759</v>
+        <v>3.424561987564922</v>
       </c>
       <c r="F455" t="n">
         <v>23066900</v>
@@ -9532,16 +9532,16 @@
         <v>45078</v>
       </c>
       <c r="B456" t="n">
-        <v>3.576764822006226</v>
+        <v>3.576764583587646</v>
       </c>
       <c r="C456" t="n">
-        <v>3.662378792166026</v>
+        <v>3.662378548040625</v>
       </c>
       <c r="D456" t="n">
-        <v>3.376998664833572</v>
+        <v>3.376998439730927</v>
       </c>
       <c r="E456" t="n">
-        <v>3.472125525144246</v>
+        <v>3.472125293700673</v>
       </c>
       <c r="F456" t="n">
         <v>28377100</v>
@@ -9572,16 +9572,16 @@
         <v>45082</v>
       </c>
       <c r="B458" t="n">
-        <v>3.586277484893799</v>
+        <v>3.586277723312378</v>
       </c>
       <c r="C458" t="n">
-        <v>3.605302811593518</v>
+        <v>3.605303051276916</v>
       </c>
       <c r="D458" t="n">
-        <v>3.500663514745063</v>
+        <v>3.500663747471958</v>
       </c>
       <c r="E458" t="n">
-        <v>3.510176178094923</v>
+        <v>3.510176411454227</v>
       </c>
       <c r="F458" t="n">
         <v>11705300</v>
@@ -9612,16 +9612,16 @@
         <v>45084</v>
       </c>
       <c r="B460" t="n">
-        <v>3.757505893707275</v>
+        <v>3.757505655288696</v>
       </c>
       <c r="C460" t="n">
-        <v>3.852632760125061</v>
+        <v>3.85263251567056</v>
       </c>
       <c r="D460" t="n">
-        <v>3.681404355213087</v>
+        <v>3.681404121623248</v>
       </c>
       <c r="E460" t="n">
-        <v>3.747993229745477</v>
+        <v>3.747992991930488</v>
       </c>
       <c r="F460" t="n">
         <v>19382700</v>
@@ -9672,16 +9672,16 @@
         <v>45090</v>
       </c>
       <c r="B463" t="n">
-        <v>3.700429916381836</v>
+        <v>3.700429677963257</v>
       </c>
       <c r="C463" t="n">
-        <v>3.814582110922048</v>
+        <v>3.814581865148647</v>
       </c>
       <c r="D463" t="n">
-        <v>3.662379033668566</v>
+        <v>3.662378797701604</v>
       </c>
       <c r="E463" t="n">
-        <v>3.786043892187145</v>
+        <v>3.78604364825246</v>
       </c>
       <c r="F463" t="n">
         <v>19986600</v>
@@ -9692,16 +9692,16 @@
         <v>45091</v>
       </c>
       <c r="B464" t="n">
-        <v>3.747993230819702</v>
+        <v>3.747992992401123</v>
       </c>
       <c r="C464" t="n">
-        <v>3.795556550642328</v>
+        <v>3.795556309198135</v>
       </c>
       <c r="D464" t="n">
-        <v>3.662379028339177</v>
+        <v>3.662378795366716</v>
       </c>
       <c r="E464" t="n">
-        <v>3.709942574961601</v>
+        <v>3.709942338963513</v>
       </c>
       <c r="F464" t="n">
         <v>25840400</v>
@@ -9712,16 +9712,16 @@
         <v>45092</v>
       </c>
       <c r="B465" t="n">
-        <v>3.757505893707275</v>
+        <v>3.757505655288696</v>
       </c>
       <c r="C465" t="n">
-        <v>3.79555654955447</v>
+        <v>3.795556308721528</v>
       </c>
       <c r="D465" t="n">
-        <v>3.71945523786008</v>
+        <v>3.719455001855864</v>
       </c>
       <c r="E465" t="n">
-        <v>3.757505893707275</v>
+        <v>3.757505655288696</v>
       </c>
       <c r="F465" t="n">
         <v>13781200</v>
@@ -9732,16 +9732,16 @@
         <v>45093</v>
       </c>
       <c r="B466" t="n">
-        <v>3.757505893707275</v>
+        <v>3.757505655288696</v>
       </c>
       <c r="C466" t="n">
-        <v>3.776531221630873</v>
+        <v>3.776530982005112</v>
       </c>
       <c r="D466" t="n">
-        <v>3.709942573898282</v>
+        <v>3.709942338497656</v>
       </c>
       <c r="E466" t="n">
-        <v>3.728967901821879</v>
+        <v>3.728967665214073</v>
       </c>
       <c r="F466" t="n">
         <v>14449100</v>
@@ -9752,16 +9752,16 @@
         <v>45096</v>
       </c>
       <c r="B467" t="n">
-        <v>3.776531219482422</v>
+        <v>3.776530742645264</v>
       </c>
       <c r="C467" t="n">
-        <v>3.814582102107769</v>
+        <v>3.814581620466182</v>
       </c>
       <c r="D467" t="n">
-        <v>3.738480563656874</v>
+        <v>3.738480091624116</v>
       </c>
       <c r="E467" t="n">
-        <v>3.786043883438809</v>
+        <v>3.786043405400551</v>
       </c>
       <c r="F467" t="n">
         <v>9550900</v>
@@ -9772,16 +9772,16 @@
         <v>45097</v>
       </c>
       <c r="B468" t="n">
-        <v>3.947758913040161</v>
+        <v>3.947759389877319</v>
       </c>
       <c r="C468" t="n">
-        <v>3.966784238618205</v>
+        <v>3.966784717753371</v>
       </c>
       <c r="D468" t="n">
-        <v>3.767018093248975</v>
+        <v>3.767018548255029</v>
       </c>
       <c r="E468" t="n">
-        <v>3.786043418827019</v>
+        <v>3.786043876131081</v>
       </c>
       <c r="F468" t="n">
         <v>35176100</v>
@@ -9792,16 +9792,16 @@
         <v>45098</v>
       </c>
       <c r="B469" t="n">
-        <v>4.023860454559326</v>
+        <v>4.023859977722168</v>
       </c>
       <c r="C469" t="n">
-        <v>4.042885781268371</v>
+        <v>4.042885302176666</v>
       </c>
       <c r="D469" t="n">
-        <v>3.90019560415075</v>
+        <v>3.900195141968175</v>
       </c>
       <c r="E469" t="n">
-        <v>3.966784474432191</v>
+        <v>3.966784004358674</v>
       </c>
       <c r="F469" t="n">
         <v>23935400</v>
@@ -9852,16 +9852,16 @@
         <v>45103</v>
       </c>
       <c r="B472" t="n">
-        <v>4.204600811004639</v>
+        <v>4.204601764678955</v>
       </c>
       <c r="C472" t="n">
-        <v>4.280702109260005</v>
+        <v>4.280703080195378</v>
       </c>
       <c r="D472" t="n">
-        <v>4.128499512749272</v>
+        <v>4.128500449162532</v>
       </c>
       <c r="E472" t="n">
-        <v>4.138011948231434</v>
+        <v>4.138012886802275</v>
       </c>
       <c r="F472" t="n">
         <v>42881900</v>
@@ -9912,16 +9912,16 @@
         <v>45106</v>
       </c>
       <c r="B475" t="n">
-        <v>4.366316795349121</v>
+        <v>4.366317272186279</v>
       </c>
       <c r="C475" t="n">
-        <v>4.366316795349121</v>
+        <v>4.366317272186279</v>
       </c>
       <c r="D475" t="n">
-        <v>4.185575964547351</v>
+        <v>4.185576421646147</v>
       </c>
       <c r="E475" t="n">
-        <v>4.185575964547351</v>
+        <v>4.185576421646147</v>
       </c>
       <c r="F475" t="n">
         <v>40765500</v>
@@ -9932,16 +9932,16 @@
         <v>45107</v>
       </c>
       <c r="B476" t="n">
-        <v>4.18557596206665</v>
+        <v>4.185575485229492</v>
       </c>
       <c r="C476" t="n">
-        <v>4.489981189679052</v>
+        <v>4.489980678162862</v>
       </c>
       <c r="D476" t="n">
-        <v>4.138012418452428</v>
+        <v>4.138011947033895</v>
       </c>
       <c r="E476" t="n">
-        <v>4.413879882775952</v>
+        <v>4.41387937992952</v>
       </c>
       <c r="F476" t="n">
         <v>35419200</v>
@@ -9972,16 +9972,16 @@
         <v>45111</v>
       </c>
       <c r="B478" t="n">
-        <v>4.195088386535645</v>
+        <v>4.195088863372803</v>
       </c>
       <c r="C478" t="n">
-        <v>4.261677256683671</v>
+        <v>4.261677741089692</v>
       </c>
       <c r="D478" t="n">
-        <v>4.138012406522865</v>
+        <v>4.138012876872448</v>
       </c>
       <c r="E478" t="n">
-        <v>4.252164366548425</v>
+        <v>4.252164849873157</v>
       </c>
       <c r="F478" t="n">
         <v>10806500</v>
@@ -9992,16 +9992,16 @@
         <v>45112</v>
       </c>
       <c r="B479" t="n">
-        <v>4.080936908721924</v>
+        <v>4.080936431884766</v>
       </c>
       <c r="C479" t="n">
-        <v>4.185576444576225</v>
+        <v>4.185575955512459</v>
       </c>
       <c r="D479" t="n">
-        <v>4.023860921964928</v>
+        <v>4.023860451796815</v>
       </c>
       <c r="E479" t="n">
-        <v>4.166551115657227</v>
+        <v>4.166550628816475</v>
       </c>
       <c r="F479" t="n">
         <v>33346200</v>
@@ -10012,16 +10012,16 @@
         <v>45113</v>
       </c>
       <c r="B480" t="n">
-        <v>3.957271575927734</v>
+        <v>3.957271814346313</v>
       </c>
       <c r="C480" t="n">
-        <v>4.061911099406468</v>
+        <v>4.061911344129392</v>
       </c>
       <c r="D480" t="n">
-        <v>3.909708486055269</v>
+        <v>3.909708721608256</v>
       </c>
       <c r="E480" t="n">
-        <v>4.061911099406468</v>
+        <v>4.061911344129392</v>
       </c>
       <c r="F480" t="n">
         <v>22675100</v>
@@ -10032,16 +10032,16 @@
         <v>45114</v>
       </c>
       <c r="B481" t="n">
-        <v>3.995322704315186</v>
+        <v>3.995322465896606</v>
       </c>
       <c r="C481" t="n">
-        <v>4.042886253442594</v>
+        <v>4.042886012185687</v>
       </c>
       <c r="D481" t="n">
-        <v>3.947759608787399</v>
+        <v>3.94775937320712</v>
       </c>
       <c r="E481" t="n">
-        <v>3.976297375384147</v>
+        <v>3.976297138100893</v>
       </c>
       <c r="F481" t="n">
         <v>19055100</v>
@@ -10052,16 +10052,16 @@
         <v>45117</v>
       </c>
       <c r="B482" t="n">
-        <v>4.033373355865479</v>
+        <v>4.03337287902832</v>
       </c>
       <c r="C482" t="n">
-        <v>4.099962233819722</v>
+        <v>4.099961749110232</v>
       </c>
       <c r="D482" t="n">
-        <v>3.94775960260959</v>
+        <v>3.947759135893939</v>
       </c>
       <c r="E482" t="n">
-        <v>3.995322698062945</v>
+        <v>3.995322225724247</v>
       </c>
       <c r="F482" t="n">
         <v>16685100</v>
@@ -10112,16 +10112,16 @@
         <v>45120</v>
       </c>
       <c r="B485" t="n">
-        <v>3.995322704315186</v>
+        <v>3.995322465896606</v>
       </c>
       <c r="C485" t="n">
-        <v>4.071424473638964</v>
+        <v>4.071424230679055</v>
       </c>
       <c r="D485" t="n">
-        <v>3.957272046453107</v>
+        <v>3.957271810305179</v>
       </c>
       <c r="E485" t="n">
-        <v>4.023860924511555</v>
+        <v>4.023860684389974</v>
       </c>
       <c r="F485" t="n">
         <v>10522300</v>
@@ -10132,16 +10132,16 @@
         <v>45121</v>
       </c>
       <c r="B486" t="n">
-        <v>3.881170511245728</v>
+        <v>3.881170272827148</v>
       </c>
       <c r="C486" t="n">
-        <v>4.014347806231721</v>
+        <v>4.01434755963212</v>
       </c>
       <c r="D486" t="n">
-        <v>3.814582090552529</v>
+        <v>3.814581856224446</v>
       </c>
       <c r="E486" t="n">
-        <v>3.995322478376579</v>
+        <v>3.995322232945695</v>
       </c>
       <c r="F486" t="n">
         <v>16845900</v>
@@ -10152,16 +10152,16 @@
         <v>45124</v>
       </c>
       <c r="B487" t="n">
-        <v>4.023860454559326</v>
+        <v>4.023859977722168</v>
       </c>
       <c r="C487" t="n">
-        <v>4.042885781268371</v>
+        <v>4.042885302176666</v>
       </c>
       <c r="D487" t="n">
-        <v>3.852632514177922</v>
+        <v>3.852632057631688</v>
       </c>
       <c r="E487" t="n">
-        <v>3.881170277441705</v>
+        <v>3.881169817513677</v>
       </c>
       <c r="F487" t="n">
         <v>20863600</v>
@@ -10172,16 +10172,16 @@
         <v>45125</v>
       </c>
       <c r="B488" t="n">
-        <v>4.071424007415771</v>
+        <v>4.07142448425293</v>
       </c>
       <c r="C488" t="n">
-        <v>4.185575967930341</v>
+        <v>4.185576458136752</v>
       </c>
       <c r="D488" t="n">
-        <v>4.004835136982487</v>
+        <v>4.004835606020889</v>
       </c>
       <c r="E488" t="n">
-        <v>4.023860463734916</v>
+        <v>4.023860935001526</v>
       </c>
       <c r="F488" t="n">
         <v>19854400</v>
@@ -10212,16 +10212,16 @@
         <v>45127</v>
       </c>
       <c r="B490" t="n">
-        <v>3.995322704315186</v>
+        <v>3.995322465896606</v>
       </c>
       <c r="C490" t="n">
-        <v>4.080936911304672</v>
+        <v>4.080936667777115</v>
       </c>
       <c r="D490" t="n">
-        <v>3.947759608787399</v>
+        <v>3.94775937320712</v>
       </c>
       <c r="E490" t="n">
-        <v>4.071424473638964</v>
+        <v>4.071424230679055</v>
       </c>
       <c r="F490" t="n">
         <v>13981900</v>
@@ -10232,16 +10232,16 @@
         <v>45128</v>
       </c>
       <c r="B491" t="n">
-        <v>4.061911582946777</v>
+        <v>4.061911106109619</v>
       </c>
       <c r="C491" t="n">
-        <v>4.099962240814224</v>
+        <v>4.099961759510212</v>
       </c>
       <c r="D491" t="n">
-        <v>3.97629737594521</v>
+        <v>3.976296909158501</v>
       </c>
       <c r="E491" t="n">
-        <v>4.004835596145607</v>
+        <v>4.00483512600873</v>
       </c>
       <c r="F491" t="n">
         <v>9991000</v>
@@ -10252,16 +10252,16 @@
         <v>45131</v>
       </c>
       <c r="B492" t="n">
-        <v>4.023860454559326</v>
+        <v>4.023859977722168</v>
       </c>
       <c r="C492" t="n">
-        <v>4.080936434686461</v>
+        <v>4.080935951085661</v>
       </c>
       <c r="D492" t="n">
-        <v>3.947759147723147</v>
+        <v>3.947758679904177</v>
       </c>
       <c r="E492" t="n">
-        <v>4.061911107977416</v>
+        <v>4.061910626631164</v>
       </c>
       <c r="F492" t="n">
         <v>17283700</v>
@@ -10272,16 +10272,16 @@
         <v>45132</v>
       </c>
       <c r="B493" t="n">
-        <v>3.995322704315186</v>
+        <v>3.995322465896606</v>
       </c>
       <c r="C493" t="n">
-        <v>4.090449802570003</v>
+        <v>4.090449558474769</v>
       </c>
       <c r="D493" t="n">
-        <v>3.966784937718438</v>
+        <v>3.966784701002833</v>
       </c>
       <c r="E493" t="n">
-        <v>4.061911582373633</v>
+        <v>4.061911339981402</v>
       </c>
       <c r="F493" t="n">
         <v>14413200</v>
@@ -10312,16 +10312,16 @@
         <v>45134</v>
       </c>
       <c r="B495" t="n">
-        <v>3.893998384475708</v>
+        <v>3.893998622894287</v>
       </c>
       <c r="C495" t="n">
-        <v>4.056646575563136</v>
+        <v>4.056646823940207</v>
       </c>
       <c r="D495" t="n">
-        <v>3.884430602296878</v>
+        <v>3.884430840129649</v>
       </c>
       <c r="E495" t="n">
-        <v>4.047079249601271</v>
+        <v>4.047079497392562</v>
       </c>
       <c r="F495" t="n">
         <v>18331700</v>
@@ -10352,16 +10352,16 @@
         <v>45138</v>
       </c>
       <c r="B497" t="n">
-        <v>3.980106353759766</v>
+        <v>3.980106115341187</v>
       </c>
       <c r="C497" t="n">
-        <v>4.008809245599202</v>
+        <v>4.008809005461245</v>
       </c>
       <c r="D497" t="n">
-        <v>3.922701026297883</v>
+        <v>3.922700791318031</v>
       </c>
       <c r="E497" t="n">
-        <v>3.941836135451844</v>
+        <v>3.941835899325749</v>
       </c>
       <c r="F497" t="n">
         <v>13989300</v>
@@ -10372,16 +10372,16 @@
         <v>45139</v>
       </c>
       <c r="B498" t="n">
-        <v>3.980106353759766</v>
+        <v>3.980106115341187</v>
       </c>
       <c r="C498" t="n">
-        <v>4.018376572067687</v>
+        <v>4.018376331356624</v>
       </c>
       <c r="D498" t="n">
-        <v>3.884430807989962</v>
+        <v>3.884430575302593</v>
       </c>
       <c r="E498" t="n">
-        <v>3.970539027291279</v>
+        <v>3.970538789445808</v>
       </c>
       <c r="F498" t="n">
         <v>24308900</v>
@@ -10412,16 +10412,16 @@
         <v>45141</v>
       </c>
       <c r="B500" t="n">
-        <v>3.922701120376587</v>
+        <v>3.922700881958008</v>
       </c>
       <c r="C500" t="n">
-        <v>4.037511778053872</v>
+        <v>4.037511532657195</v>
       </c>
       <c r="D500" t="n">
-        <v>3.893998684065766</v>
+        <v>3.893998447391697</v>
       </c>
       <c r="E500" t="n">
-        <v>4.027944451355932</v>
+        <v>4.027944206540749</v>
       </c>
       <c r="F500" t="n">
         <v>21426900</v>
@@ -10432,16 +10432,16 @@
         <v>45142</v>
       </c>
       <c r="B501" t="n">
-        <v>3.903565883636475</v>
+        <v>3.903565406799316</v>
       </c>
       <c r="C501" t="n">
-        <v>3.960971210605601</v>
+        <v>3.960970726756138</v>
       </c>
       <c r="D501" t="n">
-        <v>3.865295665657057</v>
+        <v>3.865295193494769</v>
       </c>
       <c r="E501" t="n">
-        <v>3.903565883636475</v>
+        <v>3.903565406799316</v>
       </c>
       <c r="F501" t="n">
         <v>16409800</v>
@@ -10472,16 +10472,16 @@
         <v>45146</v>
       </c>
       <c r="B503" t="n">
-        <v>3.798322916030884</v>
+        <v>3.798322677612305</v>
       </c>
       <c r="C503" t="n">
-        <v>3.817458025684763</v>
+        <v>3.817457786065083</v>
       </c>
       <c r="D503" t="n">
-        <v>3.702647139652991</v>
+        <v>3.702646907239926</v>
       </c>
       <c r="E503" t="n">
-        <v>3.798322916030884</v>
+        <v>3.798322677612305</v>
       </c>
       <c r="F503" t="n">
         <v>17862300</v>
@@ -10532,16 +10532,16 @@
         <v>45149</v>
       </c>
       <c r="B506" t="n">
-        <v>3.683511734008789</v>
+        <v>3.683511972427368</v>
       </c>
       <c r="C506" t="n">
-        <v>3.750484840524209</v>
+        <v>3.750485083277681</v>
       </c>
       <c r="D506" t="n">
-        <v>3.63567396371812</v>
+        <v>3.635674199040356</v>
       </c>
       <c r="E506" t="n">
-        <v>3.731349732407941</v>
+        <v>3.731349973922877</v>
       </c>
       <c r="F506" t="n">
         <v>13400900</v>
@@ -10552,16 +10552,16 @@
         <v>45152</v>
       </c>
       <c r="B507" t="n">
-        <v>3.606971502304077</v>
+        <v>3.606971263885498</v>
       </c>
       <c r="C507" t="n">
-        <v>3.664376829848003</v>
+        <v>3.664376587634967</v>
       </c>
       <c r="D507" t="n">
-        <v>3.56870128394146</v>
+        <v>3.568701048052518</v>
       </c>
       <c r="E507" t="n">
-        <v>3.664376829848003</v>
+        <v>3.664376587634967</v>
       </c>
       <c r="F507" t="n">
         <v>20072900</v>
@@ -10632,16 +10632,16 @@
         <v>45156</v>
       </c>
       <c r="B511" t="n">
-        <v>3.434755325317383</v>
+        <v>3.434755086898804</v>
       </c>
       <c r="C511" t="n">
-        <v>3.473025772164581</v>
+        <v>3.473025531089514</v>
       </c>
       <c r="D511" t="n">
-        <v>3.33907977847063</v>
+        <v>3.339079546693231</v>
       </c>
       <c r="E511" t="n">
-        <v>3.35821488783998</v>
+        <v>3.358214654734345</v>
       </c>
       <c r="F511" t="n">
         <v>15864700</v>
@@ -10692,16 +10692,16 @@
         <v>45161</v>
       </c>
       <c r="B514" t="n">
-        <v>3.453890323638916</v>
+        <v>3.453890085220337</v>
       </c>
       <c r="C514" t="n">
-        <v>3.559133649895108</v>
+        <v>3.559133404211688</v>
       </c>
       <c r="D514" t="n">
-        <v>3.377349888622405</v>
+        <v>3.377349655487335</v>
       </c>
       <c r="E514" t="n">
-        <v>3.396484997376533</v>
+        <v>3.396484762920585</v>
       </c>
       <c r="F514" t="n">
         <v>43718400</v>
@@ -10712,16 +10712,16 @@
         <v>45162</v>
       </c>
       <c r="B515" t="n">
-        <v>3.568701267242432</v>
+        <v>3.568701505661011</v>
       </c>
       <c r="C515" t="n">
-        <v>3.64524170360951</v>
+        <v>3.645241947141619</v>
       </c>
       <c r="D515" t="n">
-        <v>3.444322830037436</v>
+        <v>3.444323060146513</v>
       </c>
       <c r="E515" t="n">
-        <v>3.453890384583321</v>
+        <v>3.453890615331589</v>
       </c>
       <c r="F515" t="n">
         <v>42127000</v>
@@ -10772,16 +10772,16 @@
         <v>45167</v>
       </c>
       <c r="B518" t="n">
-        <v>3.65480899810791</v>
+        <v>3.654809236526489</v>
       </c>
       <c r="C518" t="n">
-        <v>3.664376551973043</v>
+        <v>3.664376791015754</v>
       </c>
       <c r="D518" t="n">
-        <v>3.578268567186847</v>
+        <v>3.578268800612372</v>
       </c>
       <c r="E518" t="n">
-        <v>3.616538782647379</v>
+        <v>3.61653901856943</v>
       </c>
       <c r="F518" t="n">
         <v>13520200</v>
@@ -10952,16 +10952,16 @@
         <v>45181</v>
       </c>
       <c r="B527" t="n">
-        <v>3.712214469909668</v>
+        <v>3.712214946746826</v>
       </c>
       <c r="C527" t="n">
-        <v>3.769619791871123</v>
+        <v>3.769620276082045</v>
       </c>
       <c r="D527" t="n">
-        <v>3.61653870519877</v>
+        <v>3.616539169746294</v>
       </c>
       <c r="E527" t="n">
-        <v>3.635673812519255</v>
+        <v>3.6356742795247</v>
       </c>
       <c r="F527" t="n">
         <v>15715300</v>
@@ -10972,16 +10972,16 @@
         <v>45182</v>
       </c>
       <c r="B528" t="n">
-        <v>3.769620180130005</v>
+        <v>3.769619941711426</v>
       </c>
       <c r="C528" t="n">
-        <v>3.846160617295367</v>
+        <v>3.846160374035806</v>
       </c>
       <c r="D528" t="n">
-        <v>3.712214852255983</v>
+        <v>3.712214617468141</v>
       </c>
       <c r="E528" t="n">
-        <v>3.712214852255983</v>
+        <v>3.712214617468141</v>
       </c>
       <c r="F528" t="n">
         <v>17575000</v>
@@ -10992,16 +10992,16 @@
         <v>45183</v>
       </c>
       <c r="B529" t="n">
-        <v>3.798322916030884</v>
+        <v>3.798322677612305</v>
       </c>
       <c r="C529" t="n">
-        <v>3.836593363447141</v>
+        <v>3.836593122626347</v>
       </c>
       <c r="D529" t="n">
-        <v>3.760052696723127</v>
+        <v>3.760052460706747</v>
       </c>
       <c r="E529" t="n">
-        <v>3.798322916030884</v>
+        <v>3.798322677612305</v>
       </c>
       <c r="F529" t="n">
         <v>9553000</v>
@@ -11032,16 +11032,16 @@
         <v>45187</v>
       </c>
       <c r="B531" t="n">
-        <v>3.817457914352417</v>
+        <v>3.817457675933838</v>
       </c>
       <c r="C531" t="n">
-        <v>3.884430796187795</v>
+        <v>3.884430553586438</v>
       </c>
       <c r="D531" t="n">
-        <v>3.740917477969129</v>
+        <v>3.740917244330867</v>
       </c>
       <c r="E531" t="n">
-        <v>3.817457914352417</v>
+        <v>3.817457675933838</v>
       </c>
       <c r="F531" t="n">
         <v>23371600</v>
@@ -11072,16 +11072,16 @@
         <v>45189</v>
       </c>
       <c r="B533" t="n">
-        <v>3.645241737365723</v>
+        <v>3.645241498947144</v>
       </c>
       <c r="C533" t="n">
-        <v>3.769620175722507</v>
+        <v>3.769619929168903</v>
       </c>
       <c r="D533" t="n">
-        <v>3.645241737365723</v>
+        <v>3.645241498947144</v>
       </c>
       <c r="E533" t="n">
-        <v>3.740917511819056</v>
+        <v>3.740917267142762</v>
       </c>
       <c r="F533" t="n">
         <v>23728500</v>
@@ -11112,16 +11112,16 @@
         <v>45191</v>
       </c>
       <c r="B535" t="n">
-        <v>3.606971502304077</v>
+        <v>3.606971263885498</v>
       </c>
       <c r="C535" t="n">
-        <v>3.664376829848003</v>
+        <v>3.664376587634967</v>
       </c>
       <c r="D535" t="n">
-        <v>3.559133729350806</v>
+        <v>3.559133494094274</v>
       </c>
       <c r="E535" t="n">
-        <v>3.597403947713423</v>
+        <v>3.597403709927253</v>
       </c>
       <c r="F535" t="n">
         <v>21984900</v>
@@ -11192,16 +11192,16 @@
         <v>45197</v>
       </c>
       <c r="B539" t="n">
-        <v>3.415620088577271</v>
+        <v>3.41562032699585</v>
       </c>
       <c r="C539" t="n">
-        <v>3.444322751560954</v>
+        <v>3.444322991983049</v>
       </c>
       <c r="D539" t="n">
-        <v>3.329512099626217</v>
+        <v>3.32951233203425</v>
       </c>
       <c r="E539" t="n">
-        <v>3.415620088577271</v>
+        <v>3.41562032699585</v>
       </c>
       <c r="F539" t="n">
         <v>16733500</v>
@@ -11212,16 +11212,16 @@
         <v>45198</v>
       </c>
       <c r="B540" t="n">
-        <v>3.425187587738037</v>
+        <v>3.425187349319458</v>
       </c>
       <c r="C540" t="n">
-        <v>3.492160695063099</v>
+        <v>3.492160451982693</v>
       </c>
       <c r="D540" t="n">
-        <v>3.38691737104285</v>
+        <v>3.386917135288163</v>
       </c>
       <c r="E540" t="n">
-        <v>3.463457804433224</v>
+        <v>3.463457563350753</v>
       </c>
       <c r="F540" t="n">
         <v>13661300</v>
@@ -11252,16 +11252,16 @@
         <v>45202</v>
       </c>
       <c r="B542" t="n">
-        <v>3.31037712097168</v>
+        <v>3.310376882553101</v>
       </c>
       <c r="C542" t="n">
-        <v>3.406052668007885</v>
+        <v>3.406052422698603</v>
       </c>
       <c r="D542" t="n">
-        <v>3.272106902157197</v>
+        <v>3.2721066664949</v>
       </c>
       <c r="E542" t="n">
-        <v>3.3199446756753</v>
+        <v>3.31994443656765</v>
       </c>
       <c r="F542" t="n">
         <v>29291500</v>
@@ -11352,16 +11352,16 @@
         <v>45209</v>
       </c>
       <c r="B547" t="n">
-        <v>3.415620088577271</v>
+        <v>3.41562032699585</v>
       </c>
       <c r="C547" t="n">
-        <v>3.425187642905165</v>
+        <v>3.425187881991583</v>
       </c>
       <c r="D547" t="n">
-        <v>3.348647208282007</v>
+        <v>3.348647442025716</v>
       </c>
       <c r="E547" t="n">
-        <v>3.367782316937797</v>
+        <v>3.367782552017183</v>
       </c>
       <c r="F547" t="n">
         <v>9595500</v>
@@ -11372,16 +11372,16 @@
         <v>45210</v>
       </c>
       <c r="B548" t="n">
-        <v>3.482593059539795</v>
+        <v>3.482593297958374</v>
       </c>
       <c r="C548" t="n">
-        <v>3.511295721390723</v>
+        <v>3.511295961774288</v>
       </c>
       <c r="D548" t="n">
-        <v>3.396484845878531</v>
+        <v>3.396485078402136</v>
       </c>
       <c r="E548" t="n">
-        <v>3.41561995377915</v>
+        <v>3.415620187612745</v>
       </c>
       <c r="F548" t="n">
         <v>15610900</v>
@@ -11412,16 +11412,16 @@
         <v>45215</v>
       </c>
       <c r="B550" t="n">
-        <v>3.386917352676392</v>
+        <v>3.386917591094971</v>
       </c>
       <c r="C550" t="n">
-        <v>3.434755123285962</v>
+        <v>3.434755365072033</v>
       </c>
       <c r="D550" t="n">
-        <v>3.348647136188735</v>
+        <v>3.348647371913321</v>
       </c>
       <c r="E550" t="n">
-        <v>3.377349798554477</v>
+        <v>3.377350036299558</v>
       </c>
       <c r="F550" t="n">
         <v>12135900</v>
@@ -26052,19 +26052,39 @@
         <v>46287</v>
       </c>
       <c r="B1282" t="n">
-        <v>0.28</v>
+        <v>0.2800000011920929</v>
       </c>
       <c r="C1282" t="n">
-        <v>0.28</v>
+        <v>0.2800000011920929</v>
       </c>
       <c r="D1282" t="n">
-        <v>0.26</v>
+        <v>0.2599999904632568</v>
       </c>
       <c r="E1282" t="n">
-        <v>0.27</v>
+        <v>0.2700000107288361</v>
       </c>
       <c r="F1282" t="n">
         <v>15773400</v>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B1283" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C1283" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="D1283" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E1283" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="F1283" t="n">
+        <v>15257900</v>
       </c>
     </row>
   </sheetData>

--- a/database/RAIZ4.xlsx
+++ b/database/RAIZ4.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1283"/>
+  <dimension ref="A1:F1284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44413</v>
       </c>
       <c r="B2" t="n">
-        <v>6.384482383728027</v>
+        <v>6.384481906890869</v>
       </c>
       <c r="C2" t="n">
-        <v>6.701942961521317</v>
+        <v>6.701942460974013</v>
       </c>
       <c r="D2" t="n">
-        <v>6.331572357511064</v>
+        <v>6.331571884625592</v>
       </c>
       <c r="E2" t="n">
-        <v>6.59612290908739</v>
+        <v>6.596122416443459</v>
       </c>
       <c r="F2" t="n">
         <v>98849900</v>
@@ -472,16 +472,16 @@
         <v>44414</v>
       </c>
       <c r="B3" t="n">
-        <v>6.261024475097656</v>
+        <v>6.261024951934814</v>
       </c>
       <c r="C3" t="n">
-        <v>6.48148308633695</v>
+        <v>6.481483579964149</v>
       </c>
       <c r="D3" t="n">
-        <v>6.19929633306517</v>
+        <v>6.199296805201136</v>
       </c>
       <c r="E3" t="n">
-        <v>6.393299725939519</v>
+        <v>6.393300212850708</v>
       </c>
       <c r="F3" t="n">
         <v>28799900</v>
@@ -492,16 +492,16 @@
         <v>44417</v>
       </c>
       <c r="B4" t="n">
-        <v>6.234570503234863</v>
+        <v>6.234570026397705</v>
       </c>
       <c r="C4" t="n">
-        <v>6.44621059622864</v>
+        <v>6.446210103204662</v>
       </c>
       <c r="D4" t="n">
-        <v>6.234570503234863</v>
+        <v>6.234570026397705</v>
       </c>
       <c r="E4" t="n">
-        <v>6.331572002277935</v>
+        <v>6.331571518021834</v>
       </c>
       <c r="F4" t="n">
         <v>14491100</v>
@@ -512,16 +512,16 @@
         <v>44418</v>
       </c>
       <c r="B5" t="n">
-        <v>6.261024475097656</v>
+        <v>6.261024951934814</v>
       </c>
       <c r="C5" t="n">
-        <v>6.313934491336116</v>
+        <v>6.313934972202879</v>
       </c>
       <c r="D5" t="n">
-        <v>6.216933005144656</v>
+        <v>6.216933478623825</v>
       </c>
       <c r="E5" t="n">
-        <v>6.278661147177143</v>
+        <v>6.278661625357502</v>
       </c>
       <c r="F5" t="n">
         <v>9988600</v>
@@ -592,16 +592,16 @@
         <v>44424</v>
       </c>
       <c r="B9" t="n">
-        <v>6.190478324890137</v>
+        <v>6.190477848052979</v>
       </c>
       <c r="C9" t="n">
-        <v>6.278661692952952</v>
+        <v>6.278661209323248</v>
       </c>
       <c r="D9" t="n">
-        <v>5.978838241539382</v>
+        <v>5.978837781004333</v>
       </c>
       <c r="E9" t="n">
-        <v>6.146386430612996</v>
+        <v>6.146385957172127</v>
       </c>
       <c r="F9" t="n">
         <v>13434600</v>
@@ -612,16 +612,16 @@
         <v>44425</v>
       </c>
       <c r="B10" t="n">
-        <v>6.014111518859863</v>
+        <v>6.014111995697021</v>
       </c>
       <c r="C10" t="n">
-        <v>6.164023032578428</v>
+        <v>6.164023521301528</v>
       </c>
       <c r="D10" t="n">
-        <v>5.961201498637171</v>
+        <v>5.961201971279285</v>
       </c>
       <c r="E10" t="n">
-        <v>6.111113012355736</v>
+        <v>6.111113496883791</v>
       </c>
       <c r="F10" t="n">
         <v>17772000</v>
@@ -632,16 +632,16 @@
         <v>44426</v>
       </c>
       <c r="B11" t="n">
-        <v>6.005291938781738</v>
+        <v>6.005292892456055</v>
       </c>
       <c r="C11" t="n">
-        <v>6.172840517574881</v>
+        <v>6.172841497856859</v>
       </c>
       <c r="D11" t="n">
-        <v>5.925926711855674</v>
+        <v>5.925927652926344</v>
       </c>
       <c r="E11" t="n">
-        <v>6.022928609155154</v>
+        <v>6.022929565630274</v>
       </c>
       <c r="F11" t="n">
         <v>8841700</v>
@@ -672,16 +672,16 @@
         <v>44428</v>
       </c>
       <c r="B13" t="n">
-        <v>6.155204296112061</v>
+        <v>6.155205249786377</v>
       </c>
       <c r="C13" t="n">
-        <v>6.21693285716669</v>
+        <v>6.216933820405099</v>
       </c>
       <c r="D13" t="n">
-        <v>6.022929048418668</v>
+        <v>6.022929981598537</v>
       </c>
       <c r="E13" t="n">
-        <v>6.075839063397741</v>
+        <v>6.075840004775376</v>
       </c>
       <c r="F13" t="n">
         <v>3109200</v>
@@ -712,16 +712,16 @@
         <v>44432</v>
       </c>
       <c r="B15" t="n">
-        <v>6.393299102783203</v>
+        <v>6.39330005645752</v>
       </c>
       <c r="C15" t="n">
-        <v>6.525574340732168</v>
+        <v>6.525575314137689</v>
       </c>
       <c r="D15" t="n">
-        <v>6.331570546275982</v>
+        <v>6.331571490742386</v>
       </c>
       <c r="E15" t="n">
-        <v>6.38448055735729</v>
+        <v>6.384481509716164</v>
       </c>
       <c r="F15" t="n">
         <v>6054100</v>
@@ -752,16 +752,16 @@
         <v>44434</v>
       </c>
       <c r="B17" t="n">
-        <v>6.261024475097656</v>
+        <v>6.261024951934814</v>
       </c>
       <c r="C17" t="n">
-        <v>6.507938304701895</v>
+        <v>6.507938800343913</v>
       </c>
       <c r="D17" t="n">
-        <v>6.261024475097656</v>
+        <v>6.261024951934814</v>
       </c>
       <c r="E17" t="n">
-        <v>6.472664960542923</v>
+        <v>6.472665453498537</v>
       </c>
       <c r="F17" t="n">
         <v>7968100</v>
@@ -812,16 +812,16 @@
         <v>44439</v>
       </c>
       <c r="B20" t="n">
-        <v>6.261024475097656</v>
+        <v>6.261024951934814</v>
       </c>
       <c r="C20" t="n">
-        <v>6.305116365542087</v>
+        <v>6.305116845737266</v>
       </c>
       <c r="D20" t="n">
-        <v>6.181659660985684</v>
+        <v>6.181660131778449</v>
       </c>
       <c r="E20" t="n">
-        <v>6.305116365542087</v>
+        <v>6.305116845737266</v>
       </c>
       <c r="F20" t="n">
         <v>3704100</v>
@@ -832,16 +832,16 @@
         <v>44440</v>
       </c>
       <c r="B21" t="n">
-        <v>6.234570503234863</v>
+        <v>6.234570026397705</v>
       </c>
       <c r="C21" t="n">
-        <v>6.305117200899455</v>
+        <v>6.305116718666691</v>
       </c>
       <c r="D21" t="n">
-        <v>6.199297154402568</v>
+        <v>6.199296680263212</v>
       </c>
       <c r="E21" t="n">
-        <v>6.261025304613343</v>
+        <v>6.261024825752847</v>
       </c>
       <c r="F21" t="n">
         <v>6468600</v>
@@ -852,16 +852,16 @@
         <v>44441</v>
       </c>
       <c r="B22" t="n">
-        <v>5.996475219726562</v>
+        <v>5.996474742889404</v>
       </c>
       <c r="C22" t="n">
-        <v>6.252207210343668</v>
+        <v>6.252206713170811</v>
       </c>
       <c r="D22" t="n">
-        <v>5.970019997718263</v>
+        <v>5.970019522984813</v>
       </c>
       <c r="E22" t="n">
-        <v>6.234570535835299</v>
+        <v>6.234570040064902</v>
       </c>
       <c r="F22" t="n">
         <v>3746900</v>
@@ -872,16 +872,16 @@
         <v>44442</v>
       </c>
       <c r="B23" t="n">
-        <v>6.17284107208252</v>
+        <v>6.172840595245361</v>
       </c>
       <c r="C23" t="n">
-        <v>6.17284107208252</v>
+        <v>6.172840595245361</v>
       </c>
       <c r="D23" t="n">
-        <v>5.934745790407565</v>
+        <v>5.934745331962696</v>
       </c>
       <c r="E23" t="n">
-        <v>6.031747696420747</v>
+        <v>6.031747230482714</v>
       </c>
       <c r="F23" t="n">
         <v>3705400</v>
@@ -912,16 +912,16 @@
         <v>44447</v>
       </c>
       <c r="B25" t="n">
-        <v>5.758379936218262</v>
+        <v>5.758378982543945</v>
       </c>
       <c r="C25" t="n">
-        <v>6.11111342838262</v>
+        <v>6.111112416290331</v>
       </c>
       <c r="D25" t="n">
-        <v>5.661378015627318</v>
+        <v>5.661377078017978</v>
       </c>
       <c r="E25" t="n">
-        <v>6.11111342838262</v>
+        <v>6.111112416290331</v>
       </c>
       <c r="F25" t="n">
         <v>10251100</v>
@@ -932,16 +932,16 @@
         <v>44448</v>
       </c>
       <c r="B26" t="n">
-        <v>5.652559280395508</v>
+        <v>5.65255880355835</v>
       </c>
       <c r="C26" t="n">
-        <v>5.837744567878833</v>
+        <v>5.837744075419861</v>
       </c>
       <c r="D26" t="n">
-        <v>5.599649258327626</v>
+        <v>5.599648785953838</v>
       </c>
       <c r="E26" t="n">
-        <v>5.758379745022749</v>
+        <v>5.758379259258814</v>
       </c>
       <c r="F26" t="n">
         <v>5428200</v>
@@ -952,16 +952,16 @@
         <v>44449</v>
       </c>
       <c r="B27" t="n">
-        <v>5.731924057006836</v>
+        <v>5.731924533843994</v>
       </c>
       <c r="C27" t="n">
-        <v>5.899472656824471</v>
+        <v>5.89947314759995</v>
       </c>
       <c r="D27" t="n">
-        <v>5.617285474948753</v>
+        <v>5.617285942249159</v>
       </c>
       <c r="E27" t="n">
-        <v>5.76719740217987</v>
+        <v>5.767197881951408</v>
       </c>
       <c r="F27" t="n">
         <v>5905500</v>
@@ -972,16 +972,16 @@
         <v>44452</v>
       </c>
       <c r="B28" t="n">
-        <v>6.128749847412109</v>
+        <v>6.128748893737793</v>
       </c>
       <c r="C28" t="n">
-        <v>6.172841742339696</v>
+        <v>6.172840781804387</v>
       </c>
       <c r="D28" t="n">
-        <v>5.92592788762986</v>
+        <v>5.925926965515992</v>
       </c>
       <c r="E28" t="n">
-        <v>5.952383108684708</v>
+        <v>5.95238218245423</v>
       </c>
       <c r="F28" t="n">
         <v>8999600</v>
@@ -1012,16 +1012,16 @@
         <v>44454</v>
       </c>
       <c r="B30" t="n">
-        <v>6.384482383728027</v>
+        <v>6.384481906890869</v>
       </c>
       <c r="C30" t="n">
-        <v>6.507939532059118</v>
+        <v>6.507939046001328</v>
       </c>
       <c r="D30" t="n">
-        <v>6.296299006699756</v>
+        <v>6.29629853644874</v>
       </c>
       <c r="E30" t="n">
-        <v>6.384482383728027</v>
+        <v>6.384481906890869</v>
       </c>
       <c r="F30" t="n">
         <v>7265900</v>
@@ -1052,16 +1052,16 @@
         <v>44456</v>
       </c>
       <c r="B32" t="n">
-        <v>6.384482383728027</v>
+        <v>6.384481906890869</v>
       </c>
       <c r="C32" t="n">
-        <v>6.384482383728027</v>
+        <v>6.384481906890869</v>
       </c>
       <c r="D32" t="n">
-        <v>5.978838849397976</v>
+        <v>5.978838402857074</v>
       </c>
       <c r="E32" t="n">
-        <v>6.261025655888447</v>
+        <v>6.261025188271888</v>
       </c>
       <c r="F32" t="n">
         <v>16008100</v>
@@ -1112,16 +1112,16 @@
         <v>44461</v>
       </c>
       <c r="B35" t="n">
-        <v>6.446209907531738</v>
+        <v>6.446210384368896</v>
       </c>
       <c r="C35" t="n">
-        <v>6.560848489234745</v>
+        <v>6.560848974551915</v>
       </c>
       <c r="D35" t="n">
-        <v>6.402118436447734</v>
+        <v>6.40211891002337</v>
       </c>
       <c r="E35" t="n">
-        <v>6.463846580063628</v>
+        <v>6.463847058205402</v>
       </c>
       <c r="F35" t="n">
         <v>10254600</v>
@@ -1132,16 +1132,16 @@
         <v>44462</v>
       </c>
       <c r="B36" t="n">
-        <v>6.375663757324219</v>
+        <v>6.375663280487061</v>
       </c>
       <c r="C36" t="n">
-        <v>6.54321237081167</v>
+        <v>6.543211881443518</v>
       </c>
       <c r="D36" t="n">
-        <v>6.340390409273332</v>
+        <v>6.340389935074274</v>
       </c>
       <c r="E36" t="n">
-        <v>6.507939022760783</v>
+        <v>6.507938536030731</v>
       </c>
       <c r="F36" t="n">
         <v>6341600</v>
@@ -1152,16 +1152,16 @@
         <v>44463</v>
       </c>
       <c r="B37" t="n">
-        <v>6.17284107208252</v>
+        <v>6.172840595245361</v>
       </c>
       <c r="C37" t="n">
-        <v>6.375663009842031</v>
+        <v>6.375662517337365</v>
       </c>
       <c r="D37" t="n">
-        <v>6.164022525857945</v>
+        <v>6.164022049701998</v>
       </c>
       <c r="E37" t="n">
-        <v>6.340389665926588</v>
+        <v>6.340389176146703</v>
       </c>
       <c r="F37" t="n">
         <v>5138200</v>
@@ -1212,16 +1212,16 @@
         <v>44468</v>
       </c>
       <c r="B40" t="n">
-        <v>6.040565967559814</v>
+        <v>6.040565490722656</v>
       </c>
       <c r="C40" t="n">
-        <v>6.25220645663842</v>
+        <v>6.252205963094541</v>
       </c>
       <c r="D40" t="n">
-        <v>6.040565967559814</v>
+        <v>6.040565490722656</v>
       </c>
       <c r="E40" t="n">
-        <v>6.216933111873892</v>
+        <v>6.216932621114461</v>
       </c>
       <c r="F40" t="n">
         <v>6482600</v>
@@ -1232,16 +1232,16 @@
         <v>44469</v>
       </c>
       <c r="B41" t="n">
-        <v>6.261024475097656</v>
+        <v>6.261024951934814</v>
       </c>
       <c r="C41" t="n">
-        <v>6.349207835495088</v>
+        <v>6.349208319048255</v>
       </c>
       <c r="D41" t="n">
-        <v>6.058202535937849</v>
+        <v>6.058202997328168</v>
       </c>
       <c r="E41" t="n">
-        <v>6.084657754302794</v>
+        <v>6.084658217707932</v>
       </c>
       <c r="F41" t="n">
         <v>15990100</v>
@@ -1252,16 +1252,16 @@
         <v>44470</v>
       </c>
       <c r="B42" t="n">
-        <v>6.499119281768799</v>
+        <v>6.499120712280273</v>
       </c>
       <c r="C42" t="n">
-        <v>6.569665964912827</v>
+        <v>6.569667410952226</v>
       </c>
       <c r="D42" t="n">
-        <v>6.331570699056035</v>
+        <v>6.331572092688639</v>
       </c>
       <c r="E42" t="n">
-        <v>6.331570699056035</v>
+        <v>6.331572092688639</v>
       </c>
       <c r="F42" t="n">
         <v>15528000</v>
@@ -1272,16 +1272,16 @@
         <v>44473</v>
       </c>
       <c r="B43" t="n">
-        <v>6.190478324890137</v>
+        <v>6.190477848052979</v>
       </c>
       <c r="C43" t="n">
-        <v>6.552030344193411</v>
+        <v>6.552029839506799</v>
       </c>
       <c r="D43" t="n">
-        <v>6.190478324890137</v>
+        <v>6.190477848052979</v>
       </c>
       <c r="E43" t="n">
-        <v>6.5255755440203</v>
+        <v>6.525575041371436</v>
       </c>
       <c r="F43" t="n">
         <v>12019000</v>
@@ -1292,16 +1292,16 @@
         <v>44474</v>
       </c>
       <c r="B44" t="n">
-        <v>6.287479877471924</v>
+        <v>6.287480354309082</v>
       </c>
       <c r="C44" t="n">
-        <v>6.366844693906587</v>
+        <v>6.366845176762705</v>
       </c>
       <c r="D44" t="n">
-        <v>6.2433879857371</v>
+        <v>6.243388459230366</v>
       </c>
       <c r="E44" t="n">
-        <v>6.296298003524023</v>
+        <v>6.29629848102994</v>
       </c>
       <c r="F44" t="n">
         <v>12888200</v>
@@ -1352,16 +1352,16 @@
         <v>44477</v>
       </c>
       <c r="B47" t="n">
-        <v>6.310671329498291</v>
+        <v>6.310670375823975</v>
       </c>
       <c r="C47" t="n">
-        <v>6.655372174193518</v>
+        <v>6.655371168427701</v>
       </c>
       <c r="D47" t="n">
-        <v>6.292994395522999</v>
+        <v>6.292993444520037</v>
       </c>
       <c r="E47" t="n">
-        <v>6.363702131424168</v>
+        <v>6.36370116973579</v>
       </c>
       <c r="F47" t="n">
         <v>20480700</v>
@@ -1372,16 +1372,16 @@
         <v>44480</v>
       </c>
       <c r="B48" t="n">
-        <v>6.213447570800781</v>
+        <v>6.213448047637939</v>
       </c>
       <c r="C48" t="n">
-        <v>6.407893818474543</v>
+        <v>6.407894310234044</v>
       </c>
       <c r="D48" t="n">
-        <v>6.213447570800781</v>
+        <v>6.213448047637939</v>
       </c>
       <c r="E48" t="n">
-        <v>6.363701278732132</v>
+        <v>6.363701767100176</v>
       </c>
       <c r="F48" t="n">
         <v>10407400</v>
@@ -1432,16 +1432,16 @@
         <v>44484</v>
       </c>
       <c r="B51" t="n">
-        <v>6.275317668914795</v>
+        <v>6.275317192077637</v>
       </c>
       <c r="C51" t="n">
-        <v>6.354864085157887</v>
+        <v>6.354863602276304</v>
       </c>
       <c r="D51" t="n">
-        <v>6.222286865236521</v>
+        <v>6.222286392428969</v>
       </c>
       <c r="E51" t="n">
-        <v>6.337187150598463</v>
+        <v>6.337186669060081</v>
       </c>
       <c r="F51" t="n">
         <v>34203500</v>
@@ -1472,16 +1472,16 @@
         <v>44488</v>
       </c>
       <c r="B53" t="n">
-        <v>5.91294002532959</v>
+        <v>5.912939548492432</v>
       </c>
       <c r="C53" t="n">
-        <v>6.186932709011659</v>
+        <v>6.186932210078912</v>
       </c>
       <c r="D53" t="n">
-        <v>5.895263091590468</v>
+        <v>5.89526261617883</v>
       </c>
       <c r="E53" t="n">
-        <v>6.169255775272537</v>
+        <v>6.169255277765311</v>
       </c>
       <c r="F53" t="n">
         <v>11473400</v>
@@ -1492,16 +1492,16 @@
         <v>44489</v>
       </c>
       <c r="B54" t="n">
-        <v>5.904101371765137</v>
+        <v>5.904101848602295</v>
       </c>
       <c r="C54" t="n">
-        <v>6.045517263705048</v>
+        <v>6.04551775196348</v>
       </c>
       <c r="D54" t="n">
-        <v>5.842232314152062</v>
+        <v>5.842232785992445</v>
       </c>
       <c r="E54" t="n">
-        <v>6.010163396082907</v>
+        <v>6.010163881486029</v>
       </c>
       <c r="F54" t="n">
         <v>6234400</v>
@@ -1512,16 +1512,16 @@
         <v>44490</v>
       </c>
       <c r="B55" t="n">
-        <v>5.683139801025391</v>
+        <v>5.683139324188232</v>
       </c>
       <c r="C55" t="n">
-        <v>5.842232635527925</v>
+        <v>5.84223214534227</v>
       </c>
       <c r="D55" t="n">
-        <v>5.471016583623838</v>
+        <v>5.471016124584628</v>
       </c>
       <c r="E55" t="n">
-        <v>5.798040087843582</v>
+        <v>5.798039601365852</v>
       </c>
       <c r="F55" t="n">
         <v>12472300</v>
@@ -1572,16 +1572,16 @@
         <v>44495</v>
       </c>
       <c r="B58" t="n">
-        <v>5.815716743469238</v>
+        <v>5.81571626663208</v>
       </c>
       <c r="C58" t="n">
-        <v>5.868747545274117</v>
+        <v>5.868747064088904</v>
       </c>
       <c r="D58" t="n">
-        <v>5.683139528231368</v>
+        <v>5.683139062264364</v>
       </c>
       <c r="E58" t="n">
-        <v>5.833393677404199</v>
+        <v>5.833393199117688</v>
       </c>
       <c r="F58" t="n">
         <v>8470300</v>
@@ -1612,16 +1612,16 @@
         <v>44497</v>
       </c>
       <c r="B60" t="n">
-        <v>5.992486000061035</v>
+        <v>5.992485523223877</v>
       </c>
       <c r="C60" t="n">
-        <v>6.027839864956272</v>
+        <v>6.027839385305918</v>
       </c>
       <c r="D60" t="n">
-        <v>5.727331591895446</v>
+        <v>5.727331136157289</v>
       </c>
       <c r="E60" t="n">
-        <v>5.75384720129253</v>
+        <v>5.75384674344446</v>
       </c>
       <c r="F60" t="n">
         <v>8299700</v>
@@ -1632,16 +1632,16 @@
         <v>44498</v>
       </c>
       <c r="B61" t="n">
-        <v>5.992486000061035</v>
+        <v>5.992485523223877</v>
       </c>
       <c r="C61" t="n">
-        <v>6.019001188006806</v>
+        <v>6.019000709059767</v>
       </c>
       <c r="D61" t="n">
-        <v>5.842231863530622</v>
+        <v>5.842231398649562</v>
       </c>
       <c r="E61" t="n">
-        <v>5.957131713714485</v>
+        <v>5.957131239690556</v>
       </c>
       <c r="F61" t="n">
         <v>3926300</v>
@@ -1652,16 +1652,16 @@
         <v>44501</v>
       </c>
       <c r="B62" t="n">
-        <v>6.001324653625488</v>
+        <v>6.00132417678833</v>
       </c>
       <c r="C62" t="n">
-        <v>6.063194132021597</v>
+        <v>6.063193650268579</v>
       </c>
       <c r="D62" t="n">
-        <v>5.948293852765114</v>
+        <v>5.948293380141535</v>
       </c>
       <c r="E62" t="n">
-        <v>5.965970786385239</v>
+        <v>5.965970312357133</v>
       </c>
       <c r="F62" t="n">
         <v>5059700</v>
@@ -1692,16 +1692,16 @@
         <v>44504</v>
       </c>
       <c r="B64" t="n">
-        <v>5.965970993041992</v>
+        <v>5.965970516204834</v>
       </c>
       <c r="C64" t="n">
-        <v>6.160417269598838</v>
+        <v>6.160416777220335</v>
       </c>
       <c r="D64" t="n">
-        <v>5.842232453414908</v>
+        <v>5.842231986467696</v>
       </c>
       <c r="E64" t="n">
-        <v>6.098548210510975</v>
+        <v>6.098547723077428</v>
       </c>
       <c r="F64" t="n">
         <v>8687600</v>
@@ -1712,16 +1712,16 @@
         <v>44505</v>
       </c>
       <c r="B65" t="n">
-        <v>5.965970993041992</v>
+        <v>5.965970516204834</v>
       </c>
       <c r="C65" t="n">
-        <v>6.054355664204195</v>
+        <v>6.054355180302789</v>
       </c>
       <c r="D65" t="n">
-        <v>5.939455380967654</v>
+        <v>5.939454906249786</v>
       </c>
       <c r="E65" t="n">
-        <v>6.001324861506873</v>
+        <v>6.001324381844015</v>
       </c>
       <c r="F65" t="n">
         <v>3123600</v>
@@ -1732,16 +1732,16 @@
         <v>44508</v>
       </c>
       <c r="B66" t="n">
-        <v>5.98364782333374</v>
+        <v>5.983647346496582</v>
       </c>
       <c r="C66" t="n">
-        <v>6.036678625109875</v>
+        <v>6.036678144046689</v>
       </c>
       <c r="D66" t="n">
-        <v>5.93945527779462</v>
+        <v>5.939454804479167</v>
       </c>
       <c r="E66" t="n">
-        <v>6.010163434947482</v>
+        <v>6.010162955997293</v>
       </c>
       <c r="F66" t="n">
         <v>3898000</v>
@@ -1752,16 +1752,16 @@
         <v>44509</v>
       </c>
       <c r="B67" t="n">
-        <v>5.948293209075928</v>
+        <v>5.948294162750244</v>
       </c>
       <c r="C67" t="n">
-        <v>6.169255066141971</v>
+        <v>6.169256055242525</v>
       </c>
       <c r="D67" t="n">
-        <v>5.948293209075928</v>
+        <v>5.948294162750244</v>
       </c>
       <c r="E67" t="n">
-        <v>5.992485749069655</v>
+        <v>5.992486709829246</v>
       </c>
       <c r="F67" t="n">
         <v>5176300</v>
@@ -1772,16 +1772,16 @@
         <v>44510</v>
       </c>
       <c r="B68" t="n">
-        <v>5.745008945465088</v>
+        <v>5.74500846862793</v>
       </c>
       <c r="C68" t="n">
-        <v>6.010163373067091</v>
+        <v>6.010162874222051</v>
       </c>
       <c r="D68" t="n">
-        <v>5.745008945465088</v>
+        <v>5.74500846862793</v>
       </c>
       <c r="E68" t="n">
-        <v>5.957132150385616</v>
+        <v>5.957131655942178</v>
       </c>
       <c r="F68" t="n">
         <v>10074000</v>
@@ -1832,16 +1832,16 @@
         <v>44516</v>
       </c>
       <c r="B71" t="n">
-        <v>5.320762157440186</v>
+        <v>5.320762634277344</v>
       </c>
       <c r="C71" t="n">
-        <v>5.815716727730977</v>
+        <v>5.815717248925075</v>
       </c>
       <c r="D71" t="n">
-        <v>5.223538810335335</v>
+        <v>5.223539278459512</v>
       </c>
       <c r="E71" t="n">
-        <v>5.789201537625966</v>
+        <v>5.789202056443821</v>
       </c>
       <c r="F71" t="n">
         <v>27445700</v>
@@ -1892,16 +1892,16 @@
         <v>44519</v>
       </c>
       <c r="B74" t="n">
-        <v>5.241215705871582</v>
+        <v>5.241215229034424</v>
       </c>
       <c r="C74" t="n">
-        <v>5.285408250991699</v>
+        <v>5.285407770133975</v>
       </c>
       <c r="D74" t="n">
-        <v>5.090961979656143</v>
+        <v>5.090961516488821</v>
       </c>
       <c r="E74" t="n">
-        <v>5.161669714687254</v>
+        <v>5.161669245087059</v>
       </c>
       <c r="F74" t="n">
         <v>11364600</v>
@@ -1932,16 +1932,16 @@
         <v>44523</v>
       </c>
       <c r="B76" t="n">
-        <v>5.011415481567383</v>
+        <v>5.011415958404541</v>
       </c>
       <c r="C76" t="n">
-        <v>5.099800148849164</v>
+        <v>5.09980063409614</v>
       </c>
       <c r="D76" t="n">
-        <v>4.781614925183414</v>
+        <v>4.781615380155004</v>
       </c>
       <c r="E76" t="n">
-        <v>5.002576804113536</v>
+        <v>5.002577280109692</v>
       </c>
       <c r="F76" t="n">
         <v>9084200</v>
@@ -1952,16 +1952,16 @@
         <v>44524</v>
       </c>
       <c r="B77" t="n">
-        <v>4.923030853271484</v>
+        <v>4.923030376434326</v>
       </c>
       <c r="C77" t="n">
-        <v>5.020253777325691</v>
+        <v>5.020253291071671</v>
       </c>
       <c r="D77" t="n">
-        <v>4.825807507765937</v>
+        <v>4.825807040345681</v>
       </c>
       <c r="E77" t="n">
-        <v>4.923030853271484</v>
+        <v>4.923030376434326</v>
       </c>
       <c r="F77" t="n">
         <v>8397000</v>
@@ -1972,16 +1972,16 @@
         <v>44525</v>
       </c>
       <c r="B78" t="n">
-        <v>5.373792171478271</v>
+        <v>5.373791694641113</v>
       </c>
       <c r="C78" t="n">
-        <v>5.373792171478271</v>
+        <v>5.373791694641113</v>
       </c>
       <c r="D78" t="n">
-        <v>4.799291272172914</v>
+        <v>4.79929084631342</v>
       </c>
       <c r="E78" t="n">
-        <v>4.949545398916761</v>
+        <v>4.949544959724644</v>
       </c>
       <c r="F78" t="n">
         <v>20546100</v>
@@ -1992,16 +1992,16 @@
         <v>44526</v>
       </c>
       <c r="B79" t="n">
-        <v>5.223538875579834</v>
+        <v>5.223538398742676</v>
       </c>
       <c r="C79" t="n">
-        <v>5.338439158006967</v>
+        <v>5.338438670680995</v>
       </c>
       <c r="D79" t="n">
-        <v>5.02025392261312</v>
+        <v>5.020253464333078</v>
       </c>
       <c r="E79" t="n">
-        <v>5.037930856721036</v>
+        <v>5.037930396827334</v>
       </c>
       <c r="F79" t="n">
         <v>8564200</v>
@@ -2032,16 +2032,16 @@
         <v>44530</v>
       </c>
       <c r="B81" t="n">
-        <v>4.825807094573975</v>
+        <v>4.825808048248291</v>
       </c>
       <c r="C81" t="n">
-        <v>5.126315361433205</v>
+        <v>5.12631637449386</v>
       </c>
       <c r="D81" t="n">
-        <v>4.790453230408336</v>
+        <v>4.790454177096034</v>
       </c>
       <c r="E81" t="n">
-        <v>5.073284143733442</v>
+        <v>5.073285146314087</v>
       </c>
       <c r="F81" t="n">
         <v>11282700</v>
@@ -2052,16 +2052,16 @@
         <v>44531</v>
       </c>
       <c r="B82" t="n">
-        <v>4.852322101593018</v>
+        <v>4.852322578430176</v>
       </c>
       <c r="C82" t="n">
-        <v>5.152830357281196</v>
+        <v>5.152830863649267</v>
       </c>
       <c r="D82" t="n">
-        <v>4.852322101593018</v>
+        <v>4.852322578430176</v>
       </c>
       <c r="E82" t="n">
-        <v>4.896514640882911</v>
+        <v>4.896515122062865</v>
       </c>
       <c r="F82" t="n">
         <v>12492100</v>
@@ -2072,16 +2072,16 @@
         <v>44532</v>
       </c>
       <c r="B83" t="n">
-        <v>5.029092311859131</v>
+        <v>5.029091835021973</v>
       </c>
       <c r="C83" t="n">
-        <v>5.029092311859131</v>
+        <v>5.029091835021973</v>
       </c>
       <c r="D83" t="n">
-        <v>4.746260960907972</v>
+        <v>4.746260510887681</v>
       </c>
       <c r="E83" t="n">
-        <v>4.905353780202955</v>
+        <v>4.905353315098159</v>
       </c>
       <c r="F83" t="n">
         <v>18379200</v>
@@ -2092,16 +2092,16 @@
         <v>44533</v>
       </c>
       <c r="B84" t="n">
-        <v>5.320762157440186</v>
+        <v>5.320762634277344</v>
       </c>
       <c r="C84" t="n">
-        <v>5.329600835109421</v>
+        <v>5.329601312738686</v>
       </c>
       <c r="D84" t="n">
-        <v>4.976061735915614</v>
+        <v>4.976062181861339</v>
       </c>
       <c r="E84" t="n">
-        <v>5.020253859907747</v>
+        <v>5.020254309813891</v>
       </c>
       <c r="F84" t="n">
         <v>10548200</v>
@@ -2152,16 +2152,16 @@
         <v>44538</v>
       </c>
       <c r="B87" t="n">
-        <v>5.285408020019531</v>
+        <v>5.285407543182373</v>
       </c>
       <c r="C87" t="n">
-        <v>5.33843881897542</v>
+        <v>5.338438337353947</v>
       </c>
       <c r="D87" t="n">
-        <v>5.126315623151864</v>
+        <v>5.12631516066765</v>
       </c>
       <c r="E87" t="n">
-        <v>5.223538543845331</v>
+        <v>5.223538072589892</v>
       </c>
       <c r="F87" t="n">
         <v>9204000</v>
@@ -2212,16 +2212,16 @@
         <v>44543</v>
       </c>
       <c r="B90" t="n">
-        <v>5.497531414031982</v>
+        <v>5.497530937194824</v>
       </c>
       <c r="C90" t="n">
-        <v>5.621270370841238</v>
+        <v>5.621269883271384</v>
       </c>
       <c r="D90" t="n">
-        <v>5.426823679541746</v>
+        <v>5.426823208837535</v>
       </c>
       <c r="E90" t="n">
-        <v>5.444500613164305</v>
+        <v>5.444500140926858</v>
       </c>
       <c r="F90" t="n">
         <v>8265100</v>
@@ -2232,16 +2232,16 @@
         <v>44544</v>
       </c>
       <c r="B91" t="n">
-        <v>5.453338623046875</v>
+        <v>5.453339576721191</v>
       </c>
       <c r="C91" t="n">
-        <v>5.603592751168627</v>
+        <v>5.603593731119232</v>
       </c>
       <c r="D91" t="n">
-        <v>5.426823015133682</v>
+        <v>5.426823964170976</v>
       </c>
       <c r="E91" t="n">
-        <v>5.497530740967144</v>
+        <v>5.497531702369733</v>
       </c>
       <c r="F91" t="n">
         <v>6640900</v>
@@ -2292,16 +2292,16 @@
         <v>44547</v>
       </c>
       <c r="B94" t="n">
-        <v>5.241215705871582</v>
+        <v>5.241215229034424</v>
       </c>
       <c r="C94" t="n">
-        <v>5.347277729869593</v>
+        <v>5.347277243383087</v>
       </c>
       <c r="D94" t="n">
-        <v>5.241215705871582</v>
+        <v>5.241215229034424</v>
       </c>
       <c r="E94" t="n">
-        <v>5.320762118507254</v>
+        <v>5.320761634433095</v>
       </c>
       <c r="F94" t="n">
         <v>50153800</v>
@@ -2312,16 +2312,16 @@
         <v>44550</v>
       </c>
       <c r="B95" t="n">
-        <v>5.143993377685547</v>
+        <v>5.14399242401123</v>
       </c>
       <c r="C95" t="n">
-        <v>5.179347249302515</v>
+        <v>5.179346289073743</v>
       </c>
       <c r="D95" t="n">
-        <v>4.94954666234083</v>
+        <v>4.949545744716101</v>
       </c>
       <c r="E95" t="n">
-        <v>5.179347249302515</v>
+        <v>5.179346289073743</v>
       </c>
       <c r="F95" t="n">
         <v>8433600</v>
@@ -2332,16 +2332,16 @@
         <v>44551</v>
       </c>
       <c r="B96" t="n">
-        <v>5.082122802734375</v>
+        <v>5.082123279571533</v>
       </c>
       <c r="C96" t="n">
-        <v>5.223538258902567</v>
+        <v>5.223538749008224</v>
       </c>
       <c r="D96" t="n">
-        <v>5.020253329935139</v>
+        <v>5.020253800967309</v>
       </c>
       <c r="E96" t="n">
-        <v>5.170507462839494</v>
+        <v>5.170507947969465</v>
       </c>
       <c r="F96" t="n">
         <v>5049800</v>
@@ -2352,16 +2352,16 @@
         <v>44552</v>
       </c>
       <c r="B97" t="n">
-        <v>5.011415481567383</v>
+        <v>5.011415958404541</v>
       </c>
       <c r="C97" t="n">
-        <v>5.073284537938961</v>
+        <v>5.073285020662972</v>
       </c>
       <c r="D97" t="n">
-        <v>4.914192136831755</v>
+        <v>4.914192604418092</v>
       </c>
       <c r="E97" t="n">
-        <v>5.055607604482605</v>
+        <v>5.055608085524652</v>
       </c>
       <c r="F97" t="n">
         <v>4649500</v>
@@ -2412,16 +2412,16 @@
         <v>44558</v>
       </c>
       <c r="B100" t="n">
-        <v>5.347277164459229</v>
+        <v>5.347277641296387</v>
       </c>
       <c r="C100" t="n">
-        <v>5.347277164459229</v>
+        <v>5.347277641296387</v>
       </c>
       <c r="D100" t="n">
-        <v>5.188184356010038</v>
+        <v>5.188184818660282</v>
       </c>
       <c r="E100" t="n">
-        <v>5.21469996456867</v>
+        <v>5.214700429583412</v>
       </c>
       <c r="F100" t="n">
         <v>4379800</v>
@@ -2472,16 +2472,16 @@
         <v>44564</v>
       </c>
       <c r="B103" t="n">
-        <v>5.54172420501709</v>
+        <v>5.541723728179932</v>
       </c>
       <c r="C103" t="n">
-        <v>5.745009161433563</v>
+        <v>5.745008667104768</v>
       </c>
       <c r="D103" t="n">
-        <v>5.5063703362013</v>
+        <v>5.506369862406162</v>
       </c>
       <c r="E103" t="n">
-        <v>5.691978358209878</v>
+        <v>5.691977868444114</v>
       </c>
       <c r="F103" t="n">
         <v>7451800</v>
@@ -2492,16 +2492,16 @@
         <v>44565</v>
       </c>
       <c r="B104" t="n">
-        <v>5.594754695892334</v>
+        <v>5.594754219055176</v>
       </c>
       <c r="C104" t="n">
-        <v>5.612431629313347</v>
+        <v>5.612431150969596</v>
       </c>
       <c r="D104" t="n">
-        <v>5.444500551088055</v>
+        <v>5.444500087056956</v>
       </c>
       <c r="E104" t="n">
-        <v>5.532885639644457</v>
+        <v>5.532885168080356</v>
       </c>
       <c r="F104" t="n">
         <v>10613100</v>
@@ -2532,16 +2532,16 @@
         <v>44567</v>
       </c>
       <c r="B106" t="n">
-        <v>4.932944774627686</v>
+        <v>4.932945251464844</v>
       </c>
       <c r="C106" t="n">
-        <v>5.190238625560705</v>
+        <v>5.190239127268864</v>
       </c>
       <c r="D106" t="n">
-        <v>4.870839201862625</v>
+        <v>4.870839672696422</v>
       </c>
       <c r="E106" t="n">
-        <v>5.145877864779607</v>
+        <v>5.145878362199686</v>
       </c>
       <c r="F106" t="n">
         <v>8427100</v>
@@ -2552,16 +2552,16 @@
         <v>44568</v>
       </c>
       <c r="B107" t="n">
-        <v>5.163623332977295</v>
+        <v>5.163622379302979</v>
       </c>
       <c r="C107" t="n">
-        <v>5.278961673563245</v>
+        <v>5.278960698586984</v>
       </c>
       <c r="D107" t="n">
-        <v>4.941818213532458</v>
+        <v>4.941817300823532</v>
       </c>
       <c r="E107" t="n">
-        <v>4.977306998798857</v>
+        <v>4.977306079535475</v>
       </c>
       <c r="F107" t="n">
         <v>10961100</v>
@@ -2592,16 +2592,16 @@
         <v>44572</v>
       </c>
       <c r="B109" t="n">
-        <v>5.23460054397583</v>
+        <v>5.234600067138672</v>
       </c>
       <c r="C109" t="n">
-        <v>5.23460054397583</v>
+        <v>5.234600067138672</v>
       </c>
       <c r="D109" t="n">
-        <v>5.021667423942884</v>
+        <v>5.021666966502512</v>
       </c>
       <c r="E109" t="n">
-        <v>5.021667423942884</v>
+        <v>5.021666966502512</v>
       </c>
       <c r="F109" t="n">
         <v>5425200</v>
@@ -2612,16 +2612,16 @@
         <v>44573</v>
       </c>
       <c r="B110" t="n">
-        <v>5.438661575317383</v>
+        <v>5.438660621643066</v>
       </c>
       <c r="C110" t="n">
-        <v>5.518511129829369</v>
+        <v>5.51851016215336</v>
       </c>
       <c r="D110" t="n">
-        <v>5.225728442812817</v>
+        <v>5.225727526476521</v>
       </c>
       <c r="E110" t="n">
-        <v>5.261217227720296</v>
+        <v>5.261216305161009</v>
       </c>
       <c r="F110" t="n">
         <v>9077500</v>
@@ -2632,16 +2632,16 @@
         <v>44574</v>
       </c>
       <c r="B111" t="n">
-        <v>5.420916080474854</v>
+        <v>5.420916557312012</v>
       </c>
       <c r="C111" t="n">
-        <v>5.509638024701201</v>
+        <v>5.50963850934256</v>
       </c>
       <c r="D111" t="n">
-        <v>5.358810507986609</v>
+        <v>5.358810979360809</v>
       </c>
       <c r="E111" t="n">
-        <v>5.358810507986609</v>
+        <v>5.358810979360809</v>
       </c>
       <c r="F111" t="n">
         <v>4388600</v>
@@ -2652,16 +2652,16 @@
         <v>44575</v>
       </c>
       <c r="B112" t="n">
-        <v>5.491894721984863</v>
+        <v>5.491894245147705</v>
       </c>
       <c r="C112" t="n">
-        <v>5.500766706632305</v>
+        <v>5.500766229024832</v>
       </c>
       <c r="D112" t="n">
-        <v>5.332195190793751</v>
+        <v>5.332194727822603</v>
       </c>
       <c r="E112" t="n">
-        <v>5.420917152566591</v>
+        <v>5.420916681892105</v>
       </c>
       <c r="F112" t="n">
         <v>4745900</v>
@@ -2732,16 +2732,16 @@
         <v>44581</v>
       </c>
       <c r="B116" t="n">
-        <v>5.713699340820312</v>
+        <v>5.713698863983154</v>
       </c>
       <c r="C116" t="n">
-        <v>5.837910076495201</v>
+        <v>5.837909589292028</v>
       </c>
       <c r="D116" t="n">
-        <v>5.633849370642346</v>
+        <v>5.633848900469072</v>
       </c>
       <c r="E116" t="n">
-        <v>5.651593761453044</v>
+        <v>5.651593289798911</v>
       </c>
       <c r="F116" t="n">
         <v>9343500</v>
@@ -2752,16 +2752,16 @@
         <v>44582</v>
       </c>
       <c r="B117" t="n">
-        <v>5.527382850646973</v>
+        <v>5.527382373809814</v>
       </c>
       <c r="C117" t="n">
-        <v>5.687082362883293</v>
+        <v>5.687081872269151</v>
       </c>
       <c r="D117" t="n">
-        <v>5.483021663495955</v>
+        <v>5.483021190485755</v>
       </c>
       <c r="E117" t="n">
-        <v>5.678210379288871</v>
+        <v>5.678209889440098</v>
       </c>
       <c r="F117" t="n">
         <v>7609900</v>
@@ -2812,16 +2812,16 @@
         <v>44587</v>
       </c>
       <c r="B120" t="n">
-        <v>5.518510818481445</v>
+        <v>5.518509864807129</v>
       </c>
       <c r="C120" t="n">
-        <v>5.678210764614708</v>
+        <v>5.678209783342052</v>
       </c>
       <c r="D120" t="n">
-        <v>5.491894442832344</v>
+        <v>5.491893493757702</v>
       </c>
       <c r="E120" t="n">
-        <v>5.598360791548077</v>
+        <v>5.59835982407459</v>
       </c>
       <c r="F120" t="n">
         <v>11610000</v>
@@ -2832,16 +2832,16 @@
         <v>44588</v>
       </c>
       <c r="B121" t="n">
-        <v>5.545126914978027</v>
+        <v>5.545127391815186</v>
       </c>
       <c r="C121" t="n">
-        <v>5.749187602371603</v>
+        <v>5.74918809675637</v>
       </c>
       <c r="D121" t="n">
-        <v>5.527382525772483</v>
+        <v>5.527383001083763</v>
       </c>
       <c r="E121" t="n">
-        <v>5.580615693389118</v>
+        <v>5.580616173278031</v>
       </c>
       <c r="F121" t="n">
         <v>8501200</v>
@@ -2852,16 +2852,16 @@
         <v>44589</v>
       </c>
       <c r="B122" t="n">
-        <v>5.660465717315674</v>
+        <v>5.660466194152832</v>
       </c>
       <c r="C122" t="n">
-        <v>5.731443274902391</v>
+        <v>5.731443757718693</v>
       </c>
       <c r="D122" t="n">
-        <v>5.509638195914094</v>
+        <v>5.509638660045554</v>
       </c>
       <c r="E122" t="n">
-        <v>5.509638195914094</v>
+        <v>5.509638660045554</v>
       </c>
       <c r="F122" t="n">
         <v>15566700</v>
@@ -2872,16 +2872,16 @@
         <v>44592</v>
       </c>
       <c r="B123" t="n">
-        <v>5.695953845977783</v>
+        <v>5.6959547996521</v>
       </c>
       <c r="C123" t="n">
-        <v>5.793548188049992</v>
+        <v>5.793549158064543</v>
       </c>
       <c r="D123" t="n">
-        <v>5.571743134378331</v>
+        <v>5.571744067256032</v>
       </c>
       <c r="E123" t="n">
-        <v>5.607231909121031</v>
+        <v>5.607232847940623</v>
       </c>
       <c r="F123" t="n">
         <v>7514700</v>
@@ -2892,16 +2892,16 @@
         <v>44593</v>
       </c>
       <c r="B124" t="n">
-        <v>5.678210258483887</v>
+        <v>5.678209781646729</v>
       </c>
       <c r="C124" t="n">
-        <v>5.793549004174971</v>
+        <v>5.79354851765205</v>
       </c>
       <c r="D124" t="n">
-        <v>5.536254716456543</v>
+        <v>5.536254251540337</v>
       </c>
       <c r="E124" t="n">
-        <v>5.766932207838711</v>
+        <v>5.76693172355098</v>
       </c>
       <c r="F124" t="n">
         <v>8050400</v>
@@ -2912,16 +2912,16 @@
         <v>44594</v>
       </c>
       <c r="B125" t="n">
-        <v>5.669337749481201</v>
+        <v>5.669337272644043</v>
       </c>
       <c r="C125" t="n">
-        <v>5.882270847141231</v>
+        <v>5.882270352394677</v>
       </c>
       <c r="D125" t="n">
-        <v>5.651593359931167</v>
+        <v>5.651592884586456</v>
       </c>
       <c r="E125" t="n">
-        <v>5.722570918131304</v>
+        <v>5.722570436816806</v>
       </c>
       <c r="F125" t="n">
         <v>8808600</v>
@@ -2932,16 +2932,16 @@
         <v>44595</v>
       </c>
       <c r="B126" t="n">
-        <v>5.731443405151367</v>
+        <v>5.731443881988525</v>
       </c>
       <c r="C126" t="n">
-        <v>5.793548980980922</v>
+        <v>5.793549462985059</v>
       </c>
       <c r="D126" t="n">
-        <v>5.616104659922033</v>
+        <v>5.616105127163388</v>
       </c>
       <c r="E126" t="n">
-        <v>5.678210235751588</v>
+        <v>5.678210708159922</v>
       </c>
       <c r="F126" t="n">
         <v>8390300</v>
@@ -2952,16 +2952,16 @@
         <v>44596</v>
       </c>
       <c r="B127" t="n">
-        <v>5.660465717315674</v>
+        <v>5.660466194152832</v>
       </c>
       <c r="C127" t="n">
-        <v>5.820165221885787</v>
+        <v>5.820165712176019</v>
       </c>
       <c r="D127" t="n">
-        <v>5.633848921690848</v>
+        <v>5.63384939628581</v>
       </c>
       <c r="E127" t="n">
-        <v>5.722570868674245</v>
+        <v>5.722571350743135</v>
       </c>
       <c r="F127" t="n">
         <v>8483700</v>
@@ -2972,16 +2972,16 @@
         <v>44599</v>
       </c>
       <c r="B128" t="n">
-        <v>5.56287145614624</v>
+        <v>5.562871932983398</v>
       </c>
       <c r="C128" t="n">
-        <v>5.775804555489152</v>
+        <v>5.775805050578469</v>
       </c>
       <c r="D128" t="n">
-        <v>5.553999472830914</v>
+        <v>5.553999948907585</v>
       </c>
       <c r="E128" t="n">
-        <v>5.704826573668434</v>
+        <v>5.704827062673674</v>
       </c>
       <c r="F128" t="n">
         <v>7178800</v>
@@ -2992,16 +2992,16 @@
         <v>44600</v>
       </c>
       <c r="B129" t="n">
-        <v>5.616104125976562</v>
+        <v>5.616104602813721</v>
       </c>
       <c r="C129" t="n">
-        <v>5.695954084014389</v>
+        <v>5.695954567631234</v>
       </c>
       <c r="D129" t="n">
-        <v>5.483021003600046</v>
+        <v>5.483021469137738</v>
       </c>
       <c r="E129" t="n">
-        <v>5.58061534975077</v>
+        <v>5.580615823574741</v>
       </c>
       <c r="F129" t="n">
         <v>9770800</v>
@@ -3012,16 +3012,16 @@
         <v>44601</v>
       </c>
       <c r="B130" t="n">
-        <v>5.633849143981934</v>
+        <v>5.633848667144775</v>
       </c>
       <c r="C130" t="n">
-        <v>5.740315484562782</v>
+        <v>5.740314998714537</v>
       </c>
       <c r="D130" t="n">
-        <v>5.58948838026973</v>
+        <v>5.589487907187173</v>
       </c>
       <c r="E130" t="n">
-        <v>5.616104753885126</v>
+        <v>5.616104278549815</v>
       </c>
       <c r="F130" t="n">
         <v>8867400</v>
@@ -3032,16 +3032,16 @@
         <v>44602</v>
       </c>
       <c r="B131" t="n">
-        <v>5.704827308654785</v>
+        <v>5.704826831817627</v>
       </c>
       <c r="C131" t="n">
-        <v>5.740316092607562</v>
+        <v>5.740315612804078</v>
       </c>
       <c r="D131" t="n">
-        <v>5.562872172843679</v>
+        <v>5.56287170787182</v>
       </c>
       <c r="E131" t="n">
-        <v>5.678210932220041</v>
+        <v>5.678210457607609</v>
       </c>
       <c r="F131" t="n">
         <v>9667400</v>
@@ -3052,16 +3052,16 @@
         <v>44603</v>
       </c>
       <c r="B132" t="n">
-        <v>5.633849143981934</v>
+        <v>5.633848667144775</v>
       </c>
       <c r="C132" t="n">
-        <v>5.775804687816029</v>
+        <v>5.775804198964051</v>
       </c>
       <c r="D132" t="n">
-        <v>5.58948838026973</v>
+        <v>5.589487907187173</v>
       </c>
       <c r="E132" t="n">
-        <v>5.731443501044193</v>
+        <v>5.731443015946853</v>
       </c>
       <c r="F132" t="n">
         <v>8001300</v>
@@ -3072,16 +3072,16 @@
         <v>44606</v>
       </c>
       <c r="B133" t="n">
-        <v>5.695953845977783</v>
+        <v>5.6959547996521</v>
       </c>
       <c r="C133" t="n">
-        <v>5.766931395463184</v>
+        <v>5.766932361021281</v>
       </c>
       <c r="D133" t="n">
-        <v>5.642720683863732</v>
+        <v>5.642721628625214</v>
       </c>
       <c r="E133" t="n">
-        <v>5.642720683863732</v>
+        <v>5.642721628625214</v>
       </c>
       <c r="F133" t="n">
         <v>12680200</v>
@@ -3092,16 +3092,16 @@
         <v>44607</v>
       </c>
       <c r="B134" t="n">
-        <v>5.695953845977783</v>
+        <v>5.6959547996521</v>
       </c>
       <c r="C134" t="n">
-        <v>5.811292575421342</v>
+        <v>5.811293548406838</v>
       </c>
       <c r="D134" t="n">
-        <v>5.518509549204714</v>
+        <v>5.518510473169509</v>
       </c>
       <c r="E134" t="n">
-        <v>5.811292575421342</v>
+        <v>5.811293548406838</v>
       </c>
       <c r="F134" t="n">
         <v>17426200</v>
@@ -3112,16 +3112,16 @@
         <v>44608</v>
       </c>
       <c r="B135" t="n">
-        <v>5.704827308654785</v>
+        <v>5.704826831817627</v>
       </c>
       <c r="C135" t="n">
-        <v>5.811294083572791</v>
+        <v>5.811293597836623</v>
       </c>
       <c r="D135" t="n">
-        <v>5.65159413272562</v>
+        <v>5.651593660337949</v>
       </c>
       <c r="E135" t="n">
-        <v>5.713699716172817</v>
+        <v>5.71369923859406</v>
       </c>
       <c r="F135" t="n">
         <v>12029900</v>
@@ -3132,16 +3132,16 @@
         <v>44609</v>
       </c>
       <c r="B136" t="n">
-        <v>5.580615997314453</v>
+        <v>5.580616474151611</v>
       </c>
       <c r="C136" t="n">
-        <v>5.740315508861739</v>
+        <v>5.740315999344462</v>
       </c>
       <c r="D136" t="n">
-        <v>5.509638436626771</v>
+        <v>5.509638907399233</v>
       </c>
       <c r="E136" t="n">
-        <v>5.731443525305595</v>
+        <v>5.73144401503025</v>
       </c>
       <c r="F136" t="n">
         <v>16171600</v>
@@ -3152,16 +3152,16 @@
         <v>44610</v>
       </c>
       <c r="B137" t="n">
-        <v>5.420916080474854</v>
+        <v>5.420916557312012</v>
       </c>
       <c r="C137" t="n">
-        <v>5.616104357772818</v>
+        <v>5.616104851779219</v>
       </c>
       <c r="D137" t="n">
-        <v>5.305577341450801</v>
+        <v>5.305577808142479</v>
       </c>
       <c r="E137" t="n">
-        <v>5.598359968927548</v>
+        <v>5.598360461373109</v>
       </c>
       <c r="F137" t="n">
         <v>12852100</v>
@@ -3172,16 +3172,16 @@
         <v>44613</v>
       </c>
       <c r="B138" t="n">
-        <v>5.119260787963867</v>
+        <v>5.119261741638184</v>
       </c>
       <c r="C138" t="n">
-        <v>5.456404582021004</v>
+        <v>5.456405598502314</v>
       </c>
       <c r="D138" t="n">
-        <v>5.074899606565978</v>
+        <v>5.074900551976187</v>
       </c>
       <c r="E138" t="n">
-        <v>5.447532176517594</v>
+        <v>5.447533191346051</v>
       </c>
       <c r="F138" t="n">
         <v>8726900</v>
@@ -3192,16 +3192,16 @@
         <v>44614</v>
       </c>
       <c r="B139" t="n">
-        <v>5.012794971466064</v>
+        <v>5.012794494628906</v>
       </c>
       <c r="C139" t="n">
-        <v>5.234600054955186</v>
+        <v>5.234599557019038</v>
       </c>
       <c r="D139" t="n">
-        <v>4.977306191952575</v>
+        <v>4.977305718491252</v>
       </c>
       <c r="E139" t="n">
-        <v>5.172494479276767</v>
+        <v>5.172493987248352</v>
       </c>
       <c r="F139" t="n">
         <v>7346000</v>
@@ -3212,16 +3212,16 @@
         <v>44615</v>
       </c>
       <c r="B140" t="n">
-        <v>5.02166748046875</v>
+        <v>5.021667003631592</v>
       </c>
       <c r="C140" t="n">
-        <v>5.101517454262385</v>
+        <v>5.101516969842998</v>
       </c>
       <c r="D140" t="n">
-        <v>4.968434305626215</v>
+        <v>4.968433833843864</v>
       </c>
       <c r="E140" t="n">
-        <v>5.057156263697106</v>
+        <v>5.057155783490078</v>
       </c>
       <c r="F140" t="n">
         <v>10772600</v>
@@ -3232,16 +3232,16 @@
         <v>44616</v>
       </c>
       <c r="B141" t="n">
-        <v>5.119260787963867</v>
+        <v>5.119261741638184</v>
       </c>
       <c r="C141" t="n">
-        <v>5.137005175911107</v>
+        <v>5.137006132891051</v>
       </c>
       <c r="D141" t="n">
-        <v>4.7732450114629</v>
+        <v>4.773245900677449</v>
       </c>
       <c r="E141" t="n">
-        <v>4.924072520544229</v>
+        <v>4.924073437856647</v>
       </c>
       <c r="F141" t="n">
         <v>11357100</v>
@@ -3252,16 +3252,16 @@
         <v>44617</v>
       </c>
       <c r="B142" t="n">
-        <v>5.066027641296387</v>
+        <v>5.066028594970703</v>
       </c>
       <c r="C142" t="n">
-        <v>5.163621986866849</v>
+        <v>5.163622958913197</v>
       </c>
       <c r="D142" t="n">
-        <v>4.986177683733319</v>
+        <v>4.986178622375967</v>
       </c>
       <c r="E142" t="n">
-        <v>5.110388822844664</v>
+        <v>5.110389784869926</v>
       </c>
       <c r="F142" t="n">
         <v>6795000</v>
@@ -3272,16 +3272,16 @@
         <v>44622</v>
       </c>
       <c r="B143" t="n">
-        <v>5.314450263977051</v>
+        <v>5.314449787139893</v>
       </c>
       <c r="C143" t="n">
-        <v>5.349939471001941</v>
+        <v>5.349938990980526</v>
       </c>
       <c r="D143" t="n">
-        <v>5.030539992255339</v>
+        <v>5.03053954089193</v>
       </c>
       <c r="E143" t="n">
-        <v>5.101517560185767</v>
+        <v>5.10151710245392</v>
       </c>
       <c r="F143" t="n">
         <v>7030100</v>
@@ -3312,16 +3312,16 @@
         <v>44624</v>
       </c>
       <c r="B145" t="n">
-        <v>5.509639263153076</v>
+        <v>5.509638786315918</v>
       </c>
       <c r="C145" t="n">
-        <v>5.536255640873986</v>
+        <v>5.536255161733287</v>
       </c>
       <c r="D145" t="n">
-        <v>5.376556105369439</v>
+        <v>5.376555640050094</v>
       </c>
       <c r="E145" t="n">
-        <v>5.48302246237247</v>
+        <v>5.483021987838889</v>
       </c>
       <c r="F145" t="n">
         <v>9336900</v>
@@ -3372,16 +3372,16 @@
         <v>44629</v>
       </c>
       <c r="B148" t="n">
-        <v>5.695953845977783</v>
+        <v>5.6959547996521</v>
       </c>
       <c r="C148" t="n">
-        <v>5.704825828133675</v>
+        <v>5.704826783293429</v>
       </c>
       <c r="D148" t="n">
-        <v>5.553998747006981</v>
+        <v>5.553999676913737</v>
       </c>
       <c r="E148" t="n">
-        <v>5.589487521749682</v>
+        <v>5.589488457598327</v>
       </c>
       <c r="F148" t="n">
         <v>9079900</v>
@@ -3392,16 +3392,16 @@
         <v>44630</v>
       </c>
       <c r="B149" t="n">
-        <v>5.695953845977783</v>
+        <v>5.6959547996521</v>
       </c>
       <c r="C149" t="n">
-        <v>5.829036962792693</v>
+        <v>5.829037938749134</v>
       </c>
       <c r="D149" t="n">
-        <v>5.553998747006981</v>
+        <v>5.553999676913737</v>
       </c>
       <c r="E149" t="n">
-        <v>5.624976296492382</v>
+        <v>5.624977238282918</v>
       </c>
       <c r="F149" t="n">
         <v>15215200</v>
@@ -3412,16 +3412,16 @@
         <v>44631</v>
       </c>
       <c r="B150" t="n">
-        <v>5.598360061645508</v>
+        <v>5.598360538482666</v>
       </c>
       <c r="C150" t="n">
-        <v>5.97986463966694</v>
+        <v>5.979865148998535</v>
       </c>
       <c r="D150" t="n">
-        <v>5.527382505088926</v>
+        <v>5.52738297588061</v>
       </c>
       <c r="E150" t="n">
-        <v>5.695954413440612</v>
+        <v>5.695954898590315</v>
       </c>
       <c r="F150" t="n">
         <v>16712700</v>
@@ -3472,16 +3472,16 @@
         <v>44636</v>
       </c>
       <c r="B153" t="n">
-        <v>5.624977111816406</v>
+        <v>5.624976634979248</v>
       </c>
       <c r="C153" t="n">
-        <v>5.766932231363189</v>
+        <v>5.766931742492297</v>
       </c>
       <c r="D153" t="n">
-        <v>5.518510349096693</v>
+        <v>5.51850988128487</v>
       </c>
       <c r="E153" t="n">
-        <v>5.713699061533146</v>
+        <v>5.713698577174903</v>
       </c>
       <c r="F153" t="n">
         <v>10739100</v>
@@ -3492,16 +3492,16 @@
         <v>44637</v>
       </c>
       <c r="B154" t="n">
-        <v>5.89114236831665</v>
+        <v>5.891143321990967</v>
       </c>
       <c r="C154" t="n">
-        <v>5.926631144633169</v>
+        <v>5.926632104052506</v>
       </c>
       <c r="D154" t="n">
-        <v>5.536254182091882</v>
+        <v>5.536255078315924</v>
       </c>
       <c r="E154" t="n">
-        <v>5.607232157784503</v>
+        <v>5.607233065498654</v>
       </c>
       <c r="F154" t="n">
         <v>10001800</v>
@@ -3512,16 +3512,16 @@
         <v>44638</v>
       </c>
       <c r="B155" t="n">
-        <v>6.201670169830322</v>
+        <v>6.201669692993164</v>
       </c>
       <c r="C155" t="n">
-        <v>6.201670169830322</v>
+        <v>6.201669692993164</v>
       </c>
       <c r="D155" t="n">
-        <v>5.891143125613262</v>
+        <v>5.891142672652063</v>
       </c>
       <c r="E155" t="n">
-        <v>5.891143125613262</v>
+        <v>5.891142672652063</v>
       </c>
       <c r="F155" t="n">
         <v>17710700</v>
@@ -3532,16 +3532,16 @@
         <v>44641</v>
       </c>
       <c r="B156" t="n">
-        <v>6.104075908660889</v>
+        <v>6.104076385498047</v>
       </c>
       <c r="C156" t="n">
-        <v>6.34362537835539</v>
+        <v>6.343625873905633</v>
       </c>
       <c r="D156" t="n">
-        <v>6.024225944409515</v>
+        <v>6.024226415008968</v>
       </c>
       <c r="E156" t="n">
-        <v>6.183925449852644</v>
+        <v>6.183925932927476</v>
       </c>
       <c r="F156" t="n">
         <v>14982100</v>
@@ -3552,16 +3552,16 @@
         <v>44642</v>
       </c>
       <c r="B157" t="n">
-        <v>6.299264430999756</v>
+        <v>6.299263954162598</v>
       </c>
       <c r="C157" t="n">
-        <v>6.308136837611495</v>
+        <v>6.308136360102719</v>
       </c>
       <c r="D157" t="n">
-        <v>6.07745934242188</v>
+        <v>6.077458882374763</v>
       </c>
       <c r="E157" t="n">
-        <v>6.07745934242188</v>
+        <v>6.077458882374763</v>
       </c>
       <c r="F157" t="n">
         <v>9703800</v>
@@ -3572,16 +3572,16 @@
         <v>44643</v>
       </c>
       <c r="B158" t="n">
-        <v>6.308136940002441</v>
+        <v>6.3081374168396</v>
       </c>
       <c r="C158" t="n">
-        <v>6.334753314150418</v>
+        <v>6.334753792999529</v>
       </c>
       <c r="D158" t="n">
-        <v>6.201670174231618</v>
+        <v>6.201670643020867</v>
       </c>
       <c r="E158" t="n">
-        <v>6.263775752342961</v>
+        <v>6.263776225826821</v>
       </c>
       <c r="F158" t="n">
         <v>8187500</v>
@@ -3592,16 +3592,16 @@
         <v>44644</v>
       </c>
       <c r="B159" t="n">
-        <v>6.343625545501709</v>
+        <v>6.343625068664551</v>
       </c>
       <c r="C159" t="n">
-        <v>6.432347495307822</v>
+        <v>6.432347011801619</v>
       </c>
       <c r="D159" t="n">
-        <v>6.254903595695596</v>
+        <v>6.254903125527482</v>
       </c>
       <c r="E159" t="n">
-        <v>6.299264359068839</v>
+        <v>6.299263885566218</v>
       </c>
       <c r="F159" t="n">
         <v>11578200</v>
@@ -3612,16 +3612,16 @@
         <v>44645</v>
       </c>
       <c r="B160" t="n">
-        <v>6.45009183883667</v>
+        <v>6.450092315673828</v>
       </c>
       <c r="C160" t="n">
-        <v>6.512197414783683</v>
+        <v>6.512197896212132</v>
       </c>
       <c r="D160" t="n">
-        <v>6.237159160834839</v>
+        <v>6.237159621930483</v>
       </c>
       <c r="E160" t="n">
-        <v>6.343625499835754</v>
+        <v>6.343625968802155</v>
       </c>
       <c r="F160" t="n">
         <v>15324200</v>
@@ -3652,16 +3652,16 @@
         <v>44649</v>
       </c>
       <c r="B162" t="n">
-        <v>6.512197017669678</v>
+        <v>6.512197971343994</v>
       </c>
       <c r="C162" t="n">
-        <v>6.645279721775622</v>
+        <v>6.645280694939145</v>
       </c>
       <c r="D162" t="n">
-        <v>6.387985873350052</v>
+        <v>6.387986808834351</v>
       </c>
       <c r="E162" t="n">
-        <v>6.476708240166813</v>
+        <v>6.476709188644</v>
       </c>
       <c r="F162" t="n">
         <v>18100700</v>
@@ -3692,16 +3692,16 @@
         <v>44651</v>
       </c>
       <c r="B164" t="n">
-        <v>6.237159252166748</v>
+        <v>6.23715877532959</v>
       </c>
       <c r="C164" t="n">
-        <v>6.529941900236349</v>
+        <v>6.52994140101566</v>
       </c>
       <c r="D164" t="n">
-        <v>6.183925658827156</v>
+        <v>6.18392518605976</v>
       </c>
       <c r="E164" t="n">
-        <v>6.503325103566553</v>
+        <v>6.503324606380745</v>
       </c>
       <c r="F164" t="n">
         <v>12972000</v>
@@ -3712,16 +3712,16 @@
         <v>44652</v>
       </c>
       <c r="B165" t="n">
-        <v>6.139564514160156</v>
+        <v>6.139564037322998</v>
       </c>
       <c r="C165" t="n">
-        <v>6.299264015090594</v>
+        <v>6.299263525850169</v>
       </c>
       <c r="D165" t="n">
-        <v>5.926631423193302</v>
+        <v>5.926630962893866</v>
       </c>
       <c r="E165" t="n">
-        <v>6.254903254139719</v>
+        <v>6.254902768344629</v>
       </c>
       <c r="F165" t="n">
         <v>18919700</v>
@@ -3732,16 +3732,16 @@
         <v>44655</v>
       </c>
       <c r="B166" t="n">
-        <v>6.21054220199585</v>
+        <v>6.210542678833008</v>
       </c>
       <c r="C166" t="n">
-        <v>6.237158997579204</v>
+        <v>6.237159476459965</v>
       </c>
       <c r="D166" t="n">
-        <v>6.050842697674559</v>
+        <v>6.050843162250203</v>
       </c>
       <c r="E166" t="n">
-        <v>6.157309033888753</v>
+        <v>6.15730950663874</v>
       </c>
       <c r="F166" t="n">
         <v>13343800</v>
@@ -3752,16 +3752,16 @@
         <v>44656</v>
       </c>
       <c r="B167" t="n">
-        <v>6.299264430999756</v>
+        <v>6.299263954162598</v>
       </c>
       <c r="C167" t="n">
-        <v>6.32588122777534</v>
+        <v>6.325880748923362</v>
       </c>
       <c r="D167" t="n">
-        <v>6.148436903077259</v>
+        <v>6.148436437657334</v>
       </c>
       <c r="E167" t="n">
-        <v>6.228286870344377</v>
+        <v>6.228286398880027</v>
       </c>
       <c r="F167" t="n">
         <v>6962400</v>
@@ -3772,16 +3772,16 @@
         <v>44657</v>
       </c>
       <c r="B168" t="n">
-        <v>6.350711345672607</v>
+        <v>6.350711822509766</v>
       </c>
       <c r="C168" t="n">
-        <v>6.39524623280219</v>
+        <v>6.395246712983208</v>
       </c>
       <c r="D168" t="n">
-        <v>6.136942443401892</v>
+        <v>6.136942904188415</v>
       </c>
       <c r="E168" t="n">
-        <v>6.243827106897355</v>
+        <v>6.243827575709211</v>
       </c>
       <c r="F168" t="n">
         <v>10002000</v>
@@ -3792,16 +3792,16 @@
         <v>44658</v>
       </c>
       <c r="B169" t="n">
-        <v>6.261641979217529</v>
+        <v>6.261641502380371</v>
       </c>
       <c r="C169" t="n">
-        <v>6.39524708309012</v>
+        <v>6.395246596078652</v>
       </c>
       <c r="D169" t="n">
-        <v>6.208199428004173</v>
+        <v>6.208198955236777</v>
       </c>
       <c r="E169" t="n">
-        <v>6.323990914432667</v>
+        <v>6.323990432847507</v>
       </c>
       <c r="F169" t="n">
         <v>10216600</v>
@@ -3852,16 +3852,16 @@
         <v>44663</v>
       </c>
       <c r="B172" t="n">
-        <v>6.217105865478516</v>
+        <v>6.217106342315674</v>
       </c>
       <c r="C172" t="n">
-        <v>6.359618184547754</v>
+        <v>6.359618672315267</v>
       </c>
       <c r="D172" t="n">
-        <v>6.145849705943896</v>
+        <v>6.145850177315878</v>
       </c>
       <c r="E172" t="n">
-        <v>6.190384593292927</v>
+        <v>6.190385068080627</v>
       </c>
       <c r="F172" t="n">
         <v>15598900</v>
@@ -3872,16 +3872,16 @@
         <v>44664</v>
       </c>
       <c r="B173" t="n">
-        <v>6.306176662445068</v>
+        <v>6.30617618560791</v>
       </c>
       <c r="C173" t="n">
-        <v>6.323990704016711</v>
+        <v>6.323990225832556</v>
       </c>
       <c r="D173" t="n">
-        <v>6.172571138297622</v>
+        <v>6.172570671562951</v>
       </c>
       <c r="E173" t="n">
-        <v>6.261641770876088</v>
+        <v>6.261641297406404</v>
       </c>
       <c r="F173" t="n">
         <v>5828500</v>
@@ -3892,16 +3892,16 @@
         <v>44665</v>
       </c>
       <c r="B174" t="n">
-        <v>6.323990345001221</v>
+        <v>6.323990821838379</v>
       </c>
       <c r="C174" t="n">
-        <v>6.350711618201833</v>
+        <v>6.350712097053812</v>
       </c>
       <c r="D174" t="n">
-        <v>6.226012909559278</v>
+        <v>6.226013379008809</v>
       </c>
       <c r="E174" t="n">
-        <v>6.297269496520836</v>
+        <v>6.297269971343208</v>
       </c>
       <c r="F174" t="n">
         <v>4947000</v>
@@ -3912,16 +3912,16 @@
         <v>44669</v>
       </c>
       <c r="B175" t="n">
-        <v>6.350711345672607</v>
+        <v>6.350711822509766</v>
       </c>
       <c r="C175" t="n">
-        <v>6.39524623280219</v>
+        <v>6.395246712983208</v>
       </c>
       <c r="D175" t="n">
-        <v>6.190384562789519</v>
+        <v>6.190385027588691</v>
       </c>
       <c r="E175" t="n">
-        <v>6.315083266080856</v>
+        <v>6.315083740242914</v>
       </c>
       <c r="F175" t="n">
         <v>6987700</v>
@@ -3992,16 +3992,16 @@
         <v>44676</v>
       </c>
       <c r="B179" t="n">
-        <v>6.279455184936523</v>
+        <v>6.279455661773682</v>
       </c>
       <c r="C179" t="n">
-        <v>6.306176032263624</v>
+        <v>6.306176511129858</v>
       </c>
       <c r="D179" t="n">
-        <v>6.038965435391561</v>
+        <v>6.038965893966873</v>
       </c>
       <c r="E179" t="n">
-        <v>6.047872242927192</v>
+        <v>6.047872702178851</v>
       </c>
       <c r="F179" t="n">
         <v>9340700</v>
@@ -4032,16 +4032,16 @@
         <v>44678</v>
       </c>
       <c r="B181" t="n">
-        <v>6.332897186279297</v>
+        <v>6.332897663116455</v>
       </c>
       <c r="C181" t="n">
-        <v>6.359618033108378</v>
+        <v>6.35961851195749</v>
       </c>
       <c r="D181" t="n">
-        <v>6.208198485342908</v>
+        <v>6.208198952790844</v>
       </c>
       <c r="E181" t="n">
-        <v>6.288361875270557</v>
+        <v>6.288362348754418</v>
       </c>
       <c r="F181" t="n">
         <v>11357200</v>
@@ -4052,16 +4052,16 @@
         <v>44679</v>
       </c>
       <c r="B182" t="n">
-        <v>6.404153347015381</v>
+        <v>6.404153823852539</v>
       </c>
       <c r="C182" t="n">
-        <v>6.404153347015381</v>
+        <v>6.404153823852539</v>
       </c>
       <c r="D182" t="n">
-        <v>6.217105720246349</v>
+        <v>6.217106183156411</v>
       </c>
       <c r="E182" t="n">
-        <v>6.332897189145312</v>
+        <v>6.332897660676916</v>
       </c>
       <c r="F182" t="n">
         <v>9691200</v>
@@ -4092,16 +4092,16 @@
         <v>44683</v>
       </c>
       <c r="B184" t="n">
-        <v>5.86973237991333</v>
+        <v>5.869732856750488</v>
       </c>
       <c r="C184" t="n">
-        <v>6.19038512538046</v>
+        <v>6.19038562826636</v>
       </c>
       <c r="D184" t="n">
-        <v>5.745033665289197</v>
+        <v>5.745034131996254</v>
       </c>
       <c r="E184" t="n">
-        <v>6.145850234203484</v>
+        <v>6.145850733471519</v>
       </c>
       <c r="F184" t="n">
         <v>12404500</v>
@@ -4132,16 +4132,16 @@
         <v>44685</v>
       </c>
       <c r="B186" t="n">
-        <v>5.388752460479736</v>
+        <v>5.388751983642578</v>
       </c>
       <c r="C186" t="n">
-        <v>5.51345074167094</v>
+        <v>5.513450253799544</v>
       </c>
       <c r="D186" t="n">
-        <v>5.210611634057798</v>
+        <v>5.210611172983874</v>
       </c>
       <c r="E186" t="n">
-        <v>5.51345074167094</v>
+        <v>5.513450253799544</v>
       </c>
       <c r="F186" t="n">
         <v>18834300</v>
@@ -4152,16 +4152,16 @@
         <v>44686</v>
       </c>
       <c r="B187" t="n">
-        <v>4.943401336669922</v>
+        <v>4.943400859832764</v>
       </c>
       <c r="C187" t="n">
-        <v>5.379845560141698</v>
+        <v>5.379845041205424</v>
       </c>
       <c r="D187" t="n">
-        <v>4.925587295400058</v>
+        <v>4.925586820281231</v>
       </c>
       <c r="E187" t="n">
-        <v>5.379845560141698</v>
+        <v>5.379845041205424</v>
       </c>
       <c r="F187" t="n">
         <v>16863600</v>
@@ -4172,16 +4172,16 @@
         <v>44687</v>
       </c>
       <c r="B188" t="n">
-        <v>4.952308177947998</v>
+        <v>4.95230770111084</v>
       </c>
       <c r="C188" t="n">
-        <v>5.068099659333893</v>
+        <v>5.068099171347654</v>
       </c>
       <c r="D188" t="n">
-        <v>4.863237971005097</v>
+        <v>4.863237502744139</v>
       </c>
       <c r="E188" t="n">
-        <v>4.970122219336578</v>
+        <v>4.97012174078418</v>
       </c>
       <c r="F188" t="n">
         <v>14479200</v>
@@ -4212,16 +4212,16 @@
         <v>44691</v>
       </c>
       <c r="B190" t="n">
-        <v>4.631654739379883</v>
+        <v>4.631655216217041</v>
       </c>
       <c r="C190" t="n">
-        <v>4.711818133335377</v>
+        <v>4.7118186184255</v>
       </c>
       <c r="D190" t="n">
-        <v>4.569305810499142</v>
+        <v>4.569306280917366</v>
       </c>
       <c r="E190" t="n">
-        <v>4.658376012271789</v>
+        <v>4.65837649185995</v>
       </c>
       <c r="F190" t="n">
         <v>9825600</v>
@@ -4232,16 +4232,16 @@
         <v>44692</v>
       </c>
       <c r="B191" t="n">
-        <v>4.640562057495117</v>
+        <v>4.640562534332275</v>
       </c>
       <c r="C191" t="n">
-        <v>4.694004179544246</v>
+        <v>4.694004661872806</v>
       </c>
       <c r="D191" t="n">
-        <v>4.489142499329136</v>
+        <v>4.489142960607302</v>
       </c>
       <c r="E191" t="n">
-        <v>4.640562057495117</v>
+        <v>4.640562534332275</v>
       </c>
       <c r="F191" t="n">
         <v>17331100</v>
@@ -4252,16 +4252,16 @@
         <v>44693</v>
       </c>
       <c r="B192" t="n">
-        <v>4.79198169708252</v>
+        <v>4.791981220245361</v>
       </c>
       <c r="C192" t="n">
-        <v>4.809795738068244</v>
+        <v>4.809795259458459</v>
       </c>
       <c r="D192" t="n">
-        <v>4.55149193141512</v>
+        <v>4.551491478508448</v>
       </c>
       <c r="E192" t="n">
-        <v>4.587120013386569</v>
+        <v>4.587119556934643</v>
       </c>
       <c r="F192" t="n">
         <v>13350100</v>
@@ -4272,16 +4272,16 @@
         <v>44694</v>
       </c>
       <c r="B193" t="n">
-        <v>4.604934215545654</v>
+        <v>4.604933261871338</v>
       </c>
       <c r="C193" t="n">
-        <v>4.800888673247058</v>
+        <v>4.800887678990895</v>
       </c>
       <c r="D193" t="n">
-        <v>4.515864007499562</v>
+        <v>4.515863072271539</v>
       </c>
       <c r="E193" t="n">
-        <v>4.800888673247058</v>
+        <v>4.800887678990895</v>
       </c>
       <c r="F193" t="n">
         <v>51332400</v>
@@ -4292,16 +4292,16 @@
         <v>44697</v>
       </c>
       <c r="B194" t="n">
-        <v>4.881052494049072</v>
+        <v>4.881052017211914</v>
       </c>
       <c r="C194" t="n">
-        <v>4.881052494049072</v>
+        <v>4.881052017211914</v>
       </c>
       <c r="D194" t="n">
-        <v>4.542585249546331</v>
+        <v>4.542584805774532</v>
       </c>
       <c r="E194" t="n">
-        <v>4.604934612919033</v>
+        <v>4.604934163056234</v>
       </c>
       <c r="F194" t="n">
         <v>29391700</v>
@@ -4312,16 +4312,16 @@
         <v>44698</v>
       </c>
       <c r="B195" t="n">
-        <v>5.00575065612793</v>
+        <v>5.005750179290771</v>
       </c>
       <c r="C195" t="n">
-        <v>5.183891507332367</v>
+        <v>5.183891013525891</v>
       </c>
       <c r="D195" t="n">
-        <v>4.881052357589018</v>
+        <v>4.881051892630355</v>
       </c>
       <c r="E195" t="n">
-        <v>4.952308528182682</v>
+        <v>4.952308056436308</v>
       </c>
       <c r="F195" t="n">
         <v>40878000</v>
@@ -4332,16 +4332,16 @@
         <v>44699</v>
       </c>
       <c r="B196" t="n">
-        <v>4.952308177947998</v>
+        <v>4.95230770111084</v>
       </c>
       <c r="C196" t="n">
-        <v>5.112634550445218</v>
+        <v>5.112634058170901</v>
       </c>
       <c r="D196" t="n">
-        <v>4.898866053782258</v>
+        <v>4.89886558209082</v>
       </c>
       <c r="E196" t="n">
-        <v>4.987936260725158</v>
+        <v>4.98793578045752</v>
       </c>
       <c r="F196" t="n">
         <v>17779600</v>
@@ -4372,16 +4372,16 @@
         <v>44701</v>
       </c>
       <c r="B198" t="n">
-        <v>4.934494018554688</v>
+        <v>4.934494495391846</v>
       </c>
       <c r="C198" t="n">
-        <v>5.121541661021799</v>
+        <v>5.121542155934015</v>
       </c>
       <c r="D198" t="n">
-        <v>4.827609772779264</v>
+        <v>4.82761023928783</v>
       </c>
       <c r="E198" t="n">
-        <v>5.094820387217823</v>
+        <v>5.09482087954787</v>
       </c>
       <c r="F198" t="n">
         <v>10517400</v>
@@ -4472,16 +4472,16 @@
         <v>44708</v>
       </c>
       <c r="B203" t="n">
-        <v>5.406567096710205</v>
+        <v>5.406566143035889</v>
       </c>
       <c r="C203" t="n">
-        <v>5.584707518051453</v>
+        <v>5.58470653295462</v>
       </c>
       <c r="D203" t="n">
-        <v>5.38875305457608</v>
+        <v>5.388752104044015</v>
       </c>
       <c r="E203" t="n">
-        <v>5.522358158221883</v>
+        <v>5.522357184122968</v>
       </c>
       <c r="F203" t="n">
         <v>11400800</v>
@@ -4492,16 +4492,16 @@
         <v>44711</v>
       </c>
       <c r="B204" t="n">
-        <v>5.60252046585083</v>
+        <v>5.602521419525146</v>
       </c>
       <c r="C204" t="n">
-        <v>5.673776620468936</v>
+        <v>5.673777586272644</v>
       </c>
       <c r="D204" t="n">
-        <v>5.317495422658225</v>
+        <v>5.317496327814903</v>
       </c>
       <c r="E204" t="n">
-        <v>5.460008156614619</v>
+        <v>5.460009086030153</v>
       </c>
       <c r="F204" t="n">
         <v>7527500</v>
@@ -4512,16 +4512,16 @@
         <v>44712</v>
       </c>
       <c r="B205" t="n">
-        <v>5.460009098052979</v>
+        <v>5.46000862121582</v>
       </c>
       <c r="C205" t="n">
-        <v>5.691591640492284</v>
+        <v>5.691591143430404</v>
       </c>
       <c r="D205" t="n">
-        <v>5.460009098052979</v>
+        <v>5.46000862121582</v>
       </c>
       <c r="E205" t="n">
-        <v>5.629242706811061</v>
+        <v>5.62924221519428</v>
       </c>
       <c r="F205" t="n">
         <v>13931800</v>
@@ -4652,16 +4652,16 @@
         <v>44721</v>
       </c>
       <c r="B212" t="n">
-        <v>4.818702220916748</v>
+        <v>4.818702697753906</v>
       </c>
       <c r="C212" t="n">
-        <v>4.996843043468919</v>
+        <v>4.996843537934095</v>
       </c>
       <c r="D212" t="n">
-        <v>4.809795413385255</v>
+        <v>4.809795889341036</v>
       </c>
       <c r="E212" t="n">
-        <v>4.881051572518039</v>
+        <v>4.88105205552501</v>
       </c>
       <c r="F212" t="n">
         <v>8480000</v>
@@ -4672,16 +4672,16 @@
         <v>44722</v>
       </c>
       <c r="B213" t="n">
-        <v>4.738539218902588</v>
+        <v>4.73853874206543</v>
       </c>
       <c r="C213" t="n">
-        <v>4.78307410566824</v>
+        <v>4.783073624349554</v>
       </c>
       <c r="D213" t="n">
-        <v>4.676189867766428</v>
+        <v>4.676189397203458</v>
       </c>
       <c r="E213" t="n">
-        <v>4.774167298203192</v>
+        <v>4.774166817780795</v>
       </c>
       <c r="F213" t="n">
         <v>4786300</v>
@@ -4692,16 +4692,16 @@
         <v>44725</v>
       </c>
       <c r="B214" t="n">
-        <v>4.569306373596191</v>
+        <v>4.569304943084717</v>
       </c>
       <c r="C214" t="n">
-        <v>4.676190628895216</v>
+        <v>4.676189164921517</v>
       </c>
       <c r="D214" t="n">
-        <v>4.506957012311623</v>
+        <v>4.506955601319845</v>
       </c>
       <c r="E214" t="n">
-        <v>4.631655310160484</v>
+        <v>4.631653860129446</v>
       </c>
       <c r="F214" t="n">
         <v>7709600</v>
@@ -4732,16 +4732,16 @@
         <v>44727</v>
       </c>
       <c r="B216" t="n">
-        <v>4.560398101806641</v>
+        <v>4.560398578643799</v>
       </c>
       <c r="C216" t="n">
-        <v>4.649468294279392</v>
+        <v>4.649468780429767</v>
       </c>
       <c r="D216" t="n">
-        <v>4.480235140941255</v>
+        <v>4.48023560939654</v>
       </c>
       <c r="E216" t="n">
-        <v>4.54258406331209</v>
+        <v>4.542584538286605</v>
       </c>
       <c r="F216" t="n">
         <v>10830000</v>
@@ -4792,16 +4792,16 @@
         <v>44733</v>
       </c>
       <c r="B219" t="n">
-        <v>4.489142417907715</v>
+        <v>4.489143371582031</v>
       </c>
       <c r="C219" t="n">
-        <v>4.596026660067369</v>
+        <v>4.596027636448196</v>
       </c>
       <c r="D219" t="n">
-        <v>4.444607104647747</v>
+        <v>4.444608048860973</v>
       </c>
       <c r="E219" t="n">
-        <v>4.560398579347484</v>
+        <v>4.560399548159474</v>
       </c>
       <c r="F219" t="n">
         <v>7411800</v>
@@ -4852,16 +4852,16 @@
         <v>44736</v>
       </c>
       <c r="B222" t="n">
-        <v>4.257560729980469</v>
+        <v>4.257560253143311</v>
       </c>
       <c r="C222" t="n">
-        <v>4.337723714994785</v>
+        <v>4.337723229179554</v>
       </c>
       <c r="D222" t="n">
-        <v>4.230839451828825</v>
+        <v>4.23083897798439</v>
       </c>
       <c r="E222" t="n">
-        <v>4.319909671133791</v>
+        <v>4.319909187313693</v>
       </c>
       <c r="F222" t="n">
         <v>7941200</v>
@@ -4892,16 +4892,16 @@
         <v>44740</v>
       </c>
       <c r="B224" t="n">
-        <v>4.293188571929932</v>
+        <v>4.293188095092773</v>
       </c>
       <c r="C224" t="n">
-        <v>4.471329000341845</v>
+        <v>4.471328503718931</v>
       </c>
       <c r="D224" t="n">
-        <v>4.293188571929932</v>
+        <v>4.293188095092773</v>
       </c>
       <c r="E224" t="n">
-        <v>4.319909423831577</v>
+        <v>4.319908944026579</v>
       </c>
       <c r="F224" t="n">
         <v>8975600</v>
@@ -5032,16 +5032,16 @@
         <v>44749</v>
       </c>
       <c r="B231" t="n">
-        <v>4.052698612213135</v>
+        <v>4.052698135375977</v>
       </c>
       <c r="C231" t="n">
-        <v>4.141768822704797</v>
+        <v>4.141768335387711</v>
       </c>
       <c r="D231" t="n">
-        <v>3.927999892804543</v>
+        <v>3.927999430639332</v>
       </c>
       <c r="E231" t="n">
-        <v>3.927999892804543</v>
+        <v>3.927999430639332</v>
       </c>
       <c r="F231" t="n">
         <v>10027800</v>
@@ -5052,16 +5052,16 @@
         <v>44750</v>
       </c>
       <c r="B232" t="n">
-        <v>3.919092655181885</v>
+        <v>3.919092416763306</v>
       </c>
       <c r="C232" t="n">
-        <v>4.132861136965516</v>
+        <v>4.1328608855423</v>
       </c>
       <c r="D232" t="n">
-        <v>3.919092655181885</v>
+        <v>3.919092416763306</v>
       </c>
       <c r="E232" t="n">
-        <v>4.034884128508128</v>
+        <v>4.034883883045357</v>
       </c>
       <c r="F232" t="n">
         <v>7050900</v>
@@ -5072,16 +5072,16 @@
         <v>44753</v>
       </c>
       <c r="B233" t="n">
-        <v>3.705323696136475</v>
+        <v>3.705323934555054</v>
       </c>
       <c r="C233" t="n">
-        <v>3.901278559713046</v>
+        <v>3.901278810740315</v>
       </c>
       <c r="D233" t="n">
-        <v>3.678602848652532</v>
+        <v>3.678603085351762</v>
       </c>
       <c r="E233" t="n">
-        <v>3.892371327404923</v>
+        <v>3.892371577859058</v>
       </c>
       <c r="F233" t="n">
         <v>13261200</v>
@@ -5092,16 +5092,16 @@
         <v>44754</v>
       </c>
       <c r="B234" t="n">
-        <v>3.580625534057617</v>
+        <v>3.580625772476196</v>
       </c>
       <c r="C234" t="n">
-        <v>3.705323817411202</v>
+        <v>3.705324064132908</v>
       </c>
       <c r="D234" t="n">
-        <v>3.580625534057617</v>
+        <v>3.580625772476196</v>
       </c>
       <c r="E234" t="n">
-        <v>3.696417009531774</v>
+        <v>3.696417255660414</v>
       </c>
       <c r="F234" t="n">
         <v>14771600</v>
@@ -5152,16 +5152,16 @@
         <v>44757</v>
       </c>
       <c r="B237" t="n">
-        <v>3.936907291412354</v>
+        <v>3.936906814575195</v>
       </c>
       <c r="C237" t="n">
-        <v>3.95472133425819</v>
+        <v>3.9547208552634</v>
       </c>
       <c r="D237" t="n">
-        <v>3.776580481079544</v>
+        <v>3.776580023661126</v>
       </c>
       <c r="E237" t="n">
-        <v>3.830023034337336</v>
+        <v>3.830022570445971</v>
       </c>
       <c r="F237" t="n">
         <v>4881500</v>
@@ -5172,16 +5172,16 @@
         <v>44760</v>
       </c>
       <c r="B238" t="n">
-        <v>3.830022573471069</v>
+        <v>3.830022811889648</v>
       </c>
       <c r="C238" t="n">
-        <v>4.088326376014163</v>
+        <v>4.088326630512132</v>
       </c>
       <c r="D238" t="n">
-        <v>3.830022573471069</v>
+        <v>3.830022811889648</v>
       </c>
       <c r="E238" t="n">
-        <v>3.990348939791538</v>
+        <v>3.99034918819042</v>
       </c>
       <c r="F238" t="n">
         <v>5011900</v>
@@ -5192,16 +5192,16 @@
         <v>44761</v>
       </c>
       <c r="B239" t="n">
-        <v>3.856743335723877</v>
+        <v>3.856743574142456</v>
       </c>
       <c r="C239" t="n">
-        <v>3.93690672944754</v>
+        <v>3.93690697282171</v>
       </c>
       <c r="D239" t="n">
-        <v>3.830022487629471</v>
+        <v>3.830022724396204</v>
       </c>
       <c r="E239" t="n">
-        <v>3.838929295420866</v>
+        <v>3.838929532738205</v>
       </c>
       <c r="F239" t="n">
         <v>5270100</v>
@@ -5212,16 +5212,16 @@
         <v>44762</v>
       </c>
       <c r="B240" t="n">
-        <v>3.999255657196045</v>
+        <v>3.999256134033203</v>
       </c>
       <c r="C240" t="n">
-        <v>4.025976930004314</v>
+        <v>4.025977410027488</v>
       </c>
       <c r="D240" t="n">
-        <v>3.803301213909561</v>
+        <v>3.803301667382781</v>
       </c>
       <c r="E240" t="n">
-        <v>3.830022486717829</v>
+        <v>3.830022943377066</v>
       </c>
       <c r="F240" t="n">
         <v>11021800</v>
@@ -5232,16 +5232,16 @@
         <v>44763</v>
       </c>
       <c r="B241" t="n">
-        <v>3.963627815246582</v>
+        <v>3.963627576828003</v>
       </c>
       <c r="C241" t="n">
-        <v>4.025977172406417</v>
+        <v>4.025976930237424</v>
       </c>
       <c r="D241" t="n">
-        <v>3.936906965549687</v>
+        <v>3.93690672873841</v>
       </c>
       <c r="E241" t="n">
-        <v>4.025977172406417</v>
+        <v>4.025976930237424</v>
       </c>
       <c r="F241" t="n">
         <v>6658500</v>
@@ -5272,16 +5272,16 @@
         <v>44767</v>
       </c>
       <c r="B243" t="n">
-        <v>3.696417093276978</v>
+        <v>3.696417331695557</v>
       </c>
       <c r="C243" t="n">
-        <v>3.78548729769035</v>
+        <v>3.78548754185395</v>
       </c>
       <c r="D243" t="n">
-        <v>3.651881778710173</v>
+        <v>3.651882014256228</v>
       </c>
       <c r="E243" t="n">
-        <v>3.767673256807676</v>
+        <v>3.767673499822271</v>
       </c>
       <c r="F243" t="n">
         <v>10514300</v>
@@ -5292,16 +5292,16 @@
         <v>44768</v>
       </c>
       <c r="B244" t="n">
-        <v>3.714231491088867</v>
+        <v>3.71423077583313</v>
       </c>
       <c r="C244" t="n">
-        <v>3.812208937719106</v>
+        <v>3.812208203595688</v>
       </c>
       <c r="D244" t="n">
-        <v>3.66969617224232</v>
+        <v>3.669695465562822</v>
       </c>
       <c r="E244" t="n">
-        <v>3.705324257431447</v>
+        <v>3.70532354389099</v>
       </c>
       <c r="F244" t="n">
         <v>4594100</v>
@@ -5312,16 +5312,16 @@
         <v>44769</v>
       </c>
       <c r="B245" t="n">
-        <v>3.999255657196045</v>
+        <v>3.999256134033203</v>
       </c>
       <c r="C245" t="n">
-        <v>3.999255657196045</v>
+        <v>3.999256134033203</v>
       </c>
       <c r="D245" t="n">
-        <v>3.723137820204979</v>
+        <v>3.723138264120199</v>
       </c>
       <c r="E245" t="n">
-        <v>3.74095186050375</v>
+        <v>3.740952306542965</v>
       </c>
       <c r="F245" t="n">
         <v>8689000</v>
@@ -5332,16 +5332,16 @@
         <v>44770</v>
       </c>
       <c r="B246" t="n">
-        <v>3.999255657196045</v>
+        <v>3.999256134033203</v>
       </c>
       <c r="C246" t="n">
-        <v>4.070512243111353</v>
+        <v>4.070512728444538</v>
       </c>
       <c r="D246" t="n">
-        <v>3.892371415403418</v>
+        <v>3.892371879496609</v>
       </c>
       <c r="E246" t="n">
-        <v>4.025976930004314</v>
+        <v>4.025977410027488</v>
       </c>
       <c r="F246" t="n">
         <v>3634200</v>
@@ -5452,16 +5452,16 @@
         <v>44778</v>
       </c>
       <c r="B252" t="n">
-        <v>4.328816413879395</v>
+        <v>4.328815937042236</v>
       </c>
       <c r="C252" t="n">
-        <v>4.542584915937508</v>
+        <v>4.542584415552859</v>
       </c>
       <c r="D252" t="n">
-        <v>4.248653013247472</v>
+        <v>4.248652545240646</v>
       </c>
       <c r="E252" t="n">
-        <v>4.542584915937508</v>
+        <v>4.542584415552859</v>
       </c>
       <c r="F252" t="n">
         <v>11124100</v>
@@ -5472,16 +5472,16 @@
         <v>44781</v>
       </c>
       <c r="B253" t="n">
-        <v>4.408979415893555</v>
+        <v>4.408978939056396</v>
       </c>
       <c r="C253" t="n">
-        <v>4.50695685894371</v>
+        <v>4.506956371510157</v>
       </c>
       <c r="D253" t="n">
-        <v>4.355537290062633</v>
+        <v>4.355536819005313</v>
       </c>
       <c r="E253" t="n">
-        <v>4.391165373949914</v>
+        <v>4.391164899039369</v>
       </c>
       <c r="F253" t="n">
         <v>6283600</v>
@@ -5492,16 +5492,16 @@
         <v>44782</v>
       </c>
       <c r="B254" t="n">
-        <v>4.382258415222168</v>
+        <v>4.38225793838501</v>
       </c>
       <c r="C254" t="n">
-        <v>4.578212869889715</v>
+        <v>4.578212371730591</v>
       </c>
       <c r="D254" t="n">
-        <v>4.364444373888754</v>
+        <v>4.364443898989957</v>
       </c>
       <c r="E254" t="n">
-        <v>4.453514580555821</v>
+        <v>4.453514095965221</v>
       </c>
       <c r="F254" t="n">
         <v>9216300</v>
@@ -5512,16 +5512,16 @@
         <v>44783</v>
       </c>
       <c r="B255" t="n">
-        <v>4.587120056152344</v>
+        <v>4.587119102478027</v>
       </c>
       <c r="C255" t="n">
-        <v>4.702911535999198</v>
+        <v>4.702910558251529</v>
       </c>
       <c r="D255" t="n">
-        <v>4.426793261065856</v>
+        <v>4.426792340723901</v>
       </c>
       <c r="E255" t="n">
-        <v>4.426793261065856</v>
+        <v>4.426792340723901</v>
       </c>
       <c r="F255" t="n">
         <v>9044400</v>
@@ -5532,16 +5532,16 @@
         <v>44784</v>
       </c>
       <c r="B256" t="n">
-        <v>4.346630096435547</v>
+        <v>4.346630573272705</v>
       </c>
       <c r="C256" t="n">
-        <v>4.685097288104267</v>
+        <v>4.685097802072197</v>
       </c>
       <c r="D256" t="n">
-        <v>4.311002015704126</v>
+        <v>4.311002488632787</v>
       </c>
       <c r="E256" t="n">
-        <v>4.613840701921201</v>
+        <v>4.61384120807209</v>
       </c>
       <c r="F256" t="n">
         <v>11482900</v>
@@ -5572,16 +5572,16 @@
         <v>44788</v>
       </c>
       <c r="B258" t="n">
-        <v>4.640562057495117</v>
+        <v>4.640562534332275</v>
       </c>
       <c r="C258" t="n">
-        <v>4.729632260910332</v>
+        <v>4.729632746899826</v>
       </c>
       <c r="D258" t="n">
-        <v>4.560398662061308</v>
+        <v>4.560399130661343</v>
       </c>
       <c r="E258" t="n">
-        <v>4.640562057495117</v>
+        <v>4.640562534332275</v>
       </c>
       <c r="F258" t="n">
         <v>10250500</v>
@@ -5612,16 +5612,16 @@
         <v>44790</v>
       </c>
       <c r="B260" t="n">
-        <v>4.702911376953125</v>
+        <v>4.702911853790283</v>
       </c>
       <c r="C260" t="n">
-        <v>4.774167539150558</v>
+        <v>4.774168023212515</v>
       </c>
       <c r="D260" t="n">
-        <v>4.560398627838029</v>
+        <v>4.560399090225548</v>
       </c>
       <c r="E260" t="n">
-        <v>4.596026708936746</v>
+        <v>4.596027174936664</v>
       </c>
       <c r="F260" t="n">
         <v>27272900</v>
@@ -5632,16 +5632,16 @@
         <v>44791</v>
       </c>
       <c r="B261" t="n">
-        <v>4.533677577972412</v>
+        <v>4.53367805480957</v>
       </c>
       <c r="C261" t="n">
-        <v>4.711817975552381</v>
+        <v>4.711818471125755</v>
       </c>
       <c r="D261" t="n">
-        <v>4.515863538214415</v>
+        <v>4.515864013177952</v>
       </c>
       <c r="E261" t="n">
-        <v>4.640561816520393</v>
+        <v>4.640562304599281</v>
       </c>
       <c r="F261" t="n">
         <v>8785600</v>
@@ -5692,16 +5692,16 @@
         <v>44796</v>
       </c>
       <c r="B264" t="n">
-        <v>4.471328258514404</v>
+        <v>4.471328735351562</v>
       </c>
       <c r="C264" t="n">
-        <v>4.471328258514404</v>
+        <v>4.471328735351562</v>
       </c>
       <c r="D264" t="n">
-        <v>4.311001899543048</v>
+        <v>4.311002359282476</v>
       </c>
       <c r="E264" t="n">
-        <v>4.311001899543048</v>
+        <v>4.311002359282476</v>
       </c>
       <c r="F264" t="n">
         <v>6333000</v>
@@ -5712,16 +5712,16 @@
         <v>44797</v>
       </c>
       <c r="B265" t="n">
-        <v>4.533677577972412</v>
+        <v>4.53367805480957</v>
       </c>
       <c r="C265" t="n">
-        <v>4.6049337370044</v>
+        <v>4.604934221336045</v>
       </c>
       <c r="D265" t="n">
-        <v>4.426792914704221</v>
+        <v>4.426793380299605</v>
       </c>
       <c r="E265" t="n">
-        <v>4.453514186701321</v>
+        <v>4.45351465510716</v>
       </c>
       <c r="F265" t="n">
         <v>5861300</v>
@@ -5732,16 +5732,16 @@
         <v>44798</v>
       </c>
       <c r="B266" t="n">
-        <v>4.480236053466797</v>
+        <v>4.480235576629639</v>
       </c>
       <c r="C266" t="n">
-        <v>4.604934348326948</v>
+        <v>4.604933858217994</v>
       </c>
       <c r="D266" t="n">
-        <v>4.453514777922345</v>
+        <v>4.453514303929166</v>
       </c>
       <c r="E266" t="n">
-        <v>4.587120306204069</v>
+        <v>4.587119817991086</v>
       </c>
       <c r="F266" t="n">
         <v>4135100</v>
@@ -5812,16 +5812,16 @@
         <v>44804</v>
       </c>
       <c r="B270" t="n">
-        <v>4.311002254486084</v>
+        <v>4.311001777648926</v>
       </c>
       <c r="C270" t="n">
-        <v>4.435700543952965</v>
+        <v>4.43570005332301</v>
       </c>
       <c r="D270" t="n">
-        <v>4.284280980097343</v>
+        <v>4.284280506215807</v>
       </c>
       <c r="E270" t="n">
-        <v>4.382258419895731</v>
+        <v>4.382257935176974</v>
       </c>
       <c r="F270" t="n">
         <v>8375100</v>
@@ -5852,16 +5852,16 @@
         <v>44806</v>
       </c>
       <c r="B272" t="n">
-        <v>4.097233772277832</v>
+        <v>4.097232818603516</v>
       </c>
       <c r="C272" t="n">
-        <v>4.355537611907676</v>
+        <v>4.35553659811042</v>
       </c>
       <c r="D272" t="n">
-        <v>4.097233772277832</v>
+        <v>4.097232818603516</v>
       </c>
       <c r="E272" t="n">
-        <v>4.319909525387717</v>
+        <v>4.319908519883274</v>
       </c>
       <c r="F272" t="n">
         <v>69570300</v>
@@ -5872,16 +5872,16 @@
         <v>44809</v>
       </c>
       <c r="B273" t="n">
-        <v>4.115047454833984</v>
+        <v>4.115046977996826</v>
       </c>
       <c r="C273" t="n">
-        <v>4.221931705024937</v>
+        <v>4.221931215802409</v>
       </c>
       <c r="D273" t="n">
-        <v>4.115047454833984</v>
+        <v>4.115046977996826</v>
       </c>
       <c r="E273" t="n">
-        <v>4.123954688043359</v>
+        <v>4.123954210174062</v>
       </c>
       <c r="F273" t="n">
         <v>7604300</v>
@@ -5952,16 +5952,16 @@
         <v>44816</v>
       </c>
       <c r="B277" t="n">
-        <v>3.856743335723877</v>
+        <v>3.856743574142456</v>
       </c>
       <c r="C277" t="n">
-        <v>3.990348850356574</v>
+        <v>3.990349097034463</v>
       </c>
       <c r="D277" t="n">
-        <v>3.838929295420866</v>
+        <v>3.838929532738205</v>
       </c>
       <c r="E277" t="n">
-        <v>3.954720769750552</v>
+        <v>3.954721014225961</v>
       </c>
       <c r="F277" t="n">
         <v>15738600</v>
@@ -5972,16 +5972,16 @@
         <v>44817</v>
       </c>
       <c r="B278" t="n">
-        <v>3.696417093276978</v>
+        <v>3.696417331695557</v>
       </c>
       <c r="C278" t="n">
-        <v>3.883464734905179</v>
+        <v>3.883464985388314</v>
       </c>
       <c r="D278" t="n">
-        <v>3.678603052394303</v>
+        <v>3.678603289663878</v>
       </c>
       <c r="E278" t="n">
-        <v>3.874557502103723</v>
+        <v>3.874557752012343</v>
       </c>
       <c r="F278" t="n">
         <v>21443000</v>
@@ -6012,16 +6012,16 @@
         <v>44819</v>
       </c>
       <c r="B280" t="n">
-        <v>3.74985933303833</v>
+        <v>3.749859094619751</v>
       </c>
       <c r="C280" t="n">
-        <v>3.758766141397721</v>
+        <v>3.758765902412841</v>
       </c>
       <c r="D280" t="n">
-        <v>3.634067851324498</v>
+        <v>3.634067620268019</v>
       </c>
       <c r="E280" t="n">
-        <v>3.740952099958689</v>
+        <v>3.740951862106438</v>
       </c>
       <c r="F280" t="n">
         <v>12717200</v>
@@ -6072,16 +6072,16 @@
         <v>44824</v>
       </c>
       <c r="B283" t="n">
-        <v>3.963627815246582</v>
+        <v>3.963627576828003</v>
       </c>
       <c r="C283" t="n">
-        <v>4.132861420634493</v>
+        <v>4.13286117203624</v>
       </c>
       <c r="D283" t="n">
-        <v>3.919092924178341</v>
+        <v>3.919092688438607</v>
       </c>
       <c r="E283" t="n">
-        <v>3.990349089663725</v>
+        <v>3.990348849637818</v>
       </c>
       <c r="F283" t="n">
         <v>10696200</v>
@@ -6112,16 +6112,16 @@
         <v>44826</v>
       </c>
       <c r="B285" t="n">
-        <v>4.052698612213135</v>
+        <v>4.052698135375977</v>
       </c>
       <c r="C285" t="n">
-        <v>4.097233505098832</v>
+        <v>4.097233023021737</v>
       </c>
       <c r="D285" t="n">
-        <v>3.901279042017177</v>
+        <v>3.90127858299592</v>
       </c>
       <c r="E285" t="n">
-        <v>3.936907126213841</v>
+        <v>3.936906663000614</v>
       </c>
       <c r="F285" t="n">
         <v>13589200</v>
@@ -6172,16 +6172,16 @@
         <v>44831</v>
       </c>
       <c r="B288" t="n">
-        <v>3.732045412063599</v>
+        <v>3.73204493522644</v>
       </c>
       <c r="C288" t="n">
-        <v>3.91909306557115</v>
+        <v>3.919092564835227</v>
       </c>
       <c r="D288" t="n">
-        <v>3.732045412063599</v>
+        <v>3.73204493522644</v>
       </c>
       <c r="E288" t="n">
-        <v>3.838929664147838</v>
+        <v>3.838929173654259</v>
       </c>
       <c r="F288" t="n">
         <v>11052300</v>
@@ -6212,16 +6212,16 @@
         <v>44833</v>
       </c>
       <c r="B290" t="n">
-        <v>3.696417093276978</v>
+        <v>3.696417331695557</v>
       </c>
       <c r="C290" t="n">
-        <v>3.714231134159652</v>
+        <v>3.714231373727235</v>
       </c>
       <c r="D290" t="n">
-        <v>3.616253696944824</v>
+        <v>3.616253930192871</v>
       </c>
       <c r="E290" t="n">
-        <v>3.660789011511628</v>
+        <v>3.660789247632199</v>
       </c>
       <c r="F290" t="n">
         <v>12380300</v>
@@ -6232,16 +6232,16 @@
         <v>44834</v>
       </c>
       <c r="B291" t="n">
-        <v>3.732045412063599</v>
+        <v>3.73204493522644</v>
       </c>
       <c r="C291" t="n">
-        <v>3.79439477147287</v>
+        <v>3.794394286669439</v>
       </c>
       <c r="D291" t="n">
-        <v>3.651882010640287</v>
+        <v>3.651881544045472</v>
       </c>
       <c r="E291" t="n">
-        <v>3.660789244007439</v>
+        <v>3.660788776274561</v>
       </c>
       <c r="F291" t="n">
         <v>11827700</v>
@@ -6272,16 +6272,16 @@
         <v>44838</v>
       </c>
       <c r="B293" t="n">
-        <v>3.930920124053955</v>
+        <v>3.930920362472534</v>
       </c>
       <c r="C293" t="n">
-        <v>4.05656584965991</v>
+        <v>4.056566095699167</v>
       </c>
       <c r="D293" t="n">
-        <v>3.895021345309396</v>
+        <v>3.895021581550639</v>
       </c>
       <c r="E293" t="n">
-        <v>3.975793383511054</v>
+        <v>3.975793624651291</v>
       </c>
       <c r="F293" t="n">
         <v>11413300</v>
@@ -6292,16 +6292,16 @@
         <v>44839</v>
       </c>
       <c r="B294" t="n">
-        <v>3.975793600082397</v>
+        <v>3.975793123245239</v>
       </c>
       <c r="C294" t="n">
-        <v>3.975793600082397</v>
+        <v>3.975793123245239</v>
       </c>
       <c r="D294" t="n">
-        <v>3.868097257982235</v>
+        <v>3.868096794061647</v>
       </c>
       <c r="E294" t="n">
-        <v>3.921945429032316</v>
+        <v>3.921944958653443</v>
       </c>
       <c r="F294" t="n">
         <v>8368900</v>
@@ -6332,16 +6332,16 @@
         <v>44841</v>
       </c>
       <c r="B296" t="n">
-        <v>3.760401010513306</v>
+        <v>3.760400533676147</v>
       </c>
       <c r="C296" t="n">
-        <v>4.002718000310238</v>
+        <v>4.002717492746105</v>
       </c>
       <c r="D296" t="n">
-        <v>3.715527319535371</v>
+        <v>3.715526848388416</v>
       </c>
       <c r="E296" t="n">
-        <v>3.984768609508511</v>
+        <v>3.984768104220449</v>
       </c>
       <c r="F296" t="n">
         <v>16354500</v>
@@ -6352,16 +6352,16 @@
         <v>44844</v>
       </c>
       <c r="B297" t="n">
-        <v>3.661678791046143</v>
+        <v>3.661679029464722</v>
       </c>
       <c r="C297" t="n">
-        <v>3.805273903495892</v>
+        <v>3.80527415126421</v>
       </c>
       <c r="D297" t="n">
-        <v>3.63475492143541</v>
+        <v>3.634755158100927</v>
       </c>
       <c r="E297" t="n">
-        <v>3.805273903495892</v>
+        <v>3.80527415126421</v>
       </c>
       <c r="F297" t="n">
         <v>18862600</v>
@@ -6372,16 +6372,16 @@
         <v>44845</v>
       </c>
       <c r="B298" t="n">
-        <v>3.903995037078857</v>
+        <v>3.903995752334595</v>
       </c>
       <c r="C298" t="n">
-        <v>3.948868715414809</v>
+        <v>3.948869438891908</v>
       </c>
       <c r="D298" t="n">
-        <v>3.634754250904485</v>
+        <v>3.634754916832287</v>
       </c>
       <c r="E298" t="n">
-        <v>3.661678115548366</v>
+        <v>3.661678786408922</v>
       </c>
       <c r="F298" t="n">
         <v>30833900</v>
@@ -6392,16 +6392,16 @@
         <v>44847</v>
       </c>
       <c r="B299" t="n">
-        <v>3.81424880027771</v>
+        <v>3.814249515533447</v>
       </c>
       <c r="C299" t="n">
-        <v>3.903995745283042</v>
+        <v>3.90399647736831</v>
       </c>
       <c r="D299" t="n">
-        <v>3.796299411276644</v>
+        <v>3.796300123166475</v>
       </c>
       <c r="E299" t="n">
-        <v>3.895021264756104</v>
+        <v>3.895021995158459</v>
       </c>
       <c r="F299" t="n">
         <v>15027200</v>
@@ -6432,16 +6432,16 @@
         <v>44851</v>
       </c>
       <c r="B301" t="n">
-        <v>3.679628133773804</v>
+        <v>3.679628372192383</v>
       </c>
       <c r="C301" t="n">
-        <v>3.769375077924933</v>
+        <v>3.769375322158595</v>
       </c>
       <c r="D301" t="n">
-        <v>3.670653653332284</v>
+        <v>3.670653891169369</v>
       </c>
       <c r="E301" t="n">
-        <v>3.724501819822962</v>
+        <v>3.724502061149096</v>
       </c>
       <c r="F301" t="n">
         <v>8129100</v>
@@ -6452,16 +6452,16 @@
         <v>44852</v>
       </c>
       <c r="B302" t="n">
-        <v>3.715527057647705</v>
+        <v>3.715527296066284</v>
       </c>
       <c r="C302" t="n">
-        <v>3.787324615793987</v>
+        <v>3.787324858819684</v>
       </c>
       <c r="D302" t="n">
-        <v>3.661678889037994</v>
+        <v>3.661679124001235</v>
       </c>
       <c r="E302" t="n">
-        <v>3.724501966389592</v>
+        <v>3.724502205384074</v>
       </c>
       <c r="F302" t="n">
         <v>13196400</v>
@@ -6472,16 +6472,16 @@
         <v>44853</v>
       </c>
       <c r="B303" t="n">
-        <v>3.733476161956787</v>
+        <v>3.733476638793945</v>
       </c>
       <c r="C303" t="n">
-        <v>3.769374938287358</v>
+        <v>3.769375419709485</v>
       </c>
       <c r="D303" t="n">
-        <v>3.670653517351873</v>
+        <v>3.670653986165363</v>
       </c>
       <c r="E303" t="n">
-        <v>3.715526773791502</v>
+        <v>3.715527248336175</v>
       </c>
       <c r="F303" t="n">
         <v>12625300</v>
@@ -6512,16 +6512,16 @@
         <v>44855</v>
       </c>
       <c r="B305" t="n">
-        <v>3.832198143005371</v>
+        <v>3.83219838142395</v>
       </c>
       <c r="C305" t="n">
-        <v>3.859122440155458</v>
+        <v>3.85912268024912</v>
       </c>
       <c r="D305" t="n">
-        <v>3.733476290717968</v>
+        <v>3.733476522994609</v>
       </c>
       <c r="E305" t="n">
-        <v>3.760400587868054</v>
+        <v>3.760400821819779</v>
       </c>
       <c r="F305" t="n">
         <v>14614900</v>
@@ -6532,16 +6532,16 @@
         <v>44858</v>
       </c>
       <c r="B306" t="n">
-        <v>3.706552982330322</v>
+        <v>3.706552743911743</v>
       </c>
       <c r="C306" t="n">
-        <v>3.778350548330878</v>
+        <v>3.778350305294026</v>
       </c>
       <c r="D306" t="n">
-        <v>3.697578072606628</v>
+        <v>3.697577834765347</v>
       </c>
       <c r="E306" t="n">
-        <v>3.769375638607184</v>
+        <v>3.76937539614763</v>
       </c>
       <c r="F306" t="n">
         <v>9021900</v>
@@ -6552,16 +6552,16 @@
         <v>44859</v>
       </c>
       <c r="B307" t="n">
-        <v>3.670654058456421</v>
+        <v>3.670653820037842</v>
       </c>
       <c r="C307" t="n">
-        <v>3.769375493944795</v>
+        <v>3.769375249114001</v>
       </c>
       <c r="D307" t="n">
-        <v>3.661679149077169</v>
+        <v>3.661678911241534</v>
       </c>
       <c r="E307" t="n">
-        <v>3.706552840078963</v>
+        <v>3.706552599328664</v>
       </c>
       <c r="F307" t="n">
         <v>12220200</v>
@@ -6572,16 +6572,16 @@
         <v>44860</v>
       </c>
       <c r="B308" t="n">
-        <v>3.562957048416138</v>
+        <v>3.562957286834717</v>
       </c>
       <c r="C308" t="n">
-        <v>3.670653593619109</v>
+        <v>3.670653839244302</v>
       </c>
       <c r="D308" t="n">
-        <v>3.545007659877907</v>
+        <v>3.545007897095387</v>
       </c>
       <c r="E308" t="n">
-        <v>3.661678685376404</v>
+        <v>3.661678930401033</v>
       </c>
       <c r="F308" t="n">
         <v>15630800</v>
@@ -6592,16 +6592,16 @@
         <v>44861</v>
       </c>
       <c r="B309" t="n">
-        <v>3.706552982330322</v>
+        <v>3.706552743911743</v>
       </c>
       <c r="C309" t="n">
-        <v>3.760401156830739</v>
+        <v>3.760400914948455</v>
       </c>
       <c r="D309" t="n">
-        <v>3.580907027855725</v>
+        <v>3.580906797519137</v>
       </c>
       <c r="E309" t="n">
-        <v>3.580907027855725</v>
+        <v>3.580906797519137</v>
       </c>
       <c r="F309" t="n">
         <v>15175200</v>
@@ -6612,16 +6612,16 @@
         <v>44862</v>
       </c>
       <c r="B310" t="n">
-        <v>3.724502086639404</v>
+        <v>3.724501848220825</v>
       </c>
       <c r="C310" t="n">
-        <v>3.73347656772384</v>
+        <v>3.733476328730772</v>
       </c>
       <c r="D310" t="n">
-        <v>3.643729617143404</v>
+        <v>3.643729383895357</v>
       </c>
       <c r="E310" t="n">
-        <v>3.68860330640723</v>
+        <v>3.688603070286659</v>
       </c>
       <c r="F310" t="n">
         <v>9985100</v>
@@ -6632,16 +6632,16 @@
         <v>44865</v>
       </c>
       <c r="B311" t="n">
-        <v>3.850147724151611</v>
+        <v>3.85014796257019</v>
       </c>
       <c r="C311" t="n">
-        <v>3.868097113832732</v>
+        <v>3.868097353362819</v>
       </c>
       <c r="D311" t="n">
-        <v>3.545007885598959</v>
+        <v>3.545008105121898</v>
       </c>
       <c r="E311" t="n">
-        <v>3.58988135980176</v>
+        <v>3.589881582103468</v>
       </c>
       <c r="F311" t="n">
         <v>19491700</v>
@@ -6652,16 +6652,16 @@
         <v>44866</v>
       </c>
       <c r="B312" t="n">
-        <v>4.047591686248779</v>
+        <v>4.047591209411621</v>
       </c>
       <c r="C312" t="n">
-        <v>4.092464949223611</v>
+        <v>4.092464467100041</v>
       </c>
       <c r="D312" t="n">
-        <v>3.814249178169614</v>
+        <v>3.814248728821982</v>
       </c>
       <c r="E312" t="n">
-        <v>3.868097350507752</v>
+        <v>3.868096894816395</v>
       </c>
       <c r="F312" t="n">
         <v>23695600</v>
@@ -6672,16 +6672,16 @@
         <v>44868</v>
       </c>
       <c r="B313" t="n">
-        <v>4.21811056137085</v>
+        <v>4.218110084533691</v>
       </c>
       <c r="C313" t="n">
-        <v>4.254009341880177</v>
+        <v>4.254008860984833</v>
       </c>
       <c r="D313" t="n">
-        <v>3.895021536786911</v>
+        <v>3.895021096473417</v>
       </c>
       <c r="E313" t="n">
-        <v>3.975793578959285</v>
+        <v>3.975793129514899</v>
       </c>
       <c r="F313" t="n">
         <v>15015300</v>
@@ -6712,16 +6712,16 @@
         <v>44872</v>
       </c>
       <c r="B315" t="n">
-        <v>4.011692523956299</v>
+        <v>4.011692047119141</v>
       </c>
       <c r="C315" t="n">
-        <v>4.379655681184977</v>
+        <v>4.37965516061104</v>
       </c>
       <c r="D315" t="n">
-        <v>4.011692523956299</v>
+        <v>4.011692047119141</v>
       </c>
       <c r="E315" t="n">
-        <v>4.316832598744169</v>
+        <v>4.3168320856375</v>
       </c>
       <c r="F315" t="n">
         <v>17217400</v>
@@ -6752,16 +6752,16 @@
         <v>44874</v>
       </c>
       <c r="B317" t="n">
-        <v>4.011692523956299</v>
+        <v>4.011692047119141</v>
       </c>
       <c r="C317" t="n">
-        <v>4.173237470819165</v>
+        <v>4.173236974780477</v>
       </c>
       <c r="D317" t="n">
-        <v>3.98476865144398</v>
+        <v>3.984768177807042</v>
       </c>
       <c r="E317" t="n">
-        <v>4.065541124875413</v>
+        <v>4.06554064163771</v>
       </c>
       <c r="F317" t="n">
         <v>11339500</v>
@@ -6792,16 +6792,16 @@
         <v>44876</v>
       </c>
       <c r="B319" t="n">
-        <v>3.715527057647705</v>
+        <v>3.715527296066284</v>
       </c>
       <c r="C319" t="n">
-        <v>3.751425836720846</v>
+        <v>3.751426077442984</v>
       </c>
       <c r="D319" t="n">
-        <v>3.437311305857262</v>
+        <v>3.437311526423245</v>
       </c>
       <c r="E319" t="n">
-        <v>3.634755018706739</v>
+        <v>3.634755251942325</v>
       </c>
       <c r="F319" t="n">
         <v>24235200</v>
@@ -6812,16 +6812,16 @@
         <v>44879</v>
       </c>
       <c r="B320" t="n">
-        <v>3.697577476501465</v>
+        <v>3.697577714920044</v>
       </c>
       <c r="C320" t="n">
-        <v>3.796299327810405</v>
+        <v>3.796299572594537</v>
       </c>
       <c r="D320" t="n">
-        <v>3.643729310682183</v>
+        <v>3.64372954562865</v>
       </c>
       <c r="E320" t="n">
-        <v>3.760400550597551</v>
+        <v>3.760400793066941</v>
       </c>
       <c r="F320" t="n">
         <v>10873300</v>
@@ -6832,16 +6832,16 @@
         <v>44881</v>
       </c>
       <c r="B321" t="n">
-        <v>3.616805553436279</v>
+        <v>3.616805791854858</v>
       </c>
       <c r="C321" t="n">
-        <v>3.760400666722041</v>
+        <v>3.760400914606361</v>
       </c>
       <c r="D321" t="n">
-        <v>3.553982477400161</v>
+        <v>3.553982711677465</v>
       </c>
       <c r="E321" t="n">
-        <v>3.697577590685923</v>
+        <v>3.697577834428968</v>
       </c>
       <c r="F321" t="n">
         <v>16148800</v>
@@ -6872,16 +6872,16 @@
         <v>44883</v>
       </c>
       <c r="B323" t="n">
-        <v>3.652704477310181</v>
+        <v>3.652704238891602</v>
       </c>
       <c r="C323" t="n">
-        <v>3.841173284981419</v>
+        <v>3.841173034261142</v>
       </c>
       <c r="D323" t="n">
-        <v>3.536033229142802</v>
+        <v>3.536032998339565</v>
       </c>
       <c r="E323" t="n">
-        <v>3.580906703832715</v>
+        <v>3.580906470100505</v>
       </c>
       <c r="F323" t="n">
         <v>23150300</v>
@@ -6892,16 +6892,16 @@
         <v>44886</v>
       </c>
       <c r="B324" t="n">
-        <v>3.616805553436279</v>
+        <v>3.616805791854858</v>
       </c>
       <c r="C324" t="n">
-        <v>3.733476369007364</v>
+        <v>3.733476615116843</v>
       </c>
       <c r="D324" t="n">
-        <v>3.545007782819801</v>
+        <v>3.545008016505496</v>
       </c>
       <c r="E324" t="n">
-        <v>3.679628201525203</v>
+        <v>3.67962844408503</v>
       </c>
       <c r="F324" t="n">
         <v>11314600</v>
@@ -6912,16 +6912,16 @@
         <v>44887</v>
       </c>
       <c r="B325" t="n">
-        <v>3.616805553436279</v>
+        <v>3.616805791854858</v>
       </c>
       <c r="C325" t="n">
-        <v>3.661678812364483</v>
+        <v>3.661679053741092</v>
       </c>
       <c r="D325" t="n">
-        <v>3.562957171980521</v>
+        <v>3.562957406849434</v>
       </c>
       <c r="E325" t="n">
-        <v>3.616805553436279</v>
+        <v>3.616805791854858</v>
       </c>
       <c r="F325" t="n">
         <v>10439300</v>
@@ -6952,16 +6952,16 @@
         <v>44889</v>
       </c>
       <c r="B327" t="n">
-        <v>3.724502086639404</v>
+        <v>3.724501848220825</v>
       </c>
       <c r="C327" t="n">
-        <v>3.742451476755492</v>
+        <v>3.742451237187908</v>
       </c>
       <c r="D327" t="n">
-        <v>3.598856355826795</v>
+        <v>3.598856125451244</v>
       </c>
       <c r="E327" t="n">
-        <v>3.634755136058969</v>
+        <v>3.63475490338541</v>
       </c>
       <c r="F327" t="n">
         <v>5511600</v>
@@ -6972,16 +6972,16 @@
         <v>44890</v>
       </c>
       <c r="B328" t="n">
-        <v>3.63475489616394</v>
+        <v>3.63475513458252</v>
       </c>
       <c r="C328" t="n">
-        <v>3.76040061868389</v>
+        <v>3.760400865344091</v>
       </c>
       <c r="D328" t="n">
-        <v>3.580906515396082</v>
+        <v>3.580906750282523</v>
       </c>
       <c r="E328" t="n">
-        <v>3.733476321313164</v>
+        <v>3.733476566207289</v>
       </c>
       <c r="F328" t="n">
         <v>8739900</v>
@@ -7032,16 +7032,16 @@
         <v>44895</v>
       </c>
       <c r="B331" t="n">
-        <v>3.63475489616394</v>
+        <v>3.63475513458252</v>
       </c>
       <c r="C331" t="n">
-        <v>3.661678765587478</v>
+        <v>3.661679005772105</v>
       </c>
       <c r="D331" t="n">
-        <v>3.518083654136107</v>
+        <v>3.518083884901738</v>
       </c>
       <c r="E331" t="n">
-        <v>3.571931820930371</v>
+        <v>3.571932055228125</v>
       </c>
       <c r="F331" t="n">
         <v>16877200</v>
@@ -7052,16 +7052,16 @@
         <v>44896</v>
       </c>
       <c r="B332" t="n">
-        <v>3.446285724639893</v>
+        <v>3.446285963058472</v>
       </c>
       <c r="C332" t="n">
-        <v>3.589881043406649</v>
+        <v>3.589881291759341</v>
       </c>
       <c r="D332" t="n">
-        <v>3.428336336540746</v>
+        <v>3.428336573717563</v>
       </c>
       <c r="E332" t="n">
-        <v>3.589881043406649</v>
+        <v>3.589881291759341</v>
       </c>
       <c r="F332" t="n">
         <v>22625600</v>
@@ -7092,16 +7092,16 @@
         <v>44900</v>
       </c>
       <c r="B334" t="n">
-        <v>3.347564458847046</v>
+        <v>3.347564697265625</v>
       </c>
       <c r="C334" t="n">
-        <v>3.545007963660719</v>
+        <v>3.545008216141522</v>
       </c>
       <c r="D334" t="n">
-        <v>3.329615068770676</v>
+        <v>3.329615305910873</v>
       </c>
       <c r="E334" t="n">
-        <v>3.545007963660719</v>
+        <v>3.545008216141522</v>
       </c>
       <c r="F334" t="n">
         <v>14607600</v>
@@ -7112,16 +7112,16 @@
         <v>44901</v>
       </c>
       <c r="B335" t="n">
-        <v>3.302690744400024</v>
+        <v>3.302690982818604</v>
       </c>
       <c r="C335" t="n">
-        <v>3.401412382668387</v>
+        <v>3.401412628213602</v>
       </c>
       <c r="D335" t="n">
-        <v>3.248842364098234</v>
+        <v>3.248842598629542</v>
       </c>
       <c r="E335" t="n">
-        <v>3.383462993892321</v>
+        <v>3.383463238141784</v>
       </c>
       <c r="F335" t="n">
         <v>13327400</v>
@@ -7312,16 +7312,16 @@
         <v>44915</v>
       </c>
       <c r="B345" t="n">
-        <v>3.257622003555298</v>
+        <v>3.257622241973877</v>
       </c>
       <c r="C345" t="n">
-        <v>3.312835883757822</v>
+        <v>3.31283612621739</v>
       </c>
       <c r="D345" t="n">
-        <v>3.036766263344746</v>
+        <v>3.036766485599353</v>
       </c>
       <c r="E345" t="n">
-        <v>3.036766263344746</v>
+        <v>3.036766485599353</v>
       </c>
       <c r="F345" t="n">
         <v>12943700</v>
@@ -7332,16 +7332,16 @@
         <v>44916</v>
       </c>
       <c r="B346" t="n">
-        <v>3.331240892410278</v>
+        <v>3.331240653991699</v>
       </c>
       <c r="C346" t="n">
-        <v>3.377252683921307</v>
+        <v>3.37725244220964</v>
       </c>
       <c r="D346" t="n">
-        <v>3.239217748189187</v>
+        <v>3.23921751635675</v>
       </c>
       <c r="E346" t="n">
-        <v>3.266824691455514</v>
+        <v>3.266824457647235</v>
       </c>
       <c r="F346" t="n">
         <v>14610300</v>
@@ -7352,16 +7352,16 @@
         <v>44917</v>
       </c>
       <c r="B347" t="n">
-        <v>3.340443134307861</v>
+        <v>3.340442895889282</v>
       </c>
       <c r="C347" t="n">
-        <v>3.358847761543679</v>
+        <v>3.3588475218115</v>
       </c>
       <c r="D347" t="n">
-        <v>3.257622092346219</v>
+        <v>3.257621859838854</v>
       </c>
       <c r="E347" t="n">
-        <v>3.33124060128949</v>
+        <v>3.331240363527726</v>
       </c>
       <c r="F347" t="n">
         <v>7727000</v>
@@ -7372,16 +7372,16 @@
         <v>44918</v>
       </c>
       <c r="B348" t="n">
-        <v>3.414061546325684</v>
+        <v>3.414061784744263</v>
       </c>
       <c r="C348" t="n">
-        <v>3.441668486395647</v>
+        <v>3.441668726742138</v>
       </c>
       <c r="D348" t="n">
-        <v>3.340443039472447</v>
+        <v>3.34044327274993</v>
       </c>
       <c r="E348" t="n">
-        <v>3.358847666185756</v>
+        <v>3.358847900748513</v>
       </c>
       <c r="F348" t="n">
         <v>4486400</v>
@@ -7392,16 +7392,16 @@
         <v>44921</v>
       </c>
       <c r="B349" t="n">
-        <v>3.340443134307861</v>
+        <v>3.340442895889282</v>
       </c>
       <c r="C349" t="n">
-        <v>3.441668584104859</v>
+        <v>3.441668338461481</v>
       </c>
       <c r="D349" t="n">
-        <v>3.285229033199945</v>
+        <v>3.28522879872218</v>
       </c>
       <c r="E349" t="n">
-        <v>3.441668584104859</v>
+        <v>3.441668338461481</v>
       </c>
       <c r="F349" t="n">
         <v>5290600</v>
@@ -7412,16 +7412,16 @@
         <v>44922</v>
       </c>
       <c r="B350" t="n">
-        <v>3.386454582214355</v>
+        <v>3.386455059051514</v>
       </c>
       <c r="C350" t="n">
-        <v>3.39565689550568</v>
+        <v>3.39565737363859</v>
       </c>
       <c r="D350" t="n">
-        <v>3.276026603318003</v>
+        <v>3.276027064606107</v>
       </c>
       <c r="E350" t="n">
-        <v>3.349645329049056</v>
+        <v>3.349645800703207</v>
       </c>
       <c r="F350" t="n">
         <v>5669100</v>
@@ -7452,16 +7452,16 @@
         <v>44924</v>
       </c>
       <c r="B352" t="n">
-        <v>3.441668748855591</v>
+        <v>3.441668510437012</v>
       </c>
       <c r="C352" t="n">
-        <v>3.598108307249177</v>
+        <v>3.598108057993386</v>
       </c>
       <c r="D352" t="n">
-        <v>3.404859492621917</v>
+        <v>3.404859256753267</v>
       </c>
       <c r="E352" t="n">
-        <v>3.524489575381356</v>
+        <v>3.524489331225437</v>
       </c>
       <c r="F352" t="n">
         <v>7177700</v>
@@ -7472,16 +7472,16 @@
         <v>44928</v>
       </c>
       <c r="B353" t="n">
-        <v>3.257622003555298</v>
+        <v>3.257622241973877</v>
       </c>
       <c r="C353" t="n">
-        <v>3.414061550196239</v>
+        <v>3.414061800064303</v>
       </c>
       <c r="D353" t="n">
-        <v>3.230015063454036</v>
+        <v>3.23001529985212</v>
       </c>
       <c r="E353" t="n">
-        <v>3.395656923462064</v>
+        <v>3.395657171983132</v>
       </c>
       <c r="F353" t="n">
         <v>9470500</v>
@@ -7512,16 +7512,16 @@
         <v>44930</v>
       </c>
       <c r="B355" t="n">
-        <v>3.055171012878418</v>
+        <v>3.055170774459839</v>
       </c>
       <c r="C355" t="n">
-        <v>3.147194369648533</v>
+        <v>3.147194124048661</v>
       </c>
       <c r="D355" t="n">
-        <v>3.036766385404488</v>
+        <v>3.036766148422164</v>
       </c>
       <c r="E355" t="n">
-        <v>3.110385114700673</v>
+        <v>3.110384871973312</v>
       </c>
       <c r="F355" t="n">
         <v>10680900</v>
@@ -7532,16 +7532,16 @@
         <v>44931</v>
       </c>
       <c r="B356" t="n">
-        <v>2.972350120544434</v>
+        <v>2.972350358963013</v>
       </c>
       <c r="C356" t="n">
-        <v>3.119587356333176</v>
+        <v>3.11958760656197</v>
       </c>
       <c r="D356" t="n">
-        <v>2.935540866447363</v>
+        <v>2.935541101913393</v>
       </c>
       <c r="E356" t="n">
-        <v>3.082777882835645</v>
+        <v>3.082778130111872</v>
       </c>
       <c r="F356" t="n">
         <v>35445300</v>
@@ -7572,16 +7572,16 @@
         <v>44935</v>
       </c>
       <c r="B358" t="n">
-        <v>2.972350120544434</v>
+        <v>2.972350358963013</v>
       </c>
       <c r="C358" t="n">
-        <v>3.027564001690039</v>
+        <v>3.027564244537442</v>
       </c>
       <c r="D358" t="n">
-        <v>2.90793392587456</v>
+        <v>2.907934159126178</v>
       </c>
       <c r="E358" t="n">
-        <v>2.944743179971631</v>
+        <v>2.944743416175798</v>
       </c>
       <c r="F358" t="n">
         <v>15633700</v>
@@ -7612,16 +7612,16 @@
         <v>44937</v>
       </c>
       <c r="B360" t="n">
-        <v>3.294431209564209</v>
+        <v>3.294431447982788</v>
       </c>
       <c r="C360" t="n">
-        <v>3.294431209564209</v>
+        <v>3.294431447982788</v>
       </c>
       <c r="D360" t="n">
-        <v>3.091980099004334</v>
+        <v>3.091980322771489</v>
       </c>
       <c r="E360" t="n">
-        <v>3.091980099004334</v>
+        <v>3.091980322771489</v>
       </c>
       <c r="F360" t="n">
         <v>21444400</v>
@@ -7732,16 +7732,16 @@
         <v>44945</v>
       </c>
       <c r="B366" t="n">
-        <v>3.137992143630981</v>
+        <v>3.137991905212402</v>
       </c>
       <c r="C366" t="n">
-        <v>3.147194457625188</v>
+        <v>3.147194218507435</v>
       </c>
       <c r="D366" t="n">
-        <v>2.990754900323207</v>
+        <v>2.99075467309143</v>
       </c>
       <c r="E366" t="n">
-        <v>3.082778040265271</v>
+        <v>3.082777806041753</v>
       </c>
       <c r="F366" t="n">
         <v>23712400</v>
@@ -7792,16 +7792,16 @@
         <v>44950</v>
       </c>
       <c r="B369" t="n">
-        <v>3.193205833435059</v>
+        <v>3.193206071853638</v>
       </c>
       <c r="C369" t="n">
-        <v>3.202408146869723</v>
+        <v>3.202408385975387</v>
       </c>
       <c r="D369" t="n">
-        <v>3.018361658775971</v>
+        <v>3.018361884139927</v>
       </c>
       <c r="E369" t="n">
-        <v>3.045968599079965</v>
+        <v>3.045968826505175</v>
       </c>
       <c r="F369" t="n">
         <v>12703800</v>
@@ -7832,16 +7832,16 @@
         <v>44952</v>
       </c>
       <c r="B371" t="n">
-        <v>3.2024085521698</v>
+        <v>3.202408313751221</v>
       </c>
       <c r="C371" t="n">
-        <v>3.28522938356367</v>
+        <v>3.2852291389791</v>
       </c>
       <c r="D371" t="n">
-        <v>3.184003922971162</v>
+        <v>3.184003685922803</v>
       </c>
       <c r="E371" t="n">
-        <v>3.257622439765714</v>
+        <v>3.257622197236473</v>
       </c>
       <c r="F371" t="n">
         <v>8271800</v>
@@ -7852,16 +7852,16 @@
         <v>44953</v>
       </c>
       <c r="B372" t="n">
-        <v>3.147194147109985</v>
+        <v>3.147194623947144</v>
       </c>
       <c r="C372" t="n">
-        <v>3.22081265180013</v>
+        <v>3.220813139791363</v>
       </c>
       <c r="D372" t="n">
-        <v>3.128789520937449</v>
+        <v>3.128789994986088</v>
       </c>
       <c r="E372" t="n">
-        <v>3.211610338713862</v>
+        <v>3.211610825310835</v>
       </c>
       <c r="F372" t="n">
         <v>8557200</v>
@@ -7932,16 +7932,16 @@
         <v>44959</v>
       </c>
       <c r="B376" t="n">
-        <v>2.806708097457886</v>
+        <v>2.806708335876465</v>
       </c>
       <c r="C376" t="n">
-        <v>2.972349950837826</v>
+        <v>2.972350203327015</v>
       </c>
       <c r="D376" t="n">
-        <v>2.797505784459025</v>
+        <v>2.797506022095904</v>
       </c>
       <c r="E376" t="n">
-        <v>2.898731446846941</v>
+        <v>2.898731693082534</v>
       </c>
       <c r="F376" t="n">
         <v>50857000</v>
@@ -8032,16 +8032,16 @@
         <v>44966</v>
       </c>
       <c r="B381" t="n">
-        <v>3.018362045288086</v>
+        <v>3.018361806869507</v>
       </c>
       <c r="C381" t="n">
-        <v>3.091980562192519</v>
+        <v>3.091980317958858</v>
       </c>
       <c r="D381" t="n">
-        <v>2.935541213770599</v>
+        <v>2.935540981893987</v>
       </c>
       <c r="E381" t="n">
-        <v>3.036766674514194</v>
+        <v>3.036766434641845</v>
       </c>
       <c r="F381" t="n">
         <v>43678900</v>
@@ -8092,16 +8092,16 @@
         <v>44971</v>
       </c>
       <c r="B384" t="n">
-        <v>2.742292404174805</v>
+        <v>2.742292165756226</v>
       </c>
       <c r="C384" t="n">
-        <v>2.953945860962829</v>
+        <v>2.953945604142814</v>
       </c>
       <c r="D384" t="n">
-        <v>2.723887774836758</v>
+        <v>2.723887538018302</v>
       </c>
       <c r="E384" t="n">
-        <v>2.953945860962829</v>
+        <v>2.953945604142814</v>
       </c>
       <c r="F384" t="n">
         <v>40924300</v>
@@ -8152,16 +8152,16 @@
         <v>44974</v>
       </c>
       <c r="B387" t="n">
-        <v>2.788303852081299</v>
+        <v>2.78830361366272</v>
       </c>
       <c r="C387" t="n">
-        <v>2.871124680376612</v>
+        <v>2.8711244348763</v>
       </c>
       <c r="D387" t="n">
-        <v>2.769899223571229</v>
+        <v>2.769898986726369</v>
       </c>
       <c r="E387" t="n">
-        <v>2.825113109101438</v>
+        <v>2.825112867535422</v>
       </c>
       <c r="F387" t="n">
         <v>27974700</v>
@@ -8212,16 +8212,16 @@
         <v>44981</v>
       </c>
       <c r="B390" t="n">
-        <v>2.65947151184082</v>
+        <v>2.659471035003662</v>
       </c>
       <c r="C390" t="n">
-        <v>2.806708543206081</v>
+        <v>2.80670803996966</v>
       </c>
       <c r="D390" t="n">
-        <v>2.650269197380491</v>
+        <v>2.650268722193287</v>
       </c>
       <c r="E390" t="n">
-        <v>2.797506228745752</v>
+        <v>2.797505727159285</v>
       </c>
       <c r="F390" t="n">
         <v>27929600</v>
@@ -8292,16 +8292,16 @@
         <v>44987</v>
       </c>
       <c r="B394" t="n">
-        <v>2.68707799911499</v>
+        <v>2.687078237533569</v>
       </c>
       <c r="C394" t="n">
-        <v>2.797505753894839</v>
+        <v>2.797506002111432</v>
       </c>
       <c r="D394" t="n">
-        <v>2.68707799911499</v>
+        <v>2.687078237533569</v>
       </c>
       <c r="E394" t="n">
-        <v>2.779101128098197</v>
+        <v>2.779101374681788</v>
       </c>
       <c r="F394" t="n">
         <v>21864000</v>
@@ -8312,16 +8312,16 @@
         <v>44988</v>
       </c>
       <c r="B395" t="n">
-        <v>2.604257106781006</v>
+        <v>2.604257345199585</v>
       </c>
       <c r="C395" t="n">
-        <v>2.714685087031328</v>
+        <v>2.71468533555954</v>
       </c>
       <c r="D395" t="n">
-        <v>2.558245539760229</v>
+        <v>2.55824577396647</v>
       </c>
       <c r="E395" t="n">
-        <v>2.714685087031328</v>
+        <v>2.71468533555954</v>
       </c>
       <c r="F395" t="n">
         <v>36019100</v>
@@ -8452,16 +8452,16 @@
         <v>44999</v>
       </c>
       <c r="B402" t="n">
-        <v>2.493829250335693</v>
+        <v>2.493829488754272</v>
       </c>
       <c r="C402" t="n">
-        <v>2.585852380849743</v>
+        <v>2.585852628066047</v>
       </c>
       <c r="D402" t="n">
-        <v>2.466222311181478</v>
+        <v>2.46622254696074</v>
       </c>
       <c r="E402" t="n">
-        <v>2.475424624232883</v>
+        <v>2.475424860891918</v>
       </c>
       <c r="F402" t="n">
         <v>40119200</v>
@@ -8472,16 +8472,16 @@
         <v>45000</v>
       </c>
       <c r="B403" t="n">
-        <v>2.493829250335693</v>
+        <v>2.493829488754272</v>
       </c>
       <c r="C403" t="n">
-        <v>2.521436189489909</v>
+        <v>2.521436430547805</v>
       </c>
       <c r="D403" t="n">
-        <v>2.447817685078669</v>
+        <v>2.447817919098385</v>
       </c>
       <c r="E403" t="n">
-        <v>2.475424624232883</v>
+        <v>2.475424860891918</v>
       </c>
       <c r="F403" t="n">
         <v>17612600</v>
@@ -8512,16 +8512,16 @@
         <v>45002</v>
       </c>
       <c r="B405" t="n">
-        <v>2.349630117416382</v>
+        <v>2.349629878997803</v>
       </c>
       <c r="C405" t="n">
-        <v>2.549396274733532</v>
+        <v>2.549396016044544</v>
       </c>
       <c r="D405" t="n">
-        <v>2.349630117416382</v>
+        <v>2.349629878997803</v>
       </c>
       <c r="E405" t="n">
-        <v>2.492320067785928</v>
+        <v>2.492319814888502</v>
       </c>
       <c r="F405" t="n">
         <v>44089800</v>
@@ -8532,16 +8532,16 @@
         <v>45005</v>
       </c>
       <c r="B406" t="n">
-        <v>2.349630117416382</v>
+        <v>2.349629878997803</v>
       </c>
       <c r="C406" t="n">
-        <v>2.406706097564201</v>
+        <v>2.406705853354083</v>
       </c>
       <c r="D406" t="n">
-        <v>2.311579463984502</v>
+        <v>2.311579229426949</v>
       </c>
       <c r="E406" t="n">
-        <v>2.359142780774352</v>
+        <v>2.359142541390516</v>
       </c>
       <c r="F406" t="n">
         <v>20939200</v>
@@ -8592,16 +8592,16 @@
         <v>45008</v>
       </c>
       <c r="B409" t="n">
-        <v>2.149863958358765</v>
+        <v>2.149864196777344</v>
       </c>
       <c r="C409" t="n">
-        <v>2.235477928511182</v>
+        <v>2.235478176424297</v>
       </c>
       <c r="D409" t="n">
-        <v>2.140351295008496</v>
+        <v>2.140351532372127</v>
       </c>
       <c r="E409" t="n">
-        <v>2.225965265160914</v>
+        <v>2.22596551201908</v>
       </c>
       <c r="F409" t="n">
         <v>30902200</v>
@@ -8612,16 +8612,16 @@
         <v>45009</v>
       </c>
       <c r="B410" t="n">
-        <v>2.292553901672363</v>
+        <v>2.292554140090942</v>
       </c>
       <c r="C410" t="n">
-        <v>2.302066564052756</v>
+        <v>2.302066803460623</v>
       </c>
       <c r="D410" t="n">
-        <v>2.149863739166705</v>
+        <v>2.149863962745944</v>
       </c>
       <c r="E410" t="n">
-        <v>2.159376401547098</v>
+        <v>2.159376626115625</v>
       </c>
       <c r="F410" t="n">
         <v>19141800</v>
@@ -8632,16 +8632,16 @@
         <v>45012</v>
       </c>
       <c r="B411" t="n">
-        <v>2.387680768966675</v>
+        <v>2.387681007385254</v>
       </c>
       <c r="C411" t="n">
-        <v>2.416218759018095</v>
+        <v>2.416219000286296</v>
       </c>
       <c r="D411" t="n">
-        <v>2.302066798812414</v>
+        <v>2.302067028682128</v>
       </c>
       <c r="E411" t="n">
-        <v>2.311579462162887</v>
+        <v>2.311579692982475</v>
       </c>
       <c r="F411" t="n">
         <v>19684900</v>
@@ -8692,16 +8692,16 @@
         <v>45015</v>
       </c>
       <c r="B414" t="n">
-        <v>2.749162197113037</v>
+        <v>2.749162435531616</v>
       </c>
       <c r="C414" t="n">
-        <v>2.796725509838225</v>
+        <v>2.796725752381689</v>
       </c>
       <c r="D414" t="n">
-        <v>2.644522682317859</v>
+        <v>2.644522911661672</v>
       </c>
       <c r="E414" t="n">
-        <v>2.673060669952971</v>
+        <v>2.673060901771716</v>
       </c>
       <c r="F414" t="n">
         <v>39786400</v>
@@ -8792,16 +8792,16 @@
         <v>45022</v>
       </c>
       <c r="B419" t="n">
-        <v>2.654035329818726</v>
+        <v>2.654035806655884</v>
       </c>
       <c r="C419" t="n">
-        <v>2.682573317292073</v>
+        <v>2.682573799256508</v>
       </c>
       <c r="D419" t="n">
-        <v>2.615984679854262</v>
+        <v>2.615985149855052</v>
       </c>
       <c r="E419" t="n">
-        <v>2.673060654800957</v>
+        <v>2.6730611350563</v>
       </c>
       <c r="F419" t="n">
         <v>14613400</v>
@@ -8892,16 +8892,16 @@
         <v>45030</v>
       </c>
       <c r="B424" t="n">
-        <v>2.891852378845215</v>
+        <v>2.891852140426636</v>
       </c>
       <c r="C424" t="n">
-        <v>2.901365042191425</v>
+        <v>2.901364802988575</v>
       </c>
       <c r="D424" t="n">
-        <v>2.815751072075536</v>
+        <v>2.815750839931124</v>
       </c>
       <c r="E424" t="n">
-        <v>2.863314388806585</v>
+        <v>2.863314152740819</v>
       </c>
       <c r="F424" t="n">
         <v>10628600</v>
@@ -8992,16 +8992,16 @@
         <v>45040</v>
       </c>
       <c r="B429" t="n">
-        <v>3.072593212127686</v>
+        <v>3.072593450546265</v>
       </c>
       <c r="C429" t="n">
-        <v>3.110643865548496</v>
+        <v>3.110644106919625</v>
       </c>
       <c r="D429" t="n">
-        <v>2.891852381579049</v>
+        <v>2.891852605973001</v>
       </c>
       <c r="E429" t="n">
-        <v>2.948928361710265</v>
+        <v>2.948928590533042</v>
       </c>
       <c r="F429" t="n">
         <v>37103600</v>
@@ -9032,16 +9032,16 @@
         <v>45042</v>
       </c>
       <c r="B431" t="n">
-        <v>2.901365280151367</v>
+        <v>2.901365041732788</v>
       </c>
       <c r="C431" t="n">
-        <v>3.03454280472085</v>
+        <v>3.034542555358458</v>
       </c>
       <c r="D431" t="n">
-        <v>2.891852616024962</v>
+        <v>2.891852378388082</v>
       </c>
       <c r="E431" t="n">
-        <v>3.015517476468038</v>
+        <v>3.015517228669046</v>
       </c>
       <c r="F431" t="n">
         <v>15122100</v>
@@ -9052,16 +9052,16 @@
         <v>45043</v>
       </c>
       <c r="B432" t="n">
-        <v>2.977466821670532</v>
+        <v>2.977466583251953</v>
       </c>
       <c r="C432" t="n">
-        <v>3.006004814066121</v>
+        <v>3.006004573362382</v>
       </c>
       <c r="D432" t="n">
-        <v>2.891852617683963</v>
+        <v>2.891852386120882</v>
       </c>
       <c r="E432" t="n">
-        <v>2.901365281815826</v>
+        <v>2.901365049491024</v>
       </c>
       <c r="F432" t="n">
         <v>12242300</v>
@@ -9072,16 +9072,16 @@
         <v>45044</v>
       </c>
       <c r="B433" t="n">
-        <v>3.034542560577393</v>
+        <v>3.034542798995972</v>
       </c>
       <c r="C433" t="n">
-        <v>3.091618540743791</v>
+        <v>3.091618783646728</v>
       </c>
       <c r="D433" t="n">
-        <v>2.939415700166944</v>
+        <v>2.939415931111576</v>
       </c>
       <c r="E433" t="n">
-        <v>2.977466580410994</v>
+        <v>2.977466814345215</v>
       </c>
       <c r="F433" t="n">
         <v>20412700</v>
@@ -9092,16 +9092,16 @@
         <v>45048</v>
       </c>
       <c r="B434" t="n">
-        <v>2.891852378845215</v>
+        <v>2.891852140426636</v>
       </c>
       <c r="C434" t="n">
-        <v>3.082105872569197</v>
+        <v>3.082105618465181</v>
       </c>
       <c r="D434" t="n">
-        <v>2.891852378845215</v>
+        <v>2.891852140426636</v>
       </c>
       <c r="E434" t="n">
-        <v>3.025029892491938</v>
+        <v>3.025029643093547</v>
       </c>
       <c r="F434" t="n">
         <v>14598900</v>
@@ -9152,16 +9152,16 @@
         <v>45051</v>
       </c>
       <c r="B437" t="n">
-        <v>3.120156764984131</v>
+        <v>3.120156526565552</v>
       </c>
       <c r="C437" t="n">
-        <v>3.12966942905909</v>
+        <v>3.129669189913626</v>
       </c>
       <c r="D437" t="n">
-        <v>3.025030124234536</v>
+        <v>3.025029893084809</v>
       </c>
       <c r="E437" t="n">
-        <v>3.034542788309496</v>
+        <v>3.034542556432883</v>
       </c>
       <c r="F437" t="n">
         <v>17709200</v>
@@ -9212,16 +9212,16 @@
         <v>45056</v>
       </c>
       <c r="B440" t="n">
-        <v>3.120156764984131</v>
+        <v>3.120156526565552</v>
       </c>
       <c r="C440" t="n">
-        <v>3.13918209313405</v>
+        <v>3.1391818532617</v>
       </c>
       <c r="D440" t="n">
-        <v>2.986979467934698</v>
+        <v>2.986979239692512</v>
       </c>
       <c r="E440" t="n">
-        <v>3.034542788309496</v>
+        <v>3.034542556432883</v>
       </c>
       <c r="F440" t="n">
         <v>20064700</v>
@@ -9252,16 +9252,16 @@
         <v>45058</v>
       </c>
       <c r="B442" t="n">
-        <v>3.129669427871704</v>
+        <v>3.129669189453125</v>
       </c>
       <c r="C442" t="n">
-        <v>3.215283631313659</v>
+        <v>3.21528338637298</v>
       </c>
       <c r="D442" t="n">
-        <v>3.091618771586302</v>
+        <v>3.091618536066427</v>
       </c>
       <c r="E442" t="n">
-        <v>3.167720084157106</v>
+        <v>3.167719842839823</v>
       </c>
       <c r="F442" t="n">
         <v>13638800</v>
@@ -9272,16 +9272,16 @@
         <v>45061</v>
       </c>
       <c r="B443" t="n">
-        <v>2.986979484558105</v>
+        <v>2.986979246139526</v>
       </c>
       <c r="C443" t="n">
-        <v>3.20577075949981</v>
+        <v>3.205770503617468</v>
       </c>
       <c r="D443" t="n">
-        <v>2.901365280607201</v>
+        <v>2.901365049022286</v>
       </c>
       <c r="E443" t="n">
-        <v>3.18674543124401</v>
+        <v>3.186745176880255</v>
       </c>
       <c r="F443" t="n">
         <v>71533500</v>
@@ -9332,16 +9332,16 @@
         <v>45064</v>
       </c>
       <c r="B446" t="n">
-        <v>3.300897598266602</v>
+        <v>3.300897359848022</v>
       </c>
       <c r="C446" t="n">
-        <v>3.338948254440312</v>
+        <v>3.338948013273395</v>
       </c>
       <c r="D446" t="n">
-        <v>3.177232738902241</v>
+        <v>3.177232509415779</v>
       </c>
       <c r="E446" t="n">
-        <v>3.253334278049463</v>
+        <v>3.253334043066307</v>
       </c>
       <c r="F446" t="n">
         <v>40825600</v>
@@ -9352,16 +9352,16 @@
         <v>45065</v>
       </c>
       <c r="B447" t="n">
-        <v>3.491150856018066</v>
+        <v>3.491151094436646</v>
       </c>
       <c r="C447" t="n">
-        <v>3.519688846105434</v>
+        <v>3.519689086472937</v>
       </c>
       <c r="D447" t="n">
-        <v>3.281872035244253</v>
+        <v>3.281872259370709</v>
       </c>
       <c r="E447" t="n">
-        <v>3.329435352056533</v>
+        <v>3.329435579431195</v>
       </c>
       <c r="F447" t="n">
         <v>32544700</v>
@@ -9372,16 +9372,16 @@
         <v>45068</v>
       </c>
       <c r="B448" t="n">
-        <v>3.47212553024292</v>
+        <v>3.472126007080078</v>
       </c>
       <c r="C448" t="n">
-        <v>3.576764827258557</v>
+        <v>3.576765318466137</v>
       </c>
       <c r="D448" t="n">
-        <v>3.453100203512804</v>
+        <v>3.453100677737158</v>
       </c>
       <c r="E448" t="n">
-        <v>3.548226837163384</v>
+        <v>3.548227324451757</v>
       </c>
       <c r="F448" t="n">
         <v>14142300</v>
@@ -9392,16 +9392,16 @@
         <v>45069</v>
       </c>
       <c r="B449" t="n">
-        <v>3.47212553024292</v>
+        <v>3.472126007080078</v>
       </c>
       <c r="C449" t="n">
-        <v>3.5672521638935</v>
+        <v>3.567252653794676</v>
       </c>
       <c r="D449" t="n">
-        <v>3.443587313347962</v>
+        <v>3.443587786265883</v>
       </c>
       <c r="E449" t="n">
-        <v>3.47212553024292</v>
+        <v>3.472126007080078</v>
       </c>
       <c r="F449" t="n">
         <v>12031500</v>
@@ -9432,16 +9432,16 @@
         <v>45071</v>
       </c>
       <c r="B451" t="n">
-        <v>3.281872034072876</v>
+        <v>3.281872272491455</v>
       </c>
       <c r="C451" t="n">
-        <v>3.424561984458784</v>
+        <v>3.424562233243379</v>
       </c>
       <c r="D451" t="n">
-        <v>3.272359370713815</v>
+        <v>3.272359608441327</v>
       </c>
       <c r="E451" t="n">
-        <v>3.376998667663482</v>
+        <v>3.376998912992737</v>
       </c>
       <c r="F451" t="n">
         <v>36092900</v>
@@ -9452,16 +9452,16 @@
         <v>45072</v>
       </c>
       <c r="B452" t="n">
-        <v>3.291384696960449</v>
+        <v>3.291384935379028</v>
       </c>
       <c r="C452" t="n">
-        <v>3.348460677106637</v>
+        <v>3.348460919659638</v>
       </c>
       <c r="D452" t="n">
-        <v>3.17723250986829</v>
+        <v>3.177232740018008</v>
       </c>
       <c r="E452" t="n">
-        <v>3.338948013748939</v>
+        <v>3.33894825561287</v>
       </c>
       <c r="F452" t="n">
         <v>25686400</v>
@@ -9472,16 +9472,16 @@
         <v>45075</v>
       </c>
       <c r="B453" t="n">
-        <v>3.357973575592041</v>
+        <v>3.357973337173462</v>
       </c>
       <c r="C453" t="n">
-        <v>3.415049559734729</v>
+        <v>3.415049317263714</v>
       </c>
       <c r="D453" t="n">
-        <v>3.291384927425571</v>
+        <v>3.291384693734835</v>
       </c>
       <c r="E453" t="n">
-        <v>3.319922919496916</v>
+        <v>3.319922683779961</v>
       </c>
       <c r="F453" t="n">
         <v>14544800</v>
@@ -9492,16 +9492,16 @@
         <v>45076</v>
       </c>
       <c r="B454" t="n">
-        <v>3.424562215805054</v>
+        <v>3.424561977386475</v>
       </c>
       <c r="C454" t="n">
-        <v>3.462613098611607</v>
+        <v>3.46261285754392</v>
       </c>
       <c r="D454" t="n">
-        <v>3.310410247784792</v>
+        <v>3.310410017313492</v>
       </c>
       <c r="E454" t="n">
-        <v>3.396024223799988</v>
+        <v>3.396023987368229</v>
       </c>
       <c r="F454" t="n">
         <v>24140700</v>
@@ -9512,16 +9512,16 @@
         <v>45077</v>
       </c>
       <c r="B455" t="n">
-        <v>3.453100204467773</v>
+        <v>3.453099966049194</v>
       </c>
       <c r="C455" t="n">
-        <v>3.557739501512349</v>
+        <v>3.557739255868972</v>
       </c>
       <c r="D455" t="n">
-        <v>3.415049324197234</v>
+        <v>3.41504908840587</v>
       </c>
       <c r="E455" t="n">
-        <v>3.424561987564922</v>
+        <v>3.424561751116759</v>
       </c>
       <c r="F455" t="n">
         <v>23066900</v>
@@ -9532,16 +9532,16 @@
         <v>45078</v>
       </c>
       <c r="B456" t="n">
-        <v>3.576764583587646</v>
+        <v>3.576765060424805</v>
       </c>
       <c r="C456" t="n">
-        <v>3.662378548040625</v>
+        <v>3.662379036291428</v>
       </c>
       <c r="D456" t="n">
-        <v>3.376998439730927</v>
+        <v>3.376998889936218</v>
       </c>
       <c r="E456" t="n">
-        <v>3.472125293700673</v>
+        <v>3.472125756587821</v>
       </c>
       <c r="F456" t="n">
         <v>28377100</v>
@@ -9552,16 +9552,16 @@
         <v>45079</v>
       </c>
       <c r="B457" t="n">
-        <v>3.529201507568359</v>
+        <v>3.529201745986938</v>
       </c>
       <c r="C457" t="n">
-        <v>3.643353467856389</v>
+        <v>3.643353713986613</v>
       </c>
       <c r="D457" t="n">
-        <v>3.491150854139016</v>
+        <v>3.491151089987047</v>
       </c>
       <c r="E457" t="n">
-        <v>3.614815477784382</v>
+        <v>3.614815721986695</v>
       </c>
       <c r="F457" t="n">
         <v>24144300</v>
@@ -9612,16 +9612,16 @@
         <v>45084</v>
       </c>
       <c r="B460" t="n">
-        <v>3.757505655288696</v>
+        <v>3.757505893707275</v>
       </c>
       <c r="C460" t="n">
-        <v>3.85263251567056</v>
+        <v>3.852632760125061</v>
       </c>
       <c r="D460" t="n">
-        <v>3.681404121623248</v>
+        <v>3.681404355213087</v>
       </c>
       <c r="E460" t="n">
-        <v>3.747992991930488</v>
+        <v>3.747993229745477</v>
       </c>
       <c r="F460" t="n">
         <v>19382700</v>
@@ -9652,16 +9652,16 @@
         <v>45089</v>
       </c>
       <c r="B462" t="n">
-        <v>3.795556306838989</v>
+        <v>3.795556545257568</v>
       </c>
       <c r="C462" t="n">
-        <v>3.805068970192479</v>
+        <v>3.805069209208598</v>
       </c>
       <c r="D462" t="n">
-        <v>3.74799299007154</v>
+        <v>3.747993225502421</v>
       </c>
       <c r="E462" t="n">
-        <v>3.786043643485499</v>
+        <v>3.786043881306539</v>
       </c>
       <c r="F462" t="n">
         <v>16242400</v>
@@ -9672,16 +9672,16 @@
         <v>45090</v>
       </c>
       <c r="B463" t="n">
-        <v>3.700429677963257</v>
+        <v>3.700429916381836</v>
       </c>
       <c r="C463" t="n">
-        <v>3.814581865148647</v>
+        <v>3.814582110922048</v>
       </c>
       <c r="D463" t="n">
-        <v>3.662378797701604</v>
+        <v>3.662379033668566</v>
       </c>
       <c r="E463" t="n">
-        <v>3.78604364825246</v>
+        <v>3.786043892187145</v>
       </c>
       <c r="F463" t="n">
         <v>19986600</v>
@@ -9692,16 +9692,16 @@
         <v>45091</v>
       </c>
       <c r="B464" t="n">
-        <v>3.747992992401123</v>
+        <v>3.747993230819702</v>
       </c>
       <c r="C464" t="n">
-        <v>3.795556309198135</v>
+        <v>3.795556550642328</v>
       </c>
       <c r="D464" t="n">
-        <v>3.662378795366716</v>
+        <v>3.662379028339177</v>
       </c>
       <c r="E464" t="n">
-        <v>3.709942338963513</v>
+        <v>3.709942574961601</v>
       </c>
       <c r="F464" t="n">
         <v>25840400</v>
@@ -9712,16 +9712,16 @@
         <v>45092</v>
       </c>
       <c r="B465" t="n">
-        <v>3.757505655288696</v>
+        <v>3.757505893707275</v>
       </c>
       <c r="C465" t="n">
-        <v>3.795556308721528</v>
+        <v>3.79555654955447</v>
       </c>
       <c r="D465" t="n">
-        <v>3.719455001855864</v>
+        <v>3.71945523786008</v>
       </c>
       <c r="E465" t="n">
-        <v>3.757505655288696</v>
+        <v>3.757505893707275</v>
       </c>
       <c r="F465" t="n">
         <v>13781200</v>
@@ -9732,16 +9732,16 @@
         <v>45093</v>
       </c>
       <c r="B466" t="n">
-        <v>3.757505655288696</v>
+        <v>3.757505893707275</v>
       </c>
       <c r="C466" t="n">
-        <v>3.776530982005112</v>
+        <v>3.776531221630873</v>
       </c>
       <c r="D466" t="n">
-        <v>3.709942338497656</v>
+        <v>3.709942573898282</v>
       </c>
       <c r="E466" t="n">
-        <v>3.728967665214073</v>
+        <v>3.728967901821879</v>
       </c>
       <c r="F466" t="n">
         <v>14449100</v>
@@ -9752,16 +9752,16 @@
         <v>45096</v>
       </c>
       <c r="B467" t="n">
-        <v>3.776530742645264</v>
+        <v>3.776530981063843</v>
       </c>
       <c r="C467" t="n">
-        <v>3.814581620466182</v>
+        <v>3.814581861286975</v>
       </c>
       <c r="D467" t="n">
-        <v>3.738480091624116</v>
+        <v>3.738480327640495</v>
       </c>
       <c r="E467" t="n">
-        <v>3.786043405400551</v>
+        <v>3.78604364441968</v>
       </c>
       <c r="F467" t="n">
         <v>9550900</v>
@@ -9792,16 +9792,16 @@
         <v>45098</v>
       </c>
       <c r="B469" t="n">
-        <v>4.023859977722168</v>
+        <v>4.023860454559326</v>
       </c>
       <c r="C469" t="n">
-        <v>4.042885302176666</v>
+        <v>4.042885781268371</v>
       </c>
       <c r="D469" t="n">
-        <v>3.900195141968175</v>
+        <v>3.90019560415075</v>
       </c>
       <c r="E469" t="n">
-        <v>3.966784004358674</v>
+        <v>3.966784474432191</v>
       </c>
       <c r="F469" t="n">
         <v>23935400</v>
@@ -9852,16 +9852,16 @@
         <v>45103</v>
       </c>
       <c r="B472" t="n">
-        <v>4.204601764678955</v>
+        <v>4.204601287841797</v>
       </c>
       <c r="C472" t="n">
-        <v>4.280703080195378</v>
+        <v>4.280702594727692</v>
       </c>
       <c r="D472" t="n">
-        <v>4.128500449162532</v>
+        <v>4.128499980955902</v>
       </c>
       <c r="E472" t="n">
-        <v>4.138012886802275</v>
+        <v>4.138012417516855</v>
       </c>
       <c r="F472" t="n">
         <v>42881900</v>
@@ -9872,16 +9872,16 @@
         <v>45104</v>
       </c>
       <c r="B473" t="n">
-        <v>4.223626136779785</v>
+        <v>4.223626613616943</v>
       </c>
       <c r="C473" t="n">
-        <v>4.290214999572086</v>
+        <v>4.290215483926966</v>
       </c>
       <c r="D473" t="n">
-        <v>4.080935975710292</v>
+        <v>4.080936436438077</v>
       </c>
       <c r="E473" t="n">
-        <v>4.233138572264675</v>
+        <v>4.233139050175764</v>
       </c>
       <c r="F473" t="n">
         <v>76576700</v>
@@ -9892,16 +9892,16 @@
         <v>45105</v>
       </c>
       <c r="B474" t="n">
-        <v>4.176063060760498</v>
+        <v>4.176063537597656</v>
       </c>
       <c r="C474" t="n">
-        <v>4.261677257597817</v>
+        <v>4.261677744210696</v>
       </c>
       <c r="D474" t="n">
-        <v>4.090449317522748</v>
+        <v>4.090449784584236</v>
       </c>
       <c r="E474" t="n">
-        <v>4.223626604247801</v>
+        <v>4.223627086515927</v>
       </c>
       <c r="F474" t="n">
         <v>30177100</v>
@@ -9912,16 +9912,16 @@
         <v>45106</v>
       </c>
       <c r="B475" t="n">
-        <v>4.366317272186279</v>
+        <v>4.366316318511963</v>
       </c>
       <c r="C475" t="n">
-        <v>4.366317272186279</v>
+        <v>4.366316318511963</v>
       </c>
       <c r="D475" t="n">
-        <v>4.185576421646147</v>
+        <v>4.185575507448556</v>
       </c>
       <c r="E475" t="n">
-        <v>4.185576421646147</v>
+        <v>4.185575507448556</v>
       </c>
       <c r="F475" t="n">
         <v>40765500</v>
@@ -9932,16 +9932,16 @@
         <v>45107</v>
       </c>
       <c r="B476" t="n">
-        <v>4.185575485229492</v>
+        <v>4.18557596206665</v>
       </c>
       <c r="C476" t="n">
-        <v>4.489980678162862</v>
+        <v>4.489981189679052</v>
       </c>
       <c r="D476" t="n">
-        <v>4.138011947033895</v>
+        <v>4.138012418452428</v>
       </c>
       <c r="E476" t="n">
-        <v>4.41387937992952</v>
+        <v>4.413879882775952</v>
       </c>
       <c r="F476" t="n">
         <v>35419200</v>
@@ -9992,16 +9992,16 @@
         <v>45112</v>
       </c>
       <c r="B479" t="n">
-        <v>4.080936431884766</v>
+        <v>4.080936908721924</v>
       </c>
       <c r="C479" t="n">
-        <v>4.185575955512459</v>
+        <v>4.185576444576225</v>
       </c>
       <c r="D479" t="n">
-        <v>4.023860451796815</v>
+        <v>4.023860921964928</v>
       </c>
       <c r="E479" t="n">
-        <v>4.166550628816475</v>
+        <v>4.166551115657227</v>
       </c>
       <c r="F479" t="n">
         <v>33346200</v>
@@ -10092,16 +10092,16 @@
         <v>45119</v>
       </c>
       <c r="B484" t="n">
-        <v>4.014348030090332</v>
+        <v>4.014347553253174</v>
       </c>
       <c r="C484" t="n">
-        <v>4.128500457186447</v>
+        <v>4.128499966789897</v>
       </c>
       <c r="D484" t="n">
-        <v>4.004835592432102</v>
+        <v>4.004835116724861</v>
       </c>
       <c r="E484" t="n">
-        <v>4.090449799354283</v>
+        <v>4.090449313477511</v>
       </c>
       <c r="F484" t="n">
         <v>6157400</v>
@@ -10132,16 +10132,16 @@
         <v>45121</v>
       </c>
       <c r="B486" t="n">
-        <v>3.881170272827148</v>
+        <v>3.881170511245728</v>
       </c>
       <c r="C486" t="n">
-        <v>4.01434755963212</v>
+        <v>4.014347806231721</v>
       </c>
       <c r="D486" t="n">
-        <v>3.814581856224446</v>
+        <v>3.814582090552529</v>
       </c>
       <c r="E486" t="n">
-        <v>3.995322232945695</v>
+        <v>3.995322478376579</v>
       </c>
       <c r="F486" t="n">
         <v>16845900</v>
@@ -10152,16 +10152,16 @@
         <v>45124</v>
       </c>
       <c r="B487" t="n">
-        <v>4.023859977722168</v>
+        <v>4.023860454559326</v>
       </c>
       <c r="C487" t="n">
-        <v>4.042885302176666</v>
+        <v>4.042885781268371</v>
       </c>
       <c r="D487" t="n">
-        <v>3.852632057631688</v>
+        <v>3.852632514177922</v>
       </c>
       <c r="E487" t="n">
-        <v>3.881169817513677</v>
+        <v>3.881170277441705</v>
       </c>
       <c r="F487" t="n">
         <v>20863600</v>
@@ -10172,16 +10172,16 @@
         <v>45125</v>
       </c>
       <c r="B488" t="n">
-        <v>4.07142448425293</v>
+        <v>4.071424007415771</v>
       </c>
       <c r="C488" t="n">
-        <v>4.185576458136752</v>
+        <v>4.185575967930341</v>
       </c>
       <c r="D488" t="n">
-        <v>4.004835606020889</v>
+        <v>4.004835136982487</v>
       </c>
       <c r="E488" t="n">
-        <v>4.023860935001526</v>
+        <v>4.023860463734916</v>
       </c>
       <c r="F488" t="n">
         <v>19854400</v>
@@ -10252,16 +10252,16 @@
         <v>45131</v>
       </c>
       <c r="B492" t="n">
-        <v>4.023859977722168</v>
+        <v>4.023860454559326</v>
       </c>
       <c r="C492" t="n">
-        <v>4.080935951085661</v>
+        <v>4.080936434686461</v>
       </c>
       <c r="D492" t="n">
-        <v>3.947758679904177</v>
+        <v>3.947759147723147</v>
       </c>
       <c r="E492" t="n">
-        <v>4.061910626631164</v>
+        <v>4.061911107977416</v>
       </c>
       <c r="F492" t="n">
         <v>17283700</v>
@@ -10292,16 +10292,16 @@
         <v>45133</v>
       </c>
       <c r="B494" t="n">
-        <v>4.014348030090332</v>
+        <v>4.014347553253174</v>
       </c>
       <c r="C494" t="n">
-        <v>4.033373359006414</v>
+        <v>4.033372879909367</v>
       </c>
       <c r="D494" t="n">
-        <v>3.957272043342085</v>
+        <v>3.957271573284596</v>
       </c>
       <c r="E494" t="n">
-        <v>3.99532270117425</v>
+        <v>3.995322226596981</v>
       </c>
       <c r="F494" t="n">
         <v>6399600</v>
@@ -10312,16 +10312,16 @@
         <v>45134</v>
       </c>
       <c r="B495" t="n">
-        <v>3.893998622894287</v>
+        <v>3.893998384475708</v>
       </c>
       <c r="C495" t="n">
-        <v>4.056646823940207</v>
+        <v>4.056646575563136</v>
       </c>
       <c r="D495" t="n">
-        <v>3.884430840129649</v>
+        <v>3.884430602296878</v>
       </c>
       <c r="E495" t="n">
-        <v>4.047079497392562</v>
+        <v>4.047079249601271</v>
       </c>
       <c r="F495" t="n">
         <v>18331700</v>
@@ -10352,16 +10352,16 @@
         <v>45138</v>
       </c>
       <c r="B497" t="n">
-        <v>3.980106115341187</v>
+        <v>3.980106353759766</v>
       </c>
       <c r="C497" t="n">
-        <v>4.008809005461245</v>
+        <v>4.008809245599202</v>
       </c>
       <c r="D497" t="n">
-        <v>3.922700791318031</v>
+        <v>3.922701026297883</v>
       </c>
       <c r="E497" t="n">
-        <v>3.941835899325749</v>
+        <v>3.941836135451844</v>
       </c>
       <c r="F497" t="n">
         <v>13989300</v>
@@ -10372,16 +10372,16 @@
         <v>45139</v>
       </c>
       <c r="B498" t="n">
-        <v>3.980106115341187</v>
+        <v>3.980106353759766</v>
       </c>
       <c r="C498" t="n">
-        <v>4.018376331356624</v>
+        <v>4.018376572067687</v>
       </c>
       <c r="D498" t="n">
-        <v>3.884430575302593</v>
+        <v>3.884430807989962</v>
       </c>
       <c r="E498" t="n">
-        <v>3.970538789445808</v>
+        <v>3.970539027291279</v>
       </c>
       <c r="F498" t="n">
         <v>24308900</v>
@@ -10392,16 +10392,16 @@
         <v>45140</v>
       </c>
       <c r="B499" t="n">
-        <v>4.008809089660645</v>
+        <v>4.008808612823486</v>
       </c>
       <c r="C499" t="n">
-        <v>4.018376415756972</v>
+        <v>4.018375937781805</v>
       </c>
       <c r="D499" t="n">
-        <v>3.932268656022146</v>
+        <v>3.932268188289268</v>
       </c>
       <c r="E499" t="n">
-        <v>3.95140376443177</v>
+        <v>3.951403294422822</v>
       </c>
       <c r="F499" t="n">
         <v>25721100</v>
@@ -10432,16 +10432,16 @@
         <v>45142</v>
       </c>
       <c r="B501" t="n">
-        <v>3.903565406799316</v>
+        <v>3.903565883636475</v>
       </c>
       <c r="C501" t="n">
-        <v>3.960970726756138</v>
+        <v>3.960971210605601</v>
       </c>
       <c r="D501" t="n">
-        <v>3.865295193494769</v>
+        <v>3.865295665657057</v>
       </c>
       <c r="E501" t="n">
-        <v>3.903565406799316</v>
+        <v>3.903565883636475</v>
       </c>
       <c r="F501" t="n">
         <v>16409800</v>
@@ -10552,16 +10552,16 @@
         <v>45152</v>
       </c>
       <c r="B507" t="n">
-        <v>3.606971263885498</v>
+        <v>3.606971502304077</v>
       </c>
       <c r="C507" t="n">
-        <v>3.664376587634967</v>
+        <v>3.664376829848003</v>
       </c>
       <c r="D507" t="n">
-        <v>3.568701048052518</v>
+        <v>3.56870128394146</v>
       </c>
       <c r="E507" t="n">
-        <v>3.664376587634967</v>
+        <v>3.664376829848003</v>
       </c>
       <c r="F507" t="n">
         <v>20072900</v>
@@ -10632,16 +10632,16 @@
         <v>45156</v>
       </c>
       <c r="B511" t="n">
-        <v>3.434755086898804</v>
+        <v>3.434755325317383</v>
       </c>
       <c r="C511" t="n">
-        <v>3.473025531089514</v>
+        <v>3.473025772164581</v>
       </c>
       <c r="D511" t="n">
-        <v>3.339079546693231</v>
+        <v>3.33907977847063</v>
       </c>
       <c r="E511" t="n">
-        <v>3.358214654734345</v>
+        <v>3.35821488783998</v>
       </c>
       <c r="F511" t="n">
         <v>15864700</v>
@@ -10692,16 +10692,16 @@
         <v>45161</v>
       </c>
       <c r="B514" t="n">
-        <v>3.453890085220337</v>
+        <v>3.453890323638916</v>
       </c>
       <c r="C514" t="n">
-        <v>3.559133404211688</v>
+        <v>3.559133649895108</v>
       </c>
       <c r="D514" t="n">
-        <v>3.377349655487335</v>
+        <v>3.377349888622405</v>
       </c>
       <c r="E514" t="n">
-        <v>3.396484762920585</v>
+        <v>3.396484997376533</v>
       </c>
       <c r="F514" t="n">
         <v>43718400</v>
@@ -10712,16 +10712,16 @@
         <v>45162</v>
       </c>
       <c r="B515" t="n">
-        <v>3.568701505661011</v>
+        <v>3.568701267242432</v>
       </c>
       <c r="C515" t="n">
-        <v>3.645241947141619</v>
+        <v>3.64524170360951</v>
       </c>
       <c r="D515" t="n">
-        <v>3.444323060146513</v>
+        <v>3.444322830037436</v>
       </c>
       <c r="E515" t="n">
-        <v>3.453890615331589</v>
+        <v>3.453890384583321</v>
       </c>
       <c r="F515" t="n">
         <v>42127000</v>
@@ -10772,16 +10772,16 @@
         <v>45167</v>
       </c>
       <c r="B518" t="n">
-        <v>3.654809236526489</v>
+        <v>3.65480899810791</v>
       </c>
       <c r="C518" t="n">
-        <v>3.664376791015754</v>
+        <v>3.664376551973043</v>
       </c>
       <c r="D518" t="n">
-        <v>3.578268800612372</v>
+        <v>3.578268567186847</v>
       </c>
       <c r="E518" t="n">
-        <v>3.61653901856943</v>
+        <v>3.616538782647379</v>
       </c>
       <c r="F518" t="n">
         <v>13520200</v>
@@ -10912,16 +10912,16 @@
         <v>45177</v>
       </c>
       <c r="B525" t="n">
-        <v>3.549566030502319</v>
+        <v>3.549566268920898</v>
       </c>
       <c r="C525" t="n">
-        <v>3.587836247309597</v>
+        <v>3.587836488298725</v>
       </c>
       <c r="D525" t="n">
-        <v>3.511295813695041</v>
+        <v>3.511296049543073</v>
       </c>
       <c r="E525" t="n">
-        <v>3.53043092209868</v>
+        <v>3.530431159231985</v>
       </c>
       <c r="F525" t="n">
         <v>26042800</v>
@@ -10952,16 +10952,16 @@
         <v>45181</v>
       </c>
       <c r="B527" t="n">
-        <v>3.712214946746826</v>
+        <v>3.712214708328247</v>
       </c>
       <c r="C527" t="n">
-        <v>3.769620276082045</v>
+        <v>3.769620033976584</v>
       </c>
       <c r="D527" t="n">
-        <v>3.616539169746294</v>
+        <v>3.616538937472532</v>
       </c>
       <c r="E527" t="n">
-        <v>3.6356742795247</v>
+        <v>3.635674046021977</v>
       </c>
       <c r="F527" t="n">
         <v>15715300</v>
@@ -10972,16 +10972,16 @@
         <v>45182</v>
       </c>
       <c r="B528" t="n">
-        <v>3.769619941711426</v>
+        <v>3.769620180130005</v>
       </c>
       <c r="C528" t="n">
-        <v>3.846160374035806</v>
+        <v>3.846160617295367</v>
       </c>
       <c r="D528" t="n">
-        <v>3.712214617468141</v>
+        <v>3.712214852255983</v>
       </c>
       <c r="E528" t="n">
-        <v>3.712214617468141</v>
+        <v>3.712214852255983</v>
       </c>
       <c r="F528" t="n">
         <v>17575000</v>
@@ -11012,16 +11012,16 @@
         <v>45184</v>
       </c>
       <c r="B530" t="n">
-        <v>3.80789041519165</v>
+        <v>3.807890176773071</v>
       </c>
       <c r="C530" t="n">
-        <v>3.941836180810695</v>
+        <v>3.941835934005541</v>
       </c>
       <c r="D530" t="n">
-        <v>3.788755305817501</v>
+        <v>3.788755068597004</v>
       </c>
       <c r="E530" t="n">
-        <v>3.788755305817501</v>
+        <v>3.788755068597004</v>
       </c>
       <c r="F530" t="n">
         <v>34682000</v>
@@ -11032,16 +11032,16 @@
         <v>45187</v>
       </c>
       <c r="B531" t="n">
-        <v>3.817457675933838</v>
+        <v>3.817457914352417</v>
       </c>
       <c r="C531" t="n">
-        <v>3.884430553586438</v>
+        <v>3.884430796187795</v>
       </c>
       <c r="D531" t="n">
-        <v>3.740917244330867</v>
+        <v>3.740917477969129</v>
       </c>
       <c r="E531" t="n">
-        <v>3.817457675933838</v>
+        <v>3.817457914352417</v>
       </c>
       <c r="F531" t="n">
         <v>23371600</v>
@@ -11112,16 +11112,16 @@
         <v>45191</v>
       </c>
       <c r="B535" t="n">
-        <v>3.606971263885498</v>
+        <v>3.606971502304077</v>
       </c>
       <c r="C535" t="n">
-        <v>3.664376587634967</v>
+        <v>3.664376829848003</v>
       </c>
       <c r="D535" t="n">
-        <v>3.559133494094274</v>
+        <v>3.559133729350806</v>
       </c>
       <c r="E535" t="n">
-        <v>3.597403709927253</v>
+        <v>3.597403947713423</v>
       </c>
       <c r="F535" t="n">
         <v>21984900</v>
@@ -11172,16 +11172,16 @@
         <v>45196</v>
       </c>
       <c r="B538" t="n">
-        <v>3.396485090255737</v>
+        <v>3.396484851837158</v>
       </c>
       <c r="C538" t="n">
-        <v>3.492160864751185</v>
+        <v>3.49216061961658</v>
       </c>
       <c r="D538" t="n">
-        <v>3.358214871700957</v>
+        <v>3.358214635968781</v>
       </c>
       <c r="E538" t="n">
-        <v>3.453890418087908</v>
+        <v>3.453890175639724</v>
       </c>
       <c r="F538" t="n">
         <v>21389800</v>
@@ -11192,16 +11192,16 @@
         <v>45197</v>
       </c>
       <c r="B539" t="n">
-        <v>3.41562032699585</v>
+        <v>3.415620088577271</v>
       </c>
       <c r="C539" t="n">
-        <v>3.444322991983049</v>
+        <v>3.444322751560954</v>
       </c>
       <c r="D539" t="n">
-        <v>3.32951233203425</v>
+        <v>3.329512099626217</v>
       </c>
       <c r="E539" t="n">
-        <v>3.41562032699585</v>
+        <v>3.415620088577271</v>
       </c>
       <c r="F539" t="n">
         <v>16733500</v>
@@ -11212,16 +11212,16 @@
         <v>45198</v>
       </c>
       <c r="B540" t="n">
-        <v>3.425187349319458</v>
+        <v>3.425187587738037</v>
       </c>
       <c r="C540" t="n">
-        <v>3.492160451982693</v>
+        <v>3.492160695063099</v>
       </c>
       <c r="D540" t="n">
-        <v>3.386917135288163</v>
+        <v>3.38691737104285</v>
       </c>
       <c r="E540" t="n">
-        <v>3.463457563350753</v>
+        <v>3.463457804433224</v>
       </c>
       <c r="F540" t="n">
         <v>13661300</v>
@@ -11252,16 +11252,16 @@
         <v>45202</v>
       </c>
       <c r="B542" t="n">
-        <v>3.310376882553101</v>
+        <v>3.31037712097168</v>
       </c>
       <c r="C542" t="n">
-        <v>3.406052422698603</v>
+        <v>3.406052668007885</v>
       </c>
       <c r="D542" t="n">
-        <v>3.2721066664949</v>
+        <v>3.272106902157197</v>
       </c>
       <c r="E542" t="n">
-        <v>3.31994443656765</v>
+        <v>3.3199446756753</v>
       </c>
       <c r="F542" t="n">
         <v>29291500</v>
@@ -11292,16 +11292,16 @@
         <v>45204</v>
       </c>
       <c r="B544" t="n">
-        <v>3.233836650848389</v>
+        <v>3.23383641242981</v>
       </c>
       <c r="C544" t="n">
-        <v>3.358214860745675</v>
+        <v>3.35821461315716</v>
       </c>
       <c r="D544" t="n">
-        <v>3.205133758917443</v>
+        <v>3.20513352261502</v>
       </c>
       <c r="E544" t="n">
-        <v>3.310377087708257</v>
+        <v>3.310376843646641</v>
       </c>
       <c r="F544" t="n">
         <v>37198300</v>
@@ -11312,16 +11312,16 @@
         <v>45205</v>
       </c>
       <c r="B545" t="n">
-        <v>3.233836650848389</v>
+        <v>3.23383641242981</v>
       </c>
       <c r="C545" t="n">
-        <v>3.262539314670839</v>
+        <v>3.262539074136121</v>
       </c>
       <c r="D545" t="n">
-        <v>3.138160876665057</v>
+        <v>3.138160645300292</v>
       </c>
       <c r="E545" t="n">
-        <v>3.205133758917443</v>
+        <v>3.20513352261502</v>
       </c>
       <c r="F545" t="n">
         <v>15875400</v>
@@ -11352,16 +11352,16 @@
         <v>45209</v>
       </c>
       <c r="B547" t="n">
-        <v>3.41562032699585</v>
+        <v>3.415620088577271</v>
       </c>
       <c r="C547" t="n">
-        <v>3.425187881991583</v>
+        <v>3.425187642905165</v>
       </c>
       <c r="D547" t="n">
-        <v>3.348647442025716</v>
+        <v>3.348647208282007</v>
       </c>
       <c r="E547" t="n">
-        <v>3.367782552017183</v>
+        <v>3.367782316937797</v>
       </c>
       <c r="F547" t="n">
         <v>9595500</v>
@@ -11372,16 +11372,16 @@
         <v>45210</v>
       </c>
       <c r="B548" t="n">
-        <v>3.482593297958374</v>
+        <v>3.482593059539795</v>
       </c>
       <c r="C548" t="n">
-        <v>3.511295961774288</v>
+        <v>3.511295721390723</v>
       </c>
       <c r="D548" t="n">
-        <v>3.396485078402136</v>
+        <v>3.396484845878531</v>
       </c>
       <c r="E548" t="n">
-        <v>3.415620187612745</v>
+        <v>3.41561995377915</v>
       </c>
       <c r="F548" t="n">
         <v>15610900</v>
@@ -11412,16 +11412,16 @@
         <v>45215</v>
       </c>
       <c r="B550" t="n">
-        <v>3.386917591094971</v>
+        <v>3.386917352676392</v>
       </c>
       <c r="C550" t="n">
-        <v>3.434755365072033</v>
+        <v>3.434755123285962</v>
       </c>
       <c r="D550" t="n">
-        <v>3.348647371913321</v>
+        <v>3.348647136188735</v>
       </c>
       <c r="E550" t="n">
-        <v>3.377350036299558</v>
+        <v>3.377349798554477</v>
       </c>
       <c r="F550" t="n">
         <v>12135900</v>
@@ -11472,16 +11472,16 @@
         <v>45218</v>
       </c>
       <c r="B553" t="n">
-        <v>3.42021107673645</v>
+        <v>3.420210838317871</v>
       </c>
       <c r="C553" t="n">
-        <v>3.449114241758219</v>
+        <v>3.449114001324837</v>
       </c>
       <c r="D553" t="n">
-        <v>3.304598416649374</v>
+        <v>3.304598186290007</v>
       </c>
       <c r="E553" t="n">
-        <v>3.314232804989964</v>
+        <v>3.314232573958996</v>
       </c>
       <c r="F553" t="n">
         <v>35125300</v>
@@ -11492,16 +11492,16 @@
         <v>45219</v>
       </c>
       <c r="B554" t="n">
-        <v>3.449113845825195</v>
+        <v>3.449114084243774</v>
       </c>
       <c r="C554" t="n">
-        <v>3.478017007529093</v>
+        <v>3.478017247945591</v>
       </c>
       <c r="D554" t="n">
-        <v>3.381673135182768</v>
+        <v>3.381673368939535</v>
       </c>
       <c r="E554" t="n">
-        <v>3.381673135182768</v>
+        <v>3.381673368939535</v>
       </c>
       <c r="F554" t="n">
         <v>22281100</v>
@@ -11532,16 +11532,16 @@
         <v>45223</v>
       </c>
       <c r="B556" t="n">
-        <v>3.612898826599121</v>
+        <v>3.6128990650177</v>
       </c>
       <c r="C556" t="n">
-        <v>3.632167601964829</v>
+        <v>3.632167841654973</v>
       </c>
       <c r="D556" t="n">
-        <v>3.487651557020096</v>
+        <v>3.48765178717349</v>
       </c>
       <c r="E556" t="n">
-        <v>3.497286174404871</v>
+        <v>3.497286405194064</v>
       </c>
       <c r="F556" t="n">
         <v>18123000</v>
@@ -11552,16 +11552,16 @@
         <v>45224</v>
       </c>
       <c r="B557" t="n">
-        <v>3.593630313873291</v>
+        <v>3.593630075454712</v>
       </c>
       <c r="C557" t="n">
-        <v>3.738146369379956</v>
+        <v>3.738146121373493</v>
       </c>
       <c r="D557" t="n">
-        <v>3.545458371938382</v>
+        <v>3.545458136715759</v>
       </c>
       <c r="E557" t="n">
-        <v>3.6418022558082</v>
+        <v>3.641802014193664</v>
       </c>
       <c r="F557" t="n">
         <v>23871300</v>
@@ -11572,16 +11572,16 @@
         <v>45225</v>
       </c>
       <c r="B558" t="n">
-        <v>3.651436328887939</v>
+        <v>3.651436567306519</v>
       </c>
       <c r="C558" t="n">
-        <v>3.670705103998014</v>
+        <v>3.670705343674738</v>
       </c>
       <c r="D558" t="n">
-        <v>3.545458065782528</v>
+        <v>3.545458297281314</v>
       </c>
       <c r="E558" t="n">
-        <v>3.593630003557715</v>
+        <v>3.593630238201861</v>
       </c>
       <c r="F558" t="n">
         <v>21310400</v>
@@ -11632,16 +11632,16 @@
         <v>45230</v>
       </c>
       <c r="B561" t="n">
-        <v>3.497286081314087</v>
+        <v>3.497286319732666</v>
       </c>
       <c r="C561" t="n">
-        <v>3.516554856166899</v>
+        <v>3.516555095899078</v>
       </c>
       <c r="D561" t="n">
-        <v>3.420210752200924</v>
+        <v>3.420210985365089</v>
       </c>
       <c r="E561" t="n">
-        <v>3.506920468740493</v>
+        <v>3.506920707815872</v>
       </c>
       <c r="F561" t="n">
         <v>11282600</v>
@@ -11652,16 +11652,16 @@
         <v>45231</v>
       </c>
       <c r="B562" t="n">
-        <v>3.612898826599121</v>
+        <v>3.6128990650177</v>
       </c>
       <c r="C562" t="n">
-        <v>3.612898826599121</v>
+        <v>3.6128990650177</v>
       </c>
       <c r="D562" t="n">
-        <v>3.506920562087725</v>
+        <v>3.5069207935127</v>
       </c>
       <c r="E562" t="n">
-        <v>3.506920562087725</v>
+        <v>3.5069207935127</v>
       </c>
       <c r="F562" t="n">
         <v>18109500</v>
@@ -11672,16 +11672,16 @@
         <v>45233</v>
       </c>
       <c r="B563" t="n">
-        <v>3.651436328887939</v>
+        <v>3.651436567306519</v>
       </c>
       <c r="C563" t="n">
-        <v>3.709242654218164</v>
+        <v>3.709242896411176</v>
       </c>
       <c r="D563" t="n">
-        <v>3.61289877866779</v>
+        <v>3.61289901457008</v>
       </c>
       <c r="E563" t="n">
-        <v>3.661070716442977</v>
+        <v>3.661070955490628</v>
       </c>
       <c r="F563" t="n">
         <v>16239100</v>
@@ -11692,16 +11692,16 @@
         <v>45236</v>
       </c>
       <c r="B564" t="n">
-        <v>3.651436328887939</v>
+        <v>3.651436567306519</v>
       </c>
       <c r="C564" t="n">
-        <v>3.699608266663126</v>
+        <v>3.699608508227067</v>
       </c>
       <c r="D564" t="n">
-        <v>3.622533166222827</v>
+        <v>3.62253340275419</v>
       </c>
       <c r="E564" t="n">
-        <v>3.670705103998014</v>
+        <v>3.670705343674738</v>
       </c>
       <c r="F564" t="n">
         <v>9299300</v>
@@ -11892,16 +11892,16 @@
         <v>45251</v>
       </c>
       <c r="B574" t="n">
-        <v>3.506920576095581</v>
+        <v>3.50692081451416</v>
       </c>
       <c r="C574" t="n">
-        <v>3.622533228751628</v>
+        <v>3.622533475030152</v>
       </c>
       <c r="D574" t="n">
-        <v>3.506920576095581</v>
+        <v>3.50692081451416</v>
       </c>
       <c r="E574" t="n">
-        <v>3.612898841030291</v>
+        <v>3.612899086653819</v>
       </c>
       <c r="F574" t="n">
         <v>23500900</v>
@@ -11912,16 +11912,16 @@
         <v>45252</v>
       </c>
       <c r="B575" t="n">
-        <v>3.516555070877075</v>
+        <v>3.516554832458496</v>
       </c>
       <c r="C575" t="n">
-        <v>3.555092622935685</v>
+        <v>3.555092381904302</v>
       </c>
       <c r="D575" t="n">
-        <v>3.497286294847771</v>
+        <v>3.497286057735593</v>
       </c>
       <c r="E575" t="n">
-        <v>3.545458234921032</v>
+        <v>3.545457994542851</v>
       </c>
       <c r="F575" t="n">
         <v>29127900</v>
@@ -11932,16 +11932,16 @@
         <v>45253</v>
       </c>
       <c r="B576" t="n">
-        <v>3.583995819091797</v>
+        <v>3.583995580673218</v>
       </c>
       <c r="C576" t="n">
-        <v>3.583995819091797</v>
+        <v>3.583995580673218</v>
       </c>
       <c r="D576" t="n">
-        <v>3.478017320279137</v>
+        <v>3.478017088910578</v>
       </c>
       <c r="E576" t="n">
-        <v>3.506920714283994</v>
+        <v>3.506920480992691</v>
       </c>
       <c r="F576" t="n">
         <v>15777100</v>
@@ -11972,16 +11972,16 @@
         <v>45257</v>
       </c>
       <c r="B578" t="n">
-        <v>3.42021107673645</v>
+        <v>3.420210838317871</v>
       </c>
       <c r="C578" t="n">
-        <v>3.63216784993136</v>
+        <v>3.632167596737543</v>
       </c>
       <c r="D578" t="n">
-        <v>3.410576688395861</v>
+        <v>3.410576450648882</v>
       </c>
       <c r="E578" t="n">
-        <v>3.603264684909591</v>
+        <v>3.603264433730577</v>
       </c>
       <c r="F578" t="n">
         <v>29619500</v>
@@ -11992,16 +11992,16 @@
         <v>45258</v>
       </c>
       <c r="B579" t="n">
-        <v>3.497286081314087</v>
+        <v>3.497286319732666</v>
       </c>
       <c r="C579" t="n">
-        <v>3.497286081314087</v>
+        <v>3.497286319732666</v>
       </c>
       <c r="D579" t="n">
-        <v>3.3816732024953</v>
+        <v>3.381673433032266</v>
       </c>
       <c r="E579" t="n">
-        <v>3.420210752200924</v>
+        <v>3.420210985365089</v>
       </c>
       <c r="F579" t="n">
         <v>15991300</v>
@@ -12032,16 +12032,16 @@
         <v>45260</v>
       </c>
       <c r="B581" t="n">
-        <v>3.516555070877075</v>
+        <v>3.516554832458496</v>
       </c>
       <c r="C581" t="n">
-        <v>3.564727010950338</v>
+        <v>3.564726769265754</v>
       </c>
       <c r="D581" t="n">
-        <v>3.468382901101884</v>
+        <v>3.468382665949325</v>
       </c>
       <c r="E581" t="n">
-        <v>3.555092622935685</v>
+        <v>3.555092381904302</v>
       </c>
       <c r="F581" t="n">
         <v>22087700</v>
@@ -12152,16 +12152,16 @@
         <v>45268</v>
       </c>
       <c r="B587" t="n">
-        <v>3.506920576095581</v>
+        <v>3.50692081451416</v>
       </c>
       <c r="C587" t="n">
-        <v>3.555092514702267</v>
+        <v>3.555092756395823</v>
       </c>
       <c r="D587" t="n">
-        <v>3.439479632344298</v>
+        <v>3.439479866177894</v>
       </c>
       <c r="E587" t="n">
-        <v>3.54545812698093</v>
+        <v>3.545458368019491</v>
       </c>
       <c r="F587" t="n">
         <v>14112100</v>
@@ -12232,16 +12232,16 @@
         <v>45274</v>
       </c>
       <c r="B591" t="n">
-        <v>3.516555070877075</v>
+        <v>3.516554832458496</v>
       </c>
       <c r="C591" t="n">
-        <v>3.805586941018577</v>
+        <v>3.805586683003954</v>
       </c>
       <c r="D591" t="n">
-        <v>3.487651677131189</v>
+        <v>3.487651440672228</v>
       </c>
       <c r="E591" t="n">
-        <v>3.487651677131189</v>
+        <v>3.487651440672228</v>
       </c>
       <c r="F591" t="n">
         <v>64134600</v>
@@ -12252,16 +12252,16 @@
         <v>45275</v>
       </c>
       <c r="B592" t="n">
-        <v>3.593630313873291</v>
+        <v>3.593630075454712</v>
       </c>
       <c r="C592" t="n">
-        <v>3.6418022558082</v>
+        <v>3.641802014193664</v>
       </c>
       <c r="D592" t="n">
-        <v>3.497286430003473</v>
+        <v>3.497286197976806</v>
       </c>
       <c r="E592" t="n">
-        <v>3.564727148712346</v>
+        <v>3.56472691221134</v>
       </c>
       <c r="F592" t="n">
         <v>53571000</v>
@@ -12312,16 +12312,16 @@
         <v>45280</v>
       </c>
       <c r="B595" t="n">
-        <v>3.873027801513672</v>
+        <v>3.873027563095093</v>
       </c>
       <c r="C595" t="n">
-        <v>3.892296578261347</v>
+        <v>3.892296338656607</v>
       </c>
       <c r="D595" t="n">
-        <v>3.76704952940146</v>
+        <v>3.767049297506766</v>
       </c>
       <c r="E595" t="n">
-        <v>3.834490248018322</v>
+        <v>3.834490011972065</v>
       </c>
       <c r="F595" t="n">
         <v>18861600</v>
@@ -26072,19 +26072,39 @@
         <v>46288</v>
       </c>
       <c r="B1283" t="n">
-        <v>0.28</v>
+        <v>0.2800000011920929</v>
       </c>
       <c r="C1283" t="n">
-        <v>0.29</v>
+        <v>0.2899999916553497</v>
       </c>
       <c r="D1283" t="n">
-        <v>0.27</v>
+        <v>0.2700000107288361</v>
       </c>
       <c r="E1283" t="n">
-        <v>0.27</v>
+        <v>0.2700000107288361</v>
       </c>
       <c r="F1283" t="n">
         <v>15257900</v>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B1284" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="C1284" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="D1284" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E1284" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F1284" t="n">
+        <v>8311500</v>
       </c>
     </row>
   </sheetData>

--- a/database/RAIZ4.xlsx
+++ b/database/RAIZ4.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1284"/>
+  <dimension ref="A1:F1285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44413</v>
       </c>
       <c r="B2" t="n">
-        <v>6.384481906890869</v>
+        <v>6.384480953216553</v>
       </c>
       <c r="C2" t="n">
-        <v>6.701942460974013</v>
+        <v>6.701941459879408</v>
       </c>
       <c r="D2" t="n">
-        <v>6.331571884625592</v>
+        <v>6.331570938854646</v>
       </c>
       <c r="E2" t="n">
-        <v>6.596122416443459</v>
+        <v>6.596121431155595</v>
       </c>
       <c r="F2" t="n">
         <v>98849900</v>
@@ -472,16 +472,16 @@
         <v>44414</v>
       </c>
       <c r="B3" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="C3" t="n">
-        <v>6.481483579964149</v>
+        <v>6.48148308633695</v>
       </c>
       <c r="D3" t="n">
-        <v>6.199296805201136</v>
+        <v>6.19929633306517</v>
       </c>
       <c r="E3" t="n">
-        <v>6.393300212850708</v>
+        <v>6.393299725939519</v>
       </c>
       <c r="F3" t="n">
         <v>28799900</v>
@@ -492,16 +492,16 @@
         <v>44417</v>
       </c>
       <c r="B4" t="n">
-        <v>6.234570026397705</v>
+        <v>6.234569549560547</v>
       </c>
       <c r="C4" t="n">
-        <v>6.446210103204662</v>
+        <v>6.446209610180686</v>
       </c>
       <c r="D4" t="n">
-        <v>6.234570026397705</v>
+        <v>6.234569549560547</v>
       </c>
       <c r="E4" t="n">
-        <v>6.331571518021834</v>
+        <v>6.331571033765733</v>
       </c>
       <c r="F4" t="n">
         <v>14491100</v>
@@ -512,16 +512,16 @@
         <v>44418</v>
       </c>
       <c r="B5" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="C5" t="n">
-        <v>6.313934972202879</v>
+        <v>6.313934491336116</v>
       </c>
       <c r="D5" t="n">
-        <v>6.216933478623825</v>
+        <v>6.216933005144656</v>
       </c>
       <c r="E5" t="n">
-        <v>6.278661625357502</v>
+        <v>6.278661147177143</v>
       </c>
       <c r="F5" t="n">
         <v>9988600</v>
@@ -532,16 +532,16 @@
         <v>44419</v>
       </c>
       <c r="B6" t="n">
-        <v>6.058202743530273</v>
+        <v>6.058203220367432</v>
       </c>
       <c r="C6" t="n">
-        <v>6.296298035007707</v>
+        <v>6.296298530585189</v>
       </c>
       <c r="D6" t="n">
-        <v>5.996474599382589</v>
+        <v>5.996475071361166</v>
       </c>
       <c r="E6" t="n">
-        <v>6.287479908911514</v>
+        <v>6.287480403794928</v>
       </c>
       <c r="F6" t="n">
         <v>31978000</v>
@@ -552,16 +552,16 @@
         <v>44420</v>
       </c>
       <c r="B7" t="n">
-        <v>6.137567520141602</v>
+        <v>6.137568473815918</v>
       </c>
       <c r="C7" t="n">
-        <v>6.155204191501549</v>
+        <v>6.155205147916306</v>
       </c>
       <c r="D7" t="n">
-        <v>5.952382260616443</v>
+        <v>5.952383185516099</v>
       </c>
       <c r="E7" t="n">
-        <v>6.146385645575868</v>
+        <v>6.146386600620373</v>
       </c>
       <c r="F7" t="n">
         <v>17054100</v>
@@ -572,16 +572,16 @@
         <v>44421</v>
       </c>
       <c r="B8" t="n">
-        <v>6.181660652160645</v>
+        <v>6.181660175323486</v>
       </c>
       <c r="C8" t="n">
-        <v>6.208115454275954</v>
+        <v>6.208114975398141</v>
       </c>
       <c r="D8" t="n">
-        <v>6.049385380109605</v>
+        <v>6.049384913475816</v>
       </c>
       <c r="E8" t="n">
-        <v>6.155205429553837</v>
+        <v>6.155204954757366</v>
       </c>
       <c r="F8" t="n">
         <v>21141500</v>
@@ -592,16 +592,16 @@
         <v>44424</v>
       </c>
       <c r="B9" t="n">
-        <v>6.190477848052979</v>
+        <v>6.190478324890137</v>
       </c>
       <c r="C9" t="n">
-        <v>6.278661209323248</v>
+        <v>6.278661692952952</v>
       </c>
       <c r="D9" t="n">
-        <v>5.978837781004333</v>
+        <v>5.978838241539382</v>
       </c>
       <c r="E9" t="n">
-        <v>6.146385957172127</v>
+        <v>6.146386430612996</v>
       </c>
       <c r="F9" t="n">
         <v>13434600</v>
@@ -692,16 +692,16 @@
         <v>44431</v>
       </c>
       <c r="B14" t="n">
-        <v>6.322753429412842</v>
+        <v>6.322752475738525</v>
       </c>
       <c r="C14" t="n">
-        <v>6.349208228925635</v>
+        <v>6.349207271261085</v>
       </c>
       <c r="D14" t="n">
-        <v>6.181660044034058</v>
+        <v>6.181659111641157</v>
       </c>
       <c r="E14" t="n">
-        <v>6.208114843546852</v>
+        <v>6.208113907163717</v>
       </c>
       <c r="F14" t="n">
         <v>6128800</v>
@@ -752,16 +752,16 @@
         <v>44434</v>
       </c>
       <c r="B17" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="C17" t="n">
-        <v>6.507938800343913</v>
+        <v>6.507938304701895</v>
       </c>
       <c r="D17" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="E17" t="n">
-        <v>6.472665453498537</v>
+        <v>6.472664960542923</v>
       </c>
       <c r="F17" t="n">
         <v>7968100</v>
@@ -772,16 +772,16 @@
         <v>44435</v>
       </c>
       <c r="B18" t="n">
-        <v>6.340390205383301</v>
+        <v>6.340389728546143</v>
       </c>
       <c r="C18" t="n">
-        <v>6.384481678783307</v>
+        <v>6.384481198630192</v>
       </c>
       <c r="D18" t="n">
-        <v>6.278661638033537</v>
+        <v>6.278661165838754</v>
       </c>
       <c r="E18" t="n">
-        <v>6.305116858466711</v>
+        <v>6.305116384282329</v>
       </c>
       <c r="F18" t="n">
         <v>5881000</v>
@@ -792,16 +792,16 @@
         <v>44438</v>
       </c>
       <c r="B19" t="n">
-        <v>6.269844055175781</v>
+        <v>6.269843101501465</v>
       </c>
       <c r="C19" t="n">
-        <v>6.419756002815109</v>
+        <v>6.419755026338443</v>
       </c>
       <c r="D19" t="n">
-        <v>6.252207380188302</v>
+        <v>6.252206429196611</v>
       </c>
       <c r="E19" t="n">
-        <v>6.39330078008814</v>
+        <v>6.393299807635444</v>
       </c>
       <c r="F19" t="n">
         <v>4966000</v>
@@ -812,16 +812,16 @@
         <v>44439</v>
       </c>
       <c r="B20" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="C20" t="n">
-        <v>6.305116845737266</v>
+        <v>6.305116365542087</v>
       </c>
       <c r="D20" t="n">
-        <v>6.181660131778449</v>
+        <v>6.181659660985684</v>
       </c>
       <c r="E20" t="n">
-        <v>6.305116845737266</v>
+        <v>6.305116365542087</v>
       </c>
       <c r="F20" t="n">
         <v>3704100</v>
@@ -832,16 +832,16 @@
         <v>44440</v>
       </c>
       <c r="B21" t="n">
-        <v>6.234570026397705</v>
+        <v>6.234569549560547</v>
       </c>
       <c r="C21" t="n">
-        <v>6.305116718666691</v>
+        <v>6.305116236433927</v>
       </c>
       <c r="D21" t="n">
-        <v>6.199296680263212</v>
+        <v>6.199296206123857</v>
       </c>
       <c r="E21" t="n">
-        <v>6.261024825752847</v>
+        <v>6.261024346892354</v>
       </c>
       <c r="F21" t="n">
         <v>6468600</v>
@@ -852,16 +852,16 @@
         <v>44441</v>
       </c>
       <c r="B22" t="n">
-        <v>5.996474742889404</v>
+        <v>5.996475696563721</v>
       </c>
       <c r="C22" t="n">
-        <v>6.252206713170811</v>
+        <v>6.252207707516526</v>
       </c>
       <c r="D22" t="n">
-        <v>5.970019522984813</v>
+        <v>5.970020472451714</v>
       </c>
       <c r="E22" t="n">
-        <v>6.234570040064902</v>
+        <v>6.234571031605695</v>
       </c>
       <c r="F22" t="n">
         <v>3746900</v>
@@ -872,16 +872,16 @@
         <v>44442</v>
       </c>
       <c r="B23" t="n">
-        <v>6.172840595245361</v>
+        <v>6.17284107208252</v>
       </c>
       <c r="C23" t="n">
-        <v>6.172840595245361</v>
+        <v>6.17284107208252</v>
       </c>
       <c r="D23" t="n">
-        <v>5.934745331962696</v>
+        <v>5.934745790407565</v>
       </c>
       <c r="E23" t="n">
-        <v>6.031747230482714</v>
+        <v>6.031747696420747</v>
       </c>
       <c r="F23" t="n">
         <v>3705400</v>
@@ -912,16 +912,16 @@
         <v>44447</v>
       </c>
       <c r="B25" t="n">
-        <v>5.758378982543945</v>
+        <v>5.758379459381104</v>
       </c>
       <c r="C25" t="n">
-        <v>6.111112416290331</v>
+        <v>6.111112922336476</v>
       </c>
       <c r="D25" t="n">
-        <v>5.661377078017978</v>
+        <v>5.661377546822648</v>
       </c>
       <c r="E25" t="n">
-        <v>6.111112416290331</v>
+        <v>6.111112922336476</v>
       </c>
       <c r="F25" t="n">
         <v>10251100</v>
@@ -952,16 +952,16 @@
         <v>44449</v>
       </c>
       <c r="B27" t="n">
-        <v>5.731924533843994</v>
+        <v>5.731924057006836</v>
       </c>
       <c r="C27" t="n">
-        <v>5.89947314759995</v>
+        <v>5.899472656824471</v>
       </c>
       <c r="D27" t="n">
-        <v>5.617285942249159</v>
+        <v>5.617285474948753</v>
       </c>
       <c r="E27" t="n">
-        <v>5.767197881951408</v>
+        <v>5.76719740217987</v>
       </c>
       <c r="F27" t="n">
         <v>5905500</v>
@@ -972,16 +972,16 @@
         <v>44452</v>
       </c>
       <c r="B28" t="n">
-        <v>6.128748893737793</v>
+        <v>6.128749370574951</v>
       </c>
       <c r="C28" t="n">
-        <v>6.172840781804387</v>
+        <v>6.172841262072042</v>
       </c>
       <c r="D28" t="n">
-        <v>5.925926965515992</v>
+        <v>5.925927426572926</v>
       </c>
       <c r="E28" t="n">
-        <v>5.95238218245423</v>
+        <v>5.952382645569469</v>
       </c>
       <c r="F28" t="n">
         <v>8999600</v>
@@ -992,16 +992,16 @@
         <v>44453</v>
       </c>
       <c r="B29" t="n">
-        <v>6.340390205383301</v>
+        <v>6.340389728546143</v>
       </c>
       <c r="C29" t="n">
-        <v>6.507938813482836</v>
+        <v>6.50793832404497</v>
       </c>
       <c r="D29" t="n">
-        <v>6.225751617658651</v>
+        <v>6.225751149443035</v>
       </c>
       <c r="E29" t="n">
-        <v>6.225751617658651</v>
+        <v>6.225751149443035</v>
       </c>
       <c r="F29" t="n">
         <v>9730300</v>
@@ -1012,16 +1012,16 @@
         <v>44454</v>
       </c>
       <c r="B30" t="n">
-        <v>6.384481906890869</v>
+        <v>6.384480953216553</v>
       </c>
       <c r="C30" t="n">
-        <v>6.507939046001328</v>
+        <v>6.50793807388575</v>
       </c>
       <c r="D30" t="n">
-        <v>6.29629853644874</v>
+        <v>6.296297595946708</v>
       </c>
       <c r="E30" t="n">
-        <v>6.384481906890869</v>
+        <v>6.384480953216553</v>
       </c>
       <c r="F30" t="n">
         <v>7265900</v>
@@ -1032,16 +1032,16 @@
         <v>44455</v>
       </c>
       <c r="B31" t="n">
-        <v>6.278661251068115</v>
+        <v>6.278661727905273</v>
       </c>
       <c r="C31" t="n">
-        <v>6.428573176470008</v>
+        <v>6.428573664692329</v>
       </c>
       <c r="D31" t="n">
-        <v>6.172841216840228</v>
+        <v>6.172841685640813</v>
       </c>
       <c r="E31" t="n">
-        <v>6.349207940553374</v>
+        <v>6.349208422748248</v>
       </c>
       <c r="F31" t="n">
         <v>6142600</v>
@@ -1052,16 +1052,16 @@
         <v>44456</v>
       </c>
       <c r="B32" t="n">
-        <v>6.384481906890869</v>
+        <v>6.384480953216553</v>
       </c>
       <c r="C32" t="n">
-        <v>6.384481906890869</v>
+        <v>6.384480953216553</v>
       </c>
       <c r="D32" t="n">
-        <v>5.978838402857074</v>
+        <v>5.978837509775269</v>
       </c>
       <c r="E32" t="n">
-        <v>6.261025188271888</v>
+        <v>6.26102425303877</v>
       </c>
       <c r="F32" t="n">
         <v>16008100</v>
@@ -1072,16 +1072,16 @@
         <v>44459</v>
       </c>
       <c r="B33" t="n">
-        <v>6.269844055175781</v>
+        <v>6.269843101501465</v>
       </c>
       <c r="C33" t="n">
-        <v>6.32275408013822</v>
+        <v>6.322753118416027</v>
       </c>
       <c r="D33" t="n">
-        <v>6.067022082574015</v>
+        <v>6.067021159749924</v>
       </c>
       <c r="E33" t="n">
-        <v>6.164023584759403</v>
+        <v>6.164022647180904</v>
       </c>
       <c r="F33" t="n">
         <v>9065700</v>
@@ -1092,16 +1092,16 @@
         <v>44460</v>
       </c>
       <c r="B34" t="n">
-        <v>6.419755458831787</v>
+        <v>6.419754981994629</v>
       </c>
       <c r="C34" t="n">
-        <v>6.525575499789916</v>
+        <v>6.525575015092812</v>
       </c>
       <c r="D34" t="n">
-        <v>6.269843523895372</v>
+        <v>6.269843058193152</v>
       </c>
       <c r="E34" t="n">
-        <v>6.349208344368237</v>
+        <v>6.349207872771073</v>
       </c>
       <c r="F34" t="n">
         <v>11102500</v>
@@ -1112,16 +1112,16 @@
         <v>44461</v>
       </c>
       <c r="B35" t="n">
-        <v>6.446210384368896</v>
+        <v>6.446209907531738</v>
       </c>
       <c r="C35" t="n">
-        <v>6.560848974551915</v>
+        <v>6.560848489234745</v>
       </c>
       <c r="D35" t="n">
-        <v>6.40211891002337</v>
+        <v>6.402118436447734</v>
       </c>
       <c r="E35" t="n">
-        <v>6.463847058205402</v>
+        <v>6.463846580063628</v>
       </c>
       <c r="F35" t="n">
         <v>10254600</v>
@@ -1132,16 +1132,16 @@
         <v>44462</v>
       </c>
       <c r="B36" t="n">
-        <v>6.375663280487061</v>
+        <v>6.375663757324219</v>
       </c>
       <c r="C36" t="n">
-        <v>6.543211881443518</v>
+        <v>6.54321237081167</v>
       </c>
       <c r="D36" t="n">
-        <v>6.340389935074274</v>
+        <v>6.340390409273332</v>
       </c>
       <c r="E36" t="n">
-        <v>6.507938536030731</v>
+        <v>6.507939022760783</v>
       </c>
       <c r="F36" t="n">
         <v>6341600</v>
@@ -1152,16 +1152,16 @@
         <v>44463</v>
       </c>
       <c r="B37" t="n">
-        <v>6.172840595245361</v>
+        <v>6.17284107208252</v>
       </c>
       <c r="C37" t="n">
-        <v>6.375662517337365</v>
+        <v>6.375663009842031</v>
       </c>
       <c r="D37" t="n">
-        <v>6.164022049701998</v>
+        <v>6.164022525857945</v>
       </c>
       <c r="E37" t="n">
-        <v>6.340389176146703</v>
+        <v>6.340389665926588</v>
       </c>
       <c r="F37" t="n">
         <v>5138200</v>
@@ -1172,16 +1172,16 @@
         <v>44466</v>
       </c>
       <c r="B38" t="n">
-        <v>6.305116653442383</v>
+        <v>6.305117130279541</v>
       </c>
       <c r="C38" t="n">
-        <v>6.340389999211985</v>
+        <v>6.340390478716762</v>
       </c>
       <c r="D38" t="n">
-        <v>6.102294705021446</v>
+        <v>6.102295166519786</v>
       </c>
       <c r="E38" t="n">
-        <v>6.17284139656065</v>
+        <v>6.172841863394225</v>
       </c>
       <c r="F38" t="n">
         <v>6343700</v>
@@ -1192,16 +1192,16 @@
         <v>44467</v>
       </c>
       <c r="B39" t="n">
-        <v>6.119931221008301</v>
+        <v>6.119931697845459</v>
       </c>
       <c r="C39" t="n">
-        <v>6.278661272902115</v>
+        <v>6.278661762106795</v>
       </c>
       <c r="D39" t="n">
-        <v>6.119931221008301</v>
+        <v>6.119931697845459</v>
       </c>
       <c r="E39" t="n">
-        <v>6.261024600469469</v>
+        <v>6.26102508829998</v>
       </c>
       <c r="F39" t="n">
         <v>6782400</v>
@@ -1212,16 +1212,16 @@
         <v>44468</v>
       </c>
       <c r="B40" t="n">
-        <v>6.040565490722656</v>
+        <v>6.040566921234131</v>
       </c>
       <c r="C40" t="n">
-        <v>6.252205963094541</v>
+        <v>6.252207443726178</v>
       </c>
       <c r="D40" t="n">
-        <v>6.040565490722656</v>
+        <v>6.040566921234131</v>
       </c>
       <c r="E40" t="n">
-        <v>6.216932621114461</v>
+        <v>6.216934093392754</v>
       </c>
       <c r="F40" t="n">
         <v>6482600</v>
@@ -1232,16 +1232,16 @@
         <v>44469</v>
       </c>
       <c r="B41" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="C41" t="n">
-        <v>6.349208319048255</v>
+        <v>6.349207835495088</v>
       </c>
       <c r="D41" t="n">
-        <v>6.058202997328168</v>
+        <v>6.058202535937849</v>
       </c>
       <c r="E41" t="n">
-        <v>6.084658217707932</v>
+        <v>6.084657754302794</v>
       </c>
       <c r="F41" t="n">
         <v>15990100</v>
@@ -1252,16 +1252,16 @@
         <v>44470</v>
       </c>
       <c r="B42" t="n">
-        <v>6.499120712280273</v>
+        <v>6.499120235443115</v>
       </c>
       <c r="C42" t="n">
-        <v>6.569667410952226</v>
+        <v>6.569666928939093</v>
       </c>
       <c r="D42" t="n">
-        <v>6.331572092688639</v>
+        <v>6.331571628144438</v>
       </c>
       <c r="E42" t="n">
-        <v>6.331572092688639</v>
+        <v>6.331571628144438</v>
       </c>
       <c r="F42" t="n">
         <v>15528000</v>
@@ -1272,16 +1272,16 @@
         <v>44473</v>
       </c>
       <c r="B43" t="n">
-        <v>6.190477848052979</v>
+        <v>6.190478324890137</v>
       </c>
       <c r="C43" t="n">
-        <v>6.552029839506799</v>
+        <v>6.552030344193411</v>
       </c>
       <c r="D43" t="n">
-        <v>6.190477848052979</v>
+        <v>6.190478324890137</v>
       </c>
       <c r="E43" t="n">
-        <v>6.525575041371436</v>
+        <v>6.5255755440203</v>
       </c>
       <c r="F43" t="n">
         <v>12019000</v>
@@ -1332,16 +1332,16 @@
         <v>44476</v>
       </c>
       <c r="B46" t="n">
-        <v>6.301833152770996</v>
+        <v>6.301832675933838</v>
       </c>
       <c r="C46" t="n">
-        <v>6.478602494754905</v>
+        <v>6.478602004542243</v>
       </c>
       <c r="D46" t="n">
-        <v>6.213448481779042</v>
+        <v>6.213448011629635</v>
       </c>
       <c r="E46" t="n">
-        <v>6.284156218572606</v>
+        <v>6.284155743072997</v>
       </c>
       <c r="F46" t="n">
         <v>18438800</v>
@@ -1352,16 +1352,16 @@
         <v>44477</v>
       </c>
       <c r="B47" t="n">
-        <v>6.310670375823975</v>
+        <v>6.310671806335449</v>
       </c>
       <c r="C47" t="n">
-        <v>6.655371168427701</v>
+        <v>6.655372677076427</v>
       </c>
       <c r="D47" t="n">
-        <v>6.292993444520037</v>
+        <v>6.292994871024479</v>
       </c>
       <c r="E47" t="n">
-        <v>6.36370116973579</v>
+        <v>6.363702612268358</v>
       </c>
       <c r="F47" t="n">
         <v>20480700</v>
@@ -1412,16 +1412,16 @@
         <v>44483</v>
       </c>
       <c r="B50" t="n">
-        <v>6.319509506225586</v>
+        <v>6.319509029388428</v>
       </c>
       <c r="C50" t="n">
-        <v>6.381378559508698</v>
+        <v>6.381378078003224</v>
       </c>
       <c r="D50" t="n">
-        <v>6.239963098917224</v>
+        <v>6.239962628082221</v>
       </c>
       <c r="E50" t="n">
-        <v>6.24880177592985</v>
+        <v>6.248801304427927</v>
       </c>
       <c r="F50" t="n">
         <v>10992200</v>
@@ -1432,16 +1432,16 @@
         <v>44484</v>
       </c>
       <c r="B51" t="n">
-        <v>6.275317192077637</v>
+        <v>6.27531623840332</v>
       </c>
       <c r="C51" t="n">
-        <v>6.354863602276304</v>
+        <v>6.354862636513137</v>
       </c>
       <c r="D51" t="n">
-        <v>6.222286392428969</v>
+        <v>6.222285446813864</v>
       </c>
       <c r="E51" t="n">
-        <v>6.337186669060081</v>
+        <v>6.337185705983319</v>
       </c>
       <c r="F51" t="n">
         <v>34203500</v>
@@ -1472,16 +1472,16 @@
         <v>44488</v>
       </c>
       <c r="B53" t="n">
-        <v>5.912939548492432</v>
+        <v>5.912939071655273</v>
       </c>
       <c r="C53" t="n">
-        <v>6.186932210078912</v>
+        <v>6.186931711146165</v>
       </c>
       <c r="D53" t="n">
-        <v>5.89526261617883</v>
+        <v>5.895262140767192</v>
       </c>
       <c r="E53" t="n">
-        <v>6.169255277765311</v>
+        <v>6.169254780258083</v>
       </c>
       <c r="F53" t="n">
         <v>11473400</v>
@@ -1492,16 +1492,16 @@
         <v>44489</v>
       </c>
       <c r="B54" t="n">
-        <v>5.904101848602295</v>
+        <v>5.904101371765137</v>
       </c>
       <c r="C54" t="n">
-        <v>6.04551775196348</v>
+        <v>6.045517263705048</v>
       </c>
       <c r="D54" t="n">
-        <v>5.842232785992445</v>
+        <v>5.842232314152062</v>
       </c>
       <c r="E54" t="n">
-        <v>6.010163881486029</v>
+        <v>6.010163396082907</v>
       </c>
       <c r="F54" t="n">
         <v>6234400</v>
@@ -1532,16 +1532,16 @@
         <v>44491</v>
       </c>
       <c r="B56" t="n">
-        <v>5.63010835647583</v>
+        <v>5.630108833312988</v>
       </c>
       <c r="C56" t="n">
-        <v>5.656623966361621</v>
+        <v>5.656624445444495</v>
       </c>
       <c r="D56" t="n">
-        <v>5.197023292801376</v>
+        <v>5.197023732958769</v>
       </c>
       <c r="E56" t="n">
-        <v>5.60359316804136</v>
+        <v>5.603593642632838</v>
       </c>
       <c r="F56" t="n">
         <v>18890200</v>
@@ -1552,16 +1552,16 @@
         <v>44494</v>
       </c>
       <c r="B57" t="n">
-        <v>5.859908580780029</v>
+        <v>5.859909057617188</v>
       </c>
       <c r="C57" t="n">
-        <v>5.877585512578483</v>
+        <v>5.877585990854064</v>
       </c>
       <c r="D57" t="n">
-        <v>5.550562063581435</v>
+        <v>5.550562515246201</v>
       </c>
       <c r="E57" t="n">
-        <v>5.683138841344191</v>
+        <v>5.683139303797101</v>
       </c>
       <c r="F57" t="n">
         <v>11428100</v>
@@ -1592,16 +1592,16 @@
         <v>44496</v>
       </c>
       <c r="B59" t="n">
-        <v>5.859908580780029</v>
+        <v>5.859909057617188</v>
       </c>
       <c r="C59" t="n">
-        <v>5.965970171570753</v>
+        <v>5.96597065703844</v>
       </c>
       <c r="D59" t="n">
-        <v>5.789200853586213</v>
+        <v>5.789201324669686</v>
       </c>
       <c r="E59" t="n">
-        <v>5.833392972356699</v>
+        <v>5.833393447036208</v>
       </c>
       <c r="F59" t="n">
         <v>7675900</v>
@@ -1612,16 +1612,16 @@
         <v>44497</v>
       </c>
       <c r="B60" t="n">
-        <v>5.992485523223877</v>
+        <v>5.992486476898193</v>
       </c>
       <c r="C60" t="n">
-        <v>6.027839385305918</v>
+        <v>6.027840344606625</v>
       </c>
       <c r="D60" t="n">
-        <v>5.727331136157289</v>
+        <v>5.727332047633601</v>
       </c>
       <c r="E60" t="n">
-        <v>5.75384674344446</v>
+        <v>5.753847659140599</v>
       </c>
       <c r="F60" t="n">
         <v>8299700</v>
@@ -1632,16 +1632,16 @@
         <v>44498</v>
       </c>
       <c r="B61" t="n">
-        <v>5.992485523223877</v>
+        <v>5.992486476898193</v>
       </c>
       <c r="C61" t="n">
-        <v>6.019000709059767</v>
+        <v>6.019001666953844</v>
       </c>
       <c r="D61" t="n">
-        <v>5.842231398649562</v>
+        <v>5.842232328411681</v>
       </c>
       <c r="E61" t="n">
-        <v>5.957131239690556</v>
+        <v>5.957132187738413</v>
       </c>
       <c r="F61" t="n">
         <v>3926300</v>
@@ -1652,16 +1652,16 @@
         <v>44501</v>
       </c>
       <c r="B62" t="n">
-        <v>6.00132417678833</v>
+        <v>6.001324653625488</v>
       </c>
       <c r="C62" t="n">
-        <v>6.063193650268579</v>
+        <v>6.063194132021597</v>
       </c>
       <c r="D62" t="n">
-        <v>5.948293380141535</v>
+        <v>5.948293852765114</v>
       </c>
       <c r="E62" t="n">
-        <v>5.965970312357133</v>
+        <v>5.965970786385239</v>
       </c>
       <c r="F62" t="n">
         <v>5059700</v>
@@ -1752,16 +1752,16 @@
         <v>44509</v>
       </c>
       <c r="B67" t="n">
-        <v>5.948294162750244</v>
+        <v>5.948293209075928</v>
       </c>
       <c r="C67" t="n">
-        <v>6.169256055242525</v>
+        <v>6.169255066141971</v>
       </c>
       <c r="D67" t="n">
-        <v>5.948294162750244</v>
+        <v>5.948293209075928</v>
       </c>
       <c r="E67" t="n">
-        <v>5.992486709829246</v>
+        <v>5.992485749069655</v>
       </c>
       <c r="F67" t="n">
         <v>5176300</v>
@@ -1772,16 +1772,16 @@
         <v>44510</v>
       </c>
       <c r="B68" t="n">
-        <v>5.74500846862793</v>
+        <v>5.745007991790771</v>
       </c>
       <c r="C68" t="n">
-        <v>6.010162874222051</v>
+        <v>6.01016237537701</v>
       </c>
       <c r="D68" t="n">
-        <v>5.74500846862793</v>
+        <v>5.745007991790771</v>
       </c>
       <c r="E68" t="n">
-        <v>5.957131655942178</v>
+        <v>5.957131161498742</v>
       </c>
       <c r="F68" t="n">
         <v>10074000</v>
@@ -1792,16 +1792,16 @@
         <v>44511</v>
       </c>
       <c r="B69" t="n">
-        <v>6.010163307189941</v>
+        <v>6.010162353515625</v>
       </c>
       <c r="C69" t="n">
-        <v>6.036678496788703</v>
+        <v>6.036677538907038</v>
       </c>
       <c r="D69" t="n">
-        <v>5.806878360643628</v>
+        <v>5.806877439225945</v>
       </c>
       <c r="E69" t="n">
-        <v>5.833393550242389</v>
+        <v>5.833392624617358</v>
       </c>
       <c r="F69" t="n">
         <v>8604300</v>
@@ -1812,16 +1812,16 @@
         <v>44512</v>
       </c>
       <c r="B70" t="n">
-        <v>5.762686252593994</v>
+        <v>5.762685775756836</v>
       </c>
       <c r="C70" t="n">
-        <v>6.080871502042515</v>
+        <v>6.080870998876915</v>
       </c>
       <c r="D70" t="n">
-        <v>5.532886099040496</v>
+        <v>5.532885641218299</v>
       </c>
       <c r="E70" t="n">
-        <v>6.080871502042515</v>
+        <v>6.080870998876915</v>
       </c>
       <c r="F70" t="n">
         <v>20568500</v>
@@ -1832,16 +1832,16 @@
         <v>44516</v>
       </c>
       <c r="B71" t="n">
-        <v>5.320762634277344</v>
+        <v>5.320761680603027</v>
       </c>
       <c r="C71" t="n">
-        <v>5.815717248925075</v>
+        <v>5.815716206536877</v>
       </c>
       <c r="D71" t="n">
-        <v>5.223539278459512</v>
+        <v>5.223538342211159</v>
       </c>
       <c r="E71" t="n">
-        <v>5.789202056443821</v>
+        <v>5.789201018808111</v>
       </c>
       <c r="F71" t="n">
         <v>27445700</v>
@@ -1872,16 +1872,16 @@
         <v>44518</v>
       </c>
       <c r="B73" t="n">
-        <v>5.161669254302979</v>
+        <v>5.161669731140137</v>
       </c>
       <c r="C73" t="n">
-        <v>5.338438576114187</v>
+        <v>5.338439069281368</v>
       </c>
       <c r="D73" t="n">
-        <v>5.073284171946066</v>
+        <v>5.073284640618174</v>
       </c>
       <c r="E73" t="n">
-        <v>5.214700050846341</v>
+        <v>5.214700532582506</v>
       </c>
       <c r="F73" t="n">
         <v>17735600</v>
@@ -1892,16 +1892,16 @@
         <v>44519</v>
       </c>
       <c r="B74" t="n">
-        <v>5.241215229034424</v>
+        <v>5.241215705871582</v>
       </c>
       <c r="C74" t="n">
-        <v>5.285407770133975</v>
+        <v>5.285408250991699</v>
       </c>
       <c r="D74" t="n">
-        <v>5.090961516488821</v>
+        <v>5.090961979656143</v>
       </c>
       <c r="E74" t="n">
-        <v>5.161669245087059</v>
+        <v>5.161669714687254</v>
       </c>
       <c r="F74" t="n">
         <v>11364600</v>
@@ -1912,16 +1912,16 @@
         <v>44522</v>
       </c>
       <c r="B75" t="n">
-        <v>4.976061344146729</v>
+        <v>4.976061820983887</v>
       </c>
       <c r="C75" t="n">
-        <v>5.32960041550615</v>
+        <v>5.329600926221622</v>
       </c>
       <c r="D75" t="n">
-        <v>4.976061344146729</v>
+        <v>4.976061820983887</v>
       </c>
       <c r="E75" t="n">
-        <v>5.232377076055763</v>
+        <v>5.23237757745469</v>
       </c>
       <c r="F75" t="n">
         <v>8516000</v>
@@ -1972,16 +1972,16 @@
         <v>44525</v>
       </c>
       <c r="B78" t="n">
-        <v>5.373791694641113</v>
+        <v>5.37379264831543</v>
       </c>
       <c r="C78" t="n">
-        <v>5.373791694641113</v>
+        <v>5.37379264831543</v>
       </c>
       <c r="D78" t="n">
-        <v>4.79929084631342</v>
+        <v>4.799291698032407</v>
       </c>
       <c r="E78" t="n">
-        <v>4.949544959724644</v>
+        <v>4.949545838108879</v>
       </c>
       <c r="F78" t="n">
         <v>20546100</v>
@@ -1992,16 +1992,16 @@
         <v>44526</v>
       </c>
       <c r="B79" t="n">
-        <v>5.223538398742676</v>
+        <v>5.223538875579834</v>
       </c>
       <c r="C79" t="n">
-        <v>5.338438670680995</v>
+        <v>5.338439158006967</v>
       </c>
       <c r="D79" t="n">
-        <v>5.020253464333078</v>
+        <v>5.02025392261312</v>
       </c>
       <c r="E79" t="n">
-        <v>5.037930396827334</v>
+        <v>5.037930856721036</v>
       </c>
       <c r="F79" t="n">
         <v>8564200</v>
@@ -2032,16 +2032,16 @@
         <v>44530</v>
       </c>
       <c r="B81" t="n">
-        <v>4.825808048248291</v>
+        <v>4.825807571411133</v>
       </c>
       <c r="C81" t="n">
-        <v>5.12631637449386</v>
+        <v>5.126315867963532</v>
       </c>
       <c r="D81" t="n">
-        <v>4.790454177096034</v>
+        <v>4.790453703752186</v>
       </c>
       <c r="E81" t="n">
-        <v>5.073285146314087</v>
+        <v>5.073284645023764</v>
       </c>
       <c r="F81" t="n">
         <v>11282700</v>
@@ -2052,16 +2052,16 @@
         <v>44531</v>
       </c>
       <c r="B82" t="n">
-        <v>4.852322578430176</v>
+        <v>4.852322101593018</v>
       </c>
       <c r="C82" t="n">
-        <v>5.152830863649267</v>
+        <v>5.152830357281196</v>
       </c>
       <c r="D82" t="n">
-        <v>4.852322578430176</v>
+        <v>4.852322101593018</v>
       </c>
       <c r="E82" t="n">
-        <v>4.896515122062865</v>
+        <v>4.896514640882911</v>
       </c>
       <c r="F82" t="n">
         <v>12492100</v>
@@ -2072,16 +2072,16 @@
         <v>44532</v>
       </c>
       <c r="B83" t="n">
-        <v>5.029091835021973</v>
+        <v>5.029092788696289</v>
       </c>
       <c r="C83" t="n">
-        <v>5.029091835021973</v>
+        <v>5.029092788696289</v>
       </c>
       <c r="D83" t="n">
-        <v>4.746260510887681</v>
+        <v>4.746261410928263</v>
       </c>
       <c r="E83" t="n">
-        <v>4.905353315098159</v>
+        <v>4.905354245307752</v>
       </c>
       <c r="F83" t="n">
         <v>18379200</v>
@@ -2092,16 +2092,16 @@
         <v>44533</v>
       </c>
       <c r="B84" t="n">
-        <v>5.320762634277344</v>
+        <v>5.320761680603027</v>
       </c>
       <c r="C84" t="n">
-        <v>5.329601312738686</v>
+        <v>5.329600357480157</v>
       </c>
       <c r="D84" t="n">
-        <v>4.976062181861339</v>
+        <v>4.97606128996989</v>
       </c>
       <c r="E84" t="n">
-        <v>5.020254309813891</v>
+        <v>5.020253410001604</v>
       </c>
       <c r="F84" t="n">
         <v>10548200</v>
@@ -2112,16 +2112,16 @@
         <v>44536</v>
       </c>
       <c r="B85" t="n">
-        <v>5.152831077575684</v>
+        <v>5.152830600738525</v>
       </c>
       <c r="C85" t="n">
-        <v>5.417985507477384</v>
+        <v>5.417985006103135</v>
       </c>
       <c r="D85" t="n">
-        <v>5.152831077575684</v>
+        <v>5.152830600738525</v>
       </c>
       <c r="E85" t="n">
-        <v>5.373792962009984</v>
+        <v>5.373792464725264</v>
       </c>
       <c r="F85" t="n">
         <v>5884400</v>
@@ -2132,16 +2132,16 @@
         <v>44537</v>
       </c>
       <c r="B86" t="n">
-        <v>5.232377052307129</v>
+        <v>5.232377529144287</v>
       </c>
       <c r="C86" t="n">
-        <v>5.258892240204233</v>
+        <v>5.258892719457774</v>
       </c>
       <c r="D86" t="n">
-        <v>4.914191847382692</v>
+        <v>4.914192295222986</v>
       </c>
       <c r="E86" t="n">
-        <v>5.24121530778906</v>
+        <v>5.241215785431666</v>
       </c>
       <c r="F86" t="n">
         <v>9906100</v>
@@ -2172,16 +2172,16 @@
         <v>44539</v>
       </c>
       <c r="B88" t="n">
-        <v>5.232377052307129</v>
+        <v>5.232377529144287</v>
       </c>
       <c r="C88" t="n">
-        <v>5.435661985807282</v>
+        <v>5.435662481170208</v>
       </c>
       <c r="D88" t="n">
-        <v>5.179346255061608</v>
+        <v>5.179346727065962</v>
       </c>
       <c r="E88" t="n">
-        <v>5.205861442958712</v>
+        <v>5.205861917379448</v>
       </c>
       <c r="F88" t="n">
         <v>9205900</v>
@@ -2192,16 +2192,16 @@
         <v>44540</v>
       </c>
       <c r="B89" t="n">
-        <v>5.44450044631958</v>
+        <v>5.444500923156738</v>
       </c>
       <c r="C89" t="n">
-        <v>5.568239399336901</v>
+        <v>5.568239887011294</v>
       </c>
       <c r="D89" t="n">
-        <v>5.241215505164072</v>
+        <v>5.241215964197243</v>
       </c>
       <c r="E89" t="n">
-        <v>5.267731115511021</v>
+        <v>5.267731576866467</v>
       </c>
       <c r="F89" t="n">
         <v>8741300</v>
@@ -2212,16 +2212,16 @@
         <v>44543</v>
       </c>
       <c r="B90" t="n">
-        <v>5.497530937194824</v>
+        <v>5.497531414031982</v>
       </c>
       <c r="C90" t="n">
-        <v>5.621269883271384</v>
+        <v>5.621270370841238</v>
       </c>
       <c r="D90" t="n">
-        <v>5.426823208837535</v>
+        <v>5.426823679541746</v>
       </c>
       <c r="E90" t="n">
-        <v>5.444500140926858</v>
+        <v>5.444500613164305</v>
       </c>
       <c r="F90" t="n">
         <v>8265100</v>
@@ -2232,16 +2232,16 @@
         <v>44544</v>
       </c>
       <c r="B91" t="n">
-        <v>5.453339576721191</v>
+        <v>5.453338623046875</v>
       </c>
       <c r="C91" t="n">
-        <v>5.603593731119232</v>
+        <v>5.603592751168627</v>
       </c>
       <c r="D91" t="n">
-        <v>5.426823964170976</v>
+        <v>5.426823015133682</v>
       </c>
       <c r="E91" t="n">
-        <v>5.497531702369733</v>
+        <v>5.497530740967144</v>
       </c>
       <c r="F91" t="n">
         <v>6640900</v>
@@ -2292,16 +2292,16 @@
         <v>44547</v>
       </c>
       <c r="B94" t="n">
-        <v>5.241215229034424</v>
+        <v>5.241215705871582</v>
       </c>
       <c r="C94" t="n">
-        <v>5.347277243383087</v>
+        <v>5.347277729869593</v>
       </c>
       <c r="D94" t="n">
-        <v>5.241215229034424</v>
+        <v>5.241215705871582</v>
       </c>
       <c r="E94" t="n">
-        <v>5.320761634433095</v>
+        <v>5.320762118507254</v>
       </c>
       <c r="F94" t="n">
         <v>50153800</v>
@@ -2392,16 +2392,16 @@
         <v>44557</v>
       </c>
       <c r="B99" t="n">
-        <v>5.232377052307129</v>
+        <v>5.232377529144287</v>
       </c>
       <c r="C99" t="n">
-        <v>5.232377052307129</v>
+        <v>5.232377529144287</v>
       </c>
       <c r="D99" t="n">
-        <v>5.011415186391803</v>
+        <v>5.011415643092257</v>
       </c>
       <c r="E99" t="n">
-        <v>5.04676905122215</v>
+        <v>5.046769511144474</v>
       </c>
       <c r="F99" t="n">
         <v>4493500</v>
@@ -2412,16 +2412,16 @@
         <v>44558</v>
       </c>
       <c r="B100" t="n">
-        <v>5.347277641296387</v>
+        <v>5.347277164459229</v>
       </c>
       <c r="C100" t="n">
-        <v>5.347277641296387</v>
+        <v>5.347277164459229</v>
       </c>
       <c r="D100" t="n">
-        <v>5.188184818660282</v>
+        <v>5.188184356010038</v>
       </c>
       <c r="E100" t="n">
-        <v>5.214700429583412</v>
+        <v>5.21469996456867</v>
       </c>
       <c r="F100" t="n">
         <v>4379800</v>
@@ -2432,16 +2432,16 @@
         <v>44559</v>
       </c>
       <c r="B101" t="n">
-        <v>5.311923503875732</v>
+        <v>5.311923027038574</v>
       </c>
       <c r="C101" t="n">
-        <v>5.38263123413509</v>
+        <v>5.382630750950688</v>
       </c>
       <c r="D101" t="n">
-        <v>5.214700164043457</v>
+        <v>5.214699695933778</v>
       </c>
       <c r="E101" t="n">
-        <v>5.320761759432494</v>
+        <v>5.320761281801949</v>
       </c>
       <c r="F101" t="n">
         <v>5394800</v>
@@ -2472,16 +2472,16 @@
         <v>44564</v>
       </c>
       <c r="B103" t="n">
-        <v>5.541723728179932</v>
+        <v>5.541724681854248</v>
       </c>
       <c r="C103" t="n">
-        <v>5.745008667104768</v>
+        <v>5.745009655762357</v>
       </c>
       <c r="D103" t="n">
-        <v>5.506369862406162</v>
+        <v>5.506370809996437</v>
       </c>
       <c r="E103" t="n">
-        <v>5.691977868444114</v>
+        <v>5.691978847975641</v>
       </c>
       <c r="F103" t="n">
         <v>7451800</v>
@@ -2492,16 +2492,16 @@
         <v>44565</v>
       </c>
       <c r="B104" t="n">
-        <v>5.594754219055176</v>
+        <v>5.594754695892334</v>
       </c>
       <c r="C104" t="n">
-        <v>5.612431150969596</v>
+        <v>5.612431629313347</v>
       </c>
       <c r="D104" t="n">
-        <v>5.444500087056956</v>
+        <v>5.444500551088055</v>
       </c>
       <c r="E104" t="n">
-        <v>5.532885168080356</v>
+        <v>5.532885639644457</v>
       </c>
       <c r="F104" t="n">
         <v>10613100</v>
@@ -2612,16 +2612,16 @@
         <v>44573</v>
       </c>
       <c r="B110" t="n">
-        <v>5.438660621643066</v>
+        <v>5.438661098480225</v>
       </c>
       <c r="C110" t="n">
-        <v>5.51851016215336</v>
+        <v>5.518510645991364</v>
       </c>
       <c r="D110" t="n">
-        <v>5.225727526476521</v>
+        <v>5.225727984644668</v>
       </c>
       <c r="E110" t="n">
-        <v>5.261216305161009</v>
+        <v>5.261216766440652</v>
       </c>
       <c r="F110" t="n">
         <v>9077500</v>
@@ -2652,16 +2652,16 @@
         <v>44575</v>
       </c>
       <c r="B112" t="n">
-        <v>5.491894245147705</v>
+        <v>5.491893768310547</v>
       </c>
       <c r="C112" t="n">
-        <v>5.500766229024832</v>
+        <v>5.500765751417357</v>
       </c>
       <c r="D112" t="n">
-        <v>5.332194727822603</v>
+        <v>5.332194264851456</v>
       </c>
       <c r="E112" t="n">
-        <v>5.420916681892105</v>
+        <v>5.420916211217618</v>
       </c>
       <c r="F112" t="n">
         <v>4745900</v>
@@ -2732,16 +2732,16 @@
         <v>44581</v>
       </c>
       <c r="B116" t="n">
-        <v>5.713698863983154</v>
+        <v>5.713699817657471</v>
       </c>
       <c r="C116" t="n">
-        <v>5.837909589292028</v>
+        <v>5.837910563698375</v>
       </c>
       <c r="D116" t="n">
-        <v>5.633848900469072</v>
+        <v>5.633849840815619</v>
       </c>
       <c r="E116" t="n">
-        <v>5.651593289798911</v>
+        <v>5.651594233107177</v>
       </c>
       <c r="F116" t="n">
         <v>9343500</v>
@@ -2752,16 +2752,16 @@
         <v>44582</v>
       </c>
       <c r="B117" t="n">
-        <v>5.527382373809814</v>
+        <v>5.527381896972656</v>
       </c>
       <c r="C117" t="n">
-        <v>5.687081872269151</v>
+        <v>5.68708138165501</v>
       </c>
       <c r="D117" t="n">
-        <v>5.483021190485755</v>
+        <v>5.483020717475555</v>
       </c>
       <c r="E117" t="n">
-        <v>5.678209889440098</v>
+        <v>5.678209399591327</v>
       </c>
       <c r="F117" t="n">
         <v>7609900</v>
@@ -2812,16 +2812,16 @@
         <v>44587</v>
       </c>
       <c r="B120" t="n">
-        <v>5.518509864807129</v>
+        <v>5.518510341644287</v>
       </c>
       <c r="C120" t="n">
-        <v>5.678209783342052</v>
+        <v>5.67821027397838</v>
       </c>
       <c r="D120" t="n">
-        <v>5.491893493757702</v>
+        <v>5.491893968295023</v>
       </c>
       <c r="E120" t="n">
-        <v>5.59835982407459</v>
+        <v>5.598360307811333</v>
       </c>
       <c r="F120" t="n">
         <v>11610000</v>
@@ -2912,16 +2912,16 @@
         <v>44594</v>
       </c>
       <c r="B125" t="n">
-        <v>5.669337272644043</v>
+        <v>5.669337749481201</v>
       </c>
       <c r="C125" t="n">
-        <v>5.882270352394677</v>
+        <v>5.882270847141231</v>
       </c>
       <c r="D125" t="n">
-        <v>5.651592884586456</v>
+        <v>5.651593359931167</v>
       </c>
       <c r="E125" t="n">
-        <v>5.722570436816806</v>
+        <v>5.722570918131304</v>
       </c>
       <c r="F125" t="n">
         <v>8808600</v>
@@ -2932,16 +2932,16 @@
         <v>44595</v>
       </c>
       <c r="B126" t="n">
-        <v>5.731443881988525</v>
+        <v>5.731443405151367</v>
       </c>
       <c r="C126" t="n">
-        <v>5.793549462985059</v>
+        <v>5.793548980980922</v>
       </c>
       <c r="D126" t="n">
-        <v>5.616105127163388</v>
+        <v>5.616104659922033</v>
       </c>
       <c r="E126" t="n">
-        <v>5.678210708159922</v>
+        <v>5.678210235751588</v>
       </c>
       <c r="F126" t="n">
         <v>8390300</v>
@@ -2972,16 +2972,16 @@
         <v>44599</v>
       </c>
       <c r="B128" t="n">
-        <v>5.562871932983398</v>
+        <v>5.562872409820557</v>
       </c>
       <c r="C128" t="n">
-        <v>5.775805050578469</v>
+        <v>5.775805545667787</v>
       </c>
       <c r="D128" t="n">
-        <v>5.553999948907585</v>
+        <v>5.554000424984256</v>
       </c>
       <c r="E128" t="n">
-        <v>5.704827062673674</v>
+        <v>5.704827551678914</v>
       </c>
       <c r="F128" t="n">
         <v>7178800</v>
@@ -3012,16 +3012,16 @@
         <v>44601</v>
       </c>
       <c r="B130" t="n">
-        <v>5.633848667144775</v>
+        <v>5.633849143981934</v>
       </c>
       <c r="C130" t="n">
-        <v>5.740314998714537</v>
+        <v>5.740315484562782</v>
       </c>
       <c r="D130" t="n">
-        <v>5.589487907187173</v>
+        <v>5.58948838026973</v>
       </c>
       <c r="E130" t="n">
-        <v>5.616104278549815</v>
+        <v>5.616104753885126</v>
       </c>
       <c r="F130" t="n">
         <v>8867400</v>
@@ -3052,16 +3052,16 @@
         <v>44603</v>
       </c>
       <c r="B132" t="n">
-        <v>5.633848667144775</v>
+        <v>5.633849143981934</v>
       </c>
       <c r="C132" t="n">
-        <v>5.775804198964051</v>
+        <v>5.775804687816029</v>
       </c>
       <c r="D132" t="n">
-        <v>5.589487907187173</v>
+        <v>5.58948838026973</v>
       </c>
       <c r="E132" t="n">
-        <v>5.731443015946853</v>
+        <v>5.731443501044193</v>
       </c>
       <c r="F132" t="n">
         <v>8001300</v>
@@ -3132,16 +3132,16 @@
         <v>44609</v>
       </c>
       <c r="B136" t="n">
-        <v>5.580616474151611</v>
+        <v>5.580615043640137</v>
       </c>
       <c r="C136" t="n">
-        <v>5.740315999344462</v>
+        <v>5.740314527896292</v>
       </c>
       <c r="D136" t="n">
-        <v>5.509638907399233</v>
+        <v>5.509637495081845</v>
       </c>
       <c r="E136" t="n">
-        <v>5.73144401503025</v>
+        <v>5.731442545856286</v>
       </c>
       <c r="F136" t="n">
         <v>16171600</v>
@@ -3172,16 +3172,16 @@
         <v>44613</v>
       </c>
       <c r="B138" t="n">
-        <v>5.119261741638184</v>
+        <v>5.119261264801025</v>
       </c>
       <c r="C138" t="n">
-        <v>5.456405598502314</v>
+        <v>5.456405090261659</v>
       </c>
       <c r="D138" t="n">
-        <v>5.074900551976187</v>
+        <v>5.074900079271083</v>
       </c>
       <c r="E138" t="n">
-        <v>5.447533191346051</v>
+        <v>5.447532683931823</v>
       </c>
       <c r="F138" t="n">
         <v>8726900</v>
@@ -3192,16 +3192,16 @@
         <v>44614</v>
       </c>
       <c r="B139" t="n">
-        <v>5.012794494628906</v>
+        <v>5.012794971466064</v>
       </c>
       <c r="C139" t="n">
-        <v>5.234599557019038</v>
+        <v>5.234600054955186</v>
       </c>
       <c r="D139" t="n">
-        <v>4.977305718491252</v>
+        <v>4.977306191952575</v>
       </c>
       <c r="E139" t="n">
-        <v>5.172493987248352</v>
+        <v>5.172494479276767</v>
       </c>
       <c r="F139" t="n">
         <v>7346000</v>
@@ -3212,16 +3212,16 @@
         <v>44615</v>
       </c>
       <c r="B140" t="n">
-        <v>5.021667003631592</v>
+        <v>5.021666526794434</v>
       </c>
       <c r="C140" t="n">
-        <v>5.101516969842998</v>
+        <v>5.10151648542361</v>
       </c>
       <c r="D140" t="n">
-        <v>4.968433833843864</v>
+        <v>4.968433362061512</v>
       </c>
       <c r="E140" t="n">
-        <v>5.057155783490078</v>
+        <v>5.057155303283048</v>
       </c>
       <c r="F140" t="n">
         <v>10772600</v>
@@ -3232,16 +3232,16 @@
         <v>44616</v>
       </c>
       <c r="B141" t="n">
-        <v>5.119261741638184</v>
+        <v>5.119261264801025</v>
       </c>
       <c r="C141" t="n">
-        <v>5.137006132891051</v>
+        <v>5.137005654401078</v>
       </c>
       <c r="D141" t="n">
-        <v>4.773245900677449</v>
+        <v>4.773245456070175</v>
       </c>
       <c r="E141" t="n">
-        <v>4.924073437856647</v>
+        <v>4.924072979200438</v>
       </c>
       <c r="F141" t="n">
         <v>11357100</v>
@@ -3252,16 +3252,16 @@
         <v>44617</v>
       </c>
       <c r="B142" t="n">
-        <v>5.066028594970703</v>
+        <v>5.066027641296387</v>
       </c>
       <c r="C142" t="n">
-        <v>5.163622958913197</v>
+        <v>5.163621986866849</v>
       </c>
       <c r="D142" t="n">
-        <v>4.986178622375967</v>
+        <v>4.986177683733319</v>
       </c>
       <c r="E142" t="n">
-        <v>5.110389784869926</v>
+        <v>5.110388822844664</v>
       </c>
       <c r="F142" t="n">
         <v>6795000</v>
@@ -3272,16 +3272,16 @@
         <v>44622</v>
       </c>
       <c r="B143" t="n">
-        <v>5.314449787139893</v>
+        <v>5.314450263977051</v>
       </c>
       <c r="C143" t="n">
-        <v>5.349938990980526</v>
+        <v>5.349939471001941</v>
       </c>
       <c r="D143" t="n">
-        <v>5.03053954089193</v>
+        <v>5.030539992255339</v>
       </c>
       <c r="E143" t="n">
-        <v>5.10151710245392</v>
+        <v>5.101517560185767</v>
       </c>
       <c r="F143" t="n">
         <v>7030100</v>
@@ -3292,16 +3292,16 @@
         <v>44623</v>
       </c>
       <c r="B144" t="n">
-        <v>5.465277194976807</v>
+        <v>5.465277671813965</v>
       </c>
       <c r="C144" t="n">
-        <v>5.545127161481217</v>
+        <v>5.545127645285164</v>
       </c>
       <c r="D144" t="n">
-        <v>5.323322075021968</v>
+        <v>5.323322539473757</v>
       </c>
       <c r="E144" t="n">
-        <v>5.323322075021968</v>
+        <v>5.323322539473757</v>
       </c>
       <c r="F144" t="n">
         <v>18057800</v>
@@ -3312,16 +3312,16 @@
         <v>44624</v>
       </c>
       <c r="B145" t="n">
-        <v>5.509638786315918</v>
+        <v>5.509639263153076</v>
       </c>
       <c r="C145" t="n">
-        <v>5.536255161733287</v>
+        <v>5.536255640873986</v>
       </c>
       <c r="D145" t="n">
-        <v>5.376555640050094</v>
+        <v>5.376556105369439</v>
       </c>
       <c r="E145" t="n">
-        <v>5.483021987838889</v>
+        <v>5.48302246237247</v>
       </c>
       <c r="F145" t="n">
         <v>9336900</v>
@@ -3492,16 +3492,16 @@
         <v>44637</v>
       </c>
       <c r="B154" t="n">
-        <v>5.891143321990967</v>
+        <v>5.891142845153809</v>
       </c>
       <c r="C154" t="n">
-        <v>5.926632104052506</v>
+        <v>5.926631624342837</v>
       </c>
       <c r="D154" t="n">
-        <v>5.536255078315924</v>
+        <v>5.536254630203903</v>
       </c>
       <c r="E154" t="n">
-        <v>5.607233065498654</v>
+        <v>5.607232611641579</v>
       </c>
       <c r="F154" t="n">
         <v>10001800</v>
@@ -3532,16 +3532,16 @@
         <v>44641</v>
       </c>
       <c r="B156" t="n">
-        <v>6.104076385498047</v>
+        <v>6.104075908660889</v>
       </c>
       <c r="C156" t="n">
-        <v>6.343625873905633</v>
+        <v>6.34362537835539</v>
       </c>
       <c r="D156" t="n">
-        <v>6.024226415008968</v>
+        <v>6.024225944409515</v>
       </c>
       <c r="E156" t="n">
-        <v>6.183925932927476</v>
+        <v>6.183925449852644</v>
       </c>
       <c r="F156" t="n">
         <v>14982100</v>
@@ -3552,16 +3552,16 @@
         <v>44642</v>
       </c>
       <c r="B157" t="n">
-        <v>6.299263954162598</v>
+        <v>6.299263477325439</v>
       </c>
       <c r="C157" t="n">
-        <v>6.308136360102719</v>
+        <v>6.308135882593944</v>
       </c>
       <c r="D157" t="n">
-        <v>6.077458882374763</v>
+        <v>6.077458422327646</v>
       </c>
       <c r="E157" t="n">
-        <v>6.077458882374763</v>
+        <v>6.077458422327646</v>
       </c>
       <c r="F157" t="n">
         <v>9703800</v>
@@ -3572,16 +3572,16 @@
         <v>44643</v>
       </c>
       <c r="B158" t="n">
-        <v>6.3081374168396</v>
+        <v>6.308136940002441</v>
       </c>
       <c r="C158" t="n">
-        <v>6.334753792999529</v>
+        <v>6.334753314150418</v>
       </c>
       <c r="D158" t="n">
-        <v>6.201670643020867</v>
+        <v>6.201670174231618</v>
       </c>
       <c r="E158" t="n">
-        <v>6.263776225826821</v>
+        <v>6.263775752342961</v>
       </c>
       <c r="F158" t="n">
         <v>8187500</v>
@@ -3612,16 +3612,16 @@
         <v>44645</v>
       </c>
       <c r="B160" t="n">
-        <v>6.450092315673828</v>
+        <v>6.450091361999512</v>
       </c>
       <c r="C160" t="n">
-        <v>6.512197896212132</v>
+        <v>6.512196933355233</v>
       </c>
       <c r="D160" t="n">
-        <v>6.237159621930483</v>
+        <v>6.237158699739195</v>
       </c>
       <c r="E160" t="n">
-        <v>6.343625968802155</v>
+        <v>6.343625030869354</v>
       </c>
       <c r="F160" t="n">
         <v>15324200</v>
@@ -3692,16 +3692,16 @@
         <v>44651</v>
       </c>
       <c r="B164" t="n">
-        <v>6.23715877532959</v>
+        <v>6.237159252166748</v>
       </c>
       <c r="C164" t="n">
-        <v>6.52994140101566</v>
+        <v>6.529941900236349</v>
       </c>
       <c r="D164" t="n">
-        <v>6.18392518605976</v>
+        <v>6.183925658827156</v>
       </c>
       <c r="E164" t="n">
-        <v>6.503324606380745</v>
+        <v>6.503325103566553</v>
       </c>
       <c r="F164" t="n">
         <v>12972000</v>
@@ -3712,16 +3712,16 @@
         <v>44652</v>
       </c>
       <c r="B165" t="n">
-        <v>6.139564037322998</v>
+        <v>6.139564990997314</v>
       </c>
       <c r="C165" t="n">
-        <v>6.299263525850169</v>
+        <v>6.299264504331019</v>
       </c>
       <c r="D165" t="n">
-        <v>5.926630962893866</v>
+        <v>5.926631883492739</v>
       </c>
       <c r="E165" t="n">
-        <v>6.254902768344629</v>
+        <v>6.254903739934808</v>
       </c>
       <c r="F165" t="n">
         <v>18919700</v>
@@ -3732,16 +3732,16 @@
         <v>44655</v>
       </c>
       <c r="B166" t="n">
-        <v>6.210542678833008</v>
+        <v>6.21054220199585</v>
       </c>
       <c r="C166" t="n">
-        <v>6.237159476459965</v>
+        <v>6.237158997579204</v>
       </c>
       <c r="D166" t="n">
-        <v>6.050843162250203</v>
+        <v>6.050842697674559</v>
       </c>
       <c r="E166" t="n">
-        <v>6.15730950663874</v>
+        <v>6.157309033888753</v>
       </c>
       <c r="F166" t="n">
         <v>13343800</v>
@@ -3752,16 +3752,16 @@
         <v>44656</v>
       </c>
       <c r="B167" t="n">
-        <v>6.299263954162598</v>
+        <v>6.299263477325439</v>
       </c>
       <c r="C167" t="n">
-        <v>6.325880748923362</v>
+        <v>6.325880270071385</v>
       </c>
       <c r="D167" t="n">
-        <v>6.148436437657334</v>
+        <v>6.148435972237409</v>
       </c>
       <c r="E167" t="n">
-        <v>6.228286398880027</v>
+        <v>6.228285927415676</v>
       </c>
       <c r="F167" t="n">
         <v>6962400</v>
@@ -3812,16 +3812,16 @@
         <v>44659</v>
       </c>
       <c r="B170" t="n">
-        <v>6.190385341644287</v>
+        <v>6.190384864807129</v>
       </c>
       <c r="C170" t="n">
-        <v>6.323990869283284</v>
+        <v>6.323990382154669</v>
       </c>
       <c r="D170" t="n">
-        <v>6.136943215532741</v>
+        <v>6.136942742812159</v>
       </c>
       <c r="E170" t="n">
-        <v>6.234920659097374</v>
+        <v>6.23492017882972</v>
       </c>
       <c r="F170" t="n">
         <v>10722400</v>
@@ -3852,16 +3852,16 @@
         <v>44663</v>
       </c>
       <c r="B172" t="n">
-        <v>6.217106342315674</v>
+        <v>6.217106819152832</v>
       </c>
       <c r="C172" t="n">
-        <v>6.359618672315267</v>
+        <v>6.359619160082779</v>
       </c>
       <c r="D172" t="n">
-        <v>6.145850177315878</v>
+        <v>6.145850648687858</v>
       </c>
       <c r="E172" t="n">
-        <v>6.190385068080627</v>
+        <v>6.190385542868328</v>
       </c>
       <c r="F172" t="n">
         <v>15598900</v>
@@ -3872,16 +3872,16 @@
         <v>44664</v>
       </c>
       <c r="B173" t="n">
-        <v>6.30617618560791</v>
+        <v>6.306176662445068</v>
       </c>
       <c r="C173" t="n">
-        <v>6.323990225832556</v>
+        <v>6.323990704016711</v>
       </c>
       <c r="D173" t="n">
-        <v>6.172570671562951</v>
+        <v>6.172571138297622</v>
       </c>
       <c r="E173" t="n">
-        <v>6.261641297406404</v>
+        <v>6.261641770876088</v>
       </c>
       <c r="F173" t="n">
         <v>5828500</v>
@@ -3892,16 +3892,16 @@
         <v>44665</v>
       </c>
       <c r="B174" t="n">
-        <v>6.323990821838379</v>
+        <v>6.323989868164062</v>
       </c>
       <c r="C174" t="n">
-        <v>6.350712097053812</v>
+        <v>6.350711139349857</v>
       </c>
       <c r="D174" t="n">
-        <v>6.226013379008809</v>
+        <v>6.226012440109747</v>
       </c>
       <c r="E174" t="n">
-        <v>6.297269971343208</v>
+        <v>6.297269021698465</v>
       </c>
       <c r="F174" t="n">
         <v>4947000</v>
@@ -3932,16 +3932,16 @@
         <v>44670</v>
       </c>
       <c r="B176" t="n">
-        <v>6.190385341644287</v>
+        <v>6.190384864807129</v>
       </c>
       <c r="C176" t="n">
-        <v>6.413061079469193</v>
+        <v>6.413060585479618</v>
       </c>
       <c r="D176" t="n">
-        <v>6.181478532985828</v>
+        <v>6.18147805683475</v>
       </c>
       <c r="E176" t="n">
-        <v>6.359618953357647</v>
+        <v>6.359618463484649</v>
       </c>
       <c r="F176" t="n">
         <v>12659600</v>
@@ -3952,16 +3952,16 @@
         <v>44671</v>
       </c>
       <c r="B177" t="n">
-        <v>6.208199024200439</v>
+        <v>6.208198547363281</v>
       </c>
       <c r="C177" t="n">
-        <v>6.279455612943373</v>
+        <v>6.279455130633163</v>
       </c>
       <c r="D177" t="n">
-        <v>6.110222011029355</v>
+        <v>6.11022154171758</v>
       </c>
       <c r="E177" t="n">
-        <v>6.190384983194765</v>
+        <v>6.190384507725862</v>
       </c>
       <c r="F177" t="n">
         <v>7897000</v>
@@ -3972,16 +3972,16 @@
         <v>44673</v>
       </c>
       <c r="B178" t="n">
-        <v>6.128035545349121</v>
+        <v>6.128036022186279</v>
       </c>
       <c r="C178" t="n">
-        <v>6.190384471353647</v>
+        <v>6.190384953042324</v>
       </c>
       <c r="D178" t="n">
-        <v>5.98552280436691</v>
+        <v>5.98552327011481</v>
       </c>
       <c r="E178" t="n">
-        <v>6.136942352755394</v>
+        <v>6.136942830285612</v>
       </c>
       <c r="F178" t="n">
         <v>9926800</v>
@@ -3992,16 +3992,16 @@
         <v>44676</v>
       </c>
       <c r="B179" t="n">
-        <v>6.279455661773682</v>
+        <v>6.279454708099365</v>
       </c>
       <c r="C179" t="n">
-        <v>6.306176511129858</v>
+        <v>6.306175553397391</v>
       </c>
       <c r="D179" t="n">
-        <v>6.038965893966873</v>
+        <v>6.038964976816251</v>
       </c>
       <c r="E179" t="n">
-        <v>6.047872702178851</v>
+        <v>6.047871783675533</v>
       </c>
       <c r="F179" t="n">
         <v>9340700</v>
@@ -4092,16 +4092,16 @@
         <v>44683</v>
       </c>
       <c r="B184" t="n">
-        <v>5.869732856750488</v>
+        <v>5.869731903076172</v>
       </c>
       <c r="C184" t="n">
-        <v>6.19038562826636</v>
+        <v>6.19038462249456</v>
       </c>
       <c r="D184" t="n">
-        <v>5.745034131996254</v>
+        <v>5.745033198582139</v>
       </c>
       <c r="E184" t="n">
-        <v>6.145850733471519</v>
+        <v>6.145849734935447</v>
       </c>
       <c r="F184" t="n">
         <v>12404500</v>
@@ -4132,16 +4132,16 @@
         <v>44685</v>
       </c>
       <c r="B186" t="n">
-        <v>5.388751983642578</v>
+        <v>5.388752937316895</v>
       </c>
       <c r="C186" t="n">
-        <v>5.513450253799544</v>
+        <v>5.513451229542335</v>
       </c>
       <c r="D186" t="n">
-        <v>5.210611172983874</v>
+        <v>5.210612095131722</v>
       </c>
       <c r="E186" t="n">
-        <v>5.513450253799544</v>
+        <v>5.513451229542335</v>
       </c>
       <c r="F186" t="n">
         <v>18834300</v>
@@ -4172,16 +4172,16 @@
         <v>44687</v>
       </c>
       <c r="B188" t="n">
-        <v>4.95230770111084</v>
+        <v>4.952308177947998</v>
       </c>
       <c r="C188" t="n">
-        <v>5.068099171347654</v>
+        <v>5.068099659333893</v>
       </c>
       <c r="D188" t="n">
-        <v>4.863237502744139</v>
+        <v>4.863237971005097</v>
       </c>
       <c r="E188" t="n">
-        <v>4.97012174078418</v>
+        <v>4.970122219336578</v>
       </c>
       <c r="F188" t="n">
         <v>14479200</v>
@@ -4192,16 +4192,16 @@
         <v>44690</v>
       </c>
       <c r="B189" t="n">
-        <v>4.622747898101807</v>
+        <v>4.622747421264648</v>
       </c>
       <c r="C189" t="n">
-        <v>4.934493814409667</v>
+        <v>4.934493305415869</v>
       </c>
       <c r="D189" t="n">
-        <v>4.435700263373046</v>
+        <v>4.435699805829881</v>
       </c>
       <c r="E189" t="n">
-        <v>4.934493814409667</v>
+        <v>4.934493305415869</v>
       </c>
       <c r="F189" t="n">
         <v>21341300</v>
@@ -4212,16 +4212,16 @@
         <v>44691</v>
       </c>
       <c r="B190" t="n">
-        <v>4.631655216217041</v>
+        <v>4.631654739379883</v>
       </c>
       <c r="C190" t="n">
-        <v>4.7118186184255</v>
+        <v>4.711818133335377</v>
       </c>
       <c r="D190" t="n">
-        <v>4.569306280917366</v>
+        <v>4.569305810499142</v>
       </c>
       <c r="E190" t="n">
-        <v>4.65837649185995</v>
+        <v>4.658376012271789</v>
       </c>
       <c r="F190" t="n">
         <v>9825600</v>
@@ -4252,16 +4252,16 @@
         <v>44693</v>
       </c>
       <c r="B192" t="n">
-        <v>4.791981220245361</v>
+        <v>4.79198169708252</v>
       </c>
       <c r="C192" t="n">
-        <v>4.809795259458459</v>
+        <v>4.809795738068244</v>
       </c>
       <c r="D192" t="n">
-        <v>4.551491478508448</v>
+        <v>4.55149193141512</v>
       </c>
       <c r="E192" t="n">
-        <v>4.587119556934643</v>
+        <v>4.587120013386569</v>
       </c>
       <c r="F192" t="n">
         <v>13350100</v>
@@ -4272,16 +4272,16 @@
         <v>44694</v>
       </c>
       <c r="B193" t="n">
-        <v>4.604933261871338</v>
+        <v>4.604934692382812</v>
       </c>
       <c r="C193" t="n">
-        <v>4.800887678990895</v>
+        <v>4.80088917037514</v>
       </c>
       <c r="D193" t="n">
-        <v>4.515863072271539</v>
+        <v>4.515864475113573</v>
       </c>
       <c r="E193" t="n">
-        <v>4.800887678990895</v>
+        <v>4.80088917037514</v>
       </c>
       <c r="F193" t="n">
         <v>51332400</v>
@@ -4332,16 +4332,16 @@
         <v>44699</v>
       </c>
       <c r="B196" t="n">
-        <v>4.95230770111084</v>
+        <v>4.952308177947998</v>
       </c>
       <c r="C196" t="n">
-        <v>5.112634058170901</v>
+        <v>5.112634550445218</v>
       </c>
       <c r="D196" t="n">
-        <v>4.89886558209082</v>
+        <v>4.898866053782258</v>
       </c>
       <c r="E196" t="n">
-        <v>4.98793578045752</v>
+        <v>4.987936260725158</v>
       </c>
       <c r="F196" t="n">
         <v>17779600</v>
@@ -4372,16 +4372,16 @@
         <v>44701</v>
       </c>
       <c r="B198" t="n">
-        <v>4.934494495391846</v>
+        <v>4.934494018554688</v>
       </c>
       <c r="C198" t="n">
-        <v>5.121542155934015</v>
+        <v>5.121541661021799</v>
       </c>
       <c r="D198" t="n">
-        <v>4.82761023928783</v>
+        <v>4.827609772779264</v>
       </c>
       <c r="E198" t="n">
-        <v>5.09482087954787</v>
+        <v>5.094820387217823</v>
       </c>
       <c r="F198" t="n">
         <v>10517400</v>
@@ -4392,16 +4392,16 @@
         <v>44704</v>
       </c>
       <c r="B199" t="n">
-        <v>5.023564338684082</v>
+        <v>5.02356481552124</v>
       </c>
       <c r="C199" t="n">
-        <v>5.10372773721593</v>
+        <v>5.103728221662204</v>
       </c>
       <c r="D199" t="n">
-        <v>4.881052007712129</v>
+        <v>4.881052471022004</v>
       </c>
       <c r="E199" t="n">
-        <v>4.979029447615471</v>
+        <v>4.979029920225373</v>
       </c>
       <c r="F199" t="n">
         <v>11444200</v>
@@ -4452,16 +4452,16 @@
         <v>44707</v>
       </c>
       <c r="B202" t="n">
-        <v>5.504543304443359</v>
+        <v>5.504544258117676</v>
       </c>
       <c r="C202" t="n">
-        <v>5.647056045223134</v>
+        <v>5.647057023588098</v>
       </c>
       <c r="D202" t="n">
-        <v>5.281867598240178</v>
+        <v>5.281868513335436</v>
       </c>
       <c r="E202" t="n">
-        <v>5.281867598240178</v>
+        <v>5.281868513335436</v>
       </c>
       <c r="F202" t="n">
         <v>14781100</v>
@@ -4492,16 +4492,16 @@
         <v>44711</v>
       </c>
       <c r="B204" t="n">
-        <v>5.602521419525146</v>
+        <v>5.602520942687988</v>
       </c>
       <c r="C204" t="n">
-        <v>5.673777586272644</v>
+        <v>5.67377710337079</v>
       </c>
       <c r="D204" t="n">
-        <v>5.317496327814903</v>
+        <v>5.317495875236564</v>
       </c>
       <c r="E204" t="n">
-        <v>5.460009086030153</v>
+        <v>5.460008621322386</v>
       </c>
       <c r="F204" t="n">
         <v>7527500</v>
@@ -4532,16 +4532,16 @@
         <v>44713</v>
       </c>
       <c r="B206" t="n">
-        <v>5.51345157623291</v>
+        <v>5.513451099395752</v>
       </c>
       <c r="C206" t="n">
-        <v>5.549079661966218</v>
+        <v>5.549079182047723</v>
       </c>
       <c r="D206" t="n">
-        <v>5.406567319032987</v>
+        <v>5.406566851439836</v>
       </c>
       <c r="E206" t="n">
-        <v>5.495637533366256</v>
+        <v>5.495637058069765</v>
       </c>
       <c r="F206" t="n">
         <v>9091200</v>
@@ -4552,16 +4552,16 @@
         <v>44714</v>
       </c>
       <c r="B207" t="n">
-        <v>5.611427783966064</v>
+        <v>5.611428260803223</v>
       </c>
       <c r="C207" t="n">
-        <v>5.65596266892822</v>
+        <v>5.655963149549779</v>
       </c>
       <c r="D207" t="n">
-        <v>5.504543125672473</v>
+        <v>5.504543593426991</v>
       </c>
       <c r="E207" t="n">
-        <v>5.549078435354819</v>
+        <v>5.549078906893773</v>
       </c>
       <c r="F207" t="n">
         <v>14163200</v>
@@ -4572,16 +4572,16 @@
         <v>44715</v>
       </c>
       <c r="B208" t="n">
-        <v>5.51345157623291</v>
+        <v>5.513451099395752</v>
       </c>
       <c r="C208" t="n">
-        <v>5.602521790566179</v>
+        <v>5.602521306025682</v>
       </c>
       <c r="D208" t="n">
-        <v>5.45110221383948</v>
+        <v>5.451101742394677</v>
       </c>
       <c r="E208" t="n">
-        <v>5.57580093862634</v>
+        <v>5.575800456396826</v>
       </c>
       <c r="F208" t="n">
         <v>9326300</v>
@@ -4612,16 +4612,16 @@
         <v>44719</v>
       </c>
       <c r="B210" t="n">
-        <v>5.023564338684082</v>
+        <v>5.02356481552124</v>
       </c>
       <c r="C210" t="n">
-        <v>5.299682192302366</v>
+        <v>5.299682695348654</v>
       </c>
       <c r="D210" t="n">
-        <v>4.987936255941094</v>
+        <v>4.987936729396432</v>
       </c>
       <c r="E210" t="n">
-        <v>5.281868150930872</v>
+        <v>5.281868652286249</v>
       </c>
       <c r="F210" t="n">
         <v>18881300</v>
@@ -4632,16 +4632,16 @@
         <v>44720</v>
       </c>
       <c r="B211" t="n">
-        <v>4.916680335998535</v>
+        <v>4.916679859161377</v>
       </c>
       <c r="C211" t="n">
-        <v>5.005750547304253</v>
+        <v>5.005750061828747</v>
       </c>
       <c r="D211" t="n">
-        <v>4.783074806679825</v>
+        <v>4.783074342800206</v>
       </c>
       <c r="E211" t="n">
-        <v>4.996843738533816</v>
+        <v>4.996843253922124</v>
       </c>
       <c r="F211" t="n">
         <v>13996400</v>
@@ -4672,16 +4672,16 @@
         <v>44722</v>
       </c>
       <c r="B213" t="n">
-        <v>4.73853874206543</v>
+        <v>4.738539218902588</v>
       </c>
       <c r="C213" t="n">
-        <v>4.783073624349554</v>
+        <v>4.78307410566824</v>
       </c>
       <c r="D213" t="n">
-        <v>4.676189397203458</v>
+        <v>4.676189867766428</v>
       </c>
       <c r="E213" t="n">
-        <v>4.774166817780795</v>
+        <v>4.774167298203192</v>
       </c>
       <c r="F213" t="n">
         <v>4786300</v>
@@ -4692,16 +4692,16 @@
         <v>44725</v>
       </c>
       <c r="B214" t="n">
-        <v>4.569304943084717</v>
+        <v>4.569305896759033</v>
       </c>
       <c r="C214" t="n">
-        <v>4.676189164921517</v>
+        <v>4.676190140903983</v>
       </c>
       <c r="D214" t="n">
-        <v>4.506955601319845</v>
+        <v>4.50695654198103</v>
       </c>
       <c r="E214" t="n">
-        <v>4.631653860129446</v>
+        <v>4.631654826816805</v>
       </c>
       <c r="F214" t="n">
         <v>7709600</v>
@@ -4712,16 +4712,16 @@
         <v>44726</v>
       </c>
       <c r="B215" t="n">
-        <v>4.462421894073486</v>
+        <v>4.462421417236328</v>
       </c>
       <c r="C215" t="n">
-        <v>4.640562310620824</v>
+        <v>4.640561814748269</v>
       </c>
       <c r="D215" t="n">
-        <v>4.453514660885992</v>
+        <v>4.453514185000626</v>
       </c>
       <c r="E215" t="n">
-        <v>4.587120185656623</v>
+        <v>4.587119695494687</v>
       </c>
       <c r="F215" t="n">
         <v>9819800</v>
@@ -4732,16 +4732,16 @@
         <v>44727</v>
       </c>
       <c r="B216" t="n">
-        <v>4.560398578643799</v>
+        <v>4.560399055480957</v>
       </c>
       <c r="C216" t="n">
-        <v>4.649468780429767</v>
+        <v>4.649469266580143</v>
       </c>
       <c r="D216" t="n">
-        <v>4.48023560939654</v>
+        <v>4.480236077851825</v>
       </c>
       <c r="E216" t="n">
-        <v>4.542584538286605</v>
+        <v>4.54258501326112</v>
       </c>
       <c r="F216" t="n">
         <v>10830000</v>
@@ -4752,16 +4752,16 @@
         <v>44729</v>
       </c>
       <c r="B217" t="n">
-        <v>4.524770259857178</v>
+        <v>4.524770736694336</v>
       </c>
       <c r="C217" t="n">
-        <v>4.524770259857178</v>
+        <v>4.524770736694336</v>
       </c>
       <c r="D217" t="n">
-        <v>4.311001786818351</v>
+        <v>4.311002241127791</v>
       </c>
       <c r="E217" t="n">
-        <v>4.506956220437275</v>
+        <v>4.506956695397124</v>
       </c>
       <c r="F217" t="n">
         <v>10891400</v>
@@ -4772,16 +4772,16 @@
         <v>44732</v>
       </c>
       <c r="B218" t="n">
-        <v>4.524770259857178</v>
+        <v>4.524770736694336</v>
       </c>
       <c r="C218" t="n">
-        <v>4.649468535796493</v>
+        <v>4.64946902577482</v>
       </c>
       <c r="D218" t="n">
-        <v>4.453514102177569</v>
+        <v>4.453514571505488</v>
       </c>
       <c r="E218" t="n">
-        <v>4.524770259857178</v>
+        <v>4.524770736694336</v>
       </c>
       <c r="F218" t="n">
         <v>7841400</v>
@@ -4792,16 +4792,16 @@
         <v>44733</v>
       </c>
       <c r="B219" t="n">
-        <v>4.489143371582031</v>
+        <v>4.489142417907715</v>
       </c>
       <c r="C219" t="n">
-        <v>4.596027636448196</v>
+        <v>4.596026660067369</v>
       </c>
       <c r="D219" t="n">
-        <v>4.444608048860973</v>
+        <v>4.444607104647747</v>
       </c>
       <c r="E219" t="n">
-        <v>4.560399548159474</v>
+        <v>4.560398579347484</v>
       </c>
       <c r="F219" t="n">
         <v>7411800</v>
@@ -4832,16 +4832,16 @@
         <v>44735</v>
       </c>
       <c r="B221" t="n">
-        <v>4.266466617584229</v>
+        <v>4.266467094421387</v>
       </c>
       <c r="C221" t="n">
-        <v>4.515863602464738</v>
+        <v>4.515864107175489</v>
       </c>
       <c r="D221" t="n">
-        <v>4.266466617584229</v>
+        <v>4.266467094421387</v>
       </c>
       <c r="E221" t="n">
-        <v>4.471328290076007</v>
+        <v>4.471328789809315</v>
       </c>
       <c r="F221" t="n">
         <v>8059200</v>
@@ -4852,16 +4852,16 @@
         <v>44736</v>
       </c>
       <c r="B222" t="n">
-        <v>4.257560253143311</v>
+        <v>4.257559776306152</v>
       </c>
       <c r="C222" t="n">
-        <v>4.337723229179554</v>
+        <v>4.337722743364323</v>
       </c>
       <c r="D222" t="n">
-        <v>4.23083897798439</v>
+        <v>4.230838504139954</v>
       </c>
       <c r="E222" t="n">
-        <v>4.319909187313693</v>
+        <v>4.319908703493595</v>
       </c>
       <c r="F222" t="n">
         <v>7941200</v>
@@ -4932,16 +4932,16 @@
         <v>44742</v>
       </c>
       <c r="B226" t="n">
-        <v>4.088326454162598</v>
+        <v>4.088325977325439</v>
       </c>
       <c r="C226" t="n">
-        <v>4.239746015386434</v>
+        <v>4.239745520888632</v>
       </c>
       <c r="D226" t="n">
-        <v>4.052698372077018</v>
+        <v>4.052697899395299</v>
       </c>
       <c r="E226" t="n">
-        <v>4.239746015386434</v>
+        <v>4.239745520888632</v>
       </c>
       <c r="F226" t="n">
         <v>6721700</v>
@@ -5012,16 +5012,16 @@
         <v>44748</v>
       </c>
       <c r="B230" t="n">
-        <v>3.910185575485229</v>
+        <v>3.91018533706665</v>
       </c>
       <c r="C230" t="n">
-        <v>4.0526983269613</v>
+        <v>4.052698079853188</v>
       </c>
       <c r="D230" t="n">
-        <v>3.785487289573874</v>
+        <v>3.785487058758614</v>
       </c>
       <c r="E230" t="n">
-        <v>4.034884286116821</v>
+        <v>4.034884040094897</v>
       </c>
       <c r="F230" t="n">
         <v>11922900</v>
@@ -5052,16 +5052,16 @@
         <v>44750</v>
       </c>
       <c r="B232" t="n">
-        <v>3.919092416763306</v>
+        <v>3.919092893600464</v>
       </c>
       <c r="C232" t="n">
-        <v>4.1328608855423</v>
+        <v>4.132861388388733</v>
       </c>
       <c r="D232" t="n">
-        <v>3.919092416763306</v>
+        <v>3.919092893600464</v>
       </c>
       <c r="E232" t="n">
-        <v>4.034883883045357</v>
+        <v>4.034884373970899</v>
       </c>
       <c r="F232" t="n">
         <v>7050900</v>
@@ -5072,16 +5072,16 @@
         <v>44753</v>
       </c>
       <c r="B233" t="n">
-        <v>3.705323934555054</v>
+        <v>3.705323457717896</v>
       </c>
       <c r="C233" t="n">
-        <v>3.901278810740315</v>
+        <v>3.901278308685776</v>
       </c>
       <c r="D233" t="n">
-        <v>3.678603085351762</v>
+        <v>3.678602611953303</v>
       </c>
       <c r="E233" t="n">
-        <v>3.892371577859058</v>
+        <v>3.892371076950788</v>
       </c>
       <c r="F233" t="n">
         <v>13261200</v>
@@ -5092,16 +5092,16 @@
         <v>44754</v>
       </c>
       <c r="B234" t="n">
-        <v>3.580625772476196</v>
+        <v>3.580625534057617</v>
       </c>
       <c r="C234" t="n">
-        <v>3.705324064132908</v>
+        <v>3.705323817411202</v>
       </c>
       <c r="D234" t="n">
-        <v>3.580625772476196</v>
+        <v>3.580625534057617</v>
       </c>
       <c r="E234" t="n">
-        <v>3.696417255660414</v>
+        <v>3.696417009531774</v>
       </c>
       <c r="F234" t="n">
         <v>14771600</v>
@@ -5112,16 +5112,16 @@
         <v>44755</v>
       </c>
       <c r="B235" t="n">
-        <v>3.687509775161743</v>
+        <v>3.687510013580322</v>
       </c>
       <c r="C235" t="n">
-        <v>3.723137856102805</v>
+        <v>3.723138096824944</v>
       </c>
       <c r="D235" t="n">
-        <v>3.47374128951537</v>
+        <v>3.473741514112596</v>
       </c>
       <c r="E235" t="n">
-        <v>3.589532764933936</v>
+        <v>3.589532997017741</v>
       </c>
       <c r="F235" t="n">
         <v>14925600</v>
@@ -5152,16 +5152,16 @@
         <v>44757</v>
       </c>
       <c r="B237" t="n">
-        <v>3.936906814575195</v>
+        <v>3.936907052993774</v>
       </c>
       <c r="C237" t="n">
-        <v>3.9547208552634</v>
+        <v>3.954721094760794</v>
       </c>
       <c r="D237" t="n">
-        <v>3.776580023661126</v>
+        <v>3.776580252370335</v>
       </c>
       <c r="E237" t="n">
-        <v>3.830022570445971</v>
+        <v>3.830022802391653</v>
       </c>
       <c r="F237" t="n">
         <v>4881500</v>
@@ -5172,16 +5172,16 @@
         <v>44760</v>
       </c>
       <c r="B238" t="n">
-        <v>3.830022811889648</v>
+        <v>3.830023050308228</v>
       </c>
       <c r="C238" t="n">
-        <v>4.088326630512132</v>
+        <v>4.0883268850101</v>
       </c>
       <c r="D238" t="n">
-        <v>3.830022811889648</v>
+        <v>3.830023050308228</v>
       </c>
       <c r="E238" t="n">
-        <v>3.99034918819042</v>
+        <v>3.990349436589301</v>
       </c>
       <c r="F238" t="n">
         <v>5011900</v>
@@ -5192,16 +5192,16 @@
         <v>44761</v>
       </c>
       <c r="B239" t="n">
-        <v>3.856743574142456</v>
+        <v>3.856743097305298</v>
       </c>
       <c r="C239" t="n">
-        <v>3.93690697282171</v>
+        <v>3.93690648607337</v>
       </c>
       <c r="D239" t="n">
-        <v>3.830022724396204</v>
+        <v>3.830022250862738</v>
       </c>
       <c r="E239" t="n">
-        <v>3.838929532738205</v>
+        <v>3.838929058103526</v>
       </c>
       <c r="F239" t="n">
         <v>5270100</v>
@@ -5212,16 +5212,16 @@
         <v>44762</v>
       </c>
       <c r="B240" t="n">
-        <v>3.999256134033203</v>
+        <v>3.999255418777466</v>
       </c>
       <c r="C240" t="n">
-        <v>4.025977410027488</v>
+        <v>4.025976689992726</v>
       </c>
       <c r="D240" t="n">
-        <v>3.803301667382781</v>
+        <v>3.803300987172951</v>
       </c>
       <c r="E240" t="n">
-        <v>3.830022943377066</v>
+        <v>3.83002225838821</v>
       </c>
       <c r="F240" t="n">
         <v>11021800</v>
@@ -5232,16 +5232,16 @@
         <v>44763</v>
       </c>
       <c r="B241" t="n">
-        <v>3.963627576828003</v>
+        <v>3.963628053665161</v>
       </c>
       <c r="C241" t="n">
-        <v>4.025976930237424</v>
+        <v>4.02597741457541</v>
       </c>
       <c r="D241" t="n">
-        <v>3.93690672873841</v>
+        <v>3.936907202360965</v>
       </c>
       <c r="E241" t="n">
-        <v>4.025976930237424</v>
+        <v>4.02597741457541</v>
       </c>
       <c r="F241" t="n">
         <v>6658500</v>
@@ -5272,16 +5272,16 @@
         <v>44767</v>
       </c>
       <c r="B243" t="n">
-        <v>3.696417331695557</v>
+        <v>3.696417570114136</v>
       </c>
       <c r="C243" t="n">
-        <v>3.78548754185395</v>
+        <v>3.78548778601755</v>
       </c>
       <c r="D243" t="n">
-        <v>3.651882014256228</v>
+        <v>3.651882249802283</v>
       </c>
       <c r="E243" t="n">
-        <v>3.767673499822271</v>
+        <v>3.767673742836867</v>
       </c>
       <c r="F243" t="n">
         <v>10514300</v>
@@ -5292,16 +5292,16 @@
         <v>44768</v>
       </c>
       <c r="B244" t="n">
-        <v>3.71423077583313</v>
+        <v>3.714231014251709</v>
       </c>
       <c r="C244" t="n">
-        <v>3.812208203595688</v>
+        <v>3.812208448303494</v>
       </c>
       <c r="D244" t="n">
-        <v>3.669695465562822</v>
+        <v>3.669695701122655</v>
       </c>
       <c r="E244" t="n">
-        <v>3.70532354389099</v>
+        <v>3.705323781737809</v>
       </c>
       <c r="F244" t="n">
         <v>4594100</v>
@@ -5312,16 +5312,16 @@
         <v>44769</v>
       </c>
       <c r="B245" t="n">
-        <v>3.999256134033203</v>
+        <v>3.999255418777466</v>
       </c>
       <c r="C245" t="n">
-        <v>3.999256134033203</v>
+        <v>3.999255418777466</v>
       </c>
       <c r="D245" t="n">
-        <v>3.723138264120199</v>
+        <v>3.723137598247368</v>
       </c>
       <c r="E245" t="n">
-        <v>3.740952306542965</v>
+        <v>3.740951637484142</v>
       </c>
       <c r="F245" t="n">
         <v>8689000</v>
@@ -5332,16 +5332,16 @@
         <v>44770</v>
       </c>
       <c r="B246" t="n">
-        <v>3.999256134033203</v>
+        <v>3.999255418777466</v>
       </c>
       <c r="C246" t="n">
-        <v>4.070512728444538</v>
+        <v>4.07051200044476</v>
       </c>
       <c r="D246" t="n">
-        <v>3.892371879496609</v>
+        <v>3.892371183356821</v>
       </c>
       <c r="E246" t="n">
-        <v>4.025977410027488</v>
+        <v>4.025976689992726</v>
       </c>
       <c r="F246" t="n">
         <v>3634200</v>
@@ -5352,16 +5352,16 @@
         <v>44771</v>
       </c>
       <c r="B247" t="n">
-        <v>3.927999496459961</v>
+        <v>3.927999973297119</v>
       </c>
       <c r="C247" t="n">
-        <v>4.08832628388786</v>
+        <v>4.088326780187793</v>
       </c>
       <c r="D247" t="n">
-        <v>3.919092688669646</v>
+        <v>3.919093164425567</v>
       </c>
       <c r="E247" t="n">
-        <v>4.025976930474763</v>
+        <v>4.025977419205834</v>
       </c>
       <c r="F247" t="n">
         <v>8694600</v>
@@ -5372,16 +5372,16 @@
         <v>44774</v>
       </c>
       <c r="B248" t="n">
-        <v>3.927999496459961</v>
+        <v>3.927999973297119</v>
       </c>
       <c r="C248" t="n">
-        <v>3.990348849873058</v>
+        <v>3.990349334279078</v>
       </c>
       <c r="D248" t="n">
-        <v>3.874557375557402</v>
+        <v>3.874557845906986</v>
       </c>
       <c r="E248" t="n">
-        <v>3.98144161736252</v>
+        <v>3.981442100687252</v>
       </c>
       <c r="F248" t="n">
         <v>7696400</v>
@@ -5392,16 +5392,16 @@
         <v>44775</v>
       </c>
       <c r="B249" t="n">
-        <v>4.10614013671875</v>
+        <v>4.106140613555908</v>
       </c>
       <c r="C249" t="n">
-        <v>4.115046944102415</v>
+        <v>4.115047421973903</v>
       </c>
       <c r="D249" t="n">
-        <v>3.901278470251996</v>
+        <v>3.901278923299012</v>
       </c>
       <c r="E249" t="n">
-        <v>3.927999317123196</v>
+        <v>3.927999773273247</v>
       </c>
       <c r="F249" t="n">
         <v>12885400</v>
@@ -5432,16 +5432,16 @@
         <v>44777</v>
       </c>
       <c r="B251" t="n">
-        <v>4.498050212860107</v>
+        <v>4.498049736022949</v>
       </c>
       <c r="C251" t="n">
-        <v>4.791982127910954</v>
+        <v>4.791981619914148</v>
       </c>
       <c r="D251" t="n">
-        <v>4.32881659592047</v>
+        <v>4.328816137023725</v>
       </c>
       <c r="E251" t="n">
-        <v>4.32881659592047</v>
+        <v>4.328816137023725</v>
       </c>
       <c r="F251" t="n">
         <v>17206200</v>
@@ -5492,16 +5492,16 @@
         <v>44782</v>
       </c>
       <c r="B254" t="n">
-        <v>4.38225793838501</v>
+        <v>4.382258892059326</v>
       </c>
       <c r="C254" t="n">
-        <v>4.578212371730591</v>
+        <v>4.578213368048839</v>
       </c>
       <c r="D254" t="n">
-        <v>4.364443898989957</v>
+        <v>4.364444848787552</v>
       </c>
       <c r="E254" t="n">
-        <v>4.453514095965221</v>
+        <v>4.453515065146422</v>
       </c>
       <c r="F254" t="n">
         <v>9216300</v>
@@ -5512,16 +5512,16 @@
         <v>44783</v>
       </c>
       <c r="B255" t="n">
-        <v>4.587119102478027</v>
+        <v>4.587119579315186</v>
       </c>
       <c r="C255" t="n">
-        <v>4.702910558251529</v>
+        <v>4.702911047125363</v>
       </c>
       <c r="D255" t="n">
-        <v>4.426792340723901</v>
+        <v>4.426792800894878</v>
       </c>
       <c r="E255" t="n">
-        <v>4.426792340723901</v>
+        <v>4.426792800894878</v>
       </c>
       <c r="F255" t="n">
         <v>9044400</v>
@@ -5532,16 +5532,16 @@
         <v>44784</v>
       </c>
       <c r="B256" t="n">
-        <v>4.346630573272705</v>
+        <v>4.346630096435547</v>
       </c>
       <c r="C256" t="n">
-        <v>4.685097802072197</v>
+        <v>4.685097288104267</v>
       </c>
       <c r="D256" t="n">
-        <v>4.311002488632787</v>
+        <v>4.311002015704126</v>
       </c>
       <c r="E256" t="n">
-        <v>4.61384120807209</v>
+        <v>4.613840701921201</v>
       </c>
       <c r="F256" t="n">
         <v>11482900</v>
@@ -5552,16 +5552,16 @@
         <v>44785</v>
       </c>
       <c r="B257" t="n">
-        <v>4.694004535675049</v>
+        <v>4.694004058837891</v>
       </c>
       <c r="C257" t="n">
-        <v>4.694004535675049</v>
+        <v>4.694004058837891</v>
       </c>
       <c r="D257" t="n">
-        <v>4.49805007329465</v>
+        <v>4.498049616363389</v>
       </c>
       <c r="E257" t="n">
-        <v>4.578213050090135</v>
+        <v>4.578212585015574</v>
       </c>
       <c r="F257" t="n">
         <v>15222800</v>
@@ -5592,16 +5592,16 @@
         <v>44789</v>
       </c>
       <c r="B259" t="n">
-        <v>4.622747898101807</v>
+        <v>4.622747421264648</v>
       </c>
       <c r="C259" t="n">
-        <v>4.702911291477053</v>
+        <v>4.702910806371028</v>
       </c>
       <c r="D259" t="n">
-        <v>4.560398544952146</v>
+        <v>4.560398074546333</v>
       </c>
       <c r="E259" t="n">
-        <v>4.676190018778564</v>
+        <v>4.676189536428843</v>
       </c>
       <c r="F259" t="n">
         <v>5754000</v>
@@ -5612,16 +5612,16 @@
         <v>44790</v>
       </c>
       <c r="B260" t="n">
-        <v>4.702911853790283</v>
+        <v>4.702911376953125</v>
       </c>
       <c r="C260" t="n">
-        <v>4.774168023212515</v>
+        <v>4.774167539150558</v>
       </c>
       <c r="D260" t="n">
-        <v>4.560399090225548</v>
+        <v>4.560398627838029</v>
       </c>
       <c r="E260" t="n">
-        <v>4.596027174936664</v>
+        <v>4.596026708936746</v>
       </c>
       <c r="F260" t="n">
         <v>27272900</v>
@@ -5632,16 +5632,16 @@
         <v>44791</v>
       </c>
       <c r="B261" t="n">
-        <v>4.53367805480957</v>
+        <v>4.533677577972412</v>
       </c>
       <c r="C261" t="n">
-        <v>4.711818471125755</v>
+        <v>4.711817975552381</v>
       </c>
       <c r="D261" t="n">
-        <v>4.515864013177952</v>
+        <v>4.515863538214415</v>
       </c>
       <c r="E261" t="n">
-        <v>4.640562304599281</v>
+        <v>4.640561816520393</v>
       </c>
       <c r="F261" t="n">
         <v>8785600</v>
@@ -5652,16 +5652,16 @@
         <v>44792</v>
       </c>
       <c r="B262" t="n">
-        <v>4.31990909576416</v>
+        <v>4.319908618927002</v>
       </c>
       <c r="C262" t="n">
-        <v>4.533678018344458</v>
+        <v>4.533677517911209</v>
       </c>
       <c r="D262" t="n">
-        <v>4.22193165521818</v>
+        <v>4.221931189195899</v>
       </c>
       <c r="E262" t="n">
-        <v>4.524770785240164</v>
+        <v>4.524770285790107</v>
       </c>
       <c r="F262" t="n">
         <v>17743000</v>
@@ -5672,16 +5672,16 @@
         <v>44795</v>
       </c>
       <c r="B263" t="n">
-        <v>4.31990909576416</v>
+        <v>4.319908618927002</v>
       </c>
       <c r="C263" t="n">
-        <v>4.364444411845128</v>
+        <v>4.364443930092105</v>
       </c>
       <c r="D263" t="n">
-        <v>4.177396763857463</v>
+        <v>4.177396302751</v>
       </c>
       <c r="E263" t="n">
-        <v>4.302095054275823</v>
+        <v>4.302094579405002</v>
       </c>
       <c r="F263" t="n">
         <v>9829500</v>
@@ -5712,16 +5712,16 @@
         <v>44797</v>
       </c>
       <c r="B265" t="n">
-        <v>4.53367805480957</v>
+        <v>4.533677577972412</v>
       </c>
       <c r="C265" t="n">
-        <v>4.604934221336045</v>
+        <v>4.6049337370044</v>
       </c>
       <c r="D265" t="n">
-        <v>4.426793380299605</v>
+        <v>4.426792914704221</v>
       </c>
       <c r="E265" t="n">
-        <v>4.45351465510716</v>
+        <v>4.453514186701321</v>
       </c>
       <c r="F265" t="n">
         <v>5861300</v>
@@ -5752,16 +5752,16 @@
         <v>44799</v>
       </c>
       <c r="B267" t="n">
-        <v>4.31990909576416</v>
+        <v>4.319908618927002</v>
       </c>
       <c r="C267" t="n">
-        <v>4.524770785240164</v>
+        <v>4.524770285790107</v>
       </c>
       <c r="D267" t="n">
-        <v>4.29318824589178</v>
+        <v>4.293187772004104</v>
       </c>
       <c r="E267" t="n">
-        <v>4.489142702263489</v>
+        <v>4.489142206746107</v>
       </c>
       <c r="F267" t="n">
         <v>6692300</v>
@@ -5772,16 +5772,16 @@
         <v>44802</v>
       </c>
       <c r="B268" t="n">
-        <v>4.453514099121094</v>
+        <v>4.453514575958252</v>
       </c>
       <c r="C268" t="n">
-        <v>4.480235370592709</v>
+        <v>4.48023585029091</v>
       </c>
       <c r="D268" t="n">
-        <v>4.266466472980391</v>
+        <v>4.266466929790385</v>
       </c>
       <c r="E268" t="n">
-        <v>4.275373705044331</v>
+        <v>4.275374162808021</v>
       </c>
       <c r="F268" t="n">
         <v>7870400</v>
@@ -5792,16 +5792,16 @@
         <v>44803</v>
       </c>
       <c r="B269" t="n">
-        <v>4.364444255828857</v>
+        <v>4.364443778991699</v>
       </c>
       <c r="C269" t="n">
-        <v>4.480235733723964</v>
+        <v>4.480235244236013</v>
       </c>
       <c r="D269" t="n">
-        <v>4.337722982191434</v>
+        <v>4.337722508273708</v>
       </c>
       <c r="E269" t="n">
-        <v>4.471328500938078</v>
+        <v>4.471328012423286</v>
       </c>
       <c r="F269" t="n">
         <v>7827400</v>
@@ -5812,16 +5812,16 @@
         <v>44804</v>
       </c>
       <c r="B270" t="n">
-        <v>4.311001777648926</v>
+        <v>4.311002254486084</v>
       </c>
       <c r="C270" t="n">
-        <v>4.43570005332301</v>
+        <v>4.435700543952965</v>
       </c>
       <c r="D270" t="n">
-        <v>4.284280506215807</v>
+        <v>4.284280980097343</v>
       </c>
       <c r="E270" t="n">
-        <v>4.382257935176974</v>
+        <v>4.382258419895731</v>
       </c>
       <c r="F270" t="n">
         <v>8375100</v>
@@ -5852,16 +5852,16 @@
         <v>44806</v>
       </c>
       <c r="B272" t="n">
-        <v>4.097232818603516</v>
+        <v>4.097233772277832</v>
       </c>
       <c r="C272" t="n">
-        <v>4.35553659811042</v>
+        <v>4.355537611907676</v>
       </c>
       <c r="D272" t="n">
-        <v>4.097232818603516</v>
+        <v>4.097233772277832</v>
       </c>
       <c r="E272" t="n">
-        <v>4.319908519883274</v>
+        <v>4.319909525387717</v>
       </c>
       <c r="F272" t="n">
         <v>69570300</v>
@@ -5872,16 +5872,16 @@
         <v>44809</v>
       </c>
       <c r="B273" t="n">
-        <v>4.115046977996826</v>
+        <v>4.115046501159668</v>
       </c>
       <c r="C273" t="n">
-        <v>4.221931215802409</v>
+        <v>4.221930726579882</v>
       </c>
       <c r="D273" t="n">
-        <v>4.115046977996826</v>
+        <v>4.115046501159668</v>
       </c>
       <c r="E273" t="n">
-        <v>4.123954210174062</v>
+        <v>4.123953732304765</v>
       </c>
       <c r="F273" t="n">
         <v>7604300</v>
@@ -5912,16 +5912,16 @@
         <v>44812</v>
       </c>
       <c r="B275" t="n">
-        <v>3.910185575485229</v>
+        <v>3.91018533706665</v>
       </c>
       <c r="C275" t="n">
-        <v>4.008163012489984</v>
+        <v>4.008162768097356</v>
       </c>
       <c r="D275" t="n">
-        <v>3.856743452951791</v>
+        <v>3.856743217791777</v>
       </c>
       <c r="E275" t="n">
-        <v>3.990348971645505</v>
+        <v>3.990348728339065</v>
       </c>
       <c r="F275" t="n">
         <v>9864000</v>
@@ -5932,16 +5932,16 @@
         <v>44813</v>
       </c>
       <c r="B276" t="n">
-        <v>3.910185575485229</v>
+        <v>3.91018533706665</v>
       </c>
       <c r="C276" t="n">
-        <v>4.043791094178943</v>
+        <v>4.043790847613938</v>
       </c>
       <c r="D276" t="n">
-        <v>3.883464726578628</v>
+        <v>3.883464489789319</v>
       </c>
       <c r="E276" t="n">
-        <v>3.945813657174188</v>
+        <v>3.945813416583232</v>
       </c>
       <c r="F276" t="n">
         <v>15548300</v>
@@ -5952,16 +5952,16 @@
         <v>44816</v>
       </c>
       <c r="B277" t="n">
-        <v>3.856743574142456</v>
+        <v>3.856743097305298</v>
       </c>
       <c r="C277" t="n">
-        <v>3.990349097034463</v>
+        <v>3.990348603678686</v>
       </c>
       <c r="D277" t="n">
-        <v>3.838929532738205</v>
+        <v>3.838929058103526</v>
       </c>
       <c r="E277" t="n">
-        <v>3.954721014225961</v>
+        <v>3.954720525275142</v>
       </c>
       <c r="F277" t="n">
         <v>15738600</v>
@@ -5972,16 +5972,16 @@
         <v>44817</v>
       </c>
       <c r="B278" t="n">
-        <v>3.696417331695557</v>
+        <v>3.696417570114136</v>
       </c>
       <c r="C278" t="n">
-        <v>3.883464985388314</v>
+        <v>3.88346523587145</v>
       </c>
       <c r="D278" t="n">
-        <v>3.678603289663878</v>
+        <v>3.678603526933453</v>
       </c>
       <c r="E278" t="n">
-        <v>3.874557752012343</v>
+        <v>3.874558001920963</v>
       </c>
       <c r="F278" t="n">
         <v>21443000</v>
@@ -6052,16 +6052,16 @@
         <v>44823</v>
       </c>
       <c r="B282" t="n">
-        <v>3.990349054336548</v>
+        <v>3.990349292755127</v>
       </c>
       <c r="C282" t="n">
-        <v>4.008163095550183</v>
+        <v>4.00816333503313</v>
       </c>
       <c r="D282" t="n">
-        <v>3.794394600986558</v>
+        <v>3.794394827697093</v>
       </c>
       <c r="E282" t="n">
-        <v>3.830022683413829</v>
+        <v>3.830022912253099</v>
       </c>
       <c r="F282" t="n">
         <v>8945000</v>
@@ -6072,16 +6072,16 @@
         <v>44824</v>
       </c>
       <c r="B283" t="n">
-        <v>3.963627576828003</v>
+        <v>3.963628053665161</v>
       </c>
       <c r="C283" t="n">
-        <v>4.13286117203624</v>
+        <v>4.132861669232745</v>
       </c>
       <c r="D283" t="n">
-        <v>3.919092688438607</v>
+        <v>3.919093159918075</v>
       </c>
       <c r="E283" t="n">
-        <v>3.990348849637818</v>
+        <v>3.990349329689632</v>
       </c>
       <c r="F283" t="n">
         <v>10696200</v>
@@ -6092,16 +6092,16 @@
         <v>44825</v>
       </c>
       <c r="B284" t="n">
-        <v>3.883464336395264</v>
+        <v>3.883465051651001</v>
       </c>
       <c r="C284" t="n">
-        <v>4.034883880719878</v>
+        <v>4.034884623864039</v>
       </c>
       <c r="D284" t="n">
-        <v>3.830022219231316</v>
+        <v>3.830022924644094</v>
       </c>
       <c r="E284" t="n">
-        <v>3.97253453166851</v>
+        <v>3.972535263329179</v>
       </c>
       <c r="F284" t="n">
         <v>18275700</v>
@@ -6132,16 +6132,16 @@
         <v>44827</v>
       </c>
       <c r="B286" t="n">
-        <v>3.910185575485229</v>
+        <v>3.91018533706665</v>
       </c>
       <c r="C286" t="n">
-        <v>3.990348971645505</v>
+        <v>3.990348728339065</v>
       </c>
       <c r="D286" t="n">
-        <v>3.847836644889669</v>
+        <v>3.847836410272737</v>
       </c>
       <c r="E286" t="n">
-        <v>3.963627698018668</v>
+        <v>3.963627456341523</v>
       </c>
       <c r="F286" t="n">
         <v>14173200</v>
@@ -6172,16 +6172,16 @@
         <v>44831</v>
       </c>
       <c r="B288" t="n">
-        <v>3.73204493522644</v>
+        <v>3.73204517364502</v>
       </c>
       <c r="C288" t="n">
-        <v>3.919092564835227</v>
+        <v>3.919092815203188</v>
       </c>
       <c r="D288" t="n">
-        <v>3.73204493522644</v>
+        <v>3.73204517364502</v>
       </c>
       <c r="E288" t="n">
-        <v>3.838929173654259</v>
+        <v>3.838929418901048</v>
       </c>
       <c r="F288" t="n">
         <v>11052300</v>
@@ -6192,16 +6192,16 @@
         <v>44832</v>
       </c>
       <c r="B289" t="n">
-        <v>3.687509775161743</v>
+        <v>3.687510013580322</v>
       </c>
       <c r="C289" t="n">
-        <v>3.767673169639246</v>
+        <v>3.767673413240847</v>
       </c>
       <c r="D289" t="n">
-        <v>3.687509775161743</v>
+        <v>3.687510013580322</v>
       </c>
       <c r="E289" t="n">
-        <v>3.749859129168715</v>
+        <v>3.749859371618537</v>
       </c>
       <c r="F289" t="n">
         <v>11148900</v>
@@ -6212,16 +6212,16 @@
         <v>44833</v>
       </c>
       <c r="B290" t="n">
-        <v>3.696417331695557</v>
+        <v>3.696417570114136</v>
       </c>
       <c r="C290" t="n">
-        <v>3.714231373727235</v>
+        <v>3.714231613294819</v>
       </c>
       <c r="D290" t="n">
-        <v>3.616253930192871</v>
+        <v>3.616254163440918</v>
       </c>
       <c r="E290" t="n">
-        <v>3.660789247632199</v>
+        <v>3.660789483752771</v>
       </c>
       <c r="F290" t="n">
         <v>12380300</v>
@@ -6232,16 +6232,16 @@
         <v>44834</v>
       </c>
       <c r="B291" t="n">
-        <v>3.73204493522644</v>
+        <v>3.73204517364502</v>
       </c>
       <c r="C291" t="n">
-        <v>3.794394286669439</v>
+        <v>3.794394529071154</v>
       </c>
       <c r="D291" t="n">
-        <v>3.651881544045472</v>
+        <v>3.651881777342879</v>
       </c>
       <c r="E291" t="n">
-        <v>3.660788776274561</v>
+        <v>3.660789010141</v>
       </c>
       <c r="F291" t="n">
         <v>11827700</v>
@@ -6272,16 +6272,16 @@
         <v>44838</v>
       </c>
       <c r="B293" t="n">
-        <v>3.930920362472534</v>
+        <v>3.930919647216797</v>
       </c>
       <c r="C293" t="n">
-        <v>4.056566095699167</v>
+        <v>4.056565357581396</v>
       </c>
       <c r="D293" t="n">
-        <v>3.895021581550639</v>
+        <v>3.895020872826911</v>
       </c>
       <c r="E293" t="n">
-        <v>3.975793624651291</v>
+        <v>3.97579290123058</v>
       </c>
       <c r="F293" t="n">
         <v>11413300</v>
@@ -6312,16 +6312,16 @@
         <v>44840</v>
       </c>
       <c r="B295" t="n">
-        <v>4.0027174949646</v>
+        <v>4.002717971801758</v>
       </c>
       <c r="C295" t="n">
-        <v>4.029641363794418</v>
+        <v>4.029641843838973</v>
       </c>
       <c r="D295" t="n">
-        <v>3.975793198187602</v>
+        <v>3.975793671817313</v>
       </c>
       <c r="E295" t="n">
-        <v>3.993742586723207</v>
+        <v>3.9937430624912</v>
       </c>
       <c r="F295" t="n">
         <v>5975200</v>
@@ -6352,16 +6352,16 @@
         <v>44844</v>
       </c>
       <c r="B297" t="n">
-        <v>3.661679029464722</v>
+        <v>3.661678791046143</v>
       </c>
       <c r="C297" t="n">
-        <v>3.80527415126421</v>
+        <v>3.805273903495892</v>
       </c>
       <c r="D297" t="n">
-        <v>3.634755158100927</v>
+        <v>3.63475492143541</v>
       </c>
       <c r="E297" t="n">
-        <v>3.80527415126421</v>
+        <v>3.805273903495892</v>
       </c>
       <c r="F297" t="n">
         <v>18862600</v>
@@ -6372,16 +6372,16 @@
         <v>44845</v>
       </c>
       <c r="B298" t="n">
-        <v>3.903995752334595</v>
+        <v>3.903996229171753</v>
       </c>
       <c r="C298" t="n">
-        <v>3.948869438891908</v>
+        <v>3.948869921209974</v>
       </c>
       <c r="D298" t="n">
-        <v>3.634754916832287</v>
+        <v>3.634755360784154</v>
       </c>
       <c r="E298" t="n">
-        <v>3.661678786408922</v>
+        <v>3.661679233649292</v>
       </c>
       <c r="F298" t="n">
         <v>30833900</v>
@@ -6392,16 +6392,16 @@
         <v>44847</v>
       </c>
       <c r="B299" t="n">
-        <v>3.814249515533447</v>
+        <v>3.814249038696289</v>
       </c>
       <c r="C299" t="n">
-        <v>3.90399647736831</v>
+        <v>3.903995989311464</v>
       </c>
       <c r="D299" t="n">
-        <v>3.796300123166475</v>
+        <v>3.796299648573254</v>
       </c>
       <c r="E299" t="n">
-        <v>3.895021995158459</v>
+        <v>3.895021508223556</v>
       </c>
       <c r="F299" t="n">
         <v>15027200</v>
@@ -6432,16 +6432,16 @@
         <v>44851</v>
       </c>
       <c r="B301" t="n">
-        <v>3.679628372192383</v>
+        <v>3.679628133773804</v>
       </c>
       <c r="C301" t="n">
-        <v>3.769375322158595</v>
+        <v>3.769375077924933</v>
       </c>
       <c r="D301" t="n">
-        <v>3.670653891169369</v>
+        <v>3.670653653332284</v>
       </c>
       <c r="E301" t="n">
-        <v>3.724502061149096</v>
+        <v>3.724501819822962</v>
       </c>
       <c r="F301" t="n">
         <v>8129100</v>
@@ -6472,16 +6472,16 @@
         <v>44853</v>
       </c>
       <c r="B303" t="n">
-        <v>3.733476638793945</v>
+        <v>3.733476161956787</v>
       </c>
       <c r="C303" t="n">
-        <v>3.769375419709485</v>
+        <v>3.769374938287358</v>
       </c>
       <c r="D303" t="n">
-        <v>3.670653986165363</v>
+        <v>3.670653517351873</v>
       </c>
       <c r="E303" t="n">
-        <v>3.715527248336175</v>
+        <v>3.715526773791502</v>
       </c>
       <c r="F303" t="n">
         <v>12625300</v>
@@ -6572,16 +6572,16 @@
         <v>44860</v>
       </c>
       <c r="B308" t="n">
-        <v>3.562957286834717</v>
+        <v>3.562957525253296</v>
       </c>
       <c r="C308" t="n">
-        <v>3.670653839244302</v>
+        <v>3.670654084869496</v>
       </c>
       <c r="D308" t="n">
-        <v>3.545007897095387</v>
+        <v>3.545008134312866</v>
       </c>
       <c r="E308" t="n">
-        <v>3.661678930401033</v>
+        <v>3.661679175425662</v>
       </c>
       <c r="F308" t="n">
         <v>15630800</v>
@@ -6612,16 +6612,16 @@
         <v>44862</v>
       </c>
       <c r="B310" t="n">
-        <v>3.724501848220825</v>
+        <v>3.724502325057983</v>
       </c>
       <c r="C310" t="n">
-        <v>3.733476328730772</v>
+        <v>3.733476806716907</v>
       </c>
       <c r="D310" t="n">
-        <v>3.643729383895357</v>
+        <v>3.643729850391451</v>
       </c>
       <c r="E310" t="n">
-        <v>3.688603070286659</v>
+        <v>3.688603542527801</v>
       </c>
       <c r="F310" t="n">
         <v>9985100</v>
@@ -6632,16 +6632,16 @@
         <v>44865</v>
       </c>
       <c r="B311" t="n">
-        <v>3.85014796257019</v>
+        <v>3.850147724151611</v>
       </c>
       <c r="C311" t="n">
-        <v>3.868097353362819</v>
+        <v>3.868097113832732</v>
       </c>
       <c r="D311" t="n">
-        <v>3.545008105121898</v>
+        <v>3.545007885598959</v>
       </c>
       <c r="E311" t="n">
-        <v>3.589881582103468</v>
+        <v>3.58988135980176</v>
       </c>
       <c r="F311" t="n">
         <v>19491700</v>
@@ -6672,16 +6672,16 @@
         <v>44868</v>
       </c>
       <c r="B313" t="n">
-        <v>4.218110084533691</v>
+        <v>4.21811056137085</v>
       </c>
       <c r="C313" t="n">
-        <v>4.254008860984833</v>
+        <v>4.254009341880177</v>
       </c>
       <c r="D313" t="n">
-        <v>3.895021096473417</v>
+        <v>3.895021536786911</v>
       </c>
       <c r="E313" t="n">
-        <v>3.975793129514899</v>
+        <v>3.975793578959285</v>
       </c>
       <c r="F313" t="n">
         <v>15015300</v>
@@ -6692,16 +6692,16 @@
         <v>44869</v>
       </c>
       <c r="B314" t="n">
-        <v>4.236059665679932</v>
+        <v>4.23606014251709</v>
       </c>
       <c r="C314" t="n">
-        <v>4.343756427885306</v>
+        <v>4.34375691684548</v>
       </c>
       <c r="D314" t="n">
-        <v>4.15528762895989</v>
+        <v>4.155288096704846</v>
       </c>
       <c r="E314" t="n">
-        <v>4.218110276636901</v>
+        <v>4.218110751453565</v>
       </c>
       <c r="F314" t="n">
         <v>12500600</v>
@@ -6712,16 +6712,16 @@
         <v>44872</v>
       </c>
       <c r="B315" t="n">
-        <v>4.011692047119141</v>
+        <v>4.011692523956299</v>
       </c>
       <c r="C315" t="n">
-        <v>4.37965516061104</v>
+        <v>4.379655681184977</v>
       </c>
       <c r="D315" t="n">
-        <v>4.011692047119141</v>
+        <v>4.011692523956299</v>
       </c>
       <c r="E315" t="n">
-        <v>4.3168320856375</v>
+        <v>4.316832598744169</v>
       </c>
       <c r="F315" t="n">
         <v>17217400</v>
@@ -6752,16 +6752,16 @@
         <v>44874</v>
       </c>
       <c r="B317" t="n">
-        <v>4.011692047119141</v>
+        <v>4.011692523956299</v>
       </c>
       <c r="C317" t="n">
-        <v>4.173236974780477</v>
+        <v>4.173237470819165</v>
       </c>
       <c r="D317" t="n">
-        <v>3.984768177807042</v>
+        <v>3.98476865144398</v>
       </c>
       <c r="E317" t="n">
-        <v>4.06554064163771</v>
+        <v>4.065541124875413</v>
       </c>
       <c r="F317" t="n">
         <v>11339500</v>
@@ -6812,16 +6812,16 @@
         <v>44879</v>
       </c>
       <c r="B320" t="n">
-        <v>3.697577714920044</v>
+        <v>3.697577953338623</v>
       </c>
       <c r="C320" t="n">
-        <v>3.796299572594537</v>
+        <v>3.796299817378669</v>
       </c>
       <c r="D320" t="n">
-        <v>3.64372954562865</v>
+        <v>3.643729780575117</v>
       </c>
       <c r="E320" t="n">
-        <v>3.760400793066941</v>
+        <v>3.760401035536331</v>
       </c>
       <c r="F320" t="n">
         <v>10873300</v>
@@ -6852,16 +6852,16 @@
         <v>44882</v>
       </c>
       <c r="B322" t="n">
-        <v>3.509109258651733</v>
+        <v>3.509108781814575</v>
       </c>
       <c r="C322" t="n">
-        <v>3.57193212526431</v>
+        <v>3.571931639890434</v>
       </c>
       <c r="D322" t="n">
-        <v>3.356539225761863</v>
+        <v>3.356538769656764</v>
       </c>
       <c r="E322" t="n">
-        <v>3.562957430033942</v>
+        <v>3.562956945879597</v>
       </c>
       <c r="F322" t="n">
         <v>25106400</v>
@@ -6952,16 +6952,16 @@
         <v>44889</v>
       </c>
       <c r="B327" t="n">
-        <v>3.724501848220825</v>
+        <v>3.724502325057983</v>
       </c>
       <c r="C327" t="n">
-        <v>3.742451237187908</v>
+        <v>3.742451716323075</v>
       </c>
       <c r="D327" t="n">
-        <v>3.598856125451244</v>
+        <v>3.598856586202345</v>
       </c>
       <c r="E327" t="n">
-        <v>3.63475490338541</v>
+        <v>3.634755368732528</v>
       </c>
       <c r="F327" t="n">
         <v>5511600</v>
@@ -6972,16 +6972,16 @@
         <v>44890</v>
       </c>
       <c r="B328" t="n">
-        <v>3.63475513458252</v>
+        <v>3.63475489616394</v>
       </c>
       <c r="C328" t="n">
-        <v>3.760400865344091</v>
+        <v>3.76040061868389</v>
       </c>
       <c r="D328" t="n">
-        <v>3.580906750282523</v>
+        <v>3.580906515396082</v>
       </c>
       <c r="E328" t="n">
-        <v>3.733476566207289</v>
+        <v>3.733476321313164</v>
       </c>
       <c r="F328" t="n">
         <v>8739900</v>
@@ -7032,16 +7032,16 @@
         <v>44895</v>
       </c>
       <c r="B331" t="n">
-        <v>3.63475513458252</v>
+        <v>3.63475489616394</v>
       </c>
       <c r="C331" t="n">
-        <v>3.661679005772105</v>
+        <v>3.661678765587478</v>
       </c>
       <c r="D331" t="n">
-        <v>3.518083884901738</v>
+        <v>3.518083654136107</v>
       </c>
       <c r="E331" t="n">
-        <v>3.571932055228125</v>
+        <v>3.571931820930371</v>
       </c>
       <c r="F331" t="n">
         <v>16877200</v>
@@ -7052,16 +7052,16 @@
         <v>44896</v>
       </c>
       <c r="B332" t="n">
-        <v>3.446285963058472</v>
+        <v>3.446286201477051</v>
       </c>
       <c r="C332" t="n">
-        <v>3.589881291759341</v>
+        <v>3.589881540112033</v>
       </c>
       <c r="D332" t="n">
-        <v>3.428336573717563</v>
+        <v>3.428336810894379</v>
       </c>
       <c r="E332" t="n">
-        <v>3.589881291759341</v>
+        <v>3.589881540112033</v>
       </c>
       <c r="F332" t="n">
         <v>22625600</v>
@@ -7092,16 +7092,16 @@
         <v>44900</v>
       </c>
       <c r="B334" t="n">
-        <v>3.347564697265625</v>
+        <v>3.347564458847046</v>
       </c>
       <c r="C334" t="n">
-        <v>3.545008216141522</v>
+        <v>3.545007963660719</v>
       </c>
       <c r="D334" t="n">
-        <v>3.329615305910873</v>
+        <v>3.329615068770676</v>
       </c>
       <c r="E334" t="n">
-        <v>3.545008216141522</v>
+        <v>3.545007963660719</v>
       </c>
       <c r="F334" t="n">
         <v>14607600</v>
@@ -7112,16 +7112,16 @@
         <v>44901</v>
       </c>
       <c r="B335" t="n">
-        <v>3.302690982818604</v>
+        <v>3.302690744400024</v>
       </c>
       <c r="C335" t="n">
-        <v>3.401412628213602</v>
+        <v>3.401412382668387</v>
       </c>
       <c r="D335" t="n">
-        <v>3.248842598629542</v>
+        <v>3.248842364098234</v>
       </c>
       <c r="E335" t="n">
-        <v>3.383463238141784</v>
+        <v>3.383462993892321</v>
       </c>
       <c r="F335" t="n">
         <v>13327400</v>
@@ -7132,16 +7132,16 @@
         <v>44902</v>
       </c>
       <c r="B336" t="n">
-        <v>3.230892896652222</v>
+        <v>3.230893611907959</v>
       </c>
       <c r="C336" t="n">
-        <v>3.320640052320865</v>
+        <v>3.320640787444846</v>
       </c>
       <c r="D336" t="n">
-        <v>3.212943508313211</v>
+        <v>3.212944219595309</v>
       </c>
       <c r="E336" t="n">
-        <v>3.302690663981854</v>
+        <v>3.302691395132195</v>
       </c>
       <c r="F336" t="n">
         <v>13628700</v>
@@ -7152,16 +7152,16 @@
         <v>44903</v>
       </c>
       <c r="B337" t="n">
-        <v>3.073575735092163</v>
+        <v>3.073575973510742</v>
       </c>
       <c r="C337" t="n">
-        <v>3.266824548925589</v>
+        <v>3.266824802334561</v>
       </c>
       <c r="D337" t="n">
-        <v>3.064373421071546</v>
+        <v>3.064373658776298</v>
       </c>
       <c r="E337" t="n">
-        <v>3.220812978822505</v>
+        <v>3.22081322866234</v>
       </c>
       <c r="F337" t="n">
         <v>19978800</v>
@@ -7172,16 +7172,16 @@
         <v>44904</v>
       </c>
       <c r="B338" t="n">
-        <v>3.082777976989746</v>
+        <v>3.082778215408325</v>
       </c>
       <c r="C338" t="n">
-        <v>3.119587451611511</v>
+        <v>3.119587692876894</v>
       </c>
       <c r="D338" t="n">
-        <v>2.990754838936502</v>
+        <v>2.990755070238115</v>
       </c>
       <c r="E338" t="n">
-        <v>3.101182604600395</v>
+        <v>3.101182844442367</v>
       </c>
       <c r="F338" t="n">
         <v>12963000</v>
@@ -7232,16 +7232,16 @@
         <v>44909</v>
       </c>
       <c r="B341" t="n">
-        <v>3.073575735092163</v>
+        <v>3.073575973510742</v>
       </c>
       <c r="C341" t="n">
-        <v>3.101182677154013</v>
+        <v>3.101182917714075</v>
       </c>
       <c r="D341" t="n">
-        <v>2.935541024782911</v>
+        <v>2.935541252494079</v>
       </c>
       <c r="E341" t="n">
-        <v>2.981552594885995</v>
+        <v>2.9815528261663</v>
       </c>
       <c r="F341" t="n">
         <v>15438000</v>
@@ -7292,16 +7292,16 @@
         <v>44914</v>
       </c>
       <c r="B344" t="n">
-        <v>3.073575735092163</v>
+        <v>3.073575973510742</v>
       </c>
       <c r="C344" t="n">
-        <v>3.091980363133397</v>
+        <v>3.091980602979631</v>
       </c>
       <c r="D344" t="n">
-        <v>2.990754908906612</v>
+        <v>2.990755140900744</v>
       </c>
       <c r="E344" t="n">
-        <v>3.009159536947845</v>
+        <v>3.009159770369632</v>
       </c>
       <c r="F344" t="n">
         <v>6693400</v>
@@ -7332,16 +7332,16 @@
         <v>44916</v>
       </c>
       <c r="B346" t="n">
-        <v>3.331240653991699</v>
+        <v>3.331240892410278</v>
       </c>
       <c r="C346" t="n">
-        <v>3.37725244220964</v>
+        <v>3.377252683921307</v>
       </c>
       <c r="D346" t="n">
-        <v>3.23921751635675</v>
+        <v>3.239217748189187</v>
       </c>
       <c r="E346" t="n">
-        <v>3.266824457647235</v>
+        <v>3.266824691455514</v>
       </c>
       <c r="F346" t="n">
         <v>14610300</v>
@@ -7352,16 +7352,16 @@
         <v>44917</v>
       </c>
       <c r="B347" t="n">
-        <v>3.340442895889282</v>
+        <v>3.340443134307861</v>
       </c>
       <c r="C347" t="n">
-        <v>3.3588475218115</v>
+        <v>3.358847761543679</v>
       </c>
       <c r="D347" t="n">
-        <v>3.257621859838854</v>
+        <v>3.257622092346219</v>
       </c>
       <c r="E347" t="n">
-        <v>3.331240363527726</v>
+        <v>3.33124060128949</v>
       </c>
       <c r="F347" t="n">
         <v>7727000</v>
@@ -7392,16 +7392,16 @@
         <v>44921</v>
       </c>
       <c r="B349" t="n">
-        <v>3.340442895889282</v>
+        <v>3.340443134307861</v>
       </c>
       <c r="C349" t="n">
-        <v>3.441668338461481</v>
+        <v>3.441668584104859</v>
       </c>
       <c r="D349" t="n">
-        <v>3.28522879872218</v>
+        <v>3.285229033199945</v>
       </c>
       <c r="E349" t="n">
-        <v>3.441668338461481</v>
+        <v>3.441668584104859</v>
       </c>
       <c r="F349" t="n">
         <v>5290600</v>
@@ -7412,16 +7412,16 @@
         <v>44922</v>
       </c>
       <c r="B350" t="n">
-        <v>3.386455059051514</v>
+        <v>3.386454820632935</v>
       </c>
       <c r="C350" t="n">
-        <v>3.39565737363859</v>
+        <v>3.395657134572136</v>
       </c>
       <c r="D350" t="n">
-        <v>3.276027064606107</v>
+        <v>3.276026833962055</v>
       </c>
       <c r="E350" t="n">
-        <v>3.349645800703207</v>
+        <v>3.349645564876132</v>
       </c>
       <c r="F350" t="n">
         <v>5669100</v>
@@ -7432,16 +7432,16 @@
         <v>44923</v>
       </c>
       <c r="B351" t="n">
-        <v>3.450870990753174</v>
+        <v>3.450871229171753</v>
       </c>
       <c r="C351" t="n">
-        <v>3.542894129413071</v>
+        <v>3.542894374189473</v>
       </c>
       <c r="D351" t="n">
-        <v>3.358847852093277</v>
+        <v>3.358848084154033</v>
       </c>
       <c r="E351" t="n">
-        <v>3.395657107557235</v>
+        <v>3.395657342161121</v>
       </c>
       <c r="F351" t="n">
         <v>9716800</v>
@@ -7452,16 +7452,16 @@
         <v>44924</v>
       </c>
       <c r="B352" t="n">
-        <v>3.441668510437012</v>
+        <v>3.44166898727417</v>
       </c>
       <c r="C352" t="n">
-        <v>3.598108057993386</v>
+        <v>3.59810855650497</v>
       </c>
       <c r="D352" t="n">
-        <v>3.404859256753267</v>
+        <v>3.404859728490568</v>
       </c>
       <c r="E352" t="n">
-        <v>3.524489331225437</v>
+        <v>3.524489819537276</v>
       </c>
       <c r="F352" t="n">
         <v>7177700</v>
@@ -7492,16 +7492,16 @@
         <v>44929</v>
       </c>
       <c r="B354" t="n">
-        <v>3.073575735092163</v>
+        <v>3.073575973510742</v>
       </c>
       <c r="C354" t="n">
-        <v>3.285229176966823</v>
+        <v>3.28522943180345</v>
       </c>
       <c r="D354" t="n">
-        <v>3.064373421071546</v>
+        <v>3.064373658776298</v>
       </c>
       <c r="E354" t="n">
-        <v>3.257622234904972</v>
+        <v>3.257622487600117</v>
       </c>
       <c r="F354" t="n">
         <v>9560100</v>
@@ -7512,16 +7512,16 @@
         <v>44930</v>
       </c>
       <c r="B355" t="n">
-        <v>3.055170774459839</v>
+        <v>3.055171012878418</v>
       </c>
       <c r="C355" t="n">
-        <v>3.147194124048661</v>
+        <v>3.147194369648533</v>
       </c>
       <c r="D355" t="n">
-        <v>3.036766148422164</v>
+        <v>3.036766385404488</v>
       </c>
       <c r="E355" t="n">
-        <v>3.110384871973312</v>
+        <v>3.110385114700673</v>
       </c>
       <c r="F355" t="n">
         <v>10680900</v>
@@ -7552,16 +7552,16 @@
         <v>44932</v>
       </c>
       <c r="B357" t="n">
-        <v>2.963147878646851</v>
+        <v>2.96314811706543</v>
       </c>
       <c r="C357" t="n">
-        <v>3.018361761127114</v>
+        <v>3.018362003988271</v>
       </c>
       <c r="D357" t="n">
-        <v>2.917136309913298</v>
+        <v>2.917136544629729</v>
       </c>
       <c r="E357" t="n">
-        <v>2.981552506140272</v>
+        <v>2.98155274603971</v>
       </c>
       <c r="F357" t="n">
         <v>37999700</v>
@@ -7592,16 +7592,16 @@
         <v>44936</v>
       </c>
       <c r="B359" t="n">
-        <v>3.082777976989746</v>
+        <v>3.082778215408325</v>
       </c>
       <c r="C359" t="n">
-        <v>3.082777976989746</v>
+        <v>3.082778215408325</v>
       </c>
       <c r="D359" t="n">
-        <v>2.953945583715205</v>
+        <v>2.953945812170032</v>
       </c>
       <c r="E359" t="n">
-        <v>2.963147897520529</v>
+        <v>2.963148126687053</v>
       </c>
       <c r="F359" t="n">
         <v>12594800</v>
@@ -7632,16 +7632,16 @@
         <v>44938</v>
       </c>
       <c r="B361" t="n">
-        <v>3.211610794067383</v>
+        <v>3.211610555648804</v>
       </c>
       <c r="C361" t="n">
-        <v>3.349645729332935</v>
+        <v>3.349645480667133</v>
       </c>
       <c r="D361" t="n">
-        <v>3.165599222112359</v>
+        <v>3.165598987109516</v>
       </c>
       <c r="E361" t="n">
-        <v>3.266824680413411</v>
+        <v>3.266824437895949</v>
       </c>
       <c r="F361" t="n">
         <v>13176700</v>
@@ -7652,16 +7652,16 @@
         <v>44939</v>
       </c>
       <c r="B362" t="n">
-        <v>3.073575735092163</v>
+        <v>3.073575973510742</v>
       </c>
       <c r="C362" t="n">
-        <v>3.220812978822505</v>
+        <v>3.22081322866234</v>
       </c>
       <c r="D362" t="n">
-        <v>3.05517110705093</v>
+        <v>3.055171344041854</v>
       </c>
       <c r="E362" t="n">
-        <v>3.184003722740037</v>
+        <v>3.184003969724563</v>
       </c>
       <c r="F362" t="n">
         <v>14486700</v>
@@ -7692,16 +7692,16 @@
         <v>44943</v>
       </c>
       <c r="B364" t="n">
-        <v>3.091980218887329</v>
+        <v>3.091980457305908</v>
       </c>
       <c r="C364" t="n">
-        <v>3.128789692653045</v>
+        <v>3.128789933909955</v>
       </c>
       <c r="D364" t="n">
-        <v>3.027564023748135</v>
+        <v>3.027564257199665</v>
       </c>
       <c r="E364" t="n">
-        <v>3.055170964522075</v>
+        <v>3.055171200102341</v>
       </c>
       <c r="F364" t="n">
         <v>11859400</v>
@@ -7712,16 +7712,16 @@
         <v>44944</v>
       </c>
       <c r="B365" t="n">
-        <v>3.082777976989746</v>
+        <v>3.082778215408325</v>
       </c>
       <c r="C365" t="n">
-        <v>3.174801334443457</v>
+        <v>3.174801579979019</v>
       </c>
       <c r="D365" t="n">
-        <v>3.064373349379097</v>
+        <v>3.064373586374283</v>
       </c>
       <c r="E365" t="n">
-        <v>3.128789765416836</v>
+        <v>3.128790007393915</v>
       </c>
       <c r="F365" t="n">
         <v>13324700</v>
@@ -7752,16 +7752,16 @@
         <v>44946</v>
       </c>
       <c r="B367" t="n">
-        <v>3.02756404876709</v>
+        <v>3.027564287185669</v>
       </c>
       <c r="C367" t="n">
-        <v>3.13799203217586</v>
+        <v>3.137992279290566</v>
       </c>
       <c r="D367" t="n">
-        <v>3.009159421432372</v>
+        <v>3.009159658401599</v>
       </c>
       <c r="E367" t="n">
-        <v>3.128789718508501</v>
+        <v>3.128789964898532</v>
       </c>
       <c r="F367" t="n">
         <v>19274300</v>
@@ -7772,16 +7772,16 @@
         <v>44949</v>
       </c>
       <c r="B368" t="n">
-        <v>3.02756404876709</v>
+        <v>3.027564287185669</v>
       </c>
       <c r="C368" t="n">
-        <v>3.082777930771243</v>
+        <v>3.082778173537877</v>
       </c>
       <c r="D368" t="n">
-        <v>2.990754794097655</v>
+        <v>2.99075502961753</v>
       </c>
       <c r="E368" t="n">
-        <v>3.018361735099731</v>
+        <v>3.018361972793634</v>
       </c>
       <c r="F368" t="n">
         <v>10637200</v>
@@ -7812,16 +7812,16 @@
         <v>44951</v>
       </c>
       <c r="B370" t="n">
-        <v>3.248420000076294</v>
+        <v>3.248419761657715</v>
       </c>
       <c r="C370" t="n">
-        <v>3.248420000076294</v>
+        <v>3.248419761657715</v>
       </c>
       <c r="D370" t="n">
-        <v>3.147194543381774</v>
+        <v>3.147194312392662</v>
       </c>
       <c r="E370" t="n">
-        <v>3.193206114606555</v>
+        <v>3.193205880240413</v>
       </c>
       <c r="F370" t="n">
         <v>7649000</v>
@@ -7852,16 +7852,16 @@
         <v>44953</v>
       </c>
       <c r="B372" t="n">
-        <v>3.147194623947144</v>
+        <v>3.147194147109985</v>
       </c>
       <c r="C372" t="n">
-        <v>3.220813139791363</v>
+        <v>3.22081265180013</v>
       </c>
       <c r="D372" t="n">
-        <v>3.128789994986088</v>
+        <v>3.128789520937449</v>
       </c>
       <c r="E372" t="n">
-        <v>3.211610825310835</v>
+        <v>3.211610338713862</v>
       </c>
       <c r="F372" t="n">
         <v>8557200</v>
@@ -7892,16 +7892,16 @@
         <v>44957</v>
       </c>
       <c r="B374" t="n">
-        <v>3.02756404876709</v>
+        <v>3.027564287185669</v>
       </c>
       <c r="C374" t="n">
-        <v>3.082777930771243</v>
+        <v>3.082778173537877</v>
       </c>
       <c r="D374" t="n">
-        <v>2.990754794097655</v>
+        <v>2.99075502961753</v>
       </c>
       <c r="E374" t="n">
-        <v>2.990754794097655</v>
+        <v>2.99075502961753</v>
       </c>
       <c r="F374" t="n">
         <v>20039900</v>
@@ -7932,16 +7932,16 @@
         <v>44959</v>
       </c>
       <c r="B376" t="n">
-        <v>2.806708335876465</v>
+        <v>2.806708574295044</v>
       </c>
       <c r="C376" t="n">
-        <v>2.972350203327015</v>
+        <v>2.972350455816205</v>
       </c>
       <c r="D376" t="n">
-        <v>2.797506022095904</v>
+        <v>2.797506259732784</v>
       </c>
       <c r="E376" t="n">
-        <v>2.898731693082534</v>
+        <v>2.898731939318127</v>
       </c>
       <c r="F376" t="n">
         <v>50857000</v>
@@ -8032,16 +8032,16 @@
         <v>44966</v>
       </c>
       <c r="B381" t="n">
-        <v>3.018361806869507</v>
+        <v>3.018362045288086</v>
       </c>
       <c r="C381" t="n">
-        <v>3.091980317958858</v>
+        <v>3.091980562192519</v>
       </c>
       <c r="D381" t="n">
-        <v>2.935540981893987</v>
+        <v>2.935541213770599</v>
       </c>
       <c r="E381" t="n">
-        <v>3.036766434641845</v>
+        <v>3.036766674514194</v>
       </c>
       <c r="F381" t="n">
         <v>43678900</v>
@@ -8052,16 +8052,16 @@
         <v>44967</v>
       </c>
       <c r="B382" t="n">
-        <v>2.953945636749268</v>
+        <v>2.953945875167847</v>
       </c>
       <c r="C382" t="n">
-        <v>3.045968776454661</v>
+        <v>3.045969022300604</v>
       </c>
       <c r="D382" t="n">
-        <v>2.92633869483765</v>
+        <v>2.92633893102802</v>
       </c>
       <c r="E382" t="n">
-        <v>3.018361834543043</v>
+        <v>3.018362078160776</v>
       </c>
       <c r="F382" t="n">
         <v>23226200</v>
@@ -8072,16 +8072,16 @@
         <v>44970</v>
       </c>
       <c r="B383" t="n">
-        <v>2.963147878646851</v>
+        <v>2.96314811706543</v>
       </c>
       <c r="C383" t="n">
-        <v>2.963147878646851</v>
+        <v>2.96314811706543</v>
       </c>
       <c r="D383" t="n">
-        <v>2.880327054926456</v>
+        <v>2.880327286681168</v>
       </c>
       <c r="E383" t="n">
-        <v>2.95394556490014</v>
+        <v>2.95394580257829</v>
       </c>
       <c r="F383" t="n">
         <v>14875700</v>
@@ -8132,16 +8132,16 @@
         <v>44973</v>
       </c>
       <c r="B386" t="n">
-        <v>2.834315299987793</v>
+        <v>2.834315538406372</v>
       </c>
       <c r="C386" t="n">
-        <v>2.871124555405743</v>
+        <v>2.871124796920665</v>
       </c>
       <c r="D386" t="n">
-        <v>2.760696789151893</v>
+        <v>2.760697021377787</v>
       </c>
       <c r="E386" t="n">
-        <v>2.825112986133305</v>
+        <v>2.825113223777799</v>
       </c>
       <c r="F386" t="n">
         <v>21149000</v>
@@ -8172,16 +8172,16 @@
         <v>44979</v>
       </c>
       <c r="B388" t="n">
-        <v>2.834315299987793</v>
+        <v>2.834315538406372</v>
       </c>
       <c r="C388" t="n">
-        <v>2.84351761384228</v>
+        <v>2.843517853034945</v>
       </c>
       <c r="D388" t="n">
-        <v>2.714685219879454</v>
+        <v>2.714685448234921</v>
       </c>
       <c r="E388" t="n">
-        <v>2.76989910300638</v>
+        <v>2.76989933600636</v>
       </c>
       <c r="F388" t="n">
         <v>20601900</v>
@@ -8192,16 +8192,16 @@
         <v>44980</v>
       </c>
       <c r="B389" t="n">
-        <v>2.797505855560303</v>
+        <v>2.797506093978882</v>
       </c>
       <c r="C389" t="n">
-        <v>2.898731520520965</v>
+        <v>2.898731767566543</v>
       </c>
       <c r="D389" t="n">
-        <v>2.751494289396572</v>
+        <v>2.751494523893796</v>
       </c>
       <c r="E389" t="n">
-        <v>2.85271973495678</v>
+        <v>2.852719978080985</v>
       </c>
       <c r="F389" t="n">
         <v>24919500</v>
@@ -8212,16 +8212,16 @@
         <v>44981</v>
       </c>
       <c r="B390" t="n">
-        <v>2.659471035003662</v>
+        <v>2.65947151184082</v>
       </c>
       <c r="C390" t="n">
-        <v>2.80670803996966</v>
+        <v>2.806708543206081</v>
       </c>
       <c r="D390" t="n">
-        <v>2.650268722193287</v>
+        <v>2.650269197380491</v>
       </c>
       <c r="E390" t="n">
-        <v>2.797505727159285</v>
+        <v>2.797506228745752</v>
       </c>
       <c r="F390" t="n">
         <v>27929600</v>
@@ -8232,16 +8232,16 @@
         <v>44984</v>
       </c>
       <c r="B391" t="n">
-        <v>2.797505855560303</v>
+        <v>2.797506093978882</v>
       </c>
       <c r="C391" t="n">
-        <v>2.834315108491288</v>
+        <v>2.83431535004695</v>
       </c>
       <c r="D391" t="n">
-        <v>2.641066311203163</v>
+        <v>2.641066536289118</v>
       </c>
       <c r="E391" t="n">
-        <v>2.677875783534602</v>
+        <v>2.677876011757659</v>
       </c>
       <c r="F391" t="n">
         <v>32246200</v>
@@ -8252,16 +8252,16 @@
         <v>44985</v>
       </c>
       <c r="B392" t="n">
-        <v>2.834315299987793</v>
+        <v>2.834315538406372</v>
       </c>
       <c r="C392" t="n">
-        <v>2.889529402515187</v>
+        <v>2.889529645578298</v>
       </c>
       <c r="D392" t="n">
-        <v>2.797506044569843</v>
+        <v>2.79750627989208</v>
       </c>
       <c r="E392" t="n">
-        <v>2.825112986133305</v>
+        <v>2.825113223777799</v>
       </c>
       <c r="F392" t="n">
         <v>28842300</v>
@@ -8332,16 +8332,16 @@
         <v>44991</v>
       </c>
       <c r="B396" t="n">
-        <v>2.677875995635986</v>
+        <v>2.677875757217407</v>
       </c>
       <c r="C396" t="n">
-        <v>2.714685251482452</v>
+        <v>2.714685009786644</v>
       </c>
       <c r="D396" t="n">
-        <v>2.576650322657736</v>
+        <v>2.576650093251554</v>
       </c>
       <c r="E396" t="n">
-        <v>2.64106652038905</v>
+        <v>2.641066285247719</v>
       </c>
       <c r="F396" t="n">
         <v>24268000</v>
@@ -8352,16 +8352,16 @@
         <v>44992</v>
       </c>
       <c r="B397" t="n">
-        <v>2.677875995635986</v>
+        <v>2.677875757217407</v>
       </c>
       <c r="C397" t="n">
-        <v>2.696280623559219</v>
+        <v>2.696280383502025</v>
       </c>
       <c r="D397" t="n">
-        <v>2.622661892465818</v>
+        <v>2.6226616589631</v>
       </c>
       <c r="E397" t="n">
-        <v>2.677875995635986</v>
+        <v>2.677875757217407</v>
       </c>
       <c r="F397" t="n">
         <v>12209500</v>
@@ -8372,16 +8372,16 @@
         <v>44993</v>
       </c>
       <c r="B398" t="n">
-        <v>2.705482721328735</v>
+        <v>2.705482959747314</v>
       </c>
       <c r="C398" t="n">
-        <v>2.733089661007544</v>
+        <v>2.733089901858964</v>
       </c>
       <c r="D398" t="n">
-        <v>2.659471155197387</v>
+        <v>2.659471389561232</v>
       </c>
       <c r="E398" t="n">
-        <v>2.677875781649926</v>
+        <v>2.677876017635665</v>
       </c>
       <c r="F398" t="n">
         <v>21816400</v>
@@ -8432,16 +8432,16 @@
         <v>44998</v>
       </c>
       <c r="B401" t="n">
-        <v>2.411008358001709</v>
+        <v>2.41100811958313</v>
       </c>
       <c r="C401" t="n">
-        <v>2.475424772623468</v>
+        <v>2.475424527834911</v>
       </c>
       <c r="D401" t="n">
-        <v>2.401806044398667</v>
+        <v>2.401805806890081</v>
       </c>
       <c r="E401" t="n">
-        <v>2.475424772623468</v>
+        <v>2.475424527834911</v>
       </c>
       <c r="F401" t="n">
         <v>31528700</v>
@@ -8452,16 +8452,16 @@
         <v>44999</v>
       </c>
       <c r="B402" t="n">
-        <v>2.493829488754272</v>
+        <v>2.493829250335693</v>
       </c>
       <c r="C402" t="n">
-        <v>2.585852628066047</v>
+        <v>2.585852380849743</v>
       </c>
       <c r="D402" t="n">
-        <v>2.46622254696074</v>
+        <v>2.466222311181478</v>
       </c>
       <c r="E402" t="n">
-        <v>2.475424860891918</v>
+        <v>2.475424624232883</v>
       </c>
       <c r="F402" t="n">
         <v>40119200</v>
@@ -8472,16 +8472,16 @@
         <v>45000</v>
       </c>
       <c r="B403" t="n">
-        <v>2.493829488754272</v>
+        <v>2.493829250335693</v>
       </c>
       <c r="C403" t="n">
-        <v>2.521436430547805</v>
+        <v>2.521436189489909</v>
       </c>
       <c r="D403" t="n">
-        <v>2.447817919098385</v>
+        <v>2.447817685078669</v>
       </c>
       <c r="E403" t="n">
-        <v>2.475424860891918</v>
+        <v>2.475424624232883</v>
       </c>
       <c r="F403" t="n">
         <v>17612600</v>
@@ -8512,16 +8512,16 @@
         <v>45002</v>
       </c>
       <c r="B405" t="n">
-        <v>2.349629878997803</v>
+        <v>2.349630117416382</v>
       </c>
       <c r="C405" t="n">
-        <v>2.549396016044544</v>
+        <v>2.549396274733532</v>
       </c>
       <c r="D405" t="n">
-        <v>2.349629878997803</v>
+        <v>2.349630117416382</v>
       </c>
       <c r="E405" t="n">
-        <v>2.492319814888502</v>
+        <v>2.492320067785928</v>
       </c>
       <c r="F405" t="n">
         <v>44089800</v>
@@ -8532,16 +8532,16 @@
         <v>45005</v>
       </c>
       <c r="B406" t="n">
-        <v>2.349629878997803</v>
+        <v>2.349630117416382</v>
       </c>
       <c r="C406" t="n">
-        <v>2.406705853354083</v>
+        <v>2.406706097564201</v>
       </c>
       <c r="D406" t="n">
-        <v>2.311579229426949</v>
+        <v>2.311579463984502</v>
       </c>
       <c r="E406" t="n">
-        <v>2.359142541390516</v>
+        <v>2.359142780774352</v>
       </c>
       <c r="F406" t="n">
         <v>20939200</v>
@@ -8612,16 +8612,16 @@
         <v>45009</v>
       </c>
       <c r="B410" t="n">
-        <v>2.292554140090942</v>
+        <v>2.292554378509521</v>
       </c>
       <c r="C410" t="n">
-        <v>2.302066803460623</v>
+        <v>2.30206704286849</v>
       </c>
       <c r="D410" t="n">
-        <v>2.149863962745944</v>
+        <v>2.149864186325184</v>
       </c>
       <c r="E410" t="n">
-        <v>2.159376626115625</v>
+        <v>2.159376850684152</v>
       </c>
       <c r="F410" t="n">
         <v>19141800</v>
@@ -8692,16 +8692,16 @@
         <v>45015</v>
       </c>
       <c r="B414" t="n">
-        <v>2.749162435531616</v>
+        <v>2.749162673950195</v>
       </c>
       <c r="C414" t="n">
-        <v>2.796725752381689</v>
+        <v>2.796725994925153</v>
       </c>
       <c r="D414" t="n">
-        <v>2.644522911661672</v>
+        <v>2.644523141005484</v>
       </c>
       <c r="E414" t="n">
-        <v>2.673060901771716</v>
+        <v>2.673061133590459</v>
       </c>
       <c r="F414" t="n">
         <v>39786400</v>
@@ -8712,16 +8712,16 @@
         <v>45016</v>
       </c>
       <c r="B415" t="n">
-        <v>2.711111545562744</v>
+        <v>2.711111783981323</v>
       </c>
       <c r="C415" t="n">
-        <v>2.787213079050672</v>
+        <v>2.787213324161716</v>
       </c>
       <c r="D415" t="n">
-        <v>2.654035565546636</v>
+        <v>2.654035798945881</v>
       </c>
       <c r="E415" t="n">
-        <v>2.777700415714654</v>
+        <v>2.777700659989142</v>
       </c>
       <c r="F415" t="n">
         <v>25812800</v>
@@ -8732,16 +8732,16 @@
         <v>45019</v>
       </c>
       <c r="B416" t="n">
-        <v>2.692086458206177</v>
+        <v>2.692085981369019</v>
       </c>
       <c r="C416" t="n">
-        <v>2.76818799845922</v>
+        <v>2.768187508142538</v>
       </c>
       <c r="D416" t="n">
-        <v>2.673061129842867</v>
+        <v>2.67306065637558</v>
       </c>
       <c r="E416" t="n">
-        <v>2.739650005914255</v>
+        <v>2.73964952065238</v>
       </c>
       <c r="F416" t="n">
         <v>18815900</v>
@@ -8752,16 +8752,16 @@
         <v>45020</v>
       </c>
       <c r="B417" t="n">
-        <v>2.692086458206177</v>
+        <v>2.692085981369019</v>
       </c>
       <c r="C417" t="n">
-        <v>2.739650005914255</v>
+        <v>2.73964952065238</v>
       </c>
       <c r="D417" t="n">
-        <v>2.654035801479557</v>
+        <v>2.654035331382141</v>
       </c>
       <c r="E417" t="n">
-        <v>2.720624450751141</v>
+        <v>2.720623968859177</v>
       </c>
       <c r="F417" t="n">
         <v>21012200</v>
@@ -8792,16 +8792,16 @@
         <v>45022</v>
       </c>
       <c r="B419" t="n">
-        <v>2.654035806655884</v>
+        <v>2.654035568237305</v>
       </c>
       <c r="C419" t="n">
-        <v>2.682573799256508</v>
+        <v>2.68257355827429</v>
       </c>
       <c r="D419" t="n">
-        <v>2.615985149855052</v>
+        <v>2.615984914854657</v>
       </c>
       <c r="E419" t="n">
-        <v>2.6730611350563</v>
+        <v>2.673060894928629</v>
       </c>
       <c r="F419" t="n">
         <v>14613400</v>
@@ -8812,16 +8812,16 @@
         <v>45026</v>
       </c>
       <c r="B420" t="n">
-        <v>2.673060894012451</v>
+        <v>2.67306113243103</v>
       </c>
       <c r="C420" t="n">
-        <v>2.701598884039655</v>
+        <v>2.701599125003626</v>
       </c>
       <c r="D420" t="n">
-        <v>2.644522903985246</v>
+        <v>2.644523139858434</v>
       </c>
       <c r="E420" t="n">
-        <v>2.673060894012451</v>
+        <v>2.67306113243103</v>
       </c>
       <c r="F420" t="n">
         <v>14149600</v>
@@ -8872,16 +8872,16 @@
         <v>45029</v>
       </c>
       <c r="B423" t="n">
-        <v>2.882339715957642</v>
+        <v>2.882339954376221</v>
       </c>
       <c r="C423" t="n">
-        <v>2.95844102273943</v>
+        <v>2.958441267452883</v>
       </c>
       <c r="D423" t="n">
-        <v>2.853801725914471</v>
+        <v>2.853801961972472</v>
       </c>
       <c r="E423" t="n">
-        <v>2.929903032696259</v>
+        <v>2.929903275049135</v>
       </c>
       <c r="F423" t="n">
         <v>15780900</v>
@@ -8892,16 +8892,16 @@
         <v>45030</v>
       </c>
       <c r="B424" t="n">
-        <v>2.891852140426636</v>
+        <v>2.891852378845215</v>
       </c>
       <c r="C424" t="n">
-        <v>2.901364802988575</v>
+        <v>2.901365042191425</v>
       </c>
       <c r="D424" t="n">
-        <v>2.815750839931124</v>
+        <v>2.815751072075536</v>
       </c>
       <c r="E424" t="n">
-        <v>2.863314152740819</v>
+        <v>2.863314388806585</v>
       </c>
       <c r="F424" t="n">
         <v>10628600</v>
@@ -8912,16 +8912,16 @@
         <v>45033</v>
       </c>
       <c r="B425" t="n">
-        <v>2.967953681945801</v>
+        <v>2.96795392036438</v>
       </c>
       <c r="C425" t="n">
-        <v>2.986979235414485</v>
+        <v>2.986979475361405</v>
       </c>
       <c r="D425" t="n">
-        <v>2.872827048601301</v>
+        <v>2.872827279378266</v>
       </c>
       <c r="E425" t="n">
-        <v>2.901365038604651</v>
+        <v>2.9013652716741</v>
       </c>
       <c r="F425" t="n">
         <v>14970900</v>
@@ -8932,16 +8932,16 @@
         <v>45034</v>
       </c>
       <c r="B426" t="n">
-        <v>3.025030136108398</v>
+        <v>3.025029897689819</v>
       </c>
       <c r="C426" t="n">
-        <v>3.034542800220697</v>
+        <v>3.034542561052375</v>
       </c>
       <c r="D426" t="n">
-        <v>2.948928596410207</v>
+        <v>2.948928363989592</v>
       </c>
       <c r="E426" t="n">
-        <v>2.986979479659204</v>
+        <v>2.986979244239598</v>
       </c>
       <c r="F426" t="n">
         <v>13884000</v>
@@ -8952,16 +8952,16 @@
         <v>45035</v>
       </c>
       <c r="B427" t="n">
-        <v>2.882339715957642</v>
+        <v>2.882339954376221</v>
       </c>
       <c r="C427" t="n">
-        <v>2.996491902930108</v>
+        <v>2.996492150791017</v>
       </c>
       <c r="D427" t="n">
-        <v>2.872827052609918</v>
+        <v>2.872827290241638</v>
       </c>
       <c r="E427" t="n">
-        <v>2.986979239582385</v>
+        <v>2.986979486656434</v>
       </c>
       <c r="F427" t="n">
         <v>19845900</v>
@@ -8972,16 +8972,16 @@
         <v>45036</v>
       </c>
       <c r="B428" t="n">
-        <v>2.958441257476807</v>
+        <v>2.958441019058228</v>
       </c>
       <c r="C428" t="n">
-        <v>2.977466812481619</v>
+        <v>2.977466572529786</v>
       </c>
       <c r="D428" t="n">
-        <v>2.844289288246741</v>
+        <v>2.844289059027585</v>
       </c>
       <c r="E428" t="n">
-        <v>2.882339944656763</v>
+        <v>2.882339712371133</v>
       </c>
       <c r="F428" t="n">
         <v>11874200</v>
@@ -9012,16 +9012,16 @@
         <v>45041</v>
       </c>
       <c r="B430" t="n">
-        <v>3.025030136108398</v>
+        <v>3.025029897689819</v>
       </c>
       <c r="C430" t="n">
-        <v>3.148694769568281</v>
+        <v>3.14869452140304</v>
       </c>
       <c r="D430" t="n">
-        <v>2.977466815546905</v>
+        <v>2.977466580877042</v>
       </c>
       <c r="E430" t="n">
-        <v>3.072593456669892</v>
+        <v>3.072593214502596</v>
       </c>
       <c r="F430" t="n">
         <v>18942800</v>
@@ -9032,16 +9032,16 @@
         <v>45042</v>
       </c>
       <c r="B431" t="n">
-        <v>2.901365041732788</v>
+        <v>2.901364803314209</v>
       </c>
       <c r="C431" t="n">
-        <v>3.034542555358458</v>
+        <v>3.034542305996067</v>
       </c>
       <c r="D431" t="n">
-        <v>2.891852378388082</v>
+        <v>2.891852140751202</v>
       </c>
       <c r="E431" t="n">
-        <v>3.015517228669046</v>
+        <v>3.015516980870054</v>
       </c>
       <c r="F431" t="n">
         <v>15122100</v>
@@ -9092,16 +9092,16 @@
         <v>45048</v>
       </c>
       <c r="B434" t="n">
-        <v>2.891852140426636</v>
+        <v>2.891852378845215</v>
       </c>
       <c r="C434" t="n">
-        <v>3.082105618465181</v>
+        <v>3.082105872569197</v>
       </c>
       <c r="D434" t="n">
-        <v>2.891852140426636</v>
+        <v>2.891852378845215</v>
       </c>
       <c r="E434" t="n">
-        <v>3.025029643093547</v>
+        <v>3.025029892491938</v>
       </c>
       <c r="F434" t="n">
         <v>14598900</v>
@@ -9132,16 +9132,16 @@
         <v>45050</v>
       </c>
       <c r="B436" t="n">
-        <v>3.025030136108398</v>
+        <v>3.025029897689819</v>
       </c>
       <c r="C436" t="n">
-        <v>3.063080792557593</v>
+        <v>3.063080551140041</v>
       </c>
       <c r="D436" t="n">
-        <v>2.958441260522505</v>
+        <v>2.958441027352147</v>
       </c>
       <c r="E436" t="n">
-        <v>3.0155174719961</v>
+        <v>3.015517234327264</v>
       </c>
       <c r="F436" t="n">
         <v>20441800</v>
@@ -9192,16 +9192,16 @@
         <v>45055</v>
       </c>
       <c r="B439" t="n">
-        <v>3.025030136108398</v>
+        <v>3.025029897689819</v>
       </c>
       <c r="C439" t="n">
-        <v>3.158207433680579</v>
+        <v>3.158207184765595</v>
       </c>
       <c r="D439" t="n">
-        <v>3.0155174719961</v>
+        <v>3.015517234327264</v>
       </c>
       <c r="E439" t="n">
-        <v>3.129669441343684</v>
+        <v>3.129669194677929</v>
       </c>
       <c r="F439" t="n">
         <v>32144800</v>
@@ -9252,16 +9252,16 @@
         <v>45058</v>
       </c>
       <c r="B442" t="n">
-        <v>3.129669189453125</v>
+        <v>3.129669427871704</v>
       </c>
       <c r="C442" t="n">
-        <v>3.21528338637298</v>
+        <v>3.215283631313659</v>
       </c>
       <c r="D442" t="n">
-        <v>3.091618536066427</v>
+        <v>3.091618771586302</v>
       </c>
       <c r="E442" t="n">
-        <v>3.167719842839823</v>
+        <v>3.167720084157106</v>
       </c>
       <c r="F442" t="n">
         <v>13638800</v>
@@ -9272,16 +9272,16 @@
         <v>45061</v>
       </c>
       <c r="B443" t="n">
-        <v>2.986979246139526</v>
+        <v>2.986979484558105</v>
       </c>
       <c r="C443" t="n">
-        <v>3.205770503617468</v>
+        <v>3.20577075949981</v>
       </c>
       <c r="D443" t="n">
-        <v>2.901365049022286</v>
+        <v>2.901365280607201</v>
       </c>
       <c r="E443" t="n">
-        <v>3.186745176880255</v>
+        <v>3.18674543124401</v>
       </c>
       <c r="F443" t="n">
         <v>71533500</v>
@@ -9312,16 +9312,16 @@
         <v>45063</v>
       </c>
       <c r="B445" t="n">
-        <v>3.253334283828735</v>
+        <v>3.253334522247314</v>
       </c>
       <c r="C445" t="n">
-        <v>3.300897604130366</v>
+        <v>3.300897846034593</v>
       </c>
       <c r="D445" t="n">
-        <v>3.082106103943065</v>
+        <v>3.082106329813293</v>
       </c>
       <c r="E445" t="n">
-        <v>3.091618768003391</v>
+        <v>3.091618994570749</v>
       </c>
       <c r="F445" t="n">
         <v>27916800</v>
@@ -9332,16 +9332,16 @@
         <v>45064</v>
       </c>
       <c r="B446" t="n">
-        <v>3.300897359848022</v>
+        <v>3.300897598266602</v>
       </c>
       <c r="C446" t="n">
-        <v>3.338948013273395</v>
+        <v>3.338948254440312</v>
       </c>
       <c r="D446" t="n">
-        <v>3.177232509415779</v>
+        <v>3.177232738902241</v>
       </c>
       <c r="E446" t="n">
-        <v>3.253334043066307</v>
+        <v>3.253334278049463</v>
       </c>
       <c r="F446" t="n">
         <v>40825600</v>
@@ -9372,16 +9372,16 @@
         <v>45068</v>
       </c>
       <c r="B448" t="n">
-        <v>3.472126007080078</v>
+        <v>3.472125291824341</v>
       </c>
       <c r="C448" t="n">
-        <v>3.576765318466137</v>
+        <v>3.576764581654768</v>
       </c>
       <c r="D448" t="n">
-        <v>3.453100677737158</v>
+        <v>3.453099966400627</v>
       </c>
       <c r="E448" t="n">
-        <v>3.548227324451757</v>
+        <v>3.548226593519197</v>
       </c>
       <c r="F448" t="n">
         <v>14142300</v>
@@ -9392,16 +9392,16 @@
         <v>45069</v>
       </c>
       <c r="B449" t="n">
-        <v>3.472126007080078</v>
+        <v>3.472125291824341</v>
       </c>
       <c r="C449" t="n">
-        <v>3.567252653794676</v>
+        <v>3.567251918942911</v>
       </c>
       <c r="D449" t="n">
-        <v>3.443587786265883</v>
+        <v>3.443587076889001</v>
       </c>
       <c r="E449" t="n">
-        <v>3.472126007080078</v>
+        <v>3.472125291824341</v>
       </c>
       <c r="F449" t="n">
         <v>12031500</v>
@@ -9412,16 +9412,16 @@
         <v>45070</v>
       </c>
       <c r="B450" t="n">
-        <v>3.319922924041748</v>
+        <v>3.319922685623169</v>
       </c>
       <c r="C450" t="n">
-        <v>3.529201759651233</v>
+        <v>3.529201506203401</v>
       </c>
       <c r="D450" t="n">
-        <v>3.262846939820925</v>
+        <v>3.262846705501229</v>
       </c>
       <c r="E450" t="n">
-        <v>3.462613111393607</v>
+        <v>3.462612862727804</v>
       </c>
       <c r="F450" t="n">
         <v>35329500</v>
@@ -9452,16 +9452,16 @@
         <v>45072</v>
       </c>
       <c r="B452" t="n">
-        <v>3.291384935379028</v>
+        <v>3.291384696960449</v>
       </c>
       <c r="C452" t="n">
-        <v>3.348460919659638</v>
+        <v>3.348460677106637</v>
       </c>
       <c r="D452" t="n">
-        <v>3.177232740018008</v>
+        <v>3.17723250986829</v>
       </c>
       <c r="E452" t="n">
-        <v>3.33894825561287</v>
+        <v>3.338948013748939</v>
       </c>
       <c r="F452" t="n">
         <v>25686400</v>
@@ -9472,16 +9472,16 @@
         <v>45075</v>
       </c>
       <c r="B453" t="n">
-        <v>3.357973337173462</v>
+        <v>3.357973575592041</v>
       </c>
       <c r="C453" t="n">
-        <v>3.415049317263714</v>
+        <v>3.415049559734729</v>
       </c>
       <c r="D453" t="n">
-        <v>3.291384693734835</v>
+        <v>3.291384927425571</v>
       </c>
       <c r="E453" t="n">
-        <v>3.319922683779961</v>
+        <v>3.319922919496916</v>
       </c>
       <c r="F453" t="n">
         <v>14544800</v>
@@ -9492,16 +9492,16 @@
         <v>45076</v>
       </c>
       <c r="B454" t="n">
-        <v>3.424561977386475</v>
+        <v>3.424562215805054</v>
       </c>
       <c r="C454" t="n">
-        <v>3.46261285754392</v>
+        <v>3.462613098611607</v>
       </c>
       <c r="D454" t="n">
-        <v>3.310410017313492</v>
+        <v>3.310410247784792</v>
       </c>
       <c r="E454" t="n">
-        <v>3.396023987368229</v>
+        <v>3.396024223799988</v>
       </c>
       <c r="F454" t="n">
         <v>24140700</v>
@@ -9512,16 +9512,16 @@
         <v>45077</v>
       </c>
       <c r="B455" t="n">
-        <v>3.453099966049194</v>
+        <v>3.453100442886353</v>
       </c>
       <c r="C455" t="n">
-        <v>3.557739255868972</v>
+        <v>3.557739747155727</v>
       </c>
       <c r="D455" t="n">
-        <v>3.41504908840587</v>
+        <v>3.415049559988598</v>
       </c>
       <c r="E455" t="n">
-        <v>3.424561751116759</v>
+        <v>3.424562224013087</v>
       </c>
       <c r="F455" t="n">
         <v>23066900</v>
@@ -9532,16 +9532,16 @@
         <v>45078</v>
       </c>
       <c r="B456" t="n">
-        <v>3.576765060424805</v>
+        <v>3.576764822006226</v>
       </c>
       <c r="C456" t="n">
-        <v>3.662379036291428</v>
+        <v>3.662378792166026</v>
       </c>
       <c r="D456" t="n">
-        <v>3.376998889936218</v>
+        <v>3.376998664833572</v>
       </c>
       <c r="E456" t="n">
-        <v>3.472125756587821</v>
+        <v>3.472125525144246</v>
       </c>
       <c r="F456" t="n">
         <v>28377100</v>
@@ -9552,16 +9552,16 @@
         <v>45079</v>
       </c>
       <c r="B457" t="n">
-        <v>3.529201745986938</v>
+        <v>3.529201507568359</v>
       </c>
       <c r="C457" t="n">
-        <v>3.643353713986613</v>
+        <v>3.643353467856389</v>
       </c>
       <c r="D457" t="n">
-        <v>3.491151089987047</v>
+        <v>3.491150854139016</v>
       </c>
       <c r="E457" t="n">
-        <v>3.614815721986695</v>
+        <v>3.614815477784382</v>
       </c>
       <c r="F457" t="n">
         <v>24144300</v>
@@ -9572,16 +9572,16 @@
         <v>45082</v>
       </c>
       <c r="B458" t="n">
-        <v>3.586277723312378</v>
+        <v>3.586277484893799</v>
       </c>
       <c r="C458" t="n">
-        <v>3.605303051276916</v>
+        <v>3.605302811593518</v>
       </c>
       <c r="D458" t="n">
-        <v>3.500663747471958</v>
+        <v>3.500663514745063</v>
       </c>
       <c r="E458" t="n">
-        <v>3.510176411454227</v>
+        <v>3.510176178094923</v>
       </c>
       <c r="F458" t="n">
         <v>11705300</v>
@@ -9652,16 +9652,16 @@
         <v>45089</v>
       </c>
       <c r="B462" t="n">
-        <v>3.795556545257568</v>
+        <v>3.795556306838989</v>
       </c>
       <c r="C462" t="n">
-        <v>3.805069209208598</v>
+        <v>3.805068970192479</v>
       </c>
       <c r="D462" t="n">
-        <v>3.747993225502421</v>
+        <v>3.74799299007154</v>
       </c>
       <c r="E462" t="n">
-        <v>3.786043881306539</v>
+        <v>3.786043643485499</v>
       </c>
       <c r="F462" t="n">
         <v>16242400</v>
@@ -9772,16 +9772,16 @@
         <v>45097</v>
       </c>
       <c r="B468" t="n">
-        <v>3.947759389877319</v>
+        <v>3.947758913040161</v>
       </c>
       <c r="C468" t="n">
-        <v>3.966784717753371</v>
+        <v>3.966784238618205</v>
       </c>
       <c r="D468" t="n">
-        <v>3.767018548255029</v>
+        <v>3.767018093248975</v>
       </c>
       <c r="E468" t="n">
-        <v>3.786043876131081</v>
+        <v>3.786043418827019</v>
       </c>
       <c r="F468" t="n">
         <v>35176100</v>
@@ -9892,16 +9892,16 @@
         <v>45105</v>
       </c>
       <c r="B474" t="n">
-        <v>4.176063537597656</v>
+        <v>4.176063060760498</v>
       </c>
       <c r="C474" t="n">
-        <v>4.261677744210696</v>
+        <v>4.261677257597817</v>
       </c>
       <c r="D474" t="n">
-        <v>4.090449784584236</v>
+        <v>4.090449317522748</v>
       </c>
       <c r="E474" t="n">
-        <v>4.223627086515927</v>
+        <v>4.223626604247801</v>
       </c>
       <c r="F474" t="n">
         <v>30177100</v>
@@ -9912,16 +9912,16 @@
         <v>45106</v>
       </c>
       <c r="B475" t="n">
-        <v>4.366316318511963</v>
+        <v>4.366317272186279</v>
       </c>
       <c r="C475" t="n">
-        <v>4.366316318511963</v>
+        <v>4.366317272186279</v>
       </c>
       <c r="D475" t="n">
-        <v>4.185575507448556</v>
+        <v>4.185576421646147</v>
       </c>
       <c r="E475" t="n">
-        <v>4.185575507448556</v>
+        <v>4.185576421646147</v>
       </c>
       <c r="F475" t="n">
         <v>40765500</v>
@@ -9932,16 +9932,16 @@
         <v>45107</v>
       </c>
       <c r="B476" t="n">
-        <v>4.18557596206665</v>
+        <v>4.185576438903809</v>
       </c>
       <c r="C476" t="n">
-        <v>4.489981189679052</v>
+        <v>4.489981701195243</v>
       </c>
       <c r="D476" t="n">
-        <v>4.138012418452428</v>
+        <v>4.138012889870962</v>
       </c>
       <c r="E476" t="n">
-        <v>4.413879882775952</v>
+        <v>4.413880385622384</v>
       </c>
       <c r="F476" t="n">
         <v>35419200</v>
@@ -9972,16 +9972,16 @@
         <v>45111</v>
       </c>
       <c r="B478" t="n">
-        <v>4.195088863372803</v>
+        <v>4.195087909698486</v>
       </c>
       <c r="C478" t="n">
-        <v>4.261677741089692</v>
+        <v>4.26167677227765</v>
       </c>
       <c r="D478" t="n">
-        <v>4.138012876872448</v>
+        <v>4.138011936173281</v>
       </c>
       <c r="E478" t="n">
-        <v>4.252164849873157</v>
+        <v>4.252163883223692</v>
       </c>
       <c r="F478" t="n">
         <v>10806500</v>
@@ -9992,16 +9992,16 @@
         <v>45112</v>
       </c>
       <c r="B479" t="n">
-        <v>4.080936908721924</v>
+        <v>4.080936431884766</v>
       </c>
       <c r="C479" t="n">
-        <v>4.185576444576225</v>
+        <v>4.185575955512459</v>
       </c>
       <c r="D479" t="n">
-        <v>4.023860921964928</v>
+        <v>4.023860451796815</v>
       </c>
       <c r="E479" t="n">
-        <v>4.166551115657227</v>
+        <v>4.166550628816475</v>
       </c>
       <c r="F479" t="n">
         <v>33346200</v>
@@ -10012,16 +10012,16 @@
         <v>45113</v>
       </c>
       <c r="B480" t="n">
-        <v>3.957271814346313</v>
+        <v>3.957271575927734</v>
       </c>
       <c r="C480" t="n">
-        <v>4.061911344129392</v>
+        <v>4.061911099406468</v>
       </c>
       <c r="D480" t="n">
-        <v>3.909708721608256</v>
+        <v>3.909708486055269</v>
       </c>
       <c r="E480" t="n">
-        <v>4.061911344129392</v>
+        <v>4.061911099406468</v>
       </c>
       <c r="F480" t="n">
         <v>22675100</v>
@@ -10032,16 +10032,16 @@
         <v>45114</v>
       </c>
       <c r="B481" t="n">
-        <v>3.995322465896606</v>
+        <v>3.995322704315186</v>
       </c>
       <c r="C481" t="n">
-        <v>4.042886012185687</v>
+        <v>4.042886253442594</v>
       </c>
       <c r="D481" t="n">
-        <v>3.94775937320712</v>
+        <v>3.947759608787399</v>
       </c>
       <c r="E481" t="n">
-        <v>3.976297138100893</v>
+        <v>3.976297375384147</v>
       </c>
       <c r="F481" t="n">
         <v>19055100</v>
@@ -10052,16 +10052,16 @@
         <v>45117</v>
       </c>
       <c r="B482" t="n">
-        <v>4.03337287902832</v>
+        <v>4.033372402191162</v>
       </c>
       <c r="C482" t="n">
-        <v>4.099961749110232</v>
+        <v>4.099961264400743</v>
       </c>
       <c r="D482" t="n">
-        <v>3.947759135893939</v>
+        <v>3.947758669178288</v>
       </c>
       <c r="E482" t="n">
-        <v>3.995322225724247</v>
+        <v>3.995321753385549</v>
       </c>
       <c r="F482" t="n">
         <v>16685100</v>
@@ -10112,16 +10112,16 @@
         <v>45120</v>
       </c>
       <c r="B485" t="n">
-        <v>3.995322465896606</v>
+        <v>3.995322704315186</v>
       </c>
       <c r="C485" t="n">
-        <v>4.071424230679055</v>
+        <v>4.071424473638964</v>
       </c>
       <c r="D485" t="n">
-        <v>3.957271810305179</v>
+        <v>3.957272046453107</v>
       </c>
       <c r="E485" t="n">
-        <v>4.023860684389974</v>
+        <v>4.023860924511555</v>
       </c>
       <c r="F485" t="n">
         <v>10522300</v>
@@ -10132,16 +10132,16 @@
         <v>45121</v>
       </c>
       <c r="B486" t="n">
-        <v>3.881170511245728</v>
+        <v>3.881170272827148</v>
       </c>
       <c r="C486" t="n">
-        <v>4.014347806231721</v>
+        <v>4.01434755963212</v>
       </c>
       <c r="D486" t="n">
-        <v>3.814582090552529</v>
+        <v>3.814581856224446</v>
       </c>
       <c r="E486" t="n">
-        <v>3.995322478376579</v>
+        <v>3.995322232945695</v>
       </c>
       <c r="F486" t="n">
         <v>16845900</v>
@@ -10172,16 +10172,16 @@
         <v>45125</v>
       </c>
       <c r="B488" t="n">
-        <v>4.071424007415771</v>
+        <v>4.07142448425293</v>
       </c>
       <c r="C488" t="n">
-        <v>4.185575967930341</v>
+        <v>4.185576458136752</v>
       </c>
       <c r="D488" t="n">
-        <v>4.004835136982487</v>
+        <v>4.004835606020889</v>
       </c>
       <c r="E488" t="n">
-        <v>4.023860463734916</v>
+        <v>4.023860935001526</v>
       </c>
       <c r="F488" t="n">
         <v>19854400</v>
@@ -10212,16 +10212,16 @@
         <v>45127</v>
       </c>
       <c r="B490" t="n">
-        <v>3.995322465896606</v>
+        <v>3.995322704315186</v>
       </c>
       <c r="C490" t="n">
-        <v>4.080936667777115</v>
+        <v>4.080936911304672</v>
       </c>
       <c r="D490" t="n">
-        <v>3.94775937320712</v>
+        <v>3.947759608787399</v>
       </c>
       <c r="E490" t="n">
-        <v>4.071424230679055</v>
+        <v>4.071424473638964</v>
       </c>
       <c r="F490" t="n">
         <v>13981900</v>
@@ -10232,16 +10232,16 @@
         <v>45128</v>
       </c>
       <c r="B491" t="n">
-        <v>4.061911106109619</v>
+        <v>4.061911582946777</v>
       </c>
       <c r="C491" t="n">
-        <v>4.099961759510212</v>
+        <v>4.099962240814224</v>
       </c>
       <c r="D491" t="n">
-        <v>3.976296909158501</v>
+        <v>3.97629737594521</v>
       </c>
       <c r="E491" t="n">
-        <v>4.00483512600873</v>
+        <v>4.004835596145607</v>
       </c>
       <c r="F491" t="n">
         <v>9991000</v>
@@ -10272,16 +10272,16 @@
         <v>45132</v>
       </c>
       <c r="B493" t="n">
-        <v>3.995322465896606</v>
+        <v>3.995322704315186</v>
       </c>
       <c r="C493" t="n">
-        <v>4.090449558474769</v>
+        <v>4.090449802570003</v>
       </c>
       <c r="D493" t="n">
-        <v>3.966784701002833</v>
+        <v>3.966784937718438</v>
       </c>
       <c r="E493" t="n">
-        <v>4.061911339981402</v>
+        <v>4.061911582373633</v>
       </c>
       <c r="F493" t="n">
         <v>14413200</v>
@@ -10312,16 +10312,16 @@
         <v>45134</v>
       </c>
       <c r="B495" t="n">
-        <v>3.893998384475708</v>
+        <v>3.893998622894287</v>
       </c>
       <c r="C495" t="n">
-        <v>4.056646575563136</v>
+        <v>4.056646823940207</v>
       </c>
       <c r="D495" t="n">
-        <v>3.884430602296878</v>
+        <v>3.884430840129649</v>
       </c>
       <c r="E495" t="n">
-        <v>4.047079249601271</v>
+        <v>4.047079497392562</v>
       </c>
       <c r="F495" t="n">
         <v>18331700</v>
@@ -10352,16 +10352,16 @@
         <v>45138</v>
       </c>
       <c r="B497" t="n">
-        <v>3.980106353759766</v>
+        <v>3.980106115341187</v>
       </c>
       <c r="C497" t="n">
-        <v>4.008809245599202</v>
+        <v>4.008809005461245</v>
       </c>
       <c r="D497" t="n">
-        <v>3.922701026297883</v>
+        <v>3.922700791318031</v>
       </c>
       <c r="E497" t="n">
-        <v>3.941836135451844</v>
+        <v>3.941835899325749</v>
       </c>
       <c r="F497" t="n">
         <v>13989300</v>
@@ -10372,16 +10372,16 @@
         <v>45139</v>
       </c>
       <c r="B498" t="n">
-        <v>3.980106353759766</v>
+        <v>3.980106115341187</v>
       </c>
       <c r="C498" t="n">
-        <v>4.018376572067687</v>
+        <v>4.018376331356624</v>
       </c>
       <c r="D498" t="n">
-        <v>3.884430807989962</v>
+        <v>3.884430575302593</v>
       </c>
       <c r="E498" t="n">
-        <v>3.970539027291279</v>
+        <v>3.970538789445808</v>
       </c>
       <c r="F498" t="n">
         <v>24308900</v>
@@ -10392,16 +10392,16 @@
         <v>45140</v>
       </c>
       <c r="B499" t="n">
-        <v>4.008808612823486</v>
+        <v>4.008809089660645</v>
       </c>
       <c r="C499" t="n">
-        <v>4.018375937781805</v>
+        <v>4.018376415756972</v>
       </c>
       <c r="D499" t="n">
-        <v>3.932268188289268</v>
+        <v>3.932268656022146</v>
       </c>
       <c r="E499" t="n">
-        <v>3.951403294422822</v>
+        <v>3.95140376443177</v>
       </c>
       <c r="F499" t="n">
         <v>25721100</v>
@@ -10432,16 +10432,16 @@
         <v>45142</v>
       </c>
       <c r="B501" t="n">
-        <v>3.903565883636475</v>
+        <v>3.903565645217896</v>
       </c>
       <c r="C501" t="n">
-        <v>3.960971210605601</v>
+        <v>3.96097096868087</v>
       </c>
       <c r="D501" t="n">
-        <v>3.865295665657057</v>
+        <v>3.865295429575913</v>
       </c>
       <c r="E501" t="n">
-        <v>3.903565883636475</v>
+        <v>3.903565645217896</v>
       </c>
       <c r="F501" t="n">
         <v>16409800</v>
@@ -10452,16 +10452,16 @@
         <v>45145</v>
       </c>
       <c r="B502" t="n">
-        <v>3.846160650253296</v>
+        <v>3.846160411834717</v>
       </c>
       <c r="C502" t="n">
-        <v>3.922701088074537</v>
+        <v>3.922700844911313</v>
       </c>
       <c r="D502" t="n">
-        <v>3.817457986070331</v>
+        <v>3.817457749430993</v>
       </c>
       <c r="E502" t="n">
-        <v>3.913133761455379</v>
+        <v>3.913133518885223</v>
       </c>
       <c r="F502" t="n">
         <v>14729300</v>
@@ -10552,16 +10552,16 @@
         <v>45152</v>
       </c>
       <c r="B507" t="n">
-        <v>3.606971502304077</v>
+        <v>3.606971263885498</v>
       </c>
       <c r="C507" t="n">
-        <v>3.664376829848003</v>
+        <v>3.664376587634967</v>
       </c>
       <c r="D507" t="n">
-        <v>3.56870128394146</v>
+        <v>3.568701048052518</v>
       </c>
       <c r="E507" t="n">
-        <v>3.664376829848003</v>
+        <v>3.664376587634967</v>
       </c>
       <c r="F507" t="n">
         <v>20072900</v>
@@ -10632,16 +10632,16 @@
         <v>45156</v>
       </c>
       <c r="B511" t="n">
-        <v>3.434755325317383</v>
+        <v>3.434755086898804</v>
       </c>
       <c r="C511" t="n">
-        <v>3.473025772164581</v>
+        <v>3.473025531089514</v>
       </c>
       <c r="D511" t="n">
-        <v>3.33907977847063</v>
+        <v>3.339079546693231</v>
       </c>
       <c r="E511" t="n">
-        <v>3.35821488783998</v>
+        <v>3.358214654734345</v>
       </c>
       <c r="F511" t="n">
         <v>15864700</v>
@@ -10652,16 +10652,16 @@
         <v>45159</v>
       </c>
       <c r="B512" t="n">
-        <v>3.348647356033325</v>
+        <v>3.348647117614746</v>
       </c>
       <c r="C512" t="n">
-        <v>3.463458013033817</v>
+        <v>3.463457766440895</v>
       </c>
       <c r="D512" t="n">
-        <v>3.329512246533243</v>
+        <v>3.329512009477055</v>
       </c>
       <c r="E512" t="n">
-        <v>3.444322903533735</v>
+        <v>3.444322658303203</v>
       </c>
       <c r="F512" t="n">
         <v>12295100</v>
@@ -10692,16 +10692,16 @@
         <v>45161</v>
       </c>
       <c r="B514" t="n">
-        <v>3.453890323638916</v>
+        <v>3.453890085220337</v>
       </c>
       <c r="C514" t="n">
-        <v>3.559133649895108</v>
+        <v>3.559133404211688</v>
       </c>
       <c r="D514" t="n">
-        <v>3.377349888622405</v>
+        <v>3.377349655487335</v>
       </c>
       <c r="E514" t="n">
-        <v>3.396484997376533</v>
+        <v>3.396484762920585</v>
       </c>
       <c r="F514" t="n">
         <v>43718400</v>
@@ -10732,16 +10732,16 @@
         <v>45163</v>
       </c>
       <c r="B516" t="n">
-        <v>3.62610650062561</v>
+        <v>3.626106739044189</v>
       </c>
       <c r="C516" t="n">
-        <v>3.664376717818205</v>
+        <v>3.664376958753072</v>
       </c>
       <c r="D516" t="n">
-        <v>3.549566066240422</v>
+        <v>3.549566299626424</v>
       </c>
       <c r="E516" t="n">
-        <v>3.616538946327462</v>
+        <v>3.616539184116969</v>
       </c>
       <c r="F516" t="n">
         <v>21198200</v>
@@ -10772,16 +10772,16 @@
         <v>45167</v>
       </c>
       <c r="B518" t="n">
-        <v>3.65480899810791</v>
+        <v>3.654809236526489</v>
       </c>
       <c r="C518" t="n">
-        <v>3.664376551973043</v>
+        <v>3.664376791015754</v>
       </c>
       <c r="D518" t="n">
-        <v>3.578268567186847</v>
+        <v>3.578268800612372</v>
       </c>
       <c r="E518" t="n">
-        <v>3.616538782647379</v>
+        <v>3.61653901856943</v>
       </c>
       <c r="F518" t="n">
         <v>13520200</v>
@@ -10792,16 +10792,16 @@
         <v>45168</v>
       </c>
       <c r="B519" t="n">
-        <v>3.587836265563965</v>
+        <v>3.587836503982544</v>
       </c>
       <c r="C519" t="n">
-        <v>3.683511808068943</v>
+        <v>3.683512052845344</v>
       </c>
       <c r="D519" t="n">
-        <v>3.549566048561974</v>
+        <v>3.549566284437424</v>
       </c>
       <c r="E519" t="n">
-        <v>3.654809145317449</v>
+        <v>3.654809388186504</v>
       </c>
       <c r="F519" t="n">
         <v>15075000</v>
@@ -10812,16 +10812,16 @@
         <v>45169</v>
       </c>
       <c r="B520" t="n">
-        <v>3.473025560379028</v>
+        <v>3.473025798797607</v>
       </c>
       <c r="C520" t="n">
-        <v>3.597403763695208</v>
+        <v>3.597404010652185</v>
       </c>
       <c r="D520" t="n">
-        <v>3.463457778169301</v>
+        <v>3.463458015931064</v>
       </c>
       <c r="E520" t="n">
-        <v>3.587836209593963</v>
+        <v>3.58783645589414</v>
       </c>
       <c r="F520" t="n">
         <v>21889800</v>
@@ -10832,16 +10832,16 @@
         <v>45170</v>
       </c>
       <c r="B521" t="n">
-        <v>3.473025560379028</v>
+        <v>3.473025798797607</v>
       </c>
       <c r="C521" t="n">
-        <v>3.578268655492719</v>
+        <v>3.578268901136096</v>
       </c>
       <c r="D521" t="n">
-        <v>3.473025560379028</v>
+        <v>3.473025798797607</v>
       </c>
       <c r="E521" t="n">
-        <v>3.501728222682762</v>
+        <v>3.50172846307174</v>
       </c>
       <c r="F521" t="n">
         <v>17307200</v>
@@ -10912,16 +10912,16 @@
         <v>45177</v>
       </c>
       <c r="B525" t="n">
-        <v>3.549566268920898</v>
+        <v>3.549566030502319</v>
       </c>
       <c r="C525" t="n">
-        <v>3.587836488298725</v>
+        <v>3.587836247309597</v>
       </c>
       <c r="D525" t="n">
-        <v>3.511296049543073</v>
+        <v>3.511295813695041</v>
       </c>
       <c r="E525" t="n">
-        <v>3.530431159231985</v>
+        <v>3.53043092209868</v>
       </c>
       <c r="F525" t="n">
         <v>26042800</v>
@@ -11012,16 +11012,16 @@
         <v>45184</v>
       </c>
       <c r="B530" t="n">
-        <v>3.807890176773071</v>
+        <v>3.80789041519165</v>
       </c>
       <c r="C530" t="n">
-        <v>3.941835934005541</v>
+        <v>3.941836180810695</v>
       </c>
       <c r="D530" t="n">
-        <v>3.788755068597004</v>
+        <v>3.788755305817501</v>
       </c>
       <c r="E530" t="n">
-        <v>3.788755068597004</v>
+        <v>3.788755305817501</v>
       </c>
       <c r="F530" t="n">
         <v>34682000</v>
@@ -11032,16 +11032,16 @@
         <v>45187</v>
       </c>
       <c r="B531" t="n">
-        <v>3.817457914352417</v>
+        <v>3.817457675933838</v>
       </c>
       <c r="C531" t="n">
-        <v>3.884430796187795</v>
+        <v>3.884430553586438</v>
       </c>
       <c r="D531" t="n">
-        <v>3.740917477969129</v>
+        <v>3.740917244330867</v>
       </c>
       <c r="E531" t="n">
-        <v>3.817457914352417</v>
+        <v>3.817457675933838</v>
       </c>
       <c r="F531" t="n">
         <v>23371600</v>
@@ -11112,16 +11112,16 @@
         <v>45191</v>
       </c>
       <c r="B535" t="n">
-        <v>3.606971502304077</v>
+        <v>3.606971263885498</v>
       </c>
       <c r="C535" t="n">
-        <v>3.664376829848003</v>
+        <v>3.664376587634967</v>
       </c>
       <c r="D535" t="n">
-        <v>3.559133729350806</v>
+        <v>3.559133494094274</v>
       </c>
       <c r="E535" t="n">
-        <v>3.597403947713423</v>
+        <v>3.597403709927253</v>
       </c>
       <c r="F535" t="n">
         <v>21984900</v>
@@ -11192,16 +11192,16 @@
         <v>45197</v>
       </c>
       <c r="B539" t="n">
-        <v>3.415620088577271</v>
+        <v>3.41562032699585</v>
       </c>
       <c r="C539" t="n">
-        <v>3.444322751560954</v>
+        <v>3.444322991983049</v>
       </c>
       <c r="D539" t="n">
-        <v>3.329512099626217</v>
+        <v>3.32951233203425</v>
       </c>
       <c r="E539" t="n">
-        <v>3.415620088577271</v>
+        <v>3.41562032699585</v>
       </c>
       <c r="F539" t="n">
         <v>16733500</v>
@@ -11252,16 +11252,16 @@
         <v>45202</v>
       </c>
       <c r="B542" t="n">
-        <v>3.31037712097168</v>
+        <v>3.310376882553101</v>
       </c>
       <c r="C542" t="n">
-        <v>3.406052668007885</v>
+        <v>3.406052422698603</v>
       </c>
       <c r="D542" t="n">
-        <v>3.272106902157197</v>
+        <v>3.2721066664949</v>
       </c>
       <c r="E542" t="n">
-        <v>3.3199446756753</v>
+        <v>3.31994443656765</v>
       </c>
       <c r="F542" t="n">
         <v>29291500</v>
@@ -11292,16 +11292,16 @@
         <v>45204</v>
       </c>
       <c r="B544" t="n">
-        <v>3.23383641242981</v>
+        <v>3.233836650848389</v>
       </c>
       <c r="C544" t="n">
-        <v>3.35821461315716</v>
+        <v>3.358214860745675</v>
       </c>
       <c r="D544" t="n">
-        <v>3.20513352261502</v>
+        <v>3.205133758917443</v>
       </c>
       <c r="E544" t="n">
-        <v>3.310376843646641</v>
+        <v>3.310377087708257</v>
       </c>
       <c r="F544" t="n">
         <v>37198300</v>
@@ -11312,16 +11312,16 @@
         <v>45205</v>
       </c>
       <c r="B545" t="n">
-        <v>3.23383641242981</v>
+        <v>3.233836650848389</v>
       </c>
       <c r="C545" t="n">
-        <v>3.262539074136121</v>
+        <v>3.262539314670839</v>
       </c>
       <c r="D545" t="n">
-        <v>3.138160645300292</v>
+        <v>3.138160876665057</v>
       </c>
       <c r="E545" t="n">
-        <v>3.20513352261502</v>
+        <v>3.205133758917443</v>
       </c>
       <c r="F545" t="n">
         <v>15875400</v>
@@ -11352,16 +11352,16 @@
         <v>45209</v>
       </c>
       <c r="B547" t="n">
-        <v>3.415620088577271</v>
+        <v>3.41562032699585</v>
       </c>
       <c r="C547" t="n">
-        <v>3.425187642905165</v>
+        <v>3.425187881991583</v>
       </c>
       <c r="D547" t="n">
-        <v>3.348647208282007</v>
+        <v>3.348647442025716</v>
       </c>
       <c r="E547" t="n">
-        <v>3.367782316937797</v>
+        <v>3.367782552017183</v>
       </c>
       <c r="F547" t="n">
         <v>9595500</v>
@@ -11372,16 +11372,16 @@
         <v>45210</v>
       </c>
       <c r="B548" t="n">
-        <v>3.482593059539795</v>
+        <v>3.482593536376953</v>
       </c>
       <c r="C548" t="n">
-        <v>3.511295721390723</v>
+        <v>3.511296202157854</v>
       </c>
       <c r="D548" t="n">
-        <v>3.396484845878531</v>
+        <v>3.39648531092574</v>
       </c>
       <c r="E548" t="n">
-        <v>3.41561995377915</v>
+        <v>3.415620421446341</v>
       </c>
       <c r="F548" t="n">
         <v>15610900</v>
@@ -26092,19 +26092,39 @@
         <v>46289</v>
       </c>
       <c r="B1284" t="n">
-        <v>0.29</v>
+        <v>0.2899999916553497</v>
       </c>
       <c r="C1284" t="n">
-        <v>0.29</v>
+        <v>0.2899999916553497</v>
       </c>
       <c r="D1284" t="n">
-        <v>0.27</v>
+        <v>0.2700000107288361</v>
       </c>
       <c r="E1284" t="n">
-        <v>0.28</v>
+        <v>0.2800000011920929</v>
       </c>
       <c r="F1284" t="n">
         <v>8311500</v>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1285" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C1285" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D1285" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E1285" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F1285" t="n">
+        <v>6197400</v>
       </c>
     </row>
   </sheetData>

--- a/database/RAIZ4.xlsx
+++ b/database/RAIZ4.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1285"/>
+  <dimension ref="A1:F1286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>44414</v>
       </c>
       <c r="B3" t="n">
-        <v>6.261024475097656</v>
+        <v>6.261024951934814</v>
       </c>
       <c r="C3" t="n">
-        <v>6.48148308633695</v>
+        <v>6.481483579964149</v>
       </c>
       <c r="D3" t="n">
-        <v>6.19929633306517</v>
+        <v>6.199296805201136</v>
       </c>
       <c r="E3" t="n">
-        <v>6.393299725939519</v>
+        <v>6.393300212850708</v>
       </c>
       <c r="F3" t="n">
         <v>28799900</v>
@@ -492,16 +492,16 @@
         <v>44417</v>
       </c>
       <c r="B4" t="n">
-        <v>6.234569549560547</v>
+        <v>6.234570503234863</v>
       </c>
       <c r="C4" t="n">
-        <v>6.446209610180686</v>
+        <v>6.44621059622864</v>
       </c>
       <c r="D4" t="n">
-        <v>6.234569549560547</v>
+        <v>6.234570503234863</v>
       </c>
       <c r="E4" t="n">
-        <v>6.331571033765733</v>
+        <v>6.331572002277935</v>
       </c>
       <c r="F4" t="n">
         <v>14491100</v>
@@ -512,16 +512,16 @@
         <v>44418</v>
       </c>
       <c r="B5" t="n">
-        <v>6.261024475097656</v>
+        <v>6.261024951934814</v>
       </c>
       <c r="C5" t="n">
-        <v>6.313934491336116</v>
+        <v>6.313934972202879</v>
       </c>
       <c r="D5" t="n">
-        <v>6.216933005144656</v>
+        <v>6.216933478623825</v>
       </c>
       <c r="E5" t="n">
-        <v>6.278661147177143</v>
+        <v>6.278661625357502</v>
       </c>
       <c r="F5" t="n">
         <v>9988600</v>
@@ -532,16 +532,16 @@
         <v>44419</v>
       </c>
       <c r="B6" t="n">
-        <v>6.058203220367432</v>
+        <v>6.058202743530273</v>
       </c>
       <c r="C6" t="n">
-        <v>6.296298530585189</v>
+        <v>6.296298035007707</v>
       </c>
       <c r="D6" t="n">
-        <v>5.996475071361166</v>
+        <v>5.996474599382589</v>
       </c>
       <c r="E6" t="n">
-        <v>6.287480403794928</v>
+        <v>6.287479908911514</v>
       </c>
       <c r="F6" t="n">
         <v>31978000</v>
@@ -572,16 +572,16 @@
         <v>44421</v>
       </c>
       <c r="B8" t="n">
-        <v>6.181660175323486</v>
+        <v>6.181659698486328</v>
       </c>
       <c r="C8" t="n">
-        <v>6.208114975398141</v>
+        <v>6.208114496520329</v>
       </c>
       <c r="D8" t="n">
-        <v>6.049384913475816</v>
+        <v>6.049384446842026</v>
       </c>
       <c r="E8" t="n">
-        <v>6.155204954757366</v>
+        <v>6.155204479960894</v>
       </c>
       <c r="F8" t="n">
         <v>21141500</v>
@@ -612,16 +612,16 @@
         <v>44425</v>
       </c>
       <c r="B10" t="n">
-        <v>6.014111995697021</v>
+        <v>6.014111518859863</v>
       </c>
       <c r="C10" t="n">
-        <v>6.164023521301528</v>
+        <v>6.164023032578428</v>
       </c>
       <c r="D10" t="n">
-        <v>5.961201971279285</v>
+        <v>5.961201498637171</v>
       </c>
       <c r="E10" t="n">
-        <v>6.111113496883791</v>
+        <v>6.111113012355736</v>
       </c>
       <c r="F10" t="n">
         <v>17772000</v>
@@ -652,16 +652,16 @@
         <v>44427</v>
       </c>
       <c r="B12" t="n">
-        <v>6.11111307144165</v>
+        <v>6.111112594604492</v>
       </c>
       <c r="C12" t="n">
-        <v>6.11111307144165</v>
+        <v>6.111112594604492</v>
       </c>
       <c r="D12" t="n">
-        <v>5.66137768495472</v>
+        <v>5.661377243209458</v>
       </c>
       <c r="E12" t="n">
-        <v>5.908291115047926</v>
+        <v>5.908290654036534</v>
       </c>
       <c r="F12" t="n">
         <v>5423700</v>
@@ -692,16 +692,16 @@
         <v>44431</v>
       </c>
       <c r="B14" t="n">
-        <v>6.322752475738525</v>
+        <v>6.32275390625</v>
       </c>
       <c r="C14" t="n">
-        <v>6.349207271261085</v>
+        <v>6.349208707757911</v>
       </c>
       <c r="D14" t="n">
-        <v>6.181659111641157</v>
+        <v>6.18166051023051</v>
       </c>
       <c r="E14" t="n">
-        <v>6.208113907163717</v>
+        <v>6.20811531173842</v>
       </c>
       <c r="F14" t="n">
         <v>6128800</v>
@@ -752,16 +752,16 @@
         <v>44434</v>
       </c>
       <c r="B17" t="n">
-        <v>6.261024475097656</v>
+        <v>6.261024951934814</v>
       </c>
       <c r="C17" t="n">
-        <v>6.507938304701895</v>
+        <v>6.507938800343913</v>
       </c>
       <c r="D17" t="n">
-        <v>6.261024475097656</v>
+        <v>6.261024951934814</v>
       </c>
       <c r="E17" t="n">
-        <v>6.472664960542923</v>
+        <v>6.472665453498537</v>
       </c>
       <c r="F17" t="n">
         <v>7968100</v>
@@ -772,16 +772,16 @@
         <v>44435</v>
       </c>
       <c r="B18" t="n">
-        <v>6.340389728546143</v>
+        <v>6.340390205383301</v>
       </c>
       <c r="C18" t="n">
-        <v>6.384481198630192</v>
+        <v>6.384481678783307</v>
       </c>
       <c r="D18" t="n">
-        <v>6.278661165838754</v>
+        <v>6.278661638033537</v>
       </c>
       <c r="E18" t="n">
-        <v>6.305116384282329</v>
+        <v>6.305116858466711</v>
       </c>
       <c r="F18" t="n">
         <v>5881000</v>
@@ -792,16 +792,16 @@
         <v>44438</v>
       </c>
       <c r="B19" t="n">
-        <v>6.269843101501465</v>
+        <v>6.269844532012939</v>
       </c>
       <c r="C19" t="n">
-        <v>6.419755026338443</v>
+        <v>6.419756491053442</v>
       </c>
       <c r="D19" t="n">
-        <v>6.252206429196611</v>
+        <v>6.252207855684147</v>
       </c>
       <c r="E19" t="n">
-        <v>6.393299807635444</v>
+        <v>6.393301266314487</v>
       </c>
       <c r="F19" t="n">
         <v>4966000</v>
@@ -812,16 +812,16 @@
         <v>44439</v>
       </c>
       <c r="B20" t="n">
-        <v>6.261024475097656</v>
+        <v>6.261024951934814</v>
       </c>
       <c r="C20" t="n">
-        <v>6.305116365542087</v>
+        <v>6.305116845737266</v>
       </c>
       <c r="D20" t="n">
-        <v>6.181659660985684</v>
+        <v>6.181660131778449</v>
       </c>
       <c r="E20" t="n">
-        <v>6.305116365542087</v>
+        <v>6.305116845737266</v>
       </c>
       <c r="F20" t="n">
         <v>3704100</v>
@@ -832,16 +832,16 @@
         <v>44440</v>
       </c>
       <c r="B21" t="n">
-        <v>6.234569549560547</v>
+        <v>6.234570503234863</v>
       </c>
       <c r="C21" t="n">
-        <v>6.305116236433927</v>
+        <v>6.305117200899455</v>
       </c>
       <c r="D21" t="n">
-        <v>6.199296206123857</v>
+        <v>6.199297154402568</v>
       </c>
       <c r="E21" t="n">
-        <v>6.261024346892354</v>
+        <v>6.261025304613343</v>
       </c>
       <c r="F21" t="n">
         <v>6468600</v>
@@ -852,16 +852,16 @@
         <v>44441</v>
       </c>
       <c r="B22" t="n">
-        <v>5.996475696563721</v>
+        <v>5.996474266052246</v>
       </c>
       <c r="C22" t="n">
-        <v>6.252207707516526</v>
+        <v>6.252206215997954</v>
       </c>
       <c r="D22" t="n">
-        <v>5.970020472451714</v>
+        <v>5.970019048251363</v>
       </c>
       <c r="E22" t="n">
-        <v>6.234571031605695</v>
+        <v>6.234569544294506</v>
       </c>
       <c r="F22" t="n">
         <v>3746900</v>
@@ -872,16 +872,16 @@
         <v>44442</v>
       </c>
       <c r="B23" t="n">
-        <v>6.17284107208252</v>
+        <v>6.172841548919678</v>
       </c>
       <c r="C23" t="n">
-        <v>6.17284107208252</v>
+        <v>6.172841548919678</v>
       </c>
       <c r="D23" t="n">
-        <v>5.934745790407565</v>
+        <v>5.934746248852434</v>
       </c>
       <c r="E23" t="n">
-        <v>6.031747696420747</v>
+        <v>6.031748162358781</v>
       </c>
       <c r="F23" t="n">
         <v>3705400</v>
@@ -892,16 +892,16 @@
         <v>44445</v>
       </c>
       <c r="B24" t="n">
-        <v>6.11111307144165</v>
+        <v>6.111112594604492</v>
       </c>
       <c r="C24" t="n">
-        <v>6.190478312788771</v>
+        <v>6.190477829758912</v>
       </c>
       <c r="D24" t="n">
-        <v>6.067021597742168</v>
+        <v>6.067021124345374</v>
       </c>
       <c r="E24" t="n">
-        <v>6.119931618476427</v>
+        <v>6.119931140951175</v>
       </c>
       <c r="F24" t="n">
         <v>1654400</v>
@@ -912,16 +912,16 @@
         <v>44447</v>
       </c>
       <c r="B25" t="n">
-        <v>5.758379459381104</v>
+        <v>5.758379936218262</v>
       </c>
       <c r="C25" t="n">
-        <v>6.111112922336476</v>
+        <v>6.11111342838262</v>
       </c>
       <c r="D25" t="n">
-        <v>5.661377546822648</v>
+        <v>5.661378015627318</v>
       </c>
       <c r="E25" t="n">
-        <v>6.111112922336476</v>
+        <v>6.11111342838262</v>
       </c>
       <c r="F25" t="n">
         <v>10251100</v>
@@ -992,16 +992,16 @@
         <v>44453</v>
       </c>
       <c r="B29" t="n">
-        <v>6.340389728546143</v>
+        <v>6.340390205383301</v>
       </c>
       <c r="C29" t="n">
-        <v>6.50793832404497</v>
+        <v>6.507938813482836</v>
       </c>
       <c r="D29" t="n">
-        <v>6.225751149443035</v>
+        <v>6.225751617658651</v>
       </c>
       <c r="E29" t="n">
-        <v>6.225751149443035</v>
+        <v>6.225751617658651</v>
       </c>
       <c r="F29" t="n">
         <v>9730300</v>
@@ -1032,16 +1032,16 @@
         <v>44455</v>
       </c>
       <c r="B31" t="n">
-        <v>6.278661727905273</v>
+        <v>6.278660774230957</v>
       </c>
       <c r="C31" t="n">
-        <v>6.428573664692329</v>
+        <v>6.428572688247688</v>
       </c>
       <c r="D31" t="n">
-        <v>6.172841685640813</v>
+        <v>6.172840748039643</v>
       </c>
       <c r="E31" t="n">
-        <v>6.349208422748248</v>
+        <v>6.349207458358499</v>
       </c>
       <c r="F31" t="n">
         <v>6142600</v>
@@ -1072,16 +1072,16 @@
         <v>44459</v>
       </c>
       <c r="B33" t="n">
-        <v>6.269843101501465</v>
+        <v>6.269844532012939</v>
       </c>
       <c r="C33" t="n">
-        <v>6.322753118416027</v>
+        <v>6.322754560999317</v>
       </c>
       <c r="D33" t="n">
-        <v>6.067021159749924</v>
+        <v>6.06702254398606</v>
       </c>
       <c r="E33" t="n">
-        <v>6.164022647180904</v>
+        <v>6.164024053548653</v>
       </c>
       <c r="F33" t="n">
         <v>9065700</v>
@@ -1112,16 +1112,16 @@
         <v>44461</v>
       </c>
       <c r="B35" t="n">
-        <v>6.446209907531738</v>
+        <v>6.44620943069458</v>
       </c>
       <c r="C35" t="n">
-        <v>6.560848489234745</v>
+        <v>6.560848003917575</v>
       </c>
       <c r="D35" t="n">
-        <v>6.402118436447734</v>
+        <v>6.402117962872096</v>
       </c>
       <c r="E35" t="n">
-        <v>6.463846580063628</v>
+        <v>6.463846101921855</v>
       </c>
       <c r="F35" t="n">
         <v>10254600</v>
@@ -1152,16 +1152,16 @@
         <v>44463</v>
       </c>
       <c r="B37" t="n">
-        <v>6.17284107208252</v>
+        <v>6.172841548919678</v>
       </c>
       <c r="C37" t="n">
-        <v>6.375663009842031</v>
+        <v>6.375663502346697</v>
       </c>
       <c r="D37" t="n">
-        <v>6.164022525857945</v>
+        <v>6.164023002013892</v>
       </c>
       <c r="E37" t="n">
-        <v>6.340389665926588</v>
+        <v>6.340390155706473</v>
       </c>
       <c r="F37" t="n">
         <v>5138200</v>
@@ -1172,16 +1172,16 @@
         <v>44466</v>
       </c>
       <c r="B38" t="n">
-        <v>6.305117130279541</v>
+        <v>6.305116653442383</v>
       </c>
       <c r="C38" t="n">
-        <v>6.340390478716762</v>
+        <v>6.340389999211985</v>
       </c>
       <c r="D38" t="n">
-        <v>6.102295166519786</v>
+        <v>6.102294705021446</v>
       </c>
       <c r="E38" t="n">
-        <v>6.172841863394225</v>
+        <v>6.17284139656065</v>
       </c>
       <c r="F38" t="n">
         <v>6343700</v>
@@ -1192,16 +1192,16 @@
         <v>44467</v>
       </c>
       <c r="B39" t="n">
-        <v>6.119931697845459</v>
+        <v>6.119932174682617</v>
       </c>
       <c r="C39" t="n">
-        <v>6.278661762106795</v>
+        <v>6.278662251311475</v>
       </c>
       <c r="D39" t="n">
-        <v>6.119931697845459</v>
+        <v>6.119932174682617</v>
       </c>
       <c r="E39" t="n">
-        <v>6.26102508829998</v>
+        <v>6.261025576130491</v>
       </c>
       <c r="F39" t="n">
         <v>6782400</v>
@@ -1212,16 +1212,16 @@
         <v>44468</v>
       </c>
       <c r="B40" t="n">
-        <v>6.040566921234131</v>
+        <v>6.040566444396973</v>
       </c>
       <c r="C40" t="n">
-        <v>6.252207443726178</v>
+        <v>6.252206950182298</v>
       </c>
       <c r="D40" t="n">
-        <v>6.040566921234131</v>
+        <v>6.040566444396973</v>
       </c>
       <c r="E40" t="n">
-        <v>6.216934093392754</v>
+        <v>6.216933602633323</v>
       </c>
       <c r="F40" t="n">
         <v>6482600</v>
@@ -1232,16 +1232,16 @@
         <v>44469</v>
       </c>
       <c r="B41" t="n">
-        <v>6.261024475097656</v>
+        <v>6.261024951934814</v>
       </c>
       <c r="C41" t="n">
-        <v>6.349207835495088</v>
+        <v>6.349208319048255</v>
       </c>
       <c r="D41" t="n">
-        <v>6.058202535937849</v>
+        <v>6.058202997328168</v>
       </c>
       <c r="E41" t="n">
-        <v>6.084657754302794</v>
+        <v>6.084658217707932</v>
       </c>
       <c r="F41" t="n">
         <v>15990100</v>
@@ -1252,16 +1252,16 @@
         <v>44470</v>
       </c>
       <c r="B42" t="n">
-        <v>6.499120235443115</v>
+        <v>6.499119758605957</v>
       </c>
       <c r="C42" t="n">
-        <v>6.569666928939093</v>
+        <v>6.569666446925959</v>
       </c>
       <c r="D42" t="n">
-        <v>6.331571628144438</v>
+        <v>6.331571163600236</v>
       </c>
       <c r="E42" t="n">
-        <v>6.331571628144438</v>
+        <v>6.331571163600236</v>
       </c>
       <c r="F42" t="n">
         <v>15528000</v>
@@ -1292,16 +1292,16 @@
         <v>44474</v>
       </c>
       <c r="B44" t="n">
-        <v>6.287480354309082</v>
+        <v>6.287479877471924</v>
       </c>
       <c r="C44" t="n">
-        <v>6.366845176762705</v>
+        <v>6.366844693906587</v>
       </c>
       <c r="D44" t="n">
-        <v>6.243388459230366</v>
+        <v>6.2433879857371</v>
       </c>
       <c r="E44" t="n">
-        <v>6.29629848102994</v>
+        <v>6.296298003524023</v>
       </c>
       <c r="F44" t="n">
         <v>12888200</v>
@@ -1312,16 +1312,16 @@
         <v>44475</v>
       </c>
       <c r="B45" t="n">
-        <v>6.178093433380127</v>
+        <v>6.178093910217285</v>
       </c>
       <c r="C45" t="n">
-        <v>6.275316770259803</v>
+        <v>6.275317254600846</v>
       </c>
       <c r="D45" t="n">
-        <v>6.080870517951754</v>
+        <v>6.080870987285061</v>
       </c>
       <c r="E45" t="n">
-        <v>6.248801582943448</v>
+        <v>6.248802065237998</v>
       </c>
       <c r="F45" t="n">
         <v>10376100</v>
@@ -1352,16 +1352,16 @@
         <v>44477</v>
       </c>
       <c r="B47" t="n">
-        <v>6.310671806335449</v>
+        <v>6.310670375823975</v>
       </c>
       <c r="C47" t="n">
-        <v>6.655372677076427</v>
+        <v>6.655371168427701</v>
       </c>
       <c r="D47" t="n">
-        <v>6.292994871024479</v>
+        <v>6.292993444520037</v>
       </c>
       <c r="E47" t="n">
-        <v>6.363702612268358</v>
+        <v>6.36370116973579</v>
       </c>
       <c r="F47" t="n">
         <v>20480700</v>
@@ -1372,16 +1372,16 @@
         <v>44480</v>
       </c>
       <c r="B48" t="n">
-        <v>6.213448047637939</v>
+        <v>6.213447570800781</v>
       </c>
       <c r="C48" t="n">
-        <v>6.407894310234044</v>
+        <v>6.407893818474543</v>
       </c>
       <c r="D48" t="n">
-        <v>6.213448047637939</v>
+        <v>6.213447570800781</v>
       </c>
       <c r="E48" t="n">
-        <v>6.363701767100176</v>
+        <v>6.363701278732132</v>
       </c>
       <c r="F48" t="n">
         <v>10407400</v>
@@ -1392,16 +1392,16 @@
         <v>44482</v>
       </c>
       <c r="B49" t="n">
-        <v>6.231124877929688</v>
+        <v>6.231125354766846</v>
       </c>
       <c r="C49" t="n">
-        <v>6.292993931556084</v>
+        <v>6.292994413127774</v>
       </c>
       <c r="D49" t="n">
-        <v>6.213447945257672</v>
+        <v>6.213448420742101</v>
       </c>
       <c r="E49" t="n">
-        <v>6.248801810601703</v>
+        <v>6.248802288791589</v>
       </c>
       <c r="F49" t="n">
         <v>8146000</v>
@@ -1412,16 +1412,16 @@
         <v>44483</v>
       </c>
       <c r="B50" t="n">
-        <v>6.319509029388428</v>
+        <v>6.319509506225586</v>
       </c>
       <c r="C50" t="n">
-        <v>6.381378078003224</v>
+        <v>6.381378559508698</v>
       </c>
       <c r="D50" t="n">
-        <v>6.239962628082221</v>
+        <v>6.239963098917224</v>
       </c>
       <c r="E50" t="n">
-        <v>6.248801304427927</v>
+        <v>6.24880177592985</v>
       </c>
       <c r="F50" t="n">
         <v>10992200</v>
@@ -1432,16 +1432,16 @@
         <v>44484</v>
       </c>
       <c r="B51" t="n">
-        <v>6.27531623840332</v>
+        <v>6.275316715240479</v>
       </c>
       <c r="C51" t="n">
-        <v>6.354862636513137</v>
+        <v>6.354863119394721</v>
       </c>
       <c r="D51" t="n">
-        <v>6.222285446813864</v>
+        <v>6.222285919621418</v>
       </c>
       <c r="E51" t="n">
-        <v>6.337185705983319</v>
+        <v>6.3371861875217</v>
       </c>
       <c r="F51" t="n">
         <v>34203500</v>
@@ -1472,16 +1472,16 @@
         <v>44488</v>
       </c>
       <c r="B53" t="n">
-        <v>5.912939071655273</v>
+        <v>5.91294002532959</v>
       </c>
       <c r="C53" t="n">
-        <v>6.186931711146165</v>
+        <v>6.186932709011659</v>
       </c>
       <c r="D53" t="n">
-        <v>5.895262140767192</v>
+        <v>5.895263091590468</v>
       </c>
       <c r="E53" t="n">
-        <v>6.169254780258083</v>
+        <v>6.169255775272537</v>
       </c>
       <c r="F53" t="n">
         <v>11473400</v>
@@ -1492,16 +1492,16 @@
         <v>44489</v>
       </c>
       <c r="B54" t="n">
-        <v>5.904101371765137</v>
+        <v>5.904100894927979</v>
       </c>
       <c r="C54" t="n">
-        <v>6.045517263705048</v>
+        <v>6.045516775446618</v>
       </c>
       <c r="D54" t="n">
-        <v>5.842232314152062</v>
+        <v>5.842231842311679</v>
       </c>
       <c r="E54" t="n">
-        <v>6.010163396082907</v>
+        <v>6.010162910679786</v>
       </c>
       <c r="F54" t="n">
         <v>6234400</v>
@@ -1512,16 +1512,16 @@
         <v>44490</v>
       </c>
       <c r="B55" t="n">
-        <v>5.683139324188232</v>
+        <v>5.683138847351074</v>
       </c>
       <c r="C55" t="n">
-        <v>5.84223214534227</v>
+        <v>5.842231655156614</v>
       </c>
       <c r="D55" t="n">
-        <v>5.471016124584628</v>
+        <v>5.471015665545419</v>
       </c>
       <c r="E55" t="n">
-        <v>5.798039601365852</v>
+        <v>5.79803911488812</v>
       </c>
       <c r="F55" t="n">
         <v>12472300</v>
@@ -1612,16 +1612,16 @@
         <v>44497</v>
       </c>
       <c r="B60" t="n">
-        <v>5.992486476898193</v>
+        <v>5.992486000061035</v>
       </c>
       <c r="C60" t="n">
-        <v>6.027840344606625</v>
+        <v>6.027839864956272</v>
       </c>
       <c r="D60" t="n">
-        <v>5.727332047633601</v>
+        <v>5.727331591895446</v>
       </c>
       <c r="E60" t="n">
-        <v>5.753847659140599</v>
+        <v>5.75384720129253</v>
       </c>
       <c r="F60" t="n">
         <v>8299700</v>
@@ -1632,16 +1632,16 @@
         <v>44498</v>
       </c>
       <c r="B61" t="n">
-        <v>5.992486476898193</v>
+        <v>5.992486000061035</v>
       </c>
       <c r="C61" t="n">
-        <v>6.019001666953844</v>
+        <v>6.019001188006806</v>
       </c>
       <c r="D61" t="n">
-        <v>5.842232328411681</v>
+        <v>5.842231863530622</v>
       </c>
       <c r="E61" t="n">
-        <v>5.957132187738413</v>
+        <v>5.957131713714485</v>
       </c>
       <c r="F61" t="n">
         <v>3926300</v>
@@ -1692,16 +1692,16 @@
         <v>44504</v>
       </c>
       <c r="B64" t="n">
-        <v>5.965970516204834</v>
+        <v>5.965970039367676</v>
       </c>
       <c r="C64" t="n">
-        <v>6.160416777220335</v>
+        <v>6.160416284841832</v>
       </c>
       <c r="D64" t="n">
-        <v>5.842231986467696</v>
+        <v>5.842231519520484</v>
       </c>
       <c r="E64" t="n">
-        <v>6.098547723077428</v>
+        <v>6.098547235643882</v>
       </c>
       <c r="F64" t="n">
         <v>8687600</v>
@@ -1712,16 +1712,16 @@
         <v>44505</v>
       </c>
       <c r="B65" t="n">
-        <v>5.965970516204834</v>
+        <v>5.965970039367676</v>
       </c>
       <c r="C65" t="n">
-        <v>6.054355180302789</v>
+        <v>6.054354696401384</v>
       </c>
       <c r="D65" t="n">
-        <v>5.939454906249786</v>
+        <v>5.939454431531919</v>
       </c>
       <c r="E65" t="n">
-        <v>6.001324381844015</v>
+        <v>6.001323902181158</v>
       </c>
       <c r="F65" t="n">
         <v>3123600</v>
@@ -1732,16 +1732,16 @@
         <v>44508</v>
       </c>
       <c r="B66" t="n">
-        <v>5.983647346496582</v>
+        <v>5.983648300170898</v>
       </c>
       <c r="C66" t="n">
-        <v>6.036678144046689</v>
+        <v>6.03667910617306</v>
       </c>
       <c r="D66" t="n">
-        <v>5.939454804479167</v>
+        <v>5.939455751110073</v>
       </c>
       <c r="E66" t="n">
-        <v>6.010162955997293</v>
+        <v>6.010163913897671</v>
       </c>
       <c r="F66" t="n">
         <v>3898000</v>
@@ -1752,16 +1752,16 @@
         <v>44509</v>
       </c>
       <c r="B67" t="n">
-        <v>5.948293209075928</v>
+        <v>5.948294162750244</v>
       </c>
       <c r="C67" t="n">
-        <v>6.169255066141971</v>
+        <v>6.169256055242525</v>
       </c>
       <c r="D67" t="n">
-        <v>5.948293209075928</v>
+        <v>5.948294162750244</v>
       </c>
       <c r="E67" t="n">
-        <v>5.992485749069655</v>
+        <v>5.992486709829246</v>
       </c>
       <c r="F67" t="n">
         <v>5176300</v>
@@ -1772,16 +1772,16 @@
         <v>44510</v>
       </c>
       <c r="B68" t="n">
-        <v>5.745007991790771</v>
+        <v>5.745008945465088</v>
       </c>
       <c r="C68" t="n">
-        <v>6.01016237537701</v>
+        <v>6.010163373067091</v>
       </c>
       <c r="D68" t="n">
-        <v>5.745007991790771</v>
+        <v>5.745008945465088</v>
       </c>
       <c r="E68" t="n">
-        <v>5.957131161498742</v>
+        <v>5.957132150385616</v>
       </c>
       <c r="F68" t="n">
         <v>10074000</v>
@@ -1792,16 +1792,16 @@
         <v>44511</v>
       </c>
       <c r="B69" t="n">
-        <v>6.010162353515625</v>
+        <v>6.010162830352783</v>
       </c>
       <c r="C69" t="n">
-        <v>6.036677538907038</v>
+        <v>6.036678017847871</v>
       </c>
       <c r="D69" t="n">
-        <v>5.806877439225945</v>
+        <v>5.806877899934787</v>
       </c>
       <c r="E69" t="n">
-        <v>5.833392624617358</v>
+        <v>5.833393087429874</v>
       </c>
       <c r="F69" t="n">
         <v>8604300</v>
@@ -1812,16 +1812,16 @@
         <v>44512</v>
       </c>
       <c r="B70" t="n">
-        <v>5.762685775756836</v>
+        <v>5.762686252593994</v>
       </c>
       <c r="C70" t="n">
-        <v>6.080870998876915</v>
+        <v>6.080871502042515</v>
       </c>
       <c r="D70" t="n">
-        <v>5.532885641218299</v>
+        <v>5.532886099040496</v>
       </c>
       <c r="E70" t="n">
-        <v>6.080870998876915</v>
+        <v>6.080871502042515</v>
       </c>
       <c r="F70" t="n">
         <v>20568500</v>
@@ -1852,16 +1852,16 @@
         <v>44517</v>
       </c>
       <c r="B72" t="n">
-        <v>5.17050838470459</v>
+        <v>5.170506954193115</v>
       </c>
       <c r="C72" t="n">
-        <v>5.462178025779772</v>
+        <v>5.462176514572795</v>
       </c>
       <c r="D72" t="n">
-        <v>5.002577289838284</v>
+        <v>5.00257590578788</v>
       </c>
       <c r="E72" t="n">
-        <v>5.364955093055631</v>
+        <v>5.364953608747077</v>
       </c>
       <c r="F72" t="n">
         <v>24600900</v>
@@ -1912,16 +1912,16 @@
         <v>44522</v>
       </c>
       <c r="B75" t="n">
-        <v>4.976061820983887</v>
+        <v>4.976061344146729</v>
       </c>
       <c r="C75" t="n">
-        <v>5.329600926221622</v>
+        <v>5.32960041550615</v>
       </c>
       <c r="D75" t="n">
-        <v>4.976061820983887</v>
+        <v>4.976061344146729</v>
       </c>
       <c r="E75" t="n">
-        <v>5.23237757745469</v>
+        <v>5.232377076055763</v>
       </c>
       <c r="F75" t="n">
         <v>8516000</v>
@@ -1932,16 +1932,16 @@
         <v>44523</v>
       </c>
       <c r="B76" t="n">
-        <v>5.011415958404541</v>
+        <v>5.011415481567383</v>
       </c>
       <c r="C76" t="n">
-        <v>5.09980063409614</v>
+        <v>5.099800148849164</v>
       </c>
       <c r="D76" t="n">
-        <v>4.781615380155004</v>
+        <v>4.781614925183414</v>
       </c>
       <c r="E76" t="n">
-        <v>5.002577280109692</v>
+        <v>5.002576804113536</v>
       </c>
       <c r="F76" t="n">
         <v>9084200</v>
@@ -1992,16 +1992,16 @@
         <v>44526</v>
       </c>
       <c r="B79" t="n">
-        <v>5.223538875579834</v>
+        <v>5.223538398742676</v>
       </c>
       <c r="C79" t="n">
-        <v>5.338439158006967</v>
+        <v>5.338438670680995</v>
       </c>
       <c r="D79" t="n">
-        <v>5.02025392261312</v>
+        <v>5.020253464333078</v>
       </c>
       <c r="E79" t="n">
-        <v>5.037930856721036</v>
+        <v>5.037930396827334</v>
       </c>
       <c r="F79" t="n">
         <v>8564200</v>
@@ -2032,16 +2032,16 @@
         <v>44530</v>
       </c>
       <c r="B81" t="n">
-        <v>4.825807571411133</v>
+        <v>4.825808048248291</v>
       </c>
       <c r="C81" t="n">
-        <v>5.126315867963532</v>
+        <v>5.12631637449386</v>
       </c>
       <c r="D81" t="n">
-        <v>4.790453703752186</v>
+        <v>4.790454177096034</v>
       </c>
       <c r="E81" t="n">
-        <v>5.073284645023764</v>
+        <v>5.073285146314087</v>
       </c>
       <c r="F81" t="n">
         <v>11282700</v>
@@ -2072,16 +2072,16 @@
         <v>44532</v>
       </c>
       <c r="B83" t="n">
-        <v>5.029092788696289</v>
+        <v>5.029092311859131</v>
       </c>
       <c r="C83" t="n">
-        <v>5.029092788696289</v>
+        <v>5.029092311859131</v>
       </c>
       <c r="D83" t="n">
-        <v>4.746261410928263</v>
+        <v>4.746260960907972</v>
       </c>
       <c r="E83" t="n">
-        <v>4.905354245307752</v>
+        <v>4.905353780202955</v>
       </c>
       <c r="F83" t="n">
         <v>18379200</v>
@@ -2112,16 +2112,16 @@
         <v>44536</v>
       </c>
       <c r="B85" t="n">
-        <v>5.152830600738525</v>
+        <v>5.152831077575684</v>
       </c>
       <c r="C85" t="n">
-        <v>5.417985006103135</v>
+        <v>5.417985507477384</v>
       </c>
       <c r="D85" t="n">
-        <v>5.152830600738525</v>
+        <v>5.152831077575684</v>
       </c>
       <c r="E85" t="n">
-        <v>5.373792464725264</v>
+        <v>5.373792962009984</v>
       </c>
       <c r="F85" t="n">
         <v>5884400</v>
@@ -2152,16 +2152,16 @@
         <v>44538</v>
       </c>
       <c r="B87" t="n">
-        <v>5.285407543182373</v>
+        <v>5.285408020019531</v>
       </c>
       <c r="C87" t="n">
-        <v>5.338438337353947</v>
+        <v>5.33843881897542</v>
       </c>
       <c r="D87" t="n">
-        <v>5.12631516066765</v>
+        <v>5.126315623151864</v>
       </c>
       <c r="E87" t="n">
-        <v>5.223538072589892</v>
+        <v>5.223538543845331</v>
       </c>
       <c r="F87" t="n">
         <v>9204000</v>
@@ -2192,16 +2192,16 @@
         <v>44540</v>
       </c>
       <c r="B89" t="n">
-        <v>5.444500923156738</v>
+        <v>5.44450044631958</v>
       </c>
       <c r="C89" t="n">
-        <v>5.568239887011294</v>
+        <v>5.568239399336901</v>
       </c>
       <c r="D89" t="n">
-        <v>5.241215964197243</v>
+        <v>5.241215505164072</v>
       </c>
       <c r="E89" t="n">
-        <v>5.267731576866467</v>
+        <v>5.267731115511021</v>
       </c>
       <c r="F89" t="n">
         <v>8741300</v>
@@ -2212,16 +2212,16 @@
         <v>44543</v>
       </c>
       <c r="B90" t="n">
-        <v>5.497531414031982</v>
+        <v>5.497530937194824</v>
       </c>
       <c r="C90" t="n">
-        <v>5.621270370841238</v>
+        <v>5.621269883271384</v>
       </c>
       <c r="D90" t="n">
-        <v>5.426823679541746</v>
+        <v>5.426823208837535</v>
       </c>
       <c r="E90" t="n">
-        <v>5.444500613164305</v>
+        <v>5.444500140926858</v>
       </c>
       <c r="F90" t="n">
         <v>8265100</v>
@@ -2272,16 +2272,16 @@
         <v>44546</v>
       </c>
       <c r="B93" t="n">
-        <v>5.400308609008789</v>
+        <v>5.400308132171631</v>
       </c>
       <c r="C93" t="n">
-        <v>5.550562758842054</v>
+        <v>5.550562268737735</v>
       </c>
       <c r="D93" t="n">
-        <v>5.347277806970816</v>
+        <v>5.347277334816178</v>
       </c>
       <c r="E93" t="n">
-        <v>5.515208469365389</v>
+        <v>5.515207982382787</v>
       </c>
       <c r="F93" t="n">
         <v>9238300</v>
@@ -2312,16 +2312,16 @@
         <v>44550</v>
       </c>
       <c r="B95" t="n">
-        <v>5.14399242401123</v>
+        <v>5.143992900848389</v>
       </c>
       <c r="C95" t="n">
-        <v>5.179346289073743</v>
+        <v>5.179346769188129</v>
       </c>
       <c r="D95" t="n">
-        <v>4.949545744716101</v>
+        <v>4.949546203528466</v>
       </c>
       <c r="E95" t="n">
-        <v>5.179346289073743</v>
+        <v>5.179346769188129</v>
       </c>
       <c r="F95" t="n">
         <v>8433600</v>
@@ -2352,16 +2352,16 @@
         <v>44552</v>
       </c>
       <c r="B97" t="n">
-        <v>5.011415958404541</v>
+        <v>5.011415481567383</v>
       </c>
       <c r="C97" t="n">
-        <v>5.073285020662972</v>
+        <v>5.073284537938961</v>
       </c>
       <c r="D97" t="n">
-        <v>4.914192604418092</v>
+        <v>4.914192136831755</v>
       </c>
       <c r="E97" t="n">
-        <v>5.055608085524652</v>
+        <v>5.055607604482605</v>
       </c>
       <c r="F97" t="n">
         <v>4649500</v>
@@ -2372,16 +2372,16 @@
         <v>44553</v>
       </c>
       <c r="B98" t="n">
-        <v>5.055607318878174</v>
+        <v>5.055606842041016</v>
       </c>
       <c r="C98" t="n">
-        <v>5.073284251335914</v>
+        <v>5.073283772831495</v>
       </c>
       <c r="D98" t="n">
-        <v>4.967222656589472</v>
+        <v>4.96722218808862</v>
       </c>
       <c r="E98" t="n">
-        <v>4.993738266001739</v>
+        <v>4.993737794999975</v>
       </c>
       <c r="F98" t="n">
         <v>3174500</v>
@@ -2432,16 +2432,16 @@
         <v>44559</v>
       </c>
       <c r="B101" t="n">
-        <v>5.311923027038574</v>
+        <v>5.311923503875732</v>
       </c>
       <c r="C101" t="n">
-        <v>5.382630750950688</v>
+        <v>5.38263123413509</v>
       </c>
       <c r="D101" t="n">
-        <v>5.214699695933778</v>
+        <v>5.214700164043457</v>
       </c>
       <c r="E101" t="n">
-        <v>5.320761281801949</v>
+        <v>5.320761759432494</v>
       </c>
       <c r="F101" t="n">
         <v>5394800</v>
@@ -2472,16 +2472,16 @@
         <v>44564</v>
       </c>
       <c r="B103" t="n">
-        <v>5.541724681854248</v>
+        <v>5.541723728179932</v>
       </c>
       <c r="C103" t="n">
-        <v>5.745009655762357</v>
+        <v>5.745008667104768</v>
       </c>
       <c r="D103" t="n">
-        <v>5.506370809996437</v>
+        <v>5.506369862406162</v>
       </c>
       <c r="E103" t="n">
-        <v>5.691978847975641</v>
+        <v>5.691977868444114</v>
       </c>
       <c r="F103" t="n">
         <v>7451800</v>
@@ -2532,16 +2532,16 @@
         <v>44567</v>
       </c>
       <c r="B106" t="n">
-        <v>4.932945251464844</v>
+        <v>4.932944774627686</v>
       </c>
       <c r="C106" t="n">
-        <v>5.190239127268864</v>
+        <v>5.190238625560705</v>
       </c>
       <c r="D106" t="n">
-        <v>4.870839672696422</v>
+        <v>4.870839201862625</v>
       </c>
       <c r="E106" t="n">
-        <v>5.145878362199686</v>
+        <v>5.145877864779607</v>
       </c>
       <c r="F106" t="n">
         <v>8427100</v>
@@ -2552,16 +2552,16 @@
         <v>44568</v>
       </c>
       <c r="B107" t="n">
-        <v>5.163622379302979</v>
+        <v>5.163622856140137</v>
       </c>
       <c r="C107" t="n">
-        <v>5.278960698586984</v>
+        <v>5.278961186075115</v>
       </c>
       <c r="D107" t="n">
-        <v>4.941817300823532</v>
+        <v>4.941817757177995</v>
       </c>
       <c r="E107" t="n">
-        <v>4.977306079535475</v>
+        <v>4.977306539167166</v>
       </c>
       <c r="F107" t="n">
         <v>10961100</v>
@@ -2612,16 +2612,16 @@
         <v>44573</v>
       </c>
       <c r="B110" t="n">
-        <v>5.438661098480225</v>
+        <v>5.438660621643066</v>
       </c>
       <c r="C110" t="n">
-        <v>5.518510645991364</v>
+        <v>5.51851016215336</v>
       </c>
       <c r="D110" t="n">
-        <v>5.225727984644668</v>
+        <v>5.225727526476521</v>
       </c>
       <c r="E110" t="n">
-        <v>5.261216766440652</v>
+        <v>5.261216305161009</v>
       </c>
       <c r="F110" t="n">
         <v>9077500</v>
@@ -2652,16 +2652,16 @@
         <v>44575</v>
       </c>
       <c r="B112" t="n">
-        <v>5.491893768310547</v>
+        <v>5.491894245147705</v>
       </c>
       <c r="C112" t="n">
-        <v>5.500765751417357</v>
+        <v>5.500766229024832</v>
       </c>
       <c r="D112" t="n">
-        <v>5.332194264851456</v>
+        <v>5.332194727822603</v>
       </c>
       <c r="E112" t="n">
-        <v>5.420916211217618</v>
+        <v>5.420916681892105</v>
       </c>
       <c r="F112" t="n">
         <v>4745900</v>
@@ -2752,16 +2752,16 @@
         <v>44582</v>
       </c>
       <c r="B117" t="n">
-        <v>5.527381896972656</v>
+        <v>5.527383327484131</v>
       </c>
       <c r="C117" t="n">
-        <v>5.68708138165501</v>
+        <v>5.687082853497435</v>
       </c>
       <c r="D117" t="n">
-        <v>5.483020717475555</v>
+        <v>5.483022136506155</v>
       </c>
       <c r="E117" t="n">
-        <v>5.678209399591327</v>
+        <v>5.678210869137642</v>
       </c>
       <c r="F117" t="n">
         <v>7609900</v>
@@ -2772,16 +2772,16 @@
         <v>44585</v>
       </c>
       <c r="B118" t="n">
-        <v>5.456405162811279</v>
+        <v>5.456405639648438</v>
       </c>
       <c r="C118" t="n">
-        <v>5.491893942483253</v>
+        <v>5.491894422421788</v>
       </c>
       <c r="D118" t="n">
-        <v>5.349938823795358</v>
+        <v>5.349939291328385</v>
       </c>
       <c r="E118" t="n">
-        <v>5.465277146199461</v>
+        <v>5.465277623811945</v>
       </c>
       <c r="F118" t="n">
         <v>8531700</v>
@@ -2832,16 +2832,16 @@
         <v>44588</v>
       </c>
       <c r="B121" t="n">
-        <v>5.545127391815186</v>
+        <v>5.545126438140869</v>
       </c>
       <c r="C121" t="n">
-        <v>5.74918809675637</v>
+        <v>5.749187107986836</v>
       </c>
       <c r="D121" t="n">
-        <v>5.527383001083763</v>
+        <v>5.527382050461201</v>
       </c>
       <c r="E121" t="n">
-        <v>5.580616173278031</v>
+        <v>5.580615213500205</v>
       </c>
       <c r="F121" t="n">
         <v>8501200</v>
@@ -2892,16 +2892,16 @@
         <v>44593</v>
       </c>
       <c r="B124" t="n">
-        <v>5.678209781646729</v>
+        <v>5.678210735321045</v>
       </c>
       <c r="C124" t="n">
-        <v>5.79354851765205</v>
+        <v>5.793549490697893</v>
       </c>
       <c r="D124" t="n">
-        <v>5.536254251540337</v>
+        <v>5.536255181372748</v>
       </c>
       <c r="E124" t="n">
-        <v>5.76693172355098</v>
+        <v>5.766932692126443</v>
       </c>
       <c r="F124" t="n">
         <v>8050400</v>
@@ -2972,16 +2972,16 @@
         <v>44599</v>
       </c>
       <c r="B128" t="n">
-        <v>5.562872409820557</v>
+        <v>5.562871932983398</v>
       </c>
       <c r="C128" t="n">
-        <v>5.775805545667787</v>
+        <v>5.775805050578469</v>
       </c>
       <c r="D128" t="n">
-        <v>5.554000424984256</v>
+        <v>5.553999948907585</v>
       </c>
       <c r="E128" t="n">
-        <v>5.704827551678914</v>
+        <v>5.704827062673674</v>
       </c>
       <c r="F128" t="n">
         <v>7178800</v>
@@ -2992,16 +2992,16 @@
         <v>44600</v>
       </c>
       <c r="B129" t="n">
-        <v>5.616104602813721</v>
+        <v>5.616105079650879</v>
       </c>
       <c r="C129" t="n">
-        <v>5.695954567631234</v>
+        <v>5.695955051248079</v>
       </c>
       <c r="D129" t="n">
-        <v>5.483021469137738</v>
+        <v>5.48302193467543</v>
       </c>
       <c r="E129" t="n">
-        <v>5.580615823574741</v>
+        <v>5.580616297398714</v>
       </c>
       <c r="F129" t="n">
         <v>9770800</v>
@@ -3032,16 +3032,16 @@
         <v>44602</v>
       </c>
       <c r="B131" t="n">
-        <v>5.704826831817627</v>
+        <v>5.704826354980469</v>
       </c>
       <c r="C131" t="n">
-        <v>5.740315612804078</v>
+        <v>5.740315133000595</v>
       </c>
       <c r="D131" t="n">
-        <v>5.56287170787182</v>
+        <v>5.562871242899961</v>
       </c>
       <c r="E131" t="n">
-        <v>5.678210457607609</v>
+        <v>5.678209982995176</v>
       </c>
       <c r="F131" t="n">
         <v>9667400</v>
@@ -3112,16 +3112,16 @@
         <v>44608</v>
       </c>
       <c r="B135" t="n">
-        <v>5.704826831817627</v>
+        <v>5.704826354980469</v>
       </c>
       <c r="C135" t="n">
-        <v>5.811293597836623</v>
+        <v>5.811293112100454</v>
       </c>
       <c r="D135" t="n">
-        <v>5.651593660337949</v>
+        <v>5.651593187950278</v>
       </c>
       <c r="E135" t="n">
-        <v>5.71369923859406</v>
+        <v>5.713698761015302</v>
       </c>
       <c r="F135" t="n">
         <v>12029900</v>
@@ -3132,16 +3132,16 @@
         <v>44609</v>
       </c>
       <c r="B136" t="n">
-        <v>5.580615043640137</v>
+        <v>5.580615997314453</v>
       </c>
       <c r="C136" t="n">
-        <v>5.740314527896292</v>
+        <v>5.740315508861739</v>
       </c>
       <c r="D136" t="n">
-        <v>5.509637495081845</v>
+        <v>5.509638436626771</v>
       </c>
       <c r="E136" t="n">
-        <v>5.731442545856286</v>
+        <v>5.731443525305595</v>
       </c>
       <c r="F136" t="n">
         <v>16171600</v>
@@ -3172,16 +3172,16 @@
         <v>44613</v>
       </c>
       <c r="B138" t="n">
-        <v>5.119261264801025</v>
+        <v>5.119261741638184</v>
       </c>
       <c r="C138" t="n">
-        <v>5.456405090261659</v>
+        <v>5.456405598502314</v>
       </c>
       <c r="D138" t="n">
-        <v>5.074900079271083</v>
+        <v>5.074900551976187</v>
       </c>
       <c r="E138" t="n">
-        <v>5.447532683931823</v>
+        <v>5.447533191346051</v>
       </c>
       <c r="F138" t="n">
         <v>8726900</v>
@@ -3192,16 +3192,16 @@
         <v>44614</v>
       </c>
       <c r="B139" t="n">
-        <v>5.012794971466064</v>
+        <v>5.012795448303223</v>
       </c>
       <c r="C139" t="n">
-        <v>5.234600054955186</v>
+        <v>5.234600552891333</v>
       </c>
       <c r="D139" t="n">
-        <v>4.977306191952575</v>
+        <v>4.977306665413898</v>
       </c>
       <c r="E139" t="n">
-        <v>5.172494479276767</v>
+        <v>5.172494971305183</v>
       </c>
       <c r="F139" t="n">
         <v>7346000</v>
@@ -3212,16 +3212,16 @@
         <v>44615</v>
       </c>
       <c r="B140" t="n">
-        <v>5.021666526794434</v>
+        <v>5.02166748046875</v>
       </c>
       <c r="C140" t="n">
-        <v>5.10151648542361</v>
+        <v>5.101517454262385</v>
       </c>
       <c r="D140" t="n">
-        <v>4.968433362061512</v>
+        <v>4.968434305626215</v>
       </c>
       <c r="E140" t="n">
-        <v>5.057155303283048</v>
+        <v>5.057156263697106</v>
       </c>
       <c r="F140" t="n">
         <v>10772600</v>
@@ -3232,16 +3232,16 @@
         <v>44616</v>
       </c>
       <c r="B141" t="n">
-        <v>5.119261264801025</v>
+        <v>5.119261741638184</v>
       </c>
       <c r="C141" t="n">
-        <v>5.137005654401078</v>
+        <v>5.137006132891051</v>
       </c>
       <c r="D141" t="n">
-        <v>4.773245456070175</v>
+        <v>4.773245900677449</v>
       </c>
       <c r="E141" t="n">
-        <v>4.924072979200438</v>
+        <v>4.924073437856647</v>
       </c>
       <c r="F141" t="n">
         <v>11357100</v>
@@ -3252,16 +3252,16 @@
         <v>44617</v>
       </c>
       <c r="B142" t="n">
-        <v>5.066027641296387</v>
+        <v>5.066028594970703</v>
       </c>
       <c r="C142" t="n">
-        <v>5.163621986866849</v>
+        <v>5.163622958913197</v>
       </c>
       <c r="D142" t="n">
-        <v>4.986177683733319</v>
+        <v>4.986178622375967</v>
       </c>
       <c r="E142" t="n">
-        <v>5.110388822844664</v>
+        <v>5.110389784869926</v>
       </c>
       <c r="F142" t="n">
         <v>6795000</v>
@@ -3272,16 +3272,16 @@
         <v>44622</v>
       </c>
       <c r="B143" t="n">
-        <v>5.314450263977051</v>
+        <v>5.314449787139893</v>
       </c>
       <c r="C143" t="n">
-        <v>5.349939471001941</v>
+        <v>5.349938990980526</v>
       </c>
       <c r="D143" t="n">
-        <v>5.030539992255339</v>
+        <v>5.03053954089193</v>
       </c>
       <c r="E143" t="n">
-        <v>5.101517560185767</v>
+        <v>5.10151710245392</v>
       </c>
       <c r="F143" t="n">
         <v>7030100</v>
@@ -3292,16 +3292,16 @@
         <v>44623</v>
       </c>
       <c r="B144" t="n">
-        <v>5.465277671813965</v>
+        <v>5.465277194976807</v>
       </c>
       <c r="C144" t="n">
-        <v>5.545127645285164</v>
+        <v>5.545127161481217</v>
       </c>
       <c r="D144" t="n">
-        <v>5.323322539473757</v>
+        <v>5.323322075021968</v>
       </c>
       <c r="E144" t="n">
-        <v>5.323322539473757</v>
+        <v>5.323322075021968</v>
       </c>
       <c r="F144" t="n">
         <v>18057800</v>
@@ -3312,16 +3312,16 @@
         <v>44624</v>
       </c>
       <c r="B145" t="n">
-        <v>5.509639263153076</v>
+        <v>5.509638786315918</v>
       </c>
       <c r="C145" t="n">
-        <v>5.536255640873986</v>
+        <v>5.536255161733287</v>
       </c>
       <c r="D145" t="n">
-        <v>5.376556105369439</v>
+        <v>5.376555640050094</v>
       </c>
       <c r="E145" t="n">
-        <v>5.48302246237247</v>
+        <v>5.483021987838889</v>
       </c>
       <c r="F145" t="n">
         <v>9336900</v>
@@ -3352,16 +3352,16 @@
         <v>44628</v>
       </c>
       <c r="B147" t="n">
-        <v>5.589488506317139</v>
+        <v>5.58948802947998</v>
       </c>
       <c r="C147" t="n">
-        <v>5.589488506317139</v>
+        <v>5.58948802947998</v>
       </c>
       <c r="D147" t="n">
-        <v>5.420916585066217</v>
+        <v>5.420916122609865</v>
       </c>
       <c r="E147" t="n">
-        <v>5.500766130772708</v>
+        <v>5.500765661504422</v>
       </c>
       <c r="F147" t="n">
         <v>5566500</v>
@@ -3412,16 +3412,16 @@
         <v>44631</v>
       </c>
       <c r="B150" t="n">
-        <v>5.598360538482666</v>
+        <v>5.598360061645508</v>
       </c>
       <c r="C150" t="n">
-        <v>5.979865148998535</v>
+        <v>5.97986463966694</v>
       </c>
       <c r="D150" t="n">
-        <v>5.52738297588061</v>
+        <v>5.527382505088926</v>
       </c>
       <c r="E150" t="n">
-        <v>5.695954898590315</v>
+        <v>5.695954413440612</v>
       </c>
       <c r="F150" t="n">
         <v>16712700</v>
@@ -3432,16 +3432,16 @@
         <v>44634</v>
       </c>
       <c r="B151" t="n">
-        <v>5.589488506317139</v>
+        <v>5.58948802947998</v>
       </c>
       <c r="C151" t="n">
-        <v>5.722571223514505</v>
+        <v>5.72257073532411</v>
       </c>
       <c r="D151" t="n">
-        <v>5.518510521269666</v>
+        <v>5.518510050487613</v>
       </c>
       <c r="E151" t="n">
-        <v>5.607232896814097</v>
+        <v>5.607232418463171</v>
       </c>
       <c r="F151" t="n">
         <v>7706100</v>
@@ -3492,16 +3492,16 @@
         <v>44637</v>
       </c>
       <c r="B154" t="n">
-        <v>5.891142845153809</v>
+        <v>5.891143321990967</v>
       </c>
       <c r="C154" t="n">
-        <v>5.926631624342837</v>
+        <v>5.926632104052506</v>
       </c>
       <c r="D154" t="n">
-        <v>5.536254630203903</v>
+        <v>5.536255078315924</v>
       </c>
       <c r="E154" t="n">
-        <v>5.607232611641579</v>
+        <v>5.607233065498654</v>
       </c>
       <c r="F154" t="n">
         <v>10001800</v>
@@ -3552,16 +3552,16 @@
         <v>44642</v>
       </c>
       <c r="B157" t="n">
-        <v>6.299263477325439</v>
+        <v>6.299263954162598</v>
       </c>
       <c r="C157" t="n">
-        <v>6.308135882593944</v>
+        <v>6.308136360102719</v>
       </c>
       <c r="D157" t="n">
-        <v>6.077458422327646</v>
+        <v>6.077458882374763</v>
       </c>
       <c r="E157" t="n">
-        <v>6.077458422327646</v>
+        <v>6.077458882374763</v>
       </c>
       <c r="F157" t="n">
         <v>9703800</v>
@@ -3572,16 +3572,16 @@
         <v>44643</v>
       </c>
       <c r="B158" t="n">
-        <v>6.308136940002441</v>
+        <v>6.3081374168396</v>
       </c>
       <c r="C158" t="n">
-        <v>6.334753314150418</v>
+        <v>6.334753792999529</v>
       </c>
       <c r="D158" t="n">
-        <v>6.201670174231618</v>
+        <v>6.201670643020867</v>
       </c>
       <c r="E158" t="n">
-        <v>6.263775752342961</v>
+        <v>6.263776225826821</v>
       </c>
       <c r="F158" t="n">
         <v>8187500</v>
@@ -3592,16 +3592,16 @@
         <v>44644</v>
       </c>
       <c r="B159" t="n">
-        <v>6.343625068664551</v>
+        <v>6.343626022338867</v>
       </c>
       <c r="C159" t="n">
-        <v>6.432347011801619</v>
+        <v>6.432347978814025</v>
       </c>
       <c r="D159" t="n">
-        <v>6.254903125527482</v>
+        <v>6.25490406586371</v>
       </c>
       <c r="E159" t="n">
-        <v>6.299263885566218</v>
+        <v>6.299264832571459</v>
       </c>
       <c r="F159" t="n">
         <v>11578200</v>
@@ -3612,16 +3612,16 @@
         <v>44645</v>
       </c>
       <c r="B160" t="n">
-        <v>6.450091361999512</v>
+        <v>6.45009183883667</v>
       </c>
       <c r="C160" t="n">
-        <v>6.512196933355233</v>
+        <v>6.512197414783683</v>
       </c>
       <c r="D160" t="n">
-        <v>6.237158699739195</v>
+        <v>6.237159160834839</v>
       </c>
       <c r="E160" t="n">
-        <v>6.343625030869354</v>
+        <v>6.343625499835754</v>
       </c>
       <c r="F160" t="n">
         <v>15324200</v>
@@ -3672,16 +3672,16 @@
         <v>44650</v>
       </c>
       <c r="B163" t="n">
-        <v>6.50332498550415</v>
+        <v>6.503324508666992</v>
       </c>
       <c r="C163" t="n">
-        <v>6.61866373054667</v>
+        <v>6.618663245252637</v>
       </c>
       <c r="D163" t="n">
-        <v>6.450091816190593</v>
+        <v>6.4500913432566</v>
       </c>
       <c r="E163" t="n">
-        <v>6.547686171461927</v>
+        <v>6.547685691372115</v>
       </c>
       <c r="F163" t="n">
         <v>10697600</v>
@@ -3692,16 +3692,16 @@
         <v>44651</v>
       </c>
       <c r="B164" t="n">
-        <v>6.237159252166748</v>
+        <v>6.23715877532959</v>
       </c>
       <c r="C164" t="n">
-        <v>6.529941900236349</v>
+        <v>6.52994140101566</v>
       </c>
       <c r="D164" t="n">
-        <v>6.183925658827156</v>
+        <v>6.18392518605976</v>
       </c>
       <c r="E164" t="n">
-        <v>6.503325103566553</v>
+        <v>6.503324606380745</v>
       </c>
       <c r="F164" t="n">
         <v>12972000</v>
@@ -3712,16 +3712,16 @@
         <v>44652</v>
       </c>
       <c r="B165" t="n">
-        <v>6.139564990997314</v>
+        <v>6.139564514160156</v>
       </c>
       <c r="C165" t="n">
-        <v>6.299264504331019</v>
+        <v>6.299264015090594</v>
       </c>
       <c r="D165" t="n">
-        <v>5.926631883492739</v>
+        <v>5.926631423193302</v>
       </c>
       <c r="E165" t="n">
-        <v>6.254903739934808</v>
+        <v>6.254903254139719</v>
       </c>
       <c r="F165" t="n">
         <v>18919700</v>
@@ -3732,16 +3732,16 @@
         <v>44655</v>
       </c>
       <c r="B166" t="n">
-        <v>6.21054220199585</v>
+        <v>6.210542678833008</v>
       </c>
       <c r="C166" t="n">
-        <v>6.237158997579204</v>
+        <v>6.237159476459965</v>
       </c>
       <c r="D166" t="n">
-        <v>6.050842697674559</v>
+        <v>6.050843162250203</v>
       </c>
       <c r="E166" t="n">
-        <v>6.157309033888753</v>
+        <v>6.15730950663874</v>
       </c>
       <c r="F166" t="n">
         <v>13343800</v>
@@ -3752,16 +3752,16 @@
         <v>44656</v>
       </c>
       <c r="B167" t="n">
-        <v>6.299263477325439</v>
+        <v>6.299263954162598</v>
       </c>
       <c r="C167" t="n">
-        <v>6.325880270071385</v>
+        <v>6.325880748923362</v>
       </c>
       <c r="D167" t="n">
-        <v>6.148435972237409</v>
+        <v>6.148436437657334</v>
       </c>
       <c r="E167" t="n">
-        <v>6.228285927415676</v>
+        <v>6.228286398880027</v>
       </c>
       <c r="F167" t="n">
         <v>6962400</v>
@@ -3832,16 +3832,16 @@
         <v>44662</v>
       </c>
       <c r="B171" t="n">
-        <v>6.14585018157959</v>
+        <v>6.145850658416748</v>
       </c>
       <c r="C171" t="n">
-        <v>6.21710634662882</v>
+        <v>6.21710682899452</v>
       </c>
       <c r="D171" t="n">
-        <v>6.021151892743435</v>
+        <v>6.021152359905646</v>
       </c>
       <c r="E171" t="n">
-        <v>6.119128907326005</v>
+        <v>6.119129382089944</v>
       </c>
       <c r="F171" t="n">
         <v>4955900</v>
@@ -3852,16 +3852,16 @@
         <v>44663</v>
       </c>
       <c r="B172" t="n">
-        <v>6.217106819152832</v>
+        <v>6.217106342315674</v>
       </c>
       <c r="C172" t="n">
-        <v>6.359619160082779</v>
+        <v>6.359618672315267</v>
       </c>
       <c r="D172" t="n">
-        <v>6.145850648687858</v>
+        <v>6.145850177315878</v>
       </c>
       <c r="E172" t="n">
-        <v>6.190385542868328</v>
+        <v>6.190385068080627</v>
       </c>
       <c r="F172" t="n">
         <v>15598900</v>
@@ -3872,16 +3872,16 @@
         <v>44664</v>
       </c>
       <c r="B173" t="n">
-        <v>6.306176662445068</v>
+        <v>6.30617618560791</v>
       </c>
       <c r="C173" t="n">
-        <v>6.323990704016711</v>
+        <v>6.323990225832556</v>
       </c>
       <c r="D173" t="n">
-        <v>6.172571138297622</v>
+        <v>6.172570671562951</v>
       </c>
       <c r="E173" t="n">
-        <v>6.261641770876088</v>
+        <v>6.261641297406404</v>
       </c>
       <c r="F173" t="n">
         <v>5828500</v>
@@ -3972,16 +3972,16 @@
         <v>44673</v>
       </c>
       <c r="B178" t="n">
-        <v>6.128036022186279</v>
+        <v>6.128036499023438</v>
       </c>
       <c r="C178" t="n">
-        <v>6.190384953042324</v>
+        <v>6.190385434731002</v>
       </c>
       <c r="D178" t="n">
-        <v>5.98552327011481</v>
+        <v>5.98552373586271</v>
       </c>
       <c r="E178" t="n">
-        <v>6.136942830285612</v>
+        <v>6.136943307815831</v>
       </c>
       <c r="F178" t="n">
         <v>9926800</v>
@@ -3992,16 +3992,16 @@
         <v>44676</v>
       </c>
       <c r="B179" t="n">
-        <v>6.279454708099365</v>
+        <v>6.279455661773682</v>
       </c>
       <c r="C179" t="n">
-        <v>6.306175553397391</v>
+        <v>6.306176511129858</v>
       </c>
       <c r="D179" t="n">
-        <v>6.038964976816251</v>
+        <v>6.038965893966873</v>
       </c>
       <c r="E179" t="n">
-        <v>6.047871783675533</v>
+        <v>6.047872702178851</v>
       </c>
       <c r="F179" t="n">
         <v>9340700</v>
@@ -4072,16 +4072,16 @@
         <v>44680</v>
       </c>
       <c r="B183" t="n">
-        <v>6.14585018157959</v>
+        <v>6.145850658416748</v>
       </c>
       <c r="C183" t="n">
-        <v>6.44868888303882</v>
+        <v>6.44868938337228</v>
       </c>
       <c r="D183" t="n">
-        <v>6.065686783539082</v>
+        <v>6.065687254156614</v>
       </c>
       <c r="E183" t="n">
-        <v>6.413060800514205</v>
+        <v>6.413061298083393</v>
       </c>
       <c r="F183" t="n">
         <v>21979100</v>
@@ -4092,16 +4092,16 @@
         <v>44683</v>
       </c>
       <c r="B184" t="n">
-        <v>5.869731903076172</v>
+        <v>5.86973237991333</v>
       </c>
       <c r="C184" t="n">
-        <v>6.19038462249456</v>
+        <v>6.19038512538046</v>
       </c>
       <c r="D184" t="n">
-        <v>5.745033198582139</v>
+        <v>5.745033665289197</v>
       </c>
       <c r="E184" t="n">
-        <v>6.145849734935447</v>
+        <v>6.145850234203484</v>
       </c>
       <c r="F184" t="n">
         <v>12404500</v>
@@ -4112,16 +4112,16 @@
         <v>44684</v>
       </c>
       <c r="B185" t="n">
-        <v>5.52235746383667</v>
+        <v>5.522357940673828</v>
       </c>
       <c r="C185" t="n">
-        <v>5.905359958641743</v>
+        <v>5.905360468549889</v>
       </c>
       <c r="D185" t="n">
-        <v>5.228425593222683</v>
+        <v>5.228426044679804</v>
       </c>
       <c r="E185" t="n">
-        <v>5.905359958641743</v>
+        <v>5.905360468549889</v>
       </c>
       <c r="F185" t="n">
         <v>36500900</v>
@@ -4132,16 +4132,16 @@
         <v>44685</v>
       </c>
       <c r="B186" t="n">
-        <v>5.388752937316895</v>
+        <v>5.388752460479736</v>
       </c>
       <c r="C186" t="n">
-        <v>5.513451229542335</v>
+        <v>5.51345074167094</v>
       </c>
       <c r="D186" t="n">
-        <v>5.210612095131722</v>
+        <v>5.210611634057798</v>
       </c>
       <c r="E186" t="n">
-        <v>5.513451229542335</v>
+        <v>5.51345074167094</v>
       </c>
       <c r="F186" t="n">
         <v>18834300</v>
@@ -4172,16 +4172,16 @@
         <v>44687</v>
       </c>
       <c r="B188" t="n">
-        <v>4.952308177947998</v>
+        <v>4.952307224273682</v>
       </c>
       <c r="C188" t="n">
-        <v>5.068099659333893</v>
+        <v>5.068098683361416</v>
       </c>
       <c r="D188" t="n">
-        <v>4.863237971005097</v>
+        <v>4.863237034483181</v>
       </c>
       <c r="E188" t="n">
-        <v>4.970122219336578</v>
+        <v>4.970121262231782</v>
       </c>
       <c r="F188" t="n">
         <v>14479200</v>
@@ -4192,16 +4192,16 @@
         <v>44690</v>
       </c>
       <c r="B189" t="n">
-        <v>4.622747421264648</v>
+        <v>4.622748374938965</v>
       </c>
       <c r="C189" t="n">
-        <v>4.934493305415869</v>
+        <v>4.934494323403464</v>
       </c>
       <c r="D189" t="n">
-        <v>4.435699805829881</v>
+        <v>4.435700720916212</v>
       </c>
       <c r="E189" t="n">
-        <v>4.934493305415869</v>
+        <v>4.934494323403464</v>
       </c>
       <c r="F189" t="n">
         <v>21341300</v>
@@ -4252,16 +4252,16 @@
         <v>44693</v>
       </c>
       <c r="B192" t="n">
-        <v>4.79198169708252</v>
+        <v>4.791981220245361</v>
       </c>
       <c r="C192" t="n">
-        <v>4.809795738068244</v>
+        <v>4.809795259458459</v>
       </c>
       <c r="D192" t="n">
-        <v>4.55149193141512</v>
+        <v>4.551491478508448</v>
       </c>
       <c r="E192" t="n">
-        <v>4.587120013386569</v>
+        <v>4.587119556934643</v>
       </c>
       <c r="F192" t="n">
         <v>13350100</v>
@@ -4272,16 +4272,16 @@
         <v>44694</v>
       </c>
       <c r="B193" t="n">
-        <v>4.604934692382812</v>
+        <v>4.604934215545654</v>
       </c>
       <c r="C193" t="n">
-        <v>4.80088917037514</v>
+        <v>4.800888673247058</v>
       </c>
       <c r="D193" t="n">
-        <v>4.515864475113573</v>
+        <v>4.515864007499562</v>
       </c>
       <c r="E193" t="n">
-        <v>4.80088917037514</v>
+        <v>4.800888673247058</v>
       </c>
       <c r="F193" t="n">
         <v>51332400</v>
@@ -4292,16 +4292,16 @@
         <v>44697</v>
       </c>
       <c r="B194" t="n">
-        <v>4.881052017211914</v>
+        <v>4.881052494049072</v>
       </c>
       <c r="C194" t="n">
-        <v>4.881052017211914</v>
+        <v>4.881052494049072</v>
       </c>
       <c r="D194" t="n">
-        <v>4.542584805774532</v>
+        <v>4.542585249546331</v>
       </c>
       <c r="E194" t="n">
-        <v>4.604934163056234</v>
+        <v>4.604934612919033</v>
       </c>
       <c r="F194" t="n">
         <v>29391700</v>
@@ -4332,16 +4332,16 @@
         <v>44699</v>
       </c>
       <c r="B196" t="n">
-        <v>4.952308177947998</v>
+        <v>4.952307224273682</v>
       </c>
       <c r="C196" t="n">
-        <v>5.112634550445218</v>
+        <v>5.112633565896584</v>
       </c>
       <c r="D196" t="n">
-        <v>4.898866053782258</v>
+        <v>4.898865110399381</v>
       </c>
       <c r="E196" t="n">
-        <v>4.987936260725158</v>
+        <v>4.987935300189882</v>
       </c>
       <c r="F196" t="n">
         <v>17779600</v>
@@ -4392,16 +4392,16 @@
         <v>44704</v>
       </c>
       <c r="B199" t="n">
-        <v>5.02356481552124</v>
+        <v>5.023564338684082</v>
       </c>
       <c r="C199" t="n">
-        <v>5.103728221662204</v>
+        <v>5.10372773721593</v>
       </c>
       <c r="D199" t="n">
-        <v>4.881052471022004</v>
+        <v>4.881052007712129</v>
       </c>
       <c r="E199" t="n">
-        <v>4.979029920225373</v>
+        <v>4.979029447615471</v>
       </c>
       <c r="F199" t="n">
         <v>11444200</v>
@@ -4452,16 +4452,16 @@
         <v>44707</v>
       </c>
       <c r="B202" t="n">
-        <v>5.504544258117676</v>
+        <v>5.504543781280518</v>
       </c>
       <c r="C202" t="n">
-        <v>5.647057023588098</v>
+        <v>5.647056534405616</v>
       </c>
       <c r="D202" t="n">
-        <v>5.281868513335436</v>
+        <v>5.281868055787807</v>
       </c>
       <c r="E202" t="n">
-        <v>5.281868513335436</v>
+        <v>5.281868055787807</v>
       </c>
       <c r="F202" t="n">
         <v>14781100</v>
@@ -4492,16 +4492,16 @@
         <v>44711</v>
       </c>
       <c r="B204" t="n">
-        <v>5.602520942687988</v>
+        <v>5.602521419525146</v>
       </c>
       <c r="C204" t="n">
-        <v>5.67377710337079</v>
+        <v>5.673777586272644</v>
       </c>
       <c r="D204" t="n">
-        <v>5.317495875236564</v>
+        <v>5.317496327814903</v>
       </c>
       <c r="E204" t="n">
-        <v>5.460008621322386</v>
+        <v>5.460009086030153</v>
       </c>
       <c r="F204" t="n">
         <v>7527500</v>
@@ -4512,16 +4512,16 @@
         <v>44712</v>
       </c>
       <c r="B205" t="n">
-        <v>5.46000862121582</v>
+        <v>5.460009098052979</v>
       </c>
       <c r="C205" t="n">
-        <v>5.691591143430404</v>
+        <v>5.691591640492284</v>
       </c>
       <c r="D205" t="n">
-        <v>5.46000862121582</v>
+        <v>5.460009098052979</v>
       </c>
       <c r="E205" t="n">
-        <v>5.62924221519428</v>
+        <v>5.629242706811061</v>
       </c>
       <c r="F205" t="n">
         <v>13931800</v>
@@ -4532,16 +4532,16 @@
         <v>44713</v>
       </c>
       <c r="B206" t="n">
-        <v>5.513451099395752</v>
+        <v>5.51345157623291</v>
       </c>
       <c r="C206" t="n">
-        <v>5.549079182047723</v>
+        <v>5.549079661966218</v>
       </c>
       <c r="D206" t="n">
-        <v>5.406566851439836</v>
+        <v>5.406567319032987</v>
       </c>
       <c r="E206" t="n">
-        <v>5.495637058069765</v>
+        <v>5.495637533366256</v>
       </c>
       <c r="F206" t="n">
         <v>9091200</v>
@@ -4552,16 +4552,16 @@
         <v>44714</v>
       </c>
       <c r="B207" t="n">
-        <v>5.611428260803223</v>
+        <v>5.611427783966064</v>
       </c>
       <c r="C207" t="n">
-        <v>5.655963149549779</v>
+        <v>5.65596266892822</v>
       </c>
       <c r="D207" t="n">
-        <v>5.504543593426991</v>
+        <v>5.504543125672473</v>
       </c>
       <c r="E207" t="n">
-        <v>5.549078906893773</v>
+        <v>5.549078435354819</v>
       </c>
       <c r="F207" t="n">
         <v>14163200</v>
@@ -4572,16 +4572,16 @@
         <v>44715</v>
       </c>
       <c r="B208" t="n">
-        <v>5.513451099395752</v>
+        <v>5.51345157623291</v>
       </c>
       <c r="C208" t="n">
-        <v>5.602521306025682</v>
+        <v>5.602521790566179</v>
       </c>
       <c r="D208" t="n">
-        <v>5.451101742394677</v>
+        <v>5.45110221383948</v>
       </c>
       <c r="E208" t="n">
-        <v>5.575800456396826</v>
+        <v>5.57580093862634</v>
       </c>
       <c r="F208" t="n">
         <v>9326300</v>
@@ -4612,16 +4612,16 @@
         <v>44719</v>
       </c>
       <c r="B210" t="n">
-        <v>5.02356481552124</v>
+        <v>5.023564338684082</v>
       </c>
       <c r="C210" t="n">
-        <v>5.299682695348654</v>
+        <v>5.299682192302366</v>
       </c>
       <c r="D210" t="n">
-        <v>4.987936729396432</v>
+        <v>4.987936255941094</v>
       </c>
       <c r="E210" t="n">
-        <v>5.281868652286249</v>
+        <v>5.281868150930872</v>
       </c>
       <c r="F210" t="n">
         <v>18881300</v>
@@ -4632,16 +4632,16 @@
         <v>44720</v>
       </c>
       <c r="B211" t="n">
-        <v>4.916679859161377</v>
+        <v>4.916679382324219</v>
       </c>
       <c r="C211" t="n">
-        <v>5.005750061828747</v>
+        <v>5.005749576353243</v>
       </c>
       <c r="D211" t="n">
-        <v>4.783074342800206</v>
+        <v>4.783073878920588</v>
       </c>
       <c r="E211" t="n">
-        <v>4.996843253922124</v>
+        <v>4.996842769310434</v>
       </c>
       <c r="F211" t="n">
         <v>13996400</v>
@@ -4692,16 +4692,16 @@
         <v>44725</v>
       </c>
       <c r="B214" t="n">
-        <v>4.569305896759033</v>
+        <v>4.569305419921875</v>
       </c>
       <c r="C214" t="n">
-        <v>4.676190140903983</v>
+        <v>4.67618965291275</v>
       </c>
       <c r="D214" t="n">
-        <v>4.50695654198103</v>
+        <v>4.506956071650437</v>
       </c>
       <c r="E214" t="n">
-        <v>4.631654826816805</v>
+        <v>4.631654343473125</v>
       </c>
       <c r="F214" t="n">
         <v>7709600</v>
@@ -4712,16 +4712,16 @@
         <v>44726</v>
       </c>
       <c r="B215" t="n">
-        <v>4.462421417236328</v>
+        <v>4.462421894073486</v>
       </c>
       <c r="C215" t="n">
-        <v>4.640561814748269</v>
+        <v>4.640562310620824</v>
       </c>
       <c r="D215" t="n">
-        <v>4.453514185000626</v>
+        <v>4.453514660885992</v>
       </c>
       <c r="E215" t="n">
-        <v>4.587119695494687</v>
+        <v>4.587120185656623</v>
       </c>
       <c r="F215" t="n">
         <v>9819800</v>
@@ -4732,16 +4732,16 @@
         <v>44727</v>
       </c>
       <c r="B216" t="n">
-        <v>4.560399055480957</v>
+        <v>4.560398578643799</v>
       </c>
       <c r="C216" t="n">
-        <v>4.649469266580143</v>
+        <v>4.649468780429767</v>
       </c>
       <c r="D216" t="n">
-        <v>4.480236077851825</v>
+        <v>4.48023560939654</v>
       </c>
       <c r="E216" t="n">
-        <v>4.54258501326112</v>
+        <v>4.542584538286605</v>
       </c>
       <c r="F216" t="n">
         <v>10830000</v>
@@ -4792,16 +4792,16 @@
         <v>44733</v>
       </c>
       <c r="B219" t="n">
-        <v>4.489142417907715</v>
+        <v>4.489142894744873</v>
       </c>
       <c r="C219" t="n">
-        <v>4.596026660067369</v>
+        <v>4.596027148257782</v>
       </c>
       <c r="D219" t="n">
-        <v>4.444607104647747</v>
+        <v>4.44460757675436</v>
       </c>
       <c r="E219" t="n">
-        <v>4.560398579347484</v>
+        <v>4.560399063753479</v>
       </c>
       <c r="F219" t="n">
         <v>7411800</v>
@@ -4812,16 +4812,16 @@
         <v>44734</v>
       </c>
       <c r="B220" t="n">
-        <v>4.444607257843018</v>
+        <v>4.444607734680176</v>
       </c>
       <c r="C220" t="n">
-        <v>4.533677887433011</v>
+        <v>4.533678373826061</v>
       </c>
       <c r="D220" t="n">
-        <v>4.40007236776826</v>
+        <v>4.400072839827518</v>
       </c>
       <c r="E220" t="n">
-        <v>4.480235764511158</v>
+        <v>4.4802362451707</v>
       </c>
       <c r="F220" t="n">
         <v>8433900</v>
@@ -4852,16 +4852,16 @@
         <v>44736</v>
       </c>
       <c r="B222" t="n">
-        <v>4.257559776306152</v>
+        <v>4.257560253143311</v>
       </c>
       <c r="C222" t="n">
-        <v>4.337722743364323</v>
+        <v>4.337723229179554</v>
       </c>
       <c r="D222" t="n">
-        <v>4.230838504139954</v>
+        <v>4.23083897798439</v>
       </c>
       <c r="E222" t="n">
-        <v>4.319908703493595</v>
+        <v>4.319909187313693</v>
       </c>
       <c r="F222" t="n">
         <v>7941200</v>
@@ -4872,16 +4872,16 @@
         <v>44739</v>
       </c>
       <c r="B223" t="n">
-        <v>4.275374412536621</v>
+        <v>4.275373458862305</v>
       </c>
       <c r="C223" t="n">
-        <v>4.337723348420938</v>
+        <v>4.337722380838932</v>
       </c>
       <c r="D223" t="n">
-        <v>4.239746327825506</v>
+        <v>4.239745382098467</v>
       </c>
       <c r="E223" t="n">
-        <v>4.275374412536621</v>
+        <v>4.275373458862305</v>
       </c>
       <c r="F223" t="n">
         <v>10516900</v>
@@ -4892,16 +4892,16 @@
         <v>44740</v>
       </c>
       <c r="B224" t="n">
-        <v>4.293188095092773</v>
+        <v>4.293187618255615</v>
       </c>
       <c r="C224" t="n">
-        <v>4.471328503718931</v>
+        <v>4.471328007096019</v>
       </c>
       <c r="D224" t="n">
-        <v>4.293188095092773</v>
+        <v>4.293187618255615</v>
       </c>
       <c r="E224" t="n">
-        <v>4.319908944026579</v>
+        <v>4.319908464221581</v>
       </c>
       <c r="F224" t="n">
         <v>8975600</v>
@@ -4912,16 +4912,16 @@
         <v>44741</v>
       </c>
       <c r="B225" t="n">
-        <v>4.275374412536621</v>
+        <v>4.275373458862305</v>
       </c>
       <c r="C225" t="n">
-        <v>4.355537390776496</v>
+        <v>4.355536419220851</v>
       </c>
       <c r="D225" t="n">
-        <v>4.248653136643148</v>
+        <v>4.248652188929338</v>
       </c>
       <c r="E225" t="n">
-        <v>4.311002497247737</v>
+        <v>4.311001535626143</v>
       </c>
       <c r="F225" t="n">
         <v>7179800</v>
@@ -4932,16 +4932,16 @@
         <v>44742</v>
       </c>
       <c r="B226" t="n">
-        <v>4.088325977325439</v>
+        <v>4.088326454162598</v>
       </c>
       <c r="C226" t="n">
-        <v>4.239745520888632</v>
+        <v>4.239746015386434</v>
       </c>
       <c r="D226" t="n">
-        <v>4.052697899395299</v>
+        <v>4.052698372077018</v>
       </c>
       <c r="E226" t="n">
-        <v>4.239745520888632</v>
+        <v>4.239746015386434</v>
       </c>
       <c r="F226" t="n">
         <v>6721700</v>
@@ -4952,16 +4952,16 @@
         <v>44743</v>
       </c>
       <c r="B227" t="n">
-        <v>4.02597713470459</v>
+        <v>4.025977611541748</v>
       </c>
       <c r="C227" t="n">
-        <v>4.186303505545305</v>
+        <v>4.186304001371536</v>
       </c>
       <c r="D227" t="n">
-        <v>4.02597713470459</v>
+        <v>4.025977611541748</v>
       </c>
       <c r="E227" t="n">
-        <v>4.02597713470459</v>
+        <v>4.025977611541748</v>
       </c>
       <c r="F227" t="n">
         <v>12849200</v>
@@ -4972,16 +4972,16 @@
         <v>44746</v>
       </c>
       <c r="B228" t="n">
-        <v>4.0437912940979</v>
+        <v>4.043790817260742</v>
       </c>
       <c r="C228" t="n">
-        <v>4.195210861122049</v>
+        <v>4.195210366429746</v>
       </c>
       <c r="D228" t="n">
-        <v>4.008163210647543</v>
+        <v>4.008162738011589</v>
       </c>
       <c r="E228" t="n">
-        <v>4.034884485595439</v>
+        <v>4.034884009808557</v>
       </c>
       <c r="F228" t="n">
         <v>5003300</v>
@@ -5012,16 +5012,16 @@
         <v>44748</v>
       </c>
       <c r="B230" t="n">
-        <v>3.91018533706665</v>
+        <v>3.910185575485229</v>
       </c>
       <c r="C230" t="n">
-        <v>4.052698079853188</v>
+        <v>4.0526983269613</v>
       </c>
       <c r="D230" t="n">
-        <v>3.785487058758614</v>
+        <v>3.785487289573874</v>
       </c>
       <c r="E230" t="n">
-        <v>4.034884040094897</v>
+        <v>4.034884286116821</v>
       </c>
       <c r="F230" t="n">
         <v>11922900</v>
@@ -5032,16 +5032,16 @@
         <v>44749</v>
       </c>
       <c r="B231" t="n">
-        <v>4.052698135375977</v>
+        <v>4.052698612213135</v>
       </c>
       <c r="C231" t="n">
-        <v>4.141768335387711</v>
+        <v>4.141768822704797</v>
       </c>
       <c r="D231" t="n">
-        <v>3.927999430639332</v>
+        <v>3.927999892804543</v>
       </c>
       <c r="E231" t="n">
-        <v>3.927999430639332</v>
+        <v>3.927999892804543</v>
       </c>
       <c r="F231" t="n">
         <v>10027800</v>
@@ -5072,16 +5072,16 @@
         <v>44753</v>
       </c>
       <c r="B233" t="n">
-        <v>3.705323457717896</v>
+        <v>3.705323696136475</v>
       </c>
       <c r="C233" t="n">
-        <v>3.901278308685776</v>
+        <v>3.901278559713046</v>
       </c>
       <c r="D233" t="n">
-        <v>3.678602611953303</v>
+        <v>3.678602848652532</v>
       </c>
       <c r="E233" t="n">
-        <v>3.892371076950788</v>
+        <v>3.892371327404923</v>
       </c>
       <c r="F233" t="n">
         <v>13261200</v>
@@ -5132,16 +5132,16 @@
         <v>44756</v>
       </c>
       <c r="B236" t="n">
-        <v>3.821115255355835</v>
+        <v>3.821115493774414</v>
       </c>
       <c r="C236" t="n">
-        <v>3.856743335964077</v>
+        <v>3.856743576605671</v>
       </c>
       <c r="D236" t="n">
-        <v>3.651881660106575</v>
+        <v>3.651881887965819</v>
       </c>
       <c r="E236" t="n">
-        <v>3.687509740714817</v>
+        <v>3.687509970797076</v>
       </c>
       <c r="F236" t="n">
         <v>9774500</v>
@@ -5152,16 +5152,16 @@
         <v>44757</v>
       </c>
       <c r="B237" t="n">
-        <v>3.936907052993774</v>
+        <v>3.936906576156616</v>
       </c>
       <c r="C237" t="n">
-        <v>3.954721094760794</v>
+        <v>3.954720615766004</v>
       </c>
       <c r="D237" t="n">
-        <v>3.776580252370335</v>
+        <v>3.776579794951918</v>
       </c>
       <c r="E237" t="n">
-        <v>3.830022802391653</v>
+        <v>3.830022338500288</v>
       </c>
       <c r="F237" t="n">
         <v>4881500</v>
@@ -5172,16 +5172,16 @@
         <v>44760</v>
       </c>
       <c r="B238" t="n">
-        <v>3.830023050308228</v>
+        <v>3.830022811889648</v>
       </c>
       <c r="C238" t="n">
-        <v>4.0883268850101</v>
+        <v>4.088326630512132</v>
       </c>
       <c r="D238" t="n">
-        <v>3.830023050308228</v>
+        <v>3.830022811889648</v>
       </c>
       <c r="E238" t="n">
-        <v>3.990349436589301</v>
+        <v>3.99034918819042</v>
       </c>
       <c r="F238" t="n">
         <v>5011900</v>
@@ -5192,16 +5192,16 @@
         <v>44761</v>
       </c>
       <c r="B239" t="n">
-        <v>3.856743097305298</v>
+        <v>3.856743812561035</v>
       </c>
       <c r="C239" t="n">
-        <v>3.93690648607337</v>
+        <v>3.93690721619588</v>
       </c>
       <c r="D239" t="n">
-        <v>3.830022250862738</v>
+        <v>3.830022961162937</v>
       </c>
       <c r="E239" t="n">
-        <v>3.838929058103526</v>
+        <v>3.838929770055544</v>
       </c>
       <c r="F239" t="n">
         <v>5270100</v>
@@ -5212,16 +5212,16 @@
         <v>44762</v>
       </c>
       <c r="B240" t="n">
-        <v>3.999255418777466</v>
+        <v>3.999256372451782</v>
       </c>
       <c r="C240" t="n">
-        <v>4.025976689992726</v>
+        <v>4.025977650039076</v>
       </c>
       <c r="D240" t="n">
-        <v>3.803300987172951</v>
+        <v>3.803301894119392</v>
       </c>
       <c r="E240" t="n">
-        <v>3.83002225838821</v>
+        <v>3.830023171706685</v>
       </c>
       <c r="F240" t="n">
         <v>11021800</v>
@@ -5232,16 +5232,16 @@
         <v>44763</v>
       </c>
       <c r="B241" t="n">
-        <v>3.963628053665161</v>
+        <v>3.963627576828003</v>
       </c>
       <c r="C241" t="n">
-        <v>4.02597741457541</v>
+        <v>4.025976930237424</v>
       </c>
       <c r="D241" t="n">
-        <v>3.936907202360965</v>
+        <v>3.93690672873841</v>
       </c>
       <c r="E241" t="n">
-        <v>4.02597741457541</v>
+        <v>4.025976930237424</v>
       </c>
       <c r="F241" t="n">
         <v>6658500</v>
@@ -5272,16 +5272,16 @@
         <v>44767</v>
       </c>
       <c r="B243" t="n">
-        <v>3.696417570114136</v>
+        <v>3.696416854858398</v>
       </c>
       <c r="C243" t="n">
-        <v>3.78548778601755</v>
+        <v>3.78548705352675</v>
       </c>
       <c r="D243" t="n">
-        <v>3.651882249802283</v>
+        <v>3.651881543164118</v>
       </c>
       <c r="E243" t="n">
-        <v>3.767673742836867</v>
+        <v>3.76767301379308</v>
       </c>
       <c r="F243" t="n">
         <v>10514300</v>
@@ -5292,16 +5292,16 @@
         <v>44768</v>
       </c>
       <c r="B244" t="n">
-        <v>3.714231014251709</v>
+        <v>3.71423077583313</v>
       </c>
       <c r="C244" t="n">
-        <v>3.812208448303494</v>
+        <v>3.812208203595688</v>
       </c>
       <c r="D244" t="n">
-        <v>3.669695701122655</v>
+        <v>3.669695465562822</v>
       </c>
       <c r="E244" t="n">
-        <v>3.705323781737809</v>
+        <v>3.70532354389099</v>
       </c>
       <c r="F244" t="n">
         <v>4594100</v>
@@ -5312,16 +5312,16 @@
         <v>44769</v>
       </c>
       <c r="B245" t="n">
-        <v>3.999255418777466</v>
+        <v>3.999256372451782</v>
       </c>
       <c r="C245" t="n">
-        <v>3.999255418777466</v>
+        <v>3.999256372451782</v>
       </c>
       <c r="D245" t="n">
-        <v>3.723137598247368</v>
+        <v>3.72313848607781</v>
       </c>
       <c r="E245" t="n">
-        <v>3.740951637484142</v>
+        <v>3.740952529562573</v>
       </c>
       <c r="F245" t="n">
         <v>8689000</v>
@@ -5332,16 +5332,16 @@
         <v>44770</v>
       </c>
       <c r="B246" t="n">
-        <v>3.999255418777466</v>
+        <v>3.999256372451782</v>
       </c>
       <c r="C246" t="n">
-        <v>4.07051200044476</v>
+        <v>4.070512971111132</v>
       </c>
       <c r="D246" t="n">
-        <v>3.892371183356821</v>
+        <v>3.892372111543206</v>
       </c>
       <c r="E246" t="n">
-        <v>4.025976689992726</v>
+        <v>4.025977650039076</v>
       </c>
       <c r="F246" t="n">
         <v>3634200</v>
@@ -5352,16 +5352,16 @@
         <v>44771</v>
       </c>
       <c r="B247" t="n">
-        <v>3.927999973297119</v>
+        <v>3.92799973487854</v>
       </c>
       <c r="C247" t="n">
-        <v>4.088326780187793</v>
+        <v>4.088326532037827</v>
       </c>
       <c r="D247" t="n">
-        <v>3.919093164425567</v>
+        <v>3.919092926547607</v>
       </c>
       <c r="E247" t="n">
-        <v>4.025977419205834</v>
+        <v>4.025977174840299</v>
       </c>
       <c r="F247" t="n">
         <v>8694600</v>
@@ -5372,16 +5372,16 @@
         <v>44774</v>
       </c>
       <c r="B248" t="n">
-        <v>3.927999973297119</v>
+        <v>3.92799973487854</v>
       </c>
       <c r="C248" t="n">
-        <v>3.990349334279078</v>
+        <v>3.990349092076068</v>
       </c>
       <c r="D248" t="n">
-        <v>3.874557845906986</v>
+        <v>3.874557610732194</v>
       </c>
       <c r="E248" t="n">
-        <v>3.981442100687252</v>
+        <v>3.981441859024886</v>
       </c>
       <c r="F248" t="n">
         <v>7696400</v>
@@ -5492,16 +5492,16 @@
         <v>44782</v>
       </c>
       <c r="B254" t="n">
-        <v>4.382258892059326</v>
+        <v>4.382258415222168</v>
       </c>
       <c r="C254" t="n">
-        <v>4.578213368048839</v>
+        <v>4.578212869889715</v>
       </c>
       <c r="D254" t="n">
-        <v>4.364444848787552</v>
+        <v>4.364444373888754</v>
       </c>
       <c r="E254" t="n">
-        <v>4.453515065146422</v>
+        <v>4.453514580555821</v>
       </c>
       <c r="F254" t="n">
         <v>9216300</v>
@@ -5532,16 +5532,16 @@
         <v>44784</v>
       </c>
       <c r="B256" t="n">
-        <v>4.346630096435547</v>
+        <v>4.346630573272705</v>
       </c>
       <c r="C256" t="n">
-        <v>4.685097288104267</v>
+        <v>4.685097802072197</v>
       </c>
       <c r="D256" t="n">
-        <v>4.311002015704126</v>
+        <v>4.311002488632787</v>
       </c>
       <c r="E256" t="n">
-        <v>4.613840701921201</v>
+        <v>4.61384120807209</v>
       </c>
       <c r="F256" t="n">
         <v>11482900</v>
@@ -5592,16 +5592,16 @@
         <v>44789</v>
       </c>
       <c r="B259" t="n">
-        <v>4.622747421264648</v>
+        <v>4.622748374938965</v>
       </c>
       <c r="C259" t="n">
-        <v>4.702910806371028</v>
+        <v>4.702911776583077</v>
       </c>
       <c r="D259" t="n">
-        <v>4.560398074546333</v>
+        <v>4.560399015357959</v>
       </c>
       <c r="E259" t="n">
-        <v>4.676189536428843</v>
+        <v>4.676190501128285</v>
       </c>
       <c r="F259" t="n">
         <v>5754000</v>
@@ -5632,16 +5632,16 @@
         <v>44791</v>
       </c>
       <c r="B261" t="n">
-        <v>4.533677577972412</v>
+        <v>4.533677101135254</v>
       </c>
       <c r="C261" t="n">
-        <v>4.711817975552381</v>
+        <v>4.711817479979008</v>
       </c>
       <c r="D261" t="n">
-        <v>4.515863538214415</v>
+        <v>4.515863063250879</v>
       </c>
       <c r="E261" t="n">
-        <v>4.640561816520393</v>
+        <v>4.640561328441506</v>
       </c>
       <c r="F261" t="n">
         <v>8785600</v>
@@ -5652,16 +5652,16 @@
         <v>44792</v>
       </c>
       <c r="B262" t="n">
-        <v>4.319908618927002</v>
+        <v>4.31990909576416</v>
       </c>
       <c r="C262" t="n">
-        <v>4.533677517911209</v>
+        <v>4.533678018344458</v>
       </c>
       <c r="D262" t="n">
-        <v>4.221931189195899</v>
+        <v>4.22193165521818</v>
       </c>
       <c r="E262" t="n">
-        <v>4.524770285790107</v>
+        <v>4.524770785240164</v>
       </c>
       <c r="F262" t="n">
         <v>17743000</v>
@@ -5672,16 +5672,16 @@
         <v>44795</v>
       </c>
       <c r="B263" t="n">
-        <v>4.319908618927002</v>
+        <v>4.31990909576416</v>
       </c>
       <c r="C263" t="n">
-        <v>4.364443930092105</v>
+        <v>4.364444411845128</v>
       </c>
       <c r="D263" t="n">
-        <v>4.177396302751</v>
+        <v>4.177396763857463</v>
       </c>
       <c r="E263" t="n">
-        <v>4.302094579405002</v>
+        <v>4.302095054275823</v>
       </c>
       <c r="F263" t="n">
         <v>9829500</v>
@@ -5712,16 +5712,16 @@
         <v>44797</v>
       </c>
       <c r="B265" t="n">
-        <v>4.533677577972412</v>
+        <v>4.533677101135254</v>
       </c>
       <c r="C265" t="n">
-        <v>4.6049337370044</v>
+        <v>4.604933252672756</v>
       </c>
       <c r="D265" t="n">
-        <v>4.426792914704221</v>
+        <v>4.426792449108837</v>
       </c>
       <c r="E265" t="n">
-        <v>4.453514186701321</v>
+        <v>4.453513718295483</v>
       </c>
       <c r="F265" t="n">
         <v>5861300</v>
@@ -5752,16 +5752,16 @@
         <v>44799</v>
       </c>
       <c r="B267" t="n">
-        <v>4.319908618927002</v>
+        <v>4.31990909576416</v>
       </c>
       <c r="C267" t="n">
-        <v>4.524770285790107</v>
+        <v>4.524770785240164</v>
       </c>
       <c r="D267" t="n">
-        <v>4.293187772004104</v>
+        <v>4.29318824589178</v>
       </c>
       <c r="E267" t="n">
-        <v>4.489142206746107</v>
+        <v>4.489142702263489</v>
       </c>
       <c r="F267" t="n">
         <v>6692300</v>
@@ -5792,16 +5792,16 @@
         <v>44803</v>
       </c>
       <c r="B269" t="n">
-        <v>4.364443778991699</v>
+        <v>4.364444255828857</v>
       </c>
       <c r="C269" t="n">
-        <v>4.480235244236013</v>
+        <v>4.480235733723964</v>
       </c>
       <c r="D269" t="n">
-        <v>4.337722508273708</v>
+        <v>4.337722982191434</v>
       </c>
       <c r="E269" t="n">
-        <v>4.471328012423286</v>
+        <v>4.471328500938078</v>
       </c>
       <c r="F269" t="n">
         <v>7827400</v>
@@ -5812,16 +5812,16 @@
         <v>44804</v>
       </c>
       <c r="B270" t="n">
-        <v>4.311002254486084</v>
+        <v>4.311001777648926</v>
       </c>
       <c r="C270" t="n">
-        <v>4.435700543952965</v>
+        <v>4.43570005332301</v>
       </c>
       <c r="D270" t="n">
-        <v>4.284280980097343</v>
+        <v>4.284280506215807</v>
       </c>
       <c r="E270" t="n">
-        <v>4.382258419895731</v>
+        <v>4.382257935176974</v>
       </c>
       <c r="F270" t="n">
         <v>8375100</v>
@@ -5852,16 +5852,16 @@
         <v>44806</v>
       </c>
       <c r="B272" t="n">
-        <v>4.097233772277832</v>
+        <v>4.097233295440674</v>
       </c>
       <c r="C272" t="n">
-        <v>4.355537611907676</v>
+        <v>4.355537105009048</v>
       </c>
       <c r="D272" t="n">
-        <v>4.097233772277832</v>
+        <v>4.097233295440674</v>
       </c>
       <c r="E272" t="n">
-        <v>4.319909525387717</v>
+        <v>4.319909022635495</v>
       </c>
       <c r="F272" t="n">
         <v>69570300</v>
@@ -5872,16 +5872,16 @@
         <v>44809</v>
       </c>
       <c r="B273" t="n">
-        <v>4.115046501159668</v>
+        <v>4.115047454833984</v>
       </c>
       <c r="C273" t="n">
-        <v>4.221930726579882</v>
+        <v>4.221931705024937</v>
       </c>
       <c r="D273" t="n">
-        <v>4.115046501159668</v>
+        <v>4.115047454833984</v>
       </c>
       <c r="E273" t="n">
-        <v>4.123953732304765</v>
+        <v>4.123954688043359</v>
       </c>
       <c r="F273" t="n">
         <v>7604300</v>
@@ -5892,16 +5892,16 @@
         <v>44810</v>
       </c>
       <c r="B274" t="n">
-        <v>3.954720973968506</v>
+        <v>3.954720497131348</v>
       </c>
       <c r="C274" t="n">
-        <v>4.177396701615019</v>
+        <v>4.177396197928922</v>
       </c>
       <c r="D274" t="n">
-        <v>3.945813740996928</v>
+        <v>3.945813265233752</v>
       </c>
       <c r="E274" t="n">
-        <v>4.141768619169197</v>
+        <v>4.141768119778925</v>
       </c>
       <c r="F274" t="n">
         <v>14609100</v>
@@ -5912,16 +5912,16 @@
         <v>44812</v>
       </c>
       <c r="B275" t="n">
-        <v>3.91018533706665</v>
+        <v>3.910185575485229</v>
       </c>
       <c r="C275" t="n">
-        <v>4.008162768097356</v>
+        <v>4.008163012489984</v>
       </c>
       <c r="D275" t="n">
-        <v>3.856743217791777</v>
+        <v>3.856743452951791</v>
       </c>
       <c r="E275" t="n">
-        <v>3.990348728339065</v>
+        <v>3.990348971645505</v>
       </c>
       <c r="F275" t="n">
         <v>9864000</v>
@@ -5932,16 +5932,16 @@
         <v>44813</v>
       </c>
       <c r="B276" t="n">
-        <v>3.91018533706665</v>
+        <v>3.910185575485229</v>
       </c>
       <c r="C276" t="n">
-        <v>4.043790847613938</v>
+        <v>4.043791094178943</v>
       </c>
       <c r="D276" t="n">
-        <v>3.883464489789319</v>
+        <v>3.883464726578628</v>
       </c>
       <c r="E276" t="n">
-        <v>3.945813416583232</v>
+        <v>3.945813657174188</v>
       </c>
       <c r="F276" t="n">
         <v>15548300</v>
@@ -5952,16 +5952,16 @@
         <v>44816</v>
       </c>
       <c r="B277" t="n">
-        <v>3.856743097305298</v>
+        <v>3.856743812561035</v>
       </c>
       <c r="C277" t="n">
-        <v>3.990348603678686</v>
+        <v>3.990349343712352</v>
       </c>
       <c r="D277" t="n">
-        <v>3.838929058103526</v>
+        <v>3.838929770055544</v>
       </c>
       <c r="E277" t="n">
-        <v>3.954720525275142</v>
+        <v>3.95472125870137</v>
       </c>
       <c r="F277" t="n">
         <v>15738600</v>
@@ -5972,16 +5972,16 @@
         <v>44817</v>
       </c>
       <c r="B278" t="n">
-        <v>3.696417570114136</v>
+        <v>3.696416854858398</v>
       </c>
       <c r="C278" t="n">
-        <v>3.88346523587145</v>
+        <v>3.883464484422043</v>
       </c>
       <c r="D278" t="n">
-        <v>3.678603526933453</v>
+        <v>3.678602815124728</v>
       </c>
       <c r="E278" t="n">
-        <v>3.874558001920963</v>
+        <v>3.874557252195103</v>
       </c>
       <c r="F278" t="n">
         <v>21443000</v>
@@ -6012,16 +6012,16 @@
         <v>44819</v>
       </c>
       <c r="B280" t="n">
-        <v>3.749859094619751</v>
+        <v>3.74985933303833</v>
       </c>
       <c r="C280" t="n">
-        <v>3.758765902412841</v>
+        <v>3.758766141397721</v>
       </c>
       <c r="D280" t="n">
-        <v>3.634067620268019</v>
+        <v>3.634067851324498</v>
       </c>
       <c r="E280" t="n">
-        <v>3.740951862106438</v>
+        <v>3.740952099958689</v>
       </c>
       <c r="F280" t="n">
         <v>12717200</v>
@@ -6032,16 +6032,16 @@
         <v>44820</v>
       </c>
       <c r="B281" t="n">
-        <v>3.821115255355835</v>
+        <v>3.821115493774414</v>
       </c>
       <c r="C281" t="n">
-        <v>3.892371416572319</v>
+        <v>3.892371659436928</v>
       </c>
       <c r="D281" t="n">
-        <v>3.660788892618747</v>
+        <v>3.660789121033758</v>
       </c>
       <c r="E281" t="n">
-        <v>3.696416973226988</v>
+        <v>3.696417203865015</v>
       </c>
       <c r="F281" t="n">
         <v>19813000</v>
@@ -6052,16 +6052,16 @@
         <v>44823</v>
       </c>
       <c r="B282" t="n">
-        <v>3.990349292755127</v>
+        <v>3.990348815917969</v>
       </c>
       <c r="C282" t="n">
-        <v>4.00816333503313</v>
+        <v>4.008162856067236</v>
       </c>
       <c r="D282" t="n">
-        <v>3.794394827697093</v>
+        <v>3.794394374276022</v>
       </c>
       <c r="E282" t="n">
-        <v>3.830022912253099</v>
+        <v>3.830022454574558</v>
       </c>
       <c r="F282" t="n">
         <v>8945000</v>
@@ -6072,16 +6072,16 @@
         <v>44824</v>
       </c>
       <c r="B283" t="n">
-        <v>3.963628053665161</v>
+        <v>3.963627576828003</v>
       </c>
       <c r="C283" t="n">
-        <v>4.132861669232745</v>
+        <v>4.13286117203624</v>
       </c>
       <c r="D283" t="n">
-        <v>3.919093159918075</v>
+        <v>3.919092688438607</v>
       </c>
       <c r="E283" t="n">
-        <v>3.990349329689632</v>
+        <v>3.990348849637818</v>
       </c>
       <c r="F283" t="n">
         <v>10696200</v>
@@ -6092,16 +6092,16 @@
         <v>44825</v>
       </c>
       <c r="B284" t="n">
-        <v>3.883465051651001</v>
+        <v>3.883464336395264</v>
       </c>
       <c r="C284" t="n">
-        <v>4.034884623864039</v>
+        <v>4.034883880719878</v>
       </c>
       <c r="D284" t="n">
-        <v>3.830022924644094</v>
+        <v>3.830022219231316</v>
       </c>
       <c r="E284" t="n">
-        <v>3.972535263329179</v>
+        <v>3.97253453166851</v>
       </c>
       <c r="F284" t="n">
         <v>18275700</v>
@@ -6112,16 +6112,16 @@
         <v>44826</v>
       </c>
       <c r="B285" t="n">
-        <v>4.052698135375977</v>
+        <v>4.052698612213135</v>
       </c>
       <c r="C285" t="n">
-        <v>4.097233023021737</v>
+        <v>4.097233505098832</v>
       </c>
       <c r="D285" t="n">
-        <v>3.90127858299592</v>
+        <v>3.901279042017177</v>
       </c>
       <c r="E285" t="n">
-        <v>3.936906663000614</v>
+        <v>3.936907126213841</v>
       </c>
       <c r="F285" t="n">
         <v>13589200</v>
@@ -6132,16 +6132,16 @@
         <v>44827</v>
       </c>
       <c r="B286" t="n">
-        <v>3.91018533706665</v>
+        <v>3.910185575485229</v>
       </c>
       <c r="C286" t="n">
-        <v>3.990348728339065</v>
+        <v>3.990348971645505</v>
       </c>
       <c r="D286" t="n">
-        <v>3.847836410272737</v>
+        <v>3.847836644889669</v>
       </c>
       <c r="E286" t="n">
-        <v>3.963627456341523</v>
+        <v>3.963627698018668</v>
       </c>
       <c r="F286" t="n">
         <v>14173200</v>
@@ -6152,16 +6152,16 @@
         <v>44830</v>
       </c>
       <c r="B287" t="n">
-        <v>3.821115255355835</v>
+        <v>3.821115493774414</v>
       </c>
       <c r="C287" t="n">
-        <v>3.936906729692732</v>
+        <v>3.936906975336123</v>
       </c>
       <c r="D287" t="n">
-        <v>3.794394407259765</v>
+        <v>3.794394644011096</v>
       </c>
       <c r="E287" t="n">
-        <v>3.901278649084491</v>
+        <v>3.901278892504866</v>
       </c>
       <c r="F287" t="n">
         <v>9718800</v>
@@ -6172,16 +6172,16 @@
         <v>44831</v>
       </c>
       <c r="B288" t="n">
-        <v>3.73204517364502</v>
+        <v>3.73204493522644</v>
       </c>
       <c r="C288" t="n">
-        <v>3.919092815203188</v>
+        <v>3.919092564835227</v>
       </c>
       <c r="D288" t="n">
-        <v>3.73204517364502</v>
+        <v>3.73204493522644</v>
       </c>
       <c r="E288" t="n">
-        <v>3.838929418901048</v>
+        <v>3.838929173654259</v>
       </c>
       <c r="F288" t="n">
         <v>11052300</v>
@@ -6212,16 +6212,16 @@
         <v>44833</v>
       </c>
       <c r="B290" t="n">
-        <v>3.696417570114136</v>
+        <v>3.696416854858398</v>
       </c>
       <c r="C290" t="n">
-        <v>3.714231613294819</v>
+        <v>3.714230894592069</v>
       </c>
       <c r="D290" t="n">
-        <v>3.616254163440918</v>
+        <v>3.616253463696776</v>
       </c>
       <c r="E290" t="n">
-        <v>3.660789483752771</v>
+        <v>3.660788775391057</v>
       </c>
       <c r="F290" t="n">
         <v>12380300</v>
@@ -6232,16 +6232,16 @@
         <v>44834</v>
       </c>
       <c r="B291" t="n">
-        <v>3.73204517364502</v>
+        <v>3.73204493522644</v>
       </c>
       <c r="C291" t="n">
-        <v>3.794394529071154</v>
+        <v>3.794394286669439</v>
       </c>
       <c r="D291" t="n">
-        <v>3.651881777342879</v>
+        <v>3.651881544045472</v>
       </c>
       <c r="E291" t="n">
-        <v>3.660789010141</v>
+        <v>3.660788776274561</v>
       </c>
       <c r="F291" t="n">
         <v>11827700</v>
@@ -6252,16 +6252,16 @@
         <v>44837</v>
       </c>
       <c r="B292" t="n">
-        <v>3.939894676208496</v>
+        <v>3.939894914627075</v>
       </c>
       <c r="C292" t="n">
-        <v>3.939894676208497</v>
+        <v>3.939894914627075</v>
       </c>
       <c r="D292" t="n">
-        <v>3.796299558626456</v>
+        <v>3.796299788355527</v>
       </c>
       <c r="E292" t="n">
-        <v>3.814248948324211</v>
+        <v>3.814249179139471</v>
       </c>
       <c r="F292" t="n">
         <v>14167700</v>
@@ -6272,16 +6272,16 @@
         <v>44838</v>
       </c>
       <c r="B293" t="n">
-        <v>3.930919647216797</v>
+        <v>3.930920124053955</v>
       </c>
       <c r="C293" t="n">
-        <v>4.056565357581396</v>
+        <v>4.05656584965991</v>
       </c>
       <c r="D293" t="n">
-        <v>3.895020872826911</v>
+        <v>3.895021345309396</v>
       </c>
       <c r="E293" t="n">
-        <v>3.97579290123058</v>
+        <v>3.975793383511054</v>
       </c>
       <c r="F293" t="n">
         <v>11413300</v>
@@ -6292,16 +6292,16 @@
         <v>44839</v>
       </c>
       <c r="B294" t="n">
-        <v>3.975793123245239</v>
+        <v>3.975793838500977</v>
       </c>
       <c r="C294" t="n">
-        <v>3.975793123245239</v>
+        <v>3.975793838500977</v>
       </c>
       <c r="D294" t="n">
-        <v>3.868096794061647</v>
+        <v>3.868097489942528</v>
       </c>
       <c r="E294" t="n">
-        <v>3.921944958653443</v>
+        <v>3.921945664221753</v>
       </c>
       <c r="F294" t="n">
         <v>8368900</v>
@@ -6312,16 +6312,16 @@
         <v>44840</v>
       </c>
       <c r="B295" t="n">
-        <v>4.002717971801758</v>
+        <v>4.0027174949646</v>
       </c>
       <c r="C295" t="n">
-        <v>4.029641843838973</v>
+        <v>4.029641363794418</v>
       </c>
       <c r="D295" t="n">
-        <v>3.975793671817313</v>
+        <v>3.975793198187602</v>
       </c>
       <c r="E295" t="n">
-        <v>3.9937430624912</v>
+        <v>3.993742586723207</v>
       </c>
       <c r="F295" t="n">
         <v>5975200</v>
@@ -6332,16 +6332,16 @@
         <v>44841</v>
       </c>
       <c r="B296" t="n">
-        <v>3.760400533676147</v>
+        <v>3.760400295257568</v>
       </c>
       <c r="C296" t="n">
-        <v>4.002717492746105</v>
+        <v>4.002717238964039</v>
       </c>
       <c r="D296" t="n">
-        <v>3.715526848388416</v>
+        <v>3.715526612814938</v>
       </c>
       <c r="E296" t="n">
-        <v>3.984768104220449</v>
+        <v>3.984767851576418</v>
       </c>
       <c r="F296" t="n">
         <v>16354500</v>
@@ -6352,16 +6352,16 @@
         <v>44844</v>
       </c>
       <c r="B297" t="n">
-        <v>3.661678791046143</v>
+        <v>3.661679029464722</v>
       </c>
       <c r="C297" t="n">
-        <v>3.805273903495892</v>
+        <v>3.80527415126421</v>
       </c>
       <c r="D297" t="n">
-        <v>3.63475492143541</v>
+        <v>3.634755158100927</v>
       </c>
       <c r="E297" t="n">
-        <v>3.805273903495892</v>
+        <v>3.80527415126421</v>
       </c>
       <c r="F297" t="n">
         <v>18862600</v>
@@ -6372,16 +6372,16 @@
         <v>44845</v>
       </c>
       <c r="B298" t="n">
-        <v>3.903996229171753</v>
+        <v>3.903995990753174</v>
       </c>
       <c r="C298" t="n">
-        <v>3.948869921209974</v>
+        <v>3.948869680050941</v>
       </c>
       <c r="D298" t="n">
-        <v>3.634755360784154</v>
+        <v>3.63475513880822</v>
       </c>
       <c r="E298" t="n">
-        <v>3.661679233649292</v>
+        <v>3.661679010029107</v>
       </c>
       <c r="F298" t="n">
         <v>30833900</v>
@@ -6392,16 +6392,16 @@
         <v>44847</v>
       </c>
       <c r="B299" t="n">
-        <v>3.814249038696289</v>
+        <v>3.814249277114868</v>
       </c>
       <c r="C299" t="n">
-        <v>3.903995989311464</v>
+        <v>3.903996233339887</v>
       </c>
       <c r="D299" t="n">
-        <v>3.796299648573254</v>
+        <v>3.796299885869864</v>
       </c>
       <c r="E299" t="n">
-        <v>3.895021508223556</v>
+        <v>3.895021751691007</v>
       </c>
       <c r="F299" t="n">
         <v>15027200</v>
@@ -6412,16 +6412,16 @@
         <v>44848</v>
       </c>
       <c r="B300" t="n">
-        <v>3.688603401184082</v>
+        <v>3.688602924346924</v>
       </c>
       <c r="C300" t="n">
-        <v>3.832198525802385</v>
+        <v>3.832198030402241</v>
       </c>
       <c r="D300" t="n">
-        <v>3.679628491921824</v>
+        <v>3.67962801624488</v>
       </c>
       <c r="E300" t="n">
-        <v>3.823224044487355</v>
+        <v>3.82322355024737</v>
       </c>
       <c r="F300" t="n">
         <v>10535000</v>
@@ -6432,16 +6432,16 @@
         <v>44851</v>
       </c>
       <c r="B301" t="n">
-        <v>3.679628133773804</v>
+        <v>3.679628372192383</v>
       </c>
       <c r="C301" t="n">
-        <v>3.769375077924933</v>
+        <v>3.769375322158595</v>
       </c>
       <c r="D301" t="n">
-        <v>3.670653653332284</v>
+        <v>3.670653891169369</v>
       </c>
       <c r="E301" t="n">
-        <v>3.724501819822962</v>
+        <v>3.724502061149096</v>
       </c>
       <c r="F301" t="n">
         <v>8129100</v>
@@ -6452,16 +6452,16 @@
         <v>44852</v>
       </c>
       <c r="B302" t="n">
-        <v>3.715527296066284</v>
+        <v>3.715527057647705</v>
       </c>
       <c r="C302" t="n">
-        <v>3.787324858819684</v>
+        <v>3.787324615793987</v>
       </c>
       <c r="D302" t="n">
-        <v>3.661679124001235</v>
+        <v>3.661678889037994</v>
       </c>
       <c r="E302" t="n">
-        <v>3.724502205384074</v>
+        <v>3.724501966389592</v>
       </c>
       <c r="F302" t="n">
         <v>13196400</v>
@@ -6472,16 +6472,16 @@
         <v>44853</v>
       </c>
       <c r="B303" t="n">
-        <v>3.733476161956787</v>
+        <v>3.733476400375366</v>
       </c>
       <c r="C303" t="n">
-        <v>3.769374938287358</v>
+        <v>3.769375178998422</v>
       </c>
       <c r="D303" t="n">
-        <v>3.670653517351873</v>
+        <v>3.670653751758618</v>
       </c>
       <c r="E303" t="n">
-        <v>3.715526773791502</v>
+        <v>3.715527011063839</v>
       </c>
       <c r="F303" t="n">
         <v>12625300</v>
@@ -6492,16 +6492,16 @@
         <v>44854</v>
       </c>
       <c r="B304" t="n">
-        <v>3.769375324249268</v>
+        <v>3.769375085830688</v>
       </c>
       <c r="C304" t="n">
-        <v>3.796299623227672</v>
+        <v>3.796299383106091</v>
       </c>
       <c r="D304" t="n">
-        <v>3.706552673211682</v>
+        <v>3.706552438766729</v>
       </c>
       <c r="E304" t="n">
-        <v>3.760400843221276</v>
+        <v>3.760400605370346</v>
       </c>
       <c r="F304" t="n">
         <v>13428400</v>
@@ -6512,16 +6512,16 @@
         <v>44855</v>
       </c>
       <c r="B305" t="n">
-        <v>3.83219838142395</v>
+        <v>3.832198619842529</v>
       </c>
       <c r="C305" t="n">
-        <v>3.85912268024912</v>
+        <v>3.859122920342783</v>
       </c>
       <c r="D305" t="n">
-        <v>3.733476522994609</v>
+        <v>3.73347675527125</v>
       </c>
       <c r="E305" t="n">
-        <v>3.760400821819779</v>
+        <v>3.760401055771503</v>
       </c>
       <c r="F305" t="n">
         <v>14614900</v>
@@ -6532,16 +6532,16 @@
         <v>44858</v>
       </c>
       <c r="B306" t="n">
-        <v>3.706552743911743</v>
+        <v>3.706552267074585</v>
       </c>
       <c r="C306" t="n">
-        <v>3.778350305294026</v>
+        <v>3.778349819220322</v>
       </c>
       <c r="D306" t="n">
-        <v>3.697577834765347</v>
+        <v>3.697577359082784</v>
       </c>
       <c r="E306" t="n">
-        <v>3.76937539614763</v>
+        <v>3.769374911228521</v>
       </c>
       <c r="F306" t="n">
         <v>9021900</v>
@@ -6552,16 +6552,16 @@
         <v>44859</v>
       </c>
       <c r="B307" t="n">
-        <v>3.670653820037842</v>
+        <v>3.670654058456421</v>
       </c>
       <c r="C307" t="n">
-        <v>3.769375249114001</v>
+        <v>3.769375493944795</v>
       </c>
       <c r="D307" t="n">
-        <v>3.661678911241534</v>
+        <v>3.661679149077169</v>
       </c>
       <c r="E307" t="n">
-        <v>3.706552599328664</v>
+        <v>3.706552840078963</v>
       </c>
       <c r="F307" t="n">
         <v>12220200</v>
@@ -6572,16 +6572,16 @@
         <v>44860</v>
       </c>
       <c r="B308" t="n">
-        <v>3.562957525253296</v>
+        <v>3.562957286834717</v>
       </c>
       <c r="C308" t="n">
-        <v>3.670654084869496</v>
+        <v>3.670653839244302</v>
       </c>
       <c r="D308" t="n">
-        <v>3.545008134312866</v>
+        <v>3.545007897095387</v>
       </c>
       <c r="E308" t="n">
-        <v>3.661679175425662</v>
+        <v>3.661678930401033</v>
       </c>
       <c r="F308" t="n">
         <v>15630800</v>
@@ -6592,16 +6592,16 @@
         <v>44861</v>
       </c>
       <c r="B309" t="n">
-        <v>3.706552743911743</v>
+        <v>3.706552267074585</v>
       </c>
       <c r="C309" t="n">
-        <v>3.760400914948455</v>
+        <v>3.760400431183887</v>
       </c>
       <c r="D309" t="n">
-        <v>3.580906797519137</v>
+        <v>3.580906336845962</v>
       </c>
       <c r="E309" t="n">
-        <v>3.580906797519137</v>
+        <v>3.580906336845962</v>
       </c>
       <c r="F309" t="n">
         <v>15175200</v>
@@ -6612,16 +6612,16 @@
         <v>44862</v>
       </c>
       <c r="B310" t="n">
-        <v>3.724502325057983</v>
+        <v>3.724502086639404</v>
       </c>
       <c r="C310" t="n">
-        <v>3.733476806716907</v>
+        <v>3.73347656772384</v>
       </c>
       <c r="D310" t="n">
-        <v>3.643729850391451</v>
+        <v>3.643729617143404</v>
       </c>
       <c r="E310" t="n">
-        <v>3.688603542527801</v>
+        <v>3.68860330640723</v>
       </c>
       <c r="F310" t="n">
         <v>9985100</v>
@@ -6632,16 +6632,16 @@
         <v>44865</v>
       </c>
       <c r="B311" t="n">
-        <v>3.850147724151611</v>
+        <v>3.850147485733032</v>
       </c>
       <c r="C311" t="n">
-        <v>3.868097113832732</v>
+        <v>3.868096874302645</v>
       </c>
       <c r="D311" t="n">
-        <v>3.545007885598959</v>
+        <v>3.54500766607602</v>
       </c>
       <c r="E311" t="n">
-        <v>3.58988135980176</v>
+        <v>3.589881137500053</v>
       </c>
       <c r="F311" t="n">
         <v>19491700</v>
@@ -6672,16 +6672,16 @@
         <v>44868</v>
       </c>
       <c r="B313" t="n">
-        <v>4.21811056137085</v>
+        <v>4.218111038208008</v>
       </c>
       <c r="C313" t="n">
-        <v>4.254009341880177</v>
+        <v>4.25400982277552</v>
       </c>
       <c r="D313" t="n">
-        <v>3.895021536786911</v>
+        <v>3.895021977100405</v>
       </c>
       <c r="E313" t="n">
-        <v>3.975793578959285</v>
+        <v>3.975794028403671</v>
       </c>
       <c r="F313" t="n">
         <v>15015300</v>
@@ -6712,16 +6712,16 @@
         <v>44872</v>
       </c>
       <c r="B315" t="n">
-        <v>4.011692523956299</v>
+        <v>4.011692047119141</v>
       </c>
       <c r="C315" t="n">
-        <v>4.379655681184977</v>
+        <v>4.37965516061104</v>
       </c>
       <c r="D315" t="n">
-        <v>4.011692523956299</v>
+        <v>4.011692047119141</v>
       </c>
       <c r="E315" t="n">
-        <v>4.316832598744169</v>
+        <v>4.3168320856375</v>
       </c>
       <c r="F315" t="n">
         <v>17217400</v>
@@ -6752,16 +6752,16 @@
         <v>44874</v>
       </c>
       <c r="B317" t="n">
-        <v>4.011692523956299</v>
+        <v>4.011692047119141</v>
       </c>
       <c r="C317" t="n">
-        <v>4.173237470819165</v>
+        <v>4.173236974780477</v>
       </c>
       <c r="D317" t="n">
-        <v>3.98476865144398</v>
+        <v>3.984768177807042</v>
       </c>
       <c r="E317" t="n">
-        <v>4.065541124875413</v>
+        <v>4.06554064163771</v>
       </c>
       <c r="F317" t="n">
         <v>11339500</v>
@@ -6772,16 +6772,16 @@
         <v>44875</v>
       </c>
       <c r="B318" t="n">
-        <v>3.688603401184082</v>
+        <v>3.688602924346924</v>
       </c>
       <c r="C318" t="n">
-        <v>3.975793650420687</v>
+        <v>3.975793136457558</v>
       </c>
       <c r="D318" t="n">
-        <v>3.670654010606794</v>
+        <v>3.670653536090009</v>
       </c>
       <c r="E318" t="n">
-        <v>3.921945478688824</v>
+        <v>3.921944971686814</v>
       </c>
       <c r="F318" t="n">
         <v>22566600</v>
@@ -6792,16 +6792,16 @@
         <v>44876</v>
       </c>
       <c r="B319" t="n">
-        <v>3.715527296066284</v>
+        <v>3.715527057647705</v>
       </c>
       <c r="C319" t="n">
-        <v>3.751426077442984</v>
+        <v>3.751425836720846</v>
       </c>
       <c r="D319" t="n">
-        <v>3.437311526423245</v>
+        <v>3.437311305857262</v>
       </c>
       <c r="E319" t="n">
-        <v>3.634755251942325</v>
+        <v>3.634755018706739</v>
       </c>
       <c r="F319" t="n">
         <v>24235200</v>
@@ -6852,16 +6852,16 @@
         <v>44882</v>
       </c>
       <c r="B322" t="n">
-        <v>3.509108781814575</v>
+        <v>3.509109258651733</v>
       </c>
       <c r="C322" t="n">
-        <v>3.571931639890434</v>
+        <v>3.57193212526431</v>
       </c>
       <c r="D322" t="n">
-        <v>3.356538769656764</v>
+        <v>3.356539225761863</v>
       </c>
       <c r="E322" t="n">
-        <v>3.562956945879597</v>
+        <v>3.562957430033942</v>
       </c>
       <c r="F322" t="n">
         <v>25106400</v>
@@ -6872,16 +6872,16 @@
         <v>44883</v>
       </c>
       <c r="B323" t="n">
-        <v>3.652704238891602</v>
+        <v>3.652704477310181</v>
       </c>
       <c r="C323" t="n">
-        <v>3.841173034261142</v>
+        <v>3.841173284981419</v>
       </c>
       <c r="D323" t="n">
-        <v>3.536032998339565</v>
+        <v>3.536033229142802</v>
       </c>
       <c r="E323" t="n">
-        <v>3.580906470100505</v>
+        <v>3.580906703832715</v>
       </c>
       <c r="F323" t="n">
         <v>23150300</v>
@@ -6932,16 +6932,16 @@
         <v>44888</v>
       </c>
       <c r="B326" t="n">
-        <v>3.589881420135498</v>
+        <v>3.589881181716919</v>
       </c>
       <c r="C326" t="n">
-        <v>3.643729590083865</v>
+        <v>3.643729348089011</v>
       </c>
       <c r="D326" t="n">
-        <v>3.545007945178526</v>
+        <v>3.545007709740176</v>
       </c>
       <c r="E326" t="n">
-        <v>3.571932030152709</v>
+        <v>3.571931792926222</v>
       </c>
       <c r="F326" t="n">
         <v>6531500</v>
@@ -6952,16 +6952,16 @@
         <v>44889</v>
       </c>
       <c r="B327" t="n">
-        <v>3.724502325057983</v>
+        <v>3.724502086639404</v>
       </c>
       <c r="C327" t="n">
-        <v>3.742451716323075</v>
+        <v>3.742451476755492</v>
       </c>
       <c r="D327" t="n">
-        <v>3.598856586202345</v>
+        <v>3.598856355826795</v>
       </c>
       <c r="E327" t="n">
-        <v>3.634755368732528</v>
+        <v>3.634755136058969</v>
       </c>
       <c r="F327" t="n">
         <v>5511600</v>
@@ -6972,16 +6972,16 @@
         <v>44890</v>
       </c>
       <c r="B328" t="n">
-        <v>3.63475489616394</v>
+        <v>3.634754657745361</v>
       </c>
       <c r="C328" t="n">
-        <v>3.76040061868389</v>
+        <v>3.760400372023689</v>
       </c>
       <c r="D328" t="n">
-        <v>3.580906515396082</v>
+        <v>3.58090628050964</v>
       </c>
       <c r="E328" t="n">
-        <v>3.733476321313164</v>
+        <v>3.733476076419039</v>
       </c>
       <c r="F328" t="n">
         <v>8739900</v>
@@ -7012,16 +7012,16 @@
         <v>44894</v>
       </c>
       <c r="B330" t="n">
-        <v>3.589881420135498</v>
+        <v>3.589881181716919</v>
       </c>
       <c r="C330" t="n">
-        <v>3.715527150015021</v>
+        <v>3.715526903251799</v>
       </c>
       <c r="D330" t="n">
-        <v>3.518083860204342</v>
+        <v>3.51808362655413</v>
       </c>
       <c r="E330" t="n">
-        <v>3.616805719083288</v>
+        <v>3.616805478876557</v>
       </c>
       <c r="F330" t="n">
         <v>13237500</v>
@@ -7032,16 +7032,16 @@
         <v>44895</v>
       </c>
       <c r="B331" t="n">
-        <v>3.63475489616394</v>
+        <v>3.634754657745361</v>
       </c>
       <c r="C331" t="n">
-        <v>3.661678765587478</v>
+        <v>3.661678525402851</v>
       </c>
       <c r="D331" t="n">
-        <v>3.518083654136107</v>
+        <v>3.518083423370476</v>
       </c>
       <c r="E331" t="n">
-        <v>3.571931820930371</v>
+        <v>3.571931586632617</v>
       </c>
       <c r="F331" t="n">
         <v>16877200</v>
@@ -7052,16 +7052,16 @@
         <v>44896</v>
       </c>
       <c r="B332" t="n">
-        <v>3.446286201477051</v>
+        <v>3.446285724639893</v>
       </c>
       <c r="C332" t="n">
-        <v>3.589881540112033</v>
+        <v>3.589881043406649</v>
       </c>
       <c r="D332" t="n">
-        <v>3.428336810894379</v>
+        <v>3.428336336540746</v>
       </c>
       <c r="E332" t="n">
-        <v>3.589881540112033</v>
+        <v>3.589881043406649</v>
       </c>
       <c r="F332" t="n">
         <v>22625600</v>
@@ -7072,16 +7072,16 @@
         <v>44897</v>
       </c>
       <c r="B333" t="n">
-        <v>3.500134468078613</v>
+        <v>3.500134706497192</v>
       </c>
       <c r="C333" t="n">
-        <v>3.62578019788121</v>
+        <v>3.625780444858396</v>
       </c>
       <c r="D333" t="n">
-        <v>3.455260779175508</v>
+        <v>3.455261014537427</v>
       </c>
       <c r="E333" t="n">
-        <v>3.473210169147307</v>
+        <v>3.473210405731884</v>
       </c>
       <c r="F333" t="n">
         <v>16610700</v>
@@ -7092,16 +7092,16 @@
         <v>44900</v>
       </c>
       <c r="B334" t="n">
-        <v>3.347564458847046</v>
+        <v>3.347564220428467</v>
       </c>
       <c r="C334" t="n">
-        <v>3.545007963660719</v>
+        <v>3.545007711179917</v>
       </c>
       <c r="D334" t="n">
-        <v>3.329615068770676</v>
+        <v>3.32961483163048</v>
       </c>
       <c r="E334" t="n">
-        <v>3.545007963660719</v>
+        <v>3.545007711179917</v>
       </c>
       <c r="F334" t="n">
         <v>14607600</v>
@@ -7112,16 +7112,16 @@
         <v>44901</v>
       </c>
       <c r="B335" t="n">
-        <v>3.302690744400024</v>
+        <v>3.302690982818604</v>
       </c>
       <c r="C335" t="n">
-        <v>3.401412382668387</v>
+        <v>3.401412628213602</v>
       </c>
       <c r="D335" t="n">
-        <v>3.248842364098234</v>
+        <v>3.248842598629542</v>
       </c>
       <c r="E335" t="n">
-        <v>3.383462993892321</v>
+        <v>3.383463238141784</v>
       </c>
       <c r="F335" t="n">
         <v>13327400</v>
@@ -7132,16 +7132,16 @@
         <v>44902</v>
       </c>
       <c r="B336" t="n">
-        <v>3.230893611907959</v>
+        <v>3.230893135070801</v>
       </c>
       <c r="C336" t="n">
-        <v>3.320640787444846</v>
+        <v>3.320640297362192</v>
       </c>
       <c r="D336" t="n">
-        <v>3.212944219595309</v>
+        <v>3.212943745407243</v>
       </c>
       <c r="E336" t="n">
-        <v>3.302691395132195</v>
+        <v>3.302690907698634</v>
       </c>
       <c r="F336" t="n">
         <v>13628700</v>
@@ -7152,16 +7152,16 @@
         <v>44903</v>
       </c>
       <c r="B337" t="n">
-        <v>3.073575973510742</v>
+        <v>3.073575496673584</v>
       </c>
       <c r="C337" t="n">
-        <v>3.266824802334561</v>
+        <v>3.266824295516617</v>
       </c>
       <c r="D337" t="n">
-        <v>3.064373658776298</v>
+        <v>3.064373183366795</v>
       </c>
       <c r="E337" t="n">
-        <v>3.22081322866234</v>
+        <v>3.22081272898267</v>
       </c>
       <c r="F337" t="n">
         <v>19978800</v>
@@ -7172,16 +7172,16 @@
         <v>44904</v>
       </c>
       <c r="B338" t="n">
-        <v>3.082778215408325</v>
+        <v>3.082777976989746</v>
       </c>
       <c r="C338" t="n">
-        <v>3.119587692876894</v>
+        <v>3.119587451611511</v>
       </c>
       <c r="D338" t="n">
-        <v>2.990755070238115</v>
+        <v>2.990754838936502</v>
       </c>
       <c r="E338" t="n">
-        <v>3.101182844442367</v>
+        <v>3.101182604600395</v>
       </c>
       <c r="F338" t="n">
         <v>12963000</v>
@@ -7212,16 +7212,16 @@
         <v>44908</v>
       </c>
       <c r="B340" t="n">
-        <v>2.999957084655762</v>
+        <v>2.999957323074341</v>
       </c>
       <c r="C340" t="n">
-        <v>3.128789694406827</v>
+        <v>3.128789943064248</v>
       </c>
       <c r="D340" t="n">
-        <v>2.99075477105929</v>
+        <v>2.990755008746524</v>
       </c>
       <c r="E340" t="n">
-        <v>3.055170966234591</v>
+        <v>3.055171209041239</v>
       </c>
       <c r="F340" t="n">
         <v>10848100</v>
@@ -7232,16 +7232,16 @@
         <v>44909</v>
       </c>
       <c r="B341" t="n">
-        <v>3.073575973510742</v>
+        <v>3.073575496673584</v>
       </c>
       <c r="C341" t="n">
-        <v>3.101182917714075</v>
+        <v>3.101182436593952</v>
       </c>
       <c r="D341" t="n">
-        <v>2.935541252494079</v>
+        <v>2.935540797071743</v>
       </c>
       <c r="E341" t="n">
-        <v>2.9815528261663</v>
+        <v>2.98155236360569</v>
       </c>
       <c r="F341" t="n">
         <v>15438000</v>
@@ -7272,16 +7272,16 @@
         <v>44911</v>
       </c>
       <c r="B343" t="n">
-        <v>2.999957084655762</v>
+        <v>2.999957323074341</v>
       </c>
       <c r="C343" t="n">
-        <v>3.064373279831063</v>
+        <v>3.064373523369055</v>
       </c>
       <c r="D343" t="n">
-        <v>2.972350143866347</v>
+        <v>2.972350380090892</v>
       </c>
       <c r="E343" t="n">
-        <v>3.036766339041648</v>
+        <v>3.036766580385606</v>
       </c>
       <c r="F343" t="n">
         <v>7695800</v>
@@ -7292,16 +7292,16 @@
         <v>44914</v>
       </c>
       <c r="B344" t="n">
-        <v>3.073575973510742</v>
+        <v>3.073575496673584</v>
       </c>
       <c r="C344" t="n">
-        <v>3.091980602979631</v>
+        <v>3.091980123287163</v>
       </c>
       <c r="D344" t="n">
-        <v>2.990755140900744</v>
+        <v>2.990754676912479</v>
       </c>
       <c r="E344" t="n">
-        <v>3.009159770369632</v>
+        <v>3.009159303526058</v>
       </c>
       <c r="F344" t="n">
         <v>6693400</v>
@@ -7332,16 +7332,16 @@
         <v>44916</v>
       </c>
       <c r="B346" t="n">
-        <v>3.331240892410278</v>
+        <v>3.33124041557312</v>
       </c>
       <c r="C346" t="n">
-        <v>3.377252683921307</v>
+        <v>3.377252200497974</v>
       </c>
       <c r="D346" t="n">
-        <v>3.239217748189187</v>
+        <v>3.239217284524313</v>
       </c>
       <c r="E346" t="n">
-        <v>3.266824691455514</v>
+        <v>3.266824223838955</v>
       </c>
       <c r="F346" t="n">
         <v>14610300</v>
@@ -7352,16 +7352,16 @@
         <v>44917</v>
       </c>
       <c r="B347" t="n">
-        <v>3.340443134307861</v>
+        <v>3.340442895889282</v>
       </c>
       <c r="C347" t="n">
-        <v>3.358847761543679</v>
+        <v>3.3588475218115</v>
       </c>
       <c r="D347" t="n">
-        <v>3.257622092346219</v>
+        <v>3.257621859838854</v>
       </c>
       <c r="E347" t="n">
-        <v>3.33124060128949</v>
+        <v>3.331240363527726</v>
       </c>
       <c r="F347" t="n">
         <v>7727000</v>
@@ -7392,16 +7392,16 @@
         <v>44921</v>
       </c>
       <c r="B349" t="n">
-        <v>3.340443134307861</v>
+        <v>3.340442895889282</v>
       </c>
       <c r="C349" t="n">
-        <v>3.441668584104859</v>
+        <v>3.441668338461481</v>
       </c>
       <c r="D349" t="n">
-        <v>3.285229033199945</v>
+        <v>3.28522879872218</v>
       </c>
       <c r="E349" t="n">
-        <v>3.441668584104859</v>
+        <v>3.441668338461481</v>
       </c>
       <c r="F349" t="n">
         <v>5290600</v>
@@ -7432,16 +7432,16 @@
         <v>44923</v>
       </c>
       <c r="B351" t="n">
-        <v>3.450871229171753</v>
+        <v>3.450870990753174</v>
       </c>
       <c r="C351" t="n">
-        <v>3.542894374189473</v>
+        <v>3.542894129413071</v>
       </c>
       <c r="D351" t="n">
-        <v>3.358848084154033</v>
+        <v>3.358847852093277</v>
       </c>
       <c r="E351" t="n">
-        <v>3.395657342161121</v>
+        <v>3.395657107557235</v>
       </c>
       <c r="F351" t="n">
         <v>9716800</v>
@@ -7452,16 +7452,16 @@
         <v>44924</v>
       </c>
       <c r="B352" t="n">
-        <v>3.44166898727417</v>
+        <v>3.441668748855591</v>
       </c>
       <c r="C352" t="n">
-        <v>3.59810855650497</v>
+        <v>3.598108307249177</v>
       </c>
       <c r="D352" t="n">
-        <v>3.404859728490568</v>
+        <v>3.404859492621917</v>
       </c>
       <c r="E352" t="n">
-        <v>3.524489819537276</v>
+        <v>3.524489575381356</v>
       </c>
       <c r="F352" t="n">
         <v>7177700</v>
@@ -7492,16 +7492,16 @@
         <v>44929</v>
       </c>
       <c r="B354" t="n">
-        <v>3.073575973510742</v>
+        <v>3.073575496673584</v>
       </c>
       <c r="C354" t="n">
-        <v>3.28522943180345</v>
+        <v>3.285228922130196</v>
       </c>
       <c r="D354" t="n">
-        <v>3.064373658776298</v>
+        <v>3.064373183366795</v>
       </c>
       <c r="E354" t="n">
-        <v>3.257622487600117</v>
+        <v>3.257621982209828</v>
       </c>
       <c r="F354" t="n">
         <v>9560100</v>
@@ -7512,16 +7512,16 @@
         <v>44930</v>
       </c>
       <c r="B355" t="n">
-        <v>3.055171012878418</v>
+        <v>3.055171251296997</v>
       </c>
       <c r="C355" t="n">
-        <v>3.147194369648533</v>
+        <v>3.147194615248405</v>
       </c>
       <c r="D355" t="n">
-        <v>3.036766385404488</v>
+        <v>3.036766622386812</v>
       </c>
       <c r="E355" t="n">
-        <v>3.110385114700673</v>
+        <v>3.110385357428035</v>
       </c>
       <c r="F355" t="n">
         <v>10680900</v>
@@ -7532,16 +7532,16 @@
         <v>44931</v>
       </c>
       <c r="B356" t="n">
-        <v>2.972350358963013</v>
+        <v>2.972350120544434</v>
       </c>
       <c r="C356" t="n">
-        <v>3.11958760656197</v>
+        <v>3.119587356333176</v>
       </c>
       <c r="D356" t="n">
-        <v>2.935541101913393</v>
+        <v>2.935540866447363</v>
       </c>
       <c r="E356" t="n">
-        <v>3.082778130111872</v>
+        <v>3.082777882835645</v>
       </c>
       <c r="F356" t="n">
         <v>35445300</v>
@@ -7572,16 +7572,16 @@
         <v>44935</v>
       </c>
       <c r="B358" t="n">
-        <v>2.972350358963013</v>
+        <v>2.972350120544434</v>
       </c>
       <c r="C358" t="n">
-        <v>3.027564244537442</v>
+        <v>3.027564001690039</v>
       </c>
       <c r="D358" t="n">
-        <v>2.907934159126178</v>
+        <v>2.90793392587456</v>
       </c>
       <c r="E358" t="n">
-        <v>2.944743416175798</v>
+        <v>2.944743179971631</v>
       </c>
       <c r="F358" t="n">
         <v>15633700</v>
@@ -7592,16 +7592,16 @@
         <v>44936</v>
       </c>
       <c r="B359" t="n">
-        <v>3.082778215408325</v>
+        <v>3.082777976989746</v>
       </c>
       <c r="C359" t="n">
-        <v>3.082778215408325</v>
+        <v>3.082777976989746</v>
       </c>
       <c r="D359" t="n">
-        <v>2.953945812170032</v>
+        <v>2.953945583715205</v>
       </c>
       <c r="E359" t="n">
-        <v>2.963148126687053</v>
+        <v>2.963147897520529</v>
       </c>
       <c r="F359" t="n">
         <v>12594800</v>
@@ -7612,16 +7612,16 @@
         <v>44937</v>
       </c>
       <c r="B360" t="n">
-        <v>3.294431447982788</v>
+        <v>3.294431686401367</v>
       </c>
       <c r="C360" t="n">
-        <v>3.294431447982788</v>
+        <v>3.294431686401367</v>
       </c>
       <c r="D360" t="n">
-        <v>3.091980322771489</v>
+        <v>3.091980546538645</v>
       </c>
       <c r="E360" t="n">
-        <v>3.091980322771489</v>
+        <v>3.091980546538645</v>
       </c>
       <c r="F360" t="n">
         <v>21444400</v>
@@ -7652,16 +7652,16 @@
         <v>44939</v>
       </c>
       <c r="B362" t="n">
-        <v>3.073575973510742</v>
+        <v>3.073575496673584</v>
       </c>
       <c r="C362" t="n">
-        <v>3.22081322866234</v>
+        <v>3.22081272898267</v>
       </c>
       <c r="D362" t="n">
-        <v>3.055171344041854</v>
+        <v>3.055170870060005</v>
       </c>
       <c r="E362" t="n">
-        <v>3.184003969724563</v>
+        <v>3.184003475755512</v>
       </c>
       <c r="F362" t="n">
         <v>14486700</v>
@@ -7692,16 +7692,16 @@
         <v>44943</v>
       </c>
       <c r="B364" t="n">
-        <v>3.091980457305908</v>
+        <v>3.091980218887329</v>
       </c>
       <c r="C364" t="n">
-        <v>3.128789933909955</v>
+        <v>3.128789692653045</v>
       </c>
       <c r="D364" t="n">
-        <v>3.027564257199665</v>
+        <v>3.027564023748135</v>
       </c>
       <c r="E364" t="n">
-        <v>3.055171200102341</v>
+        <v>3.055170964522075</v>
       </c>
       <c r="F364" t="n">
         <v>11859400</v>
@@ -7712,16 +7712,16 @@
         <v>44944</v>
       </c>
       <c r="B365" t="n">
-        <v>3.082778215408325</v>
+        <v>3.082777976989746</v>
       </c>
       <c r="C365" t="n">
-        <v>3.174801579979019</v>
+        <v>3.174801334443457</v>
       </c>
       <c r="D365" t="n">
-        <v>3.064373586374283</v>
+        <v>3.064373349379097</v>
       </c>
       <c r="E365" t="n">
-        <v>3.128790007393915</v>
+        <v>3.128789765416836</v>
       </c>
       <c r="F365" t="n">
         <v>13324700</v>
@@ -7812,16 +7812,16 @@
         <v>44951</v>
       </c>
       <c r="B370" t="n">
-        <v>3.248419761657715</v>
+        <v>3.248420000076294</v>
       </c>
       <c r="C370" t="n">
-        <v>3.248419761657715</v>
+        <v>3.248420000076294</v>
       </c>
       <c r="D370" t="n">
-        <v>3.147194312392662</v>
+        <v>3.147194543381774</v>
       </c>
       <c r="E370" t="n">
-        <v>3.193205880240413</v>
+        <v>3.193206114606555</v>
       </c>
       <c r="F370" t="n">
         <v>7649000</v>
@@ -7832,16 +7832,16 @@
         <v>44952</v>
       </c>
       <c r="B371" t="n">
-        <v>3.202408313751221</v>
+        <v>3.2024085521698</v>
       </c>
       <c r="C371" t="n">
-        <v>3.2852291389791</v>
+        <v>3.28522938356367</v>
       </c>
       <c r="D371" t="n">
-        <v>3.184003685922803</v>
+        <v>3.184003922971162</v>
       </c>
       <c r="E371" t="n">
-        <v>3.257622197236473</v>
+        <v>3.257622439765714</v>
       </c>
       <c r="F371" t="n">
         <v>8271800</v>
@@ -7852,16 +7852,16 @@
         <v>44953</v>
       </c>
       <c r="B372" t="n">
-        <v>3.147194147109985</v>
+        <v>3.147194385528564</v>
       </c>
       <c r="C372" t="n">
-        <v>3.22081265180013</v>
+        <v>3.220812895795746</v>
       </c>
       <c r="D372" t="n">
-        <v>3.128789520937449</v>
+        <v>3.128789757961769</v>
       </c>
       <c r="E372" t="n">
-        <v>3.211610338713862</v>
+        <v>3.211610582012349</v>
       </c>
       <c r="F372" t="n">
         <v>8557200</v>
@@ -7872,16 +7872,16 @@
         <v>44956</v>
       </c>
       <c r="B373" t="n">
-        <v>2.990754842758179</v>
+        <v>2.990755081176758</v>
       </c>
       <c r="C373" t="n">
-        <v>3.156396710866147</v>
+        <v>3.156396962489453</v>
       </c>
       <c r="D373" t="n">
-        <v>2.963147901306928</v>
+        <v>2.963148137524723</v>
       </c>
       <c r="E373" t="n">
-        <v>3.128789769414897</v>
+        <v>3.128790018837418</v>
       </c>
       <c r="F373" t="n">
         <v>24955900</v>
@@ -7932,16 +7932,16 @@
         <v>44959</v>
       </c>
       <c r="B376" t="n">
-        <v>2.806708574295044</v>
+        <v>2.806708335876465</v>
       </c>
       <c r="C376" t="n">
-        <v>2.972350455816205</v>
+        <v>2.972350203327015</v>
       </c>
       <c r="D376" t="n">
-        <v>2.797506259732784</v>
+        <v>2.797506022095904</v>
       </c>
       <c r="E376" t="n">
-        <v>2.898731939318127</v>
+        <v>2.898731693082534</v>
       </c>
       <c r="F376" t="n">
         <v>50857000</v>
@@ -8032,16 +8032,16 @@
         <v>44966</v>
       </c>
       <c r="B381" t="n">
-        <v>3.018362045288086</v>
+        <v>3.018361806869507</v>
       </c>
       <c r="C381" t="n">
-        <v>3.091980562192519</v>
+        <v>3.091980317958858</v>
       </c>
       <c r="D381" t="n">
-        <v>2.935541213770599</v>
+        <v>2.935540981893987</v>
       </c>
       <c r="E381" t="n">
-        <v>3.036766674514194</v>
+        <v>3.036766434641845</v>
       </c>
       <c r="F381" t="n">
         <v>43678900</v>
@@ -8132,16 +8132,16 @@
         <v>44973</v>
       </c>
       <c r="B386" t="n">
-        <v>2.834315538406372</v>
+        <v>2.834315299987793</v>
       </c>
       <c r="C386" t="n">
-        <v>2.871124796920665</v>
+        <v>2.871124555405743</v>
       </c>
       <c r="D386" t="n">
-        <v>2.760697021377787</v>
+        <v>2.760696789151893</v>
       </c>
       <c r="E386" t="n">
-        <v>2.825113223777799</v>
+        <v>2.825112986133305</v>
       </c>
       <c r="F386" t="n">
         <v>21149000</v>
@@ -8152,16 +8152,16 @@
         <v>44974</v>
       </c>
       <c r="B387" t="n">
-        <v>2.78830361366272</v>
+        <v>2.788303852081299</v>
       </c>
       <c r="C387" t="n">
-        <v>2.8711244348763</v>
+        <v>2.871124680376612</v>
       </c>
       <c r="D387" t="n">
-        <v>2.769898986726369</v>
+        <v>2.769899223571229</v>
       </c>
       <c r="E387" t="n">
-        <v>2.825112867535422</v>
+        <v>2.825113109101438</v>
       </c>
       <c r="F387" t="n">
         <v>27974700</v>
@@ -8172,16 +8172,16 @@
         <v>44979</v>
       </c>
       <c r="B388" t="n">
-        <v>2.834315538406372</v>
+        <v>2.834315299987793</v>
       </c>
       <c r="C388" t="n">
-        <v>2.843517853034945</v>
+        <v>2.84351761384228</v>
       </c>
       <c r="D388" t="n">
-        <v>2.714685448234921</v>
+        <v>2.714685219879454</v>
       </c>
       <c r="E388" t="n">
-        <v>2.76989933600636</v>
+        <v>2.76989910300638</v>
       </c>
       <c r="F388" t="n">
         <v>20601900</v>
@@ -8212,16 +8212,16 @@
         <v>44981</v>
       </c>
       <c r="B390" t="n">
-        <v>2.65947151184082</v>
+        <v>2.659471273422241</v>
       </c>
       <c r="C390" t="n">
-        <v>2.806708543206081</v>
+        <v>2.806708291587871</v>
       </c>
       <c r="D390" t="n">
-        <v>2.650269197380491</v>
+        <v>2.65026895978689</v>
       </c>
       <c r="E390" t="n">
-        <v>2.797506228745752</v>
+        <v>2.797505977952519</v>
       </c>
       <c r="F390" t="n">
         <v>27929600</v>
@@ -8252,16 +8252,16 @@
         <v>44985</v>
       </c>
       <c r="B392" t="n">
-        <v>2.834315538406372</v>
+        <v>2.834315299987793</v>
       </c>
       <c r="C392" t="n">
-        <v>2.889529645578298</v>
+        <v>2.889529402515187</v>
       </c>
       <c r="D392" t="n">
-        <v>2.79750627989208</v>
+        <v>2.797506044569843</v>
       </c>
       <c r="E392" t="n">
-        <v>2.825113223777799</v>
+        <v>2.825112986133305</v>
       </c>
       <c r="F392" t="n">
         <v>28842300</v>
@@ -8372,16 +8372,16 @@
         <v>44993</v>
       </c>
       <c r="B398" t="n">
-        <v>2.705482959747314</v>
+        <v>2.705482721328735</v>
       </c>
       <c r="C398" t="n">
-        <v>2.733089901858964</v>
+        <v>2.733089661007544</v>
       </c>
       <c r="D398" t="n">
-        <v>2.659471389561232</v>
+        <v>2.659471155197387</v>
       </c>
       <c r="E398" t="n">
-        <v>2.677876017635665</v>
+        <v>2.677875781649926</v>
       </c>
       <c r="F398" t="n">
         <v>21816400</v>
@@ -8392,16 +8392,16 @@
         <v>44994</v>
       </c>
       <c r="B399" t="n">
-        <v>2.576650381088257</v>
+        <v>2.576650142669678</v>
       </c>
       <c r="C399" t="n">
-        <v>2.705482998872884</v>
+        <v>2.705482748533367</v>
       </c>
       <c r="D399" t="n">
-        <v>2.558245752747664</v>
+        <v>2.558245516032073</v>
       </c>
       <c r="E399" t="n">
-        <v>2.687078370532291</v>
+        <v>2.687078121895762</v>
       </c>
       <c r="F399" t="n">
         <v>41324600</v>
@@ -8432,16 +8432,16 @@
         <v>44998</v>
       </c>
       <c r="B401" t="n">
-        <v>2.41100811958313</v>
+        <v>2.411008358001709</v>
       </c>
       <c r="C401" t="n">
-        <v>2.475424527834911</v>
+        <v>2.475424772623468</v>
       </c>
       <c r="D401" t="n">
-        <v>2.401805806890081</v>
+        <v>2.401806044398667</v>
       </c>
       <c r="E401" t="n">
-        <v>2.475424527834911</v>
+        <v>2.475424772623468</v>
       </c>
       <c r="F401" t="n">
         <v>31528700</v>
@@ -8452,16 +8452,16 @@
         <v>44999</v>
       </c>
       <c r="B402" t="n">
-        <v>2.493829250335693</v>
+        <v>2.493829488754272</v>
       </c>
       <c r="C402" t="n">
-        <v>2.585852380849743</v>
+        <v>2.585852628066047</v>
       </c>
       <c r="D402" t="n">
-        <v>2.466222311181478</v>
+        <v>2.46622254696074</v>
       </c>
       <c r="E402" t="n">
-        <v>2.475424624232883</v>
+        <v>2.475424860891918</v>
       </c>
       <c r="F402" t="n">
         <v>40119200</v>
@@ -8472,16 +8472,16 @@
         <v>45000</v>
       </c>
       <c r="B403" t="n">
-        <v>2.493829250335693</v>
+        <v>2.493829488754272</v>
       </c>
       <c r="C403" t="n">
-        <v>2.521436189489909</v>
+        <v>2.521436430547805</v>
       </c>
       <c r="D403" t="n">
-        <v>2.447817685078669</v>
+        <v>2.447817919098385</v>
       </c>
       <c r="E403" t="n">
-        <v>2.475424624232883</v>
+        <v>2.475424860891918</v>
       </c>
       <c r="F403" t="n">
         <v>17612600</v>
@@ -8492,16 +8492,16 @@
         <v>45001</v>
       </c>
       <c r="B404" t="n">
-        <v>2.512233972549438</v>
+        <v>2.512234210968018</v>
       </c>
       <c r="C404" t="n">
-        <v>2.539840912759816</v>
+        <v>2.539841153798378</v>
       </c>
       <c r="D404" t="n">
-        <v>2.447817778725223</v>
+        <v>2.447818011030511</v>
       </c>
       <c r="E404" t="n">
-        <v>2.530638599356357</v>
+        <v>2.530638839521591</v>
       </c>
       <c r="F404" t="n">
         <v>22197500</v>
@@ -8572,16 +8572,16 @@
         <v>45007</v>
       </c>
       <c r="B408" t="n">
-        <v>2.216452598571777</v>
+        <v>2.216452836990356</v>
       </c>
       <c r="C408" t="n">
-        <v>2.273528805389769</v>
+        <v>2.273529049947901</v>
       </c>
       <c r="D408" t="n">
-        <v>2.197427271899042</v>
+        <v>2.197427508271111</v>
       </c>
       <c r="E408" t="n">
-        <v>2.254503251917249</v>
+        <v>2.254503494428847</v>
       </c>
       <c r="F408" t="n">
         <v>26704400</v>
@@ -8592,16 +8592,16 @@
         <v>45008</v>
       </c>
       <c r="B409" t="n">
-        <v>2.149864196777344</v>
+        <v>2.149863958358765</v>
       </c>
       <c r="C409" t="n">
-        <v>2.235478176424297</v>
+        <v>2.235477928511182</v>
       </c>
       <c r="D409" t="n">
-        <v>2.140351532372127</v>
+        <v>2.140351295008496</v>
       </c>
       <c r="E409" t="n">
-        <v>2.22596551201908</v>
+        <v>2.225965265160914</v>
       </c>
       <c r="F409" t="n">
         <v>30902200</v>
@@ -8612,16 +8612,16 @@
         <v>45009</v>
       </c>
       <c r="B410" t="n">
-        <v>2.292554378509521</v>
+        <v>2.292554140090942</v>
       </c>
       <c r="C410" t="n">
-        <v>2.30206704286849</v>
+        <v>2.302066803460623</v>
       </c>
       <c r="D410" t="n">
-        <v>2.149864186325184</v>
+        <v>2.149863962745944</v>
       </c>
       <c r="E410" t="n">
-        <v>2.159376850684152</v>
+        <v>2.159376626115625</v>
       </c>
       <c r="F410" t="n">
         <v>19141800</v>
@@ -8672,16 +8672,16 @@
         <v>45014</v>
       </c>
       <c r="B413" t="n">
-        <v>2.615984916687012</v>
+        <v>2.615985155105591</v>
       </c>
       <c r="C413" t="n">
-        <v>2.644522906743987</v>
+        <v>2.644523147763493</v>
       </c>
       <c r="D413" t="n">
-        <v>2.492320066307002</v>
+        <v>2.492320293454875</v>
       </c>
       <c r="E413" t="n">
-        <v>2.539883609868411</v>
+        <v>2.539883841351184</v>
       </c>
       <c r="F413" t="n">
         <v>36856900</v>
@@ -8692,16 +8692,16 @@
         <v>45015</v>
       </c>
       <c r="B414" t="n">
-        <v>2.749162673950195</v>
+        <v>2.749162435531616</v>
       </c>
       <c r="C414" t="n">
-        <v>2.796725994925153</v>
+        <v>2.796725752381689</v>
       </c>
       <c r="D414" t="n">
-        <v>2.644523141005484</v>
+        <v>2.644522911661672</v>
       </c>
       <c r="E414" t="n">
-        <v>2.673061133590459</v>
+        <v>2.673060901771716</v>
       </c>
       <c r="F414" t="n">
         <v>39786400</v>
@@ -8712,16 +8712,16 @@
         <v>45016</v>
       </c>
       <c r="B415" t="n">
-        <v>2.711111783981323</v>
+        <v>2.711111545562744</v>
       </c>
       <c r="C415" t="n">
-        <v>2.787213324161716</v>
+        <v>2.787213079050672</v>
       </c>
       <c r="D415" t="n">
-        <v>2.654035798945881</v>
+        <v>2.654035565546636</v>
       </c>
       <c r="E415" t="n">
-        <v>2.777700659989142</v>
+        <v>2.777700415714654</v>
       </c>
       <c r="F415" t="n">
         <v>25812800</v>
@@ -8732,16 +8732,16 @@
         <v>45019</v>
       </c>
       <c r="B416" t="n">
-        <v>2.692085981369019</v>
+        <v>2.692086219787598</v>
       </c>
       <c r="C416" t="n">
-        <v>2.768187508142538</v>
+        <v>2.768187753300879</v>
       </c>
       <c r="D416" t="n">
-        <v>2.67306065637558</v>
+        <v>2.673060893109223</v>
       </c>
       <c r="E416" t="n">
-        <v>2.73964952065238</v>
+        <v>2.739649763283318</v>
       </c>
       <c r="F416" t="n">
         <v>18815900</v>
@@ -8752,16 +8752,16 @@
         <v>45020</v>
       </c>
       <c r="B417" t="n">
-        <v>2.692085981369019</v>
+        <v>2.692086219787598</v>
       </c>
       <c r="C417" t="n">
-        <v>2.73964952065238</v>
+        <v>2.739649763283318</v>
       </c>
       <c r="D417" t="n">
-        <v>2.654035331382141</v>
+        <v>2.654035566430849</v>
       </c>
       <c r="E417" t="n">
-        <v>2.720623968859177</v>
+        <v>2.720624209805159</v>
       </c>
       <c r="F417" t="n">
         <v>21012200</v>
@@ -8912,16 +8912,16 @@
         <v>45033</v>
       </c>
       <c r="B425" t="n">
-        <v>2.96795392036438</v>
+        <v>2.967953681945801</v>
       </c>
       <c r="C425" t="n">
-        <v>2.986979475361405</v>
+        <v>2.986979235414485</v>
       </c>
       <c r="D425" t="n">
-        <v>2.872827279378266</v>
+        <v>2.872827048601301</v>
       </c>
       <c r="E425" t="n">
-        <v>2.9013652716741</v>
+        <v>2.901365038604651</v>
       </c>
       <c r="F425" t="n">
         <v>14970900</v>
@@ -8932,16 +8932,16 @@
         <v>45034</v>
       </c>
       <c r="B426" t="n">
-        <v>3.025029897689819</v>
+        <v>3.025030136108398</v>
       </c>
       <c r="C426" t="n">
-        <v>3.034542561052375</v>
+        <v>3.034542800220697</v>
       </c>
       <c r="D426" t="n">
-        <v>2.948928363989592</v>
+        <v>2.948928596410207</v>
       </c>
       <c r="E426" t="n">
-        <v>2.986979244239598</v>
+        <v>2.986979479659204</v>
       </c>
       <c r="F426" t="n">
         <v>13884000</v>
@@ -8992,16 +8992,16 @@
         <v>45040</v>
       </c>
       <c r="B429" t="n">
-        <v>3.072593450546265</v>
+        <v>3.072593212127686</v>
       </c>
       <c r="C429" t="n">
-        <v>3.110644106919625</v>
+        <v>3.110643865548496</v>
       </c>
       <c r="D429" t="n">
-        <v>2.891852605973001</v>
+        <v>2.891852381579049</v>
       </c>
       <c r="E429" t="n">
-        <v>2.948928590533042</v>
+        <v>2.948928361710265</v>
       </c>
       <c r="F429" t="n">
         <v>37103600</v>
@@ -9012,16 +9012,16 @@
         <v>45041</v>
       </c>
       <c r="B430" t="n">
-        <v>3.025029897689819</v>
+        <v>3.025030136108398</v>
       </c>
       <c r="C430" t="n">
-        <v>3.14869452140304</v>
+        <v>3.148694769568281</v>
       </c>
       <c r="D430" t="n">
-        <v>2.977466580877042</v>
+        <v>2.977466815546905</v>
       </c>
       <c r="E430" t="n">
-        <v>3.072593214502596</v>
+        <v>3.072593456669892</v>
       </c>
       <c r="F430" t="n">
         <v>18942800</v>
@@ -9032,16 +9032,16 @@
         <v>45042</v>
       </c>
       <c r="B431" t="n">
-        <v>2.901364803314209</v>
+        <v>2.901365041732788</v>
       </c>
       <c r="C431" t="n">
-        <v>3.034542305996067</v>
+        <v>3.034542555358458</v>
       </c>
       <c r="D431" t="n">
-        <v>2.891852140751202</v>
+        <v>2.891852378388082</v>
       </c>
       <c r="E431" t="n">
-        <v>3.015516980870054</v>
+        <v>3.015517228669046</v>
       </c>
       <c r="F431" t="n">
         <v>15122100</v>
@@ -9052,16 +9052,16 @@
         <v>45043</v>
       </c>
       <c r="B432" t="n">
-        <v>2.977466583251953</v>
+        <v>2.977466344833374</v>
       </c>
       <c r="C432" t="n">
-        <v>3.006004573362382</v>
+        <v>3.006004332658643</v>
       </c>
       <c r="D432" t="n">
-        <v>2.891852386120882</v>
+        <v>2.8918521545578</v>
       </c>
       <c r="E432" t="n">
-        <v>2.901365049491024</v>
+        <v>2.901364817166223</v>
       </c>
       <c r="F432" t="n">
         <v>12242300</v>
@@ -9132,16 +9132,16 @@
         <v>45050</v>
       </c>
       <c r="B436" t="n">
-        <v>3.025029897689819</v>
+        <v>3.025030136108398</v>
       </c>
       <c r="C436" t="n">
-        <v>3.063080551140041</v>
+        <v>3.063080792557593</v>
       </c>
       <c r="D436" t="n">
-        <v>2.958441027352147</v>
+        <v>2.958441260522505</v>
       </c>
       <c r="E436" t="n">
-        <v>3.015517234327264</v>
+        <v>3.0155174719961</v>
       </c>
       <c r="F436" t="n">
         <v>20441800</v>
@@ -9192,16 +9192,16 @@
         <v>45055</v>
       </c>
       <c r="B439" t="n">
-        <v>3.025029897689819</v>
+        <v>3.025030136108398</v>
       </c>
       <c r="C439" t="n">
-        <v>3.158207184765595</v>
+        <v>3.158207433680579</v>
       </c>
       <c r="D439" t="n">
-        <v>3.015517234327264</v>
+        <v>3.0155174719961</v>
       </c>
       <c r="E439" t="n">
-        <v>3.129669194677929</v>
+        <v>3.129669441343684</v>
       </c>
       <c r="F439" t="n">
         <v>32144800</v>
@@ -9232,16 +9232,16 @@
         <v>45057</v>
       </c>
       <c r="B441" t="n">
-        <v>3.167719841003418</v>
+        <v>3.167720079421997</v>
       </c>
       <c r="C441" t="n">
-        <v>3.167719841003418</v>
+        <v>3.167720079421997</v>
       </c>
       <c r="D441" t="n">
-        <v>3.0535678809095</v>
+        <v>3.053568110736427</v>
       </c>
       <c r="E441" t="n">
-        <v>3.110643860956459</v>
+        <v>3.110644095079212</v>
       </c>
       <c r="F441" t="n">
         <v>17152200</v>
@@ -9272,16 +9272,16 @@
         <v>45061</v>
       </c>
       <c r="B443" t="n">
-        <v>2.986979484558105</v>
+        <v>2.986979007720947</v>
       </c>
       <c r="C443" t="n">
-        <v>3.20577075949981</v>
+        <v>3.205770247735124</v>
       </c>
       <c r="D443" t="n">
-        <v>2.901365280607201</v>
+        <v>2.901364817437372</v>
       </c>
       <c r="E443" t="n">
-        <v>3.18674543124401</v>
+        <v>3.1867449225165</v>
       </c>
       <c r="F443" t="n">
         <v>71533500</v>
@@ -9292,16 +9292,16 @@
         <v>45062</v>
       </c>
       <c r="B444" t="n">
-        <v>3.082105875015259</v>
+        <v>3.082106113433838</v>
       </c>
       <c r="C444" t="n">
-        <v>3.139181855137815</v>
+        <v>3.139182097971549</v>
       </c>
       <c r="D444" t="n">
-        <v>2.977466578123905</v>
+        <v>2.977466808448034</v>
       </c>
       <c r="E444" t="n">
-        <v>2.977466578123905</v>
+        <v>2.977466808448034</v>
       </c>
       <c r="F444" t="n">
         <v>45623200</v>
@@ -9312,16 +9312,16 @@
         <v>45063</v>
       </c>
       <c r="B445" t="n">
-        <v>3.253334522247314</v>
+        <v>3.253334283828735</v>
       </c>
       <c r="C445" t="n">
-        <v>3.300897846034593</v>
+        <v>3.300897604130366</v>
       </c>
       <c r="D445" t="n">
-        <v>3.082106329813293</v>
+        <v>3.082106103943065</v>
       </c>
       <c r="E445" t="n">
-        <v>3.091618994570749</v>
+        <v>3.091618768003391</v>
       </c>
       <c r="F445" t="n">
         <v>27916800</v>
@@ -9372,16 +9372,16 @@
         <v>45068</v>
       </c>
       <c r="B448" t="n">
-        <v>3.472125291824341</v>
+        <v>3.47212553024292</v>
       </c>
       <c r="C448" t="n">
-        <v>3.576764581654768</v>
+        <v>3.576764827258557</v>
       </c>
       <c r="D448" t="n">
-        <v>3.453099966400627</v>
+        <v>3.453100203512804</v>
       </c>
       <c r="E448" t="n">
-        <v>3.548226593519197</v>
+        <v>3.548226837163384</v>
       </c>
       <c r="F448" t="n">
         <v>14142300</v>
@@ -9392,16 +9392,16 @@
         <v>45069</v>
       </c>
       <c r="B449" t="n">
-        <v>3.472125291824341</v>
+        <v>3.47212553024292</v>
       </c>
       <c r="C449" t="n">
-        <v>3.567251918942911</v>
+        <v>3.5672521638935</v>
       </c>
       <c r="D449" t="n">
-        <v>3.443587076889001</v>
+        <v>3.443587313347962</v>
       </c>
       <c r="E449" t="n">
-        <v>3.472125291824341</v>
+        <v>3.47212553024292</v>
       </c>
       <c r="F449" t="n">
         <v>12031500</v>
@@ -9452,16 +9452,16 @@
         <v>45072</v>
       </c>
       <c r="B452" t="n">
-        <v>3.291384696960449</v>
+        <v>3.291384935379028</v>
       </c>
       <c r="C452" t="n">
-        <v>3.348460677106637</v>
+        <v>3.348460919659638</v>
       </c>
       <c r="D452" t="n">
-        <v>3.17723250986829</v>
+        <v>3.177232740018008</v>
       </c>
       <c r="E452" t="n">
-        <v>3.338948013748939</v>
+        <v>3.33894825561287</v>
       </c>
       <c r="F452" t="n">
         <v>25686400</v>
@@ -9472,16 +9472,16 @@
         <v>45075</v>
       </c>
       <c r="B453" t="n">
-        <v>3.357973575592041</v>
+        <v>3.357973337173462</v>
       </c>
       <c r="C453" t="n">
-        <v>3.415049559734729</v>
+        <v>3.415049317263714</v>
       </c>
       <c r="D453" t="n">
-        <v>3.291384927425571</v>
+        <v>3.291384693734835</v>
       </c>
       <c r="E453" t="n">
-        <v>3.319922919496916</v>
+        <v>3.319922683779961</v>
       </c>
       <c r="F453" t="n">
         <v>14544800</v>
@@ -9512,16 +9512,16 @@
         <v>45077</v>
       </c>
       <c r="B455" t="n">
-        <v>3.453100442886353</v>
+        <v>3.453100204467773</v>
       </c>
       <c r="C455" t="n">
-        <v>3.557739747155727</v>
+        <v>3.557739501512349</v>
       </c>
       <c r="D455" t="n">
-        <v>3.415049559988598</v>
+        <v>3.415049324197234</v>
       </c>
       <c r="E455" t="n">
-        <v>3.424562224013087</v>
+        <v>3.424561987564922</v>
       </c>
       <c r="F455" t="n">
         <v>23066900</v>
@@ -9532,16 +9532,16 @@
         <v>45078</v>
       </c>
       <c r="B456" t="n">
-        <v>3.576764822006226</v>
+        <v>3.576765060424805</v>
       </c>
       <c r="C456" t="n">
-        <v>3.662378792166026</v>
+        <v>3.662379036291428</v>
       </c>
       <c r="D456" t="n">
-        <v>3.376998664833572</v>
+        <v>3.376998889936218</v>
       </c>
       <c r="E456" t="n">
-        <v>3.472125525144246</v>
+        <v>3.472125756587821</v>
       </c>
       <c r="F456" t="n">
         <v>28377100</v>
@@ -9552,16 +9552,16 @@
         <v>45079</v>
       </c>
       <c r="B457" t="n">
-        <v>3.529201507568359</v>
+        <v>3.529201745986938</v>
       </c>
       <c r="C457" t="n">
-        <v>3.643353467856389</v>
+        <v>3.643353713986613</v>
       </c>
       <c r="D457" t="n">
-        <v>3.491150854139016</v>
+        <v>3.491151089987047</v>
       </c>
       <c r="E457" t="n">
-        <v>3.614815477784382</v>
+        <v>3.614815721986695</v>
       </c>
       <c r="F457" t="n">
         <v>24144300</v>
@@ -9572,16 +9572,16 @@
         <v>45082</v>
       </c>
       <c r="B458" t="n">
-        <v>3.586277484893799</v>
+        <v>3.586277723312378</v>
       </c>
       <c r="C458" t="n">
-        <v>3.605302811593518</v>
+        <v>3.605303051276916</v>
       </c>
       <c r="D458" t="n">
-        <v>3.500663514745063</v>
+        <v>3.500663747471958</v>
       </c>
       <c r="E458" t="n">
-        <v>3.510176178094923</v>
+        <v>3.510176411454227</v>
       </c>
       <c r="F458" t="n">
         <v>11705300</v>
@@ -9632,16 +9632,16 @@
         <v>45086</v>
       </c>
       <c r="B461" t="n">
-        <v>3.786043882369995</v>
+        <v>3.786043643951416</v>
       </c>
       <c r="C461" t="n">
-        <v>3.824094538184801</v>
+        <v>3.824094297370058</v>
       </c>
       <c r="D461" t="n">
-        <v>3.728967898647786</v>
+        <v>3.728967663823453</v>
       </c>
       <c r="E461" t="n">
-        <v>3.795556546323696</v>
+        <v>3.795556307306077</v>
       </c>
       <c r="F461" t="n">
         <v>14031500</v>
@@ -9652,16 +9652,16 @@
         <v>45089</v>
       </c>
       <c r="B462" t="n">
-        <v>3.795556306838989</v>
+        <v>3.795556545257568</v>
       </c>
       <c r="C462" t="n">
-        <v>3.805068970192479</v>
+        <v>3.805069209208598</v>
       </c>
       <c r="D462" t="n">
-        <v>3.74799299007154</v>
+        <v>3.747993225502421</v>
       </c>
       <c r="E462" t="n">
-        <v>3.786043643485499</v>
+        <v>3.786043881306539</v>
       </c>
       <c r="F462" t="n">
         <v>16242400</v>
@@ -9772,16 +9772,16 @@
         <v>45097</v>
       </c>
       <c r="B468" t="n">
-        <v>3.947758913040161</v>
+        <v>3.94775915145874</v>
       </c>
       <c r="C468" t="n">
-        <v>3.966784238618205</v>
+        <v>3.966784478185788</v>
       </c>
       <c r="D468" t="n">
-        <v>3.767018093248975</v>
+        <v>3.767018320752002</v>
       </c>
       <c r="E468" t="n">
-        <v>3.786043418827019</v>
+        <v>3.78604364747905</v>
       </c>
       <c r="F468" t="n">
         <v>35176100</v>
@@ -9912,16 +9912,16 @@
         <v>45106</v>
       </c>
       <c r="B475" t="n">
-        <v>4.366317272186279</v>
+        <v>4.366316795349121</v>
       </c>
       <c r="C475" t="n">
-        <v>4.366317272186279</v>
+        <v>4.366316795349121</v>
       </c>
       <c r="D475" t="n">
-        <v>4.185576421646147</v>
+        <v>4.185575964547351</v>
       </c>
       <c r="E475" t="n">
-        <v>4.185576421646147</v>
+        <v>4.185575964547351</v>
       </c>
       <c r="F475" t="n">
         <v>40765500</v>
@@ -9932,16 +9932,16 @@
         <v>45107</v>
       </c>
       <c r="B476" t="n">
-        <v>4.185576438903809</v>
+        <v>4.18557596206665</v>
       </c>
       <c r="C476" t="n">
-        <v>4.489981701195243</v>
+        <v>4.489981189679052</v>
       </c>
       <c r="D476" t="n">
-        <v>4.138012889870962</v>
+        <v>4.138012418452428</v>
       </c>
       <c r="E476" t="n">
-        <v>4.413880385622384</v>
+        <v>4.413879882775952</v>
       </c>
       <c r="F476" t="n">
         <v>35419200</v>
@@ -9972,16 +9972,16 @@
         <v>45111</v>
       </c>
       <c r="B478" t="n">
-        <v>4.195087909698486</v>
+        <v>4.195088386535645</v>
       </c>
       <c r="C478" t="n">
-        <v>4.26167677227765</v>
+        <v>4.261677256683671</v>
       </c>
       <c r="D478" t="n">
-        <v>4.138011936173281</v>
+        <v>4.138012406522865</v>
       </c>
       <c r="E478" t="n">
-        <v>4.252163883223692</v>
+        <v>4.252164366548425</v>
       </c>
       <c r="F478" t="n">
         <v>10806500</v>
@@ -9992,16 +9992,16 @@
         <v>45112</v>
       </c>
       <c r="B479" t="n">
-        <v>4.080936431884766</v>
+        <v>4.080936908721924</v>
       </c>
       <c r="C479" t="n">
-        <v>4.185575955512459</v>
+        <v>4.185576444576225</v>
       </c>
       <c r="D479" t="n">
-        <v>4.023860451796815</v>
+        <v>4.023860921964928</v>
       </c>
       <c r="E479" t="n">
-        <v>4.166550628816475</v>
+        <v>4.166551115657227</v>
       </c>
       <c r="F479" t="n">
         <v>33346200</v>
@@ -10012,16 +10012,16 @@
         <v>45113</v>
       </c>
       <c r="B480" t="n">
-        <v>3.957271575927734</v>
+        <v>3.957271814346313</v>
       </c>
       <c r="C480" t="n">
-        <v>4.061911099406468</v>
+        <v>4.061911344129392</v>
       </c>
       <c r="D480" t="n">
-        <v>3.909708486055269</v>
+        <v>3.909708721608256</v>
       </c>
       <c r="E480" t="n">
-        <v>4.061911099406468</v>
+        <v>4.061911344129392</v>
       </c>
       <c r="F480" t="n">
         <v>22675100</v>
@@ -10032,16 +10032,16 @@
         <v>45114</v>
       </c>
       <c r="B481" t="n">
-        <v>3.995322704315186</v>
+        <v>3.995322227478027</v>
       </c>
       <c r="C481" t="n">
-        <v>4.042886253442594</v>
+        <v>4.042885770928781</v>
       </c>
       <c r="D481" t="n">
-        <v>3.947759608787399</v>
+        <v>3.947759137626841</v>
       </c>
       <c r="E481" t="n">
-        <v>3.976297375384147</v>
+        <v>3.976296900817639</v>
       </c>
       <c r="F481" t="n">
         <v>19055100</v>
@@ -10052,16 +10052,16 @@
         <v>45117</v>
       </c>
       <c r="B482" t="n">
-        <v>4.033372402191162</v>
+        <v>4.03337287902832</v>
       </c>
       <c r="C482" t="n">
-        <v>4.099961264400743</v>
+        <v>4.099961749110232</v>
       </c>
       <c r="D482" t="n">
-        <v>3.947758669178288</v>
+        <v>3.947759135893939</v>
       </c>
       <c r="E482" t="n">
-        <v>3.995321753385549</v>
+        <v>3.995322225724247</v>
       </c>
       <c r="F482" t="n">
         <v>16685100</v>
@@ -10112,16 +10112,16 @@
         <v>45120</v>
       </c>
       <c r="B485" t="n">
-        <v>3.995322704315186</v>
+        <v>3.995322227478027</v>
       </c>
       <c r="C485" t="n">
-        <v>4.071424473638964</v>
+        <v>4.071423987719147</v>
       </c>
       <c r="D485" t="n">
-        <v>3.957272046453107</v>
+        <v>3.957271574157251</v>
       </c>
       <c r="E485" t="n">
-        <v>4.023860924511555</v>
+        <v>4.023860444268393</v>
       </c>
       <c r="F485" t="n">
         <v>10522300</v>
@@ -10132,16 +10132,16 @@
         <v>45121</v>
       </c>
       <c r="B486" t="n">
-        <v>3.881170272827148</v>
+        <v>3.881170511245728</v>
       </c>
       <c r="C486" t="n">
-        <v>4.01434755963212</v>
+        <v>4.014347806231721</v>
       </c>
       <c r="D486" t="n">
-        <v>3.814581856224446</v>
+        <v>3.814582090552529</v>
       </c>
       <c r="E486" t="n">
-        <v>3.995322232945695</v>
+        <v>3.995322478376579</v>
       </c>
       <c r="F486" t="n">
         <v>16845900</v>
@@ -10172,16 +10172,16 @@
         <v>45125</v>
       </c>
       <c r="B488" t="n">
-        <v>4.07142448425293</v>
+        <v>4.071424007415771</v>
       </c>
       <c r="C488" t="n">
-        <v>4.185576458136752</v>
+        <v>4.185575967930341</v>
       </c>
       <c r="D488" t="n">
-        <v>4.004835606020889</v>
+        <v>4.004835136982487</v>
       </c>
       <c r="E488" t="n">
-        <v>4.023860935001526</v>
+        <v>4.023860463734916</v>
       </c>
       <c r="F488" t="n">
         <v>19854400</v>
@@ -10212,16 +10212,16 @@
         <v>45127</v>
       </c>
       <c r="B490" t="n">
-        <v>3.995322704315186</v>
+        <v>3.995322227478027</v>
       </c>
       <c r="C490" t="n">
-        <v>4.080936911304672</v>
+        <v>4.080936424249557</v>
       </c>
       <c r="D490" t="n">
-        <v>3.947759608787399</v>
+        <v>3.947759137626841</v>
       </c>
       <c r="E490" t="n">
-        <v>4.071424473638964</v>
+        <v>4.071423987719147</v>
       </c>
       <c r="F490" t="n">
         <v>13981900</v>
@@ -10272,16 +10272,16 @@
         <v>45132</v>
       </c>
       <c r="B493" t="n">
-        <v>3.995322704315186</v>
+        <v>3.995322227478027</v>
       </c>
       <c r="C493" t="n">
-        <v>4.090449802570003</v>
+        <v>4.090449314379534</v>
       </c>
       <c r="D493" t="n">
-        <v>3.966784937718438</v>
+        <v>3.966784464287229</v>
       </c>
       <c r="E493" t="n">
-        <v>4.061911582373633</v>
+        <v>4.061911097589169</v>
       </c>
       <c r="F493" t="n">
         <v>14413200</v>
@@ -10312,16 +10312,16 @@
         <v>45134</v>
       </c>
       <c r="B495" t="n">
-        <v>3.893998622894287</v>
+        <v>3.893998384475708</v>
       </c>
       <c r="C495" t="n">
-        <v>4.056646823940207</v>
+        <v>4.056646575563136</v>
       </c>
       <c r="D495" t="n">
-        <v>3.884430840129649</v>
+        <v>3.884430602296878</v>
       </c>
       <c r="E495" t="n">
-        <v>4.047079497392562</v>
+        <v>4.047079249601271</v>
       </c>
       <c r="F495" t="n">
         <v>18331700</v>
@@ -10352,16 +10352,16 @@
         <v>45138</v>
       </c>
       <c r="B497" t="n">
-        <v>3.980106115341187</v>
+        <v>3.980106353759766</v>
       </c>
       <c r="C497" t="n">
-        <v>4.008809005461245</v>
+        <v>4.008809245599202</v>
       </c>
       <c r="D497" t="n">
-        <v>3.922700791318031</v>
+        <v>3.922701026297883</v>
       </c>
       <c r="E497" t="n">
-        <v>3.941835899325749</v>
+        <v>3.941836135451844</v>
       </c>
       <c r="F497" t="n">
         <v>13989300</v>
@@ -10372,16 +10372,16 @@
         <v>45139</v>
       </c>
       <c r="B498" t="n">
-        <v>3.980106115341187</v>
+        <v>3.980106353759766</v>
       </c>
       <c r="C498" t="n">
-        <v>4.018376331356624</v>
+        <v>4.018376572067687</v>
       </c>
       <c r="D498" t="n">
-        <v>3.884430575302593</v>
+        <v>3.884430807989962</v>
       </c>
       <c r="E498" t="n">
-        <v>3.970538789445808</v>
+        <v>3.970539027291279</v>
       </c>
       <c r="F498" t="n">
         <v>24308900</v>
@@ -10392,16 +10392,16 @@
         <v>45140</v>
       </c>
       <c r="B499" t="n">
-        <v>4.008809089660645</v>
+        <v>4.008808612823486</v>
       </c>
       <c r="C499" t="n">
-        <v>4.018376415756972</v>
+        <v>4.018375937781805</v>
       </c>
       <c r="D499" t="n">
-        <v>3.932268656022146</v>
+        <v>3.932268188289268</v>
       </c>
       <c r="E499" t="n">
-        <v>3.95140376443177</v>
+        <v>3.951403294422822</v>
       </c>
       <c r="F499" t="n">
         <v>25721100</v>
@@ -10432,16 +10432,16 @@
         <v>45142</v>
       </c>
       <c r="B501" t="n">
-        <v>3.903565645217896</v>
+        <v>3.903565883636475</v>
       </c>
       <c r="C501" t="n">
-        <v>3.96097096868087</v>
+        <v>3.960971210605601</v>
       </c>
       <c r="D501" t="n">
-        <v>3.865295429575913</v>
+        <v>3.865295665657057</v>
       </c>
       <c r="E501" t="n">
-        <v>3.903565645217896</v>
+        <v>3.903565883636475</v>
       </c>
       <c r="F501" t="n">
         <v>16409800</v>
@@ -10452,16 +10452,16 @@
         <v>45145</v>
       </c>
       <c r="B502" t="n">
-        <v>3.846160411834717</v>
+        <v>3.846160650253296</v>
       </c>
       <c r="C502" t="n">
-        <v>3.922700844911313</v>
+        <v>3.922701088074537</v>
       </c>
       <c r="D502" t="n">
-        <v>3.817457749430993</v>
+        <v>3.817457986070331</v>
       </c>
       <c r="E502" t="n">
-        <v>3.913133518885223</v>
+        <v>3.913133761455379</v>
       </c>
       <c r="F502" t="n">
         <v>14729300</v>
@@ -10552,16 +10552,16 @@
         <v>45152</v>
       </c>
       <c r="B507" t="n">
-        <v>3.606971263885498</v>
+        <v>3.606971502304077</v>
       </c>
       <c r="C507" t="n">
-        <v>3.664376587634967</v>
+        <v>3.664376829848003</v>
       </c>
       <c r="D507" t="n">
-        <v>3.568701048052518</v>
+        <v>3.56870128394146</v>
       </c>
       <c r="E507" t="n">
-        <v>3.664376587634967</v>
+        <v>3.664376829848003</v>
       </c>
       <c r="F507" t="n">
         <v>20072900</v>
@@ -10632,16 +10632,16 @@
         <v>45156</v>
       </c>
       <c r="B511" t="n">
-        <v>3.434755086898804</v>
+        <v>3.434755325317383</v>
       </c>
       <c r="C511" t="n">
-        <v>3.473025531089514</v>
+        <v>3.473025772164581</v>
       </c>
       <c r="D511" t="n">
-        <v>3.339079546693231</v>
+        <v>3.33907977847063</v>
       </c>
       <c r="E511" t="n">
-        <v>3.358214654734345</v>
+        <v>3.35821488783998</v>
       </c>
       <c r="F511" t="n">
         <v>15864700</v>
@@ -10652,16 +10652,16 @@
         <v>45159</v>
       </c>
       <c r="B512" t="n">
-        <v>3.348647117614746</v>
+        <v>3.348647356033325</v>
       </c>
       <c r="C512" t="n">
-        <v>3.463457766440895</v>
+        <v>3.463458013033817</v>
       </c>
       <c r="D512" t="n">
-        <v>3.329512009477055</v>
+        <v>3.329512246533243</v>
       </c>
       <c r="E512" t="n">
-        <v>3.444322658303203</v>
+        <v>3.444322903533735</v>
       </c>
       <c r="F512" t="n">
         <v>12295100</v>
@@ -10692,16 +10692,16 @@
         <v>45161</v>
       </c>
       <c r="B514" t="n">
-        <v>3.453890085220337</v>
+        <v>3.453890323638916</v>
       </c>
       <c r="C514" t="n">
-        <v>3.559133404211688</v>
+        <v>3.559133649895108</v>
       </c>
       <c r="D514" t="n">
-        <v>3.377349655487335</v>
+        <v>3.377349888622405</v>
       </c>
       <c r="E514" t="n">
-        <v>3.396484762920585</v>
+        <v>3.396484997376533</v>
       </c>
       <c r="F514" t="n">
         <v>43718400</v>
@@ -10732,16 +10732,16 @@
         <v>45163</v>
       </c>
       <c r="B516" t="n">
-        <v>3.626106739044189</v>
+        <v>3.62610650062561</v>
       </c>
       <c r="C516" t="n">
-        <v>3.664376958753072</v>
+        <v>3.664376717818205</v>
       </c>
       <c r="D516" t="n">
-        <v>3.549566299626424</v>
+        <v>3.549566066240422</v>
       </c>
       <c r="E516" t="n">
-        <v>3.616539184116969</v>
+        <v>3.616538946327462</v>
       </c>
       <c r="F516" t="n">
         <v>21198200</v>
@@ -10772,16 +10772,16 @@
         <v>45167</v>
       </c>
       <c r="B518" t="n">
-        <v>3.654809236526489</v>
+        <v>3.65480899810791</v>
       </c>
       <c r="C518" t="n">
-        <v>3.664376791015754</v>
+        <v>3.664376551973043</v>
       </c>
       <c r="D518" t="n">
-        <v>3.578268800612372</v>
+        <v>3.578268567186847</v>
       </c>
       <c r="E518" t="n">
-        <v>3.61653901856943</v>
+        <v>3.616538782647379</v>
       </c>
       <c r="F518" t="n">
         <v>13520200</v>
@@ -10792,16 +10792,16 @@
         <v>45168</v>
       </c>
       <c r="B519" t="n">
-        <v>3.587836503982544</v>
+        <v>3.587836265563965</v>
       </c>
       <c r="C519" t="n">
-        <v>3.683512052845344</v>
+        <v>3.683511808068943</v>
       </c>
       <c r="D519" t="n">
-        <v>3.549566284437424</v>
+        <v>3.549566048561974</v>
       </c>
       <c r="E519" t="n">
-        <v>3.654809388186504</v>
+        <v>3.654809145317449</v>
       </c>
       <c r="F519" t="n">
         <v>15075000</v>
@@ -10812,16 +10812,16 @@
         <v>45169</v>
       </c>
       <c r="B520" t="n">
-        <v>3.473025798797607</v>
+        <v>3.473025560379028</v>
       </c>
       <c r="C520" t="n">
-        <v>3.597404010652185</v>
+        <v>3.597403763695208</v>
       </c>
       <c r="D520" t="n">
-        <v>3.463458015931064</v>
+        <v>3.463457778169301</v>
       </c>
       <c r="E520" t="n">
-        <v>3.58783645589414</v>
+        <v>3.587836209593963</v>
       </c>
       <c r="F520" t="n">
         <v>21889800</v>
@@ -10832,16 +10832,16 @@
         <v>45170</v>
       </c>
       <c r="B521" t="n">
-        <v>3.473025798797607</v>
+        <v>3.473025560379028</v>
       </c>
       <c r="C521" t="n">
-        <v>3.578268901136096</v>
+        <v>3.578268655492719</v>
       </c>
       <c r="D521" t="n">
-        <v>3.473025798797607</v>
+        <v>3.473025560379028</v>
       </c>
       <c r="E521" t="n">
-        <v>3.50172846307174</v>
+        <v>3.501728222682762</v>
       </c>
       <c r="F521" t="n">
         <v>17307200</v>
@@ -10912,16 +10912,16 @@
         <v>45177</v>
       </c>
       <c r="B525" t="n">
-        <v>3.549566030502319</v>
+        <v>3.549566268920898</v>
       </c>
       <c r="C525" t="n">
-        <v>3.587836247309597</v>
+        <v>3.587836488298725</v>
       </c>
       <c r="D525" t="n">
-        <v>3.511295813695041</v>
+        <v>3.511296049543073</v>
       </c>
       <c r="E525" t="n">
-        <v>3.53043092209868</v>
+        <v>3.530431159231985</v>
       </c>
       <c r="F525" t="n">
         <v>26042800</v>
@@ -11012,16 +11012,16 @@
         <v>45184</v>
       </c>
       <c r="B530" t="n">
-        <v>3.80789041519165</v>
+        <v>3.807890176773071</v>
       </c>
       <c r="C530" t="n">
-        <v>3.941836180810695</v>
+        <v>3.941835934005541</v>
       </c>
       <c r="D530" t="n">
-        <v>3.788755305817501</v>
+        <v>3.788755068597004</v>
       </c>
       <c r="E530" t="n">
-        <v>3.788755305817501</v>
+        <v>3.788755068597004</v>
       </c>
       <c r="F530" t="n">
         <v>34682000</v>
@@ -11032,16 +11032,16 @@
         <v>45187</v>
       </c>
       <c r="B531" t="n">
-        <v>3.817457675933838</v>
+        <v>3.817457914352417</v>
       </c>
       <c r="C531" t="n">
-        <v>3.884430553586438</v>
+        <v>3.884430796187795</v>
       </c>
       <c r="D531" t="n">
-        <v>3.740917244330867</v>
+        <v>3.740917477969129</v>
       </c>
       <c r="E531" t="n">
-        <v>3.817457675933838</v>
+        <v>3.817457914352417</v>
       </c>
       <c r="F531" t="n">
         <v>23371600</v>
@@ -11112,16 +11112,16 @@
         <v>45191</v>
       </c>
       <c r="B535" t="n">
-        <v>3.606971263885498</v>
+        <v>3.606971502304077</v>
       </c>
       <c r="C535" t="n">
-        <v>3.664376587634967</v>
+        <v>3.664376829848003</v>
       </c>
       <c r="D535" t="n">
-        <v>3.559133494094274</v>
+        <v>3.559133729350806</v>
       </c>
       <c r="E535" t="n">
-        <v>3.597403709927253</v>
+        <v>3.597403947713423</v>
       </c>
       <c r="F535" t="n">
         <v>21984900</v>
@@ -11192,16 +11192,16 @@
         <v>45197</v>
       </c>
       <c r="B539" t="n">
-        <v>3.41562032699585</v>
+        <v>3.415620088577271</v>
       </c>
       <c r="C539" t="n">
-        <v>3.444322991983049</v>
+        <v>3.444322751560954</v>
       </c>
       <c r="D539" t="n">
-        <v>3.32951233203425</v>
+        <v>3.329512099626217</v>
       </c>
       <c r="E539" t="n">
-        <v>3.41562032699585</v>
+        <v>3.415620088577271</v>
       </c>
       <c r="F539" t="n">
         <v>16733500</v>
@@ -11252,16 +11252,16 @@
         <v>45202</v>
       </c>
       <c r="B542" t="n">
-        <v>3.310376882553101</v>
+        <v>3.31037712097168</v>
       </c>
       <c r="C542" t="n">
-        <v>3.406052422698603</v>
+        <v>3.406052668007885</v>
       </c>
       <c r="D542" t="n">
-        <v>3.2721066664949</v>
+        <v>3.272106902157197</v>
       </c>
       <c r="E542" t="n">
-        <v>3.31994443656765</v>
+        <v>3.3199446756753</v>
       </c>
       <c r="F542" t="n">
         <v>29291500</v>
@@ -11292,16 +11292,16 @@
         <v>45204</v>
       </c>
       <c r="B544" t="n">
-        <v>3.233836650848389</v>
+        <v>3.23383641242981</v>
       </c>
       <c r="C544" t="n">
-        <v>3.358214860745675</v>
+        <v>3.35821461315716</v>
       </c>
       <c r="D544" t="n">
-        <v>3.205133758917443</v>
+        <v>3.20513352261502</v>
       </c>
       <c r="E544" t="n">
-        <v>3.310377087708257</v>
+        <v>3.310376843646641</v>
       </c>
       <c r="F544" t="n">
         <v>37198300</v>
@@ -11312,16 +11312,16 @@
         <v>45205</v>
       </c>
       <c r="B545" t="n">
-        <v>3.233836650848389</v>
+        <v>3.23383641242981</v>
       </c>
       <c r="C545" t="n">
-        <v>3.262539314670839</v>
+        <v>3.262539074136121</v>
       </c>
       <c r="D545" t="n">
-        <v>3.138160876665057</v>
+        <v>3.138160645300292</v>
       </c>
       <c r="E545" t="n">
-        <v>3.205133758917443</v>
+        <v>3.20513352261502</v>
       </c>
       <c r="F545" t="n">
         <v>15875400</v>
@@ -11352,16 +11352,16 @@
         <v>45209</v>
       </c>
       <c r="B547" t="n">
-        <v>3.41562032699585</v>
+        <v>3.415620088577271</v>
       </c>
       <c r="C547" t="n">
-        <v>3.425187881991583</v>
+        <v>3.425187642905165</v>
       </c>
       <c r="D547" t="n">
-        <v>3.348647442025716</v>
+        <v>3.348647208282007</v>
       </c>
       <c r="E547" t="n">
-        <v>3.367782552017183</v>
+        <v>3.367782316937797</v>
       </c>
       <c r="F547" t="n">
         <v>9595500</v>
@@ -11372,16 +11372,16 @@
         <v>45210</v>
       </c>
       <c r="B548" t="n">
-        <v>3.482593536376953</v>
+        <v>3.482593059539795</v>
       </c>
       <c r="C548" t="n">
-        <v>3.511296202157854</v>
+        <v>3.511295721390723</v>
       </c>
       <c r="D548" t="n">
-        <v>3.39648531092574</v>
+        <v>3.396484845878531</v>
       </c>
       <c r="E548" t="n">
-        <v>3.415620421446341</v>
+        <v>3.41561995377915</v>
       </c>
       <c r="F548" t="n">
         <v>15610900</v>
@@ -26112,19 +26112,39 @@
         <v>46290</v>
       </c>
       <c r="B1285" t="n">
-        <v>0.28</v>
+        <v>0.2800000011920929</v>
       </c>
       <c r="C1285" t="n">
-        <v>0.3</v>
+        <v>0.300000011920929</v>
       </c>
       <c r="D1285" t="n">
-        <v>0.28</v>
+        <v>0.2800000011920929</v>
       </c>
       <c r="E1285" t="n">
-        <v>0.28</v>
+        <v>0.2800000011920929</v>
       </c>
       <c r="F1285" t="n">
         <v>6197400</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B1286" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="C1286" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="D1286" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E1286" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F1286" t="n">
+        <v>7100000</v>
       </c>
     </row>
   </sheetData>

--- a/database/RAIZ4.xlsx
+++ b/database/RAIZ4.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1286"/>
+  <dimension ref="A1:F1287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44413</v>
       </c>
       <c r="B2" t="n">
-        <v>6.384480953216553</v>
+        <v>6.384481906890869</v>
       </c>
       <c r="C2" t="n">
-        <v>6.701941459879408</v>
+        <v>6.701942460974013</v>
       </c>
       <c r="D2" t="n">
-        <v>6.331570938854646</v>
+        <v>6.331571884625592</v>
       </c>
       <c r="E2" t="n">
-        <v>6.596121431155595</v>
+        <v>6.596122416443459</v>
       </c>
       <c r="F2" t="n">
         <v>98849900</v>
@@ -472,16 +472,16 @@
         <v>44414</v>
       </c>
       <c r="B3" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261023998260498</v>
       </c>
       <c r="C3" t="n">
-        <v>6.481483579964149</v>
+        <v>6.48148259270975</v>
       </c>
       <c r="D3" t="n">
-        <v>6.199296805201136</v>
+        <v>6.199295860929202</v>
       </c>
       <c r="E3" t="n">
-        <v>6.393300212850708</v>
+        <v>6.393299239028329</v>
       </c>
       <c r="F3" t="n">
         <v>28799900</v>
@@ -492,16 +492,16 @@
         <v>44417</v>
       </c>
       <c r="B4" t="n">
-        <v>6.234570503234863</v>
+        <v>6.234570026397705</v>
       </c>
       <c r="C4" t="n">
-        <v>6.44621059622864</v>
+        <v>6.446210103204662</v>
       </c>
       <c r="D4" t="n">
-        <v>6.234570503234863</v>
+        <v>6.234570026397705</v>
       </c>
       <c r="E4" t="n">
-        <v>6.331572002277935</v>
+        <v>6.331571518021834</v>
       </c>
       <c r="F4" t="n">
         <v>14491100</v>
@@ -512,16 +512,16 @@
         <v>44418</v>
       </c>
       <c r="B5" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261023998260498</v>
       </c>
       <c r="C5" t="n">
-        <v>6.313934972202879</v>
+        <v>6.31393401046935</v>
       </c>
       <c r="D5" t="n">
-        <v>6.216933478623825</v>
+        <v>6.216932531665487</v>
       </c>
       <c r="E5" t="n">
-        <v>6.278661625357502</v>
+        <v>6.278660668996782</v>
       </c>
       <c r="F5" t="n">
         <v>9988600</v>
@@ -532,16 +532,16 @@
         <v>44419</v>
       </c>
       <c r="B6" t="n">
-        <v>6.058202743530273</v>
+        <v>6.058202266693115</v>
       </c>
       <c r="C6" t="n">
-        <v>6.296298035007707</v>
+        <v>6.296297539430225</v>
       </c>
       <c r="D6" t="n">
-        <v>5.996474599382589</v>
+        <v>5.996474127404013</v>
       </c>
       <c r="E6" t="n">
-        <v>6.287479908911514</v>
+        <v>6.287479414028101</v>
       </c>
       <c r="F6" t="n">
         <v>31978000</v>
@@ -552,16 +552,16 @@
         <v>44420</v>
       </c>
       <c r="B7" t="n">
-        <v>6.137568473815918</v>
+        <v>6.137568950653076</v>
       </c>
       <c r="C7" t="n">
-        <v>6.155205147916306</v>
+        <v>6.155205626123685</v>
       </c>
       <c r="D7" t="n">
-        <v>5.952383185516099</v>
+        <v>5.952383647965926</v>
       </c>
       <c r="E7" t="n">
-        <v>6.146386600620373</v>
+        <v>6.146387078142625</v>
       </c>
       <c r="F7" t="n">
         <v>17054100</v>
@@ -572,16 +572,16 @@
         <v>44421</v>
       </c>
       <c r="B8" t="n">
-        <v>6.181659698486328</v>
+        <v>6.181660175323486</v>
       </c>
       <c r="C8" t="n">
-        <v>6.208114496520329</v>
+        <v>6.208114975398141</v>
       </c>
       <c r="D8" t="n">
-        <v>6.049384446842026</v>
+        <v>6.049384913475816</v>
       </c>
       <c r="E8" t="n">
-        <v>6.155204479960894</v>
+        <v>6.155204954757366</v>
       </c>
       <c r="F8" t="n">
         <v>21141500</v>
@@ -592,16 +592,16 @@
         <v>44424</v>
       </c>
       <c r="B9" t="n">
-        <v>6.190478324890137</v>
+        <v>6.190478801727295</v>
       </c>
       <c r="C9" t="n">
-        <v>6.278661692952952</v>
+        <v>6.278662176582655</v>
       </c>
       <c r="D9" t="n">
-        <v>5.978838241539382</v>
+        <v>5.978838702074429</v>
       </c>
       <c r="E9" t="n">
-        <v>6.146386430612996</v>
+        <v>6.146386904053864</v>
       </c>
       <c r="F9" t="n">
         <v>13434600</v>
@@ -652,16 +652,16 @@
         <v>44427</v>
       </c>
       <c r="B12" t="n">
-        <v>6.111112594604492</v>
+        <v>6.11111307144165</v>
       </c>
       <c r="C12" t="n">
-        <v>6.111112594604492</v>
+        <v>6.11111307144165</v>
       </c>
       <c r="D12" t="n">
-        <v>5.661377243209458</v>
+        <v>5.66137768495472</v>
       </c>
       <c r="E12" t="n">
-        <v>5.908290654036534</v>
+        <v>5.908291115047926</v>
       </c>
       <c r="F12" t="n">
         <v>5423700</v>
@@ -672,16 +672,16 @@
         <v>44428</v>
       </c>
       <c r="B13" t="n">
-        <v>6.155205249786377</v>
+        <v>6.155204772949219</v>
       </c>
       <c r="C13" t="n">
-        <v>6.216933820405099</v>
+        <v>6.216933338785894</v>
       </c>
       <c r="D13" t="n">
-        <v>6.022929981598537</v>
+        <v>6.022929515008602</v>
       </c>
       <c r="E13" t="n">
-        <v>6.075840004775376</v>
+        <v>6.075839534086558</v>
       </c>
       <c r="F13" t="n">
         <v>3109200</v>
@@ -692,16 +692,16 @@
         <v>44431</v>
       </c>
       <c r="B14" t="n">
-        <v>6.32275390625</v>
+        <v>6.322752475738525</v>
       </c>
       <c r="C14" t="n">
-        <v>6.349208707757911</v>
+        <v>6.349207271261085</v>
       </c>
       <c r="D14" t="n">
-        <v>6.18166051023051</v>
+        <v>6.181659111641157</v>
       </c>
       <c r="E14" t="n">
-        <v>6.20811531173842</v>
+        <v>6.208113907163717</v>
       </c>
       <c r="F14" t="n">
         <v>6128800</v>
@@ -712,16 +712,16 @@
         <v>44432</v>
       </c>
       <c r="B15" t="n">
-        <v>6.39330005645752</v>
+        <v>6.393301010131836</v>
       </c>
       <c r="C15" t="n">
-        <v>6.525575314137689</v>
+        <v>6.525576287543212</v>
       </c>
       <c r="D15" t="n">
-        <v>6.331571490742386</v>
+        <v>6.33157243520879</v>
       </c>
       <c r="E15" t="n">
-        <v>6.384481509716164</v>
+        <v>6.384482462075037</v>
       </c>
       <c r="F15" t="n">
         <v>6054100</v>
@@ -732,16 +732,16 @@
         <v>44433</v>
       </c>
       <c r="B16" t="n">
-        <v>6.472665786743164</v>
+        <v>6.472664833068848</v>
       </c>
       <c r="C16" t="n">
-        <v>6.507939135404586</v>
+        <v>6.507938176533139</v>
       </c>
       <c r="D16" t="n">
-        <v>6.40211908942032</v>
+        <v>6.402118146140264</v>
       </c>
       <c r="E16" t="n">
-        <v>6.455029112412453</v>
+        <v>6.455028161336702</v>
       </c>
       <c r="F16" t="n">
         <v>5190100</v>
@@ -752,16 +752,16 @@
         <v>44434</v>
       </c>
       <c r="B17" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261023998260498</v>
       </c>
       <c r="C17" t="n">
-        <v>6.507938800343913</v>
+        <v>6.507937809059876</v>
       </c>
       <c r="D17" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261023998260498</v>
       </c>
       <c r="E17" t="n">
-        <v>6.472665453498537</v>
+        <v>6.472664467587308</v>
       </c>
       <c r="F17" t="n">
         <v>7968100</v>
@@ -772,16 +772,16 @@
         <v>44435</v>
       </c>
       <c r="B18" t="n">
-        <v>6.340390205383301</v>
+        <v>6.340390682220459</v>
       </c>
       <c r="C18" t="n">
-        <v>6.384481678783307</v>
+        <v>6.384482158936421</v>
       </c>
       <c r="D18" t="n">
-        <v>6.278661638033537</v>
+        <v>6.278662110228319</v>
       </c>
       <c r="E18" t="n">
-        <v>6.305116858466711</v>
+        <v>6.305117332651092</v>
       </c>
       <c r="F18" t="n">
         <v>5881000</v>
@@ -792,16 +792,16 @@
         <v>44438</v>
       </c>
       <c r="B19" t="n">
-        <v>6.269844532012939</v>
+        <v>6.269843101501465</v>
       </c>
       <c r="C19" t="n">
-        <v>6.419756491053442</v>
+        <v>6.419755026338443</v>
       </c>
       <c r="D19" t="n">
-        <v>6.252207855684147</v>
+        <v>6.252206429196611</v>
       </c>
       <c r="E19" t="n">
-        <v>6.393301266314487</v>
+        <v>6.393299807635444</v>
       </c>
       <c r="F19" t="n">
         <v>4966000</v>
@@ -812,16 +812,16 @@
         <v>44439</v>
       </c>
       <c r="B20" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261023998260498</v>
       </c>
       <c r="C20" t="n">
-        <v>6.305116845737266</v>
+        <v>6.305115885346908</v>
       </c>
       <c r="D20" t="n">
-        <v>6.181660131778449</v>
+        <v>6.181659190192918</v>
       </c>
       <c r="E20" t="n">
-        <v>6.305116845737266</v>
+        <v>6.305115885346908</v>
       </c>
       <c r="F20" t="n">
         <v>3704100</v>
@@ -832,16 +832,16 @@
         <v>44440</v>
       </c>
       <c r="B21" t="n">
-        <v>6.234570503234863</v>
+        <v>6.234570026397705</v>
       </c>
       <c r="C21" t="n">
-        <v>6.305117200899455</v>
+        <v>6.305116718666691</v>
       </c>
       <c r="D21" t="n">
-        <v>6.199297154402568</v>
+        <v>6.199296680263212</v>
       </c>
       <c r="E21" t="n">
-        <v>6.261025304613343</v>
+        <v>6.261024825752847</v>
       </c>
       <c r="F21" t="n">
         <v>6468600</v>
@@ -852,16 +852,16 @@
         <v>44441</v>
       </c>
       <c r="B22" t="n">
-        <v>5.996474266052246</v>
+        <v>5.996474742889404</v>
       </c>
       <c r="C22" t="n">
-        <v>6.252206215997954</v>
+        <v>6.252206713170811</v>
       </c>
       <c r="D22" t="n">
-        <v>5.970019048251363</v>
+        <v>5.970019522984813</v>
       </c>
       <c r="E22" t="n">
-        <v>6.234569544294506</v>
+        <v>6.234570040064902</v>
       </c>
       <c r="F22" t="n">
         <v>3746900</v>
@@ -892,16 +892,16 @@
         <v>44445</v>
       </c>
       <c r="B24" t="n">
-        <v>6.111112594604492</v>
+        <v>6.11111307144165</v>
       </c>
       <c r="C24" t="n">
-        <v>6.190477829758912</v>
+        <v>6.190478312788771</v>
       </c>
       <c r="D24" t="n">
-        <v>6.067021124345374</v>
+        <v>6.067021597742168</v>
       </c>
       <c r="E24" t="n">
-        <v>6.119931140951175</v>
+        <v>6.119931618476427</v>
       </c>
       <c r="F24" t="n">
         <v>1654400</v>
@@ -912,16 +912,16 @@
         <v>44447</v>
       </c>
       <c r="B25" t="n">
-        <v>5.758379936218262</v>
+        <v>5.758378982543945</v>
       </c>
       <c r="C25" t="n">
-        <v>6.11111342838262</v>
+        <v>6.111112416290331</v>
       </c>
       <c r="D25" t="n">
-        <v>5.661378015627318</v>
+        <v>5.661377078017978</v>
       </c>
       <c r="E25" t="n">
-        <v>6.11111342838262</v>
+        <v>6.111112416290331</v>
       </c>
       <c r="F25" t="n">
         <v>10251100</v>
@@ -992,16 +992,16 @@
         <v>44453</v>
       </c>
       <c r="B29" t="n">
-        <v>6.340390205383301</v>
+        <v>6.340390682220459</v>
       </c>
       <c r="C29" t="n">
-        <v>6.507938813482836</v>
+        <v>6.507939302920701</v>
       </c>
       <c r="D29" t="n">
-        <v>6.225751617658651</v>
+        <v>6.225752085874268</v>
       </c>
       <c r="E29" t="n">
-        <v>6.225751617658651</v>
+        <v>6.225752085874268</v>
       </c>
       <c r="F29" t="n">
         <v>9730300</v>
@@ -1012,16 +1012,16 @@
         <v>44454</v>
       </c>
       <c r="B30" t="n">
-        <v>6.384480953216553</v>
+        <v>6.384481906890869</v>
       </c>
       <c r="C30" t="n">
-        <v>6.50793807388575</v>
+        <v>6.507939046001328</v>
       </c>
       <c r="D30" t="n">
-        <v>6.296297595946708</v>
+        <v>6.29629853644874</v>
       </c>
       <c r="E30" t="n">
-        <v>6.384480953216553</v>
+        <v>6.384481906890869</v>
       </c>
       <c r="F30" t="n">
         <v>7265900</v>
@@ -1052,16 +1052,16 @@
         <v>44456</v>
       </c>
       <c r="B32" t="n">
-        <v>6.384480953216553</v>
+        <v>6.384481906890869</v>
       </c>
       <c r="C32" t="n">
-        <v>6.384480953216553</v>
+        <v>6.384481906890869</v>
       </c>
       <c r="D32" t="n">
-        <v>5.978837509775269</v>
+        <v>5.978838402857074</v>
       </c>
       <c r="E32" t="n">
-        <v>6.26102425303877</v>
+        <v>6.261025188271888</v>
       </c>
       <c r="F32" t="n">
         <v>16008100</v>
@@ -1072,16 +1072,16 @@
         <v>44459</v>
       </c>
       <c r="B33" t="n">
-        <v>6.269844532012939</v>
+        <v>6.269843101501465</v>
       </c>
       <c r="C33" t="n">
-        <v>6.322754560999317</v>
+        <v>6.322753118416027</v>
       </c>
       <c r="D33" t="n">
-        <v>6.06702254398606</v>
+        <v>6.067021159749924</v>
       </c>
       <c r="E33" t="n">
-        <v>6.164024053548653</v>
+        <v>6.164022647180904</v>
       </c>
       <c r="F33" t="n">
         <v>9065700</v>
@@ -1092,16 +1092,16 @@
         <v>44460</v>
       </c>
       <c r="B34" t="n">
-        <v>6.419754981994629</v>
+        <v>6.419755935668945</v>
       </c>
       <c r="C34" t="n">
-        <v>6.525575015092812</v>
+        <v>6.52557598448702</v>
       </c>
       <c r="D34" t="n">
-        <v>6.269843058193152</v>
+        <v>6.269843989597592</v>
       </c>
       <c r="E34" t="n">
-        <v>6.349207872771073</v>
+        <v>6.3492088159654</v>
       </c>
       <c r="F34" t="n">
         <v>11102500</v>
@@ -1192,16 +1192,16 @@
         <v>44467</v>
       </c>
       <c r="B39" t="n">
-        <v>6.119932174682617</v>
+        <v>6.119931221008301</v>
       </c>
       <c r="C39" t="n">
-        <v>6.278662251311475</v>
+        <v>6.278661272902115</v>
       </c>
       <c r="D39" t="n">
-        <v>6.119932174682617</v>
+        <v>6.119931221008301</v>
       </c>
       <c r="E39" t="n">
-        <v>6.261025576130491</v>
+        <v>6.261024600469469</v>
       </c>
       <c r="F39" t="n">
         <v>6782400</v>
@@ -1212,16 +1212,16 @@
         <v>44468</v>
       </c>
       <c r="B40" t="n">
-        <v>6.040566444396973</v>
+        <v>6.040565967559814</v>
       </c>
       <c r="C40" t="n">
-        <v>6.252206950182298</v>
+        <v>6.25220645663842</v>
       </c>
       <c r="D40" t="n">
-        <v>6.040566444396973</v>
+        <v>6.040565967559814</v>
       </c>
       <c r="E40" t="n">
-        <v>6.216933602633323</v>
+        <v>6.216933111873892</v>
       </c>
       <c r="F40" t="n">
         <v>6482600</v>
@@ -1232,16 +1232,16 @@
         <v>44469</v>
       </c>
       <c r="B41" t="n">
-        <v>6.261024951934814</v>
+        <v>6.261023998260498</v>
       </c>
       <c r="C41" t="n">
-        <v>6.349208319048255</v>
+        <v>6.349207351941919</v>
       </c>
       <c r="D41" t="n">
-        <v>6.058202997328168</v>
+        <v>6.05820207454753</v>
       </c>
       <c r="E41" t="n">
-        <v>6.084658217707932</v>
+        <v>6.084657290897655</v>
       </c>
       <c r="F41" t="n">
         <v>15990100</v>
@@ -1252,16 +1252,16 @@
         <v>44470</v>
       </c>
       <c r="B42" t="n">
-        <v>6.499119758605957</v>
+        <v>6.499120712280273</v>
       </c>
       <c r="C42" t="n">
-        <v>6.569666446925959</v>
+        <v>6.569667410952226</v>
       </c>
       <c r="D42" t="n">
-        <v>6.331571163600236</v>
+        <v>6.331572092688639</v>
       </c>
       <c r="E42" t="n">
-        <v>6.331571163600236</v>
+        <v>6.331572092688639</v>
       </c>
       <c r="F42" t="n">
         <v>15528000</v>
@@ -1272,16 +1272,16 @@
         <v>44473</v>
       </c>
       <c r="B43" t="n">
-        <v>6.190478324890137</v>
+        <v>6.190478801727295</v>
       </c>
       <c r="C43" t="n">
-        <v>6.552030344193411</v>
+        <v>6.552030848880022</v>
       </c>
       <c r="D43" t="n">
-        <v>6.190478324890137</v>
+        <v>6.190478801727295</v>
       </c>
       <c r="E43" t="n">
-        <v>6.5255755440203</v>
+        <v>6.525576046669164</v>
       </c>
       <c r="F43" t="n">
         <v>12019000</v>
@@ -1292,16 +1292,16 @@
         <v>44474</v>
       </c>
       <c r="B44" t="n">
-        <v>6.287479877471924</v>
+        <v>6.287480354309082</v>
       </c>
       <c r="C44" t="n">
-        <v>6.366844693906587</v>
+        <v>6.366845176762705</v>
       </c>
       <c r="D44" t="n">
-        <v>6.2433879857371</v>
+        <v>6.243388459230366</v>
       </c>
       <c r="E44" t="n">
-        <v>6.296298003524023</v>
+        <v>6.29629848102994</v>
       </c>
       <c r="F44" t="n">
         <v>12888200</v>
@@ -1352,16 +1352,16 @@
         <v>44477</v>
       </c>
       <c r="B47" t="n">
-        <v>6.310670375823975</v>
+        <v>6.310671329498291</v>
       </c>
       <c r="C47" t="n">
-        <v>6.655371168427701</v>
+        <v>6.655372174193518</v>
       </c>
       <c r="D47" t="n">
-        <v>6.292993444520037</v>
+        <v>6.292994395522999</v>
       </c>
       <c r="E47" t="n">
-        <v>6.36370116973579</v>
+        <v>6.363702131424168</v>
       </c>
       <c r="F47" t="n">
         <v>20480700</v>
@@ -1372,16 +1372,16 @@
         <v>44480</v>
       </c>
       <c r="B48" t="n">
-        <v>6.213447570800781</v>
+        <v>6.213448524475098</v>
       </c>
       <c r="C48" t="n">
-        <v>6.407893818474543</v>
+        <v>6.407894801993546</v>
       </c>
       <c r="D48" t="n">
-        <v>6.213447570800781</v>
+        <v>6.213448524475098</v>
       </c>
       <c r="E48" t="n">
-        <v>6.363701278732132</v>
+        <v>6.363702255468219</v>
       </c>
       <c r="F48" t="n">
         <v>10407400</v>
@@ -1392,16 +1392,16 @@
         <v>44482</v>
       </c>
       <c r="B49" t="n">
-        <v>6.231125354766846</v>
+        <v>6.231125831604004</v>
       </c>
       <c r="C49" t="n">
-        <v>6.292994413127774</v>
+        <v>6.292994894699465</v>
       </c>
       <c r="D49" t="n">
-        <v>6.213448420742101</v>
+        <v>6.213448896226532</v>
       </c>
       <c r="E49" t="n">
-        <v>6.248802288791589</v>
+        <v>6.248802766981476</v>
       </c>
       <c r="F49" t="n">
         <v>8146000</v>
@@ -1472,16 +1472,16 @@
         <v>44488</v>
       </c>
       <c r="B53" t="n">
-        <v>5.91294002532959</v>
+        <v>5.912938594818115</v>
       </c>
       <c r="C53" t="n">
-        <v>6.186932709011659</v>
+        <v>6.186931212213417</v>
       </c>
       <c r="D53" t="n">
-        <v>5.895263091590468</v>
+        <v>5.895261665355555</v>
       </c>
       <c r="E53" t="n">
-        <v>6.169255775272537</v>
+        <v>6.169254282750857</v>
       </c>
       <c r="F53" t="n">
         <v>11473400</v>
@@ -1492,16 +1492,16 @@
         <v>44489</v>
       </c>
       <c r="B54" t="n">
-        <v>5.904100894927979</v>
+        <v>5.904101371765137</v>
       </c>
       <c r="C54" t="n">
-        <v>6.045516775446618</v>
+        <v>6.045517263705048</v>
       </c>
       <c r="D54" t="n">
-        <v>5.842231842311679</v>
+        <v>5.842232314152062</v>
       </c>
       <c r="E54" t="n">
-        <v>6.010162910679786</v>
+        <v>6.010163396082907</v>
       </c>
       <c r="F54" t="n">
         <v>6234400</v>
@@ -1532,16 +1532,16 @@
         <v>44491</v>
       </c>
       <c r="B56" t="n">
-        <v>5.630108833312988</v>
+        <v>5.63010835647583</v>
       </c>
       <c r="C56" t="n">
-        <v>5.656624445444495</v>
+        <v>5.656623966361621</v>
       </c>
       <c r="D56" t="n">
-        <v>5.197023732958769</v>
+        <v>5.197023292801376</v>
       </c>
       <c r="E56" t="n">
-        <v>5.603593642632838</v>
+        <v>5.60359316804136</v>
       </c>
       <c r="F56" t="n">
         <v>18890200</v>
@@ -1552,16 +1552,16 @@
         <v>44494</v>
       </c>
       <c r="B57" t="n">
-        <v>5.859909057617188</v>
+        <v>5.859908580780029</v>
       </c>
       <c r="C57" t="n">
-        <v>5.877585990854064</v>
+        <v>5.877585512578483</v>
       </c>
       <c r="D57" t="n">
-        <v>5.550562515246201</v>
+        <v>5.550562063581435</v>
       </c>
       <c r="E57" t="n">
-        <v>5.683139303797101</v>
+        <v>5.683138841344191</v>
       </c>
       <c r="F57" t="n">
         <v>11428100</v>
@@ -1572,16 +1572,16 @@
         <v>44495</v>
       </c>
       <c r="B58" t="n">
-        <v>5.81571626663208</v>
+        <v>5.815716743469238</v>
       </c>
       <c r="C58" t="n">
-        <v>5.868747064088904</v>
+        <v>5.868747545274117</v>
       </c>
       <c r="D58" t="n">
-        <v>5.683139062264364</v>
+        <v>5.683139528231368</v>
       </c>
       <c r="E58" t="n">
-        <v>5.833393199117688</v>
+        <v>5.833393677404199</v>
       </c>
       <c r="F58" t="n">
         <v>8470300</v>
@@ -1592,16 +1592,16 @@
         <v>44496</v>
       </c>
       <c r="B59" t="n">
-        <v>5.859909057617188</v>
+        <v>5.859908580780029</v>
       </c>
       <c r="C59" t="n">
-        <v>5.96597065703844</v>
+        <v>5.965970171570753</v>
       </c>
       <c r="D59" t="n">
-        <v>5.789201324669686</v>
+        <v>5.789200853586213</v>
       </c>
       <c r="E59" t="n">
-        <v>5.833393447036208</v>
+        <v>5.833392972356699</v>
       </c>
       <c r="F59" t="n">
         <v>7675900</v>
@@ -1672,16 +1672,16 @@
         <v>44503</v>
       </c>
       <c r="B63" t="n">
-        <v>6.09854793548584</v>
+        <v>6.098547458648682</v>
       </c>
       <c r="C63" t="n">
-        <v>6.186932602662175</v>
+        <v>6.186932118914339</v>
       </c>
       <c r="D63" t="n">
-        <v>5.921778179681833</v>
+        <v>5.92177771666606</v>
       </c>
       <c r="E63" t="n">
-        <v>5.983647657430936</v>
+        <v>5.983647189577673</v>
       </c>
       <c r="F63" t="n">
         <v>5711600</v>
@@ -1692,16 +1692,16 @@
         <v>44504</v>
       </c>
       <c r="B64" t="n">
-        <v>5.965970039367676</v>
+        <v>5.965970516204834</v>
       </c>
       <c r="C64" t="n">
-        <v>6.160416284841832</v>
+        <v>6.160416777220335</v>
       </c>
       <c r="D64" t="n">
-        <v>5.842231519520484</v>
+        <v>5.842231986467696</v>
       </c>
       <c r="E64" t="n">
-        <v>6.098547235643882</v>
+        <v>6.098547723077428</v>
       </c>
       <c r="F64" t="n">
         <v>8687600</v>
@@ -1712,16 +1712,16 @@
         <v>44505</v>
       </c>
       <c r="B65" t="n">
-        <v>5.965970039367676</v>
+        <v>5.965970516204834</v>
       </c>
       <c r="C65" t="n">
-        <v>6.054354696401384</v>
+        <v>6.054355180302789</v>
       </c>
       <c r="D65" t="n">
-        <v>5.939454431531919</v>
+        <v>5.939454906249786</v>
       </c>
       <c r="E65" t="n">
-        <v>6.001323902181158</v>
+        <v>6.001324381844015</v>
       </c>
       <c r="F65" t="n">
         <v>3123600</v>
@@ -1732,16 +1732,16 @@
         <v>44508</v>
       </c>
       <c r="B66" t="n">
-        <v>5.983648300170898</v>
+        <v>5.98364782333374</v>
       </c>
       <c r="C66" t="n">
-        <v>6.03667910617306</v>
+        <v>6.036678625109875</v>
       </c>
       <c r="D66" t="n">
-        <v>5.939455751110073</v>
+        <v>5.93945527779462</v>
       </c>
       <c r="E66" t="n">
-        <v>6.010163913897671</v>
+        <v>6.010163434947482</v>
       </c>
       <c r="F66" t="n">
         <v>3898000</v>
@@ -1752,16 +1752,16 @@
         <v>44509</v>
       </c>
       <c r="B67" t="n">
-        <v>5.948294162750244</v>
+        <v>5.948293685913086</v>
       </c>
       <c r="C67" t="n">
-        <v>6.169256055242525</v>
+        <v>6.169255560692247</v>
       </c>
       <c r="D67" t="n">
-        <v>5.948294162750244</v>
+        <v>5.948293685913086</v>
       </c>
       <c r="E67" t="n">
-        <v>5.992486709829246</v>
+        <v>5.99248622944945</v>
       </c>
       <c r="F67" t="n">
         <v>5176300</v>
@@ -1792,16 +1792,16 @@
         <v>44511</v>
       </c>
       <c r="B69" t="n">
-        <v>6.010162830352783</v>
+        <v>6.0101637840271</v>
       </c>
       <c r="C69" t="n">
-        <v>6.036678017847871</v>
+        <v>6.036678975729536</v>
       </c>
       <c r="D69" t="n">
-        <v>5.806877899934787</v>
+        <v>5.80687882135247</v>
       </c>
       <c r="E69" t="n">
-        <v>5.833393087429874</v>
+        <v>5.833394013054906</v>
       </c>
       <c r="F69" t="n">
         <v>8604300</v>
@@ -1832,16 +1832,16 @@
         <v>44516</v>
       </c>
       <c r="B71" t="n">
-        <v>5.320761680603027</v>
+        <v>5.320762157440186</v>
       </c>
       <c r="C71" t="n">
-        <v>5.815716206536877</v>
+        <v>5.815716727730977</v>
       </c>
       <c r="D71" t="n">
-        <v>5.223538342211159</v>
+        <v>5.223538810335335</v>
       </c>
       <c r="E71" t="n">
-        <v>5.789201018808111</v>
+        <v>5.789201537625966</v>
       </c>
       <c r="F71" t="n">
         <v>27445700</v>
@@ -1852,16 +1852,16 @@
         <v>44517</v>
       </c>
       <c r="B72" t="n">
-        <v>5.170506954193115</v>
+        <v>5.17050838470459</v>
       </c>
       <c r="C72" t="n">
-        <v>5.462176514572795</v>
+        <v>5.462178025779772</v>
       </c>
       <c r="D72" t="n">
-        <v>5.00257590578788</v>
+        <v>5.002577289838284</v>
       </c>
       <c r="E72" t="n">
-        <v>5.364953608747077</v>
+        <v>5.364955093055631</v>
       </c>
       <c r="F72" t="n">
         <v>24600900</v>
@@ -1872,16 +1872,16 @@
         <v>44518</v>
       </c>
       <c r="B73" t="n">
-        <v>5.161669731140137</v>
+        <v>5.161669254302979</v>
       </c>
       <c r="C73" t="n">
-        <v>5.338439069281368</v>
+        <v>5.338438576114187</v>
       </c>
       <c r="D73" t="n">
-        <v>5.073284640618174</v>
+        <v>5.073284171946066</v>
       </c>
       <c r="E73" t="n">
-        <v>5.214700532582506</v>
+        <v>5.214700050846341</v>
       </c>
       <c r="F73" t="n">
         <v>17735600</v>
@@ -1912,16 +1912,16 @@
         <v>44522</v>
       </c>
       <c r="B75" t="n">
-        <v>4.976061344146729</v>
+        <v>4.976062297821045</v>
       </c>
       <c r="C75" t="n">
-        <v>5.32960041550615</v>
+        <v>5.329601436937094</v>
       </c>
       <c r="D75" t="n">
-        <v>4.976061344146729</v>
+        <v>4.976062297821045</v>
       </c>
       <c r="E75" t="n">
-        <v>5.232377076055763</v>
+        <v>5.232378078853616</v>
       </c>
       <c r="F75" t="n">
         <v>8516000</v>
@@ -1932,16 +1932,16 @@
         <v>44523</v>
       </c>
       <c r="B76" t="n">
-        <v>5.011415481567383</v>
+        <v>5.011415958404541</v>
       </c>
       <c r="C76" t="n">
-        <v>5.099800148849164</v>
+        <v>5.09980063409614</v>
       </c>
       <c r="D76" t="n">
-        <v>4.781614925183414</v>
+        <v>4.781615380155004</v>
       </c>
       <c r="E76" t="n">
-        <v>5.002576804113536</v>
+        <v>5.002577280109692</v>
       </c>
       <c r="F76" t="n">
         <v>9084200</v>
@@ -1972,16 +1972,16 @@
         <v>44525</v>
       </c>
       <c r="B78" t="n">
-        <v>5.37379264831543</v>
+        <v>5.373793125152588</v>
       </c>
       <c r="C78" t="n">
-        <v>5.37379264831543</v>
+        <v>5.373793125152588</v>
       </c>
       <c r="D78" t="n">
-        <v>4.799291698032407</v>
+        <v>4.799292123891901</v>
       </c>
       <c r="E78" t="n">
-        <v>4.949545838108879</v>
+        <v>4.949546277300996</v>
       </c>
       <c r="F78" t="n">
         <v>20546100</v>
@@ -1992,16 +1992,16 @@
         <v>44526</v>
       </c>
       <c r="B79" t="n">
-        <v>5.223538398742676</v>
+        <v>5.223539352416992</v>
       </c>
       <c r="C79" t="n">
-        <v>5.338438670680995</v>
+        <v>5.338439645332938</v>
       </c>
       <c r="D79" t="n">
-        <v>5.020253464333078</v>
+        <v>5.020254380893162</v>
       </c>
       <c r="E79" t="n">
-        <v>5.037930396827334</v>
+        <v>5.037931316614738</v>
       </c>
       <c r="F79" t="n">
         <v>8564200</v>
@@ -2032,16 +2032,16 @@
         <v>44530</v>
       </c>
       <c r="B81" t="n">
-        <v>4.825808048248291</v>
+        <v>4.825807571411133</v>
       </c>
       <c r="C81" t="n">
-        <v>5.12631637449386</v>
+        <v>5.126315867963532</v>
       </c>
       <c r="D81" t="n">
-        <v>4.790454177096034</v>
+        <v>4.790453703752186</v>
       </c>
       <c r="E81" t="n">
-        <v>5.073285146314087</v>
+        <v>5.073284645023764</v>
       </c>
       <c r="F81" t="n">
         <v>11282700</v>
@@ -2052,16 +2052,16 @@
         <v>44531</v>
       </c>
       <c r="B82" t="n">
-        <v>4.852322101593018</v>
+        <v>4.852323055267334</v>
       </c>
       <c r="C82" t="n">
-        <v>5.152830357281196</v>
+        <v>5.152831370017339</v>
       </c>
       <c r="D82" t="n">
-        <v>4.852322101593018</v>
+        <v>4.852323055267334</v>
       </c>
       <c r="E82" t="n">
-        <v>4.896514640882911</v>
+        <v>4.896515603242819</v>
       </c>
       <c r="F82" t="n">
         <v>12492100</v>
@@ -2092,16 +2092,16 @@
         <v>44533</v>
       </c>
       <c r="B84" t="n">
-        <v>5.320761680603027</v>
+        <v>5.320762157440186</v>
       </c>
       <c r="C84" t="n">
-        <v>5.329600357480157</v>
+        <v>5.329600835109421</v>
       </c>
       <c r="D84" t="n">
-        <v>4.97606128996989</v>
+        <v>4.976061735915614</v>
       </c>
       <c r="E84" t="n">
-        <v>5.020253410001604</v>
+        <v>5.020253859907747</v>
       </c>
       <c r="F84" t="n">
         <v>10548200</v>
@@ -2112,16 +2112,16 @@
         <v>44536</v>
       </c>
       <c r="B85" t="n">
-        <v>5.152831077575684</v>
+        <v>5.152830600738525</v>
       </c>
       <c r="C85" t="n">
-        <v>5.417985507477384</v>
+        <v>5.417985006103135</v>
       </c>
       <c r="D85" t="n">
-        <v>5.152831077575684</v>
+        <v>5.152830600738525</v>
       </c>
       <c r="E85" t="n">
-        <v>5.373792962009984</v>
+        <v>5.373792464725264</v>
       </c>
       <c r="F85" t="n">
         <v>5884400</v>
@@ -2192,16 +2192,16 @@
         <v>44540</v>
       </c>
       <c r="B89" t="n">
-        <v>5.44450044631958</v>
+        <v>5.444501399993896</v>
       </c>
       <c r="C89" t="n">
-        <v>5.568239399336901</v>
+        <v>5.568240374685687</v>
       </c>
       <c r="D89" t="n">
-        <v>5.241215505164072</v>
+        <v>5.241216423230415</v>
       </c>
       <c r="E89" t="n">
-        <v>5.267731115511021</v>
+        <v>5.267732038221914</v>
       </c>
       <c r="F89" t="n">
         <v>8741300</v>
@@ -2232,16 +2232,16 @@
         <v>44544</v>
       </c>
       <c r="B91" t="n">
-        <v>5.453338623046875</v>
+        <v>5.453339099884033</v>
       </c>
       <c r="C91" t="n">
-        <v>5.603592751168627</v>
+        <v>5.60359324114393</v>
       </c>
       <c r="D91" t="n">
-        <v>5.426823015133682</v>
+        <v>5.426823489652329</v>
       </c>
       <c r="E91" t="n">
-        <v>5.497530740967144</v>
+        <v>5.497531221668439</v>
       </c>
       <c r="F91" t="n">
         <v>6640900</v>
@@ -2272,16 +2272,16 @@
         <v>44546</v>
       </c>
       <c r="B93" t="n">
-        <v>5.400308132171631</v>
+        <v>5.400308609008789</v>
       </c>
       <c r="C93" t="n">
-        <v>5.550562268737735</v>
+        <v>5.550562758842054</v>
       </c>
       <c r="D93" t="n">
-        <v>5.347277334816178</v>
+        <v>5.347277806970816</v>
       </c>
       <c r="E93" t="n">
-        <v>5.515207982382787</v>
+        <v>5.515208469365389</v>
       </c>
       <c r="F93" t="n">
         <v>9238300</v>
@@ -2312,16 +2312,16 @@
         <v>44550</v>
       </c>
       <c r="B95" t="n">
-        <v>5.143992900848389</v>
+        <v>5.143991947174072</v>
       </c>
       <c r="C95" t="n">
-        <v>5.179346769188129</v>
+        <v>5.179345808959355</v>
       </c>
       <c r="D95" t="n">
-        <v>4.949546203528466</v>
+        <v>4.949545285903736</v>
       </c>
       <c r="E95" t="n">
-        <v>5.179346769188129</v>
+        <v>5.179345808959355</v>
       </c>
       <c r="F95" t="n">
         <v>8433600</v>
@@ -2352,16 +2352,16 @@
         <v>44552</v>
       </c>
       <c r="B97" t="n">
-        <v>5.011415481567383</v>
+        <v>5.011415958404541</v>
       </c>
       <c r="C97" t="n">
-        <v>5.073284537938961</v>
+        <v>5.073285020662972</v>
       </c>
       <c r="D97" t="n">
-        <v>4.914192136831755</v>
+        <v>4.914192604418092</v>
       </c>
       <c r="E97" t="n">
-        <v>5.055607604482605</v>
+        <v>5.055608085524652</v>
       </c>
       <c r="F97" t="n">
         <v>4649500</v>
@@ -2372,16 +2372,16 @@
         <v>44553</v>
       </c>
       <c r="B98" t="n">
-        <v>5.055606842041016</v>
+        <v>5.055607318878174</v>
       </c>
       <c r="C98" t="n">
-        <v>5.073283772831495</v>
+        <v>5.073284251335914</v>
       </c>
       <c r="D98" t="n">
-        <v>4.96722218808862</v>
+        <v>4.967222656589472</v>
       </c>
       <c r="E98" t="n">
-        <v>4.993737794999975</v>
+        <v>4.993738266001739</v>
       </c>
       <c r="F98" t="n">
         <v>3174500</v>
@@ -2452,16 +2452,16 @@
         <v>44560</v>
       </c>
       <c r="B102" t="n">
-        <v>5.700815677642822</v>
+        <v>5.700816631317139</v>
       </c>
       <c r="C102" t="n">
-        <v>5.709654354119633</v>
+        <v>5.709655309272549</v>
       </c>
       <c r="D102" t="n">
-        <v>5.258891968633261</v>
+        <v>5.258892848379334</v>
       </c>
       <c r="E102" t="n">
-        <v>5.320761439617065</v>
+        <v>5.320762329713117</v>
       </c>
       <c r="F102" t="n">
         <v>23096200</v>
@@ -2472,16 +2472,16 @@
         <v>44564</v>
       </c>
       <c r="B103" t="n">
-        <v>5.541723728179932</v>
+        <v>5.541724681854248</v>
       </c>
       <c r="C103" t="n">
-        <v>5.745008667104768</v>
+        <v>5.745009655762357</v>
       </c>
       <c r="D103" t="n">
-        <v>5.506369862406162</v>
+        <v>5.506370809996437</v>
       </c>
       <c r="E103" t="n">
-        <v>5.691977868444114</v>
+        <v>5.691978847975641</v>
       </c>
       <c r="F103" t="n">
         <v>7451800</v>
@@ -2552,16 +2552,16 @@
         <v>44568</v>
       </c>
       <c r="B107" t="n">
-        <v>5.163622856140137</v>
+        <v>5.16362190246582</v>
       </c>
       <c r="C107" t="n">
-        <v>5.278961186075115</v>
+        <v>5.278960211098854</v>
       </c>
       <c r="D107" t="n">
-        <v>4.941817757177995</v>
+        <v>4.941816844469068</v>
       </c>
       <c r="E107" t="n">
-        <v>4.977306539167166</v>
+        <v>4.977305619903783</v>
       </c>
       <c r="F107" t="n">
         <v>10961100</v>
@@ -2572,16 +2572,16 @@
         <v>44571</v>
       </c>
       <c r="B108" t="n">
-        <v>5.057155609130859</v>
+        <v>5.057156085968018</v>
       </c>
       <c r="C108" t="n">
-        <v>5.128133589460298</v>
+        <v>5.128134072989941</v>
       </c>
       <c r="D108" t="n">
-        <v>4.906328511462285</v>
+        <v>4.906328974078017</v>
       </c>
       <c r="E108" t="n">
-        <v>5.057155609130859</v>
+        <v>5.057156085968018</v>
       </c>
       <c r="F108" t="n">
         <v>11253600</v>
@@ -2652,16 +2652,16 @@
         <v>44575</v>
       </c>
       <c r="B112" t="n">
-        <v>5.491894245147705</v>
+        <v>5.491893291473389</v>
       </c>
       <c r="C112" t="n">
-        <v>5.500766229024832</v>
+        <v>5.500765273809884</v>
       </c>
       <c r="D112" t="n">
-        <v>5.332194727822603</v>
+        <v>5.332193801880308</v>
       </c>
       <c r="E112" t="n">
-        <v>5.420916681892105</v>
+        <v>5.420915740543131</v>
       </c>
       <c r="F112" t="n">
         <v>4745900</v>
@@ -2732,16 +2732,16 @@
         <v>44581</v>
       </c>
       <c r="B116" t="n">
-        <v>5.713699817657471</v>
+        <v>5.713698387145996</v>
       </c>
       <c r="C116" t="n">
-        <v>5.837910563698375</v>
+        <v>5.837909102088854</v>
       </c>
       <c r="D116" t="n">
-        <v>5.633849840815619</v>
+        <v>5.633848430295799</v>
       </c>
       <c r="E116" t="n">
-        <v>5.651594233107177</v>
+        <v>5.651592818144779</v>
       </c>
       <c r="F116" t="n">
         <v>9343500</v>
@@ -2752,16 +2752,16 @@
         <v>44582</v>
       </c>
       <c r="B117" t="n">
-        <v>5.527383327484131</v>
+        <v>5.527382373809814</v>
       </c>
       <c r="C117" t="n">
-        <v>5.687082853497435</v>
+        <v>5.687081872269151</v>
       </c>
       <c r="D117" t="n">
-        <v>5.483022136506155</v>
+        <v>5.483021190485755</v>
       </c>
       <c r="E117" t="n">
-        <v>5.678210869137642</v>
+        <v>5.678209889440098</v>
       </c>
       <c r="F117" t="n">
         <v>7609900</v>
@@ -2772,16 +2772,16 @@
         <v>44585</v>
       </c>
       <c r="B118" t="n">
-        <v>5.456405639648438</v>
+        <v>5.456405162811279</v>
       </c>
       <c r="C118" t="n">
-        <v>5.491894422421788</v>
+        <v>5.491893942483253</v>
       </c>
       <c r="D118" t="n">
-        <v>5.349939291328385</v>
+        <v>5.349938823795358</v>
       </c>
       <c r="E118" t="n">
-        <v>5.465277623811945</v>
+        <v>5.465277146199461</v>
       </c>
       <c r="F118" t="n">
         <v>8531700</v>
@@ -2792,16 +2792,16 @@
         <v>44586</v>
       </c>
       <c r="B119" t="n">
-        <v>5.500766277313232</v>
+        <v>5.500765800476074</v>
       </c>
       <c r="C119" t="n">
-        <v>5.57174426425156</v>
+        <v>5.571743781261634</v>
       </c>
       <c r="D119" t="n">
-        <v>5.36768355657054</v>
+        <v>5.367683091269735</v>
       </c>
       <c r="E119" t="n">
-        <v>5.394299931495218</v>
+        <v>5.394299463887157</v>
       </c>
       <c r="F119" t="n">
         <v>8097000</v>
@@ -2832,16 +2832,16 @@
         <v>44588</v>
       </c>
       <c r="B121" t="n">
-        <v>5.545126438140869</v>
+        <v>5.545126914978027</v>
       </c>
       <c r="C121" t="n">
-        <v>5.749187107986836</v>
+        <v>5.749187602371603</v>
       </c>
       <c r="D121" t="n">
-        <v>5.527382050461201</v>
+        <v>5.527382525772483</v>
       </c>
       <c r="E121" t="n">
-        <v>5.580615213500205</v>
+        <v>5.580615693389118</v>
       </c>
       <c r="F121" t="n">
         <v>8501200</v>
@@ -2852,16 +2852,16 @@
         <v>44589</v>
       </c>
       <c r="B122" t="n">
-        <v>5.660466194152832</v>
+        <v>5.660465717315674</v>
       </c>
       <c r="C122" t="n">
-        <v>5.731443757718693</v>
+        <v>5.731443274902391</v>
       </c>
       <c r="D122" t="n">
-        <v>5.509638660045554</v>
+        <v>5.509638195914094</v>
       </c>
       <c r="E122" t="n">
-        <v>5.509638660045554</v>
+        <v>5.509638195914094</v>
       </c>
       <c r="F122" t="n">
         <v>15566700</v>
@@ -2872,16 +2872,16 @@
         <v>44592</v>
       </c>
       <c r="B123" t="n">
-        <v>5.6959547996521</v>
+        <v>5.695954322814941</v>
       </c>
       <c r="C123" t="n">
-        <v>5.793549158064543</v>
+        <v>5.793548673057267</v>
       </c>
       <c r="D123" t="n">
-        <v>5.571744067256032</v>
+        <v>5.571743600817181</v>
       </c>
       <c r="E123" t="n">
-        <v>5.607232847940623</v>
+        <v>5.607232378530827</v>
       </c>
       <c r="F123" t="n">
         <v>7514700</v>
@@ -2892,16 +2892,16 @@
         <v>44593</v>
       </c>
       <c r="B124" t="n">
-        <v>5.678210735321045</v>
+        <v>5.678210258483887</v>
       </c>
       <c r="C124" t="n">
-        <v>5.793549490697893</v>
+        <v>5.793549004174971</v>
       </c>
       <c r="D124" t="n">
-        <v>5.536255181372748</v>
+        <v>5.536254716456543</v>
       </c>
       <c r="E124" t="n">
-        <v>5.766932692126443</v>
+        <v>5.766932207838711</v>
       </c>
       <c r="F124" t="n">
         <v>8050400</v>
@@ -2912,16 +2912,16 @@
         <v>44594</v>
       </c>
       <c r="B125" t="n">
-        <v>5.669337749481201</v>
+        <v>5.669338703155518</v>
       </c>
       <c r="C125" t="n">
-        <v>5.882270847141231</v>
+        <v>5.882271836634339</v>
       </c>
       <c r="D125" t="n">
-        <v>5.651593359931167</v>
+        <v>5.65159431062059</v>
       </c>
       <c r="E125" t="n">
-        <v>5.722570918131304</v>
+        <v>5.722571880760301</v>
       </c>
       <c r="F125" t="n">
         <v>8808600</v>
@@ -2932,16 +2932,16 @@
         <v>44595</v>
       </c>
       <c r="B126" t="n">
-        <v>5.731443405151367</v>
+        <v>5.731442928314209</v>
       </c>
       <c r="C126" t="n">
-        <v>5.793548980980922</v>
+        <v>5.793548498976785</v>
       </c>
       <c r="D126" t="n">
-        <v>5.616104659922033</v>
+        <v>5.616104192680678</v>
       </c>
       <c r="E126" t="n">
-        <v>5.678210235751588</v>
+        <v>5.678209763343253</v>
       </c>
       <c r="F126" t="n">
         <v>8390300</v>
@@ -2952,16 +2952,16 @@
         <v>44596</v>
       </c>
       <c r="B127" t="n">
-        <v>5.660466194152832</v>
+        <v>5.660465717315674</v>
       </c>
       <c r="C127" t="n">
-        <v>5.820165712176019</v>
+        <v>5.820165221885787</v>
       </c>
       <c r="D127" t="n">
-        <v>5.63384939628581</v>
+        <v>5.633848921690848</v>
       </c>
       <c r="E127" t="n">
-        <v>5.722571350743135</v>
+        <v>5.722570868674245</v>
       </c>
       <c r="F127" t="n">
         <v>8483700</v>
@@ -3032,16 +3032,16 @@
         <v>44602</v>
       </c>
       <c r="B131" t="n">
-        <v>5.704826354980469</v>
+        <v>5.704826831817627</v>
       </c>
       <c r="C131" t="n">
-        <v>5.740315133000595</v>
+        <v>5.740315612804078</v>
       </c>
       <c r="D131" t="n">
-        <v>5.562871242899961</v>
+        <v>5.56287170787182</v>
       </c>
       <c r="E131" t="n">
-        <v>5.678209982995176</v>
+        <v>5.678210457607609</v>
       </c>
       <c r="F131" t="n">
         <v>9667400</v>
@@ -3072,16 +3072,16 @@
         <v>44606</v>
       </c>
       <c r="B133" t="n">
-        <v>5.6959547996521</v>
+        <v>5.695954322814941</v>
       </c>
       <c r="C133" t="n">
-        <v>5.766932361021281</v>
+        <v>5.766931878242232</v>
       </c>
       <c r="D133" t="n">
-        <v>5.642721628625214</v>
+        <v>5.642721156244472</v>
       </c>
       <c r="E133" t="n">
-        <v>5.642721628625214</v>
+        <v>5.642721156244472</v>
       </c>
       <c r="F133" t="n">
         <v>12680200</v>
@@ -3092,16 +3092,16 @@
         <v>44607</v>
       </c>
       <c r="B134" t="n">
-        <v>5.6959547996521</v>
+        <v>5.695954322814941</v>
       </c>
       <c r="C134" t="n">
-        <v>5.811293548406838</v>
+        <v>5.81129306191409</v>
       </c>
       <c r="D134" t="n">
-        <v>5.518510473169509</v>
+        <v>5.518510011187112</v>
       </c>
       <c r="E134" t="n">
-        <v>5.811293548406838</v>
+        <v>5.81129306191409</v>
       </c>
       <c r="F134" t="n">
         <v>17426200</v>
@@ -3112,16 +3112,16 @@
         <v>44608</v>
       </c>
       <c r="B135" t="n">
-        <v>5.704826354980469</v>
+        <v>5.704826831817627</v>
       </c>
       <c r="C135" t="n">
-        <v>5.811293112100454</v>
+        <v>5.811293597836623</v>
       </c>
       <c r="D135" t="n">
-        <v>5.651593187950278</v>
+        <v>5.651593660337949</v>
       </c>
       <c r="E135" t="n">
-        <v>5.713698761015302</v>
+        <v>5.71369923859406</v>
       </c>
       <c r="F135" t="n">
         <v>12029900</v>
@@ -3172,16 +3172,16 @@
         <v>44613</v>
       </c>
       <c r="B138" t="n">
-        <v>5.119261741638184</v>
+        <v>5.119261264801025</v>
       </c>
       <c r="C138" t="n">
-        <v>5.456405598502314</v>
+        <v>5.456405090261659</v>
       </c>
       <c r="D138" t="n">
-        <v>5.074900551976187</v>
+        <v>5.074900079271083</v>
       </c>
       <c r="E138" t="n">
-        <v>5.447533191346051</v>
+        <v>5.447532683931823</v>
       </c>
       <c r="F138" t="n">
         <v>8726900</v>
@@ -3212,16 +3212,16 @@
         <v>44615</v>
       </c>
       <c r="B140" t="n">
-        <v>5.02166748046875</v>
+        <v>5.021666526794434</v>
       </c>
       <c r="C140" t="n">
-        <v>5.101517454262385</v>
+        <v>5.10151648542361</v>
       </c>
       <c r="D140" t="n">
-        <v>4.968434305626215</v>
+        <v>4.968433362061512</v>
       </c>
       <c r="E140" t="n">
-        <v>5.057156263697106</v>
+        <v>5.057155303283048</v>
       </c>
       <c r="F140" t="n">
         <v>10772600</v>
@@ -3232,16 +3232,16 @@
         <v>44616</v>
       </c>
       <c r="B141" t="n">
-        <v>5.119261741638184</v>
+        <v>5.119261264801025</v>
       </c>
       <c r="C141" t="n">
-        <v>5.137006132891051</v>
+        <v>5.137005654401078</v>
       </c>
       <c r="D141" t="n">
-        <v>4.773245900677449</v>
+        <v>4.773245456070175</v>
       </c>
       <c r="E141" t="n">
-        <v>4.924073437856647</v>
+        <v>4.924072979200438</v>
       </c>
       <c r="F141" t="n">
         <v>11357100</v>
@@ -3252,16 +3252,16 @@
         <v>44617</v>
       </c>
       <c r="B142" t="n">
-        <v>5.066028594970703</v>
+        <v>5.066027641296387</v>
       </c>
       <c r="C142" t="n">
-        <v>5.163622958913197</v>
+        <v>5.163621986866849</v>
       </c>
       <c r="D142" t="n">
-        <v>4.986178622375967</v>
+        <v>4.986177683733319</v>
       </c>
       <c r="E142" t="n">
-        <v>5.110389784869926</v>
+        <v>5.110388822844664</v>
       </c>
       <c r="F142" t="n">
         <v>6795000</v>
@@ -3272,16 +3272,16 @@
         <v>44622</v>
       </c>
       <c r="B143" t="n">
-        <v>5.314449787139893</v>
+        <v>5.314449310302734</v>
       </c>
       <c r="C143" t="n">
-        <v>5.349938990980526</v>
+        <v>5.349938510959111</v>
       </c>
       <c r="D143" t="n">
-        <v>5.03053954089193</v>
+        <v>5.03053908952852</v>
       </c>
       <c r="E143" t="n">
-        <v>5.10151710245392</v>
+        <v>5.101516644722073</v>
       </c>
       <c r="F143" t="n">
         <v>7030100</v>
@@ -3292,16 +3292,16 @@
         <v>44623</v>
       </c>
       <c r="B144" t="n">
-        <v>5.465277194976807</v>
+        <v>5.465278148651123</v>
       </c>
       <c r="C144" t="n">
-        <v>5.545127161481217</v>
+        <v>5.545128129089111</v>
       </c>
       <c r="D144" t="n">
-        <v>5.323322075021968</v>
+        <v>5.323323003925546</v>
       </c>
       <c r="E144" t="n">
-        <v>5.323322075021968</v>
+        <v>5.323323003925546</v>
       </c>
       <c r="F144" t="n">
         <v>18057800</v>
@@ -3312,16 +3312,16 @@
         <v>44624</v>
       </c>
       <c r="B145" t="n">
-        <v>5.509638786315918</v>
+        <v>5.50963830947876</v>
       </c>
       <c r="C145" t="n">
-        <v>5.536255161733287</v>
+        <v>5.536254682592588</v>
       </c>
       <c r="D145" t="n">
-        <v>5.376555640050094</v>
+        <v>5.376555174730749</v>
       </c>
       <c r="E145" t="n">
-        <v>5.483021987838889</v>
+        <v>5.483021513305308</v>
       </c>
       <c r="F145" t="n">
         <v>9336900</v>
@@ -3352,16 +3352,16 @@
         <v>44628</v>
       </c>
       <c r="B147" t="n">
-        <v>5.58948802947998</v>
+        <v>5.589488506317139</v>
       </c>
       <c r="C147" t="n">
-        <v>5.58948802947998</v>
+        <v>5.589488506317139</v>
       </c>
       <c r="D147" t="n">
-        <v>5.420916122609865</v>
+        <v>5.420916585066217</v>
       </c>
       <c r="E147" t="n">
-        <v>5.500765661504422</v>
+        <v>5.500766130772708</v>
       </c>
       <c r="F147" t="n">
         <v>5566500</v>
@@ -3372,16 +3372,16 @@
         <v>44629</v>
       </c>
       <c r="B148" t="n">
-        <v>5.6959547996521</v>
+        <v>5.695954322814941</v>
       </c>
       <c r="C148" t="n">
-        <v>5.704826783293429</v>
+        <v>5.704826305713552</v>
       </c>
       <c r="D148" t="n">
-        <v>5.553999676913737</v>
+        <v>5.553999211960359</v>
       </c>
       <c r="E148" t="n">
-        <v>5.589488457598327</v>
+        <v>5.589487989674004</v>
       </c>
       <c r="F148" t="n">
         <v>9079900</v>
@@ -3392,16 +3392,16 @@
         <v>44630</v>
       </c>
       <c r="B149" t="n">
-        <v>5.6959547996521</v>
+        <v>5.695954322814941</v>
       </c>
       <c r="C149" t="n">
-        <v>5.829037938749134</v>
+        <v>5.829037450770913</v>
       </c>
       <c r="D149" t="n">
-        <v>5.553999676913737</v>
+        <v>5.553999211960359</v>
       </c>
       <c r="E149" t="n">
-        <v>5.624977238282918</v>
+        <v>5.62497676738765</v>
       </c>
       <c r="F149" t="n">
         <v>15215200</v>
@@ -3412,16 +3412,16 @@
         <v>44631</v>
       </c>
       <c r="B150" t="n">
-        <v>5.598360061645508</v>
+        <v>5.598360538482666</v>
       </c>
       <c r="C150" t="n">
-        <v>5.97986463966694</v>
+        <v>5.979865148998535</v>
       </c>
       <c r="D150" t="n">
-        <v>5.527382505088926</v>
+        <v>5.52738297588061</v>
       </c>
       <c r="E150" t="n">
-        <v>5.695954413440612</v>
+        <v>5.695954898590315</v>
       </c>
       <c r="F150" t="n">
         <v>16712700</v>
@@ -3432,16 +3432,16 @@
         <v>44634</v>
       </c>
       <c r="B151" t="n">
-        <v>5.58948802947998</v>
+        <v>5.589488506317139</v>
       </c>
       <c r="C151" t="n">
-        <v>5.72257073532411</v>
+        <v>5.722571223514505</v>
       </c>
       <c r="D151" t="n">
-        <v>5.518510050487613</v>
+        <v>5.518510521269666</v>
       </c>
       <c r="E151" t="n">
-        <v>5.607232418463171</v>
+        <v>5.607232896814097</v>
       </c>
       <c r="F151" t="n">
         <v>7706100</v>
@@ -3472,16 +3472,16 @@
         <v>44636</v>
       </c>
       <c r="B153" t="n">
-        <v>5.624976634979248</v>
+        <v>5.624977111816406</v>
       </c>
       <c r="C153" t="n">
-        <v>5.766931742492297</v>
+        <v>5.766932231363189</v>
       </c>
       <c r="D153" t="n">
-        <v>5.51850988128487</v>
+        <v>5.518510349096693</v>
       </c>
       <c r="E153" t="n">
-        <v>5.713698577174903</v>
+        <v>5.713699061533146</v>
       </c>
       <c r="F153" t="n">
         <v>10739100</v>
@@ -3492,16 +3492,16 @@
         <v>44637</v>
       </c>
       <c r="B154" t="n">
-        <v>5.891143321990967</v>
+        <v>5.891142845153809</v>
       </c>
       <c r="C154" t="n">
-        <v>5.926632104052506</v>
+        <v>5.926631624342837</v>
       </c>
       <c r="D154" t="n">
-        <v>5.536255078315924</v>
+        <v>5.536254630203903</v>
       </c>
       <c r="E154" t="n">
-        <v>5.607233065498654</v>
+        <v>5.607232611641579</v>
       </c>
       <c r="F154" t="n">
         <v>10001800</v>
@@ -3512,16 +3512,16 @@
         <v>44638</v>
       </c>
       <c r="B155" t="n">
-        <v>6.201669692993164</v>
+        <v>6.201670169830322</v>
       </c>
       <c r="C155" t="n">
-        <v>6.201669692993164</v>
+        <v>6.201670169830322</v>
       </c>
       <c r="D155" t="n">
-        <v>5.891142672652063</v>
+        <v>5.891143125613262</v>
       </c>
       <c r="E155" t="n">
-        <v>5.891142672652063</v>
+        <v>5.891143125613262</v>
       </c>
       <c r="F155" t="n">
         <v>17710700</v>
@@ -3552,16 +3552,16 @@
         <v>44642</v>
       </c>
       <c r="B157" t="n">
-        <v>6.299263954162598</v>
+        <v>6.299263477325439</v>
       </c>
       <c r="C157" t="n">
-        <v>6.308136360102719</v>
+        <v>6.308135882593944</v>
       </c>
       <c r="D157" t="n">
-        <v>6.077458882374763</v>
+        <v>6.077458422327646</v>
       </c>
       <c r="E157" t="n">
-        <v>6.077458882374763</v>
+        <v>6.077458422327646</v>
       </c>
       <c r="F157" t="n">
         <v>9703800</v>
@@ -3572,16 +3572,16 @@
         <v>44643</v>
       </c>
       <c r="B158" t="n">
-        <v>6.3081374168396</v>
+        <v>6.308136940002441</v>
       </c>
       <c r="C158" t="n">
-        <v>6.334753792999529</v>
+        <v>6.334753314150418</v>
       </c>
       <c r="D158" t="n">
-        <v>6.201670643020867</v>
+        <v>6.201670174231618</v>
       </c>
       <c r="E158" t="n">
-        <v>6.263776225826821</v>
+        <v>6.263775752342961</v>
       </c>
       <c r="F158" t="n">
         <v>8187500</v>
@@ -3592,16 +3592,16 @@
         <v>44644</v>
       </c>
       <c r="B159" t="n">
-        <v>6.343626022338867</v>
+        <v>6.343625068664551</v>
       </c>
       <c r="C159" t="n">
-        <v>6.432347978814025</v>
+        <v>6.432347011801619</v>
       </c>
       <c r="D159" t="n">
-        <v>6.25490406586371</v>
+        <v>6.254903125527482</v>
       </c>
       <c r="E159" t="n">
-        <v>6.299264832571459</v>
+        <v>6.299263885566218</v>
       </c>
       <c r="F159" t="n">
         <v>11578200</v>
@@ -3652,16 +3652,16 @@
         <v>44649</v>
       </c>
       <c r="B162" t="n">
-        <v>6.512197971343994</v>
+        <v>6.512197494506836</v>
       </c>
       <c r="C162" t="n">
-        <v>6.645280694939145</v>
+        <v>6.645280208357383</v>
       </c>
       <c r="D162" t="n">
-        <v>6.387986808834351</v>
+        <v>6.387986341092201</v>
       </c>
       <c r="E162" t="n">
-        <v>6.476709188644</v>
+        <v>6.476708714405406</v>
       </c>
       <c r="F162" t="n">
         <v>18100700</v>
@@ -3672,16 +3672,16 @@
         <v>44650</v>
       </c>
       <c r="B163" t="n">
-        <v>6.503324508666992</v>
+        <v>6.50332498550415</v>
       </c>
       <c r="C163" t="n">
-        <v>6.618663245252637</v>
+        <v>6.61866373054667</v>
       </c>
       <c r="D163" t="n">
-        <v>6.4500913432566</v>
+        <v>6.450091816190593</v>
       </c>
       <c r="E163" t="n">
-        <v>6.547685691372115</v>
+        <v>6.547686171461927</v>
       </c>
       <c r="F163" t="n">
         <v>10697600</v>
@@ -3692,16 +3692,16 @@
         <v>44651</v>
       </c>
       <c r="B164" t="n">
-        <v>6.23715877532959</v>
+        <v>6.237159729003906</v>
       </c>
       <c r="C164" t="n">
-        <v>6.52994140101566</v>
+        <v>6.529942399457037</v>
       </c>
       <c r="D164" t="n">
-        <v>6.18392518605976</v>
+        <v>6.183926131594552</v>
       </c>
       <c r="E164" t="n">
-        <v>6.503324606380745</v>
+        <v>6.503325600752361</v>
       </c>
       <c r="F164" t="n">
         <v>12972000</v>
@@ -3712,16 +3712,16 @@
         <v>44652</v>
       </c>
       <c r="B165" t="n">
-        <v>6.139564514160156</v>
+        <v>6.139564990997314</v>
       </c>
       <c r="C165" t="n">
-        <v>6.299264015090594</v>
+        <v>6.299264504331019</v>
       </c>
       <c r="D165" t="n">
-        <v>5.926631423193302</v>
+        <v>5.926631883492739</v>
       </c>
       <c r="E165" t="n">
-        <v>6.254903254139719</v>
+        <v>6.254903739934808</v>
       </c>
       <c r="F165" t="n">
         <v>18919700</v>
@@ -3732,16 +3732,16 @@
         <v>44655</v>
       </c>
       <c r="B166" t="n">
-        <v>6.210542678833008</v>
+        <v>6.21054220199585</v>
       </c>
       <c r="C166" t="n">
-        <v>6.237159476459965</v>
+        <v>6.237158997579204</v>
       </c>
       <c r="D166" t="n">
-        <v>6.050843162250203</v>
+        <v>6.050842697674559</v>
       </c>
       <c r="E166" t="n">
-        <v>6.15730950663874</v>
+        <v>6.157309033888753</v>
       </c>
       <c r="F166" t="n">
         <v>13343800</v>
@@ -3752,16 +3752,16 @@
         <v>44656</v>
       </c>
       <c r="B167" t="n">
-        <v>6.299263954162598</v>
+        <v>6.299263477325439</v>
       </c>
       <c r="C167" t="n">
-        <v>6.325880748923362</v>
+        <v>6.325880270071385</v>
       </c>
       <c r="D167" t="n">
-        <v>6.148436437657334</v>
+        <v>6.148435972237409</v>
       </c>
       <c r="E167" t="n">
-        <v>6.228286398880027</v>
+        <v>6.228285927415676</v>
       </c>
       <c r="F167" t="n">
         <v>6962400</v>
@@ -3772,16 +3772,16 @@
         <v>44657</v>
       </c>
       <c r="B168" t="n">
-        <v>6.350711822509766</v>
+        <v>6.350711345672607</v>
       </c>
       <c r="C168" t="n">
-        <v>6.395246712983208</v>
+        <v>6.39524623280219</v>
       </c>
       <c r="D168" t="n">
-        <v>6.136942904188415</v>
+        <v>6.136942443401892</v>
       </c>
       <c r="E168" t="n">
-        <v>6.243827575709211</v>
+        <v>6.243827106897355</v>
       </c>
       <c r="F168" t="n">
         <v>10002000</v>
@@ -3812,16 +3812,16 @@
         <v>44659</v>
       </c>
       <c r="B170" t="n">
-        <v>6.190384864807129</v>
+        <v>6.190384387969971</v>
       </c>
       <c r="C170" t="n">
-        <v>6.323990382154669</v>
+        <v>6.323989895026054</v>
       </c>
       <c r="D170" t="n">
-        <v>6.136942742812159</v>
+        <v>6.136942270091576</v>
       </c>
       <c r="E170" t="n">
-        <v>6.23492017882972</v>
+        <v>6.234919698562065</v>
       </c>
       <c r="F170" t="n">
         <v>10722400</v>
@@ -3832,16 +3832,16 @@
         <v>44662</v>
       </c>
       <c r="B171" t="n">
-        <v>6.145850658416748</v>
+        <v>6.145849704742432</v>
       </c>
       <c r="C171" t="n">
-        <v>6.21710682899452</v>
+        <v>6.217105864263122</v>
       </c>
       <c r="D171" t="n">
-        <v>6.021152359905646</v>
+        <v>6.021151425581226</v>
       </c>
       <c r="E171" t="n">
-        <v>6.119129382089944</v>
+        <v>6.119128432562067</v>
       </c>
       <c r="F171" t="n">
         <v>4955900</v>
@@ -3852,16 +3852,16 @@
         <v>44663</v>
       </c>
       <c r="B172" t="n">
-        <v>6.217106342315674</v>
+        <v>6.217105865478516</v>
       </c>
       <c r="C172" t="n">
-        <v>6.359618672315267</v>
+        <v>6.359618184547754</v>
       </c>
       <c r="D172" t="n">
-        <v>6.145850177315878</v>
+        <v>6.145849705943896</v>
       </c>
       <c r="E172" t="n">
-        <v>6.190385068080627</v>
+        <v>6.190384593292927</v>
       </c>
       <c r="F172" t="n">
         <v>15598900</v>
@@ -3872,16 +3872,16 @@
         <v>44664</v>
       </c>
       <c r="B173" t="n">
-        <v>6.30617618560791</v>
+        <v>6.306177139282227</v>
       </c>
       <c r="C173" t="n">
-        <v>6.323990225832556</v>
+        <v>6.323991182200865</v>
       </c>
       <c r="D173" t="n">
-        <v>6.172570671562951</v>
+        <v>6.172571605032291</v>
       </c>
       <c r="E173" t="n">
-        <v>6.261641297406404</v>
+        <v>6.261642244345771</v>
       </c>
       <c r="F173" t="n">
         <v>5828500</v>
@@ -3912,16 +3912,16 @@
         <v>44669</v>
       </c>
       <c r="B175" t="n">
-        <v>6.350711822509766</v>
+        <v>6.350711345672607</v>
       </c>
       <c r="C175" t="n">
-        <v>6.395246712983208</v>
+        <v>6.39524623280219</v>
       </c>
       <c r="D175" t="n">
-        <v>6.190385027588691</v>
+        <v>6.190384562789519</v>
       </c>
       <c r="E175" t="n">
-        <v>6.315083740242914</v>
+        <v>6.315083266080856</v>
       </c>
       <c r="F175" t="n">
         <v>6987700</v>
@@ -3932,16 +3932,16 @@
         <v>44670</v>
       </c>
       <c r="B176" t="n">
-        <v>6.190384864807129</v>
+        <v>6.190384387969971</v>
       </c>
       <c r="C176" t="n">
-        <v>6.413060585479618</v>
+        <v>6.413060091490044</v>
       </c>
       <c r="D176" t="n">
-        <v>6.18147805683475</v>
+        <v>6.181477580683671</v>
       </c>
       <c r="E176" t="n">
-        <v>6.359618463484649</v>
+        <v>6.35961797361165</v>
       </c>
       <c r="F176" t="n">
         <v>12659600</v>
@@ -3952,16 +3952,16 @@
         <v>44671</v>
       </c>
       <c r="B177" t="n">
-        <v>6.208198547363281</v>
+        <v>6.208199024200439</v>
       </c>
       <c r="C177" t="n">
-        <v>6.279455130633163</v>
+        <v>6.279455612943373</v>
       </c>
       <c r="D177" t="n">
-        <v>6.11022154171758</v>
+        <v>6.110222011029355</v>
       </c>
       <c r="E177" t="n">
-        <v>6.190384507725862</v>
+        <v>6.190384983194765</v>
       </c>
       <c r="F177" t="n">
         <v>7897000</v>
@@ -3972,16 +3972,16 @@
         <v>44673</v>
       </c>
       <c r="B178" t="n">
-        <v>6.128036499023438</v>
+        <v>6.128036022186279</v>
       </c>
       <c r="C178" t="n">
-        <v>6.190385434731002</v>
+        <v>6.190384953042324</v>
       </c>
       <c r="D178" t="n">
-        <v>5.98552373586271</v>
+        <v>5.98552327011481</v>
       </c>
       <c r="E178" t="n">
-        <v>6.136943307815831</v>
+        <v>6.136942830285612</v>
       </c>
       <c r="F178" t="n">
         <v>9926800</v>
@@ -3992,16 +3992,16 @@
         <v>44676</v>
       </c>
       <c r="B179" t="n">
-        <v>6.279455661773682</v>
+        <v>6.279455184936523</v>
       </c>
       <c r="C179" t="n">
-        <v>6.306176511129858</v>
+        <v>6.306176032263624</v>
       </c>
       <c r="D179" t="n">
-        <v>6.038965893966873</v>
+        <v>6.038965435391561</v>
       </c>
       <c r="E179" t="n">
-        <v>6.047872702178851</v>
+        <v>6.047872242927192</v>
       </c>
       <c r="F179" t="n">
         <v>9340700</v>
@@ -4052,16 +4052,16 @@
         <v>44679</v>
       </c>
       <c r="B182" t="n">
-        <v>6.404153823852539</v>
+        <v>6.404154300689697</v>
       </c>
       <c r="C182" t="n">
-        <v>6.404153823852539</v>
+        <v>6.404154300689697</v>
       </c>
       <c r="D182" t="n">
-        <v>6.217106183156411</v>
+        <v>6.217106646066473</v>
       </c>
       <c r="E182" t="n">
-        <v>6.332897660676916</v>
+        <v>6.33289813220852</v>
       </c>
       <c r="F182" t="n">
         <v>9691200</v>
@@ -4072,16 +4072,16 @@
         <v>44680</v>
       </c>
       <c r="B183" t="n">
-        <v>6.145850658416748</v>
+        <v>6.145849704742432</v>
       </c>
       <c r="C183" t="n">
-        <v>6.44868938337228</v>
+        <v>6.448688382705361</v>
       </c>
       <c r="D183" t="n">
-        <v>6.065687254156614</v>
+        <v>6.06568631292155</v>
       </c>
       <c r="E183" t="n">
-        <v>6.413061298083393</v>
+        <v>6.413060302945017</v>
       </c>
       <c r="F183" t="n">
         <v>21979100</v>
@@ -4092,16 +4092,16 @@
         <v>44683</v>
       </c>
       <c r="B184" t="n">
-        <v>5.86973237991333</v>
+        <v>5.869731903076172</v>
       </c>
       <c r="C184" t="n">
-        <v>6.19038512538046</v>
+        <v>6.19038462249456</v>
       </c>
       <c r="D184" t="n">
-        <v>5.745033665289197</v>
+        <v>5.745033198582139</v>
       </c>
       <c r="E184" t="n">
-        <v>6.145850234203484</v>
+        <v>6.145849734935447</v>
       </c>
       <c r="F184" t="n">
         <v>12404500</v>
@@ -4132,16 +4132,16 @@
         <v>44685</v>
       </c>
       <c r="B186" t="n">
-        <v>5.388752460479736</v>
+        <v>5.388752937316895</v>
       </c>
       <c r="C186" t="n">
-        <v>5.51345074167094</v>
+        <v>5.513451229542335</v>
       </c>
       <c r="D186" t="n">
-        <v>5.210611634057798</v>
+        <v>5.210612095131722</v>
       </c>
       <c r="E186" t="n">
-        <v>5.51345074167094</v>
+        <v>5.513451229542335</v>
       </c>
       <c r="F186" t="n">
         <v>18834300</v>
@@ -4172,16 +4172,16 @@
         <v>44687</v>
       </c>
       <c r="B188" t="n">
-        <v>4.952307224273682</v>
+        <v>4.95230770111084</v>
       </c>
       <c r="C188" t="n">
-        <v>5.068098683361416</v>
+        <v>5.068099171347654</v>
       </c>
       <c r="D188" t="n">
-        <v>4.863237034483181</v>
+        <v>4.863237502744139</v>
       </c>
       <c r="E188" t="n">
-        <v>4.970121262231782</v>
+        <v>4.97012174078418</v>
       </c>
       <c r="F188" t="n">
         <v>14479200</v>
@@ -4192,16 +4192,16 @@
         <v>44690</v>
       </c>
       <c r="B189" t="n">
-        <v>4.622748374938965</v>
+        <v>4.622747898101807</v>
       </c>
       <c r="C189" t="n">
-        <v>4.934494323403464</v>
+        <v>4.934493814409667</v>
       </c>
       <c r="D189" t="n">
-        <v>4.435700720916212</v>
+        <v>4.435700263373046</v>
       </c>
       <c r="E189" t="n">
-        <v>4.934494323403464</v>
+        <v>4.934493814409667</v>
       </c>
       <c r="F189" t="n">
         <v>21341300</v>
@@ -4252,16 +4252,16 @@
         <v>44693</v>
       </c>
       <c r="B192" t="n">
-        <v>4.791981220245361</v>
+        <v>4.79198169708252</v>
       </c>
       <c r="C192" t="n">
-        <v>4.809795259458459</v>
+        <v>4.809795738068244</v>
       </c>
       <c r="D192" t="n">
-        <v>4.551491478508448</v>
+        <v>4.55149193141512</v>
       </c>
       <c r="E192" t="n">
-        <v>4.587119556934643</v>
+        <v>4.587120013386569</v>
       </c>
       <c r="F192" t="n">
         <v>13350100</v>
@@ -4292,16 +4292,16 @@
         <v>44697</v>
       </c>
       <c r="B194" t="n">
-        <v>4.881052494049072</v>
+        <v>4.881052017211914</v>
       </c>
       <c r="C194" t="n">
-        <v>4.881052494049072</v>
+        <v>4.881052017211914</v>
       </c>
       <c r="D194" t="n">
-        <v>4.542585249546331</v>
+        <v>4.542584805774532</v>
       </c>
       <c r="E194" t="n">
-        <v>4.604934612919033</v>
+        <v>4.604934163056234</v>
       </c>
       <c r="F194" t="n">
         <v>29391700</v>
@@ -4332,16 +4332,16 @@
         <v>44699</v>
       </c>
       <c r="B196" t="n">
-        <v>4.952307224273682</v>
+        <v>4.95230770111084</v>
       </c>
       <c r="C196" t="n">
-        <v>5.112633565896584</v>
+        <v>5.112634058170901</v>
       </c>
       <c r="D196" t="n">
-        <v>4.898865110399381</v>
+        <v>4.89886558209082</v>
       </c>
       <c r="E196" t="n">
-        <v>4.987935300189882</v>
+        <v>4.98793578045752</v>
       </c>
       <c r="F196" t="n">
         <v>17779600</v>
@@ -4352,16 +4352,16 @@
         <v>44700</v>
       </c>
       <c r="B197" t="n">
-        <v>5.050285816192627</v>
+        <v>5.050285339355469</v>
       </c>
       <c r="C197" t="n">
-        <v>5.183891344211743</v>
+        <v>5.183890854759837</v>
       </c>
       <c r="D197" t="n">
-        <v>4.898866246085646</v>
+        <v>4.898865783545199</v>
       </c>
       <c r="E197" t="n">
-        <v>4.987936456524968</v>
+        <v>4.987935985574703</v>
       </c>
       <c r="F197" t="n">
         <v>12233400</v>
@@ -4392,16 +4392,16 @@
         <v>44704</v>
       </c>
       <c r="B199" t="n">
-        <v>5.023564338684082</v>
+        <v>5.02356481552124</v>
       </c>
       <c r="C199" t="n">
-        <v>5.10372773721593</v>
+        <v>5.103728221662204</v>
       </c>
       <c r="D199" t="n">
-        <v>4.881052007712129</v>
+        <v>4.881052471022004</v>
       </c>
       <c r="E199" t="n">
-        <v>4.979029447615471</v>
+        <v>4.979029920225373</v>
       </c>
       <c r="F199" t="n">
         <v>11444200</v>
@@ -4432,16 +4432,16 @@
         <v>44706</v>
       </c>
       <c r="B201" t="n">
-        <v>5.272961139678955</v>
+        <v>5.272961616516113</v>
       </c>
       <c r="C201" t="n">
-        <v>5.326403261736754</v>
+        <v>5.326403743406717</v>
       </c>
       <c r="D201" t="n">
-        <v>5.112634348785326</v>
+        <v>5.112634811124033</v>
       </c>
       <c r="E201" t="n">
-        <v>5.148262854877424</v>
+        <v>5.148263320438039</v>
       </c>
       <c r="F201" t="n">
         <v>9738900</v>
@@ -4452,16 +4452,16 @@
         <v>44707</v>
       </c>
       <c r="B202" t="n">
-        <v>5.504543781280518</v>
+        <v>5.504542827606201</v>
       </c>
       <c r="C202" t="n">
-        <v>5.647056534405616</v>
+        <v>5.647055556040652</v>
       </c>
       <c r="D202" t="n">
-        <v>5.281868055787807</v>
+        <v>5.281867140692549</v>
       </c>
       <c r="E202" t="n">
-        <v>5.281868055787807</v>
+        <v>5.281867140692549</v>
       </c>
       <c r="F202" t="n">
         <v>14781100</v>
@@ -4512,16 +4512,16 @@
         <v>44712</v>
       </c>
       <c r="B205" t="n">
-        <v>5.460009098052979</v>
+        <v>5.46000862121582</v>
       </c>
       <c r="C205" t="n">
-        <v>5.691591640492284</v>
+        <v>5.691591143430404</v>
       </c>
       <c r="D205" t="n">
-        <v>5.460009098052979</v>
+        <v>5.46000862121582</v>
       </c>
       <c r="E205" t="n">
-        <v>5.629242706811061</v>
+        <v>5.62924221519428</v>
       </c>
       <c r="F205" t="n">
         <v>13931800</v>
@@ -4532,16 +4532,16 @@
         <v>44713</v>
       </c>
       <c r="B206" t="n">
-        <v>5.51345157623291</v>
+        <v>5.513451099395752</v>
       </c>
       <c r="C206" t="n">
-        <v>5.549079661966218</v>
+        <v>5.549079182047723</v>
       </c>
       <c r="D206" t="n">
-        <v>5.406567319032987</v>
+        <v>5.406566851439836</v>
       </c>
       <c r="E206" t="n">
-        <v>5.495637533366256</v>
+        <v>5.495637058069765</v>
       </c>
       <c r="F206" t="n">
         <v>9091200</v>
@@ -4552,16 +4552,16 @@
         <v>44714</v>
       </c>
       <c r="B207" t="n">
-        <v>5.611427783966064</v>
+        <v>5.611428260803223</v>
       </c>
       <c r="C207" t="n">
-        <v>5.65596266892822</v>
+        <v>5.655963149549779</v>
       </c>
       <c r="D207" t="n">
-        <v>5.504543125672473</v>
+        <v>5.504543593426991</v>
       </c>
       <c r="E207" t="n">
-        <v>5.549078435354819</v>
+        <v>5.549078906893773</v>
       </c>
       <c r="F207" t="n">
         <v>14163200</v>
@@ -4572,16 +4572,16 @@
         <v>44715</v>
       </c>
       <c r="B208" t="n">
-        <v>5.51345157623291</v>
+        <v>5.513451099395752</v>
       </c>
       <c r="C208" t="n">
-        <v>5.602521790566179</v>
+        <v>5.602521306025682</v>
       </c>
       <c r="D208" t="n">
-        <v>5.45110221383948</v>
+        <v>5.451101742394677</v>
       </c>
       <c r="E208" t="n">
-        <v>5.57580093862634</v>
+        <v>5.575800456396826</v>
       </c>
       <c r="F208" t="n">
         <v>9326300</v>
@@ -4612,16 +4612,16 @@
         <v>44719</v>
       </c>
       <c r="B210" t="n">
-        <v>5.023564338684082</v>
+        <v>5.02356481552124</v>
       </c>
       <c r="C210" t="n">
-        <v>5.299682192302366</v>
+        <v>5.299682695348654</v>
       </c>
       <c r="D210" t="n">
-        <v>4.987936255941094</v>
+        <v>4.987936729396432</v>
       </c>
       <c r="E210" t="n">
-        <v>5.281868150930872</v>
+        <v>5.281868652286249</v>
       </c>
       <c r="F210" t="n">
         <v>18881300</v>
@@ -4632,16 +4632,16 @@
         <v>44720</v>
       </c>
       <c r="B211" t="n">
-        <v>4.916679382324219</v>
+        <v>4.916679859161377</v>
       </c>
       <c r="C211" t="n">
-        <v>5.005749576353243</v>
+        <v>5.005750061828747</v>
       </c>
       <c r="D211" t="n">
-        <v>4.783073878920588</v>
+        <v>4.783074342800206</v>
       </c>
       <c r="E211" t="n">
-        <v>4.996842769310434</v>
+        <v>4.996843253922124</v>
       </c>
       <c r="F211" t="n">
         <v>13996400</v>
@@ -4672,16 +4672,16 @@
         <v>44722</v>
       </c>
       <c r="B213" t="n">
-        <v>4.738539218902588</v>
+        <v>4.738539695739746</v>
       </c>
       <c r="C213" t="n">
-        <v>4.78307410566824</v>
+        <v>4.783074586986924</v>
       </c>
       <c r="D213" t="n">
-        <v>4.676189867766428</v>
+        <v>4.676190338329397</v>
       </c>
       <c r="E213" t="n">
-        <v>4.774167298203192</v>
+        <v>4.774167778625588</v>
       </c>
       <c r="F213" t="n">
         <v>4786300</v>
@@ -4692,16 +4692,16 @@
         <v>44725</v>
       </c>
       <c r="B214" t="n">
-        <v>4.569305419921875</v>
+        <v>4.569305896759033</v>
       </c>
       <c r="C214" t="n">
-        <v>4.67618965291275</v>
+        <v>4.676190140903983</v>
       </c>
       <c r="D214" t="n">
-        <v>4.506956071650437</v>
+        <v>4.50695654198103</v>
       </c>
       <c r="E214" t="n">
-        <v>4.631654343473125</v>
+        <v>4.631654826816805</v>
       </c>
       <c r="F214" t="n">
         <v>7709600</v>
@@ -4732,16 +4732,16 @@
         <v>44727</v>
       </c>
       <c r="B216" t="n">
-        <v>4.560398578643799</v>
+        <v>4.560399055480957</v>
       </c>
       <c r="C216" t="n">
-        <v>4.649468780429767</v>
+        <v>4.649469266580143</v>
       </c>
       <c r="D216" t="n">
-        <v>4.48023560939654</v>
+        <v>4.480236077851825</v>
       </c>
       <c r="E216" t="n">
-        <v>4.542584538286605</v>
+        <v>4.54258501326112</v>
       </c>
       <c r="F216" t="n">
         <v>10830000</v>
@@ -4752,16 +4752,16 @@
         <v>44729</v>
       </c>
       <c r="B217" t="n">
-        <v>4.524770736694336</v>
+        <v>4.524771213531494</v>
       </c>
       <c r="C217" t="n">
-        <v>4.524770736694336</v>
+        <v>4.524771213531494</v>
       </c>
       <c r="D217" t="n">
-        <v>4.311002241127791</v>
+        <v>4.311002695437231</v>
       </c>
       <c r="E217" t="n">
-        <v>4.506956695397124</v>
+        <v>4.506957170356972</v>
       </c>
       <c r="F217" t="n">
         <v>10891400</v>
@@ -4772,16 +4772,16 @@
         <v>44732</v>
       </c>
       <c r="B218" t="n">
-        <v>4.524770736694336</v>
+        <v>4.524771213531494</v>
       </c>
       <c r="C218" t="n">
-        <v>4.64946902577482</v>
+        <v>4.649469515753148</v>
       </c>
       <c r="D218" t="n">
-        <v>4.453514571505488</v>
+        <v>4.453515040833406</v>
       </c>
       <c r="E218" t="n">
-        <v>4.524770736694336</v>
+        <v>4.524771213531494</v>
       </c>
       <c r="F218" t="n">
         <v>7841400</v>
@@ -4792,16 +4792,16 @@
         <v>44733</v>
       </c>
       <c r="B219" t="n">
-        <v>4.489142894744873</v>
+        <v>4.489141941070557</v>
       </c>
       <c r="C219" t="n">
-        <v>4.596027148257782</v>
+        <v>4.596026171876956</v>
       </c>
       <c r="D219" t="n">
-        <v>4.44460757675436</v>
+        <v>4.444606632541134</v>
       </c>
       <c r="E219" t="n">
-        <v>4.560399063753479</v>
+        <v>4.56039809494149</v>
       </c>
       <c r="F219" t="n">
         <v>7411800</v>
@@ -4812,16 +4812,16 @@
         <v>44734</v>
       </c>
       <c r="B220" t="n">
-        <v>4.444607734680176</v>
+        <v>4.444606781005859</v>
       </c>
       <c r="C220" t="n">
-        <v>4.533678373826061</v>
+        <v>4.53367740103996</v>
       </c>
       <c r="D220" t="n">
-        <v>4.400072839827518</v>
+        <v>4.400071895709002</v>
       </c>
       <c r="E220" t="n">
-        <v>4.4802362451707</v>
+        <v>4.480235283851616</v>
       </c>
       <c r="F220" t="n">
         <v>8433900</v>
@@ -4832,16 +4832,16 @@
         <v>44735</v>
       </c>
       <c r="B221" t="n">
-        <v>4.266467094421387</v>
+        <v>4.266466617584229</v>
       </c>
       <c r="C221" t="n">
-        <v>4.515864107175489</v>
+        <v>4.515863602464738</v>
       </c>
       <c r="D221" t="n">
-        <v>4.266467094421387</v>
+        <v>4.266466617584229</v>
       </c>
       <c r="E221" t="n">
-        <v>4.471328789809315</v>
+        <v>4.471328290076007</v>
       </c>
       <c r="F221" t="n">
         <v>8059200</v>
@@ -4852,16 +4852,16 @@
         <v>44736</v>
       </c>
       <c r="B222" t="n">
-        <v>4.257560253143311</v>
+        <v>4.257559776306152</v>
       </c>
       <c r="C222" t="n">
-        <v>4.337723229179554</v>
+        <v>4.337722743364323</v>
       </c>
       <c r="D222" t="n">
-        <v>4.23083897798439</v>
+        <v>4.230838504139954</v>
       </c>
       <c r="E222" t="n">
-        <v>4.319909187313693</v>
+        <v>4.319908703493595</v>
       </c>
       <c r="F222" t="n">
         <v>7941200</v>
@@ -4872,16 +4872,16 @@
         <v>44739</v>
       </c>
       <c r="B223" t="n">
-        <v>4.275373458862305</v>
+        <v>4.275374412536621</v>
       </c>
       <c r="C223" t="n">
-        <v>4.337722380838932</v>
+        <v>4.337723348420938</v>
       </c>
       <c r="D223" t="n">
-        <v>4.239745382098467</v>
+        <v>4.239746327825506</v>
       </c>
       <c r="E223" t="n">
-        <v>4.275373458862305</v>
+        <v>4.275374412536621</v>
       </c>
       <c r="F223" t="n">
         <v>10516900</v>
@@ -4892,16 +4892,16 @@
         <v>44740</v>
       </c>
       <c r="B224" t="n">
-        <v>4.293187618255615</v>
+        <v>4.293188095092773</v>
       </c>
       <c r="C224" t="n">
-        <v>4.471328007096019</v>
+        <v>4.471328503718931</v>
       </c>
       <c r="D224" t="n">
-        <v>4.293187618255615</v>
+        <v>4.293188095092773</v>
       </c>
       <c r="E224" t="n">
-        <v>4.319908464221581</v>
+        <v>4.319908944026579</v>
       </c>
       <c r="F224" t="n">
         <v>8975600</v>
@@ -4912,16 +4912,16 @@
         <v>44741</v>
       </c>
       <c r="B225" t="n">
-        <v>4.275373458862305</v>
+        <v>4.275374412536621</v>
       </c>
       <c r="C225" t="n">
-        <v>4.355536419220851</v>
+        <v>4.355537390776496</v>
       </c>
       <c r="D225" t="n">
-        <v>4.248652188929338</v>
+        <v>4.248653136643148</v>
       </c>
       <c r="E225" t="n">
-        <v>4.311001535626143</v>
+        <v>4.311002497247737</v>
       </c>
       <c r="F225" t="n">
         <v>7179800</v>
@@ -4932,16 +4932,16 @@
         <v>44742</v>
       </c>
       <c r="B226" t="n">
-        <v>4.088326454162598</v>
+        <v>4.088325977325439</v>
       </c>
       <c r="C226" t="n">
-        <v>4.239746015386434</v>
+        <v>4.239745520888632</v>
       </c>
       <c r="D226" t="n">
-        <v>4.052698372077018</v>
+        <v>4.052697899395299</v>
       </c>
       <c r="E226" t="n">
-        <v>4.239746015386434</v>
+        <v>4.239745520888632</v>
       </c>
       <c r="F226" t="n">
         <v>6721700</v>
@@ -4952,16 +4952,16 @@
         <v>44743</v>
       </c>
       <c r="B227" t="n">
-        <v>4.025977611541748</v>
+        <v>4.02597713470459</v>
       </c>
       <c r="C227" t="n">
-        <v>4.186304001371536</v>
+        <v>4.186303505545305</v>
       </c>
       <c r="D227" t="n">
-        <v>4.025977611541748</v>
+        <v>4.02597713470459</v>
       </c>
       <c r="E227" t="n">
-        <v>4.025977611541748</v>
+        <v>4.02597713470459</v>
       </c>
       <c r="F227" t="n">
         <v>12849200</v>
@@ -4972,16 +4972,16 @@
         <v>44746</v>
       </c>
       <c r="B228" t="n">
-        <v>4.043790817260742</v>
+        <v>4.0437912940979</v>
       </c>
       <c r="C228" t="n">
-        <v>4.195210366429746</v>
+        <v>4.195210861122049</v>
       </c>
       <c r="D228" t="n">
-        <v>4.008162738011589</v>
+        <v>4.008163210647543</v>
       </c>
       <c r="E228" t="n">
-        <v>4.034884009808557</v>
+        <v>4.034884485595439</v>
       </c>
       <c r="F228" t="n">
         <v>5003300</v>
@@ -4992,16 +4992,16 @@
         <v>44747</v>
       </c>
       <c r="B229" t="n">
-        <v>4.034883975982666</v>
+        <v>4.034884452819824</v>
       </c>
       <c r="C229" t="n">
-        <v>4.061604822835417</v>
+        <v>4.061605302830409</v>
       </c>
       <c r="D229" t="n">
-        <v>3.901278467558302</v>
+        <v>3.901278928606141</v>
       </c>
       <c r="E229" t="n">
-        <v>4.061604822835417</v>
+        <v>4.061605302830409</v>
       </c>
       <c r="F229" t="n">
         <v>9503300</v>
@@ -5012,16 +5012,16 @@
         <v>44748</v>
       </c>
       <c r="B230" t="n">
-        <v>3.910185575485229</v>
+        <v>3.91018533706665</v>
       </c>
       <c r="C230" t="n">
-        <v>4.0526983269613</v>
+        <v>4.052698079853188</v>
       </c>
       <c r="D230" t="n">
-        <v>3.785487289573874</v>
+        <v>3.785487058758614</v>
       </c>
       <c r="E230" t="n">
-        <v>4.034884286116821</v>
+        <v>4.034884040094897</v>
       </c>
       <c r="F230" t="n">
         <v>11922900</v>
@@ -5072,16 +5072,16 @@
         <v>44753</v>
       </c>
       <c r="B233" t="n">
-        <v>3.705323696136475</v>
+        <v>3.705323457717896</v>
       </c>
       <c r="C233" t="n">
-        <v>3.901278559713046</v>
+        <v>3.901278308685776</v>
       </c>
       <c r="D233" t="n">
-        <v>3.678602848652532</v>
+        <v>3.678602611953303</v>
       </c>
       <c r="E233" t="n">
-        <v>3.892371327404923</v>
+        <v>3.892371076950788</v>
       </c>
       <c r="F233" t="n">
         <v>13261200</v>
@@ -5132,16 +5132,16 @@
         <v>44756</v>
       </c>
       <c r="B236" t="n">
-        <v>3.821115493774414</v>
+        <v>3.821115255355835</v>
       </c>
       <c r="C236" t="n">
-        <v>3.856743576605671</v>
+        <v>3.856743335964077</v>
       </c>
       <c r="D236" t="n">
-        <v>3.651881887965819</v>
+        <v>3.651881660106575</v>
       </c>
       <c r="E236" t="n">
-        <v>3.687509970797076</v>
+        <v>3.687509740714817</v>
       </c>
       <c r="F236" t="n">
         <v>9774500</v>
@@ -5152,16 +5152,16 @@
         <v>44757</v>
       </c>
       <c r="B237" t="n">
-        <v>3.936906576156616</v>
+        <v>3.936906814575195</v>
       </c>
       <c r="C237" t="n">
-        <v>3.954720615766004</v>
+        <v>3.9547208552634</v>
       </c>
       <c r="D237" t="n">
-        <v>3.776579794951918</v>
+        <v>3.776580023661126</v>
       </c>
       <c r="E237" t="n">
-        <v>3.830022338500288</v>
+        <v>3.830022570445971</v>
       </c>
       <c r="F237" t="n">
         <v>4881500</v>
@@ -5172,16 +5172,16 @@
         <v>44760</v>
       </c>
       <c r="B238" t="n">
-        <v>3.830022811889648</v>
+        <v>3.830023050308228</v>
       </c>
       <c r="C238" t="n">
-        <v>4.088326630512132</v>
+        <v>4.0883268850101</v>
       </c>
       <c r="D238" t="n">
-        <v>3.830022811889648</v>
+        <v>3.830023050308228</v>
       </c>
       <c r="E238" t="n">
-        <v>3.99034918819042</v>
+        <v>3.990349436589301</v>
       </c>
       <c r="F238" t="n">
         <v>5011900</v>
@@ -5192,16 +5192,16 @@
         <v>44761</v>
       </c>
       <c r="B239" t="n">
-        <v>3.856743812561035</v>
+        <v>3.856743335723877</v>
       </c>
       <c r="C239" t="n">
-        <v>3.93690721619588</v>
+        <v>3.93690672944754</v>
       </c>
       <c r="D239" t="n">
-        <v>3.830022961162937</v>
+        <v>3.830022487629471</v>
       </c>
       <c r="E239" t="n">
-        <v>3.838929770055544</v>
+        <v>3.838929295420866</v>
       </c>
       <c r="F239" t="n">
         <v>5270100</v>
@@ -5212,16 +5212,16 @@
         <v>44762</v>
       </c>
       <c r="B240" t="n">
-        <v>3.999256372451782</v>
+        <v>3.999255418777466</v>
       </c>
       <c r="C240" t="n">
-        <v>4.025977650039076</v>
+        <v>4.025976689992726</v>
       </c>
       <c r="D240" t="n">
-        <v>3.803301894119392</v>
+        <v>3.803300987172951</v>
       </c>
       <c r="E240" t="n">
-        <v>3.830023171706685</v>
+        <v>3.83002225838821</v>
       </c>
       <c r="F240" t="n">
         <v>11021800</v>
@@ -5232,16 +5232,16 @@
         <v>44763</v>
       </c>
       <c r="B241" t="n">
-        <v>3.963627576828003</v>
+        <v>3.963628053665161</v>
       </c>
       <c r="C241" t="n">
-        <v>4.025976930237424</v>
+        <v>4.02597741457541</v>
       </c>
       <c r="D241" t="n">
-        <v>3.93690672873841</v>
+        <v>3.936907202360965</v>
       </c>
       <c r="E241" t="n">
-        <v>4.025976930237424</v>
+        <v>4.02597741457541</v>
       </c>
       <c r="F241" t="n">
         <v>6658500</v>
@@ -5272,16 +5272,16 @@
         <v>44767</v>
       </c>
       <c r="B243" t="n">
-        <v>3.696416854858398</v>
+        <v>3.696417331695557</v>
       </c>
       <c r="C243" t="n">
-        <v>3.78548705352675</v>
+        <v>3.78548754185395</v>
       </c>
       <c r="D243" t="n">
-        <v>3.651881543164118</v>
+        <v>3.651882014256228</v>
       </c>
       <c r="E243" t="n">
-        <v>3.76767301379308</v>
+        <v>3.767673499822271</v>
       </c>
       <c r="F243" t="n">
         <v>10514300</v>
@@ -5312,16 +5312,16 @@
         <v>44769</v>
       </c>
       <c r="B245" t="n">
-        <v>3.999256372451782</v>
+        <v>3.999255418777466</v>
       </c>
       <c r="C245" t="n">
-        <v>3.999256372451782</v>
+        <v>3.999255418777466</v>
       </c>
       <c r="D245" t="n">
-        <v>3.72313848607781</v>
+        <v>3.723137598247368</v>
       </c>
       <c r="E245" t="n">
-        <v>3.740952529562573</v>
+        <v>3.740951637484142</v>
       </c>
       <c r="F245" t="n">
         <v>8689000</v>
@@ -5332,16 +5332,16 @@
         <v>44770</v>
       </c>
       <c r="B246" t="n">
-        <v>3.999256372451782</v>
+        <v>3.999255418777466</v>
       </c>
       <c r="C246" t="n">
-        <v>4.070512971111132</v>
+        <v>4.07051200044476</v>
       </c>
       <c r="D246" t="n">
-        <v>3.892372111543206</v>
+        <v>3.892371183356821</v>
       </c>
       <c r="E246" t="n">
-        <v>4.025977650039076</v>
+        <v>4.025976689992726</v>
       </c>
       <c r="F246" t="n">
         <v>3634200</v>
@@ -5352,16 +5352,16 @@
         <v>44771</v>
       </c>
       <c r="B247" t="n">
-        <v>3.92799973487854</v>
+        <v>3.927999496459961</v>
       </c>
       <c r="C247" t="n">
-        <v>4.088326532037827</v>
+        <v>4.08832628388786</v>
       </c>
       <c r="D247" t="n">
-        <v>3.919092926547607</v>
+        <v>3.919092688669646</v>
       </c>
       <c r="E247" t="n">
-        <v>4.025977174840299</v>
+        <v>4.025976930474763</v>
       </c>
       <c r="F247" t="n">
         <v>8694600</v>
@@ -5372,16 +5372,16 @@
         <v>44774</v>
       </c>
       <c r="B248" t="n">
-        <v>3.92799973487854</v>
+        <v>3.927999496459961</v>
       </c>
       <c r="C248" t="n">
-        <v>3.990349092076068</v>
+        <v>3.990348849873058</v>
       </c>
       <c r="D248" t="n">
-        <v>3.874557610732194</v>
+        <v>3.874557375557402</v>
       </c>
       <c r="E248" t="n">
-        <v>3.981441859024886</v>
+        <v>3.98144161736252</v>
       </c>
       <c r="F248" t="n">
         <v>7696400</v>
@@ -5492,16 +5492,16 @@
         <v>44782</v>
       </c>
       <c r="B254" t="n">
-        <v>4.382258415222168</v>
+        <v>4.382258892059326</v>
       </c>
       <c r="C254" t="n">
-        <v>4.578212869889715</v>
+        <v>4.578213368048839</v>
       </c>
       <c r="D254" t="n">
-        <v>4.364444373888754</v>
+        <v>4.364444848787552</v>
       </c>
       <c r="E254" t="n">
-        <v>4.453514580555821</v>
+        <v>4.453515065146422</v>
       </c>
       <c r="F254" t="n">
         <v>9216300</v>
@@ -5532,16 +5532,16 @@
         <v>44784</v>
       </c>
       <c r="B256" t="n">
-        <v>4.346630573272705</v>
+        <v>4.346630096435547</v>
       </c>
       <c r="C256" t="n">
-        <v>4.685097802072197</v>
+        <v>4.685097288104267</v>
       </c>
       <c r="D256" t="n">
-        <v>4.311002488632787</v>
+        <v>4.311002015704126</v>
       </c>
       <c r="E256" t="n">
-        <v>4.61384120807209</v>
+        <v>4.613840701921201</v>
       </c>
       <c r="F256" t="n">
         <v>11482900</v>
@@ -5592,16 +5592,16 @@
         <v>44789</v>
       </c>
       <c r="B259" t="n">
-        <v>4.622748374938965</v>
+        <v>4.622747898101807</v>
       </c>
       <c r="C259" t="n">
-        <v>4.702911776583077</v>
+        <v>4.702911291477053</v>
       </c>
       <c r="D259" t="n">
-        <v>4.560399015357959</v>
+        <v>4.560398544952146</v>
       </c>
       <c r="E259" t="n">
-        <v>4.676190501128285</v>
+        <v>4.676190018778564</v>
       </c>
       <c r="F259" t="n">
         <v>5754000</v>
@@ -5632,16 +5632,16 @@
         <v>44791</v>
       </c>
       <c r="B261" t="n">
-        <v>4.533677101135254</v>
+        <v>4.533677577972412</v>
       </c>
       <c r="C261" t="n">
-        <v>4.711817479979008</v>
+        <v>4.711817975552381</v>
       </c>
       <c r="D261" t="n">
-        <v>4.515863063250879</v>
+        <v>4.515863538214415</v>
       </c>
       <c r="E261" t="n">
-        <v>4.640561328441506</v>
+        <v>4.640561816520393</v>
       </c>
       <c r="F261" t="n">
         <v>8785600</v>
@@ -5692,16 +5692,16 @@
         <v>44796</v>
       </c>
       <c r="B264" t="n">
-        <v>4.471328735351562</v>
+        <v>4.471328258514404</v>
       </c>
       <c r="C264" t="n">
-        <v>4.471328735351562</v>
+        <v>4.471328258514404</v>
       </c>
       <c r="D264" t="n">
-        <v>4.311002359282476</v>
+        <v>4.311001899543048</v>
       </c>
       <c r="E264" t="n">
-        <v>4.311002359282476</v>
+        <v>4.311001899543048</v>
       </c>
       <c r="F264" t="n">
         <v>6333000</v>
@@ -5712,16 +5712,16 @@
         <v>44797</v>
       </c>
       <c r="B265" t="n">
-        <v>4.533677101135254</v>
+        <v>4.533677577972412</v>
       </c>
       <c r="C265" t="n">
-        <v>4.604933252672756</v>
+        <v>4.6049337370044</v>
       </c>
       <c r="D265" t="n">
-        <v>4.426792449108837</v>
+        <v>4.426792914704221</v>
       </c>
       <c r="E265" t="n">
-        <v>4.453513718295483</v>
+        <v>4.453514186701321</v>
       </c>
       <c r="F265" t="n">
         <v>5861300</v>
@@ -5732,16 +5732,16 @@
         <v>44798</v>
       </c>
       <c r="B266" t="n">
-        <v>4.480235576629639</v>
+        <v>4.480236053466797</v>
       </c>
       <c r="C266" t="n">
-        <v>4.604933858217994</v>
+        <v>4.604934348326948</v>
       </c>
       <c r="D266" t="n">
-        <v>4.453514303929166</v>
+        <v>4.453514777922345</v>
       </c>
       <c r="E266" t="n">
-        <v>4.587119817991086</v>
+        <v>4.587120306204069</v>
       </c>
       <c r="F266" t="n">
         <v>4135100</v>
@@ -5792,16 +5792,16 @@
         <v>44803</v>
       </c>
       <c r="B269" t="n">
-        <v>4.364444255828857</v>
+        <v>4.364443778991699</v>
       </c>
       <c r="C269" t="n">
-        <v>4.480235733723964</v>
+        <v>4.480235244236013</v>
       </c>
       <c r="D269" t="n">
-        <v>4.337722982191434</v>
+        <v>4.337722508273708</v>
       </c>
       <c r="E269" t="n">
-        <v>4.471328500938078</v>
+        <v>4.471328012423286</v>
       </c>
       <c r="F269" t="n">
         <v>7827400</v>
@@ -5812,16 +5812,16 @@
         <v>44804</v>
       </c>
       <c r="B270" t="n">
-        <v>4.311001777648926</v>
+        <v>4.311002254486084</v>
       </c>
       <c r="C270" t="n">
-        <v>4.43570005332301</v>
+        <v>4.435700543952965</v>
       </c>
       <c r="D270" t="n">
-        <v>4.284280506215807</v>
+        <v>4.284280980097343</v>
       </c>
       <c r="E270" t="n">
-        <v>4.382257935176974</v>
+        <v>4.382258419895731</v>
       </c>
       <c r="F270" t="n">
         <v>8375100</v>
@@ -5832,16 +5832,16 @@
         <v>44805</v>
       </c>
       <c r="B271" t="n">
-        <v>4.248652458190918</v>
+        <v>4.248652935028076</v>
       </c>
       <c r="C271" t="n">
-        <v>4.42679285329989</v>
+        <v>4.426793350130201</v>
       </c>
       <c r="D271" t="n">
-        <v>4.177396300147329</v>
+        <v>4.177396768987227</v>
       </c>
       <c r="E271" t="n">
-        <v>4.346629887860955</v>
+        <v>4.346630375694371</v>
       </c>
       <c r="F271" t="n">
         <v>13026600</v>
@@ -5852,16 +5852,16 @@
         <v>44806</v>
       </c>
       <c r="B272" t="n">
-        <v>4.097233295440674</v>
+        <v>4.097233772277832</v>
       </c>
       <c r="C272" t="n">
-        <v>4.355537105009048</v>
+        <v>4.355537611907676</v>
       </c>
       <c r="D272" t="n">
-        <v>4.097233295440674</v>
+        <v>4.097233772277832</v>
       </c>
       <c r="E272" t="n">
-        <v>4.319909022635495</v>
+        <v>4.319909525387717</v>
       </c>
       <c r="F272" t="n">
         <v>69570300</v>
@@ -5872,16 +5872,16 @@
         <v>44809</v>
       </c>
       <c r="B273" t="n">
-        <v>4.115047454833984</v>
+        <v>4.115046977996826</v>
       </c>
       <c r="C273" t="n">
-        <v>4.221931705024937</v>
+        <v>4.221931215802409</v>
       </c>
       <c r="D273" t="n">
-        <v>4.115047454833984</v>
+        <v>4.115046977996826</v>
       </c>
       <c r="E273" t="n">
-        <v>4.123954688043359</v>
+        <v>4.123954210174062</v>
       </c>
       <c r="F273" t="n">
         <v>7604300</v>
@@ -5892,16 +5892,16 @@
         <v>44810</v>
       </c>
       <c r="B274" t="n">
-        <v>3.954720497131348</v>
+        <v>3.954720735549927</v>
       </c>
       <c r="C274" t="n">
-        <v>4.177396197928922</v>
+        <v>4.177396449771971</v>
       </c>
       <c r="D274" t="n">
-        <v>3.945813265233752</v>
+        <v>3.94581350311534</v>
       </c>
       <c r="E274" t="n">
-        <v>4.141768119778925</v>
+        <v>4.141768369474061</v>
       </c>
       <c r="F274" t="n">
         <v>14609100</v>
@@ -5912,16 +5912,16 @@
         <v>44812</v>
       </c>
       <c r="B275" t="n">
-        <v>3.910185575485229</v>
+        <v>3.91018533706665</v>
       </c>
       <c r="C275" t="n">
-        <v>4.008163012489984</v>
+        <v>4.008162768097356</v>
       </c>
       <c r="D275" t="n">
-        <v>3.856743452951791</v>
+        <v>3.856743217791777</v>
       </c>
       <c r="E275" t="n">
-        <v>3.990348971645505</v>
+        <v>3.990348728339065</v>
       </c>
       <c r="F275" t="n">
         <v>9864000</v>
@@ -5932,16 +5932,16 @@
         <v>44813</v>
       </c>
       <c r="B276" t="n">
-        <v>3.910185575485229</v>
+        <v>3.91018533706665</v>
       </c>
       <c r="C276" t="n">
-        <v>4.043791094178943</v>
+        <v>4.043790847613938</v>
       </c>
       <c r="D276" t="n">
-        <v>3.883464726578628</v>
+        <v>3.883464489789319</v>
       </c>
       <c r="E276" t="n">
-        <v>3.945813657174188</v>
+        <v>3.945813416583232</v>
       </c>
       <c r="F276" t="n">
         <v>15548300</v>
@@ -5952,16 +5952,16 @@
         <v>44816</v>
       </c>
       <c r="B277" t="n">
-        <v>3.856743812561035</v>
+        <v>3.856743335723877</v>
       </c>
       <c r="C277" t="n">
-        <v>3.990349343712352</v>
+        <v>3.990348850356574</v>
       </c>
       <c r="D277" t="n">
-        <v>3.838929770055544</v>
+        <v>3.838929295420866</v>
       </c>
       <c r="E277" t="n">
-        <v>3.95472125870137</v>
+        <v>3.954720769750552</v>
       </c>
       <c r="F277" t="n">
         <v>15738600</v>
@@ -5972,16 +5972,16 @@
         <v>44817</v>
       </c>
       <c r="B278" t="n">
-        <v>3.696416854858398</v>
+        <v>3.696417331695557</v>
       </c>
       <c r="C278" t="n">
-        <v>3.883464484422043</v>
+        <v>3.883464985388314</v>
       </c>
       <c r="D278" t="n">
-        <v>3.678602815124728</v>
+        <v>3.678603289663878</v>
       </c>
       <c r="E278" t="n">
-        <v>3.874557252195103</v>
+        <v>3.874557752012343</v>
       </c>
       <c r="F278" t="n">
         <v>21443000</v>
@@ -6012,16 +6012,16 @@
         <v>44819</v>
       </c>
       <c r="B280" t="n">
-        <v>3.74985933303833</v>
+        <v>3.749859094619751</v>
       </c>
       <c r="C280" t="n">
-        <v>3.758766141397721</v>
+        <v>3.758765902412841</v>
       </c>
       <c r="D280" t="n">
-        <v>3.634067851324498</v>
+        <v>3.634067620268019</v>
       </c>
       <c r="E280" t="n">
-        <v>3.740952099958689</v>
+        <v>3.740951862106438</v>
       </c>
       <c r="F280" t="n">
         <v>12717200</v>
@@ -6032,16 +6032,16 @@
         <v>44820</v>
       </c>
       <c r="B281" t="n">
-        <v>3.821115493774414</v>
+        <v>3.821115255355835</v>
       </c>
       <c r="C281" t="n">
-        <v>3.892371659436928</v>
+        <v>3.892371416572319</v>
       </c>
       <c r="D281" t="n">
-        <v>3.660789121033758</v>
+        <v>3.660788892618747</v>
       </c>
       <c r="E281" t="n">
-        <v>3.696417203865015</v>
+        <v>3.696416973226988</v>
       </c>
       <c r="F281" t="n">
         <v>19813000</v>
@@ -6072,16 +6072,16 @@
         <v>44824</v>
       </c>
       <c r="B283" t="n">
-        <v>3.963627576828003</v>
+        <v>3.963628053665161</v>
       </c>
       <c r="C283" t="n">
-        <v>4.13286117203624</v>
+        <v>4.132861669232745</v>
       </c>
       <c r="D283" t="n">
-        <v>3.919092688438607</v>
+        <v>3.919093159918075</v>
       </c>
       <c r="E283" t="n">
-        <v>3.990348849637818</v>
+        <v>3.990349329689632</v>
       </c>
       <c r="F283" t="n">
         <v>10696200</v>
@@ -6092,16 +6092,16 @@
         <v>44825</v>
       </c>
       <c r="B284" t="n">
-        <v>3.883464336395264</v>
+        <v>3.88346529006958</v>
       </c>
       <c r="C284" t="n">
-        <v>4.034883880719878</v>
+        <v>4.034884871578759</v>
       </c>
       <c r="D284" t="n">
-        <v>3.830022219231316</v>
+        <v>3.830023159781687</v>
       </c>
       <c r="E284" t="n">
-        <v>3.97253453166851</v>
+        <v>3.972535507216069</v>
       </c>
       <c r="F284" t="n">
         <v>18275700</v>
@@ -6132,16 +6132,16 @@
         <v>44827</v>
       </c>
       <c r="B286" t="n">
-        <v>3.910185575485229</v>
+        <v>3.91018533706665</v>
       </c>
       <c r="C286" t="n">
-        <v>3.990348971645505</v>
+        <v>3.990348728339065</v>
       </c>
       <c r="D286" t="n">
-        <v>3.847836644889669</v>
+        <v>3.847836410272737</v>
       </c>
       <c r="E286" t="n">
-        <v>3.963627698018668</v>
+        <v>3.963627456341523</v>
       </c>
       <c r="F286" t="n">
         <v>14173200</v>
@@ -6152,16 +6152,16 @@
         <v>44830</v>
       </c>
       <c r="B287" t="n">
-        <v>3.821115493774414</v>
+        <v>3.821115255355835</v>
       </c>
       <c r="C287" t="n">
-        <v>3.936906975336123</v>
+        <v>3.936906729692732</v>
       </c>
       <c r="D287" t="n">
-        <v>3.794394644011096</v>
+        <v>3.794394407259765</v>
       </c>
       <c r="E287" t="n">
-        <v>3.901278892504866</v>
+        <v>3.901278649084491</v>
       </c>
       <c r="F287" t="n">
         <v>9718800</v>
@@ -6172,16 +6172,16 @@
         <v>44831</v>
       </c>
       <c r="B288" t="n">
-        <v>3.73204493522644</v>
+        <v>3.732045412063599</v>
       </c>
       <c r="C288" t="n">
-        <v>3.919092564835227</v>
+        <v>3.91909306557115</v>
       </c>
       <c r="D288" t="n">
-        <v>3.73204493522644</v>
+        <v>3.732045412063599</v>
       </c>
       <c r="E288" t="n">
-        <v>3.838929173654259</v>
+        <v>3.838929664147838</v>
       </c>
       <c r="F288" t="n">
         <v>11052300</v>
@@ -6212,16 +6212,16 @@
         <v>44833</v>
       </c>
       <c r="B290" t="n">
-        <v>3.696416854858398</v>
+        <v>3.696417331695557</v>
       </c>
       <c r="C290" t="n">
-        <v>3.714230894592069</v>
+        <v>3.714231373727235</v>
       </c>
       <c r="D290" t="n">
-        <v>3.616253463696776</v>
+        <v>3.616253930192871</v>
       </c>
       <c r="E290" t="n">
-        <v>3.660788775391057</v>
+        <v>3.660789247632199</v>
       </c>
       <c r="F290" t="n">
         <v>12380300</v>
@@ -6232,16 +6232,16 @@
         <v>44834</v>
       </c>
       <c r="B291" t="n">
-        <v>3.73204493522644</v>
+        <v>3.732045412063599</v>
       </c>
       <c r="C291" t="n">
-        <v>3.794394286669439</v>
+        <v>3.79439477147287</v>
       </c>
       <c r="D291" t="n">
-        <v>3.651881544045472</v>
+        <v>3.651882010640287</v>
       </c>
       <c r="E291" t="n">
-        <v>3.660788776274561</v>
+        <v>3.660789244007439</v>
       </c>
       <c r="F291" t="n">
         <v>11827700</v>
@@ -6252,16 +6252,16 @@
         <v>44837</v>
       </c>
       <c r="B292" t="n">
-        <v>3.939894914627075</v>
+        <v>3.939894437789917</v>
       </c>
       <c r="C292" t="n">
-        <v>3.939894914627075</v>
+        <v>3.939894437789917</v>
       </c>
       <c r="D292" t="n">
-        <v>3.796299788355527</v>
+        <v>3.796299328897384</v>
       </c>
       <c r="E292" t="n">
-        <v>3.814249179139471</v>
+        <v>3.814248717508951</v>
       </c>
       <c r="F292" t="n">
         <v>14167700</v>
@@ -6292,16 +6292,16 @@
         <v>44839</v>
       </c>
       <c r="B294" t="n">
-        <v>3.975793838500977</v>
+        <v>3.97579288482666</v>
       </c>
       <c r="C294" t="n">
-        <v>3.975793838500977</v>
+        <v>3.97579288482666</v>
       </c>
       <c r="D294" t="n">
-        <v>3.868097489942528</v>
+        <v>3.868096562101353</v>
       </c>
       <c r="E294" t="n">
-        <v>3.921945664221753</v>
+        <v>3.921944723464007</v>
       </c>
       <c r="F294" t="n">
         <v>8368900</v>
@@ -6312,16 +6312,16 @@
         <v>44840</v>
       </c>
       <c r="B295" t="n">
-        <v>4.0027174949646</v>
+        <v>4.002717971801758</v>
       </c>
       <c r="C295" t="n">
-        <v>4.029641363794418</v>
+        <v>4.029641843838973</v>
       </c>
       <c r="D295" t="n">
-        <v>3.975793198187602</v>
+        <v>3.975793671817313</v>
       </c>
       <c r="E295" t="n">
-        <v>3.993742586723207</v>
+        <v>3.9937430624912</v>
       </c>
       <c r="F295" t="n">
         <v>5975200</v>
@@ -6332,16 +6332,16 @@
         <v>44841</v>
       </c>
       <c r="B296" t="n">
-        <v>3.760400295257568</v>
+        <v>3.760401010513306</v>
       </c>
       <c r="C296" t="n">
-        <v>4.002717238964039</v>
+        <v>4.002718000310238</v>
       </c>
       <c r="D296" t="n">
-        <v>3.715526612814938</v>
+        <v>3.715527319535371</v>
       </c>
       <c r="E296" t="n">
-        <v>3.984767851576418</v>
+        <v>3.984768609508511</v>
       </c>
       <c r="F296" t="n">
         <v>16354500</v>
@@ -6352,16 +6352,16 @@
         <v>44844</v>
       </c>
       <c r="B297" t="n">
-        <v>3.661679029464722</v>
+        <v>3.661678791046143</v>
       </c>
       <c r="C297" t="n">
-        <v>3.80527415126421</v>
+        <v>3.805273903495892</v>
       </c>
       <c r="D297" t="n">
-        <v>3.634755158100927</v>
+        <v>3.63475492143541</v>
       </c>
       <c r="E297" t="n">
-        <v>3.80527415126421</v>
+        <v>3.805273903495892</v>
       </c>
       <c r="F297" t="n">
         <v>18862600</v>
@@ -6392,16 +6392,16 @@
         <v>44847</v>
       </c>
       <c r="B299" t="n">
-        <v>3.814249277114868</v>
+        <v>3.814249038696289</v>
       </c>
       <c r="C299" t="n">
-        <v>3.903996233339887</v>
+        <v>3.903995989311464</v>
       </c>
       <c r="D299" t="n">
-        <v>3.796299885869864</v>
+        <v>3.796299648573254</v>
       </c>
       <c r="E299" t="n">
-        <v>3.895021751691007</v>
+        <v>3.895021508223556</v>
       </c>
       <c r="F299" t="n">
         <v>15027200</v>
@@ -6412,16 +6412,16 @@
         <v>44848</v>
       </c>
       <c r="B300" t="n">
-        <v>3.688602924346924</v>
+        <v>3.688603401184082</v>
       </c>
       <c r="C300" t="n">
-        <v>3.832198030402241</v>
+        <v>3.832198525802385</v>
       </c>
       <c r="D300" t="n">
-        <v>3.67962801624488</v>
+        <v>3.679628491921824</v>
       </c>
       <c r="E300" t="n">
-        <v>3.82322355024737</v>
+        <v>3.823224044487355</v>
       </c>
       <c r="F300" t="n">
         <v>10535000</v>
@@ -6432,16 +6432,16 @@
         <v>44851</v>
       </c>
       <c r="B301" t="n">
-        <v>3.679628372192383</v>
+        <v>3.679628133773804</v>
       </c>
       <c r="C301" t="n">
-        <v>3.769375322158595</v>
+        <v>3.769375077924933</v>
       </c>
       <c r="D301" t="n">
-        <v>3.670653891169369</v>
+        <v>3.670653653332284</v>
       </c>
       <c r="E301" t="n">
-        <v>3.724502061149096</v>
+        <v>3.724501819822962</v>
       </c>
       <c r="F301" t="n">
         <v>8129100</v>
@@ -6452,16 +6452,16 @@
         <v>44852</v>
       </c>
       <c r="B302" t="n">
-        <v>3.715527057647705</v>
+        <v>3.715527296066284</v>
       </c>
       <c r="C302" t="n">
-        <v>3.787324615793987</v>
+        <v>3.787324858819684</v>
       </c>
       <c r="D302" t="n">
-        <v>3.661678889037994</v>
+        <v>3.661679124001235</v>
       </c>
       <c r="E302" t="n">
-        <v>3.724501966389592</v>
+        <v>3.724502205384074</v>
       </c>
       <c r="F302" t="n">
         <v>13196400</v>
@@ -6472,16 +6472,16 @@
         <v>44853</v>
       </c>
       <c r="B303" t="n">
-        <v>3.733476400375366</v>
+        <v>3.733476161956787</v>
       </c>
       <c r="C303" t="n">
-        <v>3.769375178998422</v>
+        <v>3.769374938287358</v>
       </c>
       <c r="D303" t="n">
-        <v>3.670653751758618</v>
+        <v>3.670653517351873</v>
       </c>
       <c r="E303" t="n">
-        <v>3.715527011063839</v>
+        <v>3.715526773791502</v>
       </c>
       <c r="F303" t="n">
         <v>12625300</v>
@@ -6492,16 +6492,16 @@
         <v>44854</v>
       </c>
       <c r="B304" t="n">
-        <v>3.769375085830688</v>
+        <v>3.769375324249268</v>
       </c>
       <c r="C304" t="n">
-        <v>3.796299383106091</v>
+        <v>3.796299623227672</v>
       </c>
       <c r="D304" t="n">
-        <v>3.706552438766729</v>
+        <v>3.706552673211682</v>
       </c>
       <c r="E304" t="n">
-        <v>3.760400605370346</v>
+        <v>3.760400843221276</v>
       </c>
       <c r="F304" t="n">
         <v>13428400</v>
@@ -6512,16 +6512,16 @@
         <v>44855</v>
       </c>
       <c r="B305" t="n">
-        <v>3.832198619842529</v>
+        <v>3.832197904586792</v>
       </c>
       <c r="C305" t="n">
-        <v>3.859122920342783</v>
+        <v>3.859122200061794</v>
       </c>
       <c r="D305" t="n">
-        <v>3.73347675527125</v>
+        <v>3.733476058441326</v>
       </c>
       <c r="E305" t="n">
-        <v>3.760401055771503</v>
+        <v>3.760400353916329</v>
       </c>
       <c r="F305" t="n">
         <v>14614900</v>
@@ -6532,16 +6532,16 @@
         <v>44858</v>
       </c>
       <c r="B306" t="n">
-        <v>3.706552267074585</v>
+        <v>3.706552505493164</v>
       </c>
       <c r="C306" t="n">
-        <v>3.778349819220322</v>
+        <v>3.778350062257174</v>
       </c>
       <c r="D306" t="n">
-        <v>3.697577359082784</v>
+        <v>3.697577596924065</v>
       </c>
       <c r="E306" t="n">
-        <v>3.769374911228521</v>
+        <v>3.769375153688075</v>
       </c>
       <c r="F306" t="n">
         <v>9021900</v>
@@ -6552,16 +6552,16 @@
         <v>44859</v>
       </c>
       <c r="B307" t="n">
-        <v>3.670654058456421</v>
+        <v>3.670653820037842</v>
       </c>
       <c r="C307" t="n">
-        <v>3.769375493944795</v>
+        <v>3.769375249114001</v>
       </c>
       <c r="D307" t="n">
-        <v>3.661679149077169</v>
+        <v>3.661678911241534</v>
       </c>
       <c r="E307" t="n">
-        <v>3.706552840078963</v>
+        <v>3.706552599328664</v>
       </c>
       <c r="F307" t="n">
         <v>12220200</v>
@@ -6572,16 +6572,16 @@
         <v>44860</v>
       </c>
       <c r="B308" t="n">
-        <v>3.562957286834717</v>
+        <v>3.562957048416138</v>
       </c>
       <c r="C308" t="n">
-        <v>3.670653839244302</v>
+        <v>3.670653593619109</v>
       </c>
       <c r="D308" t="n">
-        <v>3.545007897095387</v>
+        <v>3.545007659877907</v>
       </c>
       <c r="E308" t="n">
-        <v>3.661678930401033</v>
+        <v>3.661678685376404</v>
       </c>
       <c r="F308" t="n">
         <v>15630800</v>
@@ -6592,16 +6592,16 @@
         <v>44861</v>
       </c>
       <c r="B309" t="n">
-        <v>3.706552267074585</v>
+        <v>3.706552505493164</v>
       </c>
       <c r="C309" t="n">
-        <v>3.760400431183887</v>
+        <v>3.760400673066171</v>
       </c>
       <c r="D309" t="n">
-        <v>3.580906336845962</v>
+        <v>3.580906567182549</v>
       </c>
       <c r="E309" t="n">
-        <v>3.580906336845962</v>
+        <v>3.580906567182549</v>
       </c>
       <c r="F309" t="n">
         <v>15175200</v>
@@ -6612,16 +6612,16 @@
         <v>44862</v>
       </c>
       <c r="B310" t="n">
-        <v>3.724502086639404</v>
+        <v>3.724502325057983</v>
       </c>
       <c r="C310" t="n">
-        <v>3.73347656772384</v>
+        <v>3.733476806716907</v>
       </c>
       <c r="D310" t="n">
-        <v>3.643729617143404</v>
+        <v>3.643729850391451</v>
       </c>
       <c r="E310" t="n">
-        <v>3.68860330640723</v>
+        <v>3.688603542527801</v>
       </c>
       <c r="F310" t="n">
         <v>9985100</v>
@@ -6632,16 +6632,16 @@
         <v>44865</v>
       </c>
       <c r="B311" t="n">
-        <v>3.850147485733032</v>
+        <v>3.850147724151611</v>
       </c>
       <c r="C311" t="n">
-        <v>3.868096874302645</v>
+        <v>3.868097113832732</v>
       </c>
       <c r="D311" t="n">
-        <v>3.54500766607602</v>
+        <v>3.545007885598959</v>
       </c>
       <c r="E311" t="n">
-        <v>3.589881137500053</v>
+        <v>3.58988135980176</v>
       </c>
       <c r="F311" t="n">
         <v>19491700</v>
@@ -6692,16 +6692,16 @@
         <v>44869</v>
       </c>
       <c r="B314" t="n">
-        <v>4.23606014251709</v>
+        <v>4.236059665679932</v>
       </c>
       <c r="C314" t="n">
-        <v>4.34375691684548</v>
+        <v>4.343756427885306</v>
       </c>
       <c r="D314" t="n">
-        <v>4.155288096704846</v>
+        <v>4.15528762895989</v>
       </c>
       <c r="E314" t="n">
-        <v>4.218110751453565</v>
+        <v>4.218110276636901</v>
       </c>
       <c r="F314" t="n">
         <v>12500600</v>
@@ -6712,16 +6712,16 @@
         <v>44872</v>
       </c>
       <c r="B315" t="n">
-        <v>4.011692047119141</v>
+        <v>4.011692523956299</v>
       </c>
       <c r="C315" t="n">
-        <v>4.37965516061104</v>
+        <v>4.379655681184977</v>
       </c>
       <c r="D315" t="n">
-        <v>4.011692047119141</v>
+        <v>4.011692523956299</v>
       </c>
       <c r="E315" t="n">
-        <v>4.3168320856375</v>
+        <v>4.316832598744169</v>
       </c>
       <c r="F315" t="n">
         <v>17217400</v>
@@ -6752,16 +6752,16 @@
         <v>44874</v>
       </c>
       <c r="B317" t="n">
-        <v>4.011692047119141</v>
+        <v>4.011692523956299</v>
       </c>
       <c r="C317" t="n">
-        <v>4.173236974780477</v>
+        <v>4.173237470819165</v>
       </c>
       <c r="D317" t="n">
-        <v>3.984768177807042</v>
+        <v>3.98476865144398</v>
       </c>
       <c r="E317" t="n">
-        <v>4.06554064163771</v>
+        <v>4.065541124875413</v>
       </c>
       <c r="F317" t="n">
         <v>11339500</v>
@@ -6772,16 +6772,16 @@
         <v>44875</v>
       </c>
       <c r="B318" t="n">
-        <v>3.688602924346924</v>
+        <v>3.688603401184082</v>
       </c>
       <c r="C318" t="n">
-        <v>3.975793136457558</v>
+        <v>3.975793650420687</v>
       </c>
       <c r="D318" t="n">
-        <v>3.670653536090009</v>
+        <v>3.670654010606794</v>
       </c>
       <c r="E318" t="n">
-        <v>3.921944971686814</v>
+        <v>3.921945478688824</v>
       </c>
       <c r="F318" t="n">
         <v>22566600</v>
@@ -6792,16 +6792,16 @@
         <v>44876</v>
       </c>
       <c r="B319" t="n">
-        <v>3.715527057647705</v>
+        <v>3.715527296066284</v>
       </c>
       <c r="C319" t="n">
-        <v>3.751425836720846</v>
+        <v>3.751426077442984</v>
       </c>
       <c r="D319" t="n">
-        <v>3.437311305857262</v>
+        <v>3.437311526423245</v>
       </c>
       <c r="E319" t="n">
-        <v>3.634755018706739</v>
+        <v>3.634755251942325</v>
       </c>
       <c r="F319" t="n">
         <v>24235200</v>
@@ -6812,16 +6812,16 @@
         <v>44879</v>
       </c>
       <c r="B320" t="n">
-        <v>3.697577953338623</v>
+        <v>3.697577714920044</v>
       </c>
       <c r="C320" t="n">
-        <v>3.796299817378669</v>
+        <v>3.796299572594537</v>
       </c>
       <c r="D320" t="n">
-        <v>3.643729780575117</v>
+        <v>3.64372954562865</v>
       </c>
       <c r="E320" t="n">
-        <v>3.760401035536331</v>
+        <v>3.760400793066941</v>
       </c>
       <c r="F320" t="n">
         <v>10873300</v>
@@ -6832,16 +6832,16 @@
         <v>44881</v>
       </c>
       <c r="B321" t="n">
-        <v>3.616805791854858</v>
+        <v>3.616805553436279</v>
       </c>
       <c r="C321" t="n">
-        <v>3.760400914606361</v>
+        <v>3.760400666722041</v>
       </c>
       <c r="D321" t="n">
-        <v>3.553982711677465</v>
+        <v>3.553982477400161</v>
       </c>
       <c r="E321" t="n">
-        <v>3.697577834428968</v>
+        <v>3.697577590685923</v>
       </c>
       <c r="F321" t="n">
         <v>16148800</v>
@@ -6872,16 +6872,16 @@
         <v>44883</v>
       </c>
       <c r="B323" t="n">
-        <v>3.652704477310181</v>
+        <v>3.652704238891602</v>
       </c>
       <c r="C323" t="n">
-        <v>3.841173284981419</v>
+        <v>3.841173034261142</v>
       </c>
       <c r="D323" t="n">
-        <v>3.536033229142802</v>
+        <v>3.536032998339565</v>
       </c>
       <c r="E323" t="n">
-        <v>3.580906703832715</v>
+        <v>3.580906470100505</v>
       </c>
       <c r="F323" t="n">
         <v>23150300</v>
@@ -6892,16 +6892,16 @@
         <v>44886</v>
       </c>
       <c r="B324" t="n">
-        <v>3.616805791854858</v>
+        <v>3.616805553436279</v>
       </c>
       <c r="C324" t="n">
-        <v>3.733476615116843</v>
+        <v>3.733476369007364</v>
       </c>
       <c r="D324" t="n">
-        <v>3.545008016505496</v>
+        <v>3.545007782819801</v>
       </c>
       <c r="E324" t="n">
-        <v>3.67962844408503</v>
+        <v>3.679628201525203</v>
       </c>
       <c r="F324" t="n">
         <v>11314600</v>
@@ -6912,16 +6912,16 @@
         <v>44887</v>
       </c>
       <c r="B325" t="n">
-        <v>3.616805791854858</v>
+        <v>3.616805553436279</v>
       </c>
       <c r="C325" t="n">
-        <v>3.661679053741092</v>
+        <v>3.661678812364483</v>
       </c>
       <c r="D325" t="n">
-        <v>3.562957406849434</v>
+        <v>3.562957171980521</v>
       </c>
       <c r="E325" t="n">
-        <v>3.616805791854858</v>
+        <v>3.616805553436279</v>
       </c>
       <c r="F325" t="n">
         <v>10439300</v>
@@ -6932,16 +6932,16 @@
         <v>44888</v>
       </c>
       <c r="B326" t="n">
-        <v>3.589881181716919</v>
+        <v>3.589881420135498</v>
       </c>
       <c r="C326" t="n">
-        <v>3.643729348089011</v>
+        <v>3.643729590083865</v>
       </c>
       <c r="D326" t="n">
-        <v>3.545007709740176</v>
+        <v>3.545007945178526</v>
       </c>
       <c r="E326" t="n">
-        <v>3.571931792926222</v>
+        <v>3.571932030152709</v>
       </c>
       <c r="F326" t="n">
         <v>6531500</v>
@@ -6952,16 +6952,16 @@
         <v>44889</v>
       </c>
       <c r="B327" t="n">
-        <v>3.724502086639404</v>
+        <v>3.724502325057983</v>
       </c>
       <c r="C327" t="n">
-        <v>3.742451476755492</v>
+        <v>3.742451716323075</v>
       </c>
       <c r="D327" t="n">
-        <v>3.598856355826795</v>
+        <v>3.598856586202345</v>
       </c>
       <c r="E327" t="n">
-        <v>3.634755136058969</v>
+        <v>3.634755368732528</v>
       </c>
       <c r="F327" t="n">
         <v>5511600</v>
@@ -6972,16 +6972,16 @@
         <v>44890</v>
       </c>
       <c r="B328" t="n">
-        <v>3.634754657745361</v>
+        <v>3.63475513458252</v>
       </c>
       <c r="C328" t="n">
-        <v>3.760400372023689</v>
+        <v>3.760400865344091</v>
       </c>
       <c r="D328" t="n">
-        <v>3.58090628050964</v>
+        <v>3.580906750282523</v>
       </c>
       <c r="E328" t="n">
-        <v>3.733476076419039</v>
+        <v>3.733476566207289</v>
       </c>
       <c r="F328" t="n">
         <v>8739900</v>
@@ -7012,16 +7012,16 @@
         <v>44894</v>
       </c>
       <c r="B330" t="n">
-        <v>3.589881181716919</v>
+        <v>3.589881420135498</v>
       </c>
       <c r="C330" t="n">
-        <v>3.715526903251799</v>
+        <v>3.715527150015021</v>
       </c>
       <c r="D330" t="n">
-        <v>3.51808362655413</v>
+        <v>3.518083860204342</v>
       </c>
       <c r="E330" t="n">
-        <v>3.616805478876557</v>
+        <v>3.616805719083288</v>
       </c>
       <c r="F330" t="n">
         <v>13237500</v>
@@ -7032,16 +7032,16 @@
         <v>44895</v>
       </c>
       <c r="B331" t="n">
-        <v>3.634754657745361</v>
+        <v>3.63475513458252</v>
       </c>
       <c r="C331" t="n">
-        <v>3.661678525402851</v>
+        <v>3.661679005772105</v>
       </c>
       <c r="D331" t="n">
-        <v>3.518083423370476</v>
+        <v>3.518083884901738</v>
       </c>
       <c r="E331" t="n">
-        <v>3.571931586632617</v>
+        <v>3.571932055228125</v>
       </c>
       <c r="F331" t="n">
         <v>16877200</v>
@@ -7052,16 +7052,16 @@
         <v>44896</v>
       </c>
       <c r="B332" t="n">
-        <v>3.446285724639893</v>
+        <v>3.446285963058472</v>
       </c>
       <c r="C332" t="n">
-        <v>3.589881043406649</v>
+        <v>3.589881291759341</v>
       </c>
       <c r="D332" t="n">
-        <v>3.428336336540746</v>
+        <v>3.428336573717563</v>
       </c>
       <c r="E332" t="n">
-        <v>3.589881043406649</v>
+        <v>3.589881291759341</v>
       </c>
       <c r="F332" t="n">
         <v>22625600</v>
@@ -7072,16 +7072,16 @@
         <v>44897</v>
       </c>
       <c r="B333" t="n">
-        <v>3.500134706497192</v>
+        <v>3.500134468078613</v>
       </c>
       <c r="C333" t="n">
-        <v>3.625780444858396</v>
+        <v>3.62578019788121</v>
       </c>
       <c r="D333" t="n">
-        <v>3.455261014537427</v>
+        <v>3.455260779175508</v>
       </c>
       <c r="E333" t="n">
-        <v>3.473210405731884</v>
+        <v>3.473210169147307</v>
       </c>
       <c r="F333" t="n">
         <v>16610700</v>
@@ -7092,16 +7092,16 @@
         <v>44900</v>
       </c>
       <c r="B334" t="n">
-        <v>3.347564220428467</v>
+        <v>3.347563982009888</v>
       </c>
       <c r="C334" t="n">
-        <v>3.545007711179917</v>
+        <v>3.545007458699114</v>
       </c>
       <c r="D334" t="n">
-        <v>3.32961483163048</v>
+        <v>3.329614594490283</v>
       </c>
       <c r="E334" t="n">
-        <v>3.545007711179917</v>
+        <v>3.545007458699114</v>
       </c>
       <c r="F334" t="n">
         <v>14607600</v>
@@ -7112,16 +7112,16 @@
         <v>44901</v>
       </c>
       <c r="B335" t="n">
-        <v>3.302690982818604</v>
+        <v>3.302690744400024</v>
       </c>
       <c r="C335" t="n">
-        <v>3.401412628213602</v>
+        <v>3.401412382668387</v>
       </c>
       <c r="D335" t="n">
-        <v>3.248842598629542</v>
+        <v>3.248842364098234</v>
       </c>
       <c r="E335" t="n">
-        <v>3.383463238141784</v>
+        <v>3.383462993892321</v>
       </c>
       <c r="F335" t="n">
         <v>13327400</v>
@@ -7152,16 +7152,16 @@
         <v>44903</v>
       </c>
       <c r="B337" t="n">
-        <v>3.073575496673584</v>
+        <v>3.073575973510742</v>
       </c>
       <c r="C337" t="n">
-        <v>3.266824295516617</v>
+        <v>3.266824802334561</v>
       </c>
       <c r="D337" t="n">
-        <v>3.064373183366795</v>
+        <v>3.064373658776298</v>
       </c>
       <c r="E337" t="n">
-        <v>3.22081272898267</v>
+        <v>3.22081322866234</v>
       </c>
       <c r="F337" t="n">
         <v>19978800</v>
@@ -7192,16 +7192,16 @@
         <v>44907</v>
       </c>
       <c r="B339" t="n">
-        <v>3.036766290664673</v>
+        <v>3.036766529083252</v>
       </c>
       <c r="C339" t="n">
-        <v>3.119587331114006</v>
+        <v>3.119587576034921</v>
       </c>
       <c r="D339" t="n">
-        <v>2.972350096515548</v>
+        <v>2.972350329876769</v>
       </c>
       <c r="E339" t="n">
-        <v>3.082777857914047</v>
+        <v>3.082778099945025</v>
       </c>
       <c r="F339" t="n">
         <v>24013800</v>
@@ -7232,16 +7232,16 @@
         <v>44909</v>
       </c>
       <c r="B341" t="n">
-        <v>3.073575496673584</v>
+        <v>3.073575973510742</v>
       </c>
       <c r="C341" t="n">
-        <v>3.101182436593952</v>
+        <v>3.101182917714075</v>
       </c>
       <c r="D341" t="n">
-        <v>2.935540797071743</v>
+        <v>2.935541252494079</v>
       </c>
       <c r="E341" t="n">
-        <v>2.98155236360569</v>
+        <v>2.9815528261663</v>
       </c>
       <c r="F341" t="n">
         <v>15438000</v>
@@ -7252,16 +7252,16 @@
         <v>44910</v>
       </c>
       <c r="B342" t="n">
-        <v>3.036766290664673</v>
+        <v>3.036766529083252</v>
       </c>
       <c r="C342" t="n">
-        <v>3.137991958013755</v>
+        <v>3.13799220437963</v>
       </c>
       <c r="D342" t="n">
-        <v>3.009159350315048</v>
+        <v>3.009159586566188</v>
       </c>
       <c r="E342" t="n">
-        <v>3.055170917564423</v>
+        <v>3.055171157427961</v>
       </c>
       <c r="F342" t="n">
         <v>8858500</v>
@@ -7292,16 +7292,16 @@
         <v>44914</v>
       </c>
       <c r="B344" t="n">
-        <v>3.073575496673584</v>
+        <v>3.073575973510742</v>
       </c>
       <c r="C344" t="n">
-        <v>3.091980123287163</v>
+        <v>3.091980602979631</v>
       </c>
       <c r="D344" t="n">
-        <v>2.990754676912479</v>
+        <v>2.990755140900744</v>
       </c>
       <c r="E344" t="n">
-        <v>3.009159303526058</v>
+        <v>3.009159770369632</v>
       </c>
       <c r="F344" t="n">
         <v>6693400</v>
@@ -7312,16 +7312,16 @@
         <v>44915</v>
       </c>
       <c r="B345" t="n">
-        <v>3.257622241973877</v>
+        <v>3.257622480392456</v>
       </c>
       <c r="C345" t="n">
-        <v>3.31283612621739</v>
+        <v>3.312836368676958</v>
       </c>
       <c r="D345" t="n">
-        <v>3.036766485599353</v>
+        <v>3.03676670785396</v>
       </c>
       <c r="E345" t="n">
-        <v>3.036766485599353</v>
+        <v>3.03676670785396</v>
       </c>
       <c r="F345" t="n">
         <v>12943700</v>
@@ -7332,16 +7332,16 @@
         <v>44916</v>
       </c>
       <c r="B346" t="n">
-        <v>3.33124041557312</v>
+        <v>3.331240892410278</v>
       </c>
       <c r="C346" t="n">
-        <v>3.377252200497974</v>
+        <v>3.377252683921307</v>
       </c>
       <c r="D346" t="n">
-        <v>3.239217284524313</v>
+        <v>3.239217748189187</v>
       </c>
       <c r="E346" t="n">
-        <v>3.266824223838955</v>
+        <v>3.266824691455514</v>
       </c>
       <c r="F346" t="n">
         <v>14610300</v>
@@ -7352,16 +7352,16 @@
         <v>44917</v>
       </c>
       <c r="B347" t="n">
-        <v>3.340442895889282</v>
+        <v>3.34044337272644</v>
       </c>
       <c r="C347" t="n">
-        <v>3.3588475218115</v>
+        <v>3.358848001275858</v>
       </c>
       <c r="D347" t="n">
-        <v>3.257621859838854</v>
+        <v>3.257622324853584</v>
       </c>
       <c r="E347" t="n">
-        <v>3.331240363527726</v>
+        <v>3.331240839051253</v>
       </c>
       <c r="F347" t="n">
         <v>7727000</v>
@@ -7392,16 +7392,16 @@
         <v>44921</v>
       </c>
       <c r="B349" t="n">
-        <v>3.340442895889282</v>
+        <v>3.34044337272644</v>
       </c>
       <c r="C349" t="n">
-        <v>3.441668338461481</v>
+        <v>3.441668829748236</v>
       </c>
       <c r="D349" t="n">
-        <v>3.28522879872218</v>
+        <v>3.28522926767771</v>
       </c>
       <c r="E349" t="n">
-        <v>3.441668338461481</v>
+        <v>3.441668829748236</v>
       </c>
       <c r="F349" t="n">
         <v>5290600</v>
@@ -7412,16 +7412,16 @@
         <v>44922</v>
       </c>
       <c r="B350" t="n">
-        <v>3.386454820632935</v>
+        <v>3.386454582214355</v>
       </c>
       <c r="C350" t="n">
-        <v>3.395657134572136</v>
+        <v>3.39565689550568</v>
       </c>
       <c r="D350" t="n">
-        <v>3.276026833962055</v>
+        <v>3.276026603318003</v>
       </c>
       <c r="E350" t="n">
-        <v>3.349645564876132</v>
+        <v>3.349645329049056</v>
       </c>
       <c r="F350" t="n">
         <v>5669100</v>
@@ -7432,16 +7432,16 @@
         <v>44923</v>
       </c>
       <c r="B351" t="n">
-        <v>3.450870990753174</v>
+        <v>3.450870752334595</v>
       </c>
       <c r="C351" t="n">
-        <v>3.542894129413071</v>
+        <v>3.542893884636669</v>
       </c>
       <c r="D351" t="n">
-        <v>3.358847852093277</v>
+        <v>3.35884762003252</v>
       </c>
       <c r="E351" t="n">
-        <v>3.395657107557235</v>
+        <v>3.39565687295335</v>
       </c>
       <c r="F351" t="n">
         <v>9716800</v>
@@ -7472,16 +7472,16 @@
         <v>44928</v>
       </c>
       <c r="B353" t="n">
-        <v>3.257622241973877</v>
+        <v>3.257622480392456</v>
       </c>
       <c r="C353" t="n">
-        <v>3.414061800064303</v>
+        <v>3.414062049932367</v>
       </c>
       <c r="D353" t="n">
-        <v>3.23001529985212</v>
+        <v>3.230015536250205</v>
       </c>
       <c r="E353" t="n">
-        <v>3.395657171983132</v>
+        <v>3.3956574205042</v>
       </c>
       <c r="F353" t="n">
         <v>9470500</v>
@@ -7492,16 +7492,16 @@
         <v>44929</v>
       </c>
       <c r="B354" t="n">
-        <v>3.073575496673584</v>
+        <v>3.073575973510742</v>
       </c>
       <c r="C354" t="n">
-        <v>3.285228922130196</v>
+        <v>3.28522943180345</v>
       </c>
       <c r="D354" t="n">
-        <v>3.064373183366795</v>
+        <v>3.064373658776298</v>
       </c>
       <c r="E354" t="n">
-        <v>3.257621982209828</v>
+        <v>3.257622487600117</v>
       </c>
       <c r="F354" t="n">
         <v>9560100</v>
@@ -7512,16 +7512,16 @@
         <v>44930</v>
       </c>
       <c r="B355" t="n">
-        <v>3.055171251296997</v>
+        <v>3.055170774459839</v>
       </c>
       <c r="C355" t="n">
-        <v>3.147194615248405</v>
+        <v>3.147194124048661</v>
       </c>
       <c r="D355" t="n">
-        <v>3.036766622386812</v>
+        <v>3.036766148422164</v>
       </c>
       <c r="E355" t="n">
-        <v>3.110385357428035</v>
+        <v>3.110384871973312</v>
       </c>
       <c r="F355" t="n">
         <v>10680900</v>
@@ -7552,16 +7552,16 @@
         <v>44932</v>
       </c>
       <c r="B357" t="n">
-        <v>2.96314811706543</v>
+        <v>2.963147878646851</v>
       </c>
       <c r="C357" t="n">
-        <v>3.018362003988271</v>
+        <v>3.018361761127114</v>
       </c>
       <c r="D357" t="n">
-        <v>2.917136544629729</v>
+        <v>2.917136309913298</v>
       </c>
       <c r="E357" t="n">
-        <v>2.98155274603971</v>
+        <v>2.981552506140272</v>
       </c>
       <c r="F357" t="n">
         <v>37999700</v>
@@ -7612,16 +7612,16 @@
         <v>44937</v>
       </c>
       <c r="B360" t="n">
-        <v>3.294431686401367</v>
+        <v>3.294431447982788</v>
       </c>
       <c r="C360" t="n">
-        <v>3.294431686401367</v>
+        <v>3.294431447982788</v>
       </c>
       <c r="D360" t="n">
-        <v>3.091980546538645</v>
+        <v>3.091980322771489</v>
       </c>
       <c r="E360" t="n">
-        <v>3.091980546538645</v>
+        <v>3.091980322771489</v>
       </c>
       <c r="F360" t="n">
         <v>21444400</v>
@@ -7652,16 +7652,16 @@
         <v>44939</v>
       </c>
       <c r="B362" t="n">
-        <v>3.073575496673584</v>
+        <v>3.073575973510742</v>
       </c>
       <c r="C362" t="n">
-        <v>3.22081272898267</v>
+        <v>3.22081322866234</v>
       </c>
       <c r="D362" t="n">
-        <v>3.055170870060005</v>
+        <v>3.055171344041854</v>
       </c>
       <c r="E362" t="n">
-        <v>3.184003475755512</v>
+        <v>3.184003969724563</v>
       </c>
       <c r="F362" t="n">
         <v>14486700</v>
@@ -7672,16 +7672,16 @@
         <v>44942</v>
       </c>
       <c r="B363" t="n">
-        <v>3.036766290664673</v>
+        <v>3.036766529083252</v>
       </c>
       <c r="C363" t="n">
-        <v>3.082777857914047</v>
+        <v>3.082778099945025</v>
       </c>
       <c r="D363" t="n">
-        <v>3.009159350315048</v>
+        <v>3.009159586566188</v>
       </c>
       <c r="E363" t="n">
-        <v>3.055170917564423</v>
+        <v>3.055171157427961</v>
       </c>
       <c r="F363" t="n">
         <v>8730700</v>
@@ -7752,16 +7752,16 @@
         <v>44946</v>
       </c>
       <c r="B367" t="n">
-        <v>3.027564287185669</v>
+        <v>3.02756404876709</v>
       </c>
       <c r="C367" t="n">
-        <v>3.137992279290566</v>
+        <v>3.13799203217586</v>
       </c>
       <c r="D367" t="n">
-        <v>3.009159658401599</v>
+        <v>3.009159421432372</v>
       </c>
       <c r="E367" t="n">
-        <v>3.128789964898532</v>
+        <v>3.128789718508501</v>
       </c>
       <c r="F367" t="n">
         <v>19274300</v>
@@ -7772,16 +7772,16 @@
         <v>44949</v>
       </c>
       <c r="B368" t="n">
-        <v>3.027564287185669</v>
+        <v>3.02756404876709</v>
       </c>
       <c r="C368" t="n">
-        <v>3.082778173537877</v>
+        <v>3.082777930771243</v>
       </c>
       <c r="D368" t="n">
-        <v>2.99075502961753</v>
+        <v>2.990754794097655</v>
       </c>
       <c r="E368" t="n">
-        <v>3.018361972793634</v>
+        <v>3.018361735099731</v>
       </c>
       <c r="F368" t="n">
         <v>10637200</v>
@@ -7792,16 +7792,16 @@
         <v>44950</v>
       </c>
       <c r="B369" t="n">
-        <v>3.193206071853638</v>
+        <v>3.193206310272217</v>
       </c>
       <c r="C369" t="n">
-        <v>3.202408385975387</v>
+        <v>3.202408625081051</v>
       </c>
       <c r="D369" t="n">
-        <v>3.018361884139927</v>
+        <v>3.018362109503883</v>
       </c>
       <c r="E369" t="n">
-        <v>3.045968826505175</v>
+        <v>3.045969053930385</v>
       </c>
       <c r="F369" t="n">
         <v>12703800</v>
@@ -7812,16 +7812,16 @@
         <v>44951</v>
       </c>
       <c r="B370" t="n">
-        <v>3.248420000076294</v>
+        <v>3.248419761657715</v>
       </c>
       <c r="C370" t="n">
-        <v>3.248420000076294</v>
+        <v>3.248419761657715</v>
       </c>
       <c r="D370" t="n">
-        <v>3.147194543381774</v>
+        <v>3.147194312392662</v>
       </c>
       <c r="E370" t="n">
-        <v>3.193206114606555</v>
+        <v>3.193205880240413</v>
       </c>
       <c r="F370" t="n">
         <v>7649000</v>
@@ -7832,16 +7832,16 @@
         <v>44952</v>
       </c>
       <c r="B371" t="n">
-        <v>3.2024085521698</v>
+        <v>3.202408313751221</v>
       </c>
       <c r="C371" t="n">
-        <v>3.28522938356367</v>
+        <v>3.2852291389791</v>
       </c>
       <c r="D371" t="n">
-        <v>3.184003922971162</v>
+        <v>3.184003685922803</v>
       </c>
       <c r="E371" t="n">
-        <v>3.257622439765714</v>
+        <v>3.257622197236473</v>
       </c>
       <c r="F371" t="n">
         <v>8271800</v>
@@ -7872,16 +7872,16 @@
         <v>44956</v>
       </c>
       <c r="B373" t="n">
-        <v>2.990755081176758</v>
+        <v>2.990754842758179</v>
       </c>
       <c r="C373" t="n">
-        <v>3.156396962489453</v>
+        <v>3.156396710866147</v>
       </c>
       <c r="D373" t="n">
-        <v>2.963148137524723</v>
+        <v>2.963147901306928</v>
       </c>
       <c r="E373" t="n">
-        <v>3.128790018837418</v>
+        <v>3.128789769414897</v>
       </c>
       <c r="F373" t="n">
         <v>24955900</v>
@@ -7892,16 +7892,16 @@
         <v>44957</v>
       </c>
       <c r="B374" t="n">
-        <v>3.027564287185669</v>
+        <v>3.02756404876709</v>
       </c>
       <c r="C374" t="n">
-        <v>3.082778173537877</v>
+        <v>3.082777930771243</v>
       </c>
       <c r="D374" t="n">
-        <v>2.99075502961753</v>
+        <v>2.990754794097655</v>
       </c>
       <c r="E374" t="n">
-        <v>2.99075502961753</v>
+        <v>2.990754794097655</v>
       </c>
       <c r="F374" t="n">
         <v>20039900</v>
@@ -7932,16 +7932,16 @@
         <v>44959</v>
       </c>
       <c r="B376" t="n">
-        <v>2.806708335876465</v>
+        <v>2.806708574295044</v>
       </c>
       <c r="C376" t="n">
-        <v>2.972350203327015</v>
+        <v>2.972350455816205</v>
       </c>
       <c r="D376" t="n">
-        <v>2.797506022095904</v>
+        <v>2.797506259732784</v>
       </c>
       <c r="E376" t="n">
-        <v>2.898731693082534</v>
+        <v>2.898731939318127</v>
       </c>
       <c r="F376" t="n">
         <v>50857000</v>
@@ -7952,16 +7952,16 @@
         <v>44960</v>
       </c>
       <c r="B377" t="n">
-        <v>2.843517541885376</v>
+        <v>2.843517303466797</v>
       </c>
       <c r="C377" t="n">
-        <v>2.871124482750229</v>
+        <v>2.871124242016908</v>
       </c>
       <c r="D377" t="n">
-        <v>2.705482837561113</v>
+        <v>2.705482610716241</v>
       </c>
       <c r="E377" t="n">
-        <v>2.806708287398906</v>
+        <v>2.806708052066648</v>
       </c>
       <c r="F377" t="n">
         <v>53290600</v>
@@ -8012,16 +8012,16 @@
         <v>44965</v>
       </c>
       <c r="B380" t="n">
-        <v>3.036766290664673</v>
+        <v>3.036766529083252</v>
       </c>
       <c r="C380" t="n">
-        <v>3.036766290664673</v>
+        <v>3.036766529083252</v>
       </c>
       <c r="D380" t="n">
-        <v>2.861922115716591</v>
+        <v>2.861922340408036</v>
       </c>
       <c r="E380" t="n">
-        <v>2.907933902366425</v>
+        <v>2.907934130670286</v>
       </c>
       <c r="F380" t="n">
         <v>50518000</v>
@@ -8032,16 +8032,16 @@
         <v>44966</v>
       </c>
       <c r="B381" t="n">
-        <v>3.018361806869507</v>
+        <v>3.018362045288086</v>
       </c>
       <c r="C381" t="n">
-        <v>3.091980317958858</v>
+        <v>3.091980562192519</v>
       </c>
       <c r="D381" t="n">
-        <v>2.935540981893987</v>
+        <v>2.935541213770599</v>
       </c>
       <c r="E381" t="n">
-        <v>3.036766434641845</v>
+        <v>3.036766674514194</v>
       </c>
       <c r="F381" t="n">
         <v>43678900</v>
@@ -8052,16 +8052,16 @@
         <v>44967</v>
       </c>
       <c r="B382" t="n">
-        <v>2.953945875167847</v>
+        <v>2.953945636749268</v>
       </c>
       <c r="C382" t="n">
-        <v>3.045969022300604</v>
+        <v>3.045968776454661</v>
       </c>
       <c r="D382" t="n">
-        <v>2.92633893102802</v>
+        <v>2.92633869483765</v>
       </c>
       <c r="E382" t="n">
-        <v>3.018362078160776</v>
+        <v>3.018361834543043</v>
       </c>
       <c r="F382" t="n">
         <v>23226200</v>
@@ -8072,16 +8072,16 @@
         <v>44970</v>
       </c>
       <c r="B383" t="n">
-        <v>2.96314811706543</v>
+        <v>2.963147878646851</v>
       </c>
       <c r="C383" t="n">
-        <v>2.96314811706543</v>
+        <v>2.963147878646851</v>
       </c>
       <c r="D383" t="n">
-        <v>2.880327286681168</v>
+        <v>2.880327054926456</v>
       </c>
       <c r="E383" t="n">
-        <v>2.95394580257829</v>
+        <v>2.95394556490014</v>
       </c>
       <c r="F383" t="n">
         <v>14875700</v>
@@ -8092,16 +8092,16 @@
         <v>44971</v>
       </c>
       <c r="B384" t="n">
-        <v>2.742292165756226</v>
+        <v>2.742292404174805</v>
       </c>
       <c r="C384" t="n">
-        <v>2.953945604142814</v>
+        <v>2.953945860962829</v>
       </c>
       <c r="D384" t="n">
-        <v>2.723887538018302</v>
+        <v>2.723887774836758</v>
       </c>
       <c r="E384" t="n">
-        <v>2.953945604142814</v>
+        <v>2.953945860962829</v>
       </c>
       <c r="F384" t="n">
         <v>40924300</v>
@@ -8112,16 +8112,16 @@
         <v>44972</v>
       </c>
       <c r="B385" t="n">
-        <v>2.843517541885376</v>
+        <v>2.843517303466797</v>
       </c>
       <c r="C385" t="n">
-        <v>2.852719855506993</v>
+        <v>2.852719616316834</v>
       </c>
       <c r="D385" t="n">
-        <v>2.631864109187709</v>
+        <v>2.631863888515499</v>
       </c>
       <c r="E385" t="n">
-        <v>2.733089778425966</v>
+        <v>2.733089549266352</v>
       </c>
       <c r="F385" t="n">
         <v>42760100</v>
@@ -8152,16 +8152,16 @@
         <v>44974</v>
       </c>
       <c r="B387" t="n">
-        <v>2.788303852081299</v>
+        <v>2.78830361366272</v>
       </c>
       <c r="C387" t="n">
-        <v>2.871124680376612</v>
+        <v>2.8711244348763</v>
       </c>
       <c r="D387" t="n">
-        <v>2.769899223571229</v>
+        <v>2.769898986726369</v>
       </c>
       <c r="E387" t="n">
-        <v>2.825113109101438</v>
+        <v>2.825112867535422</v>
       </c>
       <c r="F387" t="n">
         <v>27974700</v>
@@ -8192,16 +8192,16 @@
         <v>44980</v>
       </c>
       <c r="B389" t="n">
-        <v>2.797506093978882</v>
+        <v>2.797505855560303</v>
       </c>
       <c r="C389" t="n">
-        <v>2.898731767566543</v>
+        <v>2.898731520520965</v>
       </c>
       <c r="D389" t="n">
-        <v>2.751494523893796</v>
+        <v>2.751494289396572</v>
       </c>
       <c r="E389" t="n">
-        <v>2.852719978080985</v>
+        <v>2.85271973495678</v>
       </c>
       <c r="F389" t="n">
         <v>24919500</v>
@@ -8232,16 +8232,16 @@
         <v>44984</v>
       </c>
       <c r="B391" t="n">
-        <v>2.797506093978882</v>
+        <v>2.797505855560303</v>
       </c>
       <c r="C391" t="n">
-        <v>2.83431535004695</v>
+        <v>2.834315108491288</v>
       </c>
       <c r="D391" t="n">
-        <v>2.641066536289118</v>
+        <v>2.641066311203163</v>
       </c>
       <c r="E391" t="n">
-        <v>2.677876011757659</v>
+        <v>2.677875783534602</v>
       </c>
       <c r="F391" t="n">
         <v>32246200</v>
@@ -8272,16 +8272,16 @@
         <v>44986</v>
       </c>
       <c r="B393" t="n">
-        <v>2.779101371765137</v>
+        <v>2.779101610183716</v>
       </c>
       <c r="C393" t="n">
-        <v>2.917136296743063</v>
+        <v>2.917136547003632</v>
       </c>
       <c r="D393" t="n">
-        <v>2.751494430649644</v>
+        <v>2.751494666699829</v>
       </c>
       <c r="E393" t="n">
-        <v>2.843517567701285</v>
+        <v>2.843517811646118</v>
       </c>
       <c r="F393" t="n">
         <v>32788900</v>
@@ -8312,16 +8312,16 @@
         <v>44988</v>
       </c>
       <c r="B395" t="n">
-        <v>2.604257345199585</v>
+        <v>2.604257106781006</v>
       </c>
       <c r="C395" t="n">
-        <v>2.71468533555954</v>
+        <v>2.714685087031328</v>
       </c>
       <c r="D395" t="n">
-        <v>2.55824577396647</v>
+        <v>2.558245539760229</v>
       </c>
       <c r="E395" t="n">
-        <v>2.71468533555954</v>
+        <v>2.714685087031328</v>
       </c>
       <c r="F395" t="n">
         <v>36019100</v>
@@ -8332,16 +8332,16 @@
         <v>44991</v>
       </c>
       <c r="B396" t="n">
-        <v>2.677875757217407</v>
+        <v>2.677875995635986</v>
       </c>
       <c r="C396" t="n">
-        <v>2.714685009786644</v>
+        <v>2.714685251482452</v>
       </c>
       <c r="D396" t="n">
-        <v>2.576650093251554</v>
+        <v>2.576650322657736</v>
       </c>
       <c r="E396" t="n">
-        <v>2.641066285247719</v>
+        <v>2.64106652038905</v>
       </c>
       <c r="F396" t="n">
         <v>24268000</v>
@@ -8352,16 +8352,16 @@
         <v>44992</v>
       </c>
       <c r="B397" t="n">
-        <v>2.677875757217407</v>
+        <v>2.677875995635986</v>
       </c>
       <c r="C397" t="n">
-        <v>2.696280383502025</v>
+        <v>2.696280623559219</v>
       </c>
       <c r="D397" t="n">
-        <v>2.6226616589631</v>
+        <v>2.622661892465818</v>
       </c>
       <c r="E397" t="n">
-        <v>2.677875757217407</v>
+        <v>2.677875995635986</v>
       </c>
       <c r="F397" t="n">
         <v>12209500</v>
@@ -8452,16 +8452,16 @@
         <v>44999</v>
       </c>
       <c r="B402" t="n">
-        <v>2.493829488754272</v>
+        <v>2.493829250335693</v>
       </c>
       <c r="C402" t="n">
-        <v>2.585852628066047</v>
+        <v>2.585852380849743</v>
       </c>
       <c r="D402" t="n">
-        <v>2.46622254696074</v>
+        <v>2.466222311181478</v>
       </c>
       <c r="E402" t="n">
-        <v>2.475424860891918</v>
+        <v>2.475424624232883</v>
       </c>
       <c r="F402" t="n">
         <v>40119200</v>
@@ -8472,16 +8472,16 @@
         <v>45000</v>
       </c>
       <c r="B403" t="n">
-        <v>2.493829488754272</v>
+        <v>2.493829250335693</v>
       </c>
       <c r="C403" t="n">
-        <v>2.521436430547805</v>
+        <v>2.521436189489909</v>
       </c>
       <c r="D403" t="n">
-        <v>2.447817919098385</v>
+        <v>2.447817685078669</v>
       </c>
       <c r="E403" t="n">
-        <v>2.475424860891918</v>
+        <v>2.475424624232883</v>
       </c>
       <c r="F403" t="n">
         <v>17612600</v>
@@ -8492,16 +8492,16 @@
         <v>45001</v>
       </c>
       <c r="B404" t="n">
-        <v>2.512234210968018</v>
+        <v>2.512233972549438</v>
       </c>
       <c r="C404" t="n">
-        <v>2.539841153798378</v>
+        <v>2.539840912759816</v>
       </c>
       <c r="D404" t="n">
-        <v>2.447818011030511</v>
+        <v>2.447817778725223</v>
       </c>
       <c r="E404" t="n">
-        <v>2.530638839521591</v>
+        <v>2.530638599356357</v>
       </c>
       <c r="F404" t="n">
         <v>22197500</v>
@@ -8572,16 +8572,16 @@
         <v>45007</v>
       </c>
       <c r="B408" t="n">
-        <v>2.216452836990356</v>
+        <v>2.216452598571777</v>
       </c>
       <c r="C408" t="n">
-        <v>2.273529049947901</v>
+        <v>2.273528805389769</v>
       </c>
       <c r="D408" t="n">
-        <v>2.197427508271111</v>
+        <v>2.197427271899042</v>
       </c>
       <c r="E408" t="n">
-        <v>2.254503494428847</v>
+        <v>2.254503251917249</v>
       </c>
       <c r="F408" t="n">
         <v>26704400</v>
@@ -8612,16 +8612,16 @@
         <v>45009</v>
       </c>
       <c r="B410" t="n">
-        <v>2.292554140090942</v>
+        <v>2.292554378509521</v>
       </c>
       <c r="C410" t="n">
-        <v>2.302066803460623</v>
+        <v>2.30206704286849</v>
       </c>
       <c r="D410" t="n">
-        <v>2.149863962745944</v>
+        <v>2.149864186325184</v>
       </c>
       <c r="E410" t="n">
-        <v>2.159376626115625</v>
+        <v>2.159376850684152</v>
       </c>
       <c r="F410" t="n">
         <v>19141800</v>
@@ -8672,16 +8672,16 @@
         <v>45014</v>
       </c>
       <c r="B413" t="n">
-        <v>2.615985155105591</v>
+        <v>2.615984916687012</v>
       </c>
       <c r="C413" t="n">
-        <v>2.644523147763493</v>
+        <v>2.644522906743987</v>
       </c>
       <c r="D413" t="n">
-        <v>2.492320293454875</v>
+        <v>2.492320066307002</v>
       </c>
       <c r="E413" t="n">
-        <v>2.539883841351184</v>
+        <v>2.539883609868411</v>
       </c>
       <c r="F413" t="n">
         <v>36856900</v>
@@ -8692,16 +8692,16 @@
         <v>45015</v>
       </c>
       <c r="B414" t="n">
-        <v>2.749162435531616</v>
+        <v>2.749162673950195</v>
       </c>
       <c r="C414" t="n">
-        <v>2.796725752381689</v>
+        <v>2.796725994925153</v>
       </c>
       <c r="D414" t="n">
-        <v>2.644522911661672</v>
+        <v>2.644523141005484</v>
       </c>
       <c r="E414" t="n">
-        <v>2.673060901771716</v>
+        <v>2.673061133590459</v>
       </c>
       <c r="F414" t="n">
         <v>39786400</v>
@@ -8712,16 +8712,16 @@
         <v>45016</v>
       </c>
       <c r="B415" t="n">
-        <v>2.711111545562744</v>
+        <v>2.711111783981323</v>
       </c>
       <c r="C415" t="n">
-        <v>2.787213079050672</v>
+        <v>2.787213324161716</v>
       </c>
       <c r="D415" t="n">
-        <v>2.654035565546636</v>
+        <v>2.654035798945881</v>
       </c>
       <c r="E415" t="n">
-        <v>2.777700415714654</v>
+        <v>2.777700659989142</v>
       </c>
       <c r="F415" t="n">
         <v>25812800</v>
@@ -8772,16 +8772,16 @@
         <v>45021</v>
       </c>
       <c r="B418" t="n">
-        <v>2.682573556900024</v>
+        <v>2.682573795318604</v>
       </c>
       <c r="C418" t="n">
-        <v>2.720624210263179</v>
+        <v>2.720624452063579</v>
       </c>
       <c r="D418" t="n">
-        <v>2.615984913514504</v>
+        <v>2.615985146014897</v>
       </c>
       <c r="E418" t="n">
-        <v>2.701598883581602</v>
+        <v>2.701599123691091</v>
       </c>
       <c r="F418" t="n">
         <v>22336100</v>
@@ -8812,16 +8812,16 @@
         <v>45026</v>
       </c>
       <c r="B420" t="n">
-        <v>2.67306113243103</v>
+        <v>2.673060894012451</v>
       </c>
       <c r="C420" t="n">
-        <v>2.701599125003626</v>
+        <v>2.701598884039655</v>
       </c>
       <c r="D420" t="n">
-        <v>2.644523139858434</v>
+        <v>2.644522903985246</v>
       </c>
       <c r="E420" t="n">
-        <v>2.67306113243103</v>
+        <v>2.673060894012451</v>
       </c>
       <c r="F420" t="n">
         <v>14149600</v>
@@ -8832,16 +8832,16 @@
         <v>45027</v>
       </c>
       <c r="B421" t="n">
-        <v>2.910877704620361</v>
+        <v>2.91087794303894</v>
       </c>
       <c r="C421" t="n">
-        <v>2.920390367963574</v>
+        <v>2.920390607161298</v>
       </c>
       <c r="D421" t="n">
-        <v>2.692086220926695</v>
+        <v>2.692086441424922</v>
       </c>
       <c r="E421" t="n">
-        <v>2.71111154761312</v>
+        <v>2.711111769669636</v>
       </c>
       <c r="F421" t="n">
         <v>33609000</v>
@@ -8852,16 +8852,16 @@
         <v>45028</v>
       </c>
       <c r="B422" t="n">
-        <v>2.910877704620361</v>
+        <v>2.91087794303894</v>
       </c>
       <c r="C422" t="n">
-        <v>3.01551722819548</v>
+        <v>3.015517475184673</v>
       </c>
       <c r="D422" t="n">
-        <v>2.891852377933937</v>
+        <v>2.891852614794226</v>
       </c>
       <c r="E422" t="n">
-        <v>2.920390367963574</v>
+        <v>2.920390607161298</v>
       </c>
       <c r="F422" t="n">
         <v>32421000</v>
@@ -8872,16 +8872,16 @@
         <v>45029</v>
       </c>
       <c r="B423" t="n">
-        <v>2.882339954376221</v>
+        <v>2.882339715957642</v>
       </c>
       <c r="C423" t="n">
-        <v>2.958441267452883</v>
+        <v>2.95844102273943</v>
       </c>
       <c r="D423" t="n">
-        <v>2.853801961972472</v>
+        <v>2.853801725914471</v>
       </c>
       <c r="E423" t="n">
-        <v>2.929903275049135</v>
+        <v>2.929903032696259</v>
       </c>
       <c r="F423" t="n">
         <v>15780900</v>
@@ -8912,16 +8912,16 @@
         <v>45033</v>
       </c>
       <c r="B425" t="n">
-        <v>2.967953681945801</v>
+        <v>2.96795392036438</v>
       </c>
       <c r="C425" t="n">
-        <v>2.986979235414485</v>
+        <v>2.986979475361405</v>
       </c>
       <c r="D425" t="n">
-        <v>2.872827048601301</v>
+        <v>2.872827279378266</v>
       </c>
       <c r="E425" t="n">
-        <v>2.901365038604651</v>
+        <v>2.9013652716741</v>
       </c>
       <c r="F425" t="n">
         <v>14970900</v>
@@ -8932,16 +8932,16 @@
         <v>45034</v>
       </c>
       <c r="B426" t="n">
-        <v>3.025030136108398</v>
+        <v>3.025029897689819</v>
       </c>
       <c r="C426" t="n">
-        <v>3.034542800220697</v>
+        <v>3.034542561052375</v>
       </c>
       <c r="D426" t="n">
-        <v>2.948928596410207</v>
+        <v>2.948928363989592</v>
       </c>
       <c r="E426" t="n">
-        <v>2.986979479659204</v>
+        <v>2.986979244239598</v>
       </c>
       <c r="F426" t="n">
         <v>13884000</v>
@@ -8952,16 +8952,16 @@
         <v>45035</v>
       </c>
       <c r="B427" t="n">
-        <v>2.882339954376221</v>
+        <v>2.882339715957642</v>
       </c>
       <c r="C427" t="n">
-        <v>2.996492150791017</v>
+        <v>2.996491902930108</v>
       </c>
       <c r="D427" t="n">
-        <v>2.872827290241638</v>
+        <v>2.872827052609918</v>
       </c>
       <c r="E427" t="n">
-        <v>2.986979486656434</v>
+        <v>2.986979239582385</v>
       </c>
       <c r="F427" t="n">
         <v>19845900</v>
@@ -8972,16 +8972,16 @@
         <v>45036</v>
       </c>
       <c r="B428" t="n">
-        <v>2.958441019058228</v>
+        <v>2.958441257476807</v>
       </c>
       <c r="C428" t="n">
-        <v>2.977466572529786</v>
+        <v>2.977466812481619</v>
       </c>
       <c r="D428" t="n">
-        <v>2.844289059027585</v>
+        <v>2.844289288246741</v>
       </c>
       <c r="E428" t="n">
-        <v>2.882339712371133</v>
+        <v>2.882339944656763</v>
       </c>
       <c r="F428" t="n">
         <v>11874200</v>
@@ -8992,16 +8992,16 @@
         <v>45040</v>
       </c>
       <c r="B429" t="n">
-        <v>3.072593212127686</v>
+        <v>3.072593450546265</v>
       </c>
       <c r="C429" t="n">
-        <v>3.110643865548496</v>
+        <v>3.110644106919625</v>
       </c>
       <c r="D429" t="n">
-        <v>2.891852381579049</v>
+        <v>2.891852605973001</v>
       </c>
       <c r="E429" t="n">
-        <v>2.948928361710265</v>
+        <v>2.948928590533042</v>
       </c>
       <c r="F429" t="n">
         <v>37103600</v>
@@ -9012,16 +9012,16 @@
         <v>45041</v>
       </c>
       <c r="B430" t="n">
-        <v>3.025030136108398</v>
+        <v>3.025029897689819</v>
       </c>
       <c r="C430" t="n">
-        <v>3.148694769568281</v>
+        <v>3.14869452140304</v>
       </c>
       <c r="D430" t="n">
-        <v>2.977466815546905</v>
+        <v>2.977466580877042</v>
       </c>
       <c r="E430" t="n">
-        <v>3.072593456669892</v>
+        <v>3.072593214502596</v>
       </c>
       <c r="F430" t="n">
         <v>18942800</v>
@@ -9052,16 +9052,16 @@
         <v>45043</v>
       </c>
       <c r="B432" t="n">
-        <v>2.977466344833374</v>
+        <v>2.977466583251953</v>
       </c>
       <c r="C432" t="n">
-        <v>3.006004332658643</v>
+        <v>3.006004573362382</v>
       </c>
       <c r="D432" t="n">
-        <v>2.8918521545578</v>
+        <v>2.891852386120882</v>
       </c>
       <c r="E432" t="n">
-        <v>2.901364817166223</v>
+        <v>2.901365049491024</v>
       </c>
       <c r="F432" t="n">
         <v>12242300</v>
@@ -9132,16 +9132,16 @@
         <v>45050</v>
       </c>
       <c r="B436" t="n">
-        <v>3.025030136108398</v>
+        <v>3.025029897689819</v>
       </c>
       <c r="C436" t="n">
-        <v>3.063080792557593</v>
+        <v>3.063080551140041</v>
       </c>
       <c r="D436" t="n">
-        <v>2.958441260522505</v>
+        <v>2.958441027352147</v>
       </c>
       <c r="E436" t="n">
-        <v>3.0155174719961</v>
+        <v>3.015517234327264</v>
       </c>
       <c r="F436" t="n">
         <v>20441800</v>
@@ -9172,16 +9172,16 @@
         <v>45054</v>
       </c>
       <c r="B438" t="n">
-        <v>3.148694515228271</v>
+        <v>3.148694276809692</v>
       </c>
       <c r="C438" t="n">
-        <v>3.215283385435359</v>
+        <v>3.215283141974683</v>
       </c>
       <c r="D438" t="n">
-        <v>3.139181851884371</v>
+        <v>3.139181614186089</v>
       </c>
       <c r="E438" t="n">
-        <v>3.139181851884371</v>
+        <v>3.139181614186089</v>
       </c>
       <c r="F438" t="n">
         <v>16113900</v>
@@ -9192,16 +9192,16 @@
         <v>45055</v>
       </c>
       <c r="B439" t="n">
-        <v>3.025030136108398</v>
+        <v>3.025029897689819</v>
       </c>
       <c r="C439" t="n">
-        <v>3.158207433680579</v>
+        <v>3.158207184765595</v>
       </c>
       <c r="D439" t="n">
-        <v>3.0155174719961</v>
+        <v>3.015517234327264</v>
       </c>
       <c r="E439" t="n">
-        <v>3.129669441343684</v>
+        <v>3.129669194677929</v>
       </c>
       <c r="F439" t="n">
         <v>32144800</v>
@@ -9272,16 +9272,16 @@
         <v>45061</v>
       </c>
       <c r="B443" t="n">
-        <v>2.986979007720947</v>
+        <v>2.986979246139526</v>
       </c>
       <c r="C443" t="n">
-        <v>3.205770247735124</v>
+        <v>3.205770503617468</v>
       </c>
       <c r="D443" t="n">
-        <v>2.901364817437372</v>
+        <v>2.901365049022286</v>
       </c>
       <c r="E443" t="n">
-        <v>3.1867449225165</v>
+        <v>3.186745176880255</v>
       </c>
       <c r="F443" t="n">
         <v>71533500</v>
@@ -9292,16 +9292,16 @@
         <v>45062</v>
       </c>
       <c r="B444" t="n">
-        <v>3.082106113433838</v>
+        <v>3.082105875015259</v>
       </c>
       <c r="C444" t="n">
-        <v>3.139182097971549</v>
+        <v>3.139181855137815</v>
       </c>
       <c r="D444" t="n">
-        <v>2.977466808448034</v>
+        <v>2.977466578123905</v>
       </c>
       <c r="E444" t="n">
-        <v>2.977466808448034</v>
+        <v>2.977466578123905</v>
       </c>
       <c r="F444" t="n">
         <v>45623200</v>
@@ -9312,16 +9312,16 @@
         <v>45063</v>
       </c>
       <c r="B445" t="n">
-        <v>3.253334283828735</v>
+        <v>3.253334045410156</v>
       </c>
       <c r="C445" t="n">
-        <v>3.300897604130366</v>
+        <v>3.300897362226138</v>
       </c>
       <c r="D445" t="n">
-        <v>3.082106103943065</v>
+        <v>3.082105878072837</v>
       </c>
       <c r="E445" t="n">
-        <v>3.091618768003391</v>
+        <v>3.091618541436033</v>
       </c>
       <c r="F445" t="n">
         <v>27916800</v>
@@ -9332,16 +9332,16 @@
         <v>45064</v>
       </c>
       <c r="B446" t="n">
-        <v>3.300897598266602</v>
+        <v>3.300897121429443</v>
       </c>
       <c r="C446" t="n">
-        <v>3.338948254440312</v>
+        <v>3.338947772106478</v>
       </c>
       <c r="D446" t="n">
-        <v>3.177232738902241</v>
+        <v>3.177232279929315</v>
       </c>
       <c r="E446" t="n">
-        <v>3.253334278049463</v>
+        <v>3.253333808083151</v>
       </c>
       <c r="F446" t="n">
         <v>40825600</v>
@@ -9412,16 +9412,16 @@
         <v>45070</v>
       </c>
       <c r="B450" t="n">
-        <v>3.319922685623169</v>
+        <v>3.319922924041748</v>
       </c>
       <c r="C450" t="n">
-        <v>3.529201506203401</v>
+        <v>3.529201759651233</v>
       </c>
       <c r="D450" t="n">
-        <v>3.262846705501229</v>
+        <v>3.262846939820925</v>
       </c>
       <c r="E450" t="n">
-        <v>3.462612862727804</v>
+        <v>3.462613111393607</v>
       </c>
       <c r="F450" t="n">
         <v>35329500</v>
@@ -9452,16 +9452,16 @@
         <v>45072</v>
       </c>
       <c r="B452" t="n">
-        <v>3.291384935379028</v>
+        <v>3.291384696960449</v>
       </c>
       <c r="C452" t="n">
-        <v>3.348460919659638</v>
+        <v>3.348460677106637</v>
       </c>
       <c r="D452" t="n">
-        <v>3.177232740018008</v>
+        <v>3.17723250986829</v>
       </c>
       <c r="E452" t="n">
-        <v>3.33894825561287</v>
+        <v>3.338948013748939</v>
       </c>
       <c r="F452" t="n">
         <v>25686400</v>
@@ -9472,16 +9472,16 @@
         <v>45075</v>
       </c>
       <c r="B453" t="n">
-        <v>3.357973337173462</v>
+        <v>3.357973575592041</v>
       </c>
       <c r="C453" t="n">
-        <v>3.415049317263714</v>
+        <v>3.415049559734729</v>
       </c>
       <c r="D453" t="n">
-        <v>3.291384693734835</v>
+        <v>3.291384927425571</v>
       </c>
       <c r="E453" t="n">
-        <v>3.319922683779961</v>
+        <v>3.319922919496916</v>
       </c>
       <c r="F453" t="n">
         <v>14544800</v>
@@ -9532,16 +9532,16 @@
         <v>45078</v>
       </c>
       <c r="B456" t="n">
-        <v>3.576765060424805</v>
+        <v>3.576764822006226</v>
       </c>
       <c r="C456" t="n">
-        <v>3.662379036291428</v>
+        <v>3.662378792166026</v>
       </c>
       <c r="D456" t="n">
-        <v>3.376998889936218</v>
+        <v>3.376998664833572</v>
       </c>
       <c r="E456" t="n">
-        <v>3.472125756587821</v>
+        <v>3.472125525144246</v>
       </c>
       <c r="F456" t="n">
         <v>28377100</v>
@@ -9612,16 +9612,16 @@
         <v>45084</v>
       </c>
       <c r="B460" t="n">
-        <v>3.757505893707275</v>
+        <v>3.757505655288696</v>
       </c>
       <c r="C460" t="n">
-        <v>3.852632760125061</v>
+        <v>3.85263251567056</v>
       </c>
       <c r="D460" t="n">
-        <v>3.681404355213087</v>
+        <v>3.681404121623248</v>
       </c>
       <c r="E460" t="n">
-        <v>3.747993229745477</v>
+        <v>3.747992991930488</v>
       </c>
       <c r="F460" t="n">
         <v>19382700</v>
@@ -9632,16 +9632,16 @@
         <v>45086</v>
       </c>
       <c r="B461" t="n">
-        <v>3.786043643951416</v>
+        <v>3.786043882369995</v>
       </c>
       <c r="C461" t="n">
-        <v>3.824094297370058</v>
+        <v>3.824094538184801</v>
       </c>
       <c r="D461" t="n">
-        <v>3.728967663823453</v>
+        <v>3.728967898647786</v>
       </c>
       <c r="E461" t="n">
-        <v>3.795556307306077</v>
+        <v>3.795556546323696</v>
       </c>
       <c r="F461" t="n">
         <v>14031500</v>
@@ -9652,16 +9652,16 @@
         <v>45089</v>
       </c>
       <c r="B462" t="n">
-        <v>3.795556545257568</v>
+        <v>3.795556306838989</v>
       </c>
       <c r="C462" t="n">
-        <v>3.805069209208598</v>
+        <v>3.805068970192479</v>
       </c>
       <c r="D462" t="n">
-        <v>3.747993225502421</v>
+        <v>3.74799299007154</v>
       </c>
       <c r="E462" t="n">
-        <v>3.786043881306539</v>
+        <v>3.786043643485499</v>
       </c>
       <c r="F462" t="n">
         <v>16242400</v>
@@ -9672,16 +9672,16 @@
         <v>45090</v>
       </c>
       <c r="B463" t="n">
-        <v>3.700429916381836</v>
+        <v>3.700429677963257</v>
       </c>
       <c r="C463" t="n">
-        <v>3.814582110922048</v>
+        <v>3.814581865148647</v>
       </c>
       <c r="D463" t="n">
-        <v>3.662379033668566</v>
+        <v>3.662378797701604</v>
       </c>
       <c r="E463" t="n">
-        <v>3.786043892187145</v>
+        <v>3.78604364825246</v>
       </c>
       <c r="F463" t="n">
         <v>19986600</v>
@@ -9712,16 +9712,16 @@
         <v>45092</v>
       </c>
       <c r="B465" t="n">
-        <v>3.757505893707275</v>
+        <v>3.757505655288696</v>
       </c>
       <c r="C465" t="n">
-        <v>3.79555654955447</v>
+        <v>3.795556308721528</v>
       </c>
       <c r="D465" t="n">
-        <v>3.71945523786008</v>
+        <v>3.719455001855864</v>
       </c>
       <c r="E465" t="n">
-        <v>3.757505893707275</v>
+        <v>3.757505655288696</v>
       </c>
       <c r="F465" t="n">
         <v>13781200</v>
@@ -9732,16 +9732,16 @@
         <v>45093</v>
       </c>
       <c r="B466" t="n">
-        <v>3.757505893707275</v>
+        <v>3.757505655288696</v>
       </c>
       <c r="C466" t="n">
-        <v>3.776531221630873</v>
+        <v>3.776530982005112</v>
       </c>
       <c r="D466" t="n">
-        <v>3.709942573898282</v>
+        <v>3.709942338497656</v>
       </c>
       <c r="E466" t="n">
-        <v>3.728967901821879</v>
+        <v>3.728967665214073</v>
       </c>
       <c r="F466" t="n">
         <v>14449100</v>
@@ -9772,16 +9772,16 @@
         <v>45097</v>
       </c>
       <c r="B468" t="n">
-        <v>3.94775915145874</v>
+        <v>3.947758913040161</v>
       </c>
       <c r="C468" t="n">
-        <v>3.966784478185788</v>
+        <v>3.966784238618205</v>
       </c>
       <c r="D468" t="n">
-        <v>3.767018320752002</v>
+        <v>3.767018093248975</v>
       </c>
       <c r="E468" t="n">
-        <v>3.78604364747905</v>
+        <v>3.786043418827019</v>
       </c>
       <c r="F468" t="n">
         <v>35176100</v>
@@ -9892,16 +9892,16 @@
         <v>45105</v>
       </c>
       <c r="B474" t="n">
-        <v>4.176063060760498</v>
+        <v>4.176063537597656</v>
       </c>
       <c r="C474" t="n">
-        <v>4.261677257597817</v>
+        <v>4.261677744210696</v>
       </c>
       <c r="D474" t="n">
-        <v>4.090449317522748</v>
+        <v>4.090449784584236</v>
       </c>
       <c r="E474" t="n">
-        <v>4.223626604247801</v>
+        <v>4.223627086515927</v>
       </c>
       <c r="F474" t="n">
         <v>30177100</v>
@@ -9912,16 +9912,16 @@
         <v>45106</v>
       </c>
       <c r="B475" t="n">
-        <v>4.366316795349121</v>
+        <v>4.366317272186279</v>
       </c>
       <c r="C475" t="n">
-        <v>4.366316795349121</v>
+        <v>4.366317272186279</v>
       </c>
       <c r="D475" t="n">
-        <v>4.185575964547351</v>
+        <v>4.185576421646147</v>
       </c>
       <c r="E475" t="n">
-        <v>4.185575964547351</v>
+        <v>4.185576421646147</v>
       </c>
       <c r="F475" t="n">
         <v>40765500</v>
@@ -9952,16 +9952,16 @@
         <v>45110</v>
       </c>
       <c r="B477" t="n">
-        <v>4.252164363861084</v>
+        <v>4.252163887023926</v>
       </c>
       <c r="C477" t="n">
-        <v>4.299727907308124</v>
+        <v>4.299727425137196</v>
       </c>
       <c r="D477" t="n">
-        <v>4.195088383884376</v>
+        <v>4.19508791344771</v>
       </c>
       <c r="E477" t="n">
-        <v>4.233139037202181</v>
+        <v>4.233138562498521</v>
       </c>
       <c r="F477" t="n">
         <v>20197900</v>
@@ -10012,16 +10012,16 @@
         <v>45113</v>
       </c>
       <c r="B480" t="n">
-        <v>3.957271814346313</v>
+        <v>3.957271575927734</v>
       </c>
       <c r="C480" t="n">
-        <v>4.061911344129392</v>
+        <v>4.061911099406468</v>
       </c>
       <c r="D480" t="n">
-        <v>3.909708721608256</v>
+        <v>3.909708486055269</v>
       </c>
       <c r="E480" t="n">
-        <v>4.061911344129392</v>
+        <v>4.061911099406468</v>
       </c>
       <c r="F480" t="n">
         <v>22675100</v>
@@ -10032,16 +10032,16 @@
         <v>45114</v>
       </c>
       <c r="B481" t="n">
-        <v>3.995322227478027</v>
+        <v>3.995322465896606</v>
       </c>
       <c r="C481" t="n">
-        <v>4.042885770928781</v>
+        <v>4.042886012185687</v>
       </c>
       <c r="D481" t="n">
-        <v>3.947759137626841</v>
+        <v>3.94775937320712</v>
       </c>
       <c r="E481" t="n">
-        <v>3.976296900817639</v>
+        <v>3.976297138100893</v>
       </c>
       <c r="F481" t="n">
         <v>19055100</v>
@@ -10112,16 +10112,16 @@
         <v>45120</v>
       </c>
       <c r="B485" t="n">
-        <v>3.995322227478027</v>
+        <v>3.995322465896606</v>
       </c>
       <c r="C485" t="n">
-        <v>4.071423987719147</v>
+        <v>4.071424230679055</v>
       </c>
       <c r="D485" t="n">
-        <v>3.957271574157251</v>
+        <v>3.957271810305179</v>
       </c>
       <c r="E485" t="n">
-        <v>4.023860444268393</v>
+        <v>4.023860684389974</v>
       </c>
       <c r="F485" t="n">
         <v>10522300</v>
@@ -10132,16 +10132,16 @@
         <v>45121</v>
       </c>
       <c r="B486" t="n">
-        <v>3.881170511245728</v>
+        <v>3.881170272827148</v>
       </c>
       <c r="C486" t="n">
-        <v>4.014347806231721</v>
+        <v>4.01434755963212</v>
       </c>
       <c r="D486" t="n">
-        <v>3.814582090552529</v>
+        <v>3.814581856224446</v>
       </c>
       <c r="E486" t="n">
-        <v>3.995322478376579</v>
+        <v>3.995322232945695</v>
       </c>
       <c r="F486" t="n">
         <v>16845900</v>
@@ -10172,16 +10172,16 @@
         <v>45125</v>
       </c>
       <c r="B488" t="n">
-        <v>4.071424007415771</v>
+        <v>4.07142448425293</v>
       </c>
       <c r="C488" t="n">
-        <v>4.185575967930341</v>
+        <v>4.185576458136752</v>
       </c>
       <c r="D488" t="n">
-        <v>4.004835136982487</v>
+        <v>4.004835606020889</v>
       </c>
       <c r="E488" t="n">
-        <v>4.023860463734916</v>
+        <v>4.023860935001526</v>
       </c>
       <c r="F488" t="n">
         <v>19854400</v>
@@ -10212,16 +10212,16 @@
         <v>45127</v>
       </c>
       <c r="B490" t="n">
-        <v>3.995322227478027</v>
+        <v>3.995322465896606</v>
       </c>
       <c r="C490" t="n">
-        <v>4.080936424249557</v>
+        <v>4.080936667777115</v>
       </c>
       <c r="D490" t="n">
-        <v>3.947759137626841</v>
+        <v>3.94775937320712</v>
       </c>
       <c r="E490" t="n">
-        <v>4.071423987719147</v>
+        <v>4.071424230679055</v>
       </c>
       <c r="F490" t="n">
         <v>13981900</v>
@@ -10232,16 +10232,16 @@
         <v>45128</v>
       </c>
       <c r="B491" t="n">
-        <v>4.061911582946777</v>
+        <v>4.061910629272461</v>
       </c>
       <c r="C491" t="n">
-        <v>4.099962240814224</v>
+        <v>4.099961278206199</v>
       </c>
       <c r="D491" t="n">
-        <v>3.97629737594521</v>
+        <v>3.976296442371792</v>
       </c>
       <c r="E491" t="n">
-        <v>4.004835596145607</v>
+        <v>4.004834655871853</v>
       </c>
       <c r="F491" t="n">
         <v>9991000</v>
@@ -10272,16 +10272,16 @@
         <v>45132</v>
       </c>
       <c r="B493" t="n">
-        <v>3.995322227478027</v>
+        <v>3.995322465896606</v>
       </c>
       <c r="C493" t="n">
-        <v>4.090449314379534</v>
+        <v>4.090449558474769</v>
       </c>
       <c r="D493" t="n">
-        <v>3.966784464287229</v>
+        <v>3.966784701002833</v>
       </c>
       <c r="E493" t="n">
-        <v>4.061911097589169</v>
+        <v>4.061911339981402</v>
       </c>
       <c r="F493" t="n">
         <v>14413200</v>
@@ -10352,16 +10352,16 @@
         <v>45138</v>
       </c>
       <c r="B497" t="n">
-        <v>3.980106353759766</v>
+        <v>3.980106115341187</v>
       </c>
       <c r="C497" t="n">
-        <v>4.008809245599202</v>
+        <v>4.008809005461245</v>
       </c>
       <c r="D497" t="n">
-        <v>3.922701026297883</v>
+        <v>3.922700791318031</v>
       </c>
       <c r="E497" t="n">
-        <v>3.941836135451844</v>
+        <v>3.941835899325749</v>
       </c>
       <c r="F497" t="n">
         <v>13989300</v>
@@ -10372,16 +10372,16 @@
         <v>45139</v>
       </c>
       <c r="B498" t="n">
-        <v>3.980106353759766</v>
+        <v>3.980106115341187</v>
       </c>
       <c r="C498" t="n">
-        <v>4.018376572067687</v>
+        <v>4.018376331356624</v>
       </c>
       <c r="D498" t="n">
-        <v>3.884430807989962</v>
+        <v>3.884430575302593</v>
       </c>
       <c r="E498" t="n">
-        <v>3.970539027291279</v>
+        <v>3.970538789445808</v>
       </c>
       <c r="F498" t="n">
         <v>24308900</v>
@@ -10392,16 +10392,16 @@
         <v>45140</v>
       </c>
       <c r="B499" t="n">
-        <v>4.008808612823486</v>
+        <v>4.008809089660645</v>
       </c>
       <c r="C499" t="n">
-        <v>4.018375937781805</v>
+        <v>4.018376415756972</v>
       </c>
       <c r="D499" t="n">
-        <v>3.932268188289268</v>
+        <v>3.932268656022146</v>
       </c>
       <c r="E499" t="n">
-        <v>3.951403294422822</v>
+        <v>3.95140376443177</v>
       </c>
       <c r="F499" t="n">
         <v>25721100</v>
@@ -10412,16 +10412,16 @@
         <v>45141</v>
       </c>
       <c r="B500" t="n">
-        <v>3.922700881958008</v>
+        <v>3.922700643539429</v>
       </c>
       <c r="C500" t="n">
-        <v>4.037511532657195</v>
+        <v>4.037511287260518</v>
       </c>
       <c r="D500" t="n">
-        <v>3.893998447391697</v>
+        <v>3.893998210717629</v>
       </c>
       <c r="E500" t="n">
-        <v>4.027944206540749</v>
+        <v>4.027943961725565</v>
       </c>
       <c r="F500" t="n">
         <v>21426900</v>
@@ -10452,16 +10452,16 @@
         <v>45145</v>
       </c>
       <c r="B502" t="n">
-        <v>3.846160650253296</v>
+        <v>3.846160411834717</v>
       </c>
       <c r="C502" t="n">
-        <v>3.922701088074537</v>
+        <v>3.922700844911313</v>
       </c>
       <c r="D502" t="n">
-        <v>3.817457986070331</v>
+        <v>3.817457749430993</v>
       </c>
       <c r="E502" t="n">
-        <v>3.913133761455379</v>
+        <v>3.913133518885223</v>
       </c>
       <c r="F502" t="n">
         <v>14729300</v>
@@ -10512,16 +10512,16 @@
         <v>45148</v>
       </c>
       <c r="B505" t="n">
-        <v>3.740917444229126</v>
+        <v>3.740917205810547</v>
       </c>
       <c r="C505" t="n">
-        <v>3.788755216537224</v>
+        <v>3.788754975069817</v>
       </c>
       <c r="D505" t="n">
-        <v>3.702646998274156</v>
+        <v>3.702646762294654</v>
       </c>
       <c r="E505" t="n">
-        <v>3.760052553152365</v>
+        <v>3.760052313514255</v>
       </c>
       <c r="F505" t="n">
         <v>11449000</v>
@@ -10712,16 +10712,16 @@
         <v>45162</v>
       </c>
       <c r="B515" t="n">
-        <v>3.568701267242432</v>
+        <v>3.568701028823853</v>
       </c>
       <c r="C515" t="n">
-        <v>3.64524170360951</v>
+        <v>3.645241460077401</v>
       </c>
       <c r="D515" t="n">
-        <v>3.444322830037436</v>
+        <v>3.444322599928359</v>
       </c>
       <c r="E515" t="n">
-        <v>3.453890384583321</v>
+        <v>3.453890153835052</v>
       </c>
       <c r="F515" t="n">
         <v>42127000</v>
@@ -10732,16 +10732,16 @@
         <v>45163</v>
       </c>
       <c r="B516" t="n">
-        <v>3.62610650062561</v>
+        <v>3.626106739044189</v>
       </c>
       <c r="C516" t="n">
-        <v>3.664376717818205</v>
+        <v>3.664376958753072</v>
       </c>
       <c r="D516" t="n">
-        <v>3.549566066240422</v>
+        <v>3.549566299626424</v>
       </c>
       <c r="E516" t="n">
-        <v>3.616538946327462</v>
+        <v>3.616539184116969</v>
       </c>
       <c r="F516" t="n">
         <v>21198200</v>
@@ -10772,16 +10772,16 @@
         <v>45167</v>
       </c>
       <c r="B518" t="n">
-        <v>3.65480899810791</v>
+        <v>3.654809236526489</v>
       </c>
       <c r="C518" t="n">
-        <v>3.664376551973043</v>
+        <v>3.664376791015754</v>
       </c>
       <c r="D518" t="n">
-        <v>3.578268567186847</v>
+        <v>3.578268800612372</v>
       </c>
       <c r="E518" t="n">
-        <v>3.616538782647379</v>
+        <v>3.61653901856943</v>
       </c>
       <c r="F518" t="n">
         <v>13520200</v>
@@ -11012,16 +11012,16 @@
         <v>45184</v>
       </c>
       <c r="B530" t="n">
-        <v>3.807890176773071</v>
+        <v>3.80789041519165</v>
       </c>
       <c r="C530" t="n">
-        <v>3.941835934005541</v>
+        <v>3.941836180810695</v>
       </c>
       <c r="D530" t="n">
-        <v>3.788755068597004</v>
+        <v>3.788755305817501</v>
       </c>
       <c r="E530" t="n">
-        <v>3.788755068597004</v>
+        <v>3.788755305817501</v>
       </c>
       <c r="F530" t="n">
         <v>34682000</v>
@@ -11032,16 +11032,16 @@
         <v>45187</v>
       </c>
       <c r="B531" t="n">
-        <v>3.817457914352417</v>
+        <v>3.817457675933838</v>
       </c>
       <c r="C531" t="n">
-        <v>3.884430796187795</v>
+        <v>3.884430553586438</v>
       </c>
       <c r="D531" t="n">
-        <v>3.740917477969129</v>
+        <v>3.740917244330867</v>
       </c>
       <c r="E531" t="n">
-        <v>3.817457914352417</v>
+        <v>3.817457675933838</v>
       </c>
       <c r="F531" t="n">
         <v>23371600</v>
@@ -11252,16 +11252,16 @@
         <v>45202</v>
       </c>
       <c r="B542" t="n">
-        <v>3.31037712097168</v>
+        <v>3.310376882553101</v>
       </c>
       <c r="C542" t="n">
-        <v>3.406052668007885</v>
+        <v>3.406052422698603</v>
       </c>
       <c r="D542" t="n">
-        <v>3.272106902157197</v>
+        <v>3.2721066664949</v>
       </c>
       <c r="E542" t="n">
-        <v>3.3199446756753</v>
+        <v>3.31994443656765</v>
       </c>
       <c r="F542" t="n">
         <v>29291500</v>
@@ -11272,16 +11272,16 @@
         <v>45203</v>
       </c>
       <c r="B543" t="n">
-        <v>3.319944620132446</v>
+        <v>3.319944381713867</v>
       </c>
       <c r="C543" t="n">
-        <v>3.348647283763111</v>
+        <v>3.348647043283278</v>
       </c>
       <c r="D543" t="n">
-        <v>3.300809511045337</v>
+        <v>3.300809274000926</v>
       </c>
       <c r="E543" t="n">
-        <v>3.319944620132446</v>
+        <v>3.319944381713867</v>
       </c>
       <c r="F543" t="n">
         <v>10591900</v>
@@ -11292,16 +11292,16 @@
         <v>45204</v>
       </c>
       <c r="B544" t="n">
-        <v>3.23383641242981</v>
+        <v>3.233836650848389</v>
       </c>
       <c r="C544" t="n">
-        <v>3.35821461315716</v>
+        <v>3.358214860745675</v>
       </c>
       <c r="D544" t="n">
-        <v>3.20513352261502</v>
+        <v>3.205133758917443</v>
       </c>
       <c r="E544" t="n">
-        <v>3.310376843646641</v>
+        <v>3.310377087708257</v>
       </c>
       <c r="F544" t="n">
         <v>37198300</v>
@@ -11312,16 +11312,16 @@
         <v>45205</v>
       </c>
       <c r="B545" t="n">
-        <v>3.23383641242981</v>
+        <v>3.233836650848389</v>
       </c>
       <c r="C545" t="n">
-        <v>3.262539074136121</v>
+        <v>3.262539314670839</v>
       </c>
       <c r="D545" t="n">
-        <v>3.138160645300292</v>
+        <v>3.138160876665057</v>
       </c>
       <c r="E545" t="n">
-        <v>3.20513352261502</v>
+        <v>3.205133758917443</v>
       </c>
       <c r="F545" t="n">
         <v>15875400</v>
@@ -11372,16 +11372,16 @@
         <v>45210</v>
       </c>
       <c r="B548" t="n">
-        <v>3.482593059539795</v>
+        <v>3.482593297958374</v>
       </c>
       <c r="C548" t="n">
-        <v>3.511295721390723</v>
+        <v>3.511295961774288</v>
       </c>
       <c r="D548" t="n">
-        <v>3.396484845878531</v>
+        <v>3.396485078402136</v>
       </c>
       <c r="E548" t="n">
-        <v>3.41561995377915</v>
+        <v>3.415620187612745</v>
       </c>
       <c r="F548" t="n">
         <v>15610900</v>
@@ -26132,19 +26132,39 @@
         <v>46293</v>
       </c>
       <c r="B1286" t="n">
-        <v>0.29</v>
+        <v>0.2899999916553497</v>
       </c>
       <c r="C1286" t="n">
-        <v>0.29</v>
+        <v>0.2899999916553497</v>
       </c>
       <c r="D1286" t="n">
-        <v>0.28</v>
+        <v>0.2800000011920929</v>
       </c>
       <c r="E1286" t="n">
-        <v>0.28</v>
+        <v>0.2800000011920929</v>
       </c>
       <c r="F1286" t="n">
         <v>7100000</v>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B1287" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="C1287" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D1287" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E1287" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F1287" t="n">
+        <v>8565000</v>
       </c>
     </row>
   </sheetData>

--- a/database/RAIZ4.xlsx
+++ b/database/RAIZ4.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1287"/>
+  <dimension ref="A1:F1288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44413</v>
       </c>
       <c r="B2" t="n">
-        <v>6.384481906890869</v>
+        <v>6.384480953216553</v>
       </c>
       <c r="C2" t="n">
-        <v>6.701942460974013</v>
+        <v>6.701941459879408</v>
       </c>
       <c r="D2" t="n">
-        <v>6.331571884625592</v>
+        <v>6.331570938854646</v>
       </c>
       <c r="E2" t="n">
-        <v>6.596122416443459</v>
+        <v>6.596121431155595</v>
       </c>
       <c r="F2" t="n">
         <v>98849900</v>
@@ -472,16 +472,16 @@
         <v>44414</v>
       </c>
       <c r="B3" t="n">
-        <v>6.261023998260498</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="C3" t="n">
-        <v>6.48148259270975</v>
+        <v>6.48148308633695</v>
       </c>
       <c r="D3" t="n">
-        <v>6.199295860929202</v>
+        <v>6.19929633306517</v>
       </c>
       <c r="E3" t="n">
-        <v>6.393299239028329</v>
+        <v>6.393299725939519</v>
       </c>
       <c r="F3" t="n">
         <v>28799900</v>
@@ -492,16 +492,16 @@
         <v>44417</v>
       </c>
       <c r="B4" t="n">
-        <v>6.234570026397705</v>
+        <v>6.234570503234863</v>
       </c>
       <c r="C4" t="n">
-        <v>6.446210103204662</v>
+        <v>6.44621059622864</v>
       </c>
       <c r="D4" t="n">
-        <v>6.234570026397705</v>
+        <v>6.234570503234863</v>
       </c>
       <c r="E4" t="n">
-        <v>6.331571518021834</v>
+        <v>6.331572002277935</v>
       </c>
       <c r="F4" t="n">
         <v>14491100</v>
@@ -512,16 +512,16 @@
         <v>44418</v>
       </c>
       <c r="B5" t="n">
-        <v>6.261023998260498</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="C5" t="n">
-        <v>6.31393401046935</v>
+        <v>6.313934491336116</v>
       </c>
       <c r="D5" t="n">
-        <v>6.216932531665487</v>
+        <v>6.216933005144656</v>
       </c>
       <c r="E5" t="n">
-        <v>6.278660668996782</v>
+        <v>6.278661147177143</v>
       </c>
       <c r="F5" t="n">
         <v>9988600</v>
@@ -532,16 +532,16 @@
         <v>44419</v>
       </c>
       <c r="B6" t="n">
-        <v>6.058202266693115</v>
+        <v>6.05820369720459</v>
       </c>
       <c r="C6" t="n">
-        <v>6.296297539430225</v>
+        <v>6.296299026162672</v>
       </c>
       <c r="D6" t="n">
-        <v>5.996474127404013</v>
+        <v>5.996475543339743</v>
       </c>
       <c r="E6" t="n">
-        <v>6.287479414028101</v>
+        <v>6.287480898678342</v>
       </c>
       <c r="F6" t="n">
         <v>31978000</v>
@@ -552,16 +552,16 @@
         <v>44420</v>
       </c>
       <c r="B7" t="n">
-        <v>6.137568950653076</v>
+        <v>6.13756799697876</v>
       </c>
       <c r="C7" t="n">
-        <v>6.155205626123685</v>
+        <v>6.155204669708928</v>
       </c>
       <c r="D7" t="n">
-        <v>5.952383647965926</v>
+        <v>5.952382723066271</v>
       </c>
       <c r="E7" t="n">
-        <v>6.146387078142625</v>
+        <v>6.146386123098121</v>
       </c>
       <c r="F7" t="n">
         <v>17054100</v>
@@ -572,16 +572,16 @@
         <v>44421</v>
       </c>
       <c r="B8" t="n">
-        <v>6.181660175323486</v>
+        <v>6.181660652160645</v>
       </c>
       <c r="C8" t="n">
-        <v>6.208114975398141</v>
+        <v>6.208115454275954</v>
       </c>
       <c r="D8" t="n">
-        <v>6.049384913475816</v>
+        <v>6.049385380109605</v>
       </c>
       <c r="E8" t="n">
-        <v>6.155204954757366</v>
+        <v>6.155205429553837</v>
       </c>
       <c r="F8" t="n">
         <v>21141500</v>
@@ -592,16 +592,16 @@
         <v>44424</v>
       </c>
       <c r="B9" t="n">
-        <v>6.190478801727295</v>
+        <v>6.190477848052979</v>
       </c>
       <c r="C9" t="n">
-        <v>6.278662176582655</v>
+        <v>6.278661209323248</v>
       </c>
       <c r="D9" t="n">
-        <v>5.978838702074429</v>
+        <v>5.978837781004333</v>
       </c>
       <c r="E9" t="n">
-        <v>6.146386904053864</v>
+        <v>6.146385957172127</v>
       </c>
       <c r="F9" t="n">
         <v>13434600</v>
@@ -692,16 +692,16 @@
         <v>44431</v>
       </c>
       <c r="B14" t="n">
-        <v>6.322752475738525</v>
+        <v>6.322752952575684</v>
       </c>
       <c r="C14" t="n">
-        <v>6.349207271261085</v>
+        <v>6.349207750093361</v>
       </c>
       <c r="D14" t="n">
-        <v>6.181659111641157</v>
+        <v>6.181659577837608</v>
       </c>
       <c r="E14" t="n">
-        <v>6.208113907163717</v>
+        <v>6.208114375355285</v>
       </c>
       <c r="F14" t="n">
         <v>6128800</v>
@@ -712,16 +712,16 @@
         <v>44432</v>
       </c>
       <c r="B15" t="n">
-        <v>6.393301010131836</v>
+        <v>6.393300533294678</v>
       </c>
       <c r="C15" t="n">
-        <v>6.525576287543212</v>
+        <v>6.525575800840451</v>
       </c>
       <c r="D15" t="n">
-        <v>6.33157243520879</v>
+        <v>6.331571962975588</v>
       </c>
       <c r="E15" t="n">
-        <v>6.384482462075037</v>
+        <v>6.384481985895601</v>
       </c>
       <c r="F15" t="n">
         <v>6054100</v>
@@ -732,16 +732,16 @@
         <v>44433</v>
       </c>
       <c r="B16" t="n">
-        <v>6.472664833068848</v>
+        <v>6.472665786743164</v>
       </c>
       <c r="C16" t="n">
-        <v>6.507938176533139</v>
+        <v>6.507939135404586</v>
       </c>
       <c r="D16" t="n">
-        <v>6.402118146140264</v>
+        <v>6.40211908942032</v>
       </c>
       <c r="E16" t="n">
-        <v>6.455028161336702</v>
+        <v>6.455029112412453</v>
       </c>
       <c r="F16" t="n">
         <v>5190100</v>
@@ -752,16 +752,16 @@
         <v>44434</v>
       </c>
       <c r="B17" t="n">
-        <v>6.261023998260498</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="C17" t="n">
-        <v>6.507937809059876</v>
+        <v>6.507938304701895</v>
       </c>
       <c r="D17" t="n">
-        <v>6.261023998260498</v>
+        <v>6.261024475097656</v>
       </c>
       <c r="E17" t="n">
-        <v>6.472664467587308</v>
+        <v>6.472664960542923</v>
       </c>
       <c r="F17" t="n">
         <v>7968100</v>
@@ -772,16 +772,16 @@
         <v>44435</v>
       </c>
       <c r="B18" t="n">
-        <v>6.340390682220459</v>
+        <v>6.340390205383